--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -628,88 +628,88 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B2" t="n">
-        <v>180.5</v>
+        <v>168.1</v>
       </c>
       <c r="C2" t="n">
-        <v>79.2</v>
+        <v>69.7</v>
       </c>
       <c r="D2" t="n">
-        <v>30.7</v>
+        <v>30.4</v>
       </c>
       <c r="E2" t="n">
-        <v>34.6</v>
+        <v>33.9</v>
       </c>
       <c r="F2" t="n">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="H2" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="I2" t="n">
-        <v>10.3</v>
+        <v>10.6</v>
       </c>
       <c r="J2" t="n">
-        <v>41.9</v>
+        <v>41.2</v>
       </c>
       <c r="K2" t="n">
-        <v>76.09999999999999</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="M2" t="n">
         <v>5</v>
       </c>
       <c r="N2" t="n">
-        <v>37.7</v>
+        <v>38.1</v>
       </c>
       <c r="O2" t="n">
-        <v>42.7</v>
+        <v>43.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>23.1</v>
+        <v>22.6</v>
       </c>
       <c r="R2" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="S2" t="n">
         <v>17.6</v>
       </c>
       <c r="T2" t="n">
-        <v>23.1</v>
+        <v>22.6</v>
       </c>
       <c r="V2" t="n">
-        <v>9.1</v>
+        <v>11.2</v>
       </c>
       <c r="W2" t="n">
-        <v>20.8</v>
+        <v>22.9</v>
       </c>
       <c r="X2" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA2" t="n">
         <v>14.9</v>
       </c>
-      <c r="Y2" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>16</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>11.9</v>
-      </c>
       <c r="AB2" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AC2" t="n">
-        <v>7.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD2" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="AF2" t="n">
-        <v>219.64</v>
+        <v>224.93</v>
       </c>
       <c r="AG2" t="n">
-        <v>-0.72</v>
+        <v>5.29</v>
       </c>
       <c r="AH2" t="n">
         <v>215</v>
@@ -718,10 +718,10 @@
         <v>235</v>
       </c>
       <c r="AK2" t="n">
-        <v>126.03</v>
+        <v>129.28</v>
       </c>
       <c r="AL2" t="n">
-        <v>-1.1</v>
+        <v>3.25</v>
       </c>
       <c r="AM2" t="n">
         <v>110</v>
@@ -730,99 +730,99 @@
         <v>142</v>
       </c>
       <c r="AP2" t="n">
-        <v>82.95</v>
+        <v>87.43000000000001</v>
       </c>
       <c r="AS2" t="n">
-        <v>14.55</v>
+        <v>15.25</v>
       </c>
       <c r="BL2" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B3" t="n">
-        <v>168.1</v>
+        <v>158.9</v>
       </c>
       <c r="C3" t="n">
-        <v>69.7</v>
+        <v>58.8</v>
       </c>
       <c r="D3" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="E3" t="n">
         <v>30.4</v>
       </c>
-      <c r="E3" t="n">
-        <v>33.9</v>
-      </c>
       <c r="F3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="H3" t="n">
-        <v>24.1</v>
+        <v>23.7</v>
       </c>
       <c r="I3" t="n">
-        <v>10.6</v>
+        <v>11.2</v>
       </c>
       <c r="J3" t="n">
-        <v>41.2</v>
+        <v>41</v>
       </c>
       <c r="K3" t="n">
         <v>75.90000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="N3" t="n">
-        <v>38.1</v>
+        <v>37.8</v>
       </c>
       <c r="O3" t="n">
-        <v>43.1</v>
+        <v>41.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>22.6</v>
+        <v>21.5</v>
       </c>
       <c r="R3" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="S3" t="n">
-        <v>17.6</v>
+        <v>15</v>
       </c>
       <c r="T3" t="n">
-        <v>22.6</v>
+        <v>21.5</v>
       </c>
       <c r="V3" t="n">
-        <v>11.2</v>
+        <v>10.1</v>
       </c>
       <c r="W3" t="n">
-        <v>22.9</v>
+        <v>26</v>
       </c>
       <c r="X3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="Y3" t="n">
         <v>17</v>
       </c>
-      <c r="Y3" t="n">
-        <v>11</v>
-      </c>
       <c r="Z3" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AA3" t="n">
-        <v>14.9</v>
+        <v>19.3</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.800000000000001</v>
+        <v>6.7</v>
       </c>
       <c r="AD3" t="n">
-        <v>5.7</v>
+        <v>4.5</v>
       </c>
       <c r="AF3" t="n">
-        <v>224.93</v>
+        <v>232.31</v>
       </c>
       <c r="AG3" t="n">
-        <v>5.29</v>
+        <v>9.67</v>
       </c>
       <c r="AH3" t="n">
         <v>215</v>
@@ -831,10 +831,10 @@
         <v>235</v>
       </c>
       <c r="AK3" t="n">
-        <v>129.28</v>
+        <v>134.44</v>
       </c>
       <c r="AL3" t="n">
-        <v>3.25</v>
+        <v>5.16</v>
       </c>
       <c r="AM3" t="n">
         <v>110</v>
@@ -843,99 +843,66 @@
         <v>142</v>
       </c>
       <c r="AP3" t="n">
-        <v>87.43000000000001</v>
+        <v>91.73999999999999</v>
       </c>
       <c r="AS3" t="n">
-        <v>15.25</v>
+        <v>17.07</v>
       </c>
       <c r="BL3" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B4" t="n">
-        <v>158.9</v>
-      </c>
-      <c r="C4" t="n">
-        <v>58.8</v>
+        <v>136.7</v>
       </c>
       <c r="D4" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="E4" t="n">
-        <v>30.4</v>
+        <v>30.7</v>
       </c>
       <c r="F4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="H4" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="I4" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="J4" t="n">
-        <v>41</v>
+        <v>7.5</v>
       </c>
       <c r="K4" t="n">
-        <v>75.90000000000001</v>
-      </c>
-      <c r="M4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N4" t="n">
-        <v>37.8</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="S4" t="n">
-        <v>15</v>
-      </c>
-      <c r="T4" t="n">
-        <v>21.5</v>
+        <v>39.2</v>
       </c>
       <c r="V4" t="n">
-        <v>10.1</v>
+        <v>17.1</v>
       </c>
       <c r="W4" t="n">
-        <v>26</v>
+        <v>36.1</v>
       </c>
       <c r="X4" t="n">
-        <v>18.1</v>
+        <v>26.6</v>
       </c>
       <c r="Y4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Z4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AA4" t="n">
-        <v>19.3</v>
+        <v>20.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AC4" t="n">
         <v>6.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AF4" t="n">
-        <v>232.31</v>
+        <v>235.4</v>
       </c>
       <c r="AG4" t="n">
-        <v>9.67</v>
+        <v>3.09</v>
       </c>
       <c r="AH4" t="n">
         <v>215</v>
@@ -944,10 +911,10 @@
         <v>235</v>
       </c>
       <c r="AK4" t="n">
-        <v>134.44</v>
+        <v>137.5</v>
       </c>
       <c r="AL4" t="n">
-        <v>5.16</v>
+        <v>3.06</v>
       </c>
       <c r="AM4" t="n">
         <v>110</v>
@@ -955,67 +922,61 @@
       <c r="AN4" t="n">
         <v>142</v>
       </c>
-      <c r="AP4" t="n">
-        <v>91.73999999999999</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>17.07</v>
-      </c>
       <c r="BL4" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="B5" t="n">
-        <v>136.7</v>
+        <v>138.5</v>
       </c>
       <c r="D5" t="n">
-        <v>30.7</v>
+        <v>31.7</v>
       </c>
       <c r="F5" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="K5" t="n">
-        <v>92.59999999999999</v>
+        <v>91</v>
       </c>
       <c r="O5" t="n">
-        <v>39.2</v>
+        <v>37.8</v>
       </c>
       <c r="V5" t="n">
-        <v>17.1</v>
+        <v>13.2</v>
       </c>
       <c r="W5" t="n">
-        <v>36.1</v>
+        <v>22.5</v>
       </c>
       <c r="X5" t="n">
-        <v>26.6</v>
+        <v>17.9</v>
       </c>
       <c r="Y5" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="Z5" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.5</v>
+        <v>15.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.6</v>
+        <v>-1.9</v>
       </c>
       <c r="AC5" t="n">
-        <v>6.7</v>
+        <v>5.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>4.7</v>
+        <v>1.7</v>
       </c>
       <c r="AF5" t="n">
-        <v>235.4</v>
+        <v>231.99</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.09</v>
+        <v>-3.41</v>
       </c>
       <c r="AH5" t="n">
         <v>215</v>
@@ -1024,10 +985,10 @@
         <v>235</v>
       </c>
       <c r="AK5" t="n">
-        <v>137.5</v>
+        <v>136.12</v>
       </c>
       <c r="AL5" t="n">
-        <v>3.06</v>
+        <v>-1.38</v>
       </c>
       <c r="AM5" t="n">
         <v>110</v>
@@ -1036,60 +997,93 @@
         <v>142</v>
       </c>
       <c r="BL5" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B6" t="n">
-        <v>138.5</v>
+        <v>161.1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>67</v>
       </c>
       <c r="D6" t="n">
-        <v>31.7</v>
+        <v>31.9</v>
+      </c>
+      <c r="E6" t="n">
+        <v>31.5</v>
       </c>
       <c r="F6" t="n">
-        <v>7</v>
+        <v>7.7</v>
+      </c>
+      <c r="H6" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J6" t="n">
+        <v>41.1</v>
       </c>
       <c r="K6" t="n">
-        <v>91</v>
+        <v>75.59999999999999</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="N6" t="n">
+        <v>35</v>
       </c>
       <c r="O6" t="n">
-        <v>37.8</v>
+        <v>37.2</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3</v>
+      </c>
+      <c r="T6" t="n">
+        <v>20.5</v>
       </c>
       <c r="V6" t="n">
-        <v>13.2</v>
+        <v>14.1</v>
       </c>
       <c r="W6" t="n">
-        <v>22.5</v>
+        <v>19.3</v>
       </c>
       <c r="X6" t="n">
-        <v>17.9</v>
+        <v>16.7</v>
       </c>
       <c r="Y6" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="Z6" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AA6" t="n">
-        <v>15.5</v>
+        <v>11.1</v>
       </c>
       <c r="AB6" t="n">
-        <v>-1.9</v>
+        <v>-3.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.2</v>
+        <v>3.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.7</v>
+        <v>-0.3</v>
       </c>
       <c r="AF6" t="n">
-        <v>231.99</v>
+        <v>225.51</v>
       </c>
       <c r="AG6" t="n">
-        <v>-3.41</v>
+        <v>-6.48</v>
       </c>
       <c r="AH6" t="n">
         <v>215</v>
@@ -1098,10 +1092,10 @@
         <v>235</v>
       </c>
       <c r="AK6" t="n">
-        <v>136.12</v>
+        <v>133.83</v>
       </c>
       <c r="AL6" t="n">
-        <v>-1.38</v>
+        <v>-2.29</v>
       </c>
       <c r="AM6" t="n">
         <v>110</v>
@@ -1109,94 +1103,100 @@
       <c r="AN6" t="n">
         <v>142</v>
       </c>
+      <c r="AP6" t="n">
+        <v>82.93000000000001</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>15.73</v>
+      </c>
       <c r="BL6" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B7" t="n">
-        <v>161.1</v>
+        <v>176.4</v>
       </c>
       <c r="C7" t="n">
-        <v>67</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>31.9</v>
+        <v>32.7</v>
       </c>
       <c r="E7" t="n">
-        <v>31.5</v>
+        <v>35</v>
       </c>
       <c r="F7" t="n">
-        <v>7.7</v>
+        <v>6.8</v>
       </c>
       <c r="H7" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="I7" t="n">
         <v>11.4</v>
       </c>
       <c r="J7" t="n">
-        <v>41.1</v>
+        <v>41.5</v>
       </c>
       <c r="K7" t="n">
-        <v>75.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="M7" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="N7" t="n">
-        <v>35</v>
+        <v>36.4</v>
       </c>
       <c r="O7" t="n">
-        <v>37.2</v>
+        <v>39.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>20.5</v>
+        <v>22.3</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="T7" t="n">
-        <v>20.5</v>
+        <v>22.3</v>
       </c>
       <c r="V7" t="n">
-        <v>14.1</v>
+        <v>11.5</v>
       </c>
       <c r="W7" t="n">
-        <v>19.3</v>
+        <v>15.5</v>
       </c>
       <c r="X7" t="n">
-        <v>16.7</v>
+        <v>13.5</v>
       </c>
       <c r="Y7" t="n">
         <v>9</v>
       </c>
       <c r="Z7" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA7" t="n">
-        <v>11.1</v>
+        <v>11.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>-3.8</v>
+        <v>-5.6</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0.3</v>
+        <v>-1.3</v>
       </c>
       <c r="AF7" t="n">
-        <v>225.51</v>
+        <v>220.92</v>
       </c>
       <c r="AG7" t="n">
-        <v>-6.48</v>
+        <v>-4.59</v>
       </c>
       <c r="AH7" t="n">
         <v>215</v>
@@ -1205,10 +1205,10 @@
         <v>235</v>
       </c>
       <c r="AK7" t="n">
-        <v>133.83</v>
+        <v>131.85</v>
       </c>
       <c r="AL7" t="n">
-        <v>-2.29</v>
+        <v>-1.98</v>
       </c>
       <c r="AM7" t="n">
         <v>110</v>
@@ -1217,99 +1217,99 @@
         <v>142</v>
       </c>
       <c r="AP7" t="n">
-        <v>82.93000000000001</v>
+        <v>79.75</v>
       </c>
       <c r="AS7" t="n">
-        <v>15.73</v>
+        <v>15.49</v>
       </c>
       <c r="BL7" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B8" t="n">
-        <v>176.4</v>
+        <v>181</v>
       </c>
       <c r="C8" t="n">
-        <v>77.09999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="D8" t="n">
-        <v>32.7</v>
+        <v>33</v>
       </c>
       <c r="E8" t="n">
-        <v>35</v>
+        <v>35.1</v>
       </c>
       <c r="F8" t="n">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="H8" t="n">
-        <v>23.2</v>
+        <v>22.8</v>
       </c>
       <c r="I8" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="J8" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="K8" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N8" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="O8" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S8" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="T8" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="V8" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="W8" t="n">
+        <v>13</v>
+      </c>
+      <c r="X8" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA8" t="n">
         <v>11.4</v>
       </c>
-      <c r="J8" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="K8" t="n">
-        <v>76</v>
-      </c>
-      <c r="M8" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N8" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="O8" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>14</v>
-      </c>
-      <c r="T8" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="V8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="W8" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="X8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>11.6</v>
-      </c>
       <c r="AB8" t="n">
-        <v>-5.6</v>
+        <v>-6.1</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>-1.3</v>
+        <v>-0.9</v>
       </c>
       <c r="AF8" t="n">
         <v>220.92</v>
       </c>
       <c r="AG8" t="n">
-        <v>-4.59</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
         <v>215</v>
@@ -1318,10 +1318,10 @@
         <v>235</v>
       </c>
       <c r="AK8" t="n">
-        <v>131.85</v>
+        <v>130.06</v>
       </c>
       <c r="AL8" t="n">
-        <v>-1.98</v>
+        <v>-1.79</v>
       </c>
       <c r="AM8" t="n">
         <v>110</v>
@@ -1330,99 +1330,99 @@
         <v>142</v>
       </c>
       <c r="AP8" t="n">
-        <v>79.75</v>
+        <v>79.94</v>
       </c>
       <c r="AS8" t="n">
-        <v>15.49</v>
+        <v>14.93</v>
       </c>
       <c r="BL8" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B9" t="n">
-        <v>181</v>
+        <v>179.6</v>
       </c>
       <c r="C9" t="n">
-        <v>80.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>33</v>
+        <v>30.3</v>
       </c>
       <c r="E9" t="n">
-        <v>35.1</v>
+        <v>31.1</v>
       </c>
       <c r="F9" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="H9" t="n">
-        <v>22.8</v>
+        <v>21.5</v>
       </c>
       <c r="I9" t="n">
-        <v>11.2</v>
+        <v>10.8</v>
       </c>
       <c r="J9" t="n">
-        <v>41.9</v>
+        <v>42.3</v>
       </c>
       <c r="K9" t="n">
-        <v>75.90000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9</v>
+        <v>4.3</v>
       </c>
       <c r="N9" t="n">
-        <v>36.9</v>
+        <v>37.1</v>
       </c>
       <c r="O9" t="n">
-        <v>39.8</v>
+        <v>41.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="R9" t="n">
+        <v>2</v>
+      </c>
+      <c r="S9" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="V9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="W9" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="X9" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AD9" t="n">
         <v>0.5</v>
       </c>
-      <c r="S9" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="T9" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="V9" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="W9" t="n">
-        <v>13</v>
-      </c>
-      <c r="X9" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>-6.1</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>-0.9</v>
-      </c>
       <c r="AF9" t="n">
-        <v>220.92</v>
+        <v>216.02</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AH9" t="n">
         <v>215</v>
@@ -1431,10 +1431,10 @@
         <v>235</v>
       </c>
       <c r="AK9" t="n">
-        <v>130.06</v>
+        <v>127.85</v>
       </c>
       <c r="AL9" t="n">
-        <v>-1.79</v>
+        <v>-2.21</v>
       </c>
       <c r="AM9" t="n">
         <v>110</v>
@@ -1443,99 +1443,99 @@
         <v>142</v>
       </c>
       <c r="AP9" t="n">
-        <v>79.94</v>
+        <v>82.2</v>
       </c>
       <c r="AS9" t="n">
-        <v>14.93</v>
+        <v>15.16</v>
       </c>
       <c r="BL9" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B10" t="n">
-        <v>179.6</v>
+        <v>170.4</v>
       </c>
       <c r="C10" t="n">
-        <v>81.90000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="D10" t="n">
-        <v>30.3</v>
+        <v>29.8</v>
       </c>
       <c r="E10" t="n">
-        <v>31.1</v>
+        <v>29.7</v>
       </c>
       <c r="F10" t="n">
-        <v>6.8</v>
+        <v>6.3</v>
       </c>
       <c r="H10" t="n">
-        <v>21.5</v>
+        <v>22.5</v>
       </c>
       <c r="I10" t="n">
-        <v>10.8</v>
+        <v>11.2</v>
       </c>
       <c r="J10" t="n">
-        <v>42.3</v>
+        <v>41.4</v>
       </c>
       <c r="K10" t="n">
-        <v>74.59999999999999</v>
+        <v>75</v>
       </c>
       <c r="M10" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="N10" t="n">
-        <v>37.1</v>
+        <v>36.6</v>
       </c>
       <c r="O10" t="n">
-        <v>41.4</v>
+        <v>41.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>22.6</v>
+        <v>23.3</v>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="S10" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="T10" t="n">
-        <v>22.6</v>
+        <v>23.3</v>
       </c>
       <c r="V10" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="W10" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="X10" t="n">
         <v>12.6</v>
       </c>
       <c r="Y10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z10" t="n">
         <v>13</v>
       </c>
       <c r="AA10" t="n">
-        <v>11.1</v>
+        <v>12.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>-3.4</v>
+        <v>1.8</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.4</v>
+        <v>7.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.5</v>
+        <v>4.7</v>
       </c>
       <c r="AF10" t="n">
         <v>216.02</v>
       </c>
       <c r="AG10" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
         <v>215</v>
@@ -1544,10 +1544,10 @@
         <v>235</v>
       </c>
       <c r="AK10" t="n">
-        <v>127.85</v>
+        <v>128.54</v>
       </c>
       <c r="AL10" t="n">
-        <v>-2.21</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AM10" t="n">
         <v>110</v>
@@ -1556,99 +1556,66 @@
         <v>142</v>
       </c>
       <c r="AP10" t="n">
-        <v>82.2</v>
+        <v>84.73</v>
       </c>
       <c r="AS10" t="n">
-        <v>15.16</v>
+        <v>15.34</v>
       </c>
       <c r="BL10" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B11" t="n">
-        <v>170.4</v>
-      </c>
-      <c r="C11" t="n">
-        <v>78.5</v>
+        <v>156</v>
       </c>
       <c r="D11" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="E11" t="n">
-        <v>29.7</v>
+        <v>30.1</v>
       </c>
       <c r="F11" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="H11" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="I11" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="J11" t="n">
-        <v>41.4</v>
+        <v>6.8</v>
       </c>
       <c r="K11" t="n">
-        <v>75</v>
-      </c>
-      <c r="M11" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="N11" t="n">
-        <v>36.6</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S11" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="T11" t="n">
-        <v>23.3</v>
+        <v>39.2</v>
       </c>
       <c r="V11" t="n">
-        <v>9.5</v>
+        <v>7.1</v>
       </c>
       <c r="W11" t="n">
-        <v>15.7</v>
+        <v>20.9</v>
       </c>
       <c r="X11" t="n">
-        <v>12.6</v>
+        <v>14</v>
       </c>
       <c r="Y11" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Z11" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA11" t="n">
-        <v>12.7</v>
+        <v>13.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.8</v>
+        <v>-0.2</v>
       </c>
       <c r="AC11" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="AD11" t="n">
-        <v>4.7</v>
+        <v>2.4</v>
       </c>
       <c r="AF11" t="n">
-        <v>216.02</v>
+        <v>224.53</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH11" t="n">
         <v>215</v>
@@ -1657,10 +1624,10 @@
         <v>235</v>
       </c>
       <c r="AK11" t="n">
-        <v>128.54</v>
+        <v>130.92</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.6899999999999999</v>
+        <v>2.38</v>
       </c>
       <c r="AM11" t="n">
         <v>110</v>
@@ -1668,67 +1635,61 @@
       <c r="AN11" t="n">
         <v>142</v>
       </c>
-      <c r="AP11" t="n">
-        <v>84.73</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>15.34</v>
-      </c>
       <c r="BL11" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B12" t="n">
-        <v>156</v>
+        <v>147.8</v>
       </c>
       <c r="D12" t="n">
-        <v>30.1</v>
+        <v>32</v>
       </c>
       <c r="F12" t="n">
         <v>6.8</v>
       </c>
       <c r="K12" t="n">
-        <v>95.90000000000001</v>
+        <v>96.5</v>
       </c>
       <c r="O12" t="n">
-        <v>39.2</v>
+        <v>39.3</v>
       </c>
       <c r="V12" t="n">
-        <v>7.1</v>
+        <v>8</v>
       </c>
       <c r="W12" t="n">
-        <v>20.9</v>
+        <v>22.4</v>
       </c>
       <c r="X12" t="n">
-        <v>14</v>
+        <v>15.2</v>
       </c>
       <c r="Y12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA12" t="n">
         <v>13.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AF12" t="n">
-        <v>224.53</v>
+        <v>230.27</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.32</v>
+        <v>5.74</v>
       </c>
       <c r="AH12" t="n">
         <v>215</v>
@@ -1737,10 +1698,10 @@
         <v>235</v>
       </c>
       <c r="AK12" t="n">
-        <v>130.92</v>
+        <v>132.76</v>
       </c>
       <c r="AL12" t="n">
-        <v>2.38</v>
+        <v>1.84</v>
       </c>
       <c r="AM12" t="n">
         <v>110</v>
@@ -1749,60 +1710,93 @@
         <v>142</v>
       </c>
       <c r="BL12" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="B13" t="n">
-        <v>147.8</v>
+        <v>149.1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>60</v>
       </c>
       <c r="D13" t="n">
-        <v>32</v>
+        <v>29</v>
+      </c>
+      <c r="E13" t="n">
+        <v>25.9</v>
       </c>
       <c r="F13" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
+      </c>
+      <c r="H13" t="n">
+        <v>24</v>
+      </c>
+      <c r="I13" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="J13" t="n">
+        <v>38.8</v>
       </c>
       <c r="K13" t="n">
-        <v>96.5</v>
+        <v>74.5</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N13" t="n">
+        <v>36.7</v>
       </c>
       <c r="O13" t="n">
-        <v>39.3</v>
+        <v>40.1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>7</v>
+      </c>
+      <c r="T13" t="n">
+        <v>21.7</v>
       </c>
       <c r="V13" t="n">
-        <v>8</v>
+        <v>10.3</v>
       </c>
       <c r="W13" t="n">
-        <v>22.4</v>
+        <v>24.4</v>
       </c>
       <c r="X13" t="n">
-        <v>15.2</v>
+        <v>17.4</v>
       </c>
       <c r="Y13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z13" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AA13" t="n">
-        <v>13.5</v>
+        <v>15.7</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0.3</v>
+        <v>-2.4</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.6</v>
+        <v>2.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.1</v>
+        <v>-0.1</v>
       </c>
       <c r="AF13" t="n">
-        <v>230.27</v>
+        <v>237.43</v>
       </c>
       <c r="AG13" t="n">
-        <v>5.74</v>
+        <v>7.16</v>
       </c>
       <c r="AH13" t="n">
         <v>215</v>
@@ -1811,10 +1805,10 @@
         <v>235</v>
       </c>
       <c r="AK13" t="n">
-        <v>132.76</v>
+        <v>134.95</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.84</v>
+        <v>2.19</v>
       </c>
       <c r="AM13" t="n">
         <v>110</v>
@@ -1822,94 +1816,67 @@
       <c r="AN13" t="n">
         <v>142</v>
       </c>
+      <c r="AP13" t="n">
+        <v>91.28</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>16.95</v>
+      </c>
       <c r="BL13" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="B14" t="n">
-        <v>149.1</v>
-      </c>
-      <c r="C14" t="n">
-        <v>60</v>
+        <v>143.9</v>
       </c>
       <c r="D14" t="n">
-        <v>29</v>
-      </c>
-      <c r="E14" t="n">
-        <v>25.9</v>
+        <v>32.9</v>
       </c>
       <c r="F14" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="H14" t="n">
-        <v>24</v>
-      </c>
-      <c r="I14" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="J14" t="n">
-        <v>38.8</v>
+        <v>6.8</v>
       </c>
       <c r="K14" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="M14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N14" t="n">
-        <v>36.7</v>
+        <v>96.2</v>
       </c>
       <c r="O14" t="n">
-        <v>40.1</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>7</v>
-      </c>
-      <c r="T14" t="n">
-        <v>21.7</v>
+        <v>37.9</v>
       </c>
       <c r="V14" t="n">
-        <v>10.3</v>
+        <v>10</v>
       </c>
       <c r="W14" t="n">
-        <v>24.4</v>
+        <v>25.6</v>
       </c>
       <c r="X14" t="n">
-        <v>17.4</v>
+        <v>17.8</v>
       </c>
       <c r="Y14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z14" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AA14" t="n">
-        <v>15.7</v>
+        <v>16</v>
       </c>
       <c r="AB14" t="n">
-        <v>-2.4</v>
+        <v>-1.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0.1</v>
+        <v>0.9</v>
       </c>
       <c r="AF14" t="n">
-        <v>237.43</v>
+        <v>236.14</v>
       </c>
       <c r="AG14" t="n">
-        <v>7.16</v>
+        <v>-1.29</v>
       </c>
       <c r="AH14" t="n">
         <v>215</v>
@@ -1918,10 +1885,10 @@
         <v>235</v>
       </c>
       <c r="AK14" t="n">
-        <v>134.95</v>
+        <v>136.28</v>
       </c>
       <c r="AL14" t="n">
-        <v>2.19</v>
+        <v>1.33</v>
       </c>
       <c r="AM14" t="n">
         <v>110</v>
@@ -1929,67 +1896,94 @@
       <c r="AN14" t="n">
         <v>142</v>
       </c>
-      <c r="AP14" t="n">
-        <v>91.28</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>16.95</v>
-      </c>
       <c r="BL14" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B15" t="n">
-        <v>143.9</v>
+        <v>166.4</v>
+      </c>
+      <c r="C15" t="n">
+        <v>63.7</v>
       </c>
       <c r="D15" t="n">
-        <v>32.9</v>
+        <v>34.5</v>
+      </c>
+      <c r="E15" t="n">
+        <v>36.4</v>
       </c>
       <c r="F15" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
+      </c>
+      <c r="H15" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="I15" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="J15" t="n">
+        <v>39.9</v>
       </c>
       <c r="K15" t="n">
-        <v>96.2</v>
+        <v>75.2</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N15" t="n">
+        <v>35.9</v>
       </c>
       <c r="O15" t="n">
-        <v>37.9</v>
+        <v>39</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="S15" t="n">
+        <v>6</v>
+      </c>
+      <c r="T15" t="n">
+        <v>20.3</v>
       </c>
       <c r="V15" t="n">
-        <v>10</v>
+        <v>11.9</v>
       </c>
       <c r="W15" t="n">
-        <v>25.6</v>
+        <v>27</v>
       </c>
       <c r="X15" t="n">
-        <v>17.8</v>
+        <v>19.4</v>
       </c>
       <c r="Y15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z15" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AA15" t="n">
-        <v>16</v>
+        <v>14.4</v>
       </c>
       <c r="AB15" t="n">
-        <v>-1.4</v>
+        <v>-3.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.9</v>
+        <v>-0.4</v>
       </c>
       <c r="AF15" t="n">
-        <v>236.14</v>
+        <v>236.13</v>
       </c>
       <c r="AG15" t="n">
-        <v>-1.29</v>
+        <v>-0.01</v>
       </c>
       <c r="AH15" t="n">
         <v>215</v>
@@ -1998,10 +1992,10 @@
         <v>235</v>
       </c>
       <c r="AK15" t="n">
-        <v>136.28</v>
+        <v>134.54</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.33</v>
+        <v>-1.74</v>
       </c>
       <c r="AM15" t="n">
         <v>110</v>
@@ -2009,94 +2003,100 @@
       <c r="AN15" t="n">
         <v>142</v>
       </c>
+      <c r="AP15" t="n">
+        <v>82.27</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>16.28</v>
+      </c>
       <c r="BL15" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B16" t="n">
-        <v>166.4</v>
+        <v>172.9</v>
       </c>
       <c r="C16" t="n">
-        <v>63.7</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D16" t="n">
-        <v>34.5</v>
+        <v>34.9</v>
       </c>
       <c r="E16" t="n">
-        <v>36.4</v>
+        <v>35.2</v>
       </c>
       <c r="F16" t="n">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="H16" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="I16" t="n">
-        <v>11.6</v>
+        <v>11.3</v>
       </c>
       <c r="J16" t="n">
-        <v>39.9</v>
+        <v>41.7</v>
       </c>
       <c r="K16" t="n">
-        <v>75.2</v>
+        <v>76.7</v>
       </c>
       <c r="M16" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="N16" t="n">
-        <v>35.9</v>
+        <v>34.8</v>
       </c>
       <c r="O16" t="n">
-        <v>39</v>
+        <v>37.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>20.3</v>
+        <v>19</v>
       </c>
       <c r="R16" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T16" t="n">
-        <v>20.3</v>
+        <v>19</v>
       </c>
       <c r="V16" t="n">
-        <v>11.9</v>
+        <v>14.4</v>
       </c>
       <c r="W16" t="n">
-        <v>27</v>
+        <v>18.7</v>
       </c>
       <c r="X16" t="n">
-        <v>19.4</v>
+        <v>16.6</v>
       </c>
       <c r="Y16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Z16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA16" t="n">
-        <v>14.4</v>
+        <v>12.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>-3.5</v>
+        <v>-4.9</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>-0.4</v>
+        <v>-0.7</v>
       </c>
       <c r="AF16" t="n">
-        <v>236.13</v>
+        <v>218.6</v>
       </c>
       <c r="AG16" t="n">
-        <v>-0.01</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="AH16" t="n">
         <v>215</v>
@@ -2105,10 +2105,10 @@
         <v>235</v>
       </c>
       <c r="AK16" t="n">
-        <v>134.54</v>
+        <v>130.39</v>
       </c>
       <c r="AL16" t="n">
-        <v>-1.74</v>
+        <v>-4.15</v>
       </c>
       <c r="AM16" t="n">
         <v>110</v>
@@ -2117,99 +2117,99 @@
         <v>142</v>
       </c>
       <c r="AP16" t="n">
-        <v>82.27</v>
+        <v>78.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>16.28</v>
+        <v>15.79</v>
       </c>
       <c r="BL16" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B17" t="n">
-        <v>172.9</v>
+        <v>157.5</v>
       </c>
       <c r="C17" t="n">
-        <v>67.59999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="D17" t="n">
-        <v>34.9</v>
+        <v>33.2</v>
       </c>
       <c r="E17" t="n">
-        <v>35.2</v>
+        <v>27.7</v>
       </c>
       <c r="F17" t="n">
-        <v>7.3</v>
+        <v>3.6</v>
       </c>
       <c r="H17" t="n">
-        <v>23.6</v>
+        <v>23.4</v>
       </c>
       <c r="I17" t="n">
         <v>11.3</v>
       </c>
       <c r="J17" t="n">
-        <v>41.7</v>
+        <v>41.4</v>
       </c>
       <c r="K17" t="n">
-        <v>76.7</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="N17" t="n">
-        <v>34.8</v>
+        <v>34.9</v>
       </c>
       <c r="O17" t="n">
-        <v>37.2</v>
+        <v>37.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>19</v>
+        <v>21.6</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T17" t="n">
-        <v>19</v>
+        <v>21.6</v>
       </c>
       <c r="V17" t="n">
-        <v>14.4</v>
+        <v>15.1</v>
       </c>
       <c r="W17" t="n">
-        <v>18.7</v>
+        <v>23.1</v>
       </c>
       <c r="X17" t="n">
-        <v>16.6</v>
+        <v>19.1</v>
       </c>
       <c r="Y17" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z17" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AA17" t="n">
-        <v>12.5</v>
+        <v>13.6</v>
       </c>
       <c r="AB17" t="n">
-        <v>-4.9</v>
+        <v>-0</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="AD17" t="n">
-        <v>-0.7</v>
+        <v>1.5</v>
       </c>
       <c r="AF17" t="n">
-        <v>218.6</v>
+        <v>218.84</v>
       </c>
       <c r="AG17" t="n">
-        <v>-9.380000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="AH17" t="n">
         <v>215</v>
@@ -2218,10 +2218,10 @@
         <v>235</v>
       </c>
       <c r="AK17" t="n">
-        <v>130.39</v>
+        <v>133.09</v>
       </c>
       <c r="AL17" t="n">
-        <v>-4.15</v>
+        <v>2.7</v>
       </c>
       <c r="AM17" t="n">
         <v>110</v>
@@ -2230,99 +2230,66 @@
         <v>142</v>
       </c>
       <c r="AP17" t="n">
-        <v>78.5</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="AS17" t="n">
-        <v>15.79</v>
+        <v>15.63</v>
       </c>
       <c r="BL17" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B18" t="n">
-        <v>157.5</v>
-      </c>
-      <c r="C18" t="n">
-        <v>68.5</v>
+        <v>137.6</v>
       </c>
       <c r="D18" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="E18" t="n">
-        <v>27.7</v>
+        <v>35</v>
       </c>
       <c r="F18" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H18" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="I18" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J18" t="n">
-        <v>41.4</v>
+        <v>6.5</v>
       </c>
       <c r="K18" t="n">
-        <v>76.09999999999999</v>
-      </c>
-      <c r="M18" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="N18" t="n">
-        <v>34.9</v>
+        <v>96.7</v>
       </c>
       <c r="O18" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>9</v>
-      </c>
-      <c r="T18" t="n">
-        <v>21.6</v>
+        <v>35.1</v>
       </c>
       <c r="V18" t="n">
-        <v>15.1</v>
+        <v>13.6</v>
       </c>
       <c r="W18" t="n">
-        <v>23.1</v>
+        <v>24.4</v>
       </c>
       <c r="X18" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="Y18" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Z18" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AA18" t="n">
-        <v>13.6</v>
+        <v>17.5</v>
       </c>
       <c r="AB18" t="n">
         <v>-0</v>
       </c>
       <c r="AC18" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="AF18" t="n">
-        <v>218.84</v>
+        <v>221.78</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.25</v>
+        <v>2.94</v>
       </c>
       <c r="AH18" t="n">
         <v>215</v>
@@ -2331,10 +2298,10 @@
         <v>235</v>
       </c>
       <c r="AK18" t="n">
-        <v>133.09</v>
+        <v>138.76</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.7</v>
+        <v>5.67</v>
       </c>
       <c r="AM18" t="n">
         <v>110</v>
@@ -2342,67 +2309,61 @@
       <c r="AN18" t="n">
         <v>142</v>
       </c>
-      <c r="AP18" t="n">
-        <v>83.09999999999999</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>15.63</v>
-      </c>
       <c r="BL18" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B19" t="n">
-        <v>137.6</v>
+        <v>132.5</v>
       </c>
       <c r="D19" t="n">
-        <v>35</v>
+        <v>33.6</v>
       </c>
       <c r="F19" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="K19" t="n">
-        <v>96.7</v>
+        <v>97.8</v>
       </c>
       <c r="O19" t="n">
-        <v>35.1</v>
+        <v>31.6</v>
       </c>
       <c r="V19" t="n">
-        <v>13.6</v>
+        <v>14.8</v>
       </c>
       <c r="W19" t="n">
-        <v>24.4</v>
+        <v>24.7</v>
       </c>
       <c r="X19" t="n">
-        <v>19</v>
+        <v>19.8</v>
       </c>
       <c r="Y19" t="n">
         <v>14</v>
       </c>
       <c r="Z19" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AA19" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>-0</v>
+        <v>0.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="AF19" t="n">
-        <v>221.78</v>
+        <v>224.78</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="AH19" t="n">
         <v>215</v>
@@ -2411,10 +2372,10 @@
         <v>235</v>
       </c>
       <c r="AK19" t="n">
-        <v>138.76</v>
+        <v>143.55</v>
       </c>
       <c r="AL19" t="n">
-        <v>5.67</v>
+        <v>4.79</v>
       </c>
       <c r="AM19" t="n">
         <v>110</v>
@@ -2423,60 +2384,93 @@
         <v>142</v>
       </c>
       <c r="BL19" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B20" t="n">
-        <v>132.5</v>
+        <v>137.2</v>
+      </c>
+      <c r="C20" t="n">
+        <v>56.3</v>
       </c>
       <c r="D20" t="n">
-        <v>33.6</v>
+        <v>32.1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>21.2</v>
       </c>
       <c r="F20" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
+      </c>
+      <c r="H20" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="I20" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="J20" t="n">
+        <v>40.4</v>
       </c>
       <c r="K20" t="n">
-        <v>97.8</v>
+        <v>75.7</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N20" t="n">
+        <v>29</v>
       </c>
       <c r="O20" t="n">
-        <v>31.6</v>
+        <v>32.6</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>21.6</v>
       </c>
       <c r="V20" t="n">
-        <v>14.8</v>
+        <v>10.7</v>
       </c>
       <c r="W20" t="n">
-        <v>24.7</v>
+        <v>24.3</v>
       </c>
       <c r="X20" t="n">
-        <v>19.8</v>
+        <v>17.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Z20" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AA20" t="n">
-        <v>16.5</v>
+        <v>15.4</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="AF20" t="n">
-        <v>224.78</v>
+        <v>232.22</v>
       </c>
       <c r="AG20" t="n">
-        <v>3</v>
+        <v>7.43</v>
       </c>
       <c r="AH20" t="n">
         <v>215</v>
@@ -2485,10 +2479,10 @@
         <v>235</v>
       </c>
       <c r="AK20" t="n">
-        <v>143.55</v>
+        <v>143.61</v>
       </c>
       <c r="AL20" t="n">
-        <v>4.79</v>
+        <v>0.06</v>
       </c>
       <c r="AM20" t="n">
         <v>110</v>
@@ -2496,52 +2490,58 @@
       <c r="AN20" t="n">
         <v>142</v>
       </c>
+      <c r="AP20" t="n">
+        <v>89.31999999999999</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>18.02</v>
+      </c>
       <c r="BL20" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="B21" t="n">
-        <v>137.2</v>
+        <v>157.5</v>
       </c>
       <c r="C21" t="n">
-        <v>56.3</v>
+        <v>59.6</v>
       </c>
       <c r="D21" t="n">
-        <v>32.1</v>
+        <v>35</v>
       </c>
       <c r="E21" t="n">
-        <v>21.2</v>
+        <v>30.6</v>
       </c>
       <c r="F21" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="H21" t="n">
-        <v>23.7</v>
+        <v>24.2</v>
       </c>
       <c r="I21" t="n">
-        <v>11.6</v>
+        <v>11.2</v>
       </c>
       <c r="J21" t="n">
-        <v>40.4</v>
+        <v>38.9</v>
       </c>
       <c r="K21" t="n">
-        <v>75.7</v>
+        <v>74.3</v>
       </c>
       <c r="M21" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="N21" t="n">
-        <v>29</v>
+        <v>33.4</v>
       </c>
       <c r="O21" t="n">
-        <v>32.6</v>
+        <v>37.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="R21" t="n">
         <v>1.3</v>
@@ -2550,40 +2550,40 @@
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="V21" t="n">
-        <v>10.7</v>
+        <v>13</v>
       </c>
       <c r="W21" t="n">
-        <v>24.3</v>
+        <v>26.3</v>
       </c>
       <c r="X21" t="n">
-        <v>17.5</v>
+        <v>19.6</v>
       </c>
       <c r="Y21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA21" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.9</v>
+        <v>-2.1</v>
       </c>
       <c r="AC21" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="AF21" t="n">
-        <v>232.22</v>
+        <v>229.69</v>
       </c>
       <c r="AG21" t="n">
-        <v>7.43</v>
+        <v>-2.53</v>
       </c>
       <c r="AH21" t="n">
         <v>215</v>
@@ -2592,10 +2592,10 @@
         <v>235</v>
       </c>
       <c r="AK21" t="n">
-        <v>143.61</v>
+        <v>136.96</v>
       </c>
       <c r="AL21" t="n">
-        <v>0.06</v>
+        <v>-6.65</v>
       </c>
       <c r="AM21" t="n">
         <v>110</v>
@@ -2604,99 +2604,99 @@
         <v>142</v>
       </c>
       <c r="AP21" t="n">
-        <v>89.31999999999999</v>
+        <v>86.59</v>
       </c>
       <c r="AS21" t="n">
-        <v>18.02</v>
+        <v>16.96</v>
       </c>
       <c r="BL21" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B22" t="n">
-        <v>157.5</v>
+        <v>159.6</v>
       </c>
       <c r="C22" t="n">
-        <v>59.6</v>
+        <v>63</v>
       </c>
       <c r="D22" t="n">
-        <v>35</v>
+        <v>34.5</v>
       </c>
       <c r="E22" t="n">
-        <v>30.6</v>
+        <v>31.1</v>
       </c>
       <c r="F22" t="n">
-        <v>7.5</v>
+        <v>5.7</v>
       </c>
       <c r="H22" t="n">
-        <v>24.2</v>
+        <v>23.8</v>
       </c>
       <c r="I22" t="n">
-        <v>11.2</v>
+        <v>10.8</v>
       </c>
       <c r="J22" t="n">
-        <v>38.9</v>
+        <v>40.5</v>
       </c>
       <c r="K22" t="n">
-        <v>74.3</v>
+        <v>75.2</v>
       </c>
       <c r="M22" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="N22" t="n">
-        <v>33.4</v>
+        <v>34.3</v>
       </c>
       <c r="O22" t="n">
-        <v>37.1</v>
+        <v>38.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T22" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="V22" t="n">
-        <v>13</v>
+        <v>17.5</v>
       </c>
       <c r="W22" t="n">
-        <v>26.3</v>
+        <v>22.5</v>
       </c>
       <c r="X22" t="n">
-        <v>19.6</v>
+        <v>20</v>
       </c>
       <c r="Y22" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA22" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AB22" t="n">
-        <v>-2.1</v>
+        <v>-2.2</v>
       </c>
       <c r="AC22" t="n">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="AF22" t="n">
-        <v>229.69</v>
+        <v>228.57</v>
       </c>
       <c r="AG22" t="n">
-        <v>-2.53</v>
+        <v>-1.14</v>
       </c>
       <c r="AH22" t="n">
         <v>215</v>
@@ -2705,10 +2705,10 @@
         <v>235</v>
       </c>
       <c r="AK22" t="n">
-        <v>136.96</v>
+        <v>133.01</v>
       </c>
       <c r="AL22" t="n">
-        <v>-6.65</v>
+        <v>-3.95</v>
       </c>
       <c r="AM22" t="n">
         <v>110</v>
@@ -2717,99 +2717,99 @@
         <v>142</v>
       </c>
       <c r="AP22" t="n">
-        <v>86.59</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="AS22" t="n">
-        <v>16.96</v>
+        <v>15.95</v>
       </c>
       <c r="BL22" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B23" t="n">
-        <v>159.6</v>
+        <v>160.4</v>
       </c>
       <c r="C23" t="n">
-        <v>63</v>
+        <v>62.6</v>
       </c>
       <c r="D23" t="n">
-        <v>34.5</v>
+        <v>35</v>
       </c>
       <c r="E23" t="n">
-        <v>31.1</v>
+        <v>32.2</v>
       </c>
       <c r="F23" t="n">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="H23" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="I23" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="J23" t="n">
-        <v>40.5</v>
+        <v>41.1</v>
       </c>
       <c r="K23" t="n">
-        <v>75.2</v>
+        <v>75.7</v>
       </c>
       <c r="M23" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="N23" t="n">
-        <v>34.3</v>
+        <v>32.6</v>
       </c>
       <c r="O23" t="n">
-        <v>38.2</v>
+        <v>38</v>
       </c>
       <c r="Q23" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="R23" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T23" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="V23" t="n">
-        <v>17.5</v>
+        <v>16.4</v>
       </c>
       <c r="W23" t="n">
-        <v>22.5</v>
+        <v>22.8</v>
       </c>
       <c r="X23" t="n">
-        <v>20</v>
+        <v>19.6</v>
       </c>
       <c r="Y23" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Z23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA23" t="n">
-        <v>13.5</v>
+        <v>14.1</v>
       </c>
       <c r="AB23" t="n">
-        <v>-2.2</v>
+        <v>-3.1</v>
       </c>
       <c r="AC23" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="AF23" t="n">
-        <v>228.57</v>
+        <v>225.08</v>
       </c>
       <c r="AG23" t="n">
-        <v>-1.14</v>
+        <v>-3.5</v>
       </c>
       <c r="AH23" t="n">
         <v>215</v>
@@ -2818,10 +2818,10 @@
         <v>235</v>
       </c>
       <c r="AK23" t="n">
-        <v>133.01</v>
+        <v>135.24</v>
       </c>
       <c r="AL23" t="n">
-        <v>-3.95</v>
+        <v>2.23</v>
       </c>
       <c r="AM23" t="n">
         <v>110</v>
@@ -2830,99 +2830,99 @@
         <v>142</v>
       </c>
       <c r="AP23" t="n">
-        <v>84.59999999999999</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="AS23" t="n">
-        <v>15.95</v>
+        <v>15.4</v>
       </c>
       <c r="BL23" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B24" t="n">
-        <v>160.4</v>
+        <v>161.7</v>
       </c>
       <c r="C24" t="n">
-        <v>62.6</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="D24" t="n">
-        <v>35</v>
+        <v>34.9</v>
       </c>
       <c r="E24" t="n">
-        <v>32.2</v>
+        <v>27.3</v>
       </c>
       <c r="F24" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H24" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="I24" t="n">
-        <v>10.7</v>
+        <v>10.3</v>
       </c>
       <c r="J24" t="n">
-        <v>41.1</v>
+        <v>42.6</v>
       </c>
       <c r="K24" t="n">
-        <v>75.7</v>
+        <v>77</v>
       </c>
       <c r="M24" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="N24" t="n">
-        <v>32.6</v>
+        <v>31.5</v>
       </c>
       <c r="O24" t="n">
-        <v>38</v>
+        <v>37.3</v>
       </c>
       <c r="Q24" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="R24" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T24" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="V24" t="n">
-        <v>16.4</v>
+        <v>12.7</v>
       </c>
       <c r="W24" t="n">
-        <v>22.8</v>
+        <v>27</v>
       </c>
       <c r="X24" t="n">
-        <v>19.6</v>
+        <v>19.9</v>
       </c>
       <c r="Y24" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Z24" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AA24" t="n">
-        <v>14.1</v>
+        <v>11.4</v>
       </c>
       <c r="AB24" t="n">
-        <v>-3.1</v>
+        <v>-5.2</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.6</v>
+        <v>-0.3</v>
       </c>
       <c r="AF24" t="n">
-        <v>225.08</v>
+        <v>225</v>
       </c>
       <c r="AG24" t="n">
-        <v>-3.5</v>
+        <v>-0.08</v>
       </c>
       <c r="AH24" t="n">
         <v>215</v>
@@ -2931,10 +2931,10 @@
         <v>235</v>
       </c>
       <c r="AK24" t="n">
-        <v>135.24</v>
+        <v>134.62</v>
       </c>
       <c r="AL24" t="n">
-        <v>2.23</v>
+        <v>-0.62</v>
       </c>
       <c r="AM24" t="n">
         <v>110</v>
@@ -2943,99 +2943,60 @@
         <v>142</v>
       </c>
       <c r="AP24" t="n">
-        <v>84.09999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="AS24" t="n">
-        <v>15.4</v>
+        <v>13.86</v>
       </c>
       <c r="BL24" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B25" t="n">
-        <v>161.7</v>
-      </c>
-      <c r="C25" t="n">
-        <v>71.09999999999999</v>
+        <v>151.5</v>
       </c>
       <c r="D25" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="E25" t="n">
-        <v>27.3</v>
+        <v>35.1</v>
       </c>
       <c r="F25" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H25" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I25" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="J25" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="K25" t="n">
-        <v>77</v>
-      </c>
-      <c r="M25" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="N25" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="O25" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>21</v>
-      </c>
-      <c r="R25" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="S25" t="n">
-        <v>6</v>
-      </c>
-      <c r="T25" t="n">
-        <v>21</v>
+        <v>5.4</v>
       </c>
       <c r="V25" t="n">
-        <v>12.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W25" t="n">
-        <v>27</v>
+        <v>19.4</v>
       </c>
       <c r="X25" t="n">
-        <v>19.9</v>
+        <v>14</v>
       </c>
       <c r="Y25" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA25" t="n">
         <v>9</v>
       </c>
-      <c r="Z25" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>11.4</v>
-      </c>
       <c r="AB25" t="n">
-        <v>-5.2</v>
+        <v>-4.7</v>
       </c>
       <c r="AC25" t="n">
-        <v>4.6</v>
+        <v>1.9</v>
       </c>
       <c r="AD25" t="n">
-        <v>-0.3</v>
+        <v>-1.4</v>
       </c>
       <c r="AF25" t="n">
-        <v>225</v>
+        <v>221.37</v>
       </c>
       <c r="AG25" t="n">
-        <v>-0.08</v>
+        <v>0.05</v>
       </c>
       <c r="AH25" t="n">
         <v>215</v>
@@ -3044,10 +3005,10 @@
         <v>235</v>
       </c>
       <c r="AK25" t="n">
-        <v>134.62</v>
+        <v>135.21</v>
       </c>
       <c r="AL25" t="n">
-        <v>-0.62</v>
+        <v>0.59</v>
       </c>
       <c r="AM25" t="n">
         <v>110</v>
@@ -3055,61 +3016,61 @@
       <c r="AN25" t="n">
         <v>142</v>
       </c>
-      <c r="AP25" t="n">
-        <v>80.2</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>13.86</v>
-      </c>
       <c r="BL25" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B26" t="n">
-        <v>151.5</v>
+        <v>145.2</v>
       </c>
       <c r="D26" t="n">
-        <v>35.1</v>
+        <v>33.5</v>
       </c>
       <c r="F26" t="n">
-        <v>5.4</v>
+        <v>5</v>
+      </c>
+      <c r="K26" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="O26" t="n">
+        <v>35.5</v>
       </c>
       <c r="V26" t="n">
-        <v>8.699999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="W26" t="n">
-        <v>19.4</v>
+        <v>19.2</v>
       </c>
       <c r="X26" t="n">
-        <v>14</v>
+        <v>13.1</v>
       </c>
       <c r="Y26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z26" t="n">
         <v>13</v>
       </c>
       <c r="AA26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB26" t="n">
-        <v>-4.7</v>
+        <v>-5.4</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>-1.4</v>
+        <v>-1.5</v>
       </c>
       <c r="AF26" t="n">
-        <v>221.37</v>
+        <v>224.37</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.05</v>
+        <v>3</v>
       </c>
       <c r="AH26" t="n">
         <v>215</v>
@@ -3118,10 +3079,10 @@
         <v>235</v>
       </c>
       <c r="AK26" t="n">
-        <v>135.21</v>
+        <v>135.61</v>
       </c>
       <c r="AL26" t="n">
-        <v>0.59</v>
+        <v>0.4</v>
       </c>
       <c r="AM26" t="n">
         <v>110</v>
@@ -3130,60 +3091,60 @@
         <v>142</v>
       </c>
       <c r="BL26" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B27" t="n">
-        <v>145.2</v>
+        <v>146.3</v>
       </c>
       <c r="D27" t="n">
-        <v>33.5</v>
+        <v>33.4</v>
       </c>
       <c r="F27" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="K27" t="n">
-        <v>100.3</v>
+        <v>98.2</v>
       </c>
       <c r="O27" t="n">
-        <v>35.5</v>
+        <v>35.1</v>
       </c>
       <c r="V27" t="n">
-        <v>7.1</v>
+        <v>4.9</v>
       </c>
       <c r="W27" t="n">
-        <v>19.2</v>
+        <v>16.4</v>
       </c>
       <c r="X27" t="n">
-        <v>13.1</v>
+        <v>10.6</v>
       </c>
       <c r="Y27" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z27" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB27" t="n">
-        <v>-5.4</v>
+        <v>-6.4</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.4</v>
+        <v>-0.2</v>
       </c>
       <c r="AD27" t="n">
-        <v>-1.5</v>
+        <v>-3.3</v>
       </c>
       <c r="AF27" t="n">
-        <v>224.37</v>
+        <v>225.93</v>
       </c>
       <c r="AG27" t="n">
-        <v>3</v>
+        <v>1.56</v>
       </c>
       <c r="AH27" t="n">
         <v>215</v>
@@ -3192,10 +3153,10 @@
         <v>235</v>
       </c>
       <c r="AK27" t="n">
-        <v>135.61</v>
+        <v>135.28</v>
       </c>
       <c r="AL27" t="n">
-        <v>0.4</v>
+        <v>-0.33</v>
       </c>
       <c r="AM27" t="n">
         <v>110</v>
@@ -3204,60 +3165,93 @@
         <v>142</v>
       </c>
       <c r="BL27" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B28" t="n">
-        <v>146.3</v>
+        <v>182.8</v>
+      </c>
+      <c r="C28" t="n">
+        <v>86.8</v>
       </c>
       <c r="D28" t="n">
-        <v>33.4</v>
+        <v>31.8</v>
+      </c>
+      <c r="E28" t="n">
+        <v>33</v>
       </c>
       <c r="F28" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
+      </c>
+      <c r="H28" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="I28" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J28" t="n">
+        <v>41.1</v>
       </c>
       <c r="K28" t="n">
-        <v>98.2</v>
+        <v>74.2</v>
+      </c>
+      <c r="M28" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="N28" t="n">
+        <v>33.5</v>
       </c>
       <c r="O28" t="n">
-        <v>35.1</v>
+        <v>38.4</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="R28" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S28" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" t="n">
+        <v>22.4</v>
       </c>
       <c r="V28" t="n">
-        <v>4.9</v>
+        <v>9.1</v>
       </c>
       <c r="W28" t="n">
-        <v>16.4</v>
+        <v>15</v>
       </c>
       <c r="X28" t="n">
-        <v>10.6</v>
+        <v>12.1</v>
       </c>
       <c r="Y28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z28" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AA28" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>-6.4</v>
+        <v>-10.5</v>
       </c>
       <c r="AC28" t="n">
-        <v>-0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>-3.3</v>
+        <v>-5.1</v>
       </c>
       <c r="AF28" t="n">
-        <v>225.93</v>
+        <v>218.63</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.56</v>
+        <v>-7.3</v>
       </c>
       <c r="AH28" t="n">
         <v>215</v>
@@ -3266,10 +3260,10 @@
         <v>235</v>
       </c>
       <c r="AK28" t="n">
-        <v>135.28</v>
+        <v>126.27</v>
       </c>
       <c r="AL28" t="n">
-        <v>-0.33</v>
+        <v>-9.01</v>
       </c>
       <c r="AM28" t="n">
         <v>110</v>
@@ -3277,94 +3271,100 @@
       <c r="AN28" t="n">
         <v>142</v>
       </c>
+      <c r="AP28" t="n">
+        <v>82.66</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>14.7</v>
+      </c>
       <c r="BL28" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B29" t="n">
-        <v>182.8</v>
+        <v>181.8</v>
       </c>
       <c r="C29" t="n">
-        <v>86.8</v>
+        <v>86.5</v>
       </c>
       <c r="D29" t="n">
-        <v>31.8</v>
+        <v>31.4</v>
       </c>
       <c r="E29" t="n">
-        <v>33</v>
+        <v>34.2</v>
       </c>
       <c r="F29" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="H29" t="n">
-        <v>23.5</v>
+        <v>24.4</v>
       </c>
       <c r="I29" t="n">
-        <v>9.6</v>
+        <v>10.4</v>
       </c>
       <c r="J29" t="n">
-        <v>41.1</v>
+        <v>41.9</v>
       </c>
       <c r="K29" t="n">
-        <v>74.2</v>
+        <v>76.8</v>
       </c>
       <c r="M29" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="N29" t="n">
-        <v>33.5</v>
+        <v>35.7</v>
       </c>
       <c r="O29" t="n">
-        <v>38.4</v>
+        <v>39.8</v>
       </c>
       <c r="Q29" t="n">
-        <v>22.4</v>
+        <v>23</v>
       </c>
       <c r="R29" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>20.1</v>
       </c>
       <c r="T29" t="n">
-        <v>22.4</v>
+        <v>23</v>
       </c>
       <c r="V29" t="n">
-        <v>9.1</v>
+        <v>7.1</v>
       </c>
       <c r="W29" t="n">
-        <v>15</v>
+        <v>14.8</v>
       </c>
       <c r="X29" t="n">
-        <v>12.1</v>
+        <v>10.9</v>
       </c>
       <c r="Y29" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z29" t="n">
         <v>12</v>
       </c>
       <c r="AA29" t="n">
-        <v>8.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AB29" t="n">
-        <v>-10.5</v>
+        <v>-4.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>-5.1</v>
+        <v>-1.4</v>
       </c>
       <c r="AF29" t="n">
-        <v>218.63</v>
+        <v>216.39</v>
       </c>
       <c r="AG29" t="n">
-        <v>-7.3</v>
+        <v>-2.23</v>
       </c>
       <c r="AH29" t="n">
         <v>215</v>
@@ -3373,10 +3373,10 @@
         <v>235</v>
       </c>
       <c r="AK29" t="n">
-        <v>126.27</v>
+        <v>123.32</v>
       </c>
       <c r="AL29" t="n">
-        <v>-9.01</v>
+        <v>-2.95</v>
       </c>
       <c r="AM29" t="n">
         <v>110</v>
@@ -3385,99 +3385,99 @@
         <v>142</v>
       </c>
       <c r="AP29" t="n">
-        <v>82.66</v>
+        <v>79.08</v>
       </c>
       <c r="AS29" t="n">
-        <v>14.7</v>
+        <v>13.91</v>
       </c>
       <c r="BL29" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B30" t="n">
-        <v>181.8</v>
+        <v>183</v>
       </c>
       <c r="C30" t="n">
-        <v>86.5</v>
+        <v>84.7</v>
       </c>
       <c r="D30" t="n">
-        <v>31.4</v>
+        <v>30.9</v>
       </c>
       <c r="E30" t="n">
-        <v>34.2</v>
+        <v>33.7</v>
       </c>
       <c r="F30" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="H30" t="n">
-        <v>24.4</v>
+        <v>23.4</v>
       </c>
       <c r="I30" t="n">
-        <v>10.4</v>
+        <v>10.6</v>
       </c>
       <c r="J30" t="n">
-        <v>41.9</v>
+        <v>42.3</v>
       </c>
       <c r="K30" t="n">
-        <v>76.8</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="M30" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="N30" t="n">
-        <v>35.7</v>
+        <v>36.7</v>
       </c>
       <c r="O30" t="n">
-        <v>39.8</v>
+        <v>40.8</v>
       </c>
       <c r="Q30" t="n">
-        <v>23</v>
+        <v>23.6</v>
       </c>
       <c r="R30" t="n">
         <v>1.8</v>
       </c>
       <c r="S30" t="n">
-        <v>20.1</v>
+        <v>20.8</v>
       </c>
       <c r="T30" t="n">
-        <v>23</v>
+        <v>23.6</v>
       </c>
       <c r="V30" t="n">
-        <v>7.1</v>
+        <v>5.7</v>
       </c>
       <c r="W30" t="n">
-        <v>14.8</v>
+        <v>16.1</v>
       </c>
       <c r="X30" t="n">
         <v>10.9</v>
       </c>
       <c r="Y30" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA30" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AB30" t="n">
-        <v>-4.5</v>
+        <v>0.8</v>
       </c>
       <c r="AC30" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD30" t="n">
         <v>1.8</v>
       </c>
-      <c r="AD30" t="n">
-        <v>-1.4</v>
-      </c>
       <c r="AF30" t="n">
-        <v>216.39</v>
+        <v>217.16</v>
       </c>
       <c r="AG30" t="n">
-        <v>-2.23</v>
+        <v>0.76</v>
       </c>
       <c r="AH30" t="n">
         <v>215</v>
@@ -3486,10 +3486,10 @@
         <v>235</v>
       </c>
       <c r="AK30" t="n">
-        <v>123.32</v>
+        <v>117.87</v>
       </c>
       <c r="AL30" t="n">
-        <v>-2.95</v>
+        <v>-5.45</v>
       </c>
       <c r="AM30" t="n">
         <v>110</v>
@@ -3498,99 +3498,66 @@
         <v>142</v>
       </c>
       <c r="AP30" t="n">
-        <v>79.08</v>
+        <v>78.56</v>
       </c>
       <c r="AS30" t="n">
-        <v>13.91</v>
+        <v>13.45</v>
       </c>
       <c r="BL30" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B31" t="n">
-        <v>183</v>
-      </c>
-      <c r="C31" t="n">
-        <v>84.7</v>
+        <v>163.8</v>
       </c>
       <c r="D31" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="E31" t="n">
-        <v>33.7</v>
+        <v>29</v>
       </c>
       <c r="F31" t="n">
-        <v>7</v>
-      </c>
-      <c r="H31" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="I31" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="J31" t="n">
-        <v>42.3</v>
+        <v>6.5</v>
       </c>
       <c r="K31" t="n">
-        <v>76.40000000000001</v>
-      </c>
-      <c r="M31" t="n">
-        <v>4</v>
-      </c>
-      <c r="N31" t="n">
-        <v>36.7</v>
+        <v>101.2</v>
       </c>
       <c r="O31" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S31" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="T31" t="n">
-        <v>23.6</v>
+        <v>40.2</v>
       </c>
       <c r="V31" t="n">
-        <v>5.7</v>
+        <v>6.3</v>
       </c>
       <c r="W31" t="n">
-        <v>16.1</v>
+        <v>17.2</v>
       </c>
       <c r="X31" t="n">
-        <v>10.9</v>
+        <v>11.8</v>
       </c>
       <c r="Y31" t="n">
         <v>8</v>
       </c>
       <c r="Z31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA31" t="n">
         <v>10</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.7</v>
+        <v>4.3</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="AF31" t="n">
-        <v>217.16</v>
+        <v>220.31</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.76</v>
+        <v>3.16</v>
       </c>
       <c r="AH31" t="n">
         <v>215</v>
@@ -3599,10 +3566,10 @@
         <v>235</v>
       </c>
       <c r="AK31" t="n">
-        <v>117.87</v>
+        <v>116.52</v>
       </c>
       <c r="AL31" t="n">
-        <v>-5.45</v>
+        <v>-1.35</v>
       </c>
       <c r="AM31" t="n">
         <v>110</v>
@@ -3610,67 +3577,61 @@
       <c r="AN31" t="n">
         <v>142</v>
       </c>
-      <c r="AP31" t="n">
-        <v>78.56</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>13.45</v>
-      </c>
       <c r="BL31" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B32" t="n">
-        <v>163.8</v>
+        <v>155.9</v>
       </c>
       <c r="D32" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F32" t="n">
         <v>6.5</v>
       </c>
       <c r="K32" t="n">
-        <v>101.2</v>
+        <v>99.3</v>
       </c>
       <c r="O32" t="n">
-        <v>40.2</v>
+        <v>38.5</v>
       </c>
       <c r="V32" t="n">
-        <v>6.3</v>
+        <v>8.9</v>
       </c>
       <c r="W32" t="n">
-        <v>17.2</v>
+        <v>15.8</v>
       </c>
       <c r="X32" t="n">
-        <v>11.8</v>
+        <v>12.4</v>
       </c>
       <c r="Y32" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z32" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA32" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AC32" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="AF32" t="n">
-        <v>220.31</v>
+        <v>221.99</v>
       </c>
       <c r="AG32" t="n">
-        <v>3.16</v>
+        <v>1.67</v>
       </c>
       <c r="AH32" t="n">
         <v>215</v>
@@ -3679,10 +3640,10 @@
         <v>235</v>
       </c>
       <c r="AK32" t="n">
-        <v>116.52</v>
+        <v>116.37</v>
       </c>
       <c r="AL32" t="n">
-        <v>-1.35</v>
+        <v>-0.15</v>
       </c>
       <c r="AM32" t="n">
         <v>110</v>
@@ -3691,60 +3652,60 @@
         <v>142</v>
       </c>
       <c r="BL32" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B33" t="n">
-        <v>155.9</v>
+        <v>141.3</v>
       </c>
       <c r="D33" t="n">
-        <v>28</v>
+        <v>26.3</v>
       </c>
       <c r="F33" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="K33" t="n">
-        <v>99.3</v>
+        <v>97.8</v>
       </c>
       <c r="O33" t="n">
-        <v>38.5</v>
+        <v>39.8</v>
       </c>
       <c r="V33" t="n">
-        <v>8.9</v>
+        <v>9.5</v>
       </c>
       <c r="W33" t="n">
-        <v>15.8</v>
+        <v>17.7</v>
       </c>
       <c r="X33" t="n">
-        <v>12.4</v>
+        <v>13.6</v>
       </c>
       <c r="Y33" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Z33" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA33" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="AC33" t="n">
-        <v>5.7</v>
+        <v>7.5</v>
       </c>
       <c r="AD33" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="AF33" t="n">
-        <v>221.99</v>
+        <v>225.14</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.67</v>
+        <v>3.15</v>
       </c>
       <c r="AH33" t="n">
         <v>215</v>
@@ -3752,12 +3713,6 @@
       <c r="AI33" t="n">
         <v>235</v>
       </c>
-      <c r="AK33" t="n">
-        <v>116.37</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>-0.15</v>
-      </c>
       <c r="AM33" t="n">
         <v>110</v>
       </c>
@@ -3765,60 +3720,54 @@
         <v>142</v>
       </c>
       <c r="BL33" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B34" t="n">
-        <v>141.3</v>
+        <v>131.5</v>
       </c>
       <c r="D34" t="n">
-        <v>26.3</v>
+        <v>27.3</v>
       </c>
       <c r="F34" t="n">
         <v>5.5</v>
       </c>
       <c r="K34" t="n">
-        <v>97.8</v>
+        <v>97</v>
       </c>
       <c r="O34" t="n">
-        <v>39.8</v>
+        <v>35.7</v>
       </c>
       <c r="V34" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="W34" t="n">
-        <v>17.7</v>
+        <v>13.9</v>
       </c>
       <c r="X34" t="n">
-        <v>13.6</v>
+        <v>11.4</v>
       </c>
       <c r="Y34" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z34" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA34" t="n">
         <v>15</v>
       </c>
-      <c r="AA34" t="n">
-        <v>14</v>
-      </c>
       <c r="AB34" t="n">
-        <v>0.2</v>
+        <v>-3.6</v>
       </c>
       <c r="AC34" t="n">
-        <v>7.5</v>
+        <v>2.8</v>
       </c>
       <c r="AD34" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>225.14</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>3.15</v>
+        <v>-0.4</v>
       </c>
       <c r="AH34" t="n">
         <v>215</v>
@@ -3833,54 +3782,93 @@
         <v>142</v>
       </c>
       <c r="BL34" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="B35" t="n">
-        <v>131.5</v>
+        <v>153</v>
+      </c>
+      <c r="C35" t="n">
+        <v>71.8</v>
       </c>
       <c r="D35" t="n">
-        <v>27.3</v>
+        <v>28.6</v>
+      </c>
+      <c r="E35" t="n">
+        <v>24.7</v>
       </c>
       <c r="F35" t="n">
-        <v>5.5</v>
+        <v>4</v>
+      </c>
+      <c r="H35" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I35" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J35" t="n">
+        <v>41.1</v>
       </c>
       <c r="K35" t="n">
-        <v>97</v>
+        <v>75.90000000000001</v>
+      </c>
+      <c r="M35" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N35" t="n">
+        <v>33.5</v>
       </c>
       <c r="O35" t="n">
-        <v>35.7</v>
+        <v>38.3</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="R35" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>23.2</v>
       </c>
       <c r="V35" t="n">
-        <v>9</v>
+        <v>11.2</v>
       </c>
       <c r="W35" t="n">
-        <v>13.9</v>
+        <v>13</v>
       </c>
       <c r="X35" t="n">
-        <v>11.4</v>
+        <v>12.1</v>
       </c>
       <c r="Y35" t="n">
         <v>12</v>
       </c>
       <c r="Z35" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AA35" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AB35" t="n">
-        <v>-3.6</v>
+        <v>-6.6</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.8</v>
+        <v>5.3</v>
       </c>
       <c r="AD35" t="n">
-        <v>-0.4</v>
+        <v>-0.6</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>229.96</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>-0.02</v>
       </c>
       <c r="AH35" t="n">
         <v>215</v>
@@ -3888,100 +3876,112 @@
       <c r="AI35" t="n">
         <v>235</v>
       </c>
+      <c r="AK35" t="n">
+        <v>128.14</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>11.77</v>
+      </c>
       <c r="AM35" t="n">
         <v>110</v>
       </c>
       <c r="AN35" t="n">
         <v>142</v>
       </c>
+      <c r="AP35" t="n">
+        <v>87.47</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>14.8</v>
+      </c>
       <c r="BL35" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B36" t="n">
-        <v>153</v>
+        <v>165.8</v>
       </c>
       <c r="C36" t="n">
-        <v>71.8</v>
+        <v>77.3</v>
       </c>
       <c r="D36" t="n">
-        <v>28.6</v>
+        <v>29.3</v>
       </c>
       <c r="E36" t="n">
-        <v>24.7</v>
+        <v>27.7</v>
       </c>
       <c r="F36" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="H36" t="n">
         <v>24.1</v>
       </c>
       <c r="I36" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="J36" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="K36" t="n">
-        <v>75.90000000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="M36" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="N36" t="n">
-        <v>33.5</v>
+        <v>35.1</v>
       </c>
       <c r="O36" t="n">
-        <v>38.3</v>
+        <v>39.8</v>
       </c>
       <c r="Q36" t="n">
-        <v>23.2</v>
+        <v>23.8</v>
       </c>
       <c r="R36" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="T36" t="n">
-        <v>23.2</v>
+        <v>23.8</v>
       </c>
       <c r="V36" t="n">
-        <v>11.2</v>
+        <v>9.4</v>
       </c>
       <c r="W36" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="X36" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z36" t="n">
         <v>13</v>
       </c>
-      <c r="X36" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>14</v>
-      </c>
       <c r="AA36" t="n">
-        <v>12.5</v>
+        <v>10.1</v>
       </c>
       <c r="AB36" t="n">
-        <v>-6.6</v>
+        <v>-0.7</v>
       </c>
       <c r="AC36" t="n">
-        <v>5.3</v>
+        <v>9.5</v>
       </c>
       <c r="AD36" t="n">
-        <v>-0.6</v>
+        <v>4.4</v>
       </c>
       <c r="AF36" t="n">
-        <v>229.96</v>
+        <v>227.01</v>
       </c>
       <c r="AG36" t="n">
-        <v>-0.02</v>
+        <v>-2.95</v>
       </c>
       <c r="AH36" t="n">
         <v>215</v>
@@ -3990,10 +3990,10 @@
         <v>235</v>
       </c>
       <c r="AK36" t="n">
-        <v>128.14</v>
+        <v>128.15</v>
       </c>
       <c r="AL36" t="n">
-        <v>11.77</v>
+        <v>0.01</v>
       </c>
       <c r="AM36" t="n">
         <v>110</v>
@@ -4002,99 +4002,99 @@
         <v>142</v>
       </c>
       <c r="AP36" t="n">
-        <v>87.47</v>
+        <v>83.41</v>
       </c>
       <c r="AS36" t="n">
-        <v>14.8</v>
+        <v>14.52</v>
       </c>
       <c r="BL36" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B37" t="n">
-        <v>165.8</v>
+        <v>158.1</v>
       </c>
       <c r="C37" t="n">
-        <v>77.3</v>
+        <v>73.7</v>
       </c>
       <c r="D37" t="n">
-        <v>29.3</v>
+        <v>30.3</v>
       </c>
       <c r="E37" t="n">
-        <v>27.7</v>
+        <v>26</v>
       </c>
       <c r="F37" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="H37" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="I37" t="n">
-        <v>10.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J37" t="n">
-        <v>41.6</v>
+        <v>40.9</v>
       </c>
       <c r="K37" t="n">
-        <v>76.59999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="M37" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="N37" t="n">
-        <v>35.1</v>
+        <v>35.3</v>
       </c>
       <c r="O37" t="n">
-        <v>39.8</v>
+        <v>40.3</v>
       </c>
       <c r="Q37" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="R37" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S37" t="n">
         <v>7</v>
       </c>
       <c r="T37" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="V37" t="n">
-        <v>9.4</v>
+        <v>8.9</v>
       </c>
       <c r="W37" t="n">
-        <v>17.4</v>
+        <v>19.3</v>
       </c>
       <c r="X37" t="n">
-        <v>13.4</v>
+        <v>14.1</v>
       </c>
       <c r="Y37" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z37" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA37" t="n">
-        <v>10.1</v>
+        <v>11</v>
       </c>
       <c r="AB37" t="n">
-        <v>-0.7</v>
+        <v>4.4</v>
       </c>
       <c r="AC37" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="AD37" t="n">
-        <v>4.4</v>
+        <v>6.5</v>
       </c>
       <c r="AF37" t="n">
-        <v>227.01</v>
+        <v>228.35</v>
       </c>
       <c r="AG37" t="n">
-        <v>-2.95</v>
+        <v>1.33</v>
       </c>
       <c r="AH37" t="n">
         <v>215</v>
@@ -4103,10 +4103,10 @@
         <v>235</v>
       </c>
       <c r="AK37" t="n">
-        <v>128.15</v>
+        <v>128.86</v>
       </c>
       <c r="AL37" t="n">
-        <v>0.01</v>
+        <v>0.71</v>
       </c>
       <c r="AM37" t="n">
         <v>110</v>
@@ -4115,99 +4115,99 @@
         <v>142</v>
       </c>
       <c r="AP37" t="n">
-        <v>83.41</v>
+        <v>82.37</v>
       </c>
       <c r="AS37" t="n">
-        <v>14.52</v>
+        <v>14.22</v>
       </c>
       <c r="BL37" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B38" t="n">
-        <v>158.1</v>
+        <v>154.9</v>
       </c>
       <c r="C38" t="n">
-        <v>73.7</v>
+        <v>70.2</v>
       </c>
       <c r="D38" t="n">
-        <v>30.3</v>
+        <v>31.5</v>
       </c>
       <c r="E38" t="n">
-        <v>26</v>
+        <v>27.7</v>
       </c>
       <c r="F38" t="n">
-        <v>4.1</v>
+        <v>2.7</v>
       </c>
       <c r="H38" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="I38" t="n">
-        <v>9.300000000000001</v>
+        <v>11.3</v>
       </c>
       <c r="J38" t="n">
-        <v>40.9</v>
+        <v>40.3</v>
       </c>
       <c r="K38" t="n">
-        <v>74.40000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="M38" t="n">
-        <v>5</v>
+        <v>6.1</v>
       </c>
       <c r="N38" t="n">
-        <v>35.3</v>
+        <v>32.9</v>
       </c>
       <c r="O38" t="n">
-        <v>40.3</v>
+        <v>39</v>
       </c>
       <c r="Q38" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="R38" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="S38" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="T38" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="V38" t="n">
-        <v>8.9</v>
+        <v>6.3</v>
       </c>
       <c r="W38" t="n">
-        <v>19.3</v>
+        <v>25.2</v>
       </c>
       <c r="X38" t="n">
-        <v>14.1</v>
+        <v>15.8</v>
       </c>
       <c r="Y38" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z38" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA38" t="n">
-        <v>11</v>
+        <v>12.6</v>
       </c>
       <c r="AB38" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="AC38" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="AD38" t="n">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="AF38" t="n">
-        <v>228.35</v>
+        <v>231.16</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.33</v>
+        <v>2.81</v>
       </c>
       <c r="AH38" t="n">
         <v>215</v>
@@ -4216,10 +4216,10 @@
         <v>235</v>
       </c>
       <c r="AK38" t="n">
-        <v>128.86</v>
+        <v>130.88</v>
       </c>
       <c r="AL38" t="n">
-        <v>0.71</v>
+        <v>2.02</v>
       </c>
       <c r="AM38" t="n">
         <v>110</v>
@@ -4228,99 +4228,66 @@
         <v>142</v>
       </c>
       <c r="AP38" t="n">
-        <v>82.37</v>
+        <v>85.48999999999999</v>
       </c>
       <c r="AS38" t="n">
-        <v>14.22</v>
+        <v>13.1</v>
       </c>
       <c r="BL38" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B39" t="n">
-        <v>154.9</v>
-      </c>
-      <c r="C39" t="n">
-        <v>70.2</v>
+        <v>152.2</v>
       </c>
       <c r="D39" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="E39" t="n">
-        <v>27.7</v>
+        <v>31</v>
       </c>
       <c r="F39" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="H39" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I39" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J39" t="n">
-        <v>40.3</v>
+        <v>3.5</v>
       </c>
       <c r="K39" t="n">
-        <v>75.8</v>
-      </c>
-      <c r="M39" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="N39" t="n">
-        <v>32.9</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O39" t="n">
-        <v>39</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="R39" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="S39" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="T39" t="n">
-        <v>23.7</v>
+        <v>34.4</v>
       </c>
       <c r="V39" t="n">
-        <v>6.3</v>
+        <v>9.5</v>
       </c>
       <c r="W39" t="n">
-        <v>25.2</v>
+        <v>25.5</v>
       </c>
       <c r="X39" t="n">
-        <v>15.8</v>
+        <v>17.5</v>
       </c>
       <c r="Y39" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Z39" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AA39" t="n">
-        <v>12.6</v>
+        <v>9</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.9</v>
+        <v>-1.1</v>
       </c>
       <c r="AC39" t="n">
         <v>8.6</v>
       </c>
       <c r="AD39" t="n">
-        <v>5.8</v>
+        <v>3.8</v>
       </c>
       <c r="AF39" t="n">
-        <v>231.16</v>
+        <v>228.13</v>
       </c>
       <c r="AG39" t="n">
-        <v>2.81</v>
+        <v>-3.03</v>
       </c>
       <c r="AH39" t="n">
         <v>215</v>
@@ -4328,79 +4295,67 @@
       <c r="AI39" t="n">
         <v>235</v>
       </c>
-      <c r="AK39" t="n">
-        <v>130.88</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AM39" t="n">
         <v>110</v>
       </c>
       <c r="AN39" t="n">
         <v>142</v>
       </c>
-      <c r="AP39" t="n">
-        <v>85.48999999999999</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>13.1</v>
-      </c>
       <c r="BL39" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B40" t="n">
-        <v>152.2</v>
+        <v>143.9</v>
       </c>
       <c r="D40" t="n">
-        <v>31</v>
+        <v>30.8</v>
       </c>
       <c r="F40" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="K40" t="n">
-        <v>98.40000000000001</v>
+        <v>99.2</v>
       </c>
       <c r="O40" t="n">
-        <v>34.4</v>
+        <v>35.2</v>
       </c>
       <c r="V40" t="n">
-        <v>9.5</v>
+        <v>10.7</v>
       </c>
       <c r="W40" t="n">
-        <v>25.5</v>
+        <v>17.6</v>
       </c>
       <c r="X40" t="n">
-        <v>17.5</v>
+        <v>14.2</v>
       </c>
       <c r="Y40" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Z40" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA40" t="n">
         <v>9</v>
       </c>
       <c r="AB40" t="n">
-        <v>-1.1</v>
+        <v>-0.8</v>
       </c>
       <c r="AC40" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD40" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AF40" t="n">
-        <v>228.13</v>
+        <v>229.16</v>
       </c>
       <c r="AG40" t="n">
-        <v>-3.03</v>
+        <v>1.03</v>
       </c>
       <c r="AH40" t="n">
         <v>215</v>
@@ -4415,60 +4370,93 @@
         <v>142</v>
       </c>
       <c r="BL40" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B41" t="n">
-        <v>143.9</v>
+        <v>163.2</v>
+      </c>
+      <c r="C41" t="n">
+        <v>73.7</v>
       </c>
       <c r="D41" t="n">
-        <v>30.8</v>
+        <v>30</v>
+      </c>
+      <c r="E41" t="n">
+        <v>28.2</v>
       </c>
       <c r="F41" t="n">
-        <v>2.5</v>
+        <v>4.8</v>
+      </c>
+      <c r="H41" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I41" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J41" t="n">
+        <v>40.1</v>
       </c>
       <c r="K41" t="n">
-        <v>99.2</v>
+        <v>75.59999999999999</v>
+      </c>
+      <c r="M41" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="N41" t="n">
+        <v>32.9</v>
       </c>
       <c r="O41" t="n">
-        <v>35.2</v>
+        <v>39.7</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="R41" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="S41" t="n">
+        <v>6</v>
+      </c>
+      <c r="T41" t="n">
+        <v>23.5</v>
       </c>
       <c r="V41" t="n">
-        <v>10.7</v>
+        <v>9.4</v>
       </c>
       <c r="W41" t="n">
-        <v>17.6</v>
+        <v>20.1</v>
       </c>
       <c r="X41" t="n">
-        <v>14.2</v>
+        <v>14.8</v>
       </c>
       <c r="Y41" t="n">
         <v>4</v>
       </c>
       <c r="Z41" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA41" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AB41" t="n">
-        <v>-0.8</v>
+        <v>-0.9</v>
       </c>
       <c r="AC41" t="n">
-        <v>8.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="AD41" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AF41" t="n">
-        <v>229.16</v>
+        <v>228.55</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.03</v>
+        <v>-0.61</v>
       </c>
       <c r="AH41" t="n">
         <v>215</v>
@@ -4476,100 +4464,112 @@
       <c r="AI41" t="n">
         <v>235</v>
       </c>
+      <c r="AK41" t="n">
+        <v>127.06</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>-3.82</v>
+      </c>
       <c r="AM41" t="n">
         <v>110</v>
       </c>
       <c r="AN41" t="n">
         <v>142</v>
       </c>
+      <c r="AP41" t="n">
+        <v>82.81</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>12.9</v>
+      </c>
       <c r="BL41" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="B42" t="n">
-        <v>163.2</v>
+        <v>174.4</v>
       </c>
       <c r="C42" t="n">
-        <v>73.7</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="D42" t="n">
-        <v>30</v>
+        <v>32.1</v>
       </c>
       <c r="E42" t="n">
-        <v>28.2</v>
+        <v>30.8</v>
       </c>
       <c r="F42" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="H42" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="I42" t="n">
-        <v>11.4</v>
+        <v>10.5</v>
       </c>
       <c r="J42" t="n">
-        <v>40.1</v>
+        <v>39.5</v>
       </c>
       <c r="K42" t="n">
-        <v>75.59999999999999</v>
+        <v>74</v>
       </c>
       <c r="M42" t="n">
         <v>6.8</v>
       </c>
       <c r="N42" t="n">
-        <v>32.9</v>
+        <v>35.8</v>
       </c>
       <c r="O42" t="n">
-        <v>39.7</v>
+        <v>42.6</v>
       </c>
       <c r="Q42" t="n">
-        <v>23.5</v>
+        <v>23.1</v>
       </c>
       <c r="R42" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="S42" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="T42" t="n">
-        <v>23.5</v>
+        <v>23.1</v>
       </c>
       <c r="V42" t="n">
-        <v>9.4</v>
+        <v>12.8</v>
       </c>
       <c r="W42" t="n">
-        <v>20.1</v>
+        <v>22.1</v>
       </c>
       <c r="X42" t="n">
-        <v>14.8</v>
+        <v>17.5</v>
       </c>
       <c r="Y42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Z42" t="n">
         <v>13</v>
       </c>
       <c r="AA42" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AC42" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="AB42" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>9.5</v>
-      </c>
       <c r="AD42" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AF42" t="n">
-        <v>228.55</v>
+        <v>219.99</v>
       </c>
       <c r="AG42" t="n">
-        <v>-0.61</v>
+        <v>-8.56</v>
       </c>
       <c r="AH42" t="n">
         <v>215</v>
@@ -4578,10 +4578,10 @@
         <v>235</v>
       </c>
       <c r="AK42" t="n">
-        <v>127.06</v>
+        <v>125.61</v>
       </c>
       <c r="AL42" t="n">
-        <v>-3.82</v>
+        <v>-1.45</v>
       </c>
       <c r="AM42" t="n">
         <v>110</v>
@@ -4590,99 +4590,99 @@
         <v>142</v>
       </c>
       <c r="AP42" t="n">
-        <v>82.81</v>
+        <v>77.83</v>
       </c>
       <c r="AS42" t="n">
-        <v>12.9</v>
+        <v>12.96</v>
       </c>
       <c r="BL42" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B43" t="n">
-        <v>174.4</v>
+        <v>163.2</v>
       </c>
       <c r="C43" t="n">
-        <v>75.40000000000001</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="D43" t="n">
-        <v>32.1</v>
+        <v>32.9</v>
       </c>
       <c r="E43" t="n">
-        <v>30.8</v>
+        <v>26</v>
       </c>
       <c r="F43" t="n">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="H43" t="n">
-        <v>24</v>
+        <v>23.8</v>
       </c>
       <c r="I43" t="n">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="J43" t="n">
-        <v>39.5</v>
+        <v>40.1</v>
       </c>
       <c r="K43" t="n">
-        <v>74</v>
+        <v>71.3</v>
       </c>
       <c r="M43" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="N43" t="n">
-        <v>35.8</v>
+        <v>34.3</v>
       </c>
       <c r="O43" t="n">
-        <v>42.6</v>
+        <v>41.5</v>
       </c>
       <c r="Q43" t="n">
         <v>23.1</v>
       </c>
       <c r="R43" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="S43" t="n">
-        <v>8.5</v>
+        <v>6.2</v>
       </c>
       <c r="T43" t="n">
         <v>23.1</v>
       </c>
       <c r="V43" t="n">
-        <v>12.8</v>
+        <v>9.6</v>
       </c>
       <c r="W43" t="n">
-        <v>22.1</v>
+        <v>23.3</v>
       </c>
       <c r="X43" t="n">
-        <v>17.5</v>
+        <v>16.4</v>
       </c>
       <c r="Y43" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z43" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA43" t="n">
-        <v>10.1</v>
+        <v>12.2</v>
       </c>
       <c r="AB43" t="n">
-        <v>0.3</v>
+        <v>2.6</v>
       </c>
       <c r="AC43" t="n">
-        <v>9.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="AD43" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AF43" t="n">
-        <v>219.99</v>
+        <v>219.22</v>
       </c>
       <c r="AG43" t="n">
-        <v>-8.56</v>
+        <v>-0.77</v>
       </c>
       <c r="AH43" t="n">
         <v>215</v>
@@ -4691,10 +4691,10 @@
         <v>235</v>
       </c>
       <c r="AK43" t="n">
-        <v>125.61</v>
+        <v>124.36</v>
       </c>
       <c r="AL43" t="n">
-        <v>-1.45</v>
+        <v>-1.25</v>
       </c>
       <c r="AM43" t="n">
         <v>110</v>
@@ -4703,99 +4703,99 @@
         <v>142</v>
       </c>
       <c r="AP43" t="n">
-        <v>77.83</v>
+        <v>76.81</v>
       </c>
       <c r="AS43" t="n">
-        <v>12.96</v>
+        <v>12.38</v>
       </c>
       <c r="BL43" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B44" t="n">
-        <v>163.2</v>
+        <v>152.7</v>
       </c>
       <c r="C44" t="n">
-        <v>70.90000000000001</v>
+        <v>62.6</v>
       </c>
       <c r="D44" t="n">
-        <v>32.9</v>
+        <v>32.7</v>
       </c>
       <c r="E44" t="n">
-        <v>26</v>
+        <v>24.6</v>
       </c>
       <c r="F44" t="n">
-        <v>6.9</v>
+        <v>5.2</v>
       </c>
       <c r="H44" t="n">
         <v>23.8</v>
       </c>
       <c r="I44" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J44" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="K44" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="M44" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="N44" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="O44" t="n">
         <v>40.1</v>
       </c>
-      <c r="K44" t="n">
-        <v>71.3</v>
-      </c>
-      <c r="M44" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="N44" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="O44" t="n">
-        <v>41.5</v>
-      </c>
       <c r="Q44" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="R44" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="S44" t="n">
-        <v>6.2</v>
+        <v>4</v>
       </c>
       <c r="T44" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="V44" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="W44" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="X44" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC44" t="n">
         <v>9.6</v>
       </c>
-      <c r="W44" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="X44" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>8.5</v>
-      </c>
       <c r="AD44" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AF44" t="n">
-        <v>219.22</v>
+        <v>220.73</v>
       </c>
       <c r="AG44" t="n">
-        <v>-0.77</v>
+        <v>1.5</v>
       </c>
       <c r="AH44" t="n">
         <v>215</v>
@@ -4804,10 +4804,10 @@
         <v>235</v>
       </c>
       <c r="AK44" t="n">
-        <v>124.36</v>
+        <v>120.93</v>
       </c>
       <c r="AL44" t="n">
-        <v>-1.25</v>
+        <v>-3.43</v>
       </c>
       <c r="AM44" t="n">
         <v>110</v>
@@ -4816,75 +4816,75 @@
         <v>142</v>
       </c>
       <c r="AP44" t="n">
-        <v>76.81</v>
+        <v>77.87</v>
       </c>
       <c r="AS44" t="n">
-        <v>12.38</v>
+        <v>13.26</v>
       </c>
       <c r="BL44" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B45" t="n">
-        <v>152.7</v>
+        <v>150.7</v>
       </c>
       <c r="C45" t="n">
-        <v>62.6</v>
+        <v>64.8</v>
       </c>
       <c r="D45" t="n">
-        <v>32.7</v>
+        <v>33.7</v>
       </c>
       <c r="E45" t="n">
-        <v>24.6</v>
+        <v>27.1</v>
       </c>
       <c r="F45" t="n">
-        <v>5.2</v>
+        <v>3.8</v>
       </c>
       <c r="H45" t="n">
-        <v>23.8</v>
+        <v>23.4</v>
       </c>
       <c r="I45" t="n">
         <v>7.2</v>
       </c>
       <c r="J45" t="n">
-        <v>38.9</v>
+        <v>39.9</v>
       </c>
       <c r="K45" t="n">
-        <v>69.90000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="M45" t="n">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="N45" t="n">
-        <v>33.5</v>
+        <v>33</v>
       </c>
       <c r="O45" t="n">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="Q45" t="n">
         <v>23.2</v>
       </c>
       <c r="R45" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="S45" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T45" t="n">
         <v>23.2</v>
       </c>
       <c r="V45" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="W45" t="n">
-        <v>27.3</v>
+        <v>28.9</v>
       </c>
       <c r="X45" t="n">
-        <v>19.4</v>
+        <v>21.7</v>
       </c>
       <c r="Y45" t="n">
         <v>10</v>
@@ -4893,22 +4893,22 @@
         <v>18</v>
       </c>
       <c r="AA45" t="n">
-        <v>14</v>
+        <v>13.1</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="AC45" t="n">
-        <v>9.6</v>
+        <v>10.8</v>
       </c>
       <c r="AD45" t="n">
-        <v>5.7</v>
+        <v>6.7</v>
       </c>
       <c r="AF45" t="n">
-        <v>220.73</v>
+        <v>220.58</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.5</v>
+        <v>-0.15</v>
       </c>
       <c r="AH45" t="n">
         <v>215</v>
@@ -4917,10 +4917,10 @@
         <v>235</v>
       </c>
       <c r="AK45" t="n">
-        <v>120.93</v>
+        <v>120.28</v>
       </c>
       <c r="AL45" t="n">
-        <v>-3.43</v>
+        <v>-0.65</v>
       </c>
       <c r="AM45" t="n">
         <v>110</v>
@@ -4929,99 +4929,54 @@
         <v>142</v>
       </c>
       <c r="AP45" t="n">
-        <v>77.87</v>
+        <v>77.22</v>
       </c>
       <c r="AS45" t="n">
-        <v>13.26</v>
+        <v>13.79</v>
       </c>
       <c r="BL45" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B46" t="n">
-        <v>150.7</v>
-      </c>
-      <c r="C46" t="n">
-        <v>64.8</v>
+        <v>138.2</v>
       </c>
       <c r="D46" t="n">
-        <v>33.7</v>
-      </c>
-      <c r="E46" t="n">
-        <v>27.1</v>
+        <v>33.6</v>
       </c>
       <c r="F46" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H46" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="V46" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="W46" t="n">
         <v>23.4</v>
       </c>
-      <c r="I46" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="J46" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="K46" t="n">
-        <v>70.5</v>
-      </c>
-      <c r="M46" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="N46" t="n">
-        <v>33</v>
-      </c>
-      <c r="O46" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="R46" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="S46" t="n">
-        <v>3</v>
-      </c>
-      <c r="T46" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="V46" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="W46" t="n">
-        <v>28.9</v>
-      </c>
       <c r="X46" t="n">
-        <v>21.7</v>
+        <v>19.4</v>
       </c>
       <c r="Y46" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z46" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AA46" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="AB46" t="n">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="AC46" t="n">
-        <v>10.8</v>
+        <v>8.5</v>
       </c>
       <c r="AD46" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>220.58</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>-0.15</v>
+        <v>4.5</v>
       </c>
       <c r="AH46" t="n">
         <v>215</v>
@@ -5029,67 +4984,61 @@
       <c r="AI46" t="n">
         <v>235</v>
       </c>
-      <c r="AK46" t="n">
-        <v>120.28</v>
-      </c>
-      <c r="AL46" t="n">
-        <v>-0.65</v>
-      </c>
       <c r="AM46" t="n">
         <v>110</v>
       </c>
       <c r="AN46" t="n">
         <v>142</v>
       </c>
-      <c r="AP46" t="n">
-        <v>77.22</v>
-      </c>
-      <c r="AS46" t="n">
-        <v>13.79</v>
-      </c>
       <c r="BL46" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B47" t="n">
-        <v>138.2</v>
+        <v>126.5</v>
       </c>
       <c r="D47" t="n">
-        <v>33.6</v>
+        <v>33.2</v>
       </c>
       <c r="F47" t="n">
-        <v>6.1</v>
+        <v>3.4</v>
       </c>
       <c r="V47" t="n">
-        <v>15.5</v>
+        <v>12.6</v>
       </c>
       <c r="W47" t="n">
-        <v>23.4</v>
+        <v>22.3</v>
       </c>
       <c r="X47" t="n">
-        <v>19.4</v>
+        <v>17.4</v>
       </c>
       <c r="Y47" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z47" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA47" t="n">
         <v>13</v>
       </c>
       <c r="AB47" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>8.5</v>
+        <v>6.7</v>
       </c>
       <c r="AD47" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>229.48</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>6.05</v>
       </c>
       <c r="AH47" t="n">
         <v>215</v>
@@ -5104,54 +5053,93 @@
         <v>142</v>
       </c>
       <c r="BL47" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B48" t="n">
-        <v>126.5</v>
+        <v>129.4</v>
+      </c>
+      <c r="C48" t="n">
+        <v>50.6</v>
       </c>
       <c r="D48" t="n">
-        <v>33.2</v>
+        <v>31.5</v>
+      </c>
+      <c r="E48" t="n">
+        <v>19.4</v>
       </c>
       <c r="F48" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
+      </c>
+      <c r="H48" t="n">
+        <v>24</v>
+      </c>
+      <c r="I48" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J48" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="K48" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="M48" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N48" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="O48" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>21.4</v>
       </c>
       <c r="V48" t="n">
-        <v>12.6</v>
+        <v>14.3</v>
       </c>
       <c r="W48" t="n">
-        <v>22.3</v>
+        <v>23.9</v>
       </c>
       <c r="X48" t="n">
-        <v>17.4</v>
+        <v>19.1</v>
       </c>
       <c r="Y48" t="n">
         <v>8</v>
       </c>
       <c r="Z48" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AA48" t="n">
-        <v>13</v>
+        <v>16.1</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AC48" t="n">
-        <v>6.7</v>
+        <v>7.6</v>
       </c>
       <c r="AD48" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="AF48" t="n">
-        <v>229.48</v>
+        <v>229.5</v>
       </c>
       <c r="AG48" t="n">
-        <v>6.05</v>
+        <v>0.02</v>
       </c>
       <c r="AH48" t="n">
         <v>215</v>
@@ -5159,100 +5147,112 @@
       <c r="AI48" t="n">
         <v>235</v>
       </c>
+      <c r="AK48" t="n">
+        <v>128.37</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>8.09</v>
+      </c>
       <c r="AM48" t="n">
         <v>110</v>
       </c>
       <c r="AN48" t="n">
         <v>142</v>
       </c>
+      <c r="AP48" t="n">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>15.97</v>
+      </c>
       <c r="BL48" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="B49" t="n">
-        <v>129.4</v>
+        <v>142.9</v>
       </c>
       <c r="C49" t="n">
-        <v>50.6</v>
+        <v>52.7</v>
       </c>
       <c r="D49" t="n">
-        <v>31.5</v>
+        <v>34.7</v>
       </c>
       <c r="E49" t="n">
-        <v>19.4</v>
+        <v>24.8</v>
       </c>
       <c r="F49" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="H49" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I49" t="n">
-        <v>10.4</v>
+        <v>9.9</v>
       </c>
       <c r="J49" t="n">
-        <v>38.9</v>
+        <v>38.2</v>
       </c>
       <c r="K49" t="n">
-        <v>73.3</v>
+        <v>70</v>
       </c>
       <c r="M49" t="n">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="N49" t="n">
-        <v>33.3</v>
+        <v>31.9</v>
       </c>
       <c r="O49" t="n">
-        <v>38</v>
+        <v>35.8</v>
       </c>
       <c r="Q49" t="n">
-        <v>21.4</v>
+        <v>19.7</v>
       </c>
       <c r="R49" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>21.4</v>
+        <v>19.7</v>
       </c>
       <c r="V49" t="n">
-        <v>14.3</v>
+        <v>12</v>
       </c>
       <c r="W49" t="n">
-        <v>23.9</v>
+        <v>25.8</v>
       </c>
       <c r="X49" t="n">
-        <v>19.1</v>
+        <v>18.9</v>
       </c>
       <c r="Y49" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Z49" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AA49" t="n">
-        <v>16.1</v>
+        <v>15</v>
       </c>
       <c r="AB49" t="n">
-        <v>0.4</v>
+        <v>-0.1</v>
       </c>
       <c r="AC49" t="n">
-        <v>7.6</v>
+        <v>5.8</v>
       </c>
       <c r="AD49" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="AF49" t="n">
-        <v>229.5</v>
+        <v>238.69</v>
       </c>
       <c r="AG49" t="n">
-        <v>0.02</v>
+        <v>-2.8</v>
       </c>
       <c r="AH49" t="n">
         <v>215</v>
@@ -5261,10 +5261,10 @@
         <v>235</v>
       </c>
       <c r="AK49" t="n">
-        <v>128.37</v>
+        <v>134.59</v>
       </c>
       <c r="AL49" t="n">
-        <v>8.09</v>
+        <v>6.22</v>
       </c>
       <c r="AM49" t="n">
         <v>110</v>
@@ -5273,99 +5273,99 @@
         <v>142</v>
       </c>
       <c r="AP49" t="n">
-        <v>91.59999999999999</v>
+        <v>89.05</v>
       </c>
       <c r="AS49" t="n">
-        <v>15.97</v>
+        <v>17.06</v>
       </c>
       <c r="BL49" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B50" t="n">
-        <v>142.9</v>
+        <v>148.1</v>
       </c>
       <c r="C50" t="n">
-        <v>52.7</v>
+        <v>51.9</v>
       </c>
       <c r="D50" t="n">
-        <v>34.7</v>
+        <v>35.4</v>
       </c>
       <c r="E50" t="n">
-        <v>24.8</v>
+        <v>31.5</v>
       </c>
       <c r="F50" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="H50" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="I50" t="n">
-        <v>9.9</v>
+        <v>9.6</v>
       </c>
       <c r="J50" t="n">
-        <v>38.2</v>
+        <v>39.6</v>
       </c>
       <c r="K50" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M50" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="N50" t="n">
-        <v>31.9</v>
+        <v>30.8</v>
       </c>
       <c r="O50" t="n">
-        <v>35.8</v>
+        <v>33.7</v>
       </c>
       <c r="Q50" t="n">
-        <v>19.7</v>
+        <v>20.7</v>
       </c>
       <c r="R50" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>19.7</v>
+        <v>20.7</v>
       </c>
       <c r="V50" t="n">
-        <v>12</v>
+        <v>13.1</v>
       </c>
       <c r="W50" t="n">
-        <v>25.8</v>
+        <v>25.5</v>
       </c>
       <c r="X50" t="n">
-        <v>18.9</v>
+        <v>19.3</v>
       </c>
       <c r="Y50" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z50" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AA50" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AB50" t="n">
-        <v>-0.1</v>
+        <v>-1</v>
       </c>
       <c r="AC50" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AD50" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="AF50" t="n">
-        <v>238.69</v>
+        <v>233.48</v>
       </c>
       <c r="AG50" t="n">
-        <v>-2.8</v>
+        <v>-4.86</v>
       </c>
       <c r="AH50" t="n">
         <v>215</v>
@@ -5374,10 +5374,10 @@
         <v>235</v>
       </c>
       <c r="AK50" t="n">
-        <v>134.59</v>
+        <v>136.6</v>
       </c>
       <c r="AL50" t="n">
-        <v>6.22</v>
+        <v>2.01</v>
       </c>
       <c r="AM50" t="n">
         <v>110</v>
@@ -5386,99 +5386,99 @@
         <v>142</v>
       </c>
       <c r="AP50" t="n">
-        <v>89.05</v>
+        <v>86.25</v>
       </c>
       <c r="AS50" t="n">
-        <v>17.06</v>
+        <v>17.13</v>
       </c>
       <c r="BL50" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B51" t="n">
-        <v>148.1</v>
+        <v>143.4</v>
       </c>
       <c r="C51" t="n">
-        <v>51.9</v>
+        <v>50.9</v>
       </c>
       <c r="D51" t="n">
-        <v>35.4</v>
+        <v>35.7</v>
       </c>
       <c r="E51" t="n">
-        <v>31.5</v>
+        <v>26.2</v>
       </c>
       <c r="F51" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="H51" t="n">
-        <v>21.8</v>
+        <v>22.9</v>
       </c>
       <c r="I51" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J51" t="n">
-        <v>39.6</v>
+        <v>39.9</v>
       </c>
       <c r="K51" t="n">
-        <v>71</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="M51" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="N51" t="n">
-        <v>30.8</v>
+        <v>31.2</v>
       </c>
       <c r="O51" t="n">
-        <v>33.7</v>
+        <v>33.1</v>
       </c>
       <c r="Q51" t="n">
-        <v>20.7</v>
+        <v>21.6</v>
       </c>
       <c r="R51" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>20.7</v>
+        <v>21.6</v>
       </c>
       <c r="V51" t="n">
-        <v>13.1</v>
+        <v>12.9</v>
       </c>
       <c r="W51" t="n">
-        <v>25.5</v>
+        <v>28.3</v>
       </c>
       <c r="X51" t="n">
-        <v>19.3</v>
+        <v>20.6</v>
       </c>
       <c r="Y51" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z51" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AA51" t="n">
-        <v>15.5</v>
+        <v>17.9</v>
       </c>
       <c r="AB51" t="n">
-        <v>-1</v>
+        <v>-0.8</v>
       </c>
       <c r="AC51" t="n">
-        <v>6.4</v>
+        <v>8.1</v>
       </c>
       <c r="AD51" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="AF51" t="n">
-        <v>233.48</v>
+        <v>235.13</v>
       </c>
       <c r="AG51" t="n">
-        <v>-4.86</v>
+        <v>1.66</v>
       </c>
       <c r="AH51" t="n">
         <v>215</v>
@@ -5487,10 +5487,10 @@
         <v>235</v>
       </c>
       <c r="AK51" t="n">
-        <v>136.6</v>
+        <v>135.66</v>
       </c>
       <c r="AL51" t="n">
-        <v>2.01</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AM51" t="n">
         <v>110</v>
@@ -5499,57 +5499,57 @@
         <v>142</v>
       </c>
       <c r="AP51" t="n">
-        <v>86.25</v>
+        <v>88.27</v>
       </c>
       <c r="AS51" t="n">
-        <v>17.13</v>
+        <v>17.6</v>
       </c>
       <c r="BL51" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B52" t="n">
-        <v>143.4</v>
+        <v>144.9</v>
       </c>
       <c r="C52" t="n">
-        <v>50.9</v>
+        <v>53</v>
       </c>
       <c r="D52" t="n">
-        <v>35.7</v>
+        <v>35.6</v>
       </c>
       <c r="E52" t="n">
-        <v>26.2</v>
+        <v>26</v>
       </c>
       <c r="F52" t="n">
-        <v>4.3</v>
+        <v>2.8</v>
       </c>
       <c r="H52" t="n">
-        <v>22.9</v>
+        <v>24</v>
       </c>
       <c r="I52" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J52" t="n">
-        <v>39.9</v>
+        <v>40.3</v>
       </c>
       <c r="K52" t="n">
-        <v>72.59999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="M52" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="N52" t="n">
-        <v>31.2</v>
+        <v>31.6</v>
       </c>
       <c r="O52" t="n">
-        <v>33.1</v>
+        <v>33.6</v>
       </c>
       <c r="Q52" t="n">
-        <v>21.6</v>
+        <v>21</v>
       </c>
       <c r="R52" t="n">
         <v>0</v>
@@ -5558,40 +5558,40 @@
         <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>21.6</v>
+        <v>21</v>
       </c>
       <c r="V52" t="n">
-        <v>12.9</v>
+        <v>14.4</v>
       </c>
       <c r="W52" t="n">
-        <v>28.3</v>
+        <v>27.7</v>
       </c>
       <c r="X52" t="n">
-        <v>20.6</v>
+        <v>21.1</v>
       </c>
       <c r="Y52" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z52" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AA52" t="n">
-        <v>17.9</v>
+        <v>16.3</v>
       </c>
       <c r="AB52" t="n">
-        <v>-0.8</v>
+        <v>-1.1</v>
       </c>
       <c r="AC52" t="n">
-        <v>8.1</v>
+        <v>6.6</v>
       </c>
       <c r="AD52" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="AF52" t="n">
-        <v>235.13</v>
+        <v>234.87</v>
       </c>
       <c r="AG52" t="n">
-        <v>1.66</v>
+        <v>-0.26</v>
       </c>
       <c r="AH52" t="n">
         <v>215</v>
@@ -5600,10 +5600,10 @@
         <v>235</v>
       </c>
       <c r="AK52" t="n">
-        <v>135.66</v>
+        <v>136.33</v>
       </c>
       <c r="AL52" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="AM52" t="n">
         <v>110</v>
@@ -5612,99 +5612,60 @@
         <v>142</v>
       </c>
       <c r="AP52" t="n">
-        <v>88.27</v>
+        <v>87.09</v>
       </c>
       <c r="AS52" t="n">
-        <v>17.6</v>
+        <v>17.31</v>
       </c>
       <c r="BL52" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B53" t="n">
-        <v>144.9</v>
-      </c>
-      <c r="C53" t="n">
-        <v>53</v>
+        <v>132.2</v>
       </c>
       <c r="D53" t="n">
         <v>35.6</v>
       </c>
-      <c r="E53" t="n">
-        <v>26</v>
-      </c>
       <c r="F53" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="H53" t="n">
-        <v>24</v>
-      </c>
-      <c r="I53" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="J53" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="K53" t="n">
-        <v>73.7</v>
-      </c>
-      <c r="M53" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="N53" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="O53" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>21</v>
-      </c>
-      <c r="R53" t="n">
-        <v>0</v>
-      </c>
-      <c r="S53" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="V53" t="n">
-        <v>14.4</v>
+        <v>11.6</v>
       </c>
       <c r="W53" t="n">
-        <v>27.7</v>
+        <v>23.2</v>
       </c>
       <c r="X53" t="n">
-        <v>21.1</v>
+        <v>17.4</v>
       </c>
       <c r="Y53" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z53" t="n">
         <v>19</v>
       </c>
       <c r="AA53" t="n">
-        <v>16.3</v>
+        <v>13</v>
       </c>
       <c r="AB53" t="n">
-        <v>-1.1</v>
+        <v>0.9</v>
       </c>
       <c r="AC53" t="n">
-        <v>6.6</v>
+        <v>7.5</v>
       </c>
       <c r="AD53" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="AF53" t="n">
-        <v>234.87</v>
+        <v>234.78</v>
       </c>
       <c r="AG53" t="n">
-        <v>-0.26</v>
+        <v>-0.09</v>
       </c>
       <c r="AH53" t="n">
         <v>215</v>
@@ -5712,73 +5673,61 @@
       <c r="AI53" t="n">
         <v>235</v>
       </c>
-      <c r="AK53" t="n">
-        <v>136.33</v>
-      </c>
-      <c r="AL53" t="n">
-        <v>0.67</v>
-      </c>
       <c r="AM53" t="n">
         <v>110</v>
       </c>
       <c r="AN53" t="n">
         <v>142</v>
       </c>
-      <c r="AP53" t="n">
-        <v>87.09</v>
-      </c>
-      <c r="AS53" t="n">
-        <v>17.31</v>
-      </c>
       <c r="BL53" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B54" t="n">
-        <v>132.2</v>
+        <v>137.1</v>
       </c>
       <c r="D54" t="n">
-        <v>35.6</v>
+        <v>35.1</v>
       </c>
       <c r="F54" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="V54" t="n">
-        <v>11.6</v>
+        <v>11</v>
       </c>
       <c r="W54" t="n">
-        <v>23.2</v>
+        <v>22</v>
       </c>
       <c r="X54" t="n">
-        <v>17.4</v>
+        <v>16.5</v>
       </c>
       <c r="Y54" t="n">
         <v>7</v>
       </c>
       <c r="Z54" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AA54" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AB54" t="n">
-        <v>0.9</v>
+        <v>-5.3</v>
       </c>
       <c r="AC54" t="n">
-        <v>7.5</v>
+        <v>6.1</v>
       </c>
       <c r="AD54" t="n">
-        <v>4.2</v>
+        <v>0.4</v>
       </c>
       <c r="AF54" t="n">
-        <v>234.78</v>
+        <v>229.75</v>
       </c>
       <c r="AG54" t="n">
-        <v>-0.09</v>
+        <v>-5.03</v>
       </c>
       <c r="AH54" t="n">
         <v>215</v>
@@ -5793,54 +5742,93 @@
         <v>142</v>
       </c>
       <c r="BL54" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B55" t="n">
-        <v>137.1</v>
+        <v>166.2</v>
+      </c>
+      <c r="C55" t="n">
+        <v>72.40000000000001</v>
       </c>
       <c r="D55" t="n">
-        <v>35.1</v>
+        <v>32.7</v>
+      </c>
+      <c r="E55" t="n">
+        <v>28.1</v>
       </c>
       <c r="F55" t="n">
         <v>3.3</v>
       </c>
+      <c r="H55" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="I55" t="n">
+        <v>9</v>
+      </c>
+      <c r="J55" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="K55" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="M55" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="N55" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="O55" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="R55" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>23.7</v>
+      </c>
       <c r="V55" t="n">
-        <v>11</v>
+        <v>7.9</v>
       </c>
       <c r="W55" t="n">
-        <v>22</v>
+        <v>15.6</v>
       </c>
       <c r="X55" t="n">
-        <v>16.5</v>
+        <v>11.8</v>
       </c>
       <c r="Y55" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z55" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AA55" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AB55" t="n">
-        <v>-5.3</v>
+        <v>-3.5</v>
       </c>
       <c r="AC55" t="n">
-        <v>6.1</v>
+        <v>8.4</v>
       </c>
       <c r="AD55" t="n">
-        <v>0.4</v>
+        <v>2.5</v>
       </c>
       <c r="AF55" t="n">
-        <v>229.75</v>
+        <v>222.86</v>
       </c>
       <c r="AG55" t="n">
-        <v>-5.03</v>
+        <v>-6.9</v>
       </c>
       <c r="AH55" t="n">
         <v>215</v>
@@ -5848,82 +5836,94 @@
       <c r="AI55" t="n">
         <v>235</v>
       </c>
+      <c r="AK55" t="n">
+        <v>135.42</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>-0.91</v>
+      </c>
       <c r="AM55" t="n">
         <v>110</v>
       </c>
       <c r="AN55" t="n">
         <v>142</v>
       </c>
+      <c r="AP55" t="n">
+        <v>81.98</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>15.01</v>
+      </c>
       <c r="BL55" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B56" t="n">
-        <v>166.2</v>
+        <v>166.3</v>
       </c>
       <c r="C56" t="n">
-        <v>72.40000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="D56" t="n">
-        <v>32.7</v>
+        <v>32.8</v>
       </c>
       <c r="E56" t="n">
-        <v>28.1</v>
+        <v>28.8</v>
       </c>
       <c r="F56" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="H56" t="n">
         <v>23.4</v>
       </c>
       <c r="I56" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J56" t="n">
-        <v>42.1</v>
+        <v>41.2</v>
       </c>
       <c r="K56" t="n">
-        <v>74.5</v>
+        <v>73.8</v>
       </c>
       <c r="M56" t="n">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="N56" t="n">
-        <v>33.7</v>
+        <v>35.4</v>
       </c>
       <c r="O56" t="n">
-        <v>39.3</v>
+        <v>42.6</v>
       </c>
       <c r="Q56" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="R56" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="Y56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Z56" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AA56" t="n">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AF56" t="n">
-        <v>222.86</v>
+        <v>218.37</v>
       </c>
       <c r="AG56" t="n">
-        <v>-6.9</v>
+        <v>-4.49</v>
       </c>
       <c r="AH56" t="n">
         <v>215</v>
@@ -5932,10 +5932,10 @@
         <v>235</v>
       </c>
       <c r="AK56" t="n">
-        <v>135.42</v>
+        <v>131.24</v>
       </c>
       <c r="AL56" t="n">
-        <v>-0.91</v>
+        <v>-4.18</v>
       </c>
       <c r="AM56" t="n">
         <v>110</v>
@@ -5944,81 +5944,81 @@
         <v>142</v>
       </c>
       <c r="AP56" t="n">
-        <v>81.98</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="AS56" t="n">
-        <v>15.01</v>
+        <v>12.97</v>
       </c>
       <c r="BL56" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B57" t="n">
-        <v>166.3</v>
+        <v>154.1</v>
       </c>
       <c r="C57" t="n">
-        <v>74.90000000000001</v>
+        <v>65</v>
       </c>
       <c r="D57" t="n">
-        <v>32.8</v>
+        <v>32</v>
       </c>
       <c r="E57" t="n">
-        <v>28.8</v>
+        <v>25.2</v>
       </c>
       <c r="F57" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="H57" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="I57" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="J57" t="n">
-        <v>41.2</v>
+        <v>38.5</v>
       </c>
       <c r="K57" t="n">
-        <v>73.8</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="M57" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="N57" t="n">
-        <v>35.4</v>
+        <v>32.3</v>
       </c>
       <c r="O57" t="n">
-        <v>42.6</v>
+        <v>40.3</v>
       </c>
       <c r="Q57" t="n">
-        <v>23.9</v>
+        <v>21.7</v>
       </c>
       <c r="R57" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T57" t="n">
-        <v>23.9</v>
+        <v>21.7</v>
       </c>
       <c r="Y57" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Z57" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AA57" t="n">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="AF57" t="n">
-        <v>218.37</v>
+        <v>218.04</v>
       </c>
       <c r="AG57" t="n">
-        <v>-4.49</v>
+        <v>-0.33</v>
       </c>
       <c r="AH57" t="n">
         <v>215</v>
@@ -6027,10 +6027,10 @@
         <v>235</v>
       </c>
       <c r="AK57" t="n">
-        <v>131.24</v>
+        <v>129.21</v>
       </c>
       <c r="AL57" t="n">
-        <v>-4.18</v>
+        <v>-2.03</v>
       </c>
       <c r="AM57" t="n">
         <v>110</v>
@@ -6039,81 +6039,81 @@
         <v>142</v>
       </c>
       <c r="AP57" t="n">
-        <v>79.98999999999999</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="AS57" t="n">
-        <v>12.97</v>
+        <v>15.23</v>
       </c>
       <c r="BL57" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B58" t="n">
-        <v>154.1</v>
+        <v>148.8</v>
       </c>
       <c r="C58" t="n">
-        <v>65</v>
+        <v>57.6</v>
       </c>
       <c r="D58" t="n">
-        <v>32</v>
+        <v>32.7</v>
       </c>
       <c r="E58" t="n">
-        <v>25.2</v>
+        <v>26.3</v>
       </c>
       <c r="F58" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="H58" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="I58" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="J58" t="n">
-        <v>38.5</v>
+        <v>41.6</v>
       </c>
       <c r="K58" t="n">
-        <v>70.90000000000001</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="M58" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="N58" t="n">
-        <v>32.3</v>
+        <v>35</v>
       </c>
       <c r="O58" t="n">
-        <v>40.3</v>
+        <v>42.4</v>
       </c>
       <c r="Q58" t="n">
         <v>21.7</v>
       </c>
       <c r="R58" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="S58" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="T58" t="n">
         <v>21.7</v>
       </c>
       <c r="Y58" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z58" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA58" t="n">
-        <v>14.5</v>
+        <v>15.6</v>
       </c>
       <c r="AF58" t="n">
-        <v>218.04</v>
+        <v>220.84</v>
       </c>
       <c r="AG58" t="n">
-        <v>-0.33</v>
+        <v>2.8</v>
       </c>
       <c r="AH58" t="n">
         <v>215</v>
@@ -6122,10 +6122,10 @@
         <v>235</v>
       </c>
       <c r="AK58" t="n">
-        <v>129.21</v>
+        <v>129.07</v>
       </c>
       <c r="AL58" t="n">
-        <v>-2.03</v>
+        <v>-0.14</v>
       </c>
       <c r="AM58" t="n">
         <v>110</v>
@@ -6134,81 +6134,81 @@
         <v>142</v>
       </c>
       <c r="AP58" t="n">
-        <v>82.90000000000001</v>
+        <v>85.52</v>
       </c>
       <c r="AS58" t="n">
-        <v>15.23</v>
+        <v>15.82</v>
       </c>
       <c r="BL58" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B59" t="n">
-        <v>148.8</v>
+        <v>146.8</v>
       </c>
       <c r="C59" t="n">
-        <v>57.6</v>
+        <v>52.8</v>
       </c>
       <c r="D59" t="n">
-        <v>32.7</v>
+        <v>33.6</v>
       </c>
       <c r="E59" t="n">
-        <v>26.3</v>
+        <v>28.9</v>
       </c>
       <c r="F59" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="H59" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="I59" t="n">
-        <v>8.9</v>
+        <v>9.1</v>
       </c>
       <c r="J59" t="n">
-        <v>41.6</v>
+        <v>40.8</v>
       </c>
       <c r="K59" t="n">
-        <v>74.09999999999999</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="M59" t="n">
-        <v>7.4</v>
+        <v>5.6</v>
       </c>
       <c r="N59" t="n">
-        <v>35</v>
+        <v>33.1</v>
       </c>
       <c r="O59" t="n">
-        <v>42.4</v>
+        <v>38.7</v>
       </c>
       <c r="Q59" t="n">
-        <v>21.7</v>
+        <v>22</v>
       </c>
       <c r="R59" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>21.7</v>
+        <v>22</v>
       </c>
       <c r="Y59" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z59" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA59" t="n">
-        <v>15.6</v>
+        <v>16.1</v>
       </c>
       <c r="AF59" t="n">
-        <v>220.84</v>
+        <v>225.87</v>
       </c>
       <c r="AG59" t="n">
-        <v>2.8</v>
+        <v>5.03</v>
       </c>
       <c r="AH59" t="n">
         <v>215</v>
@@ -6217,10 +6217,10 @@
         <v>235</v>
       </c>
       <c r="AK59" t="n">
-        <v>129.07</v>
+        <v>130.73</v>
       </c>
       <c r="AL59" t="n">
-        <v>-0.14</v>
+        <v>1.66</v>
       </c>
       <c r="AM59" t="n">
         <v>110</v>
@@ -6229,81 +6229,36 @@
         <v>142</v>
       </c>
       <c r="AP59" t="n">
-        <v>85.52</v>
+        <v>88.2</v>
       </c>
       <c r="AS59" t="n">
-        <v>15.82</v>
+        <v>15.76</v>
       </c>
       <c r="BL59" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B60" t="n">
-        <v>146.8</v>
-      </c>
-      <c r="C60" t="n">
-        <v>52.8</v>
+        <v>133.9</v>
       </c>
       <c r="D60" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="E60" t="n">
-        <v>28.9</v>
+        <v>34.7</v>
       </c>
       <c r="F60" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="H60" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="I60" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="J60" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="K60" t="n">
-        <v>73.59999999999999</v>
-      </c>
-      <c r="M60" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="N60" t="n">
-        <v>33.1</v>
-      </c>
-      <c r="O60" t="n">
-        <v>38.7</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>22</v>
-      </c>
-      <c r="R60" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="S60" t="n">
-        <v>0</v>
-      </c>
-      <c r="T60" t="n">
-        <v>22</v>
+        <v>3.3</v>
       </c>
       <c r="Y60" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z60" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AA60" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="AF60" t="n">
-        <v>225.87</v>
-      </c>
-      <c r="AG60" t="n">
-        <v>5.03</v>
+        <v>15</v>
       </c>
       <c r="AH60" t="n">
         <v>215</v>
@@ -6311,49 +6266,37 @@
       <c r="AI60" t="n">
         <v>235</v>
       </c>
-      <c r="AK60" t="n">
-        <v>130.73</v>
-      </c>
-      <c r="AL60" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AM60" t="n">
         <v>110</v>
       </c>
       <c r="AN60" t="n">
         <v>142</v>
       </c>
-      <c r="AP60" t="n">
-        <v>88.2</v>
-      </c>
-      <c r="AS60" t="n">
-        <v>15.76</v>
-      </c>
       <c r="BL60" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B61" t="n">
-        <v>133.9</v>
+        <v>137.5</v>
       </c>
       <c r="D61" t="n">
-        <v>34.7</v>
+        <v>32.8</v>
       </c>
       <c r="F61" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="Y61" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z61" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="AA61" t="n">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="AH61" t="n">
         <v>215</v>
@@ -6368,30 +6311,30 @@
         <v>142</v>
       </c>
       <c r="BL61" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B62" t="n">
-        <v>137.5</v>
+        <v>141</v>
       </c>
       <c r="D62" t="n">
-        <v>32.8</v>
+        <v>31.9</v>
       </c>
       <c r="F62" t="n">
         <v>2.3</v>
       </c>
       <c r="Y62" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="Z62" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA62" t="n">
-        <v>10.5</v>
+        <v>7.5</v>
       </c>
       <c r="AH62" t="n">
         <v>215</v>
@@ -6406,7 +6349,7 @@
         <v>142</v>
       </c>
       <c r="BL62" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -628,88 +628,70 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B2" t="n">
-        <v>168.1</v>
+        <v>158.9</v>
       </c>
       <c r="C2" t="n">
-        <v>69.7</v>
+        <v>58.8</v>
       </c>
       <c r="D2" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="E2" t="n">
         <v>30.4</v>
       </c>
-      <c r="E2" t="n">
-        <v>33.9</v>
-      </c>
       <c r="F2" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="H2" t="n">
-        <v>24.1</v>
+        <v>23.7</v>
       </c>
       <c r="I2" t="n">
-        <v>10.6</v>
+        <v>11.2</v>
       </c>
       <c r="J2" t="n">
-        <v>41.2</v>
+        <v>41</v>
       </c>
       <c r="K2" t="n">
         <v>75.90000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="N2" t="n">
-        <v>38.1</v>
+        <v>37.8</v>
       </c>
       <c r="O2" t="n">
-        <v>43.1</v>
+        <v>41.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>22.6</v>
+        <v>21.5</v>
       </c>
       <c r="R2" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="S2" t="n">
-        <v>17.6</v>
+        <v>15</v>
       </c>
       <c r="T2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="V2" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="W2" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="X2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="Y2" t="n">
         <v>17</v>
       </c>
-      <c r="Y2" t="n">
-        <v>11</v>
-      </c>
       <c r="Z2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AA2" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>5.7</v>
+        <v>19.3</v>
       </c>
       <c r="AF2" t="n">
-        <v>224.93</v>
+        <v>232.31</v>
       </c>
       <c r="AG2" t="n">
-        <v>5.29</v>
+        <v>9.67</v>
       </c>
       <c r="AH2" t="n">
         <v>215</v>
@@ -718,10 +700,10 @@
         <v>235</v>
       </c>
       <c r="AK2" t="n">
-        <v>129.28</v>
+        <v>134.44</v>
       </c>
       <c r="AL2" t="n">
-        <v>3.25</v>
+        <v>5.16</v>
       </c>
       <c r="AM2" t="n">
         <v>110</v>
@@ -730,99 +712,48 @@
         <v>142</v>
       </c>
       <c r="AP2" t="n">
-        <v>87.43000000000001</v>
+        <v>91.73999999999999</v>
       </c>
       <c r="AS2" t="n">
-        <v>15.25</v>
+        <v>17.07</v>
       </c>
       <c r="BL2" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B3" t="n">
-        <v>158.9</v>
-      </c>
-      <c r="C3" t="n">
-        <v>58.8</v>
+        <v>136.7</v>
       </c>
       <c r="D3" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="E3" t="n">
-        <v>30.4</v>
+        <v>30.7</v>
       </c>
       <c r="F3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="H3" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="I3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="J3" t="n">
-        <v>41</v>
+        <v>7.5</v>
       </c>
       <c r="K3" t="n">
-        <v>75.90000000000001</v>
-      </c>
-      <c r="M3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N3" t="n">
-        <v>37.8</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="S3" t="n">
-        <v>15</v>
-      </c>
-      <c r="T3" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="V3" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="W3" t="n">
-        <v>26</v>
-      </c>
-      <c r="X3" t="n">
-        <v>18.1</v>
+        <v>39.2</v>
       </c>
       <c r="Y3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Z3" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AA3" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>4.5</v>
+        <v>20.5</v>
       </c>
       <c r="AF3" t="n">
-        <v>232.31</v>
+        <v>235.4</v>
       </c>
       <c r="AG3" t="n">
-        <v>9.67</v>
+        <v>3.09</v>
       </c>
       <c r="AH3" t="n">
         <v>215</v>
@@ -831,10 +762,10 @@
         <v>235</v>
       </c>
       <c r="AK3" t="n">
-        <v>134.44</v>
+        <v>137.5</v>
       </c>
       <c r="AL3" t="n">
-        <v>5.16</v>
+        <v>3.06</v>
       </c>
       <c r="AM3" t="n">
         <v>110</v>
@@ -842,67 +773,43 @@
       <c r="AN3" t="n">
         <v>142</v>
       </c>
-      <c r="AP3" t="n">
-        <v>91.73999999999999</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>17.07</v>
-      </c>
       <c r="BL3" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="B4" t="n">
-        <v>136.7</v>
+        <v>138.5</v>
       </c>
       <c r="D4" t="n">
-        <v>30.7</v>
+        <v>31.7</v>
       </c>
       <c r="F4" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="K4" t="n">
-        <v>92.59999999999999</v>
+        <v>91</v>
       </c>
       <c r="O4" t="n">
-        <v>39.2</v>
-      </c>
-      <c r="V4" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="W4" t="n">
-        <v>36.1</v>
-      </c>
-      <c r="X4" t="n">
-        <v>26.6</v>
+        <v>37.8</v>
       </c>
       <c r="Y4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="Z4" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AA4" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>4.7</v>
+        <v>15.5</v>
       </c>
       <c r="AF4" t="n">
-        <v>235.4</v>
+        <v>231.99</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.09</v>
+        <v>-3.41</v>
       </c>
       <c r="AH4" t="n">
         <v>215</v>
@@ -911,10 +818,10 @@
         <v>235</v>
       </c>
       <c r="AK4" t="n">
-        <v>137.5</v>
+        <v>136.12</v>
       </c>
       <c r="AL4" t="n">
-        <v>3.06</v>
+        <v>-1.38</v>
       </c>
       <c r="AM4" t="n">
         <v>110</v>
@@ -923,60 +830,75 @@
         <v>142</v>
       </c>
       <c r="BL4" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B5" t="n">
-        <v>138.5</v>
+        <v>161.1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>67</v>
       </c>
       <c r="D5" t="n">
-        <v>31.7</v>
+        <v>31.9</v>
+      </c>
+      <c r="E5" t="n">
+        <v>31.5</v>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>7.7</v>
+      </c>
+      <c r="H5" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J5" t="n">
+        <v>41.1</v>
       </c>
       <c r="K5" t="n">
-        <v>91</v>
+        <v>75.59999999999999</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="N5" t="n">
+        <v>35</v>
       </c>
       <c r="O5" t="n">
-        <v>37.8</v>
-      </c>
-      <c r="V5" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="W5" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="X5" t="n">
-        <v>17.9</v>
+        <v>37.2</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3</v>
+      </c>
+      <c r="T5" t="n">
+        <v>20.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="Z5" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AA5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.7</v>
+        <v>11.1</v>
       </c>
       <c r="AF5" t="n">
-        <v>231.99</v>
+        <v>225.51</v>
       </c>
       <c r="AG5" t="n">
-        <v>-3.41</v>
+        <v>-6.48</v>
       </c>
       <c r="AH5" t="n">
         <v>215</v>
@@ -985,10 +907,10 @@
         <v>235</v>
       </c>
       <c r="AK5" t="n">
-        <v>136.12</v>
+        <v>133.83</v>
       </c>
       <c r="AL5" t="n">
-        <v>-1.38</v>
+        <v>-2.29</v>
       </c>
       <c r="AM5" t="n">
         <v>110</v>
@@ -996,94 +918,82 @@
       <c r="AN5" t="n">
         <v>142</v>
       </c>
+      <c r="AP5" t="n">
+        <v>82.93000000000001</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>15.73</v>
+      </c>
       <c r="BL5" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B6" t="n">
-        <v>161.1</v>
+        <v>176.4</v>
       </c>
       <c r="C6" t="n">
-        <v>67</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>31.9</v>
+        <v>32.7</v>
       </c>
       <c r="E6" t="n">
-        <v>31.5</v>
+        <v>35</v>
       </c>
       <c r="F6" t="n">
-        <v>7.7</v>
+        <v>6.8</v>
       </c>
       <c r="H6" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="I6" t="n">
         <v>11.4</v>
       </c>
       <c r="J6" t="n">
-        <v>41.1</v>
+        <v>41.5</v>
       </c>
       <c r="K6" t="n">
-        <v>75.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="M6" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="N6" t="n">
-        <v>35</v>
+        <v>36.4</v>
       </c>
       <c r="O6" t="n">
-        <v>37.2</v>
+        <v>39.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>20.5</v>
+        <v>22.3</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="T6" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="V6" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="W6" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="X6" t="n">
-        <v>16.7</v>
+        <v>22.3</v>
       </c>
       <c r="Y6" t="n">
         <v>9</v>
       </c>
       <c r="Z6" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA6" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>-3.8</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>-0.3</v>
+        <v>11.6</v>
       </c>
       <c r="AF6" t="n">
-        <v>225.51</v>
+        <v>220.92</v>
       </c>
       <c r="AG6" t="n">
-        <v>-6.48</v>
+        <v>-4.59</v>
       </c>
       <c r="AH6" t="n">
         <v>215</v>
@@ -1092,10 +1002,10 @@
         <v>235</v>
       </c>
       <c r="AK6" t="n">
-        <v>133.83</v>
+        <v>131.85</v>
       </c>
       <c r="AL6" t="n">
-        <v>-2.29</v>
+        <v>-1.98</v>
       </c>
       <c r="AM6" t="n">
         <v>110</v>
@@ -1104,99 +1014,81 @@
         <v>142</v>
       </c>
       <c r="AP6" t="n">
-        <v>82.93000000000001</v>
+        <v>79.75</v>
       </c>
       <c r="AS6" t="n">
-        <v>15.73</v>
+        <v>15.49</v>
       </c>
       <c r="BL6" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B7" t="n">
-        <v>176.4</v>
+        <v>181</v>
       </c>
       <c r="C7" t="n">
-        <v>77.09999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="D7" t="n">
-        <v>32.7</v>
+        <v>33</v>
       </c>
       <c r="E7" t="n">
-        <v>35</v>
+        <v>35.1</v>
       </c>
       <c r="F7" t="n">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="H7" t="n">
-        <v>23.2</v>
+        <v>22.8</v>
       </c>
       <c r="I7" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="K7" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N7" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="O7" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="T7" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA7" t="n">
         <v>11.4</v>
-      </c>
-      <c r="J7" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="K7" t="n">
-        <v>76</v>
-      </c>
-      <c r="M7" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N7" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="O7" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>14</v>
-      </c>
-      <c r="T7" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="V7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="W7" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="X7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>-5.6</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>-1.3</v>
       </c>
       <c r="AF7" t="n">
         <v>220.92</v>
       </c>
       <c r="AG7" t="n">
-        <v>-4.59</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
         <v>215</v>
@@ -1205,10 +1097,10 @@
         <v>235</v>
       </c>
       <c r="AK7" t="n">
-        <v>131.85</v>
+        <v>130.06</v>
       </c>
       <c r="AL7" t="n">
-        <v>-1.98</v>
+        <v>-1.79</v>
       </c>
       <c r="AM7" t="n">
         <v>110</v>
@@ -1217,99 +1109,81 @@
         <v>142</v>
       </c>
       <c r="AP7" t="n">
-        <v>79.75</v>
+        <v>79.94</v>
       </c>
       <c r="AS7" t="n">
-        <v>15.49</v>
+        <v>14.93</v>
       </c>
       <c r="BL7" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B8" t="n">
-        <v>181</v>
+        <v>179.6</v>
       </c>
       <c r="C8" t="n">
-        <v>80.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>33</v>
+        <v>30.3</v>
       </c>
       <c r="E8" t="n">
-        <v>35.1</v>
+        <v>31.1</v>
       </c>
       <c r="F8" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="H8" t="n">
-        <v>22.8</v>
+        <v>21.5</v>
       </c>
       <c r="I8" t="n">
-        <v>11.2</v>
+        <v>10.8</v>
       </c>
       <c r="J8" t="n">
-        <v>41.9</v>
+        <v>42.3</v>
       </c>
       <c r="K8" t="n">
-        <v>75.90000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9</v>
+        <v>4.3</v>
       </c>
       <c r="N8" t="n">
-        <v>36.9</v>
+        <v>37.1</v>
       </c>
       <c r="O8" t="n">
-        <v>39.8</v>
+        <v>41.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="S8" t="n">
-        <v>20.5</v>
+        <v>21.2</v>
       </c>
       <c r="T8" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="V8" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="W8" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z8" t="n">
         <v>13</v>
       </c>
-      <c r="X8" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>14</v>
-      </c>
       <c r="AA8" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>-6.1</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>-0.9</v>
+        <v>11.1</v>
       </c>
       <c r="AF8" t="n">
-        <v>220.92</v>
+        <v>216.02</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AH8" t="n">
         <v>215</v>
@@ -1318,10 +1192,10 @@
         <v>235</v>
       </c>
       <c r="AK8" t="n">
-        <v>130.06</v>
+        <v>127.85</v>
       </c>
       <c r="AL8" t="n">
-        <v>-1.79</v>
+        <v>-2.21</v>
       </c>
       <c r="AM8" t="n">
         <v>110</v>
@@ -1330,99 +1204,81 @@
         <v>142</v>
       </c>
       <c r="AP8" t="n">
-        <v>79.94</v>
+        <v>82.2</v>
       </c>
       <c r="AS8" t="n">
-        <v>14.93</v>
+        <v>15.16</v>
       </c>
       <c r="BL8" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B9" t="n">
-        <v>179.6</v>
+        <v>170.4</v>
       </c>
       <c r="C9" t="n">
-        <v>81.90000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="D9" t="n">
-        <v>30.3</v>
+        <v>29.8</v>
       </c>
       <c r="E9" t="n">
-        <v>31.1</v>
+        <v>29.7</v>
       </c>
       <c r="F9" t="n">
-        <v>6.8</v>
+        <v>6.3</v>
       </c>
       <c r="H9" t="n">
-        <v>21.5</v>
+        <v>22.5</v>
       </c>
       <c r="I9" t="n">
-        <v>10.8</v>
+        <v>11.2</v>
       </c>
       <c r="J9" t="n">
-        <v>42.3</v>
+        <v>41.4</v>
       </c>
       <c r="K9" t="n">
-        <v>74.59999999999999</v>
+        <v>75</v>
       </c>
       <c r="M9" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="N9" t="n">
-        <v>37.1</v>
+        <v>36.6</v>
       </c>
       <c r="O9" t="n">
-        <v>41.4</v>
+        <v>41.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>22.6</v>
+        <v>23.3</v>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="S9" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="T9" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="V9" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="W9" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="X9" t="n">
-        <v>12.6</v>
+        <v>23.3</v>
       </c>
       <c r="Y9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z9" t="n">
         <v>13</v>
       </c>
       <c r="AA9" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>-3.4</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0.5</v>
+        <v>12.7</v>
       </c>
       <c r="AF9" t="n">
         <v>216.02</v>
       </c>
       <c r="AG9" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
         <v>215</v>
@@ -1431,10 +1287,10 @@
         <v>235</v>
       </c>
       <c r="AK9" t="n">
-        <v>127.85</v>
+        <v>128.54</v>
       </c>
       <c r="AL9" t="n">
-        <v>-2.21</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AM9" t="n">
         <v>110</v>
@@ -1443,99 +1299,48 @@
         <v>142</v>
       </c>
       <c r="AP9" t="n">
-        <v>82.2</v>
+        <v>84.73</v>
       </c>
       <c r="AS9" t="n">
-        <v>15.16</v>
+        <v>15.34</v>
       </c>
       <c r="BL9" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B10" t="n">
-        <v>170.4</v>
-      </c>
-      <c r="C10" t="n">
-        <v>78.5</v>
+        <v>156</v>
       </c>
       <c r="D10" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="E10" t="n">
-        <v>29.7</v>
+        <v>30.1</v>
       </c>
       <c r="F10" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="H10" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="I10" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="J10" t="n">
-        <v>41.4</v>
+        <v>6.8</v>
       </c>
       <c r="K10" t="n">
-        <v>75</v>
-      </c>
-      <c r="M10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="N10" t="n">
-        <v>36.6</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S10" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="T10" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="V10" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W10" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="X10" t="n">
-        <v>12.6</v>
+        <v>39.2</v>
       </c>
       <c r="Y10" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Z10" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA10" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>4.7</v>
+        <v>13.5</v>
       </c>
       <c r="AF10" t="n">
-        <v>216.02</v>
+        <v>224.53</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH10" t="n">
         <v>215</v>
@@ -1544,10 +1349,10 @@
         <v>235</v>
       </c>
       <c r="AK10" t="n">
-        <v>128.54</v>
+        <v>130.92</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.6899999999999999</v>
+        <v>2.38</v>
       </c>
       <c r="AM10" t="n">
         <v>110</v>
@@ -1555,67 +1360,43 @@
       <c r="AN10" t="n">
         <v>142</v>
       </c>
-      <c r="AP10" t="n">
-        <v>84.73</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>15.34</v>
-      </c>
       <c r="BL10" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B11" t="n">
-        <v>156</v>
+        <v>147.8</v>
       </c>
       <c r="D11" t="n">
-        <v>30.1</v>
+        <v>32</v>
       </c>
       <c r="F11" t="n">
         <v>6.8</v>
       </c>
       <c r="K11" t="n">
-        <v>95.90000000000001</v>
+        <v>96.5</v>
       </c>
       <c r="O11" t="n">
-        <v>39.2</v>
-      </c>
-      <c r="V11" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W11" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="X11" t="n">
-        <v>14</v>
+        <v>39.3</v>
       </c>
       <c r="Y11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA11" t="n">
         <v>13.5</v>
       </c>
-      <c r="AB11" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AF11" t="n">
-        <v>224.53</v>
+        <v>230.27</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.32</v>
+        <v>5.74</v>
       </c>
       <c r="AH11" t="n">
         <v>215</v>
@@ -1624,10 +1405,10 @@
         <v>235</v>
       </c>
       <c r="AK11" t="n">
-        <v>130.92</v>
+        <v>132.76</v>
       </c>
       <c r="AL11" t="n">
-        <v>2.38</v>
+        <v>1.84</v>
       </c>
       <c r="AM11" t="n">
         <v>110</v>
@@ -1636,60 +1417,75 @@
         <v>142</v>
       </c>
       <c r="BL11" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="B12" t="n">
-        <v>147.8</v>
+        <v>149.1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>60</v>
       </c>
       <c r="D12" t="n">
-        <v>32</v>
+        <v>29</v>
+      </c>
+      <c r="E12" t="n">
+        <v>25.9</v>
       </c>
       <c r="F12" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
+      </c>
+      <c r="H12" t="n">
+        <v>24</v>
+      </c>
+      <c r="I12" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="J12" t="n">
+        <v>38.8</v>
       </c>
       <c r="K12" t="n">
-        <v>96.5</v>
+        <v>74.5</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N12" t="n">
+        <v>36.7</v>
       </c>
       <c r="O12" t="n">
-        <v>39.3</v>
-      </c>
-      <c r="V12" t="n">
-        <v>8</v>
-      </c>
-      <c r="W12" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="X12" t="n">
-        <v>15.2</v>
+        <v>40.1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>7</v>
+      </c>
+      <c r="T12" t="n">
+        <v>21.7</v>
       </c>
       <c r="Y12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z12" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AA12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>2.1</v>
+        <v>15.7</v>
       </c>
       <c r="AF12" t="n">
-        <v>230.27</v>
+        <v>237.43</v>
       </c>
       <c r="AG12" t="n">
-        <v>5.74</v>
+        <v>7.16</v>
       </c>
       <c r="AH12" t="n">
         <v>215</v>
@@ -1698,10 +1494,10 @@
         <v>235</v>
       </c>
       <c r="AK12" t="n">
-        <v>132.76</v>
+        <v>134.95</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.84</v>
+        <v>2.19</v>
       </c>
       <c r="AM12" t="n">
         <v>110</v>
@@ -1709,94 +1505,49 @@
       <c r="AN12" t="n">
         <v>142</v>
       </c>
+      <c r="AP12" t="n">
+        <v>91.28</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>16.95</v>
+      </c>
       <c r="BL12" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="B13" t="n">
-        <v>149.1</v>
-      </c>
-      <c r="C13" t="n">
-        <v>60</v>
+        <v>143.9</v>
       </c>
       <c r="D13" t="n">
-        <v>29</v>
-      </c>
-      <c r="E13" t="n">
-        <v>25.9</v>
+        <v>32.9</v>
       </c>
       <c r="F13" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="H13" t="n">
-        <v>24</v>
-      </c>
-      <c r="I13" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="J13" t="n">
-        <v>38.8</v>
+        <v>6.8</v>
       </c>
       <c r="K13" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="M13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N13" t="n">
-        <v>36.7</v>
+        <v>96.2</v>
       </c>
       <c r="O13" t="n">
-        <v>40.1</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1</v>
-      </c>
-      <c r="S13" t="n">
-        <v>7</v>
-      </c>
-      <c r="T13" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="V13" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="W13" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="X13" t="n">
-        <v>17.4</v>
+        <v>37.9</v>
       </c>
       <c r="Y13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AA13" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>-2.4</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>-0.1</v>
+        <v>16</v>
       </c>
       <c r="AF13" t="n">
-        <v>237.43</v>
+        <v>236.14</v>
       </c>
       <c r="AG13" t="n">
-        <v>7.16</v>
+        <v>-1.29</v>
       </c>
       <c r="AH13" t="n">
         <v>215</v>
@@ -1805,10 +1556,10 @@
         <v>235</v>
       </c>
       <c r="AK13" t="n">
-        <v>134.95</v>
+        <v>136.28</v>
       </c>
       <c r="AL13" t="n">
-        <v>2.19</v>
+        <v>1.33</v>
       </c>
       <c r="AM13" t="n">
         <v>110</v>
@@ -1816,67 +1567,76 @@
       <c r="AN13" t="n">
         <v>142</v>
       </c>
-      <c r="AP13" t="n">
-        <v>91.28</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>16.95</v>
-      </c>
       <c r="BL13" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B14" t="n">
-        <v>143.9</v>
+        <v>166.4</v>
+      </c>
+      <c r="C14" t="n">
+        <v>63.7</v>
       </c>
       <c r="D14" t="n">
-        <v>32.9</v>
+        <v>34.5</v>
+      </c>
+      <c r="E14" t="n">
+        <v>36.4</v>
       </c>
       <c r="F14" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
+      </c>
+      <c r="H14" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="I14" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="J14" t="n">
+        <v>39.9</v>
       </c>
       <c r="K14" t="n">
-        <v>96.2</v>
+        <v>75.2</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>35.9</v>
       </c>
       <c r="O14" t="n">
-        <v>37.9</v>
-      </c>
-      <c r="V14" t="n">
-        <v>10</v>
-      </c>
-      <c r="W14" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="X14" t="n">
-        <v>17.8</v>
+        <v>39</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="S14" t="n">
+        <v>6</v>
+      </c>
+      <c r="T14" t="n">
+        <v>20.3</v>
       </c>
       <c r="Y14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z14" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AA14" t="n">
-        <v>16</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>-1.4</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0.9</v>
+        <v>14.4</v>
       </c>
       <c r="AF14" t="n">
-        <v>236.14</v>
+        <v>236.13</v>
       </c>
       <c r="AG14" t="n">
-        <v>-1.29</v>
+        <v>-0.01</v>
       </c>
       <c r="AH14" t="n">
         <v>215</v>
@@ -1885,10 +1645,10 @@
         <v>235</v>
       </c>
       <c r="AK14" t="n">
-        <v>136.28</v>
+        <v>134.54</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.33</v>
+        <v>-1.74</v>
       </c>
       <c r="AM14" t="n">
         <v>110</v>
@@ -1896,94 +1656,82 @@
       <c r="AN14" t="n">
         <v>142</v>
       </c>
+      <c r="AP14" t="n">
+        <v>82.27</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>16.28</v>
+      </c>
       <c r="BL14" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B15" t="n">
-        <v>166.4</v>
+        <v>172.9</v>
       </c>
       <c r="C15" t="n">
-        <v>63.7</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>34.5</v>
+        <v>34.9</v>
       </c>
       <c r="E15" t="n">
-        <v>36.4</v>
+        <v>35.2</v>
       </c>
       <c r="F15" t="n">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="H15" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="I15" t="n">
-        <v>11.6</v>
+        <v>11.3</v>
       </c>
       <c r="J15" t="n">
-        <v>39.9</v>
+        <v>41.7</v>
       </c>
       <c r="K15" t="n">
-        <v>75.2</v>
+        <v>76.7</v>
       </c>
       <c r="M15" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="N15" t="n">
-        <v>35.9</v>
+        <v>34.8</v>
       </c>
       <c r="O15" t="n">
-        <v>39</v>
+        <v>37.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>20.3</v>
+        <v>19</v>
       </c>
       <c r="R15" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T15" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="V15" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="W15" t="n">
-        <v>27</v>
-      </c>
-      <c r="X15" t="n">
-        <v>19.4</v>
+        <v>19</v>
       </c>
       <c r="Y15" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Z15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA15" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>-0.4</v>
+        <v>12.5</v>
       </c>
       <c r="AF15" t="n">
-        <v>236.13</v>
+        <v>218.6</v>
       </c>
       <c r="AG15" t="n">
-        <v>-0.01</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="AH15" t="n">
         <v>215</v>
@@ -1992,10 +1740,10 @@
         <v>235</v>
       </c>
       <c r="AK15" t="n">
-        <v>134.54</v>
+        <v>130.39</v>
       </c>
       <c r="AL15" t="n">
-        <v>-1.74</v>
+        <v>-4.15</v>
       </c>
       <c r="AM15" t="n">
         <v>110</v>
@@ -2004,99 +1752,81 @@
         <v>142</v>
       </c>
       <c r="AP15" t="n">
-        <v>82.27</v>
+        <v>78.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>16.28</v>
+        <v>15.79</v>
       </c>
       <c r="BL15" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B16" t="n">
-        <v>172.9</v>
+        <v>157.5</v>
       </c>
       <c r="C16" t="n">
-        <v>67.59999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="D16" t="n">
-        <v>34.9</v>
+        <v>33.2</v>
       </c>
       <c r="E16" t="n">
-        <v>35.2</v>
+        <v>27.7</v>
       </c>
       <c r="F16" t="n">
-        <v>7.3</v>
+        <v>3.6</v>
       </c>
       <c r="H16" t="n">
-        <v>23.6</v>
+        <v>23.4</v>
       </c>
       <c r="I16" t="n">
         <v>11.3</v>
       </c>
       <c r="J16" t="n">
-        <v>41.7</v>
+        <v>41.4</v>
       </c>
       <c r="K16" t="n">
-        <v>76.7</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="N16" t="n">
-        <v>34.8</v>
+        <v>34.9</v>
       </c>
       <c r="O16" t="n">
-        <v>37.2</v>
+        <v>37.4</v>
       </c>
       <c r="Q16" t="n">
-        <v>19</v>
+        <v>21.6</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T16" t="n">
-        <v>19</v>
-      </c>
-      <c r="V16" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="W16" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="X16" t="n">
-        <v>16.6</v>
+        <v>21.6</v>
       </c>
       <c r="Y16" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z16" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AA16" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>-4.9</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>-0.7</v>
+        <v>13.6</v>
       </c>
       <c r="AF16" t="n">
-        <v>218.6</v>
+        <v>218.84</v>
       </c>
       <c r="AG16" t="n">
-        <v>-9.380000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="AH16" t="n">
         <v>215</v>
@@ -2105,10 +1835,10 @@
         <v>235</v>
       </c>
       <c r="AK16" t="n">
-        <v>130.39</v>
+        <v>133.09</v>
       </c>
       <c r="AL16" t="n">
-        <v>-4.15</v>
+        <v>2.7</v>
       </c>
       <c r="AM16" t="n">
         <v>110</v>
@@ -2117,99 +1847,48 @@
         <v>142</v>
       </c>
       <c r="AP16" t="n">
-        <v>78.5</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="AS16" t="n">
-        <v>15.79</v>
+        <v>15.63</v>
       </c>
       <c r="BL16" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B17" t="n">
-        <v>157.5</v>
-      </c>
-      <c r="C17" t="n">
-        <v>68.5</v>
+        <v>137.6</v>
       </c>
       <c r="D17" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="E17" t="n">
-        <v>27.7</v>
+        <v>35</v>
       </c>
       <c r="F17" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H17" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="I17" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J17" t="n">
-        <v>41.4</v>
+        <v>6.5</v>
       </c>
       <c r="K17" t="n">
-        <v>76.09999999999999</v>
-      </c>
-      <c r="M17" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="N17" t="n">
-        <v>34.9</v>
+        <v>96.7</v>
       </c>
       <c r="O17" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>9</v>
-      </c>
-      <c r="T17" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="V17" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="W17" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="X17" t="n">
-        <v>19.1</v>
+        <v>35.1</v>
       </c>
       <c r="Y17" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Z17" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AA17" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.5</v>
+        <v>17.5</v>
       </c>
       <c r="AF17" t="n">
-        <v>218.84</v>
+        <v>221.78</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.25</v>
+        <v>2.94</v>
       </c>
       <c r="AH17" t="n">
         <v>215</v>
@@ -2218,10 +1897,10 @@
         <v>235</v>
       </c>
       <c r="AK17" t="n">
-        <v>133.09</v>
+        <v>138.76</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.7</v>
+        <v>5.67</v>
       </c>
       <c r="AM17" t="n">
         <v>110</v>
@@ -2229,67 +1908,43 @@
       <c r="AN17" t="n">
         <v>142</v>
       </c>
-      <c r="AP17" t="n">
-        <v>83.09999999999999</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>15.63</v>
-      </c>
       <c r="BL17" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B18" t="n">
-        <v>137.6</v>
+        <v>132.5</v>
       </c>
       <c r="D18" t="n">
-        <v>35</v>
+        <v>33.6</v>
       </c>
       <c r="F18" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="K18" t="n">
-        <v>96.7</v>
+        <v>97.8</v>
       </c>
       <c r="O18" t="n">
-        <v>35.1</v>
-      </c>
-      <c r="V18" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="W18" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="X18" t="n">
-        <v>19</v>
+        <v>31.6</v>
       </c>
       <c r="Y18" t="n">
         <v>14</v>
       </c>
       <c r="Z18" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AA18" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>2.8</v>
+        <v>16.5</v>
       </c>
       <c r="AF18" t="n">
-        <v>221.78</v>
+        <v>224.78</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="AH18" t="n">
         <v>215</v>
@@ -2298,10 +1953,10 @@
         <v>235</v>
       </c>
       <c r="AK18" t="n">
-        <v>138.76</v>
+        <v>143.55</v>
       </c>
       <c r="AL18" t="n">
-        <v>5.67</v>
+        <v>4.79</v>
       </c>
       <c r="AM18" t="n">
         <v>110</v>
@@ -2310,60 +1965,75 @@
         <v>142</v>
       </c>
       <c r="BL18" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B19" t="n">
-        <v>132.5</v>
+        <v>137.2</v>
+      </c>
+      <c r="C19" t="n">
+        <v>56.3</v>
       </c>
       <c r="D19" t="n">
-        <v>33.6</v>
+        <v>32.1</v>
+      </c>
+      <c r="E19" t="n">
+        <v>21.2</v>
       </c>
       <c r="F19" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
+      </c>
+      <c r="H19" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="I19" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="J19" t="n">
+        <v>40.4</v>
       </c>
       <c r="K19" t="n">
-        <v>97.8</v>
+        <v>75.7</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N19" t="n">
+        <v>29</v>
       </c>
       <c r="O19" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="V19" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="W19" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="X19" t="n">
-        <v>19.8</v>
+        <v>32.6</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>21.6</v>
       </c>
       <c r="Y19" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Z19" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AA19" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>2.1</v>
+        <v>15.4</v>
       </c>
       <c r="AF19" t="n">
-        <v>224.78</v>
+        <v>232.22</v>
       </c>
       <c r="AG19" t="n">
-        <v>3</v>
+        <v>7.43</v>
       </c>
       <c r="AH19" t="n">
         <v>215</v>
@@ -2372,10 +2042,10 @@
         <v>235</v>
       </c>
       <c r="AK19" t="n">
-        <v>143.55</v>
+        <v>143.61</v>
       </c>
       <c r="AL19" t="n">
-        <v>4.79</v>
+        <v>0.06</v>
       </c>
       <c r="AM19" t="n">
         <v>110</v>
@@ -2383,52 +2053,58 @@
       <c r="AN19" t="n">
         <v>142</v>
       </c>
+      <c r="AP19" t="n">
+        <v>89.31999999999999</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>18.02</v>
+      </c>
       <c r="BL19" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="B20" t="n">
-        <v>137.2</v>
+        <v>157.5</v>
       </c>
       <c r="C20" t="n">
-        <v>56.3</v>
+        <v>59.6</v>
       </c>
       <c r="D20" t="n">
-        <v>32.1</v>
+        <v>35</v>
       </c>
       <c r="E20" t="n">
-        <v>21.2</v>
+        <v>30.6</v>
       </c>
       <c r="F20" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="H20" t="n">
-        <v>23.7</v>
+        <v>24.2</v>
       </c>
       <c r="I20" t="n">
-        <v>11.6</v>
+        <v>11.2</v>
       </c>
       <c r="J20" t="n">
-        <v>40.4</v>
+        <v>38.9</v>
       </c>
       <c r="K20" t="n">
-        <v>75.7</v>
+        <v>74.3</v>
       </c>
       <c r="M20" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="N20" t="n">
-        <v>29</v>
+        <v>33.4</v>
       </c>
       <c r="O20" t="n">
-        <v>32.6</v>
+        <v>37.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="R20" t="n">
         <v>1.3</v>
@@ -2437,40 +2113,22 @@
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="V20" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="W20" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="X20" t="n">
-        <v>17.5</v>
+        <v>21.1</v>
       </c>
       <c r="Y20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA20" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>3.2</v>
+        <v>15.5</v>
       </c>
       <c r="AF20" t="n">
-        <v>232.22</v>
+        <v>229.69</v>
       </c>
       <c r="AG20" t="n">
-        <v>7.43</v>
+        <v>-2.53</v>
       </c>
       <c r="AH20" t="n">
         <v>215</v>
@@ -2479,10 +2137,10 @@
         <v>235</v>
       </c>
       <c r="AK20" t="n">
-        <v>143.61</v>
+        <v>136.96</v>
       </c>
       <c r="AL20" t="n">
-        <v>0.06</v>
+        <v>-6.65</v>
       </c>
       <c r="AM20" t="n">
         <v>110</v>
@@ -2491,99 +2149,81 @@
         <v>142</v>
       </c>
       <c r="AP20" t="n">
-        <v>89.31999999999999</v>
+        <v>86.59</v>
       </c>
       <c r="AS20" t="n">
-        <v>18.02</v>
+        <v>16.96</v>
       </c>
       <c r="BL20" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B21" t="n">
-        <v>157.5</v>
+        <v>159.6</v>
       </c>
       <c r="C21" t="n">
-        <v>59.6</v>
+        <v>63</v>
       </c>
       <c r="D21" t="n">
-        <v>35</v>
+        <v>34.5</v>
       </c>
       <c r="E21" t="n">
-        <v>30.6</v>
+        <v>31.1</v>
       </c>
       <c r="F21" t="n">
-        <v>7.5</v>
+        <v>5.7</v>
       </c>
       <c r="H21" t="n">
-        <v>24.2</v>
+        <v>23.8</v>
       </c>
       <c r="I21" t="n">
-        <v>11.2</v>
+        <v>10.8</v>
       </c>
       <c r="J21" t="n">
-        <v>38.9</v>
+        <v>40.5</v>
       </c>
       <c r="K21" t="n">
-        <v>74.3</v>
+        <v>75.2</v>
       </c>
       <c r="M21" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="N21" t="n">
-        <v>33.4</v>
+        <v>34.3</v>
       </c>
       <c r="O21" t="n">
-        <v>37.1</v>
+        <v>38.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T21" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="V21" t="n">
-        <v>13</v>
-      </c>
-      <c r="W21" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="X21" t="n">
-        <v>19.6</v>
+        <v>21.3</v>
       </c>
       <c r="Y21" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA21" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>2</v>
+        <v>13.5</v>
       </c>
       <c r="AF21" t="n">
-        <v>229.69</v>
+        <v>228.57</v>
       </c>
       <c r="AG21" t="n">
-        <v>-2.53</v>
+        <v>-1.14</v>
       </c>
       <c r="AH21" t="n">
         <v>215</v>
@@ -2592,10 +2232,10 @@
         <v>235</v>
       </c>
       <c r="AK21" t="n">
-        <v>136.96</v>
+        <v>133.01</v>
       </c>
       <c r="AL21" t="n">
-        <v>-6.65</v>
+        <v>-3.95</v>
       </c>
       <c r="AM21" t="n">
         <v>110</v>
@@ -2604,99 +2244,81 @@
         <v>142</v>
       </c>
       <c r="AP21" t="n">
-        <v>86.59</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="AS21" t="n">
-        <v>16.96</v>
+        <v>15.95</v>
       </c>
       <c r="BL21" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B22" t="n">
-        <v>159.6</v>
+        <v>160.4</v>
       </c>
       <c r="C22" t="n">
-        <v>63</v>
+        <v>62.6</v>
       </c>
       <c r="D22" t="n">
-        <v>34.5</v>
+        <v>35</v>
       </c>
       <c r="E22" t="n">
-        <v>31.1</v>
+        <v>32.2</v>
       </c>
       <c r="F22" t="n">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="H22" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="I22" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="J22" t="n">
-        <v>40.5</v>
+        <v>41.1</v>
       </c>
       <c r="K22" t="n">
-        <v>75.2</v>
+        <v>75.7</v>
       </c>
       <c r="M22" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="N22" t="n">
-        <v>34.3</v>
+        <v>32.6</v>
       </c>
       <c r="O22" t="n">
-        <v>38.2</v>
+        <v>38</v>
       </c>
       <c r="Q22" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T22" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="V22" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="W22" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="X22" t="n">
-        <v>20</v>
+        <v>20.9</v>
       </c>
       <c r="Y22" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Z22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA22" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>-2.2</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.2</v>
+        <v>14.1</v>
       </c>
       <c r="AF22" t="n">
-        <v>228.57</v>
+        <v>225.08</v>
       </c>
       <c r="AG22" t="n">
-        <v>-1.14</v>
+        <v>-3.5</v>
       </c>
       <c r="AH22" t="n">
         <v>215</v>
@@ -2705,10 +2327,10 @@
         <v>235</v>
       </c>
       <c r="AK22" t="n">
-        <v>133.01</v>
+        <v>135.24</v>
       </c>
       <c r="AL22" t="n">
-        <v>-3.95</v>
+        <v>2.23</v>
       </c>
       <c r="AM22" t="n">
         <v>110</v>
@@ -2717,99 +2339,81 @@
         <v>142</v>
       </c>
       <c r="AP22" t="n">
-        <v>84.59999999999999</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="AS22" t="n">
-        <v>15.95</v>
+        <v>15.4</v>
       </c>
       <c r="BL22" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B23" t="n">
-        <v>160.4</v>
+        <v>161.7</v>
       </c>
       <c r="C23" t="n">
-        <v>62.6</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="D23" t="n">
-        <v>35</v>
+        <v>34.9</v>
       </c>
       <c r="E23" t="n">
-        <v>32.2</v>
+        <v>27.3</v>
       </c>
       <c r="F23" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H23" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="I23" t="n">
-        <v>10.7</v>
+        <v>10.3</v>
       </c>
       <c r="J23" t="n">
-        <v>41.1</v>
+        <v>42.6</v>
       </c>
       <c r="K23" t="n">
-        <v>75.7</v>
+        <v>77</v>
       </c>
       <c r="M23" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="N23" t="n">
-        <v>32.6</v>
+        <v>31.5</v>
       </c>
       <c r="O23" t="n">
-        <v>38</v>
+        <v>37.3</v>
       </c>
       <c r="Q23" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="R23" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T23" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="V23" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="W23" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="X23" t="n">
-        <v>19.6</v>
+        <v>21</v>
       </c>
       <c r="Y23" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Z23" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AA23" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>-3.1</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0.6</v>
+        <v>11.4</v>
       </c>
       <c r="AF23" t="n">
-        <v>225.08</v>
+        <v>225</v>
       </c>
       <c r="AG23" t="n">
-        <v>-3.5</v>
+        <v>-0.08</v>
       </c>
       <c r="AH23" t="n">
         <v>215</v>
@@ -2818,10 +2422,10 @@
         <v>235</v>
       </c>
       <c r="AK23" t="n">
-        <v>135.24</v>
+        <v>134.62</v>
       </c>
       <c r="AL23" t="n">
-        <v>2.23</v>
+        <v>-0.62</v>
       </c>
       <c r="AM23" t="n">
         <v>110</v>
@@ -2830,99 +2434,42 @@
         <v>142</v>
       </c>
       <c r="AP23" t="n">
-        <v>84.09999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="AS23" t="n">
-        <v>15.4</v>
+        <v>13.86</v>
       </c>
       <c r="BL23" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B24" t="n">
-        <v>161.7</v>
-      </c>
-      <c r="C24" t="n">
-        <v>71.09999999999999</v>
+        <v>151.5</v>
       </c>
       <c r="D24" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="E24" t="n">
-        <v>27.3</v>
+        <v>35.1</v>
       </c>
       <c r="F24" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H24" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I24" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="J24" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="K24" t="n">
-        <v>77</v>
-      </c>
-      <c r="M24" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="N24" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="O24" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>21</v>
-      </c>
-      <c r="R24" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="S24" t="n">
-        <v>6</v>
-      </c>
-      <c r="T24" t="n">
-        <v>21</v>
-      </c>
-      <c r="V24" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="W24" t="n">
-        <v>27</v>
-      </c>
-      <c r="X24" t="n">
-        <v>19.9</v>
+        <v>5.4</v>
       </c>
       <c r="Y24" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA24" t="n">
         <v>9</v>
       </c>
-      <c r="Z24" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>-5.2</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>-0.3</v>
-      </c>
       <c r="AF24" t="n">
-        <v>225</v>
+        <v>221.37</v>
       </c>
       <c r="AG24" t="n">
-        <v>-0.08</v>
+        <v>0.05</v>
       </c>
       <c r="AH24" t="n">
         <v>215</v>
@@ -2931,10 +2478,10 @@
         <v>235</v>
       </c>
       <c r="AK24" t="n">
-        <v>134.62</v>
+        <v>135.21</v>
       </c>
       <c r="AL24" t="n">
-        <v>-0.62</v>
+        <v>0.59</v>
       </c>
       <c r="AM24" t="n">
         <v>110</v>
@@ -2942,61 +2489,43 @@
       <c r="AN24" t="n">
         <v>142</v>
       </c>
-      <c r="AP24" t="n">
-        <v>80.2</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>13.86</v>
-      </c>
       <c r="BL24" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B25" t="n">
-        <v>151.5</v>
+        <v>145.2</v>
       </c>
       <c r="D25" t="n">
-        <v>35.1</v>
+        <v>33.5</v>
       </c>
       <c r="F25" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="V25" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="W25" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="X25" t="n">
-        <v>14</v>
+        <v>5</v>
+      </c>
+      <c r="K25" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="O25" t="n">
+        <v>35.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z25" t="n">
         <v>13</v>
       </c>
       <c r="AA25" t="n">
-        <v>9</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>-4.7</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>-1.4</v>
+        <v>10</v>
       </c>
       <c r="AF25" t="n">
-        <v>221.37</v>
+        <v>224.37</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.05</v>
+        <v>3</v>
       </c>
       <c r="AH25" t="n">
         <v>215</v>
@@ -3005,10 +2534,10 @@
         <v>235</v>
       </c>
       <c r="AK25" t="n">
-        <v>135.21</v>
+        <v>135.61</v>
       </c>
       <c r="AL25" t="n">
-        <v>0.59</v>
+        <v>0.4</v>
       </c>
       <c r="AM25" t="n">
         <v>110</v>
@@ -3017,60 +2546,42 @@
         <v>142</v>
       </c>
       <c r="BL25" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B26" t="n">
-        <v>145.2</v>
+        <v>146.3</v>
       </c>
       <c r="D26" t="n">
-        <v>33.5</v>
+        <v>33.4</v>
       </c>
       <c r="F26" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="K26" t="n">
-        <v>100.3</v>
+        <v>98.2</v>
       </c>
       <c r="O26" t="n">
-        <v>35.5</v>
-      </c>
-      <c r="V26" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W26" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="X26" t="n">
-        <v>13.1</v>
+        <v>35.1</v>
       </c>
       <c r="Y26" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z26" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA26" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>-5.4</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>-1.5</v>
+        <v>9</v>
       </c>
       <c r="AF26" t="n">
-        <v>224.37</v>
+        <v>225.93</v>
       </c>
       <c r="AG26" t="n">
-        <v>3</v>
+        <v>1.56</v>
       </c>
       <c r="AH26" t="n">
         <v>215</v>
@@ -3079,10 +2590,10 @@
         <v>235</v>
       </c>
       <c r="AK26" t="n">
-        <v>135.61</v>
+        <v>135.28</v>
       </c>
       <c r="AL26" t="n">
-        <v>0.4</v>
+        <v>-0.33</v>
       </c>
       <c r="AM26" t="n">
         <v>110</v>
@@ -3091,60 +2602,75 @@
         <v>142</v>
       </c>
       <c r="BL26" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B27" t="n">
-        <v>146.3</v>
+        <v>182.8</v>
+      </c>
+      <c r="C27" t="n">
+        <v>86.8</v>
       </c>
       <c r="D27" t="n">
-        <v>33.4</v>
+        <v>31.8</v>
+      </c>
+      <c r="E27" t="n">
+        <v>33</v>
       </c>
       <c r="F27" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
+      </c>
+      <c r="H27" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="I27" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J27" t="n">
+        <v>41.1</v>
       </c>
       <c r="K27" t="n">
-        <v>98.2</v>
+        <v>74.2</v>
+      </c>
+      <c r="M27" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="N27" t="n">
+        <v>33.5</v>
       </c>
       <c r="O27" t="n">
-        <v>35.1</v>
-      </c>
-      <c r="V27" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="W27" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="X27" t="n">
-        <v>10.6</v>
+        <v>38.4</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="R27" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="n">
+        <v>22.4</v>
       </c>
       <c r="Y27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z27" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AA27" t="n">
-        <v>9</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>-6.4</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>-3.3</v>
+        <v>8.5</v>
       </c>
       <c r="AF27" t="n">
-        <v>225.93</v>
+        <v>218.63</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.56</v>
+        <v>-7.3</v>
       </c>
       <c r="AH27" t="n">
         <v>215</v>
@@ -3153,10 +2679,10 @@
         <v>235</v>
       </c>
       <c r="AK27" t="n">
-        <v>135.28</v>
+        <v>126.27</v>
       </c>
       <c r="AL27" t="n">
-        <v>-0.33</v>
+        <v>-9.01</v>
       </c>
       <c r="AM27" t="n">
         <v>110</v>
@@ -3164,94 +2690,82 @@
       <c r="AN27" t="n">
         <v>142</v>
       </c>
+      <c r="AP27" t="n">
+        <v>82.66</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>14.7</v>
+      </c>
       <c r="BL27" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B28" t="n">
-        <v>182.8</v>
+        <v>181.8</v>
       </c>
       <c r="C28" t="n">
-        <v>86.8</v>
+        <v>86.5</v>
       </c>
       <c r="D28" t="n">
-        <v>31.8</v>
+        <v>31.4</v>
       </c>
       <c r="E28" t="n">
-        <v>33</v>
+        <v>34.2</v>
       </c>
       <c r="F28" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="H28" t="n">
-        <v>23.5</v>
+        <v>24.4</v>
       </c>
       <c r="I28" t="n">
-        <v>9.6</v>
+        <v>10.4</v>
       </c>
       <c r="J28" t="n">
-        <v>41.1</v>
+        <v>41.9</v>
       </c>
       <c r="K28" t="n">
-        <v>74.2</v>
+        <v>76.8</v>
       </c>
       <c r="M28" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="N28" t="n">
-        <v>33.5</v>
+        <v>35.7</v>
       </c>
       <c r="O28" t="n">
-        <v>38.4</v>
+        <v>39.8</v>
       </c>
       <c r="Q28" t="n">
-        <v>22.4</v>
+        <v>23</v>
       </c>
       <c r="R28" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>20.1</v>
       </c>
       <c r="T28" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="V28" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="W28" t="n">
-        <v>15</v>
-      </c>
-      <c r="X28" t="n">
-        <v>12.1</v>
+        <v>23</v>
       </c>
       <c r="Y28" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z28" t="n">
         <v>12</v>
       </c>
       <c r="AA28" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>-10.5</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>-5.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AF28" t="n">
-        <v>218.63</v>
+        <v>216.39</v>
       </c>
       <c r="AG28" t="n">
-        <v>-7.3</v>
+        <v>-2.23</v>
       </c>
       <c r="AH28" t="n">
         <v>215</v>
@@ -3260,10 +2774,10 @@
         <v>235</v>
       </c>
       <c r="AK28" t="n">
-        <v>126.27</v>
+        <v>123.32</v>
       </c>
       <c r="AL28" t="n">
-        <v>-9.01</v>
+        <v>-2.95</v>
       </c>
       <c r="AM28" t="n">
         <v>110</v>
@@ -3272,99 +2786,81 @@
         <v>142</v>
       </c>
       <c r="AP28" t="n">
-        <v>82.66</v>
+        <v>79.08</v>
       </c>
       <c r="AS28" t="n">
-        <v>14.7</v>
+        <v>13.91</v>
       </c>
       <c r="BL28" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B29" t="n">
-        <v>181.8</v>
+        <v>183</v>
       </c>
       <c r="C29" t="n">
-        <v>86.5</v>
+        <v>84.7</v>
       </c>
       <c r="D29" t="n">
-        <v>31.4</v>
+        <v>30.9</v>
       </c>
       <c r="E29" t="n">
-        <v>34.2</v>
+        <v>33.7</v>
       </c>
       <c r="F29" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="H29" t="n">
-        <v>24.4</v>
+        <v>23.4</v>
       </c>
       <c r="I29" t="n">
-        <v>10.4</v>
+        <v>10.6</v>
       </c>
       <c r="J29" t="n">
-        <v>41.9</v>
+        <v>42.3</v>
       </c>
       <c r="K29" t="n">
-        <v>76.8</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="M29" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="N29" t="n">
-        <v>35.7</v>
+        <v>36.7</v>
       </c>
       <c r="O29" t="n">
-        <v>39.8</v>
+        <v>40.8</v>
       </c>
       <c r="Q29" t="n">
-        <v>23</v>
+        <v>23.6</v>
       </c>
       <c r="R29" t="n">
         <v>1.8</v>
       </c>
       <c r="S29" t="n">
-        <v>20.1</v>
+        <v>20.8</v>
       </c>
       <c r="T29" t="n">
-        <v>23</v>
-      </c>
-      <c r="V29" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W29" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="X29" t="n">
-        <v>10.9</v>
+        <v>23.6</v>
       </c>
       <c r="Y29" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA29" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>-1.4</v>
+        <v>10</v>
       </c>
       <c r="AF29" t="n">
-        <v>216.39</v>
+        <v>217.16</v>
       </c>
       <c r="AG29" t="n">
-        <v>-2.23</v>
+        <v>0.76</v>
       </c>
       <c r="AH29" t="n">
         <v>215</v>
@@ -3373,10 +2869,10 @@
         <v>235</v>
       </c>
       <c r="AK29" t="n">
-        <v>123.32</v>
+        <v>117.87</v>
       </c>
       <c r="AL29" t="n">
-        <v>-2.95</v>
+        <v>-5.45</v>
       </c>
       <c r="AM29" t="n">
         <v>110</v>
@@ -3385,99 +2881,48 @@
         <v>142</v>
       </c>
       <c r="AP29" t="n">
-        <v>79.08</v>
+        <v>78.56</v>
       </c>
       <c r="AS29" t="n">
-        <v>13.91</v>
+        <v>13.45</v>
       </c>
       <c r="BL29" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B30" t="n">
-        <v>183</v>
-      </c>
-      <c r="C30" t="n">
-        <v>84.7</v>
+        <v>163.8</v>
       </c>
       <c r="D30" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="E30" t="n">
-        <v>33.7</v>
+        <v>29</v>
       </c>
       <c r="F30" t="n">
-        <v>7</v>
-      </c>
-      <c r="H30" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="I30" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="J30" t="n">
-        <v>42.3</v>
+        <v>6.5</v>
       </c>
       <c r="K30" t="n">
-        <v>76.40000000000001</v>
-      </c>
-      <c r="M30" t="n">
-        <v>4</v>
-      </c>
-      <c r="N30" t="n">
-        <v>36.7</v>
+        <v>101.2</v>
       </c>
       <c r="O30" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S30" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="T30" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="V30" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="W30" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="X30" t="n">
-        <v>10.9</v>
+        <v>40.2</v>
       </c>
       <c r="Y30" t="n">
         <v>8</v>
       </c>
       <c r="Z30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA30" t="n">
         <v>10</v>
       </c>
-      <c r="AB30" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AF30" t="n">
-        <v>217.16</v>
+        <v>220.31</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.76</v>
+        <v>3.16</v>
       </c>
       <c r="AH30" t="n">
         <v>215</v>
@@ -3486,10 +2931,10 @@
         <v>235</v>
       </c>
       <c r="AK30" t="n">
-        <v>117.87</v>
+        <v>116.52</v>
       </c>
       <c r="AL30" t="n">
-        <v>-5.45</v>
+        <v>-1.35</v>
       </c>
       <c r="AM30" t="n">
         <v>110</v>
@@ -3497,67 +2942,43 @@
       <c r="AN30" t="n">
         <v>142</v>
       </c>
-      <c r="AP30" t="n">
-        <v>78.56</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>13.45</v>
-      </c>
       <c r="BL30" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B31" t="n">
-        <v>163.8</v>
+        <v>155.9</v>
       </c>
       <c r="D31" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F31" t="n">
         <v>6.5</v>
       </c>
       <c r="K31" t="n">
-        <v>101.2</v>
+        <v>99.3</v>
       </c>
       <c r="O31" t="n">
-        <v>40.2</v>
-      </c>
-      <c r="V31" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="W31" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="X31" t="n">
-        <v>11.8</v>
+        <v>38.5</v>
       </c>
       <c r="Y31" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA31" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>2.8</v>
+        <v>11.5</v>
       </c>
       <c r="AF31" t="n">
-        <v>220.31</v>
+        <v>221.99</v>
       </c>
       <c r="AG31" t="n">
-        <v>3.16</v>
+        <v>1.67</v>
       </c>
       <c r="AH31" t="n">
         <v>215</v>
@@ -3566,10 +2987,10 @@
         <v>235</v>
       </c>
       <c r="AK31" t="n">
-        <v>116.52</v>
+        <v>116.37</v>
       </c>
       <c r="AL31" t="n">
-        <v>-1.35</v>
+        <v>-0.15</v>
       </c>
       <c r="AM31" t="n">
         <v>110</v>
@@ -3578,60 +2999,42 @@
         <v>142</v>
       </c>
       <c r="BL31" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B32" t="n">
-        <v>155.9</v>
+        <v>141.3</v>
       </c>
       <c r="D32" t="n">
-        <v>28</v>
+        <v>26.3</v>
       </c>
       <c r="F32" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="K32" t="n">
-        <v>99.3</v>
+        <v>97.8</v>
       </c>
       <c r="O32" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="V32" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="W32" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="X32" t="n">
-        <v>12.4</v>
+        <v>39.8</v>
       </c>
       <c r="Y32" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Z32" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA32" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>3.5</v>
+        <v>14</v>
       </c>
       <c r="AF32" t="n">
-        <v>221.99</v>
+        <v>225.14</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.67</v>
+        <v>3.15</v>
       </c>
       <c r="AH32" t="n">
         <v>215</v>
@@ -3639,12 +3042,6 @@
       <c r="AI32" t="n">
         <v>235</v>
       </c>
-      <c r="AK32" t="n">
-        <v>116.37</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>-0.15</v>
-      </c>
       <c r="AM32" t="n">
         <v>110</v>
       </c>
@@ -3652,61 +3049,37 @@
         <v>142</v>
       </c>
       <c r="BL32" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B33" t="n">
-        <v>141.3</v>
+        <v>131.5</v>
       </c>
       <c r="D33" t="n">
-        <v>26.3</v>
+        <v>27.3</v>
       </c>
       <c r="F33" t="n">
         <v>5.5</v>
       </c>
       <c r="K33" t="n">
-        <v>97.8</v>
+        <v>97</v>
       </c>
       <c r="O33" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="V33" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W33" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="X33" t="n">
-        <v>13.6</v>
+        <v>35.7</v>
       </c>
       <c r="Y33" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z33" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA33" t="n">
         <v>15</v>
       </c>
-      <c r="AA33" t="n">
-        <v>14</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>225.14</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>3.15</v>
-      </c>
       <c r="AH33" t="n">
         <v>215</v>
       </c>
@@ -3720,54 +3093,75 @@
         <v>142</v>
       </c>
       <c r="BL33" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="B34" t="n">
-        <v>131.5</v>
+        <v>153</v>
+      </c>
+      <c r="C34" t="n">
+        <v>71.8</v>
       </c>
       <c r="D34" t="n">
-        <v>27.3</v>
+        <v>28.6</v>
+      </c>
+      <c r="E34" t="n">
+        <v>24.7</v>
       </c>
       <c r="F34" t="n">
-        <v>5.5</v>
+        <v>4</v>
+      </c>
+      <c r="H34" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J34" t="n">
+        <v>41.1</v>
       </c>
       <c r="K34" t="n">
-        <v>97</v>
+        <v>75.90000000000001</v>
+      </c>
+      <c r="M34" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N34" t="n">
+        <v>33.5</v>
       </c>
       <c r="O34" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="V34" t="n">
-        <v>9</v>
-      </c>
-      <c r="W34" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="X34" t="n">
-        <v>11.4</v>
+        <v>38.3</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="R34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>23.2</v>
       </c>
       <c r="Y34" t="n">
         <v>12</v>
       </c>
       <c r="Z34" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AA34" t="n">
-        <v>15</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>-3.6</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>-0.4</v>
+        <v>12.5</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>229.96</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>-0.02</v>
       </c>
       <c r="AH34" t="n">
         <v>215</v>
@@ -3775,100 +3169,94 @@
       <c r="AI34" t="n">
         <v>235</v>
       </c>
+      <c r="AK34" t="n">
+        <v>128.14</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>11.77</v>
+      </c>
       <c r="AM34" t="n">
         <v>110</v>
       </c>
       <c r="AN34" t="n">
         <v>142</v>
       </c>
+      <c r="AP34" t="n">
+        <v>87.47</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>14.8</v>
+      </c>
       <c r="BL34" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B35" t="n">
-        <v>153</v>
+        <v>165.8</v>
       </c>
       <c r="C35" t="n">
-        <v>71.8</v>
+        <v>77.3</v>
       </c>
       <c r="D35" t="n">
-        <v>28.6</v>
+        <v>29.3</v>
       </c>
       <c r="E35" t="n">
-        <v>24.7</v>
+        <v>27.7</v>
       </c>
       <c r="F35" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="H35" t="n">
         <v>24.1</v>
       </c>
       <c r="I35" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="J35" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="K35" t="n">
-        <v>75.90000000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="M35" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="N35" t="n">
-        <v>33.5</v>
+        <v>35.1</v>
       </c>
       <c r="O35" t="n">
-        <v>38.3</v>
+        <v>39.8</v>
       </c>
       <c r="Q35" t="n">
-        <v>23.2</v>
+        <v>23.8</v>
       </c>
       <c r="R35" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="T35" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="V35" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="W35" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z35" t="n">
         <v>13</v>
       </c>
-      <c r="X35" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>14</v>
-      </c>
       <c r="AA35" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>-6.6</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>-0.6</v>
+        <v>10.1</v>
       </c>
       <c r="AF35" t="n">
-        <v>229.96</v>
+        <v>227.01</v>
       </c>
       <c r="AG35" t="n">
-        <v>-0.02</v>
+        <v>-2.95</v>
       </c>
       <c r="AH35" t="n">
         <v>215</v>
@@ -3877,10 +3265,10 @@
         <v>235</v>
       </c>
       <c r="AK35" t="n">
-        <v>128.14</v>
+        <v>128.15</v>
       </c>
       <c r="AL35" t="n">
-        <v>11.77</v>
+        <v>0.01</v>
       </c>
       <c r="AM35" t="n">
         <v>110</v>
@@ -3889,99 +3277,81 @@
         <v>142</v>
       </c>
       <c r="AP35" t="n">
-        <v>87.47</v>
+        <v>83.41</v>
       </c>
       <c r="AS35" t="n">
-        <v>14.8</v>
+        <v>14.52</v>
       </c>
       <c r="BL35" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B36" t="n">
-        <v>165.8</v>
+        <v>158.1</v>
       </c>
       <c r="C36" t="n">
-        <v>77.3</v>
+        <v>73.7</v>
       </c>
       <c r="D36" t="n">
-        <v>29.3</v>
+        <v>30.3</v>
       </c>
       <c r="E36" t="n">
-        <v>27.7</v>
+        <v>26</v>
       </c>
       <c r="F36" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="H36" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="I36" t="n">
-        <v>10.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J36" t="n">
-        <v>41.6</v>
+        <v>40.9</v>
       </c>
       <c r="K36" t="n">
-        <v>76.59999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="M36" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="N36" t="n">
-        <v>35.1</v>
+        <v>35.3</v>
       </c>
       <c r="O36" t="n">
-        <v>39.8</v>
+        <v>40.3</v>
       </c>
       <c r="Q36" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="R36" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S36" t="n">
         <v>7</v>
       </c>
       <c r="T36" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="V36" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="W36" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="X36" t="n">
-        <v>13.4</v>
+        <v>23.6</v>
       </c>
       <c r="Y36" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z36" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA36" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>4.4</v>
+        <v>11</v>
       </c>
       <c r="AF36" t="n">
-        <v>227.01</v>
+        <v>228.35</v>
       </c>
       <c r="AG36" t="n">
-        <v>-2.95</v>
+        <v>1.33</v>
       </c>
       <c r="AH36" t="n">
         <v>215</v>
@@ -3990,10 +3360,10 @@
         <v>235</v>
       </c>
       <c r="AK36" t="n">
-        <v>128.15</v>
+        <v>128.86</v>
       </c>
       <c r="AL36" t="n">
-        <v>0.01</v>
+        <v>0.71</v>
       </c>
       <c r="AM36" t="n">
         <v>110</v>
@@ -4002,99 +3372,81 @@
         <v>142</v>
       </c>
       <c r="AP36" t="n">
-        <v>83.41</v>
+        <v>82.37</v>
       </c>
       <c r="AS36" t="n">
-        <v>14.52</v>
+        <v>14.22</v>
       </c>
       <c r="BL36" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B37" t="n">
-        <v>158.1</v>
+        <v>154.9</v>
       </c>
       <c r="C37" t="n">
-        <v>73.7</v>
+        <v>70.2</v>
       </c>
       <c r="D37" t="n">
-        <v>30.3</v>
+        <v>31.5</v>
       </c>
       <c r="E37" t="n">
-        <v>26</v>
+        <v>27.7</v>
       </c>
       <c r="F37" t="n">
-        <v>4.1</v>
+        <v>2.7</v>
       </c>
       <c r="H37" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="I37" t="n">
-        <v>9.300000000000001</v>
+        <v>11.3</v>
       </c>
       <c r="J37" t="n">
-        <v>40.9</v>
+        <v>40.3</v>
       </c>
       <c r="K37" t="n">
-        <v>74.40000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="M37" t="n">
-        <v>5</v>
+        <v>6.1</v>
       </c>
       <c r="N37" t="n">
-        <v>35.3</v>
+        <v>32.9</v>
       </c>
       <c r="O37" t="n">
-        <v>40.3</v>
+        <v>39</v>
       </c>
       <c r="Q37" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="R37" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="S37" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="T37" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="V37" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="W37" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="X37" t="n">
-        <v>14.1</v>
+        <v>23.7</v>
       </c>
       <c r="Y37" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z37" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA37" t="n">
-        <v>11</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>6.5</v>
+        <v>12.6</v>
       </c>
       <c r="AF37" t="n">
-        <v>228.35</v>
+        <v>231.16</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.33</v>
+        <v>2.81</v>
       </c>
       <c r="AH37" t="n">
         <v>215</v>
@@ -4103,10 +3455,10 @@
         <v>235</v>
       </c>
       <c r="AK37" t="n">
-        <v>128.86</v>
+        <v>130.88</v>
       </c>
       <c r="AL37" t="n">
-        <v>0.71</v>
+        <v>2.02</v>
       </c>
       <c r="AM37" t="n">
         <v>110</v>
@@ -4115,99 +3467,48 @@
         <v>142</v>
       </c>
       <c r="AP37" t="n">
-        <v>82.37</v>
+        <v>85.48999999999999</v>
       </c>
       <c r="AS37" t="n">
-        <v>14.22</v>
+        <v>13.1</v>
       </c>
       <c r="BL37" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B38" t="n">
-        <v>154.9</v>
-      </c>
-      <c r="C38" t="n">
-        <v>70.2</v>
+        <v>152.2</v>
       </c>
       <c r="D38" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="E38" t="n">
-        <v>27.7</v>
+        <v>31</v>
       </c>
       <c r="F38" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="H38" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I38" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J38" t="n">
-        <v>40.3</v>
+        <v>3.5</v>
       </c>
       <c r="K38" t="n">
-        <v>75.8</v>
-      </c>
-      <c r="M38" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="N38" t="n">
-        <v>32.9</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O38" t="n">
-        <v>39</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="R38" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="S38" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="T38" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="V38" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="W38" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="X38" t="n">
-        <v>15.8</v>
+        <v>34.4</v>
       </c>
       <c r="Y38" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Z38" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AA38" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>5.8</v>
+        <v>9</v>
       </c>
       <c r="AF38" t="n">
-        <v>231.16</v>
+        <v>228.13</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.81</v>
+        <v>-3.03</v>
       </c>
       <c r="AH38" t="n">
         <v>215</v>
@@ -4215,79 +3516,49 @@
       <c r="AI38" t="n">
         <v>235</v>
       </c>
-      <c r="AK38" t="n">
-        <v>130.88</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AM38" t="n">
         <v>110</v>
       </c>
       <c r="AN38" t="n">
         <v>142</v>
       </c>
-      <c r="AP38" t="n">
-        <v>85.48999999999999</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>13.1</v>
-      </c>
       <c r="BL38" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B39" t="n">
-        <v>152.2</v>
+        <v>143.9</v>
       </c>
       <c r="D39" t="n">
-        <v>31</v>
+        <v>30.8</v>
       </c>
       <c r="F39" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="K39" t="n">
-        <v>98.40000000000001</v>
+        <v>99.2</v>
       </c>
       <c r="O39" t="n">
-        <v>34.4</v>
-      </c>
-      <c r="V39" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W39" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="X39" t="n">
-        <v>17.5</v>
+        <v>35.2</v>
       </c>
       <c r="Y39" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Z39" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA39" t="n">
         <v>9</v>
       </c>
-      <c r="AB39" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>3.8</v>
-      </c>
       <c r="AF39" t="n">
-        <v>228.13</v>
+        <v>229.16</v>
       </c>
       <c r="AG39" t="n">
-        <v>-3.03</v>
+        <v>1.03</v>
       </c>
       <c r="AH39" t="n">
         <v>215</v>
@@ -4302,60 +3573,75 @@
         <v>142</v>
       </c>
       <c r="BL39" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B40" t="n">
-        <v>143.9</v>
+        <v>163.2</v>
+      </c>
+      <c r="C40" t="n">
+        <v>73.7</v>
       </c>
       <c r="D40" t="n">
-        <v>30.8</v>
+        <v>30</v>
+      </c>
+      <c r="E40" t="n">
+        <v>28.2</v>
       </c>
       <c r="F40" t="n">
-        <v>2.5</v>
+        <v>4.8</v>
+      </c>
+      <c r="H40" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I40" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J40" t="n">
+        <v>40.1</v>
       </c>
       <c r="K40" t="n">
-        <v>99.2</v>
+        <v>75.59999999999999</v>
+      </c>
+      <c r="M40" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="N40" t="n">
+        <v>32.9</v>
       </c>
       <c r="O40" t="n">
-        <v>35.2</v>
-      </c>
-      <c r="V40" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="W40" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="X40" t="n">
-        <v>14.2</v>
+        <v>39.7</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="R40" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="S40" t="n">
+        <v>6</v>
+      </c>
+      <c r="T40" t="n">
+        <v>23.5</v>
       </c>
       <c r="Y40" t="n">
         <v>4</v>
       </c>
       <c r="Z40" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA40" t="n">
-        <v>9</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AF40" t="n">
-        <v>229.16</v>
+        <v>228.55</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.03</v>
+        <v>-0.61</v>
       </c>
       <c r="AH40" t="n">
         <v>215</v>
@@ -4363,100 +3649,94 @@
       <c r="AI40" t="n">
         <v>235</v>
       </c>
+      <c r="AK40" t="n">
+        <v>127.06</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>-3.82</v>
+      </c>
       <c r="AM40" t="n">
         <v>110</v>
       </c>
       <c r="AN40" t="n">
         <v>142</v>
       </c>
+      <c r="AP40" t="n">
+        <v>82.81</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>12.9</v>
+      </c>
       <c r="BL40" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="B41" t="n">
-        <v>163.2</v>
+        <v>174.4</v>
       </c>
       <c r="C41" t="n">
-        <v>73.7</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="D41" t="n">
-        <v>30</v>
+        <v>32.1</v>
       </c>
       <c r="E41" t="n">
-        <v>28.2</v>
+        <v>30.8</v>
       </c>
       <c r="F41" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="H41" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="I41" t="n">
-        <v>11.4</v>
+        <v>10.5</v>
       </c>
       <c r="J41" t="n">
-        <v>40.1</v>
+        <v>39.5</v>
       </c>
       <c r="K41" t="n">
-        <v>75.59999999999999</v>
+        <v>74</v>
       </c>
       <c r="M41" t="n">
         <v>6.8</v>
       </c>
       <c r="N41" t="n">
-        <v>32.9</v>
+        <v>35.8</v>
       </c>
       <c r="O41" t="n">
-        <v>39.7</v>
+        <v>42.6</v>
       </c>
       <c r="Q41" t="n">
-        <v>23.5</v>
+        <v>23.1</v>
       </c>
       <c r="R41" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="S41" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="T41" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="V41" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="W41" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="X41" t="n">
-        <v>14.8</v>
+        <v>23.1</v>
       </c>
       <c r="Y41" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Z41" t="n">
         <v>13</v>
       </c>
       <c r="AA41" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>4.3</v>
+        <v>10.1</v>
       </c>
       <c r="AF41" t="n">
-        <v>228.55</v>
+        <v>219.99</v>
       </c>
       <c r="AG41" t="n">
-        <v>-0.61</v>
+        <v>-8.56</v>
       </c>
       <c r="AH41" t="n">
         <v>215</v>
@@ -4465,10 +3745,10 @@
         <v>235</v>
       </c>
       <c r="AK41" t="n">
-        <v>127.06</v>
+        <v>125.61</v>
       </c>
       <c r="AL41" t="n">
-        <v>-3.82</v>
+        <v>-1.45</v>
       </c>
       <c r="AM41" t="n">
         <v>110</v>
@@ -4477,99 +3757,81 @@
         <v>142</v>
       </c>
       <c r="AP41" t="n">
-        <v>82.81</v>
+        <v>77.83</v>
       </c>
       <c r="AS41" t="n">
-        <v>12.9</v>
+        <v>12.96</v>
       </c>
       <c r="BL41" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B42" t="n">
-        <v>174.4</v>
+        <v>163.2</v>
       </c>
       <c r="C42" t="n">
-        <v>75.40000000000001</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="D42" t="n">
-        <v>32.1</v>
+        <v>32.9</v>
       </c>
       <c r="E42" t="n">
-        <v>30.8</v>
+        <v>26</v>
       </c>
       <c r="F42" t="n">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="H42" t="n">
-        <v>24</v>
+        <v>23.8</v>
       </c>
       <c r="I42" t="n">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="J42" t="n">
-        <v>39.5</v>
+        <v>40.1</v>
       </c>
       <c r="K42" t="n">
-        <v>74</v>
+        <v>71.3</v>
       </c>
       <c r="M42" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="N42" t="n">
-        <v>35.8</v>
+        <v>34.3</v>
       </c>
       <c r="O42" t="n">
-        <v>42.6</v>
+        <v>41.5</v>
       </c>
       <c r="Q42" t="n">
         <v>23.1</v>
       </c>
       <c r="R42" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="S42" t="n">
-        <v>8.5</v>
+        <v>6.2</v>
       </c>
       <c r="T42" t="n">
         <v>23.1</v>
       </c>
-      <c r="V42" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="W42" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="X42" t="n">
-        <v>17.5</v>
-      </c>
       <c r="Y42" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z42" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA42" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>4.8</v>
+        <v>12.2</v>
       </c>
       <c r="AF42" t="n">
-        <v>219.99</v>
+        <v>219.22</v>
       </c>
       <c r="AG42" t="n">
-        <v>-8.56</v>
+        <v>-0.77</v>
       </c>
       <c r="AH42" t="n">
         <v>215</v>
@@ -4578,10 +3840,10 @@
         <v>235</v>
       </c>
       <c r="AK42" t="n">
-        <v>125.61</v>
+        <v>124.36</v>
       </c>
       <c r="AL42" t="n">
-        <v>-1.45</v>
+        <v>-1.25</v>
       </c>
       <c r="AM42" t="n">
         <v>110</v>
@@ -4590,99 +3852,81 @@
         <v>142</v>
       </c>
       <c r="AP42" t="n">
-        <v>77.83</v>
+        <v>76.81</v>
       </c>
       <c r="AS42" t="n">
-        <v>12.96</v>
+        <v>12.38</v>
       </c>
       <c r="BL42" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B43" t="n">
-        <v>163.2</v>
+        <v>152.7</v>
       </c>
       <c r="C43" t="n">
-        <v>70.90000000000001</v>
+        <v>62.6</v>
       </c>
       <c r="D43" t="n">
-        <v>32.9</v>
+        <v>32.7</v>
       </c>
       <c r="E43" t="n">
-        <v>26</v>
+        <v>24.6</v>
       </c>
       <c r="F43" t="n">
-        <v>6.9</v>
+        <v>5.2</v>
       </c>
       <c r="H43" t="n">
         <v>23.8</v>
       </c>
       <c r="I43" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J43" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="K43" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="M43" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="N43" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="O43" t="n">
         <v>40.1</v>
       </c>
-      <c r="K43" t="n">
-        <v>71.3</v>
-      </c>
-      <c r="M43" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="N43" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="O43" t="n">
-        <v>41.5</v>
-      </c>
       <c r="Q43" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="R43" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="S43" t="n">
-        <v>6.2</v>
+        <v>4</v>
       </c>
       <c r="T43" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="V43" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="W43" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="X43" t="n">
-        <v>16.4</v>
+        <v>23.2</v>
       </c>
       <c r="Y43" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z43" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA43" t="n">
         <v>14</v>
       </c>
-      <c r="AA43" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>5.5</v>
-      </c>
       <c r="AF43" t="n">
-        <v>219.22</v>
+        <v>220.73</v>
       </c>
       <c r="AG43" t="n">
-        <v>-0.77</v>
+        <v>1.5</v>
       </c>
       <c r="AH43" t="n">
         <v>215</v>
@@ -4691,10 +3935,10 @@
         <v>235</v>
       </c>
       <c r="AK43" t="n">
-        <v>124.36</v>
+        <v>120.93</v>
       </c>
       <c r="AL43" t="n">
-        <v>-1.25</v>
+        <v>-3.43</v>
       </c>
       <c r="AM43" t="n">
         <v>110</v>
@@ -4703,76 +3947,67 @@
         <v>142</v>
       </c>
       <c r="AP43" t="n">
-        <v>76.81</v>
+        <v>77.87</v>
       </c>
       <c r="AS43" t="n">
-        <v>12.38</v>
+        <v>13.26</v>
       </c>
       <c r="BL43" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B44" t="n">
-        <v>152.7</v>
+        <v>150.7</v>
       </c>
       <c r="C44" t="n">
-        <v>62.6</v>
+        <v>64.8</v>
       </c>
       <c r="D44" t="n">
-        <v>32.7</v>
+        <v>33.7</v>
       </c>
       <c r="E44" t="n">
-        <v>24.6</v>
+        <v>27.1</v>
       </c>
       <c r="F44" t="n">
-        <v>5.2</v>
+        <v>3.8</v>
       </c>
       <c r="H44" t="n">
-        <v>23.8</v>
+        <v>23.4</v>
       </c>
       <c r="I44" t="n">
         <v>7.2</v>
       </c>
       <c r="J44" t="n">
-        <v>38.9</v>
+        <v>39.9</v>
       </c>
       <c r="K44" t="n">
-        <v>69.90000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="M44" t="n">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="N44" t="n">
-        <v>33.5</v>
+        <v>33</v>
       </c>
       <c r="O44" t="n">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="Q44" t="n">
         <v>23.2</v>
       </c>
       <c r="R44" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="S44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T44" t="n">
         <v>23.2</v>
       </c>
-      <c r="V44" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="W44" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="X44" t="n">
-        <v>19.4</v>
-      </c>
       <c r="Y44" t="n">
         <v>10</v>
       </c>
@@ -4780,22 +4015,13 @@
         <v>18</v>
       </c>
       <c r="AA44" t="n">
-        <v>14</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>5.7</v>
+        <v>13.1</v>
       </c>
       <c r="AF44" t="n">
-        <v>220.73</v>
+        <v>220.58</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.5</v>
+        <v>-0.15</v>
       </c>
       <c r="AH44" t="n">
         <v>215</v>
@@ -4804,10 +4030,10 @@
         <v>235</v>
       </c>
       <c r="AK44" t="n">
-        <v>120.93</v>
+        <v>120.28</v>
       </c>
       <c r="AL44" t="n">
-        <v>-3.43</v>
+        <v>-0.65</v>
       </c>
       <c r="AM44" t="n">
         <v>110</v>
@@ -4816,99 +4042,36 @@
         <v>142</v>
       </c>
       <c r="AP44" t="n">
-        <v>77.87</v>
+        <v>77.22</v>
       </c>
       <c r="AS44" t="n">
-        <v>13.26</v>
+        <v>13.79</v>
       </c>
       <c r="BL44" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B45" t="n">
-        <v>150.7</v>
-      </c>
-      <c r="C45" t="n">
-        <v>64.8</v>
+        <v>138.2</v>
       </c>
       <c r="D45" t="n">
-        <v>33.7</v>
-      </c>
-      <c r="E45" t="n">
-        <v>27.1</v>
+        <v>33.6</v>
       </c>
       <c r="F45" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H45" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="I45" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="J45" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="K45" t="n">
-        <v>70.5</v>
-      </c>
-      <c r="M45" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="N45" t="n">
-        <v>33</v>
-      </c>
-      <c r="O45" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="R45" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="S45" t="n">
-        <v>3</v>
-      </c>
-      <c r="T45" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="V45" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="W45" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="X45" t="n">
-        <v>21.7</v>
+        <v>6.1</v>
       </c>
       <c r="Y45" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z45" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AA45" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>220.58</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>-0.15</v>
+        <v>13</v>
       </c>
       <c r="AH45" t="n">
         <v>215</v>
@@ -4916,67 +4079,43 @@
       <c r="AI45" t="n">
         <v>235</v>
       </c>
-      <c r="AK45" t="n">
-        <v>120.28</v>
-      </c>
-      <c r="AL45" t="n">
-        <v>-0.65</v>
-      </c>
       <c r="AM45" t="n">
         <v>110</v>
       </c>
       <c r="AN45" t="n">
         <v>142</v>
       </c>
-      <c r="AP45" t="n">
-        <v>77.22</v>
-      </c>
-      <c r="AS45" t="n">
-        <v>13.79</v>
-      </c>
       <c r="BL45" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B46" t="n">
-        <v>138.2</v>
+        <v>126.5</v>
       </c>
       <c r="D46" t="n">
-        <v>33.6</v>
+        <v>33.2</v>
       </c>
       <c r="F46" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="V46" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="W46" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="X46" t="n">
-        <v>19.4</v>
+        <v>3.4</v>
       </c>
       <c r="Y46" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z46" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA46" t="n">
         <v>13</v>
       </c>
-      <c r="AB46" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>4.5</v>
+      <c r="AF46" t="n">
+        <v>229.48</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>6.05</v>
       </c>
       <c r="AH46" t="n">
         <v>215</v>
@@ -4991,54 +4130,75 @@
         <v>142</v>
       </c>
       <c r="BL46" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B47" t="n">
-        <v>126.5</v>
+        <v>129.4</v>
+      </c>
+      <c r="C47" t="n">
+        <v>50.6</v>
       </c>
       <c r="D47" t="n">
-        <v>33.2</v>
+        <v>31.5</v>
+      </c>
+      <c r="E47" t="n">
+        <v>19.4</v>
       </c>
       <c r="F47" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="V47" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="W47" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="X47" t="n">
-        <v>17.4</v>
+        <v>2.7</v>
+      </c>
+      <c r="H47" t="n">
+        <v>24</v>
+      </c>
+      <c r="I47" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J47" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="K47" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="M47" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N47" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="O47" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>21.4</v>
       </c>
       <c r="Y47" t="n">
         <v>8</v>
       </c>
       <c r="Z47" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AA47" t="n">
-        <v>13</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>3.4</v>
+        <v>16.1</v>
       </c>
       <c r="AF47" t="n">
-        <v>229.48</v>
+        <v>229.5</v>
       </c>
       <c r="AG47" t="n">
-        <v>6.05</v>
+        <v>0.02</v>
       </c>
       <c r="AH47" t="n">
         <v>215</v>
@@ -5046,100 +4206,94 @@
       <c r="AI47" t="n">
         <v>235</v>
       </c>
+      <c r="AK47" t="n">
+        <v>128.37</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>8.09</v>
+      </c>
       <c r="AM47" t="n">
         <v>110</v>
       </c>
       <c r="AN47" t="n">
         <v>142</v>
       </c>
+      <c r="AP47" t="n">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>15.97</v>
+      </c>
       <c r="BL47" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="B48" t="n">
-        <v>129.4</v>
+        <v>142.9</v>
       </c>
       <c r="C48" t="n">
-        <v>50.6</v>
+        <v>52.7</v>
       </c>
       <c r="D48" t="n">
-        <v>31.5</v>
+        <v>34.7</v>
       </c>
       <c r="E48" t="n">
-        <v>19.4</v>
+        <v>24.8</v>
       </c>
       <c r="F48" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="H48" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I48" t="n">
-        <v>10.4</v>
+        <v>9.9</v>
       </c>
       <c r="J48" t="n">
-        <v>38.9</v>
+        <v>38.2</v>
       </c>
       <c r="K48" t="n">
-        <v>73.3</v>
+        <v>70</v>
       </c>
       <c r="M48" t="n">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="N48" t="n">
-        <v>33.3</v>
+        <v>31.9</v>
       </c>
       <c r="O48" t="n">
-        <v>38</v>
+        <v>35.8</v>
       </c>
       <c r="Q48" t="n">
-        <v>21.4</v>
+        <v>19.7</v>
       </c>
       <c r="R48" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="V48" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="W48" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="X48" t="n">
-        <v>19.1</v>
+        <v>19.7</v>
       </c>
       <c r="Y48" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Z48" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AA48" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="AF48" t="n">
-        <v>229.5</v>
+        <v>238.69</v>
       </c>
       <c r="AG48" t="n">
-        <v>0.02</v>
+        <v>-2.8</v>
       </c>
       <c r="AH48" t="n">
         <v>215</v>
@@ -5148,10 +4302,10 @@
         <v>235</v>
       </c>
       <c r="AK48" t="n">
-        <v>128.37</v>
+        <v>134.59</v>
       </c>
       <c r="AL48" t="n">
-        <v>8.09</v>
+        <v>6.22</v>
       </c>
       <c r="AM48" t="n">
         <v>110</v>
@@ -5160,99 +4314,81 @@
         <v>142</v>
       </c>
       <c r="AP48" t="n">
-        <v>91.59999999999999</v>
+        <v>89.05</v>
       </c>
       <c r="AS48" t="n">
-        <v>15.97</v>
+        <v>17.06</v>
       </c>
       <c r="BL48" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B49" t="n">
-        <v>142.9</v>
+        <v>148.1</v>
       </c>
       <c r="C49" t="n">
-        <v>52.7</v>
+        <v>51.9</v>
       </c>
       <c r="D49" t="n">
-        <v>34.7</v>
+        <v>35.4</v>
       </c>
       <c r="E49" t="n">
-        <v>24.8</v>
+        <v>31.5</v>
       </c>
       <c r="F49" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="H49" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="I49" t="n">
-        <v>9.9</v>
+        <v>9.6</v>
       </c>
       <c r="J49" t="n">
-        <v>38.2</v>
+        <v>39.6</v>
       </c>
       <c r="K49" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M49" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="N49" t="n">
-        <v>31.9</v>
+        <v>30.8</v>
       </c>
       <c r="O49" t="n">
-        <v>35.8</v>
+        <v>33.7</v>
       </c>
       <c r="Q49" t="n">
-        <v>19.7</v>
+        <v>20.7</v>
       </c>
       <c r="R49" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="V49" t="n">
-        <v>12</v>
-      </c>
-      <c r="W49" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="X49" t="n">
-        <v>18.9</v>
+        <v>20.7</v>
       </c>
       <c r="Y49" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z49" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AA49" t="n">
-        <v>15</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>2.9</v>
+        <v>15.5</v>
       </c>
       <c r="AF49" t="n">
-        <v>238.69</v>
+        <v>233.48</v>
       </c>
       <c r="AG49" t="n">
-        <v>-2.8</v>
+        <v>-4.86</v>
       </c>
       <c r="AH49" t="n">
         <v>215</v>
@@ -5261,10 +4397,10 @@
         <v>235</v>
       </c>
       <c r="AK49" t="n">
-        <v>134.59</v>
+        <v>136.6</v>
       </c>
       <c r="AL49" t="n">
-        <v>6.22</v>
+        <v>2.01</v>
       </c>
       <c r="AM49" t="n">
         <v>110</v>
@@ -5273,99 +4409,81 @@
         <v>142</v>
       </c>
       <c r="AP49" t="n">
-        <v>89.05</v>
+        <v>86.25</v>
       </c>
       <c r="AS49" t="n">
-        <v>17.06</v>
+        <v>17.13</v>
       </c>
       <c r="BL49" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B50" t="n">
-        <v>148.1</v>
+        <v>143.4</v>
       </c>
       <c r="C50" t="n">
-        <v>51.9</v>
+        <v>50.9</v>
       </c>
       <c r="D50" t="n">
-        <v>35.4</v>
+        <v>35.7</v>
       </c>
       <c r="E50" t="n">
-        <v>31.5</v>
+        <v>26.2</v>
       </c>
       <c r="F50" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="H50" t="n">
-        <v>21.8</v>
+        <v>22.9</v>
       </c>
       <c r="I50" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J50" t="n">
-        <v>39.6</v>
+        <v>39.9</v>
       </c>
       <c r="K50" t="n">
-        <v>71</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="M50" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="N50" t="n">
-        <v>30.8</v>
+        <v>31.2</v>
       </c>
       <c r="O50" t="n">
-        <v>33.7</v>
+        <v>33.1</v>
       </c>
       <c r="Q50" t="n">
-        <v>20.7</v>
+        <v>21.6</v>
       </c>
       <c r="R50" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="V50" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="W50" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="X50" t="n">
-        <v>19.3</v>
+        <v>21.6</v>
       </c>
       <c r="Y50" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z50" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AA50" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>2.7</v>
+        <v>17.9</v>
       </c>
       <c r="AF50" t="n">
-        <v>233.48</v>
+        <v>235.13</v>
       </c>
       <c r="AG50" t="n">
-        <v>-4.86</v>
+        <v>1.66</v>
       </c>
       <c r="AH50" t="n">
         <v>215</v>
@@ -5374,10 +4492,10 @@
         <v>235</v>
       </c>
       <c r="AK50" t="n">
-        <v>136.6</v>
+        <v>135.66</v>
       </c>
       <c r="AL50" t="n">
-        <v>2.01</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AM50" t="n">
         <v>110</v>
@@ -5386,57 +4504,57 @@
         <v>142</v>
       </c>
       <c r="AP50" t="n">
-        <v>86.25</v>
+        <v>88.27</v>
       </c>
       <c r="AS50" t="n">
-        <v>17.13</v>
+        <v>17.6</v>
       </c>
       <c r="BL50" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B51" t="n">
-        <v>143.4</v>
+        <v>144.9</v>
       </c>
       <c r="C51" t="n">
-        <v>50.9</v>
+        <v>53</v>
       </c>
       <c r="D51" t="n">
-        <v>35.7</v>
+        <v>35.6</v>
       </c>
       <c r="E51" t="n">
-        <v>26.2</v>
+        <v>26</v>
       </c>
       <c r="F51" t="n">
-        <v>4.3</v>
+        <v>2.8</v>
       </c>
       <c r="H51" t="n">
-        <v>22.9</v>
+        <v>24</v>
       </c>
       <c r="I51" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J51" t="n">
-        <v>39.9</v>
+        <v>40.3</v>
       </c>
       <c r="K51" t="n">
-        <v>72.59999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="M51" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="N51" t="n">
-        <v>31.2</v>
+        <v>31.6</v>
       </c>
       <c r="O51" t="n">
-        <v>33.1</v>
+        <v>33.6</v>
       </c>
       <c r="Q51" t="n">
-        <v>21.6</v>
+        <v>21</v>
       </c>
       <c r="R51" t="n">
         <v>0</v>
@@ -5445,40 +4563,22 @@
         <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="V51" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="W51" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="X51" t="n">
-        <v>20.6</v>
+        <v>21</v>
       </c>
       <c r="Y51" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z51" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AA51" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>3.6</v>
+        <v>16.3</v>
       </c>
       <c r="AF51" t="n">
-        <v>235.13</v>
+        <v>234.87</v>
       </c>
       <c r="AG51" t="n">
-        <v>1.66</v>
+        <v>-0.26</v>
       </c>
       <c r="AH51" t="n">
         <v>215</v>
@@ -5487,10 +4587,10 @@
         <v>235</v>
       </c>
       <c r="AK51" t="n">
-        <v>135.66</v>
+        <v>136.33</v>
       </c>
       <c r="AL51" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="AM51" t="n">
         <v>110</v>
@@ -5499,99 +4599,42 @@
         <v>142</v>
       </c>
       <c r="AP51" t="n">
-        <v>88.27</v>
+        <v>87.09</v>
       </c>
       <c r="AS51" t="n">
-        <v>17.6</v>
+        <v>17.31</v>
       </c>
       <c r="BL51" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B52" t="n">
-        <v>144.9</v>
-      </c>
-      <c r="C52" t="n">
-        <v>53</v>
+        <v>132.2</v>
       </c>
       <c r="D52" t="n">
         <v>35.6</v>
       </c>
-      <c r="E52" t="n">
-        <v>26</v>
-      </c>
       <c r="F52" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="H52" t="n">
-        <v>24</v>
-      </c>
-      <c r="I52" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="J52" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="K52" t="n">
-        <v>73.7</v>
-      </c>
-      <c r="M52" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="N52" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="O52" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>21</v>
-      </c>
-      <c r="R52" t="n">
-        <v>0</v>
-      </c>
-      <c r="S52" t="n">
-        <v>0</v>
-      </c>
-      <c r="T52" t="n">
-        <v>21</v>
-      </c>
-      <c r="V52" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="W52" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="X52" t="n">
-        <v>21.1</v>
+        <v>4</v>
       </c>
       <c r="Y52" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z52" t="n">
         <v>19</v>
       </c>
       <c r="AA52" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>2.8</v>
+        <v>13</v>
       </c>
       <c r="AF52" t="n">
-        <v>234.87</v>
+        <v>234.78</v>
       </c>
       <c r="AG52" t="n">
-        <v>-0.26</v>
+        <v>-0.09</v>
       </c>
       <c r="AH52" t="n">
         <v>215</v>
@@ -5599,73 +4642,43 @@
       <c r="AI52" t="n">
         <v>235</v>
       </c>
-      <c r="AK52" t="n">
-        <v>136.33</v>
-      </c>
-      <c r="AL52" t="n">
-        <v>0.67</v>
-      </c>
       <c r="AM52" t="n">
         <v>110</v>
       </c>
       <c r="AN52" t="n">
         <v>142</v>
       </c>
-      <c r="AP52" t="n">
-        <v>87.09</v>
-      </c>
-      <c r="AS52" t="n">
-        <v>17.31</v>
-      </c>
       <c r="BL52" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B53" t="n">
-        <v>132.2</v>
+        <v>137.1</v>
       </c>
       <c r="D53" t="n">
-        <v>35.6</v>
+        <v>35.1</v>
       </c>
       <c r="F53" t="n">
-        <v>4</v>
-      </c>
-      <c r="V53" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="W53" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="X53" t="n">
-        <v>17.4</v>
+        <v>3.3</v>
       </c>
       <c r="Y53" t="n">
         <v>7</v>
       </c>
       <c r="Z53" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AA53" t="n">
-        <v>13</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>4.2</v>
+        <v>10.5</v>
       </c>
       <c r="AF53" t="n">
-        <v>234.78</v>
+        <v>229.75</v>
       </c>
       <c r="AG53" t="n">
-        <v>-0.09</v>
+        <v>-5.03</v>
       </c>
       <c r="AH53" t="n">
         <v>215</v>
@@ -5680,54 +4693,75 @@
         <v>142</v>
       </c>
       <c r="BL53" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B54" t="n">
-        <v>137.1</v>
+        <v>166.2</v>
+      </c>
+      <c r="C54" t="n">
+        <v>72.40000000000001</v>
       </c>
       <c r="D54" t="n">
-        <v>35.1</v>
+        <v>32.7</v>
+      </c>
+      <c r="E54" t="n">
+        <v>28.1</v>
       </c>
       <c r="F54" t="n">
         <v>3.3</v>
       </c>
-      <c r="V54" t="n">
-        <v>11</v>
-      </c>
-      <c r="W54" t="n">
-        <v>22</v>
-      </c>
-      <c r="X54" t="n">
-        <v>16.5</v>
+      <c r="H54" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="I54" t="n">
+        <v>9</v>
+      </c>
+      <c r="J54" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="K54" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="M54" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="N54" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="O54" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="R54" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>23.7</v>
       </c>
       <c r="Y54" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z54" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AA54" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>-5.3</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>0.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AF54" t="n">
-        <v>229.75</v>
+        <v>222.86</v>
       </c>
       <c r="AG54" t="n">
-        <v>-5.03</v>
+        <v>-6.9</v>
       </c>
       <c r="AH54" t="n">
         <v>215</v>
@@ -5735,100 +4769,94 @@
       <c r="AI54" t="n">
         <v>235</v>
       </c>
+      <c r="AK54" t="n">
+        <v>135.42</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>-0.91</v>
+      </c>
       <c r="AM54" t="n">
         <v>110</v>
       </c>
       <c r="AN54" t="n">
         <v>142</v>
       </c>
+      <c r="AP54" t="n">
+        <v>81.98</v>
+      </c>
+      <c r="AS54" t="n">
+        <v>15.01</v>
+      </c>
       <c r="BL54" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B55" t="n">
-        <v>166.2</v>
+        <v>166.3</v>
       </c>
       <c r="C55" t="n">
-        <v>72.40000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="D55" t="n">
-        <v>32.7</v>
+        <v>32.8</v>
       </c>
       <c r="E55" t="n">
-        <v>28.1</v>
+        <v>28.8</v>
       </c>
       <c r="F55" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="H55" t="n">
         <v>23.4</v>
       </c>
       <c r="I55" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J55" t="n">
-        <v>42.1</v>
+        <v>41.2</v>
       </c>
       <c r="K55" t="n">
-        <v>74.5</v>
+        <v>73.8</v>
       </c>
       <c r="M55" t="n">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="N55" t="n">
-        <v>33.7</v>
+        <v>35.4</v>
       </c>
       <c r="O55" t="n">
-        <v>39.3</v>
+        <v>42.6</v>
       </c>
       <c r="Q55" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="R55" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="V55" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="W55" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="X55" t="n">
-        <v>11.8</v>
+        <v>23.9</v>
       </c>
       <c r="Y55" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Z55" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AA55" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>2.5</v>
+        <v>11</v>
       </c>
       <c r="AF55" t="n">
-        <v>222.86</v>
+        <v>218.37</v>
       </c>
       <c r="AG55" t="n">
-        <v>-6.9</v>
+        <v>-4.49</v>
       </c>
       <c r="AH55" t="n">
         <v>215</v>
@@ -5837,10 +4865,10 @@
         <v>235</v>
       </c>
       <c r="AK55" t="n">
-        <v>135.42</v>
+        <v>131.24</v>
       </c>
       <c r="AL55" t="n">
-        <v>-0.91</v>
+        <v>-4.18</v>
       </c>
       <c r="AM55" t="n">
         <v>110</v>
@@ -5849,81 +4877,81 @@
         <v>142</v>
       </c>
       <c r="AP55" t="n">
-        <v>81.98</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="AS55" t="n">
-        <v>15.01</v>
+        <v>12.97</v>
       </c>
       <c r="BL55" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B56" t="n">
-        <v>166.3</v>
+        <v>154.1</v>
       </c>
       <c r="C56" t="n">
-        <v>74.90000000000001</v>
+        <v>65</v>
       </c>
       <c r="D56" t="n">
-        <v>32.8</v>
+        <v>32</v>
       </c>
       <c r="E56" t="n">
-        <v>28.8</v>
+        <v>25.2</v>
       </c>
       <c r="F56" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="H56" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="I56" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="J56" t="n">
-        <v>41.2</v>
+        <v>38.5</v>
       </c>
       <c r="K56" t="n">
-        <v>73.8</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="M56" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="N56" t="n">
-        <v>35.4</v>
+        <v>32.3</v>
       </c>
       <c r="O56" t="n">
-        <v>42.6</v>
+        <v>40.3</v>
       </c>
       <c r="Q56" t="n">
-        <v>23.9</v>
+        <v>21.7</v>
       </c>
       <c r="R56" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T56" t="n">
-        <v>23.9</v>
+        <v>21.7</v>
       </c>
       <c r="Y56" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Z56" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AA56" t="n">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="AF56" t="n">
-        <v>218.37</v>
+        <v>218.04</v>
       </c>
       <c r="AG56" t="n">
-        <v>-4.49</v>
+        <v>-0.33</v>
       </c>
       <c r="AH56" t="n">
         <v>215</v>
@@ -5932,10 +4960,10 @@
         <v>235</v>
       </c>
       <c r="AK56" t="n">
-        <v>131.24</v>
+        <v>129.21</v>
       </c>
       <c r="AL56" t="n">
-        <v>-4.18</v>
+        <v>-2.03</v>
       </c>
       <c r="AM56" t="n">
         <v>110</v>
@@ -5944,81 +4972,81 @@
         <v>142</v>
       </c>
       <c r="AP56" t="n">
-        <v>79.98999999999999</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="AS56" t="n">
-        <v>12.97</v>
+        <v>15.23</v>
       </c>
       <c r="BL56" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B57" t="n">
-        <v>154.1</v>
+        <v>148.8</v>
       </c>
       <c r="C57" t="n">
-        <v>65</v>
+        <v>57.6</v>
       </c>
       <c r="D57" t="n">
-        <v>32</v>
+        <v>32.7</v>
       </c>
       <c r="E57" t="n">
-        <v>25.2</v>
+        <v>26.3</v>
       </c>
       <c r="F57" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="H57" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="I57" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="J57" t="n">
-        <v>38.5</v>
+        <v>41.6</v>
       </c>
       <c r="K57" t="n">
-        <v>70.90000000000001</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="M57" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="N57" t="n">
-        <v>32.3</v>
+        <v>35</v>
       </c>
       <c r="O57" t="n">
-        <v>40.3</v>
+        <v>42.4</v>
       </c>
       <c r="Q57" t="n">
         <v>21.7</v>
       </c>
       <c r="R57" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="S57" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="T57" t="n">
         <v>21.7</v>
       </c>
       <c r="Y57" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z57" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA57" t="n">
-        <v>14.5</v>
+        <v>15.6</v>
       </c>
       <c r="AF57" t="n">
-        <v>218.04</v>
+        <v>220.84</v>
       </c>
       <c r="AG57" t="n">
-        <v>-0.33</v>
+        <v>2.8</v>
       </c>
       <c r="AH57" t="n">
         <v>215</v>
@@ -6027,10 +5055,10 @@
         <v>235</v>
       </c>
       <c r="AK57" t="n">
-        <v>129.21</v>
+        <v>129.07</v>
       </c>
       <c r="AL57" t="n">
-        <v>-2.03</v>
+        <v>-0.14</v>
       </c>
       <c r="AM57" t="n">
         <v>110</v>
@@ -6039,81 +5067,81 @@
         <v>142</v>
       </c>
       <c r="AP57" t="n">
-        <v>82.90000000000001</v>
+        <v>85.52</v>
       </c>
       <c r="AS57" t="n">
-        <v>15.23</v>
+        <v>15.82</v>
       </c>
       <c r="BL57" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B58" t="n">
-        <v>148.8</v>
+        <v>146.8</v>
       </c>
       <c r="C58" t="n">
-        <v>57.6</v>
+        <v>52.8</v>
       </c>
       <c r="D58" t="n">
-        <v>32.7</v>
+        <v>33.6</v>
       </c>
       <c r="E58" t="n">
-        <v>26.3</v>
+        <v>28.9</v>
       </c>
       <c r="F58" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="H58" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="I58" t="n">
-        <v>8.9</v>
+        <v>9.1</v>
       </c>
       <c r="J58" t="n">
-        <v>41.6</v>
+        <v>40.8</v>
       </c>
       <c r="K58" t="n">
-        <v>74.09999999999999</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="M58" t="n">
-        <v>7.4</v>
+        <v>5.6</v>
       </c>
       <c r="N58" t="n">
-        <v>35</v>
+        <v>33.1</v>
       </c>
       <c r="O58" t="n">
-        <v>42.4</v>
+        <v>38.7</v>
       </c>
       <c r="Q58" t="n">
-        <v>21.7</v>
+        <v>22</v>
       </c>
       <c r="R58" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>21.7</v>
+        <v>22</v>
       </c>
       <c r="Y58" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z58" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA58" t="n">
-        <v>15.6</v>
+        <v>16.1</v>
       </c>
       <c r="AF58" t="n">
-        <v>220.84</v>
+        <v>225.87</v>
       </c>
       <c r="AG58" t="n">
-        <v>2.8</v>
+        <v>5.03</v>
       </c>
       <c r="AH58" t="n">
         <v>215</v>
@@ -6122,10 +5150,10 @@
         <v>235</v>
       </c>
       <c r="AK58" t="n">
-        <v>129.07</v>
+        <v>130.73</v>
       </c>
       <c r="AL58" t="n">
-        <v>-0.14</v>
+        <v>1.66</v>
       </c>
       <c r="AM58" t="n">
         <v>110</v>
@@ -6134,81 +5162,36 @@
         <v>142</v>
       </c>
       <c r="AP58" t="n">
-        <v>85.52</v>
+        <v>88.2</v>
       </c>
       <c r="AS58" t="n">
-        <v>15.82</v>
+        <v>15.76</v>
       </c>
       <c r="BL58" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B59" t="n">
-        <v>146.8</v>
-      </c>
-      <c r="C59" t="n">
-        <v>52.8</v>
+        <v>133.9</v>
       </c>
       <c r="D59" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="E59" t="n">
-        <v>28.9</v>
+        <v>34.7</v>
       </c>
       <c r="F59" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="H59" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="I59" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="J59" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="K59" t="n">
-        <v>73.59999999999999</v>
-      </c>
-      <c r="M59" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="N59" t="n">
-        <v>33.1</v>
-      </c>
-      <c r="O59" t="n">
-        <v>38.7</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>22</v>
-      </c>
-      <c r="R59" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="S59" t="n">
-        <v>0</v>
-      </c>
-      <c r="T59" t="n">
-        <v>22</v>
+        <v>3.3</v>
       </c>
       <c r="Y59" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z59" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AA59" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="AF59" t="n">
-        <v>225.87</v>
-      </c>
-      <c r="AG59" t="n">
-        <v>5.03</v>
+        <v>15</v>
       </c>
       <c r="AH59" t="n">
         <v>215</v>
@@ -6216,49 +5199,37 @@
       <c r="AI59" t="n">
         <v>235</v>
       </c>
-      <c r="AK59" t="n">
-        <v>130.73</v>
-      </c>
-      <c r="AL59" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AM59" t="n">
         <v>110</v>
       </c>
       <c r="AN59" t="n">
         <v>142</v>
       </c>
-      <c r="AP59" t="n">
-        <v>88.2</v>
-      </c>
-      <c r="AS59" t="n">
-        <v>15.76</v>
-      </c>
       <c r="BL59" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B60" t="n">
-        <v>133.9</v>
+        <v>137.5</v>
       </c>
       <c r="D60" t="n">
-        <v>34.7</v>
+        <v>32.8</v>
       </c>
       <c r="F60" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="Y60" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z60" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="AA60" t="n">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="AH60" t="n">
         <v>215</v>
@@ -6273,30 +5244,30 @@
         <v>142</v>
       </c>
       <c r="BL60" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B61" t="n">
-        <v>137.5</v>
+        <v>141</v>
       </c>
       <c r="D61" t="n">
-        <v>32.8</v>
+        <v>31.9</v>
       </c>
       <c r="F61" t="n">
         <v>2.3</v>
       </c>
       <c r="Y61" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="Z61" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA61" t="n">
-        <v>10.5</v>
+        <v>7.5</v>
       </c>
       <c r="AH61" t="n">
         <v>215</v>
@@ -6311,30 +5282,30 @@
         <v>142</v>
       </c>
       <c r="BL61" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B62" t="n">
-        <v>141</v>
+        <v>150.3</v>
       </c>
       <c r="D62" t="n">
-        <v>31.9</v>
+        <v>33.3</v>
       </c>
       <c r="F62" t="n">
         <v>2.3</v>
       </c>
       <c r="Y62" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Z62" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AA62" t="n">
-        <v>7.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH62" t="n">
         <v>215</v>
@@ -6349,7 +5320,7 @@
         <v>142</v>
       </c>
       <c r="BL62" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -628,70 +628,55 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B2" t="n">
-        <v>158.9</v>
-      </c>
-      <c r="C2" t="n">
-        <v>58.8</v>
+        <v>136.7</v>
       </c>
       <c r="D2" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.4</v>
+        <v>30.7</v>
       </c>
       <c r="F2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="H2" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="I2" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="J2" t="n">
-        <v>41</v>
+        <v>7.5</v>
       </c>
       <c r="K2" t="n">
-        <v>75.90000000000001</v>
-      </c>
-      <c r="M2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N2" t="n">
-        <v>37.8</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="S2" t="n">
-        <v>15</v>
-      </c>
-      <c r="T2" t="n">
-        <v>21.5</v>
+        <v>39.2</v>
+      </c>
+      <c r="V2" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="W2" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="X2" t="n">
+        <v>26.6</v>
       </c>
       <c r="Y2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Z2" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AA2" t="n">
-        <v>19.3</v>
+        <v>20.5</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>4.7</v>
       </c>
       <c r="AF2" t="n">
-        <v>232.31</v>
+        <v>235.4</v>
       </c>
       <c r="AG2" t="n">
-        <v>9.67</v>
+        <v>3.09</v>
       </c>
       <c r="AH2" t="n">
         <v>215</v>
@@ -700,10 +685,10 @@
         <v>235</v>
       </c>
       <c r="AK2" t="n">
-        <v>134.44</v>
+        <v>137.5</v>
       </c>
       <c r="AL2" t="n">
-        <v>5.16</v>
+        <v>3.06</v>
       </c>
       <c r="AM2" t="n">
         <v>110</v>
@@ -711,49 +696,61 @@
       <c r="AN2" t="n">
         <v>142</v>
       </c>
-      <c r="AP2" t="n">
-        <v>91.73999999999999</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>17.07</v>
-      </c>
       <c r="BL2" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="B3" t="n">
-        <v>136.7</v>
+        <v>138.5</v>
       </c>
       <c r="D3" t="n">
-        <v>30.7</v>
+        <v>31.7</v>
       </c>
       <c r="F3" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="K3" t="n">
-        <v>92.59999999999999</v>
+        <v>91</v>
       </c>
       <c r="O3" t="n">
-        <v>39.2</v>
+        <v>37.8</v>
+      </c>
+      <c r="V3" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="W3" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="X3" t="n">
+        <v>17.9</v>
       </c>
       <c r="Y3" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="Z3" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AA3" t="n">
-        <v>20.5</v>
+        <v>15.5</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.7</v>
       </c>
       <c r="AF3" t="n">
-        <v>235.4</v>
+        <v>231.99</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.09</v>
+        <v>-3.41</v>
       </c>
       <c r="AH3" t="n">
         <v>215</v>
@@ -762,10 +759,10 @@
         <v>235</v>
       </c>
       <c r="AK3" t="n">
-        <v>137.5</v>
+        <v>136.12</v>
       </c>
       <c r="AL3" t="n">
-        <v>3.06</v>
+        <v>-1.38</v>
       </c>
       <c r="AM3" t="n">
         <v>110</v>
@@ -774,42 +771,93 @@
         <v>142</v>
       </c>
       <c r="BL3" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B4" t="n">
-        <v>138.5</v>
+        <v>161.1</v>
+      </c>
+      <c r="C4" t="n">
+        <v>67</v>
       </c>
       <c r="D4" t="n">
-        <v>31.7</v>
+        <v>31.9</v>
+      </c>
+      <c r="E4" t="n">
+        <v>31.5</v>
       </c>
       <c r="F4" t="n">
-        <v>7</v>
+        <v>7.7</v>
+      </c>
+      <c r="H4" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J4" t="n">
+        <v>41.1</v>
       </c>
       <c r="K4" t="n">
-        <v>91</v>
+        <v>75.59999999999999</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="N4" t="n">
+        <v>35</v>
       </c>
       <c r="O4" t="n">
-        <v>37.8</v>
+        <v>37.2</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T4" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="V4" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="W4" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="X4" t="n">
+        <v>16.7</v>
       </c>
       <c r="Y4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="Z4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AA4" t="n">
-        <v>15.5</v>
+        <v>11.1</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>-0.3</v>
       </c>
       <c r="AF4" t="n">
-        <v>231.99</v>
+        <v>225.51</v>
       </c>
       <c r="AG4" t="n">
-        <v>-3.41</v>
+        <v>-6.48</v>
       </c>
       <c r="AH4" t="n">
         <v>215</v>
@@ -818,10 +866,10 @@
         <v>235</v>
       </c>
       <c r="AK4" t="n">
-        <v>136.12</v>
+        <v>133.83</v>
       </c>
       <c r="AL4" t="n">
-        <v>-1.38</v>
+        <v>-2.29</v>
       </c>
       <c r="AM4" t="n">
         <v>110</v>
@@ -829,76 +877,100 @@
       <c r="AN4" t="n">
         <v>142</v>
       </c>
+      <c r="AP4" t="n">
+        <v>82.93000000000001</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>15.73</v>
+      </c>
       <c r="BL4" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B5" t="n">
-        <v>161.1</v>
+        <v>176.4</v>
       </c>
       <c r="C5" t="n">
-        <v>67</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>31.9</v>
+        <v>32.7</v>
       </c>
       <c r="E5" t="n">
-        <v>31.5</v>
+        <v>35</v>
       </c>
       <c r="F5" t="n">
-        <v>7.7</v>
+        <v>6.8</v>
       </c>
       <c r="H5" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="I5" t="n">
         <v>11.4</v>
       </c>
       <c r="J5" t="n">
-        <v>41.1</v>
+        <v>41.5</v>
       </c>
       <c r="K5" t="n">
-        <v>75.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="M5" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="N5" t="n">
-        <v>35</v>
+        <v>36.4</v>
       </c>
       <c r="O5" t="n">
-        <v>37.2</v>
+        <v>39.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>20.5</v>
+        <v>22.3</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="T5" t="n">
-        <v>20.5</v>
+        <v>22.3</v>
+      </c>
+      <c r="V5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="W5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="X5" t="n">
+        <v>13.5</v>
       </c>
       <c r="Y5" t="n">
         <v>9</v>
       </c>
       <c r="Z5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA5" t="n">
-        <v>11.1</v>
+        <v>11.6</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>-5.6</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-1.3</v>
       </c>
       <c r="AF5" t="n">
-        <v>225.51</v>
+        <v>220.92</v>
       </c>
       <c r="AG5" t="n">
-        <v>-6.48</v>
+        <v>-4.59</v>
       </c>
       <c r="AH5" t="n">
         <v>215</v>
@@ -907,10 +979,10 @@
         <v>235</v>
       </c>
       <c r="AK5" t="n">
-        <v>133.83</v>
+        <v>131.85</v>
       </c>
       <c r="AL5" t="n">
-        <v>-2.29</v>
+        <v>-1.98</v>
       </c>
       <c r="AM5" t="n">
         <v>110</v>
@@ -919,81 +991,99 @@
         <v>142</v>
       </c>
       <c r="AP5" t="n">
-        <v>82.93000000000001</v>
+        <v>79.75</v>
       </c>
       <c r="AS5" t="n">
-        <v>15.73</v>
+        <v>15.49</v>
       </c>
       <c r="BL5" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B6" t="n">
-        <v>176.4</v>
+        <v>181</v>
       </c>
       <c r="C6" t="n">
-        <v>77.09999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="D6" t="n">
-        <v>32.7</v>
+        <v>33</v>
       </c>
       <c r="E6" t="n">
-        <v>35</v>
+        <v>35.1</v>
       </c>
       <c r="F6" t="n">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="H6" t="n">
-        <v>23.2</v>
+        <v>22.8</v>
       </c>
       <c r="I6" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="K6" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N6" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="O6" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="T6" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="V6" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="W6" t="n">
+        <v>13</v>
+      </c>
+      <c r="X6" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA6" t="n">
         <v>11.4</v>
       </c>
-      <c r="J6" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="K6" t="n">
-        <v>76</v>
-      </c>
-      <c r="M6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N6" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="O6" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>14</v>
-      </c>
-      <c r="T6" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>11.6</v>
+      <c r="AB6" t="n">
+        <v>-6.1</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-0.9</v>
       </c>
       <c r="AF6" t="n">
         <v>220.92</v>
       </c>
       <c r="AG6" t="n">
-        <v>-4.59</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
         <v>215</v>
@@ -1002,10 +1092,10 @@
         <v>235</v>
       </c>
       <c r="AK6" t="n">
-        <v>131.85</v>
+        <v>130.06</v>
       </c>
       <c r="AL6" t="n">
-        <v>-1.98</v>
+        <v>-1.79</v>
       </c>
       <c r="AM6" t="n">
         <v>110</v>
@@ -1014,81 +1104,99 @@
         <v>142</v>
       </c>
       <c r="AP6" t="n">
-        <v>79.75</v>
+        <v>79.94</v>
       </c>
       <c r="AS6" t="n">
-        <v>15.49</v>
+        <v>14.93</v>
       </c>
       <c r="BL6" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B7" t="n">
-        <v>181</v>
+        <v>179.6</v>
       </c>
       <c r="C7" t="n">
-        <v>80.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>33</v>
+        <v>30.3</v>
       </c>
       <c r="E7" t="n">
-        <v>35.1</v>
+        <v>31.1</v>
       </c>
       <c r="F7" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="H7" t="n">
-        <v>22.8</v>
+        <v>21.5</v>
       </c>
       <c r="I7" t="n">
-        <v>11.2</v>
+        <v>10.8</v>
       </c>
       <c r="J7" t="n">
-        <v>41.9</v>
+        <v>42.3</v>
       </c>
       <c r="K7" t="n">
-        <v>75.90000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>2.9</v>
+        <v>4.3</v>
       </c>
       <c r="N7" t="n">
-        <v>36.9</v>
+        <v>37.1</v>
       </c>
       <c r="O7" t="n">
-        <v>39.8</v>
+        <v>41.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="R7" t="n">
+        <v>2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="V7" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="W7" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="X7" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AD7" t="n">
         <v>0.5</v>
       </c>
-      <c r="S7" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="T7" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>11.4</v>
-      </c>
       <c r="AF7" t="n">
-        <v>220.92</v>
+        <v>216.02</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AH7" t="n">
         <v>215</v>
@@ -1097,10 +1205,10 @@
         <v>235</v>
       </c>
       <c r="AK7" t="n">
-        <v>130.06</v>
+        <v>127.85</v>
       </c>
       <c r="AL7" t="n">
-        <v>-1.79</v>
+        <v>-2.21</v>
       </c>
       <c r="AM7" t="n">
         <v>110</v>
@@ -1109,81 +1217,99 @@
         <v>142</v>
       </c>
       <c r="AP7" t="n">
-        <v>79.94</v>
+        <v>82.2</v>
       </c>
       <c r="AS7" t="n">
-        <v>14.93</v>
+        <v>15.16</v>
       </c>
       <c r="BL7" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B8" t="n">
-        <v>179.6</v>
+        <v>170.4</v>
       </c>
       <c r="C8" t="n">
-        <v>81.90000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="D8" t="n">
-        <v>30.3</v>
+        <v>29.8</v>
       </c>
       <c r="E8" t="n">
-        <v>31.1</v>
+        <v>29.7</v>
       </c>
       <c r="F8" t="n">
-        <v>6.8</v>
+        <v>6.3</v>
       </c>
       <c r="H8" t="n">
-        <v>21.5</v>
+        <v>22.5</v>
       </c>
       <c r="I8" t="n">
-        <v>10.8</v>
+        <v>11.2</v>
       </c>
       <c r="J8" t="n">
-        <v>42.3</v>
+        <v>41.4</v>
       </c>
       <c r="K8" t="n">
-        <v>74.59999999999999</v>
+        <v>75</v>
       </c>
       <c r="M8" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="N8" t="n">
-        <v>37.1</v>
+        <v>36.6</v>
       </c>
       <c r="O8" t="n">
-        <v>41.4</v>
+        <v>41.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>22.6</v>
+        <v>23.3</v>
       </c>
       <c r="R8" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="S8" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="T8" t="n">
-        <v>22.6</v>
+        <v>23.3</v>
+      </c>
+      <c r="V8" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W8" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="X8" t="n">
+        <v>12.6</v>
       </c>
       <c r="Y8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z8" t="n">
         <v>13</v>
       </c>
       <c r="AA8" t="n">
-        <v>11.1</v>
+        <v>12.7</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>4.7</v>
       </c>
       <c r="AF8" t="n">
         <v>216.02</v>
       </c>
       <c r="AG8" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
         <v>215</v>
@@ -1192,10 +1318,10 @@
         <v>235</v>
       </c>
       <c r="AK8" t="n">
-        <v>127.85</v>
+        <v>128.54</v>
       </c>
       <c r="AL8" t="n">
-        <v>-2.21</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AM8" t="n">
         <v>110</v>
@@ -1204,81 +1330,66 @@
         <v>142</v>
       </c>
       <c r="AP8" t="n">
-        <v>82.2</v>
+        <v>84.73</v>
       </c>
       <c r="AS8" t="n">
-        <v>15.16</v>
+        <v>15.34</v>
       </c>
       <c r="BL8" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B9" t="n">
-        <v>170.4</v>
-      </c>
-      <c r="C9" t="n">
-        <v>78.5</v>
+        <v>156</v>
       </c>
       <c r="D9" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="E9" t="n">
-        <v>29.7</v>
+        <v>30.1</v>
       </c>
       <c r="F9" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="H9" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="I9" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="J9" t="n">
-        <v>41.4</v>
+        <v>6.8</v>
       </c>
       <c r="K9" t="n">
-        <v>75</v>
-      </c>
-      <c r="M9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="N9" t="n">
-        <v>36.6</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S9" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="T9" t="n">
-        <v>23.3</v>
+        <v>39.2</v>
+      </c>
+      <c r="V9" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W9" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="X9" t="n">
+        <v>14</v>
       </c>
       <c r="Y9" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Z9" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA9" t="n">
-        <v>12.7</v>
+        <v>13.5</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2.4</v>
       </c>
       <c r="AF9" t="n">
-        <v>216.02</v>
+        <v>224.53</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH9" t="n">
         <v>215</v>
@@ -1287,10 +1398,10 @@
         <v>235</v>
       </c>
       <c r="AK9" t="n">
-        <v>128.54</v>
+        <v>130.92</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.6899999999999999</v>
+        <v>2.38</v>
       </c>
       <c r="AM9" t="n">
         <v>110</v>
@@ -1298,49 +1409,61 @@
       <c r="AN9" t="n">
         <v>142</v>
       </c>
-      <c r="AP9" t="n">
-        <v>84.73</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>15.34</v>
-      </c>
       <c r="BL9" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B10" t="n">
-        <v>156</v>
+        <v>147.8</v>
       </c>
       <c r="D10" t="n">
-        <v>30.1</v>
+        <v>32</v>
       </c>
       <c r="F10" t="n">
         <v>6.8</v>
       </c>
       <c r="K10" t="n">
-        <v>95.90000000000001</v>
+        <v>96.5</v>
       </c>
       <c r="O10" t="n">
-        <v>39.2</v>
+        <v>39.3</v>
+      </c>
+      <c r="V10" t="n">
+        <v>8</v>
+      </c>
+      <c r="W10" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="X10" t="n">
+        <v>15.2</v>
       </c>
       <c r="Y10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA10" t="n">
         <v>13.5</v>
       </c>
+      <c r="AB10" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>2.1</v>
+      </c>
       <c r="AF10" t="n">
-        <v>224.53</v>
+        <v>230.27</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.32</v>
+        <v>5.74</v>
       </c>
       <c r="AH10" t="n">
         <v>215</v>
@@ -1349,10 +1472,10 @@
         <v>235</v>
       </c>
       <c r="AK10" t="n">
-        <v>130.92</v>
+        <v>132.76</v>
       </c>
       <c r="AL10" t="n">
-        <v>2.38</v>
+        <v>1.84</v>
       </c>
       <c r="AM10" t="n">
         <v>110</v>
@@ -1361,42 +1484,93 @@
         <v>142</v>
       </c>
       <c r="BL10" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="B11" t="n">
-        <v>147.8</v>
+        <v>149.1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>60</v>
       </c>
       <c r="D11" t="n">
-        <v>32</v>
+        <v>29</v>
+      </c>
+      <c r="E11" t="n">
+        <v>25.9</v>
       </c>
       <c r="F11" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
+      </c>
+      <c r="H11" t="n">
+        <v>24</v>
+      </c>
+      <c r="I11" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="J11" t="n">
+        <v>38.8</v>
       </c>
       <c r="K11" t="n">
-        <v>96.5</v>
+        <v>74.5</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N11" t="n">
+        <v>36.7</v>
       </c>
       <c r="O11" t="n">
-        <v>39.3</v>
+        <v>40.1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>7</v>
+      </c>
+      <c r="T11" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="V11" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="W11" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="X11" t="n">
+        <v>17.4</v>
       </c>
       <c r="Y11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z11" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AA11" t="n">
-        <v>13.5</v>
+        <v>15.7</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>-0.1</v>
       </c>
       <c r="AF11" t="n">
-        <v>230.27</v>
+        <v>237.43</v>
       </c>
       <c r="AG11" t="n">
-        <v>5.74</v>
+        <v>7.16</v>
       </c>
       <c r="AH11" t="n">
         <v>215</v>
@@ -1405,10 +1579,10 @@
         <v>235</v>
       </c>
       <c r="AK11" t="n">
-        <v>132.76</v>
+        <v>134.95</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.84</v>
+        <v>2.19</v>
       </c>
       <c r="AM11" t="n">
         <v>110</v>
@@ -1416,76 +1590,67 @@
       <c r="AN11" t="n">
         <v>142</v>
       </c>
+      <c r="AP11" t="n">
+        <v>91.28</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>16.95</v>
+      </c>
       <c r="BL11" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="B12" t="n">
-        <v>149.1</v>
-      </c>
-      <c r="C12" t="n">
-        <v>60</v>
+        <v>143.9</v>
       </c>
       <c r="D12" t="n">
-        <v>29</v>
-      </c>
-      <c r="E12" t="n">
-        <v>25.9</v>
+        <v>32.9</v>
       </c>
       <c r="F12" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="H12" t="n">
-        <v>24</v>
-      </c>
-      <c r="I12" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="J12" t="n">
-        <v>38.8</v>
+        <v>6.8</v>
       </c>
       <c r="K12" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="M12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N12" t="n">
-        <v>36.7</v>
+        <v>96.2</v>
       </c>
       <c r="O12" t="n">
-        <v>40.1</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>7</v>
-      </c>
-      <c r="T12" t="n">
-        <v>21.7</v>
+        <v>37.9</v>
+      </c>
+      <c r="V12" t="n">
+        <v>10</v>
+      </c>
+      <c r="W12" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="X12" t="n">
+        <v>17.8</v>
       </c>
       <c r="Y12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AA12" t="n">
-        <v>15.7</v>
+        <v>16</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.9</v>
       </c>
       <c r="AF12" t="n">
-        <v>237.43</v>
+        <v>236.14</v>
       </c>
       <c r="AG12" t="n">
-        <v>7.16</v>
+        <v>-1.29</v>
       </c>
       <c r="AH12" t="n">
         <v>215</v>
@@ -1494,10 +1659,10 @@
         <v>235</v>
       </c>
       <c r="AK12" t="n">
-        <v>134.95</v>
+        <v>136.28</v>
       </c>
       <c r="AL12" t="n">
-        <v>2.19</v>
+        <v>1.33</v>
       </c>
       <c r="AM12" t="n">
         <v>110</v>
@@ -1505,49 +1670,94 @@
       <c r="AN12" t="n">
         <v>142</v>
       </c>
-      <c r="AP12" t="n">
-        <v>91.28</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>16.95</v>
-      </c>
       <c r="BL12" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B13" t="n">
-        <v>143.9</v>
+        <v>166.4</v>
+      </c>
+      <c r="C13" t="n">
+        <v>63.7</v>
       </c>
       <c r="D13" t="n">
-        <v>32.9</v>
+        <v>34.5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>36.4</v>
       </c>
       <c r="F13" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
+      </c>
+      <c r="H13" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="I13" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="J13" t="n">
+        <v>39.9</v>
       </c>
       <c r="K13" t="n">
-        <v>96.2</v>
+        <v>75.2</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>35.9</v>
       </c>
       <c r="O13" t="n">
-        <v>37.9</v>
+        <v>39</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="S13" t="n">
+        <v>6</v>
+      </c>
+      <c r="T13" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="V13" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="W13" t="n">
+        <v>27</v>
+      </c>
+      <c r="X13" t="n">
+        <v>19.4</v>
       </c>
       <c r="Y13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z13" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AA13" t="n">
-        <v>16</v>
+        <v>14.4</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-0.4</v>
       </c>
       <c r="AF13" t="n">
-        <v>236.14</v>
+        <v>236.13</v>
       </c>
       <c r="AG13" t="n">
-        <v>-1.29</v>
+        <v>-0.01</v>
       </c>
       <c r="AH13" t="n">
         <v>215</v>
@@ -1556,10 +1766,10 @@
         <v>235</v>
       </c>
       <c r="AK13" t="n">
-        <v>136.28</v>
+        <v>134.54</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.33</v>
+        <v>-1.74</v>
       </c>
       <c r="AM13" t="n">
         <v>110</v>
@@ -1567,76 +1777,100 @@
       <c r="AN13" t="n">
         <v>142</v>
       </c>
+      <c r="AP13" t="n">
+        <v>82.27</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>16.28</v>
+      </c>
       <c r="BL13" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B14" t="n">
-        <v>166.4</v>
+        <v>172.9</v>
       </c>
       <c r="C14" t="n">
-        <v>63.7</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>34.5</v>
+        <v>34.9</v>
       </c>
       <c r="E14" t="n">
-        <v>36.4</v>
+        <v>35.2</v>
       </c>
       <c r="F14" t="n">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="H14" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="I14" t="n">
-        <v>11.6</v>
+        <v>11.3</v>
       </c>
       <c r="J14" t="n">
-        <v>39.9</v>
+        <v>41.7</v>
       </c>
       <c r="K14" t="n">
-        <v>75.2</v>
+        <v>76.7</v>
       </c>
       <c r="M14" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="N14" t="n">
-        <v>35.9</v>
+        <v>34.8</v>
       </c>
       <c r="O14" t="n">
-        <v>39</v>
+        <v>37.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>20.3</v>
+        <v>19</v>
       </c>
       <c r="R14" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T14" t="n">
-        <v>20.3</v>
+        <v>19</v>
+      </c>
+      <c r="V14" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="W14" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="X14" t="n">
+        <v>16.6</v>
       </c>
       <c r="Y14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Z14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA14" t="n">
-        <v>14.4</v>
+        <v>12.5</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-4.9</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>-0.7</v>
       </c>
       <c r="AF14" t="n">
-        <v>236.13</v>
+        <v>218.6</v>
       </c>
       <c r="AG14" t="n">
-        <v>-0.01</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="AH14" t="n">
         <v>215</v>
@@ -1645,10 +1879,10 @@
         <v>235</v>
       </c>
       <c r="AK14" t="n">
-        <v>134.54</v>
+        <v>130.39</v>
       </c>
       <c r="AL14" t="n">
-        <v>-1.74</v>
+        <v>-4.15</v>
       </c>
       <c r="AM14" t="n">
         <v>110</v>
@@ -1657,81 +1891,99 @@
         <v>142</v>
       </c>
       <c r="AP14" t="n">
-        <v>82.27</v>
+        <v>78.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>16.28</v>
+        <v>15.79</v>
       </c>
       <c r="BL14" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B15" t="n">
-        <v>172.9</v>
+        <v>157.5</v>
       </c>
       <c r="C15" t="n">
-        <v>67.59999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="D15" t="n">
-        <v>34.9</v>
+        <v>33.2</v>
       </c>
       <c r="E15" t="n">
-        <v>35.2</v>
+        <v>27.7</v>
       </c>
       <c r="F15" t="n">
-        <v>7.3</v>
+        <v>3.6</v>
       </c>
       <c r="H15" t="n">
-        <v>23.6</v>
+        <v>23.4</v>
       </c>
       <c r="I15" t="n">
         <v>11.3</v>
       </c>
       <c r="J15" t="n">
-        <v>41.7</v>
+        <v>41.4</v>
       </c>
       <c r="K15" t="n">
-        <v>76.7</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="N15" t="n">
-        <v>34.8</v>
+        <v>34.9</v>
       </c>
       <c r="O15" t="n">
-        <v>37.2</v>
+        <v>37.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>19</v>
+        <v>21.6</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T15" t="n">
-        <v>19</v>
+        <v>21.6</v>
+      </c>
+      <c r="V15" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="W15" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>19.1</v>
       </c>
       <c r="Y15" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z15" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AA15" t="n">
-        <v>12.5</v>
+        <v>13.6</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.5</v>
       </c>
       <c r="AF15" t="n">
-        <v>218.6</v>
+        <v>218.84</v>
       </c>
       <c r="AG15" t="n">
-        <v>-9.380000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="AH15" t="n">
         <v>215</v>
@@ -1740,10 +1992,10 @@
         <v>235</v>
       </c>
       <c r="AK15" t="n">
-        <v>130.39</v>
+        <v>133.09</v>
       </c>
       <c r="AL15" t="n">
-        <v>-4.15</v>
+        <v>2.7</v>
       </c>
       <c r="AM15" t="n">
         <v>110</v>
@@ -1752,81 +2004,66 @@
         <v>142</v>
       </c>
       <c r="AP15" t="n">
-        <v>78.5</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="AS15" t="n">
-        <v>15.79</v>
+        <v>15.63</v>
       </c>
       <c r="BL15" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B16" t="n">
-        <v>157.5</v>
-      </c>
-      <c r="C16" t="n">
-        <v>68.5</v>
+        <v>137.6</v>
       </c>
       <c r="D16" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="E16" t="n">
-        <v>27.7</v>
+        <v>35</v>
       </c>
       <c r="F16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H16" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="I16" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J16" t="n">
-        <v>41.4</v>
+        <v>6.5</v>
       </c>
       <c r="K16" t="n">
-        <v>76.09999999999999</v>
-      </c>
-      <c r="M16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="N16" t="n">
-        <v>34.9</v>
+        <v>96.7</v>
       </c>
       <c r="O16" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>9</v>
-      </c>
-      <c r="T16" t="n">
-        <v>21.6</v>
+        <v>35.1</v>
+      </c>
+      <c r="V16" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="W16" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="X16" t="n">
+        <v>19</v>
       </c>
       <c r="Y16" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Z16" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AA16" t="n">
-        <v>13.6</v>
+        <v>17.5</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.8</v>
       </c>
       <c r="AF16" t="n">
-        <v>218.84</v>
+        <v>221.78</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.25</v>
+        <v>2.94</v>
       </c>
       <c r="AH16" t="n">
         <v>215</v>
@@ -1835,10 +2072,10 @@
         <v>235</v>
       </c>
       <c r="AK16" t="n">
-        <v>133.09</v>
+        <v>138.76</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.7</v>
+        <v>5.67</v>
       </c>
       <c r="AM16" t="n">
         <v>110</v>
@@ -1846,49 +2083,61 @@
       <c r="AN16" t="n">
         <v>142</v>
       </c>
-      <c r="AP16" t="n">
-        <v>83.09999999999999</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>15.63</v>
-      </c>
       <c r="BL16" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B17" t="n">
-        <v>137.6</v>
+        <v>132.5</v>
       </c>
       <c r="D17" t="n">
-        <v>35</v>
+        <v>33.6</v>
       </c>
       <c r="F17" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="K17" t="n">
-        <v>96.7</v>
+        <v>97.8</v>
       </c>
       <c r="O17" t="n">
-        <v>35.1</v>
+        <v>31.6</v>
+      </c>
+      <c r="V17" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="W17" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="X17" t="n">
+        <v>19.8</v>
       </c>
       <c r="Y17" t="n">
         <v>14</v>
       </c>
       <c r="Z17" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AA17" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2.1</v>
       </c>
       <c r="AF17" t="n">
-        <v>221.78</v>
+        <v>224.78</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="AH17" t="n">
         <v>215</v>
@@ -1897,10 +2146,10 @@
         <v>235</v>
       </c>
       <c r="AK17" t="n">
-        <v>138.76</v>
+        <v>143.55</v>
       </c>
       <c r="AL17" t="n">
-        <v>5.67</v>
+        <v>4.79</v>
       </c>
       <c r="AM17" t="n">
         <v>110</v>
@@ -1909,42 +2158,93 @@
         <v>142</v>
       </c>
       <c r="BL17" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B18" t="n">
-        <v>132.5</v>
+        <v>137.2</v>
+      </c>
+      <c r="C18" t="n">
+        <v>56.3</v>
       </c>
       <c r="D18" t="n">
-        <v>33.6</v>
+        <v>32.1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>21.2</v>
       </c>
       <c r="F18" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
+      </c>
+      <c r="H18" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="I18" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="J18" t="n">
+        <v>40.4</v>
       </c>
       <c r="K18" t="n">
-        <v>97.8</v>
+        <v>75.7</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N18" t="n">
+        <v>29</v>
       </c>
       <c r="O18" t="n">
-        <v>31.6</v>
+        <v>32.6</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="V18" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="W18" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="X18" t="n">
+        <v>17.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Z18" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AA18" t="n">
-        <v>16.5</v>
+        <v>15.4</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>3.2</v>
       </c>
       <c r="AF18" t="n">
-        <v>224.78</v>
+        <v>232.22</v>
       </c>
       <c r="AG18" t="n">
-        <v>3</v>
+        <v>7.43</v>
       </c>
       <c r="AH18" t="n">
         <v>215</v>
@@ -1953,10 +2253,10 @@
         <v>235</v>
       </c>
       <c r="AK18" t="n">
-        <v>143.55</v>
+        <v>143.61</v>
       </c>
       <c r="AL18" t="n">
-        <v>4.79</v>
+        <v>0.06</v>
       </c>
       <c r="AM18" t="n">
         <v>110</v>
@@ -1964,52 +2264,58 @@
       <c r="AN18" t="n">
         <v>142</v>
       </c>
+      <c r="AP18" t="n">
+        <v>89.31999999999999</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>18.02</v>
+      </c>
       <c r="BL18" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="B19" t="n">
-        <v>137.2</v>
+        <v>157.5</v>
       </c>
       <c r="C19" t="n">
-        <v>56.3</v>
+        <v>59.6</v>
       </c>
       <c r="D19" t="n">
-        <v>32.1</v>
+        <v>35</v>
       </c>
       <c r="E19" t="n">
-        <v>21.2</v>
+        <v>30.6</v>
       </c>
       <c r="F19" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="H19" t="n">
-        <v>23.7</v>
+        <v>24.2</v>
       </c>
       <c r="I19" t="n">
-        <v>11.6</v>
+        <v>11.2</v>
       </c>
       <c r="J19" t="n">
-        <v>40.4</v>
+        <v>38.9</v>
       </c>
       <c r="K19" t="n">
-        <v>75.7</v>
+        <v>74.3</v>
       </c>
       <c r="M19" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="N19" t="n">
-        <v>29</v>
+        <v>33.4</v>
       </c>
       <c r="O19" t="n">
-        <v>32.6</v>
+        <v>37.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="R19" t="n">
         <v>1.3</v>
@@ -2018,22 +2324,40 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
+      </c>
+      <c r="V19" t="n">
+        <v>13</v>
+      </c>
+      <c r="W19" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="X19" t="n">
+        <v>19.6</v>
       </c>
       <c r="Y19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA19" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>2</v>
       </c>
       <c r="AF19" t="n">
-        <v>232.22</v>
+        <v>229.69</v>
       </c>
       <c r="AG19" t="n">
-        <v>7.43</v>
+        <v>-2.53</v>
       </c>
       <c r="AH19" t="n">
         <v>215</v>
@@ -2042,10 +2366,10 @@
         <v>235</v>
       </c>
       <c r="AK19" t="n">
-        <v>143.61</v>
+        <v>136.96</v>
       </c>
       <c r="AL19" t="n">
-        <v>0.06</v>
+        <v>-6.65</v>
       </c>
       <c r="AM19" t="n">
         <v>110</v>
@@ -2054,81 +2378,99 @@
         <v>142</v>
       </c>
       <c r="AP19" t="n">
-        <v>89.31999999999999</v>
+        <v>86.59</v>
       </c>
       <c r="AS19" t="n">
-        <v>18.02</v>
+        <v>16.96</v>
       </c>
       <c r="BL19" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B20" t="n">
-        <v>157.5</v>
+        <v>159.6</v>
       </c>
       <c r="C20" t="n">
-        <v>59.6</v>
+        <v>63</v>
       </c>
       <c r="D20" t="n">
-        <v>35</v>
+        <v>34.5</v>
       </c>
       <c r="E20" t="n">
-        <v>30.6</v>
+        <v>31.1</v>
       </c>
       <c r="F20" t="n">
-        <v>7.5</v>
+        <v>5.7</v>
       </c>
       <c r="H20" t="n">
-        <v>24.2</v>
+        <v>23.8</v>
       </c>
       <c r="I20" t="n">
-        <v>11.2</v>
+        <v>10.8</v>
       </c>
       <c r="J20" t="n">
-        <v>38.9</v>
+        <v>40.5</v>
       </c>
       <c r="K20" t="n">
-        <v>74.3</v>
+        <v>75.2</v>
       </c>
       <c r="M20" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="N20" t="n">
-        <v>33.4</v>
+        <v>34.3</v>
       </c>
       <c r="O20" t="n">
-        <v>37.1</v>
+        <v>38.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T20" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
+      </c>
+      <c r="V20" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="W20" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="X20" t="n">
+        <v>20</v>
       </c>
       <c r="Y20" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA20" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.2</v>
       </c>
       <c r="AF20" t="n">
-        <v>229.69</v>
+        <v>228.57</v>
       </c>
       <c r="AG20" t="n">
-        <v>-2.53</v>
+        <v>-1.14</v>
       </c>
       <c r="AH20" t="n">
         <v>215</v>
@@ -2137,10 +2479,10 @@
         <v>235</v>
       </c>
       <c r="AK20" t="n">
-        <v>136.96</v>
+        <v>133.01</v>
       </c>
       <c r="AL20" t="n">
-        <v>-6.65</v>
+        <v>-3.95</v>
       </c>
       <c r="AM20" t="n">
         <v>110</v>
@@ -2149,81 +2491,99 @@
         <v>142</v>
       </c>
       <c r="AP20" t="n">
-        <v>86.59</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="AS20" t="n">
-        <v>16.96</v>
+        <v>15.95</v>
       </c>
       <c r="BL20" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B21" t="n">
-        <v>159.6</v>
+        <v>160.4</v>
       </c>
       <c r="C21" t="n">
-        <v>63</v>
+        <v>62.6</v>
       </c>
       <c r="D21" t="n">
-        <v>34.5</v>
+        <v>35</v>
       </c>
       <c r="E21" t="n">
-        <v>31.1</v>
+        <v>32.2</v>
       </c>
       <c r="F21" t="n">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="H21" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="I21" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="J21" t="n">
-        <v>40.5</v>
+        <v>41.1</v>
       </c>
       <c r="K21" t="n">
-        <v>75.2</v>
+        <v>75.7</v>
       </c>
       <c r="M21" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="N21" t="n">
-        <v>34.3</v>
+        <v>32.6</v>
       </c>
       <c r="O21" t="n">
-        <v>38.2</v>
+        <v>38</v>
       </c>
       <c r="Q21" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T21" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
+      </c>
+      <c r="V21" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="W21" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="X21" t="n">
+        <v>19.6</v>
       </c>
       <c r="Y21" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Z21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA21" t="n">
-        <v>13.5</v>
+        <v>14.1</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.6</v>
       </c>
       <c r="AF21" t="n">
-        <v>228.57</v>
+        <v>225.08</v>
       </c>
       <c r="AG21" t="n">
-        <v>-1.14</v>
+        <v>-3.5</v>
       </c>
       <c r="AH21" t="n">
         <v>215</v>
@@ -2232,10 +2592,10 @@
         <v>235</v>
       </c>
       <c r="AK21" t="n">
-        <v>133.01</v>
+        <v>135.24</v>
       </c>
       <c r="AL21" t="n">
-        <v>-3.95</v>
+        <v>2.23</v>
       </c>
       <c r="AM21" t="n">
         <v>110</v>
@@ -2244,81 +2604,99 @@
         <v>142</v>
       </c>
       <c r="AP21" t="n">
-        <v>84.59999999999999</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="AS21" t="n">
-        <v>15.95</v>
+        <v>15.4</v>
       </c>
       <c r="BL21" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B22" t="n">
-        <v>160.4</v>
+        <v>161.7</v>
       </c>
       <c r="C22" t="n">
-        <v>62.6</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>35</v>
+        <v>34.9</v>
       </c>
       <c r="E22" t="n">
-        <v>32.2</v>
+        <v>27.3</v>
       </c>
       <c r="F22" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H22" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="I22" t="n">
-        <v>10.7</v>
+        <v>10.3</v>
       </c>
       <c r="J22" t="n">
-        <v>41.1</v>
+        <v>42.6</v>
       </c>
       <c r="K22" t="n">
-        <v>75.7</v>
+        <v>77</v>
       </c>
       <c r="M22" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="N22" t="n">
-        <v>32.6</v>
+        <v>31.5</v>
       </c>
       <c r="O22" t="n">
-        <v>38</v>
+        <v>37.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="R22" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T22" t="n">
-        <v>20.9</v>
+        <v>21</v>
+      </c>
+      <c r="V22" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="W22" t="n">
+        <v>27</v>
+      </c>
+      <c r="X22" t="n">
+        <v>19.9</v>
       </c>
       <c r="Y22" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Z22" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AA22" t="n">
-        <v>14.1</v>
+        <v>11.4</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>-0.3</v>
       </c>
       <c r="AF22" t="n">
-        <v>225.08</v>
+        <v>225</v>
       </c>
       <c r="AG22" t="n">
-        <v>-3.5</v>
+        <v>-0.08</v>
       </c>
       <c r="AH22" t="n">
         <v>215</v>
@@ -2327,10 +2705,10 @@
         <v>235</v>
       </c>
       <c r="AK22" t="n">
-        <v>135.24</v>
+        <v>134.62</v>
       </c>
       <c r="AL22" t="n">
-        <v>2.23</v>
+        <v>-0.62</v>
       </c>
       <c r="AM22" t="n">
         <v>110</v>
@@ -2339,81 +2717,60 @@
         <v>142</v>
       </c>
       <c r="AP22" t="n">
-        <v>84.09999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="AS22" t="n">
-        <v>15.4</v>
+        <v>13.86</v>
       </c>
       <c r="BL22" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B23" t="n">
-        <v>161.7</v>
-      </c>
-      <c r="C23" t="n">
-        <v>71.09999999999999</v>
+        <v>151.5</v>
       </c>
       <c r="D23" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="E23" t="n">
-        <v>27.3</v>
+        <v>35.1</v>
       </c>
       <c r="F23" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H23" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I23" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="J23" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="K23" t="n">
-        <v>77</v>
-      </c>
-      <c r="M23" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="N23" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="O23" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>21</v>
-      </c>
-      <c r="R23" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="S23" t="n">
-        <v>6</v>
-      </c>
-      <c r="T23" t="n">
-        <v>21</v>
+        <v>5.4</v>
+      </c>
+      <c r="V23" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="W23" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="X23" t="n">
+        <v>14</v>
       </c>
       <c r="Y23" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA23" t="n">
         <v>9</v>
       </c>
-      <c r="Z23" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>11.4</v>
+      <c r="AB23" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>-1.4</v>
       </c>
       <c r="AF23" t="n">
-        <v>225</v>
+        <v>221.37</v>
       </c>
       <c r="AG23" t="n">
-        <v>-0.08</v>
+        <v>0.05</v>
       </c>
       <c r="AH23" t="n">
         <v>215</v>
@@ -2422,10 +2779,10 @@
         <v>235</v>
       </c>
       <c r="AK23" t="n">
-        <v>134.62</v>
+        <v>135.21</v>
       </c>
       <c r="AL23" t="n">
-        <v>-0.62</v>
+        <v>0.59</v>
       </c>
       <c r="AM23" t="n">
         <v>110</v>
@@ -2433,43 +2790,61 @@
       <c r="AN23" t="n">
         <v>142</v>
       </c>
-      <c r="AP23" t="n">
-        <v>80.2</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>13.86</v>
-      </c>
       <c r="BL23" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B24" t="n">
-        <v>151.5</v>
+        <v>145.2</v>
       </c>
       <c r="D24" t="n">
-        <v>35.1</v>
+        <v>33.5</v>
       </c>
       <c r="F24" t="n">
-        <v>5.4</v>
+        <v>5</v>
+      </c>
+      <c r="K24" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="O24" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="V24" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W24" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="X24" t="n">
+        <v>13.1</v>
       </c>
       <c r="Y24" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z24" t="n">
         <v>13</v>
       </c>
       <c r="AA24" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>-1.5</v>
       </c>
       <c r="AF24" t="n">
-        <v>221.37</v>
+        <v>224.37</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.05</v>
+        <v>3</v>
       </c>
       <c r="AH24" t="n">
         <v>215</v>
@@ -2478,10 +2853,10 @@
         <v>235</v>
       </c>
       <c r="AK24" t="n">
-        <v>135.21</v>
+        <v>135.61</v>
       </c>
       <c r="AL24" t="n">
-        <v>0.59</v>
+        <v>0.4</v>
       </c>
       <c r="AM24" t="n">
         <v>110</v>
@@ -2490,42 +2865,60 @@
         <v>142</v>
       </c>
       <c r="BL24" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B25" t="n">
-        <v>145.2</v>
+        <v>146.3</v>
       </c>
       <c r="D25" t="n">
-        <v>33.5</v>
+        <v>33.4</v>
       </c>
       <c r="F25" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="K25" t="n">
-        <v>100.3</v>
+        <v>98.2</v>
       </c>
       <c r="O25" t="n">
-        <v>35.5</v>
+        <v>35.1</v>
+      </c>
+      <c r="V25" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="W25" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="X25" t="n">
+        <v>10.6</v>
       </c>
       <c r="Y25" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z25" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA25" t="n">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>-6.4</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>-3.3</v>
       </c>
       <c r="AF25" t="n">
-        <v>224.37</v>
+        <v>225.93</v>
       </c>
       <c r="AG25" t="n">
-        <v>3</v>
+        <v>1.56</v>
       </c>
       <c r="AH25" t="n">
         <v>215</v>
@@ -2534,10 +2927,10 @@
         <v>235</v>
       </c>
       <c r="AK25" t="n">
-        <v>135.61</v>
+        <v>135.28</v>
       </c>
       <c r="AL25" t="n">
-        <v>0.4</v>
+        <v>-0.33</v>
       </c>
       <c r="AM25" t="n">
         <v>110</v>
@@ -2546,42 +2939,93 @@
         <v>142</v>
       </c>
       <c r="BL25" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B26" t="n">
-        <v>146.3</v>
+        <v>182.8</v>
+      </c>
+      <c r="C26" t="n">
+        <v>86.8</v>
       </c>
       <c r="D26" t="n">
-        <v>33.4</v>
+        <v>31.8</v>
+      </c>
+      <c r="E26" t="n">
+        <v>33</v>
       </c>
       <c r="F26" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
+      </c>
+      <c r="H26" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="I26" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J26" t="n">
+        <v>41.1</v>
       </c>
       <c r="K26" t="n">
-        <v>98.2</v>
+        <v>74.2</v>
+      </c>
+      <c r="M26" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="N26" t="n">
+        <v>33.5</v>
       </c>
       <c r="O26" t="n">
-        <v>35.1</v>
+        <v>38.4</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="R26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="V26" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="W26" t="n">
+        <v>15</v>
+      </c>
+      <c r="X26" t="n">
+        <v>12.1</v>
       </c>
       <c r="Y26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z26" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AA26" t="n">
-        <v>9</v>
+        <v>8.5</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>-5.1</v>
       </c>
       <c r="AF26" t="n">
-        <v>225.93</v>
+        <v>218.63</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.56</v>
+        <v>-7.3</v>
       </c>
       <c r="AH26" t="n">
         <v>215</v>
@@ -2590,10 +3034,10 @@
         <v>235</v>
       </c>
       <c r="AK26" t="n">
-        <v>135.28</v>
+        <v>126.27</v>
       </c>
       <c r="AL26" t="n">
-        <v>-0.33</v>
+        <v>-9.01</v>
       </c>
       <c r="AM26" t="n">
         <v>110</v>
@@ -2601,76 +3045,100 @@
       <c r="AN26" t="n">
         <v>142</v>
       </c>
+      <c r="AP26" t="n">
+        <v>82.66</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>14.7</v>
+      </c>
       <c r="BL26" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B27" t="n">
-        <v>182.8</v>
+        <v>181.8</v>
       </c>
       <c r="C27" t="n">
-        <v>86.8</v>
+        <v>86.5</v>
       </c>
       <c r="D27" t="n">
-        <v>31.8</v>
+        <v>31.4</v>
       </c>
       <c r="E27" t="n">
-        <v>33</v>
+        <v>34.2</v>
       </c>
       <c r="F27" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="H27" t="n">
-        <v>23.5</v>
+        <v>24.4</v>
       </c>
       <c r="I27" t="n">
-        <v>9.6</v>
+        <v>10.4</v>
       </c>
       <c r="J27" t="n">
-        <v>41.1</v>
+        <v>41.9</v>
       </c>
       <c r="K27" t="n">
-        <v>74.2</v>
+        <v>76.8</v>
       </c>
       <c r="M27" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="N27" t="n">
-        <v>33.5</v>
+        <v>35.7</v>
       </c>
       <c r="O27" t="n">
-        <v>38.4</v>
+        <v>39.8</v>
       </c>
       <c r="Q27" t="n">
-        <v>22.4</v>
+        <v>23</v>
       </c>
       <c r="R27" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>20.1</v>
       </c>
       <c r="T27" t="n">
-        <v>22.4</v>
+        <v>23</v>
+      </c>
+      <c r="V27" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W27" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="X27" t="n">
+        <v>10.9</v>
       </c>
       <c r="Y27" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z27" t="n">
         <v>12</v>
       </c>
       <c r="AA27" t="n">
-        <v>8.5</v>
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>-1.4</v>
       </c>
       <c r="AF27" t="n">
-        <v>218.63</v>
+        <v>216.39</v>
       </c>
       <c r="AG27" t="n">
-        <v>-7.3</v>
+        <v>-2.23</v>
       </c>
       <c r="AH27" t="n">
         <v>215</v>
@@ -2679,10 +3147,10 @@
         <v>235</v>
       </c>
       <c r="AK27" t="n">
-        <v>126.27</v>
+        <v>123.32</v>
       </c>
       <c r="AL27" t="n">
-        <v>-9.01</v>
+        <v>-2.95</v>
       </c>
       <c r="AM27" t="n">
         <v>110</v>
@@ -2691,81 +3159,99 @@
         <v>142</v>
       </c>
       <c r="AP27" t="n">
-        <v>82.66</v>
+        <v>79.08</v>
       </c>
       <c r="AS27" t="n">
-        <v>14.7</v>
+        <v>13.91</v>
       </c>
       <c r="BL27" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B28" t="n">
-        <v>181.8</v>
+        <v>183</v>
       </c>
       <c r="C28" t="n">
-        <v>86.5</v>
+        <v>84.7</v>
       </c>
       <c r="D28" t="n">
-        <v>31.4</v>
+        <v>30.9</v>
       </c>
       <c r="E28" t="n">
-        <v>34.2</v>
+        <v>33.7</v>
       </c>
       <c r="F28" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="H28" t="n">
-        <v>24.4</v>
+        <v>23.4</v>
       </c>
       <c r="I28" t="n">
-        <v>10.4</v>
+        <v>10.6</v>
       </c>
       <c r="J28" t="n">
-        <v>41.9</v>
+        <v>42.3</v>
       </c>
       <c r="K28" t="n">
-        <v>76.8</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="N28" t="n">
-        <v>35.7</v>
+        <v>36.7</v>
       </c>
       <c r="O28" t="n">
-        <v>39.8</v>
+        <v>40.8</v>
       </c>
       <c r="Q28" t="n">
-        <v>23</v>
+        <v>23.6</v>
       </c>
       <c r="R28" t="n">
         <v>1.8</v>
       </c>
       <c r="S28" t="n">
-        <v>20.1</v>
+        <v>20.8</v>
       </c>
       <c r="T28" t="n">
-        <v>23</v>
+        <v>23.6</v>
+      </c>
+      <c r="V28" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="W28" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="X28" t="n">
+        <v>10.9</v>
       </c>
       <c r="Y28" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA28" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.8</v>
       </c>
       <c r="AF28" t="n">
-        <v>216.39</v>
+        <v>217.16</v>
       </c>
       <c r="AG28" t="n">
-        <v>-2.23</v>
+        <v>0.76</v>
       </c>
       <c r="AH28" t="n">
         <v>215</v>
@@ -2774,10 +3260,10 @@
         <v>235</v>
       </c>
       <c r="AK28" t="n">
-        <v>123.32</v>
+        <v>117.87</v>
       </c>
       <c r="AL28" t="n">
-        <v>-2.95</v>
+        <v>-5.45</v>
       </c>
       <c r="AM28" t="n">
         <v>110</v>
@@ -2786,81 +3272,66 @@
         <v>142</v>
       </c>
       <c r="AP28" t="n">
-        <v>79.08</v>
+        <v>78.56</v>
       </c>
       <c r="AS28" t="n">
-        <v>13.91</v>
+        <v>13.45</v>
       </c>
       <c r="BL28" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B29" t="n">
-        <v>183</v>
-      </c>
-      <c r="C29" t="n">
-        <v>84.7</v>
+        <v>163.8</v>
       </c>
       <c r="D29" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="E29" t="n">
-        <v>33.7</v>
+        <v>29</v>
       </c>
       <c r="F29" t="n">
-        <v>7</v>
-      </c>
-      <c r="H29" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="I29" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="J29" t="n">
-        <v>42.3</v>
+        <v>6.5</v>
       </c>
       <c r="K29" t="n">
-        <v>76.40000000000001</v>
-      </c>
-      <c r="M29" t="n">
-        <v>4</v>
-      </c>
-      <c r="N29" t="n">
-        <v>36.7</v>
+        <v>101.2</v>
       </c>
       <c r="O29" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S29" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="T29" t="n">
-        <v>23.6</v>
+        <v>40.2</v>
+      </c>
+      <c r="V29" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="W29" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="X29" t="n">
+        <v>11.8</v>
       </c>
       <c r="Y29" t="n">
         <v>8</v>
       </c>
       <c r="Z29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA29" t="n">
         <v>10</v>
       </c>
+      <c r="AB29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>2.8</v>
+      </c>
       <c r="AF29" t="n">
-        <v>217.16</v>
+        <v>220.31</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.76</v>
+        <v>3.16</v>
       </c>
       <c r="AH29" t="n">
         <v>215</v>
@@ -2869,10 +3340,10 @@
         <v>235</v>
       </c>
       <c r="AK29" t="n">
-        <v>117.87</v>
+        <v>116.52</v>
       </c>
       <c r="AL29" t="n">
-        <v>-5.45</v>
+        <v>-1.35</v>
       </c>
       <c r="AM29" t="n">
         <v>110</v>
@@ -2880,49 +3351,61 @@
       <c r="AN29" t="n">
         <v>142</v>
       </c>
-      <c r="AP29" t="n">
-        <v>78.56</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>13.45</v>
-      </c>
       <c r="BL29" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B30" t="n">
-        <v>163.8</v>
+        <v>155.9</v>
       </c>
       <c r="D30" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F30" t="n">
         <v>6.5</v>
       </c>
       <c r="K30" t="n">
-        <v>101.2</v>
+        <v>99.3</v>
       </c>
       <c r="O30" t="n">
-        <v>40.2</v>
+        <v>38.5</v>
+      </c>
+      <c r="V30" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W30" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="X30" t="n">
+        <v>12.4</v>
       </c>
       <c r="Y30" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA30" t="n">
-        <v>10</v>
+        <v>11.5</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>3.5</v>
       </c>
       <c r="AF30" t="n">
-        <v>220.31</v>
+        <v>221.99</v>
       </c>
       <c r="AG30" t="n">
-        <v>3.16</v>
+        <v>1.67</v>
       </c>
       <c r="AH30" t="n">
         <v>215</v>
@@ -2931,10 +3414,10 @@
         <v>235</v>
       </c>
       <c r="AK30" t="n">
-        <v>116.52</v>
+        <v>116.37</v>
       </c>
       <c r="AL30" t="n">
-        <v>-1.35</v>
+        <v>-0.15</v>
       </c>
       <c r="AM30" t="n">
         <v>110</v>
@@ -2943,42 +3426,60 @@
         <v>142</v>
       </c>
       <c r="BL30" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B31" t="n">
-        <v>155.9</v>
+        <v>141.3</v>
       </c>
       <c r="D31" t="n">
-        <v>28</v>
+        <v>26.3</v>
       </c>
       <c r="F31" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="K31" t="n">
-        <v>99.3</v>
+        <v>97.8</v>
       </c>
       <c r="O31" t="n">
-        <v>38.5</v>
+        <v>39.8</v>
+      </c>
+      <c r="V31" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W31" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="X31" t="n">
+        <v>13.6</v>
       </c>
       <c r="Y31" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Z31" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA31" t="n">
-        <v>11.5</v>
+        <v>14</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>3.9</v>
       </c>
       <c r="AF31" t="n">
-        <v>221.99</v>
+        <v>225.14</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.67</v>
+        <v>3.15</v>
       </c>
       <c r="AH31" t="n">
         <v>215</v>
@@ -2986,12 +3487,6 @@
       <c r="AI31" t="n">
         <v>235</v>
       </c>
-      <c r="AK31" t="n">
-        <v>116.37</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>-0.15</v>
-      </c>
       <c r="AM31" t="n">
         <v>110</v>
       </c>
@@ -2999,42 +3494,54 @@
         <v>142</v>
       </c>
       <c r="BL31" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B32" t="n">
-        <v>141.3</v>
+        <v>131.5</v>
       </c>
       <c r="D32" t="n">
-        <v>26.3</v>
+        <v>27.3</v>
       </c>
       <c r="F32" t="n">
         <v>5.5</v>
       </c>
       <c r="K32" t="n">
-        <v>97.8</v>
+        <v>97</v>
       </c>
       <c r="O32" t="n">
-        <v>39.8</v>
+        <v>35.7</v>
+      </c>
+      <c r="V32" t="n">
+        <v>9</v>
+      </c>
+      <c r="W32" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="X32" t="n">
+        <v>11.4</v>
       </c>
       <c r="Y32" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z32" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA32" t="n">
         <v>15</v>
       </c>
-      <c r="AA32" t="n">
-        <v>14</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>225.14</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>3.15</v>
+      <c r="AB32" t="n">
+        <v>-3.6</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>-0.4</v>
       </c>
       <c r="AH32" t="n">
         <v>215</v>
@@ -3049,36 +3556,93 @@
         <v>142</v>
       </c>
       <c r="BL32" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="B33" t="n">
-        <v>131.5</v>
+        <v>153</v>
+      </c>
+      <c r="C33" t="n">
+        <v>71.8</v>
       </c>
       <c r="D33" t="n">
-        <v>27.3</v>
+        <v>28.6</v>
+      </c>
+      <c r="E33" t="n">
+        <v>24.7</v>
       </c>
       <c r="F33" t="n">
-        <v>5.5</v>
+        <v>4</v>
+      </c>
+      <c r="H33" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I33" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J33" t="n">
+        <v>41.1</v>
       </c>
       <c r="K33" t="n">
-        <v>97</v>
+        <v>75.90000000000001</v>
+      </c>
+      <c r="M33" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N33" t="n">
+        <v>33.5</v>
       </c>
       <c r="O33" t="n">
-        <v>35.7</v>
+        <v>38.3</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="R33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="V33" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="W33" t="n">
+        <v>13</v>
+      </c>
+      <c r="X33" t="n">
+        <v>12.1</v>
       </c>
       <c r="Y33" t="n">
         <v>12</v>
       </c>
       <c r="Z33" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AA33" t="n">
-        <v>15</v>
+        <v>12.5</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>-6.6</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>229.96</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>-0.02</v>
       </c>
       <c r="AH33" t="n">
         <v>215</v>
@@ -3086,82 +3650,112 @@
       <c r="AI33" t="n">
         <v>235</v>
       </c>
+      <c r="AK33" t="n">
+        <v>128.14</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>11.77</v>
+      </c>
       <c r="AM33" t="n">
         <v>110</v>
       </c>
       <c r="AN33" t="n">
         <v>142</v>
       </c>
+      <c r="AP33" t="n">
+        <v>87.47</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>14.8</v>
+      </c>
       <c r="BL33" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B34" t="n">
-        <v>153</v>
+        <v>165.8</v>
       </c>
       <c r="C34" t="n">
-        <v>71.8</v>
+        <v>77.3</v>
       </c>
       <c r="D34" t="n">
-        <v>28.6</v>
+        <v>29.3</v>
       </c>
       <c r="E34" t="n">
-        <v>24.7</v>
+        <v>27.7</v>
       </c>
       <c r="F34" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="H34" t="n">
         <v>24.1</v>
       </c>
       <c r="I34" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="J34" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="K34" t="n">
-        <v>75.90000000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="M34" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="N34" t="n">
-        <v>33.5</v>
+        <v>35.1</v>
       </c>
       <c r="O34" t="n">
-        <v>38.3</v>
+        <v>39.8</v>
       </c>
       <c r="Q34" t="n">
-        <v>23.2</v>
+        <v>23.8</v>
       </c>
       <c r="R34" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="T34" t="n">
-        <v>23.2</v>
+        <v>23.8</v>
+      </c>
+      <c r="V34" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="W34" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="X34" t="n">
+        <v>13.4</v>
       </c>
       <c r="Y34" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z34" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA34" t="n">
-        <v>12.5</v>
+        <v>10.1</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>4.4</v>
       </c>
       <c r="AF34" t="n">
-        <v>229.96</v>
+        <v>227.01</v>
       </c>
       <c r="AG34" t="n">
-        <v>-0.02</v>
+        <v>-2.95</v>
       </c>
       <c r="AH34" t="n">
         <v>215</v>
@@ -3170,10 +3764,10 @@
         <v>235</v>
       </c>
       <c r="AK34" t="n">
-        <v>128.14</v>
+        <v>128.15</v>
       </c>
       <c r="AL34" t="n">
-        <v>11.77</v>
+        <v>0.01</v>
       </c>
       <c r="AM34" t="n">
         <v>110</v>
@@ -3182,81 +3776,99 @@
         <v>142</v>
       </c>
       <c r="AP34" t="n">
-        <v>87.47</v>
+        <v>83.41</v>
       </c>
       <c r="AS34" t="n">
-        <v>14.8</v>
+        <v>14.52</v>
       </c>
       <c r="BL34" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B35" t="n">
-        <v>165.8</v>
+        <v>158.1</v>
       </c>
       <c r="C35" t="n">
-        <v>77.3</v>
+        <v>73.7</v>
       </c>
       <c r="D35" t="n">
-        <v>29.3</v>
+        <v>30.3</v>
       </c>
       <c r="E35" t="n">
-        <v>27.7</v>
+        <v>26</v>
       </c>
       <c r="F35" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="H35" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="I35" t="n">
-        <v>10.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J35" t="n">
-        <v>41.6</v>
+        <v>40.9</v>
       </c>
       <c r="K35" t="n">
-        <v>76.59999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="M35" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="N35" t="n">
-        <v>35.1</v>
+        <v>35.3</v>
       </c>
       <c r="O35" t="n">
-        <v>39.8</v>
+        <v>40.3</v>
       </c>
       <c r="Q35" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="R35" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S35" t="n">
         <v>7</v>
       </c>
       <c r="T35" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
+      </c>
+      <c r="V35" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W35" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="X35" t="n">
+        <v>14.1</v>
       </c>
       <c r="Y35" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z35" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA35" t="n">
-        <v>10.1</v>
+        <v>11</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>6.5</v>
       </c>
       <c r="AF35" t="n">
-        <v>227.01</v>
+        <v>228.35</v>
       </c>
       <c r="AG35" t="n">
-        <v>-2.95</v>
+        <v>1.33</v>
       </c>
       <c r="AH35" t="n">
         <v>215</v>
@@ -3265,10 +3877,10 @@
         <v>235</v>
       </c>
       <c r="AK35" t="n">
-        <v>128.15</v>
+        <v>128.86</v>
       </c>
       <c r="AL35" t="n">
-        <v>0.01</v>
+        <v>0.71</v>
       </c>
       <c r="AM35" t="n">
         <v>110</v>
@@ -3277,81 +3889,99 @@
         <v>142</v>
       </c>
       <c r="AP35" t="n">
-        <v>83.41</v>
+        <v>82.37</v>
       </c>
       <c r="AS35" t="n">
-        <v>14.52</v>
+        <v>14.22</v>
       </c>
       <c r="BL35" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B36" t="n">
-        <v>158.1</v>
+        <v>154.9</v>
       </c>
       <c r="C36" t="n">
-        <v>73.7</v>
+        <v>70.2</v>
       </c>
       <c r="D36" t="n">
-        <v>30.3</v>
+        <v>31.5</v>
       </c>
       <c r="E36" t="n">
-        <v>26</v>
+        <v>27.7</v>
       </c>
       <c r="F36" t="n">
-        <v>4.1</v>
+        <v>2.7</v>
       </c>
       <c r="H36" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="I36" t="n">
-        <v>9.300000000000001</v>
+        <v>11.3</v>
       </c>
       <c r="J36" t="n">
-        <v>40.9</v>
+        <v>40.3</v>
       </c>
       <c r="K36" t="n">
-        <v>74.40000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="M36" t="n">
-        <v>5</v>
+        <v>6.1</v>
       </c>
       <c r="N36" t="n">
-        <v>35.3</v>
+        <v>32.9</v>
       </c>
       <c r="O36" t="n">
-        <v>40.3</v>
+        <v>39</v>
       </c>
       <c r="Q36" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="R36" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="S36" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="T36" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
+      </c>
+      <c r="V36" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="W36" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="X36" t="n">
+        <v>15.8</v>
       </c>
       <c r="Y36" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z36" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA36" t="n">
-        <v>11</v>
+        <v>12.6</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>5.8</v>
       </c>
       <c r="AF36" t="n">
-        <v>228.35</v>
+        <v>231.16</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.33</v>
+        <v>2.81</v>
       </c>
       <c r="AH36" t="n">
         <v>215</v>
@@ -3360,10 +3990,10 @@
         <v>235</v>
       </c>
       <c r="AK36" t="n">
-        <v>128.86</v>
+        <v>130.88</v>
       </c>
       <c r="AL36" t="n">
-        <v>0.71</v>
+        <v>2.02</v>
       </c>
       <c r="AM36" t="n">
         <v>110</v>
@@ -3372,81 +4002,66 @@
         <v>142</v>
       </c>
       <c r="AP36" t="n">
-        <v>82.37</v>
+        <v>85.48999999999999</v>
       </c>
       <c r="AS36" t="n">
-        <v>14.22</v>
+        <v>13.1</v>
       </c>
       <c r="BL36" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B37" t="n">
-        <v>154.9</v>
-      </c>
-      <c r="C37" t="n">
-        <v>70.2</v>
+        <v>152.2</v>
       </c>
       <c r="D37" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="E37" t="n">
-        <v>27.7</v>
+        <v>31</v>
       </c>
       <c r="F37" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="H37" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I37" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J37" t="n">
-        <v>40.3</v>
+        <v>3.5</v>
       </c>
       <c r="K37" t="n">
-        <v>75.8</v>
-      </c>
-      <c r="M37" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="N37" t="n">
-        <v>32.9</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O37" t="n">
-        <v>39</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="R37" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="V37" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W37" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="X37" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD37" t="n">
         <v>3.8</v>
       </c>
-      <c r="S37" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="T37" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>17</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>12.6</v>
-      </c>
       <c r="AF37" t="n">
-        <v>231.16</v>
+        <v>228.13</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.81</v>
+        <v>-3.03</v>
       </c>
       <c r="AH37" t="n">
         <v>215</v>
@@ -3454,61 +4069,67 @@
       <c r="AI37" t="n">
         <v>235</v>
       </c>
-      <c r="AK37" t="n">
-        <v>130.88</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AM37" t="n">
         <v>110</v>
       </c>
       <c r="AN37" t="n">
         <v>142</v>
       </c>
-      <c r="AP37" t="n">
-        <v>85.48999999999999</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>13.1</v>
-      </c>
       <c r="BL37" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B38" t="n">
-        <v>152.2</v>
+        <v>143.9</v>
       </c>
       <c r="D38" t="n">
-        <v>31</v>
+        <v>30.8</v>
       </c>
       <c r="F38" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="K38" t="n">
-        <v>98.40000000000001</v>
+        <v>99.2</v>
       </c>
       <c r="O38" t="n">
-        <v>34.4</v>
+        <v>35.2</v>
+      </c>
+      <c r="V38" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="W38" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="X38" t="n">
+        <v>14.2</v>
       </c>
       <c r="Y38" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Z38" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA38" t="n">
         <v>9</v>
       </c>
+      <c r="AB38" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>4</v>
+      </c>
       <c r="AF38" t="n">
-        <v>228.13</v>
+        <v>229.16</v>
       </c>
       <c r="AG38" t="n">
-        <v>-3.03</v>
+        <v>1.03</v>
       </c>
       <c r="AH38" t="n">
         <v>215</v>
@@ -3523,42 +4144,93 @@
         <v>142</v>
       </c>
       <c r="BL38" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B39" t="n">
-        <v>143.9</v>
+        <v>163.2</v>
+      </c>
+      <c r="C39" t="n">
+        <v>73.7</v>
       </c>
       <c r="D39" t="n">
-        <v>30.8</v>
+        <v>30</v>
+      </c>
+      <c r="E39" t="n">
+        <v>28.2</v>
       </c>
       <c r="F39" t="n">
-        <v>2.5</v>
+        <v>4.8</v>
+      </c>
+      <c r="H39" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I39" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J39" t="n">
+        <v>40.1</v>
       </c>
       <c r="K39" t="n">
-        <v>99.2</v>
+        <v>75.59999999999999</v>
+      </c>
+      <c r="M39" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="N39" t="n">
+        <v>32.9</v>
       </c>
       <c r="O39" t="n">
-        <v>35.2</v>
+        <v>39.7</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="R39" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="S39" t="n">
+        <v>6</v>
+      </c>
+      <c r="T39" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="V39" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="W39" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="X39" t="n">
+        <v>14.8</v>
       </c>
       <c r="Y39" t="n">
         <v>4</v>
       </c>
       <c r="Z39" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA39" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>4.3</v>
       </c>
       <c r="AF39" t="n">
-        <v>229.16</v>
+        <v>228.55</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.03</v>
+        <v>-0.61</v>
       </c>
       <c r="AH39" t="n">
         <v>215</v>
@@ -3566,82 +4238,112 @@
       <c r="AI39" t="n">
         <v>235</v>
       </c>
+      <c r="AK39" t="n">
+        <v>127.06</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>-3.82</v>
+      </c>
       <c r="AM39" t="n">
         <v>110</v>
       </c>
       <c r="AN39" t="n">
         <v>142</v>
       </c>
+      <c r="AP39" t="n">
+        <v>82.81</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>12.9</v>
+      </c>
       <c r="BL39" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="B40" t="n">
-        <v>163.2</v>
+        <v>174.4</v>
       </c>
       <c r="C40" t="n">
-        <v>73.7</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="D40" t="n">
-        <v>30</v>
+        <v>32.1</v>
       </c>
       <c r="E40" t="n">
-        <v>28.2</v>
+        <v>30.8</v>
       </c>
       <c r="F40" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="H40" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="I40" t="n">
-        <v>11.4</v>
+        <v>10.5</v>
       </c>
       <c r="J40" t="n">
-        <v>40.1</v>
+        <v>39.5</v>
       </c>
       <c r="K40" t="n">
-        <v>75.59999999999999</v>
+        <v>74</v>
       </c>
       <c r="M40" t="n">
         <v>6.8</v>
       </c>
       <c r="N40" t="n">
-        <v>32.9</v>
+        <v>35.8</v>
       </c>
       <c r="O40" t="n">
-        <v>39.7</v>
+        <v>42.6</v>
       </c>
       <c r="Q40" t="n">
-        <v>23.5</v>
+        <v>23.1</v>
       </c>
       <c r="R40" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="S40" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="T40" t="n">
-        <v>23.5</v>
+        <v>23.1</v>
+      </c>
+      <c r="V40" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="W40" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="X40" t="n">
+        <v>17.5</v>
       </c>
       <c r="Y40" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Z40" t="n">
         <v>13</v>
       </c>
       <c r="AA40" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AC40" t="n">
         <v>9.300000000000001</v>
       </c>
+      <c r="AD40" t="n">
+        <v>4.8</v>
+      </c>
       <c r="AF40" t="n">
-        <v>228.55</v>
+        <v>219.99</v>
       </c>
       <c r="AG40" t="n">
-        <v>-0.61</v>
+        <v>-8.56</v>
       </c>
       <c r="AH40" t="n">
         <v>215</v>
@@ -3650,10 +4352,10 @@
         <v>235</v>
       </c>
       <c r="AK40" t="n">
-        <v>127.06</v>
+        <v>125.61</v>
       </c>
       <c r="AL40" t="n">
-        <v>-3.82</v>
+        <v>-1.45</v>
       </c>
       <c r="AM40" t="n">
         <v>110</v>
@@ -3662,81 +4364,99 @@
         <v>142</v>
       </c>
       <c r="AP40" t="n">
-        <v>82.81</v>
+        <v>77.83</v>
       </c>
       <c r="AS40" t="n">
-        <v>12.9</v>
+        <v>12.96</v>
       </c>
       <c r="BL40" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B41" t="n">
-        <v>174.4</v>
+        <v>163.2</v>
       </c>
       <c r="C41" t="n">
-        <v>75.40000000000001</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="D41" t="n">
-        <v>32.1</v>
+        <v>32.9</v>
       </c>
       <c r="E41" t="n">
-        <v>30.8</v>
+        <v>26</v>
       </c>
       <c r="F41" t="n">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="H41" t="n">
-        <v>24</v>
+        <v>23.8</v>
       </c>
       <c r="I41" t="n">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="J41" t="n">
-        <v>39.5</v>
+        <v>40.1</v>
       </c>
       <c r="K41" t="n">
-        <v>74</v>
+        <v>71.3</v>
       </c>
       <c r="M41" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="N41" t="n">
-        <v>35.8</v>
+        <v>34.3</v>
       </c>
       <c r="O41" t="n">
-        <v>42.6</v>
+        <v>41.5</v>
       </c>
       <c r="Q41" t="n">
         <v>23.1</v>
       </c>
       <c r="R41" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="S41" t="n">
-        <v>8.5</v>
+        <v>6.2</v>
       </c>
       <c r="T41" t="n">
         <v>23.1</v>
       </c>
+      <c r="V41" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="W41" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="X41" t="n">
+        <v>16.4</v>
+      </c>
       <c r="Y41" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z41" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA41" t="n">
-        <v>10.1</v>
+        <v>12.2</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>5.5</v>
       </c>
       <c r="AF41" t="n">
-        <v>219.99</v>
+        <v>219.22</v>
       </c>
       <c r="AG41" t="n">
-        <v>-8.56</v>
+        <v>-0.77</v>
       </c>
       <c r="AH41" t="n">
         <v>215</v>
@@ -3745,10 +4465,10 @@
         <v>235</v>
       </c>
       <c r="AK41" t="n">
-        <v>125.61</v>
+        <v>124.36</v>
       </c>
       <c r="AL41" t="n">
-        <v>-1.45</v>
+        <v>-1.25</v>
       </c>
       <c r="AM41" t="n">
         <v>110</v>
@@ -3757,81 +4477,99 @@
         <v>142</v>
       </c>
       <c r="AP41" t="n">
-        <v>77.83</v>
+        <v>76.81</v>
       </c>
       <c r="AS41" t="n">
-        <v>12.96</v>
+        <v>12.38</v>
       </c>
       <c r="BL41" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B42" t="n">
-        <v>163.2</v>
+        <v>152.7</v>
       </c>
       <c r="C42" t="n">
-        <v>70.90000000000001</v>
+        <v>62.6</v>
       </c>
       <c r="D42" t="n">
-        <v>32.9</v>
+        <v>32.7</v>
       </c>
       <c r="E42" t="n">
-        <v>26</v>
+        <v>24.6</v>
       </c>
       <c r="F42" t="n">
-        <v>6.9</v>
+        <v>5.2</v>
       </c>
       <c r="H42" t="n">
         <v>23.8</v>
       </c>
       <c r="I42" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J42" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="K42" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="M42" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="N42" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="O42" t="n">
         <v>40.1</v>
       </c>
-      <c r="K42" t="n">
-        <v>71.3</v>
-      </c>
-      <c r="M42" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="N42" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="O42" t="n">
-        <v>41.5</v>
-      </c>
       <c r="Q42" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="R42" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="S42" t="n">
-        <v>6.2</v>
+        <v>4</v>
       </c>
       <c r="T42" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
+      </c>
+      <c r="V42" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="W42" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="X42" t="n">
+        <v>19.4</v>
       </c>
       <c r="Y42" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z42" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA42" t="n">
         <v>14</v>
       </c>
-      <c r="AA42" t="n">
-        <v>12.2</v>
+      <c r="AB42" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>5.7</v>
       </c>
       <c r="AF42" t="n">
-        <v>219.22</v>
+        <v>220.73</v>
       </c>
       <c r="AG42" t="n">
-        <v>-0.77</v>
+        <v>1.5</v>
       </c>
       <c r="AH42" t="n">
         <v>215</v>
@@ -3840,10 +4578,10 @@
         <v>235</v>
       </c>
       <c r="AK42" t="n">
-        <v>124.36</v>
+        <v>120.93</v>
       </c>
       <c r="AL42" t="n">
-        <v>-1.25</v>
+        <v>-3.43</v>
       </c>
       <c r="AM42" t="n">
         <v>110</v>
@@ -3852,67 +4590,76 @@
         <v>142</v>
       </c>
       <c r="AP42" t="n">
-        <v>76.81</v>
+        <v>77.87</v>
       </c>
       <c r="AS42" t="n">
-        <v>12.38</v>
+        <v>13.26</v>
       </c>
       <c r="BL42" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B43" t="n">
-        <v>152.7</v>
+        <v>150.7</v>
       </c>
       <c r="C43" t="n">
-        <v>62.6</v>
+        <v>64.8</v>
       </c>
       <c r="D43" t="n">
-        <v>32.7</v>
+        <v>33.7</v>
       </c>
       <c r="E43" t="n">
-        <v>24.6</v>
+        <v>27.1</v>
       </c>
       <c r="F43" t="n">
-        <v>5.2</v>
+        <v>3.8</v>
       </c>
       <c r="H43" t="n">
-        <v>23.8</v>
+        <v>23.4</v>
       </c>
       <c r="I43" t="n">
         <v>7.2</v>
       </c>
       <c r="J43" t="n">
-        <v>38.9</v>
+        <v>39.9</v>
       </c>
       <c r="K43" t="n">
-        <v>69.90000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="M43" t="n">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="N43" t="n">
-        <v>33.5</v>
+        <v>33</v>
       </c>
       <c r="O43" t="n">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="Q43" t="n">
         <v>23.2</v>
       </c>
       <c r="R43" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="S43" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T43" t="n">
         <v>23.2</v>
       </c>
+      <c r="V43" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="W43" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="X43" t="n">
+        <v>21.7</v>
+      </c>
       <c r="Y43" t="n">
         <v>10</v>
       </c>
@@ -3920,13 +4667,22 @@
         <v>18</v>
       </c>
       <c r="AA43" t="n">
-        <v>14</v>
+        <v>13.1</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>6.7</v>
       </c>
       <c r="AF43" t="n">
-        <v>220.73</v>
+        <v>220.58</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.5</v>
+        <v>-0.15</v>
       </c>
       <c r="AH43" t="n">
         <v>215</v>
@@ -3935,10 +4691,10 @@
         <v>235</v>
       </c>
       <c r="AK43" t="n">
-        <v>120.93</v>
+        <v>120.28</v>
       </c>
       <c r="AL43" t="n">
-        <v>-3.43</v>
+        <v>-0.65</v>
       </c>
       <c r="AM43" t="n">
         <v>110</v>
@@ -3947,81 +4703,54 @@
         <v>142</v>
       </c>
       <c r="AP43" t="n">
-        <v>77.87</v>
+        <v>77.22</v>
       </c>
       <c r="AS43" t="n">
-        <v>13.26</v>
+        <v>13.79</v>
       </c>
       <c r="BL43" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B44" t="n">
-        <v>150.7</v>
-      </c>
-      <c r="C44" t="n">
-        <v>64.8</v>
+        <v>138.2</v>
       </c>
       <c r="D44" t="n">
-        <v>33.7</v>
-      </c>
-      <c r="E44" t="n">
-        <v>27.1</v>
+        <v>33.6</v>
       </c>
       <c r="F44" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H44" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="V44" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="W44" t="n">
         <v>23.4</v>
       </c>
-      <c r="I44" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="J44" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="K44" t="n">
-        <v>70.5</v>
-      </c>
-      <c r="M44" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="N44" t="n">
-        <v>33</v>
-      </c>
-      <c r="O44" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="R44" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="S44" t="n">
-        <v>3</v>
-      </c>
-      <c r="T44" t="n">
-        <v>23.2</v>
+      <c r="X44" t="n">
+        <v>19.4</v>
       </c>
       <c r="Y44" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z44" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AA44" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>220.58</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>-0.15</v>
+        <v>13</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>4.5</v>
       </c>
       <c r="AH44" t="n">
         <v>215</v>
@@ -4029,50 +4758,62 @@
       <c r="AI44" t="n">
         <v>235</v>
       </c>
-      <c r="AK44" t="n">
-        <v>120.28</v>
-      </c>
-      <c r="AL44" t="n">
-        <v>-0.65</v>
-      </c>
       <c r="AM44" t="n">
         <v>110</v>
       </c>
       <c r="AN44" t="n">
         <v>142</v>
       </c>
-      <c r="AP44" t="n">
-        <v>77.22</v>
-      </c>
-      <c r="AS44" t="n">
-        <v>13.79</v>
-      </c>
       <c r="BL44" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B45" t="n">
-        <v>138.2</v>
+        <v>126.5</v>
       </c>
       <c r="D45" t="n">
-        <v>33.6</v>
+        <v>33.2</v>
       </c>
       <c r="F45" t="n">
-        <v>6.1</v>
+        <v>3.4</v>
+      </c>
+      <c r="V45" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="W45" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="X45" t="n">
+        <v>17.4</v>
       </c>
       <c r="Y45" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z45" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA45" t="n">
         <v>13</v>
       </c>
+      <c r="AB45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>229.48</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>6.05</v>
+      </c>
       <c r="AH45" t="n">
         <v>215</v>
       </c>
@@ -4086,36 +4827,93 @@
         <v>142</v>
       </c>
       <c r="BL45" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B46" t="n">
-        <v>126.5</v>
+        <v>129.4</v>
+      </c>
+      <c r="C46" t="n">
+        <v>50.6</v>
       </c>
       <c r="D46" t="n">
-        <v>33.2</v>
+        <v>31.5</v>
+      </c>
+      <c r="E46" t="n">
+        <v>19.4</v>
       </c>
       <c r="F46" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
+      </c>
+      <c r="H46" t="n">
+        <v>24</v>
+      </c>
+      <c r="I46" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J46" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="K46" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="M46" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N46" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="O46" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="V46" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="W46" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="X46" t="n">
+        <v>19.1</v>
       </c>
       <c r="Y46" t="n">
         <v>8</v>
       </c>
       <c r="Z46" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AA46" t="n">
-        <v>13</v>
+        <v>16.1</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>4</v>
       </c>
       <c r="AF46" t="n">
-        <v>229.48</v>
+        <v>229.5</v>
       </c>
       <c r="AG46" t="n">
-        <v>6.05</v>
+        <v>0.02</v>
       </c>
       <c r="AH46" t="n">
         <v>215</v>
@@ -4123,82 +4921,112 @@
       <c r="AI46" t="n">
         <v>235</v>
       </c>
+      <c r="AK46" t="n">
+        <v>128.37</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>8.09</v>
+      </c>
       <c r="AM46" t="n">
         <v>110</v>
       </c>
       <c r="AN46" t="n">
         <v>142</v>
       </c>
+      <c r="AP46" t="n">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>15.97</v>
+      </c>
       <c r="BL46" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="B47" t="n">
-        <v>129.4</v>
+        <v>142.9</v>
       </c>
       <c r="C47" t="n">
-        <v>50.6</v>
+        <v>52.7</v>
       </c>
       <c r="D47" t="n">
-        <v>31.5</v>
+        <v>34.7</v>
       </c>
       <c r="E47" t="n">
-        <v>19.4</v>
+        <v>24.8</v>
       </c>
       <c r="F47" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="H47" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I47" t="n">
-        <v>10.4</v>
+        <v>9.9</v>
       </c>
       <c r="J47" t="n">
-        <v>38.9</v>
+        <v>38.2</v>
       </c>
       <c r="K47" t="n">
-        <v>73.3</v>
+        <v>70</v>
       </c>
       <c r="M47" t="n">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="N47" t="n">
-        <v>33.3</v>
+        <v>31.9</v>
       </c>
       <c r="O47" t="n">
-        <v>38</v>
+        <v>35.8</v>
       </c>
       <c r="Q47" t="n">
-        <v>21.4</v>
+        <v>19.7</v>
       </c>
       <c r="R47" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>21.4</v>
+        <v>19.7</v>
+      </c>
+      <c r="V47" t="n">
+        <v>12</v>
+      </c>
+      <c r="W47" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="X47" t="n">
+        <v>18.9</v>
       </c>
       <c r="Y47" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Z47" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AA47" t="n">
-        <v>16.1</v>
+        <v>15</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>2.9</v>
       </c>
       <c r="AF47" t="n">
-        <v>229.5</v>
+        <v>238.69</v>
       </c>
       <c r="AG47" t="n">
-        <v>0.02</v>
+        <v>-2.8</v>
       </c>
       <c r="AH47" t="n">
         <v>215</v>
@@ -4207,10 +5035,10 @@
         <v>235</v>
       </c>
       <c r="AK47" t="n">
-        <v>128.37</v>
+        <v>134.59</v>
       </c>
       <c r="AL47" t="n">
-        <v>8.09</v>
+        <v>6.22</v>
       </c>
       <c r="AM47" t="n">
         <v>110</v>
@@ -4219,81 +5047,99 @@
         <v>142</v>
       </c>
       <c r="AP47" t="n">
-        <v>91.59999999999999</v>
+        <v>89.05</v>
       </c>
       <c r="AS47" t="n">
-        <v>15.97</v>
+        <v>17.06</v>
       </c>
       <c r="BL47" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B48" t="n">
-        <v>142.9</v>
+        <v>148.1</v>
       </c>
       <c r="C48" t="n">
-        <v>52.7</v>
+        <v>51.9</v>
       </c>
       <c r="D48" t="n">
-        <v>34.7</v>
+        <v>35.4</v>
       </c>
       <c r="E48" t="n">
-        <v>24.8</v>
+        <v>31.5</v>
       </c>
       <c r="F48" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="H48" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="I48" t="n">
-        <v>9.9</v>
+        <v>9.6</v>
       </c>
       <c r="J48" t="n">
-        <v>38.2</v>
+        <v>39.6</v>
       </c>
       <c r="K48" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M48" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="N48" t="n">
-        <v>31.9</v>
+        <v>30.8</v>
       </c>
       <c r="O48" t="n">
-        <v>35.8</v>
+        <v>33.7</v>
       </c>
       <c r="Q48" t="n">
-        <v>19.7</v>
+        <v>20.7</v>
       </c>
       <c r="R48" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>19.7</v>
+        <v>20.7</v>
+      </c>
+      <c r="V48" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="W48" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="X48" t="n">
+        <v>19.3</v>
       </c>
       <c r="Y48" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z48" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AA48" t="n">
-        <v>15</v>
+        <v>15.5</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>2.7</v>
       </c>
       <c r="AF48" t="n">
-        <v>238.69</v>
+        <v>233.48</v>
       </c>
       <c r="AG48" t="n">
-        <v>-2.8</v>
+        <v>-4.86</v>
       </c>
       <c r="AH48" t="n">
         <v>215</v>
@@ -4302,10 +5148,10 @@
         <v>235</v>
       </c>
       <c r="AK48" t="n">
-        <v>134.59</v>
+        <v>136.6</v>
       </c>
       <c r="AL48" t="n">
-        <v>6.22</v>
+        <v>2.01</v>
       </c>
       <c r="AM48" t="n">
         <v>110</v>
@@ -4314,81 +5160,99 @@
         <v>142</v>
       </c>
       <c r="AP48" t="n">
-        <v>89.05</v>
+        <v>86.25</v>
       </c>
       <c r="AS48" t="n">
-        <v>17.06</v>
+        <v>17.13</v>
       </c>
       <c r="BL48" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B49" t="n">
-        <v>148.1</v>
+        <v>143.4</v>
       </c>
       <c r="C49" t="n">
-        <v>51.9</v>
+        <v>50.9</v>
       </c>
       <c r="D49" t="n">
-        <v>35.4</v>
+        <v>35.7</v>
       </c>
       <c r="E49" t="n">
-        <v>31.5</v>
+        <v>26.2</v>
       </c>
       <c r="F49" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="H49" t="n">
-        <v>21.8</v>
+        <v>22.9</v>
       </c>
       <c r="I49" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J49" t="n">
-        <v>39.6</v>
+        <v>39.9</v>
       </c>
       <c r="K49" t="n">
-        <v>71</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="M49" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="N49" t="n">
-        <v>30.8</v>
+        <v>31.2</v>
       </c>
       <c r="O49" t="n">
-        <v>33.7</v>
+        <v>33.1</v>
       </c>
       <c r="Q49" t="n">
-        <v>20.7</v>
+        <v>21.6</v>
       </c>
       <c r="R49" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>20.7</v>
+        <v>21.6</v>
+      </c>
+      <c r="V49" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="W49" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="X49" t="n">
+        <v>20.6</v>
       </c>
       <c r="Y49" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z49" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AA49" t="n">
-        <v>15.5</v>
+        <v>17.9</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>3.6</v>
       </c>
       <c r="AF49" t="n">
-        <v>233.48</v>
+        <v>235.13</v>
       </c>
       <c r="AG49" t="n">
-        <v>-4.86</v>
+        <v>1.66</v>
       </c>
       <c r="AH49" t="n">
         <v>215</v>
@@ -4397,10 +5261,10 @@
         <v>235</v>
       </c>
       <c r="AK49" t="n">
-        <v>136.6</v>
+        <v>135.66</v>
       </c>
       <c r="AL49" t="n">
-        <v>2.01</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AM49" t="n">
         <v>110</v>
@@ -4409,57 +5273,57 @@
         <v>142</v>
       </c>
       <c r="AP49" t="n">
-        <v>86.25</v>
+        <v>88.27</v>
       </c>
       <c r="AS49" t="n">
-        <v>17.13</v>
+        <v>17.6</v>
       </c>
       <c r="BL49" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B50" t="n">
-        <v>143.4</v>
+        <v>144.9</v>
       </c>
       <c r="C50" t="n">
-        <v>50.9</v>
+        <v>53</v>
       </c>
       <c r="D50" t="n">
-        <v>35.7</v>
+        <v>35.6</v>
       </c>
       <c r="E50" t="n">
-        <v>26.2</v>
+        <v>26</v>
       </c>
       <c r="F50" t="n">
-        <v>4.3</v>
+        <v>2.8</v>
       </c>
       <c r="H50" t="n">
-        <v>22.9</v>
+        <v>24</v>
       </c>
       <c r="I50" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J50" t="n">
-        <v>39.9</v>
+        <v>40.3</v>
       </c>
       <c r="K50" t="n">
-        <v>72.59999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="M50" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="N50" t="n">
-        <v>31.2</v>
+        <v>31.6</v>
       </c>
       <c r="O50" t="n">
-        <v>33.1</v>
+        <v>33.6</v>
       </c>
       <c r="Q50" t="n">
-        <v>21.6</v>
+        <v>21</v>
       </c>
       <c r="R50" t="n">
         <v>0</v>
@@ -4468,22 +5332,40 @@
         <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>21.6</v>
+        <v>21</v>
+      </c>
+      <c r="V50" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="W50" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="X50" t="n">
+        <v>21.1</v>
       </c>
       <c r="Y50" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z50" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AA50" t="n">
-        <v>17.9</v>
+        <v>16.3</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>2.8</v>
       </c>
       <c r="AF50" t="n">
-        <v>235.13</v>
+        <v>234.87</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.66</v>
+        <v>-0.26</v>
       </c>
       <c r="AH50" t="n">
         <v>215</v>
@@ -4492,10 +5374,10 @@
         <v>235</v>
       </c>
       <c r="AK50" t="n">
-        <v>135.66</v>
+        <v>136.33</v>
       </c>
       <c r="AL50" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="AM50" t="n">
         <v>110</v>
@@ -4504,81 +5386,60 @@
         <v>142</v>
       </c>
       <c r="AP50" t="n">
-        <v>88.27</v>
+        <v>87.09</v>
       </c>
       <c r="AS50" t="n">
-        <v>17.6</v>
+        <v>17.31</v>
       </c>
       <c r="BL50" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B51" t="n">
-        <v>144.9</v>
-      </c>
-      <c r="C51" t="n">
-        <v>53</v>
+        <v>132.2</v>
       </c>
       <c r="D51" t="n">
         <v>35.6</v>
       </c>
-      <c r="E51" t="n">
-        <v>26</v>
-      </c>
       <c r="F51" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="H51" t="n">
-        <v>24</v>
-      </c>
-      <c r="I51" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="J51" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="K51" t="n">
-        <v>73.7</v>
-      </c>
-      <c r="M51" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="N51" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="O51" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>21</v>
-      </c>
-      <c r="R51" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" t="n">
-        <v>21</v>
+        <v>4</v>
+      </c>
+      <c r="V51" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="W51" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="X51" t="n">
+        <v>17.4</v>
       </c>
       <c r="Y51" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z51" t="n">
         <v>19</v>
       </c>
       <c r="AA51" t="n">
-        <v>16.3</v>
+        <v>13</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>4.2</v>
       </c>
       <c r="AF51" t="n">
-        <v>234.87</v>
+        <v>234.78</v>
       </c>
       <c r="AG51" t="n">
-        <v>-0.26</v>
+        <v>-0.09</v>
       </c>
       <c r="AH51" t="n">
         <v>215</v>
@@ -4586,55 +5447,61 @@
       <c r="AI51" t="n">
         <v>235</v>
       </c>
-      <c r="AK51" t="n">
-        <v>136.33</v>
-      </c>
-      <c r="AL51" t="n">
-        <v>0.67</v>
-      </c>
       <c r="AM51" t="n">
         <v>110</v>
       </c>
       <c r="AN51" t="n">
         <v>142</v>
       </c>
-      <c r="AP51" t="n">
-        <v>87.09</v>
-      </c>
-      <c r="AS51" t="n">
-        <v>17.31</v>
-      </c>
       <c r="BL51" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B52" t="n">
-        <v>132.2</v>
+        <v>137.1</v>
       </c>
       <c r="D52" t="n">
-        <v>35.6</v>
+        <v>35.1</v>
       </c>
       <c r="F52" t="n">
-        <v>4</v>
+        <v>3.3</v>
+      </c>
+      <c r="V52" t="n">
+        <v>11</v>
+      </c>
+      <c r="W52" t="n">
+        <v>22</v>
+      </c>
+      <c r="X52" t="n">
+        <v>16.5</v>
       </c>
       <c r="Y52" t="n">
         <v>7</v>
       </c>
       <c r="Z52" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AA52" t="n">
-        <v>13</v>
+        <v>10.5</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>0.4</v>
       </c>
       <c r="AF52" t="n">
-        <v>234.78</v>
+        <v>229.75</v>
       </c>
       <c r="AG52" t="n">
-        <v>-0.09</v>
+        <v>-5.03</v>
       </c>
       <c r="AH52" t="n">
         <v>215</v>
@@ -4649,36 +5516,93 @@
         <v>142</v>
       </c>
       <c r="BL52" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B53" t="n">
-        <v>137.1</v>
+        <v>166.2</v>
+      </c>
+      <c r="C53" t="n">
+        <v>72.40000000000001</v>
       </c>
       <c r="D53" t="n">
-        <v>35.1</v>
+        <v>32.7</v>
+      </c>
+      <c r="E53" t="n">
+        <v>28.1</v>
       </c>
       <c r="F53" t="n">
         <v>3.3</v>
       </c>
+      <c r="H53" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="I53" t="n">
+        <v>9</v>
+      </c>
+      <c r="J53" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="K53" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="M53" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="N53" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="O53" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="R53" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="V53" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="W53" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="X53" t="n">
+        <v>11.8</v>
+      </c>
       <c r="Y53" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z53" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AA53" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>2.5</v>
       </c>
       <c r="AF53" t="n">
-        <v>229.75</v>
+        <v>222.86</v>
       </c>
       <c r="AG53" t="n">
-        <v>-5.03</v>
+        <v>-6.9</v>
       </c>
       <c r="AH53" t="n">
         <v>215</v>
@@ -4686,82 +5610,112 @@
       <c r="AI53" t="n">
         <v>235</v>
       </c>
+      <c r="AK53" t="n">
+        <v>135.42</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>-0.91</v>
+      </c>
       <c r="AM53" t="n">
         <v>110</v>
       </c>
       <c r="AN53" t="n">
         <v>142</v>
       </c>
+      <c r="AP53" t="n">
+        <v>81.98</v>
+      </c>
+      <c r="AS53" t="n">
+        <v>15.01</v>
+      </c>
       <c r="BL53" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B54" t="n">
-        <v>166.2</v>
+        <v>166.3</v>
       </c>
       <c r="C54" t="n">
-        <v>72.40000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="D54" t="n">
-        <v>32.7</v>
+        <v>32.8</v>
       </c>
       <c r="E54" t="n">
-        <v>28.1</v>
+        <v>28.8</v>
       </c>
       <c r="F54" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="H54" t="n">
         <v>23.4</v>
       </c>
       <c r="I54" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J54" t="n">
-        <v>42.1</v>
+        <v>41.2</v>
       </c>
       <c r="K54" t="n">
-        <v>74.5</v>
+        <v>73.8</v>
       </c>
       <c r="M54" t="n">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="N54" t="n">
-        <v>33.7</v>
+        <v>35.4</v>
       </c>
       <c r="O54" t="n">
-        <v>39.3</v>
+        <v>42.6</v>
       </c>
       <c r="Q54" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="R54" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
+      </c>
+      <c r="V54" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="W54" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="X54" t="n">
+        <v>12.4</v>
       </c>
       <c r="Y54" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Z54" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AA54" t="n">
-        <v>8.199999999999999</v>
+        <v>11</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>4.3</v>
       </c>
       <c r="AF54" t="n">
-        <v>222.86</v>
+        <v>218.37</v>
       </c>
       <c r="AG54" t="n">
-        <v>-6.9</v>
+        <v>-4.49</v>
       </c>
       <c r="AH54" t="n">
         <v>215</v>
@@ -4770,10 +5724,10 @@
         <v>235</v>
       </c>
       <c r="AK54" t="n">
-        <v>135.42</v>
+        <v>131.24</v>
       </c>
       <c r="AL54" t="n">
-        <v>-0.91</v>
+        <v>-4.18</v>
       </c>
       <c r="AM54" t="n">
         <v>110</v>
@@ -4782,81 +5736,99 @@
         <v>142</v>
       </c>
       <c r="AP54" t="n">
-        <v>81.98</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="AS54" t="n">
-        <v>15.01</v>
+        <v>12.97</v>
       </c>
       <c r="BL54" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B55" t="n">
-        <v>166.3</v>
+        <v>154.1</v>
       </c>
       <c r="C55" t="n">
-        <v>74.90000000000001</v>
+        <v>65</v>
       </c>
       <c r="D55" t="n">
-        <v>32.8</v>
+        <v>32</v>
       </c>
       <c r="E55" t="n">
-        <v>28.8</v>
+        <v>25.2</v>
       </c>
       <c r="F55" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="H55" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="I55" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="J55" t="n">
-        <v>41.2</v>
+        <v>38.5</v>
       </c>
       <c r="K55" t="n">
-        <v>73.8</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="M55" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="N55" t="n">
-        <v>35.4</v>
+        <v>32.3</v>
       </c>
       <c r="O55" t="n">
-        <v>42.6</v>
+        <v>40.3</v>
       </c>
       <c r="Q55" t="n">
-        <v>23.9</v>
+        <v>21.7</v>
       </c>
       <c r="R55" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="S55" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T55" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="V55" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="W55" t="n">
+        <v>21</v>
+      </c>
+      <c r="X55" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AD55" t="n">
         <v>3.9</v>
       </c>
-      <c r="S55" t="n">
-        <v>0</v>
-      </c>
-      <c r="T55" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>11</v>
-      </c>
       <c r="AF55" t="n">
-        <v>218.37</v>
+        <v>218.04</v>
       </c>
       <c r="AG55" t="n">
-        <v>-4.49</v>
+        <v>-0.33</v>
       </c>
       <c r="AH55" t="n">
         <v>215</v>
@@ -4865,10 +5837,10 @@
         <v>235</v>
       </c>
       <c r="AK55" t="n">
-        <v>131.24</v>
+        <v>129.21</v>
       </c>
       <c r="AL55" t="n">
-        <v>-4.18</v>
+        <v>-2.03</v>
       </c>
       <c r="AM55" t="n">
         <v>110</v>
@@ -4877,81 +5849,81 @@
         <v>142</v>
       </c>
       <c r="AP55" t="n">
-        <v>79.98999999999999</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="AS55" t="n">
-        <v>12.97</v>
+        <v>15.23</v>
       </c>
       <c r="BL55" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B56" t="n">
-        <v>154.1</v>
+        <v>148.8</v>
       </c>
       <c r="C56" t="n">
-        <v>65</v>
+        <v>57.6</v>
       </c>
       <c r="D56" t="n">
-        <v>32</v>
+        <v>32.7</v>
       </c>
       <c r="E56" t="n">
-        <v>25.2</v>
+        <v>26.3</v>
       </c>
       <c r="F56" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="H56" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="I56" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="J56" t="n">
-        <v>38.5</v>
+        <v>41.6</v>
       </c>
       <c r="K56" t="n">
-        <v>70.90000000000001</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="M56" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="N56" t="n">
-        <v>32.3</v>
+        <v>35</v>
       </c>
       <c r="O56" t="n">
-        <v>40.3</v>
+        <v>42.4</v>
       </c>
       <c r="Q56" t="n">
         <v>21.7</v>
       </c>
       <c r="R56" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="S56" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="T56" t="n">
         <v>21.7</v>
       </c>
       <c r="Y56" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z56" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA56" t="n">
-        <v>14.5</v>
+        <v>15.6</v>
       </c>
       <c r="AF56" t="n">
-        <v>218.04</v>
+        <v>220.84</v>
       </c>
       <c r="AG56" t="n">
-        <v>-0.33</v>
+        <v>2.8</v>
       </c>
       <c r="AH56" t="n">
         <v>215</v>
@@ -4960,10 +5932,10 @@
         <v>235</v>
       </c>
       <c r="AK56" t="n">
-        <v>129.21</v>
+        <v>129.07</v>
       </c>
       <c r="AL56" t="n">
-        <v>-2.03</v>
+        <v>-0.14</v>
       </c>
       <c r="AM56" t="n">
         <v>110</v>
@@ -4972,81 +5944,81 @@
         <v>142</v>
       </c>
       <c r="AP56" t="n">
-        <v>82.90000000000001</v>
+        <v>85.52</v>
       </c>
       <c r="AS56" t="n">
-        <v>15.23</v>
+        <v>15.82</v>
       </c>
       <c r="BL56" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B57" t="n">
-        <v>148.8</v>
+        <v>146.8</v>
       </c>
       <c r="C57" t="n">
-        <v>57.6</v>
+        <v>52.8</v>
       </c>
       <c r="D57" t="n">
-        <v>32.7</v>
+        <v>33.6</v>
       </c>
       <c r="E57" t="n">
-        <v>26.3</v>
+        <v>28.9</v>
       </c>
       <c r="F57" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="H57" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="I57" t="n">
-        <v>8.9</v>
+        <v>9.1</v>
       </c>
       <c r="J57" t="n">
-        <v>41.6</v>
+        <v>40.8</v>
       </c>
       <c r="K57" t="n">
-        <v>74.09999999999999</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="M57" t="n">
-        <v>7.4</v>
+        <v>5.6</v>
       </c>
       <c r="N57" t="n">
-        <v>35</v>
+        <v>33.1</v>
       </c>
       <c r="O57" t="n">
-        <v>42.4</v>
+        <v>38.7</v>
       </c>
       <c r="Q57" t="n">
-        <v>21.7</v>
+        <v>22</v>
       </c>
       <c r="R57" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>21.7</v>
+        <v>22</v>
       </c>
       <c r="Y57" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z57" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA57" t="n">
-        <v>15.6</v>
+        <v>16.1</v>
       </c>
       <c r="AF57" t="n">
-        <v>220.84</v>
+        <v>225.87</v>
       </c>
       <c r="AG57" t="n">
-        <v>2.8</v>
+        <v>5.03</v>
       </c>
       <c r="AH57" t="n">
         <v>215</v>
@@ -5055,10 +6027,10 @@
         <v>235</v>
       </c>
       <c r="AK57" t="n">
-        <v>129.07</v>
+        <v>130.73</v>
       </c>
       <c r="AL57" t="n">
-        <v>-0.14</v>
+        <v>1.66</v>
       </c>
       <c r="AM57" t="n">
         <v>110</v>
@@ -5067,81 +6039,36 @@
         <v>142</v>
       </c>
       <c r="AP57" t="n">
-        <v>85.52</v>
+        <v>88.2</v>
       </c>
       <c r="AS57" t="n">
-        <v>15.82</v>
+        <v>15.76</v>
       </c>
       <c r="BL57" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B58" t="n">
-        <v>146.8</v>
-      </c>
-      <c r="C58" t="n">
-        <v>52.8</v>
+        <v>133.9</v>
       </c>
       <c r="D58" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="E58" t="n">
-        <v>28.9</v>
+        <v>34.7</v>
       </c>
       <c r="F58" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="H58" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="I58" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="J58" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="K58" t="n">
-        <v>73.59999999999999</v>
-      </c>
-      <c r="M58" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="N58" t="n">
-        <v>33.1</v>
-      </c>
-      <c r="O58" t="n">
-        <v>38.7</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>22</v>
-      </c>
-      <c r="R58" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="S58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T58" t="n">
-        <v>22</v>
+        <v>3.3</v>
       </c>
       <c r="Y58" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z58" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AA58" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="AF58" t="n">
-        <v>225.87</v>
-      </c>
-      <c r="AG58" t="n">
-        <v>5.03</v>
+        <v>15</v>
       </c>
       <c r="AH58" t="n">
         <v>215</v>
@@ -5149,49 +6076,37 @@
       <c r="AI58" t="n">
         <v>235</v>
       </c>
-      <c r="AK58" t="n">
-        <v>130.73</v>
-      </c>
-      <c r="AL58" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AM58" t="n">
         <v>110</v>
       </c>
       <c r="AN58" t="n">
         <v>142</v>
       </c>
-      <c r="AP58" t="n">
-        <v>88.2</v>
-      </c>
-      <c r="AS58" t="n">
-        <v>15.76</v>
-      </c>
       <c r="BL58" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B59" t="n">
-        <v>133.9</v>
+        <v>137.5</v>
       </c>
       <c r="D59" t="n">
-        <v>34.7</v>
+        <v>32.8</v>
       </c>
       <c r="F59" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="Y59" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z59" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="AA59" t="n">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="AH59" t="n">
         <v>215</v>
@@ -5206,30 +6121,75 @@
         <v>142</v>
       </c>
       <c r="BL59" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B60" t="n">
-        <v>137.5</v>
+        <v>157.1</v>
+      </c>
+      <c r="C60" t="n">
+        <v>73.09999999999999</v>
       </c>
       <c r="D60" t="n">
-        <v>32.8</v>
+        <v>31.7</v>
+      </c>
+      <c r="E60" t="n">
+        <v>26.1</v>
       </c>
       <c r="F60" t="n">
-        <v>2.3</v>
+        <v>2</v>
+      </c>
+      <c r="H60" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="I60" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="J60" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="K60" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="M60" t="n">
+        <v>6</v>
+      </c>
+      <c r="N60" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="O60" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="R60" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>23.8</v>
       </c>
       <c r="Y60" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="Z60" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA60" t="n">
-        <v>10.5</v>
+        <v>7.9</v>
+      </c>
+      <c r="AF60" t="n">
+        <v>224.2</v>
+      </c>
+      <c r="AG60" t="n">
+        <v>-1.67</v>
       </c>
       <c r="AH60" t="n">
         <v>215</v>
@@ -5237,37 +6197,49 @@
       <c r="AI60" t="n">
         <v>235</v>
       </c>
+      <c r="AK60" t="n">
+        <v>128.6</v>
+      </c>
+      <c r="AL60" t="n">
+        <v>-2.13</v>
+      </c>
       <c r="AM60" t="n">
         <v>110</v>
       </c>
       <c r="AN60" t="n">
         <v>142</v>
       </c>
+      <c r="AP60" t="n">
+        <v>81.18000000000001</v>
+      </c>
+      <c r="AS60" t="n">
+        <v>14.06</v>
+      </c>
       <c r="BL60" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B61" t="n">
-        <v>141</v>
+        <v>150.3</v>
       </c>
       <c r="D61" t="n">
-        <v>31.9</v>
+        <v>33.3</v>
       </c>
       <c r="F61" t="n">
         <v>2.3</v>
       </c>
       <c r="Y61" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Z61" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AA61" t="n">
-        <v>7.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH61" t="n">
         <v>215</v>
@@ -5282,30 +6254,30 @@
         <v>142</v>
       </c>
       <c r="BL61" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B62" t="n">
-        <v>150.3</v>
+        <v>132.8</v>
       </c>
       <c r="D62" t="n">
-        <v>33.3</v>
+        <v>33.8</v>
       </c>
       <c r="F62" t="n">
         <v>2.3</v>
       </c>
       <c r="Y62" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="Z62" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA62" t="n">
         <v>16</v>
-      </c>
-      <c r="AA62" t="n">
-        <v>10.5</v>
       </c>
       <c r="AH62" t="n">
         <v>215</v>
@@ -5320,7 +6292,7 @@
         <v>142</v>
       </c>
       <c r="BL62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -628,55 +628,55 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="B2" t="n">
-        <v>136.7</v>
+        <v>138.5</v>
       </c>
       <c r="D2" t="n">
-        <v>30.7</v>
+        <v>31.7</v>
       </c>
       <c r="F2" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="K2" t="n">
-        <v>92.59999999999999</v>
+        <v>91</v>
       </c>
       <c r="O2" t="n">
-        <v>39.2</v>
+        <v>37.8</v>
       </c>
       <c r="V2" t="n">
-        <v>17.1</v>
+        <v>13.2</v>
       </c>
       <c r="W2" t="n">
-        <v>36.1</v>
+        <v>22.5</v>
       </c>
       <c r="X2" t="n">
-        <v>26.6</v>
+        <v>17.9</v>
       </c>
       <c r="Y2" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="Z2" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AA2" t="n">
-        <v>20.5</v>
+        <v>15.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.6</v>
+        <v>-1.9</v>
       </c>
       <c r="AC2" t="n">
-        <v>6.7</v>
+        <v>5.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>4.7</v>
+        <v>1.7</v>
       </c>
       <c r="AF2" t="n">
-        <v>235.4</v>
+        <v>231.99</v>
       </c>
       <c r="AG2" t="n">
-        <v>3.09</v>
+        <v>-3.41</v>
       </c>
       <c r="AH2" t="n">
         <v>215</v>
@@ -685,10 +685,10 @@
         <v>235</v>
       </c>
       <c r="AK2" t="n">
-        <v>137.5</v>
+        <v>136.12</v>
       </c>
       <c r="AL2" t="n">
-        <v>3.06</v>
+        <v>-1.38</v>
       </c>
       <c r="AM2" t="n">
         <v>110</v>
@@ -697,60 +697,93 @@
         <v>142</v>
       </c>
       <c r="BL2" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B3" t="n">
-        <v>138.5</v>
+        <v>161.1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>67</v>
       </c>
       <c r="D3" t="n">
-        <v>31.7</v>
+        <v>31.9</v>
+      </c>
+      <c r="E3" t="n">
+        <v>31.5</v>
       </c>
       <c r="F3" t="n">
-        <v>7</v>
+        <v>7.7</v>
+      </c>
+      <c r="H3" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J3" t="n">
+        <v>41.1</v>
       </c>
       <c r="K3" t="n">
-        <v>91</v>
+        <v>75.59999999999999</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="N3" t="n">
+        <v>35</v>
       </c>
       <c r="O3" t="n">
-        <v>37.8</v>
+        <v>37.2</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3</v>
+      </c>
+      <c r="T3" t="n">
+        <v>20.5</v>
       </c>
       <c r="V3" t="n">
-        <v>13.2</v>
+        <v>14.1</v>
       </c>
       <c r="W3" t="n">
-        <v>22.5</v>
+        <v>19.3</v>
       </c>
       <c r="X3" t="n">
-        <v>17.9</v>
+        <v>16.7</v>
       </c>
       <c r="Y3" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="Z3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AA3" t="n">
-        <v>15.5</v>
+        <v>11.1</v>
       </c>
       <c r="AB3" t="n">
-        <v>-1.9</v>
+        <v>-3.8</v>
       </c>
       <c r="AC3" t="n">
-        <v>5.2</v>
+        <v>3.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.7</v>
+        <v>-0.3</v>
       </c>
       <c r="AF3" t="n">
-        <v>231.99</v>
+        <v>225.51</v>
       </c>
       <c r="AG3" t="n">
-        <v>-3.41</v>
+        <v>-6.48</v>
       </c>
       <c r="AH3" t="n">
         <v>215</v>
@@ -759,10 +792,10 @@
         <v>235</v>
       </c>
       <c r="AK3" t="n">
-        <v>136.12</v>
+        <v>133.83</v>
       </c>
       <c r="AL3" t="n">
-        <v>-1.38</v>
+        <v>-2.29</v>
       </c>
       <c r="AM3" t="n">
         <v>110</v>
@@ -770,94 +803,100 @@
       <c r="AN3" t="n">
         <v>142</v>
       </c>
+      <c r="AP3" t="n">
+        <v>82.93000000000001</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>15.73</v>
+      </c>
       <c r="BL3" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B4" t="n">
-        <v>161.1</v>
+        <v>176.4</v>
       </c>
       <c r="C4" t="n">
-        <v>67</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>31.9</v>
+        <v>32.7</v>
       </c>
       <c r="E4" t="n">
-        <v>31.5</v>
+        <v>35</v>
       </c>
       <c r="F4" t="n">
-        <v>7.7</v>
+        <v>6.8</v>
       </c>
       <c r="H4" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="I4" t="n">
         <v>11.4</v>
       </c>
       <c r="J4" t="n">
-        <v>41.1</v>
+        <v>41.5</v>
       </c>
       <c r="K4" t="n">
-        <v>75.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="M4" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="N4" t="n">
-        <v>35</v>
+        <v>36.4</v>
       </c>
       <c r="O4" t="n">
-        <v>37.2</v>
+        <v>39.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>20.5</v>
+        <v>22.3</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="T4" t="n">
-        <v>20.5</v>
+        <v>22.3</v>
       </c>
       <c r="V4" t="n">
-        <v>14.1</v>
+        <v>11.5</v>
       </c>
       <c r="W4" t="n">
-        <v>19.3</v>
+        <v>15.5</v>
       </c>
       <c r="X4" t="n">
-        <v>16.7</v>
+        <v>13.5</v>
       </c>
       <c r="Y4" t="n">
         <v>9</v>
       </c>
       <c r="Z4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA4" t="n">
-        <v>11.1</v>
+        <v>11.6</v>
       </c>
       <c r="AB4" t="n">
-        <v>-3.8</v>
+        <v>-5.6</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0.3</v>
+        <v>-1.3</v>
       </c>
       <c r="AF4" t="n">
-        <v>225.51</v>
+        <v>220.92</v>
       </c>
       <c r="AG4" t="n">
-        <v>-6.48</v>
+        <v>-4.59</v>
       </c>
       <c r="AH4" t="n">
         <v>215</v>
@@ -866,10 +905,10 @@
         <v>235</v>
       </c>
       <c r="AK4" t="n">
-        <v>133.83</v>
+        <v>131.85</v>
       </c>
       <c r="AL4" t="n">
-        <v>-2.29</v>
+        <v>-1.98</v>
       </c>
       <c r="AM4" t="n">
         <v>110</v>
@@ -878,99 +917,99 @@
         <v>142</v>
       </c>
       <c r="AP4" t="n">
-        <v>82.93000000000001</v>
+        <v>79.75</v>
       </c>
       <c r="AS4" t="n">
-        <v>15.73</v>
+        <v>15.49</v>
       </c>
       <c r="BL4" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B5" t="n">
-        <v>176.4</v>
+        <v>181</v>
       </c>
       <c r="C5" t="n">
-        <v>77.09999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="D5" t="n">
-        <v>32.7</v>
+        <v>33</v>
       </c>
       <c r="E5" t="n">
-        <v>35</v>
+        <v>35.1</v>
       </c>
       <c r="F5" t="n">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="H5" t="n">
-        <v>23.2</v>
+        <v>22.8</v>
       </c>
       <c r="I5" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="K5" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N5" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="O5" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S5" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="T5" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="V5" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="W5" t="n">
+        <v>13</v>
+      </c>
+      <c r="X5" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA5" t="n">
         <v>11.4</v>
       </c>
-      <c r="J5" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="K5" t="n">
-        <v>76</v>
-      </c>
-      <c r="M5" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N5" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="O5" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>14</v>
-      </c>
-      <c r="T5" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="V5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="W5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="X5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>11.6</v>
-      </c>
       <c r="AB5" t="n">
-        <v>-5.6</v>
+        <v>-6.1</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>-1.3</v>
+        <v>-0.9</v>
       </c>
       <c r="AF5" t="n">
         <v>220.92</v>
       </c>
       <c r="AG5" t="n">
-        <v>-4.59</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
         <v>215</v>
@@ -979,10 +1018,10 @@
         <v>235</v>
       </c>
       <c r="AK5" t="n">
-        <v>131.85</v>
+        <v>130.06</v>
       </c>
       <c r="AL5" t="n">
-        <v>-1.98</v>
+        <v>-1.79</v>
       </c>
       <c r="AM5" t="n">
         <v>110</v>
@@ -991,99 +1030,99 @@
         <v>142</v>
       </c>
       <c r="AP5" t="n">
-        <v>79.75</v>
+        <v>79.94</v>
       </c>
       <c r="AS5" t="n">
-        <v>15.49</v>
+        <v>14.93</v>
       </c>
       <c r="BL5" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B6" t="n">
-        <v>181</v>
+        <v>179.6</v>
       </c>
       <c r="C6" t="n">
-        <v>80.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>33</v>
+        <v>30.3</v>
       </c>
       <c r="E6" t="n">
-        <v>35.1</v>
+        <v>31.1</v>
       </c>
       <c r="F6" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="H6" t="n">
-        <v>22.8</v>
+        <v>21.5</v>
       </c>
       <c r="I6" t="n">
-        <v>11.2</v>
+        <v>10.8</v>
       </c>
       <c r="J6" t="n">
-        <v>41.9</v>
+        <v>42.3</v>
       </c>
       <c r="K6" t="n">
-        <v>75.90000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>2.9</v>
+        <v>4.3</v>
       </c>
       <c r="N6" t="n">
-        <v>36.9</v>
+        <v>37.1</v>
       </c>
       <c r="O6" t="n">
-        <v>39.8</v>
+        <v>41.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="R6" t="n">
+        <v>2</v>
+      </c>
+      <c r="S6" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="T6" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="V6" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="W6" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="X6" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AD6" t="n">
         <v>0.5</v>
       </c>
-      <c r="S6" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="T6" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="V6" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="W6" t="n">
-        <v>13</v>
-      </c>
-      <c r="X6" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>-6.1</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>-0.9</v>
-      </c>
       <c r="AF6" t="n">
-        <v>220.92</v>
+        <v>216.02</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AH6" t="n">
         <v>215</v>
@@ -1092,10 +1131,10 @@
         <v>235</v>
       </c>
       <c r="AK6" t="n">
-        <v>130.06</v>
+        <v>127.85</v>
       </c>
       <c r="AL6" t="n">
-        <v>-1.79</v>
+        <v>-2.21</v>
       </c>
       <c r="AM6" t="n">
         <v>110</v>
@@ -1104,99 +1143,99 @@
         <v>142</v>
       </c>
       <c r="AP6" t="n">
-        <v>79.94</v>
+        <v>82.2</v>
       </c>
       <c r="AS6" t="n">
-        <v>14.93</v>
+        <v>15.16</v>
       </c>
       <c r="BL6" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B7" t="n">
-        <v>179.6</v>
+        <v>170.4</v>
       </c>
       <c r="C7" t="n">
-        <v>81.90000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="D7" t="n">
-        <v>30.3</v>
+        <v>29.8</v>
       </c>
       <c r="E7" t="n">
-        <v>31.1</v>
+        <v>29.7</v>
       </c>
       <c r="F7" t="n">
-        <v>6.8</v>
+        <v>6.3</v>
       </c>
       <c r="H7" t="n">
-        <v>21.5</v>
+        <v>22.5</v>
       </c>
       <c r="I7" t="n">
-        <v>10.8</v>
+        <v>11.2</v>
       </c>
       <c r="J7" t="n">
-        <v>42.3</v>
+        <v>41.4</v>
       </c>
       <c r="K7" t="n">
-        <v>74.59999999999999</v>
+        <v>75</v>
       </c>
       <c r="M7" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="N7" t="n">
-        <v>37.1</v>
+        <v>36.6</v>
       </c>
       <c r="O7" t="n">
-        <v>41.4</v>
+        <v>41.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>22.6</v>
+        <v>23.3</v>
       </c>
       <c r="R7" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="S7" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="T7" t="n">
-        <v>22.6</v>
+        <v>23.3</v>
       </c>
       <c r="V7" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="W7" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="X7" t="n">
         <v>12.6</v>
       </c>
       <c r="Y7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
         <v>13</v>
       </c>
       <c r="AA7" t="n">
-        <v>11.1</v>
+        <v>12.7</v>
       </c>
       <c r="AB7" t="n">
-        <v>-3.4</v>
+        <v>1.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.4</v>
+        <v>7.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.5</v>
+        <v>4.7</v>
       </c>
       <c r="AF7" t="n">
         <v>216.02</v>
       </c>
       <c r="AG7" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
         <v>215</v>
@@ -1205,10 +1244,10 @@
         <v>235</v>
       </c>
       <c r="AK7" t="n">
-        <v>127.85</v>
+        <v>128.54</v>
       </c>
       <c r="AL7" t="n">
-        <v>-2.21</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AM7" t="n">
         <v>110</v>
@@ -1217,99 +1256,66 @@
         <v>142</v>
       </c>
       <c r="AP7" t="n">
-        <v>82.2</v>
+        <v>84.73</v>
       </c>
       <c r="AS7" t="n">
-        <v>15.16</v>
+        <v>15.34</v>
       </c>
       <c r="BL7" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B8" t="n">
-        <v>170.4</v>
-      </c>
-      <c r="C8" t="n">
-        <v>78.5</v>
+        <v>156</v>
       </c>
       <c r="D8" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="E8" t="n">
-        <v>29.7</v>
+        <v>30.1</v>
       </c>
       <c r="F8" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="H8" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="I8" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="J8" t="n">
-        <v>41.4</v>
+        <v>6.8</v>
       </c>
       <c r="K8" t="n">
-        <v>75</v>
-      </c>
-      <c r="M8" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="N8" t="n">
-        <v>36.6</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S8" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="T8" t="n">
-        <v>23.3</v>
+        <v>39.2</v>
       </c>
       <c r="V8" t="n">
-        <v>9.5</v>
+        <v>7.1</v>
       </c>
       <c r="W8" t="n">
-        <v>15.7</v>
+        <v>20.9</v>
       </c>
       <c r="X8" t="n">
-        <v>12.6</v>
+        <v>14</v>
       </c>
       <c r="Y8" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Z8" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA8" t="n">
-        <v>12.7</v>
+        <v>13.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.8</v>
+        <v>-0.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="AD8" t="n">
-        <v>4.7</v>
+        <v>2.4</v>
       </c>
       <c r="AF8" t="n">
-        <v>216.02</v>
+        <v>224.53</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH8" t="n">
         <v>215</v>
@@ -1318,10 +1324,10 @@
         <v>235</v>
       </c>
       <c r="AK8" t="n">
-        <v>128.54</v>
+        <v>130.92</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.6899999999999999</v>
+        <v>2.38</v>
       </c>
       <c r="AM8" t="n">
         <v>110</v>
@@ -1329,67 +1335,61 @@
       <c r="AN8" t="n">
         <v>142</v>
       </c>
-      <c r="AP8" t="n">
-        <v>84.73</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>15.34</v>
-      </c>
       <c r="BL8" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B9" t="n">
-        <v>156</v>
+        <v>147.8</v>
       </c>
       <c r="D9" t="n">
-        <v>30.1</v>
+        <v>32</v>
       </c>
       <c r="F9" t="n">
         <v>6.8</v>
       </c>
       <c r="K9" t="n">
-        <v>95.90000000000001</v>
+        <v>96.5</v>
       </c>
       <c r="O9" t="n">
-        <v>39.2</v>
+        <v>39.3</v>
       </c>
       <c r="V9" t="n">
-        <v>7.1</v>
+        <v>8</v>
       </c>
       <c r="W9" t="n">
-        <v>20.9</v>
+        <v>22.4</v>
       </c>
       <c r="X9" t="n">
-        <v>14</v>
+        <v>15.2</v>
       </c>
       <c r="Y9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA9" t="n">
         <v>13.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="AC9" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AF9" t="n">
-        <v>224.53</v>
+        <v>230.27</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.32</v>
+        <v>5.74</v>
       </c>
       <c r="AH9" t="n">
         <v>215</v>
@@ -1398,10 +1398,10 @@
         <v>235</v>
       </c>
       <c r="AK9" t="n">
-        <v>130.92</v>
+        <v>132.76</v>
       </c>
       <c r="AL9" t="n">
-        <v>2.38</v>
+        <v>1.84</v>
       </c>
       <c r="AM9" t="n">
         <v>110</v>
@@ -1410,60 +1410,93 @@
         <v>142</v>
       </c>
       <c r="BL9" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="B10" t="n">
-        <v>147.8</v>
+        <v>149.1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>60</v>
       </c>
       <c r="D10" t="n">
-        <v>32</v>
+        <v>29</v>
+      </c>
+      <c r="E10" t="n">
+        <v>25.9</v>
       </c>
       <c r="F10" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
+      </c>
+      <c r="H10" t="n">
+        <v>24</v>
+      </c>
+      <c r="I10" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="J10" t="n">
+        <v>38.8</v>
       </c>
       <c r="K10" t="n">
-        <v>96.5</v>
+        <v>74.5</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N10" t="n">
+        <v>36.7</v>
       </c>
       <c r="O10" t="n">
-        <v>39.3</v>
+        <v>40.1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>7</v>
+      </c>
+      <c r="T10" t="n">
+        <v>21.7</v>
       </c>
       <c r="V10" t="n">
-        <v>8</v>
+        <v>10.3</v>
       </c>
       <c r="W10" t="n">
-        <v>22.4</v>
+        <v>24.4</v>
       </c>
       <c r="X10" t="n">
-        <v>15.2</v>
+        <v>17.4</v>
       </c>
       <c r="Y10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z10" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AA10" t="n">
-        <v>13.5</v>
+        <v>15.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0.3</v>
+        <v>-2.4</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.6</v>
+        <v>2.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.1</v>
+        <v>-0.1</v>
       </c>
       <c r="AF10" t="n">
-        <v>230.27</v>
+        <v>237.43</v>
       </c>
       <c r="AG10" t="n">
-        <v>5.74</v>
+        <v>7.16</v>
       </c>
       <c r="AH10" t="n">
         <v>215</v>
@@ -1472,10 +1505,10 @@
         <v>235</v>
       </c>
       <c r="AK10" t="n">
-        <v>132.76</v>
+        <v>134.95</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.84</v>
+        <v>2.19</v>
       </c>
       <c r="AM10" t="n">
         <v>110</v>
@@ -1483,94 +1516,67 @@
       <c r="AN10" t="n">
         <v>142</v>
       </c>
+      <c r="AP10" t="n">
+        <v>91.28</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>16.95</v>
+      </c>
       <c r="BL10" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="B11" t="n">
-        <v>149.1</v>
-      </c>
-      <c r="C11" t="n">
-        <v>60</v>
+        <v>143.9</v>
       </c>
       <c r="D11" t="n">
-        <v>29</v>
-      </c>
-      <c r="E11" t="n">
-        <v>25.9</v>
+        <v>32.9</v>
       </c>
       <c r="F11" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="H11" t="n">
-        <v>24</v>
-      </c>
-      <c r="I11" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="J11" t="n">
-        <v>38.8</v>
+        <v>6.8</v>
       </c>
       <c r="K11" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="M11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N11" t="n">
-        <v>36.7</v>
+        <v>96.2</v>
       </c>
       <c r="O11" t="n">
-        <v>40.1</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>7</v>
-      </c>
-      <c r="T11" t="n">
-        <v>21.7</v>
+        <v>37.9</v>
       </c>
       <c r="V11" t="n">
-        <v>10.3</v>
+        <v>10</v>
       </c>
       <c r="W11" t="n">
-        <v>24.4</v>
+        <v>25.6</v>
       </c>
       <c r="X11" t="n">
-        <v>17.4</v>
+        <v>17.8</v>
       </c>
       <c r="Y11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AA11" t="n">
-        <v>15.7</v>
+        <v>16</v>
       </c>
       <c r="AB11" t="n">
-        <v>-2.4</v>
+        <v>-1.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0.1</v>
+        <v>0.9</v>
       </c>
       <c r="AF11" t="n">
-        <v>237.43</v>
+        <v>236.14</v>
       </c>
       <c r="AG11" t="n">
-        <v>7.16</v>
+        <v>-1.29</v>
       </c>
       <c r="AH11" t="n">
         <v>215</v>
@@ -1579,10 +1585,10 @@
         <v>235</v>
       </c>
       <c r="AK11" t="n">
-        <v>134.95</v>
+        <v>136.28</v>
       </c>
       <c r="AL11" t="n">
-        <v>2.19</v>
+        <v>1.33</v>
       </c>
       <c r="AM11" t="n">
         <v>110</v>
@@ -1590,67 +1596,94 @@
       <c r="AN11" t="n">
         <v>142</v>
       </c>
-      <c r="AP11" t="n">
-        <v>91.28</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>16.95</v>
-      </c>
       <c r="BL11" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B12" t="n">
-        <v>143.9</v>
+        <v>166.4</v>
+      </c>
+      <c r="C12" t="n">
+        <v>63.7</v>
       </c>
       <c r="D12" t="n">
-        <v>32.9</v>
+        <v>34.5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>36.4</v>
       </c>
       <c r="F12" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
+      </c>
+      <c r="H12" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="I12" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="J12" t="n">
+        <v>39.9</v>
       </c>
       <c r="K12" t="n">
-        <v>96.2</v>
+        <v>75.2</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>35.9</v>
       </c>
       <c r="O12" t="n">
-        <v>37.9</v>
+        <v>39</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="S12" t="n">
+        <v>6</v>
+      </c>
+      <c r="T12" t="n">
+        <v>20.3</v>
       </c>
       <c r="V12" t="n">
-        <v>10</v>
+        <v>11.9</v>
       </c>
       <c r="W12" t="n">
-        <v>25.6</v>
+        <v>27</v>
       </c>
       <c r="X12" t="n">
-        <v>17.8</v>
+        <v>19.4</v>
       </c>
       <c r="Y12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z12" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AA12" t="n">
-        <v>16</v>
+        <v>14.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>-1.4</v>
+        <v>-3.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.9</v>
+        <v>-0.4</v>
       </c>
       <c r="AF12" t="n">
-        <v>236.14</v>
+        <v>236.13</v>
       </c>
       <c r="AG12" t="n">
-        <v>-1.29</v>
+        <v>-0.01</v>
       </c>
       <c r="AH12" t="n">
         <v>215</v>
@@ -1659,10 +1692,10 @@
         <v>235</v>
       </c>
       <c r="AK12" t="n">
-        <v>136.28</v>
+        <v>134.54</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.33</v>
+        <v>-1.74</v>
       </c>
       <c r="AM12" t="n">
         <v>110</v>
@@ -1670,94 +1703,100 @@
       <c r="AN12" t="n">
         <v>142</v>
       </c>
+      <c r="AP12" t="n">
+        <v>82.27</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>16.28</v>
+      </c>
       <c r="BL12" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B13" t="n">
-        <v>166.4</v>
+        <v>172.9</v>
       </c>
       <c r="C13" t="n">
-        <v>63.7</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>34.5</v>
+        <v>34.9</v>
       </c>
       <c r="E13" t="n">
-        <v>36.4</v>
+        <v>35.2</v>
       </c>
       <c r="F13" t="n">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="H13" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="I13" t="n">
-        <v>11.6</v>
+        <v>11.3</v>
       </c>
       <c r="J13" t="n">
-        <v>39.9</v>
+        <v>41.7</v>
       </c>
       <c r="K13" t="n">
-        <v>75.2</v>
+        <v>76.7</v>
       </c>
       <c r="M13" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="N13" t="n">
-        <v>35.9</v>
+        <v>34.8</v>
       </c>
       <c r="O13" t="n">
-        <v>39</v>
+        <v>37.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>20.3</v>
+        <v>19</v>
       </c>
       <c r="R13" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T13" t="n">
-        <v>20.3</v>
+        <v>19</v>
       </c>
       <c r="V13" t="n">
-        <v>11.9</v>
+        <v>14.4</v>
       </c>
       <c r="W13" t="n">
-        <v>27</v>
+        <v>18.7</v>
       </c>
       <c r="X13" t="n">
-        <v>19.4</v>
+        <v>16.6</v>
       </c>
       <c r="Y13" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Z13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA13" t="n">
-        <v>14.4</v>
+        <v>12.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>-3.5</v>
+        <v>-4.9</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0.4</v>
+        <v>-0.7</v>
       </c>
       <c r="AF13" t="n">
-        <v>236.13</v>
+        <v>218.6</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.01</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="AH13" t="n">
         <v>215</v>
@@ -1766,10 +1805,10 @@
         <v>235</v>
       </c>
       <c r="AK13" t="n">
-        <v>134.54</v>
+        <v>130.39</v>
       </c>
       <c r="AL13" t="n">
-        <v>-1.74</v>
+        <v>-4.15</v>
       </c>
       <c r="AM13" t="n">
         <v>110</v>
@@ -1778,99 +1817,99 @@
         <v>142</v>
       </c>
       <c r="AP13" t="n">
-        <v>82.27</v>
+        <v>78.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>16.28</v>
+        <v>15.79</v>
       </c>
       <c r="BL13" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B14" t="n">
-        <v>172.9</v>
+        <v>157.5</v>
       </c>
       <c r="C14" t="n">
-        <v>67.59999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="D14" t="n">
-        <v>34.9</v>
+        <v>33.2</v>
       </c>
       <c r="E14" t="n">
-        <v>35.2</v>
+        <v>27.7</v>
       </c>
       <c r="F14" t="n">
-        <v>7.3</v>
+        <v>3.6</v>
       </c>
       <c r="H14" t="n">
-        <v>23.6</v>
+        <v>23.4</v>
       </c>
       <c r="I14" t="n">
         <v>11.3</v>
       </c>
       <c r="J14" t="n">
-        <v>41.7</v>
+        <v>41.4</v>
       </c>
       <c r="K14" t="n">
-        <v>76.7</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="N14" t="n">
-        <v>34.8</v>
+        <v>34.9</v>
       </c>
       <c r="O14" t="n">
-        <v>37.2</v>
+        <v>37.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>19</v>
+        <v>21.6</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T14" t="n">
-        <v>19</v>
+        <v>21.6</v>
       </c>
       <c r="V14" t="n">
-        <v>14.4</v>
+        <v>15.1</v>
       </c>
       <c r="W14" t="n">
-        <v>18.7</v>
+        <v>23.1</v>
       </c>
       <c r="X14" t="n">
-        <v>16.6</v>
+        <v>19.1</v>
       </c>
       <c r="Y14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z14" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AA14" t="n">
-        <v>12.5</v>
+        <v>13.6</v>
       </c>
       <c r="AB14" t="n">
-        <v>-4.9</v>
+        <v>-0</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0.7</v>
+        <v>1.5</v>
       </c>
       <c r="AF14" t="n">
-        <v>218.6</v>
+        <v>218.84</v>
       </c>
       <c r="AG14" t="n">
-        <v>-9.380000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="AH14" t="n">
         <v>215</v>
@@ -1879,10 +1918,10 @@
         <v>235</v>
       </c>
       <c r="AK14" t="n">
-        <v>130.39</v>
+        <v>133.09</v>
       </c>
       <c r="AL14" t="n">
-        <v>-4.15</v>
+        <v>2.7</v>
       </c>
       <c r="AM14" t="n">
         <v>110</v>
@@ -1891,99 +1930,66 @@
         <v>142</v>
       </c>
       <c r="AP14" t="n">
-        <v>78.5</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="AS14" t="n">
-        <v>15.79</v>
+        <v>15.63</v>
       </c>
       <c r="BL14" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B15" t="n">
-        <v>157.5</v>
-      </c>
-      <c r="C15" t="n">
-        <v>68.5</v>
+        <v>137.6</v>
       </c>
       <c r="D15" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="E15" t="n">
-        <v>27.7</v>
+        <v>35</v>
       </c>
       <c r="F15" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H15" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="I15" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J15" t="n">
-        <v>41.4</v>
+        <v>6.5</v>
       </c>
       <c r="K15" t="n">
-        <v>76.09999999999999</v>
-      </c>
-      <c r="M15" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="N15" t="n">
-        <v>34.9</v>
+        <v>96.7</v>
       </c>
       <c r="O15" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>9</v>
-      </c>
-      <c r="T15" t="n">
-        <v>21.6</v>
+        <v>35.1</v>
       </c>
       <c r="V15" t="n">
-        <v>15.1</v>
+        <v>13.6</v>
       </c>
       <c r="W15" t="n">
-        <v>23.1</v>
+        <v>24.4</v>
       </c>
       <c r="X15" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="Y15" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Z15" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AA15" t="n">
-        <v>13.6</v>
+        <v>17.5</v>
       </c>
       <c r="AB15" t="n">
         <v>-0</v>
       </c>
       <c r="AC15" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="AF15" t="n">
-        <v>218.84</v>
+        <v>221.78</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.25</v>
+        <v>2.94</v>
       </c>
       <c r="AH15" t="n">
         <v>215</v>
@@ -1992,10 +1998,10 @@
         <v>235</v>
       </c>
       <c r="AK15" t="n">
-        <v>133.09</v>
+        <v>138.76</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.7</v>
+        <v>5.67</v>
       </c>
       <c r="AM15" t="n">
         <v>110</v>
@@ -2003,67 +2009,61 @@
       <c r="AN15" t="n">
         <v>142</v>
       </c>
-      <c r="AP15" t="n">
-        <v>83.09999999999999</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>15.63</v>
-      </c>
       <c r="BL15" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B16" t="n">
-        <v>137.6</v>
+        <v>132.5</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>33.6</v>
       </c>
       <c r="F16" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="K16" t="n">
-        <v>96.7</v>
+        <v>97.8</v>
       </c>
       <c r="O16" t="n">
-        <v>35.1</v>
+        <v>31.6</v>
       </c>
       <c r="V16" t="n">
-        <v>13.6</v>
+        <v>14.8</v>
       </c>
       <c r="W16" t="n">
-        <v>24.4</v>
+        <v>24.7</v>
       </c>
       <c r="X16" t="n">
-        <v>19</v>
+        <v>19.8</v>
       </c>
       <c r="Y16" t="n">
         <v>14</v>
       </c>
       <c r="Z16" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AA16" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>-0</v>
+        <v>0.6</v>
       </c>
       <c r="AC16" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="AF16" t="n">
-        <v>221.78</v>
+        <v>224.78</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="AH16" t="n">
         <v>215</v>
@@ -2072,10 +2072,10 @@
         <v>235</v>
       </c>
       <c r="AK16" t="n">
-        <v>138.76</v>
+        <v>143.55</v>
       </c>
       <c r="AL16" t="n">
-        <v>5.67</v>
+        <v>4.79</v>
       </c>
       <c r="AM16" t="n">
         <v>110</v>
@@ -2084,60 +2084,93 @@
         <v>142</v>
       </c>
       <c r="BL16" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B17" t="n">
-        <v>132.5</v>
+        <v>137.2</v>
+      </c>
+      <c r="C17" t="n">
+        <v>56.3</v>
       </c>
       <c r="D17" t="n">
-        <v>33.6</v>
+        <v>32.1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>21.2</v>
       </c>
       <c r="F17" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
+      </c>
+      <c r="H17" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="I17" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="J17" t="n">
+        <v>40.4</v>
       </c>
       <c r="K17" t="n">
-        <v>97.8</v>
+        <v>75.7</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N17" t="n">
+        <v>29</v>
       </c>
       <c r="O17" t="n">
-        <v>31.6</v>
+        <v>32.6</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>21.6</v>
       </c>
       <c r="V17" t="n">
-        <v>14.8</v>
+        <v>10.7</v>
       </c>
       <c r="W17" t="n">
-        <v>24.7</v>
+        <v>24.3</v>
       </c>
       <c r="X17" t="n">
-        <v>19.8</v>
+        <v>17.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Z17" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AA17" t="n">
-        <v>16.5</v>
+        <v>15.4</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="AF17" t="n">
-        <v>224.78</v>
+        <v>232.22</v>
       </c>
       <c r="AG17" t="n">
-        <v>3</v>
+        <v>7.43</v>
       </c>
       <c r="AH17" t="n">
         <v>215</v>
@@ -2146,10 +2179,10 @@
         <v>235</v>
       </c>
       <c r="AK17" t="n">
-        <v>143.55</v>
+        <v>143.61</v>
       </c>
       <c r="AL17" t="n">
-        <v>4.79</v>
+        <v>0.06</v>
       </c>
       <c r="AM17" t="n">
         <v>110</v>
@@ -2157,52 +2190,58 @@
       <c r="AN17" t="n">
         <v>142</v>
       </c>
+      <c r="AP17" t="n">
+        <v>89.31999999999999</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>18.02</v>
+      </c>
       <c r="BL17" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="B18" t="n">
-        <v>137.2</v>
+        <v>157.5</v>
       </c>
       <c r="C18" t="n">
-        <v>56.3</v>
+        <v>59.6</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1</v>
+        <v>35</v>
       </c>
       <c r="E18" t="n">
-        <v>21.2</v>
+        <v>30.6</v>
       </c>
       <c r="F18" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="H18" t="n">
-        <v>23.7</v>
+        <v>24.2</v>
       </c>
       <c r="I18" t="n">
-        <v>11.6</v>
+        <v>11.2</v>
       </c>
       <c r="J18" t="n">
-        <v>40.4</v>
+        <v>38.9</v>
       </c>
       <c r="K18" t="n">
-        <v>75.7</v>
+        <v>74.3</v>
       </c>
       <c r="M18" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="N18" t="n">
-        <v>29</v>
+        <v>33.4</v>
       </c>
       <c r="O18" t="n">
-        <v>32.6</v>
+        <v>37.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="R18" t="n">
         <v>1.3</v>
@@ -2211,40 +2250,40 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="V18" t="n">
-        <v>10.7</v>
+        <v>13</v>
       </c>
       <c r="W18" t="n">
-        <v>24.3</v>
+        <v>26.3</v>
       </c>
       <c r="X18" t="n">
-        <v>17.5</v>
+        <v>19.6</v>
       </c>
       <c r="Y18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA18" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.9</v>
+        <v>-2.1</v>
       </c>
       <c r="AC18" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="AF18" t="n">
-        <v>232.22</v>
+        <v>229.69</v>
       </c>
       <c r="AG18" t="n">
-        <v>7.43</v>
+        <v>-2.53</v>
       </c>
       <c r="AH18" t="n">
         <v>215</v>
@@ -2253,10 +2292,10 @@
         <v>235</v>
       </c>
       <c r="AK18" t="n">
-        <v>143.61</v>
+        <v>136.96</v>
       </c>
       <c r="AL18" t="n">
-        <v>0.06</v>
+        <v>-6.65</v>
       </c>
       <c r="AM18" t="n">
         <v>110</v>
@@ -2265,99 +2304,99 @@
         <v>142</v>
       </c>
       <c r="AP18" t="n">
-        <v>89.31999999999999</v>
+        <v>86.59</v>
       </c>
       <c r="AS18" t="n">
-        <v>18.02</v>
+        <v>16.96</v>
       </c>
       <c r="BL18" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B19" t="n">
-        <v>157.5</v>
+        <v>159.6</v>
       </c>
       <c r="C19" t="n">
-        <v>59.6</v>
+        <v>63</v>
       </c>
       <c r="D19" t="n">
-        <v>35</v>
+        <v>34.5</v>
       </c>
       <c r="E19" t="n">
-        <v>30.6</v>
+        <v>31.1</v>
       </c>
       <c r="F19" t="n">
-        <v>7.5</v>
+        <v>5.7</v>
       </c>
       <c r="H19" t="n">
-        <v>24.2</v>
+        <v>23.8</v>
       </c>
       <c r="I19" t="n">
-        <v>11.2</v>
+        <v>10.8</v>
       </c>
       <c r="J19" t="n">
-        <v>38.9</v>
+        <v>40.5</v>
       </c>
       <c r="K19" t="n">
-        <v>74.3</v>
+        <v>75.2</v>
       </c>
       <c r="M19" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="N19" t="n">
-        <v>33.4</v>
+        <v>34.3</v>
       </c>
       <c r="O19" t="n">
-        <v>37.1</v>
+        <v>38.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T19" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="V19" t="n">
-        <v>13</v>
+        <v>17.5</v>
       </c>
       <c r="W19" t="n">
-        <v>26.3</v>
+        <v>22.5</v>
       </c>
       <c r="X19" t="n">
-        <v>19.6</v>
+        <v>20</v>
       </c>
       <c r="Y19" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA19" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>-2.1</v>
+        <v>-2.2</v>
       </c>
       <c r="AC19" t="n">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="AF19" t="n">
-        <v>229.69</v>
+        <v>228.57</v>
       </c>
       <c r="AG19" t="n">
-        <v>-2.53</v>
+        <v>-1.14</v>
       </c>
       <c r="AH19" t="n">
         <v>215</v>
@@ -2366,10 +2405,10 @@
         <v>235</v>
       </c>
       <c r="AK19" t="n">
-        <v>136.96</v>
+        <v>133.01</v>
       </c>
       <c r="AL19" t="n">
-        <v>-6.65</v>
+        <v>-3.95</v>
       </c>
       <c r="AM19" t="n">
         <v>110</v>
@@ -2378,99 +2417,99 @@
         <v>142</v>
       </c>
       <c r="AP19" t="n">
-        <v>86.59</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="AS19" t="n">
-        <v>16.96</v>
+        <v>15.95</v>
       </c>
       <c r="BL19" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B20" t="n">
-        <v>159.6</v>
+        <v>160.4</v>
       </c>
       <c r="C20" t="n">
-        <v>63</v>
+        <v>62.6</v>
       </c>
       <c r="D20" t="n">
-        <v>34.5</v>
+        <v>35</v>
       </c>
       <c r="E20" t="n">
-        <v>31.1</v>
+        <v>32.2</v>
       </c>
       <c r="F20" t="n">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="H20" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="I20" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="J20" t="n">
-        <v>40.5</v>
+        <v>41.1</v>
       </c>
       <c r="K20" t="n">
-        <v>75.2</v>
+        <v>75.7</v>
       </c>
       <c r="M20" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="N20" t="n">
-        <v>34.3</v>
+        <v>32.6</v>
       </c>
       <c r="O20" t="n">
-        <v>38.2</v>
+        <v>38</v>
       </c>
       <c r="Q20" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T20" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="V20" t="n">
-        <v>17.5</v>
+        <v>16.4</v>
       </c>
       <c r="W20" t="n">
-        <v>22.5</v>
+        <v>22.8</v>
       </c>
       <c r="X20" t="n">
-        <v>20</v>
+        <v>19.6</v>
       </c>
       <c r="Y20" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Z20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA20" t="n">
-        <v>13.5</v>
+        <v>14.1</v>
       </c>
       <c r="AB20" t="n">
-        <v>-2.2</v>
+        <v>-3.1</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="AF20" t="n">
-        <v>228.57</v>
+        <v>225.08</v>
       </c>
       <c r="AG20" t="n">
-        <v>-1.14</v>
+        <v>-3.5</v>
       </c>
       <c r="AH20" t="n">
         <v>215</v>
@@ -2479,10 +2518,10 @@
         <v>235</v>
       </c>
       <c r="AK20" t="n">
-        <v>133.01</v>
+        <v>135.24</v>
       </c>
       <c r="AL20" t="n">
-        <v>-3.95</v>
+        <v>2.23</v>
       </c>
       <c r="AM20" t="n">
         <v>110</v>
@@ -2491,99 +2530,99 @@
         <v>142</v>
       </c>
       <c r="AP20" t="n">
-        <v>84.59999999999999</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="AS20" t="n">
-        <v>15.95</v>
+        <v>15.4</v>
       </c>
       <c r="BL20" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B21" t="n">
-        <v>160.4</v>
+        <v>161.7</v>
       </c>
       <c r="C21" t="n">
-        <v>62.6</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>35</v>
+        <v>34.9</v>
       </c>
       <c r="E21" t="n">
-        <v>32.2</v>
+        <v>27.3</v>
       </c>
       <c r="F21" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H21" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="I21" t="n">
-        <v>10.7</v>
+        <v>10.3</v>
       </c>
       <c r="J21" t="n">
-        <v>41.1</v>
+        <v>42.6</v>
       </c>
       <c r="K21" t="n">
-        <v>75.7</v>
+        <v>77</v>
       </c>
       <c r="M21" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="N21" t="n">
-        <v>32.6</v>
+        <v>31.5</v>
       </c>
       <c r="O21" t="n">
-        <v>38</v>
+        <v>37.3</v>
       </c>
       <c r="Q21" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="R21" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T21" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="V21" t="n">
-        <v>16.4</v>
+        <v>12.7</v>
       </c>
       <c r="W21" t="n">
-        <v>22.8</v>
+        <v>27</v>
       </c>
       <c r="X21" t="n">
-        <v>19.6</v>
+        <v>19.9</v>
       </c>
       <c r="Y21" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Z21" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AA21" t="n">
-        <v>14.1</v>
+        <v>11.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>-3.1</v>
+        <v>-5.2</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.6</v>
+        <v>-0.3</v>
       </c>
       <c r="AF21" t="n">
-        <v>225.08</v>
+        <v>225</v>
       </c>
       <c r="AG21" t="n">
-        <v>-3.5</v>
+        <v>-0.08</v>
       </c>
       <c r="AH21" t="n">
         <v>215</v>
@@ -2592,10 +2631,10 @@
         <v>235</v>
       </c>
       <c r="AK21" t="n">
-        <v>135.24</v>
+        <v>134.62</v>
       </c>
       <c r="AL21" t="n">
-        <v>2.23</v>
+        <v>-0.62</v>
       </c>
       <c r="AM21" t="n">
         <v>110</v>
@@ -2604,99 +2643,60 @@
         <v>142</v>
       </c>
       <c r="AP21" t="n">
-        <v>84.09999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="AS21" t="n">
-        <v>15.4</v>
+        <v>13.86</v>
       </c>
       <c r="BL21" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B22" t="n">
-        <v>161.7</v>
-      </c>
-      <c r="C22" t="n">
-        <v>71.09999999999999</v>
+        <v>151.5</v>
       </c>
       <c r="D22" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="E22" t="n">
-        <v>27.3</v>
+        <v>35.1</v>
       </c>
       <c r="F22" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H22" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I22" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="J22" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="K22" t="n">
-        <v>77</v>
-      </c>
-      <c r="M22" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="N22" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="O22" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>21</v>
-      </c>
-      <c r="R22" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="S22" t="n">
-        <v>6</v>
-      </c>
-      <c r="T22" t="n">
-        <v>21</v>
+        <v>5.4</v>
       </c>
       <c r="V22" t="n">
-        <v>12.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W22" t="n">
-        <v>27</v>
+        <v>19.4</v>
       </c>
       <c r="X22" t="n">
-        <v>19.9</v>
+        <v>14</v>
       </c>
       <c r="Y22" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA22" t="n">
         <v>9</v>
       </c>
-      <c r="Z22" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>11.4</v>
-      </c>
       <c r="AB22" t="n">
-        <v>-5.2</v>
+        <v>-4.7</v>
       </c>
       <c r="AC22" t="n">
-        <v>4.6</v>
+        <v>1.9</v>
       </c>
       <c r="AD22" t="n">
-        <v>-0.3</v>
+        <v>-1.4</v>
       </c>
       <c r="AF22" t="n">
-        <v>225</v>
+        <v>221.37</v>
       </c>
       <c r="AG22" t="n">
-        <v>-0.08</v>
+        <v>0.05</v>
       </c>
       <c r="AH22" t="n">
         <v>215</v>
@@ -2705,10 +2705,10 @@
         <v>235</v>
       </c>
       <c r="AK22" t="n">
-        <v>134.62</v>
+        <v>135.21</v>
       </c>
       <c r="AL22" t="n">
-        <v>-0.62</v>
+        <v>0.59</v>
       </c>
       <c r="AM22" t="n">
         <v>110</v>
@@ -2716,61 +2716,61 @@
       <c r="AN22" t="n">
         <v>142</v>
       </c>
-      <c r="AP22" t="n">
-        <v>80.2</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>13.86</v>
-      </c>
       <c r="BL22" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B23" t="n">
-        <v>151.5</v>
+        <v>145.2</v>
       </c>
       <c r="D23" t="n">
-        <v>35.1</v>
+        <v>33.5</v>
       </c>
       <c r="F23" t="n">
-        <v>5.4</v>
+        <v>5</v>
+      </c>
+      <c r="K23" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="O23" t="n">
+        <v>35.5</v>
       </c>
       <c r="V23" t="n">
-        <v>8.699999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="W23" t="n">
-        <v>19.4</v>
+        <v>19.2</v>
       </c>
       <c r="X23" t="n">
-        <v>14</v>
+        <v>13.1</v>
       </c>
       <c r="Y23" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z23" t="n">
         <v>13</v>
       </c>
       <c r="AA23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB23" t="n">
-        <v>-4.7</v>
+        <v>-5.4</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>-1.4</v>
+        <v>-1.5</v>
       </c>
       <c r="AF23" t="n">
-        <v>221.37</v>
+        <v>224.37</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.05</v>
+        <v>3</v>
       </c>
       <c r="AH23" t="n">
         <v>215</v>
@@ -2779,10 +2779,10 @@
         <v>235</v>
       </c>
       <c r="AK23" t="n">
-        <v>135.21</v>
+        <v>135.61</v>
       </c>
       <c r="AL23" t="n">
-        <v>0.59</v>
+        <v>0.4</v>
       </c>
       <c r="AM23" t="n">
         <v>110</v>
@@ -2791,60 +2791,60 @@
         <v>142</v>
       </c>
       <c r="BL23" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B24" t="n">
-        <v>145.2</v>
+        <v>146.3</v>
       </c>
       <c r="D24" t="n">
-        <v>33.5</v>
+        <v>33.4</v>
       </c>
       <c r="F24" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="K24" t="n">
-        <v>100.3</v>
+        <v>98.2</v>
       </c>
       <c r="O24" t="n">
-        <v>35.5</v>
+        <v>35.1</v>
       </c>
       <c r="V24" t="n">
-        <v>7.1</v>
+        <v>4.9</v>
       </c>
       <c r="W24" t="n">
-        <v>19.2</v>
+        <v>16.4</v>
       </c>
       <c r="X24" t="n">
-        <v>13.1</v>
+        <v>10.6</v>
       </c>
       <c r="Y24" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z24" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB24" t="n">
-        <v>-5.4</v>
+        <v>-6.4</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.4</v>
+        <v>-0.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>-1.5</v>
+        <v>-3.3</v>
       </c>
       <c r="AF24" t="n">
-        <v>224.37</v>
+        <v>225.93</v>
       </c>
       <c r="AG24" t="n">
-        <v>3</v>
+        <v>1.56</v>
       </c>
       <c r="AH24" t="n">
         <v>215</v>
@@ -2853,10 +2853,10 @@
         <v>235</v>
       </c>
       <c r="AK24" t="n">
-        <v>135.61</v>
+        <v>135.28</v>
       </c>
       <c r="AL24" t="n">
-        <v>0.4</v>
+        <v>-0.33</v>
       </c>
       <c r="AM24" t="n">
         <v>110</v>
@@ -2865,60 +2865,93 @@
         <v>142</v>
       </c>
       <c r="BL24" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B25" t="n">
-        <v>146.3</v>
+        <v>182.8</v>
+      </c>
+      <c r="C25" t="n">
+        <v>86.8</v>
       </c>
       <c r="D25" t="n">
-        <v>33.4</v>
+        <v>31.8</v>
+      </c>
+      <c r="E25" t="n">
+        <v>33</v>
       </c>
       <c r="F25" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
+      </c>
+      <c r="H25" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="I25" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J25" t="n">
+        <v>41.1</v>
       </c>
       <c r="K25" t="n">
-        <v>98.2</v>
+        <v>74.2</v>
+      </c>
+      <c r="M25" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="N25" t="n">
+        <v>33.5</v>
       </c>
       <c r="O25" t="n">
-        <v>35.1</v>
+        <v>38.4</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S25" t="n">
+        <v>15</v>
+      </c>
+      <c r="T25" t="n">
+        <v>22.4</v>
       </c>
       <c r="V25" t="n">
-        <v>4.9</v>
+        <v>9.1</v>
       </c>
       <c r="W25" t="n">
-        <v>16.4</v>
+        <v>15</v>
       </c>
       <c r="X25" t="n">
-        <v>10.6</v>
+        <v>12.1</v>
       </c>
       <c r="Y25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z25" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AA25" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>-6.4</v>
+        <v>-10.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>-0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AD25" t="n">
-        <v>-3.3</v>
+        <v>-5.1</v>
       </c>
       <c r="AF25" t="n">
-        <v>225.93</v>
+        <v>218.63</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.56</v>
+        <v>-7.3</v>
       </c>
       <c r="AH25" t="n">
         <v>215</v>
@@ -2927,10 +2960,10 @@
         <v>235</v>
       </c>
       <c r="AK25" t="n">
-        <v>135.28</v>
+        <v>126.27</v>
       </c>
       <c r="AL25" t="n">
-        <v>-0.33</v>
+        <v>-9.01</v>
       </c>
       <c r="AM25" t="n">
         <v>110</v>
@@ -2938,94 +2971,100 @@
       <c r="AN25" t="n">
         <v>142</v>
       </c>
+      <c r="AP25" t="n">
+        <v>82.66</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>14.7</v>
+      </c>
       <c r="BL25" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B26" t="n">
-        <v>182.8</v>
+        <v>181.8</v>
       </c>
       <c r="C26" t="n">
-        <v>86.8</v>
+        <v>86.5</v>
       </c>
       <c r="D26" t="n">
-        <v>31.8</v>
+        <v>31.4</v>
       </c>
       <c r="E26" t="n">
-        <v>33</v>
+        <v>34.2</v>
       </c>
       <c r="F26" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="H26" t="n">
-        <v>23.5</v>
+        <v>24.4</v>
       </c>
       <c r="I26" t="n">
-        <v>9.6</v>
+        <v>10.4</v>
       </c>
       <c r="J26" t="n">
-        <v>41.1</v>
+        <v>41.9</v>
       </c>
       <c r="K26" t="n">
-        <v>74.2</v>
+        <v>76.8</v>
       </c>
       <c r="M26" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="N26" t="n">
-        <v>33.5</v>
+        <v>35.7</v>
       </c>
       <c r="O26" t="n">
-        <v>38.4</v>
+        <v>39.8</v>
       </c>
       <c r="Q26" t="n">
-        <v>22.4</v>
+        <v>23</v>
       </c>
       <c r="R26" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>20.1</v>
       </c>
       <c r="T26" t="n">
-        <v>22.4</v>
+        <v>23</v>
       </c>
       <c r="V26" t="n">
-        <v>9.1</v>
+        <v>7.1</v>
       </c>
       <c r="W26" t="n">
-        <v>15</v>
+        <v>14.8</v>
       </c>
       <c r="X26" t="n">
-        <v>12.1</v>
+        <v>10.9</v>
       </c>
       <c r="Y26" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z26" t="n">
         <v>12</v>
       </c>
       <c r="AA26" t="n">
-        <v>8.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AB26" t="n">
-        <v>-10.5</v>
+        <v>-4.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>-5.1</v>
+        <v>-1.4</v>
       </c>
       <c r="AF26" t="n">
-        <v>218.63</v>
+        <v>216.39</v>
       </c>
       <c r="AG26" t="n">
-        <v>-7.3</v>
+        <v>-2.23</v>
       </c>
       <c r="AH26" t="n">
         <v>215</v>
@@ -3034,10 +3073,10 @@
         <v>235</v>
       </c>
       <c r="AK26" t="n">
-        <v>126.27</v>
+        <v>123.32</v>
       </c>
       <c r="AL26" t="n">
-        <v>-9.01</v>
+        <v>-2.95</v>
       </c>
       <c r="AM26" t="n">
         <v>110</v>
@@ -3046,99 +3085,99 @@
         <v>142</v>
       </c>
       <c r="AP26" t="n">
-        <v>82.66</v>
+        <v>79.08</v>
       </c>
       <c r="AS26" t="n">
-        <v>14.7</v>
+        <v>13.91</v>
       </c>
       <c r="BL26" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B27" t="n">
-        <v>181.8</v>
+        <v>183</v>
       </c>
       <c r="C27" t="n">
-        <v>86.5</v>
+        <v>84.7</v>
       </c>
       <c r="D27" t="n">
-        <v>31.4</v>
+        <v>30.9</v>
       </c>
       <c r="E27" t="n">
-        <v>34.2</v>
+        <v>33.7</v>
       </c>
       <c r="F27" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="H27" t="n">
-        <v>24.4</v>
+        <v>23.4</v>
       </c>
       <c r="I27" t="n">
-        <v>10.4</v>
+        <v>10.6</v>
       </c>
       <c r="J27" t="n">
-        <v>41.9</v>
+        <v>42.3</v>
       </c>
       <c r="K27" t="n">
-        <v>76.8</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="M27" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="N27" t="n">
-        <v>35.7</v>
+        <v>36.7</v>
       </c>
       <c r="O27" t="n">
-        <v>39.8</v>
+        <v>40.8</v>
       </c>
       <c r="Q27" t="n">
-        <v>23</v>
+        <v>23.6</v>
       </c>
       <c r="R27" t="n">
         <v>1.8</v>
       </c>
       <c r="S27" t="n">
-        <v>20.1</v>
+        <v>20.8</v>
       </c>
       <c r="T27" t="n">
-        <v>23</v>
+        <v>23.6</v>
       </c>
       <c r="V27" t="n">
-        <v>7.1</v>
+        <v>5.7</v>
       </c>
       <c r="W27" t="n">
-        <v>14.8</v>
+        <v>16.1</v>
       </c>
       <c r="X27" t="n">
         <v>10.9</v>
       </c>
       <c r="Y27" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA27" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AB27" t="n">
-        <v>-4.5</v>
+        <v>0.8</v>
       </c>
       <c r="AC27" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD27" t="n">
         <v>1.8</v>
       </c>
-      <c r="AD27" t="n">
-        <v>-1.4</v>
-      </c>
       <c r="AF27" t="n">
-        <v>216.39</v>
+        <v>217.16</v>
       </c>
       <c r="AG27" t="n">
-        <v>-2.23</v>
+        <v>0.76</v>
       </c>
       <c r="AH27" t="n">
         <v>215</v>
@@ -3147,10 +3186,10 @@
         <v>235</v>
       </c>
       <c r="AK27" t="n">
-        <v>123.32</v>
+        <v>117.87</v>
       </c>
       <c r="AL27" t="n">
-        <v>-2.95</v>
+        <v>-5.45</v>
       </c>
       <c r="AM27" t="n">
         <v>110</v>
@@ -3159,99 +3198,66 @@
         <v>142</v>
       </c>
       <c r="AP27" t="n">
-        <v>79.08</v>
+        <v>78.56</v>
       </c>
       <c r="AS27" t="n">
-        <v>13.91</v>
+        <v>13.45</v>
       </c>
       <c r="BL27" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B28" t="n">
-        <v>183</v>
-      </c>
-      <c r="C28" t="n">
-        <v>84.7</v>
+        <v>163.8</v>
       </c>
       <c r="D28" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="E28" t="n">
-        <v>33.7</v>
+        <v>29</v>
       </c>
       <c r="F28" t="n">
-        <v>7</v>
-      </c>
-      <c r="H28" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="I28" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="J28" t="n">
-        <v>42.3</v>
+        <v>6.5</v>
       </c>
       <c r="K28" t="n">
-        <v>76.40000000000001</v>
-      </c>
-      <c r="M28" t="n">
-        <v>4</v>
-      </c>
-      <c r="N28" t="n">
-        <v>36.7</v>
+        <v>101.2</v>
       </c>
       <c r="O28" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S28" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="T28" t="n">
-        <v>23.6</v>
+        <v>40.2</v>
       </c>
       <c r="V28" t="n">
-        <v>5.7</v>
+        <v>6.3</v>
       </c>
       <c r="W28" t="n">
-        <v>16.1</v>
+        <v>17.2</v>
       </c>
       <c r="X28" t="n">
-        <v>10.9</v>
+        <v>11.8</v>
       </c>
       <c r="Y28" t="n">
         <v>8</v>
       </c>
       <c r="Z28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA28" t="n">
         <v>10</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.7</v>
+        <v>4.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="AF28" t="n">
-        <v>217.16</v>
+        <v>220.31</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.76</v>
+        <v>3.16</v>
       </c>
       <c r="AH28" t="n">
         <v>215</v>
@@ -3260,10 +3266,10 @@
         <v>235</v>
       </c>
       <c r="AK28" t="n">
-        <v>117.87</v>
+        <v>116.52</v>
       </c>
       <c r="AL28" t="n">
-        <v>-5.45</v>
+        <v>-1.35</v>
       </c>
       <c r="AM28" t="n">
         <v>110</v>
@@ -3271,67 +3277,61 @@
       <c r="AN28" t="n">
         <v>142</v>
       </c>
-      <c r="AP28" t="n">
-        <v>78.56</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>13.45</v>
-      </c>
       <c r="BL28" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B29" t="n">
-        <v>163.8</v>
+        <v>155.9</v>
       </c>
       <c r="D29" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F29" t="n">
         <v>6.5</v>
       </c>
       <c r="K29" t="n">
-        <v>101.2</v>
+        <v>99.3</v>
       </c>
       <c r="O29" t="n">
-        <v>40.2</v>
+        <v>38.5</v>
       </c>
       <c r="V29" t="n">
-        <v>6.3</v>
+        <v>8.9</v>
       </c>
       <c r="W29" t="n">
-        <v>17.2</v>
+        <v>15.8</v>
       </c>
       <c r="X29" t="n">
-        <v>11.8</v>
+        <v>12.4</v>
       </c>
       <c r="Y29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA29" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AC29" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="AF29" t="n">
-        <v>220.31</v>
+        <v>221.99</v>
       </c>
       <c r="AG29" t="n">
-        <v>3.16</v>
+        <v>1.67</v>
       </c>
       <c r="AH29" t="n">
         <v>215</v>
@@ -3340,10 +3340,10 @@
         <v>235</v>
       </c>
       <c r="AK29" t="n">
-        <v>116.52</v>
+        <v>116.37</v>
       </c>
       <c r="AL29" t="n">
-        <v>-1.35</v>
+        <v>-0.15</v>
       </c>
       <c r="AM29" t="n">
         <v>110</v>
@@ -3352,60 +3352,60 @@
         <v>142</v>
       </c>
       <c r="BL29" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B30" t="n">
-        <v>155.9</v>
+        <v>141.3</v>
       </c>
       <c r="D30" t="n">
-        <v>28</v>
+        <v>26.3</v>
       </c>
       <c r="F30" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="K30" t="n">
-        <v>99.3</v>
+        <v>97.8</v>
       </c>
       <c r="O30" t="n">
-        <v>38.5</v>
+        <v>39.8</v>
       </c>
       <c r="V30" t="n">
-        <v>8.9</v>
+        <v>9.5</v>
       </c>
       <c r="W30" t="n">
-        <v>15.8</v>
+        <v>17.7</v>
       </c>
       <c r="X30" t="n">
-        <v>12.4</v>
+        <v>13.6</v>
       </c>
       <c r="Y30" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Z30" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA30" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="AC30" t="n">
-        <v>5.7</v>
+        <v>7.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="AF30" t="n">
-        <v>221.99</v>
+        <v>225.14</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.67</v>
+        <v>3.15</v>
       </c>
       <c r="AH30" t="n">
         <v>215</v>
@@ -3413,12 +3413,6 @@
       <c r="AI30" t="n">
         <v>235</v>
       </c>
-      <c r="AK30" t="n">
-        <v>116.37</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>-0.15</v>
-      </c>
       <c r="AM30" t="n">
         <v>110</v>
       </c>
@@ -3426,60 +3420,54 @@
         <v>142</v>
       </c>
       <c r="BL30" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B31" t="n">
-        <v>141.3</v>
+        <v>131.5</v>
       </c>
       <c r="D31" t="n">
-        <v>26.3</v>
+        <v>27.3</v>
       </c>
       <c r="F31" t="n">
         <v>5.5</v>
       </c>
       <c r="K31" t="n">
-        <v>97.8</v>
+        <v>97</v>
       </c>
       <c r="O31" t="n">
-        <v>39.8</v>
+        <v>35.7</v>
       </c>
       <c r="V31" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="W31" t="n">
-        <v>17.7</v>
+        <v>13.9</v>
       </c>
       <c r="X31" t="n">
-        <v>13.6</v>
+        <v>11.4</v>
       </c>
       <c r="Y31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z31" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA31" t="n">
         <v>15</v>
       </c>
-      <c r="AA31" t="n">
-        <v>14</v>
-      </c>
       <c r="AB31" t="n">
-        <v>0.2</v>
+        <v>-3.6</v>
       </c>
       <c r="AC31" t="n">
-        <v>7.5</v>
+        <v>2.8</v>
       </c>
       <c r="AD31" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>225.14</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>3.15</v>
+        <v>-0.4</v>
       </c>
       <c r="AH31" t="n">
         <v>215</v>
@@ -3494,54 +3482,93 @@
         <v>142</v>
       </c>
       <c r="BL31" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="B32" t="n">
-        <v>131.5</v>
+        <v>153</v>
+      </c>
+      <c r="C32" t="n">
+        <v>71.8</v>
       </c>
       <c r="D32" t="n">
-        <v>27.3</v>
+        <v>28.6</v>
+      </c>
+      <c r="E32" t="n">
+        <v>24.7</v>
       </c>
       <c r="F32" t="n">
-        <v>5.5</v>
+        <v>4</v>
+      </c>
+      <c r="H32" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J32" t="n">
+        <v>41.1</v>
       </c>
       <c r="K32" t="n">
-        <v>97</v>
+        <v>75.90000000000001</v>
+      </c>
+      <c r="M32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N32" t="n">
+        <v>33.5</v>
       </c>
       <c r="O32" t="n">
-        <v>35.7</v>
+        <v>38.3</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="R32" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>23.2</v>
       </c>
       <c r="V32" t="n">
-        <v>9</v>
+        <v>11.2</v>
       </c>
       <c r="W32" t="n">
-        <v>13.9</v>
+        <v>13</v>
       </c>
       <c r="X32" t="n">
-        <v>11.4</v>
+        <v>12.1</v>
       </c>
       <c r="Y32" t="n">
         <v>12</v>
       </c>
       <c r="Z32" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AA32" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AB32" t="n">
-        <v>-3.6</v>
+        <v>-6.6</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.8</v>
+        <v>5.3</v>
       </c>
       <c r="AD32" t="n">
-        <v>-0.4</v>
+        <v>-0.6</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>229.96</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>-0.02</v>
       </c>
       <c r="AH32" t="n">
         <v>215</v>
@@ -3549,100 +3576,112 @@
       <c r="AI32" t="n">
         <v>235</v>
       </c>
+      <c r="AK32" t="n">
+        <v>128.14</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>11.77</v>
+      </c>
       <c r="AM32" t="n">
         <v>110</v>
       </c>
       <c r="AN32" t="n">
         <v>142</v>
       </c>
+      <c r="AP32" t="n">
+        <v>87.47</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>14.8</v>
+      </c>
       <c r="BL32" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B33" t="n">
-        <v>153</v>
+        <v>165.8</v>
       </c>
       <c r="C33" t="n">
-        <v>71.8</v>
+        <v>77.3</v>
       </c>
       <c r="D33" t="n">
-        <v>28.6</v>
+        <v>29.3</v>
       </c>
       <c r="E33" t="n">
-        <v>24.7</v>
+        <v>27.7</v>
       </c>
       <c r="F33" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="H33" t="n">
         <v>24.1</v>
       </c>
       <c r="I33" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="J33" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="K33" t="n">
-        <v>75.90000000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="M33" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="N33" t="n">
-        <v>33.5</v>
+        <v>35.1</v>
       </c>
       <c r="O33" t="n">
-        <v>38.3</v>
+        <v>39.8</v>
       </c>
       <c r="Q33" t="n">
-        <v>23.2</v>
+        <v>23.8</v>
       </c>
       <c r="R33" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="T33" t="n">
-        <v>23.2</v>
+        <v>23.8</v>
       </c>
       <c r="V33" t="n">
-        <v>11.2</v>
+        <v>9.4</v>
       </c>
       <c r="W33" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="X33" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z33" t="n">
         <v>13</v>
       </c>
-      <c r="X33" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>14</v>
-      </c>
       <c r="AA33" t="n">
-        <v>12.5</v>
+        <v>10.1</v>
       </c>
       <c r="AB33" t="n">
-        <v>-6.6</v>
+        <v>-0.7</v>
       </c>
       <c r="AC33" t="n">
-        <v>5.3</v>
+        <v>9.5</v>
       </c>
       <c r="AD33" t="n">
-        <v>-0.6</v>
+        <v>4.4</v>
       </c>
       <c r="AF33" t="n">
-        <v>229.96</v>
+        <v>227.01</v>
       </c>
       <c r="AG33" t="n">
-        <v>-0.02</v>
+        <v>-2.95</v>
       </c>
       <c r="AH33" t="n">
         <v>215</v>
@@ -3651,10 +3690,10 @@
         <v>235</v>
       </c>
       <c r="AK33" t="n">
-        <v>128.14</v>
+        <v>128.15</v>
       </c>
       <c r="AL33" t="n">
-        <v>11.77</v>
+        <v>0.01</v>
       </c>
       <c r="AM33" t="n">
         <v>110</v>
@@ -3663,99 +3702,99 @@
         <v>142</v>
       </c>
       <c r="AP33" t="n">
-        <v>87.47</v>
+        <v>83.41</v>
       </c>
       <c r="AS33" t="n">
-        <v>14.8</v>
+        <v>14.52</v>
       </c>
       <c r="BL33" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B34" t="n">
-        <v>165.8</v>
+        <v>158.1</v>
       </c>
       <c r="C34" t="n">
-        <v>77.3</v>
+        <v>73.7</v>
       </c>
       <c r="D34" t="n">
-        <v>29.3</v>
+        <v>30.3</v>
       </c>
       <c r="E34" t="n">
-        <v>27.7</v>
+        <v>26</v>
       </c>
       <c r="F34" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="H34" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="I34" t="n">
-        <v>10.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J34" t="n">
-        <v>41.6</v>
+        <v>40.9</v>
       </c>
       <c r="K34" t="n">
-        <v>76.59999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="M34" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="N34" t="n">
-        <v>35.1</v>
+        <v>35.3</v>
       </c>
       <c r="O34" t="n">
-        <v>39.8</v>
+        <v>40.3</v>
       </c>
       <c r="Q34" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="R34" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S34" t="n">
         <v>7</v>
       </c>
       <c r="T34" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="V34" t="n">
-        <v>9.4</v>
+        <v>8.9</v>
       </c>
       <c r="W34" t="n">
-        <v>17.4</v>
+        <v>19.3</v>
       </c>
       <c r="X34" t="n">
-        <v>13.4</v>
+        <v>14.1</v>
       </c>
       <c r="Y34" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z34" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA34" t="n">
-        <v>10.1</v>
+        <v>11</v>
       </c>
       <c r="AB34" t="n">
-        <v>-0.7</v>
+        <v>4.4</v>
       </c>
       <c r="AC34" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="AD34" t="n">
-        <v>4.4</v>
+        <v>6.5</v>
       </c>
       <c r="AF34" t="n">
-        <v>227.01</v>
+        <v>228.35</v>
       </c>
       <c r="AG34" t="n">
-        <v>-2.95</v>
+        <v>1.33</v>
       </c>
       <c r="AH34" t="n">
         <v>215</v>
@@ -3764,10 +3803,10 @@
         <v>235</v>
       </c>
       <c r="AK34" t="n">
-        <v>128.15</v>
+        <v>128.86</v>
       </c>
       <c r="AL34" t="n">
-        <v>0.01</v>
+        <v>0.71</v>
       </c>
       <c r="AM34" t="n">
         <v>110</v>
@@ -3776,99 +3815,99 @@
         <v>142</v>
       </c>
       <c r="AP34" t="n">
-        <v>83.41</v>
+        <v>82.37</v>
       </c>
       <c r="AS34" t="n">
-        <v>14.52</v>
+        <v>14.22</v>
       </c>
       <c r="BL34" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B35" t="n">
-        <v>158.1</v>
+        <v>154.9</v>
       </c>
       <c r="C35" t="n">
-        <v>73.7</v>
+        <v>70.2</v>
       </c>
       <c r="D35" t="n">
-        <v>30.3</v>
+        <v>31.5</v>
       </c>
       <c r="E35" t="n">
-        <v>26</v>
+        <v>27.7</v>
       </c>
       <c r="F35" t="n">
-        <v>4.1</v>
+        <v>2.7</v>
       </c>
       <c r="H35" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="I35" t="n">
-        <v>9.300000000000001</v>
+        <v>11.3</v>
       </c>
       <c r="J35" t="n">
-        <v>40.9</v>
+        <v>40.3</v>
       </c>
       <c r="K35" t="n">
-        <v>74.40000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="M35" t="n">
-        <v>5</v>
+        <v>6.1</v>
       </c>
       <c r="N35" t="n">
-        <v>35.3</v>
+        <v>32.9</v>
       </c>
       <c r="O35" t="n">
-        <v>40.3</v>
+        <v>39</v>
       </c>
       <c r="Q35" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="R35" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="S35" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="T35" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="V35" t="n">
-        <v>8.9</v>
+        <v>6.3</v>
       </c>
       <c r="W35" t="n">
-        <v>19.3</v>
+        <v>25.2</v>
       </c>
       <c r="X35" t="n">
-        <v>14.1</v>
+        <v>15.8</v>
       </c>
       <c r="Y35" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z35" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA35" t="n">
-        <v>11</v>
+        <v>12.6</v>
       </c>
       <c r="AB35" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="AC35" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="AD35" t="n">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="AF35" t="n">
-        <v>228.35</v>
+        <v>231.16</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.33</v>
+        <v>2.81</v>
       </c>
       <c r="AH35" t="n">
         <v>215</v>
@@ -3877,10 +3916,10 @@
         <v>235</v>
       </c>
       <c r="AK35" t="n">
-        <v>128.86</v>
+        <v>130.88</v>
       </c>
       <c r="AL35" t="n">
-        <v>0.71</v>
+        <v>2.02</v>
       </c>
       <c r="AM35" t="n">
         <v>110</v>
@@ -3889,99 +3928,66 @@
         <v>142</v>
       </c>
       <c r="AP35" t="n">
-        <v>82.37</v>
+        <v>85.48999999999999</v>
       </c>
       <c r="AS35" t="n">
-        <v>14.22</v>
+        <v>13.1</v>
       </c>
       <c r="BL35" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B36" t="n">
-        <v>154.9</v>
-      </c>
-      <c r="C36" t="n">
-        <v>70.2</v>
+        <v>152.2</v>
       </c>
       <c r="D36" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="E36" t="n">
-        <v>27.7</v>
+        <v>31</v>
       </c>
       <c r="F36" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="H36" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I36" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J36" t="n">
-        <v>40.3</v>
+        <v>3.5</v>
       </c>
       <c r="K36" t="n">
-        <v>75.8</v>
-      </c>
-      <c r="M36" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="N36" t="n">
-        <v>32.9</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O36" t="n">
-        <v>39</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="R36" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="S36" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="T36" t="n">
-        <v>23.7</v>
+        <v>34.4</v>
       </c>
       <c r="V36" t="n">
-        <v>6.3</v>
+        <v>9.5</v>
       </c>
       <c r="W36" t="n">
-        <v>25.2</v>
+        <v>25.5</v>
       </c>
       <c r="X36" t="n">
-        <v>15.8</v>
+        <v>17.5</v>
       </c>
       <c r="Y36" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Z36" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AA36" t="n">
-        <v>12.6</v>
+        <v>9</v>
       </c>
       <c r="AB36" t="n">
-        <v>2.9</v>
+        <v>-1.1</v>
       </c>
       <c r="AC36" t="n">
         <v>8.6</v>
       </c>
       <c r="AD36" t="n">
-        <v>5.8</v>
+        <v>3.8</v>
       </c>
       <c r="AF36" t="n">
-        <v>231.16</v>
+        <v>228.13</v>
       </c>
       <c r="AG36" t="n">
-        <v>2.81</v>
+        <v>-3.03</v>
       </c>
       <c r="AH36" t="n">
         <v>215</v>
@@ -3989,79 +3995,67 @@
       <c r="AI36" t="n">
         <v>235</v>
       </c>
-      <c r="AK36" t="n">
-        <v>130.88</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AM36" t="n">
         <v>110</v>
       </c>
       <c r="AN36" t="n">
         <v>142</v>
       </c>
-      <c r="AP36" t="n">
-        <v>85.48999999999999</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>13.1</v>
-      </c>
       <c r="BL36" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B37" t="n">
-        <v>152.2</v>
+        <v>143.9</v>
       </c>
       <c r="D37" t="n">
-        <v>31</v>
+        <v>30.8</v>
       </c>
       <c r="F37" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="K37" t="n">
-        <v>98.40000000000001</v>
+        <v>99.2</v>
       </c>
       <c r="O37" t="n">
-        <v>34.4</v>
+        <v>35.2</v>
       </c>
       <c r="V37" t="n">
-        <v>9.5</v>
+        <v>10.7</v>
       </c>
       <c r="W37" t="n">
-        <v>25.5</v>
+        <v>17.6</v>
       </c>
       <c r="X37" t="n">
-        <v>17.5</v>
+        <v>14.2</v>
       </c>
       <c r="Y37" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Z37" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA37" t="n">
         <v>9</v>
       </c>
       <c r="AB37" t="n">
-        <v>-1.1</v>
+        <v>-0.8</v>
       </c>
       <c r="AC37" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD37" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AF37" t="n">
-        <v>228.13</v>
+        <v>229.16</v>
       </c>
       <c r="AG37" t="n">
-        <v>-3.03</v>
+        <v>1.03</v>
       </c>
       <c r="AH37" t="n">
         <v>215</v>
@@ -4076,60 +4070,93 @@
         <v>142</v>
       </c>
       <c r="BL37" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B38" t="n">
-        <v>143.9</v>
+        <v>163.2</v>
+      </c>
+      <c r="C38" t="n">
+        <v>73.7</v>
       </c>
       <c r="D38" t="n">
-        <v>30.8</v>
+        <v>30</v>
+      </c>
+      <c r="E38" t="n">
+        <v>28.2</v>
       </c>
       <c r="F38" t="n">
-        <v>2.5</v>
+        <v>4.8</v>
+      </c>
+      <c r="H38" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I38" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J38" t="n">
+        <v>40.1</v>
       </c>
       <c r="K38" t="n">
-        <v>99.2</v>
+        <v>75.59999999999999</v>
+      </c>
+      <c r="M38" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="N38" t="n">
+        <v>32.9</v>
       </c>
       <c r="O38" t="n">
-        <v>35.2</v>
+        <v>39.7</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="R38" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="S38" t="n">
+        <v>6</v>
+      </c>
+      <c r="T38" t="n">
+        <v>23.5</v>
       </c>
       <c r="V38" t="n">
-        <v>10.7</v>
+        <v>9.4</v>
       </c>
       <c r="W38" t="n">
-        <v>17.6</v>
+        <v>20.1</v>
       </c>
       <c r="X38" t="n">
-        <v>14.2</v>
+        <v>14.8</v>
       </c>
       <c r="Y38" t="n">
         <v>4</v>
       </c>
       <c r="Z38" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA38" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AB38" t="n">
-        <v>-0.8</v>
+        <v>-0.9</v>
       </c>
       <c r="AC38" t="n">
-        <v>8.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="AD38" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AF38" t="n">
-        <v>229.16</v>
+        <v>228.55</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.03</v>
+        <v>-0.61</v>
       </c>
       <c r="AH38" t="n">
         <v>215</v>
@@ -4137,100 +4164,112 @@
       <c r="AI38" t="n">
         <v>235</v>
       </c>
+      <c r="AK38" t="n">
+        <v>127.06</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>-3.82</v>
+      </c>
       <c r="AM38" t="n">
         <v>110</v>
       </c>
       <c r="AN38" t="n">
         <v>142</v>
       </c>
+      <c r="AP38" t="n">
+        <v>82.81</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>12.9</v>
+      </c>
       <c r="BL38" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="B39" t="n">
-        <v>163.2</v>
+        <v>174.4</v>
       </c>
       <c r="C39" t="n">
-        <v>73.7</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="D39" t="n">
-        <v>30</v>
+        <v>32.1</v>
       </c>
       <c r="E39" t="n">
-        <v>28.2</v>
+        <v>30.8</v>
       </c>
       <c r="F39" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="H39" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="I39" t="n">
-        <v>11.4</v>
+        <v>10.5</v>
       </c>
       <c r="J39" t="n">
-        <v>40.1</v>
+        <v>39.5</v>
       </c>
       <c r="K39" t="n">
-        <v>75.59999999999999</v>
+        <v>74</v>
       </c>
       <c r="M39" t="n">
         <v>6.8</v>
       </c>
       <c r="N39" t="n">
-        <v>32.9</v>
+        <v>35.8</v>
       </c>
       <c r="O39" t="n">
-        <v>39.7</v>
+        <v>42.6</v>
       </c>
       <c r="Q39" t="n">
-        <v>23.5</v>
+        <v>23.1</v>
       </c>
       <c r="R39" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="S39" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="T39" t="n">
-        <v>23.5</v>
+        <v>23.1</v>
       </c>
       <c r="V39" t="n">
-        <v>9.4</v>
+        <v>12.8</v>
       </c>
       <c r="W39" t="n">
-        <v>20.1</v>
+        <v>22.1</v>
       </c>
       <c r="X39" t="n">
-        <v>14.8</v>
+        <v>17.5</v>
       </c>
       <c r="Y39" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Z39" t="n">
         <v>13</v>
       </c>
       <c r="AA39" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AC39" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="AB39" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>9.5</v>
-      </c>
       <c r="AD39" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AF39" t="n">
-        <v>228.55</v>
+        <v>219.99</v>
       </c>
       <c r="AG39" t="n">
-        <v>-0.61</v>
+        <v>-8.56</v>
       </c>
       <c r="AH39" t="n">
         <v>215</v>
@@ -4239,10 +4278,10 @@
         <v>235</v>
       </c>
       <c r="AK39" t="n">
-        <v>127.06</v>
+        <v>125.61</v>
       </c>
       <c r="AL39" t="n">
-        <v>-3.82</v>
+        <v>-1.45</v>
       </c>
       <c r="AM39" t="n">
         <v>110</v>
@@ -4251,99 +4290,99 @@
         <v>142</v>
       </c>
       <c r="AP39" t="n">
-        <v>82.81</v>
+        <v>77.83</v>
       </c>
       <c r="AS39" t="n">
-        <v>12.9</v>
+        <v>12.96</v>
       </c>
       <c r="BL39" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B40" t="n">
-        <v>174.4</v>
+        <v>163.2</v>
       </c>
       <c r="C40" t="n">
-        <v>75.40000000000001</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="D40" t="n">
-        <v>32.1</v>
+        <v>32.9</v>
       </c>
       <c r="E40" t="n">
-        <v>30.8</v>
+        <v>26</v>
       </c>
       <c r="F40" t="n">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="H40" t="n">
-        <v>24</v>
+        <v>23.8</v>
       </c>
       <c r="I40" t="n">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="J40" t="n">
-        <v>39.5</v>
+        <v>40.1</v>
       </c>
       <c r="K40" t="n">
-        <v>74</v>
+        <v>71.3</v>
       </c>
       <c r="M40" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="N40" t="n">
-        <v>35.8</v>
+        <v>34.3</v>
       </c>
       <c r="O40" t="n">
-        <v>42.6</v>
+        <v>41.5</v>
       </c>
       <c r="Q40" t="n">
         <v>23.1</v>
       </c>
       <c r="R40" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="S40" t="n">
-        <v>8.5</v>
+        <v>6.2</v>
       </c>
       <c r="T40" t="n">
         <v>23.1</v>
       </c>
       <c r="V40" t="n">
-        <v>12.8</v>
+        <v>9.6</v>
       </c>
       <c r="W40" t="n">
-        <v>22.1</v>
+        <v>23.3</v>
       </c>
       <c r="X40" t="n">
-        <v>17.5</v>
+        <v>16.4</v>
       </c>
       <c r="Y40" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z40" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA40" t="n">
-        <v>10.1</v>
+        <v>12.2</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.3</v>
+        <v>2.6</v>
       </c>
       <c r="AC40" t="n">
-        <v>9.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="AD40" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AF40" t="n">
-        <v>219.99</v>
+        <v>219.22</v>
       </c>
       <c r="AG40" t="n">
-        <v>-8.56</v>
+        <v>-0.77</v>
       </c>
       <c r="AH40" t="n">
         <v>215</v>
@@ -4352,10 +4391,10 @@
         <v>235</v>
       </c>
       <c r="AK40" t="n">
-        <v>125.61</v>
+        <v>124.36</v>
       </c>
       <c r="AL40" t="n">
-        <v>-1.45</v>
+        <v>-1.25</v>
       </c>
       <c r="AM40" t="n">
         <v>110</v>
@@ -4364,99 +4403,99 @@
         <v>142</v>
       </c>
       <c r="AP40" t="n">
-        <v>77.83</v>
+        <v>76.81</v>
       </c>
       <c r="AS40" t="n">
-        <v>12.96</v>
+        <v>12.38</v>
       </c>
       <c r="BL40" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B41" t="n">
-        <v>163.2</v>
+        <v>152.7</v>
       </c>
       <c r="C41" t="n">
-        <v>70.90000000000001</v>
+        <v>62.6</v>
       </c>
       <c r="D41" t="n">
-        <v>32.9</v>
+        <v>32.7</v>
       </c>
       <c r="E41" t="n">
-        <v>26</v>
+        <v>24.6</v>
       </c>
       <c r="F41" t="n">
-        <v>6.9</v>
+        <v>5.2</v>
       </c>
       <c r="H41" t="n">
         <v>23.8</v>
       </c>
       <c r="I41" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J41" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="K41" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="M41" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="N41" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="O41" t="n">
         <v>40.1</v>
       </c>
-      <c r="K41" t="n">
-        <v>71.3</v>
-      </c>
-      <c r="M41" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="N41" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="O41" t="n">
-        <v>41.5</v>
-      </c>
       <c r="Q41" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="R41" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="S41" t="n">
-        <v>6.2</v>
+        <v>4</v>
       </c>
       <c r="T41" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="V41" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="W41" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="X41" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC41" t="n">
         <v>9.6</v>
       </c>
-      <c r="W41" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="X41" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>8.5</v>
-      </c>
       <c r="AD41" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AF41" t="n">
-        <v>219.22</v>
+        <v>220.73</v>
       </c>
       <c r="AG41" t="n">
-        <v>-0.77</v>
+        <v>1.5</v>
       </c>
       <c r="AH41" t="n">
         <v>215</v>
@@ -4465,10 +4504,10 @@
         <v>235</v>
       </c>
       <c r="AK41" t="n">
-        <v>124.36</v>
+        <v>120.93</v>
       </c>
       <c r="AL41" t="n">
-        <v>-1.25</v>
+        <v>-3.43</v>
       </c>
       <c r="AM41" t="n">
         <v>110</v>
@@ -4477,75 +4516,75 @@
         <v>142</v>
       </c>
       <c r="AP41" t="n">
-        <v>76.81</v>
+        <v>77.87</v>
       </c>
       <c r="AS41" t="n">
-        <v>12.38</v>
+        <v>13.26</v>
       </c>
       <c r="BL41" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B42" t="n">
-        <v>152.7</v>
+        <v>150.7</v>
       </c>
       <c r="C42" t="n">
-        <v>62.6</v>
+        <v>64.8</v>
       </c>
       <c r="D42" t="n">
-        <v>32.7</v>
+        <v>33.7</v>
       </c>
       <c r="E42" t="n">
-        <v>24.6</v>
+        <v>27.1</v>
       </c>
       <c r="F42" t="n">
-        <v>5.2</v>
+        <v>3.8</v>
       </c>
       <c r="H42" t="n">
-        <v>23.8</v>
+        <v>23.4</v>
       </c>
       <c r="I42" t="n">
         <v>7.2</v>
       </c>
       <c r="J42" t="n">
-        <v>38.9</v>
+        <v>39.9</v>
       </c>
       <c r="K42" t="n">
-        <v>69.90000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="M42" t="n">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="N42" t="n">
-        <v>33.5</v>
+        <v>33</v>
       </c>
       <c r="O42" t="n">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="Q42" t="n">
         <v>23.2</v>
       </c>
       <c r="R42" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="S42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T42" t="n">
         <v>23.2</v>
       </c>
       <c r="V42" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="W42" t="n">
-        <v>27.3</v>
+        <v>28.9</v>
       </c>
       <c r="X42" t="n">
-        <v>19.4</v>
+        <v>21.7</v>
       </c>
       <c r="Y42" t="n">
         <v>10</v>
@@ -4554,22 +4593,22 @@
         <v>18</v>
       </c>
       <c r="AA42" t="n">
-        <v>14</v>
+        <v>13.1</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="AC42" t="n">
-        <v>9.6</v>
+        <v>10.8</v>
       </c>
       <c r="AD42" t="n">
-        <v>5.7</v>
+        <v>6.7</v>
       </c>
       <c r="AF42" t="n">
-        <v>220.73</v>
+        <v>220.58</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.5</v>
+        <v>-0.15</v>
       </c>
       <c r="AH42" t="n">
         <v>215</v>
@@ -4578,10 +4617,10 @@
         <v>235</v>
       </c>
       <c r="AK42" t="n">
-        <v>120.93</v>
+        <v>120.28</v>
       </c>
       <c r="AL42" t="n">
-        <v>-3.43</v>
+        <v>-0.65</v>
       </c>
       <c r="AM42" t="n">
         <v>110</v>
@@ -4590,99 +4629,54 @@
         <v>142</v>
       </c>
       <c r="AP42" t="n">
-        <v>77.87</v>
+        <v>77.22</v>
       </c>
       <c r="AS42" t="n">
-        <v>13.26</v>
+        <v>13.79</v>
       </c>
       <c r="BL42" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B43" t="n">
-        <v>150.7</v>
-      </c>
-      <c r="C43" t="n">
-        <v>64.8</v>
+        <v>138.2</v>
       </c>
       <c r="D43" t="n">
-        <v>33.7</v>
-      </c>
-      <c r="E43" t="n">
-        <v>27.1</v>
+        <v>33.6</v>
       </c>
       <c r="F43" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H43" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="V43" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="W43" t="n">
         <v>23.4</v>
       </c>
-      <c r="I43" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="J43" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="K43" t="n">
-        <v>70.5</v>
-      </c>
-      <c r="M43" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="N43" t="n">
-        <v>33</v>
-      </c>
-      <c r="O43" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="R43" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="S43" t="n">
-        <v>3</v>
-      </c>
-      <c r="T43" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="V43" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="W43" t="n">
-        <v>28.9</v>
-      </c>
       <c r="X43" t="n">
-        <v>21.7</v>
+        <v>19.4</v>
       </c>
       <c r="Y43" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z43" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AA43" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="AB43" t="n">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="AC43" t="n">
-        <v>10.8</v>
+        <v>8.5</v>
       </c>
       <c r="AD43" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>220.58</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>-0.15</v>
+        <v>4.5</v>
       </c>
       <c r="AH43" t="n">
         <v>215</v>
@@ -4690,67 +4684,61 @@
       <c r="AI43" t="n">
         <v>235</v>
       </c>
-      <c r="AK43" t="n">
-        <v>120.28</v>
-      </c>
-      <c r="AL43" t="n">
-        <v>-0.65</v>
-      </c>
       <c r="AM43" t="n">
         <v>110</v>
       </c>
       <c r="AN43" t="n">
         <v>142</v>
       </c>
-      <c r="AP43" t="n">
-        <v>77.22</v>
-      </c>
-      <c r="AS43" t="n">
-        <v>13.79</v>
-      </c>
       <c r="BL43" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B44" t="n">
-        <v>138.2</v>
+        <v>126.5</v>
       </c>
       <c r="D44" t="n">
-        <v>33.6</v>
+        <v>33.2</v>
       </c>
       <c r="F44" t="n">
-        <v>6.1</v>
+        <v>3.4</v>
       </c>
       <c r="V44" t="n">
-        <v>15.5</v>
+        <v>12.6</v>
       </c>
       <c r="W44" t="n">
-        <v>23.4</v>
+        <v>22.3</v>
       </c>
       <c r="X44" t="n">
-        <v>19.4</v>
+        <v>17.4</v>
       </c>
       <c r="Y44" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z44" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA44" t="n">
         <v>13</v>
       </c>
       <c r="AB44" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>8.5</v>
+        <v>6.7</v>
       </c>
       <c r="AD44" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>229.48</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>6.05</v>
       </c>
       <c r="AH44" t="n">
         <v>215</v>
@@ -4765,54 +4753,93 @@
         <v>142</v>
       </c>
       <c r="BL44" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B45" t="n">
-        <v>126.5</v>
+        <v>129.4</v>
+      </c>
+      <c r="C45" t="n">
+        <v>50.6</v>
       </c>
       <c r="D45" t="n">
-        <v>33.2</v>
+        <v>31.5</v>
+      </c>
+      <c r="E45" t="n">
+        <v>19.4</v>
       </c>
       <c r="F45" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
+      </c>
+      <c r="H45" t="n">
+        <v>24</v>
+      </c>
+      <c r="I45" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J45" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="K45" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="M45" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N45" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="O45" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>21.4</v>
       </c>
       <c r="V45" t="n">
-        <v>12.6</v>
+        <v>14.3</v>
       </c>
       <c r="W45" t="n">
-        <v>22.3</v>
+        <v>23.9</v>
       </c>
       <c r="X45" t="n">
-        <v>17.4</v>
+        <v>19.1</v>
       </c>
       <c r="Y45" t="n">
         <v>8</v>
       </c>
       <c r="Z45" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AA45" t="n">
-        <v>13</v>
+        <v>16.1</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AC45" t="n">
-        <v>6.7</v>
+        <v>7.6</v>
       </c>
       <c r="AD45" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="AF45" t="n">
-        <v>229.48</v>
+        <v>229.5</v>
       </c>
       <c r="AG45" t="n">
-        <v>6.05</v>
+        <v>0.02</v>
       </c>
       <c r="AH45" t="n">
         <v>215</v>
@@ -4820,100 +4847,112 @@
       <c r="AI45" t="n">
         <v>235</v>
       </c>
+      <c r="AK45" t="n">
+        <v>128.37</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>8.09</v>
+      </c>
       <c r="AM45" t="n">
         <v>110</v>
       </c>
       <c r="AN45" t="n">
         <v>142</v>
       </c>
+      <c r="AP45" t="n">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>15.97</v>
+      </c>
       <c r="BL45" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="B46" t="n">
-        <v>129.4</v>
+        <v>142.9</v>
       </c>
       <c r="C46" t="n">
-        <v>50.6</v>
+        <v>52.7</v>
       </c>
       <c r="D46" t="n">
-        <v>31.5</v>
+        <v>34.7</v>
       </c>
       <c r="E46" t="n">
-        <v>19.4</v>
+        <v>24.8</v>
       </c>
       <c r="F46" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="H46" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I46" t="n">
-        <v>10.4</v>
+        <v>9.9</v>
       </c>
       <c r="J46" t="n">
-        <v>38.9</v>
+        <v>38.2</v>
       </c>
       <c r="K46" t="n">
-        <v>73.3</v>
+        <v>70</v>
       </c>
       <c r="M46" t="n">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="N46" t="n">
-        <v>33.3</v>
+        <v>31.9</v>
       </c>
       <c r="O46" t="n">
-        <v>38</v>
+        <v>35.8</v>
       </c>
       <c r="Q46" t="n">
-        <v>21.4</v>
+        <v>19.7</v>
       </c>
       <c r="R46" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>21.4</v>
+        <v>19.7</v>
       </c>
       <c r="V46" t="n">
-        <v>14.3</v>
+        <v>12</v>
       </c>
       <c r="W46" t="n">
-        <v>23.9</v>
+        <v>25.8</v>
       </c>
       <c r="X46" t="n">
-        <v>19.1</v>
+        <v>18.9</v>
       </c>
       <c r="Y46" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Z46" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AA46" t="n">
-        <v>16.1</v>
+        <v>15</v>
       </c>
       <c r="AB46" t="n">
-        <v>0.4</v>
+        <v>-0.1</v>
       </c>
       <c r="AC46" t="n">
-        <v>7.6</v>
+        <v>5.8</v>
       </c>
       <c r="AD46" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="AF46" t="n">
-        <v>229.5</v>
+        <v>238.69</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.02</v>
+        <v>-2.8</v>
       </c>
       <c r="AH46" t="n">
         <v>215</v>
@@ -4922,10 +4961,10 @@
         <v>235</v>
       </c>
       <c r="AK46" t="n">
-        <v>128.37</v>
+        <v>134.59</v>
       </c>
       <c r="AL46" t="n">
-        <v>8.09</v>
+        <v>6.22</v>
       </c>
       <c r="AM46" t="n">
         <v>110</v>
@@ -4934,99 +4973,99 @@
         <v>142</v>
       </c>
       <c r="AP46" t="n">
-        <v>91.59999999999999</v>
+        <v>89.05</v>
       </c>
       <c r="AS46" t="n">
-        <v>15.97</v>
+        <v>17.06</v>
       </c>
       <c r="BL46" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B47" t="n">
-        <v>142.9</v>
+        <v>148.1</v>
       </c>
       <c r="C47" t="n">
-        <v>52.7</v>
+        <v>51.9</v>
       </c>
       <c r="D47" t="n">
-        <v>34.7</v>
+        <v>35.4</v>
       </c>
       <c r="E47" t="n">
-        <v>24.8</v>
+        <v>31.5</v>
       </c>
       <c r="F47" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="H47" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="I47" t="n">
-        <v>9.9</v>
+        <v>9.6</v>
       </c>
       <c r="J47" t="n">
-        <v>38.2</v>
+        <v>39.6</v>
       </c>
       <c r="K47" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M47" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="N47" t="n">
-        <v>31.9</v>
+        <v>30.8</v>
       </c>
       <c r="O47" t="n">
-        <v>35.8</v>
+        <v>33.7</v>
       </c>
       <c r="Q47" t="n">
-        <v>19.7</v>
+        <v>20.7</v>
       </c>
       <c r="R47" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>19.7</v>
+        <v>20.7</v>
       </c>
       <c r="V47" t="n">
-        <v>12</v>
+        <v>13.1</v>
       </c>
       <c r="W47" t="n">
-        <v>25.8</v>
+        <v>25.5</v>
       </c>
       <c r="X47" t="n">
-        <v>18.9</v>
+        <v>19.3</v>
       </c>
       <c r="Y47" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z47" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AA47" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AB47" t="n">
-        <v>-0.1</v>
+        <v>-1</v>
       </c>
       <c r="AC47" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AD47" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="AF47" t="n">
-        <v>238.69</v>
+        <v>233.48</v>
       </c>
       <c r="AG47" t="n">
-        <v>-2.8</v>
+        <v>-4.86</v>
       </c>
       <c r="AH47" t="n">
         <v>215</v>
@@ -5035,10 +5074,10 @@
         <v>235</v>
       </c>
       <c r="AK47" t="n">
-        <v>134.59</v>
+        <v>136.6</v>
       </c>
       <c r="AL47" t="n">
-        <v>6.22</v>
+        <v>2.01</v>
       </c>
       <c r="AM47" t="n">
         <v>110</v>
@@ -5047,99 +5086,99 @@
         <v>142</v>
       </c>
       <c r="AP47" t="n">
-        <v>89.05</v>
+        <v>86.25</v>
       </c>
       <c r="AS47" t="n">
-        <v>17.06</v>
+        <v>17.13</v>
       </c>
       <c r="BL47" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B48" t="n">
-        <v>148.1</v>
+        <v>143.4</v>
       </c>
       <c r="C48" t="n">
-        <v>51.9</v>
+        <v>50.9</v>
       </c>
       <c r="D48" t="n">
-        <v>35.4</v>
+        <v>35.7</v>
       </c>
       <c r="E48" t="n">
-        <v>31.5</v>
+        <v>26.2</v>
       </c>
       <c r="F48" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="H48" t="n">
-        <v>21.8</v>
+        <v>22.9</v>
       </c>
       <c r="I48" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J48" t="n">
-        <v>39.6</v>
+        <v>39.9</v>
       </c>
       <c r="K48" t="n">
-        <v>71</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="M48" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="N48" t="n">
-        <v>30.8</v>
+        <v>31.2</v>
       </c>
       <c r="O48" t="n">
-        <v>33.7</v>
+        <v>33.1</v>
       </c>
       <c r="Q48" t="n">
-        <v>20.7</v>
+        <v>21.6</v>
       </c>
       <c r="R48" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>20.7</v>
+        <v>21.6</v>
       </c>
       <c r="V48" t="n">
-        <v>13.1</v>
+        <v>12.9</v>
       </c>
       <c r="W48" t="n">
-        <v>25.5</v>
+        <v>28.3</v>
       </c>
       <c r="X48" t="n">
-        <v>19.3</v>
+        <v>20.6</v>
       </c>
       <c r="Y48" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z48" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AA48" t="n">
-        <v>15.5</v>
+        <v>17.9</v>
       </c>
       <c r="AB48" t="n">
-        <v>-1</v>
+        <v>-0.8</v>
       </c>
       <c r="AC48" t="n">
-        <v>6.4</v>
+        <v>8.1</v>
       </c>
       <c r="AD48" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="AF48" t="n">
-        <v>233.48</v>
+        <v>235.13</v>
       </c>
       <c r="AG48" t="n">
-        <v>-4.86</v>
+        <v>1.66</v>
       </c>
       <c r="AH48" t="n">
         <v>215</v>
@@ -5148,10 +5187,10 @@
         <v>235</v>
       </c>
       <c r="AK48" t="n">
-        <v>136.6</v>
+        <v>135.66</v>
       </c>
       <c r="AL48" t="n">
-        <v>2.01</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AM48" t="n">
         <v>110</v>
@@ -5160,57 +5199,57 @@
         <v>142</v>
       </c>
       <c r="AP48" t="n">
-        <v>86.25</v>
+        <v>88.27</v>
       </c>
       <c r="AS48" t="n">
-        <v>17.13</v>
+        <v>17.6</v>
       </c>
       <c r="BL48" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B49" t="n">
-        <v>143.4</v>
+        <v>144.9</v>
       </c>
       <c r="C49" t="n">
-        <v>50.9</v>
+        <v>53</v>
       </c>
       <c r="D49" t="n">
-        <v>35.7</v>
+        <v>35.6</v>
       </c>
       <c r="E49" t="n">
-        <v>26.2</v>
+        <v>26</v>
       </c>
       <c r="F49" t="n">
-        <v>4.3</v>
+        <v>2.8</v>
       </c>
       <c r="H49" t="n">
-        <v>22.9</v>
+        <v>24</v>
       </c>
       <c r="I49" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J49" t="n">
-        <v>39.9</v>
+        <v>40.3</v>
       </c>
       <c r="K49" t="n">
-        <v>72.59999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="M49" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="N49" t="n">
-        <v>31.2</v>
+        <v>31.6</v>
       </c>
       <c r="O49" t="n">
-        <v>33.1</v>
+        <v>33.6</v>
       </c>
       <c r="Q49" t="n">
-        <v>21.6</v>
+        <v>21</v>
       </c>
       <c r="R49" t="n">
         <v>0</v>
@@ -5219,40 +5258,40 @@
         <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>21.6</v>
+        <v>21</v>
       </c>
       <c r="V49" t="n">
-        <v>12.9</v>
+        <v>14.4</v>
       </c>
       <c r="W49" t="n">
-        <v>28.3</v>
+        <v>27.7</v>
       </c>
       <c r="X49" t="n">
-        <v>20.6</v>
+        <v>21.1</v>
       </c>
       <c r="Y49" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z49" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AA49" t="n">
-        <v>17.9</v>
+        <v>16.3</v>
       </c>
       <c r="AB49" t="n">
-        <v>-0.8</v>
+        <v>-1.1</v>
       </c>
       <c r="AC49" t="n">
-        <v>8.1</v>
+        <v>6.6</v>
       </c>
       <c r="AD49" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="AF49" t="n">
-        <v>235.13</v>
+        <v>234.87</v>
       </c>
       <c r="AG49" t="n">
-        <v>1.66</v>
+        <v>-0.26</v>
       </c>
       <c r="AH49" t="n">
         <v>215</v>
@@ -5261,10 +5300,10 @@
         <v>235</v>
       </c>
       <c r="AK49" t="n">
-        <v>135.66</v>
+        <v>136.33</v>
       </c>
       <c r="AL49" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="AM49" t="n">
         <v>110</v>
@@ -5273,99 +5312,60 @@
         <v>142</v>
       </c>
       <c r="AP49" t="n">
-        <v>88.27</v>
+        <v>87.09</v>
       </c>
       <c r="AS49" t="n">
-        <v>17.6</v>
+        <v>17.31</v>
       </c>
       <c r="BL49" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B50" t="n">
-        <v>144.9</v>
-      </c>
-      <c r="C50" t="n">
-        <v>53</v>
+        <v>132.2</v>
       </c>
       <c r="D50" t="n">
         <v>35.6</v>
       </c>
-      <c r="E50" t="n">
-        <v>26</v>
-      </c>
       <c r="F50" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="H50" t="n">
-        <v>24</v>
-      </c>
-      <c r="I50" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="J50" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="K50" t="n">
-        <v>73.7</v>
-      </c>
-      <c r="M50" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="N50" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="O50" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>21</v>
-      </c>
-      <c r="R50" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" t="n">
-        <v>0</v>
-      </c>
-      <c r="T50" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="V50" t="n">
-        <v>14.4</v>
+        <v>11.6</v>
       </c>
       <c r="W50" t="n">
-        <v>27.7</v>
+        <v>23.2</v>
       </c>
       <c r="X50" t="n">
-        <v>21.1</v>
+        <v>17.4</v>
       </c>
       <c r="Y50" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z50" t="n">
         <v>19</v>
       </c>
       <c r="AA50" t="n">
-        <v>16.3</v>
+        <v>13</v>
       </c>
       <c r="AB50" t="n">
-        <v>-1.1</v>
+        <v>0.9</v>
       </c>
       <c r="AC50" t="n">
-        <v>6.6</v>
+        <v>7.5</v>
       </c>
       <c r="AD50" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="AF50" t="n">
-        <v>234.87</v>
+        <v>234.78</v>
       </c>
       <c r="AG50" t="n">
-        <v>-0.26</v>
+        <v>-0.09</v>
       </c>
       <c r="AH50" t="n">
         <v>215</v>
@@ -5373,73 +5373,61 @@
       <c r="AI50" t="n">
         <v>235</v>
       </c>
-      <c r="AK50" t="n">
-        <v>136.33</v>
-      </c>
-      <c r="AL50" t="n">
-        <v>0.67</v>
-      </c>
       <c r="AM50" t="n">
         <v>110</v>
       </c>
       <c r="AN50" t="n">
         <v>142</v>
       </c>
-      <c r="AP50" t="n">
-        <v>87.09</v>
-      </c>
-      <c r="AS50" t="n">
-        <v>17.31</v>
-      </c>
       <c r="BL50" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B51" t="n">
-        <v>132.2</v>
+        <v>137.1</v>
       </c>
       <c r="D51" t="n">
-        <v>35.6</v>
+        <v>35.1</v>
       </c>
       <c r="F51" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="V51" t="n">
-        <v>11.6</v>
+        <v>11</v>
       </c>
       <c r="W51" t="n">
-        <v>23.2</v>
+        <v>22</v>
       </c>
       <c r="X51" t="n">
-        <v>17.4</v>
+        <v>16.5</v>
       </c>
       <c r="Y51" t="n">
         <v>7</v>
       </c>
       <c r="Z51" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AA51" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AB51" t="n">
-        <v>0.9</v>
+        <v>-5.3</v>
       </c>
       <c r="AC51" t="n">
-        <v>7.5</v>
+        <v>6.1</v>
       </c>
       <c r="AD51" t="n">
-        <v>4.2</v>
+        <v>0.4</v>
       </c>
       <c r="AF51" t="n">
-        <v>234.78</v>
+        <v>229.75</v>
       </c>
       <c r="AG51" t="n">
-        <v>-0.09</v>
+        <v>-5.03</v>
       </c>
       <c r="AH51" t="n">
         <v>215</v>
@@ -5454,54 +5442,93 @@
         <v>142</v>
       </c>
       <c r="BL51" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B52" t="n">
-        <v>137.1</v>
+        <v>166.2</v>
+      </c>
+      <c r="C52" t="n">
+        <v>72.40000000000001</v>
       </c>
       <c r="D52" t="n">
-        <v>35.1</v>
+        <v>32.7</v>
+      </c>
+      <c r="E52" t="n">
+        <v>28.1</v>
       </c>
       <c r="F52" t="n">
         <v>3.3</v>
       </c>
+      <c r="H52" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="I52" t="n">
+        <v>9</v>
+      </c>
+      <c r="J52" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="K52" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="M52" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="N52" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="O52" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="R52" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>23.7</v>
+      </c>
       <c r="V52" t="n">
-        <v>11</v>
+        <v>7.9</v>
       </c>
       <c r="W52" t="n">
-        <v>22</v>
+        <v>15.6</v>
       </c>
       <c r="X52" t="n">
-        <v>16.5</v>
+        <v>11.8</v>
       </c>
       <c r="Y52" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z52" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AA52" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AB52" t="n">
-        <v>-5.3</v>
+        <v>-3.5</v>
       </c>
       <c r="AC52" t="n">
-        <v>6.1</v>
+        <v>8.4</v>
       </c>
       <c r="AD52" t="n">
-        <v>0.4</v>
+        <v>2.5</v>
       </c>
       <c r="AF52" t="n">
-        <v>229.75</v>
+        <v>222.86</v>
       </c>
       <c r="AG52" t="n">
-        <v>-5.03</v>
+        <v>-6.9</v>
       </c>
       <c r="AH52" t="n">
         <v>215</v>
@@ -5509,100 +5536,112 @@
       <c r="AI52" t="n">
         <v>235</v>
       </c>
+      <c r="AK52" t="n">
+        <v>135.42</v>
+      </c>
+      <c r="AL52" t="n">
+        <v>-0.91</v>
+      </c>
       <c r="AM52" t="n">
         <v>110</v>
       </c>
       <c r="AN52" t="n">
         <v>142</v>
       </c>
+      <c r="AP52" t="n">
+        <v>81.98</v>
+      </c>
+      <c r="AS52" t="n">
+        <v>15.01</v>
+      </c>
       <c r="BL52" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B53" t="n">
-        <v>166.2</v>
+        <v>166.3</v>
       </c>
       <c r="C53" t="n">
-        <v>72.40000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="D53" t="n">
-        <v>32.7</v>
+        <v>32.8</v>
       </c>
       <c r="E53" t="n">
-        <v>28.1</v>
+        <v>28.8</v>
       </c>
       <c r="F53" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="H53" t="n">
         <v>23.4</v>
       </c>
       <c r="I53" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J53" t="n">
-        <v>42.1</v>
+        <v>41.2</v>
       </c>
       <c r="K53" t="n">
-        <v>74.5</v>
+        <v>73.8</v>
       </c>
       <c r="M53" t="n">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="N53" t="n">
-        <v>33.7</v>
+        <v>35.4</v>
       </c>
       <c r="O53" t="n">
-        <v>39.3</v>
+        <v>42.6</v>
       </c>
       <c r="Q53" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="R53" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="V53" t="n">
-        <v>7.9</v>
+        <v>6.7</v>
       </c>
       <c r="W53" t="n">
-        <v>15.6</v>
+        <v>18.1</v>
       </c>
       <c r="X53" t="n">
-        <v>11.8</v>
+        <v>12.4</v>
       </c>
       <c r="Y53" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Z53" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AA53" t="n">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AB53" t="n">
-        <v>-3.5</v>
+        <v>-2.9</v>
       </c>
       <c r="AC53" t="n">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="AD53" t="n">
-        <v>2.5</v>
+        <v>4.3</v>
       </c>
       <c r="AF53" t="n">
-        <v>222.86</v>
+        <v>218.37</v>
       </c>
       <c r="AG53" t="n">
-        <v>-6.9</v>
+        <v>-4.49</v>
       </c>
       <c r="AH53" t="n">
         <v>215</v>
@@ -5611,10 +5650,10 @@
         <v>235</v>
       </c>
       <c r="AK53" t="n">
-        <v>135.42</v>
+        <v>131.24</v>
       </c>
       <c r="AL53" t="n">
-        <v>-0.91</v>
+        <v>-4.18</v>
       </c>
       <c r="AM53" t="n">
         <v>110</v>
@@ -5623,99 +5662,99 @@
         <v>142</v>
       </c>
       <c r="AP53" t="n">
-        <v>81.98</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="AS53" t="n">
-        <v>15.01</v>
+        <v>12.97</v>
       </c>
       <c r="BL53" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B54" t="n">
-        <v>166.3</v>
+        <v>154.1</v>
       </c>
       <c r="C54" t="n">
-        <v>74.90000000000001</v>
+        <v>65</v>
       </c>
       <c r="D54" t="n">
-        <v>32.8</v>
+        <v>32</v>
       </c>
       <c r="E54" t="n">
-        <v>28.8</v>
+        <v>25.2</v>
       </c>
       <c r="F54" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="H54" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="I54" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="J54" t="n">
-        <v>41.2</v>
+        <v>38.5</v>
       </c>
       <c r="K54" t="n">
-        <v>73.8</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="M54" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="N54" t="n">
-        <v>35.4</v>
+        <v>32.3</v>
       </c>
       <c r="O54" t="n">
-        <v>42.6</v>
+        <v>40.3</v>
       </c>
       <c r="Q54" t="n">
-        <v>23.9</v>
+        <v>21.7</v>
       </c>
       <c r="R54" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="S54" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T54" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="V54" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="W54" t="n">
+        <v>21</v>
+      </c>
+      <c r="X54" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AD54" t="n">
         <v>3.9</v>
       </c>
-      <c r="S54" t="n">
-        <v>0</v>
-      </c>
-      <c r="T54" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="V54" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="W54" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="X54" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>11</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>-2.9</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AF54" t="n">
-        <v>218.37</v>
+        <v>218.04</v>
       </c>
       <c r="AG54" t="n">
-        <v>-4.49</v>
+        <v>-0.33</v>
       </c>
       <c r="AH54" t="n">
         <v>215</v>
@@ -5724,10 +5763,10 @@
         <v>235</v>
       </c>
       <c r="AK54" t="n">
-        <v>131.24</v>
+        <v>129.21</v>
       </c>
       <c r="AL54" t="n">
-        <v>-4.18</v>
+        <v>-2.03</v>
       </c>
       <c r="AM54" t="n">
         <v>110</v>
@@ -5736,99 +5775,99 @@
         <v>142</v>
       </c>
       <c r="AP54" t="n">
-        <v>79.98999999999999</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="AS54" t="n">
-        <v>12.97</v>
+        <v>15.23</v>
       </c>
       <c r="BL54" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B55" t="n">
-        <v>154.1</v>
+        <v>148.8</v>
       </c>
       <c r="C55" t="n">
-        <v>65</v>
+        <v>57.6</v>
       </c>
       <c r="D55" t="n">
-        <v>32</v>
+        <v>32.7</v>
       </c>
       <c r="E55" t="n">
-        <v>25.2</v>
+        <v>26.3</v>
       </c>
       <c r="F55" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="H55" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="I55" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="J55" t="n">
-        <v>38.5</v>
+        <v>41.6</v>
       </c>
       <c r="K55" t="n">
-        <v>70.90000000000001</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="M55" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="N55" t="n">
-        <v>32.3</v>
+        <v>35</v>
       </c>
       <c r="O55" t="n">
-        <v>40.3</v>
+        <v>42.4</v>
       </c>
       <c r="Q55" t="n">
         <v>21.7</v>
       </c>
       <c r="R55" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="S55" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="T55" t="n">
         <v>21.7</v>
       </c>
       <c r="V55" t="n">
-        <v>5.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W55" t="n">
-        <v>21</v>
+        <v>24.1</v>
       </c>
       <c r="X55" t="n">
-        <v>13.2</v>
+        <v>16.1</v>
       </c>
       <c r="Y55" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z55" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA55" t="n">
-        <v>14.5</v>
+        <v>15.6</v>
       </c>
       <c r="AB55" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="AC55" t="n">
-        <v>7.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AD55" t="n">
-        <v>3.9</v>
+        <v>6.3</v>
       </c>
       <c r="AF55" t="n">
-        <v>218.04</v>
+        <v>220.84</v>
       </c>
       <c r="AG55" t="n">
-        <v>-0.33</v>
+        <v>2.8</v>
       </c>
       <c r="AH55" t="n">
         <v>215</v>
@@ -5837,10 +5876,10 @@
         <v>235</v>
       </c>
       <c r="AK55" t="n">
-        <v>129.21</v>
+        <v>129.07</v>
       </c>
       <c r="AL55" t="n">
-        <v>-2.03</v>
+        <v>-0.14</v>
       </c>
       <c r="AM55" t="n">
         <v>110</v>
@@ -5849,81 +5888,81 @@
         <v>142</v>
       </c>
       <c r="AP55" t="n">
-        <v>82.90000000000001</v>
+        <v>85.52</v>
       </c>
       <c r="AS55" t="n">
-        <v>15.23</v>
+        <v>15.82</v>
       </c>
       <c r="BL55" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B56" t="n">
-        <v>148.8</v>
+        <v>146.8</v>
       </c>
       <c r="C56" t="n">
-        <v>57.6</v>
+        <v>52.8</v>
       </c>
       <c r="D56" t="n">
-        <v>32.7</v>
+        <v>33.6</v>
       </c>
       <c r="E56" t="n">
-        <v>26.3</v>
+        <v>28.9</v>
       </c>
       <c r="F56" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="H56" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="I56" t="n">
-        <v>8.9</v>
+        <v>9.1</v>
       </c>
       <c r="J56" t="n">
-        <v>41.6</v>
+        <v>40.8</v>
       </c>
       <c r="K56" t="n">
-        <v>74.09999999999999</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="M56" t="n">
-        <v>7.4</v>
+        <v>5.6</v>
       </c>
       <c r="N56" t="n">
-        <v>35</v>
+        <v>33.1</v>
       </c>
       <c r="O56" t="n">
-        <v>42.4</v>
+        <v>38.7</v>
       </c>
       <c r="Q56" t="n">
-        <v>21.7</v>
+        <v>22</v>
       </c>
       <c r="R56" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>21.7</v>
+        <v>22</v>
       </c>
       <c r="Y56" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z56" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA56" t="n">
-        <v>15.6</v>
+        <v>16.1</v>
       </c>
       <c r="AF56" t="n">
-        <v>220.84</v>
+        <v>225.87</v>
       </c>
       <c r="AG56" t="n">
-        <v>2.8</v>
+        <v>5.03</v>
       </c>
       <c r="AH56" t="n">
         <v>215</v>
@@ -5932,10 +5971,10 @@
         <v>235</v>
       </c>
       <c r="AK56" t="n">
-        <v>129.07</v>
+        <v>130.73</v>
       </c>
       <c r="AL56" t="n">
-        <v>-0.14</v>
+        <v>1.66</v>
       </c>
       <c r="AM56" t="n">
         <v>110</v>
@@ -5944,81 +5983,36 @@
         <v>142</v>
       </c>
       <c r="AP56" t="n">
-        <v>85.52</v>
+        <v>88.2</v>
       </c>
       <c r="AS56" t="n">
-        <v>15.82</v>
+        <v>15.76</v>
       </c>
       <c r="BL56" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B57" t="n">
-        <v>146.8</v>
-      </c>
-      <c r="C57" t="n">
-        <v>52.8</v>
+        <v>133.9</v>
       </c>
       <c r="D57" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="E57" t="n">
-        <v>28.9</v>
+        <v>34.7</v>
       </c>
       <c r="F57" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="H57" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="I57" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="J57" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="K57" t="n">
-        <v>73.59999999999999</v>
-      </c>
-      <c r="M57" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="N57" t="n">
-        <v>33.1</v>
-      </c>
-      <c r="O57" t="n">
-        <v>38.7</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>22</v>
-      </c>
-      <c r="R57" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="S57" t="n">
-        <v>0</v>
-      </c>
-      <c r="T57" t="n">
-        <v>22</v>
+        <v>3.3</v>
       </c>
       <c r="Y57" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z57" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AA57" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="AF57" t="n">
-        <v>225.87</v>
-      </c>
-      <c r="AG57" t="n">
-        <v>5.03</v>
+        <v>15</v>
       </c>
       <c r="AH57" t="n">
         <v>215</v>
@@ -6026,49 +6020,37 @@
       <c r="AI57" t="n">
         <v>235</v>
       </c>
-      <c r="AK57" t="n">
-        <v>130.73</v>
-      </c>
-      <c r="AL57" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AM57" t="n">
         <v>110</v>
       </c>
       <c r="AN57" t="n">
         <v>142</v>
       </c>
-      <c r="AP57" t="n">
-        <v>88.2</v>
-      </c>
-      <c r="AS57" t="n">
-        <v>15.76</v>
-      </c>
       <c r="BL57" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B58" t="n">
-        <v>133.9</v>
+        <v>137.5</v>
       </c>
       <c r="D58" t="n">
-        <v>34.7</v>
+        <v>32.8</v>
       </c>
       <c r="F58" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="Y58" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z58" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="AA58" t="n">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="AH58" t="n">
         <v>215</v>
@@ -6083,30 +6065,75 @@
         <v>142</v>
       </c>
       <c r="BL58" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B59" t="n">
-        <v>137.5</v>
+        <v>157.1</v>
+      </c>
+      <c r="C59" t="n">
+        <v>73.09999999999999</v>
       </c>
       <c r="D59" t="n">
-        <v>32.8</v>
+        <v>31.7</v>
+      </c>
+      <c r="E59" t="n">
+        <v>26.1</v>
       </c>
       <c r="F59" t="n">
-        <v>2.3</v>
+        <v>2</v>
+      </c>
+      <c r="H59" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="I59" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="J59" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="K59" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="M59" t="n">
+        <v>6</v>
+      </c>
+      <c r="N59" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="O59" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="R59" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>23.8</v>
       </c>
       <c r="Y59" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="Z59" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA59" t="n">
-        <v>10.5</v>
+        <v>7.9</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>224.2</v>
+      </c>
+      <c r="AG59" t="n">
+        <v>-1.67</v>
       </c>
       <c r="AH59" t="n">
         <v>215</v>
@@ -6114,82 +6141,94 @@
       <c r="AI59" t="n">
         <v>235</v>
       </c>
+      <c r="AK59" t="n">
+        <v>128.6</v>
+      </c>
+      <c r="AL59" t="n">
+        <v>-2.13</v>
+      </c>
       <c r="AM59" t="n">
         <v>110</v>
       </c>
       <c r="AN59" t="n">
         <v>142</v>
       </c>
+      <c r="AP59" t="n">
+        <v>81.18000000000001</v>
+      </c>
+      <c r="AS59" t="n">
+        <v>14.06</v>
+      </c>
       <c r="BL59" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B60" t="n">
-        <v>157.1</v>
+        <v>153.1</v>
       </c>
       <c r="C60" t="n">
-        <v>73.09999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="D60" t="n">
-        <v>31.7</v>
+        <v>32.2</v>
       </c>
       <c r="E60" t="n">
-        <v>26.1</v>
+        <v>25.9</v>
       </c>
       <c r="F60" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="H60" t="n">
-        <v>23.6</v>
+        <v>24.4</v>
       </c>
       <c r="I60" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="J60" t="n">
-        <v>40.5</v>
+        <v>39.6</v>
       </c>
       <c r="K60" t="n">
-        <v>73.5</v>
+        <v>73.3</v>
       </c>
       <c r="M60" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="N60" t="n">
-        <v>33.4</v>
+        <v>34.4</v>
       </c>
       <c r="O60" t="n">
-        <v>39.5</v>
+        <v>40.1</v>
       </c>
       <c r="Q60" t="n">
         <v>23.8</v>
       </c>
       <c r="R60" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="S60" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T60" t="n">
         <v>23.8</v>
       </c>
       <c r="Y60" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Z60" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA60" t="n">
         <v>12</v>
       </c>
-      <c r="AA60" t="n">
-        <v>7.9</v>
-      </c>
       <c r="AF60" t="n">
-        <v>224.2</v>
+        <v>223.35</v>
       </c>
       <c r="AG60" t="n">
-        <v>-1.67</v>
+        <v>-0.85</v>
       </c>
       <c r="AH60" t="n">
         <v>215</v>
@@ -6198,10 +6237,10 @@
         <v>235</v>
       </c>
       <c r="AK60" t="n">
-        <v>128.6</v>
+        <v>127.19</v>
       </c>
       <c r="AL60" t="n">
-        <v>-2.13</v>
+        <v>-1.41</v>
       </c>
       <c r="AM60" t="n">
         <v>110</v>
@@ -6210,36 +6249,36 @@
         <v>142</v>
       </c>
       <c r="AP60" t="n">
-        <v>81.18000000000001</v>
+        <v>81.06</v>
       </c>
       <c r="AS60" t="n">
-        <v>14.06</v>
+        <v>13.63</v>
       </c>
       <c r="BL60" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B61" t="n">
-        <v>150.3</v>
+        <v>132.8</v>
       </c>
       <c r="D61" t="n">
-        <v>33.3</v>
+        <v>33.8</v>
       </c>
       <c r="F61" t="n">
         <v>2.3</v>
       </c>
       <c r="Y61" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="Z61" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA61" t="n">
         <v>16</v>
-      </c>
-      <c r="AA61" t="n">
-        <v>10.5</v>
       </c>
       <c r="AH61" t="n">
         <v>215</v>
@@ -6254,30 +6293,30 @@
         <v>142</v>
       </c>
       <c r="BL61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B62" t="n">
-        <v>132.8</v>
+        <v>132.5</v>
       </c>
       <c r="D62" t="n">
-        <v>33.8</v>
+        <v>33.4</v>
       </c>
       <c r="F62" t="n">
         <v>2.3</v>
       </c>
       <c r="Y62" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="Z62" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AA62" t="n">
-        <v>16</v>
+        <v>10.5</v>
       </c>
       <c r="AH62" t="n">
         <v>215</v>
@@ -6292,7 +6331,7 @@
         <v>142</v>
       </c>
       <c r="BL62" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -628,55 +628,88 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B2" t="n">
-        <v>138.5</v>
+        <v>161.1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>67</v>
       </c>
       <c r="D2" t="n">
-        <v>31.7</v>
+        <v>31.9</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.5</v>
       </c>
       <c r="F2" t="n">
-        <v>7</v>
+        <v>7.7</v>
+      </c>
+      <c r="H2" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J2" t="n">
+        <v>41.1</v>
       </c>
       <c r="K2" t="n">
-        <v>91</v>
+        <v>75.59999999999999</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="N2" t="n">
+        <v>35</v>
       </c>
       <c r="O2" t="n">
-        <v>37.8</v>
+        <v>37.2</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T2" t="n">
+        <v>20.5</v>
       </c>
       <c r="V2" t="n">
-        <v>13.2</v>
+        <v>14.1</v>
       </c>
       <c r="W2" t="n">
-        <v>22.5</v>
+        <v>19.3</v>
       </c>
       <c r="X2" t="n">
-        <v>17.9</v>
+        <v>16.7</v>
       </c>
       <c r="Y2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="Z2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AA2" t="n">
-        <v>15.5</v>
+        <v>11.1</v>
       </c>
       <c r="AB2" t="n">
-        <v>-1.9</v>
+        <v>-3.8</v>
       </c>
       <c r="AC2" t="n">
-        <v>5.2</v>
+        <v>3.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.7</v>
+        <v>-0.3</v>
       </c>
       <c r="AF2" t="n">
-        <v>231.99</v>
+        <v>225.51</v>
       </c>
       <c r="AG2" t="n">
-        <v>-3.41</v>
+        <v>-6.48</v>
       </c>
       <c r="AH2" t="n">
         <v>215</v>
@@ -685,10 +718,10 @@
         <v>235</v>
       </c>
       <c r="AK2" t="n">
-        <v>136.12</v>
+        <v>133.83</v>
       </c>
       <c r="AL2" t="n">
-        <v>-1.38</v>
+        <v>-2.29</v>
       </c>
       <c r="AM2" t="n">
         <v>110</v>
@@ -696,94 +729,100 @@
       <c r="AN2" t="n">
         <v>142</v>
       </c>
+      <c r="AP2" t="n">
+        <v>82.93000000000001</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>15.73</v>
+      </c>
       <c r="BL2" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B3" t="n">
-        <v>161.1</v>
+        <v>176.4</v>
       </c>
       <c r="C3" t="n">
-        <v>67</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>31.9</v>
+        <v>32.7</v>
       </c>
       <c r="E3" t="n">
-        <v>31.5</v>
+        <v>35</v>
       </c>
       <c r="F3" t="n">
-        <v>7.7</v>
+        <v>6.8</v>
       </c>
       <c r="H3" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="I3" t="n">
         <v>11.4</v>
       </c>
       <c r="J3" t="n">
-        <v>41.1</v>
+        <v>41.5</v>
       </c>
       <c r="K3" t="n">
-        <v>75.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="M3" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="N3" t="n">
-        <v>35</v>
+        <v>36.4</v>
       </c>
       <c r="O3" t="n">
-        <v>37.2</v>
+        <v>39.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>20.5</v>
+        <v>22.3</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="T3" t="n">
-        <v>20.5</v>
+        <v>22.3</v>
       </c>
       <c r="V3" t="n">
-        <v>14.1</v>
+        <v>11.5</v>
       </c>
       <c r="W3" t="n">
-        <v>19.3</v>
+        <v>15.5</v>
       </c>
       <c r="X3" t="n">
-        <v>16.7</v>
+        <v>13.5</v>
       </c>
       <c r="Y3" t="n">
         <v>9</v>
       </c>
       <c r="Z3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA3" t="n">
-        <v>11.1</v>
+        <v>11.6</v>
       </c>
       <c r="AB3" t="n">
-        <v>-3.8</v>
+        <v>-5.6</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.3</v>
+        <v>-1.3</v>
       </c>
       <c r="AF3" t="n">
-        <v>225.51</v>
+        <v>220.92</v>
       </c>
       <c r="AG3" t="n">
-        <v>-6.48</v>
+        <v>-4.59</v>
       </c>
       <c r="AH3" t="n">
         <v>215</v>
@@ -792,10 +831,10 @@
         <v>235</v>
       </c>
       <c r="AK3" t="n">
-        <v>133.83</v>
+        <v>131.85</v>
       </c>
       <c r="AL3" t="n">
-        <v>-2.29</v>
+        <v>-1.98</v>
       </c>
       <c r="AM3" t="n">
         <v>110</v>
@@ -804,99 +843,99 @@
         <v>142</v>
       </c>
       <c r="AP3" t="n">
-        <v>82.93000000000001</v>
+        <v>79.75</v>
       </c>
       <c r="AS3" t="n">
-        <v>15.73</v>
+        <v>15.49</v>
       </c>
       <c r="BL3" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B4" t="n">
-        <v>176.4</v>
+        <v>181</v>
       </c>
       <c r="C4" t="n">
-        <v>77.09999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="D4" t="n">
-        <v>32.7</v>
+        <v>33</v>
       </c>
       <c r="E4" t="n">
-        <v>35</v>
+        <v>35.1</v>
       </c>
       <c r="F4" t="n">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="H4" t="n">
-        <v>23.2</v>
+        <v>22.8</v>
       </c>
       <c r="I4" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="J4" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="K4" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N4" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="O4" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S4" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="T4" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="V4" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="W4" t="n">
+        <v>13</v>
+      </c>
+      <c r="X4" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA4" t="n">
         <v>11.4</v>
       </c>
-      <c r="J4" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="K4" t="n">
-        <v>76</v>
-      </c>
-      <c r="M4" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N4" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="O4" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>14</v>
-      </c>
-      <c r="T4" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="V4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="W4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="X4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>11.6</v>
-      </c>
       <c r="AB4" t="n">
-        <v>-5.6</v>
+        <v>-6.1</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>-1.3</v>
+        <v>-0.9</v>
       </c>
       <c r="AF4" t="n">
         <v>220.92</v>
       </c>
       <c r="AG4" t="n">
-        <v>-4.59</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
         <v>215</v>
@@ -905,10 +944,10 @@
         <v>235</v>
       </c>
       <c r="AK4" t="n">
-        <v>131.85</v>
+        <v>130.06</v>
       </c>
       <c r="AL4" t="n">
-        <v>-1.98</v>
+        <v>-1.79</v>
       </c>
       <c r="AM4" t="n">
         <v>110</v>
@@ -917,99 +956,99 @@
         <v>142</v>
       </c>
       <c r="AP4" t="n">
-        <v>79.75</v>
+        <v>79.94</v>
       </c>
       <c r="AS4" t="n">
-        <v>15.49</v>
+        <v>14.93</v>
       </c>
       <c r="BL4" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B5" t="n">
-        <v>181</v>
+        <v>179.6</v>
       </c>
       <c r="C5" t="n">
-        <v>80.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>33</v>
+        <v>30.3</v>
       </c>
       <c r="E5" t="n">
-        <v>35.1</v>
+        <v>31.1</v>
       </c>
       <c r="F5" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="H5" t="n">
-        <v>22.8</v>
+        <v>21.5</v>
       </c>
       <c r="I5" t="n">
-        <v>11.2</v>
+        <v>10.8</v>
       </c>
       <c r="J5" t="n">
-        <v>41.9</v>
+        <v>42.3</v>
       </c>
       <c r="K5" t="n">
-        <v>75.90000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>2.9</v>
+        <v>4.3</v>
       </c>
       <c r="N5" t="n">
-        <v>36.9</v>
+        <v>37.1</v>
       </c>
       <c r="O5" t="n">
-        <v>39.8</v>
+        <v>41.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="R5" t="n">
+        <v>2</v>
+      </c>
+      <c r="S5" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="V5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="W5" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="X5" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AD5" t="n">
         <v>0.5</v>
       </c>
-      <c r="S5" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="T5" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="V5" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="W5" t="n">
-        <v>13</v>
-      </c>
-      <c r="X5" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>-6.1</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>-0.9</v>
-      </c>
       <c r="AF5" t="n">
-        <v>220.92</v>
+        <v>216.02</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AH5" t="n">
         <v>215</v>
@@ -1018,10 +1057,10 @@
         <v>235</v>
       </c>
       <c r="AK5" t="n">
-        <v>130.06</v>
+        <v>127.85</v>
       </c>
       <c r="AL5" t="n">
-        <v>-1.79</v>
+        <v>-2.21</v>
       </c>
       <c r="AM5" t="n">
         <v>110</v>
@@ -1030,99 +1069,99 @@
         <v>142</v>
       </c>
       <c r="AP5" t="n">
-        <v>79.94</v>
+        <v>82.2</v>
       </c>
       <c r="AS5" t="n">
-        <v>14.93</v>
+        <v>15.16</v>
       </c>
       <c r="BL5" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B6" t="n">
-        <v>179.6</v>
+        <v>170.4</v>
       </c>
       <c r="C6" t="n">
-        <v>81.90000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="D6" t="n">
-        <v>30.3</v>
+        <v>29.8</v>
       </c>
       <c r="E6" t="n">
-        <v>31.1</v>
+        <v>29.7</v>
       </c>
       <c r="F6" t="n">
-        <v>6.8</v>
+        <v>6.3</v>
       </c>
       <c r="H6" t="n">
-        <v>21.5</v>
+        <v>22.5</v>
       </c>
       <c r="I6" t="n">
-        <v>10.8</v>
+        <v>11.2</v>
       </c>
       <c r="J6" t="n">
-        <v>42.3</v>
+        <v>41.4</v>
       </c>
       <c r="K6" t="n">
-        <v>74.59999999999999</v>
+        <v>75</v>
       </c>
       <c r="M6" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="N6" t="n">
-        <v>37.1</v>
+        <v>36.6</v>
       </c>
       <c r="O6" t="n">
-        <v>41.4</v>
+        <v>41.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>22.6</v>
+        <v>23.3</v>
       </c>
       <c r="R6" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="S6" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="T6" t="n">
-        <v>22.6</v>
+        <v>23.3</v>
       </c>
       <c r="V6" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="W6" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="X6" t="n">
         <v>12.6</v>
       </c>
       <c r="Y6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z6" t="n">
         <v>13</v>
       </c>
       <c r="AA6" t="n">
-        <v>11.1</v>
+        <v>12.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>-3.4</v>
+        <v>1.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.4</v>
+        <v>7.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.5</v>
+        <v>4.7</v>
       </c>
       <c r="AF6" t="n">
         <v>216.02</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
         <v>215</v>
@@ -1131,10 +1170,10 @@
         <v>235</v>
       </c>
       <c r="AK6" t="n">
-        <v>127.85</v>
+        <v>128.54</v>
       </c>
       <c r="AL6" t="n">
-        <v>-2.21</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AM6" t="n">
         <v>110</v>
@@ -1143,99 +1182,66 @@
         <v>142</v>
       </c>
       <c r="AP6" t="n">
-        <v>82.2</v>
+        <v>84.73</v>
       </c>
       <c r="AS6" t="n">
-        <v>15.16</v>
+        <v>15.34</v>
       </c>
       <c r="BL6" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B7" t="n">
-        <v>170.4</v>
-      </c>
-      <c r="C7" t="n">
-        <v>78.5</v>
+        <v>156</v>
       </c>
       <c r="D7" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="E7" t="n">
-        <v>29.7</v>
+        <v>30.1</v>
       </c>
       <c r="F7" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="H7" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="I7" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>41.4</v>
+        <v>6.8</v>
       </c>
       <c r="K7" t="n">
-        <v>75</v>
-      </c>
-      <c r="M7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="N7" t="n">
-        <v>36.6</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S7" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>23.3</v>
+        <v>39.2</v>
       </c>
       <c r="V7" t="n">
-        <v>9.5</v>
+        <v>7.1</v>
       </c>
       <c r="W7" t="n">
-        <v>15.7</v>
+        <v>20.9</v>
       </c>
       <c r="X7" t="n">
-        <v>12.6</v>
+        <v>14</v>
       </c>
       <c r="Y7" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Z7" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA7" t="n">
-        <v>12.7</v>
+        <v>13.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.8</v>
+        <v>-0.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="AD7" t="n">
-        <v>4.7</v>
+        <v>2.4</v>
       </c>
       <c r="AF7" t="n">
-        <v>216.02</v>
+        <v>224.53</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH7" t="n">
         <v>215</v>
@@ -1244,10 +1250,10 @@
         <v>235</v>
       </c>
       <c r="AK7" t="n">
-        <v>128.54</v>
+        <v>130.92</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.6899999999999999</v>
+        <v>2.38</v>
       </c>
       <c r="AM7" t="n">
         <v>110</v>
@@ -1255,67 +1261,61 @@
       <c r="AN7" t="n">
         <v>142</v>
       </c>
-      <c r="AP7" t="n">
-        <v>84.73</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>15.34</v>
-      </c>
       <c r="BL7" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B8" t="n">
-        <v>156</v>
+        <v>147.8</v>
       </c>
       <c r="D8" t="n">
-        <v>30.1</v>
+        <v>32</v>
       </c>
       <c r="F8" t="n">
         <v>6.8</v>
       </c>
       <c r="K8" t="n">
-        <v>95.90000000000001</v>
+        <v>96.5</v>
       </c>
       <c r="O8" t="n">
-        <v>39.2</v>
+        <v>39.3</v>
       </c>
       <c r="V8" t="n">
-        <v>7.1</v>
+        <v>8</v>
       </c>
       <c r="W8" t="n">
-        <v>20.9</v>
+        <v>22.4</v>
       </c>
       <c r="X8" t="n">
-        <v>14</v>
+        <v>15.2</v>
       </c>
       <c r="Y8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA8" t="n">
         <v>13.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="AC8" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AF8" t="n">
-        <v>224.53</v>
+        <v>230.27</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.32</v>
+        <v>5.74</v>
       </c>
       <c r="AH8" t="n">
         <v>215</v>
@@ -1324,10 +1324,10 @@
         <v>235</v>
       </c>
       <c r="AK8" t="n">
-        <v>130.92</v>
+        <v>132.76</v>
       </c>
       <c r="AL8" t="n">
-        <v>2.38</v>
+        <v>1.84</v>
       </c>
       <c r="AM8" t="n">
         <v>110</v>
@@ -1336,60 +1336,93 @@
         <v>142</v>
       </c>
       <c r="BL8" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="B9" t="n">
-        <v>147.8</v>
+        <v>149.1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>60</v>
       </c>
       <c r="D9" t="n">
-        <v>32</v>
+        <v>29</v>
+      </c>
+      <c r="E9" t="n">
+        <v>25.9</v>
       </c>
       <c r="F9" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
+      </c>
+      <c r="H9" t="n">
+        <v>24</v>
+      </c>
+      <c r="I9" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="J9" t="n">
+        <v>38.8</v>
       </c>
       <c r="K9" t="n">
-        <v>96.5</v>
+        <v>74.5</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N9" t="n">
+        <v>36.7</v>
       </c>
       <c r="O9" t="n">
-        <v>39.3</v>
+        <v>40.1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>7</v>
+      </c>
+      <c r="T9" t="n">
+        <v>21.7</v>
       </c>
       <c r="V9" t="n">
-        <v>8</v>
+        <v>10.3</v>
       </c>
       <c r="W9" t="n">
-        <v>22.4</v>
+        <v>24.4</v>
       </c>
       <c r="X9" t="n">
-        <v>15.2</v>
+        <v>17.4</v>
       </c>
       <c r="Y9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z9" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AA9" t="n">
-        <v>13.5</v>
+        <v>15.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0.3</v>
+        <v>-2.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.6</v>
+        <v>2.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.1</v>
+        <v>-0.1</v>
       </c>
       <c r="AF9" t="n">
-        <v>230.27</v>
+        <v>237.43</v>
       </c>
       <c r="AG9" t="n">
-        <v>5.74</v>
+        <v>7.16</v>
       </c>
       <c r="AH9" t="n">
         <v>215</v>
@@ -1398,10 +1431,10 @@
         <v>235</v>
       </c>
       <c r="AK9" t="n">
-        <v>132.76</v>
+        <v>134.95</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.84</v>
+        <v>2.19</v>
       </c>
       <c r="AM9" t="n">
         <v>110</v>
@@ -1409,94 +1442,67 @@
       <c r="AN9" t="n">
         <v>142</v>
       </c>
+      <c r="AP9" t="n">
+        <v>91.28</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>16.95</v>
+      </c>
       <c r="BL9" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="B10" t="n">
-        <v>149.1</v>
-      </c>
-      <c r="C10" t="n">
-        <v>60</v>
+        <v>143.9</v>
       </c>
       <c r="D10" t="n">
-        <v>29</v>
-      </c>
-      <c r="E10" t="n">
-        <v>25.9</v>
+        <v>32.9</v>
       </c>
       <c r="F10" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="H10" t="n">
-        <v>24</v>
-      </c>
-      <c r="I10" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="J10" t="n">
-        <v>38.8</v>
+        <v>6.8</v>
       </c>
       <c r="K10" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="M10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N10" t="n">
-        <v>36.7</v>
+        <v>96.2</v>
       </c>
       <c r="O10" t="n">
-        <v>40.1</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>7</v>
-      </c>
-      <c r="T10" t="n">
-        <v>21.7</v>
+        <v>37.9</v>
       </c>
       <c r="V10" t="n">
-        <v>10.3</v>
+        <v>10</v>
       </c>
       <c r="W10" t="n">
-        <v>24.4</v>
+        <v>25.6</v>
       </c>
       <c r="X10" t="n">
-        <v>17.4</v>
+        <v>17.8</v>
       </c>
       <c r="Y10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AA10" t="n">
-        <v>15.7</v>
+        <v>16</v>
       </c>
       <c r="AB10" t="n">
-        <v>-2.4</v>
+        <v>-1.4</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0.1</v>
+        <v>0.9</v>
       </c>
       <c r="AF10" t="n">
-        <v>237.43</v>
+        <v>236.14</v>
       </c>
       <c r="AG10" t="n">
-        <v>7.16</v>
+        <v>-1.29</v>
       </c>
       <c r="AH10" t="n">
         <v>215</v>
@@ -1505,10 +1511,10 @@
         <v>235</v>
       </c>
       <c r="AK10" t="n">
-        <v>134.95</v>
+        <v>136.28</v>
       </c>
       <c r="AL10" t="n">
-        <v>2.19</v>
+        <v>1.33</v>
       </c>
       <c r="AM10" t="n">
         <v>110</v>
@@ -1516,67 +1522,94 @@
       <c r="AN10" t="n">
         <v>142</v>
       </c>
-      <c r="AP10" t="n">
-        <v>91.28</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>16.95</v>
-      </c>
       <c r="BL10" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B11" t="n">
-        <v>143.9</v>
+        <v>166.4</v>
+      </c>
+      <c r="C11" t="n">
+        <v>63.7</v>
       </c>
       <c r="D11" t="n">
-        <v>32.9</v>
+        <v>34.5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>36.4</v>
       </c>
       <c r="F11" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
+      </c>
+      <c r="H11" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="I11" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="J11" t="n">
+        <v>39.9</v>
       </c>
       <c r="K11" t="n">
-        <v>96.2</v>
+        <v>75.2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>35.9</v>
       </c>
       <c r="O11" t="n">
-        <v>37.9</v>
+        <v>39</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="S11" t="n">
+        <v>6</v>
+      </c>
+      <c r="T11" t="n">
+        <v>20.3</v>
       </c>
       <c r="V11" t="n">
-        <v>10</v>
+        <v>11.9</v>
       </c>
       <c r="W11" t="n">
-        <v>25.6</v>
+        <v>27</v>
       </c>
       <c r="X11" t="n">
-        <v>17.8</v>
+        <v>19.4</v>
       </c>
       <c r="Y11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z11" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AA11" t="n">
-        <v>16</v>
+        <v>14.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>-1.4</v>
+        <v>-3.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.9</v>
+        <v>-0.4</v>
       </c>
       <c r="AF11" t="n">
-        <v>236.14</v>
+        <v>236.13</v>
       </c>
       <c r="AG11" t="n">
-        <v>-1.29</v>
+        <v>-0.01</v>
       </c>
       <c r="AH11" t="n">
         <v>215</v>
@@ -1585,10 +1618,10 @@
         <v>235</v>
       </c>
       <c r="AK11" t="n">
-        <v>136.28</v>
+        <v>134.54</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.33</v>
+        <v>-1.74</v>
       </c>
       <c r="AM11" t="n">
         <v>110</v>
@@ -1596,94 +1629,100 @@
       <c r="AN11" t="n">
         <v>142</v>
       </c>
+      <c r="AP11" t="n">
+        <v>82.27</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>16.28</v>
+      </c>
       <c r="BL11" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B12" t="n">
-        <v>166.4</v>
+        <v>172.9</v>
       </c>
       <c r="C12" t="n">
-        <v>63.7</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>34.5</v>
+        <v>34.9</v>
       </c>
       <c r="E12" t="n">
-        <v>36.4</v>
+        <v>35.2</v>
       </c>
       <c r="F12" t="n">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="H12" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="I12" t="n">
-        <v>11.6</v>
+        <v>11.3</v>
       </c>
       <c r="J12" t="n">
-        <v>39.9</v>
+        <v>41.7</v>
       </c>
       <c r="K12" t="n">
-        <v>75.2</v>
+        <v>76.7</v>
       </c>
       <c r="M12" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="N12" t="n">
-        <v>35.9</v>
+        <v>34.8</v>
       </c>
       <c r="O12" t="n">
-        <v>39</v>
+        <v>37.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>20.3</v>
+        <v>19</v>
       </c>
       <c r="R12" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T12" t="n">
-        <v>20.3</v>
+        <v>19</v>
       </c>
       <c r="V12" t="n">
-        <v>11.9</v>
+        <v>14.4</v>
       </c>
       <c r="W12" t="n">
-        <v>27</v>
+        <v>18.7</v>
       </c>
       <c r="X12" t="n">
-        <v>19.4</v>
+        <v>16.6</v>
       </c>
       <c r="Y12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Z12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA12" t="n">
-        <v>14.4</v>
+        <v>12.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>-3.5</v>
+        <v>-4.9</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0.4</v>
+        <v>-0.7</v>
       </c>
       <c r="AF12" t="n">
-        <v>236.13</v>
+        <v>218.6</v>
       </c>
       <c r="AG12" t="n">
-        <v>-0.01</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="AH12" t="n">
         <v>215</v>
@@ -1692,10 +1731,10 @@
         <v>235</v>
       </c>
       <c r="AK12" t="n">
-        <v>134.54</v>
+        <v>130.39</v>
       </c>
       <c r="AL12" t="n">
-        <v>-1.74</v>
+        <v>-4.15</v>
       </c>
       <c r="AM12" t="n">
         <v>110</v>
@@ -1704,99 +1743,99 @@
         <v>142</v>
       </c>
       <c r="AP12" t="n">
-        <v>82.27</v>
+        <v>78.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>16.28</v>
+        <v>15.79</v>
       </c>
       <c r="BL12" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B13" t="n">
-        <v>172.9</v>
+        <v>157.5</v>
       </c>
       <c r="C13" t="n">
-        <v>67.59999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="D13" t="n">
-        <v>34.9</v>
+        <v>33.2</v>
       </c>
       <c r="E13" t="n">
-        <v>35.2</v>
+        <v>27.7</v>
       </c>
       <c r="F13" t="n">
-        <v>7.3</v>
+        <v>3.6</v>
       </c>
       <c r="H13" t="n">
-        <v>23.6</v>
+        <v>23.4</v>
       </c>
       <c r="I13" t="n">
         <v>11.3</v>
       </c>
       <c r="J13" t="n">
-        <v>41.7</v>
+        <v>41.4</v>
       </c>
       <c r="K13" t="n">
-        <v>76.7</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="N13" t="n">
-        <v>34.8</v>
+        <v>34.9</v>
       </c>
       <c r="O13" t="n">
-        <v>37.2</v>
+        <v>37.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>19</v>
+        <v>21.6</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T13" t="n">
-        <v>19</v>
+        <v>21.6</v>
       </c>
       <c r="V13" t="n">
-        <v>14.4</v>
+        <v>15.1</v>
       </c>
       <c r="W13" t="n">
-        <v>18.7</v>
+        <v>23.1</v>
       </c>
       <c r="X13" t="n">
-        <v>16.6</v>
+        <v>19.1</v>
       </c>
       <c r="Y13" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z13" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AA13" t="n">
-        <v>12.5</v>
+        <v>13.6</v>
       </c>
       <c r="AB13" t="n">
-        <v>-4.9</v>
+        <v>-0</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0.7</v>
+        <v>1.5</v>
       </c>
       <c r="AF13" t="n">
-        <v>218.6</v>
+        <v>218.84</v>
       </c>
       <c r="AG13" t="n">
-        <v>-9.380000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="AH13" t="n">
         <v>215</v>
@@ -1805,10 +1844,10 @@
         <v>235</v>
       </c>
       <c r="AK13" t="n">
-        <v>130.39</v>
+        <v>133.09</v>
       </c>
       <c r="AL13" t="n">
-        <v>-4.15</v>
+        <v>2.7</v>
       </c>
       <c r="AM13" t="n">
         <v>110</v>
@@ -1817,99 +1856,66 @@
         <v>142</v>
       </c>
       <c r="AP13" t="n">
-        <v>78.5</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="AS13" t="n">
-        <v>15.79</v>
+        <v>15.63</v>
       </c>
       <c r="BL13" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B14" t="n">
-        <v>157.5</v>
-      </c>
-      <c r="C14" t="n">
-        <v>68.5</v>
+        <v>137.6</v>
       </c>
       <c r="D14" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="E14" t="n">
-        <v>27.7</v>
+        <v>35</v>
       </c>
       <c r="F14" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H14" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="I14" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J14" t="n">
-        <v>41.4</v>
+        <v>6.5</v>
       </c>
       <c r="K14" t="n">
-        <v>76.09999999999999</v>
-      </c>
-      <c r="M14" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="N14" t="n">
-        <v>34.9</v>
+        <v>96.7</v>
       </c>
       <c r="O14" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>9</v>
-      </c>
-      <c r="T14" t="n">
-        <v>21.6</v>
+        <v>35.1</v>
       </c>
       <c r="V14" t="n">
-        <v>15.1</v>
+        <v>13.6</v>
       </c>
       <c r="W14" t="n">
-        <v>23.1</v>
+        <v>24.4</v>
       </c>
       <c r="X14" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="Y14" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Z14" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AA14" t="n">
-        <v>13.6</v>
+        <v>17.5</v>
       </c>
       <c r="AB14" t="n">
         <v>-0</v>
       </c>
       <c r="AC14" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="AF14" t="n">
-        <v>218.84</v>
+        <v>221.78</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.25</v>
+        <v>2.94</v>
       </c>
       <c r="AH14" t="n">
         <v>215</v>
@@ -1918,10 +1924,10 @@
         <v>235</v>
       </c>
       <c r="AK14" t="n">
-        <v>133.09</v>
+        <v>138.76</v>
       </c>
       <c r="AL14" t="n">
-        <v>2.7</v>
+        <v>5.67</v>
       </c>
       <c r="AM14" t="n">
         <v>110</v>
@@ -1929,67 +1935,61 @@
       <c r="AN14" t="n">
         <v>142</v>
       </c>
-      <c r="AP14" t="n">
-        <v>83.09999999999999</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>15.63</v>
-      </c>
       <c r="BL14" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B15" t="n">
-        <v>137.6</v>
+        <v>132.5</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>33.6</v>
       </c>
       <c r="F15" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="K15" t="n">
-        <v>96.7</v>
+        <v>97.8</v>
       </c>
       <c r="O15" t="n">
-        <v>35.1</v>
+        <v>31.6</v>
       </c>
       <c r="V15" t="n">
-        <v>13.6</v>
+        <v>14.8</v>
       </c>
       <c r="W15" t="n">
-        <v>24.4</v>
+        <v>24.7</v>
       </c>
       <c r="X15" t="n">
-        <v>19</v>
+        <v>19.8</v>
       </c>
       <c r="Y15" t="n">
         <v>14</v>
       </c>
       <c r="Z15" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AA15" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0</v>
+        <v>0.6</v>
       </c>
       <c r="AC15" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="AF15" t="n">
-        <v>221.78</v>
+        <v>224.78</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="AH15" t="n">
         <v>215</v>
@@ -1998,10 +1998,10 @@
         <v>235</v>
       </c>
       <c r="AK15" t="n">
-        <v>138.76</v>
+        <v>143.55</v>
       </c>
       <c r="AL15" t="n">
-        <v>5.67</v>
+        <v>4.79</v>
       </c>
       <c r="AM15" t="n">
         <v>110</v>
@@ -2010,60 +2010,93 @@
         <v>142</v>
       </c>
       <c r="BL15" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B16" t="n">
-        <v>132.5</v>
+        <v>137.2</v>
+      </c>
+      <c r="C16" t="n">
+        <v>56.3</v>
       </c>
       <c r="D16" t="n">
-        <v>33.6</v>
+        <v>32.1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>21.2</v>
       </c>
       <c r="F16" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
+      </c>
+      <c r="H16" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="I16" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="J16" t="n">
+        <v>40.4</v>
       </c>
       <c r="K16" t="n">
-        <v>97.8</v>
+        <v>75.7</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N16" t="n">
+        <v>29</v>
       </c>
       <c r="O16" t="n">
-        <v>31.6</v>
+        <v>32.6</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>21.6</v>
       </c>
       <c r="V16" t="n">
-        <v>14.8</v>
+        <v>10.7</v>
       </c>
       <c r="W16" t="n">
-        <v>24.7</v>
+        <v>24.3</v>
       </c>
       <c r="X16" t="n">
-        <v>19.8</v>
+        <v>17.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Z16" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AA16" t="n">
-        <v>16.5</v>
+        <v>15.4</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="AF16" t="n">
-        <v>224.78</v>
+        <v>232.22</v>
       </c>
       <c r="AG16" t="n">
-        <v>3</v>
+        <v>7.43</v>
       </c>
       <c r="AH16" t="n">
         <v>215</v>
@@ -2072,10 +2105,10 @@
         <v>235</v>
       </c>
       <c r="AK16" t="n">
-        <v>143.55</v>
+        <v>143.61</v>
       </c>
       <c r="AL16" t="n">
-        <v>4.79</v>
+        <v>0.06</v>
       </c>
       <c r="AM16" t="n">
         <v>110</v>
@@ -2083,52 +2116,58 @@
       <c r="AN16" t="n">
         <v>142</v>
       </c>
+      <c r="AP16" t="n">
+        <v>89.31999999999999</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>18.02</v>
+      </c>
       <c r="BL16" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="B17" t="n">
-        <v>137.2</v>
+        <v>157.5</v>
       </c>
       <c r="C17" t="n">
-        <v>56.3</v>
+        <v>59.6</v>
       </c>
       <c r="D17" t="n">
-        <v>32.1</v>
+        <v>35</v>
       </c>
       <c r="E17" t="n">
-        <v>21.2</v>
+        <v>30.6</v>
       </c>
       <c r="F17" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="H17" t="n">
-        <v>23.7</v>
+        <v>24.2</v>
       </c>
       <c r="I17" t="n">
-        <v>11.6</v>
+        <v>11.2</v>
       </c>
       <c r="J17" t="n">
-        <v>40.4</v>
+        <v>38.9</v>
       </c>
       <c r="K17" t="n">
-        <v>75.7</v>
+        <v>74.3</v>
       </c>
       <c r="M17" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="N17" t="n">
-        <v>29</v>
+        <v>33.4</v>
       </c>
       <c r="O17" t="n">
-        <v>32.6</v>
+        <v>37.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="R17" t="n">
         <v>1.3</v>
@@ -2137,40 +2176,40 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="V17" t="n">
-        <v>10.7</v>
+        <v>13</v>
       </c>
       <c r="W17" t="n">
-        <v>24.3</v>
+        <v>26.3</v>
       </c>
       <c r="X17" t="n">
-        <v>17.5</v>
+        <v>19.6</v>
       </c>
       <c r="Y17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA17" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.9</v>
+        <v>-2.1</v>
       </c>
       <c r="AC17" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="AF17" t="n">
-        <v>232.22</v>
+        <v>229.69</v>
       </c>
       <c r="AG17" t="n">
-        <v>7.43</v>
+        <v>-2.53</v>
       </c>
       <c r="AH17" t="n">
         <v>215</v>
@@ -2179,10 +2218,10 @@
         <v>235</v>
       </c>
       <c r="AK17" t="n">
-        <v>143.61</v>
+        <v>136.96</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.06</v>
+        <v>-6.65</v>
       </c>
       <c r="AM17" t="n">
         <v>110</v>
@@ -2191,99 +2230,99 @@
         <v>142</v>
       </c>
       <c r="AP17" t="n">
-        <v>89.31999999999999</v>
+        <v>86.59</v>
       </c>
       <c r="AS17" t="n">
-        <v>18.02</v>
+        <v>16.96</v>
       </c>
       <c r="BL17" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B18" t="n">
-        <v>157.5</v>
+        <v>159.6</v>
       </c>
       <c r="C18" t="n">
-        <v>59.6</v>
+        <v>63</v>
       </c>
       <c r="D18" t="n">
-        <v>35</v>
+        <v>34.5</v>
       </c>
       <c r="E18" t="n">
-        <v>30.6</v>
+        <v>31.1</v>
       </c>
       <c r="F18" t="n">
-        <v>7.5</v>
+        <v>5.7</v>
       </c>
       <c r="H18" t="n">
-        <v>24.2</v>
+        <v>23.8</v>
       </c>
       <c r="I18" t="n">
-        <v>11.2</v>
+        <v>10.8</v>
       </c>
       <c r="J18" t="n">
-        <v>38.9</v>
+        <v>40.5</v>
       </c>
       <c r="K18" t="n">
-        <v>74.3</v>
+        <v>75.2</v>
       </c>
       <c r="M18" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="N18" t="n">
-        <v>33.4</v>
+        <v>34.3</v>
       </c>
       <c r="O18" t="n">
-        <v>37.1</v>
+        <v>38.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T18" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="V18" t="n">
-        <v>13</v>
+        <v>17.5</v>
       </c>
       <c r="W18" t="n">
-        <v>26.3</v>
+        <v>22.5</v>
       </c>
       <c r="X18" t="n">
-        <v>19.6</v>
+        <v>20</v>
       </c>
       <c r="Y18" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA18" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>-2.1</v>
+        <v>-2.2</v>
       </c>
       <c r="AC18" t="n">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="AF18" t="n">
-        <v>229.69</v>
+        <v>228.57</v>
       </c>
       <c r="AG18" t="n">
-        <v>-2.53</v>
+        <v>-1.14</v>
       </c>
       <c r="AH18" t="n">
         <v>215</v>
@@ -2292,10 +2331,10 @@
         <v>235</v>
       </c>
       <c r="AK18" t="n">
-        <v>136.96</v>
+        <v>133.01</v>
       </c>
       <c r="AL18" t="n">
-        <v>-6.65</v>
+        <v>-3.95</v>
       </c>
       <c r="AM18" t="n">
         <v>110</v>
@@ -2304,99 +2343,99 @@
         <v>142</v>
       </c>
       <c r="AP18" t="n">
-        <v>86.59</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="AS18" t="n">
-        <v>16.96</v>
+        <v>15.95</v>
       </c>
       <c r="BL18" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B19" t="n">
-        <v>159.6</v>
+        <v>160.4</v>
       </c>
       <c r="C19" t="n">
-        <v>63</v>
+        <v>62.6</v>
       </c>
       <c r="D19" t="n">
-        <v>34.5</v>
+        <v>35</v>
       </c>
       <c r="E19" t="n">
-        <v>31.1</v>
+        <v>32.2</v>
       </c>
       <c r="F19" t="n">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="H19" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="I19" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="J19" t="n">
-        <v>40.5</v>
+        <v>41.1</v>
       </c>
       <c r="K19" t="n">
-        <v>75.2</v>
+        <v>75.7</v>
       </c>
       <c r="M19" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="N19" t="n">
-        <v>34.3</v>
+        <v>32.6</v>
       </c>
       <c r="O19" t="n">
-        <v>38.2</v>
+        <v>38</v>
       </c>
       <c r="Q19" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T19" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="V19" t="n">
-        <v>17.5</v>
+        <v>16.4</v>
       </c>
       <c r="W19" t="n">
-        <v>22.5</v>
+        <v>22.8</v>
       </c>
       <c r="X19" t="n">
-        <v>20</v>
+        <v>19.6</v>
       </c>
       <c r="Y19" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Z19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA19" t="n">
-        <v>13.5</v>
+        <v>14.1</v>
       </c>
       <c r="AB19" t="n">
-        <v>-2.2</v>
+        <v>-3.1</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="AF19" t="n">
-        <v>228.57</v>
+        <v>225.08</v>
       </c>
       <c r="AG19" t="n">
-        <v>-1.14</v>
+        <v>-3.5</v>
       </c>
       <c r="AH19" t="n">
         <v>215</v>
@@ -2405,10 +2444,10 @@
         <v>235</v>
       </c>
       <c r="AK19" t="n">
-        <v>133.01</v>
+        <v>135.24</v>
       </c>
       <c r="AL19" t="n">
-        <v>-3.95</v>
+        <v>2.23</v>
       </c>
       <c r="AM19" t="n">
         <v>110</v>
@@ -2417,99 +2456,99 @@
         <v>142</v>
       </c>
       <c r="AP19" t="n">
-        <v>84.59999999999999</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="AS19" t="n">
-        <v>15.95</v>
+        <v>15.4</v>
       </c>
       <c r="BL19" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B20" t="n">
-        <v>160.4</v>
+        <v>161.7</v>
       </c>
       <c r="C20" t="n">
-        <v>62.6</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>35</v>
+        <v>34.9</v>
       </c>
       <c r="E20" t="n">
-        <v>32.2</v>
+        <v>27.3</v>
       </c>
       <c r="F20" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H20" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="I20" t="n">
-        <v>10.7</v>
+        <v>10.3</v>
       </c>
       <c r="J20" t="n">
-        <v>41.1</v>
+        <v>42.6</v>
       </c>
       <c r="K20" t="n">
-        <v>75.7</v>
+        <v>77</v>
       </c>
       <c r="M20" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="N20" t="n">
-        <v>32.6</v>
+        <v>31.5</v>
       </c>
       <c r="O20" t="n">
-        <v>38</v>
+        <v>37.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="R20" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T20" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="V20" t="n">
-        <v>16.4</v>
+        <v>12.7</v>
       </c>
       <c r="W20" t="n">
-        <v>22.8</v>
+        <v>27</v>
       </c>
       <c r="X20" t="n">
-        <v>19.6</v>
+        <v>19.9</v>
       </c>
       <c r="Y20" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Z20" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AA20" t="n">
-        <v>14.1</v>
+        <v>11.4</v>
       </c>
       <c r="AB20" t="n">
-        <v>-3.1</v>
+        <v>-5.2</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.6</v>
+        <v>-0.3</v>
       </c>
       <c r="AF20" t="n">
-        <v>225.08</v>
+        <v>225</v>
       </c>
       <c r="AG20" t="n">
-        <v>-3.5</v>
+        <v>-0.08</v>
       </c>
       <c r="AH20" t="n">
         <v>215</v>
@@ -2518,10 +2557,10 @@
         <v>235</v>
       </c>
       <c r="AK20" t="n">
-        <v>135.24</v>
+        <v>134.62</v>
       </c>
       <c r="AL20" t="n">
-        <v>2.23</v>
+        <v>-0.62</v>
       </c>
       <c r="AM20" t="n">
         <v>110</v>
@@ -2530,99 +2569,60 @@
         <v>142</v>
       </c>
       <c r="AP20" t="n">
-        <v>84.09999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="AS20" t="n">
-        <v>15.4</v>
+        <v>13.86</v>
       </c>
       <c r="BL20" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B21" t="n">
-        <v>161.7</v>
-      </c>
-      <c r="C21" t="n">
-        <v>71.09999999999999</v>
+        <v>151.5</v>
       </c>
       <c r="D21" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="E21" t="n">
-        <v>27.3</v>
+        <v>35.1</v>
       </c>
       <c r="F21" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H21" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I21" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="J21" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="K21" t="n">
-        <v>77</v>
-      </c>
-      <c r="M21" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="N21" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="O21" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>21</v>
-      </c>
-      <c r="R21" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="S21" t="n">
-        <v>6</v>
-      </c>
-      <c r="T21" t="n">
-        <v>21</v>
+        <v>5.4</v>
       </c>
       <c r="V21" t="n">
-        <v>12.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W21" t="n">
-        <v>27</v>
+        <v>19.4</v>
       </c>
       <c r="X21" t="n">
-        <v>19.9</v>
+        <v>14</v>
       </c>
       <c r="Y21" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA21" t="n">
         <v>9</v>
       </c>
-      <c r="Z21" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>11.4</v>
-      </c>
       <c r="AB21" t="n">
-        <v>-5.2</v>
+        <v>-4.7</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.6</v>
+        <v>1.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>-0.3</v>
+        <v>-1.4</v>
       </c>
       <c r="AF21" t="n">
-        <v>225</v>
+        <v>221.37</v>
       </c>
       <c r="AG21" t="n">
-        <v>-0.08</v>
+        <v>0.05</v>
       </c>
       <c r="AH21" t="n">
         <v>215</v>
@@ -2631,10 +2631,10 @@
         <v>235</v>
       </c>
       <c r="AK21" t="n">
-        <v>134.62</v>
+        <v>135.21</v>
       </c>
       <c r="AL21" t="n">
-        <v>-0.62</v>
+        <v>0.59</v>
       </c>
       <c r="AM21" t="n">
         <v>110</v>
@@ -2642,61 +2642,61 @@
       <c r="AN21" t="n">
         <v>142</v>
       </c>
-      <c r="AP21" t="n">
-        <v>80.2</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>13.86</v>
-      </c>
       <c r="BL21" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B22" t="n">
-        <v>151.5</v>
+        <v>145.2</v>
       </c>
       <c r="D22" t="n">
-        <v>35.1</v>
+        <v>33.5</v>
       </c>
       <c r="F22" t="n">
-        <v>5.4</v>
+        <v>5</v>
+      </c>
+      <c r="K22" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="O22" t="n">
+        <v>35.5</v>
       </c>
       <c r="V22" t="n">
-        <v>8.699999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="W22" t="n">
-        <v>19.4</v>
+        <v>19.2</v>
       </c>
       <c r="X22" t="n">
-        <v>14</v>
+        <v>13.1</v>
       </c>
       <c r="Y22" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z22" t="n">
         <v>13</v>
       </c>
       <c r="AA22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB22" t="n">
-        <v>-4.7</v>
+        <v>-5.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>-1.4</v>
+        <v>-1.5</v>
       </c>
       <c r="AF22" t="n">
-        <v>221.37</v>
+        <v>224.37</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.05</v>
+        <v>3</v>
       </c>
       <c r="AH22" t="n">
         <v>215</v>
@@ -2705,10 +2705,10 @@
         <v>235</v>
       </c>
       <c r="AK22" t="n">
-        <v>135.21</v>
+        <v>135.61</v>
       </c>
       <c r="AL22" t="n">
-        <v>0.59</v>
+        <v>0.4</v>
       </c>
       <c r="AM22" t="n">
         <v>110</v>
@@ -2717,60 +2717,60 @@
         <v>142</v>
       </c>
       <c r="BL22" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B23" t="n">
-        <v>145.2</v>
+        <v>146.3</v>
       </c>
       <c r="D23" t="n">
-        <v>33.5</v>
+        <v>33.4</v>
       </c>
       <c r="F23" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="K23" t="n">
-        <v>100.3</v>
+        <v>98.2</v>
       </c>
       <c r="O23" t="n">
-        <v>35.5</v>
+        <v>35.1</v>
       </c>
       <c r="V23" t="n">
-        <v>7.1</v>
+        <v>4.9</v>
       </c>
       <c r="W23" t="n">
-        <v>19.2</v>
+        <v>16.4</v>
       </c>
       <c r="X23" t="n">
-        <v>13.1</v>
+        <v>10.6</v>
       </c>
       <c r="Y23" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z23" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB23" t="n">
-        <v>-5.4</v>
+        <v>-6.4</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.4</v>
+        <v>-0.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>-1.5</v>
+        <v>-3.3</v>
       </c>
       <c r="AF23" t="n">
-        <v>224.37</v>
+        <v>225.93</v>
       </c>
       <c r="AG23" t="n">
-        <v>3</v>
+        <v>1.56</v>
       </c>
       <c r="AH23" t="n">
         <v>215</v>
@@ -2779,10 +2779,10 @@
         <v>235</v>
       </c>
       <c r="AK23" t="n">
-        <v>135.61</v>
+        <v>135.28</v>
       </c>
       <c r="AL23" t="n">
-        <v>0.4</v>
+        <v>-0.33</v>
       </c>
       <c r="AM23" t="n">
         <v>110</v>
@@ -2791,60 +2791,93 @@
         <v>142</v>
       </c>
       <c r="BL23" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B24" t="n">
-        <v>146.3</v>
+        <v>182.8</v>
+      </c>
+      <c r="C24" t="n">
+        <v>86.8</v>
       </c>
       <c r="D24" t="n">
-        <v>33.4</v>
+        <v>31.8</v>
+      </c>
+      <c r="E24" t="n">
+        <v>33</v>
       </c>
       <c r="F24" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
+      </c>
+      <c r="H24" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="I24" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J24" t="n">
+        <v>41.1</v>
       </c>
       <c r="K24" t="n">
-        <v>98.2</v>
+        <v>74.2</v>
+      </c>
+      <c r="M24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="N24" t="n">
+        <v>33.5</v>
       </c>
       <c r="O24" t="n">
-        <v>35.1</v>
+        <v>38.4</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="R24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="n">
+        <v>22.4</v>
       </c>
       <c r="V24" t="n">
-        <v>4.9</v>
+        <v>9.1</v>
       </c>
       <c r="W24" t="n">
-        <v>16.4</v>
+        <v>15</v>
       </c>
       <c r="X24" t="n">
-        <v>10.6</v>
+        <v>12.1</v>
       </c>
       <c r="Y24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z24" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AA24" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="AB24" t="n">
-        <v>-6.4</v>
+        <v>-10.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>-0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>-3.3</v>
+        <v>-5.1</v>
       </c>
       <c r="AF24" t="n">
-        <v>225.93</v>
+        <v>218.63</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.56</v>
+        <v>-7.3</v>
       </c>
       <c r="AH24" t="n">
         <v>215</v>
@@ -2853,10 +2886,10 @@
         <v>235</v>
       </c>
       <c r="AK24" t="n">
-        <v>135.28</v>
+        <v>126.27</v>
       </c>
       <c r="AL24" t="n">
-        <v>-0.33</v>
+        <v>-9.01</v>
       </c>
       <c r="AM24" t="n">
         <v>110</v>
@@ -2864,94 +2897,100 @@
       <c r="AN24" t="n">
         <v>142</v>
       </c>
+      <c r="AP24" t="n">
+        <v>82.66</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>14.7</v>
+      </c>
       <c r="BL24" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B25" t="n">
-        <v>182.8</v>
+        <v>181.8</v>
       </c>
       <c r="C25" t="n">
-        <v>86.8</v>
+        <v>86.5</v>
       </c>
       <c r="D25" t="n">
-        <v>31.8</v>
+        <v>31.4</v>
       </c>
       <c r="E25" t="n">
-        <v>33</v>
+        <v>34.2</v>
       </c>
       <c r="F25" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="H25" t="n">
-        <v>23.5</v>
+        <v>24.4</v>
       </c>
       <c r="I25" t="n">
-        <v>9.6</v>
+        <v>10.4</v>
       </c>
       <c r="J25" t="n">
-        <v>41.1</v>
+        <v>41.9</v>
       </c>
       <c r="K25" t="n">
-        <v>74.2</v>
+        <v>76.8</v>
       </c>
       <c r="M25" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="N25" t="n">
-        <v>33.5</v>
+        <v>35.7</v>
       </c>
       <c r="O25" t="n">
-        <v>38.4</v>
+        <v>39.8</v>
       </c>
       <c r="Q25" t="n">
-        <v>22.4</v>
+        <v>23</v>
       </c>
       <c r="R25" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>20.1</v>
       </c>
       <c r="T25" t="n">
-        <v>22.4</v>
+        <v>23</v>
       </c>
       <c r="V25" t="n">
-        <v>9.1</v>
+        <v>7.1</v>
       </c>
       <c r="W25" t="n">
-        <v>15</v>
+        <v>14.8</v>
       </c>
       <c r="X25" t="n">
-        <v>12.1</v>
+        <v>10.9</v>
       </c>
       <c r="Y25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z25" t="n">
         <v>12</v>
       </c>
       <c r="AA25" t="n">
-        <v>8.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AB25" t="n">
-        <v>-10.5</v>
+        <v>-4.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="AD25" t="n">
-        <v>-5.1</v>
+        <v>-1.4</v>
       </c>
       <c r="AF25" t="n">
-        <v>218.63</v>
+        <v>216.39</v>
       </c>
       <c r="AG25" t="n">
-        <v>-7.3</v>
+        <v>-2.23</v>
       </c>
       <c r="AH25" t="n">
         <v>215</v>
@@ -2960,10 +2999,10 @@
         <v>235</v>
       </c>
       <c r="AK25" t="n">
-        <v>126.27</v>
+        <v>123.32</v>
       </c>
       <c r="AL25" t="n">
-        <v>-9.01</v>
+        <v>-2.95</v>
       </c>
       <c r="AM25" t="n">
         <v>110</v>
@@ -2972,99 +3011,99 @@
         <v>142</v>
       </c>
       <c r="AP25" t="n">
-        <v>82.66</v>
+        <v>79.08</v>
       </c>
       <c r="AS25" t="n">
-        <v>14.7</v>
+        <v>13.91</v>
       </c>
       <c r="BL25" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B26" t="n">
-        <v>181.8</v>
+        <v>183</v>
       </c>
       <c r="C26" t="n">
-        <v>86.5</v>
+        <v>84.7</v>
       </c>
       <c r="D26" t="n">
-        <v>31.4</v>
+        <v>30.9</v>
       </c>
       <c r="E26" t="n">
-        <v>34.2</v>
+        <v>33.7</v>
       </c>
       <c r="F26" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="H26" t="n">
-        <v>24.4</v>
+        <v>23.4</v>
       </c>
       <c r="I26" t="n">
-        <v>10.4</v>
+        <v>10.6</v>
       </c>
       <c r="J26" t="n">
-        <v>41.9</v>
+        <v>42.3</v>
       </c>
       <c r="K26" t="n">
-        <v>76.8</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="M26" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="N26" t="n">
-        <v>35.7</v>
+        <v>36.7</v>
       </c>
       <c r="O26" t="n">
-        <v>39.8</v>
+        <v>40.8</v>
       </c>
       <c r="Q26" t="n">
-        <v>23</v>
+        <v>23.6</v>
       </c>
       <c r="R26" t="n">
         <v>1.8</v>
       </c>
       <c r="S26" t="n">
-        <v>20.1</v>
+        <v>20.8</v>
       </c>
       <c r="T26" t="n">
-        <v>23</v>
+        <v>23.6</v>
       </c>
       <c r="V26" t="n">
-        <v>7.1</v>
+        <v>5.7</v>
       </c>
       <c r="W26" t="n">
-        <v>14.8</v>
+        <v>16.1</v>
       </c>
       <c r="X26" t="n">
         <v>10.9</v>
       </c>
       <c r="Y26" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA26" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AB26" t="n">
-        <v>-4.5</v>
+        <v>0.8</v>
       </c>
       <c r="AC26" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD26" t="n">
         <v>1.8</v>
       </c>
-      <c r="AD26" t="n">
-        <v>-1.4</v>
-      </c>
       <c r="AF26" t="n">
-        <v>216.39</v>
+        <v>217.16</v>
       </c>
       <c r="AG26" t="n">
-        <v>-2.23</v>
+        <v>0.76</v>
       </c>
       <c r="AH26" t="n">
         <v>215</v>
@@ -3073,10 +3112,10 @@
         <v>235</v>
       </c>
       <c r="AK26" t="n">
-        <v>123.32</v>
+        <v>117.87</v>
       </c>
       <c r="AL26" t="n">
-        <v>-2.95</v>
+        <v>-5.45</v>
       </c>
       <c r="AM26" t="n">
         <v>110</v>
@@ -3085,99 +3124,66 @@
         <v>142</v>
       </c>
       <c r="AP26" t="n">
-        <v>79.08</v>
+        <v>78.56</v>
       </c>
       <c r="AS26" t="n">
-        <v>13.91</v>
+        <v>13.45</v>
       </c>
       <c r="BL26" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B27" t="n">
-        <v>183</v>
-      </c>
-      <c r="C27" t="n">
-        <v>84.7</v>
+        <v>163.8</v>
       </c>
       <c r="D27" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="E27" t="n">
-        <v>33.7</v>
+        <v>29</v>
       </c>
       <c r="F27" t="n">
-        <v>7</v>
-      </c>
-      <c r="H27" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="I27" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="J27" t="n">
-        <v>42.3</v>
+        <v>6.5</v>
       </c>
       <c r="K27" t="n">
-        <v>76.40000000000001</v>
-      </c>
-      <c r="M27" t="n">
-        <v>4</v>
-      </c>
-      <c r="N27" t="n">
-        <v>36.7</v>
+        <v>101.2</v>
       </c>
       <c r="O27" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S27" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="T27" t="n">
-        <v>23.6</v>
+        <v>40.2</v>
       </c>
       <c r="V27" t="n">
-        <v>5.7</v>
+        <v>6.3</v>
       </c>
       <c r="W27" t="n">
-        <v>16.1</v>
+        <v>17.2</v>
       </c>
       <c r="X27" t="n">
-        <v>10.9</v>
+        <v>11.8</v>
       </c>
       <c r="Y27" t="n">
         <v>8</v>
       </c>
       <c r="Z27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA27" t="n">
         <v>10</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.7</v>
+        <v>4.3</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="AF27" t="n">
-        <v>217.16</v>
+        <v>220.31</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.76</v>
+        <v>3.16</v>
       </c>
       <c r="AH27" t="n">
         <v>215</v>
@@ -3186,10 +3192,10 @@
         <v>235</v>
       </c>
       <c r="AK27" t="n">
-        <v>117.87</v>
+        <v>116.52</v>
       </c>
       <c r="AL27" t="n">
-        <v>-5.45</v>
+        <v>-1.35</v>
       </c>
       <c r="AM27" t="n">
         <v>110</v>
@@ -3197,67 +3203,61 @@
       <c r="AN27" t="n">
         <v>142</v>
       </c>
-      <c r="AP27" t="n">
-        <v>78.56</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>13.45</v>
-      </c>
       <c r="BL27" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B28" t="n">
-        <v>163.8</v>
+        <v>155.9</v>
       </c>
       <c r="D28" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F28" t="n">
         <v>6.5</v>
       </c>
       <c r="K28" t="n">
-        <v>101.2</v>
+        <v>99.3</v>
       </c>
       <c r="O28" t="n">
-        <v>40.2</v>
+        <v>38.5</v>
       </c>
       <c r="V28" t="n">
-        <v>6.3</v>
+        <v>8.9</v>
       </c>
       <c r="W28" t="n">
-        <v>17.2</v>
+        <v>15.8</v>
       </c>
       <c r="X28" t="n">
-        <v>11.8</v>
+        <v>12.4</v>
       </c>
       <c r="Y28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA28" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AC28" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="AF28" t="n">
-        <v>220.31</v>
+        <v>221.99</v>
       </c>
       <c r="AG28" t="n">
-        <v>3.16</v>
+        <v>1.67</v>
       </c>
       <c r="AH28" t="n">
         <v>215</v>
@@ -3266,10 +3266,10 @@
         <v>235</v>
       </c>
       <c r="AK28" t="n">
-        <v>116.52</v>
+        <v>116.37</v>
       </c>
       <c r="AL28" t="n">
-        <v>-1.35</v>
+        <v>-0.15</v>
       </c>
       <c r="AM28" t="n">
         <v>110</v>
@@ -3278,60 +3278,60 @@
         <v>142</v>
       </c>
       <c r="BL28" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B29" t="n">
-        <v>155.9</v>
+        <v>141.3</v>
       </c>
       <c r="D29" t="n">
-        <v>28</v>
+        <v>26.3</v>
       </c>
       <c r="F29" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="K29" t="n">
-        <v>99.3</v>
+        <v>97.8</v>
       </c>
       <c r="O29" t="n">
-        <v>38.5</v>
+        <v>39.8</v>
       </c>
       <c r="V29" t="n">
-        <v>8.9</v>
+        <v>9.5</v>
       </c>
       <c r="W29" t="n">
-        <v>15.8</v>
+        <v>17.7</v>
       </c>
       <c r="X29" t="n">
-        <v>12.4</v>
+        <v>13.6</v>
       </c>
       <c r="Y29" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Z29" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA29" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="AC29" t="n">
-        <v>5.7</v>
+        <v>7.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="AF29" t="n">
-        <v>221.99</v>
+        <v>225.14</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.67</v>
+        <v>3.15</v>
       </c>
       <c r="AH29" t="n">
         <v>215</v>
@@ -3339,12 +3339,6 @@
       <c r="AI29" t="n">
         <v>235</v>
       </c>
-      <c r="AK29" t="n">
-        <v>116.37</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>-0.15</v>
-      </c>
       <c r="AM29" t="n">
         <v>110</v>
       </c>
@@ -3352,60 +3346,54 @@
         <v>142</v>
       </c>
       <c r="BL29" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B30" t="n">
-        <v>141.3</v>
+        <v>131.5</v>
       </c>
       <c r="D30" t="n">
-        <v>26.3</v>
+        <v>27.3</v>
       </c>
       <c r="F30" t="n">
         <v>5.5</v>
       </c>
       <c r="K30" t="n">
-        <v>97.8</v>
+        <v>97</v>
       </c>
       <c r="O30" t="n">
-        <v>39.8</v>
+        <v>35.7</v>
       </c>
       <c r="V30" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="W30" t="n">
-        <v>17.7</v>
+        <v>13.9</v>
       </c>
       <c r="X30" t="n">
-        <v>13.6</v>
+        <v>11.4</v>
       </c>
       <c r="Y30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z30" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA30" t="n">
         <v>15</v>
       </c>
-      <c r="AA30" t="n">
-        <v>14</v>
-      </c>
       <c r="AB30" t="n">
-        <v>0.2</v>
+        <v>-3.6</v>
       </c>
       <c r="AC30" t="n">
-        <v>7.5</v>
+        <v>2.8</v>
       </c>
       <c r="AD30" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>225.14</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>3.15</v>
+        <v>-0.4</v>
       </c>
       <c r="AH30" t="n">
         <v>215</v>
@@ -3420,54 +3408,93 @@
         <v>142</v>
       </c>
       <c r="BL30" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="B31" t="n">
-        <v>131.5</v>
+        <v>153</v>
+      </c>
+      <c r="C31" t="n">
+        <v>71.8</v>
       </c>
       <c r="D31" t="n">
-        <v>27.3</v>
+        <v>28.6</v>
+      </c>
+      <c r="E31" t="n">
+        <v>24.7</v>
       </c>
       <c r="F31" t="n">
-        <v>5.5</v>
+        <v>4</v>
+      </c>
+      <c r="H31" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I31" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J31" t="n">
+        <v>41.1</v>
       </c>
       <c r="K31" t="n">
-        <v>97</v>
+        <v>75.90000000000001</v>
+      </c>
+      <c r="M31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N31" t="n">
+        <v>33.5</v>
       </c>
       <c r="O31" t="n">
-        <v>35.7</v>
+        <v>38.3</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="R31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>23.2</v>
       </c>
       <c r="V31" t="n">
-        <v>9</v>
+        <v>11.2</v>
       </c>
       <c r="W31" t="n">
-        <v>13.9</v>
+        <v>13</v>
       </c>
       <c r="X31" t="n">
-        <v>11.4</v>
+        <v>12.1</v>
       </c>
       <c r="Y31" t="n">
         <v>12</v>
       </c>
       <c r="Z31" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AA31" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AB31" t="n">
-        <v>-3.6</v>
+        <v>-6.6</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.8</v>
+        <v>5.3</v>
       </c>
       <c r="AD31" t="n">
-        <v>-0.4</v>
+        <v>-0.6</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>229.96</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>-0.02</v>
       </c>
       <c r="AH31" t="n">
         <v>215</v>
@@ -3475,100 +3502,112 @@
       <c r="AI31" t="n">
         <v>235</v>
       </c>
+      <c r="AK31" t="n">
+        <v>128.14</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>11.77</v>
+      </c>
       <c r="AM31" t="n">
         <v>110</v>
       </c>
       <c r="AN31" t="n">
         <v>142</v>
       </c>
+      <c r="AP31" t="n">
+        <v>87.47</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>14.8</v>
+      </c>
       <c r="BL31" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B32" t="n">
-        <v>153</v>
+        <v>165.8</v>
       </c>
       <c r="C32" t="n">
-        <v>71.8</v>
+        <v>77.3</v>
       </c>
       <c r="D32" t="n">
-        <v>28.6</v>
+        <v>29.3</v>
       </c>
       <c r="E32" t="n">
-        <v>24.7</v>
+        <v>27.7</v>
       </c>
       <c r="F32" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="H32" t="n">
         <v>24.1</v>
       </c>
       <c r="I32" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="J32" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="K32" t="n">
-        <v>75.90000000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="M32" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="N32" t="n">
-        <v>33.5</v>
+        <v>35.1</v>
       </c>
       <c r="O32" t="n">
-        <v>38.3</v>
+        <v>39.8</v>
       </c>
       <c r="Q32" t="n">
-        <v>23.2</v>
+        <v>23.8</v>
       </c>
       <c r="R32" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="T32" t="n">
-        <v>23.2</v>
+        <v>23.8</v>
       </c>
       <c r="V32" t="n">
-        <v>11.2</v>
+        <v>9.4</v>
       </c>
       <c r="W32" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="X32" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z32" t="n">
         <v>13</v>
       </c>
-      <c r="X32" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>14</v>
-      </c>
       <c r="AA32" t="n">
-        <v>12.5</v>
+        <v>10.1</v>
       </c>
       <c r="AB32" t="n">
-        <v>-6.6</v>
+        <v>-0.7</v>
       </c>
       <c r="AC32" t="n">
-        <v>5.3</v>
+        <v>9.5</v>
       </c>
       <c r="AD32" t="n">
-        <v>-0.6</v>
+        <v>4.4</v>
       </c>
       <c r="AF32" t="n">
-        <v>229.96</v>
+        <v>227.01</v>
       </c>
       <c r="AG32" t="n">
-        <v>-0.02</v>
+        <v>-2.95</v>
       </c>
       <c r="AH32" t="n">
         <v>215</v>
@@ -3577,10 +3616,10 @@
         <v>235</v>
       </c>
       <c r="AK32" t="n">
-        <v>128.14</v>
+        <v>128.15</v>
       </c>
       <c r="AL32" t="n">
-        <v>11.77</v>
+        <v>0.01</v>
       </c>
       <c r="AM32" t="n">
         <v>110</v>
@@ -3589,99 +3628,99 @@
         <v>142</v>
       </c>
       <c r="AP32" t="n">
-        <v>87.47</v>
+        <v>83.41</v>
       </c>
       <c r="AS32" t="n">
-        <v>14.8</v>
+        <v>14.52</v>
       </c>
       <c r="BL32" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B33" t="n">
-        <v>165.8</v>
+        <v>158.1</v>
       </c>
       <c r="C33" t="n">
-        <v>77.3</v>
+        <v>73.7</v>
       </c>
       <c r="D33" t="n">
-        <v>29.3</v>
+        <v>30.3</v>
       </c>
       <c r="E33" t="n">
-        <v>27.7</v>
+        <v>26</v>
       </c>
       <c r="F33" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="H33" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="I33" t="n">
-        <v>10.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J33" t="n">
-        <v>41.6</v>
+        <v>40.9</v>
       </c>
       <c r="K33" t="n">
-        <v>76.59999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="M33" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="N33" t="n">
-        <v>35.1</v>
+        <v>35.3</v>
       </c>
       <c r="O33" t="n">
-        <v>39.8</v>
+        <v>40.3</v>
       </c>
       <c r="Q33" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="R33" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S33" t="n">
         <v>7</v>
       </c>
       <c r="T33" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="V33" t="n">
-        <v>9.4</v>
+        <v>8.9</v>
       </c>
       <c r="W33" t="n">
-        <v>17.4</v>
+        <v>19.3</v>
       </c>
       <c r="X33" t="n">
-        <v>13.4</v>
+        <v>14.1</v>
       </c>
       <c r="Y33" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z33" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA33" t="n">
-        <v>10.1</v>
+        <v>11</v>
       </c>
       <c r="AB33" t="n">
-        <v>-0.7</v>
+        <v>4.4</v>
       </c>
       <c r="AC33" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="AD33" t="n">
-        <v>4.4</v>
+        <v>6.5</v>
       </c>
       <c r="AF33" t="n">
-        <v>227.01</v>
+        <v>228.35</v>
       </c>
       <c r="AG33" t="n">
-        <v>-2.95</v>
+        <v>1.33</v>
       </c>
       <c r="AH33" t="n">
         <v>215</v>
@@ -3690,10 +3729,10 @@
         <v>235</v>
       </c>
       <c r="AK33" t="n">
-        <v>128.15</v>
+        <v>128.86</v>
       </c>
       <c r="AL33" t="n">
-        <v>0.01</v>
+        <v>0.71</v>
       </c>
       <c r="AM33" t="n">
         <v>110</v>
@@ -3702,99 +3741,99 @@
         <v>142</v>
       </c>
       <c r="AP33" t="n">
-        <v>83.41</v>
+        <v>82.37</v>
       </c>
       <c r="AS33" t="n">
-        <v>14.52</v>
+        <v>14.22</v>
       </c>
       <c r="BL33" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B34" t="n">
-        <v>158.1</v>
+        <v>154.9</v>
       </c>
       <c r="C34" t="n">
-        <v>73.7</v>
+        <v>70.2</v>
       </c>
       <c r="D34" t="n">
-        <v>30.3</v>
+        <v>31.5</v>
       </c>
       <c r="E34" t="n">
-        <v>26</v>
+        <v>27.7</v>
       </c>
       <c r="F34" t="n">
-        <v>4.1</v>
+        <v>2.7</v>
       </c>
       <c r="H34" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="I34" t="n">
-        <v>9.300000000000001</v>
+        <v>11.3</v>
       </c>
       <c r="J34" t="n">
-        <v>40.9</v>
+        <v>40.3</v>
       </c>
       <c r="K34" t="n">
-        <v>74.40000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="M34" t="n">
-        <v>5</v>
+        <v>6.1</v>
       </c>
       <c r="N34" t="n">
-        <v>35.3</v>
+        <v>32.9</v>
       </c>
       <c r="O34" t="n">
-        <v>40.3</v>
+        <v>39</v>
       </c>
       <c r="Q34" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="R34" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="S34" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="T34" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="V34" t="n">
-        <v>8.9</v>
+        <v>6.3</v>
       </c>
       <c r="W34" t="n">
-        <v>19.3</v>
+        <v>25.2</v>
       </c>
       <c r="X34" t="n">
-        <v>14.1</v>
+        <v>15.8</v>
       </c>
       <c r="Y34" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z34" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA34" t="n">
-        <v>11</v>
+        <v>12.6</v>
       </c>
       <c r="AB34" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="AC34" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="AD34" t="n">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="AF34" t="n">
-        <v>228.35</v>
+        <v>231.16</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.33</v>
+        <v>2.81</v>
       </c>
       <c r="AH34" t="n">
         <v>215</v>
@@ -3803,10 +3842,10 @@
         <v>235</v>
       </c>
       <c r="AK34" t="n">
-        <v>128.86</v>
+        <v>130.88</v>
       </c>
       <c r="AL34" t="n">
-        <v>0.71</v>
+        <v>2.02</v>
       </c>
       <c r="AM34" t="n">
         <v>110</v>
@@ -3815,99 +3854,66 @@
         <v>142</v>
       </c>
       <c r="AP34" t="n">
-        <v>82.37</v>
+        <v>85.48999999999999</v>
       </c>
       <c r="AS34" t="n">
-        <v>14.22</v>
+        <v>13.1</v>
       </c>
       <c r="BL34" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B35" t="n">
-        <v>154.9</v>
-      </c>
-      <c r="C35" t="n">
-        <v>70.2</v>
+        <v>152.2</v>
       </c>
       <c r="D35" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="E35" t="n">
-        <v>27.7</v>
+        <v>31</v>
       </c>
       <c r="F35" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="H35" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I35" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J35" t="n">
-        <v>40.3</v>
+        <v>3.5</v>
       </c>
       <c r="K35" t="n">
-        <v>75.8</v>
-      </c>
-      <c r="M35" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="N35" t="n">
-        <v>32.9</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O35" t="n">
-        <v>39</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="R35" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="S35" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="T35" t="n">
-        <v>23.7</v>
+        <v>34.4</v>
       </c>
       <c r="V35" t="n">
-        <v>6.3</v>
+        <v>9.5</v>
       </c>
       <c r="W35" t="n">
-        <v>25.2</v>
+        <v>25.5</v>
       </c>
       <c r="X35" t="n">
-        <v>15.8</v>
+        <v>17.5</v>
       </c>
       <c r="Y35" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Z35" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AA35" t="n">
-        <v>12.6</v>
+        <v>9</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.9</v>
+        <v>-1.1</v>
       </c>
       <c r="AC35" t="n">
         <v>8.6</v>
       </c>
       <c r="AD35" t="n">
-        <v>5.8</v>
+        <v>3.8</v>
       </c>
       <c r="AF35" t="n">
-        <v>231.16</v>
+        <v>228.13</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.81</v>
+        <v>-3.03</v>
       </c>
       <c r="AH35" t="n">
         <v>215</v>
@@ -3915,79 +3921,67 @@
       <c r="AI35" t="n">
         <v>235</v>
       </c>
-      <c r="AK35" t="n">
-        <v>130.88</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AM35" t="n">
         <v>110</v>
       </c>
       <c r="AN35" t="n">
         <v>142</v>
       </c>
-      <c r="AP35" t="n">
-        <v>85.48999999999999</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>13.1</v>
-      </c>
       <c r="BL35" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B36" t="n">
-        <v>152.2</v>
+        <v>143.9</v>
       </c>
       <c r="D36" t="n">
-        <v>31</v>
+        <v>30.8</v>
       </c>
       <c r="F36" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="K36" t="n">
-        <v>98.40000000000001</v>
+        <v>99.2</v>
       </c>
       <c r="O36" t="n">
-        <v>34.4</v>
+        <v>35.2</v>
       </c>
       <c r="V36" t="n">
-        <v>9.5</v>
+        <v>10.7</v>
       </c>
       <c r="W36" t="n">
-        <v>25.5</v>
+        <v>17.6</v>
       </c>
       <c r="X36" t="n">
-        <v>17.5</v>
+        <v>14.2</v>
       </c>
       <c r="Y36" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Z36" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA36" t="n">
         <v>9</v>
       </c>
       <c r="AB36" t="n">
-        <v>-1.1</v>
+        <v>-0.8</v>
       </c>
       <c r="AC36" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD36" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AF36" t="n">
-        <v>228.13</v>
+        <v>229.16</v>
       </c>
       <c r="AG36" t="n">
-        <v>-3.03</v>
+        <v>1.03</v>
       </c>
       <c r="AH36" t="n">
         <v>215</v>
@@ -4002,60 +3996,93 @@
         <v>142</v>
       </c>
       <c r="BL36" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B37" t="n">
-        <v>143.9</v>
+        <v>163.2</v>
+      </c>
+      <c r="C37" t="n">
+        <v>73.7</v>
       </c>
       <c r="D37" t="n">
-        <v>30.8</v>
+        <v>30</v>
+      </c>
+      <c r="E37" t="n">
+        <v>28.2</v>
       </c>
       <c r="F37" t="n">
-        <v>2.5</v>
+        <v>4.8</v>
+      </c>
+      <c r="H37" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I37" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J37" t="n">
+        <v>40.1</v>
       </c>
       <c r="K37" t="n">
-        <v>99.2</v>
+        <v>75.59999999999999</v>
+      </c>
+      <c r="M37" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="N37" t="n">
+        <v>32.9</v>
       </c>
       <c r="O37" t="n">
-        <v>35.2</v>
+        <v>39.7</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="R37" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="S37" t="n">
+        <v>6</v>
+      </c>
+      <c r="T37" t="n">
+        <v>23.5</v>
       </c>
       <c r="V37" t="n">
-        <v>10.7</v>
+        <v>9.4</v>
       </c>
       <c r="W37" t="n">
-        <v>17.6</v>
+        <v>20.1</v>
       </c>
       <c r="X37" t="n">
-        <v>14.2</v>
+        <v>14.8</v>
       </c>
       <c r="Y37" t="n">
         <v>4</v>
       </c>
       <c r="Z37" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA37" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AB37" t="n">
-        <v>-0.8</v>
+        <v>-0.9</v>
       </c>
       <c r="AC37" t="n">
-        <v>8.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="AD37" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AF37" t="n">
-        <v>229.16</v>
+        <v>228.55</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.03</v>
+        <v>-0.61</v>
       </c>
       <c r="AH37" t="n">
         <v>215</v>
@@ -4063,100 +4090,112 @@
       <c r="AI37" t="n">
         <v>235</v>
       </c>
+      <c r="AK37" t="n">
+        <v>127.06</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>-3.82</v>
+      </c>
       <c r="AM37" t="n">
         <v>110</v>
       </c>
       <c r="AN37" t="n">
         <v>142</v>
       </c>
+      <c r="AP37" t="n">
+        <v>82.81</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>12.9</v>
+      </c>
       <c r="BL37" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="B38" t="n">
-        <v>163.2</v>
+        <v>174.4</v>
       </c>
       <c r="C38" t="n">
-        <v>73.7</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="D38" t="n">
-        <v>30</v>
+        <v>32.1</v>
       </c>
       <c r="E38" t="n">
-        <v>28.2</v>
+        <v>30.8</v>
       </c>
       <c r="F38" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="H38" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="I38" t="n">
-        <v>11.4</v>
+        <v>10.5</v>
       </c>
       <c r="J38" t="n">
-        <v>40.1</v>
+        <v>39.5</v>
       </c>
       <c r="K38" t="n">
-        <v>75.59999999999999</v>
+        <v>74</v>
       </c>
       <c r="M38" t="n">
         <v>6.8</v>
       </c>
       <c r="N38" t="n">
-        <v>32.9</v>
+        <v>35.8</v>
       </c>
       <c r="O38" t="n">
-        <v>39.7</v>
+        <v>42.6</v>
       </c>
       <c r="Q38" t="n">
-        <v>23.5</v>
+        <v>23.1</v>
       </c>
       <c r="R38" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="S38" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="T38" t="n">
-        <v>23.5</v>
+        <v>23.1</v>
       </c>
       <c r="V38" t="n">
-        <v>9.4</v>
+        <v>12.8</v>
       </c>
       <c r="W38" t="n">
-        <v>20.1</v>
+        <v>22.1</v>
       </c>
       <c r="X38" t="n">
-        <v>14.8</v>
+        <v>17.5</v>
       </c>
       <c r="Y38" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Z38" t="n">
         <v>13</v>
       </c>
       <c r="AA38" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AC38" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="AB38" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>9.5</v>
-      </c>
       <c r="AD38" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AF38" t="n">
-        <v>228.55</v>
+        <v>219.99</v>
       </c>
       <c r="AG38" t="n">
-        <v>-0.61</v>
+        <v>-8.56</v>
       </c>
       <c r="AH38" t="n">
         <v>215</v>
@@ -4165,10 +4204,10 @@
         <v>235</v>
       </c>
       <c r="AK38" t="n">
-        <v>127.06</v>
+        <v>125.61</v>
       </c>
       <c r="AL38" t="n">
-        <v>-3.82</v>
+        <v>-1.45</v>
       </c>
       <c r="AM38" t="n">
         <v>110</v>
@@ -4177,99 +4216,99 @@
         <v>142</v>
       </c>
       <c r="AP38" t="n">
-        <v>82.81</v>
+        <v>77.83</v>
       </c>
       <c r="AS38" t="n">
-        <v>12.9</v>
+        <v>12.96</v>
       </c>
       <c r="BL38" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B39" t="n">
-        <v>174.4</v>
+        <v>163.2</v>
       </c>
       <c r="C39" t="n">
-        <v>75.40000000000001</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="D39" t="n">
-        <v>32.1</v>
+        <v>32.9</v>
       </c>
       <c r="E39" t="n">
-        <v>30.8</v>
+        <v>26</v>
       </c>
       <c r="F39" t="n">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="H39" t="n">
-        <v>24</v>
+        <v>23.8</v>
       </c>
       <c r="I39" t="n">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="J39" t="n">
-        <v>39.5</v>
+        <v>40.1</v>
       </c>
       <c r="K39" t="n">
-        <v>74</v>
+        <v>71.3</v>
       </c>
       <c r="M39" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="N39" t="n">
-        <v>35.8</v>
+        <v>34.3</v>
       </c>
       <c r="O39" t="n">
-        <v>42.6</v>
+        <v>41.5</v>
       </c>
       <c r="Q39" t="n">
         <v>23.1</v>
       </c>
       <c r="R39" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="S39" t="n">
-        <v>8.5</v>
+        <v>6.2</v>
       </c>
       <c r="T39" t="n">
         <v>23.1</v>
       </c>
       <c r="V39" t="n">
-        <v>12.8</v>
+        <v>9.6</v>
       </c>
       <c r="W39" t="n">
-        <v>22.1</v>
+        <v>23.3</v>
       </c>
       <c r="X39" t="n">
-        <v>17.5</v>
+        <v>16.4</v>
       </c>
       <c r="Y39" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z39" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA39" t="n">
-        <v>10.1</v>
+        <v>12.2</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.3</v>
+        <v>2.6</v>
       </c>
       <c r="AC39" t="n">
-        <v>9.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="AD39" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AF39" t="n">
-        <v>219.99</v>
+        <v>219.22</v>
       </c>
       <c r="AG39" t="n">
-        <v>-8.56</v>
+        <v>-0.77</v>
       </c>
       <c r="AH39" t="n">
         <v>215</v>
@@ -4278,10 +4317,10 @@
         <v>235</v>
       </c>
       <c r="AK39" t="n">
-        <v>125.61</v>
+        <v>124.36</v>
       </c>
       <c r="AL39" t="n">
-        <v>-1.45</v>
+        <v>-1.25</v>
       </c>
       <c r="AM39" t="n">
         <v>110</v>
@@ -4290,99 +4329,99 @@
         <v>142</v>
       </c>
       <c r="AP39" t="n">
-        <v>77.83</v>
+        <v>76.81</v>
       </c>
       <c r="AS39" t="n">
-        <v>12.96</v>
+        <v>12.38</v>
       </c>
       <c r="BL39" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B40" t="n">
-        <v>163.2</v>
+        <v>152.7</v>
       </c>
       <c r="C40" t="n">
-        <v>70.90000000000001</v>
+        <v>62.6</v>
       </c>
       <c r="D40" t="n">
-        <v>32.9</v>
+        <v>32.7</v>
       </c>
       <c r="E40" t="n">
-        <v>26</v>
+        <v>24.6</v>
       </c>
       <c r="F40" t="n">
-        <v>6.9</v>
+        <v>5.2</v>
       </c>
       <c r="H40" t="n">
         <v>23.8</v>
       </c>
       <c r="I40" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J40" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="K40" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="M40" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="N40" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="O40" t="n">
         <v>40.1</v>
       </c>
-      <c r="K40" t="n">
-        <v>71.3</v>
-      </c>
-      <c r="M40" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="N40" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="O40" t="n">
-        <v>41.5</v>
-      </c>
       <c r="Q40" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="R40" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="S40" t="n">
-        <v>6.2</v>
+        <v>4</v>
       </c>
       <c r="T40" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="V40" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="W40" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="X40" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC40" t="n">
         <v>9.6</v>
       </c>
-      <c r="W40" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="X40" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>8.5</v>
-      </c>
       <c r="AD40" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AF40" t="n">
-        <v>219.22</v>
+        <v>220.73</v>
       </c>
       <c r="AG40" t="n">
-        <v>-0.77</v>
+        <v>1.5</v>
       </c>
       <c r="AH40" t="n">
         <v>215</v>
@@ -4391,10 +4430,10 @@
         <v>235</v>
       </c>
       <c r="AK40" t="n">
-        <v>124.36</v>
+        <v>120.93</v>
       </c>
       <c r="AL40" t="n">
-        <v>-1.25</v>
+        <v>-3.43</v>
       </c>
       <c r="AM40" t="n">
         <v>110</v>
@@ -4403,75 +4442,75 @@
         <v>142</v>
       </c>
       <c r="AP40" t="n">
-        <v>76.81</v>
+        <v>77.87</v>
       </c>
       <c r="AS40" t="n">
-        <v>12.38</v>
+        <v>13.26</v>
       </c>
       <c r="BL40" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B41" t="n">
-        <v>152.7</v>
+        <v>150.7</v>
       </c>
       <c r="C41" t="n">
-        <v>62.6</v>
+        <v>64.8</v>
       </c>
       <c r="D41" t="n">
-        <v>32.7</v>
+        <v>33.7</v>
       </c>
       <c r="E41" t="n">
-        <v>24.6</v>
+        <v>27.1</v>
       </c>
       <c r="F41" t="n">
-        <v>5.2</v>
+        <v>3.8</v>
       </c>
       <c r="H41" t="n">
-        <v>23.8</v>
+        <v>23.4</v>
       </c>
       <c r="I41" t="n">
         <v>7.2</v>
       </c>
       <c r="J41" t="n">
-        <v>38.9</v>
+        <v>39.9</v>
       </c>
       <c r="K41" t="n">
-        <v>69.90000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="M41" t="n">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="N41" t="n">
-        <v>33.5</v>
+        <v>33</v>
       </c>
       <c r="O41" t="n">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="Q41" t="n">
         <v>23.2</v>
       </c>
       <c r="R41" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T41" t="n">
         <v>23.2</v>
       </c>
       <c r="V41" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="W41" t="n">
-        <v>27.3</v>
+        <v>28.9</v>
       </c>
       <c r="X41" t="n">
-        <v>19.4</v>
+        <v>21.7</v>
       </c>
       <c r="Y41" t="n">
         <v>10</v>
@@ -4480,22 +4519,22 @@
         <v>18</v>
       </c>
       <c r="AA41" t="n">
-        <v>14</v>
+        <v>13.1</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="AC41" t="n">
-        <v>9.6</v>
+        <v>10.8</v>
       </c>
       <c r="AD41" t="n">
-        <v>5.7</v>
+        <v>6.7</v>
       </c>
       <c r="AF41" t="n">
-        <v>220.73</v>
+        <v>220.58</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.5</v>
+        <v>-0.15</v>
       </c>
       <c r="AH41" t="n">
         <v>215</v>
@@ -4504,10 +4543,10 @@
         <v>235</v>
       </c>
       <c r="AK41" t="n">
-        <v>120.93</v>
+        <v>120.28</v>
       </c>
       <c r="AL41" t="n">
-        <v>-3.43</v>
+        <v>-0.65</v>
       </c>
       <c r="AM41" t="n">
         <v>110</v>
@@ -4516,99 +4555,54 @@
         <v>142</v>
       </c>
       <c r="AP41" t="n">
-        <v>77.87</v>
+        <v>77.22</v>
       </c>
       <c r="AS41" t="n">
-        <v>13.26</v>
+        <v>13.79</v>
       </c>
       <c r="BL41" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B42" t="n">
-        <v>150.7</v>
-      </c>
-      <c r="C42" t="n">
-        <v>64.8</v>
+        <v>138.2</v>
       </c>
       <c r="D42" t="n">
-        <v>33.7</v>
-      </c>
-      <c r="E42" t="n">
-        <v>27.1</v>
+        <v>33.6</v>
       </c>
       <c r="F42" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H42" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="V42" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="W42" t="n">
         <v>23.4</v>
       </c>
-      <c r="I42" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="J42" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="K42" t="n">
-        <v>70.5</v>
-      </c>
-      <c r="M42" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="N42" t="n">
-        <v>33</v>
-      </c>
-      <c r="O42" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="R42" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="S42" t="n">
-        <v>3</v>
-      </c>
-      <c r="T42" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="V42" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="W42" t="n">
-        <v>28.9</v>
-      </c>
       <c r="X42" t="n">
-        <v>21.7</v>
+        <v>19.4</v>
       </c>
       <c r="Y42" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z42" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AA42" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="AC42" t="n">
-        <v>10.8</v>
+        <v>8.5</v>
       </c>
       <c r="AD42" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>220.58</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>-0.15</v>
+        <v>4.5</v>
       </c>
       <c r="AH42" t="n">
         <v>215</v>
@@ -4616,67 +4610,61 @@
       <c r="AI42" t="n">
         <v>235</v>
       </c>
-      <c r="AK42" t="n">
-        <v>120.28</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>-0.65</v>
-      </c>
       <c r="AM42" t="n">
         <v>110</v>
       </c>
       <c r="AN42" t="n">
         <v>142</v>
       </c>
-      <c r="AP42" t="n">
-        <v>77.22</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>13.79</v>
-      </c>
       <c r="BL42" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B43" t="n">
-        <v>138.2</v>
+        <v>126.5</v>
       </c>
       <c r="D43" t="n">
-        <v>33.6</v>
+        <v>33.2</v>
       </c>
       <c r="F43" t="n">
-        <v>6.1</v>
+        <v>3.4</v>
       </c>
       <c r="V43" t="n">
-        <v>15.5</v>
+        <v>12.6</v>
       </c>
       <c r="W43" t="n">
-        <v>23.4</v>
+        <v>22.3</v>
       </c>
       <c r="X43" t="n">
-        <v>19.4</v>
+        <v>17.4</v>
       </c>
       <c r="Y43" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z43" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA43" t="n">
         <v>13</v>
       </c>
       <c r="AB43" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>8.5</v>
+        <v>6.7</v>
       </c>
       <c r="AD43" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>229.48</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>6.05</v>
       </c>
       <c r="AH43" t="n">
         <v>215</v>
@@ -4691,54 +4679,93 @@
         <v>142</v>
       </c>
       <c r="BL43" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B44" t="n">
-        <v>126.5</v>
+        <v>129.4</v>
+      </c>
+      <c r="C44" t="n">
+        <v>50.6</v>
       </c>
       <c r="D44" t="n">
-        <v>33.2</v>
+        <v>31.5</v>
+      </c>
+      <c r="E44" t="n">
+        <v>19.4</v>
       </c>
       <c r="F44" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
+      </c>
+      <c r="H44" t="n">
+        <v>24</v>
+      </c>
+      <c r="I44" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J44" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="K44" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="M44" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N44" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="O44" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>21.4</v>
       </c>
       <c r="V44" t="n">
-        <v>12.6</v>
+        <v>14.3</v>
       </c>
       <c r="W44" t="n">
-        <v>22.3</v>
+        <v>23.9</v>
       </c>
       <c r="X44" t="n">
-        <v>17.4</v>
+        <v>19.1</v>
       </c>
       <c r="Y44" t="n">
         <v>8</v>
       </c>
       <c r="Z44" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AA44" t="n">
-        <v>13</v>
+        <v>16.1</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AC44" t="n">
-        <v>6.7</v>
+        <v>7.6</v>
       </c>
       <c r="AD44" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="AF44" t="n">
-        <v>229.48</v>
+        <v>229.5</v>
       </c>
       <c r="AG44" t="n">
-        <v>6.05</v>
+        <v>0.02</v>
       </c>
       <c r="AH44" t="n">
         <v>215</v>
@@ -4746,100 +4773,112 @@
       <c r="AI44" t="n">
         <v>235</v>
       </c>
+      <c r="AK44" t="n">
+        <v>128.37</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>8.09</v>
+      </c>
       <c r="AM44" t="n">
         <v>110</v>
       </c>
       <c r="AN44" t="n">
         <v>142</v>
       </c>
+      <c r="AP44" t="n">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>15.97</v>
+      </c>
       <c r="BL44" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="B45" t="n">
-        <v>129.4</v>
+        <v>142.9</v>
       </c>
       <c r="C45" t="n">
-        <v>50.6</v>
+        <v>52.7</v>
       </c>
       <c r="D45" t="n">
-        <v>31.5</v>
+        <v>34.7</v>
       </c>
       <c r="E45" t="n">
-        <v>19.4</v>
+        <v>24.8</v>
       </c>
       <c r="F45" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="H45" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I45" t="n">
-        <v>10.4</v>
+        <v>9.9</v>
       </c>
       <c r="J45" t="n">
-        <v>38.9</v>
+        <v>38.2</v>
       </c>
       <c r="K45" t="n">
-        <v>73.3</v>
+        <v>70</v>
       </c>
       <c r="M45" t="n">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="N45" t="n">
-        <v>33.3</v>
+        <v>31.9</v>
       </c>
       <c r="O45" t="n">
-        <v>38</v>
+        <v>35.8</v>
       </c>
       <c r="Q45" t="n">
-        <v>21.4</v>
+        <v>19.7</v>
       </c>
       <c r="R45" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>21.4</v>
+        <v>19.7</v>
       </c>
       <c r="V45" t="n">
-        <v>14.3</v>
+        <v>12</v>
       </c>
       <c r="W45" t="n">
-        <v>23.9</v>
+        <v>25.8</v>
       </c>
       <c r="X45" t="n">
-        <v>19.1</v>
+        <v>18.9</v>
       </c>
       <c r="Y45" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Z45" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AA45" t="n">
-        <v>16.1</v>
+        <v>15</v>
       </c>
       <c r="AB45" t="n">
-        <v>0.4</v>
+        <v>-0.1</v>
       </c>
       <c r="AC45" t="n">
-        <v>7.6</v>
+        <v>5.8</v>
       </c>
       <c r="AD45" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="AF45" t="n">
-        <v>229.5</v>
+        <v>238.69</v>
       </c>
       <c r="AG45" t="n">
-        <v>0.02</v>
+        <v>-2.8</v>
       </c>
       <c r="AH45" t="n">
         <v>215</v>
@@ -4848,10 +4887,10 @@
         <v>235</v>
       </c>
       <c r="AK45" t="n">
-        <v>128.37</v>
+        <v>134.59</v>
       </c>
       <c r="AL45" t="n">
-        <v>8.09</v>
+        <v>6.22</v>
       </c>
       <c r="AM45" t="n">
         <v>110</v>
@@ -4860,99 +4899,99 @@
         <v>142</v>
       </c>
       <c r="AP45" t="n">
-        <v>91.59999999999999</v>
+        <v>89.05</v>
       </c>
       <c r="AS45" t="n">
-        <v>15.97</v>
+        <v>17.06</v>
       </c>
       <c r="BL45" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B46" t="n">
-        <v>142.9</v>
+        <v>148.1</v>
       </c>
       <c r="C46" t="n">
-        <v>52.7</v>
+        <v>51.9</v>
       </c>
       <c r="D46" t="n">
-        <v>34.7</v>
+        <v>35.4</v>
       </c>
       <c r="E46" t="n">
-        <v>24.8</v>
+        <v>31.5</v>
       </c>
       <c r="F46" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="H46" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="I46" t="n">
-        <v>9.9</v>
+        <v>9.6</v>
       </c>
       <c r="J46" t="n">
-        <v>38.2</v>
+        <v>39.6</v>
       </c>
       <c r="K46" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M46" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="N46" t="n">
-        <v>31.9</v>
+        <v>30.8</v>
       </c>
       <c r="O46" t="n">
-        <v>35.8</v>
+        <v>33.7</v>
       </c>
       <c r="Q46" t="n">
-        <v>19.7</v>
+        <v>20.7</v>
       </c>
       <c r="R46" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>19.7</v>
+        <v>20.7</v>
       </c>
       <c r="V46" t="n">
-        <v>12</v>
+        <v>13.1</v>
       </c>
       <c r="W46" t="n">
-        <v>25.8</v>
+        <v>25.5</v>
       </c>
       <c r="X46" t="n">
-        <v>18.9</v>
+        <v>19.3</v>
       </c>
       <c r="Y46" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z46" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AA46" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AB46" t="n">
-        <v>-0.1</v>
+        <v>-1</v>
       </c>
       <c r="AC46" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="AF46" t="n">
-        <v>238.69</v>
+        <v>233.48</v>
       </c>
       <c r="AG46" t="n">
-        <v>-2.8</v>
+        <v>-4.86</v>
       </c>
       <c r="AH46" t="n">
         <v>215</v>
@@ -4961,10 +5000,10 @@
         <v>235</v>
       </c>
       <c r="AK46" t="n">
-        <v>134.59</v>
+        <v>136.6</v>
       </c>
       <c r="AL46" t="n">
-        <v>6.22</v>
+        <v>2.01</v>
       </c>
       <c r="AM46" t="n">
         <v>110</v>
@@ -4973,99 +5012,99 @@
         <v>142</v>
       </c>
       <c r="AP46" t="n">
-        <v>89.05</v>
+        <v>86.25</v>
       </c>
       <c r="AS46" t="n">
-        <v>17.06</v>
+        <v>17.13</v>
       </c>
       <c r="BL46" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B47" t="n">
-        <v>148.1</v>
+        <v>143.4</v>
       </c>
       <c r="C47" t="n">
-        <v>51.9</v>
+        <v>50.9</v>
       </c>
       <c r="D47" t="n">
-        <v>35.4</v>
+        <v>35.7</v>
       </c>
       <c r="E47" t="n">
-        <v>31.5</v>
+        <v>26.2</v>
       </c>
       <c r="F47" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="H47" t="n">
-        <v>21.8</v>
+        <v>22.9</v>
       </c>
       <c r="I47" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J47" t="n">
-        <v>39.6</v>
+        <v>39.9</v>
       </c>
       <c r="K47" t="n">
-        <v>71</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="M47" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="N47" t="n">
-        <v>30.8</v>
+        <v>31.2</v>
       </c>
       <c r="O47" t="n">
-        <v>33.7</v>
+        <v>33.1</v>
       </c>
       <c r="Q47" t="n">
-        <v>20.7</v>
+        <v>21.6</v>
       </c>
       <c r="R47" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>20.7</v>
+        <v>21.6</v>
       </c>
       <c r="V47" t="n">
-        <v>13.1</v>
+        <v>12.9</v>
       </c>
       <c r="W47" t="n">
-        <v>25.5</v>
+        <v>28.3</v>
       </c>
       <c r="X47" t="n">
-        <v>19.3</v>
+        <v>20.6</v>
       </c>
       <c r="Y47" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z47" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AA47" t="n">
-        <v>15.5</v>
+        <v>17.9</v>
       </c>
       <c r="AB47" t="n">
-        <v>-1</v>
+        <v>-0.8</v>
       </c>
       <c r="AC47" t="n">
-        <v>6.4</v>
+        <v>8.1</v>
       </c>
       <c r="AD47" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="AF47" t="n">
-        <v>233.48</v>
+        <v>235.13</v>
       </c>
       <c r="AG47" t="n">
-        <v>-4.86</v>
+        <v>1.66</v>
       </c>
       <c r="AH47" t="n">
         <v>215</v>
@@ -5074,10 +5113,10 @@
         <v>235</v>
       </c>
       <c r="AK47" t="n">
-        <v>136.6</v>
+        <v>135.66</v>
       </c>
       <c r="AL47" t="n">
-        <v>2.01</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AM47" t="n">
         <v>110</v>
@@ -5086,57 +5125,57 @@
         <v>142</v>
       </c>
       <c r="AP47" t="n">
-        <v>86.25</v>
+        <v>88.27</v>
       </c>
       <c r="AS47" t="n">
-        <v>17.13</v>
+        <v>17.6</v>
       </c>
       <c r="BL47" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B48" t="n">
-        <v>143.4</v>
+        <v>144.9</v>
       </c>
       <c r="C48" t="n">
-        <v>50.9</v>
+        <v>53</v>
       </c>
       <c r="D48" t="n">
-        <v>35.7</v>
+        <v>35.6</v>
       </c>
       <c r="E48" t="n">
-        <v>26.2</v>
+        <v>26</v>
       </c>
       <c r="F48" t="n">
-        <v>4.3</v>
+        <v>2.8</v>
       </c>
       <c r="H48" t="n">
-        <v>22.9</v>
+        <v>24</v>
       </c>
       <c r="I48" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J48" t="n">
-        <v>39.9</v>
+        <v>40.3</v>
       </c>
       <c r="K48" t="n">
-        <v>72.59999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="M48" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="N48" t="n">
-        <v>31.2</v>
+        <v>31.6</v>
       </c>
       <c r="O48" t="n">
-        <v>33.1</v>
+        <v>33.6</v>
       </c>
       <c r="Q48" t="n">
-        <v>21.6</v>
+        <v>21</v>
       </c>
       <c r="R48" t="n">
         <v>0</v>
@@ -5145,40 +5184,40 @@
         <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>21.6</v>
+        <v>21</v>
       </c>
       <c r="V48" t="n">
-        <v>12.9</v>
+        <v>14.4</v>
       </c>
       <c r="W48" t="n">
-        <v>28.3</v>
+        <v>27.7</v>
       </c>
       <c r="X48" t="n">
-        <v>20.6</v>
+        <v>21.1</v>
       </c>
       <c r="Y48" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z48" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AA48" t="n">
-        <v>17.9</v>
+        <v>16.3</v>
       </c>
       <c r="AB48" t="n">
-        <v>-0.8</v>
+        <v>-1.1</v>
       </c>
       <c r="AC48" t="n">
-        <v>8.1</v>
+        <v>6.6</v>
       </c>
       <c r="AD48" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="AF48" t="n">
-        <v>235.13</v>
+        <v>234.87</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.66</v>
+        <v>-0.26</v>
       </c>
       <c r="AH48" t="n">
         <v>215</v>
@@ -5187,10 +5226,10 @@
         <v>235</v>
       </c>
       <c r="AK48" t="n">
-        <v>135.66</v>
+        <v>136.33</v>
       </c>
       <c r="AL48" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="AM48" t="n">
         <v>110</v>
@@ -5199,99 +5238,60 @@
         <v>142</v>
       </c>
       <c r="AP48" t="n">
-        <v>88.27</v>
+        <v>87.09</v>
       </c>
       <c r="AS48" t="n">
-        <v>17.6</v>
+        <v>17.31</v>
       </c>
       <c r="BL48" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B49" t="n">
-        <v>144.9</v>
-      </c>
-      <c r="C49" t="n">
-        <v>53</v>
+        <v>132.2</v>
       </c>
       <c r="D49" t="n">
         <v>35.6</v>
       </c>
-      <c r="E49" t="n">
-        <v>26</v>
-      </c>
       <c r="F49" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="H49" t="n">
-        <v>24</v>
-      </c>
-      <c r="I49" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="J49" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="K49" t="n">
-        <v>73.7</v>
-      </c>
-      <c r="M49" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="N49" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="O49" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>21</v>
-      </c>
-      <c r="R49" t="n">
-        <v>0</v>
-      </c>
-      <c r="S49" t="n">
-        <v>0</v>
-      </c>
-      <c r="T49" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="V49" t="n">
-        <v>14.4</v>
+        <v>11.6</v>
       </c>
       <c r="W49" t="n">
-        <v>27.7</v>
+        <v>23.2</v>
       </c>
       <c r="X49" t="n">
-        <v>21.1</v>
+        <v>17.4</v>
       </c>
       <c r="Y49" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z49" t="n">
         <v>19</v>
       </c>
       <c r="AA49" t="n">
-        <v>16.3</v>
+        <v>13</v>
       </c>
       <c r="AB49" t="n">
-        <v>-1.1</v>
+        <v>0.9</v>
       </c>
       <c r="AC49" t="n">
-        <v>6.6</v>
+        <v>7.5</v>
       </c>
       <c r="AD49" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="AF49" t="n">
-        <v>234.87</v>
+        <v>234.78</v>
       </c>
       <c r="AG49" t="n">
-        <v>-0.26</v>
+        <v>-0.09</v>
       </c>
       <c r="AH49" t="n">
         <v>215</v>
@@ -5299,73 +5299,61 @@
       <c r="AI49" t="n">
         <v>235</v>
       </c>
-      <c r="AK49" t="n">
-        <v>136.33</v>
-      </c>
-      <c r="AL49" t="n">
-        <v>0.67</v>
-      </c>
       <c r="AM49" t="n">
         <v>110</v>
       </c>
       <c r="AN49" t="n">
         <v>142</v>
       </c>
-      <c r="AP49" t="n">
-        <v>87.09</v>
-      </c>
-      <c r="AS49" t="n">
-        <v>17.31</v>
-      </c>
       <c r="BL49" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B50" t="n">
-        <v>132.2</v>
+        <v>137.1</v>
       </c>
       <c r="D50" t="n">
-        <v>35.6</v>
+        <v>35.1</v>
       </c>
       <c r="F50" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="V50" t="n">
-        <v>11.6</v>
+        <v>11</v>
       </c>
       <c r="W50" t="n">
-        <v>23.2</v>
+        <v>22</v>
       </c>
       <c r="X50" t="n">
-        <v>17.4</v>
+        <v>16.5</v>
       </c>
       <c r="Y50" t="n">
         <v>7</v>
       </c>
       <c r="Z50" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AA50" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AB50" t="n">
-        <v>0.9</v>
+        <v>-5.3</v>
       </c>
       <c r="AC50" t="n">
-        <v>7.5</v>
+        <v>6.1</v>
       </c>
       <c r="AD50" t="n">
-        <v>4.2</v>
+        <v>0.4</v>
       </c>
       <c r="AF50" t="n">
-        <v>234.78</v>
+        <v>229.75</v>
       </c>
       <c r="AG50" t="n">
-        <v>-0.09</v>
+        <v>-5.03</v>
       </c>
       <c r="AH50" t="n">
         <v>215</v>
@@ -5380,54 +5368,93 @@
         <v>142</v>
       </c>
       <c r="BL50" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B51" t="n">
-        <v>137.1</v>
+        <v>166.2</v>
+      </c>
+      <c r="C51" t="n">
+        <v>72.40000000000001</v>
       </c>
       <c r="D51" t="n">
-        <v>35.1</v>
+        <v>32.7</v>
+      </c>
+      <c r="E51" t="n">
+        <v>28.1</v>
       </c>
       <c r="F51" t="n">
         <v>3.3</v>
       </c>
+      <c r="H51" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="I51" t="n">
+        <v>9</v>
+      </c>
+      <c r="J51" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="K51" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="M51" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="N51" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="O51" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="R51" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>23.7</v>
+      </c>
       <c r="V51" t="n">
-        <v>11</v>
+        <v>7.9</v>
       </c>
       <c r="W51" t="n">
-        <v>22</v>
+        <v>15.6</v>
       </c>
       <c r="X51" t="n">
-        <v>16.5</v>
+        <v>11.8</v>
       </c>
       <c r="Y51" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z51" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AA51" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AB51" t="n">
-        <v>-5.3</v>
+        <v>-3.5</v>
       </c>
       <c r="AC51" t="n">
-        <v>6.1</v>
+        <v>8.4</v>
       </c>
       <c r="AD51" t="n">
-        <v>0.4</v>
+        <v>2.5</v>
       </c>
       <c r="AF51" t="n">
-        <v>229.75</v>
+        <v>222.86</v>
       </c>
       <c r="AG51" t="n">
-        <v>-5.03</v>
+        <v>-6.9</v>
       </c>
       <c r="AH51" t="n">
         <v>215</v>
@@ -5435,100 +5462,112 @@
       <c r="AI51" t="n">
         <v>235</v>
       </c>
+      <c r="AK51" t="n">
+        <v>135.42</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>-0.91</v>
+      </c>
       <c r="AM51" t="n">
         <v>110</v>
       </c>
       <c r="AN51" t="n">
         <v>142</v>
       </c>
+      <c r="AP51" t="n">
+        <v>81.98</v>
+      </c>
+      <c r="AS51" t="n">
+        <v>15.01</v>
+      </c>
       <c r="BL51" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B52" t="n">
-        <v>166.2</v>
+        <v>166.3</v>
       </c>
       <c r="C52" t="n">
-        <v>72.40000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="D52" t="n">
-        <v>32.7</v>
+        <v>32.8</v>
       </c>
       <c r="E52" t="n">
-        <v>28.1</v>
+        <v>28.8</v>
       </c>
       <c r="F52" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="H52" t="n">
         <v>23.4</v>
       </c>
       <c r="I52" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J52" t="n">
-        <v>42.1</v>
+        <v>41.2</v>
       </c>
       <c r="K52" t="n">
-        <v>74.5</v>
+        <v>73.8</v>
       </c>
       <c r="M52" t="n">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="N52" t="n">
-        <v>33.7</v>
+        <v>35.4</v>
       </c>
       <c r="O52" t="n">
-        <v>39.3</v>
+        <v>42.6</v>
       </c>
       <c r="Q52" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="R52" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="V52" t="n">
-        <v>7.9</v>
+        <v>6.7</v>
       </c>
       <c r="W52" t="n">
-        <v>15.6</v>
+        <v>18.1</v>
       </c>
       <c r="X52" t="n">
-        <v>11.8</v>
+        <v>12.4</v>
       </c>
       <c r="Y52" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Z52" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AA52" t="n">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AB52" t="n">
-        <v>-3.5</v>
+        <v>-2.9</v>
       </c>
       <c r="AC52" t="n">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="AD52" t="n">
-        <v>2.5</v>
+        <v>4.3</v>
       </c>
       <c r="AF52" t="n">
-        <v>222.86</v>
+        <v>218.37</v>
       </c>
       <c r="AG52" t="n">
-        <v>-6.9</v>
+        <v>-4.49</v>
       </c>
       <c r="AH52" t="n">
         <v>215</v>
@@ -5537,10 +5576,10 @@
         <v>235</v>
       </c>
       <c r="AK52" t="n">
-        <v>135.42</v>
+        <v>131.24</v>
       </c>
       <c r="AL52" t="n">
-        <v>-0.91</v>
+        <v>-4.18</v>
       </c>
       <c r="AM52" t="n">
         <v>110</v>
@@ -5549,99 +5588,99 @@
         <v>142</v>
       </c>
       <c r="AP52" t="n">
-        <v>81.98</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="AS52" t="n">
-        <v>15.01</v>
+        <v>12.97</v>
       </c>
       <c r="BL52" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B53" t="n">
-        <v>166.3</v>
+        <v>154.1</v>
       </c>
       <c r="C53" t="n">
-        <v>74.90000000000001</v>
+        <v>65</v>
       </c>
       <c r="D53" t="n">
-        <v>32.8</v>
+        <v>32</v>
       </c>
       <c r="E53" t="n">
-        <v>28.8</v>
+        <v>25.2</v>
       </c>
       <c r="F53" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="H53" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="I53" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="J53" t="n">
-        <v>41.2</v>
+        <v>38.5</v>
       </c>
       <c r="K53" t="n">
-        <v>73.8</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="M53" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="N53" t="n">
-        <v>35.4</v>
+        <v>32.3</v>
       </c>
       <c r="O53" t="n">
-        <v>42.6</v>
+        <v>40.3</v>
       </c>
       <c r="Q53" t="n">
-        <v>23.9</v>
+        <v>21.7</v>
       </c>
       <c r="R53" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="S53" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T53" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="V53" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="W53" t="n">
+        <v>21</v>
+      </c>
+      <c r="X53" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AD53" t="n">
         <v>3.9</v>
       </c>
-      <c r="S53" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="V53" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="W53" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="X53" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>11</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>-2.9</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AF53" t="n">
-        <v>218.37</v>
+        <v>218.04</v>
       </c>
       <c r="AG53" t="n">
-        <v>-4.49</v>
+        <v>-0.33</v>
       </c>
       <c r="AH53" t="n">
         <v>215</v>
@@ -5650,10 +5689,10 @@
         <v>235</v>
       </c>
       <c r="AK53" t="n">
-        <v>131.24</v>
+        <v>129.21</v>
       </c>
       <c r="AL53" t="n">
-        <v>-4.18</v>
+        <v>-2.03</v>
       </c>
       <c r="AM53" t="n">
         <v>110</v>
@@ -5662,99 +5701,99 @@
         <v>142</v>
       </c>
       <c r="AP53" t="n">
-        <v>79.98999999999999</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="AS53" t="n">
-        <v>12.97</v>
+        <v>15.23</v>
       </c>
       <c r="BL53" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B54" t="n">
-        <v>154.1</v>
+        <v>148.8</v>
       </c>
       <c r="C54" t="n">
-        <v>65</v>
+        <v>57.6</v>
       </c>
       <c r="D54" t="n">
-        <v>32</v>
+        <v>32.7</v>
       </c>
       <c r="E54" t="n">
-        <v>25.2</v>
+        <v>26.3</v>
       </c>
       <c r="F54" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="H54" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="I54" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="J54" t="n">
-        <v>38.5</v>
+        <v>41.6</v>
       </c>
       <c r="K54" t="n">
-        <v>70.90000000000001</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="M54" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="N54" t="n">
-        <v>32.3</v>
+        <v>35</v>
       </c>
       <c r="O54" t="n">
-        <v>40.3</v>
+        <v>42.4</v>
       </c>
       <c r="Q54" t="n">
         <v>21.7</v>
       </c>
       <c r="R54" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="S54" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="T54" t="n">
         <v>21.7</v>
       </c>
       <c r="V54" t="n">
-        <v>5.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W54" t="n">
-        <v>21</v>
+        <v>24.1</v>
       </c>
       <c r="X54" t="n">
-        <v>13.2</v>
+        <v>16.1</v>
       </c>
       <c r="Y54" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z54" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA54" t="n">
-        <v>14.5</v>
+        <v>15.6</v>
       </c>
       <c r="AB54" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="AC54" t="n">
-        <v>7.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AD54" t="n">
-        <v>3.9</v>
+        <v>6.3</v>
       </c>
       <c r="AF54" t="n">
-        <v>218.04</v>
+        <v>220.84</v>
       </c>
       <c r="AG54" t="n">
-        <v>-0.33</v>
+        <v>2.8</v>
       </c>
       <c r="AH54" t="n">
         <v>215</v>
@@ -5763,10 +5802,10 @@
         <v>235</v>
       </c>
       <c r="AK54" t="n">
-        <v>129.21</v>
+        <v>129.07</v>
       </c>
       <c r="AL54" t="n">
-        <v>-2.03</v>
+        <v>-0.14</v>
       </c>
       <c r="AM54" t="n">
         <v>110</v>
@@ -5775,99 +5814,99 @@
         <v>142</v>
       </c>
       <c r="AP54" t="n">
-        <v>82.90000000000001</v>
+        <v>85.52</v>
       </c>
       <c r="AS54" t="n">
-        <v>15.23</v>
+        <v>15.82</v>
       </c>
       <c r="BL54" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B55" t="n">
-        <v>148.8</v>
+        <v>146.8</v>
       </c>
       <c r="C55" t="n">
-        <v>57.6</v>
+        <v>52.8</v>
       </c>
       <c r="D55" t="n">
-        <v>32.7</v>
+        <v>33.6</v>
       </c>
       <c r="E55" t="n">
-        <v>26.3</v>
+        <v>28.9</v>
       </c>
       <c r="F55" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="H55" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="I55" t="n">
-        <v>8.9</v>
+        <v>9.1</v>
       </c>
       <c r="J55" t="n">
-        <v>41.6</v>
+        <v>40.8</v>
       </c>
       <c r="K55" t="n">
-        <v>74.09999999999999</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="M55" t="n">
-        <v>7.4</v>
+        <v>5.6</v>
       </c>
       <c r="N55" t="n">
-        <v>35</v>
+        <v>33.1</v>
       </c>
       <c r="O55" t="n">
-        <v>42.4</v>
+        <v>38.7</v>
       </c>
       <c r="Q55" t="n">
-        <v>21.7</v>
+        <v>22</v>
       </c>
       <c r="R55" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>21.7</v>
+        <v>22</v>
       </c>
       <c r="V55" t="n">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="W55" t="n">
-        <v>24.1</v>
+        <v>22.9</v>
       </c>
       <c r="X55" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA55" t="n">
         <v>16.1</v>
       </c>
-      <c r="Y55" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>19</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>15.6</v>
-      </c>
       <c r="AB55" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="AC55" t="n">
-        <v>9.699999999999999</v>
+        <v>7</v>
       </c>
       <c r="AD55" t="n">
-        <v>6.3</v>
+        <v>4.5</v>
       </c>
       <c r="AF55" t="n">
-        <v>220.84</v>
+        <v>225.87</v>
       </c>
       <c r="AG55" t="n">
-        <v>2.8</v>
+        <v>5.03</v>
       </c>
       <c r="AH55" t="n">
         <v>215</v>
@@ -5876,10 +5915,10 @@
         <v>235</v>
       </c>
       <c r="AK55" t="n">
-        <v>129.07</v>
+        <v>130.73</v>
       </c>
       <c r="AL55" t="n">
-        <v>-0.14</v>
+        <v>1.66</v>
       </c>
       <c r="AM55" t="n">
         <v>110</v>
@@ -5888,81 +5927,36 @@
         <v>142</v>
       </c>
       <c r="AP55" t="n">
-        <v>85.52</v>
+        <v>88.2</v>
       </c>
       <c r="AS55" t="n">
-        <v>15.82</v>
+        <v>15.76</v>
       </c>
       <c r="BL55" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B56" t="n">
-        <v>146.8</v>
-      </c>
-      <c r="C56" t="n">
-        <v>52.8</v>
+        <v>133.9</v>
       </c>
       <c r="D56" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="E56" t="n">
-        <v>28.9</v>
+        <v>34.7</v>
       </c>
       <c r="F56" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="H56" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="I56" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="J56" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="K56" t="n">
-        <v>73.59999999999999</v>
-      </c>
-      <c r="M56" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="N56" t="n">
-        <v>33.1</v>
-      </c>
-      <c r="O56" t="n">
-        <v>38.7</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>22</v>
-      </c>
-      <c r="R56" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="S56" t="n">
-        <v>0</v>
-      </c>
-      <c r="T56" t="n">
-        <v>22</v>
+        <v>3.3</v>
       </c>
       <c r="Y56" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z56" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AA56" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="AF56" t="n">
-        <v>225.87</v>
-      </c>
-      <c r="AG56" t="n">
-        <v>5.03</v>
+        <v>15</v>
       </c>
       <c r="AH56" t="n">
         <v>215</v>
@@ -5970,49 +5964,37 @@
       <c r="AI56" t="n">
         <v>235</v>
       </c>
-      <c r="AK56" t="n">
-        <v>130.73</v>
-      </c>
-      <c r="AL56" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AM56" t="n">
         <v>110</v>
       </c>
       <c r="AN56" t="n">
         <v>142</v>
       </c>
-      <c r="AP56" t="n">
-        <v>88.2</v>
-      </c>
-      <c r="AS56" t="n">
-        <v>15.76</v>
-      </c>
       <c r="BL56" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B57" t="n">
-        <v>133.9</v>
+        <v>137.5</v>
       </c>
       <c r="D57" t="n">
-        <v>34.7</v>
+        <v>32.8</v>
       </c>
       <c r="F57" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="Y57" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z57" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="AA57" t="n">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="AH57" t="n">
         <v>215</v>
@@ -6027,30 +6009,75 @@
         <v>142</v>
       </c>
       <c r="BL57" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B58" t="n">
-        <v>137.5</v>
+        <v>157.1</v>
+      </c>
+      <c r="C58" t="n">
+        <v>73.09999999999999</v>
       </c>
       <c r="D58" t="n">
-        <v>32.8</v>
+        <v>31.7</v>
+      </c>
+      <c r="E58" t="n">
+        <v>26.1</v>
       </c>
       <c r="F58" t="n">
-        <v>2.3</v>
+        <v>2</v>
+      </c>
+      <c r="H58" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="I58" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="J58" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="K58" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="M58" t="n">
+        <v>6</v>
+      </c>
+      <c r="N58" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="O58" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="R58" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>23.8</v>
       </c>
       <c r="Y58" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="Z58" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA58" t="n">
-        <v>10.5</v>
+        <v>7.9</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>224.2</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>-1.67</v>
       </c>
       <c r="AH58" t="n">
         <v>215</v>
@@ -6058,82 +6085,94 @@
       <c r="AI58" t="n">
         <v>235</v>
       </c>
+      <c r="AK58" t="n">
+        <v>128.6</v>
+      </c>
+      <c r="AL58" t="n">
+        <v>-2.13</v>
+      </c>
       <c r="AM58" t="n">
         <v>110</v>
       </c>
       <c r="AN58" t="n">
         <v>142</v>
       </c>
+      <c r="AP58" t="n">
+        <v>81.18000000000001</v>
+      </c>
+      <c r="AS58" t="n">
+        <v>14.06</v>
+      </c>
       <c r="BL58" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B59" t="n">
-        <v>157.1</v>
+        <v>153.1</v>
       </c>
       <c r="C59" t="n">
-        <v>73.09999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="D59" t="n">
-        <v>31.7</v>
+        <v>32.2</v>
       </c>
       <c r="E59" t="n">
-        <v>26.1</v>
+        <v>25.9</v>
       </c>
       <c r="F59" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="H59" t="n">
-        <v>23.6</v>
+        <v>24.4</v>
       </c>
       <c r="I59" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="J59" t="n">
-        <v>40.5</v>
+        <v>39.6</v>
       </c>
       <c r="K59" t="n">
-        <v>73.5</v>
+        <v>73.3</v>
       </c>
       <c r="M59" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="N59" t="n">
-        <v>33.4</v>
+        <v>34.4</v>
       </c>
       <c r="O59" t="n">
-        <v>39.5</v>
+        <v>40.1</v>
       </c>
       <c r="Q59" t="n">
         <v>23.8</v>
       </c>
       <c r="R59" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="S59" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T59" t="n">
         <v>23.8</v>
       </c>
       <c r="Y59" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Z59" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA59" t="n">
         <v>12</v>
       </c>
-      <c r="AA59" t="n">
-        <v>7.9</v>
-      </c>
       <c r="AF59" t="n">
-        <v>224.2</v>
+        <v>223.35</v>
       </c>
       <c r="AG59" t="n">
-        <v>-1.67</v>
+        <v>-0.85</v>
       </c>
       <c r="AH59" t="n">
         <v>215</v>
@@ -6142,10 +6181,10 @@
         <v>235</v>
       </c>
       <c r="AK59" t="n">
-        <v>128.6</v>
+        <v>127.19</v>
       </c>
       <c r="AL59" t="n">
-        <v>-2.13</v>
+        <v>-1.41</v>
       </c>
       <c r="AM59" t="n">
         <v>110</v>
@@ -6154,81 +6193,81 @@
         <v>142</v>
       </c>
       <c r="AP59" t="n">
-        <v>81.18000000000001</v>
+        <v>81.06</v>
       </c>
       <c r="AS59" t="n">
-        <v>14.06</v>
+        <v>13.63</v>
       </c>
       <c r="BL59" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B60" t="n">
-        <v>153.1</v>
+        <v>145.5</v>
       </c>
       <c r="C60" t="n">
-        <v>69.59999999999999</v>
+        <v>62.3</v>
       </c>
       <c r="D60" t="n">
-        <v>32.2</v>
+        <v>34</v>
       </c>
       <c r="E60" t="n">
-        <v>25.9</v>
+        <v>22.5</v>
       </c>
       <c r="F60" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="H60" t="n">
-        <v>24.4</v>
+        <v>24.8</v>
       </c>
       <c r="I60" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J60" t="n">
-        <v>39.6</v>
+        <v>40.8</v>
       </c>
       <c r="K60" t="n">
-        <v>73.3</v>
+        <v>75</v>
       </c>
       <c r="M60" t="n">
-        <v>5.7</v>
+        <v>6.9</v>
       </c>
       <c r="N60" t="n">
-        <v>34.4</v>
+        <v>30.4</v>
       </c>
       <c r="O60" t="n">
-        <v>40.1</v>
+        <v>37.3</v>
       </c>
       <c r="Q60" t="n">
-        <v>23.8</v>
+        <v>22.1</v>
       </c>
       <c r="R60" t="n">
-        <v>3.8</v>
+        <v>4.9</v>
       </c>
       <c r="S60" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>23.8</v>
+        <v>22.1</v>
       </c>
       <c r="Y60" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="Z60" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AA60" t="n">
-        <v>12</v>
+        <v>12.9</v>
       </c>
       <c r="AF60" t="n">
-        <v>223.35</v>
+        <v>223.06</v>
       </c>
       <c r="AG60" t="n">
-        <v>-0.85</v>
+        <v>-0.29</v>
       </c>
       <c r="AH60" t="n">
         <v>215</v>
@@ -6237,10 +6276,10 @@
         <v>235</v>
       </c>
       <c r="AK60" t="n">
-        <v>127.19</v>
+        <v>129.17</v>
       </c>
       <c r="AL60" t="n">
-        <v>-1.41</v>
+        <v>1.98</v>
       </c>
       <c r="AM60" t="n">
         <v>110</v>
@@ -6249,36 +6288,36 @@
         <v>142</v>
       </c>
       <c r="AP60" t="n">
-        <v>81.06</v>
+        <v>82.36</v>
       </c>
       <c r="AS60" t="n">
-        <v>13.63</v>
+        <v>13.91</v>
       </c>
       <c r="BL60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B61" t="n">
-        <v>132.8</v>
+        <v>132.5</v>
       </c>
       <c r="D61" t="n">
-        <v>33.8</v>
+        <v>33.4</v>
       </c>
       <c r="F61" t="n">
         <v>2.3</v>
       </c>
       <c r="Y61" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="Z61" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AA61" t="n">
-        <v>16</v>
+        <v>10.5</v>
       </c>
       <c r="AH61" t="n">
         <v>215</v>
@@ -6293,30 +6332,30 @@
         <v>142</v>
       </c>
       <c r="BL61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B62" t="n">
-        <v>132.5</v>
+        <v>125</v>
       </c>
       <c r="D62" t="n">
-        <v>33.4</v>
+        <v>34.2</v>
       </c>
       <c r="F62" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="Y62" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Z62" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="AA62" t="n">
-        <v>10.5</v>
+        <v>16.5</v>
       </c>
       <c r="AH62" t="n">
         <v>215</v>
@@ -6331,7 +6370,7 @@
         <v>142</v>
       </c>
       <c r="BL62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -628,88 +628,88 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B2" t="n">
-        <v>161.1</v>
+        <v>176.4</v>
       </c>
       <c r="C2" t="n">
-        <v>67</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>31.9</v>
+        <v>32.7</v>
       </c>
       <c r="E2" t="n">
-        <v>31.5</v>
+        <v>35</v>
       </c>
       <c r="F2" t="n">
-        <v>7.7</v>
+        <v>6.8</v>
       </c>
       <c r="H2" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="I2" t="n">
         <v>11.4</v>
       </c>
       <c r="J2" t="n">
-        <v>41.1</v>
+        <v>41.5</v>
       </c>
       <c r="K2" t="n">
-        <v>75.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="M2" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="N2" t="n">
-        <v>35</v>
+        <v>36.4</v>
       </c>
       <c r="O2" t="n">
-        <v>37.2</v>
+        <v>39.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>20.5</v>
+        <v>22.3</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="T2" t="n">
-        <v>20.5</v>
+        <v>22.3</v>
       </c>
       <c r="V2" t="n">
-        <v>14.1</v>
+        <v>11.5</v>
       </c>
       <c r="W2" t="n">
-        <v>19.3</v>
+        <v>15.5</v>
       </c>
       <c r="X2" t="n">
-        <v>16.7</v>
+        <v>13.5</v>
       </c>
       <c r="Y2" t="n">
         <v>9</v>
       </c>
       <c r="Z2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA2" t="n">
-        <v>11.1</v>
+        <v>11.6</v>
       </c>
       <c r="AB2" t="n">
-        <v>-3.8</v>
+        <v>-5.6</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.3</v>
+        <v>-1.3</v>
       </c>
       <c r="AF2" t="n">
-        <v>225.51</v>
+        <v>220.92</v>
       </c>
       <c r="AG2" t="n">
-        <v>-6.48</v>
+        <v>-4.59</v>
       </c>
       <c r="AH2" t="n">
         <v>215</v>
@@ -718,10 +718,10 @@
         <v>235</v>
       </c>
       <c r="AK2" t="n">
-        <v>133.83</v>
+        <v>131.85</v>
       </c>
       <c r="AL2" t="n">
-        <v>-2.29</v>
+        <v>-1.98</v>
       </c>
       <c r="AM2" t="n">
         <v>110</v>
@@ -730,99 +730,99 @@
         <v>142</v>
       </c>
       <c r="AP2" t="n">
-        <v>82.93000000000001</v>
+        <v>79.75</v>
       </c>
       <c r="AS2" t="n">
-        <v>15.73</v>
+        <v>15.49</v>
       </c>
       <c r="BL2" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B3" t="n">
-        <v>176.4</v>
+        <v>181</v>
       </c>
       <c r="C3" t="n">
-        <v>77.09999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="D3" t="n">
-        <v>32.7</v>
+        <v>33</v>
       </c>
       <c r="E3" t="n">
-        <v>35</v>
+        <v>35.1</v>
       </c>
       <c r="F3" t="n">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="H3" t="n">
-        <v>23.2</v>
+        <v>22.8</v>
       </c>
       <c r="I3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="J3" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="K3" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N3" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="O3" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S3" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="T3" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="V3" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="W3" t="n">
+        <v>13</v>
+      </c>
+      <c r="X3" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA3" t="n">
         <v>11.4</v>
       </c>
-      <c r="J3" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="K3" t="n">
-        <v>76</v>
-      </c>
-      <c r="M3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N3" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="O3" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>14</v>
-      </c>
-      <c r="T3" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="V3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="W3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="X3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>11.6</v>
-      </c>
       <c r="AB3" t="n">
-        <v>-5.6</v>
+        <v>-6.1</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>-1.3</v>
+        <v>-0.9</v>
       </c>
       <c r="AF3" t="n">
         <v>220.92</v>
       </c>
       <c r="AG3" t="n">
-        <v>-4.59</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
         <v>215</v>
@@ -831,10 +831,10 @@
         <v>235</v>
       </c>
       <c r="AK3" t="n">
-        <v>131.85</v>
+        <v>130.06</v>
       </c>
       <c r="AL3" t="n">
-        <v>-1.98</v>
+        <v>-1.79</v>
       </c>
       <c r="AM3" t="n">
         <v>110</v>
@@ -843,99 +843,99 @@
         <v>142</v>
       </c>
       <c r="AP3" t="n">
-        <v>79.75</v>
+        <v>79.94</v>
       </c>
       <c r="AS3" t="n">
-        <v>15.49</v>
+        <v>14.93</v>
       </c>
       <c r="BL3" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B4" t="n">
-        <v>181</v>
+        <v>179.6</v>
       </c>
       <c r="C4" t="n">
-        <v>80.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>33</v>
+        <v>30.3</v>
       </c>
       <c r="E4" t="n">
-        <v>35.1</v>
+        <v>31.1</v>
       </c>
       <c r="F4" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="H4" t="n">
-        <v>22.8</v>
+        <v>21.5</v>
       </c>
       <c r="I4" t="n">
-        <v>11.2</v>
+        <v>10.8</v>
       </c>
       <c r="J4" t="n">
-        <v>41.9</v>
+        <v>42.3</v>
       </c>
       <c r="K4" t="n">
-        <v>75.90000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>2.9</v>
+        <v>4.3</v>
       </c>
       <c r="N4" t="n">
-        <v>36.9</v>
+        <v>37.1</v>
       </c>
       <c r="O4" t="n">
-        <v>39.8</v>
+        <v>41.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="R4" t="n">
+        <v>2</v>
+      </c>
+      <c r="S4" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="T4" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="V4" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="W4" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="X4" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AD4" t="n">
         <v>0.5</v>
       </c>
-      <c r="S4" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="T4" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="V4" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="W4" t="n">
-        <v>13</v>
-      </c>
-      <c r="X4" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>-6.1</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>-0.9</v>
-      </c>
       <c r="AF4" t="n">
-        <v>220.92</v>
+        <v>216.02</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AH4" t="n">
         <v>215</v>
@@ -944,10 +944,10 @@
         <v>235</v>
       </c>
       <c r="AK4" t="n">
-        <v>130.06</v>
+        <v>127.85</v>
       </c>
       <c r="AL4" t="n">
-        <v>-1.79</v>
+        <v>-2.21</v>
       </c>
       <c r="AM4" t="n">
         <v>110</v>
@@ -956,99 +956,99 @@
         <v>142</v>
       </c>
       <c r="AP4" t="n">
-        <v>79.94</v>
+        <v>82.2</v>
       </c>
       <c r="AS4" t="n">
-        <v>14.93</v>
+        <v>15.16</v>
       </c>
       <c r="BL4" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B5" t="n">
-        <v>179.6</v>
+        <v>170.4</v>
       </c>
       <c r="C5" t="n">
-        <v>81.90000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="D5" t="n">
-        <v>30.3</v>
+        <v>29.8</v>
       </c>
       <c r="E5" t="n">
-        <v>31.1</v>
+        <v>29.7</v>
       </c>
       <c r="F5" t="n">
-        <v>6.8</v>
+        <v>6.3</v>
       </c>
       <c r="H5" t="n">
-        <v>21.5</v>
+        <v>22.5</v>
       </c>
       <c r="I5" t="n">
-        <v>10.8</v>
+        <v>11.2</v>
       </c>
       <c r="J5" t="n">
-        <v>42.3</v>
+        <v>41.4</v>
       </c>
       <c r="K5" t="n">
-        <v>74.59999999999999</v>
+        <v>75</v>
       </c>
       <c r="M5" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="N5" t="n">
-        <v>37.1</v>
+        <v>36.6</v>
       </c>
       <c r="O5" t="n">
-        <v>41.4</v>
+        <v>41.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>22.6</v>
+        <v>23.3</v>
       </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="S5" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="T5" t="n">
-        <v>22.6</v>
+        <v>23.3</v>
       </c>
       <c r="V5" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="W5" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="X5" t="n">
         <v>12.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z5" t="n">
         <v>13</v>
       </c>
       <c r="AA5" t="n">
-        <v>11.1</v>
+        <v>12.7</v>
       </c>
       <c r="AB5" t="n">
-        <v>-3.4</v>
+        <v>1.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.4</v>
+        <v>7.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.5</v>
+        <v>4.7</v>
       </c>
       <c r="AF5" t="n">
         <v>216.02</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
         <v>215</v>
@@ -1057,10 +1057,10 @@
         <v>235</v>
       </c>
       <c r="AK5" t="n">
-        <v>127.85</v>
+        <v>128.54</v>
       </c>
       <c r="AL5" t="n">
-        <v>-2.21</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AM5" t="n">
         <v>110</v>
@@ -1069,99 +1069,66 @@
         <v>142</v>
       </c>
       <c r="AP5" t="n">
-        <v>82.2</v>
+        <v>84.73</v>
       </c>
       <c r="AS5" t="n">
-        <v>15.16</v>
+        <v>15.34</v>
       </c>
       <c r="BL5" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B6" t="n">
-        <v>170.4</v>
-      </c>
-      <c r="C6" t="n">
-        <v>78.5</v>
+        <v>156</v>
       </c>
       <c r="D6" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="E6" t="n">
-        <v>29.7</v>
+        <v>30.1</v>
       </c>
       <c r="F6" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="H6" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="I6" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="J6" t="n">
-        <v>41.4</v>
+        <v>6.8</v>
       </c>
       <c r="K6" t="n">
-        <v>75</v>
-      </c>
-      <c r="M6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="N6" t="n">
-        <v>36.6</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S6" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="T6" t="n">
-        <v>23.3</v>
+        <v>39.2</v>
       </c>
       <c r="V6" t="n">
-        <v>9.5</v>
+        <v>7.1</v>
       </c>
       <c r="W6" t="n">
-        <v>15.7</v>
+        <v>20.9</v>
       </c>
       <c r="X6" t="n">
-        <v>12.6</v>
+        <v>14</v>
       </c>
       <c r="Y6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Z6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA6" t="n">
-        <v>12.7</v>
+        <v>13.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.8</v>
+        <v>-0.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="AD6" t="n">
-        <v>4.7</v>
+        <v>2.4</v>
       </c>
       <c r="AF6" t="n">
-        <v>216.02</v>
+        <v>224.53</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH6" t="n">
         <v>215</v>
@@ -1170,10 +1137,10 @@
         <v>235</v>
       </c>
       <c r="AK6" t="n">
-        <v>128.54</v>
+        <v>130.92</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.6899999999999999</v>
+        <v>2.38</v>
       </c>
       <c r="AM6" t="n">
         <v>110</v>
@@ -1181,67 +1148,61 @@
       <c r="AN6" t="n">
         <v>142</v>
       </c>
-      <c r="AP6" t="n">
-        <v>84.73</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>15.34</v>
-      </c>
       <c r="BL6" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B7" t="n">
-        <v>156</v>
+        <v>147.8</v>
       </c>
       <c r="D7" t="n">
-        <v>30.1</v>
+        <v>32</v>
       </c>
       <c r="F7" t="n">
         <v>6.8</v>
       </c>
       <c r="K7" t="n">
-        <v>95.90000000000001</v>
+        <v>96.5</v>
       </c>
       <c r="O7" t="n">
-        <v>39.2</v>
+        <v>39.3</v>
       </c>
       <c r="V7" t="n">
-        <v>7.1</v>
+        <v>8</v>
       </c>
       <c r="W7" t="n">
-        <v>20.9</v>
+        <v>22.4</v>
       </c>
       <c r="X7" t="n">
-        <v>14</v>
+        <v>15.2</v>
       </c>
       <c r="Y7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA7" t="n">
         <v>13.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="AC7" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AF7" t="n">
-        <v>224.53</v>
+        <v>230.27</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.32</v>
+        <v>5.74</v>
       </c>
       <c r="AH7" t="n">
         <v>215</v>
@@ -1250,10 +1211,10 @@
         <v>235</v>
       </c>
       <c r="AK7" t="n">
-        <v>130.92</v>
+        <v>132.76</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.38</v>
+        <v>1.84</v>
       </c>
       <c r="AM7" t="n">
         <v>110</v>
@@ -1262,60 +1223,93 @@
         <v>142</v>
       </c>
       <c r="BL7" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="B8" t="n">
-        <v>147.8</v>
+        <v>149.1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>60</v>
       </c>
       <c r="D8" t="n">
-        <v>32</v>
+        <v>29</v>
+      </c>
+      <c r="E8" t="n">
+        <v>25.9</v>
       </c>
       <c r="F8" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
+      </c>
+      <c r="H8" t="n">
+        <v>24</v>
+      </c>
+      <c r="I8" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="J8" t="n">
+        <v>38.8</v>
       </c>
       <c r="K8" t="n">
-        <v>96.5</v>
+        <v>74.5</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N8" t="n">
+        <v>36.7</v>
       </c>
       <c r="O8" t="n">
-        <v>39.3</v>
+        <v>40.1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>7</v>
+      </c>
+      <c r="T8" t="n">
+        <v>21.7</v>
       </c>
       <c r="V8" t="n">
-        <v>8</v>
+        <v>10.3</v>
       </c>
       <c r="W8" t="n">
-        <v>22.4</v>
+        <v>24.4</v>
       </c>
       <c r="X8" t="n">
-        <v>15.2</v>
+        <v>17.4</v>
       </c>
       <c r="Y8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z8" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AA8" t="n">
-        <v>13.5</v>
+        <v>15.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0.3</v>
+        <v>-2.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.6</v>
+        <v>2.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.1</v>
+        <v>-0.1</v>
       </c>
       <c r="AF8" t="n">
-        <v>230.27</v>
+        <v>237.43</v>
       </c>
       <c r="AG8" t="n">
-        <v>5.74</v>
+        <v>7.16</v>
       </c>
       <c r="AH8" t="n">
         <v>215</v>
@@ -1324,10 +1318,10 @@
         <v>235</v>
       </c>
       <c r="AK8" t="n">
-        <v>132.76</v>
+        <v>134.95</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.84</v>
+        <v>2.19</v>
       </c>
       <c r="AM8" t="n">
         <v>110</v>
@@ -1335,94 +1329,67 @@
       <c r="AN8" t="n">
         <v>142</v>
       </c>
+      <c r="AP8" t="n">
+        <v>91.28</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>16.95</v>
+      </c>
       <c r="BL8" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="B9" t="n">
-        <v>149.1</v>
-      </c>
-      <c r="C9" t="n">
-        <v>60</v>
+        <v>143.9</v>
       </c>
       <c r="D9" t="n">
-        <v>29</v>
-      </c>
-      <c r="E9" t="n">
-        <v>25.9</v>
+        <v>32.9</v>
       </c>
       <c r="F9" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="H9" t="n">
-        <v>24</v>
-      </c>
-      <c r="I9" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="J9" t="n">
-        <v>38.8</v>
+        <v>6.8</v>
       </c>
       <c r="K9" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="M9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N9" t="n">
-        <v>36.7</v>
+        <v>96.2</v>
       </c>
       <c r="O9" t="n">
-        <v>40.1</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
-        <v>7</v>
-      </c>
-      <c r="T9" t="n">
-        <v>21.7</v>
+        <v>37.9</v>
       </c>
       <c r="V9" t="n">
-        <v>10.3</v>
+        <v>10</v>
       </c>
       <c r="W9" t="n">
-        <v>24.4</v>
+        <v>25.6</v>
       </c>
       <c r="X9" t="n">
-        <v>17.4</v>
+        <v>17.8</v>
       </c>
       <c r="Y9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AA9" t="n">
-        <v>15.7</v>
+        <v>16</v>
       </c>
       <c r="AB9" t="n">
-        <v>-2.4</v>
+        <v>-1.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0.1</v>
+        <v>0.9</v>
       </c>
       <c r="AF9" t="n">
-        <v>237.43</v>
+        <v>236.14</v>
       </c>
       <c r="AG9" t="n">
-        <v>7.16</v>
+        <v>-1.29</v>
       </c>
       <c r="AH9" t="n">
         <v>215</v>
@@ -1431,10 +1398,10 @@
         <v>235</v>
       </c>
       <c r="AK9" t="n">
-        <v>134.95</v>
+        <v>136.28</v>
       </c>
       <c r="AL9" t="n">
-        <v>2.19</v>
+        <v>1.33</v>
       </c>
       <c r="AM9" t="n">
         <v>110</v>
@@ -1442,67 +1409,94 @@
       <c r="AN9" t="n">
         <v>142</v>
       </c>
-      <c r="AP9" t="n">
-        <v>91.28</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>16.95</v>
-      </c>
       <c r="BL9" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B10" t="n">
-        <v>143.9</v>
+        <v>166.4</v>
+      </c>
+      <c r="C10" t="n">
+        <v>63.7</v>
       </c>
       <c r="D10" t="n">
-        <v>32.9</v>
+        <v>34.5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>36.4</v>
       </c>
       <c r="F10" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
+      </c>
+      <c r="H10" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="I10" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>39.9</v>
       </c>
       <c r="K10" t="n">
-        <v>96.2</v>
+        <v>75.2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>35.9</v>
       </c>
       <c r="O10" t="n">
-        <v>37.9</v>
+        <v>39</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="S10" t="n">
+        <v>6</v>
+      </c>
+      <c r="T10" t="n">
+        <v>20.3</v>
       </c>
       <c r="V10" t="n">
-        <v>10</v>
+        <v>11.9</v>
       </c>
       <c r="W10" t="n">
-        <v>25.6</v>
+        <v>27</v>
       </c>
       <c r="X10" t="n">
-        <v>17.8</v>
+        <v>19.4</v>
       </c>
       <c r="Y10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z10" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AA10" t="n">
-        <v>16</v>
+        <v>14.4</v>
       </c>
       <c r="AB10" t="n">
-        <v>-1.4</v>
+        <v>-3.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.9</v>
+        <v>-0.4</v>
       </c>
       <c r="AF10" t="n">
-        <v>236.14</v>
+        <v>236.13</v>
       </c>
       <c r="AG10" t="n">
-        <v>-1.29</v>
+        <v>-0.01</v>
       </c>
       <c r="AH10" t="n">
         <v>215</v>
@@ -1511,10 +1505,10 @@
         <v>235</v>
       </c>
       <c r="AK10" t="n">
-        <v>136.28</v>
+        <v>134.54</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.33</v>
+        <v>-1.74</v>
       </c>
       <c r="AM10" t="n">
         <v>110</v>
@@ -1522,94 +1516,100 @@
       <c r="AN10" t="n">
         <v>142</v>
       </c>
+      <c r="AP10" t="n">
+        <v>82.27</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>16.28</v>
+      </c>
       <c r="BL10" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B11" t="n">
-        <v>166.4</v>
+        <v>172.9</v>
       </c>
       <c r="C11" t="n">
-        <v>63.7</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>34.5</v>
+        <v>34.9</v>
       </c>
       <c r="E11" t="n">
-        <v>36.4</v>
+        <v>35.2</v>
       </c>
       <c r="F11" t="n">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="H11" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="I11" t="n">
-        <v>11.6</v>
+        <v>11.3</v>
       </c>
       <c r="J11" t="n">
-        <v>39.9</v>
+        <v>41.7</v>
       </c>
       <c r="K11" t="n">
-        <v>75.2</v>
+        <v>76.7</v>
       </c>
       <c r="M11" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="N11" t="n">
-        <v>35.9</v>
+        <v>34.8</v>
       </c>
       <c r="O11" t="n">
-        <v>39</v>
+        <v>37.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>20.3</v>
+        <v>19</v>
       </c>
       <c r="R11" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T11" t="n">
-        <v>20.3</v>
+        <v>19</v>
       </c>
       <c r="V11" t="n">
-        <v>11.9</v>
+        <v>14.4</v>
       </c>
       <c r="W11" t="n">
-        <v>27</v>
+        <v>18.7</v>
       </c>
       <c r="X11" t="n">
-        <v>19.4</v>
+        <v>16.6</v>
       </c>
       <c r="Y11" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Z11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA11" t="n">
-        <v>14.4</v>
+        <v>12.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>-3.5</v>
+        <v>-4.9</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0.4</v>
+        <v>-0.7</v>
       </c>
       <c r="AF11" t="n">
-        <v>236.13</v>
+        <v>218.6</v>
       </c>
       <c r="AG11" t="n">
-        <v>-0.01</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="AH11" t="n">
         <v>215</v>
@@ -1618,10 +1618,10 @@
         <v>235</v>
       </c>
       <c r="AK11" t="n">
-        <v>134.54</v>
+        <v>130.39</v>
       </c>
       <c r="AL11" t="n">
-        <v>-1.74</v>
+        <v>-4.15</v>
       </c>
       <c r="AM11" t="n">
         <v>110</v>
@@ -1630,99 +1630,99 @@
         <v>142</v>
       </c>
       <c r="AP11" t="n">
-        <v>82.27</v>
+        <v>78.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>16.28</v>
+        <v>15.79</v>
       </c>
       <c r="BL11" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B12" t="n">
-        <v>172.9</v>
+        <v>157.5</v>
       </c>
       <c r="C12" t="n">
-        <v>67.59999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="D12" t="n">
-        <v>34.9</v>
+        <v>33.2</v>
       </c>
       <c r="E12" t="n">
-        <v>35.2</v>
+        <v>27.7</v>
       </c>
       <c r="F12" t="n">
-        <v>7.3</v>
+        <v>3.6</v>
       </c>
       <c r="H12" t="n">
-        <v>23.6</v>
+        <v>23.4</v>
       </c>
       <c r="I12" t="n">
         <v>11.3</v>
       </c>
       <c r="J12" t="n">
-        <v>41.7</v>
+        <v>41.4</v>
       </c>
       <c r="K12" t="n">
-        <v>76.7</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="N12" t="n">
-        <v>34.8</v>
+        <v>34.9</v>
       </c>
       <c r="O12" t="n">
-        <v>37.2</v>
+        <v>37.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>19</v>
+        <v>21.6</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T12" t="n">
-        <v>19</v>
+        <v>21.6</v>
       </c>
       <c r="V12" t="n">
-        <v>14.4</v>
+        <v>15.1</v>
       </c>
       <c r="W12" t="n">
-        <v>18.7</v>
+        <v>23.1</v>
       </c>
       <c r="X12" t="n">
-        <v>16.6</v>
+        <v>19.1</v>
       </c>
       <c r="Y12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AA12" t="n">
-        <v>12.5</v>
+        <v>13.6</v>
       </c>
       <c r="AB12" t="n">
-        <v>-4.9</v>
+        <v>-0</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0.7</v>
+        <v>1.5</v>
       </c>
       <c r="AF12" t="n">
-        <v>218.6</v>
+        <v>218.84</v>
       </c>
       <c r="AG12" t="n">
-        <v>-9.380000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="AH12" t="n">
         <v>215</v>
@@ -1731,10 +1731,10 @@
         <v>235</v>
       </c>
       <c r="AK12" t="n">
-        <v>130.39</v>
+        <v>133.09</v>
       </c>
       <c r="AL12" t="n">
-        <v>-4.15</v>
+        <v>2.7</v>
       </c>
       <c r="AM12" t="n">
         <v>110</v>
@@ -1743,99 +1743,66 @@
         <v>142</v>
       </c>
       <c r="AP12" t="n">
-        <v>78.5</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="AS12" t="n">
-        <v>15.79</v>
+        <v>15.63</v>
       </c>
       <c r="BL12" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B13" t="n">
-        <v>157.5</v>
-      </c>
-      <c r="C13" t="n">
-        <v>68.5</v>
+        <v>137.6</v>
       </c>
       <c r="D13" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="E13" t="n">
-        <v>27.7</v>
+        <v>35</v>
       </c>
       <c r="F13" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H13" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="I13" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J13" t="n">
-        <v>41.4</v>
+        <v>6.5</v>
       </c>
       <c r="K13" t="n">
-        <v>76.09999999999999</v>
-      </c>
-      <c r="M13" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="N13" t="n">
-        <v>34.9</v>
+        <v>96.7</v>
       </c>
       <c r="O13" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>9</v>
-      </c>
-      <c r="T13" t="n">
-        <v>21.6</v>
+        <v>35.1</v>
       </c>
       <c r="V13" t="n">
-        <v>15.1</v>
+        <v>13.6</v>
       </c>
       <c r="W13" t="n">
-        <v>23.1</v>
+        <v>24.4</v>
       </c>
       <c r="X13" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="Y13" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Z13" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AA13" t="n">
-        <v>13.6</v>
+        <v>17.5</v>
       </c>
       <c r="AB13" t="n">
         <v>-0</v>
       </c>
       <c r="AC13" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="AF13" t="n">
-        <v>218.84</v>
+        <v>221.78</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.25</v>
+        <v>2.94</v>
       </c>
       <c r="AH13" t="n">
         <v>215</v>
@@ -1844,10 +1811,10 @@
         <v>235</v>
       </c>
       <c r="AK13" t="n">
-        <v>133.09</v>
+        <v>138.76</v>
       </c>
       <c r="AL13" t="n">
-        <v>2.7</v>
+        <v>5.67</v>
       </c>
       <c r="AM13" t="n">
         <v>110</v>
@@ -1855,67 +1822,61 @@
       <c r="AN13" t="n">
         <v>142</v>
       </c>
-      <c r="AP13" t="n">
-        <v>83.09999999999999</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>15.63</v>
-      </c>
       <c r="BL13" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B14" t="n">
-        <v>137.6</v>
+        <v>132.5</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>33.6</v>
       </c>
       <c r="F14" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="K14" t="n">
-        <v>96.7</v>
+        <v>97.8</v>
       </c>
       <c r="O14" t="n">
-        <v>35.1</v>
+        <v>31.6</v>
       </c>
       <c r="V14" t="n">
-        <v>13.6</v>
+        <v>14.8</v>
       </c>
       <c r="W14" t="n">
-        <v>24.4</v>
+        <v>24.7</v>
       </c>
       <c r="X14" t="n">
-        <v>19</v>
+        <v>19.8</v>
       </c>
       <c r="Y14" t="n">
         <v>14</v>
       </c>
       <c r="Z14" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AA14" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0</v>
+        <v>0.6</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="AF14" t="n">
-        <v>221.78</v>
+        <v>224.78</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="AH14" t="n">
         <v>215</v>
@@ -1924,10 +1885,10 @@
         <v>235</v>
       </c>
       <c r="AK14" t="n">
-        <v>138.76</v>
+        <v>143.55</v>
       </c>
       <c r="AL14" t="n">
-        <v>5.67</v>
+        <v>4.79</v>
       </c>
       <c r="AM14" t="n">
         <v>110</v>
@@ -1936,60 +1897,93 @@
         <v>142</v>
       </c>
       <c r="BL14" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B15" t="n">
-        <v>132.5</v>
+        <v>137.2</v>
+      </c>
+      <c r="C15" t="n">
+        <v>56.3</v>
       </c>
       <c r="D15" t="n">
-        <v>33.6</v>
+        <v>32.1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>21.2</v>
       </c>
       <c r="F15" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="I15" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="J15" t="n">
+        <v>40.4</v>
       </c>
       <c r="K15" t="n">
-        <v>97.8</v>
+        <v>75.7</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N15" t="n">
+        <v>29</v>
       </c>
       <c r="O15" t="n">
-        <v>31.6</v>
+        <v>32.6</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>21.6</v>
       </c>
       <c r="V15" t="n">
-        <v>14.8</v>
+        <v>10.7</v>
       </c>
       <c r="W15" t="n">
-        <v>24.7</v>
+        <v>24.3</v>
       </c>
       <c r="X15" t="n">
-        <v>19.8</v>
+        <v>17.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Z15" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AA15" t="n">
-        <v>16.5</v>
+        <v>15.4</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="AF15" t="n">
-        <v>224.78</v>
+        <v>232.22</v>
       </c>
       <c r="AG15" t="n">
-        <v>3</v>
+        <v>7.43</v>
       </c>
       <c r="AH15" t="n">
         <v>215</v>
@@ -1998,10 +1992,10 @@
         <v>235</v>
       </c>
       <c r="AK15" t="n">
-        <v>143.55</v>
+        <v>143.61</v>
       </c>
       <c r="AL15" t="n">
-        <v>4.79</v>
+        <v>0.06</v>
       </c>
       <c r="AM15" t="n">
         <v>110</v>
@@ -2009,52 +2003,58 @@
       <c r="AN15" t="n">
         <v>142</v>
       </c>
+      <c r="AP15" t="n">
+        <v>89.31999999999999</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>18.02</v>
+      </c>
       <c r="BL15" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="B16" t="n">
-        <v>137.2</v>
+        <v>157.5</v>
       </c>
       <c r="C16" t="n">
-        <v>56.3</v>
+        <v>59.6</v>
       </c>
       <c r="D16" t="n">
-        <v>32.1</v>
+        <v>35</v>
       </c>
       <c r="E16" t="n">
-        <v>21.2</v>
+        <v>30.6</v>
       </c>
       <c r="F16" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="H16" t="n">
-        <v>23.7</v>
+        <v>24.2</v>
       </c>
       <c r="I16" t="n">
-        <v>11.6</v>
+        <v>11.2</v>
       </c>
       <c r="J16" t="n">
-        <v>40.4</v>
+        <v>38.9</v>
       </c>
       <c r="K16" t="n">
-        <v>75.7</v>
+        <v>74.3</v>
       </c>
       <c r="M16" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="N16" t="n">
-        <v>29</v>
+        <v>33.4</v>
       </c>
       <c r="O16" t="n">
-        <v>32.6</v>
+        <v>37.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="R16" t="n">
         <v>1.3</v>
@@ -2063,40 +2063,40 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="V16" t="n">
-        <v>10.7</v>
+        <v>13</v>
       </c>
       <c r="W16" t="n">
-        <v>24.3</v>
+        <v>26.3</v>
       </c>
       <c r="X16" t="n">
-        <v>17.5</v>
+        <v>19.6</v>
       </c>
       <c r="Y16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA16" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.9</v>
+        <v>-2.1</v>
       </c>
       <c r="AC16" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="AF16" t="n">
-        <v>232.22</v>
+        <v>229.69</v>
       </c>
       <c r="AG16" t="n">
-        <v>7.43</v>
+        <v>-2.53</v>
       </c>
       <c r="AH16" t="n">
         <v>215</v>
@@ -2105,10 +2105,10 @@
         <v>235</v>
       </c>
       <c r="AK16" t="n">
-        <v>143.61</v>
+        <v>136.96</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.06</v>
+        <v>-6.65</v>
       </c>
       <c r="AM16" t="n">
         <v>110</v>
@@ -2117,99 +2117,99 @@
         <v>142</v>
       </c>
       <c r="AP16" t="n">
-        <v>89.31999999999999</v>
+        <v>86.59</v>
       </c>
       <c r="AS16" t="n">
-        <v>18.02</v>
+        <v>16.96</v>
       </c>
       <c r="BL16" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B17" t="n">
-        <v>157.5</v>
+        <v>159.6</v>
       </c>
       <c r="C17" t="n">
-        <v>59.6</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>35</v>
+        <v>34.5</v>
       </c>
       <c r="E17" t="n">
-        <v>30.6</v>
+        <v>31.1</v>
       </c>
       <c r="F17" t="n">
-        <v>7.5</v>
+        <v>5.7</v>
       </c>
       <c r="H17" t="n">
-        <v>24.2</v>
+        <v>23.8</v>
       </c>
       <c r="I17" t="n">
-        <v>11.2</v>
+        <v>10.8</v>
       </c>
       <c r="J17" t="n">
-        <v>38.9</v>
+        <v>40.5</v>
       </c>
       <c r="K17" t="n">
-        <v>74.3</v>
+        <v>75.2</v>
       </c>
       <c r="M17" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="N17" t="n">
-        <v>33.4</v>
+        <v>34.3</v>
       </c>
       <c r="O17" t="n">
-        <v>37.1</v>
+        <v>38.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T17" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="V17" t="n">
-        <v>13</v>
+        <v>17.5</v>
       </c>
       <c r="W17" t="n">
-        <v>26.3</v>
+        <v>22.5</v>
       </c>
       <c r="X17" t="n">
-        <v>19.6</v>
+        <v>20</v>
       </c>
       <c r="Y17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA17" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>-2.1</v>
+        <v>-2.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="AF17" t="n">
-        <v>229.69</v>
+        <v>228.57</v>
       </c>
       <c r="AG17" t="n">
-        <v>-2.53</v>
+        <v>-1.14</v>
       </c>
       <c r="AH17" t="n">
         <v>215</v>
@@ -2218,10 +2218,10 @@
         <v>235</v>
       </c>
       <c r="AK17" t="n">
-        <v>136.96</v>
+        <v>133.01</v>
       </c>
       <c r="AL17" t="n">
-        <v>-6.65</v>
+        <v>-3.95</v>
       </c>
       <c r="AM17" t="n">
         <v>110</v>
@@ -2230,99 +2230,99 @@
         <v>142</v>
       </c>
       <c r="AP17" t="n">
-        <v>86.59</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="AS17" t="n">
-        <v>16.96</v>
+        <v>15.95</v>
       </c>
       <c r="BL17" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B18" t="n">
-        <v>159.6</v>
+        <v>160.4</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>62.6</v>
       </c>
       <c r="D18" t="n">
-        <v>34.5</v>
+        <v>35</v>
       </c>
       <c r="E18" t="n">
-        <v>31.1</v>
+        <v>32.2</v>
       </c>
       <c r="F18" t="n">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="H18" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="I18" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="J18" t="n">
-        <v>40.5</v>
+        <v>41.1</v>
       </c>
       <c r="K18" t="n">
-        <v>75.2</v>
+        <v>75.7</v>
       </c>
       <c r="M18" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="N18" t="n">
-        <v>34.3</v>
+        <v>32.6</v>
       </c>
       <c r="O18" t="n">
-        <v>38.2</v>
+        <v>38</v>
       </c>
       <c r="Q18" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T18" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="V18" t="n">
-        <v>17.5</v>
+        <v>16.4</v>
       </c>
       <c r="W18" t="n">
-        <v>22.5</v>
+        <v>22.8</v>
       </c>
       <c r="X18" t="n">
-        <v>20</v>
+        <v>19.6</v>
       </c>
       <c r="Y18" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Z18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA18" t="n">
-        <v>13.5</v>
+        <v>14.1</v>
       </c>
       <c r="AB18" t="n">
-        <v>-2.2</v>
+        <v>-3.1</v>
       </c>
       <c r="AC18" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="AF18" t="n">
-        <v>228.57</v>
+        <v>225.08</v>
       </c>
       <c r="AG18" t="n">
-        <v>-1.14</v>
+        <v>-3.5</v>
       </c>
       <c r="AH18" t="n">
         <v>215</v>
@@ -2331,10 +2331,10 @@
         <v>235</v>
       </c>
       <c r="AK18" t="n">
-        <v>133.01</v>
+        <v>135.24</v>
       </c>
       <c r="AL18" t="n">
-        <v>-3.95</v>
+        <v>2.23</v>
       </c>
       <c r="AM18" t="n">
         <v>110</v>
@@ -2343,99 +2343,99 @@
         <v>142</v>
       </c>
       <c r="AP18" t="n">
-        <v>84.59999999999999</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="AS18" t="n">
-        <v>15.95</v>
+        <v>15.4</v>
       </c>
       <c r="BL18" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B19" t="n">
-        <v>160.4</v>
+        <v>161.7</v>
       </c>
       <c r="C19" t="n">
-        <v>62.6</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="D19" t="n">
-        <v>35</v>
+        <v>34.9</v>
       </c>
       <c r="E19" t="n">
-        <v>32.2</v>
+        <v>27.3</v>
       </c>
       <c r="F19" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H19" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="I19" t="n">
-        <v>10.7</v>
+        <v>10.3</v>
       </c>
       <c r="J19" t="n">
-        <v>41.1</v>
+        <v>42.6</v>
       </c>
       <c r="K19" t="n">
-        <v>75.7</v>
+        <v>77</v>
       </c>
       <c r="M19" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="N19" t="n">
-        <v>32.6</v>
+        <v>31.5</v>
       </c>
       <c r="O19" t="n">
-        <v>38</v>
+        <v>37.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="R19" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T19" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="V19" t="n">
-        <v>16.4</v>
+        <v>12.7</v>
       </c>
       <c r="W19" t="n">
-        <v>22.8</v>
+        <v>27</v>
       </c>
       <c r="X19" t="n">
-        <v>19.6</v>
+        <v>19.9</v>
       </c>
       <c r="Y19" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Z19" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AA19" t="n">
-        <v>14.1</v>
+        <v>11.4</v>
       </c>
       <c r="AB19" t="n">
-        <v>-3.1</v>
+        <v>-5.2</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.6</v>
+        <v>-0.3</v>
       </c>
       <c r="AF19" t="n">
-        <v>225.08</v>
+        <v>225</v>
       </c>
       <c r="AG19" t="n">
-        <v>-3.5</v>
+        <v>-0.08</v>
       </c>
       <c r="AH19" t="n">
         <v>215</v>
@@ -2444,10 +2444,10 @@
         <v>235</v>
       </c>
       <c r="AK19" t="n">
-        <v>135.24</v>
+        <v>134.62</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.23</v>
+        <v>-0.62</v>
       </c>
       <c r="AM19" t="n">
         <v>110</v>
@@ -2456,99 +2456,60 @@
         <v>142</v>
       </c>
       <c r="AP19" t="n">
-        <v>84.09999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="AS19" t="n">
-        <v>15.4</v>
+        <v>13.86</v>
       </c>
       <c r="BL19" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B20" t="n">
-        <v>161.7</v>
-      </c>
-      <c r="C20" t="n">
-        <v>71.09999999999999</v>
+        <v>151.5</v>
       </c>
       <c r="D20" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="E20" t="n">
-        <v>27.3</v>
+        <v>35.1</v>
       </c>
       <c r="F20" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H20" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I20" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="J20" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="K20" t="n">
-        <v>77</v>
-      </c>
-      <c r="M20" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="N20" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="O20" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>21</v>
-      </c>
-      <c r="R20" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="S20" t="n">
-        <v>6</v>
-      </c>
-      <c r="T20" t="n">
-        <v>21</v>
+        <v>5.4</v>
       </c>
       <c r="V20" t="n">
-        <v>12.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W20" t="n">
-        <v>27</v>
+        <v>19.4</v>
       </c>
       <c r="X20" t="n">
-        <v>19.9</v>
+        <v>14</v>
       </c>
       <c r="Y20" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA20" t="n">
         <v>9</v>
       </c>
-      <c r="Z20" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>11.4</v>
-      </c>
       <c r="AB20" t="n">
-        <v>-5.2</v>
+        <v>-4.7</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.6</v>
+        <v>1.9</v>
       </c>
       <c r="AD20" t="n">
-        <v>-0.3</v>
+        <v>-1.4</v>
       </c>
       <c r="AF20" t="n">
-        <v>225</v>
+        <v>221.37</v>
       </c>
       <c r="AG20" t="n">
-        <v>-0.08</v>
+        <v>0.05</v>
       </c>
       <c r="AH20" t="n">
         <v>215</v>
@@ -2557,10 +2518,10 @@
         <v>235</v>
       </c>
       <c r="AK20" t="n">
-        <v>134.62</v>
+        <v>135.21</v>
       </c>
       <c r="AL20" t="n">
-        <v>-0.62</v>
+        <v>0.59</v>
       </c>
       <c r="AM20" t="n">
         <v>110</v>
@@ -2568,61 +2529,61 @@
       <c r="AN20" t="n">
         <v>142</v>
       </c>
-      <c r="AP20" t="n">
-        <v>80.2</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>13.86</v>
-      </c>
       <c r="BL20" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B21" t="n">
-        <v>151.5</v>
+        <v>145.2</v>
       </c>
       <c r="D21" t="n">
-        <v>35.1</v>
+        <v>33.5</v>
       </c>
       <c r="F21" t="n">
-        <v>5.4</v>
+        <v>5</v>
+      </c>
+      <c r="K21" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="O21" t="n">
+        <v>35.5</v>
       </c>
       <c r="V21" t="n">
-        <v>8.699999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="W21" t="n">
-        <v>19.4</v>
+        <v>19.2</v>
       </c>
       <c r="X21" t="n">
-        <v>14</v>
+        <v>13.1</v>
       </c>
       <c r="Y21" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z21" t="n">
         <v>13</v>
       </c>
       <c r="AA21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB21" t="n">
-        <v>-4.7</v>
+        <v>-5.4</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>-1.4</v>
+        <v>-1.5</v>
       </c>
       <c r="AF21" t="n">
-        <v>221.37</v>
+        <v>224.37</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.05</v>
+        <v>3</v>
       </c>
       <c r="AH21" t="n">
         <v>215</v>
@@ -2631,10 +2592,10 @@
         <v>235</v>
       </c>
       <c r="AK21" t="n">
-        <v>135.21</v>
+        <v>135.61</v>
       </c>
       <c r="AL21" t="n">
-        <v>0.59</v>
+        <v>0.4</v>
       </c>
       <c r="AM21" t="n">
         <v>110</v>
@@ -2643,60 +2604,60 @@
         <v>142</v>
       </c>
       <c r="BL21" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B22" t="n">
-        <v>145.2</v>
+        <v>146.3</v>
       </c>
       <c r="D22" t="n">
-        <v>33.5</v>
+        <v>33.4</v>
       </c>
       <c r="F22" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="K22" t="n">
-        <v>100.3</v>
+        <v>98.2</v>
       </c>
       <c r="O22" t="n">
-        <v>35.5</v>
+        <v>35.1</v>
       </c>
       <c r="V22" t="n">
-        <v>7.1</v>
+        <v>4.9</v>
       </c>
       <c r="W22" t="n">
-        <v>19.2</v>
+        <v>16.4</v>
       </c>
       <c r="X22" t="n">
-        <v>13.1</v>
+        <v>10.6</v>
       </c>
       <c r="Y22" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z22" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB22" t="n">
-        <v>-5.4</v>
+        <v>-6.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.4</v>
+        <v>-0.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>-1.5</v>
+        <v>-3.3</v>
       </c>
       <c r="AF22" t="n">
-        <v>224.37</v>
+        <v>225.93</v>
       </c>
       <c r="AG22" t="n">
-        <v>3</v>
+        <v>1.56</v>
       </c>
       <c r="AH22" t="n">
         <v>215</v>
@@ -2705,10 +2666,10 @@
         <v>235</v>
       </c>
       <c r="AK22" t="n">
-        <v>135.61</v>
+        <v>135.28</v>
       </c>
       <c r="AL22" t="n">
-        <v>0.4</v>
+        <v>-0.33</v>
       </c>
       <c r="AM22" t="n">
         <v>110</v>
@@ -2717,60 +2678,93 @@
         <v>142</v>
       </c>
       <c r="BL22" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B23" t="n">
-        <v>146.3</v>
+        <v>182.8</v>
+      </c>
+      <c r="C23" t="n">
+        <v>86.8</v>
       </c>
       <c r="D23" t="n">
-        <v>33.4</v>
+        <v>31.8</v>
+      </c>
+      <c r="E23" t="n">
+        <v>33</v>
       </c>
       <c r="F23" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
+      </c>
+      <c r="H23" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="I23" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J23" t="n">
+        <v>41.1</v>
       </c>
       <c r="K23" t="n">
-        <v>98.2</v>
+        <v>74.2</v>
+      </c>
+      <c r="M23" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="N23" t="n">
+        <v>33.5</v>
       </c>
       <c r="O23" t="n">
-        <v>35.1</v>
+        <v>38.4</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="R23" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S23" t="n">
+        <v>15</v>
+      </c>
+      <c r="T23" t="n">
+        <v>22.4</v>
       </c>
       <c r="V23" t="n">
-        <v>4.9</v>
+        <v>9.1</v>
       </c>
       <c r="W23" t="n">
-        <v>16.4</v>
+        <v>15</v>
       </c>
       <c r="X23" t="n">
-        <v>10.6</v>
+        <v>12.1</v>
       </c>
       <c r="Y23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z23" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AA23" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>-6.4</v>
+        <v>-10.5</v>
       </c>
       <c r="AC23" t="n">
-        <v>-0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>-3.3</v>
+        <v>-5.1</v>
       </c>
       <c r="AF23" t="n">
-        <v>225.93</v>
+        <v>218.63</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.56</v>
+        <v>-7.3</v>
       </c>
       <c r="AH23" t="n">
         <v>215</v>
@@ -2779,10 +2773,10 @@
         <v>235</v>
       </c>
       <c r="AK23" t="n">
-        <v>135.28</v>
+        <v>126.27</v>
       </c>
       <c r="AL23" t="n">
-        <v>-0.33</v>
+        <v>-9.01</v>
       </c>
       <c r="AM23" t="n">
         <v>110</v>
@@ -2790,94 +2784,100 @@
       <c r="AN23" t="n">
         <v>142</v>
       </c>
+      <c r="AP23" t="n">
+        <v>82.66</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>14.7</v>
+      </c>
       <c r="BL23" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B24" t="n">
-        <v>182.8</v>
+        <v>181.8</v>
       </c>
       <c r="C24" t="n">
-        <v>86.8</v>
+        <v>86.5</v>
       </c>
       <c r="D24" t="n">
-        <v>31.8</v>
+        <v>31.4</v>
       </c>
       <c r="E24" t="n">
-        <v>33</v>
+        <v>34.2</v>
       </c>
       <c r="F24" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="H24" t="n">
-        <v>23.5</v>
+        <v>24.4</v>
       </c>
       <c r="I24" t="n">
-        <v>9.6</v>
+        <v>10.4</v>
       </c>
       <c r="J24" t="n">
-        <v>41.1</v>
+        <v>41.9</v>
       </c>
       <c r="K24" t="n">
-        <v>74.2</v>
+        <v>76.8</v>
       </c>
       <c r="M24" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="N24" t="n">
-        <v>33.5</v>
+        <v>35.7</v>
       </c>
       <c r="O24" t="n">
-        <v>38.4</v>
+        <v>39.8</v>
       </c>
       <c r="Q24" t="n">
-        <v>22.4</v>
+        <v>23</v>
       </c>
       <c r="R24" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>20.1</v>
       </c>
       <c r="T24" t="n">
-        <v>22.4</v>
+        <v>23</v>
       </c>
       <c r="V24" t="n">
-        <v>9.1</v>
+        <v>7.1</v>
       </c>
       <c r="W24" t="n">
-        <v>15</v>
+        <v>14.8</v>
       </c>
       <c r="X24" t="n">
-        <v>12.1</v>
+        <v>10.9</v>
       </c>
       <c r="Y24" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z24" t="n">
         <v>12</v>
       </c>
       <c r="AA24" t="n">
-        <v>8.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AB24" t="n">
-        <v>-10.5</v>
+        <v>-4.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>-5.1</v>
+        <v>-1.4</v>
       </c>
       <c r="AF24" t="n">
-        <v>218.63</v>
+        <v>216.39</v>
       </c>
       <c r="AG24" t="n">
-        <v>-7.3</v>
+        <v>-2.23</v>
       </c>
       <c r="AH24" t="n">
         <v>215</v>
@@ -2886,10 +2886,10 @@
         <v>235</v>
       </c>
       <c r="AK24" t="n">
-        <v>126.27</v>
+        <v>123.32</v>
       </c>
       <c r="AL24" t="n">
-        <v>-9.01</v>
+        <v>-2.95</v>
       </c>
       <c r="AM24" t="n">
         <v>110</v>
@@ -2898,99 +2898,99 @@
         <v>142</v>
       </c>
       <c r="AP24" t="n">
-        <v>82.66</v>
+        <v>79.08</v>
       </c>
       <c r="AS24" t="n">
-        <v>14.7</v>
+        <v>13.91</v>
       </c>
       <c r="BL24" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B25" t="n">
-        <v>181.8</v>
+        <v>183</v>
       </c>
       <c r="C25" t="n">
-        <v>86.5</v>
+        <v>84.7</v>
       </c>
       <c r="D25" t="n">
-        <v>31.4</v>
+        <v>30.9</v>
       </c>
       <c r="E25" t="n">
-        <v>34.2</v>
+        <v>33.7</v>
       </c>
       <c r="F25" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="H25" t="n">
-        <v>24.4</v>
+        <v>23.4</v>
       </c>
       <c r="I25" t="n">
-        <v>10.4</v>
+        <v>10.6</v>
       </c>
       <c r="J25" t="n">
-        <v>41.9</v>
+        <v>42.3</v>
       </c>
       <c r="K25" t="n">
-        <v>76.8</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="N25" t="n">
-        <v>35.7</v>
+        <v>36.7</v>
       </c>
       <c r="O25" t="n">
-        <v>39.8</v>
+        <v>40.8</v>
       </c>
       <c r="Q25" t="n">
-        <v>23</v>
+        <v>23.6</v>
       </c>
       <c r="R25" t="n">
         <v>1.8</v>
       </c>
       <c r="S25" t="n">
-        <v>20.1</v>
+        <v>20.8</v>
       </c>
       <c r="T25" t="n">
-        <v>23</v>
+        <v>23.6</v>
       </c>
       <c r="V25" t="n">
-        <v>7.1</v>
+        <v>5.7</v>
       </c>
       <c r="W25" t="n">
-        <v>14.8</v>
+        <v>16.1</v>
       </c>
       <c r="X25" t="n">
         <v>10.9</v>
       </c>
       <c r="Y25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA25" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AB25" t="n">
-        <v>-4.5</v>
+        <v>0.8</v>
       </c>
       <c r="AC25" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD25" t="n">
         <v>1.8</v>
       </c>
-      <c r="AD25" t="n">
-        <v>-1.4</v>
-      </c>
       <c r="AF25" t="n">
-        <v>216.39</v>
+        <v>217.16</v>
       </c>
       <c r="AG25" t="n">
-        <v>-2.23</v>
+        <v>0.76</v>
       </c>
       <c r="AH25" t="n">
         <v>215</v>
@@ -2999,10 +2999,10 @@
         <v>235</v>
       </c>
       <c r="AK25" t="n">
-        <v>123.32</v>
+        <v>117.87</v>
       </c>
       <c r="AL25" t="n">
-        <v>-2.95</v>
+        <v>-5.45</v>
       </c>
       <c r="AM25" t="n">
         <v>110</v>
@@ -3011,99 +3011,66 @@
         <v>142</v>
       </c>
       <c r="AP25" t="n">
-        <v>79.08</v>
+        <v>78.56</v>
       </c>
       <c r="AS25" t="n">
-        <v>13.91</v>
+        <v>13.45</v>
       </c>
       <c r="BL25" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B26" t="n">
-        <v>183</v>
-      </c>
-      <c r="C26" t="n">
-        <v>84.7</v>
+        <v>163.8</v>
       </c>
       <c r="D26" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="E26" t="n">
-        <v>33.7</v>
+        <v>29</v>
       </c>
       <c r="F26" t="n">
-        <v>7</v>
-      </c>
-      <c r="H26" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="I26" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="J26" t="n">
-        <v>42.3</v>
+        <v>6.5</v>
       </c>
       <c r="K26" t="n">
-        <v>76.40000000000001</v>
-      </c>
-      <c r="M26" t="n">
-        <v>4</v>
-      </c>
-      <c r="N26" t="n">
-        <v>36.7</v>
+        <v>101.2</v>
       </c>
       <c r="O26" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S26" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="T26" t="n">
-        <v>23.6</v>
+        <v>40.2</v>
       </c>
       <c r="V26" t="n">
-        <v>5.7</v>
+        <v>6.3</v>
       </c>
       <c r="W26" t="n">
-        <v>16.1</v>
+        <v>17.2</v>
       </c>
       <c r="X26" t="n">
-        <v>10.9</v>
+        <v>11.8</v>
       </c>
       <c r="Y26" t="n">
         <v>8</v>
       </c>
       <c r="Z26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA26" t="n">
         <v>10</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.7</v>
+        <v>4.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="AF26" t="n">
-        <v>217.16</v>
+        <v>220.31</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.76</v>
+        <v>3.16</v>
       </c>
       <c r="AH26" t="n">
         <v>215</v>
@@ -3112,10 +3079,10 @@
         <v>235</v>
       </c>
       <c r="AK26" t="n">
-        <v>117.87</v>
+        <v>116.52</v>
       </c>
       <c r="AL26" t="n">
-        <v>-5.45</v>
+        <v>-1.35</v>
       </c>
       <c r="AM26" t="n">
         <v>110</v>
@@ -3123,67 +3090,61 @@
       <c r="AN26" t="n">
         <v>142</v>
       </c>
-      <c r="AP26" t="n">
-        <v>78.56</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>13.45</v>
-      </c>
       <c r="BL26" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B27" t="n">
-        <v>163.8</v>
+        <v>155.9</v>
       </c>
       <c r="D27" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F27" t="n">
         <v>6.5</v>
       </c>
       <c r="K27" t="n">
-        <v>101.2</v>
+        <v>99.3</v>
       </c>
       <c r="O27" t="n">
-        <v>40.2</v>
+        <v>38.5</v>
       </c>
       <c r="V27" t="n">
-        <v>6.3</v>
+        <v>8.9</v>
       </c>
       <c r="W27" t="n">
-        <v>17.2</v>
+        <v>15.8</v>
       </c>
       <c r="X27" t="n">
-        <v>11.8</v>
+        <v>12.4</v>
       </c>
       <c r="Y27" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA27" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AC27" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="AF27" t="n">
-        <v>220.31</v>
+        <v>221.99</v>
       </c>
       <c r="AG27" t="n">
-        <v>3.16</v>
+        <v>1.67</v>
       </c>
       <c r="AH27" t="n">
         <v>215</v>
@@ -3192,10 +3153,10 @@
         <v>235</v>
       </c>
       <c r="AK27" t="n">
-        <v>116.52</v>
+        <v>116.37</v>
       </c>
       <c r="AL27" t="n">
-        <v>-1.35</v>
+        <v>-0.15</v>
       </c>
       <c r="AM27" t="n">
         <v>110</v>
@@ -3204,60 +3165,60 @@
         <v>142</v>
       </c>
       <c r="BL27" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B28" t="n">
-        <v>155.9</v>
+        <v>141.3</v>
       </c>
       <c r="D28" t="n">
-        <v>28</v>
+        <v>26.3</v>
       </c>
       <c r="F28" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="K28" t="n">
-        <v>99.3</v>
+        <v>97.8</v>
       </c>
       <c r="O28" t="n">
-        <v>38.5</v>
+        <v>39.8</v>
       </c>
       <c r="V28" t="n">
-        <v>8.9</v>
+        <v>9.5</v>
       </c>
       <c r="W28" t="n">
-        <v>15.8</v>
+        <v>17.7</v>
       </c>
       <c r="X28" t="n">
-        <v>12.4</v>
+        <v>13.6</v>
       </c>
       <c r="Y28" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Z28" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA28" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="AC28" t="n">
-        <v>5.7</v>
+        <v>7.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="AF28" t="n">
-        <v>221.99</v>
+        <v>225.14</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.67</v>
+        <v>3.15</v>
       </c>
       <c r="AH28" t="n">
         <v>215</v>
@@ -3265,12 +3226,6 @@
       <c r="AI28" t="n">
         <v>235</v>
       </c>
-      <c r="AK28" t="n">
-        <v>116.37</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>-0.15</v>
-      </c>
       <c r="AM28" t="n">
         <v>110</v>
       </c>
@@ -3278,60 +3233,54 @@
         <v>142</v>
       </c>
       <c r="BL28" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B29" t="n">
-        <v>141.3</v>
+        <v>131.5</v>
       </c>
       <c r="D29" t="n">
-        <v>26.3</v>
+        <v>27.3</v>
       </c>
       <c r="F29" t="n">
         <v>5.5</v>
       </c>
       <c r="K29" t="n">
-        <v>97.8</v>
+        <v>97</v>
       </c>
       <c r="O29" t="n">
-        <v>39.8</v>
+        <v>35.7</v>
       </c>
       <c r="V29" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="W29" t="n">
-        <v>17.7</v>
+        <v>13.9</v>
       </c>
       <c r="X29" t="n">
-        <v>13.6</v>
+        <v>11.4</v>
       </c>
       <c r="Y29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z29" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA29" t="n">
         <v>15</v>
       </c>
-      <c r="AA29" t="n">
-        <v>14</v>
-      </c>
       <c r="AB29" t="n">
-        <v>0.2</v>
+        <v>-3.6</v>
       </c>
       <c r="AC29" t="n">
-        <v>7.5</v>
+        <v>2.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>225.14</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>3.15</v>
+        <v>-0.4</v>
       </c>
       <c r="AH29" t="n">
         <v>215</v>
@@ -3346,54 +3295,93 @@
         <v>142</v>
       </c>
       <c r="BL29" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="B30" t="n">
-        <v>131.5</v>
+        <v>153</v>
+      </c>
+      <c r="C30" t="n">
+        <v>71.8</v>
       </c>
       <c r="D30" t="n">
-        <v>27.3</v>
+        <v>28.6</v>
+      </c>
+      <c r="E30" t="n">
+        <v>24.7</v>
       </c>
       <c r="F30" t="n">
-        <v>5.5</v>
+        <v>4</v>
+      </c>
+      <c r="H30" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I30" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J30" t="n">
+        <v>41.1</v>
       </c>
       <c r="K30" t="n">
-        <v>97</v>
+        <v>75.90000000000001</v>
+      </c>
+      <c r="M30" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N30" t="n">
+        <v>33.5</v>
       </c>
       <c r="O30" t="n">
-        <v>35.7</v>
+        <v>38.3</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="R30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>23.2</v>
       </c>
       <c r="V30" t="n">
-        <v>9</v>
+        <v>11.2</v>
       </c>
       <c r="W30" t="n">
-        <v>13.9</v>
+        <v>13</v>
       </c>
       <c r="X30" t="n">
-        <v>11.4</v>
+        <v>12.1</v>
       </c>
       <c r="Y30" t="n">
         <v>12</v>
       </c>
       <c r="Z30" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AA30" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AB30" t="n">
-        <v>-3.6</v>
+        <v>-6.6</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.8</v>
+        <v>5.3</v>
       </c>
       <c r="AD30" t="n">
-        <v>-0.4</v>
+        <v>-0.6</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>229.96</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>-0.02</v>
       </c>
       <c r="AH30" t="n">
         <v>215</v>
@@ -3401,100 +3389,112 @@
       <c r="AI30" t="n">
         <v>235</v>
       </c>
+      <c r="AK30" t="n">
+        <v>128.14</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>11.77</v>
+      </c>
       <c r="AM30" t="n">
         <v>110</v>
       </c>
       <c r="AN30" t="n">
         <v>142</v>
       </c>
+      <c r="AP30" t="n">
+        <v>87.47</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>14.8</v>
+      </c>
       <c r="BL30" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B31" t="n">
-        <v>153</v>
+        <v>165.8</v>
       </c>
       <c r="C31" t="n">
-        <v>71.8</v>
+        <v>77.3</v>
       </c>
       <c r="D31" t="n">
-        <v>28.6</v>
+        <v>29.3</v>
       </c>
       <c r="E31" t="n">
-        <v>24.7</v>
+        <v>27.7</v>
       </c>
       <c r="F31" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="H31" t="n">
         <v>24.1</v>
       </c>
       <c r="I31" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="J31" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="K31" t="n">
-        <v>75.90000000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="M31" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="N31" t="n">
-        <v>33.5</v>
+        <v>35.1</v>
       </c>
       <c r="O31" t="n">
-        <v>38.3</v>
+        <v>39.8</v>
       </c>
       <c r="Q31" t="n">
-        <v>23.2</v>
+        <v>23.8</v>
       </c>
       <c r="R31" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="T31" t="n">
-        <v>23.2</v>
+        <v>23.8</v>
       </c>
       <c r="V31" t="n">
-        <v>11.2</v>
+        <v>9.4</v>
       </c>
       <c r="W31" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="X31" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z31" t="n">
         <v>13</v>
       </c>
-      <c r="X31" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>14</v>
-      </c>
       <c r="AA31" t="n">
-        <v>12.5</v>
+        <v>10.1</v>
       </c>
       <c r="AB31" t="n">
-        <v>-6.6</v>
+        <v>-0.7</v>
       </c>
       <c r="AC31" t="n">
-        <v>5.3</v>
+        <v>9.5</v>
       </c>
       <c r="AD31" t="n">
-        <v>-0.6</v>
+        <v>4.4</v>
       </c>
       <c r="AF31" t="n">
-        <v>229.96</v>
+        <v>227.01</v>
       </c>
       <c r="AG31" t="n">
-        <v>-0.02</v>
+        <v>-2.95</v>
       </c>
       <c r="AH31" t="n">
         <v>215</v>
@@ -3503,10 +3503,10 @@
         <v>235</v>
       </c>
       <c r="AK31" t="n">
-        <v>128.14</v>
+        <v>128.15</v>
       </c>
       <c r="AL31" t="n">
-        <v>11.77</v>
+        <v>0.01</v>
       </c>
       <c r="AM31" t="n">
         <v>110</v>
@@ -3515,99 +3515,99 @@
         <v>142</v>
       </c>
       <c r="AP31" t="n">
-        <v>87.47</v>
+        <v>83.41</v>
       </c>
       <c r="AS31" t="n">
-        <v>14.8</v>
+        <v>14.52</v>
       </c>
       <c r="BL31" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B32" t="n">
-        <v>165.8</v>
+        <v>158.1</v>
       </c>
       <c r="C32" t="n">
-        <v>77.3</v>
+        <v>73.7</v>
       </c>
       <c r="D32" t="n">
-        <v>29.3</v>
+        <v>30.3</v>
       </c>
       <c r="E32" t="n">
-        <v>27.7</v>
+        <v>26</v>
       </c>
       <c r="F32" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="H32" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="I32" t="n">
-        <v>10.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J32" t="n">
-        <v>41.6</v>
+        <v>40.9</v>
       </c>
       <c r="K32" t="n">
-        <v>76.59999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="M32" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="N32" t="n">
-        <v>35.1</v>
+        <v>35.3</v>
       </c>
       <c r="O32" t="n">
-        <v>39.8</v>
+        <v>40.3</v>
       </c>
       <c r="Q32" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="R32" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S32" t="n">
         <v>7</v>
       </c>
       <c r="T32" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="V32" t="n">
-        <v>9.4</v>
+        <v>8.9</v>
       </c>
       <c r="W32" t="n">
-        <v>17.4</v>
+        <v>19.3</v>
       </c>
       <c r="X32" t="n">
-        <v>13.4</v>
+        <v>14.1</v>
       </c>
       <c r="Y32" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z32" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA32" t="n">
-        <v>10.1</v>
+        <v>11</v>
       </c>
       <c r="AB32" t="n">
-        <v>-0.7</v>
+        <v>4.4</v>
       </c>
       <c r="AC32" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="AD32" t="n">
-        <v>4.4</v>
+        <v>6.5</v>
       </c>
       <c r="AF32" t="n">
-        <v>227.01</v>
+        <v>228.35</v>
       </c>
       <c r="AG32" t="n">
-        <v>-2.95</v>
+        <v>1.33</v>
       </c>
       <c r="AH32" t="n">
         <v>215</v>
@@ -3616,10 +3616,10 @@
         <v>235</v>
       </c>
       <c r="AK32" t="n">
-        <v>128.15</v>
+        <v>128.86</v>
       </c>
       <c r="AL32" t="n">
-        <v>0.01</v>
+        <v>0.71</v>
       </c>
       <c r="AM32" t="n">
         <v>110</v>
@@ -3628,99 +3628,99 @@
         <v>142</v>
       </c>
       <c r="AP32" t="n">
-        <v>83.41</v>
+        <v>82.37</v>
       </c>
       <c r="AS32" t="n">
-        <v>14.52</v>
+        <v>14.22</v>
       </c>
       <c r="BL32" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B33" t="n">
-        <v>158.1</v>
+        <v>154.9</v>
       </c>
       <c r="C33" t="n">
-        <v>73.7</v>
+        <v>70.2</v>
       </c>
       <c r="D33" t="n">
-        <v>30.3</v>
+        <v>31.5</v>
       </c>
       <c r="E33" t="n">
-        <v>26</v>
+        <v>27.7</v>
       </c>
       <c r="F33" t="n">
-        <v>4.1</v>
+        <v>2.7</v>
       </c>
       <c r="H33" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="I33" t="n">
-        <v>9.300000000000001</v>
+        <v>11.3</v>
       </c>
       <c r="J33" t="n">
-        <v>40.9</v>
+        <v>40.3</v>
       </c>
       <c r="K33" t="n">
-        <v>74.40000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="M33" t="n">
-        <v>5</v>
+        <v>6.1</v>
       </c>
       <c r="N33" t="n">
-        <v>35.3</v>
+        <v>32.9</v>
       </c>
       <c r="O33" t="n">
-        <v>40.3</v>
+        <v>39</v>
       </c>
       <c r="Q33" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="R33" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="S33" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="T33" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="V33" t="n">
-        <v>8.9</v>
+        <v>6.3</v>
       </c>
       <c r="W33" t="n">
-        <v>19.3</v>
+        <v>25.2</v>
       </c>
       <c r="X33" t="n">
-        <v>14.1</v>
+        <v>15.8</v>
       </c>
       <c r="Y33" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z33" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA33" t="n">
-        <v>11</v>
+        <v>12.6</v>
       </c>
       <c r="AB33" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="AC33" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="AD33" t="n">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="AF33" t="n">
-        <v>228.35</v>
+        <v>231.16</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.33</v>
+        <v>2.81</v>
       </c>
       <c r="AH33" t="n">
         <v>215</v>
@@ -3729,10 +3729,10 @@
         <v>235</v>
       </c>
       <c r="AK33" t="n">
-        <v>128.86</v>
+        <v>130.88</v>
       </c>
       <c r="AL33" t="n">
-        <v>0.71</v>
+        <v>2.02</v>
       </c>
       <c r="AM33" t="n">
         <v>110</v>
@@ -3741,99 +3741,66 @@
         <v>142</v>
       </c>
       <c r="AP33" t="n">
-        <v>82.37</v>
+        <v>85.48999999999999</v>
       </c>
       <c r="AS33" t="n">
-        <v>14.22</v>
+        <v>13.1</v>
       </c>
       <c r="BL33" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B34" t="n">
-        <v>154.9</v>
-      </c>
-      <c r="C34" t="n">
-        <v>70.2</v>
+        <v>152.2</v>
       </c>
       <c r="D34" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="E34" t="n">
-        <v>27.7</v>
+        <v>31</v>
       </c>
       <c r="F34" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="H34" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I34" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J34" t="n">
-        <v>40.3</v>
+        <v>3.5</v>
       </c>
       <c r="K34" t="n">
-        <v>75.8</v>
-      </c>
-      <c r="M34" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="N34" t="n">
-        <v>32.9</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O34" t="n">
-        <v>39</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="R34" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="S34" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="T34" t="n">
-        <v>23.7</v>
+        <v>34.4</v>
       </c>
       <c r="V34" t="n">
-        <v>6.3</v>
+        <v>9.5</v>
       </c>
       <c r="W34" t="n">
-        <v>25.2</v>
+        <v>25.5</v>
       </c>
       <c r="X34" t="n">
-        <v>15.8</v>
+        <v>17.5</v>
       </c>
       <c r="Y34" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Z34" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AA34" t="n">
-        <v>12.6</v>
+        <v>9</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.9</v>
+        <v>-1.1</v>
       </c>
       <c r="AC34" t="n">
         <v>8.6</v>
       </c>
       <c r="AD34" t="n">
-        <v>5.8</v>
+        <v>3.8</v>
       </c>
       <c r="AF34" t="n">
-        <v>231.16</v>
+        <v>228.13</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.81</v>
+        <v>-3.03</v>
       </c>
       <c r="AH34" t="n">
         <v>215</v>
@@ -3841,79 +3808,67 @@
       <c r="AI34" t="n">
         <v>235</v>
       </c>
-      <c r="AK34" t="n">
-        <v>130.88</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AM34" t="n">
         <v>110</v>
       </c>
       <c r="AN34" t="n">
         <v>142</v>
       </c>
-      <c r="AP34" t="n">
-        <v>85.48999999999999</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>13.1</v>
-      </c>
       <c r="BL34" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B35" t="n">
-        <v>152.2</v>
+        <v>143.9</v>
       </c>
       <c r="D35" t="n">
-        <v>31</v>
+        <v>30.8</v>
       </c>
       <c r="F35" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="K35" t="n">
-        <v>98.40000000000001</v>
+        <v>99.2</v>
       </c>
       <c r="O35" t="n">
-        <v>34.4</v>
+        <v>35.2</v>
       </c>
       <c r="V35" t="n">
-        <v>9.5</v>
+        <v>10.7</v>
       </c>
       <c r="W35" t="n">
-        <v>25.5</v>
+        <v>17.6</v>
       </c>
       <c r="X35" t="n">
-        <v>17.5</v>
+        <v>14.2</v>
       </c>
       <c r="Y35" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Z35" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA35" t="n">
         <v>9</v>
       </c>
       <c r="AB35" t="n">
-        <v>-1.1</v>
+        <v>-0.8</v>
       </c>
       <c r="AC35" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD35" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AF35" t="n">
-        <v>228.13</v>
+        <v>229.16</v>
       </c>
       <c r="AG35" t="n">
-        <v>-3.03</v>
+        <v>1.03</v>
       </c>
       <c r="AH35" t="n">
         <v>215</v>
@@ -3928,60 +3883,93 @@
         <v>142</v>
       </c>
       <c r="BL35" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B36" t="n">
-        <v>143.9</v>
+        <v>163.2</v>
+      </c>
+      <c r="C36" t="n">
+        <v>73.7</v>
       </c>
       <c r="D36" t="n">
-        <v>30.8</v>
+        <v>30</v>
+      </c>
+      <c r="E36" t="n">
+        <v>28.2</v>
       </c>
       <c r="F36" t="n">
-        <v>2.5</v>
+        <v>4.8</v>
+      </c>
+      <c r="H36" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I36" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J36" t="n">
+        <v>40.1</v>
       </c>
       <c r="K36" t="n">
-        <v>99.2</v>
+        <v>75.59999999999999</v>
+      </c>
+      <c r="M36" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="N36" t="n">
+        <v>32.9</v>
       </c>
       <c r="O36" t="n">
-        <v>35.2</v>
+        <v>39.7</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="R36" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="S36" t="n">
+        <v>6</v>
+      </c>
+      <c r="T36" t="n">
+        <v>23.5</v>
       </c>
       <c r="V36" t="n">
-        <v>10.7</v>
+        <v>9.4</v>
       </c>
       <c r="W36" t="n">
-        <v>17.6</v>
+        <v>20.1</v>
       </c>
       <c r="X36" t="n">
-        <v>14.2</v>
+        <v>14.8</v>
       </c>
       <c r="Y36" t="n">
         <v>4</v>
       </c>
       <c r="Z36" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA36" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AB36" t="n">
-        <v>-0.8</v>
+        <v>-0.9</v>
       </c>
       <c r="AC36" t="n">
-        <v>8.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="AD36" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AF36" t="n">
-        <v>229.16</v>
+        <v>228.55</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.03</v>
+        <v>-0.61</v>
       </c>
       <c r="AH36" t="n">
         <v>215</v>
@@ -3989,100 +3977,112 @@
       <c r="AI36" t="n">
         <v>235</v>
       </c>
+      <c r="AK36" t="n">
+        <v>127.06</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>-3.82</v>
+      </c>
       <c r="AM36" t="n">
         <v>110</v>
       </c>
       <c r="AN36" t="n">
         <v>142</v>
       </c>
+      <c r="AP36" t="n">
+        <v>82.81</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>12.9</v>
+      </c>
       <c r="BL36" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="B37" t="n">
-        <v>163.2</v>
+        <v>174.4</v>
       </c>
       <c r="C37" t="n">
-        <v>73.7</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="D37" t="n">
-        <v>30</v>
+        <v>32.1</v>
       </c>
       <c r="E37" t="n">
-        <v>28.2</v>
+        <v>30.8</v>
       </c>
       <c r="F37" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="H37" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="I37" t="n">
-        <v>11.4</v>
+        <v>10.5</v>
       </c>
       <c r="J37" t="n">
-        <v>40.1</v>
+        <v>39.5</v>
       </c>
       <c r="K37" t="n">
-        <v>75.59999999999999</v>
+        <v>74</v>
       </c>
       <c r="M37" t="n">
         <v>6.8</v>
       </c>
       <c r="N37" t="n">
-        <v>32.9</v>
+        <v>35.8</v>
       </c>
       <c r="O37" t="n">
-        <v>39.7</v>
+        <v>42.6</v>
       </c>
       <c r="Q37" t="n">
-        <v>23.5</v>
+        <v>23.1</v>
       </c>
       <c r="R37" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="S37" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="T37" t="n">
-        <v>23.5</v>
+        <v>23.1</v>
       </c>
       <c r="V37" t="n">
-        <v>9.4</v>
+        <v>12.8</v>
       </c>
       <c r="W37" t="n">
-        <v>20.1</v>
+        <v>22.1</v>
       </c>
       <c r="X37" t="n">
-        <v>14.8</v>
+        <v>17.5</v>
       </c>
       <c r="Y37" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Z37" t="n">
         <v>13</v>
       </c>
       <c r="AA37" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AC37" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="AB37" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>9.5</v>
-      </c>
       <c r="AD37" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AF37" t="n">
-        <v>228.55</v>
+        <v>219.99</v>
       </c>
       <c r="AG37" t="n">
-        <v>-0.61</v>
+        <v>-8.56</v>
       </c>
       <c r="AH37" t="n">
         <v>215</v>
@@ -4091,10 +4091,10 @@
         <v>235</v>
       </c>
       <c r="AK37" t="n">
-        <v>127.06</v>
+        <v>125.61</v>
       </c>
       <c r="AL37" t="n">
-        <v>-3.82</v>
+        <v>-1.45</v>
       </c>
       <c r="AM37" t="n">
         <v>110</v>
@@ -4103,99 +4103,99 @@
         <v>142</v>
       </c>
       <c r="AP37" t="n">
-        <v>82.81</v>
+        <v>77.83</v>
       </c>
       <c r="AS37" t="n">
-        <v>12.9</v>
+        <v>12.96</v>
       </c>
       <c r="BL37" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B38" t="n">
-        <v>174.4</v>
+        <v>163.2</v>
       </c>
       <c r="C38" t="n">
-        <v>75.40000000000001</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="D38" t="n">
-        <v>32.1</v>
+        <v>32.9</v>
       </c>
       <c r="E38" t="n">
-        <v>30.8</v>
+        <v>26</v>
       </c>
       <c r="F38" t="n">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="H38" t="n">
-        <v>24</v>
+        <v>23.8</v>
       </c>
       <c r="I38" t="n">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="J38" t="n">
-        <v>39.5</v>
+        <v>40.1</v>
       </c>
       <c r="K38" t="n">
-        <v>74</v>
+        <v>71.3</v>
       </c>
       <c r="M38" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="N38" t="n">
-        <v>35.8</v>
+        <v>34.3</v>
       </c>
       <c r="O38" t="n">
-        <v>42.6</v>
+        <v>41.5</v>
       </c>
       <c r="Q38" t="n">
         <v>23.1</v>
       </c>
       <c r="R38" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="S38" t="n">
-        <v>8.5</v>
+        <v>6.2</v>
       </c>
       <c r="T38" t="n">
         <v>23.1</v>
       </c>
       <c r="V38" t="n">
-        <v>12.8</v>
+        <v>9.6</v>
       </c>
       <c r="W38" t="n">
-        <v>22.1</v>
+        <v>23.3</v>
       </c>
       <c r="X38" t="n">
-        <v>17.5</v>
+        <v>16.4</v>
       </c>
       <c r="Y38" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z38" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA38" t="n">
-        <v>10.1</v>
+        <v>12.2</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.3</v>
+        <v>2.6</v>
       </c>
       <c r="AC38" t="n">
-        <v>9.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="AD38" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AF38" t="n">
-        <v>219.99</v>
+        <v>219.22</v>
       </c>
       <c r="AG38" t="n">
-        <v>-8.56</v>
+        <v>-0.77</v>
       </c>
       <c r="AH38" t="n">
         <v>215</v>
@@ -4204,10 +4204,10 @@
         <v>235</v>
       </c>
       <c r="AK38" t="n">
-        <v>125.61</v>
+        <v>124.36</v>
       </c>
       <c r="AL38" t="n">
-        <v>-1.45</v>
+        <v>-1.25</v>
       </c>
       <c r="AM38" t="n">
         <v>110</v>
@@ -4216,99 +4216,99 @@
         <v>142</v>
       </c>
       <c r="AP38" t="n">
-        <v>77.83</v>
+        <v>76.81</v>
       </c>
       <c r="AS38" t="n">
-        <v>12.96</v>
+        <v>12.38</v>
       </c>
       <c r="BL38" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B39" t="n">
-        <v>163.2</v>
+        <v>152.7</v>
       </c>
       <c r="C39" t="n">
-        <v>70.90000000000001</v>
+        <v>62.6</v>
       </c>
       <c r="D39" t="n">
-        <v>32.9</v>
+        <v>32.7</v>
       </c>
       <c r="E39" t="n">
-        <v>26</v>
+        <v>24.6</v>
       </c>
       <c r="F39" t="n">
-        <v>6.9</v>
+        <v>5.2</v>
       </c>
       <c r="H39" t="n">
         <v>23.8</v>
       </c>
       <c r="I39" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J39" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="K39" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="M39" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="N39" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="O39" t="n">
         <v>40.1</v>
       </c>
-      <c r="K39" t="n">
-        <v>71.3</v>
-      </c>
-      <c r="M39" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="N39" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="O39" t="n">
-        <v>41.5</v>
-      </c>
       <c r="Q39" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="R39" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="S39" t="n">
-        <v>6.2</v>
+        <v>4</v>
       </c>
       <c r="T39" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="V39" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="W39" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="X39" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC39" t="n">
         <v>9.6</v>
       </c>
-      <c r="W39" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="X39" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>8.5</v>
-      </c>
       <c r="AD39" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AF39" t="n">
-        <v>219.22</v>
+        <v>220.73</v>
       </c>
       <c r="AG39" t="n">
-        <v>-0.77</v>
+        <v>1.5</v>
       </c>
       <c r="AH39" t="n">
         <v>215</v>
@@ -4317,10 +4317,10 @@
         <v>235</v>
       </c>
       <c r="AK39" t="n">
-        <v>124.36</v>
+        <v>120.93</v>
       </c>
       <c r="AL39" t="n">
-        <v>-1.25</v>
+        <v>-3.43</v>
       </c>
       <c r="AM39" t="n">
         <v>110</v>
@@ -4329,75 +4329,75 @@
         <v>142</v>
       </c>
       <c r="AP39" t="n">
-        <v>76.81</v>
+        <v>77.87</v>
       </c>
       <c r="AS39" t="n">
-        <v>12.38</v>
+        <v>13.26</v>
       </c>
       <c r="BL39" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B40" t="n">
-        <v>152.7</v>
+        <v>150.7</v>
       </c>
       <c r="C40" t="n">
-        <v>62.6</v>
+        <v>64.8</v>
       </c>
       <c r="D40" t="n">
-        <v>32.7</v>
+        <v>33.7</v>
       </c>
       <c r="E40" t="n">
-        <v>24.6</v>
+        <v>27.1</v>
       </c>
       <c r="F40" t="n">
-        <v>5.2</v>
+        <v>3.8</v>
       </c>
       <c r="H40" t="n">
-        <v>23.8</v>
+        <v>23.4</v>
       </c>
       <c r="I40" t="n">
         <v>7.2</v>
       </c>
       <c r="J40" t="n">
-        <v>38.9</v>
+        <v>39.9</v>
       </c>
       <c r="K40" t="n">
-        <v>69.90000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="M40" t="n">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="N40" t="n">
-        <v>33.5</v>
+        <v>33</v>
       </c>
       <c r="O40" t="n">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="Q40" t="n">
         <v>23.2</v>
       </c>
       <c r="R40" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="S40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T40" t="n">
         <v>23.2</v>
       </c>
       <c r="V40" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="W40" t="n">
-        <v>27.3</v>
+        <v>28.9</v>
       </c>
       <c r="X40" t="n">
-        <v>19.4</v>
+        <v>21.7</v>
       </c>
       <c r="Y40" t="n">
         <v>10</v>
@@ -4406,22 +4406,22 @@
         <v>18</v>
       </c>
       <c r="AA40" t="n">
-        <v>14</v>
+        <v>13.1</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="AC40" t="n">
-        <v>9.6</v>
+        <v>10.8</v>
       </c>
       <c r="AD40" t="n">
-        <v>5.7</v>
+        <v>6.7</v>
       </c>
       <c r="AF40" t="n">
-        <v>220.73</v>
+        <v>220.58</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.5</v>
+        <v>-0.15</v>
       </c>
       <c r="AH40" t="n">
         <v>215</v>
@@ -4430,10 +4430,10 @@
         <v>235</v>
       </c>
       <c r="AK40" t="n">
-        <v>120.93</v>
+        <v>120.28</v>
       </c>
       <c r="AL40" t="n">
-        <v>-3.43</v>
+        <v>-0.65</v>
       </c>
       <c r="AM40" t="n">
         <v>110</v>
@@ -4442,99 +4442,54 @@
         <v>142</v>
       </c>
       <c r="AP40" t="n">
-        <v>77.87</v>
+        <v>77.22</v>
       </c>
       <c r="AS40" t="n">
-        <v>13.26</v>
+        <v>13.79</v>
       </c>
       <c r="BL40" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B41" t="n">
-        <v>150.7</v>
-      </c>
-      <c r="C41" t="n">
-        <v>64.8</v>
+        <v>138.2</v>
       </c>
       <c r="D41" t="n">
-        <v>33.7</v>
-      </c>
-      <c r="E41" t="n">
-        <v>27.1</v>
+        <v>33.6</v>
       </c>
       <c r="F41" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H41" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="V41" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="W41" t="n">
         <v>23.4</v>
       </c>
-      <c r="I41" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="J41" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="K41" t="n">
-        <v>70.5</v>
-      </c>
-      <c r="M41" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="N41" t="n">
-        <v>33</v>
-      </c>
-      <c r="O41" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="R41" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="S41" t="n">
-        <v>3</v>
-      </c>
-      <c r="T41" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="V41" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="W41" t="n">
-        <v>28.9</v>
-      </c>
       <c r="X41" t="n">
-        <v>21.7</v>
+        <v>19.4</v>
       </c>
       <c r="Y41" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z41" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AA41" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="AC41" t="n">
-        <v>10.8</v>
+        <v>8.5</v>
       </c>
       <c r="AD41" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>220.58</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>-0.15</v>
+        <v>4.5</v>
       </c>
       <c r="AH41" t="n">
         <v>215</v>
@@ -4542,67 +4497,61 @@
       <c r="AI41" t="n">
         <v>235</v>
       </c>
-      <c r="AK41" t="n">
-        <v>120.28</v>
-      </c>
-      <c r="AL41" t="n">
-        <v>-0.65</v>
-      </c>
       <c r="AM41" t="n">
         <v>110</v>
       </c>
       <c r="AN41" t="n">
         <v>142</v>
       </c>
-      <c r="AP41" t="n">
-        <v>77.22</v>
-      </c>
-      <c r="AS41" t="n">
-        <v>13.79</v>
-      </c>
       <c r="BL41" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B42" t="n">
-        <v>138.2</v>
+        <v>126.5</v>
       </c>
       <c r="D42" t="n">
-        <v>33.6</v>
+        <v>33.2</v>
       </c>
       <c r="F42" t="n">
-        <v>6.1</v>
+        <v>3.4</v>
       </c>
       <c r="V42" t="n">
-        <v>15.5</v>
+        <v>12.6</v>
       </c>
       <c r="W42" t="n">
-        <v>23.4</v>
+        <v>22.3</v>
       </c>
       <c r="X42" t="n">
-        <v>19.4</v>
+        <v>17.4</v>
       </c>
       <c r="Y42" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z42" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA42" t="n">
         <v>13</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>8.5</v>
+        <v>6.7</v>
       </c>
       <c r="AD42" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>229.48</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>6.05</v>
       </c>
       <c r="AH42" t="n">
         <v>215</v>
@@ -4617,54 +4566,93 @@
         <v>142</v>
       </c>
       <c r="BL42" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B43" t="n">
-        <v>126.5</v>
+        <v>129.4</v>
+      </c>
+      <c r="C43" t="n">
+        <v>50.6</v>
       </c>
       <c r="D43" t="n">
-        <v>33.2</v>
+        <v>31.5</v>
+      </c>
+      <c r="E43" t="n">
+        <v>19.4</v>
       </c>
       <c r="F43" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
+      </c>
+      <c r="H43" t="n">
+        <v>24</v>
+      </c>
+      <c r="I43" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J43" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="K43" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="M43" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N43" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="O43" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>21.4</v>
       </c>
       <c r="V43" t="n">
-        <v>12.6</v>
+        <v>14.3</v>
       </c>
       <c r="W43" t="n">
-        <v>22.3</v>
+        <v>23.9</v>
       </c>
       <c r="X43" t="n">
-        <v>17.4</v>
+        <v>19.1</v>
       </c>
       <c r="Y43" t="n">
         <v>8</v>
       </c>
       <c r="Z43" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AA43" t="n">
-        <v>13</v>
+        <v>16.1</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AC43" t="n">
-        <v>6.7</v>
+        <v>7.6</v>
       </c>
       <c r="AD43" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="AF43" t="n">
-        <v>229.48</v>
+        <v>229.5</v>
       </c>
       <c r="AG43" t="n">
-        <v>6.05</v>
+        <v>0.02</v>
       </c>
       <c r="AH43" t="n">
         <v>215</v>
@@ -4672,100 +4660,112 @@
       <c r="AI43" t="n">
         <v>235</v>
       </c>
+      <c r="AK43" t="n">
+        <v>128.37</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>8.09</v>
+      </c>
       <c r="AM43" t="n">
         <v>110</v>
       </c>
       <c r="AN43" t="n">
         <v>142</v>
       </c>
+      <c r="AP43" t="n">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>15.97</v>
+      </c>
       <c r="BL43" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="B44" t="n">
-        <v>129.4</v>
+        <v>142.9</v>
       </c>
       <c r="C44" t="n">
-        <v>50.6</v>
+        <v>52.7</v>
       </c>
       <c r="D44" t="n">
-        <v>31.5</v>
+        <v>34.7</v>
       </c>
       <c r="E44" t="n">
-        <v>19.4</v>
+        <v>24.8</v>
       </c>
       <c r="F44" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="H44" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I44" t="n">
-        <v>10.4</v>
+        <v>9.9</v>
       </c>
       <c r="J44" t="n">
-        <v>38.9</v>
+        <v>38.2</v>
       </c>
       <c r="K44" t="n">
-        <v>73.3</v>
+        <v>70</v>
       </c>
       <c r="M44" t="n">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="N44" t="n">
-        <v>33.3</v>
+        <v>31.9</v>
       </c>
       <c r="O44" t="n">
-        <v>38</v>
+        <v>35.8</v>
       </c>
       <c r="Q44" t="n">
-        <v>21.4</v>
+        <v>19.7</v>
       </c>
       <c r="R44" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>21.4</v>
+        <v>19.7</v>
       </c>
       <c r="V44" t="n">
-        <v>14.3</v>
+        <v>12</v>
       </c>
       <c r="W44" t="n">
-        <v>23.9</v>
+        <v>25.8</v>
       </c>
       <c r="X44" t="n">
-        <v>19.1</v>
+        <v>18.9</v>
       </c>
       <c r="Y44" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Z44" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AA44" t="n">
-        <v>16.1</v>
+        <v>15</v>
       </c>
       <c r="AB44" t="n">
-        <v>0.4</v>
+        <v>-0.1</v>
       </c>
       <c r="AC44" t="n">
-        <v>7.6</v>
+        <v>5.8</v>
       </c>
       <c r="AD44" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="AF44" t="n">
-        <v>229.5</v>
+        <v>238.69</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.02</v>
+        <v>-2.8</v>
       </c>
       <c r="AH44" t="n">
         <v>215</v>
@@ -4774,10 +4774,10 @@
         <v>235</v>
       </c>
       <c r="AK44" t="n">
-        <v>128.37</v>
+        <v>134.59</v>
       </c>
       <c r="AL44" t="n">
-        <v>8.09</v>
+        <v>6.22</v>
       </c>
       <c r="AM44" t="n">
         <v>110</v>
@@ -4786,99 +4786,99 @@
         <v>142</v>
       </c>
       <c r="AP44" t="n">
-        <v>91.59999999999999</v>
+        <v>89.05</v>
       </c>
       <c r="AS44" t="n">
-        <v>15.97</v>
+        <v>17.06</v>
       </c>
       <c r="BL44" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B45" t="n">
-        <v>142.9</v>
+        <v>148.1</v>
       </c>
       <c r="C45" t="n">
-        <v>52.7</v>
+        <v>51.9</v>
       </c>
       <c r="D45" t="n">
-        <v>34.7</v>
+        <v>35.4</v>
       </c>
       <c r="E45" t="n">
-        <v>24.8</v>
+        <v>31.5</v>
       </c>
       <c r="F45" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="H45" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="I45" t="n">
-        <v>9.9</v>
+        <v>9.6</v>
       </c>
       <c r="J45" t="n">
-        <v>38.2</v>
+        <v>39.6</v>
       </c>
       <c r="K45" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M45" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="N45" t="n">
-        <v>31.9</v>
+        <v>30.8</v>
       </c>
       <c r="O45" t="n">
-        <v>35.8</v>
+        <v>33.7</v>
       </c>
       <c r="Q45" t="n">
-        <v>19.7</v>
+        <v>20.7</v>
       </c>
       <c r="R45" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>19.7</v>
+        <v>20.7</v>
       </c>
       <c r="V45" t="n">
-        <v>12</v>
+        <v>13.1</v>
       </c>
       <c r="W45" t="n">
-        <v>25.8</v>
+        <v>25.5</v>
       </c>
       <c r="X45" t="n">
-        <v>18.9</v>
+        <v>19.3</v>
       </c>
       <c r="Y45" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z45" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AA45" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AB45" t="n">
-        <v>-0.1</v>
+        <v>-1</v>
       </c>
       <c r="AC45" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AD45" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="AF45" t="n">
-        <v>238.69</v>
+        <v>233.48</v>
       </c>
       <c r="AG45" t="n">
-        <v>-2.8</v>
+        <v>-4.86</v>
       </c>
       <c r="AH45" t="n">
         <v>215</v>
@@ -4887,10 +4887,10 @@
         <v>235</v>
       </c>
       <c r="AK45" t="n">
-        <v>134.59</v>
+        <v>136.6</v>
       </c>
       <c r="AL45" t="n">
-        <v>6.22</v>
+        <v>2.01</v>
       </c>
       <c r="AM45" t="n">
         <v>110</v>
@@ -4899,99 +4899,99 @@
         <v>142</v>
       </c>
       <c r="AP45" t="n">
-        <v>89.05</v>
+        <v>86.25</v>
       </c>
       <c r="AS45" t="n">
-        <v>17.06</v>
+        <v>17.13</v>
       </c>
       <c r="BL45" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B46" t="n">
-        <v>148.1</v>
+        <v>143.4</v>
       </c>
       <c r="C46" t="n">
-        <v>51.9</v>
+        <v>50.9</v>
       </c>
       <c r="D46" t="n">
-        <v>35.4</v>
+        <v>35.7</v>
       </c>
       <c r="E46" t="n">
-        <v>31.5</v>
+        <v>26.2</v>
       </c>
       <c r="F46" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="H46" t="n">
-        <v>21.8</v>
+        <v>22.9</v>
       </c>
       <c r="I46" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J46" t="n">
-        <v>39.6</v>
+        <v>39.9</v>
       </c>
       <c r="K46" t="n">
-        <v>71</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="M46" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="N46" t="n">
-        <v>30.8</v>
+        <v>31.2</v>
       </c>
       <c r="O46" t="n">
-        <v>33.7</v>
+        <v>33.1</v>
       </c>
       <c r="Q46" t="n">
-        <v>20.7</v>
+        <v>21.6</v>
       </c>
       <c r="R46" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>20.7</v>
+        <v>21.6</v>
       </c>
       <c r="V46" t="n">
-        <v>13.1</v>
+        <v>12.9</v>
       </c>
       <c r="W46" t="n">
-        <v>25.5</v>
+        <v>28.3</v>
       </c>
       <c r="X46" t="n">
-        <v>19.3</v>
+        <v>20.6</v>
       </c>
       <c r="Y46" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z46" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AA46" t="n">
-        <v>15.5</v>
+        <v>17.9</v>
       </c>
       <c r="AB46" t="n">
-        <v>-1</v>
+        <v>-0.8</v>
       </c>
       <c r="AC46" t="n">
-        <v>6.4</v>
+        <v>8.1</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="AF46" t="n">
-        <v>233.48</v>
+        <v>235.13</v>
       </c>
       <c r="AG46" t="n">
-        <v>-4.86</v>
+        <v>1.66</v>
       </c>
       <c r="AH46" t="n">
         <v>215</v>
@@ -5000,10 +5000,10 @@
         <v>235</v>
       </c>
       <c r="AK46" t="n">
-        <v>136.6</v>
+        <v>135.66</v>
       </c>
       <c r="AL46" t="n">
-        <v>2.01</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AM46" t="n">
         <v>110</v>
@@ -5012,57 +5012,57 @@
         <v>142</v>
       </c>
       <c r="AP46" t="n">
-        <v>86.25</v>
+        <v>88.27</v>
       </c>
       <c r="AS46" t="n">
-        <v>17.13</v>
+        <v>17.6</v>
       </c>
       <c r="BL46" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B47" t="n">
-        <v>143.4</v>
+        <v>144.9</v>
       </c>
       <c r="C47" t="n">
-        <v>50.9</v>
+        <v>53</v>
       </c>
       <c r="D47" t="n">
-        <v>35.7</v>
+        <v>35.6</v>
       </c>
       <c r="E47" t="n">
-        <v>26.2</v>
+        <v>26</v>
       </c>
       <c r="F47" t="n">
-        <v>4.3</v>
+        <v>2.8</v>
       </c>
       <c r="H47" t="n">
-        <v>22.9</v>
+        <v>24</v>
       </c>
       <c r="I47" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J47" t="n">
-        <v>39.9</v>
+        <v>40.3</v>
       </c>
       <c r="K47" t="n">
-        <v>72.59999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="M47" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="N47" t="n">
-        <v>31.2</v>
+        <v>31.6</v>
       </c>
       <c r="O47" t="n">
-        <v>33.1</v>
+        <v>33.6</v>
       </c>
       <c r="Q47" t="n">
-        <v>21.6</v>
+        <v>21</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
@@ -5071,40 +5071,40 @@
         <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>21.6</v>
+        <v>21</v>
       </c>
       <c r="V47" t="n">
-        <v>12.9</v>
+        <v>14.4</v>
       </c>
       <c r="W47" t="n">
-        <v>28.3</v>
+        <v>27.7</v>
       </c>
       <c r="X47" t="n">
-        <v>20.6</v>
+        <v>21.1</v>
       </c>
       <c r="Y47" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z47" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AA47" t="n">
-        <v>17.9</v>
+        <v>16.3</v>
       </c>
       <c r="AB47" t="n">
-        <v>-0.8</v>
+        <v>-1.1</v>
       </c>
       <c r="AC47" t="n">
-        <v>8.1</v>
+        <v>6.6</v>
       </c>
       <c r="AD47" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="AF47" t="n">
-        <v>235.13</v>
+        <v>234.87</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.66</v>
+        <v>-0.26</v>
       </c>
       <c r="AH47" t="n">
         <v>215</v>
@@ -5113,10 +5113,10 @@
         <v>235</v>
       </c>
       <c r="AK47" t="n">
-        <v>135.66</v>
+        <v>136.33</v>
       </c>
       <c r="AL47" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="AM47" t="n">
         <v>110</v>
@@ -5125,99 +5125,60 @@
         <v>142</v>
       </c>
       <c r="AP47" t="n">
-        <v>88.27</v>
+        <v>87.09</v>
       </c>
       <c r="AS47" t="n">
-        <v>17.6</v>
+        <v>17.31</v>
       </c>
       <c r="BL47" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B48" t="n">
-        <v>144.9</v>
-      </c>
-      <c r="C48" t="n">
-        <v>53</v>
+        <v>132.2</v>
       </c>
       <c r="D48" t="n">
         <v>35.6</v>
       </c>
-      <c r="E48" t="n">
-        <v>26</v>
-      </c>
       <c r="F48" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="H48" t="n">
-        <v>24</v>
-      </c>
-      <c r="I48" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="J48" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="K48" t="n">
-        <v>73.7</v>
-      </c>
-      <c r="M48" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="N48" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="O48" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>21</v>
-      </c>
-      <c r="R48" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="V48" t="n">
-        <v>14.4</v>
+        <v>11.6</v>
       </c>
       <c r="W48" t="n">
-        <v>27.7</v>
+        <v>23.2</v>
       </c>
       <c r="X48" t="n">
-        <v>21.1</v>
+        <v>17.4</v>
       </c>
       <c r="Y48" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z48" t="n">
         <v>19</v>
       </c>
       <c r="AA48" t="n">
-        <v>16.3</v>
+        <v>13</v>
       </c>
       <c r="AB48" t="n">
-        <v>-1.1</v>
+        <v>0.9</v>
       </c>
       <c r="AC48" t="n">
-        <v>6.6</v>
+        <v>7.5</v>
       </c>
       <c r="AD48" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="AF48" t="n">
-        <v>234.87</v>
+        <v>234.78</v>
       </c>
       <c r="AG48" t="n">
-        <v>-0.26</v>
+        <v>-0.09</v>
       </c>
       <c r="AH48" t="n">
         <v>215</v>
@@ -5225,73 +5186,61 @@
       <c r="AI48" t="n">
         <v>235</v>
       </c>
-      <c r="AK48" t="n">
-        <v>136.33</v>
-      </c>
-      <c r="AL48" t="n">
-        <v>0.67</v>
-      </c>
       <c r="AM48" t="n">
         <v>110</v>
       </c>
       <c r="AN48" t="n">
         <v>142</v>
       </c>
-      <c r="AP48" t="n">
-        <v>87.09</v>
-      </c>
-      <c r="AS48" t="n">
-        <v>17.31</v>
-      </c>
       <c r="BL48" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B49" t="n">
-        <v>132.2</v>
+        <v>137.1</v>
       </c>
       <c r="D49" t="n">
-        <v>35.6</v>
+        <v>35.1</v>
       </c>
       <c r="F49" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="V49" t="n">
-        <v>11.6</v>
+        <v>11</v>
       </c>
       <c r="W49" t="n">
-        <v>23.2</v>
+        <v>22</v>
       </c>
       <c r="X49" t="n">
-        <v>17.4</v>
+        <v>16.5</v>
       </c>
       <c r="Y49" t="n">
         <v>7</v>
       </c>
       <c r="Z49" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AA49" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AB49" t="n">
-        <v>0.9</v>
+        <v>-5.3</v>
       </c>
       <c r="AC49" t="n">
-        <v>7.5</v>
+        <v>6.1</v>
       </c>
       <c r="AD49" t="n">
-        <v>4.2</v>
+        <v>0.4</v>
       </c>
       <c r="AF49" t="n">
-        <v>234.78</v>
+        <v>229.75</v>
       </c>
       <c r="AG49" t="n">
-        <v>-0.09</v>
+        <v>-5.03</v>
       </c>
       <c r="AH49" t="n">
         <v>215</v>
@@ -5306,54 +5255,93 @@
         <v>142</v>
       </c>
       <c r="BL49" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B50" t="n">
-        <v>137.1</v>
+        <v>166.2</v>
+      </c>
+      <c r="C50" t="n">
+        <v>72.40000000000001</v>
       </c>
       <c r="D50" t="n">
-        <v>35.1</v>
+        <v>32.7</v>
+      </c>
+      <c r="E50" t="n">
+        <v>28.1</v>
       </c>
       <c r="F50" t="n">
         <v>3.3</v>
       </c>
+      <c r="H50" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="I50" t="n">
+        <v>9</v>
+      </c>
+      <c r="J50" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="K50" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="M50" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="N50" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="O50" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="R50" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>23.7</v>
+      </c>
       <c r="V50" t="n">
-        <v>11</v>
+        <v>7.9</v>
       </c>
       <c r="W50" t="n">
-        <v>22</v>
+        <v>15.6</v>
       </c>
       <c r="X50" t="n">
-        <v>16.5</v>
+        <v>11.8</v>
       </c>
       <c r="Y50" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z50" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AA50" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AB50" t="n">
-        <v>-5.3</v>
+        <v>-3.5</v>
       </c>
       <c r="AC50" t="n">
-        <v>6.1</v>
+        <v>8.4</v>
       </c>
       <c r="AD50" t="n">
-        <v>0.4</v>
+        <v>2.5</v>
       </c>
       <c r="AF50" t="n">
-        <v>229.75</v>
+        <v>222.86</v>
       </c>
       <c r="AG50" t="n">
-        <v>-5.03</v>
+        <v>-6.9</v>
       </c>
       <c r="AH50" t="n">
         <v>215</v>
@@ -5361,100 +5349,112 @@
       <c r="AI50" t="n">
         <v>235</v>
       </c>
+      <c r="AK50" t="n">
+        <v>135.42</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>-0.91</v>
+      </c>
       <c r="AM50" t="n">
         <v>110</v>
       </c>
       <c r="AN50" t="n">
         <v>142</v>
       </c>
+      <c r="AP50" t="n">
+        <v>81.98</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>15.01</v>
+      </c>
       <c r="BL50" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B51" t="n">
-        <v>166.2</v>
+        <v>166.3</v>
       </c>
       <c r="C51" t="n">
-        <v>72.40000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="D51" t="n">
-        <v>32.7</v>
+        <v>32.8</v>
       </c>
       <c r="E51" t="n">
-        <v>28.1</v>
+        <v>28.8</v>
       </c>
       <c r="F51" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="H51" t="n">
         <v>23.4</v>
       </c>
       <c r="I51" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J51" t="n">
-        <v>42.1</v>
+        <v>41.2</v>
       </c>
       <c r="K51" t="n">
-        <v>74.5</v>
+        <v>73.8</v>
       </c>
       <c r="M51" t="n">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="N51" t="n">
-        <v>33.7</v>
+        <v>35.4</v>
       </c>
       <c r="O51" t="n">
-        <v>39.3</v>
+        <v>42.6</v>
       </c>
       <c r="Q51" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="R51" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="V51" t="n">
-        <v>7.9</v>
+        <v>6.7</v>
       </c>
       <c r="W51" t="n">
-        <v>15.6</v>
+        <v>18.1</v>
       </c>
       <c r="X51" t="n">
-        <v>11.8</v>
+        <v>12.4</v>
       </c>
       <c r="Y51" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Z51" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AA51" t="n">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AB51" t="n">
-        <v>-3.5</v>
+        <v>-2.9</v>
       </c>
       <c r="AC51" t="n">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="AD51" t="n">
-        <v>2.5</v>
+        <v>4.3</v>
       </c>
       <c r="AF51" t="n">
-        <v>222.86</v>
+        <v>218.37</v>
       </c>
       <c r="AG51" t="n">
-        <v>-6.9</v>
+        <v>-4.49</v>
       </c>
       <c r="AH51" t="n">
         <v>215</v>
@@ -5463,10 +5463,10 @@
         <v>235</v>
       </c>
       <c r="AK51" t="n">
-        <v>135.42</v>
+        <v>131.24</v>
       </c>
       <c r="AL51" t="n">
-        <v>-0.91</v>
+        <v>-4.18</v>
       </c>
       <c r="AM51" t="n">
         <v>110</v>
@@ -5475,99 +5475,99 @@
         <v>142</v>
       </c>
       <c r="AP51" t="n">
-        <v>81.98</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="AS51" t="n">
-        <v>15.01</v>
+        <v>12.97</v>
       </c>
       <c r="BL51" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B52" t="n">
-        <v>166.3</v>
+        <v>154.1</v>
       </c>
       <c r="C52" t="n">
-        <v>74.90000000000001</v>
+        <v>65</v>
       </c>
       <c r="D52" t="n">
-        <v>32.8</v>
+        <v>32</v>
       </c>
       <c r="E52" t="n">
-        <v>28.8</v>
+        <v>25.2</v>
       </c>
       <c r="F52" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="H52" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="I52" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="J52" t="n">
-        <v>41.2</v>
+        <v>38.5</v>
       </c>
       <c r="K52" t="n">
-        <v>73.8</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="M52" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="N52" t="n">
-        <v>35.4</v>
+        <v>32.3</v>
       </c>
       <c r="O52" t="n">
-        <v>42.6</v>
+        <v>40.3</v>
       </c>
       <c r="Q52" t="n">
-        <v>23.9</v>
+        <v>21.7</v>
       </c>
       <c r="R52" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="S52" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T52" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="V52" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="W52" t="n">
+        <v>21</v>
+      </c>
+      <c r="X52" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AD52" t="n">
         <v>3.9</v>
       </c>
-      <c r="S52" t="n">
-        <v>0</v>
-      </c>
-      <c r="T52" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="V52" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="W52" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="X52" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>11</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>-2.9</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AF52" t="n">
-        <v>218.37</v>
+        <v>218.04</v>
       </c>
       <c r="AG52" t="n">
-        <v>-4.49</v>
+        <v>-0.33</v>
       </c>
       <c r="AH52" t="n">
         <v>215</v>
@@ -5576,10 +5576,10 @@
         <v>235</v>
       </c>
       <c r="AK52" t="n">
-        <v>131.24</v>
+        <v>129.21</v>
       </c>
       <c r="AL52" t="n">
-        <v>-4.18</v>
+        <v>-2.03</v>
       </c>
       <c r="AM52" t="n">
         <v>110</v>
@@ -5588,99 +5588,99 @@
         <v>142</v>
       </c>
       <c r="AP52" t="n">
-        <v>79.98999999999999</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="AS52" t="n">
-        <v>12.97</v>
+        <v>15.23</v>
       </c>
       <c r="BL52" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B53" t="n">
-        <v>154.1</v>
+        <v>148.8</v>
       </c>
       <c r="C53" t="n">
-        <v>65</v>
+        <v>57.6</v>
       </c>
       <c r="D53" t="n">
-        <v>32</v>
+        <v>32.7</v>
       </c>
       <c r="E53" t="n">
-        <v>25.2</v>
+        <v>26.3</v>
       </c>
       <c r="F53" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="H53" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="I53" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="J53" t="n">
-        <v>38.5</v>
+        <v>41.6</v>
       </c>
       <c r="K53" t="n">
-        <v>70.90000000000001</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="M53" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="N53" t="n">
-        <v>32.3</v>
+        <v>35</v>
       </c>
       <c r="O53" t="n">
-        <v>40.3</v>
+        <v>42.4</v>
       </c>
       <c r="Q53" t="n">
         <v>21.7</v>
       </c>
       <c r="R53" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="S53" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="T53" t="n">
         <v>21.7</v>
       </c>
       <c r="V53" t="n">
-        <v>5.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W53" t="n">
-        <v>21</v>
+        <v>24.1</v>
       </c>
       <c r="X53" t="n">
-        <v>13.2</v>
+        <v>16.1</v>
       </c>
       <c r="Y53" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z53" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA53" t="n">
-        <v>14.5</v>
+        <v>15.6</v>
       </c>
       <c r="AB53" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="AC53" t="n">
-        <v>7.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AD53" t="n">
-        <v>3.9</v>
+        <v>6.3</v>
       </c>
       <c r="AF53" t="n">
-        <v>218.04</v>
+        <v>220.84</v>
       </c>
       <c r="AG53" t="n">
-        <v>-0.33</v>
+        <v>2.8</v>
       </c>
       <c r="AH53" t="n">
         <v>215</v>
@@ -5689,10 +5689,10 @@
         <v>235</v>
       </c>
       <c r="AK53" t="n">
-        <v>129.21</v>
+        <v>129.07</v>
       </c>
       <c r="AL53" t="n">
-        <v>-2.03</v>
+        <v>-0.14</v>
       </c>
       <c r="AM53" t="n">
         <v>110</v>
@@ -5701,99 +5701,99 @@
         <v>142</v>
       </c>
       <c r="AP53" t="n">
-        <v>82.90000000000001</v>
+        <v>85.52</v>
       </c>
       <c r="AS53" t="n">
-        <v>15.23</v>
+        <v>15.82</v>
       </c>
       <c r="BL53" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B54" t="n">
-        <v>148.8</v>
+        <v>146.8</v>
       </c>
       <c r="C54" t="n">
-        <v>57.6</v>
+        <v>52.8</v>
       </c>
       <c r="D54" t="n">
-        <v>32.7</v>
+        <v>33.6</v>
       </c>
       <c r="E54" t="n">
-        <v>26.3</v>
+        <v>28.9</v>
       </c>
       <c r="F54" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="H54" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="I54" t="n">
-        <v>8.9</v>
+        <v>9.1</v>
       </c>
       <c r="J54" t="n">
-        <v>41.6</v>
+        <v>40.8</v>
       </c>
       <c r="K54" t="n">
-        <v>74.09999999999999</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="M54" t="n">
-        <v>7.4</v>
+        <v>5.6</v>
       </c>
       <c r="N54" t="n">
-        <v>35</v>
+        <v>33.1</v>
       </c>
       <c r="O54" t="n">
-        <v>42.4</v>
+        <v>38.7</v>
       </c>
       <c r="Q54" t="n">
-        <v>21.7</v>
+        <v>22</v>
       </c>
       <c r="R54" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>21.7</v>
+        <v>22</v>
       </c>
       <c r="V54" t="n">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="W54" t="n">
-        <v>24.1</v>
+        <v>22.9</v>
       </c>
       <c r="X54" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA54" t="n">
         <v>16.1</v>
       </c>
-      <c r="Y54" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>19</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>15.6</v>
-      </c>
       <c r="AB54" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="AC54" t="n">
-        <v>9.699999999999999</v>
+        <v>7</v>
       </c>
       <c r="AD54" t="n">
-        <v>6.3</v>
+        <v>4.5</v>
       </c>
       <c r="AF54" t="n">
-        <v>220.84</v>
+        <v>225.87</v>
       </c>
       <c r="AG54" t="n">
-        <v>2.8</v>
+        <v>5.03</v>
       </c>
       <c r="AH54" t="n">
         <v>215</v>
@@ -5802,10 +5802,10 @@
         <v>235</v>
       </c>
       <c r="AK54" t="n">
-        <v>129.07</v>
+        <v>130.73</v>
       </c>
       <c r="AL54" t="n">
-        <v>-0.14</v>
+        <v>1.66</v>
       </c>
       <c r="AM54" t="n">
         <v>110</v>
@@ -5814,99 +5814,54 @@
         <v>142</v>
       </c>
       <c r="AP54" t="n">
-        <v>85.52</v>
+        <v>88.2</v>
       </c>
       <c r="AS54" t="n">
-        <v>15.82</v>
+        <v>15.76</v>
       </c>
       <c r="BL54" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B55" t="n">
-        <v>146.8</v>
-      </c>
-      <c r="C55" t="n">
-        <v>52.8</v>
+        <v>133.9</v>
       </c>
       <c r="D55" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="E55" t="n">
-        <v>28.9</v>
+        <v>34.7</v>
       </c>
       <c r="F55" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="H55" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="I55" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="J55" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="K55" t="n">
-        <v>73.59999999999999</v>
-      </c>
-      <c r="M55" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="N55" t="n">
-        <v>33.1</v>
-      </c>
-      <c r="O55" t="n">
-        <v>38.7</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>22</v>
-      </c>
-      <c r="R55" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="S55" t="n">
-        <v>0</v>
-      </c>
-      <c r="T55" t="n">
-        <v>22</v>
+        <v>3.3</v>
       </c>
       <c r="V55" t="n">
-        <v>11</v>
+        <v>14.3</v>
       </c>
       <c r="W55" t="n">
-        <v>22.9</v>
+        <v>21.7</v>
       </c>
       <c r="X55" t="n">
-        <v>16.9</v>
+        <v>18</v>
       </c>
       <c r="Y55" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z55" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AA55" t="n">
-        <v>16.1</v>
+        <v>15</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.9</v>
+        <v>-3.5</v>
       </c>
       <c r="AC55" t="n">
-        <v>7</v>
+        <v>3.2</v>
       </c>
       <c r="AD55" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AF55" t="n">
-        <v>225.87</v>
-      </c>
-      <c r="AG55" t="n">
-        <v>5.03</v>
+        <v>-0.1</v>
       </c>
       <c r="AH55" t="n">
         <v>215</v>
@@ -5914,49 +5869,37 @@
       <c r="AI55" t="n">
         <v>235</v>
       </c>
-      <c r="AK55" t="n">
-        <v>130.73</v>
-      </c>
-      <c r="AL55" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AM55" t="n">
         <v>110</v>
       </c>
       <c r="AN55" t="n">
         <v>142</v>
       </c>
-      <c r="AP55" t="n">
-        <v>88.2</v>
-      </c>
-      <c r="AS55" t="n">
-        <v>15.76</v>
-      </c>
       <c r="BL55" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B56" t="n">
-        <v>133.9</v>
+        <v>137.5</v>
       </c>
       <c r="D56" t="n">
-        <v>34.7</v>
+        <v>32.8</v>
       </c>
       <c r="F56" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="Y56" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z56" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="AA56" t="n">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="AH56" t="n">
         <v>215</v>
@@ -5971,30 +5914,75 @@
         <v>142</v>
       </c>
       <c r="BL56" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B57" t="n">
-        <v>137.5</v>
+        <v>157.1</v>
+      </c>
+      <c r="C57" t="n">
+        <v>73.09999999999999</v>
       </c>
       <c r="D57" t="n">
-        <v>32.8</v>
+        <v>31.7</v>
+      </c>
+      <c r="E57" t="n">
+        <v>26.1</v>
       </c>
       <c r="F57" t="n">
-        <v>2.3</v>
+        <v>2</v>
+      </c>
+      <c r="H57" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="I57" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="J57" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="K57" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="M57" t="n">
+        <v>6</v>
+      </c>
+      <c r="N57" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="O57" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="R57" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>23.8</v>
       </c>
       <c r="Y57" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="Z57" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA57" t="n">
-        <v>10.5</v>
+        <v>7.9</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>224.2</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>-1.67</v>
       </c>
       <c r="AH57" t="n">
         <v>215</v>
@@ -6002,82 +5990,94 @@
       <c r="AI57" t="n">
         <v>235</v>
       </c>
+      <c r="AK57" t="n">
+        <v>128.6</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>-2.13</v>
+      </c>
       <c r="AM57" t="n">
         <v>110</v>
       </c>
       <c r="AN57" t="n">
         <v>142</v>
       </c>
+      <c r="AP57" t="n">
+        <v>81.18000000000001</v>
+      </c>
+      <c r="AS57" t="n">
+        <v>14.06</v>
+      </c>
       <c r="BL57" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B58" t="n">
-        <v>157.1</v>
+        <v>153.1</v>
       </c>
       <c r="C58" t="n">
-        <v>73.09999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="D58" t="n">
-        <v>31.7</v>
+        <v>32.2</v>
       </c>
       <c r="E58" t="n">
-        <v>26.1</v>
+        <v>25.9</v>
       </c>
       <c r="F58" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="H58" t="n">
-        <v>23.6</v>
+        <v>24.4</v>
       </c>
       <c r="I58" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="J58" t="n">
-        <v>40.5</v>
+        <v>39.6</v>
       </c>
       <c r="K58" t="n">
-        <v>73.5</v>
+        <v>73.3</v>
       </c>
       <c r="M58" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="N58" t="n">
-        <v>33.4</v>
+        <v>34.4</v>
       </c>
       <c r="O58" t="n">
-        <v>39.5</v>
+        <v>40.1</v>
       </c>
       <c r="Q58" t="n">
         <v>23.8</v>
       </c>
       <c r="R58" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="S58" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T58" t="n">
         <v>23.8</v>
       </c>
       <c r="Y58" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Z58" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA58" t="n">
         <v>12</v>
       </c>
-      <c r="AA58" t="n">
-        <v>7.9</v>
-      </c>
       <c r="AF58" t="n">
-        <v>224.2</v>
+        <v>223.35</v>
       </c>
       <c r="AG58" t="n">
-        <v>-1.67</v>
+        <v>-0.85</v>
       </c>
       <c r="AH58" t="n">
         <v>215</v>
@@ -6086,10 +6086,10 @@
         <v>235</v>
       </c>
       <c r="AK58" t="n">
-        <v>128.6</v>
+        <v>127.19</v>
       </c>
       <c r="AL58" t="n">
-        <v>-2.13</v>
+        <v>-1.41</v>
       </c>
       <c r="AM58" t="n">
         <v>110</v>
@@ -6098,81 +6098,81 @@
         <v>142</v>
       </c>
       <c r="AP58" t="n">
-        <v>81.18000000000001</v>
+        <v>81.06</v>
       </c>
       <c r="AS58" t="n">
-        <v>14.06</v>
+        <v>13.63</v>
       </c>
       <c r="BL58" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B59" t="n">
-        <v>153.1</v>
+        <v>145.5</v>
       </c>
       <c r="C59" t="n">
-        <v>69.59999999999999</v>
+        <v>62.3</v>
       </c>
       <c r="D59" t="n">
-        <v>32.2</v>
+        <v>34</v>
       </c>
       <c r="E59" t="n">
-        <v>25.9</v>
+        <v>22.5</v>
       </c>
       <c r="F59" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="H59" t="n">
-        <v>24.4</v>
+        <v>24.8</v>
       </c>
       <c r="I59" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J59" t="n">
-        <v>39.6</v>
+        <v>40.8</v>
       </c>
       <c r="K59" t="n">
-        <v>73.3</v>
+        <v>75</v>
       </c>
       <c r="M59" t="n">
-        <v>5.7</v>
+        <v>6.9</v>
       </c>
       <c r="N59" t="n">
-        <v>34.4</v>
+        <v>30.4</v>
       </c>
       <c r="O59" t="n">
-        <v>40.1</v>
+        <v>37.3</v>
       </c>
       <c r="Q59" t="n">
-        <v>23.8</v>
+        <v>22.1</v>
       </c>
       <c r="R59" t="n">
-        <v>3.8</v>
+        <v>4.9</v>
       </c>
       <c r="S59" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>23.8</v>
+        <v>22.1</v>
       </c>
       <c r="Y59" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="Z59" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AA59" t="n">
-        <v>12</v>
+        <v>12.9</v>
       </c>
       <c r="AF59" t="n">
-        <v>223.35</v>
+        <v>223.06</v>
       </c>
       <c r="AG59" t="n">
-        <v>-0.85</v>
+        <v>-0.29</v>
       </c>
       <c r="AH59" t="n">
         <v>215</v>
@@ -6181,10 +6181,10 @@
         <v>235</v>
       </c>
       <c r="AK59" t="n">
-        <v>127.19</v>
+        <v>129.17</v>
       </c>
       <c r="AL59" t="n">
-        <v>-1.41</v>
+        <v>1.98</v>
       </c>
       <c r="AM59" t="n">
         <v>110</v>
@@ -6193,78 +6193,78 @@
         <v>142</v>
       </c>
       <c r="AP59" t="n">
-        <v>81.06</v>
+        <v>82.36</v>
       </c>
       <c r="AS59" t="n">
-        <v>13.63</v>
+        <v>13.91</v>
       </c>
       <c r="BL59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B60" t="n">
-        <v>145.5</v>
+        <v>148</v>
       </c>
       <c r="C60" t="n">
-        <v>62.3</v>
+        <v>61.6</v>
       </c>
       <c r="D60" t="n">
-        <v>34</v>
+        <v>33.9</v>
       </c>
       <c r="E60" t="n">
-        <v>22.5</v>
+        <v>25</v>
       </c>
       <c r="F60" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="H60" t="n">
-        <v>24.8</v>
+        <v>25.1</v>
       </c>
       <c r="I60" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="J60" t="n">
-        <v>40.8</v>
+        <v>39.5</v>
       </c>
       <c r="K60" t="n">
-        <v>75</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="M60" t="n">
-        <v>6.9</v>
+        <v>5.9</v>
       </c>
       <c r="N60" t="n">
-        <v>30.4</v>
+        <v>28.6</v>
       </c>
       <c r="O60" t="n">
-        <v>37.3</v>
+        <v>34.5</v>
       </c>
       <c r="Q60" t="n">
-        <v>22.1</v>
+        <v>23.3</v>
       </c>
       <c r="R60" t="n">
-        <v>4.9</v>
+        <v>3.9</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>22.1</v>
+        <v>23.3</v>
       </c>
       <c r="Y60" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="Z60" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AA60" t="n">
-        <v>12.9</v>
+        <v>11.6</v>
       </c>
       <c r="AF60" t="n">
-        <v>223.06</v>
+        <v>222.77</v>
       </c>
       <c r="AG60" t="n">
         <v>-0.29</v>
@@ -6276,10 +6276,10 @@
         <v>235</v>
       </c>
       <c r="AK60" t="n">
-        <v>129.17</v>
+        <v>130.42</v>
       </c>
       <c r="AL60" t="n">
-        <v>1.98</v>
+        <v>1.25</v>
       </c>
       <c r="AM60" t="n">
         <v>110</v>
@@ -6288,36 +6288,36 @@
         <v>142</v>
       </c>
       <c r="AP60" t="n">
-        <v>82.36</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="AS60" t="n">
-        <v>13.91</v>
+        <v>14</v>
       </c>
       <c r="BL60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B61" t="n">
-        <v>132.5</v>
+        <v>125</v>
       </c>
       <c r="D61" t="n">
-        <v>33.4</v>
+        <v>34.2</v>
       </c>
       <c r="F61" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="Y61" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Z61" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="AA61" t="n">
-        <v>10.5</v>
+        <v>16.5</v>
       </c>
       <c r="AH61" t="n">
         <v>215</v>
@@ -6332,30 +6332,30 @@
         <v>142</v>
       </c>
       <c r="BL61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B62" t="n">
-        <v>125</v>
+        <v>118.1</v>
       </c>
       <c r="D62" t="n">
-        <v>34.2</v>
+        <v>34.7</v>
       </c>
       <c r="F62" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="Y62" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Z62" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA62" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AH62" t="n">
         <v>215</v>
@@ -6370,7 +6370,7 @@
         <v>142</v>
       </c>
       <c r="BL62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -628,88 +628,88 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46223</v>
+        <v>46232</v>
       </c>
       <c r="B2" t="n">
-        <v>176.4</v>
+        <v>172.9</v>
       </c>
       <c r="C2" t="n">
-        <v>77.09999999999999</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>32.7</v>
+        <v>34.9</v>
       </c>
       <c r="E2" t="n">
-        <v>35</v>
+        <v>35.2</v>
       </c>
       <c r="F2" t="n">
-        <v>6.8</v>
+        <v>7.3</v>
       </c>
       <c r="H2" t="n">
-        <v>23.2</v>
+        <v>23.6</v>
       </c>
       <c r="I2" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="J2" t="n">
-        <v>41.5</v>
+        <v>41.7</v>
       </c>
       <c r="K2" t="n">
-        <v>76</v>
+        <v>76.7</v>
       </c>
       <c r="M2" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="N2" t="n">
-        <v>36.4</v>
+        <v>34.8</v>
       </c>
       <c r="O2" t="n">
-        <v>39.1</v>
+        <v>37.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>22.3</v>
+        <v>19</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T2" t="n">
-        <v>22.3</v>
+        <v>19</v>
       </c>
       <c r="V2" t="n">
-        <v>11.5</v>
+        <v>14.4</v>
       </c>
       <c r="W2" t="n">
-        <v>15.5</v>
+        <v>18.7</v>
       </c>
       <c r="X2" t="n">
-        <v>13.5</v>
+        <v>16.6</v>
       </c>
       <c r="Y2" t="n">
         <v>9</v>
       </c>
       <c r="Z2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA2" t="n">
-        <v>11.6</v>
+        <v>12.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>-5.6</v>
+        <v>-4.9</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>-1.3</v>
+        <v>-0.7</v>
       </c>
       <c r="AF2" t="n">
-        <v>220.92</v>
+        <v>218.6</v>
       </c>
       <c r="AG2" t="n">
-        <v>-4.59</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="AH2" t="n">
         <v>215</v>
@@ -718,10 +718,10 @@
         <v>235</v>
       </c>
       <c r="AK2" t="n">
-        <v>131.85</v>
+        <v>130.39</v>
       </c>
       <c r="AL2" t="n">
-        <v>-1.98</v>
+        <v>-4.15</v>
       </c>
       <c r="AM2" t="n">
         <v>110</v>
@@ -730,99 +730,99 @@
         <v>142</v>
       </c>
       <c r="AP2" t="n">
-        <v>79.75</v>
+        <v>78.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>15.49</v>
+        <v>15.79</v>
       </c>
       <c r="BL2" s="1" t="n">
-        <v>46223</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46224</v>
+        <v>46233</v>
       </c>
       <c r="B3" t="n">
-        <v>181</v>
+        <v>157.5</v>
       </c>
       <c r="C3" t="n">
-        <v>80.7</v>
+        <v>68.5</v>
       </c>
       <c r="D3" t="n">
-        <v>33</v>
+        <v>33.2</v>
       </c>
       <c r="E3" t="n">
-        <v>35.1</v>
+        <v>27.7</v>
       </c>
       <c r="F3" t="n">
-        <v>5.7</v>
+        <v>3.6</v>
       </c>
       <c r="H3" t="n">
-        <v>22.8</v>
+        <v>23.4</v>
       </c>
       <c r="I3" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="J3" t="n">
-        <v>41.9</v>
+        <v>41.4</v>
       </c>
       <c r="K3" t="n">
-        <v>75.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="N3" t="n">
-        <v>36.9</v>
+        <v>34.9</v>
       </c>
       <c r="O3" t="n">
-        <v>39.8</v>
+        <v>37.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>22.5</v>
+        <v>21.6</v>
       </c>
       <c r="R3" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>20.5</v>
+        <v>9</v>
       </c>
       <c r="T3" t="n">
-        <v>22.5</v>
+        <v>21.6</v>
       </c>
       <c r="V3" t="n">
-        <v>10.6</v>
+        <v>15.1</v>
       </c>
       <c r="W3" t="n">
-        <v>13</v>
+        <v>23.1</v>
       </c>
       <c r="X3" t="n">
-        <v>11.8</v>
+        <v>19.1</v>
       </c>
       <c r="Y3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z3" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AA3" t="n">
-        <v>11.4</v>
+        <v>13.6</v>
       </c>
       <c r="AB3" t="n">
-        <v>-6.1</v>
+        <v>-0</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.9</v>
+        <v>1.5</v>
       </c>
       <c r="AF3" t="n">
-        <v>220.92</v>
+        <v>218.84</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AH3" t="n">
         <v>215</v>
@@ -831,10 +831,10 @@
         <v>235</v>
       </c>
       <c r="AK3" t="n">
-        <v>130.06</v>
+        <v>133.09</v>
       </c>
       <c r="AL3" t="n">
-        <v>-1.79</v>
+        <v>2.7</v>
       </c>
       <c r="AM3" t="n">
         <v>110</v>
@@ -843,99 +843,66 @@
         <v>142</v>
       </c>
       <c r="AP3" t="n">
-        <v>79.94</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="AS3" t="n">
-        <v>14.93</v>
+        <v>15.63</v>
       </c>
       <c r="BL3" s="1" t="n">
-        <v>46224</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46225</v>
+        <v>46234</v>
       </c>
       <c r="B4" t="n">
-        <v>179.6</v>
-      </c>
-      <c r="C4" t="n">
-        <v>81.90000000000001</v>
+        <v>137.6</v>
       </c>
       <c r="D4" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="E4" t="n">
-        <v>31.1</v>
+        <v>35</v>
       </c>
       <c r="F4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="H4" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="I4" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="J4" t="n">
-        <v>42.3</v>
+        <v>6.5</v>
       </c>
       <c r="K4" t="n">
-        <v>74.59999999999999</v>
-      </c>
-      <c r="M4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="N4" t="n">
-        <v>37.1</v>
+        <v>96.7</v>
       </c>
       <c r="O4" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2</v>
-      </c>
-      <c r="S4" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="T4" t="n">
-        <v>22.6</v>
+        <v>35.1</v>
       </c>
       <c r="V4" t="n">
-        <v>9.6</v>
+        <v>13.6</v>
       </c>
       <c r="W4" t="n">
-        <v>15.6</v>
+        <v>24.4</v>
       </c>
       <c r="X4" t="n">
-        <v>12.6</v>
+        <v>19</v>
       </c>
       <c r="Y4" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="Z4" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AA4" t="n">
-        <v>11.1</v>
+        <v>17.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>-3.4</v>
+        <v>-0</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="AF4" t="n">
-        <v>216.02</v>
+        <v>221.78</v>
       </c>
       <c r="AG4" t="n">
-        <v>-0.9399999999999999</v>
+        <v>2.94</v>
       </c>
       <c r="AH4" t="n">
         <v>215</v>
@@ -944,10 +911,10 @@
         <v>235</v>
       </c>
       <c r="AK4" t="n">
-        <v>127.85</v>
+        <v>138.76</v>
       </c>
       <c r="AL4" t="n">
-        <v>-2.21</v>
+        <v>5.67</v>
       </c>
       <c r="AM4" t="n">
         <v>110</v>
@@ -955,100 +922,61 @@
       <c r="AN4" t="n">
         <v>142</v>
       </c>
-      <c r="AP4" t="n">
-        <v>82.2</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>15.16</v>
-      </c>
       <c r="BL4" s="1" t="n">
-        <v>46225</v>
+        <v>46234</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46226</v>
+        <v>46235</v>
       </c>
       <c r="B5" t="n">
-        <v>170.4</v>
-      </c>
-      <c r="C5" t="n">
-        <v>78.5</v>
+        <v>132.5</v>
       </c>
       <c r="D5" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="E5" t="n">
-        <v>29.7</v>
+        <v>33.6</v>
       </c>
       <c r="F5" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="H5" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="I5" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="J5" t="n">
-        <v>41.4</v>
+        <v>3.5</v>
       </c>
       <c r="K5" t="n">
-        <v>75</v>
-      </c>
-      <c r="M5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="N5" t="n">
-        <v>36.6</v>
+        <v>97.8</v>
       </c>
       <c r="O5" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S5" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>23.3</v>
+        <v>31.6</v>
       </c>
       <c r="V5" t="n">
-        <v>9.5</v>
+        <v>14.8</v>
       </c>
       <c r="W5" t="n">
-        <v>15.7</v>
+        <v>24.7</v>
       </c>
       <c r="X5" t="n">
-        <v>12.6</v>
+        <v>19.8</v>
       </c>
       <c r="Y5" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="Z5" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="AA5" t="n">
-        <v>12.7</v>
+        <v>16.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.5</v>
+        <v>3.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>4.7</v>
+        <v>2.1</v>
       </c>
       <c r="AF5" t="n">
-        <v>216.02</v>
+        <v>224.78</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH5" t="n">
         <v>215</v>
@@ -1057,10 +985,10 @@
         <v>235</v>
       </c>
       <c r="AK5" t="n">
-        <v>128.54</v>
+        <v>143.55</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.6899999999999999</v>
+        <v>4.79</v>
       </c>
       <c r="AM5" t="n">
         <v>110</v>
@@ -1068,43 +996,70 @@
       <c r="AN5" t="n">
         <v>142</v>
       </c>
-      <c r="AP5" t="n">
-        <v>84.73</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>15.34</v>
-      </c>
       <c r="BL5" s="1" t="n">
-        <v>46226</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46227</v>
+        <v>46236</v>
       </c>
       <c r="B6" t="n">
-        <v>156</v>
+        <v>137.2</v>
+      </c>
+      <c r="C6" t="n">
+        <v>56.3</v>
       </c>
       <c r="D6" t="n">
-        <v>30.1</v>
+        <v>32.1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>21.2</v>
       </c>
       <c r="F6" t="n">
-        <v>6.8</v>
+        <v>4.5</v>
+      </c>
+      <c r="H6" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="I6" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="J6" t="n">
+        <v>40.4</v>
       </c>
       <c r="K6" t="n">
-        <v>95.90000000000001</v>
+        <v>75.7</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N6" t="n">
+        <v>29</v>
       </c>
       <c r="O6" t="n">
-        <v>39.2</v>
+        <v>32.6</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>21.6</v>
       </c>
       <c r="V6" t="n">
-        <v>7.1</v>
+        <v>10.7</v>
       </c>
       <c r="W6" t="n">
-        <v>20.9</v>
+        <v>24.3</v>
       </c>
       <c r="X6" t="n">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="Y6" t="n">
         <v>12</v>
@@ -1113,22 +1068,22 @@
         <v>15</v>
       </c>
       <c r="AA6" t="n">
-        <v>13.5</v>
+        <v>15.4</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.2</v>
+        <v>0.9</v>
       </c>
       <c r="AC6" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="AF6" t="n">
-        <v>224.53</v>
+        <v>232.22</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.32</v>
+        <v>7.43</v>
       </c>
       <c r="AH6" t="n">
         <v>215</v>
@@ -1137,10 +1092,10 @@
         <v>235</v>
       </c>
       <c r="AK6" t="n">
-        <v>130.92</v>
+        <v>143.61</v>
       </c>
       <c r="AL6" t="n">
-        <v>2.38</v>
+        <v>0.06</v>
       </c>
       <c r="AM6" t="n">
         <v>110</v>
@@ -1148,61 +1103,100 @@
       <c r="AN6" t="n">
         <v>142</v>
       </c>
+      <c r="AP6" t="n">
+        <v>89.31999999999999</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>18.02</v>
+      </c>
       <c r="BL6" s="1" t="n">
-        <v>46227</v>
+        <v>46236</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46228</v>
+        <v>46237</v>
       </c>
       <c r="B7" t="n">
-        <v>147.8</v>
+        <v>157.5</v>
+      </c>
+      <c r="C7" t="n">
+        <v>59.6</v>
       </c>
       <c r="D7" t="n">
-        <v>32</v>
+        <v>35</v>
+      </c>
+      <c r="E7" t="n">
+        <v>30.6</v>
       </c>
       <c r="F7" t="n">
-        <v>6.8</v>
+        <v>7.5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="I7" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>38.9</v>
       </c>
       <c r="K7" t="n">
-        <v>96.5</v>
+        <v>74.3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N7" t="n">
+        <v>33.4</v>
       </c>
       <c r="O7" t="n">
-        <v>39.3</v>
+        <v>37.1</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>21.1</v>
       </c>
       <c r="V7" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="W7" t="n">
-        <v>22.4</v>
+        <v>26.3</v>
       </c>
       <c r="X7" t="n">
-        <v>15.2</v>
+        <v>19.6</v>
       </c>
       <c r="Y7" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Z7" t="n">
         <v>16</v>
       </c>
       <c r="AA7" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.3</v>
+        <v>-2.1</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AF7" t="n">
-        <v>230.27</v>
+        <v>229.69</v>
       </c>
       <c r="AG7" t="n">
-        <v>5.74</v>
+        <v>-2.53</v>
       </c>
       <c r="AH7" t="n">
         <v>215</v>
@@ -1211,10 +1205,10 @@
         <v>235</v>
       </c>
       <c r="AK7" t="n">
-        <v>132.76</v>
+        <v>136.96</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.84</v>
+        <v>-6.65</v>
       </c>
       <c r="AM7" t="n">
         <v>110</v>
@@ -1222,94 +1216,100 @@
       <c r="AN7" t="n">
         <v>142</v>
       </c>
+      <c r="AP7" t="n">
+        <v>86.59</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>16.96</v>
+      </c>
       <c r="BL7" s="1" t="n">
-        <v>46228</v>
+        <v>46237</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46229</v>
+        <v>46238</v>
       </c>
       <c r="B8" t="n">
-        <v>149.1</v>
+        <v>159.6</v>
       </c>
       <c r="C8" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D8" t="n">
-        <v>29</v>
+        <v>34.5</v>
       </c>
       <c r="E8" t="n">
-        <v>25.9</v>
+        <v>31.1</v>
       </c>
       <c r="F8" t="n">
-        <v>7.4</v>
+        <v>5.7</v>
       </c>
       <c r="H8" t="n">
-        <v>24</v>
+        <v>23.8</v>
       </c>
       <c r="I8" t="n">
-        <v>11.7</v>
+        <v>10.8</v>
       </c>
       <c r="J8" t="n">
-        <v>38.8</v>
+        <v>40.5</v>
       </c>
       <c r="K8" t="n">
-        <v>74.5</v>
+        <v>75.2</v>
       </c>
       <c r="M8" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="N8" t="n">
-        <v>36.7</v>
+        <v>34.3</v>
       </c>
       <c r="O8" t="n">
-        <v>40.1</v>
+        <v>38.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>21.7</v>
+        <v>21.3</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T8" t="n">
-        <v>21.7</v>
+        <v>21.3</v>
       </c>
       <c r="V8" t="n">
-        <v>10.3</v>
+        <v>17.5</v>
       </c>
       <c r="W8" t="n">
-        <v>24.4</v>
+        <v>22.5</v>
       </c>
       <c r="X8" t="n">
-        <v>17.4</v>
+        <v>20</v>
       </c>
       <c r="Y8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AA8" t="n">
-        <v>15.7</v>
+        <v>13.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>-2.4</v>
+        <v>-2.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.2</v>
+        <v>4.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0.1</v>
+        <v>1.2</v>
       </c>
       <c r="AF8" t="n">
-        <v>237.43</v>
+        <v>228.57</v>
       </c>
       <c r="AG8" t="n">
-        <v>7.16</v>
+        <v>-1.14</v>
       </c>
       <c r="AH8" t="n">
         <v>215</v>
@@ -1318,10 +1318,10 @@
         <v>235</v>
       </c>
       <c r="AK8" t="n">
-        <v>134.95</v>
+        <v>133.01</v>
       </c>
       <c r="AL8" t="n">
-        <v>2.19</v>
+        <v>-3.95</v>
       </c>
       <c r="AM8" t="n">
         <v>110</v>
@@ -1330,66 +1330,99 @@
         <v>142</v>
       </c>
       <c r="AP8" t="n">
-        <v>91.28</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="AS8" t="n">
-        <v>16.95</v>
+        <v>15.95</v>
       </c>
       <c r="BL8" s="1" t="n">
-        <v>46229</v>
+        <v>46238</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46230</v>
+        <v>46239</v>
       </c>
       <c r="B9" t="n">
-        <v>143.9</v>
+        <v>160.4</v>
+      </c>
+      <c r="C9" t="n">
+        <v>62.6</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9</v>
+        <v>35</v>
+      </c>
+      <c r="E9" t="n">
+        <v>32.2</v>
       </c>
       <c r="F9" t="n">
-        <v>6.8</v>
+        <v>4.7</v>
+      </c>
+      <c r="H9" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="I9" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J9" t="n">
+        <v>41.1</v>
       </c>
       <c r="K9" t="n">
-        <v>96.2</v>
+        <v>75.7</v>
+      </c>
+      <c r="M9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="N9" t="n">
+        <v>32.6</v>
       </c>
       <c r="O9" t="n">
-        <v>37.9</v>
+        <v>38</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="S9" t="n">
+        <v>8</v>
+      </c>
+      <c r="T9" t="n">
+        <v>20.9</v>
       </c>
       <c r="V9" t="n">
-        <v>10</v>
+        <v>16.4</v>
       </c>
       <c r="W9" t="n">
-        <v>25.6</v>
+        <v>22.8</v>
       </c>
       <c r="X9" t="n">
-        <v>17.8</v>
+        <v>19.6</v>
       </c>
       <c r="Y9" t="n">
         <v>13</v>
       </c>
       <c r="Z9" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AA9" t="n">
-        <v>16</v>
+        <v>14.1</v>
       </c>
       <c r="AB9" t="n">
-        <v>-1.4</v>
+        <v>-3.1</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="AF9" t="n">
-        <v>236.14</v>
+        <v>225.08</v>
       </c>
       <c r="AG9" t="n">
-        <v>-1.29</v>
+        <v>-3.5</v>
       </c>
       <c r="AH9" t="n">
         <v>215</v>
@@ -1398,10 +1431,10 @@
         <v>235</v>
       </c>
       <c r="AK9" t="n">
-        <v>136.28</v>
+        <v>135.24</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.33</v>
+        <v>2.23</v>
       </c>
       <c r="AM9" t="n">
         <v>110</v>
@@ -1409,94 +1442,100 @@
       <c r="AN9" t="n">
         <v>142</v>
       </c>
+      <c r="AP9" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>15.4</v>
+      </c>
       <c r="BL9" s="1" t="n">
-        <v>46230</v>
+        <v>46239</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46231</v>
+        <v>46240</v>
       </c>
       <c r="B10" t="n">
-        <v>166.4</v>
+        <v>161.7</v>
       </c>
       <c r="C10" t="n">
-        <v>63.7</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>34.5</v>
+        <v>34.9</v>
       </c>
       <c r="E10" t="n">
-        <v>36.4</v>
+        <v>27.3</v>
       </c>
       <c r="F10" t="n">
-        <v>7.6</v>
+        <v>4.6</v>
       </c>
       <c r="H10" t="n">
-        <v>23.7</v>
+        <v>24.1</v>
       </c>
       <c r="I10" t="n">
-        <v>11.6</v>
+        <v>10.3</v>
       </c>
       <c r="J10" t="n">
-        <v>39.9</v>
+        <v>42.6</v>
       </c>
       <c r="K10" t="n">
-        <v>75.2</v>
+        <v>77</v>
       </c>
       <c r="M10" t="n">
-        <v>3.1</v>
+        <v>5.8</v>
       </c>
       <c r="N10" t="n">
-        <v>35.9</v>
+        <v>31.5</v>
       </c>
       <c r="O10" t="n">
-        <v>39</v>
+        <v>37.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>20.3</v>
+        <v>21</v>
       </c>
       <c r="R10" t="n">
-        <v>0.8</v>
+        <v>3.7</v>
       </c>
       <c r="S10" t="n">
         <v>6</v>
       </c>
       <c r="T10" t="n">
-        <v>20.3</v>
+        <v>21</v>
       </c>
       <c r="V10" t="n">
-        <v>11.9</v>
+        <v>12.7</v>
       </c>
       <c r="W10" t="n">
         <v>27</v>
       </c>
       <c r="X10" t="n">
-        <v>19.4</v>
+        <v>19.9</v>
       </c>
       <c r="Y10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Z10" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AA10" t="n">
-        <v>14.4</v>
+        <v>11.4</v>
       </c>
       <c r="AB10" t="n">
-        <v>-3.5</v>
+        <v>-5.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.6</v>
+        <v>4.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="AF10" t="n">
-        <v>236.13</v>
+        <v>225</v>
       </c>
       <c r="AG10" t="n">
-        <v>-0.01</v>
+        <v>-0.08</v>
       </c>
       <c r="AH10" t="n">
         <v>215</v>
@@ -1505,10 +1544,10 @@
         <v>235</v>
       </c>
       <c r="AK10" t="n">
-        <v>134.54</v>
+        <v>134.62</v>
       </c>
       <c r="AL10" t="n">
-        <v>-1.74</v>
+        <v>-0.62</v>
       </c>
       <c r="AM10" t="n">
         <v>110</v>
@@ -1517,99 +1556,60 @@
         <v>142</v>
       </c>
       <c r="AP10" t="n">
-        <v>82.27</v>
+        <v>80.2</v>
       </c>
       <c r="AS10" t="n">
-        <v>16.28</v>
+        <v>13.86</v>
       </c>
       <c r="BL10" s="1" t="n">
-        <v>46231</v>
+        <v>46240</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46232</v>
+        <v>46241</v>
       </c>
       <c r="B11" t="n">
-        <v>172.9</v>
-      </c>
-      <c r="C11" t="n">
-        <v>67.59999999999999</v>
+        <v>151.5</v>
       </c>
       <c r="D11" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="E11" t="n">
-        <v>35.2</v>
+        <v>35.1</v>
       </c>
       <c r="F11" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="H11" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="I11" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J11" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="K11" t="n">
-        <v>76.7</v>
-      </c>
-      <c r="M11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="N11" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="O11" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>19</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>10</v>
-      </c>
-      <c r="T11" t="n">
-        <v>19</v>
+        <v>5.4</v>
       </c>
       <c r="V11" t="n">
-        <v>14.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>18.7</v>
+        <v>19.4</v>
       </c>
       <c r="X11" t="n">
-        <v>16.6</v>
+        <v>14</v>
       </c>
       <c r="Y11" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA11" t="n">
         <v>9</v>
       </c>
-      <c r="Z11" t="n">
-        <v>15</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AB11" t="n">
-        <v>-4.9</v>
+        <v>-4.7</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.6</v>
+        <v>1.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0.7</v>
+        <v>-1.4</v>
       </c>
       <c r="AF11" t="n">
-        <v>218.6</v>
+        <v>221.37</v>
       </c>
       <c r="AG11" t="n">
-        <v>-9.380000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="AH11" t="n">
         <v>215</v>
@@ -1618,10 +1618,10 @@
         <v>235</v>
       </c>
       <c r="AK11" t="n">
-        <v>130.39</v>
+        <v>135.21</v>
       </c>
       <c r="AL11" t="n">
-        <v>-4.15</v>
+        <v>0.59</v>
       </c>
       <c r="AM11" t="n">
         <v>110</v>
@@ -1629,101 +1629,62 @@
       <c r="AN11" t="n">
         <v>142</v>
       </c>
-      <c r="AP11" t="n">
-        <v>78.5</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>15.79</v>
-      </c>
       <c r="BL11" s="1" t="n">
-        <v>46232</v>
+        <v>46241</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46233</v>
+        <v>46242</v>
       </c>
       <c r="B12" t="n">
-        <v>157.5</v>
-      </c>
-      <c r="C12" t="n">
-        <v>68.5</v>
+        <v>145.2</v>
       </c>
       <c r="D12" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="E12" t="n">
-        <v>27.7</v>
+        <v>33.5</v>
       </c>
       <c r="F12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H12" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="I12" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J12" t="n">
-        <v>41.4</v>
+        <v>5</v>
       </c>
       <c r="K12" t="n">
-        <v>76.09999999999999</v>
-      </c>
-      <c r="M12" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="N12" t="n">
-        <v>34.9</v>
+        <v>100.3</v>
       </c>
       <c r="O12" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>9</v>
-      </c>
-      <c r="T12" t="n">
-        <v>21.6</v>
+        <v>35.5</v>
       </c>
       <c r="V12" t="n">
-        <v>15.1</v>
+        <v>7.1</v>
       </c>
       <c r="W12" t="n">
-        <v>23.1</v>
+        <v>19.2</v>
       </c>
       <c r="X12" t="n">
-        <v>19.1</v>
+        <v>13.1</v>
       </c>
       <c r="Y12" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Z12" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AA12" t="n">
-        <v>13.6</v>
+        <v>10</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0</v>
+        <v>-5.4</v>
       </c>
       <c r="AC12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>224.37</v>
+      </c>
+      <c r="AG12" t="n">
         <v>3</v>
       </c>
-      <c r="AD12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>218.84</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0.25</v>
-      </c>
       <c r="AH12" t="n">
         <v>215</v>
       </c>
@@ -1731,10 +1692,10 @@
         <v>235</v>
       </c>
       <c r="AK12" t="n">
-        <v>133.09</v>
+        <v>135.61</v>
       </c>
       <c r="AL12" t="n">
-        <v>2.7</v>
+        <v>0.4</v>
       </c>
       <c r="AM12" t="n">
         <v>110</v>
@@ -1742,67 +1703,61 @@
       <c r="AN12" t="n">
         <v>142</v>
       </c>
-      <c r="AP12" t="n">
-        <v>83.09999999999999</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>15.63</v>
-      </c>
       <c r="BL12" s="1" t="n">
-        <v>46233</v>
+        <v>46242</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46234</v>
+        <v>46243</v>
       </c>
       <c r="B13" t="n">
-        <v>137.6</v>
+        <v>146.3</v>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>33.4</v>
       </c>
       <c r="F13" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="K13" t="n">
-        <v>96.7</v>
+        <v>98.2</v>
       </c>
       <c r="O13" t="n">
         <v>35.1</v>
       </c>
       <c r="V13" t="n">
-        <v>13.6</v>
+        <v>4.9</v>
       </c>
       <c r="W13" t="n">
-        <v>24.4</v>
+        <v>16.4</v>
       </c>
       <c r="X13" t="n">
-        <v>19</v>
+        <v>10.6</v>
       </c>
       <c r="Y13" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="Z13" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AA13" t="n">
-        <v>17.5</v>
+        <v>9</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0</v>
+        <v>-6.4</v>
       </c>
       <c r="AC13" t="n">
-        <v>5.5</v>
+        <v>-0.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.8</v>
+        <v>-3.3</v>
       </c>
       <c r="AF13" t="n">
-        <v>221.78</v>
+        <v>225.93</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.94</v>
+        <v>1.56</v>
       </c>
       <c r="AH13" t="n">
         <v>215</v>
@@ -1811,10 +1766,10 @@
         <v>235</v>
       </c>
       <c r="AK13" t="n">
-        <v>138.76</v>
+        <v>135.28</v>
       </c>
       <c r="AL13" t="n">
-        <v>5.67</v>
+        <v>-0.33</v>
       </c>
       <c r="AM13" t="n">
         <v>110</v>
@@ -1823,60 +1778,93 @@
         <v>142</v>
       </c>
       <c r="BL13" s="1" t="n">
-        <v>46234</v>
+        <v>46243</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46235</v>
+        <v>46244</v>
       </c>
       <c r="B14" t="n">
-        <v>132.5</v>
+        <v>182.8</v>
+      </c>
+      <c r="C14" t="n">
+        <v>86.8</v>
       </c>
       <c r="D14" t="n">
-        <v>33.6</v>
+        <v>31.8</v>
+      </c>
+      <c r="E14" t="n">
+        <v>33</v>
       </c>
       <c r="F14" t="n">
-        <v>3.5</v>
+        <v>5.7</v>
+      </c>
+      <c r="H14" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="I14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J14" t="n">
+        <v>41.1</v>
       </c>
       <c r="K14" t="n">
-        <v>97.8</v>
+        <v>74.2</v>
+      </c>
+      <c r="M14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="N14" t="n">
+        <v>33.5</v>
       </c>
       <c r="O14" t="n">
-        <v>31.6</v>
+        <v>38.4</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="n">
+        <v>22.4</v>
       </c>
       <c r="V14" t="n">
-        <v>14.8</v>
+        <v>9.1</v>
       </c>
       <c r="W14" t="n">
-        <v>24.7</v>
+        <v>15</v>
       </c>
       <c r="X14" t="n">
-        <v>19.8</v>
+        <v>12.1</v>
       </c>
       <c r="Y14" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="Z14" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AA14" t="n">
-        <v>16.5</v>
+        <v>8.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.6</v>
+        <v>-10.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.6</v>
+        <v>0.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.1</v>
+        <v>-5.1</v>
       </c>
       <c r="AF14" t="n">
-        <v>224.78</v>
+        <v>218.63</v>
       </c>
       <c r="AG14" t="n">
-        <v>3</v>
+        <v>-7.3</v>
       </c>
       <c r="AH14" t="n">
         <v>215</v>
@@ -1885,10 +1873,10 @@
         <v>235</v>
       </c>
       <c r="AK14" t="n">
-        <v>143.55</v>
+        <v>126.27</v>
       </c>
       <c r="AL14" t="n">
-        <v>4.79</v>
+        <v>-9.01</v>
       </c>
       <c r="AM14" t="n">
         <v>110</v>
@@ -1896,94 +1884,100 @@
       <c r="AN14" t="n">
         <v>142</v>
       </c>
+      <c r="AP14" t="n">
+        <v>82.66</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>14.7</v>
+      </c>
       <c r="BL14" s="1" t="n">
-        <v>46235</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46236</v>
+        <v>46245</v>
       </c>
       <c r="B15" t="n">
-        <v>137.2</v>
+        <v>181.8</v>
       </c>
       <c r="C15" t="n">
-        <v>56.3</v>
+        <v>86.5</v>
       </c>
       <c r="D15" t="n">
-        <v>32.1</v>
+        <v>31.4</v>
       </c>
       <c r="E15" t="n">
-        <v>21.2</v>
+        <v>34.2</v>
       </c>
       <c r="F15" t="n">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="H15" t="n">
-        <v>23.7</v>
+        <v>24.4</v>
       </c>
       <c r="I15" t="n">
-        <v>11.6</v>
+        <v>10.4</v>
       </c>
       <c r="J15" t="n">
-        <v>40.4</v>
+        <v>41.9</v>
       </c>
       <c r="K15" t="n">
-        <v>75.7</v>
+        <v>76.8</v>
       </c>
       <c r="M15" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="N15" t="n">
-        <v>29</v>
+        <v>35.7</v>
       </c>
       <c r="O15" t="n">
-        <v>32.6</v>
+        <v>39.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>21.6</v>
+        <v>23</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>20.1</v>
       </c>
       <c r="T15" t="n">
-        <v>21.6</v>
+        <v>23</v>
       </c>
       <c r="V15" t="n">
-        <v>10.7</v>
+        <v>7.1</v>
       </c>
       <c r="W15" t="n">
-        <v>24.3</v>
+        <v>14.8</v>
       </c>
       <c r="X15" t="n">
-        <v>17.5</v>
+        <v>10.9</v>
       </c>
       <c r="Y15" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z15" t="n">
         <v>12</v>
       </c>
-      <c r="Z15" t="n">
-        <v>15</v>
-      </c>
       <c r="AA15" t="n">
-        <v>15.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.9</v>
+        <v>-4.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>5.5</v>
+        <v>1.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>3.2</v>
+        <v>-1.4</v>
       </c>
       <c r="AF15" t="n">
-        <v>232.22</v>
+        <v>216.39</v>
       </c>
       <c r="AG15" t="n">
-        <v>7.43</v>
+        <v>-2.23</v>
       </c>
       <c r="AH15" t="n">
         <v>215</v>
@@ -1992,10 +1986,10 @@
         <v>235</v>
       </c>
       <c r="AK15" t="n">
-        <v>143.61</v>
+        <v>123.32</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.06</v>
+        <v>-2.95</v>
       </c>
       <c r="AM15" t="n">
         <v>110</v>
@@ -2004,99 +1998,99 @@
         <v>142</v>
       </c>
       <c r="AP15" t="n">
-        <v>89.31999999999999</v>
+        <v>79.08</v>
       </c>
       <c r="AS15" t="n">
-        <v>18.02</v>
+        <v>13.91</v>
       </c>
       <c r="BL15" s="1" t="n">
-        <v>46236</v>
+        <v>46245</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46237</v>
+        <v>46246</v>
       </c>
       <c r="B16" t="n">
-        <v>157.5</v>
+        <v>183</v>
       </c>
       <c r="C16" t="n">
-        <v>59.6</v>
+        <v>84.7</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>30.9</v>
       </c>
       <c r="E16" t="n">
-        <v>30.6</v>
+        <v>33.7</v>
       </c>
       <c r="F16" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="H16" t="n">
-        <v>24.2</v>
+        <v>23.4</v>
       </c>
       <c r="I16" t="n">
-        <v>11.2</v>
+        <v>10.6</v>
       </c>
       <c r="J16" t="n">
-        <v>38.9</v>
+        <v>42.3</v>
       </c>
       <c r="K16" t="n">
-        <v>74.3</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>33.4</v>
+        <v>36.7</v>
       </c>
       <c r="O16" t="n">
-        <v>37.1</v>
+        <v>40.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>21.1</v>
+        <v>23.6</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>20.8</v>
       </c>
       <c r="T16" t="n">
-        <v>21.1</v>
+        <v>23.6</v>
       </c>
       <c r="V16" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="W16" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="X16" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z16" t="n">
         <v>13</v>
       </c>
-      <c r="W16" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="X16" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>16</v>
-      </c>
       <c r="AA16" t="n">
-        <v>15.5</v>
+        <v>10</v>
       </c>
       <c r="AB16" t="n">
-        <v>-2.1</v>
+        <v>0.8</v>
       </c>
       <c r="AC16" t="n">
-        <v>6.2</v>
+        <v>2.7</v>
       </c>
       <c r="AD16" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AF16" t="n">
-        <v>229.69</v>
+        <v>217.16</v>
       </c>
       <c r="AG16" t="n">
-        <v>-2.53</v>
+        <v>0.76</v>
       </c>
       <c r="AH16" t="n">
         <v>215</v>
@@ -2105,10 +2099,10 @@
         <v>235</v>
       </c>
       <c r="AK16" t="n">
-        <v>136.96</v>
+        <v>117.87</v>
       </c>
       <c r="AL16" t="n">
-        <v>-6.65</v>
+        <v>-5.45</v>
       </c>
       <c r="AM16" t="n">
         <v>110</v>
@@ -2117,99 +2111,66 @@
         <v>142</v>
       </c>
       <c r="AP16" t="n">
-        <v>86.59</v>
+        <v>78.56</v>
       </c>
       <c r="AS16" t="n">
-        <v>16.96</v>
+        <v>13.45</v>
       </c>
       <c r="BL16" s="1" t="n">
-        <v>46237</v>
+        <v>46246</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46238</v>
+        <v>46247</v>
       </c>
       <c r="B17" t="n">
-        <v>159.6</v>
-      </c>
-      <c r="C17" t="n">
-        <v>63</v>
+        <v>163.8</v>
       </c>
       <c r="D17" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="E17" t="n">
-        <v>31.1</v>
+        <v>29</v>
       </c>
       <c r="F17" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="H17" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="I17" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="J17" t="n">
-        <v>40.5</v>
+        <v>6.5</v>
       </c>
       <c r="K17" t="n">
-        <v>75.2</v>
-      </c>
-      <c r="M17" t="n">
-        <v>4</v>
-      </c>
-      <c r="N17" t="n">
-        <v>34.3</v>
+        <v>101.2</v>
       </c>
       <c r="O17" t="n">
-        <v>38.2</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>21.3</v>
+        <v>40.2</v>
       </c>
       <c r="V17" t="n">
-        <v>17.5</v>
+        <v>6.3</v>
       </c>
       <c r="W17" t="n">
-        <v>22.5</v>
+        <v>17.2</v>
       </c>
       <c r="X17" t="n">
-        <v>20</v>
+        <v>11.8</v>
       </c>
       <c r="Y17" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Z17" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AA17" t="n">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="AB17" t="n">
-        <v>-2.2</v>
+        <v>1.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="AF17" t="n">
-        <v>228.57</v>
+        <v>220.31</v>
       </c>
       <c r="AG17" t="n">
-        <v>-1.14</v>
+        <v>3.16</v>
       </c>
       <c r="AH17" t="n">
         <v>215</v>
@@ -2218,10 +2179,10 @@
         <v>235</v>
       </c>
       <c r="AK17" t="n">
-        <v>133.01</v>
+        <v>116.52</v>
       </c>
       <c r="AL17" t="n">
-        <v>-3.95</v>
+        <v>-1.35</v>
       </c>
       <c r="AM17" t="n">
         <v>110</v>
@@ -2229,100 +2190,61 @@
       <c r="AN17" t="n">
         <v>142</v>
       </c>
-      <c r="AP17" t="n">
-        <v>84.59999999999999</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>15.95</v>
-      </c>
       <c r="BL17" s="1" t="n">
-        <v>46238</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46239</v>
+        <v>46248</v>
       </c>
       <c r="B18" t="n">
-        <v>160.4</v>
-      </c>
-      <c r="C18" t="n">
-        <v>62.6</v>
+        <v>155.9</v>
       </c>
       <c r="D18" t="n">
-        <v>35</v>
-      </c>
-      <c r="E18" t="n">
-        <v>32.2</v>
+        <v>28</v>
       </c>
       <c r="F18" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H18" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="I18" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="J18" t="n">
-        <v>41.1</v>
+        <v>6.5</v>
       </c>
       <c r="K18" t="n">
-        <v>75.7</v>
-      </c>
-      <c r="M18" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="N18" t="n">
-        <v>32.6</v>
+        <v>99.3</v>
       </c>
       <c r="O18" t="n">
-        <v>38</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="S18" t="n">
-        <v>8</v>
-      </c>
-      <c r="T18" t="n">
-        <v>20.9</v>
+        <v>38.5</v>
       </c>
       <c r="V18" t="n">
-        <v>16.4</v>
+        <v>8.9</v>
       </c>
       <c r="W18" t="n">
-        <v>22.8</v>
+        <v>15.8</v>
       </c>
       <c r="X18" t="n">
-        <v>19.6</v>
+        <v>12.4</v>
       </c>
       <c r="Y18" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z18" t="n">
         <v>13</v>
       </c>
-      <c r="Z18" t="n">
-        <v>16</v>
-      </c>
       <c r="AA18" t="n">
-        <v>14.1</v>
+        <v>11.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>-3.1</v>
+        <v>1.4</v>
       </c>
       <c r="AC18" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="AF18" t="n">
-        <v>225.08</v>
+        <v>221.99</v>
       </c>
       <c r="AG18" t="n">
-        <v>-3.5</v>
+        <v>1.67</v>
       </c>
       <c r="AH18" t="n">
         <v>215</v>
@@ -2331,10 +2253,10 @@
         <v>235</v>
       </c>
       <c r="AK18" t="n">
-        <v>135.24</v>
+        <v>116.37</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.23</v>
+        <v>-0.15</v>
       </c>
       <c r="AM18" t="n">
         <v>110</v>
@@ -2342,100 +2264,61 @@
       <c r="AN18" t="n">
         <v>142</v>
       </c>
-      <c r="AP18" t="n">
-        <v>84.09999999999999</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>15.4</v>
-      </c>
       <c r="BL18" s="1" t="n">
-        <v>46239</v>
+        <v>46248</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46240</v>
+        <v>46249</v>
       </c>
       <c r="B19" t="n">
-        <v>161.7</v>
-      </c>
-      <c r="C19" t="n">
-        <v>71.09999999999999</v>
+        <v>141.3</v>
       </c>
       <c r="D19" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="E19" t="n">
-        <v>27.3</v>
+        <v>26.3</v>
       </c>
       <c r="F19" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H19" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I19" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="J19" t="n">
-        <v>42.6</v>
+        <v>5.5</v>
       </c>
       <c r="K19" t="n">
-        <v>77</v>
-      </c>
-      <c r="M19" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="N19" t="n">
-        <v>31.5</v>
+        <v>97.8</v>
       </c>
       <c r="O19" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>21</v>
-      </c>
-      <c r="R19" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="S19" t="n">
-        <v>6</v>
-      </c>
-      <c r="T19" t="n">
-        <v>21</v>
+        <v>39.8</v>
       </c>
       <c r="V19" t="n">
-        <v>12.7</v>
+        <v>9.5</v>
       </c>
       <c r="W19" t="n">
-        <v>27</v>
+        <v>17.7</v>
       </c>
       <c r="X19" t="n">
-        <v>19.9</v>
+        <v>13.6</v>
       </c>
       <c r="Y19" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="Z19" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA19" t="n">
         <v>14</v>
       </c>
-      <c r="AA19" t="n">
-        <v>11.4</v>
-      </c>
       <c r="AB19" t="n">
-        <v>-5.2</v>
+        <v>0.2</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.6</v>
+        <v>7.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>-0.3</v>
+        <v>3.9</v>
       </c>
       <c r="AF19" t="n">
-        <v>225</v>
+        <v>225.14</v>
       </c>
       <c r="AG19" t="n">
-        <v>-0.08</v>
+        <v>3.15</v>
       </c>
       <c r="AH19" t="n">
         <v>215</v>
@@ -2443,73 +2326,61 @@
       <c r="AI19" t="n">
         <v>235</v>
       </c>
-      <c r="AK19" t="n">
-        <v>134.62</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>-0.62</v>
-      </c>
       <c r="AM19" t="n">
         <v>110</v>
       </c>
       <c r="AN19" t="n">
         <v>142</v>
       </c>
-      <c r="AP19" t="n">
-        <v>80.2</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>13.86</v>
-      </c>
       <c r="BL19" s="1" t="n">
-        <v>46240</v>
+        <v>46249</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46241</v>
+        <v>46250</v>
       </c>
       <c r="B20" t="n">
-        <v>151.5</v>
+        <v>131.5</v>
       </c>
       <c r="D20" t="n">
-        <v>35.1</v>
+        <v>27.3</v>
       </c>
       <c r="F20" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
+      </c>
+      <c r="K20" t="n">
+        <v>97</v>
+      </c>
+      <c r="O20" t="n">
+        <v>35.7</v>
       </c>
       <c r="V20" t="n">
-        <v>8.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="W20" t="n">
-        <v>19.4</v>
+        <v>13.9</v>
       </c>
       <c r="X20" t="n">
-        <v>14</v>
+        <v>11.4</v>
       </c>
       <c r="Y20" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="Z20" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AA20" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AB20" t="n">
-        <v>-4.7</v>
+        <v>-3.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>-1.4</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>221.37</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>0.05</v>
+        <v>-0.4</v>
       </c>
       <c r="AH20" t="n">
         <v>215</v>
@@ -2517,12 +2388,6 @@
       <c r="AI20" t="n">
         <v>235</v>
       </c>
-      <c r="AK20" t="n">
-        <v>135.21</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>0.59</v>
-      </c>
       <c r="AM20" t="n">
         <v>110</v>
       </c>
@@ -2530,60 +2395,93 @@
         <v>142</v>
       </c>
       <c r="BL20" s="1" t="n">
-        <v>46241</v>
+        <v>46250</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46242</v>
+        <v>46251</v>
       </c>
       <c r="B21" t="n">
-        <v>145.2</v>
+        <v>153</v>
+      </c>
+      <c r="C21" t="n">
+        <v>71.8</v>
       </c>
       <c r="D21" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="E21" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="F21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H21" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J21" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="M21" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N21" t="n">
         <v>33.5</v>
       </c>
-      <c r="F21" t="n">
-        <v>5</v>
-      </c>
-      <c r="K21" t="n">
-        <v>100.3</v>
-      </c>
       <c r="O21" t="n">
-        <v>35.5</v>
+        <v>38.3</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>23.2</v>
       </c>
       <c r="V21" t="n">
-        <v>7.1</v>
+        <v>11.2</v>
       </c>
       <c r="W21" t="n">
-        <v>19.2</v>
+        <v>13</v>
       </c>
       <c r="X21" t="n">
-        <v>13.1</v>
+        <v>12.1</v>
       </c>
       <c r="Y21" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="Z21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA21" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>-5.4</v>
+        <v>-6.6</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.4</v>
+        <v>5.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>-1.5</v>
+        <v>-0.6</v>
       </c>
       <c r="AF21" t="n">
-        <v>224.37</v>
+        <v>229.96</v>
       </c>
       <c r="AG21" t="n">
-        <v>3</v>
+        <v>-0.02</v>
       </c>
       <c r="AH21" t="n">
         <v>215</v>
@@ -2592,10 +2490,10 @@
         <v>235</v>
       </c>
       <c r="AK21" t="n">
-        <v>135.61</v>
+        <v>128.14</v>
       </c>
       <c r="AL21" t="n">
-        <v>0.4</v>
+        <v>11.77</v>
       </c>
       <c r="AM21" t="n">
         <v>110</v>
@@ -2603,61 +2501,100 @@
       <c r="AN21" t="n">
         <v>142</v>
       </c>
+      <c r="AP21" t="n">
+        <v>87.47</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>14.8</v>
+      </c>
       <c r="BL21" s="1" t="n">
-        <v>46242</v>
+        <v>46251</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46243</v>
+        <v>46252</v>
       </c>
       <c r="B22" t="n">
-        <v>146.3</v>
+        <v>165.8</v>
+      </c>
+      <c r="C22" t="n">
+        <v>77.3</v>
       </c>
       <c r="D22" t="n">
-        <v>33.4</v>
+        <v>29.3</v>
+      </c>
+      <c r="E22" t="n">
+        <v>27.7</v>
       </c>
       <c r="F22" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
+      </c>
+      <c r="H22" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="J22" t="n">
+        <v>41.6</v>
       </c>
       <c r="K22" t="n">
-        <v>98.2</v>
+        <v>76.59999999999999</v>
+      </c>
+      <c r="M22" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N22" t="n">
+        <v>35.1</v>
       </c>
       <c r="O22" t="n">
-        <v>35.1</v>
+        <v>39.8</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="R22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S22" t="n">
+        <v>7</v>
+      </c>
+      <c r="T22" t="n">
+        <v>23.8</v>
       </c>
       <c r="V22" t="n">
-        <v>4.9</v>
+        <v>9.4</v>
       </c>
       <c r="W22" t="n">
-        <v>16.4</v>
+        <v>17.4</v>
       </c>
       <c r="X22" t="n">
-        <v>10.6</v>
+        <v>13.4</v>
       </c>
       <c r="Y22" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Z22" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA22" t="n">
-        <v>9</v>
+        <v>10.1</v>
       </c>
       <c r="AB22" t="n">
-        <v>-6.4</v>
+        <v>-0.7</v>
       </c>
       <c r="AC22" t="n">
-        <v>-0.2</v>
+        <v>9.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>-3.3</v>
+        <v>4.4</v>
       </c>
       <c r="AF22" t="n">
-        <v>225.93</v>
+        <v>227.01</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.56</v>
+        <v>-2.95</v>
       </c>
       <c r="AH22" t="n">
         <v>215</v>
@@ -2666,10 +2603,10 @@
         <v>235</v>
       </c>
       <c r="AK22" t="n">
-        <v>135.28</v>
+        <v>128.15</v>
       </c>
       <c r="AL22" t="n">
-        <v>-0.33</v>
+        <v>0.01</v>
       </c>
       <c r="AM22" t="n">
         <v>110</v>
@@ -2677,94 +2614,100 @@
       <c r="AN22" t="n">
         <v>142</v>
       </c>
+      <c r="AP22" t="n">
+        <v>83.41</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>14.52</v>
+      </c>
       <c r="BL22" s="1" t="n">
-        <v>46243</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46244</v>
+        <v>46253</v>
       </c>
       <c r="B23" t="n">
-        <v>182.8</v>
+        <v>158.1</v>
       </c>
       <c r="C23" t="n">
-        <v>86.8</v>
+        <v>73.7</v>
       </c>
       <c r="D23" t="n">
-        <v>31.8</v>
+        <v>30.3</v>
       </c>
       <c r="E23" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F23" t="n">
-        <v>5.7</v>
+        <v>4.1</v>
       </c>
       <c r="H23" t="n">
-        <v>23.5</v>
+        <v>24.2</v>
       </c>
       <c r="I23" t="n">
-        <v>9.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>41.1</v>
+        <v>40.9</v>
       </c>
       <c r="K23" t="n">
-        <v>74.2</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="N23" t="n">
-        <v>33.5</v>
+        <v>35.3</v>
       </c>
       <c r="O23" t="n">
-        <v>38.4</v>
+        <v>40.3</v>
       </c>
       <c r="Q23" t="n">
-        <v>22.4</v>
+        <v>23.6</v>
       </c>
       <c r="R23" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S23" t="n">
+        <v>7</v>
+      </c>
+      <c r="T23" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="V23" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W23" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="X23" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z23" t="n">
         <v>15</v>
       </c>
-      <c r="T23" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="V23" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="W23" t="n">
-        <v>15</v>
-      </c>
-      <c r="X23" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>12</v>
-      </c>
       <c r="AA23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AC23" t="n">
         <v>8.5</v>
       </c>
-      <c r="AB23" t="n">
-        <v>-10.5</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>0.3</v>
-      </c>
       <c r="AD23" t="n">
-        <v>-5.1</v>
+        <v>6.5</v>
       </c>
       <c r="AF23" t="n">
-        <v>218.63</v>
+        <v>228.35</v>
       </c>
       <c r="AG23" t="n">
-        <v>-7.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH23" t="n">
         <v>215</v>
@@ -2773,10 +2716,10 @@
         <v>235</v>
       </c>
       <c r="AK23" t="n">
-        <v>126.27</v>
+        <v>128.86</v>
       </c>
       <c r="AL23" t="n">
-        <v>-9.01</v>
+        <v>0.71</v>
       </c>
       <c r="AM23" t="n">
         <v>110</v>
@@ -2785,99 +2728,99 @@
         <v>142</v>
       </c>
       <c r="AP23" t="n">
-        <v>82.66</v>
+        <v>82.37</v>
       </c>
       <c r="AS23" t="n">
-        <v>14.7</v>
+        <v>14.22</v>
       </c>
       <c r="BL23" s="1" t="n">
-        <v>46244</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46245</v>
+        <v>46254</v>
       </c>
       <c r="B24" t="n">
-        <v>181.8</v>
+        <v>154.9</v>
       </c>
       <c r="C24" t="n">
-        <v>86.5</v>
+        <v>70.2</v>
       </c>
       <c r="D24" t="n">
-        <v>31.4</v>
+        <v>31.5</v>
       </c>
       <c r="E24" t="n">
-        <v>34.2</v>
+        <v>27.7</v>
       </c>
       <c r="F24" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H24" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="J24" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="K24" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="M24" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="N24" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="O24" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="R24" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="T24" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="V24" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="W24" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="X24" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD24" t="n">
         <v>5.8</v>
       </c>
-      <c r="H24" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="I24" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="J24" t="n">
-        <v>41.9</v>
-      </c>
-      <c r="K24" t="n">
-        <v>76.8</v>
-      </c>
-      <c r="M24" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N24" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="O24" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>23</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S24" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="T24" t="n">
-        <v>23</v>
-      </c>
-      <c r="V24" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W24" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="X24" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>12</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>-1.4</v>
-      </c>
       <c r="AF24" t="n">
-        <v>216.39</v>
+        <v>231.16</v>
       </c>
       <c r="AG24" t="n">
-        <v>-2.23</v>
+        <v>2.81</v>
       </c>
       <c r="AH24" t="n">
         <v>215</v>
@@ -2886,10 +2829,10 @@
         <v>235</v>
       </c>
       <c r="AK24" t="n">
-        <v>123.32</v>
+        <v>130.88</v>
       </c>
       <c r="AL24" t="n">
-        <v>-2.95</v>
+        <v>2.02</v>
       </c>
       <c r="AM24" t="n">
         <v>110</v>
@@ -2898,99 +2841,66 @@
         <v>142</v>
       </c>
       <c r="AP24" t="n">
-        <v>79.08</v>
+        <v>85.48999999999999</v>
       </c>
       <c r="AS24" t="n">
-        <v>13.91</v>
+        <v>13.1</v>
       </c>
       <c r="BL24" s="1" t="n">
-        <v>46245</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46246</v>
+        <v>46255</v>
       </c>
       <c r="B25" t="n">
-        <v>183</v>
-      </c>
-      <c r="C25" t="n">
-        <v>84.7</v>
+        <v>152.2</v>
       </c>
       <c r="D25" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="E25" t="n">
-        <v>33.7</v>
+        <v>31</v>
       </c>
       <c r="F25" t="n">
-        <v>7</v>
-      </c>
-      <c r="H25" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="I25" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="J25" t="n">
-        <v>42.3</v>
+        <v>3.5</v>
       </c>
       <c r="K25" t="n">
-        <v>76.40000000000001</v>
-      </c>
-      <c r="M25" t="n">
-        <v>4</v>
-      </c>
-      <c r="N25" t="n">
-        <v>36.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O25" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S25" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="T25" t="n">
-        <v>23.6</v>
+        <v>34.4</v>
       </c>
       <c r="V25" t="n">
-        <v>5.7</v>
+        <v>9.5</v>
       </c>
       <c r="W25" t="n">
-        <v>16.1</v>
+        <v>25.5</v>
       </c>
       <c r="X25" t="n">
-        <v>10.9</v>
+        <v>17.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Z25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.8</v>
+        <v>-1.1</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.7</v>
+        <v>8.6</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.8</v>
+        <v>3.8</v>
       </c>
       <c r="AF25" t="n">
-        <v>217.16</v>
+        <v>228.13</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.76</v>
+        <v>-3.03</v>
       </c>
       <c r="AH25" t="n">
         <v>215</v>
@@ -2998,79 +2908,67 @@
       <c r="AI25" t="n">
         <v>235</v>
       </c>
-      <c r="AK25" t="n">
-        <v>117.87</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>-5.45</v>
-      </c>
       <c r="AM25" t="n">
         <v>110</v>
       </c>
       <c r="AN25" t="n">
         <v>142</v>
       </c>
-      <c r="AP25" t="n">
-        <v>78.56</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>13.45</v>
-      </c>
       <c r="BL25" s="1" t="n">
-        <v>46246</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46247</v>
+        <v>46256</v>
       </c>
       <c r="B26" t="n">
-        <v>163.8</v>
+        <v>143.9</v>
       </c>
       <c r="D26" t="n">
-        <v>29</v>
+        <v>30.8</v>
       </c>
       <c r="F26" t="n">
-        <v>6.5</v>
+        <v>2.5</v>
       </c>
       <c r="K26" t="n">
-        <v>101.2</v>
+        <v>99.2</v>
       </c>
       <c r="O26" t="n">
-        <v>40.2</v>
+        <v>35.2</v>
       </c>
       <c r="V26" t="n">
-        <v>6.3</v>
+        <v>10.7</v>
       </c>
       <c r="W26" t="n">
-        <v>17.2</v>
+        <v>17.6</v>
       </c>
       <c r="X26" t="n">
-        <v>11.8</v>
+        <v>14.2</v>
       </c>
       <c r="Y26" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Z26" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.2</v>
+        <v>-0.8</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="AF26" t="n">
-        <v>220.31</v>
+        <v>229.16</v>
       </c>
       <c r="AG26" t="n">
-        <v>3.16</v>
+        <v>1.03</v>
       </c>
       <c r="AH26" t="n">
         <v>215</v>
@@ -3078,12 +2976,6 @@
       <c r="AI26" t="n">
         <v>235</v>
       </c>
-      <c r="AK26" t="n">
-        <v>116.52</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>-1.35</v>
-      </c>
       <c r="AM26" t="n">
         <v>110</v>
       </c>
@@ -3091,60 +2983,93 @@
         <v>142</v>
       </c>
       <c r="BL26" s="1" t="n">
-        <v>46247</v>
+        <v>46256</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46248</v>
+        <v>46257</v>
       </c>
       <c r="B27" t="n">
-        <v>155.9</v>
+        <v>163.2</v>
+      </c>
+      <c r="C27" t="n">
+        <v>73.7</v>
       </c>
       <c r="D27" t="n">
-        <v>28</v>
+        <v>30</v>
+      </c>
+      <c r="E27" t="n">
+        <v>28.2</v>
       </c>
       <c r="F27" t="n">
-        <v>6.5</v>
+        <v>4.8</v>
+      </c>
+      <c r="H27" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J27" t="n">
+        <v>40.1</v>
       </c>
       <c r="K27" t="n">
-        <v>99.3</v>
+        <v>75.59999999999999</v>
+      </c>
+      <c r="M27" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="N27" t="n">
+        <v>32.9</v>
       </c>
       <c r="O27" t="n">
-        <v>38.5</v>
+        <v>39.7</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="R27" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="S27" t="n">
+        <v>6</v>
+      </c>
+      <c r="T27" t="n">
+        <v>23.5</v>
       </c>
       <c r="V27" t="n">
-        <v>8.9</v>
+        <v>9.4</v>
       </c>
       <c r="W27" t="n">
-        <v>15.8</v>
+        <v>20.1</v>
       </c>
       <c r="X27" t="n">
-        <v>12.4</v>
+        <v>14.8</v>
       </c>
       <c r="Y27" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="Z27" t="n">
         <v>13</v>
       </c>
       <c r="AA27" t="n">
-        <v>11.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.4</v>
+        <v>-0.9</v>
       </c>
       <c r="AC27" t="n">
-        <v>5.7</v>
+        <v>9.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="AF27" t="n">
-        <v>221.99</v>
+        <v>228.55</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.67</v>
+        <v>-0.61</v>
       </c>
       <c r="AH27" t="n">
         <v>215</v>
@@ -3153,10 +3078,10 @@
         <v>235</v>
       </c>
       <c r="AK27" t="n">
-        <v>116.37</v>
+        <v>127.06</v>
       </c>
       <c r="AL27" t="n">
-        <v>-0.15</v>
+        <v>-3.82</v>
       </c>
       <c r="AM27" t="n">
         <v>110</v>
@@ -3164,61 +3089,100 @@
       <c r="AN27" t="n">
         <v>142</v>
       </c>
+      <c r="AP27" t="n">
+        <v>82.81</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>12.9</v>
+      </c>
       <c r="BL27" s="1" t="n">
-        <v>46248</v>
+        <v>46257</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46249</v>
+        <v>46258</v>
       </c>
       <c r="B28" t="n">
-        <v>141.3</v>
+        <v>174.4</v>
+      </c>
+      <c r="C28" t="n">
+        <v>75.40000000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>26.3</v>
+        <v>32.1</v>
+      </c>
+      <c r="E28" t="n">
+        <v>30.8</v>
       </c>
       <c r="F28" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
+      </c>
+      <c r="H28" t="n">
+        <v>24</v>
+      </c>
+      <c r="I28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J28" t="n">
+        <v>39.5</v>
       </c>
       <c r="K28" t="n">
-        <v>97.8</v>
+        <v>74</v>
+      </c>
+      <c r="M28" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="N28" t="n">
+        <v>35.8</v>
       </c>
       <c r="O28" t="n">
-        <v>39.8</v>
+        <v>42.6</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="R28" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="S28" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="T28" t="n">
+        <v>23.1</v>
       </c>
       <c r="V28" t="n">
-        <v>9.5</v>
+        <v>12.8</v>
       </c>
       <c r="W28" t="n">
-        <v>17.7</v>
+        <v>22.1</v>
       </c>
       <c r="X28" t="n">
-        <v>13.6</v>
+        <v>17.5</v>
       </c>
       <c r="Y28" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z28" t="n">
         <v>13</v>
       </c>
-      <c r="Z28" t="n">
-        <v>15</v>
-      </c>
       <c r="AA28" t="n">
-        <v>14</v>
+        <v>10.1</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AC28" t="n">
-        <v>7.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AD28" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="AF28" t="n">
-        <v>225.14</v>
+        <v>219.99</v>
       </c>
       <c r="AG28" t="n">
-        <v>3.15</v>
+        <v>-8.56</v>
       </c>
       <c r="AH28" t="n">
         <v>215</v>
@@ -3226,61 +3190,112 @@
       <c r="AI28" t="n">
         <v>235</v>
       </c>
+      <c r="AK28" t="n">
+        <v>125.61</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>-1.45</v>
+      </c>
       <c r="AM28" t="n">
         <v>110</v>
       </c>
       <c r="AN28" t="n">
         <v>142</v>
       </c>
+      <c r="AP28" t="n">
+        <v>77.83</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>12.96</v>
+      </c>
       <c r="BL28" s="1" t="n">
-        <v>46249</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46250</v>
+        <v>46259</v>
       </c>
       <c r="B29" t="n">
-        <v>131.5</v>
+        <v>163.2</v>
+      </c>
+      <c r="C29" t="n">
+        <v>70.90000000000001</v>
       </c>
       <c r="D29" t="n">
-        <v>27.3</v>
+        <v>32.9</v>
+      </c>
+      <c r="E29" t="n">
+        <v>26</v>
       </c>
       <c r="F29" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="H29" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="I29" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J29" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="M29" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="N29" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="O29" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="R29" t="n">
+        <v>5</v>
+      </c>
+      <c r="S29" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="T29" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="V29" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="W29" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="X29" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AD29" t="n">
         <v>5.5</v>
       </c>
-      <c r="K29" t="n">
-        <v>97</v>
-      </c>
-      <c r="O29" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="V29" t="n">
-        <v>9</v>
-      </c>
-      <c r="W29" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="X29" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>15</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>-3.6</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>-0.4</v>
+      <c r="AF29" t="n">
+        <v>219.22</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>-0.77</v>
       </c>
       <c r="AH29" t="n">
         <v>215</v>
@@ -3288,100 +3303,112 @@
       <c r="AI29" t="n">
         <v>235</v>
       </c>
+      <c r="AK29" t="n">
+        <v>124.36</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>-1.25</v>
+      </c>
       <c r="AM29" t="n">
         <v>110</v>
       </c>
       <c r="AN29" t="n">
         <v>142</v>
       </c>
+      <c r="AP29" t="n">
+        <v>76.81</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>12.38</v>
+      </c>
       <c r="BL29" s="1" t="n">
-        <v>46250</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46251</v>
+        <v>46260</v>
       </c>
       <c r="B30" t="n">
-        <v>153</v>
+        <v>152.7</v>
       </c>
       <c r="C30" t="n">
-        <v>71.8</v>
+        <v>62.6</v>
       </c>
       <c r="D30" t="n">
-        <v>28.6</v>
+        <v>32.7</v>
       </c>
       <c r="E30" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
       <c r="F30" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="H30" t="n">
-        <v>24.1</v>
+        <v>23.8</v>
       </c>
       <c r="I30" t="n">
-        <v>10.7</v>
+        <v>7.2</v>
       </c>
       <c r="J30" t="n">
-        <v>41.1</v>
+        <v>38.9</v>
       </c>
       <c r="K30" t="n">
-        <v>75.90000000000001</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="M30" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="N30" t="n">
         <v>33.5</v>
       </c>
       <c r="O30" t="n">
-        <v>38.3</v>
+        <v>40.1</v>
       </c>
       <c r="Q30" t="n">
         <v>23.2</v>
       </c>
       <c r="R30" t="n">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T30" t="n">
         <v>23.2</v>
       </c>
       <c r="V30" t="n">
-        <v>11.2</v>
+        <v>11.5</v>
       </c>
       <c r="W30" t="n">
-        <v>13</v>
+        <v>27.3</v>
       </c>
       <c r="X30" t="n">
-        <v>12.1</v>
+        <v>19.4</v>
       </c>
       <c r="Y30" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z30" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA30" t="n">
         <v>14</v>
       </c>
-      <c r="AA30" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AB30" t="n">
-        <v>-6.6</v>
+        <v>1.8</v>
       </c>
       <c r="AC30" t="n">
-        <v>5.3</v>
+        <v>9.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>-0.6</v>
+        <v>5.7</v>
       </c>
       <c r="AF30" t="n">
-        <v>229.96</v>
+        <v>220.73</v>
       </c>
       <c r="AG30" t="n">
-        <v>-0.02</v>
+        <v>1.5</v>
       </c>
       <c r="AH30" t="n">
         <v>215</v>
@@ -3390,10 +3417,10 @@
         <v>235</v>
       </c>
       <c r="AK30" t="n">
-        <v>128.14</v>
+        <v>120.93</v>
       </c>
       <c r="AL30" t="n">
-        <v>11.77</v>
+        <v>-3.43</v>
       </c>
       <c r="AM30" t="n">
         <v>110</v>
@@ -3402,99 +3429,99 @@
         <v>142</v>
       </c>
       <c r="AP30" t="n">
-        <v>87.47</v>
+        <v>77.87</v>
       </c>
       <c r="AS30" t="n">
-        <v>14.8</v>
+        <v>13.26</v>
       </c>
       <c r="BL30" s="1" t="n">
-        <v>46251</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46252</v>
+        <v>46261</v>
       </c>
       <c r="B31" t="n">
-        <v>165.8</v>
+        <v>150.7</v>
       </c>
       <c r="C31" t="n">
-        <v>77.3</v>
+        <v>64.8</v>
       </c>
       <c r="D31" t="n">
-        <v>29.3</v>
+        <v>33.7</v>
       </c>
       <c r="E31" t="n">
-        <v>27.7</v>
+        <v>27.1</v>
       </c>
       <c r="F31" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="H31" t="n">
-        <v>24.1</v>
+        <v>23.4</v>
       </c>
       <c r="I31" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J31" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="K31" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="M31" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="N31" t="n">
+        <v>33</v>
+      </c>
+      <c r="O31" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="R31" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3</v>
+      </c>
+      <c r="T31" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="V31" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="W31" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="X31" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC31" t="n">
         <v>10.8</v>
       </c>
-      <c r="J31" t="n">
-        <v>41.6</v>
-      </c>
-      <c r="K31" t="n">
-        <v>76.59999999999999</v>
-      </c>
-      <c r="M31" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="N31" t="n">
-        <v>35.1</v>
-      </c>
-      <c r="O31" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="R31" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="S31" t="n">
-        <v>7</v>
-      </c>
-      <c r="T31" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="V31" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="W31" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="X31" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>9.5</v>
-      </c>
       <c r="AD31" t="n">
-        <v>4.4</v>
+        <v>6.7</v>
       </c>
       <c r="AF31" t="n">
-        <v>227.01</v>
+        <v>220.58</v>
       </c>
       <c r="AG31" t="n">
-        <v>-2.95</v>
+        <v>-0.15</v>
       </c>
       <c r="AH31" t="n">
         <v>215</v>
@@ -3503,10 +3530,10 @@
         <v>235</v>
       </c>
       <c r="AK31" t="n">
-        <v>128.15</v>
+        <v>120.28</v>
       </c>
       <c r="AL31" t="n">
-        <v>0.01</v>
+        <v>-0.65</v>
       </c>
       <c r="AM31" t="n">
         <v>110</v>
@@ -3515,99 +3542,54 @@
         <v>142</v>
       </c>
       <c r="AP31" t="n">
-        <v>83.41</v>
+        <v>77.22</v>
       </c>
       <c r="AS31" t="n">
-        <v>14.52</v>
+        <v>13.79</v>
       </c>
       <c r="BL31" s="1" t="n">
-        <v>46252</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46253</v>
+        <v>46262</v>
       </c>
       <c r="B32" t="n">
-        <v>158.1</v>
-      </c>
-      <c r="C32" t="n">
-        <v>73.7</v>
+        <v>138.2</v>
       </c>
       <c r="D32" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="E32" t="n">
-        <v>26</v>
+        <v>33.6</v>
       </c>
       <c r="F32" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H32" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="I32" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="J32" t="n">
-        <v>40.9</v>
-      </c>
-      <c r="K32" t="n">
-        <v>74.40000000000001</v>
-      </c>
-      <c r="M32" t="n">
-        <v>5</v>
-      </c>
-      <c r="N32" t="n">
-        <v>35.3</v>
-      </c>
-      <c r="O32" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="R32" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S32" t="n">
-        <v>7</v>
-      </c>
-      <c r="T32" t="n">
-        <v>23.6</v>
+        <v>6.1</v>
       </c>
       <c r="V32" t="n">
-        <v>8.9</v>
+        <v>15.5</v>
       </c>
       <c r="W32" t="n">
-        <v>19.3</v>
+        <v>23.4</v>
       </c>
       <c r="X32" t="n">
-        <v>14.1</v>
+        <v>19.4</v>
       </c>
       <c r="Y32" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Z32" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA32" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AB32" t="n">
-        <v>4.4</v>
+        <v>0.4</v>
       </c>
       <c r="AC32" t="n">
         <v>8.5</v>
       </c>
       <c r="AD32" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>228.35</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.33</v>
+        <v>4.5</v>
       </c>
       <c r="AH32" t="n">
         <v>215</v>
@@ -3615,112 +3597,61 @@
       <c r="AI32" t="n">
         <v>235</v>
       </c>
-      <c r="AK32" t="n">
-        <v>128.86</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>0.71</v>
-      </c>
       <c r="AM32" t="n">
         <v>110</v>
       </c>
       <c r="AN32" t="n">
         <v>142</v>
       </c>
-      <c r="AP32" t="n">
-        <v>82.37</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>14.22</v>
-      </c>
       <c r="BL32" s="1" t="n">
-        <v>46253</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46254</v>
+        <v>46263</v>
       </c>
       <c r="B33" t="n">
-        <v>154.9</v>
-      </c>
-      <c r="C33" t="n">
-        <v>70.2</v>
+        <v>126.5</v>
       </c>
       <c r="D33" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="E33" t="n">
-        <v>27.7</v>
+        <v>33.2</v>
       </c>
       <c r="F33" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="H33" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I33" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J33" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="K33" t="n">
-        <v>75.8</v>
-      </c>
-      <c r="M33" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="N33" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="O33" t="n">
-        <v>39</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="R33" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="S33" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="T33" t="n">
-        <v>23.7</v>
+        <v>3.4</v>
       </c>
       <c r="V33" t="n">
-        <v>6.3</v>
+        <v>12.6</v>
       </c>
       <c r="W33" t="n">
-        <v>25.2</v>
+        <v>22.3</v>
       </c>
       <c r="X33" t="n">
-        <v>15.8</v>
+        <v>17.4</v>
       </c>
       <c r="Y33" t="n">
         <v>8</v>
       </c>
       <c r="Z33" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA33" t="n">
-        <v>12.6</v>
+        <v>13</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>8.6</v>
+        <v>6.7</v>
       </c>
       <c r="AD33" t="n">
-        <v>5.8</v>
+        <v>3.4</v>
       </c>
       <c r="AF33" t="n">
-        <v>231.16</v>
+        <v>229.48</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.81</v>
+        <v>6.05</v>
       </c>
       <c r="AH33" t="n">
         <v>215</v>
@@ -3728,79 +3659,100 @@
       <c r="AI33" t="n">
         <v>235</v>
       </c>
-      <c r="AK33" t="n">
-        <v>130.88</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AM33" t="n">
         <v>110</v>
       </c>
       <c r="AN33" t="n">
         <v>142</v>
       </c>
-      <c r="AP33" t="n">
-        <v>85.48999999999999</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>13.1</v>
-      </c>
       <c r="BL33" s="1" t="n">
-        <v>46254</v>
+        <v>46263</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>46255</v>
+        <v>46264</v>
       </c>
       <c r="B34" t="n">
-        <v>152.2</v>
+        <v>129.4</v>
+      </c>
+      <c r="C34" t="n">
+        <v>50.6</v>
       </c>
       <c r="D34" t="n">
-        <v>31</v>
+        <v>31.5</v>
+      </c>
+      <c r="E34" t="n">
+        <v>19.4</v>
       </c>
       <c r="F34" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
+      </c>
+      <c r="H34" t="n">
+        <v>24</v>
+      </c>
+      <c r="I34" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J34" t="n">
+        <v>38.9</v>
       </c>
       <c r="K34" t="n">
-        <v>98.40000000000001</v>
+        <v>73.3</v>
+      </c>
+      <c r="M34" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N34" t="n">
+        <v>33.3</v>
       </c>
       <c r="O34" t="n">
-        <v>34.4</v>
+        <v>38</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>21.4</v>
       </c>
       <c r="V34" t="n">
-        <v>9.5</v>
+        <v>14.3</v>
       </c>
       <c r="W34" t="n">
-        <v>25.5</v>
+        <v>23.9</v>
       </c>
       <c r="X34" t="n">
-        <v>17.5</v>
+        <v>19.1</v>
       </c>
       <c r="Y34" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z34" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AA34" t="n">
-        <v>9</v>
+        <v>16.1</v>
       </c>
       <c r="AB34" t="n">
-        <v>-1.1</v>
+        <v>0.4</v>
       </c>
       <c r="AC34" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AD34" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AF34" t="n">
-        <v>228.13</v>
+        <v>229.5</v>
       </c>
       <c r="AG34" t="n">
-        <v>-3.03</v>
+        <v>0.02</v>
       </c>
       <c r="AH34" t="n">
         <v>215</v>
@@ -3808,67 +3760,112 @@
       <c r="AI34" t="n">
         <v>235</v>
       </c>
+      <c r="AK34" t="n">
+        <v>128.37</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>8.09</v>
+      </c>
       <c r="AM34" t="n">
         <v>110</v>
       </c>
       <c r="AN34" t="n">
         <v>142</v>
       </c>
+      <c r="AP34" t="n">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>15.97</v>
+      </c>
       <c r="BL34" s="1" t="n">
-        <v>46255</v>
+        <v>46264</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>46256</v>
+        <v>46265</v>
       </c>
       <c r="B35" t="n">
-        <v>143.9</v>
+        <v>142.9</v>
+      </c>
+      <c r="C35" t="n">
+        <v>52.7</v>
       </c>
       <c r="D35" t="n">
-        <v>30.8</v>
+        <v>34.7</v>
+      </c>
+      <c r="E35" t="n">
+        <v>24.8</v>
       </c>
       <c r="F35" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
+      </c>
+      <c r="H35" t="n">
+        <v>22</v>
+      </c>
+      <c r="I35" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="J35" t="n">
+        <v>38.2</v>
       </c>
       <c r="K35" t="n">
-        <v>99.2</v>
+        <v>70</v>
+      </c>
+      <c r="M35" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N35" t="n">
+        <v>31.9</v>
       </c>
       <c r="O35" t="n">
-        <v>35.2</v>
+        <v>35.8</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>19.7</v>
       </c>
       <c r="V35" t="n">
-        <v>10.7</v>
+        <v>12</v>
       </c>
       <c r="W35" t="n">
-        <v>17.6</v>
+        <v>25.8</v>
       </c>
       <c r="X35" t="n">
-        <v>14.2</v>
+        <v>18.9</v>
       </c>
       <c r="Y35" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="Z35" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AA35" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AB35" t="n">
-        <v>-0.8</v>
+        <v>-0.1</v>
       </c>
       <c r="AC35" t="n">
-        <v>8.800000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="AD35" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="AF35" t="n">
-        <v>229.16</v>
+        <v>238.69</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.03</v>
+        <v>-2.8</v>
       </c>
       <c r="AH35" t="n">
         <v>215</v>
@@ -3876,100 +3873,112 @@
       <c r="AI35" t="n">
         <v>235</v>
       </c>
+      <c r="AK35" t="n">
+        <v>134.59</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>6.22</v>
+      </c>
       <c r="AM35" t="n">
         <v>110</v>
       </c>
       <c r="AN35" t="n">
         <v>142</v>
       </c>
+      <c r="AP35" t="n">
+        <v>89.05</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>17.06</v>
+      </c>
       <c r="BL35" s="1" t="n">
-        <v>46256</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>46257</v>
+        <v>46266</v>
       </c>
       <c r="B36" t="n">
-        <v>163.2</v>
+        <v>148.1</v>
       </c>
       <c r="C36" t="n">
-        <v>73.7</v>
+        <v>51.9</v>
       </c>
       <c r="D36" t="n">
-        <v>30</v>
+        <v>35.4</v>
       </c>
       <c r="E36" t="n">
-        <v>28.2</v>
+        <v>31.5</v>
       </c>
       <c r="F36" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="H36" t="n">
-        <v>24.1</v>
+        <v>21.8</v>
       </c>
       <c r="I36" t="n">
-        <v>11.4</v>
+        <v>9.6</v>
       </c>
       <c r="J36" t="n">
-        <v>40.1</v>
+        <v>39.6</v>
       </c>
       <c r="K36" t="n">
-        <v>75.59999999999999</v>
+        <v>71</v>
       </c>
       <c r="M36" t="n">
-        <v>6.8</v>
+        <v>2.9</v>
       </c>
       <c r="N36" t="n">
-        <v>32.9</v>
+        <v>30.8</v>
       </c>
       <c r="O36" t="n">
-        <v>39.7</v>
+        <v>33.7</v>
       </c>
       <c r="Q36" t="n">
-        <v>23.5</v>
+        <v>20.7</v>
       </c>
       <c r="R36" t="n">
-        <v>4.5</v>
+        <v>0.9</v>
       </c>
       <c r="S36" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>23.5</v>
+        <v>20.7</v>
       </c>
       <c r="V36" t="n">
-        <v>9.4</v>
+        <v>13.1</v>
       </c>
       <c r="W36" t="n">
-        <v>20.1</v>
+        <v>25.5</v>
       </c>
       <c r="X36" t="n">
-        <v>14.8</v>
+        <v>19.3</v>
       </c>
       <c r="Y36" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="Z36" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AA36" t="n">
-        <v>9.300000000000001</v>
+        <v>15.5</v>
       </c>
       <c r="AB36" t="n">
-        <v>-0.9</v>
+        <v>-1</v>
       </c>
       <c r="AC36" t="n">
-        <v>9.5</v>
+        <v>6.4</v>
       </c>
       <c r="AD36" t="n">
-        <v>4.3</v>
+        <v>2.7</v>
       </c>
       <c r="AF36" t="n">
-        <v>228.55</v>
+        <v>233.48</v>
       </c>
       <c r="AG36" t="n">
-        <v>-0.61</v>
+        <v>-4.86</v>
       </c>
       <c r="AH36" t="n">
         <v>215</v>
@@ -3978,10 +3987,10 @@
         <v>235</v>
       </c>
       <c r="AK36" t="n">
-        <v>127.06</v>
+        <v>136.6</v>
       </c>
       <c r="AL36" t="n">
-        <v>-3.82</v>
+        <v>2.01</v>
       </c>
       <c r="AM36" t="n">
         <v>110</v>
@@ -3990,99 +3999,99 @@
         <v>142</v>
       </c>
       <c r="AP36" t="n">
-        <v>82.81</v>
+        <v>86.25</v>
       </c>
       <c r="AS36" t="n">
-        <v>12.9</v>
+        <v>17.13</v>
       </c>
       <c r="BL36" s="1" t="n">
-        <v>46257</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>46258</v>
+        <v>46267</v>
       </c>
       <c r="B37" t="n">
-        <v>174.4</v>
+        <v>143.4</v>
       </c>
       <c r="C37" t="n">
-        <v>75.40000000000001</v>
+        <v>50.9</v>
       </c>
       <c r="D37" t="n">
-        <v>32.1</v>
+        <v>35.7</v>
       </c>
       <c r="E37" t="n">
-        <v>30.8</v>
+        <v>26.2</v>
       </c>
       <c r="F37" t="n">
-        <v>6.6</v>
+        <v>4.3</v>
       </c>
       <c r="H37" t="n">
-        <v>24</v>
+        <v>22.9</v>
       </c>
       <c r="I37" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J37" t="n">
-        <v>39.5</v>
+        <v>39.9</v>
       </c>
       <c r="K37" t="n">
-        <v>74</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="M37" t="n">
-        <v>6.8</v>
+        <v>2</v>
       </c>
       <c r="N37" t="n">
-        <v>35.8</v>
+        <v>31.2</v>
       </c>
       <c r="O37" t="n">
-        <v>42.6</v>
+        <v>33.1</v>
       </c>
       <c r="Q37" t="n">
-        <v>23.1</v>
+        <v>21.6</v>
       </c>
       <c r="R37" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>23.1</v>
+        <v>21.6</v>
       </c>
       <c r="V37" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="W37" t="n">
-        <v>22.1</v>
+        <v>28.3</v>
       </c>
       <c r="X37" t="n">
-        <v>17.5</v>
+        <v>20.6</v>
       </c>
       <c r="Y37" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="Z37" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="AA37" t="n">
-        <v>10.1</v>
+        <v>17.9</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.3</v>
+        <v>-0.8</v>
       </c>
       <c r="AC37" t="n">
-        <v>9.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="AD37" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="AF37" t="n">
-        <v>219.99</v>
+        <v>235.13</v>
       </c>
       <c r="AG37" t="n">
-        <v>-8.56</v>
+        <v>1.66</v>
       </c>
       <c r="AH37" t="n">
         <v>215</v>
@@ -4091,10 +4100,10 @@
         <v>235</v>
       </c>
       <c r="AK37" t="n">
-        <v>125.61</v>
+        <v>135.66</v>
       </c>
       <c r="AL37" t="n">
-        <v>-1.45</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AM37" t="n">
         <v>110</v>
@@ -4103,99 +4112,99 @@
         <v>142</v>
       </c>
       <c r="AP37" t="n">
-        <v>77.83</v>
+        <v>88.27</v>
       </c>
       <c r="AS37" t="n">
-        <v>12.96</v>
+        <v>17.6</v>
       </c>
       <c r="BL37" s="1" t="n">
-        <v>46258</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>46259</v>
+        <v>46268</v>
       </c>
       <c r="B38" t="n">
-        <v>163.2</v>
+        <v>144.9</v>
       </c>
       <c r="C38" t="n">
-        <v>70.90000000000001</v>
+        <v>53</v>
       </c>
       <c r="D38" t="n">
-        <v>32.9</v>
+        <v>35.6</v>
       </c>
       <c r="E38" t="n">
         <v>26</v>
       </c>
       <c r="F38" t="n">
-        <v>6.9</v>
+        <v>2.8</v>
       </c>
       <c r="H38" t="n">
-        <v>23.8</v>
+        <v>24</v>
       </c>
       <c r="I38" t="n">
-        <v>7.4</v>
+        <v>9.4</v>
       </c>
       <c r="J38" t="n">
-        <v>40.1</v>
+        <v>40.3</v>
       </c>
       <c r="K38" t="n">
-        <v>71.3</v>
+        <v>73.7</v>
       </c>
       <c r="M38" t="n">
-        <v>7.2</v>
+        <v>1.9</v>
       </c>
       <c r="N38" t="n">
-        <v>34.3</v>
+        <v>31.6</v>
       </c>
       <c r="O38" t="n">
-        <v>41.5</v>
+        <v>33.6</v>
       </c>
       <c r="Q38" t="n">
-        <v>23.1</v>
+        <v>21</v>
       </c>
       <c r="R38" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>23.1</v>
+        <v>21</v>
       </c>
       <c r="V38" t="n">
-        <v>9.6</v>
+        <v>14.4</v>
       </c>
       <c r="W38" t="n">
-        <v>23.3</v>
+        <v>27.7</v>
       </c>
       <c r="X38" t="n">
-        <v>16.4</v>
+        <v>21.1</v>
       </c>
       <c r="Y38" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Z38" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AA38" t="n">
-        <v>12.2</v>
+        <v>16.3</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.6</v>
+        <v>-1.1</v>
       </c>
       <c r="AC38" t="n">
-        <v>8.5</v>
+        <v>6.6</v>
       </c>
       <c r="AD38" t="n">
-        <v>5.5</v>
+        <v>2.8</v>
       </c>
       <c r="AF38" t="n">
-        <v>219.22</v>
+        <v>234.87</v>
       </c>
       <c r="AG38" t="n">
-        <v>-0.77</v>
+        <v>-0.26</v>
       </c>
       <c r="AH38" t="n">
         <v>215</v>
@@ -4204,10 +4213,10 @@
         <v>235</v>
       </c>
       <c r="AK38" t="n">
-        <v>124.36</v>
+        <v>136.33</v>
       </c>
       <c r="AL38" t="n">
-        <v>-1.25</v>
+        <v>0.67</v>
       </c>
       <c r="AM38" t="n">
         <v>110</v>
@@ -4216,99 +4225,60 @@
         <v>142</v>
       </c>
       <c r="AP38" t="n">
-        <v>76.81</v>
+        <v>87.09</v>
       </c>
       <c r="AS38" t="n">
-        <v>12.38</v>
+        <v>17.31</v>
       </c>
       <c r="BL38" s="1" t="n">
-        <v>46259</v>
+        <v>46268</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>46260</v>
+        <v>46269</v>
       </c>
       <c r="B39" t="n">
-        <v>152.7</v>
-      </c>
-      <c r="C39" t="n">
-        <v>62.6</v>
+        <v>132.2</v>
       </c>
       <c r="D39" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="E39" t="n">
-        <v>24.6</v>
+        <v>35.6</v>
       </c>
       <c r="F39" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="H39" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="I39" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="J39" t="n">
-        <v>38.9</v>
-      </c>
-      <c r="K39" t="n">
-        <v>69.90000000000001</v>
-      </c>
-      <c r="M39" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="N39" t="n">
-        <v>33.5</v>
-      </c>
-      <c r="O39" t="n">
-        <v>40.1</v>
-      </c>
-      <c r="Q39" t="n">
+        <v>4</v>
+      </c>
+      <c r="V39" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="W39" t="n">
         <v>23.2</v>
       </c>
-      <c r="R39" t="n">
+      <c r="X39" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>13</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AD39" t="n">
         <v>4.2</v>
       </c>
-      <c r="S39" t="n">
-        <v>4</v>
-      </c>
-      <c r="T39" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="V39" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="W39" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="X39" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>14</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>5.7</v>
-      </c>
       <c r="AF39" t="n">
-        <v>220.73</v>
+        <v>234.78</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.5</v>
+        <v>-0.09</v>
       </c>
       <c r="AH39" t="n">
         <v>215</v>
@@ -4316,112 +4286,61 @@
       <c r="AI39" t="n">
         <v>235</v>
       </c>
-      <c r="AK39" t="n">
-        <v>120.93</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>-3.43</v>
-      </c>
       <c r="AM39" t="n">
         <v>110</v>
       </c>
       <c r="AN39" t="n">
         <v>142</v>
       </c>
-      <c r="AP39" t="n">
-        <v>77.87</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>13.26</v>
-      </c>
       <c r="BL39" s="1" t="n">
-        <v>46260</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>46261</v>
+        <v>46270</v>
       </c>
       <c r="B40" t="n">
-        <v>150.7</v>
-      </c>
-      <c r="C40" t="n">
-        <v>64.8</v>
+        <v>137.1</v>
       </c>
       <c r="D40" t="n">
-        <v>33.7</v>
-      </c>
-      <c r="E40" t="n">
-        <v>27.1</v>
+        <v>35.1</v>
       </c>
       <c r="F40" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H40" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="I40" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="J40" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="K40" t="n">
-        <v>70.5</v>
-      </c>
-      <c r="M40" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="N40" t="n">
-        <v>33</v>
-      </c>
-      <c r="O40" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="R40" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="S40" t="n">
-        <v>3</v>
-      </c>
-      <c r="T40" t="n">
-        <v>23.2</v>
+        <v>3.3</v>
       </c>
       <c r="V40" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="W40" t="n">
-        <v>28.9</v>
+        <v>22</v>
       </c>
       <c r="X40" t="n">
-        <v>21.7</v>
+        <v>16.5</v>
       </c>
       <c r="Y40" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Z40" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AA40" t="n">
-        <v>13.1</v>
+        <v>10.5</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.5</v>
+        <v>-5.3</v>
       </c>
       <c r="AC40" t="n">
-        <v>10.8</v>
+        <v>6.1</v>
       </c>
       <c r="AD40" t="n">
-        <v>6.7</v>
+        <v>0.4</v>
       </c>
       <c r="AF40" t="n">
-        <v>220.58</v>
+        <v>229.75</v>
       </c>
       <c r="AG40" t="n">
-        <v>-0.15</v>
+        <v>-5.03</v>
       </c>
       <c r="AH40" t="n">
         <v>215</v>
@@ -4429,67 +4348,100 @@
       <c r="AI40" t="n">
         <v>235</v>
       </c>
-      <c r="AK40" t="n">
-        <v>120.28</v>
-      </c>
-      <c r="AL40" t="n">
-        <v>-0.65</v>
-      </c>
       <c r="AM40" t="n">
         <v>110</v>
       </c>
       <c r="AN40" t="n">
         <v>142</v>
       </c>
-      <c r="AP40" t="n">
-        <v>77.22</v>
-      </c>
-      <c r="AS40" t="n">
-        <v>13.79</v>
-      </c>
       <c r="BL40" s="1" t="n">
-        <v>46261</v>
+        <v>46270</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>46262</v>
+        <v>46271</v>
       </c>
       <c r="B41" t="n">
-        <v>138.2</v>
+        <v>166.2</v>
+      </c>
+      <c r="C41" t="n">
+        <v>72.40000000000001</v>
       </c>
       <c r="D41" t="n">
-        <v>33.6</v>
+        <v>32.7</v>
+      </c>
+      <c r="E41" t="n">
+        <v>28.1</v>
       </c>
       <c r="F41" t="n">
-        <v>6.1</v>
+        <v>3.3</v>
+      </c>
+      <c r="H41" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="I41" t="n">
+        <v>9</v>
+      </c>
+      <c r="J41" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="K41" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="M41" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="N41" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="O41" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="R41" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>23.7</v>
       </c>
       <c r="V41" t="n">
-        <v>15.5</v>
+        <v>7.9</v>
       </c>
       <c r="W41" t="n">
-        <v>23.4</v>
+        <v>15.6</v>
       </c>
       <c r="X41" t="n">
-        <v>19.4</v>
+        <v>11.8</v>
       </c>
       <c r="Y41" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Z41" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="AA41" t="n">
-        <v>13</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.4</v>
+        <v>-3.5</v>
       </c>
       <c r="AC41" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="AD41" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>222.86</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>-6.9</v>
       </c>
       <c r="AH41" t="n">
         <v>215</v>
@@ -4497,61 +4449,112 @@
       <c r="AI41" t="n">
         <v>235</v>
       </c>
+      <c r="AK41" t="n">
+        <v>135.42</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>-0.91</v>
+      </c>
       <c r="AM41" t="n">
         <v>110</v>
       </c>
       <c r="AN41" t="n">
         <v>142</v>
       </c>
+      <c r="AP41" t="n">
+        <v>81.98</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>15.01</v>
+      </c>
       <c r="BL41" s="1" t="n">
-        <v>46262</v>
+        <v>46271</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>46263</v>
+        <v>46272</v>
       </c>
       <c r="B42" t="n">
-        <v>126.5</v>
+        <v>166.3</v>
+      </c>
+      <c r="C42" t="n">
+        <v>74.90000000000001</v>
       </c>
       <c r="D42" t="n">
-        <v>33.2</v>
+        <v>32.8</v>
+      </c>
+      <c r="E42" t="n">
+        <v>28.8</v>
       </c>
       <c r="F42" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
+      </c>
+      <c r="H42" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="I42" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J42" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="K42" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="M42" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="N42" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="O42" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="R42" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>23.9</v>
       </c>
       <c r="V42" t="n">
-        <v>12.6</v>
+        <v>6.7</v>
       </c>
       <c r="W42" t="n">
-        <v>22.3</v>
+        <v>18.1</v>
       </c>
       <c r="X42" t="n">
-        <v>17.4</v>
+        <v>12.4</v>
       </c>
       <c r="Y42" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Z42" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AA42" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>-2.9</v>
       </c>
       <c r="AC42" t="n">
-        <v>6.7</v>
+        <v>11.5</v>
       </c>
       <c r="AD42" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="AF42" t="n">
-        <v>229.48</v>
+        <v>218.37</v>
       </c>
       <c r="AG42" t="n">
-        <v>6.05</v>
+        <v>-4.49</v>
       </c>
       <c r="AH42" t="n">
         <v>215</v>
@@ -4559,100 +4562,112 @@
       <c r="AI42" t="n">
         <v>235</v>
       </c>
+      <c r="AK42" t="n">
+        <v>131.24</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>-4.18</v>
+      </c>
       <c r="AM42" t="n">
         <v>110</v>
       </c>
       <c r="AN42" t="n">
         <v>142</v>
       </c>
+      <c r="AP42" t="n">
+        <v>79.98999999999999</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>12.97</v>
+      </c>
       <c r="BL42" s="1" t="n">
-        <v>46263</v>
+        <v>46272</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>46264</v>
+        <v>46273</v>
       </c>
       <c r="B43" t="n">
-        <v>129.4</v>
+        <v>154.1</v>
       </c>
       <c r="C43" t="n">
-        <v>50.6</v>
+        <v>65</v>
       </c>
       <c r="D43" t="n">
-        <v>31.5</v>
+        <v>32</v>
       </c>
       <c r="E43" t="n">
-        <v>19.4</v>
+        <v>25.2</v>
       </c>
       <c r="F43" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="H43" t="n">
-        <v>24</v>
+        <v>23.5</v>
       </c>
       <c r="I43" t="n">
-        <v>10.4</v>
+        <v>9</v>
       </c>
       <c r="J43" t="n">
-        <v>38.9</v>
+        <v>38.5</v>
       </c>
       <c r="K43" t="n">
-        <v>73.3</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="M43" t="n">
-        <v>4.7</v>
+        <v>8</v>
       </c>
       <c r="N43" t="n">
-        <v>33.3</v>
+        <v>32.3</v>
       </c>
       <c r="O43" t="n">
-        <v>38</v>
+        <v>40.3</v>
       </c>
       <c r="Q43" t="n">
-        <v>21.4</v>
+        <v>21.7</v>
       </c>
       <c r="R43" t="n">
-        <v>1.5</v>
+        <v>4.4</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T43" t="n">
-        <v>21.4</v>
+        <v>21.7</v>
       </c>
       <c r="V43" t="n">
-        <v>14.3</v>
+        <v>5.4</v>
       </c>
       <c r="W43" t="n">
-        <v>23.9</v>
+        <v>21</v>
       </c>
       <c r="X43" t="n">
-        <v>19.1</v>
+        <v>13.2</v>
       </c>
       <c r="Y43" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z43" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AA43" t="n">
-        <v>16.1</v>
+        <v>14.5</v>
       </c>
       <c r="AB43" t="n">
         <v>0.4</v>
       </c>
       <c r="AC43" t="n">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="AD43" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AF43" t="n">
-        <v>229.5</v>
+        <v>218.04</v>
       </c>
       <c r="AG43" t="n">
-        <v>0.02</v>
+        <v>-0.33</v>
       </c>
       <c r="AH43" t="n">
         <v>215</v>
@@ -4661,10 +4676,10 @@
         <v>235</v>
       </c>
       <c r="AK43" t="n">
-        <v>128.37</v>
+        <v>129.21</v>
       </c>
       <c r="AL43" t="n">
-        <v>8.09</v>
+        <v>-2.03</v>
       </c>
       <c r="AM43" t="n">
         <v>110</v>
@@ -4673,99 +4688,99 @@
         <v>142</v>
       </c>
       <c r="AP43" t="n">
-        <v>91.59999999999999</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="AS43" t="n">
-        <v>15.97</v>
+        <v>15.23</v>
       </c>
       <c r="BL43" s="1" t="n">
-        <v>46264</v>
+        <v>46273</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>46265</v>
+        <v>46274</v>
       </c>
       <c r="B44" t="n">
-        <v>142.9</v>
+        <v>148.8</v>
       </c>
       <c r="C44" t="n">
-        <v>52.7</v>
+        <v>57.6</v>
       </c>
       <c r="D44" t="n">
-        <v>34.7</v>
+        <v>32.7</v>
       </c>
       <c r="E44" t="n">
-        <v>24.8</v>
+        <v>26.3</v>
       </c>
       <c r="F44" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="H44" t="n">
-        <v>22</v>
+        <v>23.6</v>
       </c>
       <c r="I44" t="n">
-        <v>9.9</v>
+        <v>8.9</v>
       </c>
       <c r="J44" t="n">
-        <v>38.2</v>
+        <v>41.6</v>
       </c>
       <c r="K44" t="n">
-        <v>70</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="M44" t="n">
-        <v>3.9</v>
+        <v>7.4</v>
       </c>
       <c r="N44" t="n">
-        <v>31.9</v>
+        <v>35</v>
       </c>
       <c r="O44" t="n">
-        <v>35.8</v>
+        <v>42.4</v>
       </c>
       <c r="Q44" t="n">
-        <v>19.7</v>
+        <v>21.7</v>
       </c>
       <c r="R44" t="n">
-        <v>1.7</v>
+        <v>4.6</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>19.7</v>
+        <v>21.7</v>
       </c>
       <c r="V44" t="n">
-        <v>12</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W44" t="n">
-        <v>25.8</v>
+        <v>24.1</v>
       </c>
       <c r="X44" t="n">
-        <v>18.9</v>
+        <v>16.1</v>
       </c>
       <c r="Y44" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z44" t="n">
         <v>19</v>
       </c>
       <c r="AA44" t="n">
-        <v>15</v>
+        <v>15.6</v>
       </c>
       <c r="AB44" t="n">
-        <v>-0.1</v>
+        <v>2.9</v>
       </c>
       <c r="AC44" t="n">
-        <v>5.8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AD44" t="n">
-        <v>2.9</v>
+        <v>6.3</v>
       </c>
       <c r="AF44" t="n">
-        <v>238.69</v>
+        <v>220.84</v>
       </c>
       <c r="AG44" t="n">
-        <v>-2.8</v>
+        <v>2.8</v>
       </c>
       <c r="AH44" t="n">
         <v>215</v>
@@ -4774,10 +4789,10 @@
         <v>235</v>
       </c>
       <c r="AK44" t="n">
-        <v>134.59</v>
+        <v>129.07</v>
       </c>
       <c r="AL44" t="n">
-        <v>6.22</v>
+        <v>-0.14</v>
       </c>
       <c r="AM44" t="n">
         <v>110</v>
@@ -4786,99 +4801,99 @@
         <v>142</v>
       </c>
       <c r="AP44" t="n">
-        <v>89.05</v>
+        <v>85.52</v>
       </c>
       <c r="AS44" t="n">
-        <v>17.06</v>
+        <v>15.82</v>
       </c>
       <c r="BL44" s="1" t="n">
-        <v>46265</v>
+        <v>46274</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>46266</v>
+        <v>46275</v>
       </c>
       <c r="B45" t="n">
-        <v>148.1</v>
+        <v>146.8</v>
       </c>
       <c r="C45" t="n">
-        <v>51.9</v>
+        <v>52.8</v>
       </c>
       <c r="D45" t="n">
-        <v>35.4</v>
+        <v>33.6</v>
       </c>
       <c r="E45" t="n">
-        <v>31.5</v>
+        <v>28.9</v>
       </c>
       <c r="F45" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="H45" t="n">
-        <v>21.8</v>
+        <v>23.7</v>
       </c>
       <c r="I45" t="n">
-        <v>9.6</v>
+        <v>9.1</v>
       </c>
       <c r="J45" t="n">
-        <v>39.6</v>
+        <v>40.8</v>
       </c>
       <c r="K45" t="n">
-        <v>71</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="M45" t="n">
-        <v>2.9</v>
+        <v>5.6</v>
       </c>
       <c r="N45" t="n">
-        <v>30.8</v>
+        <v>33.1</v>
       </c>
       <c r="O45" t="n">
-        <v>33.7</v>
+        <v>38.7</v>
       </c>
       <c r="Q45" t="n">
-        <v>20.7</v>
+        <v>22</v>
       </c>
       <c r="R45" t="n">
-        <v>0.9</v>
+        <v>3.6</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>20.7</v>
+        <v>22</v>
       </c>
       <c r="V45" t="n">
-        <v>13.1</v>
+        <v>11</v>
       </c>
       <c r="W45" t="n">
-        <v>25.5</v>
+        <v>22.9</v>
       </c>
       <c r="X45" t="n">
-        <v>19.3</v>
+        <v>16.9</v>
       </c>
       <c r="Y45" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z45" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AA45" t="n">
-        <v>15.5</v>
+        <v>16.1</v>
       </c>
       <c r="AB45" t="n">
-        <v>-1</v>
+        <v>1.9</v>
       </c>
       <c r="AC45" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AD45" t="n">
-        <v>2.7</v>
+        <v>4.5</v>
       </c>
       <c r="AF45" t="n">
-        <v>233.48</v>
+        <v>225.87</v>
       </c>
       <c r="AG45" t="n">
-        <v>-4.86</v>
+        <v>5.03</v>
       </c>
       <c r="AH45" t="n">
         <v>215</v>
@@ -4887,10 +4902,10 @@
         <v>235</v>
       </c>
       <c r="AK45" t="n">
-        <v>136.6</v>
+        <v>130.73</v>
       </c>
       <c r="AL45" t="n">
-        <v>2.01</v>
+        <v>1.66</v>
       </c>
       <c r="AM45" t="n">
         <v>110</v>
@@ -4899,99 +4914,54 @@
         <v>142</v>
       </c>
       <c r="AP45" t="n">
-        <v>86.25</v>
+        <v>88.2</v>
       </c>
       <c r="AS45" t="n">
-        <v>17.13</v>
+        <v>15.76</v>
       </c>
       <c r="BL45" s="1" t="n">
-        <v>46266</v>
+        <v>46275</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46267</v>
+        <v>46276</v>
       </c>
       <c r="B46" t="n">
-        <v>143.4</v>
-      </c>
-      <c r="C46" t="n">
-        <v>50.9</v>
+        <v>133.9</v>
       </c>
       <c r="D46" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="E46" t="n">
-        <v>26.2</v>
+        <v>34.7</v>
       </c>
       <c r="F46" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H46" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="I46" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="J46" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="K46" t="n">
-        <v>72.59999999999999</v>
-      </c>
-      <c r="M46" t="n">
-        <v>2</v>
-      </c>
-      <c r="N46" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="O46" t="n">
-        <v>33.1</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="R46" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" t="n">
-        <v>21.6</v>
+        <v>3.3</v>
       </c>
       <c r="V46" t="n">
-        <v>12.9</v>
+        <v>14.3</v>
       </c>
       <c r="W46" t="n">
-        <v>28.3</v>
+        <v>21.7</v>
       </c>
       <c r="X46" t="n">
-        <v>20.6</v>
+        <v>18</v>
       </c>
       <c r="Y46" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z46" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AA46" t="n">
-        <v>17.9</v>
+        <v>15</v>
       </c>
       <c r="AB46" t="n">
-        <v>-0.8</v>
+        <v>-3.5</v>
       </c>
       <c r="AC46" t="n">
-        <v>8.1</v>
+        <v>3.2</v>
       </c>
       <c r="AD46" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>235.13</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>1.66</v>
+        <v>-0.1</v>
       </c>
       <c r="AH46" t="n">
         <v>215</v>
@@ -4999,112 +4969,55 @@
       <c r="AI46" t="n">
         <v>235</v>
       </c>
-      <c r="AK46" t="n">
-        <v>135.66</v>
-      </c>
-      <c r="AL46" t="n">
-        <v>-0.9399999999999999</v>
-      </c>
       <c r="AM46" t="n">
         <v>110</v>
       </c>
       <c r="AN46" t="n">
         <v>142</v>
       </c>
-      <c r="AP46" t="n">
-        <v>88.27</v>
-      </c>
-      <c r="AS46" t="n">
-        <v>17.6</v>
-      </c>
       <c r="BL46" s="1" t="n">
-        <v>46267</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46268</v>
+        <v>46277</v>
       </c>
       <c r="B47" t="n">
-        <v>144.9</v>
-      </c>
-      <c r="C47" t="n">
-        <v>53</v>
+        <v>137.5</v>
       </c>
       <c r="D47" t="n">
-        <v>35.6</v>
-      </c>
-      <c r="E47" t="n">
-        <v>26</v>
+        <v>32.8</v>
       </c>
       <c r="F47" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="H47" t="n">
-        <v>24</v>
-      </c>
-      <c r="I47" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="J47" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="K47" t="n">
-        <v>73.7</v>
-      </c>
-      <c r="M47" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="N47" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="O47" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>21</v>
-      </c>
-      <c r="R47" t="n">
-        <v>0</v>
-      </c>
-      <c r="S47" t="n">
-        <v>0</v>
-      </c>
-      <c r="T47" t="n">
-        <v>21</v>
+        <v>2.3</v>
       </c>
       <c r="V47" t="n">
-        <v>14.4</v>
+        <v>9</v>
       </c>
       <c r="W47" t="n">
-        <v>27.7</v>
+        <v>15.7</v>
       </c>
       <c r="X47" t="n">
-        <v>21.1</v>
+        <v>12.3</v>
       </c>
       <c r="Y47" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z47" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="AA47" t="n">
-        <v>16.3</v>
+        <v>10.5</v>
       </c>
       <c r="AB47" t="n">
-        <v>-1.1</v>
+        <v>-6.6</v>
       </c>
       <c r="AC47" t="n">
-        <v>6.6</v>
+        <v>8.1</v>
       </c>
       <c r="AD47" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>234.87</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>-0.26</v>
+        <v>0.8</v>
       </c>
       <c r="AH47" t="n">
         <v>215</v>
@@ -5112,73 +5025,82 @@
       <c r="AI47" t="n">
         <v>235</v>
       </c>
-      <c r="AK47" t="n">
-        <v>136.33</v>
-      </c>
-      <c r="AL47" t="n">
-        <v>0.67</v>
-      </c>
       <c r="AM47" t="n">
         <v>110</v>
       </c>
       <c r="AN47" t="n">
         <v>142</v>
       </c>
-      <c r="AP47" t="n">
-        <v>87.09</v>
-      </c>
-      <c r="AS47" t="n">
-        <v>17.31</v>
-      </c>
       <c r="BL47" s="1" t="n">
-        <v>46268</v>
+        <v>46277</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46269</v>
+        <v>46278</v>
       </c>
       <c r="B48" t="n">
-        <v>132.2</v>
+        <v>157.1</v>
+      </c>
+      <c r="C48" t="n">
+        <v>73.09999999999999</v>
       </c>
       <c r="D48" t="n">
-        <v>35.6</v>
+        <v>31.7</v>
+      </c>
+      <c r="E48" t="n">
+        <v>26.1</v>
       </c>
       <c r="F48" t="n">
-        <v>4</v>
-      </c>
-      <c r="V48" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="W48" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="X48" t="n">
-        <v>17.4</v>
+        <v>2</v>
+      </c>
+      <c r="H48" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="I48" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="J48" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="K48" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="M48" t="n">
+        <v>6</v>
+      </c>
+      <c r="N48" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="O48" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="R48" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>23.8</v>
       </c>
       <c r="Y48" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z48" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AA48" t="n">
-        <v>13</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>4.2</v>
+        <v>7.9</v>
       </c>
       <c r="AF48" t="n">
-        <v>234.78</v>
+        <v>224.2</v>
       </c>
       <c r="AG48" t="n">
-        <v>-0.09</v>
+        <v>-1.67</v>
       </c>
       <c r="AH48" t="n">
         <v>215</v>
@@ -5186,61 +5108,94 @@
       <c r="AI48" t="n">
         <v>235</v>
       </c>
+      <c r="AK48" t="n">
+        <v>128.6</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>-2.13</v>
+      </c>
       <c r="AM48" t="n">
         <v>110</v>
       </c>
       <c r="AN48" t="n">
         <v>142</v>
       </c>
+      <c r="AP48" t="n">
+        <v>81.18000000000001</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>14.06</v>
+      </c>
       <c r="BL48" s="1" t="n">
-        <v>46269</v>
+        <v>46278</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46270</v>
+        <v>46279</v>
       </c>
       <c r="B49" t="n">
-        <v>137.1</v>
+        <v>153.1</v>
+      </c>
+      <c r="C49" t="n">
+        <v>69.59999999999999</v>
       </c>
       <c r="D49" t="n">
-        <v>35.1</v>
+        <v>32.2</v>
+      </c>
+      <c r="E49" t="n">
+        <v>25.9</v>
       </c>
       <c r="F49" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="V49" t="n">
-        <v>11</v>
-      </c>
-      <c r="W49" t="n">
-        <v>22</v>
-      </c>
-      <c r="X49" t="n">
-        <v>16.5</v>
+        <v>2.2</v>
+      </c>
+      <c r="H49" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="I49" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="J49" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="K49" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="M49" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="N49" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="O49" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="R49" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="S49" t="n">
+        <v>4</v>
+      </c>
+      <c r="T49" t="n">
+        <v>23.8</v>
       </c>
       <c r="Y49" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z49" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AA49" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>-5.3</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>0.4</v>
+        <v>12</v>
       </c>
       <c r="AF49" t="n">
-        <v>229.75</v>
+        <v>223.35</v>
       </c>
       <c r="AG49" t="n">
-        <v>-5.03</v>
+        <v>-0.85</v>
       </c>
       <c r="AH49" t="n">
         <v>215</v>
@@ -5248,100 +5203,94 @@
       <c r="AI49" t="n">
         <v>235</v>
       </c>
+      <c r="AK49" t="n">
+        <v>127.19</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>-1.41</v>
+      </c>
       <c r="AM49" t="n">
         <v>110</v>
       </c>
       <c r="AN49" t="n">
         <v>142</v>
       </c>
+      <c r="AP49" t="n">
+        <v>81.06</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>13.63</v>
+      </c>
       <c r="BL49" s="1" t="n">
-        <v>46270</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46271</v>
+        <v>46280</v>
       </c>
       <c r="B50" t="n">
-        <v>166.2</v>
+        <v>145.5</v>
       </c>
       <c r="C50" t="n">
-        <v>72.40000000000001</v>
+        <v>62.3</v>
       </c>
       <c r="D50" t="n">
-        <v>32.7</v>
+        <v>34</v>
       </c>
       <c r="E50" t="n">
-        <v>28.1</v>
+        <v>22.5</v>
       </c>
       <c r="F50" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="H50" t="n">
-        <v>23.4</v>
+        <v>24.8</v>
       </c>
       <c r="I50" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="J50" t="n">
-        <v>42.1</v>
+        <v>40.8</v>
       </c>
       <c r="K50" t="n">
-        <v>74.5</v>
+        <v>75</v>
       </c>
       <c r="M50" t="n">
-        <v>5.6</v>
+        <v>6.9</v>
       </c>
       <c r="N50" t="n">
-        <v>33.7</v>
+        <v>30.4</v>
       </c>
       <c r="O50" t="n">
-        <v>39.3</v>
+        <v>37.3</v>
       </c>
       <c r="Q50" t="n">
-        <v>23.7</v>
+        <v>22.1</v>
       </c>
       <c r="R50" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="V50" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="W50" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="X50" t="n">
-        <v>11.8</v>
+        <v>22.1</v>
       </c>
       <c r="Y50" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="Z50" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="AA50" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>2.5</v>
+        <v>12.9</v>
       </c>
       <c r="AF50" t="n">
-        <v>222.86</v>
+        <v>223.06</v>
       </c>
       <c r="AG50" t="n">
-        <v>-6.9</v>
+        <v>-0.29</v>
       </c>
       <c r="AH50" t="n">
         <v>215</v>
@@ -5350,10 +5299,10 @@
         <v>235</v>
       </c>
       <c r="AK50" t="n">
-        <v>135.42</v>
+        <v>129.17</v>
       </c>
       <c r="AL50" t="n">
-        <v>-0.91</v>
+        <v>1.98</v>
       </c>
       <c r="AM50" t="n">
         <v>110</v>
@@ -5362,57 +5311,57 @@
         <v>142</v>
       </c>
       <c r="AP50" t="n">
-        <v>81.98</v>
+        <v>82.36</v>
       </c>
       <c r="AS50" t="n">
-        <v>15.01</v>
+        <v>13.91</v>
       </c>
       <c r="BL50" s="1" t="n">
-        <v>46271</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46272</v>
+        <v>46281</v>
       </c>
       <c r="B51" t="n">
-        <v>166.3</v>
+        <v>148</v>
       </c>
       <c r="C51" t="n">
-        <v>74.90000000000001</v>
+        <v>61.6</v>
       </c>
       <c r="D51" t="n">
-        <v>32.8</v>
+        <v>33.9</v>
       </c>
       <c r="E51" t="n">
-        <v>28.8</v>
+        <v>25</v>
       </c>
       <c r="F51" t="n">
-        <v>4.2</v>
+        <v>2.2</v>
       </c>
       <c r="H51" t="n">
-        <v>23.4</v>
+        <v>25.1</v>
       </c>
       <c r="I51" t="n">
-        <v>9.199999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="J51" t="n">
-        <v>41.2</v>
+        <v>39.5</v>
       </c>
       <c r="K51" t="n">
-        <v>73.8</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="M51" t="n">
-        <v>7.2</v>
+        <v>5.9</v>
       </c>
       <c r="N51" t="n">
-        <v>35.4</v>
+        <v>28.6</v>
       </c>
       <c r="O51" t="n">
-        <v>42.6</v>
+        <v>34.5</v>
       </c>
       <c r="Q51" t="n">
-        <v>23.9</v>
+        <v>23.3</v>
       </c>
       <c r="R51" t="n">
         <v>3.9</v>
@@ -5421,153 +5370,117 @@
         <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="V51" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="W51" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="X51" t="n">
-        <v>12.4</v>
+        <v>23.3</v>
       </c>
       <c r="Y51" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z51" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>222.77</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>215</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>235</v>
+      </c>
+      <c r="AK51" t="n">
+        <v>130.42</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>142</v>
+      </c>
+      <c r="AP51" t="n">
+        <v>80.90000000000001</v>
+      </c>
+      <c r="AS51" t="n">
         <v>14</v>
       </c>
-      <c r="AA51" t="n">
-        <v>11</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>-2.9</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>218.37</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>-4.49</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>215</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>235</v>
-      </c>
-      <c r="AK51" t="n">
-        <v>131.24</v>
-      </c>
-      <c r="AL51" t="n">
-        <v>-4.18</v>
-      </c>
-      <c r="AM51" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN51" t="n">
-        <v>142</v>
-      </c>
-      <c r="AP51" t="n">
-        <v>79.98999999999999</v>
-      </c>
-      <c r="AS51" t="n">
-        <v>12.97</v>
-      </c>
       <c r="BL51" s="1" t="n">
-        <v>46272</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46273</v>
+        <v>46282</v>
       </c>
       <c r="B52" t="n">
-        <v>154.1</v>
+        <v>135.5</v>
       </c>
       <c r="C52" t="n">
-        <v>65</v>
+        <v>47.7</v>
       </c>
       <c r="D52" t="n">
-        <v>32</v>
+        <v>34.2</v>
       </c>
       <c r="E52" t="n">
-        <v>25.2</v>
+        <v>24.1</v>
       </c>
       <c r="F52" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="H52" t="n">
-        <v>23.5</v>
+        <v>24.9</v>
       </c>
       <c r="I52" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J52" t="n">
-        <v>38.5</v>
+        <v>38.4</v>
       </c>
       <c r="K52" t="n">
-        <v>70.90000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="M52" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="N52" t="n">
-        <v>32.3</v>
+        <v>30.3</v>
       </c>
       <c r="O52" t="n">
-        <v>40.3</v>
+        <v>33.3</v>
       </c>
       <c r="Q52" t="n">
-        <v>21.7</v>
+        <v>23.3</v>
       </c>
       <c r="R52" t="n">
-        <v>4.4</v>
+        <v>1</v>
       </c>
       <c r="S52" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="V52" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="W52" t="n">
-        <v>21</v>
-      </c>
-      <c r="X52" t="n">
-        <v>13.2</v>
+        <v>23.3</v>
       </c>
       <c r="Y52" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z52" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AA52" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>3.9</v>
+        <v>18.8</v>
       </c>
       <c r="AF52" t="n">
-        <v>218.04</v>
+        <v>221.86</v>
       </c>
       <c r="AG52" t="n">
-        <v>-0.33</v>
+        <v>-0.91</v>
       </c>
       <c r="AH52" t="n">
         <v>215</v>
@@ -5576,10 +5489,10 @@
         <v>235</v>
       </c>
       <c r="AK52" t="n">
-        <v>129.21</v>
+        <v>129.71</v>
       </c>
       <c r="AL52" t="n">
-        <v>-2.03</v>
+        <v>-0.71</v>
       </c>
       <c r="AM52" t="n">
         <v>110</v>
@@ -5588,280 +5501,94 @@
         <v>142</v>
       </c>
       <c r="AP52" t="n">
-        <v>82.90000000000001</v>
+        <v>86.42</v>
       </c>
       <c r="AS52" t="n">
-        <v>15.23</v>
+        <v>16.05</v>
       </c>
       <c r="BL52" s="1" t="n">
-        <v>46273</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46274</v>
+        <v>46283</v>
       </c>
       <c r="B53" t="n">
-        <v>148.8</v>
-      </c>
-      <c r="C53" t="n">
-        <v>57.6</v>
+        <v>118.1</v>
       </c>
       <c r="D53" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="E53" t="n">
-        <v>26.3</v>
+        <v>34.7</v>
       </c>
       <c r="F53" t="n">
         <v>3.3</v>
       </c>
-      <c r="H53" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="I53" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="J53" t="n">
-        <v>41.6</v>
-      </c>
-      <c r="K53" t="n">
-        <v>74.09999999999999</v>
-      </c>
-      <c r="M53" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="N53" t="n">
-        <v>35</v>
-      </c>
-      <c r="O53" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="R53" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="S53" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="V53" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="W53" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="X53" t="n">
-        <v>16.1</v>
-      </c>
       <c r="Y53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Z53" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA53" t="n">
         <v>19</v>
       </c>
-      <c r="AA53" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="AF53" t="n">
-        <v>220.84</v>
-      </c>
-      <c r="AG53" t="n">
-        <v>2.8</v>
-      </c>
       <c r="AH53" t="n">
         <v>215</v>
       </c>
       <c r="AI53" t="n">
         <v>235</v>
       </c>
-      <c r="AK53" t="n">
-        <v>129.07</v>
-      </c>
-      <c r="AL53" t="n">
-        <v>-0.14</v>
-      </c>
       <c r="AM53" t="n">
         <v>110</v>
       </c>
       <c r="AN53" t="n">
         <v>142</v>
       </c>
-      <c r="AP53" t="n">
-        <v>85.52</v>
-      </c>
-      <c r="AS53" t="n">
-        <v>15.82</v>
-      </c>
       <c r="BL53" s="1" t="n">
-        <v>46274</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46275</v>
+        <v>46284</v>
       </c>
       <c r="B54" t="n">
-        <v>146.8</v>
-      </c>
-      <c r="C54" t="n">
-        <v>52.8</v>
+        <v>100.3</v>
       </c>
       <c r="D54" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="E54" t="n">
-        <v>28.9</v>
+        <v>34</v>
       </c>
       <c r="F54" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="H54" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="I54" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="J54" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="K54" t="n">
-        <v>73.59999999999999</v>
-      </c>
-      <c r="M54" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="N54" t="n">
-        <v>33.1</v>
-      </c>
-      <c r="O54" t="n">
-        <v>38.7</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>22</v>
-      </c>
-      <c r="R54" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="S54" t="n">
-        <v>0</v>
-      </c>
-      <c r="T54" t="n">
-        <v>22</v>
-      </c>
-      <c r="V54" t="n">
-        <v>11</v>
-      </c>
-      <c r="W54" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="X54" t="n">
-        <v>16.9</v>
+        <v>2.5</v>
       </c>
       <c r="Y54" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="Z54" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA54" t="n">
         <v>20</v>
       </c>
-      <c r="AA54" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AF54" t="n">
-        <v>225.87</v>
-      </c>
-      <c r="AG54" t="n">
-        <v>5.03</v>
-      </c>
       <c r="AH54" t="n">
         <v>215</v>
       </c>
       <c r="AI54" t="n">
         <v>235</v>
       </c>
-      <c r="AK54" t="n">
-        <v>130.73</v>
-      </c>
-      <c r="AL54" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AM54" t="n">
         <v>110</v>
       </c>
       <c r="AN54" t="n">
         <v>142</v>
       </c>
-      <c r="AP54" t="n">
-        <v>88.2</v>
-      </c>
-      <c r="AS54" t="n">
-        <v>15.76</v>
-      </c>
       <c r="BL54" s="1" t="n">
-        <v>46275</v>
+        <v>46284</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46276</v>
-      </c>
-      <c r="B55" t="n">
-        <v>133.9</v>
-      </c>
-      <c r="D55" t="n">
-        <v>34.7</v>
-      </c>
-      <c r="F55" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="V55" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="W55" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="X55" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>15</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>-0.1</v>
+        <v>46285</v>
       </c>
       <c r="AH55" t="n">
         <v>215</v>
@@ -5876,30 +5603,12 @@
         <v>142</v>
       </c>
       <c r="BL55" s="1" t="n">
-        <v>46276</v>
+        <v>46285</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46277</v>
-      </c>
-      <c r="B56" t="n">
-        <v>137.5</v>
-      </c>
-      <c r="D56" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="F56" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>11</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>10.5</v>
+        <v>46286</v>
       </c>
       <c r="AH56" t="n">
         <v>215</v>
@@ -5914,75 +5623,12 @@
         <v>142</v>
       </c>
       <c r="BL56" s="1" t="n">
-        <v>46277</v>
+        <v>46286</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46278</v>
-      </c>
-      <c r="B57" t="n">
-        <v>157.1</v>
-      </c>
-      <c r="C57" t="n">
-        <v>73.09999999999999</v>
-      </c>
-      <c r="D57" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="E57" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="F57" t="n">
-        <v>2</v>
-      </c>
-      <c r="H57" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="I57" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="J57" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="K57" t="n">
-        <v>73.5</v>
-      </c>
-      <c r="M57" t="n">
-        <v>6</v>
-      </c>
-      <c r="N57" t="n">
-        <v>33.4</v>
-      </c>
-      <c r="O57" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="R57" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="S57" t="n">
-        <v>0</v>
-      </c>
-      <c r="T57" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>12</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="AF57" t="n">
-        <v>224.2</v>
-      </c>
-      <c r="AG57" t="n">
-        <v>-1.67</v>
+        <v>46287</v>
       </c>
       <c r="AH57" t="n">
         <v>215</v>
@@ -5990,94 +5636,19 @@
       <c r="AI57" t="n">
         <v>235</v>
       </c>
-      <c r="AK57" t="n">
-        <v>128.6</v>
-      </c>
-      <c r="AL57" t="n">
-        <v>-2.13</v>
-      </c>
       <c r="AM57" t="n">
         <v>110</v>
       </c>
       <c r="AN57" t="n">
         <v>142</v>
       </c>
-      <c r="AP57" t="n">
-        <v>81.18000000000001</v>
-      </c>
-      <c r="AS57" t="n">
-        <v>14.06</v>
-      </c>
       <c r="BL57" s="1" t="n">
-        <v>46278</v>
+        <v>46287</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="B58" t="n">
-        <v>153.1</v>
-      </c>
-      <c r="C58" t="n">
-        <v>69.59999999999999</v>
-      </c>
-      <c r="D58" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="E58" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="F58" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="H58" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="I58" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="J58" t="n">
-        <v>39.6</v>
-      </c>
-      <c r="K58" t="n">
-        <v>73.3</v>
-      </c>
-      <c r="M58" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="N58" t="n">
-        <v>34.4</v>
-      </c>
-      <c r="O58" t="n">
-        <v>40.1</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="R58" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="S58" t="n">
-        <v>4</v>
-      </c>
-      <c r="T58" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="Y58" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z58" t="n">
-        <v>16</v>
-      </c>
-      <c r="AA58" t="n">
-        <v>12</v>
-      </c>
-      <c r="AF58" t="n">
-        <v>223.35</v>
-      </c>
-      <c r="AG58" t="n">
-        <v>-0.85</v>
+        <v>46288</v>
       </c>
       <c r="AH58" t="n">
         <v>215</v>
@@ -6085,94 +5656,19 @@
       <c r="AI58" t="n">
         <v>235</v>
       </c>
-      <c r="AK58" t="n">
-        <v>127.19</v>
-      </c>
-      <c r="AL58" t="n">
-        <v>-1.41</v>
-      </c>
       <c r="AM58" t="n">
         <v>110</v>
       </c>
       <c r="AN58" t="n">
         <v>142</v>
       </c>
-      <c r="AP58" t="n">
-        <v>81.06</v>
-      </c>
-      <c r="AS58" t="n">
-        <v>13.63</v>
-      </c>
       <c r="BL58" s="1" t="n">
-        <v>46279</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="B59" t="n">
-        <v>145.5</v>
-      </c>
-      <c r="C59" t="n">
-        <v>62.3</v>
-      </c>
-      <c r="D59" t="n">
-        <v>34</v>
-      </c>
-      <c r="E59" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="F59" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="H59" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="I59" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="J59" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="K59" t="n">
-        <v>75</v>
-      </c>
-      <c r="M59" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="N59" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="O59" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="R59" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="S59" t="n">
-        <v>0</v>
-      </c>
-      <c r="T59" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="Y59" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z59" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA59" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="AF59" t="n">
-        <v>223.06</v>
-      </c>
-      <c r="AG59" t="n">
-        <v>-0.29</v>
+        <v>46289</v>
       </c>
       <c r="AH59" t="n">
         <v>215</v>
@@ -6180,94 +5676,19 @@
       <c r="AI59" t="n">
         <v>235</v>
       </c>
-      <c r="AK59" t="n">
-        <v>129.17</v>
-      </c>
-      <c r="AL59" t="n">
-        <v>1.98</v>
-      </c>
       <c r="AM59" t="n">
         <v>110</v>
       </c>
       <c r="AN59" t="n">
         <v>142</v>
       </c>
-      <c r="AP59" t="n">
-        <v>82.36</v>
-      </c>
-      <c r="AS59" t="n">
-        <v>13.91</v>
-      </c>
       <c r="BL59" s="1" t="n">
-        <v>46280</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="B60" t="n">
-        <v>148</v>
-      </c>
-      <c r="C60" t="n">
-        <v>61.6</v>
-      </c>
-      <c r="D60" t="n">
-        <v>33.9</v>
-      </c>
-      <c r="E60" t="n">
-        <v>25</v>
-      </c>
-      <c r="F60" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="H60" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="I60" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="J60" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="K60" t="n">
-        <v>74.09999999999999</v>
-      </c>
-      <c r="M60" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="N60" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="O60" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="R60" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="S60" t="n">
-        <v>0</v>
-      </c>
-      <c r="T60" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="Y60" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z60" t="n">
-        <v>15</v>
-      </c>
-      <c r="AA60" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="AF60" t="n">
-        <v>222.77</v>
-      </c>
-      <c r="AG60" t="n">
-        <v>-0.29</v>
+        <v>46290</v>
       </c>
       <c r="AH60" t="n">
         <v>215</v>
@@ -6275,49 +5696,19 @@
       <c r="AI60" t="n">
         <v>235</v>
       </c>
-      <c r="AK60" t="n">
-        <v>130.42</v>
-      </c>
-      <c r="AL60" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AM60" t="n">
         <v>110</v>
       </c>
       <c r="AN60" t="n">
         <v>142</v>
       </c>
-      <c r="AP60" t="n">
-        <v>80.90000000000001</v>
-      </c>
-      <c r="AS60" t="n">
-        <v>14</v>
-      </c>
       <c r="BL60" s="1" t="n">
-        <v>46281</v>
+        <v>46290</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="B61" t="n">
-        <v>125</v>
-      </c>
-      <c r="D61" t="n">
-        <v>34.2</v>
-      </c>
-      <c r="F61" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y61" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z61" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA61" t="n">
-        <v>16.5</v>
+        <v>46291</v>
       </c>
       <c r="AH61" t="n">
         <v>215</v>
@@ -6332,30 +5723,12 @@
         <v>142</v>
       </c>
       <c r="BL61" s="1" t="n">
-        <v>46282</v>
+        <v>46291</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="B62" t="n">
-        <v>118.1</v>
-      </c>
-      <c r="D62" t="n">
-        <v>34.7</v>
-      </c>
-      <c r="F62" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y62" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z62" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA62" t="n">
-        <v>19</v>
+        <v>46292</v>
       </c>
       <c r="AH62" t="n">
         <v>215</v>
@@ -6370,7 +5743,7 @@
         <v>142</v>
       </c>
       <c r="BL62" s="1" t="n">
-        <v>46283</v>
+        <v>46292</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -5087,6 +5087,15 @@
       <c r="T48" t="n">
         <v>23.8</v>
       </c>
+      <c r="V48" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="W48" t="n">
+        <v>11</v>
+      </c>
+      <c r="X48" t="n">
+        <v>8.9</v>
+      </c>
       <c r="Y48" t="n">
         <v>3</v>
       </c>
@@ -5095,6 +5104,15 @@
       </c>
       <c r="AA48" t="n">
         <v>7.9</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>5.7</v>
       </c>
       <c r="AF48" t="n">
         <v>224.2</v>
@@ -5589,6 +5607,24 @@
     <row r="55">
       <c r="A55" s="1" t="n">
         <v>46285</v>
+      </c>
+      <c r="B55" t="n">
+        <v>96.09999999999999</v>
+      </c>
+      <c r="D55" t="n">
+        <v>34</v>
+      </c>
+      <c r="F55" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>20.5</v>
       </c>
       <c r="AH55" t="n">
         <v>215</v>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -5200,6 +5200,15 @@
       <c r="T49" t="n">
         <v>23.8</v>
       </c>
+      <c r="V49" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="W49" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="X49" t="n">
+        <v>10.9</v>
+      </c>
       <c r="Y49" t="n">
         <v>5</v>
       </c>
@@ -5208,6 +5217,15 @@
       </c>
       <c r="AA49" t="n">
         <v>12</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>5.8</v>
       </c>
       <c r="AF49" t="n">
         <v>223.35</v>
@@ -5645,6 +5663,24 @@
     <row r="56">
       <c r="A56" s="1" t="n">
         <v>46286</v>
+      </c>
+      <c r="B56" t="n">
+        <v>111</v>
+      </c>
+      <c r="D56" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="F56" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>15</v>
       </c>
       <c r="AH56" t="n">
         <v>215</v>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -5313,6 +5313,15 @@
       <c r="T50" t="n">
         <v>22.1</v>
       </c>
+      <c r="V50" t="n">
+        <v>4</v>
+      </c>
+      <c r="W50" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="X50" t="n">
+        <v>13.4</v>
+      </c>
       <c r="Y50" t="n">
         <v>11</v>
       </c>
@@ -5321,6 +5330,15 @@
       </c>
       <c r="AA50" t="n">
         <v>12.9</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>6.7</v>
       </c>
       <c r="AF50" t="n">
         <v>223.06</v>
@@ -5627,13 +5645,52 @@
         <v>46285</v>
       </c>
       <c r="B55" t="n">
-        <v>96.09999999999999</v>
+        <v>104.9</v>
+      </c>
+      <c r="C55" t="n">
+        <v>36.3</v>
       </c>
       <c r="D55" t="n">
-        <v>34</v>
+        <v>32.7</v>
+      </c>
+      <c r="E55" t="n">
+        <v>17</v>
       </c>
       <c r="F55" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
+      </c>
+      <c r="H55" t="n">
+        <v>16</v>
+      </c>
+      <c r="I55" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="J55" t="n">
+        <v>25</v>
+      </c>
+      <c r="K55" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="M55" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N55" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="O55" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>10.5</v>
       </c>
       <c r="Y55" t="n">
         <v>16</v>
@@ -5642,7 +5699,13 @@
         <v>25</v>
       </c>
       <c r="AA55" t="n">
-        <v>20.5</v>
+        <v>16.9</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>234.9</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>13.04</v>
       </c>
       <c r="AH55" t="n">
         <v>215</v>
@@ -5650,11 +5713,23 @@
       <c r="AI55" t="n">
         <v>235</v>
       </c>
+      <c r="AK55" t="n">
+        <v>137.51</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>7.8</v>
+      </c>
       <c r="AM55" t="n">
         <v>110</v>
       </c>
       <c r="AN55" t="n">
         <v>142</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>94</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>18.87</v>
       </c>
       <c r="BL55" s="1" t="n">
         <v>46285</v>
@@ -5701,6 +5776,24 @@
     <row r="57">
       <c r="A57" s="1" t="n">
         <v>46287</v>
+      </c>
+      <c r="B57" t="n">
+        <v>125.6</v>
+      </c>
+      <c r="D57" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="F57" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>9</v>
       </c>
       <c r="AH57" t="n">
         <v>215</v>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -5426,6 +5426,15 @@
       <c r="T51" t="n">
         <v>23.3</v>
       </c>
+      <c r="V51" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="W51" t="n">
+        <v>26</v>
+      </c>
+      <c r="X51" t="n">
+        <v>16.9</v>
+      </c>
       <c r="Y51" t="n">
         <v>6</v>
       </c>
@@ -5434,6 +5443,15 @@
       </c>
       <c r="AA51" t="n">
         <v>11.6</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>7.8</v>
       </c>
       <c r="AF51" t="n">
         <v>222.77</v>
@@ -5740,13 +5758,52 @@
         <v>46286</v>
       </c>
       <c r="B56" t="n">
-        <v>111</v>
+        <v>134.9</v>
+      </c>
+      <c r="C56" t="n">
+        <v>53.3</v>
       </c>
       <c r="D56" t="n">
-        <v>35.3</v>
+        <v>36.3</v>
+      </c>
+      <c r="E56" t="n">
+        <v>20.6</v>
       </c>
       <c r="F56" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
+      </c>
+      <c r="H56" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="I56" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="J56" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="K56" t="n">
+        <v>66</v>
+      </c>
+      <c r="M56" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="N56" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="O56" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>18.3</v>
       </c>
       <c r="Y56" t="n">
         <v>12</v>
@@ -5755,7 +5812,13 @@
         <v>18</v>
       </c>
       <c r="AA56" t="n">
-        <v>15</v>
+        <v>13.8</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>229.2</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>-5.7</v>
       </c>
       <c r="AH56" t="n">
         <v>215</v>
@@ -5763,11 +5826,23 @@
       <c r="AI56" t="n">
         <v>235</v>
       </c>
+      <c r="AK56" t="n">
+        <v>138.98</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>1.47</v>
+      </c>
       <c r="AM56" t="n">
         <v>110</v>
       </c>
       <c r="AN56" t="n">
         <v>142</v>
+      </c>
+      <c r="AP56" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="AS56" t="n">
+        <v>16.02</v>
       </c>
       <c r="BL56" s="1" t="n">
         <v>46286</v>
@@ -5814,6 +5889,24 @@
     <row r="58">
       <c r="A58" s="1" t="n">
         <v>46288</v>
+      </c>
+      <c r="B58" t="n">
+        <v>120.5</v>
+      </c>
+      <c r="D58" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="F58" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>12.5</v>
       </c>
       <c r="AH58" t="n">
         <v>215</v>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -5539,6 +5539,15 @@
       <c r="T52" t="n">
         <v>23.3</v>
       </c>
+      <c r="V52" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="W52" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="X52" t="n">
+        <v>19.5</v>
+      </c>
       <c r="Y52" t="n">
         <v>11</v>
       </c>
@@ -5547,6 +5556,15 @@
       </c>
       <c r="AA52" t="n">
         <v>18.8</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>8.699999999999999</v>
       </c>
       <c r="AF52" t="n">
         <v>221.86</v>
@@ -5853,13 +5871,52 @@
         <v>46287</v>
       </c>
       <c r="B57" t="n">
-        <v>125.6</v>
+        <v>146.4</v>
+      </c>
+      <c r="C57" t="n">
+        <v>60.2</v>
       </c>
       <c r="D57" t="n">
-        <v>35.3</v>
+        <v>35.6</v>
+      </c>
+      <c r="E57" t="n">
+        <v>24.2</v>
       </c>
       <c r="F57" t="n">
-        <v>3.5</v>
+        <v>1.4</v>
+      </c>
+      <c r="H57" t="n">
+        <v>23</v>
+      </c>
+      <c r="I57" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="J57" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="K57" t="n">
+        <v>70</v>
+      </c>
+      <c r="M57" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N57" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="O57" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>20.2</v>
       </c>
       <c r="Y57" t="n">
         <v>5</v>
@@ -5868,7 +5925,13 @@
         <v>13</v>
       </c>
       <c r="AA57" t="n">
-        <v>9</v>
+        <v>9.6</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>224.9</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>-4.3</v>
       </c>
       <c r="AH57" t="n">
         <v>215</v>
@@ -5876,11 +5939,23 @@
       <c r="AI57" t="n">
         <v>235</v>
       </c>
+      <c r="AK57" t="n">
+        <v>134.04</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>-4.94</v>
+      </c>
       <c r="AM57" t="n">
         <v>110</v>
       </c>
       <c r="AN57" t="n">
         <v>142</v>
+      </c>
+      <c r="AP57" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="AS57" t="n">
+        <v>13.68</v>
       </c>
       <c r="BL57" s="1" t="n">
         <v>46287</v>
@@ -5927,6 +6002,24 @@
     <row r="59">
       <c r="A59" s="1" t="n">
         <v>46289</v>
+      </c>
+      <c r="B59" t="n">
+        <v>121</v>
+      </c>
+      <c r="D59" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="F59" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>17.5</v>
       </c>
       <c r="AH59" t="n">
         <v>215</v>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -5613,6 +5613,15 @@
       <c r="F53" t="n">
         <v>3.3</v>
       </c>
+      <c r="V53" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="W53" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="X53" t="n">
+        <v>20.9</v>
+      </c>
       <c r="Y53" t="n">
         <v>15</v>
       </c>
@@ -5621,6 +5630,15 @@
       </c>
       <c r="AA53" t="n">
         <v>19</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>9.199999999999999</v>
       </c>
       <c r="AH53" t="n">
         <v>215</v>
@@ -5966,13 +5984,52 @@
         <v>46288</v>
       </c>
       <c r="B58" t="n">
-        <v>120.5</v>
+        <v>131.4</v>
+      </c>
+      <c r="C58" t="n">
+        <v>53.7</v>
       </c>
       <c r="D58" t="n">
-        <v>36.4</v>
+        <v>34.7</v>
+      </c>
+      <c r="E58" t="n">
+        <v>20.1</v>
       </c>
       <c r="F58" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
+      </c>
+      <c r="H58" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I58" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J58" t="n">
+        <v>37</v>
+      </c>
+      <c r="K58" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="M58" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="N58" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="O58" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>22.3</v>
       </c>
       <c r="Y58" t="n">
         <v>7</v>
@@ -5981,7 +6038,13 @@
         <v>18</v>
       </c>
       <c r="AA58" t="n">
-        <v>12.5</v>
+        <v>14</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>220.8</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>-4.1</v>
       </c>
       <c r="AH58" t="n">
         <v>215</v>
@@ -5989,11 +6052,23 @@
       <c r="AI58" t="n">
         <v>235</v>
       </c>
+      <c r="AK58" t="n">
+        <v>131.01</v>
+      </c>
+      <c r="AL58" t="n">
+        <v>-3.03</v>
+      </c>
       <c r="AM58" t="n">
         <v>110</v>
       </c>
       <c r="AN58" t="n">
         <v>142</v>
+      </c>
+      <c r="AP58" t="n">
+        <v>81.28</v>
+      </c>
+      <c r="AS58" t="n">
+        <v>13.92</v>
       </c>
       <c r="BL58" s="1" t="n">
         <v>46288</v>
@@ -6040,6 +6115,24 @@
     <row r="60">
       <c r="A60" s="1" t="n">
         <v>46290</v>
+      </c>
+      <c r="B60" t="n">
+        <v>116.2</v>
+      </c>
+      <c r="D60" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="F60" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>21</v>
       </c>
       <c r="AH60" t="n">
         <v>215</v>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -628,88 +628,85 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46232</v>
+        <v>46231</v>
       </c>
       <c r="B2" t="n">
-        <v>172.9</v>
+        <v>166.4</v>
       </c>
       <c r="C2" t="n">
-        <v>67.59999999999999</v>
+        <v>63.7</v>
       </c>
       <c r="D2" t="n">
-        <v>34.9</v>
+        <v>34.5</v>
       </c>
       <c r="E2" t="n">
-        <v>35.2</v>
+        <v>36.4</v>
       </c>
       <c r="F2" t="n">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="H2" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="I2" t="n">
-        <v>11.3</v>
+        <v>11.6</v>
       </c>
       <c r="J2" t="n">
-        <v>41.7</v>
+        <v>39.9</v>
       </c>
       <c r="K2" t="n">
-        <v>76.7</v>
+        <v>75.2</v>
       </c>
       <c r="M2" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="N2" t="n">
-        <v>34.8</v>
+        <v>35.9</v>
       </c>
       <c r="O2" t="n">
-        <v>37.2</v>
+        <v>39</v>
       </c>
       <c r="Q2" t="n">
-        <v>19</v>
+        <v>20.3</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T2" t="n">
-        <v>19</v>
+        <v>20.3</v>
       </c>
       <c r="V2" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="W2" t="n">
+        <v>27</v>
+      </c>
+      <c r="X2" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA2" t="n">
         <v>14.4</v>
       </c>
-      <c r="W2" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="X2" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>15</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AB2" t="n">
-        <v>-4.9</v>
+        <v>-3.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.7</v>
+        <v>-0.4</v>
       </c>
       <c r="AF2" t="n">
-        <v>218.6</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-9.380000000000001</v>
+        <v>236.13</v>
       </c>
       <c r="AH2" t="n">
         <v>215</v>
@@ -718,10 +715,10 @@
         <v>235</v>
       </c>
       <c r="AK2" t="n">
-        <v>130.39</v>
+        <v>134.54</v>
       </c>
       <c r="AL2" t="n">
-        <v>-4.15</v>
+        <v>-1.74</v>
       </c>
       <c r="AM2" t="n">
         <v>110</v>
@@ -730,99 +727,99 @@
         <v>142</v>
       </c>
       <c r="AP2" t="n">
-        <v>78.5</v>
+        <v>82.27</v>
       </c>
       <c r="AS2" t="n">
-        <v>15.79</v>
+        <v>16.28</v>
       </c>
       <c r="BL2" s="1" t="n">
-        <v>46232</v>
+        <v>46231</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46233</v>
+        <v>46232</v>
       </c>
       <c r="B3" t="n">
-        <v>157.5</v>
+        <v>172.9</v>
       </c>
       <c r="C3" t="n">
-        <v>68.5</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>33.2</v>
+        <v>34.9</v>
       </c>
       <c r="E3" t="n">
-        <v>27.7</v>
+        <v>35.2</v>
       </c>
       <c r="F3" t="n">
-        <v>3.6</v>
+        <v>7.3</v>
       </c>
       <c r="H3" t="n">
-        <v>23.4</v>
+        <v>23.6</v>
       </c>
       <c r="I3" t="n">
         <v>11.3</v>
       </c>
       <c r="J3" t="n">
-        <v>41.4</v>
+        <v>41.7</v>
       </c>
       <c r="K3" t="n">
-        <v>76.09999999999999</v>
+        <v>76.7</v>
       </c>
       <c r="M3" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="N3" t="n">
-        <v>34.9</v>
+        <v>34.8</v>
       </c>
       <c r="O3" t="n">
-        <v>37.4</v>
+        <v>37.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>21.6</v>
+        <v>19</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
       <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="n">
+        <v>19</v>
+      </c>
+      <c r="V3" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="W3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="X3" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="Y3" t="n">
         <v>9</v>
       </c>
-      <c r="T3" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="V3" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="W3" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="X3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>11</v>
-      </c>
       <c r="Z3" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AA3" t="n">
-        <v>13.6</v>
+        <v>12.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0</v>
+        <v>-4.9</v>
       </c>
       <c r="AC3" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.5</v>
+        <v>-0.7</v>
       </c>
       <c r="AF3" t="n">
-        <v>218.84</v>
+        <v>218.6</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.25</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="AH3" t="n">
         <v>215</v>
@@ -831,10 +828,10 @@
         <v>235</v>
       </c>
       <c r="AK3" t="n">
-        <v>133.09</v>
+        <v>130.39</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.7</v>
+        <v>-4.15</v>
       </c>
       <c r="AM3" t="n">
         <v>110</v>
@@ -843,66 +840,99 @@
         <v>142</v>
       </c>
       <c r="AP3" t="n">
-        <v>83.09999999999999</v>
+        <v>78.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>15.63</v>
+        <v>15.79</v>
       </c>
       <c r="BL3" s="1" t="n">
-        <v>46233</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46234</v>
+        <v>46233</v>
       </c>
       <c r="B4" t="n">
-        <v>137.6</v>
+        <v>157.5</v>
+      </c>
+      <c r="C4" t="n">
+        <v>68.5</v>
       </c>
       <c r="D4" t="n">
-        <v>35</v>
+        <v>33.2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>27.7</v>
       </c>
       <c r="F4" t="n">
-        <v>6.5</v>
+        <v>3.6</v>
+      </c>
+      <c r="H4" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="I4" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="J4" t="n">
+        <v>41.4</v>
       </c>
       <c r="K4" t="n">
-        <v>96.7</v>
+        <v>76.09999999999999</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="N4" t="n">
+        <v>34.9</v>
       </c>
       <c r="O4" t="n">
-        <v>35.1</v>
+        <v>37.4</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>9</v>
+      </c>
+      <c r="T4" t="n">
+        <v>21.6</v>
       </c>
       <c r="V4" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="W4" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="X4" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA4" t="n">
         <v>13.6</v>
-      </c>
-      <c r="W4" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="X4" t="n">
-        <v>19</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>14</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>17.5</v>
       </c>
       <c r="AB4" t="n">
         <v>-0</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.5</v>
+        <v>3</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="AF4" t="n">
-        <v>221.78</v>
+        <v>218.84</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.94</v>
+        <v>0.25</v>
       </c>
       <c r="AH4" t="n">
         <v>215</v>
@@ -911,10 +941,10 @@
         <v>235</v>
       </c>
       <c r="AK4" t="n">
-        <v>138.76</v>
+        <v>133.09</v>
       </c>
       <c r="AL4" t="n">
-        <v>5.67</v>
+        <v>2.7</v>
       </c>
       <c r="AM4" t="n">
         <v>110</v>
@@ -922,61 +952,67 @@
       <c r="AN4" t="n">
         <v>142</v>
       </c>
+      <c r="AP4" t="n">
+        <v>83.09999999999999</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>15.63</v>
+      </c>
       <c r="BL4" s="1" t="n">
-        <v>46234</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46235</v>
+        <v>46234</v>
       </c>
       <c r="B5" t="n">
-        <v>132.5</v>
+        <v>137.6</v>
       </c>
       <c r="D5" t="n">
-        <v>33.6</v>
+        <v>35</v>
       </c>
       <c r="F5" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="K5" t="n">
-        <v>97.8</v>
+        <v>96.7</v>
       </c>
       <c r="O5" t="n">
-        <v>31.6</v>
+        <v>35.1</v>
       </c>
       <c r="V5" t="n">
-        <v>14.8</v>
+        <v>13.6</v>
       </c>
       <c r="W5" t="n">
-        <v>24.7</v>
+        <v>24.4</v>
       </c>
       <c r="X5" t="n">
-        <v>19.8</v>
+        <v>19</v>
       </c>
       <c r="Y5" t="n">
         <v>14</v>
       </c>
       <c r="Z5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AA5" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.6</v>
+        <v>-0</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="AF5" t="n">
-        <v>224.78</v>
+        <v>221.78</v>
       </c>
       <c r="AG5" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="AH5" t="n">
         <v>215</v>
@@ -985,10 +1021,10 @@
         <v>235</v>
       </c>
       <c r="AK5" t="n">
-        <v>143.55</v>
+        <v>138.76</v>
       </c>
       <c r="AL5" t="n">
-        <v>4.79</v>
+        <v>5.67</v>
       </c>
       <c r="AM5" t="n">
         <v>110</v>
@@ -997,93 +1033,60 @@
         <v>142</v>
       </c>
       <c r="BL5" s="1" t="n">
-        <v>46235</v>
+        <v>46234</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46236</v>
+        <v>46235</v>
       </c>
       <c r="B6" t="n">
-        <v>137.2</v>
-      </c>
-      <c r="C6" t="n">
-        <v>56.3</v>
+        <v>132.5</v>
       </c>
       <c r="D6" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="E6" t="n">
-        <v>21.2</v>
+        <v>33.6</v>
       </c>
       <c r="F6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H6" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="I6" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="J6" t="n">
-        <v>40.4</v>
+        <v>3.5</v>
       </c>
       <c r="K6" t="n">
-        <v>75.7</v>
-      </c>
-      <c r="M6" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="O6" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="V6" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="W6" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="X6" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AC6" t="n">
         <v>3.6</v>
       </c>
-      <c r="N6" t="n">
-        <v>29</v>
-      </c>
-      <c r="O6" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="V6" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="W6" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="X6" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>15</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>5.5</v>
-      </c>
       <c r="AD6" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="AF6" t="n">
-        <v>232.22</v>
+        <v>224.78</v>
       </c>
       <c r="AG6" t="n">
-        <v>7.43</v>
+        <v>3</v>
       </c>
       <c r="AH6" t="n">
         <v>215</v>
@@ -1092,10 +1095,10 @@
         <v>235</v>
       </c>
       <c r="AK6" t="n">
-        <v>143.61</v>
+        <v>143.55</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.06</v>
+        <v>4.79</v>
       </c>
       <c r="AM6" t="n">
         <v>110</v>
@@ -1103,58 +1106,52 @@
       <c r="AN6" t="n">
         <v>142</v>
       </c>
-      <c r="AP6" t="n">
-        <v>89.31999999999999</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>18.02</v>
-      </c>
       <c r="BL6" s="1" t="n">
-        <v>46236</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46237</v>
+        <v>46236</v>
       </c>
       <c r="B7" t="n">
-        <v>157.5</v>
+        <v>137.2</v>
       </c>
       <c r="C7" t="n">
-        <v>59.6</v>
+        <v>56.3</v>
       </c>
       <c r="D7" t="n">
-        <v>35</v>
+        <v>32.1</v>
       </c>
       <c r="E7" t="n">
-        <v>30.6</v>
+        <v>21.2</v>
       </c>
       <c r="F7" t="n">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="H7" t="n">
-        <v>24.2</v>
+        <v>23.7</v>
       </c>
       <c r="I7" t="n">
-        <v>11.2</v>
+        <v>11.6</v>
       </c>
       <c r="J7" t="n">
-        <v>38.9</v>
+        <v>40.4</v>
       </c>
       <c r="K7" t="n">
-        <v>74.3</v>
+        <v>75.7</v>
       </c>
       <c r="M7" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="N7" t="n">
-        <v>33.4</v>
+        <v>29</v>
       </c>
       <c r="O7" t="n">
-        <v>37.1</v>
+        <v>32.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>21.1</v>
+        <v>21.6</v>
       </c>
       <c r="R7" t="n">
         <v>1.3</v>
@@ -1163,40 +1160,40 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>21.1</v>
+        <v>21.6</v>
       </c>
       <c r="V7" t="n">
-        <v>13</v>
+        <v>10.7</v>
       </c>
       <c r="W7" t="n">
-        <v>26.3</v>
+        <v>24.3</v>
       </c>
       <c r="X7" t="n">
-        <v>19.6</v>
+        <v>17.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA7" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="AB7" t="n">
-        <v>-2.1</v>
+        <v>0.9</v>
       </c>
       <c r="AC7" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="AF7" t="n">
-        <v>229.69</v>
+        <v>232.22</v>
       </c>
       <c r="AG7" t="n">
-        <v>-2.53</v>
+        <v>7.43</v>
       </c>
       <c r="AH7" t="n">
         <v>215</v>
@@ -1205,10 +1202,10 @@
         <v>235</v>
       </c>
       <c r="AK7" t="n">
-        <v>136.96</v>
+        <v>143.61</v>
       </c>
       <c r="AL7" t="n">
-        <v>-6.65</v>
+        <v>0.06</v>
       </c>
       <c r="AM7" t="n">
         <v>110</v>
@@ -1217,99 +1214,99 @@
         <v>142</v>
       </c>
       <c r="AP7" t="n">
-        <v>86.59</v>
+        <v>89.31999999999999</v>
       </c>
       <c r="AS7" t="n">
-        <v>16.96</v>
+        <v>18.02</v>
       </c>
       <c r="BL7" s="1" t="n">
-        <v>46237</v>
+        <v>46236</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="B8" t="n">
-        <v>159.6</v>
+        <v>157.5</v>
       </c>
       <c r="C8" t="n">
-        <v>63</v>
+        <v>59.6</v>
       </c>
       <c r="D8" t="n">
-        <v>34.5</v>
+        <v>35</v>
       </c>
       <c r="E8" t="n">
-        <v>31.1</v>
+        <v>30.6</v>
       </c>
       <c r="F8" t="n">
-        <v>5.7</v>
+        <v>7.5</v>
       </c>
       <c r="H8" t="n">
-        <v>23.8</v>
+        <v>24.2</v>
       </c>
       <c r="I8" t="n">
-        <v>10.8</v>
+        <v>11.2</v>
       </c>
       <c r="J8" t="n">
-        <v>40.5</v>
+        <v>38.9</v>
       </c>
       <c r="K8" t="n">
-        <v>75.2</v>
+        <v>74.3</v>
       </c>
       <c r="M8" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="N8" t="n">
-        <v>34.3</v>
+        <v>33.4</v>
       </c>
       <c r="O8" t="n">
-        <v>38.2</v>
+        <v>37.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>21.3</v>
+        <v>21.1</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>21.3</v>
+        <v>21.1</v>
       </c>
       <c r="V8" t="n">
-        <v>17.5</v>
+        <v>13</v>
       </c>
       <c r="W8" t="n">
-        <v>22.5</v>
+        <v>26.3</v>
       </c>
       <c r="X8" t="n">
-        <v>20</v>
+        <v>19.6</v>
       </c>
       <c r="Y8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Z8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA8" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>-2.2</v>
+        <v>-2.1</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="AF8" t="n">
-        <v>228.57</v>
+        <v>229.69</v>
       </c>
       <c r="AG8" t="n">
-        <v>-1.14</v>
+        <v>-2.53</v>
       </c>
       <c r="AH8" t="n">
         <v>215</v>
@@ -1318,10 +1315,10 @@
         <v>235</v>
       </c>
       <c r="AK8" t="n">
-        <v>133.01</v>
+        <v>136.96</v>
       </c>
       <c r="AL8" t="n">
-        <v>-3.95</v>
+        <v>-6.65</v>
       </c>
       <c r="AM8" t="n">
         <v>110</v>
@@ -1330,99 +1327,99 @@
         <v>142</v>
       </c>
       <c r="AP8" t="n">
-        <v>84.59999999999999</v>
+        <v>86.59</v>
       </c>
       <c r="AS8" t="n">
-        <v>15.95</v>
+        <v>16.96</v>
       </c>
       <c r="BL8" s="1" t="n">
-        <v>46238</v>
+        <v>46237</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46239</v>
+        <v>46238</v>
       </c>
       <c r="B9" t="n">
-        <v>160.4</v>
+        <v>159.6</v>
       </c>
       <c r="C9" t="n">
-        <v>62.6</v>
+        <v>63</v>
       </c>
       <c r="D9" t="n">
-        <v>35</v>
+        <v>34.5</v>
       </c>
       <c r="E9" t="n">
-        <v>32.2</v>
+        <v>31.1</v>
       </c>
       <c r="F9" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="H9" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="I9" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="J9" t="n">
-        <v>41.1</v>
+        <v>40.5</v>
       </c>
       <c r="K9" t="n">
-        <v>75.7</v>
+        <v>75.2</v>
       </c>
       <c r="M9" t="n">
-        <v>5.4</v>
+        <v>4</v>
       </c>
       <c r="N9" t="n">
-        <v>32.6</v>
+        <v>34.3</v>
       </c>
       <c r="O9" t="n">
-        <v>38</v>
+        <v>38.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>20.9</v>
+        <v>21.3</v>
       </c>
       <c r="R9" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T9" t="n">
-        <v>20.9</v>
+        <v>21.3</v>
       </c>
       <c r="V9" t="n">
-        <v>16.4</v>
+        <v>17.5</v>
       </c>
       <c r="W9" t="n">
-        <v>22.8</v>
+        <v>22.5</v>
       </c>
       <c r="X9" t="n">
-        <v>19.6</v>
+        <v>20</v>
       </c>
       <c r="Y9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA9" t="n">
-        <v>14.1</v>
+        <v>13.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>-3.1</v>
+        <v>-2.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="AF9" t="n">
-        <v>225.08</v>
+        <v>228.57</v>
       </c>
       <c r="AG9" t="n">
-        <v>-3.5</v>
+        <v>-1.14</v>
       </c>
       <c r="AH9" t="n">
         <v>215</v>
@@ -1431,10 +1428,10 @@
         <v>235</v>
       </c>
       <c r="AK9" t="n">
-        <v>135.24</v>
+        <v>133.01</v>
       </c>
       <c r="AL9" t="n">
-        <v>2.23</v>
+        <v>-3.95</v>
       </c>
       <c r="AM9" t="n">
         <v>110</v>
@@ -1443,99 +1440,99 @@
         <v>142</v>
       </c>
       <c r="AP9" t="n">
-        <v>84.09999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="AS9" t="n">
-        <v>15.4</v>
+        <v>15.95</v>
       </c>
       <c r="BL9" s="1" t="n">
-        <v>46239</v>
+        <v>46238</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46240</v>
+        <v>46239</v>
       </c>
       <c r="B10" t="n">
-        <v>161.7</v>
+        <v>160.4</v>
       </c>
       <c r="C10" t="n">
-        <v>71.09999999999999</v>
+        <v>62.6</v>
       </c>
       <c r="D10" t="n">
-        <v>34.9</v>
+        <v>35</v>
       </c>
       <c r="E10" t="n">
-        <v>27.3</v>
+        <v>32.2</v>
       </c>
       <c r="F10" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="H10" t="n">
-        <v>24.1</v>
+        <v>23.9</v>
       </c>
       <c r="I10" t="n">
-        <v>10.3</v>
+        <v>10.7</v>
       </c>
       <c r="J10" t="n">
-        <v>42.6</v>
+        <v>41.1</v>
       </c>
       <c r="K10" t="n">
-        <v>77</v>
+        <v>75.7</v>
       </c>
       <c r="M10" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="N10" t="n">
-        <v>31.5</v>
+        <v>32.6</v>
       </c>
       <c r="O10" t="n">
-        <v>37.3</v>
+        <v>38</v>
       </c>
       <c r="Q10" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="R10" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T10" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="V10" t="n">
-        <v>12.7</v>
+        <v>16.4</v>
       </c>
       <c r="W10" t="n">
-        <v>27</v>
+        <v>22.8</v>
       </c>
       <c r="X10" t="n">
-        <v>19.9</v>
+        <v>19.6</v>
       </c>
       <c r="Y10" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="Z10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AA10" t="n">
-        <v>11.4</v>
+        <v>14.1</v>
       </c>
       <c r="AB10" t="n">
-        <v>-5.2</v>
+        <v>-3.1</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0.3</v>
+        <v>0.6</v>
       </c>
       <c r="AF10" t="n">
-        <v>225</v>
+        <v>225.08</v>
       </c>
       <c r="AG10" t="n">
-        <v>-0.08</v>
+        <v>-3.5</v>
       </c>
       <c r="AH10" t="n">
         <v>215</v>
@@ -1544,10 +1541,10 @@
         <v>235</v>
       </c>
       <c r="AK10" t="n">
-        <v>134.62</v>
+        <v>135.24</v>
       </c>
       <c r="AL10" t="n">
-        <v>-0.62</v>
+        <v>2.23</v>
       </c>
       <c r="AM10" t="n">
         <v>110</v>
@@ -1556,60 +1553,99 @@
         <v>142</v>
       </c>
       <c r="AP10" t="n">
-        <v>80.2</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="AS10" t="n">
-        <v>13.86</v>
+        <v>15.4</v>
       </c>
       <c r="BL10" s="1" t="n">
-        <v>46240</v>
+        <v>46239</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46241</v>
+        <v>46240</v>
       </c>
       <c r="B11" t="n">
-        <v>151.5</v>
+        <v>161.7</v>
+      </c>
+      <c r="C11" t="n">
+        <v>71.09999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>35.1</v>
+        <v>34.9</v>
+      </c>
+      <c r="E11" t="n">
+        <v>27.3</v>
       </c>
       <c r="F11" t="n">
-        <v>5.4</v>
+        <v>4.6</v>
+      </c>
+      <c r="H11" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="J11" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="K11" t="n">
+        <v>77</v>
+      </c>
+      <c r="M11" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="N11" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="O11" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>21</v>
+      </c>
+      <c r="R11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="S11" t="n">
+        <v>6</v>
+      </c>
+      <c r="T11" t="n">
+        <v>21</v>
       </c>
       <c r="V11" t="n">
-        <v>8.699999999999999</v>
+        <v>12.7</v>
       </c>
       <c r="W11" t="n">
-        <v>19.4</v>
+        <v>27</v>
       </c>
       <c r="X11" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z11" t="n">
         <v>14</v>
       </c>
-      <c r="Y11" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>13</v>
-      </c>
       <c r="AA11" t="n">
-        <v>9</v>
+        <v>11.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>-4.7</v>
+        <v>-5.2</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.9</v>
+        <v>4.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>-1.4</v>
+        <v>-0.3</v>
       </c>
       <c r="AF11" t="n">
-        <v>221.37</v>
+        <v>225</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.05</v>
+        <v>-0.08</v>
       </c>
       <c r="AH11" t="n">
         <v>215</v>
@@ -1618,10 +1654,10 @@
         <v>235</v>
       </c>
       <c r="AK11" t="n">
-        <v>135.21</v>
+        <v>134.62</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.59</v>
+        <v>-0.62</v>
       </c>
       <c r="AM11" t="n">
         <v>110</v>
@@ -1629,61 +1665,61 @@
       <c r="AN11" t="n">
         <v>142</v>
       </c>
+      <c r="AP11" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>13.86</v>
+      </c>
       <c r="BL11" s="1" t="n">
-        <v>46241</v>
+        <v>46240</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46242</v>
+        <v>46241</v>
       </c>
       <c r="B12" t="n">
-        <v>145.2</v>
+        <v>151.5</v>
       </c>
       <c r="D12" t="n">
-        <v>33.5</v>
+        <v>35.1</v>
       </c>
       <c r="F12" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="V12" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="W12" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="X12" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y12" t="n">
         <v>5</v>
-      </c>
-      <c r="K12" t="n">
-        <v>100.3</v>
-      </c>
-      <c r="O12" t="n">
-        <v>35.5</v>
-      </c>
-      <c r="V12" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W12" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="X12" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>7</v>
       </c>
       <c r="Z12" t="n">
         <v>13</v>
       </c>
       <c r="AA12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB12" t="n">
-        <v>-5.4</v>
+        <v>-4.7</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="AD12" t="n">
-        <v>-1.5</v>
+        <v>-1.4</v>
       </c>
       <c r="AF12" t="n">
-        <v>224.37</v>
+        <v>221.37</v>
       </c>
       <c r="AG12" t="n">
-        <v>3</v>
+        <v>0.05</v>
       </c>
       <c r="AH12" t="n">
         <v>215</v>
@@ -1692,10 +1728,10 @@
         <v>235</v>
       </c>
       <c r="AK12" t="n">
-        <v>135.61</v>
+        <v>135.21</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.4</v>
+        <v>0.59</v>
       </c>
       <c r="AM12" t="n">
         <v>110</v>
@@ -1704,60 +1740,60 @@
         <v>142</v>
       </c>
       <c r="BL12" s="1" t="n">
-        <v>46242</v>
+        <v>46241</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46243</v>
+        <v>46242</v>
       </c>
       <c r="B13" t="n">
-        <v>146.3</v>
+        <v>145.2</v>
       </c>
       <c r="D13" t="n">
-        <v>33.4</v>
+        <v>33.5</v>
       </c>
       <c r="F13" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="K13" t="n">
-        <v>98.2</v>
+        <v>100.3</v>
       </c>
       <c r="O13" t="n">
-        <v>35.1</v>
+        <v>35.5</v>
       </c>
       <c r="V13" t="n">
-        <v>4.9</v>
+        <v>7.1</v>
       </c>
       <c r="W13" t="n">
-        <v>16.4</v>
+        <v>19.2</v>
       </c>
       <c r="X13" t="n">
-        <v>10.6</v>
+        <v>13.1</v>
       </c>
       <c r="Y13" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>224.37</v>
+      </c>
+      <c r="AG13" t="n">
         <v>3</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>15</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>9</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>-6.4</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>-3.3</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>225.93</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.56</v>
       </c>
       <c r="AH13" t="n">
         <v>215</v>
@@ -1766,10 +1802,10 @@
         <v>235</v>
       </c>
       <c r="AK13" t="n">
-        <v>135.28</v>
+        <v>135.61</v>
       </c>
       <c r="AL13" t="n">
-        <v>-0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AM13" t="n">
         <v>110</v>
@@ -1778,93 +1814,60 @@
         <v>142</v>
       </c>
       <c r="BL13" s="1" t="n">
-        <v>46243</v>
+        <v>46242</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46244</v>
+        <v>46243</v>
       </c>
       <c r="B14" t="n">
-        <v>182.8</v>
-      </c>
-      <c r="C14" t="n">
-        <v>86.8</v>
+        <v>146.3</v>
       </c>
       <c r="D14" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="E14" t="n">
-        <v>33</v>
+        <v>33.4</v>
       </c>
       <c r="F14" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="H14" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="I14" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="J14" t="n">
-        <v>41.1</v>
+        <v>5.5</v>
       </c>
       <c r="K14" t="n">
-        <v>74.2</v>
-      </c>
-      <c r="M14" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="O14" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="V14" t="n">
         <v>4.9</v>
       </c>
-      <c r="N14" t="n">
-        <v>33.5</v>
-      </c>
-      <c r="O14" t="n">
-        <v>38.4</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="S14" t="n">
+      <c r="W14" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="X14" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z14" t="n">
         <v>15</v>
       </c>
-      <c r="T14" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="V14" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="W14" t="n">
-        <v>15</v>
-      </c>
-      <c r="X14" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>12</v>
-      </c>
       <c r="AA14" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="AB14" t="n">
-        <v>-10.5</v>
+        <v>-6.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.3</v>
+        <v>-0.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>-5.1</v>
+        <v>-3.3</v>
       </c>
       <c r="AF14" t="n">
-        <v>218.63</v>
+        <v>225.93</v>
       </c>
       <c r="AG14" t="n">
-        <v>-7.3</v>
+        <v>1.56</v>
       </c>
       <c r="AH14" t="n">
         <v>215</v>
@@ -1873,10 +1876,10 @@
         <v>235</v>
       </c>
       <c r="AK14" t="n">
-        <v>126.27</v>
+        <v>135.28</v>
       </c>
       <c r="AL14" t="n">
-        <v>-9.01</v>
+        <v>-0.33</v>
       </c>
       <c r="AM14" t="n">
         <v>110</v>
@@ -1884,100 +1887,94 @@
       <c r="AN14" t="n">
         <v>142</v>
       </c>
-      <c r="AP14" t="n">
-        <v>82.66</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>14.7</v>
-      </c>
       <c r="BL14" s="1" t="n">
-        <v>46244</v>
+        <v>46243</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46245</v>
+        <v>46244</v>
       </c>
       <c r="B15" t="n">
-        <v>181.8</v>
+        <v>182.8</v>
       </c>
       <c r="C15" t="n">
-        <v>86.5</v>
+        <v>86.8</v>
       </c>
       <c r="D15" t="n">
-        <v>31.4</v>
+        <v>31.8</v>
       </c>
       <c r="E15" t="n">
-        <v>34.2</v>
+        <v>33</v>
       </c>
       <c r="F15" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="H15" t="n">
-        <v>24.4</v>
+        <v>23.5</v>
       </c>
       <c r="I15" t="n">
-        <v>10.4</v>
+        <v>9.6</v>
       </c>
       <c r="J15" t="n">
-        <v>41.9</v>
+        <v>41.1</v>
       </c>
       <c r="K15" t="n">
-        <v>76.8</v>
+        <v>74.2</v>
       </c>
       <c r="M15" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="N15" t="n">
-        <v>35.7</v>
+        <v>33.5</v>
       </c>
       <c r="O15" t="n">
-        <v>39.8</v>
+        <v>38.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>23</v>
+        <v>22.4</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="S15" t="n">
-        <v>20.1</v>
+        <v>15</v>
       </c>
       <c r="T15" t="n">
-        <v>23</v>
+        <v>22.4</v>
       </c>
       <c r="V15" t="n">
-        <v>7.1</v>
+        <v>9.1</v>
       </c>
       <c r="W15" t="n">
-        <v>14.8</v>
+        <v>15</v>
       </c>
       <c r="X15" t="n">
-        <v>10.9</v>
+        <v>12.1</v>
       </c>
       <c r="Y15" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Z15" t="n">
         <v>12</v>
       </c>
       <c r="AA15" t="n">
-        <v>9.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>-4.5</v>
+        <v>-10.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.8</v>
+        <v>0.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>-1.4</v>
+        <v>-5.1</v>
       </c>
       <c r="AF15" t="n">
-        <v>216.39</v>
+        <v>218.63</v>
       </c>
       <c r="AG15" t="n">
-        <v>-2.23</v>
+        <v>-7.3</v>
       </c>
       <c r="AH15" t="n">
         <v>215</v>
@@ -1986,10 +1983,10 @@
         <v>235</v>
       </c>
       <c r="AK15" t="n">
-        <v>123.32</v>
+        <v>126.27</v>
       </c>
       <c r="AL15" t="n">
-        <v>-2.95</v>
+        <v>-9.01</v>
       </c>
       <c r="AM15" t="n">
         <v>110</v>
@@ -1998,99 +1995,99 @@
         <v>142</v>
       </c>
       <c r="AP15" t="n">
-        <v>79.08</v>
+        <v>82.66</v>
       </c>
       <c r="AS15" t="n">
-        <v>13.91</v>
+        <v>14.7</v>
       </c>
       <c r="BL15" s="1" t="n">
-        <v>46245</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46246</v>
+        <v>46245</v>
       </c>
       <c r="B16" t="n">
-        <v>183</v>
+        <v>181.8</v>
       </c>
       <c r="C16" t="n">
-        <v>84.7</v>
+        <v>86.5</v>
       </c>
       <c r="D16" t="n">
-        <v>30.9</v>
+        <v>31.4</v>
       </c>
       <c r="E16" t="n">
-        <v>33.7</v>
+        <v>34.2</v>
       </c>
       <c r="F16" t="n">
-        <v>7</v>
+        <v>5.8</v>
       </c>
       <c r="H16" t="n">
-        <v>23.4</v>
+        <v>24.4</v>
       </c>
       <c r="I16" t="n">
-        <v>10.6</v>
+        <v>10.4</v>
       </c>
       <c r="J16" t="n">
-        <v>42.3</v>
+        <v>41.9</v>
       </c>
       <c r="K16" t="n">
-        <v>76.40000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="M16" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="N16" t="n">
-        <v>36.7</v>
+        <v>35.7</v>
       </c>
       <c r="O16" t="n">
-        <v>40.8</v>
+        <v>39.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>23.6</v>
+        <v>23</v>
       </c>
       <c r="R16" t="n">
         <v>1.8</v>
       </c>
       <c r="S16" t="n">
-        <v>20.8</v>
+        <v>20.1</v>
       </c>
       <c r="T16" t="n">
-        <v>23.6</v>
+        <v>23</v>
       </c>
       <c r="V16" t="n">
-        <v>5.7</v>
+        <v>7.1</v>
       </c>
       <c r="W16" t="n">
-        <v>16.1</v>
+        <v>14.8</v>
       </c>
       <c r="X16" t="n">
         <v>10.9</v>
       </c>
       <c r="Y16" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Z16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA16" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.8</v>
+        <v>-4.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.8</v>
+        <v>-1.4</v>
       </c>
       <c r="AF16" t="n">
-        <v>217.16</v>
+        <v>216.39</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.76</v>
+        <v>-2.23</v>
       </c>
       <c r="AH16" t="n">
         <v>215</v>
@@ -2099,10 +2096,10 @@
         <v>235</v>
       </c>
       <c r="AK16" t="n">
-        <v>117.87</v>
+        <v>123.32</v>
       </c>
       <c r="AL16" t="n">
-        <v>-5.45</v>
+        <v>-2.95</v>
       </c>
       <c r="AM16" t="n">
         <v>110</v>
@@ -2111,66 +2108,99 @@
         <v>142</v>
       </c>
       <c r="AP16" t="n">
-        <v>78.56</v>
+        <v>79.08</v>
       </c>
       <c r="AS16" t="n">
-        <v>13.45</v>
+        <v>13.91</v>
       </c>
       <c r="BL16" s="1" t="n">
-        <v>46246</v>
+        <v>46245</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46247</v>
+        <v>46246</v>
       </c>
       <c r="B17" t="n">
-        <v>163.8</v>
+        <v>183</v>
+      </c>
+      <c r="C17" t="n">
+        <v>84.7</v>
       </c>
       <c r="D17" t="n">
-        <v>29</v>
+        <v>30.9</v>
+      </c>
+      <c r="E17" t="n">
+        <v>33.7</v>
       </c>
       <c r="F17" t="n">
-        <v>6.5</v>
+        <v>7</v>
+      </c>
+      <c r="H17" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="I17" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="J17" t="n">
+        <v>42.3</v>
       </c>
       <c r="K17" t="n">
-        <v>101.2</v>
+        <v>76.40000000000001</v>
+      </c>
+      <c r="M17" t="n">
+        <v>4</v>
+      </c>
+      <c r="N17" t="n">
+        <v>36.7</v>
       </c>
       <c r="O17" t="n">
-        <v>40.2</v>
+        <v>40.8</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S17" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="T17" t="n">
+        <v>23.6</v>
       </c>
       <c r="V17" t="n">
-        <v>6.3</v>
+        <v>5.7</v>
       </c>
       <c r="W17" t="n">
-        <v>17.2</v>
+        <v>16.1</v>
       </c>
       <c r="X17" t="n">
-        <v>11.8</v>
+        <v>10.9</v>
       </c>
       <c r="Y17" t="n">
         <v>8</v>
       </c>
       <c r="Z17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA17" t="n">
         <v>10</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.3</v>
+        <v>2.7</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="AF17" t="n">
-        <v>220.31</v>
+        <v>217.16</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.16</v>
+        <v>0.76</v>
       </c>
       <c r="AH17" t="n">
         <v>215</v>
@@ -2179,10 +2209,10 @@
         <v>235</v>
       </c>
       <c r="AK17" t="n">
-        <v>116.52</v>
+        <v>117.87</v>
       </c>
       <c r="AL17" t="n">
-        <v>-1.35</v>
+        <v>-5.45</v>
       </c>
       <c r="AM17" t="n">
         <v>110</v>
@@ -2190,61 +2220,67 @@
       <c r="AN17" t="n">
         <v>142</v>
       </c>
+      <c r="AP17" t="n">
+        <v>78.56</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>13.45</v>
+      </c>
       <c r="BL17" s="1" t="n">
-        <v>46247</v>
+        <v>46246</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46248</v>
+        <v>46247</v>
       </c>
       <c r="B18" t="n">
-        <v>155.9</v>
+        <v>163.8</v>
       </c>
       <c r="D18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F18" t="n">
         <v>6.5</v>
       </c>
       <c r="K18" t="n">
-        <v>99.3</v>
+        <v>101.2</v>
       </c>
       <c r="O18" t="n">
-        <v>38.5</v>
+        <v>40.2</v>
       </c>
       <c r="V18" t="n">
-        <v>8.9</v>
+        <v>6.3</v>
       </c>
       <c r="W18" t="n">
-        <v>15.8</v>
+        <v>17.2</v>
       </c>
       <c r="X18" t="n">
-        <v>12.4</v>
+        <v>11.8</v>
       </c>
       <c r="Y18" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA18" t="n">
         <v>10</v>
       </c>
-      <c r="Z18" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AB18" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AC18" t="n">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="AF18" t="n">
-        <v>221.99</v>
+        <v>220.31</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.67</v>
+        <v>3.16</v>
       </c>
       <c r="AH18" t="n">
         <v>215</v>
@@ -2253,10 +2289,10 @@
         <v>235</v>
       </c>
       <c r="AK18" t="n">
-        <v>116.37</v>
+        <v>116.52</v>
       </c>
       <c r="AL18" t="n">
-        <v>-0.15</v>
+        <v>-1.35</v>
       </c>
       <c r="AM18" t="n">
         <v>110</v>
@@ -2265,60 +2301,60 @@
         <v>142</v>
       </c>
       <c r="BL18" s="1" t="n">
-        <v>46248</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46249</v>
+        <v>46248</v>
       </c>
       <c r="B19" t="n">
-        <v>141.3</v>
+        <v>155.9</v>
       </c>
       <c r="D19" t="n">
-        <v>26.3</v>
+        <v>28</v>
       </c>
       <c r="F19" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="K19" t="n">
-        <v>97.8</v>
+        <v>99.3</v>
       </c>
       <c r="O19" t="n">
-        <v>39.8</v>
+        <v>38.5</v>
       </c>
       <c r="V19" t="n">
-        <v>9.5</v>
+        <v>8.9</v>
       </c>
       <c r="W19" t="n">
-        <v>17.7</v>
+        <v>15.8</v>
       </c>
       <c r="X19" t="n">
-        <v>13.6</v>
+        <v>12.4</v>
       </c>
       <c r="Y19" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z19" t="n">
         <v>13</v>
       </c>
-      <c r="Z19" t="n">
-        <v>15</v>
-      </c>
       <c r="AA19" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="AC19" t="n">
-        <v>7.5</v>
+        <v>5.7</v>
       </c>
       <c r="AD19" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="AF19" t="n">
-        <v>225.14</v>
+        <v>221.99</v>
       </c>
       <c r="AG19" t="n">
-        <v>3.15</v>
+        <v>1.67</v>
       </c>
       <c r="AH19" t="n">
         <v>215</v>
@@ -2326,6 +2362,12 @@
       <c r="AI19" t="n">
         <v>235</v>
       </c>
+      <c r="AK19" t="n">
+        <v>116.37</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>-0.15</v>
+      </c>
       <c r="AM19" t="n">
         <v>110</v>
       </c>
@@ -2333,54 +2375,60 @@
         <v>142</v>
       </c>
       <c r="BL19" s="1" t="n">
-        <v>46249</v>
+        <v>46248</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46250</v>
+        <v>46249</v>
       </c>
       <c r="B20" t="n">
-        <v>131.5</v>
+        <v>141.3</v>
       </c>
       <c r="D20" t="n">
-        <v>27.3</v>
+        <v>26.3</v>
       </c>
       <c r="F20" t="n">
         <v>5.5</v>
       </c>
       <c r="K20" t="n">
-        <v>97</v>
+        <v>97.8</v>
       </c>
       <c r="O20" t="n">
-        <v>35.7</v>
+        <v>39.8</v>
       </c>
       <c r="V20" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="W20" t="n">
-        <v>13.9</v>
+        <v>17.7</v>
       </c>
       <c r="X20" t="n">
-        <v>11.4</v>
+        <v>13.6</v>
       </c>
       <c r="Y20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z20" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AA20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AB20" t="n">
-        <v>-3.6</v>
+        <v>0.2</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.8</v>
+        <v>7.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>-0.4</v>
+        <v>3.9</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>225.14</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>3.15</v>
       </c>
       <c r="AH20" t="n">
         <v>215</v>
@@ -2395,93 +2443,54 @@
         <v>142</v>
       </c>
       <c r="BL20" s="1" t="n">
-        <v>46250</v>
+        <v>46249</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46251</v>
+        <v>46250</v>
       </c>
       <c r="B21" t="n">
-        <v>153</v>
-      </c>
-      <c r="C21" t="n">
-        <v>71.8</v>
+        <v>131.5</v>
       </c>
       <c r="D21" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="E21" t="n">
-        <v>24.7</v>
+        <v>27.3</v>
       </c>
       <c r="F21" t="n">
-        <v>4</v>
-      </c>
-      <c r="H21" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I21" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="J21" t="n">
-        <v>41.1</v>
+        <v>5.5</v>
       </c>
       <c r="K21" t="n">
-        <v>75.90000000000001</v>
-      </c>
-      <c r="M21" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="N21" t="n">
-        <v>33.5</v>
+        <v>97</v>
       </c>
       <c r="O21" t="n">
-        <v>38.3</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="R21" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>23.2</v>
+        <v>35.7</v>
       </c>
       <c r="V21" t="n">
-        <v>11.2</v>
+        <v>9</v>
       </c>
       <c r="W21" t="n">
-        <v>13</v>
+        <v>13.9</v>
       </c>
       <c r="X21" t="n">
-        <v>12.1</v>
+        <v>11.4</v>
       </c>
       <c r="Y21" t="n">
         <v>12</v>
       </c>
       <c r="Z21" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AA21" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AB21" t="n">
-        <v>-6.6</v>
+        <v>-3.6</v>
       </c>
       <c r="AC21" t="n">
-        <v>5.3</v>
+        <v>2.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>229.96</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>-0.02</v>
+        <v>-0.4</v>
       </c>
       <c r="AH21" t="n">
         <v>215</v>
@@ -2489,112 +2498,100 @@
       <c r="AI21" t="n">
         <v>235</v>
       </c>
-      <c r="AK21" t="n">
-        <v>128.14</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>11.77</v>
-      </c>
       <c r="AM21" t="n">
         <v>110</v>
       </c>
       <c r="AN21" t="n">
         <v>142</v>
       </c>
-      <c r="AP21" t="n">
-        <v>87.47</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>14.8</v>
-      </c>
       <c r="BL21" s="1" t="n">
-        <v>46251</v>
+        <v>46250</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46252</v>
+        <v>46251</v>
       </c>
       <c r="B22" t="n">
-        <v>165.8</v>
+        <v>153</v>
       </c>
       <c r="C22" t="n">
-        <v>77.3</v>
+        <v>71.8</v>
       </c>
       <c r="D22" t="n">
-        <v>29.3</v>
+        <v>28.6</v>
       </c>
       <c r="E22" t="n">
-        <v>27.7</v>
+        <v>24.7</v>
       </c>
       <c r="F22" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="H22" t="n">
         <v>24.1</v>
       </c>
       <c r="I22" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="J22" t="n">
-        <v>41.6</v>
+        <v>41.1</v>
       </c>
       <c r="K22" t="n">
-        <v>76.59999999999999</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="N22" t="n">
-        <v>35.1</v>
+        <v>33.5</v>
       </c>
       <c r="O22" t="n">
-        <v>39.8</v>
+        <v>38.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>23.8</v>
+        <v>23.2</v>
       </c>
       <c r="R22" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S22" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>23.8</v>
+        <v>23.2</v>
       </c>
       <c r="V22" t="n">
-        <v>9.4</v>
+        <v>11.2</v>
       </c>
       <c r="W22" t="n">
-        <v>17.4</v>
+        <v>13</v>
       </c>
       <c r="X22" t="n">
-        <v>13.4</v>
+        <v>12.1</v>
       </c>
       <c r="Y22" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="Z22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA22" t="n">
-        <v>10.1</v>
+        <v>12.5</v>
       </c>
       <c r="AB22" t="n">
-        <v>-0.7</v>
+        <v>-6.6</v>
       </c>
       <c r="AC22" t="n">
-        <v>9.5</v>
+        <v>5.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>4.4</v>
+        <v>-0.6</v>
       </c>
       <c r="AF22" t="n">
-        <v>227.01</v>
+        <v>229.96</v>
       </c>
       <c r="AG22" t="n">
-        <v>-2.95</v>
+        <v>-0.02</v>
       </c>
       <c r="AH22" t="n">
         <v>215</v>
@@ -2603,10 +2600,10 @@
         <v>235</v>
       </c>
       <c r="AK22" t="n">
-        <v>128.15</v>
+        <v>128.14</v>
       </c>
       <c r="AL22" t="n">
-        <v>0.01</v>
+        <v>11.77</v>
       </c>
       <c r="AM22" t="n">
         <v>110</v>
@@ -2615,99 +2612,99 @@
         <v>142</v>
       </c>
       <c r="AP22" t="n">
-        <v>83.41</v>
+        <v>87.47</v>
       </c>
       <c r="AS22" t="n">
-        <v>14.52</v>
+        <v>14.8</v>
       </c>
       <c r="BL22" s="1" t="n">
-        <v>46252</v>
+        <v>46251</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="B23" t="n">
-        <v>158.1</v>
+        <v>165.8</v>
       </c>
       <c r="C23" t="n">
-        <v>73.7</v>
+        <v>77.3</v>
       </c>
       <c r="D23" t="n">
-        <v>30.3</v>
+        <v>29.3</v>
       </c>
       <c r="E23" t="n">
-        <v>26</v>
+        <v>27.7</v>
       </c>
       <c r="F23" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="H23" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="I23" t="n">
-        <v>9.300000000000001</v>
+        <v>10.8</v>
       </c>
       <c r="J23" t="n">
-        <v>40.9</v>
+        <v>41.6</v>
       </c>
       <c r="K23" t="n">
-        <v>74.40000000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="N23" t="n">
-        <v>35.3</v>
+        <v>35.1</v>
       </c>
       <c r="O23" t="n">
-        <v>40.3</v>
+        <v>39.8</v>
       </c>
       <c r="Q23" t="n">
-        <v>23.6</v>
+        <v>23.8</v>
       </c>
       <c r="R23" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S23" t="n">
         <v>7</v>
       </c>
       <c r="T23" t="n">
-        <v>23.6</v>
+        <v>23.8</v>
       </c>
       <c r="V23" t="n">
-        <v>8.9</v>
+        <v>9.4</v>
       </c>
       <c r="W23" t="n">
-        <v>19.3</v>
+        <v>17.4</v>
       </c>
       <c r="X23" t="n">
-        <v>14.1</v>
+        <v>13.4</v>
       </c>
       <c r="Y23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z23" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA23" t="n">
-        <v>11</v>
+        <v>10.1</v>
       </c>
       <c r="AB23" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AD23" t="n">
         <v>4.4</v>
       </c>
-      <c r="AC23" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>6.5</v>
-      </c>
       <c r="AF23" t="n">
-        <v>228.35</v>
+        <v>227.01</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.33</v>
+        <v>-2.95</v>
       </c>
       <c r="AH23" t="n">
         <v>215</v>
@@ -2716,10 +2713,10 @@
         <v>235</v>
       </c>
       <c r="AK23" t="n">
-        <v>128.86</v>
+        <v>128.15</v>
       </c>
       <c r="AL23" t="n">
-        <v>0.71</v>
+        <v>0.01</v>
       </c>
       <c r="AM23" t="n">
         <v>110</v>
@@ -2728,99 +2725,99 @@
         <v>142</v>
       </c>
       <c r="AP23" t="n">
-        <v>82.37</v>
+        <v>83.41</v>
       </c>
       <c r="AS23" t="n">
-        <v>14.22</v>
+        <v>14.52</v>
       </c>
       <c r="BL23" s="1" t="n">
-        <v>46253</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="B24" t="n">
-        <v>154.9</v>
+        <v>158.1</v>
       </c>
       <c r="C24" t="n">
-        <v>70.2</v>
+        <v>73.7</v>
       </c>
       <c r="D24" t="n">
-        <v>31.5</v>
+        <v>30.3</v>
       </c>
       <c r="E24" t="n">
-        <v>27.7</v>
+        <v>26</v>
       </c>
       <c r="F24" t="n">
-        <v>2.7</v>
+        <v>4.1</v>
       </c>
       <c r="H24" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="I24" t="n">
-        <v>11.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J24" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="K24" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="M24" t="n">
+        <v>5</v>
+      </c>
+      <c r="N24" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="O24" t="n">
         <v>40.3</v>
       </c>
-      <c r="K24" t="n">
-        <v>75.8</v>
-      </c>
-      <c r="M24" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="N24" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="O24" t="n">
-        <v>39</v>
-      </c>
       <c r="Q24" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="R24" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="S24" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="T24" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="V24" t="n">
-        <v>6.3</v>
+        <v>8.9</v>
       </c>
       <c r="W24" t="n">
-        <v>25.2</v>
+        <v>19.3</v>
       </c>
       <c r="X24" t="n">
-        <v>15.8</v>
+        <v>14.1</v>
       </c>
       <c r="Y24" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Z24" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AA24" t="n">
-        <v>12.6</v>
+        <v>11</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.9</v>
+        <v>4.4</v>
       </c>
       <c r="AC24" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="AF24" t="n">
-        <v>231.16</v>
+        <v>228.35</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.81</v>
+        <v>1.33</v>
       </c>
       <c r="AH24" t="n">
         <v>215</v>
@@ -2829,10 +2826,10 @@
         <v>235</v>
       </c>
       <c r="AK24" t="n">
-        <v>130.88</v>
+        <v>128.86</v>
       </c>
       <c r="AL24" t="n">
-        <v>2.02</v>
+        <v>0.71</v>
       </c>
       <c r="AM24" t="n">
         <v>110</v>
@@ -2841,66 +2838,99 @@
         <v>142</v>
       </c>
       <c r="AP24" t="n">
-        <v>85.48999999999999</v>
+        <v>82.37</v>
       </c>
       <c r="AS24" t="n">
-        <v>13.1</v>
+        <v>14.22</v>
       </c>
       <c r="BL24" s="1" t="n">
-        <v>46254</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="B25" t="n">
-        <v>152.2</v>
+        <v>154.9</v>
+      </c>
+      <c r="C25" t="n">
+        <v>70.2</v>
       </c>
       <c r="D25" t="n">
-        <v>31</v>
+        <v>31.5</v>
+      </c>
+      <c r="E25" t="n">
+        <v>27.7</v>
       </c>
       <c r="F25" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
+      </c>
+      <c r="H25" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="J25" t="n">
+        <v>40.3</v>
       </c>
       <c r="K25" t="n">
-        <v>98.40000000000001</v>
+        <v>75.8</v>
+      </c>
+      <c r="M25" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="N25" t="n">
+        <v>32.9</v>
       </c>
       <c r="O25" t="n">
-        <v>34.4</v>
+        <v>39</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="R25" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="T25" t="n">
+        <v>23.7</v>
       </c>
       <c r="V25" t="n">
-        <v>9.5</v>
+        <v>6.3</v>
       </c>
       <c r="W25" t="n">
-        <v>25.5</v>
+        <v>25.2</v>
       </c>
       <c r="X25" t="n">
-        <v>17.5</v>
+        <v>15.8</v>
       </c>
       <c r="Y25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z25" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AA25" t="n">
-        <v>9</v>
+        <v>12.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>-1.1</v>
+        <v>2.9</v>
       </c>
       <c r="AC25" t="n">
         <v>8.6</v>
       </c>
       <c r="AD25" t="n">
-        <v>3.8</v>
+        <v>5.8</v>
       </c>
       <c r="AF25" t="n">
-        <v>228.13</v>
+        <v>231.16</v>
       </c>
       <c r="AG25" t="n">
-        <v>-3.03</v>
+        <v>2.81</v>
       </c>
       <c r="AH25" t="n">
         <v>215</v>
@@ -2908,67 +2938,79 @@
       <c r="AI25" t="n">
         <v>235</v>
       </c>
+      <c r="AK25" t="n">
+        <v>130.88</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>2.02</v>
+      </c>
       <c r="AM25" t="n">
         <v>110</v>
       </c>
       <c r="AN25" t="n">
         <v>142</v>
       </c>
+      <c r="AP25" t="n">
+        <v>85.48999999999999</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>13.1</v>
+      </c>
       <c r="BL25" s="1" t="n">
-        <v>46255</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46256</v>
+        <v>46255</v>
       </c>
       <c r="B26" t="n">
-        <v>143.9</v>
+        <v>152.2</v>
       </c>
       <c r="D26" t="n">
-        <v>30.8</v>
+        <v>31</v>
       </c>
       <c r="F26" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="K26" t="n">
-        <v>99.2</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O26" t="n">
-        <v>35.2</v>
+        <v>34.4</v>
       </c>
       <c r="V26" t="n">
-        <v>10.7</v>
+        <v>9.5</v>
       </c>
       <c r="W26" t="n">
-        <v>17.6</v>
+        <v>25.5</v>
       </c>
       <c r="X26" t="n">
-        <v>14.2</v>
+        <v>17.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z26" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AA26" t="n">
         <v>9</v>
       </c>
       <c r="AB26" t="n">
-        <v>-0.8</v>
+        <v>-1.1</v>
       </c>
       <c r="AC26" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AF26" t="n">
-        <v>229.16</v>
+        <v>228.13</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.03</v>
+        <v>-3.03</v>
       </c>
       <c r="AH26" t="n">
         <v>215</v>
@@ -2983,93 +3025,60 @@
         <v>142</v>
       </c>
       <c r="BL26" s="1" t="n">
-        <v>46256</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46257</v>
+        <v>46256</v>
       </c>
       <c r="B27" t="n">
-        <v>163.2</v>
-      </c>
-      <c r="C27" t="n">
-        <v>73.7</v>
+        <v>143.9</v>
       </c>
       <c r="D27" t="n">
-        <v>30</v>
-      </c>
-      <c r="E27" t="n">
-        <v>28.2</v>
+        <v>30.8</v>
       </c>
       <c r="F27" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H27" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I27" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="J27" t="n">
-        <v>40.1</v>
+        <v>2.5</v>
       </c>
       <c r="K27" t="n">
-        <v>75.59999999999999</v>
-      </c>
-      <c r="M27" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="N27" t="n">
-        <v>32.9</v>
+        <v>99.2</v>
       </c>
       <c r="O27" t="n">
-        <v>39.7</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="R27" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="S27" t="n">
-        <v>6</v>
-      </c>
-      <c r="T27" t="n">
-        <v>23.5</v>
+        <v>35.2</v>
       </c>
       <c r="V27" t="n">
-        <v>9.4</v>
+        <v>10.7</v>
       </c>
       <c r="W27" t="n">
-        <v>20.1</v>
+        <v>17.6</v>
       </c>
       <c r="X27" t="n">
-        <v>14.8</v>
+        <v>14.2</v>
       </c>
       <c r="Y27" t="n">
         <v>4</v>
       </c>
       <c r="Z27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA27" t="n">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="AB27" t="n">
-        <v>-0.9</v>
+        <v>-0.8</v>
       </c>
       <c r="AC27" t="n">
-        <v>9.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD27" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="AF27" t="n">
-        <v>228.55</v>
+        <v>229.16</v>
       </c>
       <c r="AG27" t="n">
-        <v>-0.61</v>
+        <v>1.03</v>
       </c>
       <c r="AH27" t="n">
         <v>215</v>
@@ -3077,112 +3086,100 @@
       <c r="AI27" t="n">
         <v>235</v>
       </c>
-      <c r="AK27" t="n">
-        <v>127.06</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>-3.82</v>
-      </c>
       <c r="AM27" t="n">
         <v>110</v>
       </c>
       <c r="AN27" t="n">
         <v>142</v>
       </c>
-      <c r="AP27" t="n">
-        <v>82.81</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>12.9</v>
-      </c>
       <c r="BL27" s="1" t="n">
-        <v>46257</v>
+        <v>46256</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46258</v>
+        <v>46257</v>
       </c>
       <c r="B28" t="n">
-        <v>174.4</v>
+        <v>163.2</v>
       </c>
       <c r="C28" t="n">
-        <v>75.40000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="D28" t="n">
-        <v>32.1</v>
+        <v>30</v>
       </c>
       <c r="E28" t="n">
-        <v>30.8</v>
+        <v>28.2</v>
       </c>
       <c r="F28" t="n">
-        <v>6.6</v>
+        <v>4.8</v>
       </c>
       <c r="H28" t="n">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="I28" t="n">
-        <v>10.5</v>
+        <v>11.4</v>
       </c>
       <c r="J28" t="n">
-        <v>39.5</v>
+        <v>40.1</v>
       </c>
       <c r="K28" t="n">
-        <v>74</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="M28" t="n">
         <v>6.8</v>
       </c>
       <c r="N28" t="n">
-        <v>35.8</v>
+        <v>32.9</v>
       </c>
       <c r="O28" t="n">
-        <v>42.6</v>
+        <v>39.7</v>
       </c>
       <c r="Q28" t="n">
-        <v>23.1</v>
+        <v>23.5</v>
       </c>
       <c r="R28" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="S28" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="T28" t="n">
-        <v>23.1</v>
+        <v>23.5</v>
       </c>
       <c r="V28" t="n">
-        <v>12.8</v>
+        <v>9.4</v>
       </c>
       <c r="W28" t="n">
-        <v>22.1</v>
+        <v>20.1</v>
       </c>
       <c r="X28" t="n">
-        <v>17.5</v>
+        <v>14.8</v>
       </c>
       <c r="Y28" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Z28" t="n">
         <v>13</v>
       </c>
       <c r="AA28" t="n">
-        <v>10.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.3</v>
+        <v>-0.9</v>
       </c>
       <c r="AC28" t="n">
-        <v>9.300000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="AF28" t="n">
-        <v>219.99</v>
+        <v>228.55</v>
       </c>
       <c r="AG28" t="n">
-        <v>-8.56</v>
+        <v>-0.61</v>
       </c>
       <c r="AH28" t="n">
         <v>215</v>
@@ -3191,10 +3188,10 @@
         <v>235</v>
       </c>
       <c r="AK28" t="n">
-        <v>125.61</v>
+        <v>127.06</v>
       </c>
       <c r="AL28" t="n">
-        <v>-1.45</v>
+        <v>-3.82</v>
       </c>
       <c r="AM28" t="n">
         <v>110</v>
@@ -3203,99 +3200,99 @@
         <v>142</v>
       </c>
       <c r="AP28" t="n">
-        <v>77.83</v>
+        <v>82.81</v>
       </c>
       <c r="AS28" t="n">
-        <v>12.96</v>
+        <v>12.9</v>
       </c>
       <c r="BL28" s="1" t="n">
-        <v>46258</v>
+        <v>46257</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46259</v>
+        <v>46258</v>
       </c>
       <c r="B29" t="n">
-        <v>163.2</v>
+        <v>174.4</v>
       </c>
       <c r="C29" t="n">
-        <v>70.90000000000001</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="D29" t="n">
-        <v>32.9</v>
+        <v>32.1</v>
       </c>
       <c r="E29" t="n">
-        <v>26</v>
+        <v>30.8</v>
       </c>
       <c r="F29" t="n">
-        <v>6.9</v>
+        <v>6.6</v>
       </c>
       <c r="H29" t="n">
-        <v>23.8</v>
+        <v>24</v>
       </c>
       <c r="I29" t="n">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="J29" t="n">
-        <v>40.1</v>
+        <v>39.5</v>
       </c>
       <c r="K29" t="n">
-        <v>71.3</v>
+        <v>74</v>
       </c>
       <c r="M29" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="N29" t="n">
-        <v>34.3</v>
+        <v>35.8</v>
       </c>
       <c r="O29" t="n">
-        <v>41.5</v>
+        <v>42.6</v>
       </c>
       <c r="Q29" t="n">
         <v>23.1</v>
       </c>
       <c r="R29" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="S29" t="n">
-        <v>6.2</v>
+        <v>8.5</v>
       </c>
       <c r="T29" t="n">
         <v>23.1</v>
       </c>
       <c r="V29" t="n">
-        <v>9.6</v>
+        <v>12.8</v>
       </c>
       <c r="W29" t="n">
-        <v>23.3</v>
+        <v>22.1</v>
       </c>
       <c r="X29" t="n">
-        <v>16.4</v>
+        <v>17.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA29" t="n">
-        <v>12.2</v>
+        <v>10.1</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.6</v>
+        <v>0.3</v>
       </c>
       <c r="AC29" t="n">
-        <v>8.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AD29" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="AF29" t="n">
-        <v>219.22</v>
+        <v>219.99</v>
       </c>
       <c r="AG29" t="n">
-        <v>-0.77</v>
+        <v>-8.56</v>
       </c>
       <c r="AH29" t="n">
         <v>215</v>
@@ -3304,10 +3301,10 @@
         <v>235</v>
       </c>
       <c r="AK29" t="n">
-        <v>124.36</v>
+        <v>125.61</v>
       </c>
       <c r="AL29" t="n">
-        <v>-1.25</v>
+        <v>-1.45</v>
       </c>
       <c r="AM29" t="n">
         <v>110</v>
@@ -3316,99 +3313,99 @@
         <v>142</v>
       </c>
       <c r="AP29" t="n">
-        <v>76.81</v>
+        <v>77.83</v>
       </c>
       <c r="AS29" t="n">
-        <v>12.38</v>
+        <v>12.96</v>
       </c>
       <c r="BL29" s="1" t="n">
-        <v>46259</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46260</v>
+        <v>46259</v>
       </c>
       <c r="B30" t="n">
-        <v>152.7</v>
+        <v>163.2</v>
       </c>
       <c r="C30" t="n">
-        <v>62.6</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="D30" t="n">
-        <v>32.7</v>
+        <v>32.9</v>
       </c>
       <c r="E30" t="n">
-        <v>24.6</v>
+        <v>26</v>
       </c>
       <c r="F30" t="n">
-        <v>5.2</v>
+        <v>6.9</v>
       </c>
       <c r="H30" t="n">
         <v>23.8</v>
       </c>
       <c r="I30" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J30" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="K30" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="M30" t="n">
         <v>7.2</v>
       </c>
-      <c r="J30" t="n">
-        <v>38.9</v>
-      </c>
-      <c r="K30" t="n">
-        <v>69.90000000000001</v>
-      </c>
-      <c r="M30" t="n">
-        <v>6.6</v>
-      </c>
       <c r="N30" t="n">
-        <v>33.5</v>
+        <v>34.3</v>
       </c>
       <c r="O30" t="n">
-        <v>40.1</v>
+        <v>41.5</v>
       </c>
       <c r="Q30" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="R30" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>6.2</v>
       </c>
       <c r="T30" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="V30" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="W30" t="n">
-        <v>27.3</v>
+        <v>23.3</v>
       </c>
       <c r="X30" t="n">
-        <v>19.4</v>
+        <v>16.4</v>
       </c>
       <c r="Y30" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z30" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AA30" t="n">
-        <v>14</v>
+        <v>12.2</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="AC30" t="n">
-        <v>9.6</v>
+        <v>8.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AF30" t="n">
-        <v>220.73</v>
+        <v>219.22</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.5</v>
+        <v>-0.77</v>
       </c>
       <c r="AH30" t="n">
         <v>215</v>
@@ -3417,10 +3414,10 @@
         <v>235</v>
       </c>
       <c r="AK30" t="n">
-        <v>120.93</v>
+        <v>124.36</v>
       </c>
       <c r="AL30" t="n">
-        <v>-3.43</v>
+        <v>-1.25</v>
       </c>
       <c r="AM30" t="n">
         <v>110</v>
@@ -3429,75 +3426,75 @@
         <v>142</v>
       </c>
       <c r="AP30" t="n">
-        <v>77.87</v>
+        <v>76.81</v>
       </c>
       <c r="AS30" t="n">
-        <v>13.26</v>
+        <v>12.38</v>
       </c>
       <c r="BL30" s="1" t="n">
-        <v>46260</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46261</v>
+        <v>46260</v>
       </c>
       <c r="B31" t="n">
-        <v>150.7</v>
+        <v>152.7</v>
       </c>
       <c r="C31" t="n">
-        <v>64.8</v>
+        <v>62.6</v>
       </c>
       <c r="D31" t="n">
-        <v>33.7</v>
+        <v>32.7</v>
       </c>
       <c r="E31" t="n">
-        <v>27.1</v>
+        <v>24.6</v>
       </c>
       <c r="F31" t="n">
-        <v>3.8</v>
+        <v>5.2</v>
       </c>
       <c r="H31" t="n">
-        <v>23.4</v>
+        <v>23.8</v>
       </c>
       <c r="I31" t="n">
         <v>7.2</v>
       </c>
       <c r="J31" t="n">
-        <v>39.9</v>
+        <v>38.9</v>
       </c>
       <c r="K31" t="n">
-        <v>70.5</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="M31" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="N31" t="n">
-        <v>33</v>
+        <v>33.5</v>
       </c>
       <c r="O31" t="n">
-        <v>38.6</v>
+        <v>40.1</v>
       </c>
       <c r="Q31" t="n">
         <v>23.2</v>
       </c>
       <c r="R31" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T31" t="n">
         <v>23.2</v>
       </c>
       <c r="V31" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="W31" t="n">
-        <v>28.9</v>
+        <v>27.3</v>
       </c>
       <c r="X31" t="n">
-        <v>21.7</v>
+        <v>19.4</v>
       </c>
       <c r="Y31" t="n">
         <v>10</v>
@@ -3506,22 +3503,22 @@
         <v>18</v>
       </c>
       <c r="AA31" t="n">
-        <v>13.1</v>
+        <v>14</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="AC31" t="n">
-        <v>10.8</v>
+        <v>9.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>6.7</v>
+        <v>5.7</v>
       </c>
       <c r="AF31" t="n">
-        <v>220.58</v>
+        <v>220.73</v>
       </c>
       <c r="AG31" t="n">
-        <v>-0.15</v>
+        <v>1.5</v>
       </c>
       <c r="AH31" t="n">
         <v>215</v>
@@ -3530,10 +3527,10 @@
         <v>235</v>
       </c>
       <c r="AK31" t="n">
-        <v>120.28</v>
+        <v>120.93</v>
       </c>
       <c r="AL31" t="n">
-        <v>-0.65</v>
+        <v>-3.43</v>
       </c>
       <c r="AM31" t="n">
         <v>110</v>
@@ -3542,54 +3539,99 @@
         <v>142</v>
       </c>
       <c r="AP31" t="n">
-        <v>77.22</v>
+        <v>77.87</v>
       </c>
       <c r="AS31" t="n">
-        <v>13.79</v>
+        <v>13.26</v>
       </c>
       <c r="BL31" s="1" t="n">
-        <v>46261</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46262</v>
+        <v>46261</v>
       </c>
       <c r="B32" t="n">
-        <v>138.2</v>
+        <v>150.7</v>
+      </c>
+      <c r="C32" t="n">
+        <v>64.8</v>
       </c>
       <c r="D32" t="n">
-        <v>33.6</v>
+        <v>33.7</v>
+      </c>
+      <c r="E32" t="n">
+        <v>27.1</v>
       </c>
       <c r="F32" t="n">
-        <v>6.1</v>
+        <v>3.8</v>
+      </c>
+      <c r="H32" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="I32" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J32" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="K32" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="M32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="N32" t="n">
+        <v>33</v>
+      </c>
+      <c r="O32" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="R32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3</v>
+      </c>
+      <c r="T32" t="n">
+        <v>23.2</v>
       </c>
       <c r="V32" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="W32" t="n">
-        <v>23.4</v>
+        <v>28.9</v>
       </c>
       <c r="X32" t="n">
-        <v>19.4</v>
+        <v>21.7</v>
       </c>
       <c r="Y32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z32" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA32" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.4</v>
+        <v>2.5</v>
       </c>
       <c r="AC32" t="n">
-        <v>8.5</v>
+        <v>10.8</v>
       </c>
       <c r="AD32" t="n">
-        <v>4.5</v>
+        <v>6.7</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>220.58</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>-0.15</v>
       </c>
       <c r="AH32" t="n">
         <v>215</v>
@@ -3597,61 +3639,67 @@
       <c r="AI32" t="n">
         <v>235</v>
       </c>
+      <c r="AK32" t="n">
+        <v>120.28</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>-0.65</v>
+      </c>
       <c r="AM32" t="n">
         <v>110</v>
       </c>
       <c r="AN32" t="n">
         <v>142</v>
       </c>
+      <c r="AP32" t="n">
+        <v>77.22</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>13.79</v>
+      </c>
       <c r="BL32" s="1" t="n">
-        <v>46262</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46263</v>
+        <v>46262</v>
       </c>
       <c r="B33" t="n">
-        <v>126.5</v>
+        <v>138.2</v>
       </c>
       <c r="D33" t="n">
-        <v>33.2</v>
+        <v>33.6</v>
       </c>
       <c r="F33" t="n">
-        <v>3.4</v>
+        <v>6.1</v>
       </c>
       <c r="V33" t="n">
-        <v>12.6</v>
+        <v>15.5</v>
       </c>
       <c r="W33" t="n">
-        <v>22.3</v>
+        <v>23.4</v>
       </c>
       <c r="X33" t="n">
-        <v>17.4</v>
+        <v>19.4</v>
       </c>
       <c r="Y33" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z33" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AA33" t="n">
         <v>13</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AC33" t="n">
-        <v>6.7</v>
+        <v>8.5</v>
       </c>
       <c r="AD33" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>229.48</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>6.05</v>
+        <v>4.5</v>
       </c>
       <c r="AH33" t="n">
         <v>215</v>
@@ -3666,93 +3714,54 @@
         <v>142</v>
       </c>
       <c r="BL33" s="1" t="n">
-        <v>46263</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>46264</v>
+        <v>46263</v>
       </c>
       <c r="B34" t="n">
-        <v>129.4</v>
-      </c>
-      <c r="C34" t="n">
-        <v>50.6</v>
+        <v>126.5</v>
       </c>
       <c r="D34" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="E34" t="n">
-        <v>19.4</v>
+        <v>33.2</v>
       </c>
       <c r="F34" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="H34" t="n">
-        <v>24</v>
-      </c>
-      <c r="I34" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="J34" t="n">
-        <v>38.9</v>
-      </c>
-      <c r="K34" t="n">
-        <v>73.3</v>
-      </c>
-      <c r="M34" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="N34" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="O34" t="n">
-        <v>38</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>21.4</v>
+        <v>3.4</v>
       </c>
       <c r="V34" t="n">
-        <v>14.3</v>
+        <v>12.6</v>
       </c>
       <c r="W34" t="n">
-        <v>23.9</v>
+        <v>22.3</v>
       </c>
       <c r="X34" t="n">
-        <v>19.1</v>
+        <v>17.4</v>
       </c>
       <c r="Y34" t="n">
         <v>8</v>
       </c>
       <c r="Z34" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AA34" t="n">
-        <v>16.1</v>
+        <v>13</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>7.6</v>
+        <v>6.7</v>
       </c>
       <c r="AD34" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="AF34" t="n">
-        <v>229.5</v>
+        <v>229.48</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.02</v>
+        <v>6.05</v>
       </c>
       <c r="AH34" t="n">
         <v>215</v>
@@ -3760,112 +3769,100 @@
       <c r="AI34" t="n">
         <v>235</v>
       </c>
-      <c r="AK34" t="n">
-        <v>128.37</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>8.09</v>
-      </c>
       <c r="AM34" t="n">
         <v>110</v>
       </c>
       <c r="AN34" t="n">
         <v>142</v>
       </c>
-      <c r="AP34" t="n">
-        <v>91.59999999999999</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>15.97</v>
-      </c>
       <c r="BL34" s="1" t="n">
-        <v>46264</v>
+        <v>46263</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>46265</v>
+        <v>46264</v>
       </c>
       <c r="B35" t="n">
-        <v>142.9</v>
+        <v>129.4</v>
       </c>
       <c r="C35" t="n">
-        <v>52.7</v>
+        <v>50.6</v>
       </c>
       <c r="D35" t="n">
-        <v>34.7</v>
+        <v>31.5</v>
       </c>
       <c r="E35" t="n">
-        <v>24.8</v>
+        <v>19.4</v>
       </c>
       <c r="F35" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="H35" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I35" t="n">
-        <v>9.9</v>
+        <v>10.4</v>
       </c>
       <c r="J35" t="n">
-        <v>38.2</v>
+        <v>38.9</v>
       </c>
       <c r="K35" t="n">
-        <v>70</v>
+        <v>73.3</v>
       </c>
       <c r="M35" t="n">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="N35" t="n">
-        <v>31.9</v>
+        <v>33.3</v>
       </c>
       <c r="O35" t="n">
-        <v>35.8</v>
+        <v>38</v>
       </c>
       <c r="Q35" t="n">
-        <v>19.7</v>
+        <v>21.4</v>
       </c>
       <c r="R35" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>19.7</v>
+        <v>21.4</v>
       </c>
       <c r="V35" t="n">
-        <v>12</v>
+        <v>14.3</v>
       </c>
       <c r="W35" t="n">
-        <v>25.8</v>
+        <v>23.9</v>
       </c>
       <c r="X35" t="n">
-        <v>18.9</v>
+        <v>19.1</v>
       </c>
       <c r="Y35" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Z35" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA35" t="n">
-        <v>15</v>
+        <v>16.1</v>
       </c>
       <c r="AB35" t="n">
-        <v>-0.1</v>
+        <v>0.4</v>
       </c>
       <c r="AC35" t="n">
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="AF35" t="n">
-        <v>238.69</v>
+        <v>229.5</v>
       </c>
       <c r="AG35" t="n">
-        <v>-2.8</v>
+        <v>0.02</v>
       </c>
       <c r="AH35" t="n">
         <v>215</v>
@@ -3874,10 +3871,10 @@
         <v>235</v>
       </c>
       <c r="AK35" t="n">
-        <v>134.59</v>
+        <v>128.37</v>
       </c>
       <c r="AL35" t="n">
-        <v>6.22</v>
+        <v>8.09</v>
       </c>
       <c r="AM35" t="n">
         <v>110</v>
@@ -3886,99 +3883,99 @@
         <v>142</v>
       </c>
       <c r="AP35" t="n">
-        <v>89.05</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="AS35" t="n">
-        <v>17.06</v>
+        <v>15.97</v>
       </c>
       <c r="BL35" s="1" t="n">
-        <v>46265</v>
+        <v>46264</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="B36" t="n">
-        <v>148.1</v>
+        <v>142.9</v>
       </c>
       <c r="C36" t="n">
-        <v>51.9</v>
+        <v>52.7</v>
       </c>
       <c r="D36" t="n">
-        <v>35.4</v>
+        <v>34.7</v>
       </c>
       <c r="E36" t="n">
-        <v>31.5</v>
+        <v>24.8</v>
       </c>
       <c r="F36" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="H36" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="I36" t="n">
-        <v>9.6</v>
+        <v>9.9</v>
       </c>
       <c r="J36" t="n">
-        <v>39.6</v>
+        <v>38.2</v>
       </c>
       <c r="K36" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M36" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="N36" t="n">
-        <v>30.8</v>
+        <v>31.9</v>
       </c>
       <c r="O36" t="n">
-        <v>33.7</v>
+        <v>35.8</v>
       </c>
       <c r="Q36" t="n">
-        <v>20.7</v>
+        <v>19.7</v>
       </c>
       <c r="R36" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>20.7</v>
+        <v>19.7</v>
       </c>
       <c r="V36" t="n">
-        <v>13.1</v>
+        <v>12</v>
       </c>
       <c r="W36" t="n">
-        <v>25.5</v>
+        <v>25.8</v>
       </c>
       <c r="X36" t="n">
-        <v>19.3</v>
+        <v>18.9</v>
       </c>
       <c r="Y36" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z36" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA36" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AB36" t="n">
-        <v>-1</v>
+        <v>-0.1</v>
       </c>
       <c r="AC36" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AF36" t="n">
-        <v>233.48</v>
+        <v>238.69</v>
       </c>
       <c r="AG36" t="n">
-        <v>-4.86</v>
+        <v>-2.8</v>
       </c>
       <c r="AH36" t="n">
         <v>215</v>
@@ -3987,10 +3984,10 @@
         <v>235</v>
       </c>
       <c r="AK36" t="n">
-        <v>136.6</v>
+        <v>134.59</v>
       </c>
       <c r="AL36" t="n">
-        <v>2.01</v>
+        <v>6.22</v>
       </c>
       <c r="AM36" t="n">
         <v>110</v>
@@ -3999,99 +3996,99 @@
         <v>142</v>
       </c>
       <c r="AP36" t="n">
-        <v>86.25</v>
+        <v>89.05</v>
       </c>
       <c r="AS36" t="n">
-        <v>17.13</v>
+        <v>17.06</v>
       </c>
       <c r="BL36" s="1" t="n">
-        <v>46266</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>46267</v>
+        <v>46266</v>
       </c>
       <c r="B37" t="n">
-        <v>143.4</v>
+        <v>148.1</v>
       </c>
       <c r="C37" t="n">
-        <v>50.9</v>
+        <v>51.9</v>
       </c>
       <c r="D37" t="n">
-        <v>35.7</v>
+        <v>35.4</v>
       </c>
       <c r="E37" t="n">
-        <v>26.2</v>
+        <v>31.5</v>
       </c>
       <c r="F37" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="H37" t="n">
-        <v>22.9</v>
+        <v>21.8</v>
       </c>
       <c r="I37" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J37" t="n">
-        <v>39.9</v>
+        <v>39.6</v>
       </c>
       <c r="K37" t="n">
-        <v>72.59999999999999</v>
+        <v>71</v>
       </c>
       <c r="M37" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="N37" t="n">
-        <v>31.2</v>
+        <v>30.8</v>
       </c>
       <c r="O37" t="n">
-        <v>33.1</v>
+        <v>33.7</v>
       </c>
       <c r="Q37" t="n">
-        <v>21.6</v>
+        <v>20.7</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>21.6</v>
+        <v>20.7</v>
       </c>
       <c r="V37" t="n">
-        <v>12.9</v>
+        <v>13.1</v>
       </c>
       <c r="W37" t="n">
-        <v>28.3</v>
+        <v>25.5</v>
       </c>
       <c r="X37" t="n">
-        <v>20.6</v>
+        <v>19.3</v>
       </c>
       <c r="Y37" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z37" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AA37" t="n">
-        <v>17.9</v>
+        <v>15.5</v>
       </c>
       <c r="AB37" t="n">
-        <v>-0.8</v>
+        <v>-1</v>
       </c>
       <c r="AC37" t="n">
-        <v>8.1</v>
+        <v>6.4</v>
       </c>
       <c r="AD37" t="n">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="AF37" t="n">
-        <v>235.13</v>
+        <v>233.48</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.66</v>
+        <v>-4.86</v>
       </c>
       <c r="AH37" t="n">
         <v>215</v>
@@ -4100,10 +4097,10 @@
         <v>235</v>
       </c>
       <c r="AK37" t="n">
-        <v>135.66</v>
+        <v>136.6</v>
       </c>
       <c r="AL37" t="n">
-        <v>-0.9399999999999999</v>
+        <v>2.01</v>
       </c>
       <c r="AM37" t="n">
         <v>110</v>
@@ -4112,57 +4109,57 @@
         <v>142</v>
       </c>
       <c r="AP37" t="n">
-        <v>88.27</v>
+        <v>86.25</v>
       </c>
       <c r="AS37" t="n">
-        <v>17.6</v>
+        <v>17.13</v>
       </c>
       <c r="BL37" s="1" t="n">
-        <v>46267</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>46268</v>
+        <v>46267</v>
       </c>
       <c r="B38" t="n">
-        <v>144.9</v>
+        <v>143.4</v>
       </c>
       <c r="C38" t="n">
-        <v>53</v>
+        <v>50.9</v>
       </c>
       <c r="D38" t="n">
-        <v>35.6</v>
+        <v>35.7</v>
       </c>
       <c r="E38" t="n">
-        <v>26</v>
+        <v>26.2</v>
       </c>
       <c r="F38" t="n">
-        <v>2.8</v>
+        <v>4.3</v>
       </c>
       <c r="H38" t="n">
-        <v>24</v>
+        <v>22.9</v>
       </c>
       <c r="I38" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J38" t="n">
-        <v>40.3</v>
+        <v>39.9</v>
       </c>
       <c r="K38" t="n">
-        <v>73.7</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="M38" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="N38" t="n">
-        <v>31.6</v>
+        <v>31.2</v>
       </c>
       <c r="O38" t="n">
-        <v>33.6</v>
+        <v>33.1</v>
       </c>
       <c r="Q38" t="n">
-        <v>21</v>
+        <v>21.6</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -4171,40 +4168,40 @@
         <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>21</v>
+        <v>21.6</v>
       </c>
       <c r="V38" t="n">
-        <v>14.4</v>
+        <v>12.9</v>
       </c>
       <c r="W38" t="n">
-        <v>27.7</v>
+        <v>28.3</v>
       </c>
       <c r="X38" t="n">
-        <v>21.1</v>
+        <v>20.6</v>
       </c>
       <c r="Y38" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z38" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AA38" t="n">
-        <v>16.3</v>
+        <v>17.9</v>
       </c>
       <c r="AB38" t="n">
-        <v>-1.1</v>
+        <v>-0.8</v>
       </c>
       <c r="AC38" t="n">
-        <v>6.6</v>
+        <v>8.1</v>
       </c>
       <c r="AD38" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="AF38" t="n">
-        <v>234.87</v>
+        <v>235.13</v>
       </c>
       <c r="AG38" t="n">
-        <v>-0.26</v>
+        <v>1.66</v>
       </c>
       <c r="AH38" t="n">
         <v>215</v>
@@ -4213,10 +4210,10 @@
         <v>235</v>
       </c>
       <c r="AK38" t="n">
-        <v>136.33</v>
+        <v>135.66</v>
       </c>
       <c r="AL38" t="n">
-        <v>0.67</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AM38" t="n">
         <v>110</v>
@@ -4225,60 +4222,99 @@
         <v>142</v>
       </c>
       <c r="AP38" t="n">
-        <v>87.09</v>
+        <v>88.27</v>
       </c>
       <c r="AS38" t="n">
-        <v>17.31</v>
+        <v>17.6</v>
       </c>
       <c r="BL38" s="1" t="n">
-        <v>46268</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>46269</v>
+        <v>46268</v>
       </c>
       <c r="B39" t="n">
-        <v>132.2</v>
+        <v>144.9</v>
+      </c>
+      <c r="C39" t="n">
+        <v>53</v>
       </c>
       <c r="D39" t="n">
         <v>35.6</v>
       </c>
+      <c r="E39" t="n">
+        <v>26</v>
+      </c>
       <c r="F39" t="n">
-        <v>4</v>
+        <v>2.8</v>
+      </c>
+      <c r="H39" t="n">
+        <v>24</v>
+      </c>
+      <c r="I39" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="J39" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="K39" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="N39" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="O39" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>21</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>21</v>
       </c>
       <c r="V39" t="n">
-        <v>11.6</v>
+        <v>14.4</v>
       </c>
       <c r="W39" t="n">
-        <v>23.2</v>
+        <v>27.7</v>
       </c>
       <c r="X39" t="n">
-        <v>17.4</v>
+        <v>21.1</v>
       </c>
       <c r="Y39" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="Z39" t="n">
         <v>19</v>
       </c>
       <c r="AA39" t="n">
-        <v>13</v>
+        <v>16.3</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.9</v>
+        <v>-1.1</v>
       </c>
       <c r="AC39" t="n">
-        <v>7.5</v>
+        <v>6.6</v>
       </c>
       <c r="AD39" t="n">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="AF39" t="n">
-        <v>234.78</v>
+        <v>234.87</v>
       </c>
       <c r="AG39" t="n">
-        <v>-0.09</v>
+        <v>-0.26</v>
       </c>
       <c r="AH39" t="n">
         <v>215</v>
@@ -4286,61 +4322,73 @@
       <c r="AI39" t="n">
         <v>235</v>
       </c>
+      <c r="AK39" t="n">
+        <v>136.33</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>0.67</v>
+      </c>
       <c r="AM39" t="n">
         <v>110</v>
       </c>
       <c r="AN39" t="n">
         <v>142</v>
       </c>
+      <c r="AP39" t="n">
+        <v>87.09</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>17.31</v>
+      </c>
       <c r="BL39" s="1" t="n">
-        <v>46269</v>
+        <v>46268</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>46270</v>
+        <v>46269</v>
       </c>
       <c r="B40" t="n">
-        <v>137.1</v>
+        <v>132.2</v>
       </c>
       <c r="D40" t="n">
-        <v>35.1</v>
+        <v>35.6</v>
       </c>
       <c r="F40" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="V40" t="n">
-        <v>11</v>
+        <v>11.6</v>
       </c>
       <c r="W40" t="n">
-        <v>22</v>
+        <v>23.2</v>
       </c>
       <c r="X40" t="n">
-        <v>16.5</v>
+        <v>17.4</v>
       </c>
       <c r="Y40" t="n">
         <v>7</v>
       </c>
       <c r="Z40" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AA40" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AB40" t="n">
-        <v>-5.3</v>
+        <v>0.9</v>
       </c>
       <c r="AC40" t="n">
-        <v>6.1</v>
+        <v>7.5</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.4</v>
+        <v>4.2</v>
       </c>
       <c r="AF40" t="n">
-        <v>229.75</v>
+        <v>234.78</v>
       </c>
       <c r="AG40" t="n">
-        <v>-5.03</v>
+        <v>-0.09</v>
       </c>
       <c r="AH40" t="n">
         <v>215</v>
@@ -4355,93 +4403,54 @@
         <v>142</v>
       </c>
       <c r="BL40" s="1" t="n">
-        <v>46270</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>46271</v>
+        <v>46270</v>
       </c>
       <c r="B41" t="n">
-        <v>166.2</v>
-      </c>
-      <c r="C41" t="n">
-        <v>72.40000000000001</v>
+        <v>137.1</v>
       </c>
       <c r="D41" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="E41" t="n">
-        <v>28.1</v>
+        <v>35.1</v>
       </c>
       <c r="F41" t="n">
         <v>3.3</v>
       </c>
-      <c r="H41" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="I41" t="n">
-        <v>9</v>
-      </c>
-      <c r="J41" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="K41" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="M41" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="N41" t="n">
-        <v>33.7</v>
-      </c>
-      <c r="O41" t="n">
-        <v>39.3</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="R41" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="S41" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" t="n">
-        <v>23.7</v>
-      </c>
       <c r="V41" t="n">
-        <v>7.9</v>
+        <v>11</v>
       </c>
       <c r="W41" t="n">
-        <v>15.6</v>
+        <v>22</v>
       </c>
       <c r="X41" t="n">
-        <v>11.8</v>
+        <v>16.5</v>
       </c>
       <c r="Y41" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Z41" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AA41" t="n">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AB41" t="n">
-        <v>-3.5</v>
+        <v>-5.3</v>
       </c>
       <c r="AC41" t="n">
-        <v>8.4</v>
+        <v>6.1</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="AF41" t="n">
-        <v>222.86</v>
+        <v>229.75</v>
       </c>
       <c r="AG41" t="n">
-        <v>-6.9</v>
+        <v>-5.03</v>
       </c>
       <c r="AH41" t="n">
         <v>215</v>
@@ -4449,112 +4458,100 @@
       <c r="AI41" t="n">
         <v>235</v>
       </c>
-      <c r="AK41" t="n">
-        <v>135.42</v>
-      </c>
-      <c r="AL41" t="n">
-        <v>-0.91</v>
-      </c>
       <c r="AM41" t="n">
         <v>110</v>
       </c>
       <c r="AN41" t="n">
         <v>142</v>
       </c>
-      <c r="AP41" t="n">
-        <v>81.98</v>
-      </c>
-      <c r="AS41" t="n">
-        <v>15.01</v>
-      </c>
       <c r="BL41" s="1" t="n">
-        <v>46271</v>
+        <v>46270</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>46272</v>
+        <v>46271</v>
       </c>
       <c r="B42" t="n">
-        <v>166.3</v>
+        <v>166.2</v>
       </c>
       <c r="C42" t="n">
-        <v>74.90000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D42" t="n">
-        <v>32.8</v>
+        <v>32.7</v>
       </c>
       <c r="E42" t="n">
-        <v>28.8</v>
+        <v>28.1</v>
       </c>
       <c r="F42" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="H42" t="n">
         <v>23.4</v>
       </c>
       <c r="I42" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="J42" t="n">
-        <v>41.2</v>
+        <v>42.1</v>
       </c>
       <c r="K42" t="n">
-        <v>73.8</v>
+        <v>74.5</v>
       </c>
       <c r="M42" t="n">
-        <v>7.2</v>
+        <v>5.6</v>
       </c>
       <c r="N42" t="n">
-        <v>35.4</v>
+        <v>33.7</v>
       </c>
       <c r="O42" t="n">
-        <v>42.6</v>
+        <v>39.3</v>
       </c>
       <c r="Q42" t="n">
-        <v>23.9</v>
+        <v>23.7</v>
       </c>
       <c r="R42" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>23.9</v>
+        <v>23.7</v>
       </c>
       <c r="V42" t="n">
-        <v>6.7</v>
+        <v>7.9</v>
       </c>
       <c r="W42" t="n">
-        <v>18.1</v>
+        <v>15.6</v>
       </c>
       <c r="X42" t="n">
-        <v>12.4</v>
+        <v>11.8</v>
       </c>
       <c r="Y42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Z42" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AA42" t="n">
-        <v>11</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AB42" t="n">
-        <v>-2.9</v>
+        <v>-3.5</v>
       </c>
       <c r="AC42" t="n">
-        <v>11.5</v>
+        <v>8.4</v>
       </c>
       <c r="AD42" t="n">
-        <v>4.3</v>
+        <v>2.5</v>
       </c>
       <c r="AF42" t="n">
-        <v>218.37</v>
+        <v>222.86</v>
       </c>
       <c r="AG42" t="n">
-        <v>-4.49</v>
+        <v>-6.9</v>
       </c>
       <c r="AH42" t="n">
         <v>215</v>
@@ -4563,10 +4560,10 @@
         <v>235</v>
       </c>
       <c r="AK42" t="n">
-        <v>131.24</v>
+        <v>135.42</v>
       </c>
       <c r="AL42" t="n">
-        <v>-4.18</v>
+        <v>-0.91</v>
       </c>
       <c r="AM42" t="n">
         <v>110</v>
@@ -4575,99 +4572,99 @@
         <v>142</v>
       </c>
       <c r="AP42" t="n">
-        <v>79.98999999999999</v>
+        <v>81.98</v>
       </c>
       <c r="AS42" t="n">
-        <v>12.97</v>
+        <v>15.01</v>
       </c>
       <c r="BL42" s="1" t="n">
-        <v>46272</v>
+        <v>46271</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="B43" t="n">
-        <v>154.1</v>
+        <v>166.3</v>
       </c>
       <c r="C43" t="n">
-        <v>65</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="D43" t="n">
-        <v>32</v>
+        <v>32.8</v>
       </c>
       <c r="E43" t="n">
-        <v>25.2</v>
+        <v>28.8</v>
       </c>
       <c r="F43" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="H43" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="I43" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J43" t="n">
-        <v>38.5</v>
+        <v>41.2</v>
       </c>
       <c r="K43" t="n">
-        <v>70.90000000000001</v>
+        <v>73.8</v>
       </c>
       <c r="M43" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="N43" t="n">
-        <v>32.3</v>
+        <v>35.4</v>
       </c>
       <c r="O43" t="n">
-        <v>40.3</v>
+        <v>42.6</v>
       </c>
       <c r="Q43" t="n">
-        <v>21.7</v>
+        <v>23.9</v>
       </c>
       <c r="R43" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="S43" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>21.7</v>
+        <v>23.9</v>
       </c>
       <c r="V43" t="n">
-        <v>5.4</v>
+        <v>6.7</v>
       </c>
       <c r="W43" t="n">
-        <v>21</v>
+        <v>18.1</v>
       </c>
       <c r="X43" t="n">
-        <v>13.2</v>
+        <v>12.4</v>
       </c>
       <c r="Y43" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Z43" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AA43" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="AB43" t="n">
-        <v>0.4</v>
+        <v>-2.9</v>
       </c>
       <c r="AC43" t="n">
-        <v>7.3</v>
+        <v>11.5</v>
       </c>
       <c r="AD43" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="AF43" t="n">
-        <v>218.04</v>
+        <v>218.37</v>
       </c>
       <c r="AG43" t="n">
-        <v>-0.33</v>
+        <v>-4.49</v>
       </c>
       <c r="AH43" t="n">
         <v>215</v>
@@ -4676,10 +4673,10 @@
         <v>235</v>
       </c>
       <c r="AK43" t="n">
-        <v>129.21</v>
+        <v>131.24</v>
       </c>
       <c r="AL43" t="n">
-        <v>-2.03</v>
+        <v>-4.18</v>
       </c>
       <c r="AM43" t="n">
         <v>110</v>
@@ -4688,99 +4685,99 @@
         <v>142</v>
       </c>
       <c r="AP43" t="n">
-        <v>82.90000000000001</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="AS43" t="n">
-        <v>15.23</v>
+        <v>12.97</v>
       </c>
       <c r="BL43" s="1" t="n">
-        <v>46273</v>
+        <v>46272</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="B44" t="n">
-        <v>148.8</v>
+        <v>154.1</v>
       </c>
       <c r="C44" t="n">
-        <v>57.6</v>
+        <v>65</v>
       </c>
       <c r="D44" t="n">
-        <v>32.7</v>
+        <v>32</v>
       </c>
       <c r="E44" t="n">
-        <v>26.3</v>
+        <v>25.2</v>
       </c>
       <c r="F44" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="H44" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="I44" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="J44" t="n">
-        <v>41.6</v>
+        <v>38.5</v>
       </c>
       <c r="K44" t="n">
-        <v>74.09999999999999</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="M44" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="N44" t="n">
-        <v>35</v>
+        <v>32.3</v>
       </c>
       <c r="O44" t="n">
-        <v>42.4</v>
+        <v>40.3</v>
       </c>
       <c r="Q44" t="n">
         <v>21.7</v>
       </c>
       <c r="R44" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T44" t="n">
         <v>21.7</v>
       </c>
       <c r="V44" t="n">
-        <v>8.199999999999999</v>
+        <v>5.4</v>
       </c>
       <c r="W44" t="n">
-        <v>24.1</v>
+        <v>21</v>
       </c>
       <c r="X44" t="n">
-        <v>16.1</v>
+        <v>13.2</v>
       </c>
       <c r="Y44" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z44" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AA44" t="n">
-        <v>15.6</v>
+        <v>14.5</v>
       </c>
       <c r="AB44" t="n">
-        <v>2.9</v>
+        <v>0.4</v>
       </c>
       <c r="AC44" t="n">
-        <v>9.699999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="AD44" t="n">
-        <v>6.3</v>
+        <v>3.9</v>
       </c>
       <c r="AF44" t="n">
-        <v>220.84</v>
+        <v>218.04</v>
       </c>
       <c r="AG44" t="n">
-        <v>2.8</v>
+        <v>-0.33</v>
       </c>
       <c r="AH44" t="n">
         <v>215</v>
@@ -4789,10 +4786,10 @@
         <v>235</v>
       </c>
       <c r="AK44" t="n">
-        <v>129.07</v>
+        <v>129.21</v>
       </c>
       <c r="AL44" t="n">
-        <v>-0.14</v>
+        <v>-2.03</v>
       </c>
       <c r="AM44" t="n">
         <v>110</v>
@@ -4801,99 +4798,99 @@
         <v>142</v>
       </c>
       <c r="AP44" t="n">
-        <v>85.52</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="AS44" t="n">
-        <v>15.82</v>
+        <v>15.23</v>
       </c>
       <c r="BL44" s="1" t="n">
-        <v>46274</v>
+        <v>46273</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="B45" t="n">
-        <v>146.8</v>
+        <v>148.8</v>
       </c>
       <c r="C45" t="n">
-        <v>52.8</v>
+        <v>57.6</v>
       </c>
       <c r="D45" t="n">
-        <v>33.6</v>
+        <v>32.7</v>
       </c>
       <c r="E45" t="n">
-        <v>28.9</v>
+        <v>26.3</v>
       </c>
       <c r="F45" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="H45" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="I45" t="n">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
       <c r="J45" t="n">
-        <v>40.8</v>
+        <v>41.6</v>
       </c>
       <c r="K45" t="n">
-        <v>73.59999999999999</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="M45" t="n">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="N45" t="n">
-        <v>33.1</v>
+        <v>35</v>
       </c>
       <c r="O45" t="n">
-        <v>38.7</v>
+        <v>42.4</v>
       </c>
       <c r="Q45" t="n">
-        <v>22</v>
+        <v>21.7</v>
       </c>
       <c r="R45" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>22</v>
+        <v>21.7</v>
       </c>
       <c r="V45" t="n">
-        <v>11</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W45" t="n">
-        <v>22.9</v>
+        <v>24.1</v>
       </c>
       <c r="X45" t="n">
-        <v>16.9</v>
+        <v>16.1</v>
       </c>
       <c r="Y45" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z45" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AA45" t="n">
-        <v>16.1</v>
+        <v>15.6</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="AC45" t="n">
-        <v>7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AD45" t="n">
-        <v>4.5</v>
+        <v>6.3</v>
       </c>
       <c r="AF45" t="n">
-        <v>225.87</v>
+        <v>220.84</v>
       </c>
       <c r="AG45" t="n">
-        <v>5.03</v>
+        <v>2.8</v>
       </c>
       <c r="AH45" t="n">
         <v>215</v>
@@ -4902,10 +4899,10 @@
         <v>235</v>
       </c>
       <c r="AK45" t="n">
-        <v>130.73</v>
+        <v>129.07</v>
       </c>
       <c r="AL45" t="n">
-        <v>1.66</v>
+        <v>-0.14</v>
       </c>
       <c r="AM45" t="n">
         <v>110</v>
@@ -4914,54 +4911,99 @@
         <v>142</v>
       </c>
       <c r="AP45" t="n">
-        <v>88.2</v>
+        <v>85.52</v>
       </c>
       <c r="AS45" t="n">
-        <v>15.76</v>
+        <v>15.82</v>
       </c>
       <c r="BL45" s="1" t="n">
-        <v>46275</v>
+        <v>46274</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="B46" t="n">
-        <v>133.9</v>
+        <v>146.8</v>
+      </c>
+      <c r="C46" t="n">
+        <v>52.8</v>
       </c>
       <c r="D46" t="n">
-        <v>34.7</v>
+        <v>33.6</v>
+      </c>
+      <c r="E46" t="n">
+        <v>28.9</v>
       </c>
       <c r="F46" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
+      </c>
+      <c r="H46" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="I46" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="J46" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="K46" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="M46" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="N46" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="O46" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>22</v>
+      </c>
+      <c r="R46" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>22</v>
       </c>
       <c r="V46" t="n">
-        <v>14.3</v>
+        <v>11</v>
       </c>
       <c r="W46" t="n">
-        <v>21.7</v>
+        <v>22.9</v>
       </c>
       <c r="X46" t="n">
-        <v>18</v>
+        <v>16.9</v>
       </c>
       <c r="Y46" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z46" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AA46" t="n">
-        <v>15</v>
+        <v>16.1</v>
       </c>
       <c r="AB46" t="n">
-        <v>-3.5</v>
+        <v>1.9</v>
       </c>
       <c r="AC46" t="n">
-        <v>3.2</v>
+        <v>7</v>
       </c>
       <c r="AD46" t="n">
-        <v>-0.1</v>
+        <v>4.5</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>225.87</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>5.03</v>
       </c>
       <c r="AH46" t="n">
         <v>215</v>
@@ -4969,55 +5011,67 @@
       <c r="AI46" t="n">
         <v>235</v>
       </c>
+      <c r="AK46" t="n">
+        <v>130.73</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>1.66</v>
+      </c>
       <c r="AM46" t="n">
         <v>110</v>
       </c>
       <c r="AN46" t="n">
         <v>142</v>
       </c>
+      <c r="AP46" t="n">
+        <v>88.2</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>15.76</v>
+      </c>
       <c r="BL46" s="1" t="n">
-        <v>46276</v>
+        <v>46275</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46277</v>
+        <v>46276</v>
       </c>
       <c r="B47" t="n">
-        <v>137.5</v>
+        <v>133.9</v>
       </c>
       <c r="D47" t="n">
-        <v>32.8</v>
+        <v>34.7</v>
       </c>
       <c r="F47" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="V47" t="n">
-        <v>9</v>
+        <v>14.3</v>
       </c>
       <c r="W47" t="n">
-        <v>15.7</v>
+        <v>21.7</v>
       </c>
       <c r="X47" t="n">
-        <v>12.3</v>
+        <v>18</v>
       </c>
       <c r="Y47" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z47" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="AA47" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="AB47" t="n">
-        <v>-6.6</v>
+        <v>-3.5</v>
       </c>
       <c r="AC47" t="n">
-        <v>8.1</v>
+        <v>3.2</v>
       </c>
       <c r="AD47" t="n">
-        <v>0.8</v>
+        <v>-0.1</v>
       </c>
       <c r="AH47" t="n">
         <v>215</v>
@@ -5032,93 +5086,48 @@
         <v>142</v>
       </c>
       <c r="BL47" s="1" t="n">
-        <v>46277</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="B48" t="n">
-        <v>157.1</v>
-      </c>
-      <c r="C48" t="n">
-        <v>73.09999999999999</v>
+        <v>137.5</v>
       </c>
       <c r="D48" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="E48" t="n">
-        <v>26.1</v>
+        <v>32.8</v>
       </c>
       <c r="F48" t="n">
-        <v>2</v>
-      </c>
-      <c r="H48" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="I48" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="J48" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="K48" t="n">
-        <v>73.5</v>
-      </c>
-      <c r="M48" t="n">
-        <v>6</v>
-      </c>
-      <c r="N48" t="n">
-        <v>33.4</v>
-      </c>
-      <c r="O48" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="R48" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="S48" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" t="n">
-        <v>23.8</v>
+        <v>2.3</v>
       </c>
       <c r="V48" t="n">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="W48" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="X48" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z48" t="n">
         <v>11</v>
       </c>
-      <c r="X48" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>12</v>
-      </c>
       <c r="AA48" t="n">
-        <v>7.9</v>
+        <v>10.5</v>
       </c>
       <c r="AB48" t="n">
-        <v>-1.2</v>
+        <v>-6.6</v>
       </c>
       <c r="AC48" t="n">
-        <v>12.6</v>
+        <v>8.1</v>
       </c>
       <c r="AD48" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>224.2</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>-1.67</v>
+        <v>0.8</v>
       </c>
       <c r="AH48" t="n">
         <v>215</v>
@@ -5126,112 +5135,100 @@
       <c r="AI48" t="n">
         <v>235</v>
       </c>
-      <c r="AK48" t="n">
-        <v>128.6</v>
-      </c>
-      <c r="AL48" t="n">
-        <v>-2.13</v>
-      </c>
       <c r="AM48" t="n">
         <v>110</v>
       </c>
       <c r="AN48" t="n">
         <v>142</v>
       </c>
-      <c r="AP48" t="n">
-        <v>81.18000000000001</v>
-      </c>
-      <c r="AS48" t="n">
-        <v>14.06</v>
-      </c>
       <c r="BL48" s="1" t="n">
-        <v>46278</v>
+        <v>46277</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46279</v>
+        <v>46278</v>
       </c>
       <c r="B49" t="n">
-        <v>153.1</v>
+        <v>157.1</v>
       </c>
       <c r="C49" t="n">
-        <v>69.59999999999999</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="D49" t="n">
-        <v>32.2</v>
+        <v>31.7</v>
       </c>
       <c r="E49" t="n">
-        <v>25.9</v>
+        <v>26.1</v>
       </c>
       <c r="F49" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="H49" t="n">
-        <v>24.4</v>
+        <v>23.6</v>
       </c>
       <c r="I49" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="J49" t="n">
-        <v>39.6</v>
+        <v>40.5</v>
       </c>
       <c r="K49" t="n">
-        <v>73.3</v>
+        <v>73.5</v>
       </c>
       <c r="M49" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="N49" t="n">
-        <v>34.4</v>
+        <v>33.4</v>
       </c>
       <c r="O49" t="n">
-        <v>40.1</v>
+        <v>39.5</v>
       </c>
       <c r="Q49" t="n">
         <v>23.8</v>
       </c>
       <c r="R49" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="S49" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
         <v>23.8</v>
       </c>
       <c r="V49" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="W49" t="n">
-        <v>15.2</v>
+        <v>11</v>
       </c>
       <c r="X49" t="n">
-        <v>10.9</v>
+        <v>8.9</v>
       </c>
       <c r="Y49" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Z49" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AA49" t="n">
-        <v>12</v>
+        <v>7.9</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.7</v>
+        <v>-1.2</v>
       </c>
       <c r="AC49" t="n">
-        <v>10</v>
+        <v>12.6</v>
       </c>
       <c r="AD49" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AF49" t="n">
-        <v>223.35</v>
+        <v>224.2</v>
       </c>
       <c r="AG49" t="n">
-        <v>-0.85</v>
+        <v>-1.67</v>
       </c>
       <c r="AH49" t="n">
         <v>215</v>
@@ -5240,10 +5237,10 @@
         <v>235</v>
       </c>
       <c r="AK49" t="n">
-        <v>127.19</v>
+        <v>128.6</v>
       </c>
       <c r="AL49" t="n">
-        <v>-1.41</v>
+        <v>-2.13</v>
       </c>
       <c r="AM49" t="n">
         <v>110</v>
@@ -5252,99 +5249,99 @@
         <v>142</v>
       </c>
       <c r="AP49" t="n">
-        <v>81.06</v>
+        <v>81.18000000000001</v>
       </c>
       <c r="AS49" t="n">
-        <v>13.63</v>
+        <v>14.06</v>
       </c>
       <c r="BL49" s="1" t="n">
-        <v>46279</v>
+        <v>46278</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B50" t="n">
-        <v>145.5</v>
+        <v>153.1</v>
       </c>
       <c r="C50" t="n">
-        <v>62.3</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="D50" t="n">
-        <v>34</v>
+        <v>32.2</v>
       </c>
       <c r="E50" t="n">
-        <v>22.5</v>
+        <v>25.9</v>
       </c>
       <c r="F50" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="H50" t="n">
-        <v>24.8</v>
+        <v>24.4</v>
       </c>
       <c r="I50" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J50" t="n">
-        <v>40.8</v>
+        <v>39.6</v>
       </c>
       <c r="K50" t="n">
-        <v>75</v>
+        <v>73.3</v>
       </c>
       <c r="M50" t="n">
-        <v>6.9</v>
+        <v>5.7</v>
       </c>
       <c r="N50" t="n">
-        <v>30.4</v>
+        <v>34.4</v>
       </c>
       <c r="O50" t="n">
-        <v>37.3</v>
+        <v>40.1</v>
       </c>
       <c r="Q50" t="n">
-        <v>22.1</v>
+        <v>23.8</v>
       </c>
       <c r="R50" t="n">
-        <v>4.9</v>
+        <v>3.8</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T50" t="n">
-        <v>22.1</v>
+        <v>23.8</v>
       </c>
       <c r="V50" t="n">
-        <v>4</v>
+        <v>6.6</v>
       </c>
       <c r="W50" t="n">
-        <v>22.9</v>
+        <v>15.2</v>
       </c>
       <c r="X50" t="n">
-        <v>13.4</v>
+        <v>10.9</v>
       </c>
       <c r="Y50" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="Z50" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AA50" t="n">
-        <v>12.9</v>
+        <v>12</v>
       </c>
       <c r="AB50" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="AC50" t="n">
-        <v>12.7</v>
+        <v>10</v>
       </c>
       <c r="AD50" t="n">
-        <v>6.7</v>
+        <v>5.8</v>
       </c>
       <c r="AF50" t="n">
-        <v>223.06</v>
+        <v>223.35</v>
       </c>
       <c r="AG50" t="n">
-        <v>-0.29</v>
+        <v>-0.85</v>
       </c>
       <c r="AH50" t="n">
         <v>215</v>
@@ -5353,10 +5350,10 @@
         <v>235</v>
       </c>
       <c r="AK50" t="n">
-        <v>129.17</v>
+        <v>127.19</v>
       </c>
       <c r="AL50" t="n">
-        <v>1.98</v>
+        <v>-1.41</v>
       </c>
       <c r="AM50" t="n">
         <v>110</v>
@@ -5365,96 +5362,96 @@
         <v>142</v>
       </c>
       <c r="AP50" t="n">
-        <v>82.36</v>
+        <v>81.06</v>
       </c>
       <c r="AS50" t="n">
-        <v>13.91</v>
+        <v>13.63</v>
       </c>
       <c r="BL50" s="1" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B51" t="n">
-        <v>148</v>
+        <v>145.5</v>
       </c>
       <c r="C51" t="n">
-        <v>61.6</v>
+        <v>62.3</v>
       </c>
       <c r="D51" t="n">
-        <v>33.9</v>
+        <v>34</v>
       </c>
       <c r="E51" t="n">
-        <v>25</v>
+        <v>22.5</v>
       </c>
       <c r="F51" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="H51" t="n">
-        <v>25.1</v>
+        <v>24.8</v>
       </c>
       <c r="I51" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="J51" t="n">
-        <v>39.5</v>
+        <v>40.8</v>
       </c>
       <c r="K51" t="n">
-        <v>74.09999999999999</v>
+        <v>75</v>
       </c>
       <c r="M51" t="n">
-        <v>5.9</v>
+        <v>6.9</v>
       </c>
       <c r="N51" t="n">
-        <v>28.6</v>
+        <v>30.4</v>
       </c>
       <c r="O51" t="n">
-        <v>34.5</v>
+        <v>37.3</v>
       </c>
       <c r="Q51" t="n">
-        <v>23.3</v>
+        <v>22.1</v>
       </c>
       <c r="R51" t="n">
-        <v>3.9</v>
+        <v>4.9</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>23.3</v>
+        <v>22.1</v>
       </c>
       <c r="V51" t="n">
-        <v>7.8</v>
+        <v>4</v>
       </c>
       <c r="W51" t="n">
-        <v>26</v>
+        <v>22.9</v>
       </c>
       <c r="X51" t="n">
-        <v>16.9</v>
+        <v>13.4</v>
       </c>
       <c r="Y51" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Z51" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AA51" t="n">
-        <v>11.6</v>
+        <v>12.9</v>
       </c>
       <c r="AB51" t="n">
-        <v>4.2</v>
+        <v>0.7</v>
       </c>
       <c r="AC51" t="n">
-        <v>11.4</v>
+        <v>12.7</v>
       </c>
       <c r="AD51" t="n">
-        <v>7.8</v>
+        <v>6.7</v>
       </c>
       <c r="AF51" t="n">
-        <v>222.77</v>
+        <v>223.06</v>
       </c>
       <c r="AG51" t="n">
         <v>-0.29</v>
@@ -5466,10 +5463,10 @@
         <v>235</v>
       </c>
       <c r="AK51" t="n">
-        <v>130.42</v>
+        <v>129.17</v>
       </c>
       <c r="AL51" t="n">
-        <v>1.25</v>
+        <v>1.98</v>
       </c>
       <c r="AM51" t="n">
         <v>110</v>
@@ -5478,60 +5475,60 @@
         <v>142</v>
       </c>
       <c r="AP51" t="n">
-        <v>80.90000000000001</v>
+        <v>82.36</v>
       </c>
       <c r="AS51" t="n">
-        <v>14</v>
+        <v>13.91</v>
       </c>
       <c r="BL51" s="1" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B52" t="n">
-        <v>135.5</v>
+        <v>148</v>
       </c>
       <c r="C52" t="n">
-        <v>47.7</v>
+        <v>61.6</v>
       </c>
       <c r="D52" t="n">
-        <v>34.2</v>
+        <v>33.9</v>
       </c>
       <c r="E52" t="n">
-        <v>24.1</v>
+        <v>25</v>
       </c>
       <c r="F52" t="n">
-        <v>3.5</v>
+        <v>2.2</v>
       </c>
       <c r="H52" t="n">
-        <v>24.9</v>
+        <v>25.1</v>
       </c>
       <c r="I52" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="J52" t="n">
-        <v>38.4</v>
+        <v>39.5</v>
       </c>
       <c r="K52" t="n">
-        <v>73.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="M52" t="n">
-        <v>3</v>
+        <v>5.9</v>
       </c>
       <c r="N52" t="n">
-        <v>30.3</v>
+        <v>28.6</v>
       </c>
       <c r="O52" t="n">
-        <v>33.3</v>
+        <v>34.5</v>
       </c>
       <c r="Q52" t="n">
         <v>23.3</v>
       </c>
       <c r="R52" t="n">
-        <v>1</v>
+        <v>3.9</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -5540,37 +5537,37 @@
         <v>23.3</v>
       </c>
       <c r="V52" t="n">
-        <v>11.3</v>
+        <v>7.8</v>
       </c>
       <c r="W52" t="n">
-        <v>27.6</v>
+        <v>26</v>
       </c>
       <c r="X52" t="n">
-        <v>19.5</v>
+        <v>16.9</v>
       </c>
       <c r="Y52" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="Z52" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="AA52" t="n">
-        <v>18.8</v>
+        <v>11.6</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
       <c r="AC52" t="n">
-        <v>15.5</v>
+        <v>11.4</v>
       </c>
       <c r="AD52" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AF52" t="n">
-        <v>221.86</v>
+        <v>222.77</v>
       </c>
       <c r="AG52" t="n">
-        <v>-0.91</v>
+        <v>-0.29</v>
       </c>
       <c r="AH52" t="n">
         <v>215</v>
@@ -5579,10 +5576,10 @@
         <v>235</v>
       </c>
       <c r="AK52" t="n">
-        <v>129.71</v>
+        <v>130.42</v>
       </c>
       <c r="AL52" t="n">
-        <v>-0.71</v>
+        <v>1.25</v>
       </c>
       <c r="AM52" t="n">
         <v>110</v>
@@ -5591,54 +5588,99 @@
         <v>142</v>
       </c>
       <c r="AP52" t="n">
-        <v>86.42</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="AS52" t="n">
-        <v>16.05</v>
+        <v>14</v>
       </c>
       <c r="BL52" s="1" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B53" t="n">
-        <v>118.1</v>
+        <v>135.5</v>
+      </c>
+      <c r="C53" t="n">
+        <v>47.7</v>
       </c>
       <c r="D53" t="n">
-        <v>34.7</v>
+        <v>34.2</v>
+      </c>
+      <c r="E53" t="n">
+        <v>24.1</v>
       </c>
       <c r="F53" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
+      </c>
+      <c r="H53" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="I53" t="n">
+        <v>10</v>
+      </c>
+      <c r="J53" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="K53" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="M53" t="n">
+        <v>3</v>
+      </c>
+      <c r="N53" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="O53" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>23.3</v>
       </c>
       <c r="V53" t="n">
-        <v>14.1</v>
+        <v>11.3</v>
       </c>
       <c r="W53" t="n">
         <v>27.6</v>
       </c>
       <c r="X53" t="n">
-        <v>20.9</v>
+        <v>19.5</v>
       </c>
       <c r="Y53" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="Z53" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA53" t="n">
-        <v>19</v>
+        <v>18.8</v>
       </c>
       <c r="AB53" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="AC53" t="n">
-        <v>14.9</v>
+        <v>15.5</v>
       </c>
       <c r="AD53" t="n">
-        <v>9.199999999999999</v>
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>221.86</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>-0.91</v>
       </c>
       <c r="AH53" t="n">
         <v>215</v>
@@ -5646,37 +5688,67 @@
       <c r="AI53" t="n">
         <v>235</v>
       </c>
+      <c r="AK53" t="n">
+        <v>129.71</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>-0.71</v>
+      </c>
       <c r="AM53" t="n">
         <v>110</v>
       </c>
       <c r="AN53" t="n">
         <v>142</v>
       </c>
+      <c r="AP53" t="n">
+        <v>86.42</v>
+      </c>
+      <c r="AS53" t="n">
+        <v>16.05</v>
+      </c>
       <c r="BL53" s="1" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B54" t="n">
-        <v>100.3</v>
+        <v>118.1</v>
       </c>
       <c r="D54" t="n">
-        <v>34</v>
+        <v>34.7</v>
       </c>
       <c r="F54" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
+      </c>
+      <c r="V54" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="W54" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="X54" t="n">
+        <v>20.9</v>
       </c>
       <c r="Y54" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z54" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA54" t="n">
-        <v>20</v>
+        <v>19</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>9.199999999999999</v>
       </c>
       <c r="AH54" t="n">
         <v>215</v>
@@ -5691,75 +5763,48 @@
         <v>142</v>
       </c>
       <c r="BL54" s="1" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B55" t="n">
-        <v>104.9</v>
-      </c>
-      <c r="C55" t="n">
-        <v>36.3</v>
+        <v>100.3</v>
       </c>
       <c r="D55" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="E55" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F55" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="H55" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V55" t="n">
         <v>16</v>
       </c>
-      <c r="I55" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="J55" t="n">
-        <v>25</v>
-      </c>
-      <c r="K55" t="n">
-        <v>51.2</v>
-      </c>
-      <c r="M55" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="N55" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="O55" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="R55" t="n">
-        <v>0</v>
-      </c>
-      <c r="S55" t="n">
-        <v>0</v>
-      </c>
-      <c r="T55" t="n">
-        <v>10.5</v>
+      <c r="W55" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="X55" t="n">
+        <v>23.3</v>
       </c>
       <c r="Y55" t="n">
         <v>16</v>
       </c>
       <c r="Z55" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA55" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="AF55" t="n">
-        <v>234.9</v>
-      </c>
-      <c r="AG55" t="n">
-        <v>13.04</v>
+        <v>20</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>12.8</v>
       </c>
       <c r="AH55" t="n">
         <v>215</v>
@@ -5767,70 +5812,58 @@
       <c r="AI55" t="n">
         <v>235</v>
       </c>
-      <c r="AK55" t="n">
-        <v>137.51</v>
-      </c>
-      <c r="AL55" t="n">
-        <v>7.8</v>
-      </c>
       <c r="AM55" t="n">
         <v>110</v>
       </c>
       <c r="AN55" t="n">
         <v>142</v>
       </c>
-      <c r="AP55" t="n">
-        <v>94</v>
-      </c>
-      <c r="AS55" t="n">
-        <v>18.87</v>
-      </c>
       <c r="BL55" s="1" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B56" t="n">
-        <v>134.9</v>
+        <v>104.9</v>
       </c>
       <c r="C56" t="n">
-        <v>53.3</v>
+        <v>36.3</v>
       </c>
       <c r="D56" t="n">
-        <v>36.3</v>
+        <v>32.7</v>
       </c>
       <c r="E56" t="n">
-        <v>20.6</v>
+        <v>17</v>
       </c>
       <c r="F56" t="n">
         <v>1.6</v>
       </c>
       <c r="H56" t="n">
-        <v>21.2</v>
+        <v>16</v>
       </c>
       <c r="I56" t="n">
-        <v>9.4</v>
+        <v>10.1</v>
       </c>
       <c r="J56" t="n">
-        <v>35.4</v>
+        <v>25</v>
       </c>
       <c r="K56" t="n">
-        <v>66</v>
+        <v>51.2</v>
       </c>
       <c r="M56" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="N56" t="n">
-        <v>24.8</v>
+        <v>25.5</v>
       </c>
       <c r="O56" t="n">
-        <v>26.7</v>
+        <v>27.3</v>
       </c>
       <c r="Q56" t="n">
-        <v>18.3</v>
+        <v>10.5</v>
       </c>
       <c r="R56" t="n">
         <v>0</v>
@@ -5839,22 +5872,22 @@
         <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>18.3</v>
+        <v>10.5</v>
       </c>
       <c r="Y56" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="Z56" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="AA56" t="n">
-        <v>13.8</v>
+        <v>16.9</v>
       </c>
       <c r="AF56" t="n">
-        <v>229.2</v>
+        <v>234.9</v>
       </c>
       <c r="AG56" t="n">
-        <v>-5.7</v>
+        <v>13.04</v>
       </c>
       <c r="AH56" t="n">
         <v>215</v>
@@ -5863,10 +5896,10 @@
         <v>235</v>
       </c>
       <c r="AK56" t="n">
-        <v>138.98</v>
+        <v>137.51</v>
       </c>
       <c r="AL56" t="n">
-        <v>1.47</v>
+        <v>7.8</v>
       </c>
       <c r="AM56" t="n">
         <v>110</v>
@@ -5875,57 +5908,57 @@
         <v>142</v>
       </c>
       <c r="AP56" t="n">
-        <v>84.90000000000001</v>
+        <v>94</v>
       </c>
       <c r="AS56" t="n">
-        <v>16.02</v>
+        <v>18.87</v>
       </c>
       <c r="BL56" s="1" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B57" t="n">
-        <v>146.4</v>
+        <v>134.9</v>
       </c>
       <c r="C57" t="n">
-        <v>60.2</v>
+        <v>53.3</v>
       </c>
       <c r="D57" t="n">
-        <v>35.6</v>
+        <v>36.3</v>
       </c>
       <c r="E57" t="n">
-        <v>24.2</v>
+        <v>20.6</v>
       </c>
       <c r="F57" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="H57" t="n">
-        <v>23</v>
+        <v>21.2</v>
       </c>
       <c r="I57" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J57" t="n">
-        <v>38.2</v>
+        <v>35.4</v>
       </c>
       <c r="K57" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="M57" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="N57" t="n">
-        <v>30.2</v>
+        <v>24.8</v>
       </c>
       <c r="O57" t="n">
-        <v>31.9</v>
+        <v>26.7</v>
       </c>
       <c r="Q57" t="n">
-        <v>20.2</v>
+        <v>18.3</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
@@ -5934,22 +5967,22 @@
         <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>20.2</v>
+        <v>18.3</v>
       </c>
       <c r="Y57" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="Z57" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AA57" t="n">
-        <v>9.6</v>
+        <v>13.8</v>
       </c>
       <c r="AF57" t="n">
-        <v>224.9</v>
+        <v>229.2</v>
       </c>
       <c r="AG57" t="n">
-        <v>-4.3</v>
+        <v>-5.7</v>
       </c>
       <c r="AH57" t="n">
         <v>215</v>
@@ -5958,10 +5991,10 @@
         <v>235</v>
       </c>
       <c r="AK57" t="n">
-        <v>134.04</v>
+        <v>138.98</v>
       </c>
       <c r="AL57" t="n">
-        <v>-4.94</v>
+        <v>1.47</v>
       </c>
       <c r="AM57" t="n">
         <v>110</v>
@@ -5970,57 +6003,57 @@
         <v>142</v>
       </c>
       <c r="AP57" t="n">
-        <v>76.5</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="AS57" t="n">
-        <v>13.68</v>
+        <v>16.02</v>
       </c>
       <c r="BL57" s="1" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B58" t="n">
-        <v>131.4</v>
+        <v>146.4</v>
       </c>
       <c r="C58" t="n">
-        <v>53.7</v>
+        <v>60.2</v>
       </c>
       <c r="D58" t="n">
-        <v>34.7</v>
+        <v>35.6</v>
       </c>
       <c r="E58" t="n">
-        <v>20.1</v>
+        <v>24.2</v>
       </c>
       <c r="F58" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="H58" t="n">
-        <v>24.1</v>
+        <v>23</v>
       </c>
       <c r="I58" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J58" t="n">
-        <v>37</v>
+        <v>38.2</v>
       </c>
       <c r="K58" t="n">
-        <v>69.8</v>
+        <v>70</v>
       </c>
       <c r="M58" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="N58" t="n">
-        <v>31.4</v>
+        <v>30.2</v>
       </c>
       <c r="O58" t="n">
-        <v>33.3</v>
+        <v>31.9</v>
       </c>
       <c r="Q58" t="n">
-        <v>22.3</v>
+        <v>20.2</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
@@ -6029,22 +6062,22 @@
         <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>22.3</v>
+        <v>20.2</v>
       </c>
       <c r="Y58" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z58" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AA58" t="n">
-        <v>14</v>
+        <v>9.6</v>
       </c>
       <c r="AF58" t="n">
-        <v>220.8</v>
+        <v>224.9</v>
       </c>
       <c r="AG58" t="n">
-        <v>-4.1</v>
+        <v>-4.3</v>
       </c>
       <c r="AH58" t="n">
         <v>215</v>
@@ -6053,10 +6086,10 @@
         <v>235</v>
       </c>
       <c r="AK58" t="n">
-        <v>131.01</v>
+        <v>134.04</v>
       </c>
       <c r="AL58" t="n">
-        <v>-3.03</v>
+        <v>-4.94</v>
       </c>
       <c r="AM58" t="n">
         <v>110</v>
@@ -6065,36 +6098,81 @@
         <v>142</v>
       </c>
       <c r="AP58" t="n">
-        <v>81.28</v>
+        <v>76.5</v>
       </c>
       <c r="AS58" t="n">
-        <v>13.92</v>
+        <v>13.68</v>
       </c>
       <c r="BL58" s="1" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B59" t="n">
-        <v>121</v>
+        <v>131.4</v>
+      </c>
+      <c r="C59" t="n">
+        <v>53.7</v>
       </c>
       <c r="D59" t="n">
-        <v>36.1</v>
+        <v>34.7</v>
+      </c>
+      <c r="E59" t="n">
+        <v>20.1</v>
       </c>
       <c r="F59" t="n">
-        <v>4</v>
+        <v>2.2</v>
+      </c>
+      <c r="H59" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I59" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J59" t="n">
+        <v>37</v>
+      </c>
+      <c r="K59" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="M59" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="N59" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="O59" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>22.3</v>
       </c>
       <c r="Y59" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z59" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AA59" t="n">
-        <v>17.5</v>
+        <v>14</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>220.8</v>
+      </c>
+      <c r="AG59" t="n">
+        <v>-4.1</v>
       </c>
       <c r="AH59" t="n">
         <v>215</v>
@@ -6102,37 +6180,94 @@
       <c r="AI59" t="n">
         <v>235</v>
       </c>
+      <c r="AK59" t="n">
+        <v>131.01</v>
+      </c>
+      <c r="AL59" t="n">
+        <v>-3.03</v>
+      </c>
       <c r="AM59" t="n">
         <v>110</v>
       </c>
       <c r="AN59" t="n">
         <v>142</v>
       </c>
+      <c r="AP59" t="n">
+        <v>81.28</v>
+      </c>
+      <c r="AS59" t="n">
+        <v>13.92</v>
+      </c>
       <c r="BL59" s="1" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B60" t="n">
-        <v>116.2</v>
+        <v>127.2</v>
+      </c>
+      <c r="C60" t="n">
+        <v>42.7</v>
       </c>
       <c r="D60" t="n">
-        <v>35.4</v>
+        <v>34.6</v>
+      </c>
+      <c r="E60" t="n">
+        <v>20.7</v>
       </c>
       <c r="F60" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
+      </c>
+      <c r="H60" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="I60" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="J60" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="K60" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="M60" t="n">
+        <v>2</v>
+      </c>
+      <c r="N60" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="O60" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>22.2</v>
       </c>
       <c r="Y60" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="Z60" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AA60" t="n">
-        <v>21</v>
+        <v>19.7</v>
+      </c>
+      <c r="AF60" t="n">
+        <v>228.06</v>
+      </c>
+      <c r="AG60" t="n">
+        <v>7.26</v>
       </c>
       <c r="AH60" t="n">
         <v>215</v>
@@ -6140,19 +6275,49 @@
       <c r="AI60" t="n">
         <v>235</v>
       </c>
+      <c r="AK60" t="n">
+        <v>131.96</v>
+      </c>
+      <c r="AL60" t="n">
+        <v>0.95</v>
+      </c>
       <c r="AM60" t="n">
         <v>110</v>
       </c>
       <c r="AN60" t="n">
         <v>142</v>
       </c>
+      <c r="AP60" t="n">
+        <v>84.34</v>
+      </c>
+      <c r="AS60" t="n">
+        <v>17.57</v>
+      </c>
       <c r="BL60" s="1" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46291</v>
+        <v>46290</v>
+      </c>
+      <c r="B61" t="n">
+        <v>116.2</v>
+      </c>
+      <c r="D61" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="F61" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>21</v>
       </c>
       <c r="AH61" t="n">
         <v>215</v>
@@ -6167,12 +6332,30 @@
         <v>142</v>
       </c>
       <c r="BL61" s="1" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46292</v>
+        <v>46291</v>
+      </c>
+      <c r="B62" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="D62" t="n">
+        <v>34</v>
+      </c>
+      <c r="F62" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>18.5</v>
       </c>
       <c r="AH62" t="n">
         <v>215</v>
@@ -6187,7 +6370,7 @@
         <v>142</v>
       </c>
       <c r="BL62" s="1" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -628,85 +628,88 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B2" t="n">
-        <v>166.4</v>
+        <v>172.9</v>
       </c>
       <c r="C2" t="n">
-        <v>63.7</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>34.5</v>
+        <v>34.9</v>
       </c>
       <c r="E2" t="n">
-        <v>36.4</v>
+        <v>35.2</v>
       </c>
       <c r="F2" t="n">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="H2" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="I2" t="n">
-        <v>11.6</v>
+        <v>11.3</v>
       </c>
       <c r="J2" t="n">
-        <v>39.9</v>
+        <v>41.7</v>
       </c>
       <c r="K2" t="n">
-        <v>75.2</v>
+        <v>76.7</v>
       </c>
       <c r="M2" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="N2" t="n">
-        <v>35.9</v>
+        <v>34.8</v>
       </c>
       <c r="O2" t="n">
-        <v>39</v>
+        <v>37.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>20.3</v>
+        <v>19</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T2" t="n">
-        <v>20.3</v>
+        <v>19</v>
       </c>
       <c r="V2" t="n">
-        <v>11.9</v>
+        <v>14.4</v>
       </c>
       <c r="W2" t="n">
-        <v>27</v>
+        <v>18.7</v>
       </c>
       <c r="X2" t="n">
-        <v>19.4</v>
+        <v>16.6</v>
       </c>
       <c r="Y2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Z2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA2" t="n">
-        <v>14.4</v>
+        <v>12.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>-3.5</v>
+        <v>-4.9</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.4</v>
+        <v>-0.7</v>
       </c>
       <c r="AF2" t="n">
-        <v>236.13</v>
+        <v>218.6</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>-9.380000000000001</v>
       </c>
       <c r="AH2" t="n">
         <v>215</v>
@@ -715,10 +718,10 @@
         <v>235</v>
       </c>
       <c r="AK2" t="n">
-        <v>134.54</v>
+        <v>130.39</v>
       </c>
       <c r="AL2" t="n">
-        <v>-1.74</v>
+        <v>-4.15</v>
       </c>
       <c r="AM2" t="n">
         <v>110</v>
@@ -727,99 +730,99 @@
         <v>142</v>
       </c>
       <c r="AP2" t="n">
-        <v>82.27</v>
+        <v>78.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>16.28</v>
+        <v>15.79</v>
       </c>
       <c r="BL2" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B3" t="n">
-        <v>172.9</v>
+        <v>157.5</v>
       </c>
       <c r="C3" t="n">
-        <v>67.59999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="D3" t="n">
-        <v>34.9</v>
+        <v>33.2</v>
       </c>
       <c r="E3" t="n">
-        <v>35.2</v>
+        <v>27.7</v>
       </c>
       <c r="F3" t="n">
-        <v>7.3</v>
+        <v>3.6</v>
       </c>
       <c r="H3" t="n">
-        <v>23.6</v>
+        <v>23.4</v>
       </c>
       <c r="I3" t="n">
         <v>11.3</v>
       </c>
       <c r="J3" t="n">
-        <v>41.7</v>
+        <v>41.4</v>
       </c>
       <c r="K3" t="n">
-        <v>76.7</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="N3" t="n">
-        <v>34.8</v>
+        <v>34.9</v>
       </c>
       <c r="O3" t="n">
-        <v>37.2</v>
+        <v>37.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>19</v>
+        <v>21.6</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T3" t="n">
-        <v>19</v>
+        <v>21.6</v>
       </c>
       <c r="V3" t="n">
-        <v>14.4</v>
+        <v>15.1</v>
       </c>
       <c r="W3" t="n">
-        <v>18.7</v>
+        <v>23.1</v>
       </c>
       <c r="X3" t="n">
-        <v>16.6</v>
+        <v>19.1</v>
       </c>
       <c r="Y3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AA3" t="n">
-        <v>12.5</v>
+        <v>13.6</v>
       </c>
       <c r="AB3" t="n">
-        <v>-4.9</v>
+        <v>-0</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.7</v>
+        <v>1.5</v>
       </c>
       <c r="AF3" t="n">
-        <v>218.6</v>
+        <v>218.84</v>
       </c>
       <c r="AG3" t="n">
-        <v>-9.380000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="AH3" t="n">
         <v>215</v>
@@ -828,10 +831,10 @@
         <v>235</v>
       </c>
       <c r="AK3" t="n">
-        <v>130.39</v>
+        <v>133.09</v>
       </c>
       <c r="AL3" t="n">
-        <v>-4.15</v>
+        <v>2.7</v>
       </c>
       <c r="AM3" t="n">
         <v>110</v>
@@ -840,99 +843,66 @@
         <v>142</v>
       </c>
       <c r="AP3" t="n">
-        <v>78.5</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="AS3" t="n">
-        <v>15.79</v>
+        <v>15.63</v>
       </c>
       <c r="BL3" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B4" t="n">
-        <v>157.5</v>
-      </c>
-      <c r="C4" t="n">
-        <v>68.5</v>
+        <v>137.6</v>
       </c>
       <c r="D4" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="E4" t="n">
-        <v>27.7</v>
+        <v>35</v>
       </c>
       <c r="F4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H4" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="I4" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J4" t="n">
-        <v>41.4</v>
+        <v>6.5</v>
       </c>
       <c r="K4" t="n">
-        <v>76.09999999999999</v>
-      </c>
-      <c r="M4" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="N4" t="n">
-        <v>34.9</v>
+        <v>96.7</v>
       </c>
       <c r="O4" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>9</v>
-      </c>
-      <c r="T4" t="n">
-        <v>21.6</v>
+        <v>35.1</v>
       </c>
       <c r="V4" t="n">
-        <v>15.1</v>
+        <v>13.6</v>
       </c>
       <c r="W4" t="n">
-        <v>23.1</v>
+        <v>24.4</v>
       </c>
       <c r="X4" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="Y4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Z4" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AA4" t="n">
-        <v>13.6</v>
+        <v>17.5</v>
       </c>
       <c r="AB4" t="n">
         <v>-0</v>
       </c>
       <c r="AC4" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="AF4" t="n">
-        <v>218.84</v>
+        <v>221.78</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.25</v>
+        <v>2.94</v>
       </c>
       <c r="AH4" t="n">
         <v>215</v>
@@ -941,10 +911,10 @@
         <v>235</v>
       </c>
       <c r="AK4" t="n">
-        <v>133.09</v>
+        <v>138.76</v>
       </c>
       <c r="AL4" t="n">
-        <v>2.7</v>
+        <v>5.67</v>
       </c>
       <c r="AM4" t="n">
         <v>110</v>
@@ -952,67 +922,61 @@
       <c r="AN4" t="n">
         <v>142</v>
       </c>
-      <c r="AP4" t="n">
-        <v>83.09999999999999</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>15.63</v>
-      </c>
       <c r="BL4" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B5" t="n">
-        <v>137.6</v>
+        <v>132.5</v>
       </c>
       <c r="D5" t="n">
-        <v>35</v>
+        <v>33.6</v>
       </c>
       <c r="F5" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="K5" t="n">
-        <v>96.7</v>
+        <v>97.8</v>
       </c>
       <c r="O5" t="n">
-        <v>35.1</v>
+        <v>31.6</v>
       </c>
       <c r="V5" t="n">
-        <v>13.6</v>
+        <v>14.8</v>
       </c>
       <c r="W5" t="n">
-        <v>24.4</v>
+        <v>24.7</v>
       </c>
       <c r="X5" t="n">
-        <v>19</v>
+        <v>19.8</v>
       </c>
       <c r="Y5" t="n">
         <v>14</v>
       </c>
       <c r="Z5" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AA5" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0</v>
+        <v>0.6</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="AF5" t="n">
-        <v>221.78</v>
+        <v>224.78</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="AH5" t="n">
         <v>215</v>
@@ -1021,10 +985,10 @@
         <v>235</v>
       </c>
       <c r="AK5" t="n">
-        <v>138.76</v>
+        <v>143.55</v>
       </c>
       <c r="AL5" t="n">
-        <v>5.67</v>
+        <v>4.79</v>
       </c>
       <c r="AM5" t="n">
         <v>110</v>
@@ -1033,60 +997,93 @@
         <v>142</v>
       </c>
       <c r="BL5" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B6" t="n">
-        <v>132.5</v>
+        <v>137.2</v>
+      </c>
+      <c r="C6" t="n">
+        <v>56.3</v>
       </c>
       <c r="D6" t="n">
-        <v>33.6</v>
+        <v>32.1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>21.2</v>
       </c>
       <c r="F6" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
+      </c>
+      <c r="H6" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="I6" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="J6" t="n">
+        <v>40.4</v>
       </c>
       <c r="K6" t="n">
-        <v>97.8</v>
+        <v>75.7</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N6" t="n">
+        <v>29</v>
       </c>
       <c r="O6" t="n">
-        <v>31.6</v>
+        <v>32.6</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>21.6</v>
       </c>
       <c r="V6" t="n">
-        <v>14.8</v>
+        <v>10.7</v>
       </c>
       <c r="W6" t="n">
-        <v>24.7</v>
+        <v>24.3</v>
       </c>
       <c r="X6" t="n">
-        <v>19.8</v>
+        <v>17.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Z6" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AA6" t="n">
-        <v>16.5</v>
+        <v>15.4</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="AF6" t="n">
-        <v>224.78</v>
+        <v>232.22</v>
       </c>
       <c r="AG6" t="n">
-        <v>3</v>
+        <v>7.43</v>
       </c>
       <c r="AH6" t="n">
         <v>215</v>
@@ -1095,10 +1092,10 @@
         <v>235</v>
       </c>
       <c r="AK6" t="n">
-        <v>143.55</v>
+        <v>143.61</v>
       </c>
       <c r="AL6" t="n">
-        <v>4.79</v>
+        <v>0.06</v>
       </c>
       <c r="AM6" t="n">
         <v>110</v>
@@ -1106,52 +1103,58 @@
       <c r="AN6" t="n">
         <v>142</v>
       </c>
+      <c r="AP6" t="n">
+        <v>89.31999999999999</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>18.02</v>
+      </c>
       <c r="BL6" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="B7" t="n">
-        <v>137.2</v>
+        <v>157.5</v>
       </c>
       <c r="C7" t="n">
-        <v>56.3</v>
+        <v>59.6</v>
       </c>
       <c r="D7" t="n">
-        <v>32.1</v>
+        <v>35</v>
       </c>
       <c r="E7" t="n">
-        <v>21.2</v>
+        <v>30.6</v>
       </c>
       <c r="F7" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="H7" t="n">
-        <v>23.7</v>
+        <v>24.2</v>
       </c>
       <c r="I7" t="n">
-        <v>11.6</v>
+        <v>11.2</v>
       </c>
       <c r="J7" t="n">
-        <v>40.4</v>
+        <v>38.9</v>
       </c>
       <c r="K7" t="n">
-        <v>75.7</v>
+        <v>74.3</v>
       </c>
       <c r="M7" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="N7" t="n">
-        <v>29</v>
+        <v>33.4</v>
       </c>
       <c r="O7" t="n">
-        <v>32.6</v>
+        <v>37.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="R7" t="n">
         <v>1.3</v>
@@ -1160,40 +1163,40 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="V7" t="n">
-        <v>10.7</v>
+        <v>13</v>
       </c>
       <c r="W7" t="n">
-        <v>24.3</v>
+        <v>26.3</v>
       </c>
       <c r="X7" t="n">
-        <v>17.5</v>
+        <v>19.6</v>
       </c>
       <c r="Y7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA7" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9</v>
+        <v>-2.1</v>
       </c>
       <c r="AC7" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="AF7" t="n">
-        <v>232.22</v>
+        <v>229.69</v>
       </c>
       <c r="AG7" t="n">
-        <v>7.43</v>
+        <v>-2.53</v>
       </c>
       <c r="AH7" t="n">
         <v>215</v>
@@ -1202,10 +1205,10 @@
         <v>235</v>
       </c>
       <c r="AK7" t="n">
-        <v>143.61</v>
+        <v>136.96</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.06</v>
+        <v>-6.65</v>
       </c>
       <c r="AM7" t="n">
         <v>110</v>
@@ -1214,99 +1217,99 @@
         <v>142</v>
       </c>
       <c r="AP7" t="n">
-        <v>89.31999999999999</v>
+        <v>86.59</v>
       </c>
       <c r="AS7" t="n">
-        <v>18.02</v>
+        <v>16.96</v>
       </c>
       <c r="BL7" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B8" t="n">
-        <v>157.5</v>
+        <v>159.6</v>
       </c>
       <c r="C8" t="n">
-        <v>59.6</v>
+        <v>63</v>
       </c>
       <c r="D8" t="n">
-        <v>35</v>
+        <v>34.5</v>
       </c>
       <c r="E8" t="n">
-        <v>30.6</v>
+        <v>31.1</v>
       </c>
       <c r="F8" t="n">
-        <v>7.5</v>
+        <v>5.7</v>
       </c>
       <c r="H8" t="n">
-        <v>24.2</v>
+        <v>23.8</v>
       </c>
       <c r="I8" t="n">
-        <v>11.2</v>
+        <v>10.8</v>
       </c>
       <c r="J8" t="n">
-        <v>38.9</v>
+        <v>40.5</v>
       </c>
       <c r="K8" t="n">
-        <v>74.3</v>
+        <v>75.2</v>
       </c>
       <c r="M8" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="N8" t="n">
-        <v>33.4</v>
+        <v>34.3</v>
       </c>
       <c r="O8" t="n">
-        <v>37.1</v>
+        <v>38.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T8" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="V8" t="n">
-        <v>13</v>
+        <v>17.5</v>
       </c>
       <c r="W8" t="n">
-        <v>26.3</v>
+        <v>22.5</v>
       </c>
       <c r="X8" t="n">
-        <v>19.6</v>
+        <v>20</v>
       </c>
       <c r="Y8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA8" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>-2.1</v>
+        <v>-2.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="AF8" t="n">
-        <v>229.69</v>
+        <v>228.57</v>
       </c>
       <c r="AG8" t="n">
-        <v>-2.53</v>
+        <v>-1.14</v>
       </c>
       <c r="AH8" t="n">
         <v>215</v>
@@ -1315,10 +1318,10 @@
         <v>235</v>
       </c>
       <c r="AK8" t="n">
-        <v>136.96</v>
+        <v>133.01</v>
       </c>
       <c r="AL8" t="n">
-        <v>-6.65</v>
+        <v>-3.95</v>
       </c>
       <c r="AM8" t="n">
         <v>110</v>
@@ -1327,99 +1330,99 @@
         <v>142</v>
       </c>
       <c r="AP8" t="n">
-        <v>86.59</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="AS8" t="n">
-        <v>16.96</v>
+        <v>15.95</v>
       </c>
       <c r="BL8" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B9" t="n">
-        <v>159.6</v>
+        <v>160.4</v>
       </c>
       <c r="C9" t="n">
-        <v>63</v>
+        <v>62.6</v>
       </c>
       <c r="D9" t="n">
-        <v>34.5</v>
+        <v>35</v>
       </c>
       <c r="E9" t="n">
-        <v>31.1</v>
+        <v>32.2</v>
       </c>
       <c r="F9" t="n">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="H9" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="I9" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="J9" t="n">
-        <v>40.5</v>
+        <v>41.1</v>
       </c>
       <c r="K9" t="n">
-        <v>75.2</v>
+        <v>75.7</v>
       </c>
       <c r="M9" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="N9" t="n">
-        <v>34.3</v>
+        <v>32.6</v>
       </c>
       <c r="O9" t="n">
-        <v>38.2</v>
+        <v>38</v>
       </c>
       <c r="Q9" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T9" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="V9" t="n">
-        <v>17.5</v>
+        <v>16.4</v>
       </c>
       <c r="W9" t="n">
-        <v>22.5</v>
+        <v>22.8</v>
       </c>
       <c r="X9" t="n">
-        <v>20</v>
+        <v>19.6</v>
       </c>
       <c r="Y9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Z9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA9" t="n">
-        <v>13.5</v>
+        <v>14.1</v>
       </c>
       <c r="AB9" t="n">
-        <v>-2.2</v>
+        <v>-3.1</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="AF9" t="n">
-        <v>228.57</v>
+        <v>225.08</v>
       </c>
       <c r="AG9" t="n">
-        <v>-1.14</v>
+        <v>-3.5</v>
       </c>
       <c r="AH9" t="n">
         <v>215</v>
@@ -1428,10 +1431,10 @@
         <v>235</v>
       </c>
       <c r="AK9" t="n">
-        <v>133.01</v>
+        <v>135.24</v>
       </c>
       <c r="AL9" t="n">
-        <v>-3.95</v>
+        <v>2.23</v>
       </c>
       <c r="AM9" t="n">
         <v>110</v>
@@ -1440,99 +1443,99 @@
         <v>142</v>
       </c>
       <c r="AP9" t="n">
-        <v>84.59999999999999</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="AS9" t="n">
-        <v>15.95</v>
+        <v>15.4</v>
       </c>
       <c r="BL9" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B10" t="n">
-        <v>160.4</v>
+        <v>161.7</v>
       </c>
       <c r="C10" t="n">
-        <v>62.6</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>35</v>
+        <v>34.9</v>
       </c>
       <c r="E10" t="n">
-        <v>32.2</v>
+        <v>27.3</v>
       </c>
       <c r="F10" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H10" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="I10" t="n">
-        <v>10.7</v>
+        <v>10.3</v>
       </c>
       <c r="J10" t="n">
-        <v>41.1</v>
+        <v>42.6</v>
       </c>
       <c r="K10" t="n">
-        <v>75.7</v>
+        <v>77</v>
       </c>
       <c r="M10" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="N10" t="n">
-        <v>32.6</v>
+        <v>31.5</v>
       </c>
       <c r="O10" t="n">
-        <v>38</v>
+        <v>37.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="R10" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T10" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="V10" t="n">
-        <v>16.4</v>
+        <v>12.7</v>
       </c>
       <c r="W10" t="n">
-        <v>22.8</v>
+        <v>27</v>
       </c>
       <c r="X10" t="n">
-        <v>19.6</v>
+        <v>19.9</v>
       </c>
       <c r="Y10" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Z10" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AA10" t="n">
-        <v>14.1</v>
+        <v>11.4</v>
       </c>
       <c r="AB10" t="n">
-        <v>-3.1</v>
+        <v>-5.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.6</v>
+        <v>-0.3</v>
       </c>
       <c r="AF10" t="n">
-        <v>225.08</v>
+        <v>225</v>
       </c>
       <c r="AG10" t="n">
-        <v>-3.5</v>
+        <v>-0.08</v>
       </c>
       <c r="AH10" t="n">
         <v>215</v>
@@ -1541,10 +1544,10 @@
         <v>235</v>
       </c>
       <c r="AK10" t="n">
-        <v>135.24</v>
+        <v>134.62</v>
       </c>
       <c r="AL10" t="n">
-        <v>2.23</v>
+        <v>-0.62</v>
       </c>
       <c r="AM10" t="n">
         <v>110</v>
@@ -1553,99 +1556,60 @@
         <v>142</v>
       </c>
       <c r="AP10" t="n">
-        <v>84.09999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="AS10" t="n">
-        <v>15.4</v>
+        <v>13.86</v>
       </c>
       <c r="BL10" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B11" t="n">
-        <v>161.7</v>
-      </c>
-      <c r="C11" t="n">
-        <v>71.09999999999999</v>
+        <v>151.5</v>
       </c>
       <c r="D11" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="E11" t="n">
-        <v>27.3</v>
+        <v>35.1</v>
       </c>
       <c r="F11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H11" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I11" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="J11" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="K11" t="n">
-        <v>77</v>
-      </c>
-      <c r="M11" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="N11" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="O11" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>21</v>
-      </c>
-      <c r="R11" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="S11" t="n">
-        <v>6</v>
-      </c>
-      <c r="T11" t="n">
-        <v>21</v>
+        <v>5.4</v>
       </c>
       <c r="V11" t="n">
-        <v>12.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>27</v>
+        <v>19.4</v>
       </c>
       <c r="X11" t="n">
-        <v>19.9</v>
+        <v>14</v>
       </c>
       <c r="Y11" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA11" t="n">
         <v>9</v>
       </c>
-      <c r="Z11" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>11.4</v>
-      </c>
       <c r="AB11" t="n">
-        <v>-5.2</v>
+        <v>-4.7</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.6</v>
+        <v>1.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0.3</v>
+        <v>-1.4</v>
       </c>
       <c r="AF11" t="n">
-        <v>225</v>
+        <v>221.37</v>
       </c>
       <c r="AG11" t="n">
-        <v>-0.08</v>
+        <v>0.05</v>
       </c>
       <c r="AH11" t="n">
         <v>215</v>
@@ -1654,10 +1618,10 @@
         <v>235</v>
       </c>
       <c r="AK11" t="n">
-        <v>134.62</v>
+        <v>135.21</v>
       </c>
       <c r="AL11" t="n">
-        <v>-0.62</v>
+        <v>0.59</v>
       </c>
       <c r="AM11" t="n">
         <v>110</v>
@@ -1665,61 +1629,61 @@
       <c r="AN11" t="n">
         <v>142</v>
       </c>
-      <c r="AP11" t="n">
-        <v>80.2</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>13.86</v>
-      </c>
       <c r="BL11" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B12" t="n">
-        <v>151.5</v>
+        <v>145.2</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1</v>
+        <v>33.5</v>
       </c>
       <c r="F12" t="n">
-        <v>5.4</v>
+        <v>5</v>
+      </c>
+      <c r="K12" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="O12" t="n">
+        <v>35.5</v>
       </c>
       <c r="V12" t="n">
-        <v>8.699999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="W12" t="n">
-        <v>19.4</v>
+        <v>19.2</v>
       </c>
       <c r="X12" t="n">
-        <v>14</v>
+        <v>13.1</v>
       </c>
       <c r="Y12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z12" t="n">
         <v>13</v>
       </c>
       <c r="AA12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB12" t="n">
-        <v>-4.7</v>
+        <v>-5.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>-1.4</v>
+        <v>-1.5</v>
       </c>
       <c r="AF12" t="n">
-        <v>221.37</v>
+        <v>224.37</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.05</v>
+        <v>3</v>
       </c>
       <c r="AH12" t="n">
         <v>215</v>
@@ -1728,10 +1692,10 @@
         <v>235</v>
       </c>
       <c r="AK12" t="n">
-        <v>135.21</v>
+        <v>135.61</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.59</v>
+        <v>0.4</v>
       </c>
       <c r="AM12" t="n">
         <v>110</v>
@@ -1740,60 +1704,60 @@
         <v>142</v>
       </c>
       <c r="BL12" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B13" t="n">
-        <v>145.2</v>
+        <v>146.3</v>
       </c>
       <c r="D13" t="n">
-        <v>33.5</v>
+        <v>33.4</v>
       </c>
       <c r="F13" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="K13" t="n">
-        <v>100.3</v>
+        <v>98.2</v>
       </c>
       <c r="O13" t="n">
-        <v>35.5</v>
+        <v>35.1</v>
       </c>
       <c r="V13" t="n">
-        <v>7.1</v>
+        <v>4.9</v>
       </c>
       <c r="W13" t="n">
-        <v>19.2</v>
+        <v>16.4</v>
       </c>
       <c r="X13" t="n">
-        <v>13.1</v>
+        <v>10.6</v>
       </c>
       <c r="Y13" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z13" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB13" t="n">
-        <v>-5.4</v>
+        <v>-6.4</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.4</v>
+        <v>-0.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>-1.5</v>
+        <v>-3.3</v>
       </c>
       <c r="AF13" t="n">
-        <v>224.37</v>
+        <v>225.93</v>
       </c>
       <c r="AG13" t="n">
-        <v>3</v>
+        <v>1.56</v>
       </c>
       <c r="AH13" t="n">
         <v>215</v>
@@ -1802,10 +1766,10 @@
         <v>235</v>
       </c>
       <c r="AK13" t="n">
-        <v>135.61</v>
+        <v>135.28</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.4</v>
+        <v>-0.33</v>
       </c>
       <c r="AM13" t="n">
         <v>110</v>
@@ -1814,60 +1778,93 @@
         <v>142</v>
       </c>
       <c r="BL13" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B14" t="n">
-        <v>146.3</v>
+        <v>182.8</v>
+      </c>
+      <c r="C14" t="n">
+        <v>86.8</v>
       </c>
       <c r="D14" t="n">
-        <v>33.4</v>
+        <v>31.8</v>
+      </c>
+      <c r="E14" t="n">
+        <v>33</v>
       </c>
       <c r="F14" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
+      </c>
+      <c r="H14" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="I14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J14" t="n">
+        <v>41.1</v>
       </c>
       <c r="K14" t="n">
-        <v>98.2</v>
+        <v>74.2</v>
+      </c>
+      <c r="M14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="N14" t="n">
+        <v>33.5</v>
       </c>
       <c r="O14" t="n">
-        <v>35.1</v>
+        <v>38.4</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="n">
+        <v>22.4</v>
       </c>
       <c r="V14" t="n">
-        <v>4.9</v>
+        <v>9.1</v>
       </c>
       <c r="W14" t="n">
-        <v>16.4</v>
+        <v>15</v>
       </c>
       <c r="X14" t="n">
-        <v>10.6</v>
+        <v>12.1</v>
       </c>
       <c r="Y14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AA14" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>-6.4</v>
+        <v>-10.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>-0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>-3.3</v>
+        <v>-5.1</v>
       </c>
       <c r="AF14" t="n">
-        <v>225.93</v>
+        <v>218.63</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.56</v>
+        <v>-7.3</v>
       </c>
       <c r="AH14" t="n">
         <v>215</v>
@@ -1876,10 +1873,10 @@
         <v>235</v>
       </c>
       <c r="AK14" t="n">
-        <v>135.28</v>
+        <v>126.27</v>
       </c>
       <c r="AL14" t="n">
-        <v>-0.33</v>
+        <v>-9.01</v>
       </c>
       <c r="AM14" t="n">
         <v>110</v>
@@ -1887,94 +1884,100 @@
       <c r="AN14" t="n">
         <v>142</v>
       </c>
+      <c r="AP14" t="n">
+        <v>82.66</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>14.7</v>
+      </c>
       <c r="BL14" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B15" t="n">
-        <v>182.8</v>
+        <v>181.8</v>
       </c>
       <c r="C15" t="n">
-        <v>86.8</v>
+        <v>86.5</v>
       </c>
       <c r="D15" t="n">
-        <v>31.8</v>
+        <v>31.4</v>
       </c>
       <c r="E15" t="n">
-        <v>33</v>
+        <v>34.2</v>
       </c>
       <c r="F15" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="H15" t="n">
-        <v>23.5</v>
+        <v>24.4</v>
       </c>
       <c r="I15" t="n">
-        <v>9.6</v>
+        <v>10.4</v>
       </c>
       <c r="J15" t="n">
-        <v>41.1</v>
+        <v>41.9</v>
       </c>
       <c r="K15" t="n">
-        <v>74.2</v>
+        <v>76.8</v>
       </c>
       <c r="M15" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="N15" t="n">
-        <v>33.5</v>
+        <v>35.7</v>
       </c>
       <c r="O15" t="n">
-        <v>38.4</v>
+        <v>39.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>22.4</v>
+        <v>23</v>
       </c>
       <c r="R15" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>20.1</v>
       </c>
       <c r="T15" t="n">
-        <v>22.4</v>
+        <v>23</v>
       </c>
       <c r="V15" t="n">
-        <v>9.1</v>
+        <v>7.1</v>
       </c>
       <c r="W15" t="n">
-        <v>15</v>
+        <v>14.8</v>
       </c>
       <c r="X15" t="n">
-        <v>12.1</v>
+        <v>10.9</v>
       </c>
       <c r="Y15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z15" t="n">
         <v>12</v>
       </c>
       <c r="AA15" t="n">
-        <v>8.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AB15" t="n">
-        <v>-10.5</v>
+        <v>-4.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>-5.1</v>
+        <v>-1.4</v>
       </c>
       <c r="AF15" t="n">
-        <v>218.63</v>
+        <v>216.39</v>
       </c>
       <c r="AG15" t="n">
-        <v>-7.3</v>
+        <v>-2.23</v>
       </c>
       <c r="AH15" t="n">
         <v>215</v>
@@ -1983,10 +1986,10 @@
         <v>235</v>
       </c>
       <c r="AK15" t="n">
-        <v>126.27</v>
+        <v>123.32</v>
       </c>
       <c r="AL15" t="n">
-        <v>-9.01</v>
+        <v>-2.95</v>
       </c>
       <c r="AM15" t="n">
         <v>110</v>
@@ -1995,99 +1998,99 @@
         <v>142</v>
       </c>
       <c r="AP15" t="n">
-        <v>82.66</v>
+        <v>79.08</v>
       </c>
       <c r="AS15" t="n">
-        <v>14.7</v>
+        <v>13.91</v>
       </c>
       <c r="BL15" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B16" t="n">
-        <v>181.8</v>
+        <v>183</v>
       </c>
       <c r="C16" t="n">
-        <v>86.5</v>
+        <v>84.7</v>
       </c>
       <c r="D16" t="n">
-        <v>31.4</v>
+        <v>30.9</v>
       </c>
       <c r="E16" t="n">
-        <v>34.2</v>
+        <v>33.7</v>
       </c>
       <c r="F16" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="H16" t="n">
-        <v>24.4</v>
+        <v>23.4</v>
       </c>
       <c r="I16" t="n">
-        <v>10.4</v>
+        <v>10.6</v>
       </c>
       <c r="J16" t="n">
-        <v>41.9</v>
+        <v>42.3</v>
       </c>
       <c r="K16" t="n">
-        <v>76.8</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>35.7</v>
+        <v>36.7</v>
       </c>
       <c r="O16" t="n">
-        <v>39.8</v>
+        <v>40.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>23</v>
+        <v>23.6</v>
       </c>
       <c r="R16" t="n">
         <v>1.8</v>
       </c>
       <c r="S16" t="n">
-        <v>20.1</v>
+        <v>20.8</v>
       </c>
       <c r="T16" t="n">
-        <v>23</v>
+        <v>23.6</v>
       </c>
       <c r="V16" t="n">
-        <v>7.1</v>
+        <v>5.7</v>
       </c>
       <c r="W16" t="n">
-        <v>14.8</v>
+        <v>16.1</v>
       </c>
       <c r="X16" t="n">
         <v>10.9</v>
       </c>
       <c r="Y16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA16" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AB16" t="n">
-        <v>-4.5</v>
+        <v>0.8</v>
       </c>
       <c r="AC16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD16" t="n">
         <v>1.8</v>
       </c>
-      <c r="AD16" t="n">
-        <v>-1.4</v>
-      </c>
       <c r="AF16" t="n">
-        <v>216.39</v>
+        <v>217.16</v>
       </c>
       <c r="AG16" t="n">
-        <v>-2.23</v>
+        <v>0.76</v>
       </c>
       <c r="AH16" t="n">
         <v>215</v>
@@ -2096,10 +2099,10 @@
         <v>235</v>
       </c>
       <c r="AK16" t="n">
-        <v>123.32</v>
+        <v>117.87</v>
       </c>
       <c r="AL16" t="n">
-        <v>-2.95</v>
+        <v>-5.45</v>
       </c>
       <c r="AM16" t="n">
         <v>110</v>
@@ -2108,99 +2111,66 @@
         <v>142</v>
       </c>
       <c r="AP16" t="n">
-        <v>79.08</v>
+        <v>78.56</v>
       </c>
       <c r="AS16" t="n">
-        <v>13.91</v>
+        <v>13.45</v>
       </c>
       <c r="BL16" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B17" t="n">
-        <v>183</v>
-      </c>
-      <c r="C17" t="n">
-        <v>84.7</v>
+        <v>163.8</v>
       </c>
       <c r="D17" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="E17" t="n">
-        <v>33.7</v>
+        <v>29</v>
       </c>
       <c r="F17" t="n">
-        <v>7</v>
-      </c>
-      <c r="H17" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="I17" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="J17" t="n">
-        <v>42.3</v>
+        <v>6.5</v>
       </c>
       <c r="K17" t="n">
-        <v>76.40000000000001</v>
-      </c>
-      <c r="M17" t="n">
-        <v>4</v>
-      </c>
-      <c r="N17" t="n">
-        <v>36.7</v>
+        <v>101.2</v>
       </c>
       <c r="O17" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S17" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="T17" t="n">
-        <v>23.6</v>
+        <v>40.2</v>
       </c>
       <c r="V17" t="n">
-        <v>5.7</v>
+        <v>6.3</v>
       </c>
       <c r="W17" t="n">
-        <v>16.1</v>
+        <v>17.2</v>
       </c>
       <c r="X17" t="n">
-        <v>10.9</v>
+        <v>11.8</v>
       </c>
       <c r="Y17" t="n">
         <v>8</v>
       </c>
       <c r="Z17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA17" t="n">
         <v>10</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.7</v>
+        <v>4.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="AF17" t="n">
-        <v>217.16</v>
+        <v>220.31</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.76</v>
+        <v>3.16</v>
       </c>
       <c r="AH17" t="n">
         <v>215</v>
@@ -2209,10 +2179,10 @@
         <v>235</v>
       </c>
       <c r="AK17" t="n">
-        <v>117.87</v>
+        <v>116.52</v>
       </c>
       <c r="AL17" t="n">
-        <v>-5.45</v>
+        <v>-1.35</v>
       </c>
       <c r="AM17" t="n">
         <v>110</v>
@@ -2220,67 +2190,61 @@
       <c r="AN17" t="n">
         <v>142</v>
       </c>
-      <c r="AP17" t="n">
-        <v>78.56</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>13.45</v>
-      </c>
       <c r="BL17" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B18" t="n">
-        <v>163.8</v>
+        <v>155.9</v>
       </c>
       <c r="D18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F18" t="n">
         <v>6.5</v>
       </c>
       <c r="K18" t="n">
-        <v>101.2</v>
+        <v>99.3</v>
       </c>
       <c r="O18" t="n">
-        <v>40.2</v>
+        <v>38.5</v>
       </c>
       <c r="V18" t="n">
-        <v>6.3</v>
+        <v>8.9</v>
       </c>
       <c r="W18" t="n">
-        <v>17.2</v>
+        <v>15.8</v>
       </c>
       <c r="X18" t="n">
-        <v>11.8</v>
+        <v>12.4</v>
       </c>
       <c r="Y18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA18" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AC18" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="AF18" t="n">
-        <v>220.31</v>
+        <v>221.99</v>
       </c>
       <c r="AG18" t="n">
-        <v>3.16</v>
+        <v>1.67</v>
       </c>
       <c r="AH18" t="n">
         <v>215</v>
@@ -2289,10 +2253,10 @@
         <v>235</v>
       </c>
       <c r="AK18" t="n">
-        <v>116.52</v>
+        <v>116.37</v>
       </c>
       <c r="AL18" t="n">
-        <v>-1.35</v>
+        <v>-0.15</v>
       </c>
       <c r="AM18" t="n">
         <v>110</v>
@@ -2301,60 +2265,60 @@
         <v>142</v>
       </c>
       <c r="BL18" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B19" t="n">
-        <v>155.9</v>
+        <v>141.3</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>26.3</v>
       </c>
       <c r="F19" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="K19" t="n">
-        <v>99.3</v>
+        <v>97.8</v>
       </c>
       <c r="O19" t="n">
-        <v>38.5</v>
+        <v>39.8</v>
       </c>
       <c r="V19" t="n">
-        <v>8.9</v>
+        <v>9.5</v>
       </c>
       <c r="W19" t="n">
-        <v>15.8</v>
+        <v>17.7</v>
       </c>
       <c r="X19" t="n">
-        <v>12.4</v>
+        <v>13.6</v>
       </c>
       <c r="Y19" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Z19" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA19" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="AC19" t="n">
-        <v>5.7</v>
+        <v>7.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="AF19" t="n">
-        <v>221.99</v>
+        <v>225.14</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.67</v>
+        <v>3.15</v>
       </c>
       <c r="AH19" t="n">
         <v>215</v>
@@ -2362,12 +2326,6 @@
       <c r="AI19" t="n">
         <v>235</v>
       </c>
-      <c r="AK19" t="n">
-        <v>116.37</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>-0.15</v>
-      </c>
       <c r="AM19" t="n">
         <v>110</v>
       </c>
@@ -2375,60 +2333,54 @@
         <v>142</v>
       </c>
       <c r="BL19" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B20" t="n">
-        <v>141.3</v>
+        <v>131.5</v>
       </c>
       <c r="D20" t="n">
-        <v>26.3</v>
+        <v>27.3</v>
       </c>
       <c r="F20" t="n">
         <v>5.5</v>
       </c>
       <c r="K20" t="n">
-        <v>97.8</v>
+        <v>97</v>
       </c>
       <c r="O20" t="n">
-        <v>39.8</v>
+        <v>35.7</v>
       </c>
       <c r="V20" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="W20" t="n">
-        <v>17.7</v>
+        <v>13.9</v>
       </c>
       <c r="X20" t="n">
-        <v>13.6</v>
+        <v>11.4</v>
       </c>
       <c r="Y20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z20" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA20" t="n">
         <v>15</v>
       </c>
-      <c r="AA20" t="n">
-        <v>14</v>
-      </c>
       <c r="AB20" t="n">
-        <v>0.2</v>
+        <v>-3.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>7.5</v>
+        <v>2.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>225.14</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>3.15</v>
+        <v>-0.4</v>
       </c>
       <c r="AH20" t="n">
         <v>215</v>
@@ -2443,54 +2395,93 @@
         <v>142</v>
       </c>
       <c r="BL20" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="B21" t="n">
-        <v>131.5</v>
+        <v>153</v>
+      </c>
+      <c r="C21" t="n">
+        <v>71.8</v>
       </c>
       <c r="D21" t="n">
-        <v>27.3</v>
+        <v>28.6</v>
+      </c>
+      <c r="E21" t="n">
+        <v>24.7</v>
       </c>
       <c r="F21" t="n">
-        <v>5.5</v>
+        <v>4</v>
+      </c>
+      <c r="H21" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J21" t="n">
+        <v>41.1</v>
       </c>
       <c r="K21" t="n">
-        <v>97</v>
+        <v>75.90000000000001</v>
+      </c>
+      <c r="M21" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N21" t="n">
+        <v>33.5</v>
       </c>
       <c r="O21" t="n">
-        <v>35.7</v>
+        <v>38.3</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>23.2</v>
       </c>
       <c r="V21" t="n">
-        <v>9</v>
+        <v>11.2</v>
       </c>
       <c r="W21" t="n">
-        <v>13.9</v>
+        <v>13</v>
       </c>
       <c r="X21" t="n">
-        <v>11.4</v>
+        <v>12.1</v>
       </c>
       <c r="Y21" t="n">
         <v>12</v>
       </c>
       <c r="Z21" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AA21" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>-3.6</v>
+        <v>-6.6</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.8</v>
+        <v>5.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>-0.4</v>
+        <v>-0.6</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>229.96</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>-0.02</v>
       </c>
       <c r="AH21" t="n">
         <v>215</v>
@@ -2498,100 +2489,112 @@
       <c r="AI21" t="n">
         <v>235</v>
       </c>
+      <c r="AK21" t="n">
+        <v>128.14</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>11.77</v>
+      </c>
       <c r="AM21" t="n">
         <v>110</v>
       </c>
       <c r="AN21" t="n">
         <v>142</v>
       </c>
+      <c r="AP21" t="n">
+        <v>87.47</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>14.8</v>
+      </c>
       <c r="BL21" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B22" t="n">
-        <v>153</v>
+        <v>165.8</v>
       </c>
       <c r="C22" t="n">
-        <v>71.8</v>
+        <v>77.3</v>
       </c>
       <c r="D22" t="n">
-        <v>28.6</v>
+        <v>29.3</v>
       </c>
       <c r="E22" t="n">
-        <v>24.7</v>
+        <v>27.7</v>
       </c>
       <c r="F22" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="H22" t="n">
         <v>24.1</v>
       </c>
       <c r="I22" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="J22" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="K22" t="n">
-        <v>75.90000000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="N22" t="n">
-        <v>33.5</v>
+        <v>35.1</v>
       </c>
       <c r="O22" t="n">
-        <v>38.3</v>
+        <v>39.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>23.2</v>
+        <v>23.8</v>
       </c>
       <c r="R22" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="T22" t="n">
-        <v>23.2</v>
+        <v>23.8</v>
       </c>
       <c r="V22" t="n">
-        <v>11.2</v>
+        <v>9.4</v>
       </c>
       <c r="W22" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="X22" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z22" t="n">
         <v>13</v>
       </c>
-      <c r="X22" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>14</v>
-      </c>
       <c r="AA22" t="n">
-        <v>12.5</v>
+        <v>10.1</v>
       </c>
       <c r="AB22" t="n">
-        <v>-6.6</v>
+        <v>-0.7</v>
       </c>
       <c r="AC22" t="n">
-        <v>5.3</v>
+        <v>9.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>-0.6</v>
+        <v>4.4</v>
       </c>
       <c r="AF22" t="n">
-        <v>229.96</v>
+        <v>227.01</v>
       </c>
       <c r="AG22" t="n">
-        <v>-0.02</v>
+        <v>-2.95</v>
       </c>
       <c r="AH22" t="n">
         <v>215</v>
@@ -2600,10 +2603,10 @@
         <v>235</v>
       </c>
       <c r="AK22" t="n">
-        <v>128.14</v>
+        <v>128.15</v>
       </c>
       <c r="AL22" t="n">
-        <v>11.77</v>
+        <v>0.01</v>
       </c>
       <c r="AM22" t="n">
         <v>110</v>
@@ -2612,99 +2615,99 @@
         <v>142</v>
       </c>
       <c r="AP22" t="n">
-        <v>87.47</v>
+        <v>83.41</v>
       </c>
       <c r="AS22" t="n">
-        <v>14.8</v>
+        <v>14.52</v>
       </c>
       <c r="BL22" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B23" t="n">
-        <v>165.8</v>
+        <v>158.1</v>
       </c>
       <c r="C23" t="n">
-        <v>77.3</v>
+        <v>73.7</v>
       </c>
       <c r="D23" t="n">
-        <v>29.3</v>
+        <v>30.3</v>
       </c>
       <c r="E23" t="n">
-        <v>27.7</v>
+        <v>26</v>
       </c>
       <c r="F23" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="H23" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="I23" t="n">
-        <v>10.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>41.6</v>
+        <v>40.9</v>
       </c>
       <c r="K23" t="n">
-        <v>76.59999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="N23" t="n">
-        <v>35.1</v>
+        <v>35.3</v>
       </c>
       <c r="O23" t="n">
-        <v>39.8</v>
+        <v>40.3</v>
       </c>
       <c r="Q23" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="R23" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S23" t="n">
         <v>7</v>
       </c>
       <c r="T23" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="V23" t="n">
-        <v>9.4</v>
+        <v>8.9</v>
       </c>
       <c r="W23" t="n">
-        <v>17.4</v>
+        <v>19.3</v>
       </c>
       <c r="X23" t="n">
-        <v>13.4</v>
+        <v>14.1</v>
       </c>
       <c r="Y23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z23" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA23" t="n">
-        <v>10.1</v>
+        <v>11</v>
       </c>
       <c r="AB23" t="n">
-        <v>-0.7</v>
+        <v>4.4</v>
       </c>
       <c r="AC23" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>4.4</v>
+        <v>6.5</v>
       </c>
       <c r="AF23" t="n">
-        <v>227.01</v>
+        <v>228.35</v>
       </c>
       <c r="AG23" t="n">
-        <v>-2.95</v>
+        <v>1.33</v>
       </c>
       <c r="AH23" t="n">
         <v>215</v>
@@ -2713,10 +2716,10 @@
         <v>235</v>
       </c>
       <c r="AK23" t="n">
-        <v>128.15</v>
+        <v>128.86</v>
       </c>
       <c r="AL23" t="n">
-        <v>0.01</v>
+        <v>0.71</v>
       </c>
       <c r="AM23" t="n">
         <v>110</v>
@@ -2725,99 +2728,99 @@
         <v>142</v>
       </c>
       <c r="AP23" t="n">
-        <v>83.41</v>
+        <v>82.37</v>
       </c>
       <c r="AS23" t="n">
-        <v>14.52</v>
+        <v>14.22</v>
       </c>
       <c r="BL23" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B24" t="n">
-        <v>158.1</v>
+        <v>154.9</v>
       </c>
       <c r="C24" t="n">
-        <v>73.7</v>
+        <v>70.2</v>
       </c>
       <c r="D24" t="n">
-        <v>30.3</v>
+        <v>31.5</v>
       </c>
       <c r="E24" t="n">
-        <v>26</v>
+        <v>27.7</v>
       </c>
       <c r="F24" t="n">
-        <v>4.1</v>
+        <v>2.7</v>
       </c>
       <c r="H24" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="I24" t="n">
-        <v>9.300000000000001</v>
+        <v>11.3</v>
       </c>
       <c r="J24" t="n">
-        <v>40.9</v>
+        <v>40.3</v>
       </c>
       <c r="K24" t="n">
-        <v>74.40000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="M24" t="n">
-        <v>5</v>
+        <v>6.1</v>
       </c>
       <c r="N24" t="n">
-        <v>35.3</v>
+        <v>32.9</v>
       </c>
       <c r="O24" t="n">
-        <v>40.3</v>
+        <v>39</v>
       </c>
       <c r="Q24" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="R24" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="S24" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="T24" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="V24" t="n">
-        <v>8.9</v>
+        <v>6.3</v>
       </c>
       <c r="W24" t="n">
-        <v>19.3</v>
+        <v>25.2</v>
       </c>
       <c r="X24" t="n">
-        <v>14.1</v>
+        <v>15.8</v>
       </c>
       <c r="Y24" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z24" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA24" t="n">
-        <v>11</v>
+        <v>12.6</v>
       </c>
       <c r="AB24" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="AC24" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="AF24" t="n">
-        <v>228.35</v>
+        <v>231.16</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.33</v>
+        <v>2.81</v>
       </c>
       <c r="AH24" t="n">
         <v>215</v>
@@ -2826,10 +2829,10 @@
         <v>235</v>
       </c>
       <c r="AK24" t="n">
-        <v>128.86</v>
+        <v>130.88</v>
       </c>
       <c r="AL24" t="n">
-        <v>0.71</v>
+        <v>2.02</v>
       </c>
       <c r="AM24" t="n">
         <v>110</v>
@@ -2838,99 +2841,66 @@
         <v>142</v>
       </c>
       <c r="AP24" t="n">
-        <v>82.37</v>
+        <v>85.48999999999999</v>
       </c>
       <c r="AS24" t="n">
-        <v>14.22</v>
+        <v>13.1</v>
       </c>
       <c r="BL24" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B25" t="n">
-        <v>154.9</v>
-      </c>
-      <c r="C25" t="n">
-        <v>70.2</v>
+        <v>152.2</v>
       </c>
       <c r="D25" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="E25" t="n">
-        <v>27.7</v>
+        <v>31</v>
       </c>
       <c r="F25" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="H25" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I25" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J25" t="n">
-        <v>40.3</v>
+        <v>3.5</v>
       </c>
       <c r="K25" t="n">
-        <v>75.8</v>
-      </c>
-      <c r="M25" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="N25" t="n">
-        <v>32.9</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O25" t="n">
-        <v>39</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="R25" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="S25" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="T25" t="n">
-        <v>23.7</v>
+        <v>34.4</v>
       </c>
       <c r="V25" t="n">
-        <v>6.3</v>
+        <v>9.5</v>
       </c>
       <c r="W25" t="n">
-        <v>25.2</v>
+        <v>25.5</v>
       </c>
       <c r="X25" t="n">
-        <v>15.8</v>
+        <v>17.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Z25" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AA25" t="n">
-        <v>12.6</v>
+        <v>9</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.9</v>
+        <v>-1.1</v>
       </c>
       <c r="AC25" t="n">
         <v>8.6</v>
       </c>
       <c r="AD25" t="n">
-        <v>5.8</v>
+        <v>3.8</v>
       </c>
       <c r="AF25" t="n">
-        <v>231.16</v>
+        <v>228.13</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.81</v>
+        <v>-3.03</v>
       </c>
       <c r="AH25" t="n">
         <v>215</v>
@@ -2938,79 +2908,67 @@
       <c r="AI25" t="n">
         <v>235</v>
       </c>
-      <c r="AK25" t="n">
-        <v>130.88</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AM25" t="n">
         <v>110</v>
       </c>
       <c r="AN25" t="n">
         <v>142</v>
       </c>
-      <c r="AP25" t="n">
-        <v>85.48999999999999</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>13.1</v>
-      </c>
       <c r="BL25" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B26" t="n">
-        <v>152.2</v>
+        <v>143.9</v>
       </c>
       <c r="D26" t="n">
-        <v>31</v>
+        <v>30.8</v>
       </c>
       <c r="F26" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="K26" t="n">
-        <v>98.40000000000001</v>
+        <v>99.2</v>
       </c>
       <c r="O26" t="n">
-        <v>34.4</v>
+        <v>35.2</v>
       </c>
       <c r="V26" t="n">
-        <v>9.5</v>
+        <v>10.7</v>
       </c>
       <c r="W26" t="n">
-        <v>25.5</v>
+        <v>17.6</v>
       </c>
       <c r="X26" t="n">
-        <v>17.5</v>
+        <v>14.2</v>
       </c>
       <c r="Y26" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Z26" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA26" t="n">
         <v>9</v>
       </c>
       <c r="AB26" t="n">
-        <v>-1.1</v>
+        <v>-0.8</v>
       </c>
       <c r="AC26" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD26" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AF26" t="n">
-        <v>228.13</v>
+        <v>229.16</v>
       </c>
       <c r="AG26" t="n">
-        <v>-3.03</v>
+        <v>1.03</v>
       </c>
       <c r="AH26" t="n">
         <v>215</v>
@@ -3025,60 +2983,93 @@
         <v>142</v>
       </c>
       <c r="BL26" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B27" t="n">
-        <v>143.9</v>
+        <v>163.2</v>
+      </c>
+      <c r="C27" t="n">
+        <v>73.7</v>
       </c>
       <c r="D27" t="n">
-        <v>30.8</v>
+        <v>30</v>
+      </c>
+      <c r="E27" t="n">
+        <v>28.2</v>
       </c>
       <c r="F27" t="n">
-        <v>2.5</v>
+        <v>4.8</v>
+      </c>
+      <c r="H27" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J27" t="n">
+        <v>40.1</v>
       </c>
       <c r="K27" t="n">
-        <v>99.2</v>
+        <v>75.59999999999999</v>
+      </c>
+      <c r="M27" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="N27" t="n">
+        <v>32.9</v>
       </c>
       <c r="O27" t="n">
-        <v>35.2</v>
+        <v>39.7</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="R27" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="S27" t="n">
+        <v>6</v>
+      </c>
+      <c r="T27" t="n">
+        <v>23.5</v>
       </c>
       <c r="V27" t="n">
-        <v>10.7</v>
+        <v>9.4</v>
       </c>
       <c r="W27" t="n">
-        <v>17.6</v>
+        <v>20.1</v>
       </c>
       <c r="X27" t="n">
-        <v>14.2</v>
+        <v>14.8</v>
       </c>
       <c r="Y27" t="n">
         <v>4</v>
       </c>
       <c r="Z27" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA27" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AB27" t="n">
-        <v>-0.8</v>
+        <v>-0.9</v>
       </c>
       <c r="AC27" t="n">
-        <v>8.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AF27" t="n">
-        <v>229.16</v>
+        <v>228.55</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.03</v>
+        <v>-0.61</v>
       </c>
       <c r="AH27" t="n">
         <v>215</v>
@@ -3086,100 +3077,112 @@
       <c r="AI27" t="n">
         <v>235</v>
       </c>
+      <c r="AK27" t="n">
+        <v>127.06</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>-3.82</v>
+      </c>
       <c r="AM27" t="n">
         <v>110</v>
       </c>
       <c r="AN27" t="n">
         <v>142</v>
       </c>
+      <c r="AP27" t="n">
+        <v>82.81</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>12.9</v>
+      </c>
       <c r="BL27" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="B28" t="n">
-        <v>163.2</v>
+        <v>174.4</v>
       </c>
       <c r="C28" t="n">
-        <v>73.7</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>30</v>
+        <v>32.1</v>
       </c>
       <c r="E28" t="n">
-        <v>28.2</v>
+        <v>30.8</v>
       </c>
       <c r="F28" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="H28" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="I28" t="n">
-        <v>11.4</v>
+        <v>10.5</v>
       </c>
       <c r="J28" t="n">
-        <v>40.1</v>
+        <v>39.5</v>
       </c>
       <c r="K28" t="n">
-        <v>75.59999999999999</v>
+        <v>74</v>
       </c>
       <c r="M28" t="n">
         <v>6.8</v>
       </c>
       <c r="N28" t="n">
-        <v>32.9</v>
+        <v>35.8</v>
       </c>
       <c r="O28" t="n">
-        <v>39.7</v>
+        <v>42.6</v>
       </c>
       <c r="Q28" t="n">
-        <v>23.5</v>
+        <v>23.1</v>
       </c>
       <c r="R28" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="S28" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="T28" t="n">
-        <v>23.5</v>
+        <v>23.1</v>
       </c>
       <c r="V28" t="n">
-        <v>9.4</v>
+        <v>12.8</v>
       </c>
       <c r="W28" t="n">
-        <v>20.1</v>
+        <v>22.1</v>
       </c>
       <c r="X28" t="n">
-        <v>14.8</v>
+        <v>17.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Z28" t="n">
         <v>13</v>
       </c>
       <c r="AA28" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AC28" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="AB28" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>9.5</v>
-      </c>
       <c r="AD28" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AF28" t="n">
-        <v>228.55</v>
+        <v>219.99</v>
       </c>
       <c r="AG28" t="n">
-        <v>-0.61</v>
+        <v>-8.56</v>
       </c>
       <c r="AH28" t="n">
         <v>215</v>
@@ -3188,10 +3191,10 @@
         <v>235</v>
       </c>
       <c r="AK28" t="n">
-        <v>127.06</v>
+        <v>125.61</v>
       </c>
       <c r="AL28" t="n">
-        <v>-3.82</v>
+        <v>-1.45</v>
       </c>
       <c r="AM28" t="n">
         <v>110</v>
@@ -3200,99 +3203,99 @@
         <v>142</v>
       </c>
       <c r="AP28" t="n">
-        <v>82.81</v>
+        <v>77.83</v>
       </c>
       <c r="AS28" t="n">
-        <v>12.9</v>
+        <v>12.96</v>
       </c>
       <c r="BL28" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B29" t="n">
-        <v>174.4</v>
+        <v>163.2</v>
       </c>
       <c r="C29" t="n">
-        <v>75.40000000000001</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="D29" t="n">
-        <v>32.1</v>
+        <v>32.9</v>
       </c>
       <c r="E29" t="n">
-        <v>30.8</v>
+        <v>26</v>
       </c>
       <c r="F29" t="n">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="H29" t="n">
-        <v>24</v>
+        <v>23.8</v>
       </c>
       <c r="I29" t="n">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="J29" t="n">
-        <v>39.5</v>
+        <v>40.1</v>
       </c>
       <c r="K29" t="n">
-        <v>74</v>
+        <v>71.3</v>
       </c>
       <c r="M29" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="N29" t="n">
-        <v>35.8</v>
+        <v>34.3</v>
       </c>
       <c r="O29" t="n">
-        <v>42.6</v>
+        <v>41.5</v>
       </c>
       <c r="Q29" t="n">
         <v>23.1</v>
       </c>
       <c r="R29" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="S29" t="n">
-        <v>8.5</v>
+        <v>6.2</v>
       </c>
       <c r="T29" t="n">
         <v>23.1</v>
       </c>
       <c r="V29" t="n">
-        <v>12.8</v>
+        <v>9.6</v>
       </c>
       <c r="W29" t="n">
-        <v>22.1</v>
+        <v>23.3</v>
       </c>
       <c r="X29" t="n">
-        <v>17.5</v>
+        <v>16.4</v>
       </c>
       <c r="Y29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z29" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA29" t="n">
-        <v>10.1</v>
+        <v>12.2</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.3</v>
+        <v>2.6</v>
       </c>
       <c r="AC29" t="n">
-        <v>9.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AF29" t="n">
-        <v>219.99</v>
+        <v>219.22</v>
       </c>
       <c r="AG29" t="n">
-        <v>-8.56</v>
+        <v>-0.77</v>
       </c>
       <c r="AH29" t="n">
         <v>215</v>
@@ -3301,10 +3304,10 @@
         <v>235</v>
       </c>
       <c r="AK29" t="n">
-        <v>125.61</v>
+        <v>124.36</v>
       </c>
       <c r="AL29" t="n">
-        <v>-1.45</v>
+        <v>-1.25</v>
       </c>
       <c r="AM29" t="n">
         <v>110</v>
@@ -3313,99 +3316,99 @@
         <v>142</v>
       </c>
       <c r="AP29" t="n">
-        <v>77.83</v>
+        <v>76.81</v>
       </c>
       <c r="AS29" t="n">
-        <v>12.96</v>
+        <v>12.38</v>
       </c>
       <c r="BL29" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B30" t="n">
-        <v>163.2</v>
+        <v>152.7</v>
       </c>
       <c r="C30" t="n">
-        <v>70.90000000000001</v>
+        <v>62.6</v>
       </c>
       <c r="D30" t="n">
-        <v>32.9</v>
+        <v>32.7</v>
       </c>
       <c r="E30" t="n">
-        <v>26</v>
+        <v>24.6</v>
       </c>
       <c r="F30" t="n">
-        <v>6.9</v>
+        <v>5.2</v>
       </c>
       <c r="H30" t="n">
         <v>23.8</v>
       </c>
       <c r="I30" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J30" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="K30" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="M30" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="N30" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="O30" t="n">
         <v>40.1</v>
       </c>
-      <c r="K30" t="n">
-        <v>71.3</v>
-      </c>
-      <c r="M30" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="N30" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="O30" t="n">
-        <v>41.5</v>
-      </c>
       <c r="Q30" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="R30" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="S30" t="n">
-        <v>6.2</v>
+        <v>4</v>
       </c>
       <c r="T30" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="V30" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="W30" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="X30" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC30" t="n">
         <v>9.6</v>
       </c>
-      <c r="W30" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="X30" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>8.5</v>
-      </c>
       <c r="AD30" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AF30" t="n">
-        <v>219.22</v>
+        <v>220.73</v>
       </c>
       <c r="AG30" t="n">
-        <v>-0.77</v>
+        <v>1.5</v>
       </c>
       <c r="AH30" t="n">
         <v>215</v>
@@ -3414,10 +3417,10 @@
         <v>235</v>
       </c>
       <c r="AK30" t="n">
-        <v>124.36</v>
+        <v>120.93</v>
       </c>
       <c r="AL30" t="n">
-        <v>-1.25</v>
+        <v>-3.43</v>
       </c>
       <c r="AM30" t="n">
         <v>110</v>
@@ -3426,75 +3429,75 @@
         <v>142</v>
       </c>
       <c r="AP30" t="n">
-        <v>76.81</v>
+        <v>77.87</v>
       </c>
       <c r="AS30" t="n">
-        <v>12.38</v>
+        <v>13.26</v>
       </c>
       <c r="BL30" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B31" t="n">
-        <v>152.7</v>
+        <v>150.7</v>
       </c>
       <c r="C31" t="n">
-        <v>62.6</v>
+        <v>64.8</v>
       </c>
       <c r="D31" t="n">
-        <v>32.7</v>
+        <v>33.7</v>
       </c>
       <c r="E31" t="n">
-        <v>24.6</v>
+        <v>27.1</v>
       </c>
       <c r="F31" t="n">
-        <v>5.2</v>
+        <v>3.8</v>
       </c>
       <c r="H31" t="n">
-        <v>23.8</v>
+        <v>23.4</v>
       </c>
       <c r="I31" t="n">
         <v>7.2</v>
       </c>
       <c r="J31" t="n">
-        <v>38.9</v>
+        <v>39.9</v>
       </c>
       <c r="K31" t="n">
-        <v>69.90000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="M31" t="n">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="N31" t="n">
-        <v>33.5</v>
+        <v>33</v>
       </c>
       <c r="O31" t="n">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="Q31" t="n">
         <v>23.2</v>
       </c>
       <c r="R31" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="S31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T31" t="n">
         <v>23.2</v>
       </c>
       <c r="V31" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="W31" t="n">
-        <v>27.3</v>
+        <v>28.9</v>
       </c>
       <c r="X31" t="n">
-        <v>19.4</v>
+        <v>21.7</v>
       </c>
       <c r="Y31" t="n">
         <v>10</v>
@@ -3503,22 +3506,22 @@
         <v>18</v>
       </c>
       <c r="AA31" t="n">
-        <v>14</v>
+        <v>13.1</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="AC31" t="n">
-        <v>9.6</v>
+        <v>10.8</v>
       </c>
       <c r="AD31" t="n">
-        <v>5.7</v>
+        <v>6.7</v>
       </c>
       <c r="AF31" t="n">
-        <v>220.73</v>
+        <v>220.58</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.5</v>
+        <v>-0.15</v>
       </c>
       <c r="AH31" t="n">
         <v>215</v>
@@ -3527,10 +3530,10 @@
         <v>235</v>
       </c>
       <c r="AK31" t="n">
-        <v>120.93</v>
+        <v>120.28</v>
       </c>
       <c r="AL31" t="n">
-        <v>-3.43</v>
+        <v>-0.65</v>
       </c>
       <c r="AM31" t="n">
         <v>110</v>
@@ -3539,99 +3542,54 @@
         <v>142</v>
       </c>
       <c r="AP31" t="n">
-        <v>77.87</v>
+        <v>77.22</v>
       </c>
       <c r="AS31" t="n">
-        <v>13.26</v>
+        <v>13.79</v>
       </c>
       <c r="BL31" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B32" t="n">
-        <v>150.7</v>
-      </c>
-      <c r="C32" t="n">
-        <v>64.8</v>
+        <v>138.2</v>
       </c>
       <c r="D32" t="n">
-        <v>33.7</v>
-      </c>
-      <c r="E32" t="n">
-        <v>27.1</v>
+        <v>33.6</v>
       </c>
       <c r="F32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H32" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="V32" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="W32" t="n">
         <v>23.4</v>
       </c>
-      <c r="I32" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="J32" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="K32" t="n">
-        <v>70.5</v>
-      </c>
-      <c r="M32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="N32" t="n">
-        <v>33</v>
-      </c>
-      <c r="O32" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="R32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="S32" t="n">
-        <v>3</v>
-      </c>
-      <c r="T32" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="V32" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="W32" t="n">
-        <v>28.9</v>
-      </c>
       <c r="X32" t="n">
-        <v>21.7</v>
+        <v>19.4</v>
       </c>
       <c r="Y32" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z32" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AA32" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="AC32" t="n">
-        <v>10.8</v>
+        <v>8.5</v>
       </c>
       <c r="AD32" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>220.58</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>-0.15</v>
+        <v>4.5</v>
       </c>
       <c r="AH32" t="n">
         <v>215</v>
@@ -3639,67 +3597,61 @@
       <c r="AI32" t="n">
         <v>235</v>
       </c>
-      <c r="AK32" t="n">
-        <v>120.28</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>-0.65</v>
-      </c>
       <c r="AM32" t="n">
         <v>110</v>
       </c>
       <c r="AN32" t="n">
         <v>142</v>
       </c>
-      <c r="AP32" t="n">
-        <v>77.22</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>13.79</v>
-      </c>
       <c r="BL32" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B33" t="n">
-        <v>138.2</v>
+        <v>126.5</v>
       </c>
       <c r="D33" t="n">
-        <v>33.6</v>
+        <v>33.2</v>
       </c>
       <c r="F33" t="n">
-        <v>6.1</v>
+        <v>3.4</v>
       </c>
       <c r="V33" t="n">
-        <v>15.5</v>
+        <v>12.6</v>
       </c>
       <c r="W33" t="n">
-        <v>23.4</v>
+        <v>22.3</v>
       </c>
       <c r="X33" t="n">
-        <v>19.4</v>
+        <v>17.4</v>
       </c>
       <c r="Y33" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z33" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA33" t="n">
         <v>13</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>8.5</v>
+        <v>6.7</v>
       </c>
       <c r="AD33" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>229.48</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>6.05</v>
       </c>
       <c r="AH33" t="n">
         <v>215</v>
@@ -3714,54 +3666,93 @@
         <v>142</v>
       </c>
       <c r="BL33" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B34" t="n">
-        <v>126.5</v>
+        <v>129.4</v>
+      </c>
+      <c r="C34" t="n">
+        <v>50.6</v>
       </c>
       <c r="D34" t="n">
-        <v>33.2</v>
+        <v>31.5</v>
+      </c>
+      <c r="E34" t="n">
+        <v>19.4</v>
       </c>
       <c r="F34" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
+      </c>
+      <c r="H34" t="n">
+        <v>24</v>
+      </c>
+      <c r="I34" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J34" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="K34" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="M34" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N34" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="O34" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>21.4</v>
       </c>
       <c r="V34" t="n">
-        <v>12.6</v>
+        <v>14.3</v>
       </c>
       <c r="W34" t="n">
-        <v>22.3</v>
+        <v>23.9</v>
       </c>
       <c r="X34" t="n">
-        <v>17.4</v>
+        <v>19.1</v>
       </c>
       <c r="Y34" t="n">
         <v>8</v>
       </c>
       <c r="Z34" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AA34" t="n">
-        <v>13</v>
+        <v>16.1</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AC34" t="n">
-        <v>6.7</v>
+        <v>7.6</v>
       </c>
       <c r="AD34" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="AF34" t="n">
-        <v>229.48</v>
+        <v>229.5</v>
       </c>
       <c r="AG34" t="n">
-        <v>6.05</v>
+        <v>0.02</v>
       </c>
       <c r="AH34" t="n">
         <v>215</v>
@@ -3769,100 +3760,112 @@
       <c r="AI34" t="n">
         <v>235</v>
       </c>
+      <c r="AK34" t="n">
+        <v>128.37</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>8.09</v>
+      </c>
       <c r="AM34" t="n">
         <v>110</v>
       </c>
       <c r="AN34" t="n">
         <v>142</v>
       </c>
+      <c r="AP34" t="n">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>15.97</v>
+      </c>
       <c r="BL34" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="B35" t="n">
-        <v>129.4</v>
+        <v>142.9</v>
       </c>
       <c r="C35" t="n">
-        <v>50.6</v>
+        <v>52.7</v>
       </c>
       <c r="D35" t="n">
-        <v>31.5</v>
+        <v>34.7</v>
       </c>
       <c r="E35" t="n">
-        <v>19.4</v>
+        <v>24.8</v>
       </c>
       <c r="F35" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="H35" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I35" t="n">
-        <v>10.4</v>
+        <v>9.9</v>
       </c>
       <c r="J35" t="n">
-        <v>38.9</v>
+        <v>38.2</v>
       </c>
       <c r="K35" t="n">
-        <v>73.3</v>
+        <v>70</v>
       </c>
       <c r="M35" t="n">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="N35" t="n">
-        <v>33.3</v>
+        <v>31.9</v>
       </c>
       <c r="O35" t="n">
-        <v>38</v>
+        <v>35.8</v>
       </c>
       <c r="Q35" t="n">
-        <v>21.4</v>
+        <v>19.7</v>
       </c>
       <c r="R35" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>21.4</v>
+        <v>19.7</v>
       </c>
       <c r="V35" t="n">
-        <v>14.3</v>
+        <v>12</v>
       </c>
       <c r="W35" t="n">
-        <v>23.9</v>
+        <v>25.8</v>
       </c>
       <c r="X35" t="n">
-        <v>19.1</v>
+        <v>18.9</v>
       </c>
       <c r="Y35" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Z35" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AA35" t="n">
-        <v>16.1</v>
+        <v>15</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.4</v>
+        <v>-0.1</v>
       </c>
       <c r="AC35" t="n">
-        <v>7.6</v>
+        <v>5.8</v>
       </c>
       <c r="AD35" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="AF35" t="n">
-        <v>229.5</v>
+        <v>238.69</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.02</v>
+        <v>-2.8</v>
       </c>
       <c r="AH35" t="n">
         <v>215</v>
@@ -3871,10 +3874,10 @@
         <v>235</v>
       </c>
       <c r="AK35" t="n">
-        <v>128.37</v>
+        <v>134.59</v>
       </c>
       <c r="AL35" t="n">
-        <v>8.09</v>
+        <v>6.22</v>
       </c>
       <c r="AM35" t="n">
         <v>110</v>
@@ -3883,99 +3886,99 @@
         <v>142</v>
       </c>
       <c r="AP35" t="n">
-        <v>91.59999999999999</v>
+        <v>89.05</v>
       </c>
       <c r="AS35" t="n">
-        <v>15.97</v>
+        <v>17.06</v>
       </c>
       <c r="BL35" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B36" t="n">
-        <v>142.9</v>
+        <v>148.1</v>
       </c>
       <c r="C36" t="n">
-        <v>52.7</v>
+        <v>51.9</v>
       </c>
       <c r="D36" t="n">
-        <v>34.7</v>
+        <v>35.4</v>
       </c>
       <c r="E36" t="n">
-        <v>24.8</v>
+        <v>31.5</v>
       </c>
       <c r="F36" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="H36" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="I36" t="n">
-        <v>9.9</v>
+        <v>9.6</v>
       </c>
       <c r="J36" t="n">
-        <v>38.2</v>
+        <v>39.6</v>
       </c>
       <c r="K36" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M36" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="N36" t="n">
-        <v>31.9</v>
+        <v>30.8</v>
       </c>
       <c r="O36" t="n">
-        <v>35.8</v>
+        <v>33.7</v>
       </c>
       <c r="Q36" t="n">
-        <v>19.7</v>
+        <v>20.7</v>
       </c>
       <c r="R36" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>19.7</v>
+        <v>20.7</v>
       </c>
       <c r="V36" t="n">
-        <v>12</v>
+        <v>13.1</v>
       </c>
       <c r="W36" t="n">
-        <v>25.8</v>
+        <v>25.5</v>
       </c>
       <c r="X36" t="n">
-        <v>18.9</v>
+        <v>19.3</v>
       </c>
       <c r="Y36" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z36" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AA36" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AB36" t="n">
-        <v>-0.1</v>
+        <v>-1</v>
       </c>
       <c r="AC36" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="AF36" t="n">
-        <v>238.69</v>
+        <v>233.48</v>
       </c>
       <c r="AG36" t="n">
-        <v>-2.8</v>
+        <v>-4.86</v>
       </c>
       <c r="AH36" t="n">
         <v>215</v>
@@ -3984,10 +3987,10 @@
         <v>235</v>
       </c>
       <c r="AK36" t="n">
-        <v>134.59</v>
+        <v>136.6</v>
       </c>
       <c r="AL36" t="n">
-        <v>6.22</v>
+        <v>2.01</v>
       </c>
       <c r="AM36" t="n">
         <v>110</v>
@@ -3996,99 +3999,99 @@
         <v>142</v>
       </c>
       <c r="AP36" t="n">
-        <v>89.05</v>
+        <v>86.25</v>
       </c>
       <c r="AS36" t="n">
-        <v>17.06</v>
+        <v>17.13</v>
       </c>
       <c r="BL36" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B37" t="n">
-        <v>148.1</v>
+        <v>143.4</v>
       </c>
       <c r="C37" t="n">
-        <v>51.9</v>
+        <v>50.9</v>
       </c>
       <c r="D37" t="n">
-        <v>35.4</v>
+        <v>35.7</v>
       </c>
       <c r="E37" t="n">
-        <v>31.5</v>
+        <v>26.2</v>
       </c>
       <c r="F37" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="H37" t="n">
-        <v>21.8</v>
+        <v>22.9</v>
       </c>
       <c r="I37" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J37" t="n">
-        <v>39.6</v>
+        <v>39.9</v>
       </c>
       <c r="K37" t="n">
-        <v>71</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="M37" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="N37" t="n">
-        <v>30.8</v>
+        <v>31.2</v>
       </c>
       <c r="O37" t="n">
-        <v>33.7</v>
+        <v>33.1</v>
       </c>
       <c r="Q37" t="n">
-        <v>20.7</v>
+        <v>21.6</v>
       </c>
       <c r="R37" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>20.7</v>
+        <v>21.6</v>
       </c>
       <c r="V37" t="n">
-        <v>13.1</v>
+        <v>12.9</v>
       </c>
       <c r="W37" t="n">
-        <v>25.5</v>
+        <v>28.3</v>
       </c>
       <c r="X37" t="n">
-        <v>19.3</v>
+        <v>20.6</v>
       </c>
       <c r="Y37" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z37" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AA37" t="n">
-        <v>15.5</v>
+        <v>17.9</v>
       </c>
       <c r="AB37" t="n">
-        <v>-1</v>
+        <v>-0.8</v>
       </c>
       <c r="AC37" t="n">
-        <v>6.4</v>
+        <v>8.1</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="AF37" t="n">
-        <v>233.48</v>
+        <v>235.13</v>
       </c>
       <c r="AG37" t="n">
-        <v>-4.86</v>
+        <v>1.66</v>
       </c>
       <c r="AH37" t="n">
         <v>215</v>
@@ -4097,10 +4100,10 @@
         <v>235</v>
       </c>
       <c r="AK37" t="n">
-        <v>136.6</v>
+        <v>135.66</v>
       </c>
       <c r="AL37" t="n">
-        <v>2.01</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AM37" t="n">
         <v>110</v>
@@ -4109,57 +4112,57 @@
         <v>142</v>
       </c>
       <c r="AP37" t="n">
-        <v>86.25</v>
+        <v>88.27</v>
       </c>
       <c r="AS37" t="n">
-        <v>17.13</v>
+        <v>17.6</v>
       </c>
       <c r="BL37" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B38" t="n">
-        <v>143.4</v>
+        <v>144.9</v>
       </c>
       <c r="C38" t="n">
-        <v>50.9</v>
+        <v>53</v>
       </c>
       <c r="D38" t="n">
-        <v>35.7</v>
+        <v>35.6</v>
       </c>
       <c r="E38" t="n">
-        <v>26.2</v>
+        <v>26</v>
       </c>
       <c r="F38" t="n">
-        <v>4.3</v>
+        <v>2.8</v>
       </c>
       <c r="H38" t="n">
-        <v>22.9</v>
+        <v>24</v>
       </c>
       <c r="I38" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J38" t="n">
-        <v>39.9</v>
+        <v>40.3</v>
       </c>
       <c r="K38" t="n">
-        <v>72.59999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="M38" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="N38" t="n">
-        <v>31.2</v>
+        <v>31.6</v>
       </c>
       <c r="O38" t="n">
-        <v>33.1</v>
+        <v>33.6</v>
       </c>
       <c r="Q38" t="n">
-        <v>21.6</v>
+        <v>21</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -4168,40 +4171,40 @@
         <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>21.6</v>
+        <v>21</v>
       </c>
       <c r="V38" t="n">
-        <v>12.9</v>
+        <v>14.4</v>
       </c>
       <c r="W38" t="n">
-        <v>28.3</v>
+        <v>27.7</v>
       </c>
       <c r="X38" t="n">
-        <v>20.6</v>
+        <v>21.1</v>
       </c>
       <c r="Y38" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z38" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AA38" t="n">
-        <v>17.9</v>
+        <v>16.3</v>
       </c>
       <c r="AB38" t="n">
-        <v>-0.8</v>
+        <v>-1.1</v>
       </c>
       <c r="AC38" t="n">
-        <v>8.1</v>
+        <v>6.6</v>
       </c>
       <c r="AD38" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="AF38" t="n">
-        <v>235.13</v>
+        <v>234.87</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.66</v>
+        <v>-0.26</v>
       </c>
       <c r="AH38" t="n">
         <v>215</v>
@@ -4210,10 +4213,10 @@
         <v>235</v>
       </c>
       <c r="AK38" t="n">
-        <v>135.66</v>
+        <v>136.33</v>
       </c>
       <c r="AL38" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="AM38" t="n">
         <v>110</v>
@@ -4222,99 +4225,60 @@
         <v>142</v>
       </c>
       <c r="AP38" t="n">
-        <v>88.27</v>
+        <v>87.09</v>
       </c>
       <c r="AS38" t="n">
-        <v>17.6</v>
+        <v>17.31</v>
       </c>
       <c r="BL38" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B39" t="n">
-        <v>144.9</v>
-      </c>
-      <c r="C39" t="n">
-        <v>53</v>
+        <v>132.2</v>
       </c>
       <c r="D39" t="n">
         <v>35.6</v>
       </c>
-      <c r="E39" t="n">
-        <v>26</v>
-      </c>
       <c r="F39" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="H39" t="n">
-        <v>24</v>
-      </c>
-      <c r="I39" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="J39" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="K39" t="n">
-        <v>73.7</v>
-      </c>
-      <c r="M39" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="N39" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="O39" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>21</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="V39" t="n">
-        <v>14.4</v>
+        <v>11.6</v>
       </c>
       <c r="W39" t="n">
-        <v>27.7</v>
+        <v>23.2</v>
       </c>
       <c r="X39" t="n">
-        <v>21.1</v>
+        <v>17.4</v>
       </c>
       <c r="Y39" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z39" t="n">
         <v>19</v>
       </c>
       <c r="AA39" t="n">
-        <v>16.3</v>
+        <v>13</v>
       </c>
       <c r="AB39" t="n">
-        <v>-1.1</v>
+        <v>0.9</v>
       </c>
       <c r="AC39" t="n">
-        <v>6.6</v>
+        <v>7.5</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="AF39" t="n">
-        <v>234.87</v>
+        <v>234.78</v>
       </c>
       <c r="AG39" t="n">
-        <v>-0.26</v>
+        <v>-0.09</v>
       </c>
       <c r="AH39" t="n">
         <v>215</v>
@@ -4322,73 +4286,61 @@
       <c r="AI39" t="n">
         <v>235</v>
       </c>
-      <c r="AK39" t="n">
-        <v>136.33</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>0.67</v>
-      </c>
       <c r="AM39" t="n">
         <v>110</v>
       </c>
       <c r="AN39" t="n">
         <v>142</v>
       </c>
-      <c r="AP39" t="n">
-        <v>87.09</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>17.31</v>
-      </c>
       <c r="BL39" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B40" t="n">
-        <v>132.2</v>
+        <v>137.1</v>
       </c>
       <c r="D40" t="n">
-        <v>35.6</v>
+        <v>35.1</v>
       </c>
       <c r="F40" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="V40" t="n">
-        <v>11.6</v>
+        <v>11</v>
       </c>
       <c r="W40" t="n">
-        <v>23.2</v>
+        <v>22</v>
       </c>
       <c r="X40" t="n">
-        <v>17.4</v>
+        <v>16.5</v>
       </c>
       <c r="Y40" t="n">
         <v>7</v>
       </c>
       <c r="Z40" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AA40" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.9</v>
+        <v>-5.3</v>
       </c>
       <c r="AC40" t="n">
-        <v>7.5</v>
+        <v>6.1</v>
       </c>
       <c r="AD40" t="n">
-        <v>4.2</v>
+        <v>0.4</v>
       </c>
       <c r="AF40" t="n">
-        <v>234.78</v>
+        <v>229.75</v>
       </c>
       <c r="AG40" t="n">
-        <v>-0.09</v>
+        <v>-5.03</v>
       </c>
       <c r="AH40" t="n">
         <v>215</v>
@@ -4403,54 +4355,93 @@
         <v>142</v>
       </c>
       <c r="BL40" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B41" t="n">
-        <v>137.1</v>
+        <v>166.2</v>
+      </c>
+      <c r="C41" t="n">
+        <v>72.40000000000001</v>
       </c>
       <c r="D41" t="n">
-        <v>35.1</v>
+        <v>32.7</v>
+      </c>
+      <c r="E41" t="n">
+        <v>28.1</v>
       </c>
       <c r="F41" t="n">
         <v>3.3</v>
       </c>
+      <c r="H41" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="I41" t="n">
+        <v>9</v>
+      </c>
+      <c r="J41" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="K41" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="M41" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="N41" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="O41" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="R41" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>23.7</v>
+      </c>
       <c r="V41" t="n">
-        <v>11</v>
+        <v>7.9</v>
       </c>
       <c r="W41" t="n">
-        <v>22</v>
+        <v>15.6</v>
       </c>
       <c r="X41" t="n">
-        <v>16.5</v>
+        <v>11.8</v>
       </c>
       <c r="Y41" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z41" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AA41" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AB41" t="n">
-        <v>-5.3</v>
+        <v>-3.5</v>
       </c>
       <c r="AC41" t="n">
-        <v>6.1</v>
+        <v>8.4</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.4</v>
+        <v>2.5</v>
       </c>
       <c r="AF41" t="n">
-        <v>229.75</v>
+        <v>222.86</v>
       </c>
       <c r="AG41" t="n">
-        <v>-5.03</v>
+        <v>-6.9</v>
       </c>
       <c r="AH41" t="n">
         <v>215</v>
@@ -4458,100 +4449,112 @@
       <c r="AI41" t="n">
         <v>235</v>
       </c>
+      <c r="AK41" t="n">
+        <v>135.42</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>-0.91</v>
+      </c>
       <c r="AM41" t="n">
         <v>110</v>
       </c>
       <c r="AN41" t="n">
         <v>142</v>
       </c>
+      <c r="AP41" t="n">
+        <v>81.98</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>15.01</v>
+      </c>
       <c r="BL41" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B42" t="n">
-        <v>166.2</v>
+        <v>166.3</v>
       </c>
       <c r="C42" t="n">
-        <v>72.40000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="D42" t="n">
-        <v>32.7</v>
+        <v>32.8</v>
       </c>
       <c r="E42" t="n">
-        <v>28.1</v>
+        <v>28.8</v>
       </c>
       <c r="F42" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="H42" t="n">
         <v>23.4</v>
       </c>
       <c r="I42" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J42" t="n">
-        <v>42.1</v>
+        <v>41.2</v>
       </c>
       <c r="K42" t="n">
-        <v>74.5</v>
+        <v>73.8</v>
       </c>
       <c r="M42" t="n">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="N42" t="n">
-        <v>33.7</v>
+        <v>35.4</v>
       </c>
       <c r="O42" t="n">
-        <v>39.3</v>
+        <v>42.6</v>
       </c>
       <c r="Q42" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="R42" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="V42" t="n">
-        <v>7.9</v>
+        <v>6.7</v>
       </c>
       <c r="W42" t="n">
-        <v>15.6</v>
+        <v>18.1</v>
       </c>
       <c r="X42" t="n">
-        <v>11.8</v>
+        <v>12.4</v>
       </c>
       <c r="Y42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Z42" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AA42" t="n">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AB42" t="n">
-        <v>-3.5</v>
+        <v>-2.9</v>
       </c>
       <c r="AC42" t="n">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.5</v>
+        <v>4.3</v>
       </c>
       <c r="AF42" t="n">
-        <v>222.86</v>
+        <v>218.37</v>
       </c>
       <c r="AG42" t="n">
-        <v>-6.9</v>
+        <v>-4.49</v>
       </c>
       <c r="AH42" t="n">
         <v>215</v>
@@ -4560,10 +4563,10 @@
         <v>235</v>
       </c>
       <c r="AK42" t="n">
-        <v>135.42</v>
+        <v>131.24</v>
       </c>
       <c r="AL42" t="n">
-        <v>-0.91</v>
+        <v>-4.18</v>
       </c>
       <c r="AM42" t="n">
         <v>110</v>
@@ -4572,99 +4575,99 @@
         <v>142</v>
       </c>
       <c r="AP42" t="n">
-        <v>81.98</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="AS42" t="n">
-        <v>15.01</v>
+        <v>12.97</v>
       </c>
       <c r="BL42" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B43" t="n">
-        <v>166.3</v>
+        <v>154.1</v>
       </c>
       <c r="C43" t="n">
-        <v>74.90000000000001</v>
+        <v>65</v>
       </c>
       <c r="D43" t="n">
-        <v>32.8</v>
+        <v>32</v>
       </c>
       <c r="E43" t="n">
-        <v>28.8</v>
+        <v>25.2</v>
       </c>
       <c r="F43" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="H43" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="I43" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="J43" t="n">
-        <v>41.2</v>
+        <v>38.5</v>
       </c>
       <c r="K43" t="n">
-        <v>73.8</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="M43" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="N43" t="n">
-        <v>35.4</v>
+        <v>32.3</v>
       </c>
       <c r="O43" t="n">
-        <v>42.6</v>
+        <v>40.3</v>
       </c>
       <c r="Q43" t="n">
-        <v>23.9</v>
+        <v>21.7</v>
       </c>
       <c r="R43" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="S43" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T43" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="V43" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="W43" t="n">
+        <v>21</v>
+      </c>
+      <c r="X43" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AD43" t="n">
         <v>3.9</v>
       </c>
-      <c r="S43" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="V43" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="W43" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="X43" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>11</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>-2.9</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AF43" t="n">
-        <v>218.37</v>
+        <v>218.04</v>
       </c>
       <c r="AG43" t="n">
-        <v>-4.49</v>
+        <v>-0.33</v>
       </c>
       <c r="AH43" t="n">
         <v>215</v>
@@ -4673,10 +4676,10 @@
         <v>235</v>
       </c>
       <c r="AK43" t="n">
-        <v>131.24</v>
+        <v>129.21</v>
       </c>
       <c r="AL43" t="n">
-        <v>-4.18</v>
+        <v>-2.03</v>
       </c>
       <c r="AM43" t="n">
         <v>110</v>
@@ -4685,99 +4688,99 @@
         <v>142</v>
       </c>
       <c r="AP43" t="n">
-        <v>79.98999999999999</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="AS43" t="n">
-        <v>12.97</v>
+        <v>15.23</v>
       </c>
       <c r="BL43" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B44" t="n">
-        <v>154.1</v>
+        <v>148.8</v>
       </c>
       <c r="C44" t="n">
-        <v>65</v>
+        <v>57.6</v>
       </c>
       <c r="D44" t="n">
-        <v>32</v>
+        <v>32.7</v>
       </c>
       <c r="E44" t="n">
-        <v>25.2</v>
+        <v>26.3</v>
       </c>
       <c r="F44" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="H44" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="I44" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="J44" t="n">
-        <v>38.5</v>
+        <v>41.6</v>
       </c>
       <c r="K44" t="n">
-        <v>70.90000000000001</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="M44" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="N44" t="n">
-        <v>32.3</v>
+        <v>35</v>
       </c>
       <c r="O44" t="n">
-        <v>40.3</v>
+        <v>42.4</v>
       </c>
       <c r="Q44" t="n">
         <v>21.7</v>
       </c>
       <c r="R44" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="S44" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
         <v>21.7</v>
       </c>
       <c r="V44" t="n">
-        <v>5.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W44" t="n">
-        <v>21</v>
+        <v>24.1</v>
       </c>
       <c r="X44" t="n">
-        <v>13.2</v>
+        <v>16.1</v>
       </c>
       <c r="Y44" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z44" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA44" t="n">
-        <v>14.5</v>
+        <v>15.6</v>
       </c>
       <c r="AB44" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="AC44" t="n">
-        <v>7.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AD44" t="n">
-        <v>3.9</v>
+        <v>6.3</v>
       </c>
       <c r="AF44" t="n">
-        <v>218.04</v>
+        <v>220.84</v>
       </c>
       <c r="AG44" t="n">
-        <v>-0.33</v>
+        <v>2.8</v>
       </c>
       <c r="AH44" t="n">
         <v>215</v>
@@ -4786,10 +4789,10 @@
         <v>235</v>
       </c>
       <c r="AK44" t="n">
-        <v>129.21</v>
+        <v>129.07</v>
       </c>
       <c r="AL44" t="n">
-        <v>-2.03</v>
+        <v>-0.14</v>
       </c>
       <c r="AM44" t="n">
         <v>110</v>
@@ -4798,99 +4801,99 @@
         <v>142</v>
       </c>
       <c r="AP44" t="n">
-        <v>82.90000000000001</v>
+        <v>85.52</v>
       </c>
       <c r="AS44" t="n">
-        <v>15.23</v>
+        <v>15.82</v>
       </c>
       <c r="BL44" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B45" t="n">
-        <v>148.8</v>
+        <v>146.8</v>
       </c>
       <c r="C45" t="n">
-        <v>57.6</v>
+        <v>52.8</v>
       </c>
       <c r="D45" t="n">
-        <v>32.7</v>
+        <v>33.6</v>
       </c>
       <c r="E45" t="n">
-        <v>26.3</v>
+        <v>28.9</v>
       </c>
       <c r="F45" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="H45" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="I45" t="n">
-        <v>8.9</v>
+        <v>9.1</v>
       </c>
       <c r="J45" t="n">
-        <v>41.6</v>
+        <v>40.8</v>
       </c>
       <c r="K45" t="n">
-        <v>74.09999999999999</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="M45" t="n">
-        <v>7.4</v>
+        <v>5.6</v>
       </c>
       <c r="N45" t="n">
-        <v>35</v>
+        <v>33.1</v>
       </c>
       <c r="O45" t="n">
-        <v>42.4</v>
+        <v>38.7</v>
       </c>
       <c r="Q45" t="n">
-        <v>21.7</v>
+        <v>22</v>
       </c>
       <c r="R45" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>21.7</v>
+        <v>22</v>
       </c>
       <c r="V45" t="n">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="W45" t="n">
-        <v>24.1</v>
+        <v>22.9</v>
       </c>
       <c r="X45" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA45" t="n">
         <v>16.1</v>
       </c>
-      <c r="Y45" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>19</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>15.6</v>
-      </c>
       <c r="AB45" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="AC45" t="n">
-        <v>9.699999999999999</v>
+        <v>7</v>
       </c>
       <c r="AD45" t="n">
-        <v>6.3</v>
+        <v>4.5</v>
       </c>
       <c r="AF45" t="n">
-        <v>220.84</v>
+        <v>225.87</v>
       </c>
       <c r="AG45" t="n">
-        <v>2.8</v>
+        <v>5.03</v>
       </c>
       <c r="AH45" t="n">
         <v>215</v>
@@ -4899,10 +4902,10 @@
         <v>235</v>
       </c>
       <c r="AK45" t="n">
-        <v>129.07</v>
+        <v>130.73</v>
       </c>
       <c r="AL45" t="n">
-        <v>-0.14</v>
+        <v>1.66</v>
       </c>
       <c r="AM45" t="n">
         <v>110</v>
@@ -4911,99 +4914,54 @@
         <v>142</v>
       </c>
       <c r="AP45" t="n">
-        <v>85.52</v>
+        <v>88.2</v>
       </c>
       <c r="AS45" t="n">
-        <v>15.82</v>
+        <v>15.76</v>
       </c>
       <c r="BL45" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B46" t="n">
-        <v>146.8</v>
-      </c>
-      <c r="C46" t="n">
-        <v>52.8</v>
+        <v>133.9</v>
       </c>
       <c r="D46" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="E46" t="n">
-        <v>28.9</v>
+        <v>34.7</v>
       </c>
       <c r="F46" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="H46" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="I46" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="J46" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="K46" t="n">
-        <v>73.59999999999999</v>
-      </c>
-      <c r="M46" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="N46" t="n">
-        <v>33.1</v>
-      </c>
-      <c r="O46" t="n">
-        <v>38.7</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>22</v>
-      </c>
-      <c r="R46" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="S46" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" t="n">
-        <v>22</v>
+        <v>3.3</v>
       </c>
       <c r="V46" t="n">
-        <v>11</v>
+        <v>14.3</v>
       </c>
       <c r="W46" t="n">
-        <v>22.9</v>
+        <v>21.7</v>
       </c>
       <c r="X46" t="n">
-        <v>16.9</v>
+        <v>18</v>
       </c>
       <c r="Y46" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z46" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AA46" t="n">
-        <v>16.1</v>
+        <v>15</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.9</v>
+        <v>-3.5</v>
       </c>
       <c r="AC46" t="n">
-        <v>7</v>
+        <v>3.2</v>
       </c>
       <c r="AD46" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>225.87</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>5.03</v>
+        <v>-0.1</v>
       </c>
       <c r="AH46" t="n">
         <v>215</v>
@@ -5011,67 +4969,55 @@
       <c r="AI46" t="n">
         <v>235</v>
       </c>
-      <c r="AK46" t="n">
-        <v>130.73</v>
-      </c>
-      <c r="AL46" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AM46" t="n">
         <v>110</v>
       </c>
       <c r="AN46" t="n">
         <v>142</v>
       </c>
-      <c r="AP46" t="n">
-        <v>88.2</v>
-      </c>
-      <c r="AS46" t="n">
-        <v>15.76</v>
-      </c>
       <c r="BL46" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B47" t="n">
-        <v>133.9</v>
+        <v>137.5</v>
       </c>
       <c r="D47" t="n">
-        <v>34.7</v>
+        <v>32.8</v>
       </c>
       <c r="F47" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="V47" t="n">
-        <v>14.3</v>
+        <v>9</v>
       </c>
       <c r="W47" t="n">
-        <v>21.7</v>
+        <v>15.7</v>
       </c>
       <c r="X47" t="n">
-        <v>18</v>
+        <v>12.3</v>
       </c>
       <c r="Y47" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z47" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="AA47" t="n">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="AB47" t="n">
-        <v>-3.5</v>
+        <v>-6.6</v>
       </c>
       <c r="AC47" t="n">
-        <v>3.2</v>
+        <v>8.1</v>
       </c>
       <c r="AD47" t="n">
-        <v>-0.1</v>
+        <v>0.8</v>
       </c>
       <c r="AH47" t="n">
         <v>215</v>
@@ -5086,48 +5032,93 @@
         <v>142</v>
       </c>
       <c r="BL47" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B48" t="n">
-        <v>137.5</v>
+        <v>157.1</v>
+      </c>
+      <c r="C48" t="n">
+        <v>73.09999999999999</v>
       </c>
       <c r="D48" t="n">
-        <v>32.8</v>
+        <v>31.7</v>
+      </c>
+      <c r="E48" t="n">
+        <v>26.1</v>
       </c>
       <c r="F48" t="n">
-        <v>2.3</v>
+        <v>2</v>
+      </c>
+      <c r="H48" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="I48" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="J48" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="K48" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="M48" t="n">
+        <v>6</v>
+      </c>
+      <c r="N48" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="O48" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="R48" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>23.8</v>
       </c>
       <c r="V48" t="n">
-        <v>9</v>
+        <v>6.8</v>
       </c>
       <c r="W48" t="n">
-        <v>15.7</v>
+        <v>11</v>
       </c>
       <c r="X48" t="n">
-        <v>12.3</v>
+        <v>8.9</v>
       </c>
       <c r="Y48" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="Z48" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA48" t="n">
-        <v>10.5</v>
+        <v>7.9</v>
       </c>
       <c r="AB48" t="n">
-        <v>-6.6</v>
+        <v>-1.2</v>
       </c>
       <c r="AC48" t="n">
-        <v>8.1</v>
+        <v>12.6</v>
       </c>
       <c r="AD48" t="n">
-        <v>0.8</v>
+        <v>5.7</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>224.2</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>-1.67</v>
       </c>
       <c r="AH48" t="n">
         <v>215</v>
@@ -5135,100 +5126,112 @@
       <c r="AI48" t="n">
         <v>235</v>
       </c>
+      <c r="AK48" t="n">
+        <v>128.6</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>-2.13</v>
+      </c>
       <c r="AM48" t="n">
         <v>110</v>
       </c>
       <c r="AN48" t="n">
         <v>142</v>
       </c>
+      <c r="AP48" t="n">
+        <v>81.18000000000001</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>14.06</v>
+      </c>
       <c r="BL48" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B49" t="n">
-        <v>157.1</v>
+        <v>153.1</v>
       </c>
       <c r="C49" t="n">
-        <v>73.09999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="D49" t="n">
-        <v>31.7</v>
+        <v>32.2</v>
       </c>
       <c r="E49" t="n">
-        <v>26.1</v>
+        <v>25.9</v>
       </c>
       <c r="F49" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="H49" t="n">
-        <v>23.6</v>
+        <v>24.4</v>
       </c>
       <c r="I49" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="J49" t="n">
-        <v>40.5</v>
+        <v>39.6</v>
       </c>
       <c r="K49" t="n">
-        <v>73.5</v>
+        <v>73.3</v>
       </c>
       <c r="M49" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="N49" t="n">
-        <v>33.4</v>
+        <v>34.4</v>
       </c>
       <c r="O49" t="n">
-        <v>39.5</v>
+        <v>40.1</v>
       </c>
       <c r="Q49" t="n">
         <v>23.8</v>
       </c>
       <c r="R49" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T49" t="n">
         <v>23.8</v>
       </c>
       <c r="V49" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="W49" t="n">
-        <v>11</v>
+        <v>15.2</v>
       </c>
       <c r="X49" t="n">
-        <v>8.9</v>
+        <v>10.9</v>
       </c>
       <c r="Y49" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Z49" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA49" t="n">
         <v>12</v>
       </c>
-      <c r="AA49" t="n">
-        <v>7.9</v>
-      </c>
       <c r="AB49" t="n">
-        <v>-1.2</v>
+        <v>1.7</v>
       </c>
       <c r="AC49" t="n">
-        <v>12.6</v>
+        <v>10</v>
       </c>
       <c r="AD49" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AF49" t="n">
-        <v>224.2</v>
+        <v>223.35</v>
       </c>
       <c r="AG49" t="n">
-        <v>-1.67</v>
+        <v>-0.85</v>
       </c>
       <c r="AH49" t="n">
         <v>215</v>
@@ -5237,10 +5240,10 @@
         <v>235</v>
       </c>
       <c r="AK49" t="n">
-        <v>128.6</v>
+        <v>127.19</v>
       </c>
       <c r="AL49" t="n">
-        <v>-2.13</v>
+        <v>-1.41</v>
       </c>
       <c r="AM49" t="n">
         <v>110</v>
@@ -5249,99 +5252,99 @@
         <v>142</v>
       </c>
       <c r="AP49" t="n">
-        <v>81.18000000000001</v>
+        <v>81.06</v>
       </c>
       <c r="AS49" t="n">
-        <v>14.06</v>
+        <v>13.63</v>
       </c>
       <c r="BL49" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B50" t="n">
-        <v>153.1</v>
+        <v>145.5</v>
       </c>
       <c r="C50" t="n">
-        <v>69.59999999999999</v>
+        <v>62.3</v>
       </c>
       <c r="D50" t="n">
-        <v>32.2</v>
+        <v>34</v>
       </c>
       <c r="E50" t="n">
-        <v>25.9</v>
+        <v>22.5</v>
       </c>
       <c r="F50" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="H50" t="n">
-        <v>24.4</v>
+        <v>24.8</v>
       </c>
       <c r="I50" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J50" t="n">
-        <v>39.6</v>
+        <v>40.8</v>
       </c>
       <c r="K50" t="n">
-        <v>73.3</v>
+        <v>75</v>
       </c>
       <c r="M50" t="n">
-        <v>5.7</v>
+        <v>6.9</v>
       </c>
       <c r="N50" t="n">
-        <v>34.4</v>
+        <v>30.4</v>
       </c>
       <c r="O50" t="n">
-        <v>40.1</v>
+        <v>37.3</v>
       </c>
       <c r="Q50" t="n">
-        <v>23.8</v>
+        <v>22.1</v>
       </c>
       <c r="R50" t="n">
-        <v>3.8</v>
+        <v>4.9</v>
       </c>
       <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="V50" t="n">
         <v>4</v>
       </c>
-      <c r="T50" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="V50" t="n">
-        <v>6.6</v>
-      </c>
       <c r="W50" t="n">
-        <v>15.2</v>
+        <v>22.9</v>
       </c>
       <c r="X50" t="n">
-        <v>10.9</v>
+        <v>13.4</v>
       </c>
       <c r="Y50" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="Z50" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AA50" t="n">
-        <v>12</v>
+        <v>12.9</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="AC50" t="n">
-        <v>10</v>
+        <v>12.7</v>
       </c>
       <c r="AD50" t="n">
-        <v>5.8</v>
+        <v>6.7</v>
       </c>
       <c r="AF50" t="n">
-        <v>223.35</v>
+        <v>223.06</v>
       </c>
       <c r="AG50" t="n">
-        <v>-0.85</v>
+        <v>-0.29</v>
       </c>
       <c r="AH50" t="n">
         <v>215</v>
@@ -5350,10 +5353,10 @@
         <v>235</v>
       </c>
       <c r="AK50" t="n">
-        <v>127.19</v>
+        <v>129.17</v>
       </c>
       <c r="AL50" t="n">
-        <v>-1.41</v>
+        <v>1.98</v>
       </c>
       <c r="AM50" t="n">
         <v>110</v>
@@ -5362,96 +5365,96 @@
         <v>142</v>
       </c>
       <c r="AP50" t="n">
-        <v>81.06</v>
+        <v>82.36</v>
       </c>
       <c r="AS50" t="n">
-        <v>13.63</v>
+        <v>13.91</v>
       </c>
       <c r="BL50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B51" t="n">
-        <v>145.5</v>
+        <v>148</v>
       </c>
       <c r="C51" t="n">
-        <v>62.3</v>
+        <v>61.6</v>
       </c>
       <c r="D51" t="n">
-        <v>34</v>
+        <v>33.9</v>
       </c>
       <c r="E51" t="n">
-        <v>22.5</v>
+        <v>25</v>
       </c>
       <c r="F51" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="H51" t="n">
-        <v>24.8</v>
+        <v>25.1</v>
       </c>
       <c r="I51" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="J51" t="n">
-        <v>40.8</v>
+        <v>39.5</v>
       </c>
       <c r="K51" t="n">
-        <v>75</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="M51" t="n">
-        <v>6.9</v>
+        <v>5.9</v>
       </c>
       <c r="N51" t="n">
-        <v>30.4</v>
+        <v>28.6</v>
       </c>
       <c r="O51" t="n">
-        <v>37.3</v>
+        <v>34.5</v>
       </c>
       <c r="Q51" t="n">
-        <v>22.1</v>
+        <v>23.3</v>
       </c>
       <c r="R51" t="n">
-        <v>4.9</v>
+        <v>3.9</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>22.1</v>
+        <v>23.3</v>
       </c>
       <c r="V51" t="n">
-        <v>4</v>
+        <v>7.8</v>
       </c>
       <c r="W51" t="n">
-        <v>22.9</v>
+        <v>26</v>
       </c>
       <c r="X51" t="n">
-        <v>13.4</v>
+        <v>16.9</v>
       </c>
       <c r="Y51" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="Z51" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AA51" t="n">
-        <v>12.9</v>
+        <v>11.6</v>
       </c>
       <c r="AB51" t="n">
-        <v>0.7</v>
+        <v>4.2</v>
       </c>
       <c r="AC51" t="n">
-        <v>12.7</v>
+        <v>11.4</v>
       </c>
       <c r="AD51" t="n">
-        <v>6.7</v>
+        <v>7.8</v>
       </c>
       <c r="AF51" t="n">
-        <v>223.06</v>
+        <v>222.77</v>
       </c>
       <c r="AG51" t="n">
         <v>-0.29</v>
@@ -5463,10 +5466,10 @@
         <v>235</v>
       </c>
       <c r="AK51" t="n">
-        <v>129.17</v>
+        <v>130.42</v>
       </c>
       <c r="AL51" t="n">
-        <v>1.98</v>
+        <v>1.25</v>
       </c>
       <c r="AM51" t="n">
         <v>110</v>
@@ -5475,60 +5478,60 @@
         <v>142</v>
       </c>
       <c r="AP51" t="n">
-        <v>82.36</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="AS51" t="n">
-        <v>13.91</v>
+        <v>14</v>
       </c>
       <c r="BL51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B52" t="n">
-        <v>148</v>
+        <v>135.5</v>
       </c>
       <c r="C52" t="n">
-        <v>61.6</v>
+        <v>47.7</v>
       </c>
       <c r="D52" t="n">
-        <v>33.9</v>
+        <v>34.2</v>
       </c>
       <c r="E52" t="n">
-        <v>25</v>
+        <v>24.1</v>
       </c>
       <c r="F52" t="n">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="H52" t="n">
-        <v>25.1</v>
+        <v>24.9</v>
       </c>
       <c r="I52" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="J52" t="n">
-        <v>39.5</v>
+        <v>38.4</v>
       </c>
       <c r="K52" t="n">
-        <v>74.09999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="M52" t="n">
-        <v>5.9</v>
+        <v>3</v>
       </c>
       <c r="N52" t="n">
-        <v>28.6</v>
+        <v>30.3</v>
       </c>
       <c r="O52" t="n">
-        <v>34.5</v>
+        <v>33.3</v>
       </c>
       <c r="Q52" t="n">
         <v>23.3</v>
       </c>
       <c r="R52" t="n">
-        <v>3.9</v>
+        <v>1</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -5537,37 +5540,37 @@
         <v>23.3</v>
       </c>
       <c r="V52" t="n">
-        <v>7.8</v>
+        <v>11.3</v>
       </c>
       <c r="W52" t="n">
-        <v>26</v>
+        <v>27.6</v>
       </c>
       <c r="X52" t="n">
-        <v>16.9</v>
+        <v>19.5</v>
       </c>
       <c r="Y52" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Z52" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="AA52" t="n">
-        <v>11.6</v>
+        <v>18.8</v>
       </c>
       <c r="AB52" t="n">
-        <v>4.2</v>
+        <v>1.8</v>
       </c>
       <c r="AC52" t="n">
-        <v>11.4</v>
+        <v>15.5</v>
       </c>
       <c r="AD52" t="n">
-        <v>7.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AF52" t="n">
-        <v>222.77</v>
+        <v>221.86</v>
       </c>
       <c r="AG52" t="n">
-        <v>-0.29</v>
+        <v>-0.91</v>
       </c>
       <c r="AH52" t="n">
         <v>215</v>
@@ -5576,10 +5579,10 @@
         <v>235</v>
       </c>
       <c r="AK52" t="n">
-        <v>130.42</v>
+        <v>129.71</v>
       </c>
       <c r="AL52" t="n">
-        <v>1.25</v>
+        <v>-0.71</v>
       </c>
       <c r="AM52" t="n">
         <v>110</v>
@@ -5588,99 +5591,54 @@
         <v>142</v>
       </c>
       <c r="AP52" t="n">
-        <v>80.90000000000001</v>
+        <v>86.42</v>
       </c>
       <c r="AS52" t="n">
-        <v>14</v>
+        <v>16.05</v>
       </c>
       <c r="BL52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B53" t="n">
-        <v>135.5</v>
-      </c>
-      <c r="C53" t="n">
-        <v>47.7</v>
+        <v>118.1</v>
       </c>
       <c r="D53" t="n">
-        <v>34.2</v>
-      </c>
-      <c r="E53" t="n">
-        <v>24.1</v>
+        <v>34.7</v>
       </c>
       <c r="F53" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H53" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="I53" t="n">
-        <v>10</v>
-      </c>
-      <c r="J53" t="n">
-        <v>38.4</v>
-      </c>
-      <c r="K53" t="n">
-        <v>73.2</v>
-      </c>
-      <c r="M53" t="n">
-        <v>3</v>
-      </c>
-      <c r="N53" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="O53" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="R53" t="n">
-        <v>1</v>
-      </c>
-      <c r="S53" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" t="n">
-        <v>23.3</v>
+        <v>3.3</v>
       </c>
       <c r="V53" t="n">
-        <v>11.3</v>
+        <v>14.1</v>
       </c>
       <c r="W53" t="n">
         <v>27.6</v>
       </c>
       <c r="X53" t="n">
-        <v>19.5</v>
+        <v>20.9</v>
       </c>
       <c r="Y53" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Z53" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA53" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="AC53" t="n">
-        <v>15.5</v>
+        <v>14.9</v>
       </c>
       <c r="AD53" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="AF53" t="n">
-        <v>221.86</v>
-      </c>
-      <c r="AG53" t="n">
-        <v>-0.91</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AH53" t="n">
         <v>215</v>
@@ -5688,67 +5646,55 @@
       <c r="AI53" t="n">
         <v>235</v>
       </c>
-      <c r="AK53" t="n">
-        <v>129.71</v>
-      </c>
-      <c r="AL53" t="n">
-        <v>-0.71</v>
-      </c>
       <c r="AM53" t="n">
         <v>110</v>
       </c>
       <c r="AN53" t="n">
         <v>142</v>
       </c>
-      <c r="AP53" t="n">
-        <v>86.42</v>
-      </c>
-      <c r="AS53" t="n">
-        <v>16.05</v>
-      </c>
       <c r="BL53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B54" t="n">
-        <v>118.1</v>
+        <v>100.3</v>
       </c>
       <c r="D54" t="n">
-        <v>34.7</v>
+        <v>34</v>
       </c>
       <c r="F54" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="V54" t="n">
-        <v>14.1</v>
+        <v>16</v>
       </c>
       <c r="W54" t="n">
-        <v>27.6</v>
+        <v>30.6</v>
       </c>
       <c r="X54" t="n">
-        <v>20.9</v>
+        <v>23.3</v>
       </c>
       <c r="Y54" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z54" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA54" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AB54" t="n">
-        <v>3.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC54" t="n">
-        <v>14.9</v>
+        <v>16.7</v>
       </c>
       <c r="AD54" t="n">
-        <v>9.199999999999999</v>
+        <v>12.8</v>
       </c>
       <c r="AH54" t="n">
         <v>215</v>
@@ -5763,48 +5709,93 @@
         <v>142</v>
       </c>
       <c r="BL54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="B55" t="n">
-        <v>100.3</v>
+        <v>104.9</v>
+      </c>
+      <c r="C55" t="n">
+        <v>36.3</v>
       </c>
       <c r="D55" t="n">
-        <v>34</v>
+        <v>32.7</v>
+      </c>
+      <c r="E55" t="n">
+        <v>17</v>
       </c>
       <c r="F55" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
+      </c>
+      <c r="H55" t="n">
+        <v>16</v>
+      </c>
+      <c r="I55" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="J55" t="n">
+        <v>25</v>
+      </c>
+      <c r="K55" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="M55" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N55" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="O55" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>10.5</v>
       </c>
       <c r="V55" t="n">
-        <v>16</v>
+        <v>15.8</v>
       </c>
       <c r="W55" t="n">
-        <v>30.6</v>
+        <v>33.6</v>
       </c>
       <c r="X55" t="n">
-        <v>23.3</v>
+        <v>24.7</v>
       </c>
       <c r="Y55" t="n">
         <v>16</v>
       </c>
       <c r="Z55" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA55" t="n">
-        <v>20</v>
+        <v>16.9</v>
       </c>
       <c r="AB55" t="n">
-        <v>8.800000000000001</v>
+        <v>4</v>
       </c>
       <c r="AC55" t="n">
-        <v>16.7</v>
+        <v>10.1</v>
       </c>
       <c r="AD55" t="n">
-        <v>12.8</v>
+        <v>7</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>234.9</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>13.04</v>
       </c>
       <c r="AH55" t="n">
         <v>215</v>
@@ -5812,58 +5803,70 @@
       <c r="AI55" t="n">
         <v>235</v>
       </c>
+      <c r="AK55" t="n">
+        <v>137.51</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>7.8</v>
+      </c>
       <c r="AM55" t="n">
         <v>110</v>
       </c>
       <c r="AN55" t="n">
         <v>142</v>
       </c>
+      <c r="AP55" t="n">
+        <v>94</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>18.87</v>
+      </c>
       <c r="BL55" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="B56" t="n">
-        <v>104.9</v>
+        <v>134.9</v>
       </c>
       <c r="C56" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="D56" t="n">
         <v>36.3</v>
       </c>
-      <c r="D56" t="n">
-        <v>32.7</v>
-      </c>
       <c r="E56" t="n">
-        <v>17</v>
+        <v>20.6</v>
       </c>
       <c r="F56" t="n">
         <v>1.6</v>
       </c>
       <c r="H56" t="n">
-        <v>16</v>
+        <v>21.2</v>
       </c>
       <c r="I56" t="n">
-        <v>10.1</v>
+        <v>9.4</v>
       </c>
       <c r="J56" t="n">
-        <v>25</v>
+        <v>35.4</v>
       </c>
       <c r="K56" t="n">
-        <v>51.2</v>
+        <v>66</v>
       </c>
       <c r="M56" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="N56" t="n">
-        <v>25.5</v>
+        <v>24.8</v>
       </c>
       <c r="O56" t="n">
-        <v>27.3</v>
+        <v>26.7</v>
       </c>
       <c r="Q56" t="n">
-        <v>10.5</v>
+        <v>18.3</v>
       </c>
       <c r="R56" t="n">
         <v>0</v>
@@ -5872,22 +5875,22 @@
         <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>10.5</v>
+        <v>18.3</v>
       </c>
       <c r="Y56" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="Z56" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AA56" t="n">
-        <v>16.9</v>
+        <v>13.8</v>
       </c>
       <c r="AF56" t="n">
-        <v>234.9</v>
+        <v>229.2</v>
       </c>
       <c r="AG56" t="n">
-        <v>13.04</v>
+        <v>-5.7</v>
       </c>
       <c r="AH56" t="n">
         <v>215</v>
@@ -5896,10 +5899,10 @@
         <v>235</v>
       </c>
       <c r="AK56" t="n">
-        <v>137.51</v>
+        <v>138.98</v>
       </c>
       <c r="AL56" t="n">
-        <v>7.8</v>
+        <v>1.47</v>
       </c>
       <c r="AM56" t="n">
         <v>110</v>
@@ -5908,57 +5911,57 @@
         <v>142</v>
       </c>
       <c r="AP56" t="n">
-        <v>94</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="AS56" t="n">
-        <v>18.87</v>
+        <v>16.02</v>
       </c>
       <c r="BL56" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B57" t="n">
-        <v>134.9</v>
+        <v>146.4</v>
       </c>
       <c r="C57" t="n">
-        <v>53.3</v>
+        <v>60.2</v>
       </c>
       <c r="D57" t="n">
-        <v>36.3</v>
+        <v>35.6</v>
       </c>
       <c r="E57" t="n">
-        <v>20.6</v>
+        <v>24.2</v>
       </c>
       <c r="F57" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="H57" t="n">
-        <v>21.2</v>
+        <v>23</v>
       </c>
       <c r="I57" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J57" t="n">
-        <v>35.4</v>
+        <v>38.2</v>
       </c>
       <c r="K57" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="M57" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="N57" t="n">
-        <v>24.8</v>
+        <v>30.2</v>
       </c>
       <c r="O57" t="n">
-        <v>26.7</v>
+        <v>31.9</v>
       </c>
       <c r="Q57" t="n">
-        <v>18.3</v>
+        <v>20.2</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
@@ -5967,22 +5970,22 @@
         <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>18.3</v>
+        <v>20.2</v>
       </c>
       <c r="Y57" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="Z57" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AA57" t="n">
-        <v>13.8</v>
+        <v>9.6</v>
       </c>
       <c r="AF57" t="n">
-        <v>229.2</v>
+        <v>224.9</v>
       </c>
       <c r="AG57" t="n">
-        <v>-5.7</v>
+        <v>-4.3</v>
       </c>
       <c r="AH57" t="n">
         <v>215</v>
@@ -5991,10 +5994,10 @@
         <v>235</v>
       </c>
       <c r="AK57" t="n">
-        <v>138.98</v>
+        <v>134.04</v>
       </c>
       <c r="AL57" t="n">
-        <v>1.47</v>
+        <v>-4.94</v>
       </c>
       <c r="AM57" t="n">
         <v>110</v>
@@ -6003,57 +6006,57 @@
         <v>142</v>
       </c>
       <c r="AP57" t="n">
-        <v>84.90000000000001</v>
+        <v>76.5</v>
       </c>
       <c r="AS57" t="n">
-        <v>16.02</v>
+        <v>13.68</v>
       </c>
       <c r="BL57" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B58" t="n">
-        <v>146.4</v>
+        <v>131.4</v>
       </c>
       <c r="C58" t="n">
-        <v>60.2</v>
+        <v>53.7</v>
       </c>
       <c r="D58" t="n">
-        <v>35.6</v>
+        <v>34.7</v>
       </c>
       <c r="E58" t="n">
-        <v>24.2</v>
+        <v>20.1</v>
       </c>
       <c r="F58" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="H58" t="n">
-        <v>23</v>
+        <v>24.1</v>
       </c>
       <c r="I58" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J58" t="n">
-        <v>38.2</v>
+        <v>37</v>
       </c>
       <c r="K58" t="n">
-        <v>70</v>
+        <v>69.8</v>
       </c>
       <c r="M58" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="N58" t="n">
-        <v>30.2</v>
+        <v>31.4</v>
       </c>
       <c r="O58" t="n">
-        <v>31.9</v>
+        <v>33.3</v>
       </c>
       <c r="Q58" t="n">
-        <v>20.2</v>
+        <v>22.3</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
@@ -6062,22 +6065,22 @@
         <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>20.2</v>
+        <v>22.3</v>
       </c>
       <c r="Y58" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z58" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AA58" t="n">
-        <v>9.6</v>
+        <v>14</v>
       </c>
       <c r="AF58" t="n">
-        <v>224.9</v>
+        <v>220.8</v>
       </c>
       <c r="AG58" t="n">
-        <v>-4.3</v>
+        <v>-4.1</v>
       </c>
       <c r="AH58" t="n">
         <v>215</v>
@@ -6086,10 +6089,10 @@
         <v>235</v>
       </c>
       <c r="AK58" t="n">
-        <v>134.04</v>
+        <v>131.01</v>
       </c>
       <c r="AL58" t="n">
-        <v>-4.94</v>
+        <v>-3.03</v>
       </c>
       <c r="AM58" t="n">
         <v>110</v>
@@ -6098,57 +6101,57 @@
         <v>142</v>
       </c>
       <c r="AP58" t="n">
-        <v>76.5</v>
+        <v>81.28</v>
       </c>
       <c r="AS58" t="n">
-        <v>13.68</v>
+        <v>13.92</v>
       </c>
       <c r="BL58" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B59" t="n">
-        <v>131.4</v>
+        <v>127.2</v>
       </c>
       <c r="C59" t="n">
-        <v>53.7</v>
+        <v>42.7</v>
       </c>
       <c r="D59" t="n">
-        <v>34.7</v>
+        <v>34.6</v>
       </c>
       <c r="E59" t="n">
-        <v>20.1</v>
+        <v>20.7</v>
       </c>
       <c r="F59" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="H59" t="n">
-        <v>24.1</v>
+        <v>21.2</v>
       </c>
       <c r="I59" t="n">
-        <v>8.6</v>
+        <v>9.1</v>
       </c>
       <c r="J59" t="n">
-        <v>37</v>
+        <v>36.8</v>
       </c>
       <c r="K59" t="n">
-        <v>69.8</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="M59" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="N59" t="n">
-        <v>31.4</v>
+        <v>27.9</v>
       </c>
       <c r="O59" t="n">
-        <v>33.3</v>
+        <v>29.8</v>
       </c>
       <c r="Q59" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="R59" t="n">
         <v>0</v>
@@ -6157,22 +6160,22 @@
         <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="Y59" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="Z59" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AA59" t="n">
-        <v>14</v>
+        <v>19.7</v>
       </c>
       <c r="AF59" t="n">
-        <v>220.8</v>
+        <v>228.06</v>
       </c>
       <c r="AG59" t="n">
-        <v>-4.1</v>
+        <v>7.26</v>
       </c>
       <c r="AH59" t="n">
         <v>215</v>
@@ -6181,10 +6184,10 @@
         <v>235</v>
       </c>
       <c r="AK59" t="n">
-        <v>131.01</v>
+        <v>131.96</v>
       </c>
       <c r="AL59" t="n">
-        <v>-3.03</v>
+        <v>0.95</v>
       </c>
       <c r="AM59" t="n">
         <v>110</v>
@@ -6193,81 +6196,36 @@
         <v>142</v>
       </c>
       <c r="AP59" t="n">
-        <v>81.28</v>
+        <v>84.34</v>
       </c>
       <c r="AS59" t="n">
-        <v>13.92</v>
+        <v>17.57</v>
       </c>
       <c r="BL59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B60" t="n">
-        <v>127.2</v>
-      </c>
-      <c r="C60" t="n">
-        <v>42.7</v>
+        <v>116.2</v>
       </c>
       <c r="D60" t="n">
-        <v>34.6</v>
-      </c>
-      <c r="E60" t="n">
-        <v>20.7</v>
+        <v>35.4</v>
       </c>
       <c r="F60" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H60" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="I60" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="J60" t="n">
-        <v>36.8</v>
-      </c>
-      <c r="K60" t="n">
-        <v>67.09999999999999</v>
-      </c>
-      <c r="M60" t="n">
-        <v>2</v>
-      </c>
-      <c r="N60" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="O60" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="R60" t="n">
-        <v>0</v>
-      </c>
-      <c r="S60" t="n">
-        <v>0</v>
-      </c>
-      <c r="T60" t="n">
-        <v>22.2</v>
+        <v>4.5</v>
       </c>
       <c r="Y60" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="Z60" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AA60" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="AF60" t="n">
-        <v>228.06</v>
-      </c>
-      <c r="AG60" t="n">
-        <v>7.26</v>
+        <v>21</v>
       </c>
       <c r="AH60" t="n">
         <v>215</v>
@@ -6275,49 +6233,37 @@
       <c r="AI60" t="n">
         <v>235</v>
       </c>
-      <c r="AK60" t="n">
-        <v>131.96</v>
-      </c>
-      <c r="AL60" t="n">
-        <v>0.95</v>
-      </c>
       <c r="AM60" t="n">
         <v>110</v>
       </c>
       <c r="AN60" t="n">
         <v>142</v>
       </c>
-      <c r="AP60" t="n">
-        <v>84.34</v>
-      </c>
-      <c r="AS60" t="n">
-        <v>17.57</v>
-      </c>
       <c r="BL60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B61" t="n">
-        <v>116.2</v>
+        <v>105.5</v>
       </c>
       <c r="D61" t="n">
-        <v>35.4</v>
+        <v>34</v>
       </c>
       <c r="F61" t="n">
         <v>4.5</v>
       </c>
       <c r="Y61" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Z61" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AA61" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AH61" t="n">
         <v>215</v>
@@ -6332,18 +6278,18 @@
         <v>142</v>
       </c>
       <c r="BL61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="B62" t="n">
-        <v>105.5</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="D62" t="n">
-        <v>34</v>
+        <v>33.5</v>
       </c>
       <c r="F62" t="n">
         <v>4.5</v>
@@ -6352,10 +6298,10 @@
         <v>15</v>
       </c>
       <c r="Z62" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AA62" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AH62" t="n">
         <v>215</v>
@@ -6370,7 +6316,7 @@
         <v>142</v>
       </c>
       <c r="BL62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -628,88 +628,88 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B2" t="n">
-        <v>172.9</v>
+        <v>157.5</v>
       </c>
       <c r="C2" t="n">
-        <v>67.59999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="D2" t="n">
-        <v>34.9</v>
+        <v>33.2</v>
       </c>
       <c r="E2" t="n">
-        <v>35.2</v>
+        <v>27.7</v>
       </c>
       <c r="F2" t="n">
-        <v>7.3</v>
+        <v>3.6</v>
       </c>
       <c r="H2" t="n">
-        <v>23.6</v>
+        <v>23.4</v>
       </c>
       <c r="I2" t="n">
         <v>11.3</v>
       </c>
       <c r="J2" t="n">
-        <v>41.7</v>
+        <v>41.4</v>
       </c>
       <c r="K2" t="n">
-        <v>76.7</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="N2" t="n">
-        <v>34.8</v>
+        <v>34.9</v>
       </c>
       <c r="O2" t="n">
-        <v>37.2</v>
+        <v>37.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>19</v>
+        <v>21.6</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T2" t="n">
-        <v>19</v>
+        <v>21.6</v>
       </c>
       <c r="V2" t="n">
-        <v>14.4</v>
+        <v>15.1</v>
       </c>
       <c r="W2" t="n">
-        <v>18.7</v>
+        <v>23.1</v>
       </c>
       <c r="X2" t="n">
-        <v>16.6</v>
+        <v>19.1</v>
       </c>
       <c r="Y2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AA2" t="n">
-        <v>12.5</v>
+        <v>13.6</v>
       </c>
       <c r="AB2" t="n">
-        <v>-4.9</v>
+        <v>-0</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.7</v>
+        <v>1.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>218.6</v>
+        <v>218.84</v>
       </c>
       <c r="AG2" t="n">
-        <v>-9.380000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="AH2" t="n">
         <v>215</v>
@@ -718,10 +718,10 @@
         <v>235</v>
       </c>
       <c r="AK2" t="n">
-        <v>130.39</v>
+        <v>133.09</v>
       </c>
       <c r="AL2" t="n">
-        <v>-4.15</v>
+        <v>2.7</v>
       </c>
       <c r="AM2" t="n">
         <v>110</v>
@@ -730,99 +730,66 @@
         <v>142</v>
       </c>
       <c r="AP2" t="n">
-        <v>78.5</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="AS2" t="n">
-        <v>15.79</v>
+        <v>15.63</v>
       </c>
       <c r="BL2" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B3" t="n">
-        <v>157.5</v>
-      </c>
-      <c r="C3" t="n">
-        <v>68.5</v>
+        <v>137.6</v>
       </c>
       <c r="D3" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="E3" t="n">
-        <v>27.7</v>
+        <v>35</v>
       </c>
       <c r="F3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H3" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="I3" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J3" t="n">
-        <v>41.4</v>
+        <v>6.5</v>
       </c>
       <c r="K3" t="n">
-        <v>76.09999999999999</v>
-      </c>
-      <c r="M3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="N3" t="n">
-        <v>34.9</v>
+        <v>96.7</v>
       </c>
       <c r="O3" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>9</v>
-      </c>
-      <c r="T3" t="n">
-        <v>21.6</v>
+        <v>35.1</v>
       </c>
       <c r="V3" t="n">
-        <v>15.1</v>
+        <v>13.6</v>
       </c>
       <c r="W3" t="n">
-        <v>23.1</v>
+        <v>24.4</v>
       </c>
       <c r="X3" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="Y3" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Z3" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AA3" t="n">
-        <v>13.6</v>
+        <v>17.5</v>
       </c>
       <c r="AB3" t="n">
         <v>-0</v>
       </c>
       <c r="AC3" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="AF3" t="n">
-        <v>218.84</v>
+        <v>221.78</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.25</v>
+        <v>2.94</v>
       </c>
       <c r="AH3" t="n">
         <v>215</v>
@@ -831,10 +798,10 @@
         <v>235</v>
       </c>
       <c r="AK3" t="n">
-        <v>133.09</v>
+        <v>138.76</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.7</v>
+        <v>5.67</v>
       </c>
       <c r="AM3" t="n">
         <v>110</v>
@@ -842,67 +809,61 @@
       <c r="AN3" t="n">
         <v>142</v>
       </c>
-      <c r="AP3" t="n">
-        <v>83.09999999999999</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>15.63</v>
-      </c>
       <c r="BL3" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B4" t="n">
-        <v>137.6</v>
+        <v>132.5</v>
       </c>
       <c r="D4" t="n">
-        <v>35</v>
+        <v>33.6</v>
       </c>
       <c r="F4" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="K4" t="n">
-        <v>96.7</v>
+        <v>97.8</v>
       </c>
       <c r="O4" t="n">
-        <v>35.1</v>
+        <v>31.6</v>
       </c>
       <c r="V4" t="n">
-        <v>13.6</v>
+        <v>14.8</v>
       </c>
       <c r="W4" t="n">
-        <v>24.4</v>
+        <v>24.7</v>
       </c>
       <c r="X4" t="n">
-        <v>19</v>
+        <v>19.8</v>
       </c>
       <c r="Y4" t="n">
         <v>14</v>
       </c>
       <c r="Z4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AA4" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0</v>
+        <v>0.6</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="AF4" t="n">
-        <v>221.78</v>
+        <v>224.78</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="AH4" t="n">
         <v>215</v>
@@ -911,10 +872,10 @@
         <v>235</v>
       </c>
       <c r="AK4" t="n">
-        <v>138.76</v>
+        <v>143.55</v>
       </c>
       <c r="AL4" t="n">
-        <v>5.67</v>
+        <v>4.79</v>
       </c>
       <c r="AM4" t="n">
         <v>110</v>
@@ -923,60 +884,93 @@
         <v>142</v>
       </c>
       <c r="BL4" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B5" t="n">
-        <v>132.5</v>
+        <v>137.2</v>
+      </c>
+      <c r="C5" t="n">
+        <v>56.3</v>
       </c>
       <c r="D5" t="n">
-        <v>33.6</v>
+        <v>32.1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>21.2</v>
       </c>
       <c r="F5" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="I5" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>40.4</v>
       </c>
       <c r="K5" t="n">
-        <v>97.8</v>
+        <v>75.7</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N5" t="n">
+        <v>29</v>
       </c>
       <c r="O5" t="n">
-        <v>31.6</v>
+        <v>32.6</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>21.6</v>
       </c>
       <c r="V5" t="n">
-        <v>14.8</v>
+        <v>10.7</v>
       </c>
       <c r="W5" t="n">
-        <v>24.7</v>
+        <v>24.3</v>
       </c>
       <c r="X5" t="n">
-        <v>19.8</v>
+        <v>17.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Z5" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AA5" t="n">
-        <v>16.5</v>
+        <v>15.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="AF5" t="n">
-        <v>224.78</v>
+        <v>232.22</v>
       </c>
       <c r="AG5" t="n">
-        <v>3</v>
+        <v>7.43</v>
       </c>
       <c r="AH5" t="n">
         <v>215</v>
@@ -985,10 +979,10 @@
         <v>235</v>
       </c>
       <c r="AK5" t="n">
-        <v>143.55</v>
+        <v>143.61</v>
       </c>
       <c r="AL5" t="n">
-        <v>4.79</v>
+        <v>0.06</v>
       </c>
       <c r="AM5" t="n">
         <v>110</v>
@@ -996,52 +990,58 @@
       <c r="AN5" t="n">
         <v>142</v>
       </c>
+      <c r="AP5" t="n">
+        <v>89.31999999999999</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>18.02</v>
+      </c>
       <c r="BL5" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="B6" t="n">
-        <v>137.2</v>
+        <v>157.5</v>
       </c>
       <c r="C6" t="n">
-        <v>56.3</v>
+        <v>59.6</v>
       </c>
       <c r="D6" t="n">
-        <v>32.1</v>
+        <v>35</v>
       </c>
       <c r="E6" t="n">
-        <v>21.2</v>
+        <v>30.6</v>
       </c>
       <c r="F6" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="H6" t="n">
-        <v>23.7</v>
+        <v>24.2</v>
       </c>
       <c r="I6" t="n">
-        <v>11.6</v>
+        <v>11.2</v>
       </c>
       <c r="J6" t="n">
-        <v>40.4</v>
+        <v>38.9</v>
       </c>
       <c r="K6" t="n">
-        <v>75.7</v>
+        <v>74.3</v>
       </c>
       <c r="M6" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="N6" t="n">
-        <v>29</v>
+        <v>33.4</v>
       </c>
       <c r="O6" t="n">
-        <v>32.6</v>
+        <v>37.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="R6" t="n">
         <v>1.3</v>
@@ -1050,40 +1050,40 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="V6" t="n">
-        <v>10.7</v>
+        <v>13</v>
       </c>
       <c r="W6" t="n">
-        <v>24.3</v>
+        <v>26.3</v>
       </c>
       <c r="X6" t="n">
-        <v>17.5</v>
+        <v>19.6</v>
       </c>
       <c r="Y6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA6" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.9</v>
+        <v>-2.1</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="AF6" t="n">
-        <v>232.22</v>
+        <v>229.69</v>
       </c>
       <c r="AG6" t="n">
-        <v>7.43</v>
+        <v>-2.53</v>
       </c>
       <c r="AH6" t="n">
         <v>215</v>
@@ -1092,10 +1092,10 @@
         <v>235</v>
       </c>
       <c r="AK6" t="n">
-        <v>143.61</v>
+        <v>136.96</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.06</v>
+        <v>-6.65</v>
       </c>
       <c r="AM6" t="n">
         <v>110</v>
@@ -1104,99 +1104,99 @@
         <v>142</v>
       </c>
       <c r="AP6" t="n">
-        <v>89.31999999999999</v>
+        <v>86.59</v>
       </c>
       <c r="AS6" t="n">
-        <v>18.02</v>
+        <v>16.96</v>
       </c>
       <c r="BL6" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B7" t="n">
-        <v>157.5</v>
+        <v>159.6</v>
       </c>
       <c r="C7" t="n">
-        <v>59.6</v>
+        <v>63</v>
       </c>
       <c r="D7" t="n">
-        <v>35</v>
+        <v>34.5</v>
       </c>
       <c r="E7" t="n">
-        <v>30.6</v>
+        <v>31.1</v>
       </c>
       <c r="F7" t="n">
-        <v>7.5</v>
+        <v>5.7</v>
       </c>
       <c r="H7" t="n">
-        <v>24.2</v>
+        <v>23.8</v>
       </c>
       <c r="I7" t="n">
-        <v>11.2</v>
+        <v>10.8</v>
       </c>
       <c r="J7" t="n">
-        <v>38.9</v>
+        <v>40.5</v>
       </c>
       <c r="K7" t="n">
-        <v>74.3</v>
+        <v>75.2</v>
       </c>
       <c r="M7" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="N7" t="n">
-        <v>33.4</v>
+        <v>34.3</v>
       </c>
       <c r="O7" t="n">
-        <v>37.1</v>
+        <v>38.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T7" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="V7" t="n">
-        <v>13</v>
+        <v>17.5</v>
       </c>
       <c r="W7" t="n">
-        <v>26.3</v>
+        <v>22.5</v>
       </c>
       <c r="X7" t="n">
-        <v>19.6</v>
+        <v>20</v>
       </c>
       <c r="Y7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA7" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>-2.1</v>
+        <v>-2.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="AF7" t="n">
-        <v>229.69</v>
+        <v>228.57</v>
       </c>
       <c r="AG7" t="n">
-        <v>-2.53</v>
+        <v>-1.14</v>
       </c>
       <c r="AH7" t="n">
         <v>215</v>
@@ -1205,10 +1205,10 @@
         <v>235</v>
       </c>
       <c r="AK7" t="n">
-        <v>136.96</v>
+        <v>133.01</v>
       </c>
       <c r="AL7" t="n">
-        <v>-6.65</v>
+        <v>-3.95</v>
       </c>
       <c r="AM7" t="n">
         <v>110</v>
@@ -1217,99 +1217,99 @@
         <v>142</v>
       </c>
       <c r="AP7" t="n">
-        <v>86.59</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="AS7" t="n">
-        <v>16.96</v>
+        <v>15.95</v>
       </c>
       <c r="BL7" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B8" t="n">
-        <v>159.6</v>
+        <v>160.4</v>
       </c>
       <c r="C8" t="n">
-        <v>63</v>
+        <v>62.6</v>
       </c>
       <c r="D8" t="n">
-        <v>34.5</v>
+        <v>35</v>
       </c>
       <c r="E8" t="n">
-        <v>31.1</v>
+        <v>32.2</v>
       </c>
       <c r="F8" t="n">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="H8" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="I8" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="J8" t="n">
-        <v>40.5</v>
+        <v>41.1</v>
       </c>
       <c r="K8" t="n">
-        <v>75.2</v>
+        <v>75.7</v>
       </c>
       <c r="M8" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="N8" t="n">
-        <v>34.3</v>
+        <v>32.6</v>
       </c>
       <c r="O8" t="n">
-        <v>38.2</v>
+        <v>38</v>
       </c>
       <c r="Q8" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T8" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="V8" t="n">
-        <v>17.5</v>
+        <v>16.4</v>
       </c>
       <c r="W8" t="n">
-        <v>22.5</v>
+        <v>22.8</v>
       </c>
       <c r="X8" t="n">
-        <v>20</v>
+        <v>19.6</v>
       </c>
       <c r="Y8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Z8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA8" t="n">
-        <v>13.5</v>
+        <v>14.1</v>
       </c>
       <c r="AB8" t="n">
-        <v>-2.2</v>
+        <v>-3.1</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="AF8" t="n">
-        <v>228.57</v>
+        <v>225.08</v>
       </c>
       <c r="AG8" t="n">
-        <v>-1.14</v>
+        <v>-3.5</v>
       </c>
       <c r="AH8" t="n">
         <v>215</v>
@@ -1318,10 +1318,10 @@
         <v>235</v>
       </c>
       <c r="AK8" t="n">
-        <v>133.01</v>
+        <v>135.24</v>
       </c>
       <c r="AL8" t="n">
-        <v>-3.95</v>
+        <v>2.23</v>
       </c>
       <c r="AM8" t="n">
         <v>110</v>
@@ -1330,99 +1330,99 @@
         <v>142</v>
       </c>
       <c r="AP8" t="n">
-        <v>84.59999999999999</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="AS8" t="n">
-        <v>15.95</v>
+        <v>15.4</v>
       </c>
       <c r="BL8" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B9" t="n">
-        <v>160.4</v>
+        <v>161.7</v>
       </c>
       <c r="C9" t="n">
-        <v>62.6</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>35</v>
+        <v>34.9</v>
       </c>
       <c r="E9" t="n">
-        <v>32.2</v>
+        <v>27.3</v>
       </c>
       <c r="F9" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H9" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="I9" t="n">
-        <v>10.7</v>
+        <v>10.3</v>
       </c>
       <c r="J9" t="n">
-        <v>41.1</v>
+        <v>42.6</v>
       </c>
       <c r="K9" t="n">
-        <v>75.7</v>
+        <v>77</v>
       </c>
       <c r="M9" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="N9" t="n">
-        <v>32.6</v>
+        <v>31.5</v>
       </c>
       <c r="O9" t="n">
-        <v>38</v>
+        <v>37.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="R9" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T9" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="V9" t="n">
-        <v>16.4</v>
+        <v>12.7</v>
       </c>
       <c r="W9" t="n">
-        <v>22.8</v>
+        <v>27</v>
       </c>
       <c r="X9" t="n">
-        <v>19.6</v>
+        <v>19.9</v>
       </c>
       <c r="Y9" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Z9" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AA9" t="n">
-        <v>14.1</v>
+        <v>11.4</v>
       </c>
       <c r="AB9" t="n">
-        <v>-3.1</v>
+        <v>-5.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.6</v>
+        <v>-0.3</v>
       </c>
       <c r="AF9" t="n">
-        <v>225.08</v>
+        <v>225</v>
       </c>
       <c r="AG9" t="n">
-        <v>-3.5</v>
+        <v>-0.08</v>
       </c>
       <c r="AH9" t="n">
         <v>215</v>
@@ -1431,10 +1431,10 @@
         <v>235</v>
       </c>
       <c r="AK9" t="n">
-        <v>135.24</v>
+        <v>134.62</v>
       </c>
       <c r="AL9" t="n">
-        <v>2.23</v>
+        <v>-0.62</v>
       </c>
       <c r="AM9" t="n">
         <v>110</v>
@@ -1443,99 +1443,60 @@
         <v>142</v>
       </c>
       <c r="AP9" t="n">
-        <v>84.09999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="AS9" t="n">
-        <v>15.4</v>
+        <v>13.86</v>
       </c>
       <c r="BL9" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B10" t="n">
-        <v>161.7</v>
-      </c>
-      <c r="C10" t="n">
-        <v>71.09999999999999</v>
+        <v>151.5</v>
       </c>
       <c r="D10" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="E10" t="n">
-        <v>27.3</v>
+        <v>35.1</v>
       </c>
       <c r="F10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H10" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I10" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="J10" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="K10" t="n">
-        <v>77</v>
-      </c>
-      <c r="M10" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="N10" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="O10" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>21</v>
-      </c>
-      <c r="R10" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="S10" t="n">
-        <v>6</v>
-      </c>
-      <c r="T10" t="n">
-        <v>21</v>
+        <v>5.4</v>
       </c>
       <c r="V10" t="n">
-        <v>12.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>27</v>
+        <v>19.4</v>
       </c>
       <c r="X10" t="n">
-        <v>19.9</v>
+        <v>14</v>
       </c>
       <c r="Y10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA10" t="n">
         <v>9</v>
       </c>
-      <c r="Z10" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>11.4</v>
-      </c>
       <c r="AB10" t="n">
-        <v>-5.2</v>
+        <v>-4.7</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.6</v>
+        <v>1.9</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0.3</v>
+        <v>-1.4</v>
       </c>
       <c r="AF10" t="n">
-        <v>225</v>
+        <v>221.37</v>
       </c>
       <c r="AG10" t="n">
-        <v>-0.08</v>
+        <v>0.05</v>
       </c>
       <c r="AH10" t="n">
         <v>215</v>
@@ -1544,10 +1505,10 @@
         <v>235</v>
       </c>
       <c r="AK10" t="n">
-        <v>134.62</v>
+        <v>135.21</v>
       </c>
       <c r="AL10" t="n">
-        <v>-0.62</v>
+        <v>0.59</v>
       </c>
       <c r="AM10" t="n">
         <v>110</v>
@@ -1555,61 +1516,61 @@
       <c r="AN10" t="n">
         <v>142</v>
       </c>
-      <c r="AP10" t="n">
-        <v>80.2</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>13.86</v>
-      </c>
       <c r="BL10" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B11" t="n">
-        <v>151.5</v>
+        <v>145.2</v>
       </c>
       <c r="D11" t="n">
-        <v>35.1</v>
+        <v>33.5</v>
       </c>
       <c r="F11" t="n">
-        <v>5.4</v>
+        <v>5</v>
+      </c>
+      <c r="K11" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="O11" t="n">
+        <v>35.5</v>
       </c>
       <c r="V11" t="n">
-        <v>8.699999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="W11" t="n">
-        <v>19.4</v>
+        <v>19.2</v>
       </c>
       <c r="X11" t="n">
-        <v>14</v>
+        <v>13.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z11" t="n">
         <v>13</v>
       </c>
       <c r="AA11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB11" t="n">
-        <v>-4.7</v>
+        <v>-5.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>-1.4</v>
+        <v>-1.5</v>
       </c>
       <c r="AF11" t="n">
-        <v>221.37</v>
+        <v>224.37</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.05</v>
+        <v>3</v>
       </c>
       <c r="AH11" t="n">
         <v>215</v>
@@ -1618,10 +1579,10 @@
         <v>235</v>
       </c>
       <c r="AK11" t="n">
-        <v>135.21</v>
+        <v>135.61</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.59</v>
+        <v>0.4</v>
       </c>
       <c r="AM11" t="n">
         <v>110</v>
@@ -1630,60 +1591,60 @@
         <v>142</v>
       </c>
       <c r="BL11" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B12" t="n">
-        <v>145.2</v>
+        <v>146.3</v>
       </c>
       <c r="D12" t="n">
-        <v>33.5</v>
+        <v>33.4</v>
       </c>
       <c r="F12" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="K12" t="n">
-        <v>100.3</v>
+        <v>98.2</v>
       </c>
       <c r="O12" t="n">
-        <v>35.5</v>
+        <v>35.1</v>
       </c>
       <c r="V12" t="n">
-        <v>7.1</v>
+        <v>4.9</v>
       </c>
       <c r="W12" t="n">
-        <v>19.2</v>
+        <v>16.4</v>
       </c>
       <c r="X12" t="n">
-        <v>13.1</v>
+        <v>10.6</v>
       </c>
       <c r="Y12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB12" t="n">
-        <v>-5.4</v>
+        <v>-6.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.4</v>
+        <v>-0.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>-1.5</v>
+        <v>-3.3</v>
       </c>
       <c r="AF12" t="n">
-        <v>224.37</v>
+        <v>225.93</v>
       </c>
       <c r="AG12" t="n">
-        <v>3</v>
+        <v>1.56</v>
       </c>
       <c r="AH12" t="n">
         <v>215</v>
@@ -1692,10 +1653,10 @@
         <v>235</v>
       </c>
       <c r="AK12" t="n">
-        <v>135.61</v>
+        <v>135.28</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.4</v>
+        <v>-0.33</v>
       </c>
       <c r="AM12" t="n">
         <v>110</v>
@@ -1704,60 +1665,93 @@
         <v>142</v>
       </c>
       <c r="BL12" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B13" t="n">
-        <v>146.3</v>
+        <v>182.8</v>
+      </c>
+      <c r="C13" t="n">
+        <v>86.8</v>
       </c>
       <c r="D13" t="n">
-        <v>33.4</v>
+        <v>31.8</v>
+      </c>
+      <c r="E13" t="n">
+        <v>33</v>
       </c>
       <c r="F13" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
+      </c>
+      <c r="H13" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="I13" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J13" t="n">
+        <v>41.1</v>
       </c>
       <c r="K13" t="n">
-        <v>98.2</v>
+        <v>74.2</v>
+      </c>
+      <c r="M13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="N13" t="n">
+        <v>33.5</v>
       </c>
       <c r="O13" t="n">
-        <v>35.1</v>
+        <v>38.4</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="n">
+        <v>22.4</v>
       </c>
       <c r="V13" t="n">
-        <v>4.9</v>
+        <v>9.1</v>
       </c>
       <c r="W13" t="n">
-        <v>16.4</v>
+        <v>15</v>
       </c>
       <c r="X13" t="n">
-        <v>10.6</v>
+        <v>12.1</v>
       </c>
       <c r="Y13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z13" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AA13" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>-6.4</v>
+        <v>-10.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>-0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>-3.3</v>
+        <v>-5.1</v>
       </c>
       <c r="AF13" t="n">
-        <v>225.93</v>
+        <v>218.63</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.56</v>
+        <v>-7.3</v>
       </c>
       <c r="AH13" t="n">
         <v>215</v>
@@ -1766,10 +1760,10 @@
         <v>235</v>
       </c>
       <c r="AK13" t="n">
-        <v>135.28</v>
+        <v>126.27</v>
       </c>
       <c r="AL13" t="n">
-        <v>-0.33</v>
+        <v>-9.01</v>
       </c>
       <c r="AM13" t="n">
         <v>110</v>
@@ -1777,94 +1771,100 @@
       <c r="AN13" t="n">
         <v>142</v>
       </c>
+      <c r="AP13" t="n">
+        <v>82.66</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>14.7</v>
+      </c>
       <c r="BL13" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B14" t="n">
-        <v>182.8</v>
+        <v>181.8</v>
       </c>
       <c r="C14" t="n">
-        <v>86.8</v>
+        <v>86.5</v>
       </c>
       <c r="D14" t="n">
-        <v>31.8</v>
+        <v>31.4</v>
       </c>
       <c r="E14" t="n">
-        <v>33</v>
+        <v>34.2</v>
       </c>
       <c r="F14" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="H14" t="n">
-        <v>23.5</v>
+        <v>24.4</v>
       </c>
       <c r="I14" t="n">
-        <v>9.6</v>
+        <v>10.4</v>
       </c>
       <c r="J14" t="n">
-        <v>41.1</v>
+        <v>41.9</v>
       </c>
       <c r="K14" t="n">
-        <v>74.2</v>
+        <v>76.8</v>
       </c>
       <c r="M14" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="N14" t="n">
-        <v>33.5</v>
+        <v>35.7</v>
       </c>
       <c r="O14" t="n">
-        <v>38.4</v>
+        <v>39.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>22.4</v>
+        <v>23</v>
       </c>
       <c r="R14" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>20.1</v>
       </c>
       <c r="T14" t="n">
-        <v>22.4</v>
+        <v>23</v>
       </c>
       <c r="V14" t="n">
-        <v>9.1</v>
+        <v>7.1</v>
       </c>
       <c r="W14" t="n">
-        <v>15</v>
+        <v>14.8</v>
       </c>
       <c r="X14" t="n">
-        <v>12.1</v>
+        <v>10.9</v>
       </c>
       <c r="Y14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z14" t="n">
         <v>12</v>
       </c>
       <c r="AA14" t="n">
-        <v>8.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AB14" t="n">
-        <v>-10.5</v>
+        <v>-4.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>-5.1</v>
+        <v>-1.4</v>
       </c>
       <c r="AF14" t="n">
-        <v>218.63</v>
+        <v>216.39</v>
       </c>
       <c r="AG14" t="n">
-        <v>-7.3</v>
+        <v>-2.23</v>
       </c>
       <c r="AH14" t="n">
         <v>215</v>
@@ -1873,10 +1873,10 @@
         <v>235</v>
       </c>
       <c r="AK14" t="n">
-        <v>126.27</v>
+        <v>123.32</v>
       </c>
       <c r="AL14" t="n">
-        <v>-9.01</v>
+        <v>-2.95</v>
       </c>
       <c r="AM14" t="n">
         <v>110</v>
@@ -1885,99 +1885,99 @@
         <v>142</v>
       </c>
       <c r="AP14" t="n">
-        <v>82.66</v>
+        <v>79.08</v>
       </c>
       <c r="AS14" t="n">
-        <v>14.7</v>
+        <v>13.91</v>
       </c>
       <c r="BL14" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B15" t="n">
-        <v>181.8</v>
+        <v>183</v>
       </c>
       <c r="C15" t="n">
-        <v>86.5</v>
+        <v>84.7</v>
       </c>
       <c r="D15" t="n">
-        <v>31.4</v>
+        <v>30.9</v>
       </c>
       <c r="E15" t="n">
-        <v>34.2</v>
+        <v>33.7</v>
       </c>
       <c r="F15" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="H15" t="n">
-        <v>24.4</v>
+        <v>23.4</v>
       </c>
       <c r="I15" t="n">
-        <v>10.4</v>
+        <v>10.6</v>
       </c>
       <c r="J15" t="n">
-        <v>41.9</v>
+        <v>42.3</v>
       </c>
       <c r="K15" t="n">
-        <v>76.8</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="N15" t="n">
-        <v>35.7</v>
+        <v>36.7</v>
       </c>
       <c r="O15" t="n">
-        <v>39.8</v>
+        <v>40.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>23</v>
+        <v>23.6</v>
       </c>
       <c r="R15" t="n">
         <v>1.8</v>
       </c>
       <c r="S15" t="n">
-        <v>20.1</v>
+        <v>20.8</v>
       </c>
       <c r="T15" t="n">
-        <v>23</v>
+        <v>23.6</v>
       </c>
       <c r="V15" t="n">
-        <v>7.1</v>
+        <v>5.7</v>
       </c>
       <c r="W15" t="n">
-        <v>14.8</v>
+        <v>16.1</v>
       </c>
       <c r="X15" t="n">
         <v>10.9</v>
       </c>
       <c r="Y15" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA15" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AB15" t="n">
-        <v>-4.5</v>
+        <v>0.8</v>
       </c>
       <c r="AC15" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD15" t="n">
         <v>1.8</v>
       </c>
-      <c r="AD15" t="n">
-        <v>-1.4</v>
-      </c>
       <c r="AF15" t="n">
-        <v>216.39</v>
+        <v>217.16</v>
       </c>
       <c r="AG15" t="n">
-        <v>-2.23</v>
+        <v>0.76</v>
       </c>
       <c r="AH15" t="n">
         <v>215</v>
@@ -1986,10 +1986,10 @@
         <v>235</v>
       </c>
       <c r="AK15" t="n">
-        <v>123.32</v>
+        <v>117.87</v>
       </c>
       <c r="AL15" t="n">
-        <v>-2.95</v>
+        <v>-5.45</v>
       </c>
       <c r="AM15" t="n">
         <v>110</v>
@@ -1998,99 +1998,66 @@
         <v>142</v>
       </c>
       <c r="AP15" t="n">
-        <v>79.08</v>
+        <v>78.56</v>
       </c>
       <c r="AS15" t="n">
-        <v>13.91</v>
+        <v>13.45</v>
       </c>
       <c r="BL15" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B16" t="n">
-        <v>183</v>
-      </c>
-      <c r="C16" t="n">
-        <v>84.7</v>
+        <v>163.8</v>
       </c>
       <c r="D16" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="E16" t="n">
-        <v>33.7</v>
+        <v>29</v>
       </c>
       <c r="F16" t="n">
-        <v>7</v>
-      </c>
-      <c r="H16" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="I16" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="J16" t="n">
-        <v>42.3</v>
+        <v>6.5</v>
       </c>
       <c r="K16" t="n">
-        <v>76.40000000000001</v>
-      </c>
-      <c r="M16" t="n">
-        <v>4</v>
-      </c>
-      <c r="N16" t="n">
-        <v>36.7</v>
+        <v>101.2</v>
       </c>
       <c r="O16" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S16" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="T16" t="n">
-        <v>23.6</v>
+        <v>40.2</v>
       </c>
       <c r="V16" t="n">
-        <v>5.7</v>
+        <v>6.3</v>
       </c>
       <c r="W16" t="n">
-        <v>16.1</v>
+        <v>17.2</v>
       </c>
       <c r="X16" t="n">
-        <v>10.9</v>
+        <v>11.8</v>
       </c>
       <c r="Y16" t="n">
         <v>8</v>
       </c>
       <c r="Z16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA16" t="n">
         <v>10</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.7</v>
+        <v>4.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="AF16" t="n">
-        <v>217.16</v>
+        <v>220.31</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.76</v>
+        <v>3.16</v>
       </c>
       <c r="AH16" t="n">
         <v>215</v>
@@ -2099,10 +2066,10 @@
         <v>235</v>
       </c>
       <c r="AK16" t="n">
-        <v>117.87</v>
+        <v>116.52</v>
       </c>
       <c r="AL16" t="n">
-        <v>-5.45</v>
+        <v>-1.35</v>
       </c>
       <c r="AM16" t="n">
         <v>110</v>
@@ -2110,67 +2077,61 @@
       <c r="AN16" t="n">
         <v>142</v>
       </c>
-      <c r="AP16" t="n">
-        <v>78.56</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>13.45</v>
-      </c>
       <c r="BL16" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B17" t="n">
-        <v>163.8</v>
+        <v>155.9</v>
       </c>
       <c r="D17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F17" t="n">
         <v>6.5</v>
       </c>
       <c r="K17" t="n">
-        <v>101.2</v>
+        <v>99.3</v>
       </c>
       <c r="O17" t="n">
-        <v>40.2</v>
+        <v>38.5</v>
       </c>
       <c r="V17" t="n">
-        <v>6.3</v>
+        <v>8.9</v>
       </c>
       <c r="W17" t="n">
-        <v>17.2</v>
+        <v>15.8</v>
       </c>
       <c r="X17" t="n">
-        <v>11.8</v>
+        <v>12.4</v>
       </c>
       <c r="Y17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA17" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="AF17" t="n">
-        <v>220.31</v>
+        <v>221.99</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.16</v>
+        <v>1.67</v>
       </c>
       <c r="AH17" t="n">
         <v>215</v>
@@ -2179,10 +2140,10 @@
         <v>235</v>
       </c>
       <c r="AK17" t="n">
-        <v>116.52</v>
+        <v>116.37</v>
       </c>
       <c r="AL17" t="n">
-        <v>-1.35</v>
+        <v>-0.15</v>
       </c>
       <c r="AM17" t="n">
         <v>110</v>
@@ -2191,60 +2152,60 @@
         <v>142</v>
       </c>
       <c r="BL17" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B18" t="n">
-        <v>155.9</v>
+        <v>141.3</v>
       </c>
       <c r="D18" t="n">
-        <v>28</v>
+        <v>26.3</v>
       </c>
       <c r="F18" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="K18" t="n">
-        <v>99.3</v>
+        <v>97.8</v>
       </c>
       <c r="O18" t="n">
-        <v>38.5</v>
+        <v>39.8</v>
       </c>
       <c r="V18" t="n">
-        <v>8.9</v>
+        <v>9.5</v>
       </c>
       <c r="W18" t="n">
-        <v>15.8</v>
+        <v>17.7</v>
       </c>
       <c r="X18" t="n">
-        <v>12.4</v>
+        <v>13.6</v>
       </c>
       <c r="Y18" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Z18" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA18" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="AC18" t="n">
-        <v>5.7</v>
+        <v>7.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="AF18" t="n">
-        <v>221.99</v>
+        <v>225.14</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.67</v>
+        <v>3.15</v>
       </c>
       <c r="AH18" t="n">
         <v>215</v>
@@ -2252,12 +2213,6 @@
       <c r="AI18" t="n">
         <v>235</v>
       </c>
-      <c r="AK18" t="n">
-        <v>116.37</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>-0.15</v>
-      </c>
       <c r="AM18" t="n">
         <v>110</v>
       </c>
@@ -2265,60 +2220,54 @@
         <v>142</v>
       </c>
       <c r="BL18" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B19" t="n">
-        <v>141.3</v>
+        <v>131.5</v>
       </c>
       <c r="D19" t="n">
-        <v>26.3</v>
+        <v>27.3</v>
       </c>
       <c r="F19" t="n">
         <v>5.5</v>
       </c>
       <c r="K19" t="n">
-        <v>97.8</v>
+        <v>97</v>
       </c>
       <c r="O19" t="n">
-        <v>39.8</v>
+        <v>35.7</v>
       </c>
       <c r="V19" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="W19" t="n">
-        <v>17.7</v>
+        <v>13.9</v>
       </c>
       <c r="X19" t="n">
-        <v>13.6</v>
+        <v>11.4</v>
       </c>
       <c r="Y19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z19" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA19" t="n">
         <v>15</v>
       </c>
-      <c r="AA19" t="n">
-        <v>14</v>
-      </c>
       <c r="AB19" t="n">
-        <v>0.2</v>
+        <v>-3.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>7.5</v>
+        <v>2.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>225.14</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>3.15</v>
+        <v>-0.4</v>
       </c>
       <c r="AH19" t="n">
         <v>215</v>
@@ -2333,54 +2282,93 @@
         <v>142</v>
       </c>
       <c r="BL19" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="B20" t="n">
-        <v>131.5</v>
+        <v>153</v>
+      </c>
+      <c r="C20" t="n">
+        <v>71.8</v>
       </c>
       <c r="D20" t="n">
-        <v>27.3</v>
+        <v>28.6</v>
+      </c>
+      <c r="E20" t="n">
+        <v>24.7</v>
       </c>
       <c r="F20" t="n">
-        <v>5.5</v>
+        <v>4</v>
+      </c>
+      <c r="H20" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J20" t="n">
+        <v>41.1</v>
       </c>
       <c r="K20" t="n">
-        <v>97</v>
+        <v>75.90000000000001</v>
+      </c>
+      <c r="M20" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N20" t="n">
+        <v>33.5</v>
       </c>
       <c r="O20" t="n">
-        <v>35.7</v>
+        <v>38.3</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>23.2</v>
       </c>
       <c r="V20" t="n">
-        <v>9</v>
+        <v>11.2</v>
       </c>
       <c r="W20" t="n">
-        <v>13.9</v>
+        <v>13</v>
       </c>
       <c r="X20" t="n">
-        <v>11.4</v>
+        <v>12.1</v>
       </c>
       <c r="Y20" t="n">
         <v>12</v>
       </c>
       <c r="Z20" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AA20" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AB20" t="n">
-        <v>-3.6</v>
+        <v>-6.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.8</v>
+        <v>5.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>-0.4</v>
+        <v>-0.6</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>229.96</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>-0.02</v>
       </c>
       <c r="AH20" t="n">
         <v>215</v>
@@ -2388,100 +2376,112 @@
       <c r="AI20" t="n">
         <v>235</v>
       </c>
+      <c r="AK20" t="n">
+        <v>128.14</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>11.77</v>
+      </c>
       <c r="AM20" t="n">
         <v>110</v>
       </c>
       <c r="AN20" t="n">
         <v>142</v>
       </c>
+      <c r="AP20" t="n">
+        <v>87.47</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>14.8</v>
+      </c>
       <c r="BL20" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B21" t="n">
-        <v>153</v>
+        <v>165.8</v>
       </c>
       <c r="C21" t="n">
-        <v>71.8</v>
+        <v>77.3</v>
       </c>
       <c r="D21" t="n">
-        <v>28.6</v>
+        <v>29.3</v>
       </c>
       <c r="E21" t="n">
-        <v>24.7</v>
+        <v>27.7</v>
       </c>
       <c r="F21" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="H21" t="n">
         <v>24.1</v>
       </c>
       <c r="I21" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="J21" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="K21" t="n">
-        <v>75.90000000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="N21" t="n">
-        <v>33.5</v>
+        <v>35.1</v>
       </c>
       <c r="O21" t="n">
-        <v>38.3</v>
+        <v>39.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>23.2</v>
+        <v>23.8</v>
       </c>
       <c r="R21" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="T21" t="n">
-        <v>23.2</v>
+        <v>23.8</v>
       </c>
       <c r="V21" t="n">
-        <v>11.2</v>
+        <v>9.4</v>
       </c>
       <c r="W21" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="X21" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z21" t="n">
         <v>13</v>
       </c>
-      <c r="X21" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>14</v>
-      </c>
       <c r="AA21" t="n">
-        <v>12.5</v>
+        <v>10.1</v>
       </c>
       <c r="AB21" t="n">
-        <v>-6.6</v>
+        <v>-0.7</v>
       </c>
       <c r="AC21" t="n">
-        <v>5.3</v>
+        <v>9.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>-0.6</v>
+        <v>4.4</v>
       </c>
       <c r="AF21" t="n">
-        <v>229.96</v>
+        <v>227.01</v>
       </c>
       <c r="AG21" t="n">
-        <v>-0.02</v>
+        <v>-2.95</v>
       </c>
       <c r="AH21" t="n">
         <v>215</v>
@@ -2490,10 +2490,10 @@
         <v>235</v>
       </c>
       <c r="AK21" t="n">
-        <v>128.14</v>
+        <v>128.15</v>
       </c>
       <c r="AL21" t="n">
-        <v>11.77</v>
+        <v>0.01</v>
       </c>
       <c r="AM21" t="n">
         <v>110</v>
@@ -2502,99 +2502,99 @@
         <v>142</v>
       </c>
       <c r="AP21" t="n">
-        <v>87.47</v>
+        <v>83.41</v>
       </c>
       <c r="AS21" t="n">
-        <v>14.8</v>
+        <v>14.52</v>
       </c>
       <c r="BL21" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B22" t="n">
-        <v>165.8</v>
+        <v>158.1</v>
       </c>
       <c r="C22" t="n">
-        <v>77.3</v>
+        <v>73.7</v>
       </c>
       <c r="D22" t="n">
-        <v>29.3</v>
+        <v>30.3</v>
       </c>
       <c r="E22" t="n">
-        <v>27.7</v>
+        <v>26</v>
       </c>
       <c r="F22" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="H22" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="I22" t="n">
-        <v>10.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>41.6</v>
+        <v>40.9</v>
       </c>
       <c r="K22" t="n">
-        <v>76.59999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="N22" t="n">
-        <v>35.1</v>
+        <v>35.3</v>
       </c>
       <c r="O22" t="n">
-        <v>39.8</v>
+        <v>40.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="R22" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S22" t="n">
         <v>7</v>
       </c>
       <c r="T22" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="V22" t="n">
-        <v>9.4</v>
+        <v>8.9</v>
       </c>
       <c r="W22" t="n">
-        <v>17.4</v>
+        <v>19.3</v>
       </c>
       <c r="X22" t="n">
-        <v>13.4</v>
+        <v>14.1</v>
       </c>
       <c r="Y22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z22" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA22" t="n">
-        <v>10.1</v>
+        <v>11</v>
       </c>
       <c r="AB22" t="n">
-        <v>-0.7</v>
+        <v>4.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>4.4</v>
+        <v>6.5</v>
       </c>
       <c r="AF22" t="n">
-        <v>227.01</v>
+        <v>228.35</v>
       </c>
       <c r="AG22" t="n">
-        <v>-2.95</v>
+        <v>1.33</v>
       </c>
       <c r="AH22" t="n">
         <v>215</v>
@@ -2603,10 +2603,10 @@
         <v>235</v>
       </c>
       <c r="AK22" t="n">
-        <v>128.15</v>
+        <v>128.86</v>
       </c>
       <c r="AL22" t="n">
-        <v>0.01</v>
+        <v>0.71</v>
       </c>
       <c r="AM22" t="n">
         <v>110</v>
@@ -2615,99 +2615,99 @@
         <v>142</v>
       </c>
       <c r="AP22" t="n">
-        <v>83.41</v>
+        <v>82.37</v>
       </c>
       <c r="AS22" t="n">
-        <v>14.52</v>
+        <v>14.22</v>
       </c>
       <c r="BL22" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B23" t="n">
-        <v>158.1</v>
+        <v>154.9</v>
       </c>
       <c r="C23" t="n">
-        <v>73.7</v>
+        <v>70.2</v>
       </c>
       <c r="D23" t="n">
-        <v>30.3</v>
+        <v>31.5</v>
       </c>
       <c r="E23" t="n">
-        <v>26</v>
+        <v>27.7</v>
       </c>
       <c r="F23" t="n">
-        <v>4.1</v>
+        <v>2.7</v>
       </c>
       <c r="H23" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="I23" t="n">
-        <v>9.300000000000001</v>
+        <v>11.3</v>
       </c>
       <c r="J23" t="n">
-        <v>40.9</v>
+        <v>40.3</v>
       </c>
       <c r="K23" t="n">
-        <v>74.40000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="M23" t="n">
-        <v>5</v>
+        <v>6.1</v>
       </c>
       <c r="N23" t="n">
-        <v>35.3</v>
+        <v>32.9</v>
       </c>
       <c r="O23" t="n">
-        <v>40.3</v>
+        <v>39</v>
       </c>
       <c r="Q23" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="R23" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="S23" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="T23" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="V23" t="n">
-        <v>8.9</v>
+        <v>6.3</v>
       </c>
       <c r="W23" t="n">
-        <v>19.3</v>
+        <v>25.2</v>
       </c>
       <c r="X23" t="n">
-        <v>14.1</v>
+        <v>15.8</v>
       </c>
       <c r="Y23" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z23" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA23" t="n">
-        <v>11</v>
+        <v>12.6</v>
       </c>
       <c r="AB23" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="AC23" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="AD23" t="n">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="AF23" t="n">
-        <v>228.35</v>
+        <v>231.16</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.33</v>
+        <v>2.81</v>
       </c>
       <c r="AH23" t="n">
         <v>215</v>
@@ -2716,10 +2716,10 @@
         <v>235</v>
       </c>
       <c r="AK23" t="n">
-        <v>128.86</v>
+        <v>130.88</v>
       </c>
       <c r="AL23" t="n">
-        <v>0.71</v>
+        <v>2.02</v>
       </c>
       <c r="AM23" t="n">
         <v>110</v>
@@ -2728,99 +2728,66 @@
         <v>142</v>
       </c>
       <c r="AP23" t="n">
-        <v>82.37</v>
+        <v>85.48999999999999</v>
       </c>
       <c r="AS23" t="n">
-        <v>14.22</v>
+        <v>13.1</v>
       </c>
       <c r="BL23" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B24" t="n">
-        <v>154.9</v>
-      </c>
-      <c r="C24" t="n">
-        <v>70.2</v>
+        <v>152.2</v>
       </c>
       <c r="D24" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="E24" t="n">
-        <v>27.7</v>
+        <v>31</v>
       </c>
       <c r="F24" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="H24" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I24" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J24" t="n">
-        <v>40.3</v>
+        <v>3.5</v>
       </c>
       <c r="K24" t="n">
-        <v>75.8</v>
-      </c>
-      <c r="M24" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="N24" t="n">
-        <v>32.9</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O24" t="n">
-        <v>39</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="R24" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="S24" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="T24" t="n">
-        <v>23.7</v>
+        <v>34.4</v>
       </c>
       <c r="V24" t="n">
-        <v>6.3</v>
+        <v>9.5</v>
       </c>
       <c r="W24" t="n">
-        <v>25.2</v>
+        <v>25.5</v>
       </c>
       <c r="X24" t="n">
-        <v>15.8</v>
+        <v>17.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Z24" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AA24" t="n">
-        <v>12.6</v>
+        <v>9</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.9</v>
+        <v>-1.1</v>
       </c>
       <c r="AC24" t="n">
         <v>8.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>5.8</v>
+        <v>3.8</v>
       </c>
       <c r="AF24" t="n">
-        <v>231.16</v>
+        <v>228.13</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.81</v>
+        <v>-3.03</v>
       </c>
       <c r="AH24" t="n">
         <v>215</v>
@@ -2828,79 +2795,67 @@
       <c r="AI24" t="n">
         <v>235</v>
       </c>
-      <c r="AK24" t="n">
-        <v>130.88</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AM24" t="n">
         <v>110</v>
       </c>
       <c r="AN24" t="n">
         <v>142</v>
       </c>
-      <c r="AP24" t="n">
-        <v>85.48999999999999</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>13.1</v>
-      </c>
       <c r="BL24" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B25" t="n">
-        <v>152.2</v>
+        <v>143.9</v>
       </c>
       <c r="D25" t="n">
-        <v>31</v>
+        <v>30.8</v>
       </c>
       <c r="F25" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="K25" t="n">
-        <v>98.40000000000001</v>
+        <v>99.2</v>
       </c>
       <c r="O25" t="n">
-        <v>34.4</v>
+        <v>35.2</v>
       </c>
       <c r="V25" t="n">
-        <v>9.5</v>
+        <v>10.7</v>
       </c>
       <c r="W25" t="n">
-        <v>25.5</v>
+        <v>17.6</v>
       </c>
       <c r="X25" t="n">
-        <v>17.5</v>
+        <v>14.2</v>
       </c>
       <c r="Y25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Z25" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA25" t="n">
         <v>9</v>
       </c>
       <c r="AB25" t="n">
-        <v>-1.1</v>
+        <v>-0.8</v>
       </c>
       <c r="AC25" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD25" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AF25" t="n">
-        <v>228.13</v>
+        <v>229.16</v>
       </c>
       <c r="AG25" t="n">
-        <v>-3.03</v>
+        <v>1.03</v>
       </c>
       <c r="AH25" t="n">
         <v>215</v>
@@ -2915,60 +2870,93 @@
         <v>142</v>
       </c>
       <c r="BL25" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B26" t="n">
-        <v>143.9</v>
+        <v>163.2</v>
+      </c>
+      <c r="C26" t="n">
+        <v>73.7</v>
       </c>
       <c r="D26" t="n">
-        <v>30.8</v>
+        <v>30</v>
+      </c>
+      <c r="E26" t="n">
+        <v>28.2</v>
       </c>
       <c r="F26" t="n">
-        <v>2.5</v>
+        <v>4.8</v>
+      </c>
+      <c r="H26" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J26" t="n">
+        <v>40.1</v>
       </c>
       <c r="K26" t="n">
-        <v>99.2</v>
+        <v>75.59999999999999</v>
+      </c>
+      <c r="M26" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="N26" t="n">
+        <v>32.9</v>
       </c>
       <c r="O26" t="n">
-        <v>35.2</v>
+        <v>39.7</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="R26" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="S26" t="n">
+        <v>6</v>
+      </c>
+      <c r="T26" t="n">
+        <v>23.5</v>
       </c>
       <c r="V26" t="n">
-        <v>10.7</v>
+        <v>9.4</v>
       </c>
       <c r="W26" t="n">
-        <v>17.6</v>
+        <v>20.1</v>
       </c>
       <c r="X26" t="n">
-        <v>14.2</v>
+        <v>14.8</v>
       </c>
       <c r="Y26" t="n">
         <v>4</v>
       </c>
       <c r="Z26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA26" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AB26" t="n">
-        <v>-0.8</v>
+        <v>-0.9</v>
       </c>
       <c r="AC26" t="n">
-        <v>8.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AF26" t="n">
-        <v>229.16</v>
+        <v>228.55</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.03</v>
+        <v>-0.61</v>
       </c>
       <c r="AH26" t="n">
         <v>215</v>
@@ -2976,100 +2964,112 @@
       <c r="AI26" t="n">
         <v>235</v>
       </c>
+      <c r="AK26" t="n">
+        <v>127.06</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>-3.82</v>
+      </c>
       <c r="AM26" t="n">
         <v>110</v>
       </c>
       <c r="AN26" t="n">
         <v>142</v>
       </c>
+      <c r="AP26" t="n">
+        <v>82.81</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>12.9</v>
+      </c>
       <c r="BL26" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="B27" t="n">
-        <v>163.2</v>
+        <v>174.4</v>
       </c>
       <c r="C27" t="n">
-        <v>73.7</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="D27" t="n">
-        <v>30</v>
+        <v>32.1</v>
       </c>
       <c r="E27" t="n">
-        <v>28.2</v>
+        <v>30.8</v>
       </c>
       <c r="F27" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="H27" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="I27" t="n">
-        <v>11.4</v>
+        <v>10.5</v>
       </c>
       <c r="J27" t="n">
-        <v>40.1</v>
+        <v>39.5</v>
       </c>
       <c r="K27" t="n">
-        <v>75.59999999999999</v>
+        <v>74</v>
       </c>
       <c r="M27" t="n">
         <v>6.8</v>
       </c>
       <c r="N27" t="n">
-        <v>32.9</v>
+        <v>35.8</v>
       </c>
       <c r="O27" t="n">
-        <v>39.7</v>
+        <v>42.6</v>
       </c>
       <c r="Q27" t="n">
-        <v>23.5</v>
+        <v>23.1</v>
       </c>
       <c r="R27" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="S27" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="T27" t="n">
-        <v>23.5</v>
+        <v>23.1</v>
       </c>
       <c r="V27" t="n">
-        <v>9.4</v>
+        <v>12.8</v>
       </c>
       <c r="W27" t="n">
-        <v>20.1</v>
+        <v>22.1</v>
       </c>
       <c r="X27" t="n">
-        <v>14.8</v>
+        <v>17.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Z27" t="n">
         <v>13</v>
       </c>
       <c r="AA27" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AC27" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="AB27" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>9.5</v>
-      </c>
       <c r="AD27" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AF27" t="n">
-        <v>228.55</v>
+        <v>219.99</v>
       </c>
       <c r="AG27" t="n">
-        <v>-0.61</v>
+        <v>-8.56</v>
       </c>
       <c r="AH27" t="n">
         <v>215</v>
@@ -3078,10 +3078,10 @@
         <v>235</v>
       </c>
       <c r="AK27" t="n">
-        <v>127.06</v>
+        <v>125.61</v>
       </c>
       <c r="AL27" t="n">
-        <v>-3.82</v>
+        <v>-1.45</v>
       </c>
       <c r="AM27" t="n">
         <v>110</v>
@@ -3090,99 +3090,99 @@
         <v>142</v>
       </c>
       <c r="AP27" t="n">
-        <v>82.81</v>
+        <v>77.83</v>
       </c>
       <c r="AS27" t="n">
-        <v>12.9</v>
+        <v>12.96</v>
       </c>
       <c r="BL27" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B28" t="n">
-        <v>174.4</v>
+        <v>163.2</v>
       </c>
       <c r="C28" t="n">
-        <v>75.40000000000001</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>32.1</v>
+        <v>32.9</v>
       </c>
       <c r="E28" t="n">
-        <v>30.8</v>
+        <v>26</v>
       </c>
       <c r="F28" t="n">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="H28" t="n">
-        <v>24</v>
+        <v>23.8</v>
       </c>
       <c r="I28" t="n">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="J28" t="n">
-        <v>39.5</v>
+        <v>40.1</v>
       </c>
       <c r="K28" t="n">
-        <v>74</v>
+        <v>71.3</v>
       </c>
       <c r="M28" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="N28" t="n">
-        <v>35.8</v>
+        <v>34.3</v>
       </c>
       <c r="O28" t="n">
-        <v>42.6</v>
+        <v>41.5</v>
       </c>
       <c r="Q28" t="n">
         <v>23.1</v>
       </c>
       <c r="R28" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="S28" t="n">
-        <v>8.5</v>
+        <v>6.2</v>
       </c>
       <c r="T28" t="n">
         <v>23.1</v>
       </c>
       <c r="V28" t="n">
-        <v>12.8</v>
+        <v>9.6</v>
       </c>
       <c r="W28" t="n">
-        <v>22.1</v>
+        <v>23.3</v>
       </c>
       <c r="X28" t="n">
-        <v>17.5</v>
+        <v>16.4</v>
       </c>
       <c r="Y28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA28" t="n">
-        <v>10.1</v>
+        <v>12.2</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.3</v>
+        <v>2.6</v>
       </c>
       <c r="AC28" t="n">
-        <v>9.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AF28" t="n">
-        <v>219.99</v>
+        <v>219.22</v>
       </c>
       <c r="AG28" t="n">
-        <v>-8.56</v>
+        <v>-0.77</v>
       </c>
       <c r="AH28" t="n">
         <v>215</v>
@@ -3191,10 +3191,10 @@
         <v>235</v>
       </c>
       <c r="AK28" t="n">
-        <v>125.61</v>
+        <v>124.36</v>
       </c>
       <c r="AL28" t="n">
-        <v>-1.45</v>
+        <v>-1.25</v>
       </c>
       <c r="AM28" t="n">
         <v>110</v>
@@ -3203,99 +3203,99 @@
         <v>142</v>
       </c>
       <c r="AP28" t="n">
-        <v>77.83</v>
+        <v>76.81</v>
       </c>
       <c r="AS28" t="n">
-        <v>12.96</v>
+        <v>12.38</v>
       </c>
       <c r="BL28" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B29" t="n">
-        <v>163.2</v>
+        <v>152.7</v>
       </c>
       <c r="C29" t="n">
-        <v>70.90000000000001</v>
+        <v>62.6</v>
       </c>
       <c r="D29" t="n">
-        <v>32.9</v>
+        <v>32.7</v>
       </c>
       <c r="E29" t="n">
-        <v>26</v>
+        <v>24.6</v>
       </c>
       <c r="F29" t="n">
-        <v>6.9</v>
+        <v>5.2</v>
       </c>
       <c r="H29" t="n">
         <v>23.8</v>
       </c>
       <c r="I29" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J29" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="K29" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="M29" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="N29" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="O29" t="n">
         <v>40.1</v>
       </c>
-      <c r="K29" t="n">
-        <v>71.3</v>
-      </c>
-      <c r="M29" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="N29" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="O29" t="n">
-        <v>41.5</v>
-      </c>
       <c r="Q29" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="R29" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="S29" t="n">
-        <v>6.2</v>
+        <v>4</v>
       </c>
       <c r="T29" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="V29" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="W29" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="X29" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC29" t="n">
         <v>9.6</v>
       </c>
-      <c r="W29" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="X29" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>8.5</v>
-      </c>
       <c r="AD29" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AF29" t="n">
-        <v>219.22</v>
+        <v>220.73</v>
       </c>
       <c r="AG29" t="n">
-        <v>-0.77</v>
+        <v>1.5</v>
       </c>
       <c r="AH29" t="n">
         <v>215</v>
@@ -3304,10 +3304,10 @@
         <v>235</v>
       </c>
       <c r="AK29" t="n">
-        <v>124.36</v>
+        <v>120.93</v>
       </c>
       <c r="AL29" t="n">
-        <v>-1.25</v>
+        <v>-3.43</v>
       </c>
       <c r="AM29" t="n">
         <v>110</v>
@@ -3316,75 +3316,75 @@
         <v>142</v>
       </c>
       <c r="AP29" t="n">
-        <v>76.81</v>
+        <v>77.87</v>
       </c>
       <c r="AS29" t="n">
-        <v>12.38</v>
+        <v>13.26</v>
       </c>
       <c r="BL29" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B30" t="n">
-        <v>152.7</v>
+        <v>150.7</v>
       </c>
       <c r="C30" t="n">
-        <v>62.6</v>
+        <v>64.8</v>
       </c>
       <c r="D30" t="n">
-        <v>32.7</v>
+        <v>33.7</v>
       </c>
       <c r="E30" t="n">
-        <v>24.6</v>
+        <v>27.1</v>
       </c>
       <c r="F30" t="n">
-        <v>5.2</v>
+        <v>3.8</v>
       </c>
       <c r="H30" t="n">
-        <v>23.8</v>
+        <v>23.4</v>
       </c>
       <c r="I30" t="n">
         <v>7.2</v>
       </c>
       <c r="J30" t="n">
-        <v>38.9</v>
+        <v>39.9</v>
       </c>
       <c r="K30" t="n">
-        <v>69.90000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="M30" t="n">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="N30" t="n">
-        <v>33.5</v>
+        <v>33</v>
       </c>
       <c r="O30" t="n">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="Q30" t="n">
         <v>23.2</v>
       </c>
       <c r="R30" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T30" t="n">
         <v>23.2</v>
       </c>
       <c r="V30" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="W30" t="n">
-        <v>27.3</v>
+        <v>28.9</v>
       </c>
       <c r="X30" t="n">
-        <v>19.4</v>
+        <v>21.7</v>
       </c>
       <c r="Y30" t="n">
         <v>10</v>
@@ -3393,22 +3393,22 @@
         <v>18</v>
       </c>
       <c r="AA30" t="n">
-        <v>14</v>
+        <v>13.1</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>9.6</v>
+        <v>10.8</v>
       </c>
       <c r="AD30" t="n">
-        <v>5.7</v>
+        <v>6.7</v>
       </c>
       <c r="AF30" t="n">
-        <v>220.73</v>
+        <v>220.58</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.5</v>
+        <v>-0.15</v>
       </c>
       <c r="AH30" t="n">
         <v>215</v>
@@ -3417,10 +3417,10 @@
         <v>235</v>
       </c>
       <c r="AK30" t="n">
-        <v>120.93</v>
+        <v>120.28</v>
       </c>
       <c r="AL30" t="n">
-        <v>-3.43</v>
+        <v>-0.65</v>
       </c>
       <c r="AM30" t="n">
         <v>110</v>
@@ -3429,99 +3429,54 @@
         <v>142</v>
       </c>
       <c r="AP30" t="n">
-        <v>77.87</v>
+        <v>77.22</v>
       </c>
       <c r="AS30" t="n">
-        <v>13.26</v>
+        <v>13.79</v>
       </c>
       <c r="BL30" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B31" t="n">
-        <v>150.7</v>
-      </c>
-      <c r="C31" t="n">
-        <v>64.8</v>
+        <v>138.2</v>
       </c>
       <c r="D31" t="n">
-        <v>33.7</v>
-      </c>
-      <c r="E31" t="n">
-        <v>27.1</v>
+        <v>33.6</v>
       </c>
       <c r="F31" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H31" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="V31" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="W31" t="n">
         <v>23.4</v>
       </c>
-      <c r="I31" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="J31" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="K31" t="n">
-        <v>70.5</v>
-      </c>
-      <c r="M31" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="N31" t="n">
-        <v>33</v>
-      </c>
-      <c r="O31" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="R31" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="S31" t="n">
-        <v>3</v>
-      </c>
-      <c r="T31" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="V31" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="W31" t="n">
-        <v>28.9</v>
-      </c>
       <c r="X31" t="n">
-        <v>21.7</v>
+        <v>19.4</v>
       </c>
       <c r="Y31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AA31" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="AC31" t="n">
-        <v>10.8</v>
+        <v>8.5</v>
       </c>
       <c r="AD31" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>220.58</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>-0.15</v>
+        <v>4.5</v>
       </c>
       <c r="AH31" t="n">
         <v>215</v>
@@ -3529,67 +3484,61 @@
       <c r="AI31" t="n">
         <v>235</v>
       </c>
-      <c r="AK31" t="n">
-        <v>120.28</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>-0.65</v>
-      </c>
       <c r="AM31" t="n">
         <v>110</v>
       </c>
       <c r="AN31" t="n">
         <v>142</v>
       </c>
-      <c r="AP31" t="n">
-        <v>77.22</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>13.79</v>
-      </c>
       <c r="BL31" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B32" t="n">
-        <v>138.2</v>
+        <v>126.5</v>
       </c>
       <c r="D32" t="n">
-        <v>33.6</v>
+        <v>33.2</v>
       </c>
       <c r="F32" t="n">
-        <v>6.1</v>
+        <v>3.4</v>
       </c>
       <c r="V32" t="n">
-        <v>15.5</v>
+        <v>12.6</v>
       </c>
       <c r="W32" t="n">
-        <v>23.4</v>
+        <v>22.3</v>
       </c>
       <c r="X32" t="n">
-        <v>19.4</v>
+        <v>17.4</v>
       </c>
       <c r="Y32" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z32" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA32" t="n">
         <v>13</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>8.5</v>
+        <v>6.7</v>
       </c>
       <c r="AD32" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>229.48</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>6.05</v>
       </c>
       <c r="AH32" t="n">
         <v>215</v>
@@ -3604,54 +3553,93 @@
         <v>142</v>
       </c>
       <c r="BL32" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B33" t="n">
-        <v>126.5</v>
+        <v>129.4</v>
+      </c>
+      <c r="C33" t="n">
+        <v>50.6</v>
       </c>
       <c r="D33" t="n">
-        <v>33.2</v>
+        <v>31.5</v>
+      </c>
+      <c r="E33" t="n">
+        <v>19.4</v>
       </c>
       <c r="F33" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
+      </c>
+      <c r="H33" t="n">
+        <v>24</v>
+      </c>
+      <c r="I33" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J33" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="K33" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="M33" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N33" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="O33" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>21.4</v>
       </c>
       <c r="V33" t="n">
-        <v>12.6</v>
+        <v>14.3</v>
       </c>
       <c r="W33" t="n">
-        <v>22.3</v>
+        <v>23.9</v>
       </c>
       <c r="X33" t="n">
-        <v>17.4</v>
+        <v>19.1</v>
       </c>
       <c r="Y33" t="n">
         <v>8</v>
       </c>
       <c r="Z33" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AA33" t="n">
-        <v>13</v>
+        <v>16.1</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AC33" t="n">
-        <v>6.7</v>
+        <v>7.6</v>
       </c>
       <c r="AD33" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="AF33" t="n">
-        <v>229.48</v>
+        <v>229.5</v>
       </c>
       <c r="AG33" t="n">
-        <v>6.05</v>
+        <v>0.02</v>
       </c>
       <c r="AH33" t="n">
         <v>215</v>
@@ -3659,100 +3647,112 @@
       <c r="AI33" t="n">
         <v>235</v>
       </c>
+      <c r="AK33" t="n">
+        <v>128.37</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>8.09</v>
+      </c>
       <c r="AM33" t="n">
         <v>110</v>
       </c>
       <c r="AN33" t="n">
         <v>142</v>
       </c>
+      <c r="AP33" t="n">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>15.97</v>
+      </c>
       <c r="BL33" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="B34" t="n">
-        <v>129.4</v>
+        <v>142.9</v>
       </c>
       <c r="C34" t="n">
-        <v>50.6</v>
+        <v>52.7</v>
       </c>
       <c r="D34" t="n">
-        <v>31.5</v>
+        <v>34.7</v>
       </c>
       <c r="E34" t="n">
-        <v>19.4</v>
+        <v>24.8</v>
       </c>
       <c r="F34" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="H34" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I34" t="n">
-        <v>10.4</v>
+        <v>9.9</v>
       </c>
       <c r="J34" t="n">
-        <v>38.9</v>
+        <v>38.2</v>
       </c>
       <c r="K34" t="n">
-        <v>73.3</v>
+        <v>70</v>
       </c>
       <c r="M34" t="n">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="N34" t="n">
-        <v>33.3</v>
+        <v>31.9</v>
       </c>
       <c r="O34" t="n">
-        <v>38</v>
+        <v>35.8</v>
       </c>
       <c r="Q34" t="n">
-        <v>21.4</v>
+        <v>19.7</v>
       </c>
       <c r="R34" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>21.4</v>
+        <v>19.7</v>
       </c>
       <c r="V34" t="n">
-        <v>14.3</v>
+        <v>12</v>
       </c>
       <c r="W34" t="n">
-        <v>23.9</v>
+        <v>25.8</v>
       </c>
       <c r="X34" t="n">
-        <v>19.1</v>
+        <v>18.9</v>
       </c>
       <c r="Y34" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Z34" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AA34" t="n">
-        <v>16.1</v>
+        <v>15</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.4</v>
+        <v>-0.1</v>
       </c>
       <c r="AC34" t="n">
-        <v>7.6</v>
+        <v>5.8</v>
       </c>
       <c r="AD34" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="AF34" t="n">
-        <v>229.5</v>
+        <v>238.69</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.02</v>
+        <v>-2.8</v>
       </c>
       <c r="AH34" t="n">
         <v>215</v>
@@ -3761,10 +3761,10 @@
         <v>235</v>
       </c>
       <c r="AK34" t="n">
-        <v>128.37</v>
+        <v>134.59</v>
       </c>
       <c r="AL34" t="n">
-        <v>8.09</v>
+        <v>6.22</v>
       </c>
       <c r="AM34" t="n">
         <v>110</v>
@@ -3773,99 +3773,99 @@
         <v>142</v>
       </c>
       <c r="AP34" t="n">
-        <v>91.59999999999999</v>
+        <v>89.05</v>
       </c>
       <c r="AS34" t="n">
-        <v>15.97</v>
+        <v>17.06</v>
       </c>
       <c r="BL34" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B35" t="n">
-        <v>142.9</v>
+        <v>148.1</v>
       </c>
       <c r="C35" t="n">
-        <v>52.7</v>
+        <v>51.9</v>
       </c>
       <c r="D35" t="n">
-        <v>34.7</v>
+        <v>35.4</v>
       </c>
       <c r="E35" t="n">
-        <v>24.8</v>
+        <v>31.5</v>
       </c>
       <c r="F35" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="H35" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="I35" t="n">
-        <v>9.9</v>
+        <v>9.6</v>
       </c>
       <c r="J35" t="n">
-        <v>38.2</v>
+        <v>39.6</v>
       </c>
       <c r="K35" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M35" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="N35" t="n">
-        <v>31.9</v>
+        <v>30.8</v>
       </c>
       <c r="O35" t="n">
-        <v>35.8</v>
+        <v>33.7</v>
       </c>
       <c r="Q35" t="n">
-        <v>19.7</v>
+        <v>20.7</v>
       </c>
       <c r="R35" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>19.7</v>
+        <v>20.7</v>
       </c>
       <c r="V35" t="n">
-        <v>12</v>
+        <v>13.1</v>
       </c>
       <c r="W35" t="n">
-        <v>25.8</v>
+        <v>25.5</v>
       </c>
       <c r="X35" t="n">
-        <v>18.9</v>
+        <v>19.3</v>
       </c>
       <c r="Y35" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z35" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AA35" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AB35" t="n">
-        <v>-0.1</v>
+        <v>-1</v>
       </c>
       <c r="AC35" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="AF35" t="n">
-        <v>238.69</v>
+        <v>233.48</v>
       </c>
       <c r="AG35" t="n">
-        <v>-2.8</v>
+        <v>-4.86</v>
       </c>
       <c r="AH35" t="n">
         <v>215</v>
@@ -3874,10 +3874,10 @@
         <v>235</v>
       </c>
       <c r="AK35" t="n">
-        <v>134.59</v>
+        <v>136.6</v>
       </c>
       <c r="AL35" t="n">
-        <v>6.22</v>
+        <v>2.01</v>
       </c>
       <c r="AM35" t="n">
         <v>110</v>
@@ -3886,99 +3886,99 @@
         <v>142</v>
       </c>
       <c r="AP35" t="n">
-        <v>89.05</v>
+        <v>86.25</v>
       </c>
       <c r="AS35" t="n">
-        <v>17.06</v>
+        <v>17.13</v>
       </c>
       <c r="BL35" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B36" t="n">
-        <v>148.1</v>
+        <v>143.4</v>
       </c>
       <c r="C36" t="n">
-        <v>51.9</v>
+        <v>50.9</v>
       </c>
       <c r="D36" t="n">
-        <v>35.4</v>
+        <v>35.7</v>
       </c>
       <c r="E36" t="n">
-        <v>31.5</v>
+        <v>26.2</v>
       </c>
       <c r="F36" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="H36" t="n">
-        <v>21.8</v>
+        <v>22.9</v>
       </c>
       <c r="I36" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J36" t="n">
-        <v>39.6</v>
+        <v>39.9</v>
       </c>
       <c r="K36" t="n">
-        <v>71</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="M36" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="N36" t="n">
-        <v>30.8</v>
+        <v>31.2</v>
       </c>
       <c r="O36" t="n">
-        <v>33.7</v>
+        <v>33.1</v>
       </c>
       <c r="Q36" t="n">
-        <v>20.7</v>
+        <v>21.6</v>
       </c>
       <c r="R36" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>20.7</v>
+        <v>21.6</v>
       </c>
       <c r="V36" t="n">
-        <v>13.1</v>
+        <v>12.9</v>
       </c>
       <c r="W36" t="n">
-        <v>25.5</v>
+        <v>28.3</v>
       </c>
       <c r="X36" t="n">
-        <v>19.3</v>
+        <v>20.6</v>
       </c>
       <c r="Y36" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z36" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AA36" t="n">
-        <v>15.5</v>
+        <v>17.9</v>
       </c>
       <c r="AB36" t="n">
-        <v>-1</v>
+        <v>-0.8</v>
       </c>
       <c r="AC36" t="n">
-        <v>6.4</v>
+        <v>8.1</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="AF36" t="n">
-        <v>233.48</v>
+        <v>235.13</v>
       </c>
       <c r="AG36" t="n">
-        <v>-4.86</v>
+        <v>1.66</v>
       </c>
       <c r="AH36" t="n">
         <v>215</v>
@@ -3987,10 +3987,10 @@
         <v>235</v>
       </c>
       <c r="AK36" t="n">
-        <v>136.6</v>
+        <v>135.66</v>
       </c>
       <c r="AL36" t="n">
-        <v>2.01</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AM36" t="n">
         <v>110</v>
@@ -3999,57 +3999,57 @@
         <v>142</v>
       </c>
       <c r="AP36" t="n">
-        <v>86.25</v>
+        <v>88.27</v>
       </c>
       <c r="AS36" t="n">
-        <v>17.13</v>
+        <v>17.6</v>
       </c>
       <c r="BL36" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B37" t="n">
-        <v>143.4</v>
+        <v>144.9</v>
       </c>
       <c r="C37" t="n">
-        <v>50.9</v>
+        <v>53</v>
       </c>
       <c r="D37" t="n">
-        <v>35.7</v>
+        <v>35.6</v>
       </c>
       <c r="E37" t="n">
-        <v>26.2</v>
+        <v>26</v>
       </c>
       <c r="F37" t="n">
-        <v>4.3</v>
+        <v>2.8</v>
       </c>
       <c r="H37" t="n">
-        <v>22.9</v>
+        <v>24</v>
       </c>
       <c r="I37" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J37" t="n">
-        <v>39.9</v>
+        <v>40.3</v>
       </c>
       <c r="K37" t="n">
-        <v>72.59999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="M37" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="N37" t="n">
-        <v>31.2</v>
+        <v>31.6</v>
       </c>
       <c r="O37" t="n">
-        <v>33.1</v>
+        <v>33.6</v>
       </c>
       <c r="Q37" t="n">
-        <v>21.6</v>
+        <v>21</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -4058,40 +4058,40 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>21.6</v>
+        <v>21</v>
       </c>
       <c r="V37" t="n">
-        <v>12.9</v>
+        <v>14.4</v>
       </c>
       <c r="W37" t="n">
-        <v>28.3</v>
+        <v>27.7</v>
       </c>
       <c r="X37" t="n">
-        <v>20.6</v>
+        <v>21.1</v>
       </c>
       <c r="Y37" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z37" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AA37" t="n">
-        <v>17.9</v>
+        <v>16.3</v>
       </c>
       <c r="AB37" t="n">
-        <v>-0.8</v>
+        <v>-1.1</v>
       </c>
       <c r="AC37" t="n">
-        <v>8.1</v>
+        <v>6.6</v>
       </c>
       <c r="AD37" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="AF37" t="n">
-        <v>235.13</v>
+        <v>234.87</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.66</v>
+        <v>-0.26</v>
       </c>
       <c r="AH37" t="n">
         <v>215</v>
@@ -4100,10 +4100,10 @@
         <v>235</v>
       </c>
       <c r="AK37" t="n">
-        <v>135.66</v>
+        <v>136.33</v>
       </c>
       <c r="AL37" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="AM37" t="n">
         <v>110</v>
@@ -4112,99 +4112,60 @@
         <v>142</v>
       </c>
       <c r="AP37" t="n">
-        <v>88.27</v>
+        <v>87.09</v>
       </c>
       <c r="AS37" t="n">
-        <v>17.6</v>
+        <v>17.31</v>
       </c>
       <c r="BL37" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B38" t="n">
-        <v>144.9</v>
-      </c>
-      <c r="C38" t="n">
-        <v>53</v>
+        <v>132.2</v>
       </c>
       <c r="D38" t="n">
         <v>35.6</v>
       </c>
-      <c r="E38" t="n">
-        <v>26</v>
-      </c>
       <c r="F38" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="H38" t="n">
-        <v>24</v>
-      </c>
-      <c r="I38" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="J38" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="K38" t="n">
-        <v>73.7</v>
-      </c>
-      <c r="M38" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="N38" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="O38" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>21</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="V38" t="n">
-        <v>14.4</v>
+        <v>11.6</v>
       </c>
       <c r="W38" t="n">
-        <v>27.7</v>
+        <v>23.2</v>
       </c>
       <c r="X38" t="n">
-        <v>21.1</v>
+        <v>17.4</v>
       </c>
       <c r="Y38" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z38" t="n">
         <v>19</v>
       </c>
       <c r="AA38" t="n">
-        <v>16.3</v>
+        <v>13</v>
       </c>
       <c r="AB38" t="n">
-        <v>-1.1</v>
+        <v>0.9</v>
       </c>
       <c r="AC38" t="n">
-        <v>6.6</v>
+        <v>7.5</v>
       </c>
       <c r="AD38" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="AF38" t="n">
-        <v>234.87</v>
+        <v>234.78</v>
       </c>
       <c r="AG38" t="n">
-        <v>-0.26</v>
+        <v>-0.09</v>
       </c>
       <c r="AH38" t="n">
         <v>215</v>
@@ -4212,73 +4173,61 @@
       <c r="AI38" t="n">
         <v>235</v>
       </c>
-      <c r="AK38" t="n">
-        <v>136.33</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>0.67</v>
-      </c>
       <c r="AM38" t="n">
         <v>110</v>
       </c>
       <c r="AN38" t="n">
         <v>142</v>
       </c>
-      <c r="AP38" t="n">
-        <v>87.09</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>17.31</v>
-      </c>
       <c r="BL38" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B39" t="n">
-        <v>132.2</v>
+        <v>137.1</v>
       </c>
       <c r="D39" t="n">
-        <v>35.6</v>
+        <v>35.1</v>
       </c>
       <c r="F39" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="V39" t="n">
-        <v>11.6</v>
+        <v>11</v>
       </c>
       <c r="W39" t="n">
-        <v>23.2</v>
+        <v>22</v>
       </c>
       <c r="X39" t="n">
-        <v>17.4</v>
+        <v>16.5</v>
       </c>
       <c r="Y39" t="n">
         <v>7</v>
       </c>
       <c r="Z39" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AA39" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.9</v>
+        <v>-5.3</v>
       </c>
       <c r="AC39" t="n">
-        <v>7.5</v>
+        <v>6.1</v>
       </c>
       <c r="AD39" t="n">
-        <v>4.2</v>
+        <v>0.4</v>
       </c>
       <c r="AF39" t="n">
-        <v>234.78</v>
+        <v>229.75</v>
       </c>
       <c r="AG39" t="n">
-        <v>-0.09</v>
+        <v>-5.03</v>
       </c>
       <c r="AH39" t="n">
         <v>215</v>
@@ -4293,54 +4242,93 @@
         <v>142</v>
       </c>
       <c r="BL39" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B40" t="n">
-        <v>137.1</v>
+        <v>166.2</v>
+      </c>
+      <c r="C40" t="n">
+        <v>72.40000000000001</v>
       </c>
       <c r="D40" t="n">
-        <v>35.1</v>
+        <v>32.7</v>
+      </c>
+      <c r="E40" t="n">
+        <v>28.1</v>
       </c>
       <c r="F40" t="n">
         <v>3.3</v>
       </c>
+      <c r="H40" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="I40" t="n">
+        <v>9</v>
+      </c>
+      <c r="J40" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="K40" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="M40" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="N40" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="O40" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="R40" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>23.7</v>
+      </c>
       <c r="V40" t="n">
-        <v>11</v>
+        <v>7.9</v>
       </c>
       <c r="W40" t="n">
-        <v>22</v>
+        <v>15.6</v>
       </c>
       <c r="X40" t="n">
-        <v>16.5</v>
+        <v>11.8</v>
       </c>
       <c r="Y40" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z40" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AA40" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AB40" t="n">
-        <v>-5.3</v>
+        <v>-3.5</v>
       </c>
       <c r="AC40" t="n">
-        <v>6.1</v>
+        <v>8.4</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.4</v>
+        <v>2.5</v>
       </c>
       <c r="AF40" t="n">
-        <v>229.75</v>
+        <v>222.86</v>
       </c>
       <c r="AG40" t="n">
-        <v>-5.03</v>
+        <v>-6.9</v>
       </c>
       <c r="AH40" t="n">
         <v>215</v>
@@ -4348,100 +4336,112 @@
       <c r="AI40" t="n">
         <v>235</v>
       </c>
+      <c r="AK40" t="n">
+        <v>135.42</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>-0.91</v>
+      </c>
       <c r="AM40" t="n">
         <v>110</v>
       </c>
       <c r="AN40" t="n">
         <v>142</v>
       </c>
+      <c r="AP40" t="n">
+        <v>81.98</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>15.01</v>
+      </c>
       <c r="BL40" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B41" t="n">
-        <v>166.2</v>
+        <v>166.3</v>
       </c>
       <c r="C41" t="n">
-        <v>72.40000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="D41" t="n">
-        <v>32.7</v>
+        <v>32.8</v>
       </c>
       <c r="E41" t="n">
-        <v>28.1</v>
+        <v>28.8</v>
       </c>
       <c r="F41" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="H41" t="n">
         <v>23.4</v>
       </c>
       <c r="I41" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J41" t="n">
-        <v>42.1</v>
+        <v>41.2</v>
       </c>
       <c r="K41" t="n">
-        <v>74.5</v>
+        <v>73.8</v>
       </c>
       <c r="M41" t="n">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="N41" t="n">
-        <v>33.7</v>
+        <v>35.4</v>
       </c>
       <c r="O41" t="n">
-        <v>39.3</v>
+        <v>42.6</v>
       </c>
       <c r="Q41" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="R41" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="V41" t="n">
-        <v>7.9</v>
+        <v>6.7</v>
       </c>
       <c r="W41" t="n">
-        <v>15.6</v>
+        <v>18.1</v>
       </c>
       <c r="X41" t="n">
-        <v>11.8</v>
+        <v>12.4</v>
       </c>
       <c r="Y41" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Z41" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AA41" t="n">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AB41" t="n">
-        <v>-3.5</v>
+        <v>-2.9</v>
       </c>
       <c r="AC41" t="n">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.5</v>
+        <v>4.3</v>
       </c>
       <c r="AF41" t="n">
-        <v>222.86</v>
+        <v>218.37</v>
       </c>
       <c r="AG41" t="n">
-        <v>-6.9</v>
+        <v>-4.49</v>
       </c>
       <c r="AH41" t="n">
         <v>215</v>
@@ -4450,10 +4450,10 @@
         <v>235</v>
       </c>
       <c r="AK41" t="n">
-        <v>135.42</v>
+        <v>131.24</v>
       </c>
       <c r="AL41" t="n">
-        <v>-0.91</v>
+        <v>-4.18</v>
       </c>
       <c r="AM41" t="n">
         <v>110</v>
@@ -4462,99 +4462,99 @@
         <v>142</v>
       </c>
       <c r="AP41" t="n">
-        <v>81.98</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="AS41" t="n">
-        <v>15.01</v>
+        <v>12.97</v>
       </c>
       <c r="BL41" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B42" t="n">
-        <v>166.3</v>
+        <v>154.1</v>
       </c>
       <c r="C42" t="n">
-        <v>74.90000000000001</v>
+        <v>65</v>
       </c>
       <c r="D42" t="n">
-        <v>32.8</v>
+        <v>32</v>
       </c>
       <c r="E42" t="n">
-        <v>28.8</v>
+        <v>25.2</v>
       </c>
       <c r="F42" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="H42" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="I42" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="J42" t="n">
-        <v>41.2</v>
+        <v>38.5</v>
       </c>
       <c r="K42" t="n">
-        <v>73.8</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="M42" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="N42" t="n">
-        <v>35.4</v>
+        <v>32.3</v>
       </c>
       <c r="O42" t="n">
-        <v>42.6</v>
+        <v>40.3</v>
       </c>
       <c r="Q42" t="n">
-        <v>23.9</v>
+        <v>21.7</v>
       </c>
       <c r="R42" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="S42" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T42" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="V42" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="W42" t="n">
+        <v>21</v>
+      </c>
+      <c r="X42" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AD42" t="n">
         <v>3.9</v>
       </c>
-      <c r="S42" t="n">
-        <v>0</v>
-      </c>
-      <c r="T42" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="V42" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="W42" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="X42" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>11</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>-2.9</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AF42" t="n">
-        <v>218.37</v>
+        <v>218.04</v>
       </c>
       <c r="AG42" t="n">
-        <v>-4.49</v>
+        <v>-0.33</v>
       </c>
       <c r="AH42" t="n">
         <v>215</v>
@@ -4563,10 +4563,10 @@
         <v>235</v>
       </c>
       <c r="AK42" t="n">
-        <v>131.24</v>
+        <v>129.21</v>
       </c>
       <c r="AL42" t="n">
-        <v>-4.18</v>
+        <v>-2.03</v>
       </c>
       <c r="AM42" t="n">
         <v>110</v>
@@ -4575,99 +4575,99 @@
         <v>142</v>
       </c>
       <c r="AP42" t="n">
-        <v>79.98999999999999</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="AS42" t="n">
-        <v>12.97</v>
+        <v>15.23</v>
       </c>
       <c r="BL42" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B43" t="n">
-        <v>154.1</v>
+        <v>148.8</v>
       </c>
       <c r="C43" t="n">
-        <v>65</v>
+        <v>57.6</v>
       </c>
       <c r="D43" t="n">
-        <v>32</v>
+        <v>32.7</v>
       </c>
       <c r="E43" t="n">
-        <v>25.2</v>
+        <v>26.3</v>
       </c>
       <c r="F43" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="H43" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="I43" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="J43" t="n">
-        <v>38.5</v>
+        <v>41.6</v>
       </c>
       <c r="K43" t="n">
-        <v>70.90000000000001</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="M43" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="N43" t="n">
-        <v>32.3</v>
+        <v>35</v>
       </c>
       <c r="O43" t="n">
-        <v>40.3</v>
+        <v>42.4</v>
       </c>
       <c r="Q43" t="n">
         <v>21.7</v>
       </c>
       <c r="R43" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="S43" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
         <v>21.7</v>
       </c>
       <c r="V43" t="n">
-        <v>5.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W43" t="n">
-        <v>21</v>
+        <v>24.1</v>
       </c>
       <c r="X43" t="n">
-        <v>13.2</v>
+        <v>16.1</v>
       </c>
       <c r="Y43" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z43" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA43" t="n">
-        <v>14.5</v>
+        <v>15.6</v>
       </c>
       <c r="AB43" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="AC43" t="n">
-        <v>7.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AD43" t="n">
-        <v>3.9</v>
+        <v>6.3</v>
       </c>
       <c r="AF43" t="n">
-        <v>218.04</v>
+        <v>220.84</v>
       </c>
       <c r="AG43" t="n">
-        <v>-0.33</v>
+        <v>2.8</v>
       </c>
       <c r="AH43" t="n">
         <v>215</v>
@@ -4676,10 +4676,10 @@
         <v>235</v>
       </c>
       <c r="AK43" t="n">
-        <v>129.21</v>
+        <v>129.07</v>
       </c>
       <c r="AL43" t="n">
-        <v>-2.03</v>
+        <v>-0.14</v>
       </c>
       <c r="AM43" t="n">
         <v>110</v>
@@ -4688,99 +4688,99 @@
         <v>142</v>
       </c>
       <c r="AP43" t="n">
-        <v>82.90000000000001</v>
+        <v>85.52</v>
       </c>
       <c r="AS43" t="n">
-        <v>15.23</v>
+        <v>15.82</v>
       </c>
       <c r="BL43" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B44" t="n">
-        <v>148.8</v>
+        <v>146.8</v>
       </c>
       <c r="C44" t="n">
-        <v>57.6</v>
+        <v>52.8</v>
       </c>
       <c r="D44" t="n">
-        <v>32.7</v>
+        <v>33.6</v>
       </c>
       <c r="E44" t="n">
-        <v>26.3</v>
+        <v>28.9</v>
       </c>
       <c r="F44" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="H44" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="I44" t="n">
-        <v>8.9</v>
+        <v>9.1</v>
       </c>
       <c r="J44" t="n">
-        <v>41.6</v>
+        <v>40.8</v>
       </c>
       <c r="K44" t="n">
-        <v>74.09999999999999</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="M44" t="n">
-        <v>7.4</v>
+        <v>5.6</v>
       </c>
       <c r="N44" t="n">
-        <v>35</v>
+        <v>33.1</v>
       </c>
       <c r="O44" t="n">
-        <v>42.4</v>
+        <v>38.7</v>
       </c>
       <c r="Q44" t="n">
-        <v>21.7</v>
+        <v>22</v>
       </c>
       <c r="R44" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>21.7</v>
+        <v>22</v>
       </c>
       <c r="V44" t="n">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="W44" t="n">
-        <v>24.1</v>
+        <v>22.9</v>
       </c>
       <c r="X44" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA44" t="n">
         <v>16.1</v>
       </c>
-      <c r="Y44" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>19</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>15.6</v>
-      </c>
       <c r="AB44" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="AC44" t="n">
-        <v>9.699999999999999</v>
+        <v>7</v>
       </c>
       <c r="AD44" t="n">
-        <v>6.3</v>
+        <v>4.5</v>
       </c>
       <c r="AF44" t="n">
-        <v>220.84</v>
+        <v>225.87</v>
       </c>
       <c r="AG44" t="n">
-        <v>2.8</v>
+        <v>5.03</v>
       </c>
       <c r="AH44" t="n">
         <v>215</v>
@@ -4789,10 +4789,10 @@
         <v>235</v>
       </c>
       <c r="AK44" t="n">
-        <v>129.07</v>
+        <v>130.73</v>
       </c>
       <c r="AL44" t="n">
-        <v>-0.14</v>
+        <v>1.66</v>
       </c>
       <c r="AM44" t="n">
         <v>110</v>
@@ -4801,99 +4801,54 @@
         <v>142</v>
       </c>
       <c r="AP44" t="n">
-        <v>85.52</v>
+        <v>88.2</v>
       </c>
       <c r="AS44" t="n">
-        <v>15.82</v>
+        <v>15.76</v>
       </c>
       <c r="BL44" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B45" t="n">
-        <v>146.8</v>
-      </c>
-      <c r="C45" t="n">
-        <v>52.8</v>
+        <v>133.9</v>
       </c>
       <c r="D45" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="E45" t="n">
-        <v>28.9</v>
+        <v>34.7</v>
       </c>
       <c r="F45" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="H45" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="I45" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="J45" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="K45" t="n">
-        <v>73.59999999999999</v>
-      </c>
-      <c r="M45" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="N45" t="n">
-        <v>33.1</v>
-      </c>
-      <c r="O45" t="n">
-        <v>38.7</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>22</v>
-      </c>
-      <c r="R45" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="S45" t="n">
-        <v>0</v>
-      </c>
-      <c r="T45" t="n">
-        <v>22</v>
+        <v>3.3</v>
       </c>
       <c r="V45" t="n">
-        <v>11</v>
+        <v>14.3</v>
       </c>
       <c r="W45" t="n">
-        <v>22.9</v>
+        <v>21.7</v>
       </c>
       <c r="X45" t="n">
-        <v>16.9</v>
+        <v>18</v>
       </c>
       <c r="Y45" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z45" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AA45" t="n">
-        <v>16.1</v>
+        <v>15</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.9</v>
+        <v>-3.5</v>
       </c>
       <c r="AC45" t="n">
-        <v>7</v>
+        <v>3.2</v>
       </c>
       <c r="AD45" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>225.87</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>5.03</v>
+        <v>-0.1</v>
       </c>
       <c r="AH45" t="n">
         <v>215</v>
@@ -4901,67 +4856,55 @@
       <c r="AI45" t="n">
         <v>235</v>
       </c>
-      <c r="AK45" t="n">
-        <v>130.73</v>
-      </c>
-      <c r="AL45" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AM45" t="n">
         <v>110</v>
       </c>
       <c r="AN45" t="n">
         <v>142</v>
       </c>
-      <c r="AP45" t="n">
-        <v>88.2</v>
-      </c>
-      <c r="AS45" t="n">
-        <v>15.76</v>
-      </c>
       <c r="BL45" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B46" t="n">
-        <v>133.9</v>
+        <v>137.5</v>
       </c>
       <c r="D46" t="n">
-        <v>34.7</v>
+        <v>32.8</v>
       </c>
       <c r="F46" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="V46" t="n">
-        <v>14.3</v>
+        <v>9</v>
       </c>
       <c r="W46" t="n">
-        <v>21.7</v>
+        <v>15.7</v>
       </c>
       <c r="X46" t="n">
-        <v>18</v>
+        <v>12.3</v>
       </c>
       <c r="Y46" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z46" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="AA46" t="n">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="AB46" t="n">
-        <v>-3.5</v>
+        <v>-6.6</v>
       </c>
       <c r="AC46" t="n">
-        <v>3.2</v>
+        <v>8.1</v>
       </c>
       <c r="AD46" t="n">
-        <v>-0.1</v>
+        <v>0.8</v>
       </c>
       <c r="AH46" t="n">
         <v>215</v>
@@ -4976,48 +4919,93 @@
         <v>142</v>
       </c>
       <c r="BL46" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B47" t="n">
-        <v>137.5</v>
+        <v>157.1</v>
+      </c>
+      <c r="C47" t="n">
+        <v>73.09999999999999</v>
       </c>
       <c r="D47" t="n">
-        <v>32.8</v>
+        <v>31.7</v>
+      </c>
+      <c r="E47" t="n">
+        <v>26.1</v>
       </c>
       <c r="F47" t="n">
-        <v>2.3</v>
+        <v>2</v>
+      </c>
+      <c r="H47" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="I47" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="J47" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="K47" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="M47" t="n">
+        <v>6</v>
+      </c>
+      <c r="N47" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="O47" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="R47" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>23.8</v>
       </c>
       <c r="V47" t="n">
-        <v>9</v>
+        <v>6.8</v>
       </c>
       <c r="W47" t="n">
-        <v>15.7</v>
+        <v>11</v>
       </c>
       <c r="X47" t="n">
-        <v>12.3</v>
+        <v>8.9</v>
       </c>
       <c r="Y47" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="Z47" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA47" t="n">
-        <v>10.5</v>
+        <v>7.9</v>
       </c>
       <c r="AB47" t="n">
-        <v>-6.6</v>
+        <v>-1.2</v>
       </c>
       <c r="AC47" t="n">
-        <v>8.1</v>
+        <v>12.6</v>
       </c>
       <c r="AD47" t="n">
-        <v>0.8</v>
+        <v>5.7</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>224.2</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>-1.67</v>
       </c>
       <c r="AH47" t="n">
         <v>215</v>
@@ -5025,100 +5013,112 @@
       <c r="AI47" t="n">
         <v>235</v>
       </c>
+      <c r="AK47" t="n">
+        <v>128.6</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>-2.13</v>
+      </c>
       <c r="AM47" t="n">
         <v>110</v>
       </c>
       <c r="AN47" t="n">
         <v>142</v>
       </c>
+      <c r="AP47" t="n">
+        <v>81.18000000000001</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>14.06</v>
+      </c>
       <c r="BL47" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B48" t="n">
-        <v>157.1</v>
+        <v>153.1</v>
       </c>
       <c r="C48" t="n">
-        <v>73.09999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="D48" t="n">
-        <v>31.7</v>
+        <v>32.2</v>
       </c>
       <c r="E48" t="n">
-        <v>26.1</v>
+        <v>25.9</v>
       </c>
       <c r="F48" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="H48" t="n">
-        <v>23.6</v>
+        <v>24.4</v>
       </c>
       <c r="I48" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="J48" t="n">
-        <v>40.5</v>
+        <v>39.6</v>
       </c>
       <c r="K48" t="n">
-        <v>73.5</v>
+        <v>73.3</v>
       </c>
       <c r="M48" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="N48" t="n">
-        <v>33.4</v>
+        <v>34.4</v>
       </c>
       <c r="O48" t="n">
-        <v>39.5</v>
+        <v>40.1</v>
       </c>
       <c r="Q48" t="n">
         <v>23.8</v>
       </c>
       <c r="R48" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T48" t="n">
         <v>23.8</v>
       </c>
       <c r="V48" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="W48" t="n">
-        <v>11</v>
+        <v>15.2</v>
       </c>
       <c r="X48" t="n">
-        <v>8.9</v>
+        <v>10.9</v>
       </c>
       <c r="Y48" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Z48" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA48" t="n">
         <v>12</v>
       </c>
-      <c r="AA48" t="n">
-        <v>7.9</v>
-      </c>
       <c r="AB48" t="n">
-        <v>-1.2</v>
+        <v>1.7</v>
       </c>
       <c r="AC48" t="n">
-        <v>12.6</v>
+        <v>10</v>
       </c>
       <c r="AD48" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AF48" t="n">
-        <v>224.2</v>
+        <v>223.35</v>
       </c>
       <c r="AG48" t="n">
-        <v>-1.67</v>
+        <v>-0.85</v>
       </c>
       <c r="AH48" t="n">
         <v>215</v>
@@ -5127,10 +5127,10 @@
         <v>235</v>
       </c>
       <c r="AK48" t="n">
-        <v>128.6</v>
+        <v>127.19</v>
       </c>
       <c r="AL48" t="n">
-        <v>-2.13</v>
+        <v>-1.41</v>
       </c>
       <c r="AM48" t="n">
         <v>110</v>
@@ -5139,99 +5139,99 @@
         <v>142</v>
       </c>
       <c r="AP48" t="n">
-        <v>81.18000000000001</v>
+        <v>81.06</v>
       </c>
       <c r="AS48" t="n">
-        <v>14.06</v>
+        <v>13.63</v>
       </c>
       <c r="BL48" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B49" t="n">
-        <v>153.1</v>
+        <v>145.5</v>
       </c>
       <c r="C49" t="n">
-        <v>69.59999999999999</v>
+        <v>62.3</v>
       </c>
       <c r="D49" t="n">
-        <v>32.2</v>
+        <v>34</v>
       </c>
       <c r="E49" t="n">
-        <v>25.9</v>
+        <v>22.5</v>
       </c>
       <c r="F49" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="H49" t="n">
-        <v>24.4</v>
+        <v>24.8</v>
       </c>
       <c r="I49" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J49" t="n">
-        <v>39.6</v>
+        <v>40.8</v>
       </c>
       <c r="K49" t="n">
-        <v>73.3</v>
+        <v>75</v>
       </c>
       <c r="M49" t="n">
-        <v>5.7</v>
+        <v>6.9</v>
       </c>
       <c r="N49" t="n">
-        <v>34.4</v>
+        <v>30.4</v>
       </c>
       <c r="O49" t="n">
-        <v>40.1</v>
+        <v>37.3</v>
       </c>
       <c r="Q49" t="n">
-        <v>23.8</v>
+        <v>22.1</v>
       </c>
       <c r="R49" t="n">
-        <v>3.8</v>
+        <v>4.9</v>
       </c>
       <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="V49" t="n">
         <v>4</v>
       </c>
-      <c r="T49" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="V49" t="n">
-        <v>6.6</v>
-      </c>
       <c r="W49" t="n">
-        <v>15.2</v>
+        <v>22.9</v>
       </c>
       <c r="X49" t="n">
-        <v>10.9</v>
+        <v>13.4</v>
       </c>
       <c r="Y49" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="Z49" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AA49" t="n">
-        <v>12</v>
+        <v>12.9</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="AC49" t="n">
-        <v>10</v>
+        <v>12.7</v>
       </c>
       <c r="AD49" t="n">
-        <v>5.8</v>
+        <v>6.7</v>
       </c>
       <c r="AF49" t="n">
-        <v>223.35</v>
+        <v>223.06</v>
       </c>
       <c r="AG49" t="n">
-        <v>-0.85</v>
+        <v>-0.29</v>
       </c>
       <c r="AH49" t="n">
         <v>215</v>
@@ -5240,10 +5240,10 @@
         <v>235</v>
       </c>
       <c r="AK49" t="n">
-        <v>127.19</v>
+        <v>129.17</v>
       </c>
       <c r="AL49" t="n">
-        <v>-1.41</v>
+        <v>1.98</v>
       </c>
       <c r="AM49" t="n">
         <v>110</v>
@@ -5252,96 +5252,96 @@
         <v>142</v>
       </c>
       <c r="AP49" t="n">
-        <v>81.06</v>
+        <v>82.36</v>
       </c>
       <c r="AS49" t="n">
-        <v>13.63</v>
+        <v>13.91</v>
       </c>
       <c r="BL49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B50" t="n">
-        <v>145.5</v>
+        <v>148</v>
       </c>
       <c r="C50" t="n">
-        <v>62.3</v>
+        <v>61.6</v>
       </c>
       <c r="D50" t="n">
-        <v>34</v>
+        <v>33.9</v>
       </c>
       <c r="E50" t="n">
-        <v>22.5</v>
+        <v>25</v>
       </c>
       <c r="F50" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="H50" t="n">
-        <v>24.8</v>
+        <v>25.1</v>
       </c>
       <c r="I50" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="J50" t="n">
-        <v>40.8</v>
+        <v>39.5</v>
       </c>
       <c r="K50" t="n">
-        <v>75</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="M50" t="n">
-        <v>6.9</v>
+        <v>5.9</v>
       </c>
       <c r="N50" t="n">
-        <v>30.4</v>
+        <v>28.6</v>
       </c>
       <c r="O50" t="n">
-        <v>37.3</v>
+        <v>34.5</v>
       </c>
       <c r="Q50" t="n">
-        <v>22.1</v>
+        <v>23.3</v>
       </c>
       <c r="R50" t="n">
-        <v>4.9</v>
+        <v>3.9</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>22.1</v>
+        <v>23.3</v>
       </c>
       <c r="V50" t="n">
-        <v>4</v>
+        <v>7.8</v>
       </c>
       <c r="W50" t="n">
-        <v>22.9</v>
+        <v>26</v>
       </c>
       <c r="X50" t="n">
-        <v>13.4</v>
+        <v>16.9</v>
       </c>
       <c r="Y50" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="Z50" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AA50" t="n">
-        <v>12.9</v>
+        <v>11.6</v>
       </c>
       <c r="AB50" t="n">
-        <v>0.7</v>
+        <v>4.2</v>
       </c>
       <c r="AC50" t="n">
-        <v>12.7</v>
+        <v>11.4</v>
       </c>
       <c r="AD50" t="n">
-        <v>6.7</v>
+        <v>7.8</v>
       </c>
       <c r="AF50" t="n">
-        <v>223.06</v>
+        <v>222.77</v>
       </c>
       <c r="AG50" t="n">
         <v>-0.29</v>
@@ -5353,10 +5353,10 @@
         <v>235</v>
       </c>
       <c r="AK50" t="n">
-        <v>129.17</v>
+        <v>130.42</v>
       </c>
       <c r="AL50" t="n">
-        <v>1.98</v>
+        <v>1.25</v>
       </c>
       <c r="AM50" t="n">
         <v>110</v>
@@ -5365,60 +5365,60 @@
         <v>142</v>
       </c>
       <c r="AP50" t="n">
-        <v>82.36</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="AS50" t="n">
-        <v>13.91</v>
+        <v>14</v>
       </c>
       <c r="BL50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B51" t="n">
-        <v>148</v>
+        <v>135.5</v>
       </c>
       <c r="C51" t="n">
-        <v>61.6</v>
+        <v>47.7</v>
       </c>
       <c r="D51" t="n">
-        <v>33.9</v>
+        <v>34.2</v>
       </c>
       <c r="E51" t="n">
-        <v>25</v>
+        <v>24.1</v>
       </c>
       <c r="F51" t="n">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="H51" t="n">
-        <v>25.1</v>
+        <v>24.9</v>
       </c>
       <c r="I51" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="J51" t="n">
-        <v>39.5</v>
+        <v>38.4</v>
       </c>
       <c r="K51" t="n">
-        <v>74.09999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="M51" t="n">
-        <v>5.9</v>
+        <v>3</v>
       </c>
       <c r="N51" t="n">
-        <v>28.6</v>
+        <v>30.3</v>
       </c>
       <c r="O51" t="n">
-        <v>34.5</v>
+        <v>33.3</v>
       </c>
       <c r="Q51" t="n">
         <v>23.3</v>
       </c>
       <c r="R51" t="n">
-        <v>3.9</v>
+        <v>1</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -5427,37 +5427,37 @@
         <v>23.3</v>
       </c>
       <c r="V51" t="n">
-        <v>7.8</v>
+        <v>11.3</v>
       </c>
       <c r="W51" t="n">
-        <v>26</v>
+        <v>27.6</v>
       </c>
       <c r="X51" t="n">
-        <v>16.9</v>
+        <v>19.5</v>
       </c>
       <c r="Y51" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Z51" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="AA51" t="n">
-        <v>11.6</v>
+        <v>18.8</v>
       </c>
       <c r="AB51" t="n">
-        <v>4.2</v>
+        <v>1.8</v>
       </c>
       <c r="AC51" t="n">
-        <v>11.4</v>
+        <v>15.5</v>
       </c>
       <c r="AD51" t="n">
-        <v>7.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AF51" t="n">
-        <v>222.77</v>
+        <v>221.86</v>
       </c>
       <c r="AG51" t="n">
-        <v>-0.29</v>
+        <v>-0.91</v>
       </c>
       <c r="AH51" t="n">
         <v>215</v>
@@ -5466,10 +5466,10 @@
         <v>235</v>
       </c>
       <c r="AK51" t="n">
-        <v>130.42</v>
+        <v>129.71</v>
       </c>
       <c r="AL51" t="n">
-        <v>1.25</v>
+        <v>-0.71</v>
       </c>
       <c r="AM51" t="n">
         <v>110</v>
@@ -5478,99 +5478,54 @@
         <v>142</v>
       </c>
       <c r="AP51" t="n">
-        <v>80.90000000000001</v>
+        <v>86.42</v>
       </c>
       <c r="AS51" t="n">
-        <v>14</v>
+        <v>16.05</v>
       </c>
       <c r="BL51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B52" t="n">
-        <v>135.5</v>
-      </c>
-      <c r="C52" t="n">
-        <v>47.7</v>
+        <v>118.1</v>
       </c>
       <c r="D52" t="n">
-        <v>34.2</v>
-      </c>
-      <c r="E52" t="n">
-        <v>24.1</v>
+        <v>34.7</v>
       </c>
       <c r="F52" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H52" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="I52" t="n">
-        <v>10</v>
-      </c>
-      <c r="J52" t="n">
-        <v>38.4</v>
-      </c>
-      <c r="K52" t="n">
-        <v>73.2</v>
-      </c>
-      <c r="M52" t="n">
-        <v>3</v>
-      </c>
-      <c r="N52" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="O52" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="R52" t="n">
-        <v>1</v>
-      </c>
-      <c r="S52" t="n">
-        <v>0</v>
-      </c>
-      <c r="T52" t="n">
-        <v>23.3</v>
+        <v>3.3</v>
       </c>
       <c r="V52" t="n">
-        <v>11.3</v>
+        <v>14.1</v>
       </c>
       <c r="W52" t="n">
         <v>27.6</v>
       </c>
       <c r="X52" t="n">
-        <v>19.5</v>
+        <v>20.9</v>
       </c>
       <c r="Y52" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Z52" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA52" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="AC52" t="n">
-        <v>15.5</v>
+        <v>14.9</v>
       </c>
       <c r="AD52" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="AF52" t="n">
-        <v>221.86</v>
-      </c>
-      <c r="AG52" t="n">
-        <v>-0.91</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AH52" t="n">
         <v>215</v>
@@ -5578,67 +5533,55 @@
       <c r="AI52" t="n">
         <v>235</v>
       </c>
-      <c r="AK52" t="n">
-        <v>129.71</v>
-      </c>
-      <c r="AL52" t="n">
-        <v>-0.71</v>
-      </c>
       <c r="AM52" t="n">
         <v>110</v>
       </c>
       <c r="AN52" t="n">
         <v>142</v>
       </c>
-      <c r="AP52" t="n">
-        <v>86.42</v>
-      </c>
-      <c r="AS52" t="n">
-        <v>16.05</v>
-      </c>
       <c r="BL52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B53" t="n">
-        <v>118.1</v>
+        <v>100.3</v>
       </c>
       <c r="D53" t="n">
-        <v>34.7</v>
+        <v>34</v>
       </c>
       <c r="F53" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="V53" t="n">
-        <v>14.1</v>
+        <v>16</v>
       </c>
       <c r="W53" t="n">
-        <v>27.6</v>
+        <v>30.6</v>
       </c>
       <c r="X53" t="n">
-        <v>20.9</v>
+        <v>23.3</v>
       </c>
       <c r="Y53" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z53" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA53" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AB53" t="n">
-        <v>3.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC53" t="n">
-        <v>14.9</v>
+        <v>16.7</v>
       </c>
       <c r="AD53" t="n">
-        <v>9.199999999999999</v>
+        <v>12.8</v>
       </c>
       <c r="AH53" t="n">
         <v>215</v>
@@ -5653,48 +5596,93 @@
         <v>142</v>
       </c>
       <c r="BL53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="B54" t="n">
-        <v>100.3</v>
+        <v>104.9</v>
+      </c>
+      <c r="C54" t="n">
+        <v>36.3</v>
       </c>
       <c r="D54" t="n">
-        <v>34</v>
+        <v>32.7</v>
+      </c>
+      <c r="E54" t="n">
+        <v>17</v>
       </c>
       <c r="F54" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
+      </c>
+      <c r="H54" t="n">
+        <v>16</v>
+      </c>
+      <c r="I54" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="J54" t="n">
+        <v>25</v>
+      </c>
+      <c r="K54" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="M54" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N54" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="O54" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>10.5</v>
       </c>
       <c r="V54" t="n">
-        <v>16</v>
+        <v>15.8</v>
       </c>
       <c r="W54" t="n">
-        <v>30.6</v>
+        <v>33.6</v>
       </c>
       <c r="X54" t="n">
-        <v>23.3</v>
+        <v>24.7</v>
       </c>
       <c r="Y54" t="n">
         <v>16</v>
       </c>
       <c r="Z54" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA54" t="n">
-        <v>20</v>
+        <v>16.9</v>
       </c>
       <c r="AB54" t="n">
-        <v>8.800000000000001</v>
+        <v>4</v>
       </c>
       <c r="AC54" t="n">
-        <v>16.7</v>
+        <v>10.1</v>
       </c>
       <c r="AD54" t="n">
-        <v>12.8</v>
+        <v>7</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>234.9</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>13.04</v>
       </c>
       <c r="AH54" t="n">
         <v>215</v>
@@ -5702,58 +5690,70 @@
       <c r="AI54" t="n">
         <v>235</v>
       </c>
+      <c r="AK54" t="n">
+        <v>137.51</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>7.8</v>
+      </c>
       <c r="AM54" t="n">
         <v>110</v>
       </c>
       <c r="AN54" t="n">
         <v>142</v>
       </c>
+      <c r="AP54" t="n">
+        <v>94</v>
+      </c>
+      <c r="AS54" t="n">
+        <v>18.87</v>
+      </c>
       <c r="BL54" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="B55" t="n">
-        <v>104.9</v>
+        <v>134.9</v>
       </c>
       <c r="C55" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="D55" t="n">
         <v>36.3</v>
       </c>
-      <c r="D55" t="n">
-        <v>32.7</v>
-      </c>
       <c r="E55" t="n">
-        <v>17</v>
+        <v>20.6</v>
       </c>
       <c r="F55" t="n">
         <v>1.6</v>
       </c>
       <c r="H55" t="n">
-        <v>16</v>
+        <v>21.2</v>
       </c>
       <c r="I55" t="n">
-        <v>10.1</v>
+        <v>9.4</v>
       </c>
       <c r="J55" t="n">
-        <v>25</v>
+        <v>35.4</v>
       </c>
       <c r="K55" t="n">
-        <v>51.2</v>
+        <v>66</v>
       </c>
       <c r="M55" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="N55" t="n">
-        <v>25.5</v>
+        <v>24.8</v>
       </c>
       <c r="O55" t="n">
-        <v>27.3</v>
+        <v>26.7</v>
       </c>
       <c r="Q55" t="n">
-        <v>10.5</v>
+        <v>18.3</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
@@ -5762,40 +5762,40 @@
         <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>10.5</v>
+        <v>18.3</v>
       </c>
       <c r="V55" t="n">
-        <v>15.8</v>
+        <v>18.5</v>
       </c>
       <c r="W55" t="n">
-        <v>33.6</v>
+        <v>22.5</v>
       </c>
       <c r="X55" t="n">
-        <v>24.7</v>
+        <v>20.5</v>
       </c>
       <c r="Y55" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="Z55" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AA55" t="n">
-        <v>16.9</v>
+        <v>13.8</v>
       </c>
       <c r="AB55" t="n">
-        <v>4</v>
+        <v>1.3</v>
       </c>
       <c r="AC55" t="n">
-        <v>10.1</v>
+        <v>9.5</v>
       </c>
       <c r="AD55" t="n">
-        <v>7</v>
+        <v>5.4</v>
       </c>
       <c r="AF55" t="n">
-        <v>234.9</v>
+        <v>229.2</v>
       </c>
       <c r="AG55" t="n">
-        <v>13.04</v>
+        <v>-5.7</v>
       </c>
       <c r="AH55" t="n">
         <v>215</v>
@@ -5804,10 +5804,10 @@
         <v>235</v>
       </c>
       <c r="AK55" t="n">
-        <v>137.51</v>
+        <v>138.98</v>
       </c>
       <c r="AL55" t="n">
-        <v>7.8</v>
+        <v>1.47</v>
       </c>
       <c r="AM55" t="n">
         <v>110</v>
@@ -5816,57 +5816,57 @@
         <v>142</v>
       </c>
       <c r="AP55" t="n">
-        <v>94</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="AS55" t="n">
-        <v>18.87</v>
+        <v>16.02</v>
       </c>
       <c r="BL55" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B56" t="n">
-        <v>134.9</v>
+        <v>146.4</v>
       </c>
       <c r="C56" t="n">
-        <v>53.3</v>
+        <v>60.2</v>
       </c>
       <c r="D56" t="n">
-        <v>36.3</v>
+        <v>35.6</v>
       </c>
       <c r="E56" t="n">
-        <v>20.6</v>
+        <v>24.2</v>
       </c>
       <c r="F56" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="H56" t="n">
-        <v>21.2</v>
+        <v>23</v>
       </c>
       <c r="I56" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J56" t="n">
-        <v>35.4</v>
+        <v>38.2</v>
       </c>
       <c r="K56" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="M56" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="N56" t="n">
-        <v>24.8</v>
+        <v>30.2</v>
       </c>
       <c r="O56" t="n">
-        <v>26.7</v>
+        <v>31.9</v>
       </c>
       <c r="Q56" t="n">
-        <v>18.3</v>
+        <v>20.2</v>
       </c>
       <c r="R56" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
         <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>18.3</v>
+        <v>20.2</v>
       </c>
       <c r="Y56" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="Z56" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AA56" t="n">
-        <v>13.8</v>
+        <v>9.6</v>
       </c>
       <c r="AF56" t="n">
-        <v>229.2</v>
+        <v>224.9</v>
       </c>
       <c r="AG56" t="n">
-        <v>-5.7</v>
+        <v>-4.3</v>
       </c>
       <c r="AH56" t="n">
         <v>215</v>
@@ -5899,10 +5899,10 @@
         <v>235</v>
       </c>
       <c r="AK56" t="n">
-        <v>138.98</v>
+        <v>134.04</v>
       </c>
       <c r="AL56" t="n">
-        <v>1.47</v>
+        <v>-4.94</v>
       </c>
       <c r="AM56" t="n">
         <v>110</v>
@@ -5911,57 +5911,57 @@
         <v>142</v>
       </c>
       <c r="AP56" t="n">
-        <v>84.90000000000001</v>
+        <v>76.5</v>
       </c>
       <c r="AS56" t="n">
-        <v>16.02</v>
+        <v>13.68</v>
       </c>
       <c r="BL56" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B57" t="n">
-        <v>146.4</v>
+        <v>131.4</v>
       </c>
       <c r="C57" t="n">
-        <v>60.2</v>
+        <v>53.7</v>
       </c>
       <c r="D57" t="n">
-        <v>35.6</v>
+        <v>34.7</v>
       </c>
       <c r="E57" t="n">
-        <v>24.2</v>
+        <v>20.1</v>
       </c>
       <c r="F57" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="H57" t="n">
-        <v>23</v>
+        <v>24.1</v>
       </c>
       <c r="I57" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J57" t="n">
-        <v>38.2</v>
+        <v>37</v>
       </c>
       <c r="K57" t="n">
-        <v>70</v>
+        <v>69.8</v>
       </c>
       <c r="M57" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="N57" t="n">
-        <v>30.2</v>
+        <v>31.4</v>
       </c>
       <c r="O57" t="n">
-        <v>31.9</v>
+        <v>33.3</v>
       </c>
       <c r="Q57" t="n">
-        <v>20.2</v>
+        <v>22.3</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
@@ -5970,22 +5970,22 @@
         <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>20.2</v>
+        <v>22.3</v>
       </c>
       <c r="Y57" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z57" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AA57" t="n">
-        <v>9.6</v>
+        <v>14</v>
       </c>
       <c r="AF57" t="n">
-        <v>224.9</v>
+        <v>220.8</v>
       </c>
       <c r="AG57" t="n">
-        <v>-4.3</v>
+        <v>-4.1</v>
       </c>
       <c r="AH57" t="n">
         <v>215</v>
@@ -5994,10 +5994,10 @@
         <v>235</v>
       </c>
       <c r="AK57" t="n">
-        <v>134.04</v>
+        <v>131.01</v>
       </c>
       <c r="AL57" t="n">
-        <v>-4.94</v>
+        <v>-3.03</v>
       </c>
       <c r="AM57" t="n">
         <v>110</v>
@@ -6006,57 +6006,57 @@
         <v>142</v>
       </c>
       <c r="AP57" t="n">
-        <v>76.5</v>
+        <v>81.28</v>
       </c>
       <c r="AS57" t="n">
-        <v>13.68</v>
+        <v>13.92</v>
       </c>
       <c r="BL57" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B58" t="n">
-        <v>131.4</v>
+        <v>127.2</v>
       </c>
       <c r="C58" t="n">
-        <v>53.7</v>
+        <v>42.7</v>
       </c>
       <c r="D58" t="n">
-        <v>34.7</v>
+        <v>34.6</v>
       </c>
       <c r="E58" t="n">
-        <v>20.1</v>
+        <v>20.7</v>
       </c>
       <c r="F58" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="H58" t="n">
-        <v>24.1</v>
+        <v>21.2</v>
       </c>
       <c r="I58" t="n">
-        <v>8.6</v>
+        <v>9.1</v>
       </c>
       <c r="J58" t="n">
-        <v>37</v>
+        <v>36.8</v>
       </c>
       <c r="K58" t="n">
-        <v>69.8</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="M58" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="N58" t="n">
-        <v>31.4</v>
+        <v>27.9</v>
       </c>
       <c r="O58" t="n">
-        <v>33.3</v>
+        <v>29.8</v>
       </c>
       <c r="Q58" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
@@ -6065,22 +6065,22 @@
         <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="Y58" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="Z58" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AA58" t="n">
-        <v>14</v>
+        <v>19.7</v>
       </c>
       <c r="AF58" t="n">
-        <v>220.8</v>
+        <v>228.06</v>
       </c>
       <c r="AG58" t="n">
-        <v>-4.1</v>
+        <v>7.26</v>
       </c>
       <c r="AH58" t="n">
         <v>215</v>
@@ -6089,10 +6089,10 @@
         <v>235</v>
       </c>
       <c r="AK58" t="n">
-        <v>131.01</v>
+        <v>131.96</v>
       </c>
       <c r="AL58" t="n">
-        <v>-3.03</v>
+        <v>0.95</v>
       </c>
       <c r="AM58" t="n">
         <v>110</v>
@@ -6101,81 +6101,36 @@
         <v>142</v>
       </c>
       <c r="AP58" t="n">
-        <v>81.28</v>
+        <v>84.34</v>
       </c>
       <c r="AS58" t="n">
-        <v>13.92</v>
+        <v>17.57</v>
       </c>
       <c r="BL58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B59" t="n">
-        <v>127.2</v>
-      </c>
-      <c r="C59" t="n">
-        <v>42.7</v>
+        <v>116.2</v>
       </c>
       <c r="D59" t="n">
-        <v>34.6</v>
-      </c>
-      <c r="E59" t="n">
-        <v>20.7</v>
+        <v>35.4</v>
       </c>
       <c r="F59" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H59" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="I59" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="J59" t="n">
-        <v>36.8</v>
-      </c>
-      <c r="K59" t="n">
-        <v>67.09999999999999</v>
-      </c>
-      <c r="M59" t="n">
-        <v>2</v>
-      </c>
-      <c r="N59" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="O59" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="R59" t="n">
-        <v>0</v>
-      </c>
-      <c r="S59" t="n">
-        <v>0</v>
-      </c>
-      <c r="T59" t="n">
-        <v>22.2</v>
+        <v>4.5</v>
       </c>
       <c r="Y59" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="Z59" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AA59" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="AF59" t="n">
-        <v>228.06</v>
-      </c>
-      <c r="AG59" t="n">
-        <v>7.26</v>
+        <v>21</v>
       </c>
       <c r="AH59" t="n">
         <v>215</v>
@@ -6183,49 +6138,37 @@
       <c r="AI59" t="n">
         <v>235</v>
       </c>
-      <c r="AK59" t="n">
-        <v>131.96</v>
-      </c>
-      <c r="AL59" t="n">
-        <v>0.95</v>
-      </c>
       <c r="AM59" t="n">
         <v>110</v>
       </c>
       <c r="AN59" t="n">
         <v>142</v>
       </c>
-      <c r="AP59" t="n">
-        <v>84.34</v>
-      </c>
-      <c r="AS59" t="n">
-        <v>17.57</v>
-      </c>
       <c r="BL59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B60" t="n">
-        <v>116.2</v>
+        <v>105.5</v>
       </c>
       <c r="D60" t="n">
-        <v>35.4</v>
+        <v>34</v>
       </c>
       <c r="F60" t="n">
         <v>4.5</v>
       </c>
       <c r="Y60" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Z60" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AA60" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AH60" t="n">
         <v>215</v>
@@ -6240,18 +6183,18 @@
         <v>142</v>
       </c>
       <c r="BL60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="B61" t="n">
-        <v>105.5</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="D61" t="n">
-        <v>34</v>
+        <v>33.5</v>
       </c>
       <c r="F61" t="n">
         <v>4.5</v>
@@ -6260,10 +6203,10 @@
         <v>15</v>
       </c>
       <c r="Z61" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AA61" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AH61" t="n">
         <v>215</v>
@@ -6278,21 +6221,21 @@
         <v>142</v>
       </c>
       <c r="BL61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="B62" t="n">
-        <v>99.59999999999999</v>
+        <v>116.4</v>
       </c>
       <c r="D62" t="n">
-        <v>33.5</v>
+        <v>35.3</v>
       </c>
       <c r="F62" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="Y62" t="n">
         <v>15</v>
@@ -6316,7 +6259,7 @@
         <v>142</v>
       </c>
       <c r="BL62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -628,88 +628,55 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B2" t="n">
-        <v>157.5</v>
-      </c>
-      <c r="C2" t="n">
-        <v>68.5</v>
+        <v>137.6</v>
       </c>
       <c r="D2" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.7</v>
+        <v>35</v>
       </c>
       <c r="F2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H2" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="I2" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J2" t="n">
-        <v>41.4</v>
+        <v>6.5</v>
       </c>
       <c r="K2" t="n">
-        <v>76.09999999999999</v>
-      </c>
-      <c r="M2" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="N2" t="n">
-        <v>34.9</v>
+        <v>96.7</v>
       </c>
       <c r="O2" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>9</v>
-      </c>
-      <c r="T2" t="n">
-        <v>21.6</v>
+        <v>35.1</v>
       </c>
       <c r="V2" t="n">
-        <v>15.1</v>
+        <v>13.6</v>
       </c>
       <c r="W2" t="n">
-        <v>23.1</v>
+        <v>24.4</v>
       </c>
       <c r="X2" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="Y2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Z2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AA2" t="n">
-        <v>13.6</v>
+        <v>17.5</v>
       </c>
       <c r="AB2" t="n">
         <v>-0</v>
       </c>
       <c r="AC2" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="AF2" t="n">
-        <v>218.84</v>
+        <v>221.78</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.25</v>
+        <v>2.94</v>
       </c>
       <c r="AH2" t="n">
         <v>215</v>
@@ -718,10 +685,10 @@
         <v>235</v>
       </c>
       <c r="AK2" t="n">
-        <v>133.09</v>
+        <v>138.76</v>
       </c>
       <c r="AL2" t="n">
-        <v>2.7</v>
+        <v>5.67</v>
       </c>
       <c r="AM2" t="n">
         <v>110</v>
@@ -729,67 +696,61 @@
       <c r="AN2" t="n">
         <v>142</v>
       </c>
-      <c r="AP2" t="n">
-        <v>83.09999999999999</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>15.63</v>
-      </c>
       <c r="BL2" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B3" t="n">
-        <v>137.6</v>
+        <v>132.5</v>
       </c>
       <c r="D3" t="n">
-        <v>35</v>
+        <v>33.6</v>
       </c>
       <c r="F3" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="K3" t="n">
-        <v>96.7</v>
+        <v>97.8</v>
       </c>
       <c r="O3" t="n">
-        <v>35.1</v>
+        <v>31.6</v>
       </c>
       <c r="V3" t="n">
-        <v>13.6</v>
+        <v>14.8</v>
       </c>
       <c r="W3" t="n">
-        <v>24.4</v>
+        <v>24.7</v>
       </c>
       <c r="X3" t="n">
-        <v>19</v>
+        <v>19.8</v>
       </c>
       <c r="Y3" t="n">
         <v>14</v>
       </c>
       <c r="Z3" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AA3" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0</v>
+        <v>0.6</v>
       </c>
       <c r="AC3" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="AF3" t="n">
-        <v>221.78</v>
+        <v>224.78</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="AH3" t="n">
         <v>215</v>
@@ -798,10 +759,10 @@
         <v>235</v>
       </c>
       <c r="AK3" t="n">
-        <v>138.76</v>
+        <v>143.55</v>
       </c>
       <c r="AL3" t="n">
-        <v>5.67</v>
+        <v>4.79</v>
       </c>
       <c r="AM3" t="n">
         <v>110</v>
@@ -810,60 +771,93 @@
         <v>142</v>
       </c>
       <c r="BL3" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B4" t="n">
-        <v>132.5</v>
+        <v>137.2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>56.3</v>
       </c>
       <c r="D4" t="n">
-        <v>33.6</v>
+        <v>32.1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>21.2</v>
       </c>
       <c r="F4" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
+      </c>
+      <c r="H4" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="I4" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="J4" t="n">
+        <v>40.4</v>
       </c>
       <c r="K4" t="n">
-        <v>97.8</v>
+        <v>75.7</v>
+      </c>
+      <c r="M4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N4" t="n">
+        <v>29</v>
       </c>
       <c r="O4" t="n">
-        <v>31.6</v>
+        <v>32.6</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>21.6</v>
       </c>
       <c r="V4" t="n">
-        <v>14.8</v>
+        <v>10.7</v>
       </c>
       <c r="W4" t="n">
-        <v>24.7</v>
+        <v>24.3</v>
       </c>
       <c r="X4" t="n">
-        <v>19.8</v>
+        <v>17.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Z4" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AA4" t="n">
-        <v>16.5</v>
+        <v>15.4</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="AF4" t="n">
-        <v>224.78</v>
+        <v>232.22</v>
       </c>
       <c r="AG4" t="n">
-        <v>3</v>
+        <v>7.43</v>
       </c>
       <c r="AH4" t="n">
         <v>215</v>
@@ -872,10 +866,10 @@
         <v>235</v>
       </c>
       <c r="AK4" t="n">
-        <v>143.55</v>
+        <v>143.61</v>
       </c>
       <c r="AL4" t="n">
-        <v>4.79</v>
+        <v>0.06</v>
       </c>
       <c r="AM4" t="n">
         <v>110</v>
@@ -883,52 +877,58 @@
       <c r="AN4" t="n">
         <v>142</v>
       </c>
+      <c r="AP4" t="n">
+        <v>89.31999999999999</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>18.02</v>
+      </c>
       <c r="BL4" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="B5" t="n">
-        <v>137.2</v>
+        <v>157.5</v>
       </c>
       <c r="C5" t="n">
-        <v>56.3</v>
+        <v>59.6</v>
       </c>
       <c r="D5" t="n">
-        <v>32.1</v>
+        <v>35</v>
       </c>
       <c r="E5" t="n">
-        <v>21.2</v>
+        <v>30.6</v>
       </c>
       <c r="F5" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="H5" t="n">
-        <v>23.7</v>
+        <v>24.2</v>
       </c>
       <c r="I5" t="n">
-        <v>11.6</v>
+        <v>11.2</v>
       </c>
       <c r="J5" t="n">
-        <v>40.4</v>
+        <v>38.9</v>
       </c>
       <c r="K5" t="n">
-        <v>75.7</v>
+        <v>74.3</v>
       </c>
       <c r="M5" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="N5" t="n">
-        <v>29</v>
+        <v>33.4</v>
       </c>
       <c r="O5" t="n">
-        <v>32.6</v>
+        <v>37.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="R5" t="n">
         <v>1.3</v>
@@ -937,40 +937,40 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="V5" t="n">
-        <v>10.7</v>
+        <v>13</v>
       </c>
       <c r="W5" t="n">
-        <v>24.3</v>
+        <v>26.3</v>
       </c>
       <c r="X5" t="n">
-        <v>17.5</v>
+        <v>19.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA5" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.9</v>
+        <v>-2.1</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="AF5" t="n">
-        <v>232.22</v>
+        <v>229.69</v>
       </c>
       <c r="AG5" t="n">
-        <v>7.43</v>
+        <v>-2.53</v>
       </c>
       <c r="AH5" t="n">
         <v>215</v>
@@ -979,10 +979,10 @@
         <v>235</v>
       </c>
       <c r="AK5" t="n">
-        <v>143.61</v>
+        <v>136.96</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.06</v>
+        <v>-6.65</v>
       </c>
       <c r="AM5" t="n">
         <v>110</v>
@@ -991,99 +991,99 @@
         <v>142</v>
       </c>
       <c r="AP5" t="n">
-        <v>89.31999999999999</v>
+        <v>86.59</v>
       </c>
       <c r="AS5" t="n">
-        <v>18.02</v>
+        <v>16.96</v>
       </c>
       <c r="BL5" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B6" t="n">
-        <v>157.5</v>
+        <v>159.6</v>
       </c>
       <c r="C6" t="n">
-        <v>59.6</v>
+        <v>63</v>
       </c>
       <c r="D6" t="n">
-        <v>35</v>
+        <v>34.5</v>
       </c>
       <c r="E6" t="n">
-        <v>30.6</v>
+        <v>31.1</v>
       </c>
       <c r="F6" t="n">
-        <v>7.5</v>
+        <v>5.7</v>
       </c>
       <c r="H6" t="n">
-        <v>24.2</v>
+        <v>23.8</v>
       </c>
       <c r="I6" t="n">
-        <v>11.2</v>
+        <v>10.8</v>
       </c>
       <c r="J6" t="n">
-        <v>38.9</v>
+        <v>40.5</v>
       </c>
       <c r="K6" t="n">
-        <v>74.3</v>
+        <v>75.2</v>
       </c>
       <c r="M6" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="N6" t="n">
-        <v>33.4</v>
+        <v>34.3</v>
       </c>
       <c r="O6" t="n">
-        <v>37.1</v>
+        <v>38.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T6" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="V6" t="n">
-        <v>13</v>
+        <v>17.5</v>
       </c>
       <c r="W6" t="n">
-        <v>26.3</v>
+        <v>22.5</v>
       </c>
       <c r="X6" t="n">
-        <v>19.6</v>
+        <v>20</v>
       </c>
       <c r="Y6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA6" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>-2.1</v>
+        <v>-2.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="AF6" t="n">
-        <v>229.69</v>
+        <v>228.57</v>
       </c>
       <c r="AG6" t="n">
-        <v>-2.53</v>
+        <v>-1.14</v>
       </c>
       <c r="AH6" t="n">
         <v>215</v>
@@ -1092,10 +1092,10 @@
         <v>235</v>
       </c>
       <c r="AK6" t="n">
-        <v>136.96</v>
+        <v>133.01</v>
       </c>
       <c r="AL6" t="n">
-        <v>-6.65</v>
+        <v>-3.95</v>
       </c>
       <c r="AM6" t="n">
         <v>110</v>
@@ -1104,99 +1104,99 @@
         <v>142</v>
       </c>
       <c r="AP6" t="n">
-        <v>86.59</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="AS6" t="n">
-        <v>16.96</v>
+        <v>15.95</v>
       </c>
       <c r="BL6" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B7" t="n">
-        <v>159.6</v>
+        <v>160.4</v>
       </c>
       <c r="C7" t="n">
-        <v>63</v>
+        <v>62.6</v>
       </c>
       <c r="D7" t="n">
-        <v>34.5</v>
+        <v>35</v>
       </c>
       <c r="E7" t="n">
-        <v>31.1</v>
+        <v>32.2</v>
       </c>
       <c r="F7" t="n">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="H7" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="I7" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="J7" t="n">
-        <v>40.5</v>
+        <v>41.1</v>
       </c>
       <c r="K7" t="n">
-        <v>75.2</v>
+        <v>75.7</v>
       </c>
       <c r="M7" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="N7" t="n">
-        <v>34.3</v>
+        <v>32.6</v>
       </c>
       <c r="O7" t="n">
-        <v>38.2</v>
+        <v>38</v>
       </c>
       <c r="Q7" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T7" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="V7" t="n">
-        <v>17.5</v>
+        <v>16.4</v>
       </c>
       <c r="W7" t="n">
-        <v>22.5</v>
+        <v>22.8</v>
       </c>
       <c r="X7" t="n">
-        <v>20</v>
+        <v>19.6</v>
       </c>
       <c r="Y7" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Z7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA7" t="n">
-        <v>13.5</v>
+        <v>14.1</v>
       </c>
       <c r="AB7" t="n">
-        <v>-2.2</v>
+        <v>-3.1</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="AF7" t="n">
-        <v>228.57</v>
+        <v>225.08</v>
       </c>
       <c r="AG7" t="n">
-        <v>-1.14</v>
+        <v>-3.5</v>
       </c>
       <c r="AH7" t="n">
         <v>215</v>
@@ -1205,10 +1205,10 @@
         <v>235</v>
       </c>
       <c r="AK7" t="n">
-        <v>133.01</v>
+        <v>135.24</v>
       </c>
       <c r="AL7" t="n">
-        <v>-3.95</v>
+        <v>2.23</v>
       </c>
       <c r="AM7" t="n">
         <v>110</v>
@@ -1217,99 +1217,99 @@
         <v>142</v>
       </c>
       <c r="AP7" t="n">
-        <v>84.59999999999999</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="AS7" t="n">
-        <v>15.95</v>
+        <v>15.4</v>
       </c>
       <c r="BL7" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B8" t="n">
-        <v>160.4</v>
+        <v>161.7</v>
       </c>
       <c r="C8" t="n">
-        <v>62.6</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>35</v>
+        <v>34.9</v>
       </c>
       <c r="E8" t="n">
-        <v>32.2</v>
+        <v>27.3</v>
       </c>
       <c r="F8" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H8" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="I8" t="n">
-        <v>10.7</v>
+        <v>10.3</v>
       </c>
       <c r="J8" t="n">
-        <v>41.1</v>
+        <v>42.6</v>
       </c>
       <c r="K8" t="n">
-        <v>75.7</v>
+        <v>77</v>
       </c>
       <c r="M8" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="N8" t="n">
-        <v>32.6</v>
+        <v>31.5</v>
       </c>
       <c r="O8" t="n">
-        <v>38</v>
+        <v>37.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="R8" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T8" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="V8" t="n">
-        <v>16.4</v>
+        <v>12.7</v>
       </c>
       <c r="W8" t="n">
-        <v>22.8</v>
+        <v>27</v>
       </c>
       <c r="X8" t="n">
-        <v>19.6</v>
+        <v>19.9</v>
       </c>
       <c r="Y8" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Z8" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AA8" t="n">
-        <v>14.1</v>
+        <v>11.4</v>
       </c>
       <c r="AB8" t="n">
-        <v>-3.1</v>
+        <v>-5.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.6</v>
+        <v>-0.3</v>
       </c>
       <c r="AF8" t="n">
-        <v>225.08</v>
+        <v>225</v>
       </c>
       <c r="AG8" t="n">
-        <v>-3.5</v>
+        <v>-0.08</v>
       </c>
       <c r="AH8" t="n">
         <v>215</v>
@@ -1318,10 +1318,10 @@
         <v>235</v>
       </c>
       <c r="AK8" t="n">
-        <v>135.24</v>
+        <v>134.62</v>
       </c>
       <c r="AL8" t="n">
-        <v>2.23</v>
+        <v>-0.62</v>
       </c>
       <c r="AM8" t="n">
         <v>110</v>
@@ -1330,99 +1330,60 @@
         <v>142</v>
       </c>
       <c r="AP8" t="n">
-        <v>84.09999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="AS8" t="n">
-        <v>15.4</v>
+        <v>13.86</v>
       </c>
       <c r="BL8" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B9" t="n">
-        <v>161.7</v>
-      </c>
-      <c r="C9" t="n">
-        <v>71.09999999999999</v>
+        <v>151.5</v>
       </c>
       <c r="D9" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="E9" t="n">
-        <v>27.3</v>
+        <v>35.1</v>
       </c>
       <c r="F9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H9" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I9" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="J9" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="K9" t="n">
-        <v>77</v>
-      </c>
-      <c r="M9" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="N9" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="O9" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>21</v>
-      </c>
-      <c r="R9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="S9" t="n">
-        <v>6</v>
-      </c>
-      <c r="T9" t="n">
-        <v>21</v>
+        <v>5.4</v>
       </c>
       <c r="V9" t="n">
-        <v>12.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W9" t="n">
-        <v>27</v>
+        <v>19.4</v>
       </c>
       <c r="X9" t="n">
-        <v>19.9</v>
+        <v>14</v>
       </c>
       <c r="Y9" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA9" t="n">
         <v>9</v>
       </c>
-      <c r="Z9" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>11.4</v>
-      </c>
       <c r="AB9" t="n">
-        <v>-5.2</v>
+        <v>-4.7</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.6</v>
+        <v>1.9</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0.3</v>
+        <v>-1.4</v>
       </c>
       <c r="AF9" t="n">
-        <v>225</v>
+        <v>221.37</v>
       </c>
       <c r="AG9" t="n">
-        <v>-0.08</v>
+        <v>0.05</v>
       </c>
       <c r="AH9" t="n">
         <v>215</v>
@@ -1431,10 +1392,10 @@
         <v>235</v>
       </c>
       <c r="AK9" t="n">
-        <v>134.62</v>
+        <v>135.21</v>
       </c>
       <c r="AL9" t="n">
-        <v>-0.62</v>
+        <v>0.59</v>
       </c>
       <c r="AM9" t="n">
         <v>110</v>
@@ -1442,61 +1403,61 @@
       <c r="AN9" t="n">
         <v>142</v>
       </c>
-      <c r="AP9" t="n">
-        <v>80.2</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>13.86</v>
-      </c>
       <c r="BL9" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B10" t="n">
-        <v>151.5</v>
+        <v>145.2</v>
       </c>
       <c r="D10" t="n">
-        <v>35.1</v>
+        <v>33.5</v>
       </c>
       <c r="F10" t="n">
-        <v>5.4</v>
+        <v>5</v>
+      </c>
+      <c r="K10" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="O10" t="n">
+        <v>35.5</v>
       </c>
       <c r="V10" t="n">
-        <v>8.699999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="W10" t="n">
-        <v>19.4</v>
+        <v>19.2</v>
       </c>
       <c r="X10" t="n">
-        <v>14</v>
+        <v>13.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z10" t="n">
         <v>13</v>
       </c>
       <c r="AA10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB10" t="n">
-        <v>-4.7</v>
+        <v>-5.4</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>-1.4</v>
+        <v>-1.5</v>
       </c>
       <c r="AF10" t="n">
-        <v>221.37</v>
+        <v>224.37</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.05</v>
+        <v>3</v>
       </c>
       <c r="AH10" t="n">
         <v>215</v>
@@ -1505,10 +1466,10 @@
         <v>235</v>
       </c>
       <c r="AK10" t="n">
-        <v>135.21</v>
+        <v>135.61</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.59</v>
+        <v>0.4</v>
       </c>
       <c r="AM10" t="n">
         <v>110</v>
@@ -1517,60 +1478,60 @@
         <v>142</v>
       </c>
       <c r="BL10" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B11" t="n">
-        <v>145.2</v>
+        <v>146.3</v>
       </c>
       <c r="D11" t="n">
-        <v>33.5</v>
+        <v>33.4</v>
       </c>
       <c r="F11" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="K11" t="n">
-        <v>100.3</v>
+        <v>98.2</v>
       </c>
       <c r="O11" t="n">
-        <v>35.5</v>
+        <v>35.1</v>
       </c>
       <c r="V11" t="n">
-        <v>7.1</v>
+        <v>4.9</v>
       </c>
       <c r="W11" t="n">
-        <v>19.2</v>
+        <v>16.4</v>
       </c>
       <c r="X11" t="n">
-        <v>13.1</v>
+        <v>10.6</v>
       </c>
       <c r="Y11" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z11" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB11" t="n">
-        <v>-5.4</v>
+        <v>-6.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.4</v>
+        <v>-0.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>-1.5</v>
+        <v>-3.3</v>
       </c>
       <c r="AF11" t="n">
-        <v>224.37</v>
+        <v>225.93</v>
       </c>
       <c r="AG11" t="n">
-        <v>3</v>
+        <v>1.56</v>
       </c>
       <c r="AH11" t="n">
         <v>215</v>
@@ -1579,10 +1540,10 @@
         <v>235</v>
       </c>
       <c r="AK11" t="n">
-        <v>135.61</v>
+        <v>135.28</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.4</v>
+        <v>-0.33</v>
       </c>
       <c r="AM11" t="n">
         <v>110</v>
@@ -1591,60 +1552,93 @@
         <v>142</v>
       </c>
       <c r="BL11" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B12" t="n">
-        <v>146.3</v>
+        <v>182.8</v>
+      </c>
+      <c r="C12" t="n">
+        <v>86.8</v>
       </c>
       <c r="D12" t="n">
-        <v>33.4</v>
+        <v>31.8</v>
+      </c>
+      <c r="E12" t="n">
+        <v>33</v>
       </c>
       <c r="F12" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
+      </c>
+      <c r="H12" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="I12" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J12" t="n">
+        <v>41.1</v>
       </c>
       <c r="K12" t="n">
-        <v>98.2</v>
+        <v>74.2</v>
+      </c>
+      <c r="M12" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="N12" t="n">
+        <v>33.5</v>
       </c>
       <c r="O12" t="n">
-        <v>35.1</v>
+        <v>38.4</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="n">
+        <v>22.4</v>
       </c>
       <c r="V12" t="n">
-        <v>4.9</v>
+        <v>9.1</v>
       </c>
       <c r="W12" t="n">
-        <v>16.4</v>
+        <v>15</v>
       </c>
       <c r="X12" t="n">
-        <v>10.6</v>
+        <v>12.1</v>
       </c>
       <c r="Y12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z12" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AA12" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>-6.4</v>
+        <v>-10.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>-0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>-3.3</v>
+        <v>-5.1</v>
       </c>
       <c r="AF12" t="n">
-        <v>225.93</v>
+        <v>218.63</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.56</v>
+        <v>-7.3</v>
       </c>
       <c r="AH12" t="n">
         <v>215</v>
@@ -1653,10 +1647,10 @@
         <v>235</v>
       </c>
       <c r="AK12" t="n">
-        <v>135.28</v>
+        <v>126.27</v>
       </c>
       <c r="AL12" t="n">
-        <v>-0.33</v>
+        <v>-9.01</v>
       </c>
       <c r="AM12" t="n">
         <v>110</v>
@@ -1664,94 +1658,100 @@
       <c r="AN12" t="n">
         <v>142</v>
       </c>
+      <c r="AP12" t="n">
+        <v>82.66</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>14.7</v>
+      </c>
       <c r="BL12" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B13" t="n">
-        <v>182.8</v>
+        <v>181.8</v>
       </c>
       <c r="C13" t="n">
-        <v>86.8</v>
+        <v>86.5</v>
       </c>
       <c r="D13" t="n">
-        <v>31.8</v>
+        <v>31.4</v>
       </c>
       <c r="E13" t="n">
-        <v>33</v>
+        <v>34.2</v>
       </c>
       <c r="F13" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="H13" t="n">
-        <v>23.5</v>
+        <v>24.4</v>
       </c>
       <c r="I13" t="n">
-        <v>9.6</v>
+        <v>10.4</v>
       </c>
       <c r="J13" t="n">
-        <v>41.1</v>
+        <v>41.9</v>
       </c>
       <c r="K13" t="n">
-        <v>74.2</v>
+        <v>76.8</v>
       </c>
       <c r="M13" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="N13" t="n">
-        <v>33.5</v>
+        <v>35.7</v>
       </c>
       <c r="O13" t="n">
-        <v>38.4</v>
+        <v>39.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>22.4</v>
+        <v>23</v>
       </c>
       <c r="R13" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>20.1</v>
       </c>
       <c r="T13" t="n">
-        <v>22.4</v>
+        <v>23</v>
       </c>
       <c r="V13" t="n">
-        <v>9.1</v>
+        <v>7.1</v>
       </c>
       <c r="W13" t="n">
-        <v>15</v>
+        <v>14.8</v>
       </c>
       <c r="X13" t="n">
-        <v>12.1</v>
+        <v>10.9</v>
       </c>
       <c r="Y13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z13" t="n">
         <v>12</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AB13" t="n">
-        <v>-10.5</v>
+        <v>-4.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>-5.1</v>
+        <v>-1.4</v>
       </c>
       <c r="AF13" t="n">
-        <v>218.63</v>
+        <v>216.39</v>
       </c>
       <c r="AG13" t="n">
-        <v>-7.3</v>
+        <v>-2.23</v>
       </c>
       <c r="AH13" t="n">
         <v>215</v>
@@ -1760,10 +1760,10 @@
         <v>235</v>
       </c>
       <c r="AK13" t="n">
-        <v>126.27</v>
+        <v>123.32</v>
       </c>
       <c r="AL13" t="n">
-        <v>-9.01</v>
+        <v>-2.95</v>
       </c>
       <c r="AM13" t="n">
         <v>110</v>
@@ -1772,99 +1772,99 @@
         <v>142</v>
       </c>
       <c r="AP13" t="n">
-        <v>82.66</v>
+        <v>79.08</v>
       </c>
       <c r="AS13" t="n">
-        <v>14.7</v>
+        <v>13.91</v>
       </c>
       <c r="BL13" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B14" t="n">
-        <v>181.8</v>
+        <v>183</v>
       </c>
       <c r="C14" t="n">
-        <v>86.5</v>
+        <v>84.7</v>
       </c>
       <c r="D14" t="n">
-        <v>31.4</v>
+        <v>30.9</v>
       </c>
       <c r="E14" t="n">
-        <v>34.2</v>
+        <v>33.7</v>
       </c>
       <c r="F14" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="H14" t="n">
-        <v>24.4</v>
+        <v>23.4</v>
       </c>
       <c r="I14" t="n">
-        <v>10.4</v>
+        <v>10.6</v>
       </c>
       <c r="J14" t="n">
-        <v>41.9</v>
+        <v>42.3</v>
       </c>
       <c r="K14" t="n">
-        <v>76.8</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="N14" t="n">
-        <v>35.7</v>
+        <v>36.7</v>
       </c>
       <c r="O14" t="n">
-        <v>39.8</v>
+        <v>40.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>23</v>
+        <v>23.6</v>
       </c>
       <c r="R14" t="n">
         <v>1.8</v>
       </c>
       <c r="S14" t="n">
-        <v>20.1</v>
+        <v>20.8</v>
       </c>
       <c r="T14" t="n">
-        <v>23</v>
+        <v>23.6</v>
       </c>
       <c r="V14" t="n">
-        <v>7.1</v>
+        <v>5.7</v>
       </c>
       <c r="W14" t="n">
-        <v>14.8</v>
+        <v>16.1</v>
       </c>
       <c r="X14" t="n">
         <v>10.9</v>
       </c>
       <c r="Y14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA14" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AB14" t="n">
-        <v>-4.5</v>
+        <v>0.8</v>
       </c>
       <c r="AC14" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD14" t="n">
         <v>1.8</v>
       </c>
-      <c r="AD14" t="n">
-        <v>-1.4</v>
-      </c>
       <c r="AF14" t="n">
-        <v>216.39</v>
+        <v>217.16</v>
       </c>
       <c r="AG14" t="n">
-        <v>-2.23</v>
+        <v>0.76</v>
       </c>
       <c r="AH14" t="n">
         <v>215</v>
@@ -1873,10 +1873,10 @@
         <v>235</v>
       </c>
       <c r="AK14" t="n">
-        <v>123.32</v>
+        <v>117.87</v>
       </c>
       <c r="AL14" t="n">
-        <v>-2.95</v>
+        <v>-5.45</v>
       </c>
       <c r="AM14" t="n">
         <v>110</v>
@@ -1885,99 +1885,66 @@
         <v>142</v>
       </c>
       <c r="AP14" t="n">
-        <v>79.08</v>
+        <v>78.56</v>
       </c>
       <c r="AS14" t="n">
-        <v>13.91</v>
+        <v>13.45</v>
       </c>
       <c r="BL14" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B15" t="n">
-        <v>183</v>
-      </c>
-      <c r="C15" t="n">
-        <v>84.7</v>
+        <v>163.8</v>
       </c>
       <c r="D15" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="E15" t="n">
-        <v>33.7</v>
+        <v>29</v>
       </c>
       <c r="F15" t="n">
-        <v>7</v>
-      </c>
-      <c r="H15" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="I15" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="J15" t="n">
-        <v>42.3</v>
+        <v>6.5</v>
       </c>
       <c r="K15" t="n">
-        <v>76.40000000000001</v>
-      </c>
-      <c r="M15" t="n">
-        <v>4</v>
-      </c>
-      <c r="N15" t="n">
-        <v>36.7</v>
+        <v>101.2</v>
       </c>
       <c r="O15" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S15" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="T15" t="n">
-        <v>23.6</v>
+        <v>40.2</v>
       </c>
       <c r="V15" t="n">
-        <v>5.7</v>
+        <v>6.3</v>
       </c>
       <c r="W15" t="n">
-        <v>16.1</v>
+        <v>17.2</v>
       </c>
       <c r="X15" t="n">
-        <v>10.9</v>
+        <v>11.8</v>
       </c>
       <c r="Y15" t="n">
         <v>8</v>
       </c>
       <c r="Z15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA15" t="n">
         <v>10</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.7</v>
+        <v>4.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="AF15" t="n">
-        <v>217.16</v>
+        <v>220.31</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.76</v>
+        <v>3.16</v>
       </c>
       <c r="AH15" t="n">
         <v>215</v>
@@ -1986,10 +1953,10 @@
         <v>235</v>
       </c>
       <c r="AK15" t="n">
-        <v>117.87</v>
+        <v>116.52</v>
       </c>
       <c r="AL15" t="n">
-        <v>-5.45</v>
+        <v>-1.35</v>
       </c>
       <c r="AM15" t="n">
         <v>110</v>
@@ -1997,67 +1964,61 @@
       <c r="AN15" t="n">
         <v>142</v>
       </c>
-      <c r="AP15" t="n">
-        <v>78.56</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>13.45</v>
-      </c>
       <c r="BL15" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B16" t="n">
-        <v>163.8</v>
+        <v>155.9</v>
       </c>
       <c r="D16" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F16" t="n">
         <v>6.5</v>
       </c>
       <c r="K16" t="n">
-        <v>101.2</v>
+        <v>99.3</v>
       </c>
       <c r="O16" t="n">
-        <v>40.2</v>
+        <v>38.5</v>
       </c>
       <c r="V16" t="n">
-        <v>6.3</v>
+        <v>8.9</v>
       </c>
       <c r="W16" t="n">
-        <v>17.2</v>
+        <v>15.8</v>
       </c>
       <c r="X16" t="n">
-        <v>11.8</v>
+        <v>12.4</v>
       </c>
       <c r="Y16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA16" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="AF16" t="n">
-        <v>220.31</v>
+        <v>221.99</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.16</v>
+        <v>1.67</v>
       </c>
       <c r="AH16" t="n">
         <v>215</v>
@@ -2066,10 +2027,10 @@
         <v>235</v>
       </c>
       <c r="AK16" t="n">
-        <v>116.52</v>
+        <v>116.37</v>
       </c>
       <c r="AL16" t="n">
-        <v>-1.35</v>
+        <v>-0.15</v>
       </c>
       <c r="AM16" t="n">
         <v>110</v>
@@ -2078,60 +2039,60 @@
         <v>142</v>
       </c>
       <c r="BL16" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B17" t="n">
-        <v>155.9</v>
+        <v>141.3</v>
       </c>
       <c r="D17" t="n">
-        <v>28</v>
+        <v>26.3</v>
       </c>
       <c r="F17" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="K17" t="n">
-        <v>99.3</v>
+        <v>97.8</v>
       </c>
       <c r="O17" t="n">
-        <v>38.5</v>
+        <v>39.8</v>
       </c>
       <c r="V17" t="n">
-        <v>8.9</v>
+        <v>9.5</v>
       </c>
       <c r="W17" t="n">
-        <v>15.8</v>
+        <v>17.7</v>
       </c>
       <c r="X17" t="n">
-        <v>12.4</v>
+        <v>13.6</v>
       </c>
       <c r="Y17" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Z17" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA17" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>5.7</v>
+        <v>7.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="AF17" t="n">
-        <v>221.99</v>
+        <v>225.14</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.67</v>
+        <v>3.15</v>
       </c>
       <c r="AH17" t="n">
         <v>215</v>
@@ -2139,12 +2100,6 @@
       <c r="AI17" t="n">
         <v>235</v>
       </c>
-      <c r="AK17" t="n">
-        <v>116.37</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>-0.15</v>
-      </c>
       <c r="AM17" t="n">
         <v>110</v>
       </c>
@@ -2152,60 +2107,54 @@
         <v>142</v>
       </c>
       <c r="BL17" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B18" t="n">
-        <v>141.3</v>
+        <v>131.5</v>
       </c>
       <c r="D18" t="n">
-        <v>26.3</v>
+        <v>27.3</v>
       </c>
       <c r="F18" t="n">
         <v>5.5</v>
       </c>
       <c r="K18" t="n">
-        <v>97.8</v>
+        <v>97</v>
       </c>
       <c r="O18" t="n">
-        <v>39.8</v>
+        <v>35.7</v>
       </c>
       <c r="V18" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="W18" t="n">
-        <v>17.7</v>
+        <v>13.9</v>
       </c>
       <c r="X18" t="n">
-        <v>13.6</v>
+        <v>11.4</v>
       </c>
       <c r="Y18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z18" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA18" t="n">
         <v>15</v>
       </c>
-      <c r="AA18" t="n">
-        <v>14</v>
-      </c>
       <c r="AB18" t="n">
-        <v>0.2</v>
+        <v>-3.6</v>
       </c>
       <c r="AC18" t="n">
-        <v>7.5</v>
+        <v>2.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>225.14</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>3.15</v>
+        <v>-0.4</v>
       </c>
       <c r="AH18" t="n">
         <v>215</v>
@@ -2220,54 +2169,93 @@
         <v>142</v>
       </c>
       <c r="BL18" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="B19" t="n">
-        <v>131.5</v>
+        <v>153</v>
+      </c>
+      <c r="C19" t="n">
+        <v>71.8</v>
       </c>
       <c r="D19" t="n">
-        <v>27.3</v>
+        <v>28.6</v>
+      </c>
+      <c r="E19" t="n">
+        <v>24.7</v>
       </c>
       <c r="F19" t="n">
-        <v>5.5</v>
+        <v>4</v>
+      </c>
+      <c r="H19" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J19" t="n">
+        <v>41.1</v>
       </c>
       <c r="K19" t="n">
-        <v>97</v>
+        <v>75.90000000000001</v>
+      </c>
+      <c r="M19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N19" t="n">
+        <v>33.5</v>
       </c>
       <c r="O19" t="n">
-        <v>35.7</v>
+        <v>38.3</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>23.2</v>
       </c>
       <c r="V19" t="n">
-        <v>9</v>
+        <v>11.2</v>
       </c>
       <c r="W19" t="n">
-        <v>13.9</v>
+        <v>13</v>
       </c>
       <c r="X19" t="n">
-        <v>11.4</v>
+        <v>12.1</v>
       </c>
       <c r="Y19" t="n">
         <v>12</v>
       </c>
       <c r="Z19" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AA19" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>-3.6</v>
+        <v>-6.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.8</v>
+        <v>5.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>-0.4</v>
+        <v>-0.6</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>229.96</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>-0.02</v>
       </c>
       <c r="AH19" t="n">
         <v>215</v>
@@ -2275,100 +2263,112 @@
       <c r="AI19" t="n">
         <v>235</v>
       </c>
+      <c r="AK19" t="n">
+        <v>128.14</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>11.77</v>
+      </c>
       <c r="AM19" t="n">
         <v>110</v>
       </c>
       <c r="AN19" t="n">
         <v>142</v>
       </c>
+      <c r="AP19" t="n">
+        <v>87.47</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>14.8</v>
+      </c>
       <c r="BL19" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B20" t="n">
-        <v>153</v>
+        <v>165.8</v>
       </c>
       <c r="C20" t="n">
-        <v>71.8</v>
+        <v>77.3</v>
       </c>
       <c r="D20" t="n">
-        <v>28.6</v>
+        <v>29.3</v>
       </c>
       <c r="E20" t="n">
-        <v>24.7</v>
+        <v>27.7</v>
       </c>
       <c r="F20" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="H20" t="n">
         <v>24.1</v>
       </c>
       <c r="I20" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="J20" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="K20" t="n">
-        <v>75.90000000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="N20" t="n">
-        <v>33.5</v>
+        <v>35.1</v>
       </c>
       <c r="O20" t="n">
-        <v>38.3</v>
+        <v>39.8</v>
       </c>
       <c r="Q20" t="n">
-        <v>23.2</v>
+        <v>23.8</v>
       </c>
       <c r="R20" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="T20" t="n">
-        <v>23.2</v>
+        <v>23.8</v>
       </c>
       <c r="V20" t="n">
-        <v>11.2</v>
+        <v>9.4</v>
       </c>
       <c r="W20" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="X20" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z20" t="n">
         <v>13</v>
       </c>
-      <c r="X20" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>14</v>
-      </c>
       <c r="AA20" t="n">
-        <v>12.5</v>
+        <v>10.1</v>
       </c>
       <c r="AB20" t="n">
-        <v>-6.6</v>
+        <v>-0.7</v>
       </c>
       <c r="AC20" t="n">
-        <v>5.3</v>
+        <v>9.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>-0.6</v>
+        <v>4.4</v>
       </c>
       <c r="AF20" t="n">
-        <v>229.96</v>
+        <v>227.01</v>
       </c>
       <c r="AG20" t="n">
-        <v>-0.02</v>
+        <v>-2.95</v>
       </c>
       <c r="AH20" t="n">
         <v>215</v>
@@ -2377,10 +2377,10 @@
         <v>235</v>
       </c>
       <c r="AK20" t="n">
-        <v>128.14</v>
+        <v>128.15</v>
       </c>
       <c r="AL20" t="n">
-        <v>11.77</v>
+        <v>0.01</v>
       </c>
       <c r="AM20" t="n">
         <v>110</v>
@@ -2389,99 +2389,99 @@
         <v>142</v>
       </c>
       <c r="AP20" t="n">
-        <v>87.47</v>
+        <v>83.41</v>
       </c>
       <c r="AS20" t="n">
-        <v>14.8</v>
+        <v>14.52</v>
       </c>
       <c r="BL20" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B21" t="n">
-        <v>165.8</v>
+        <v>158.1</v>
       </c>
       <c r="C21" t="n">
-        <v>77.3</v>
+        <v>73.7</v>
       </c>
       <c r="D21" t="n">
-        <v>29.3</v>
+        <v>30.3</v>
       </c>
       <c r="E21" t="n">
-        <v>27.7</v>
+        <v>26</v>
       </c>
       <c r="F21" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="H21" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="I21" t="n">
-        <v>10.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>41.6</v>
+        <v>40.9</v>
       </c>
       <c r="K21" t="n">
-        <v>76.59999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="N21" t="n">
-        <v>35.1</v>
+        <v>35.3</v>
       </c>
       <c r="O21" t="n">
-        <v>39.8</v>
+        <v>40.3</v>
       </c>
       <c r="Q21" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="R21" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S21" t="n">
         <v>7</v>
       </c>
       <c r="T21" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="V21" t="n">
-        <v>9.4</v>
+        <v>8.9</v>
       </c>
       <c r="W21" t="n">
-        <v>17.4</v>
+        <v>19.3</v>
       </c>
       <c r="X21" t="n">
-        <v>13.4</v>
+        <v>14.1</v>
       </c>
       <c r="Y21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z21" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA21" t="n">
-        <v>10.1</v>
+        <v>11</v>
       </c>
       <c r="AB21" t="n">
-        <v>-0.7</v>
+        <v>4.4</v>
       </c>
       <c r="AC21" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>4.4</v>
+        <v>6.5</v>
       </c>
       <c r="AF21" t="n">
-        <v>227.01</v>
+        <v>228.35</v>
       </c>
       <c r="AG21" t="n">
-        <v>-2.95</v>
+        <v>1.33</v>
       </c>
       <c r="AH21" t="n">
         <v>215</v>
@@ -2490,10 +2490,10 @@
         <v>235</v>
       </c>
       <c r="AK21" t="n">
-        <v>128.15</v>
+        <v>128.86</v>
       </c>
       <c r="AL21" t="n">
-        <v>0.01</v>
+        <v>0.71</v>
       </c>
       <c r="AM21" t="n">
         <v>110</v>
@@ -2502,99 +2502,99 @@
         <v>142</v>
       </c>
       <c r="AP21" t="n">
-        <v>83.41</v>
+        <v>82.37</v>
       </c>
       <c r="AS21" t="n">
-        <v>14.52</v>
+        <v>14.22</v>
       </c>
       <c r="BL21" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B22" t="n">
-        <v>158.1</v>
+        <v>154.9</v>
       </c>
       <c r="C22" t="n">
-        <v>73.7</v>
+        <v>70.2</v>
       </c>
       <c r="D22" t="n">
-        <v>30.3</v>
+        <v>31.5</v>
       </c>
       <c r="E22" t="n">
-        <v>26</v>
+        <v>27.7</v>
       </c>
       <c r="F22" t="n">
-        <v>4.1</v>
+        <v>2.7</v>
       </c>
       <c r="H22" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="I22" t="n">
-        <v>9.300000000000001</v>
+        <v>11.3</v>
       </c>
       <c r="J22" t="n">
-        <v>40.9</v>
+        <v>40.3</v>
       </c>
       <c r="K22" t="n">
-        <v>74.40000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="M22" t="n">
-        <v>5</v>
+        <v>6.1</v>
       </c>
       <c r="N22" t="n">
-        <v>35.3</v>
+        <v>32.9</v>
       </c>
       <c r="O22" t="n">
-        <v>40.3</v>
+        <v>39</v>
       </c>
       <c r="Q22" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="R22" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="S22" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="T22" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="V22" t="n">
-        <v>8.9</v>
+        <v>6.3</v>
       </c>
       <c r="W22" t="n">
-        <v>19.3</v>
+        <v>25.2</v>
       </c>
       <c r="X22" t="n">
-        <v>14.1</v>
+        <v>15.8</v>
       </c>
       <c r="Y22" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z22" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA22" t="n">
-        <v>11</v>
+        <v>12.6</v>
       </c>
       <c r="AB22" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="AC22" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="AF22" t="n">
-        <v>228.35</v>
+        <v>231.16</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.33</v>
+        <v>2.81</v>
       </c>
       <c r="AH22" t="n">
         <v>215</v>
@@ -2603,10 +2603,10 @@
         <v>235</v>
       </c>
       <c r="AK22" t="n">
-        <v>128.86</v>
+        <v>130.88</v>
       </c>
       <c r="AL22" t="n">
-        <v>0.71</v>
+        <v>2.02</v>
       </c>
       <c r="AM22" t="n">
         <v>110</v>
@@ -2615,99 +2615,66 @@
         <v>142</v>
       </c>
       <c r="AP22" t="n">
-        <v>82.37</v>
+        <v>85.48999999999999</v>
       </c>
       <c r="AS22" t="n">
-        <v>14.22</v>
+        <v>13.1</v>
       </c>
       <c r="BL22" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B23" t="n">
-        <v>154.9</v>
-      </c>
-      <c r="C23" t="n">
-        <v>70.2</v>
+        <v>152.2</v>
       </c>
       <c r="D23" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="E23" t="n">
-        <v>27.7</v>
+        <v>31</v>
       </c>
       <c r="F23" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="H23" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I23" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J23" t="n">
-        <v>40.3</v>
+        <v>3.5</v>
       </c>
       <c r="K23" t="n">
-        <v>75.8</v>
-      </c>
-      <c r="M23" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="N23" t="n">
-        <v>32.9</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O23" t="n">
-        <v>39</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="R23" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="S23" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="T23" t="n">
-        <v>23.7</v>
+        <v>34.4</v>
       </c>
       <c r="V23" t="n">
-        <v>6.3</v>
+        <v>9.5</v>
       </c>
       <c r="W23" t="n">
-        <v>25.2</v>
+        <v>25.5</v>
       </c>
       <c r="X23" t="n">
-        <v>15.8</v>
+        <v>17.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Z23" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AA23" t="n">
-        <v>12.6</v>
+        <v>9</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.9</v>
+        <v>-1.1</v>
       </c>
       <c r="AC23" t="n">
         <v>8.6</v>
       </c>
       <c r="AD23" t="n">
-        <v>5.8</v>
+        <v>3.8</v>
       </c>
       <c r="AF23" t="n">
-        <v>231.16</v>
+        <v>228.13</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.81</v>
+        <v>-3.03</v>
       </c>
       <c r="AH23" t="n">
         <v>215</v>
@@ -2715,79 +2682,67 @@
       <c r="AI23" t="n">
         <v>235</v>
       </c>
-      <c r="AK23" t="n">
-        <v>130.88</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AM23" t="n">
         <v>110</v>
       </c>
       <c r="AN23" t="n">
         <v>142</v>
       </c>
-      <c r="AP23" t="n">
-        <v>85.48999999999999</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>13.1</v>
-      </c>
       <c r="BL23" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B24" t="n">
-        <v>152.2</v>
+        <v>143.9</v>
       </c>
       <c r="D24" t="n">
-        <v>31</v>
+        <v>30.8</v>
       </c>
       <c r="F24" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="K24" t="n">
-        <v>98.40000000000001</v>
+        <v>99.2</v>
       </c>
       <c r="O24" t="n">
-        <v>34.4</v>
+        <v>35.2</v>
       </c>
       <c r="V24" t="n">
-        <v>9.5</v>
+        <v>10.7</v>
       </c>
       <c r="W24" t="n">
-        <v>25.5</v>
+        <v>17.6</v>
       </c>
       <c r="X24" t="n">
-        <v>17.5</v>
+        <v>14.2</v>
       </c>
       <c r="Y24" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Z24" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA24" t="n">
         <v>9</v>
       </c>
       <c r="AB24" t="n">
-        <v>-1.1</v>
+        <v>-0.8</v>
       </c>
       <c r="AC24" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AF24" t="n">
-        <v>228.13</v>
+        <v>229.16</v>
       </c>
       <c r="AG24" t="n">
-        <v>-3.03</v>
+        <v>1.03</v>
       </c>
       <c r="AH24" t="n">
         <v>215</v>
@@ -2802,60 +2757,93 @@
         <v>142</v>
       </c>
       <c r="BL24" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B25" t="n">
-        <v>143.9</v>
+        <v>163.2</v>
+      </c>
+      <c r="C25" t="n">
+        <v>73.7</v>
       </c>
       <c r="D25" t="n">
-        <v>30.8</v>
+        <v>30</v>
+      </c>
+      <c r="E25" t="n">
+        <v>28.2</v>
       </c>
       <c r="F25" t="n">
-        <v>2.5</v>
+        <v>4.8</v>
+      </c>
+      <c r="H25" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J25" t="n">
+        <v>40.1</v>
       </c>
       <c r="K25" t="n">
-        <v>99.2</v>
+        <v>75.59999999999999</v>
+      </c>
+      <c r="M25" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="N25" t="n">
+        <v>32.9</v>
       </c>
       <c r="O25" t="n">
-        <v>35.2</v>
+        <v>39.7</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="R25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="S25" t="n">
+        <v>6</v>
+      </c>
+      <c r="T25" t="n">
+        <v>23.5</v>
       </c>
       <c r="V25" t="n">
-        <v>10.7</v>
+        <v>9.4</v>
       </c>
       <c r="W25" t="n">
-        <v>17.6</v>
+        <v>20.1</v>
       </c>
       <c r="X25" t="n">
-        <v>14.2</v>
+        <v>14.8</v>
       </c>
       <c r="Y25" t="n">
         <v>4</v>
       </c>
       <c r="Z25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA25" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AB25" t="n">
-        <v>-0.8</v>
+        <v>-0.9</v>
       </c>
       <c r="AC25" t="n">
-        <v>8.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AF25" t="n">
-        <v>229.16</v>
+        <v>228.55</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.03</v>
+        <v>-0.61</v>
       </c>
       <c r="AH25" t="n">
         <v>215</v>
@@ -2863,100 +2851,112 @@
       <c r="AI25" t="n">
         <v>235</v>
       </c>
+      <c r="AK25" t="n">
+        <v>127.06</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>-3.82</v>
+      </c>
       <c r="AM25" t="n">
         <v>110</v>
       </c>
       <c r="AN25" t="n">
         <v>142</v>
       </c>
+      <c r="AP25" t="n">
+        <v>82.81</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>12.9</v>
+      </c>
       <c r="BL25" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="B26" t="n">
-        <v>163.2</v>
+        <v>174.4</v>
       </c>
       <c r="C26" t="n">
-        <v>73.7</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="D26" t="n">
-        <v>30</v>
+        <v>32.1</v>
       </c>
       <c r="E26" t="n">
-        <v>28.2</v>
+        <v>30.8</v>
       </c>
       <c r="F26" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="H26" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="I26" t="n">
-        <v>11.4</v>
+        <v>10.5</v>
       </c>
       <c r="J26" t="n">
-        <v>40.1</v>
+        <v>39.5</v>
       </c>
       <c r="K26" t="n">
-        <v>75.59999999999999</v>
+        <v>74</v>
       </c>
       <c r="M26" t="n">
         <v>6.8</v>
       </c>
       <c r="N26" t="n">
-        <v>32.9</v>
+        <v>35.8</v>
       </c>
       <c r="O26" t="n">
-        <v>39.7</v>
+        <v>42.6</v>
       </c>
       <c r="Q26" t="n">
-        <v>23.5</v>
+        <v>23.1</v>
       </c>
       <c r="R26" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="S26" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="T26" t="n">
-        <v>23.5</v>
+        <v>23.1</v>
       </c>
       <c r="V26" t="n">
-        <v>9.4</v>
+        <v>12.8</v>
       </c>
       <c r="W26" t="n">
-        <v>20.1</v>
+        <v>22.1</v>
       </c>
       <c r="X26" t="n">
-        <v>14.8</v>
+        <v>17.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Z26" t="n">
         <v>13</v>
       </c>
       <c r="AA26" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AC26" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="AB26" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>9.5</v>
-      </c>
       <c r="AD26" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AF26" t="n">
-        <v>228.55</v>
+        <v>219.99</v>
       </c>
       <c r="AG26" t="n">
-        <v>-0.61</v>
+        <v>-8.56</v>
       </c>
       <c r="AH26" t="n">
         <v>215</v>
@@ -2965,10 +2965,10 @@
         <v>235</v>
       </c>
       <c r="AK26" t="n">
-        <v>127.06</v>
+        <v>125.61</v>
       </c>
       <c r="AL26" t="n">
-        <v>-3.82</v>
+        <v>-1.45</v>
       </c>
       <c r="AM26" t="n">
         <v>110</v>
@@ -2977,99 +2977,99 @@
         <v>142</v>
       </c>
       <c r="AP26" t="n">
-        <v>82.81</v>
+        <v>77.83</v>
       </c>
       <c r="AS26" t="n">
-        <v>12.9</v>
+        <v>12.96</v>
       </c>
       <c r="BL26" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B27" t="n">
-        <v>174.4</v>
+        <v>163.2</v>
       </c>
       <c r="C27" t="n">
-        <v>75.40000000000001</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="D27" t="n">
-        <v>32.1</v>
+        <v>32.9</v>
       </c>
       <c r="E27" t="n">
-        <v>30.8</v>
+        <v>26</v>
       </c>
       <c r="F27" t="n">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="H27" t="n">
-        <v>24</v>
+        <v>23.8</v>
       </c>
       <c r="I27" t="n">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="J27" t="n">
-        <v>39.5</v>
+        <v>40.1</v>
       </c>
       <c r="K27" t="n">
-        <v>74</v>
+        <v>71.3</v>
       </c>
       <c r="M27" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="N27" t="n">
-        <v>35.8</v>
+        <v>34.3</v>
       </c>
       <c r="O27" t="n">
-        <v>42.6</v>
+        <v>41.5</v>
       </c>
       <c r="Q27" t="n">
         <v>23.1</v>
       </c>
       <c r="R27" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="S27" t="n">
-        <v>8.5</v>
+        <v>6.2</v>
       </c>
       <c r="T27" t="n">
         <v>23.1</v>
       </c>
       <c r="V27" t="n">
-        <v>12.8</v>
+        <v>9.6</v>
       </c>
       <c r="W27" t="n">
-        <v>22.1</v>
+        <v>23.3</v>
       </c>
       <c r="X27" t="n">
-        <v>17.5</v>
+        <v>16.4</v>
       </c>
       <c r="Y27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA27" t="n">
-        <v>10.1</v>
+        <v>12.2</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.3</v>
+        <v>2.6</v>
       </c>
       <c r="AC27" t="n">
-        <v>9.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AF27" t="n">
-        <v>219.99</v>
+        <v>219.22</v>
       </c>
       <c r="AG27" t="n">
-        <v>-8.56</v>
+        <v>-0.77</v>
       </c>
       <c r="AH27" t="n">
         <v>215</v>
@@ -3078,10 +3078,10 @@
         <v>235</v>
       </c>
       <c r="AK27" t="n">
-        <v>125.61</v>
+        <v>124.36</v>
       </c>
       <c r="AL27" t="n">
-        <v>-1.45</v>
+        <v>-1.25</v>
       </c>
       <c r="AM27" t="n">
         <v>110</v>
@@ -3090,99 +3090,99 @@
         <v>142</v>
       </c>
       <c r="AP27" t="n">
-        <v>77.83</v>
+        <v>76.81</v>
       </c>
       <c r="AS27" t="n">
-        <v>12.96</v>
+        <v>12.38</v>
       </c>
       <c r="BL27" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B28" t="n">
-        <v>163.2</v>
+        <v>152.7</v>
       </c>
       <c r="C28" t="n">
-        <v>70.90000000000001</v>
+        <v>62.6</v>
       </c>
       <c r="D28" t="n">
-        <v>32.9</v>
+        <v>32.7</v>
       </c>
       <c r="E28" t="n">
-        <v>26</v>
+        <v>24.6</v>
       </c>
       <c r="F28" t="n">
-        <v>6.9</v>
+        <v>5.2</v>
       </c>
       <c r="H28" t="n">
         <v>23.8</v>
       </c>
       <c r="I28" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J28" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="K28" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="M28" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="N28" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="O28" t="n">
         <v>40.1</v>
       </c>
-      <c r="K28" t="n">
-        <v>71.3</v>
-      </c>
-      <c r="M28" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="N28" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="O28" t="n">
-        <v>41.5</v>
-      </c>
       <c r="Q28" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="R28" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="S28" t="n">
-        <v>6.2</v>
+        <v>4</v>
       </c>
       <c r="T28" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="V28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="W28" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="X28" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC28" t="n">
         <v>9.6</v>
       </c>
-      <c r="W28" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="X28" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>8.5</v>
-      </c>
       <c r="AD28" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AF28" t="n">
-        <v>219.22</v>
+        <v>220.73</v>
       </c>
       <c r="AG28" t="n">
-        <v>-0.77</v>
+        <v>1.5</v>
       </c>
       <c r="AH28" t="n">
         <v>215</v>
@@ -3191,10 +3191,10 @@
         <v>235</v>
       </c>
       <c r="AK28" t="n">
-        <v>124.36</v>
+        <v>120.93</v>
       </c>
       <c r="AL28" t="n">
-        <v>-1.25</v>
+        <v>-3.43</v>
       </c>
       <c r="AM28" t="n">
         <v>110</v>
@@ -3203,75 +3203,75 @@
         <v>142</v>
       </c>
       <c r="AP28" t="n">
-        <v>76.81</v>
+        <v>77.87</v>
       </c>
       <c r="AS28" t="n">
-        <v>12.38</v>
+        <v>13.26</v>
       </c>
       <c r="BL28" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B29" t="n">
-        <v>152.7</v>
+        <v>150.7</v>
       </c>
       <c r="C29" t="n">
-        <v>62.6</v>
+        <v>64.8</v>
       </c>
       <c r="D29" t="n">
-        <v>32.7</v>
+        <v>33.7</v>
       </c>
       <c r="E29" t="n">
-        <v>24.6</v>
+        <v>27.1</v>
       </c>
       <c r="F29" t="n">
-        <v>5.2</v>
+        <v>3.8</v>
       </c>
       <c r="H29" t="n">
-        <v>23.8</v>
+        <v>23.4</v>
       </c>
       <c r="I29" t="n">
         <v>7.2</v>
       </c>
       <c r="J29" t="n">
-        <v>38.9</v>
+        <v>39.9</v>
       </c>
       <c r="K29" t="n">
-        <v>69.90000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="M29" t="n">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="N29" t="n">
-        <v>33.5</v>
+        <v>33</v>
       </c>
       <c r="O29" t="n">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="Q29" t="n">
         <v>23.2</v>
       </c>
       <c r="R29" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T29" t="n">
         <v>23.2</v>
       </c>
       <c r="V29" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="W29" t="n">
-        <v>27.3</v>
+        <v>28.9</v>
       </c>
       <c r="X29" t="n">
-        <v>19.4</v>
+        <v>21.7</v>
       </c>
       <c r="Y29" t="n">
         <v>10</v>
@@ -3280,22 +3280,22 @@
         <v>18</v>
       </c>
       <c r="AA29" t="n">
-        <v>14</v>
+        <v>13.1</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>9.6</v>
+        <v>10.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>5.7</v>
+        <v>6.7</v>
       </c>
       <c r="AF29" t="n">
-        <v>220.73</v>
+        <v>220.58</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.5</v>
+        <v>-0.15</v>
       </c>
       <c r="AH29" t="n">
         <v>215</v>
@@ -3304,10 +3304,10 @@
         <v>235</v>
       </c>
       <c r="AK29" t="n">
-        <v>120.93</v>
+        <v>120.28</v>
       </c>
       <c r="AL29" t="n">
-        <v>-3.43</v>
+        <v>-0.65</v>
       </c>
       <c r="AM29" t="n">
         <v>110</v>
@@ -3316,99 +3316,54 @@
         <v>142</v>
       </c>
       <c r="AP29" t="n">
-        <v>77.87</v>
+        <v>77.22</v>
       </c>
       <c r="AS29" t="n">
-        <v>13.26</v>
+        <v>13.79</v>
       </c>
       <c r="BL29" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B30" t="n">
-        <v>150.7</v>
-      </c>
-      <c r="C30" t="n">
-        <v>64.8</v>
+        <v>138.2</v>
       </c>
       <c r="D30" t="n">
-        <v>33.7</v>
-      </c>
-      <c r="E30" t="n">
-        <v>27.1</v>
+        <v>33.6</v>
       </c>
       <c r="F30" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H30" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="V30" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="W30" t="n">
         <v>23.4</v>
       </c>
-      <c r="I30" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="J30" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="K30" t="n">
-        <v>70.5</v>
-      </c>
-      <c r="M30" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="N30" t="n">
-        <v>33</v>
-      </c>
-      <c r="O30" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="R30" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="S30" t="n">
-        <v>3</v>
-      </c>
-      <c r="T30" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="V30" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="W30" t="n">
-        <v>28.9</v>
-      </c>
       <c r="X30" t="n">
-        <v>21.7</v>
+        <v>19.4</v>
       </c>
       <c r="Y30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AA30" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="AC30" t="n">
-        <v>10.8</v>
+        <v>8.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>220.58</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>-0.15</v>
+        <v>4.5</v>
       </c>
       <c r="AH30" t="n">
         <v>215</v>
@@ -3416,67 +3371,61 @@
       <c r="AI30" t="n">
         <v>235</v>
       </c>
-      <c r="AK30" t="n">
-        <v>120.28</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>-0.65</v>
-      </c>
       <c r="AM30" t="n">
         <v>110</v>
       </c>
       <c r="AN30" t="n">
         <v>142</v>
       </c>
-      <c r="AP30" t="n">
-        <v>77.22</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>13.79</v>
-      </c>
       <c r="BL30" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B31" t="n">
-        <v>138.2</v>
+        <v>126.5</v>
       </c>
       <c r="D31" t="n">
-        <v>33.6</v>
+        <v>33.2</v>
       </c>
       <c r="F31" t="n">
-        <v>6.1</v>
+        <v>3.4</v>
       </c>
       <c r="V31" t="n">
-        <v>15.5</v>
+        <v>12.6</v>
       </c>
       <c r="W31" t="n">
-        <v>23.4</v>
+        <v>22.3</v>
       </c>
       <c r="X31" t="n">
-        <v>19.4</v>
+        <v>17.4</v>
       </c>
       <c r="Y31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z31" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA31" t="n">
         <v>13</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>8.5</v>
+        <v>6.7</v>
       </c>
       <c r="AD31" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>229.48</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>6.05</v>
       </c>
       <c r="AH31" t="n">
         <v>215</v>
@@ -3491,54 +3440,93 @@
         <v>142</v>
       </c>
       <c r="BL31" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B32" t="n">
-        <v>126.5</v>
+        <v>129.4</v>
+      </c>
+      <c r="C32" t="n">
+        <v>50.6</v>
       </c>
       <c r="D32" t="n">
-        <v>33.2</v>
+        <v>31.5</v>
+      </c>
+      <c r="E32" t="n">
+        <v>19.4</v>
       </c>
       <c r="F32" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
+      </c>
+      <c r="H32" t="n">
+        <v>24</v>
+      </c>
+      <c r="I32" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J32" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="K32" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="M32" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N32" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="O32" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>21.4</v>
       </c>
       <c r="V32" t="n">
-        <v>12.6</v>
+        <v>14.3</v>
       </c>
       <c r="W32" t="n">
-        <v>22.3</v>
+        <v>23.9</v>
       </c>
       <c r="X32" t="n">
-        <v>17.4</v>
+        <v>19.1</v>
       </c>
       <c r="Y32" t="n">
         <v>8</v>
       </c>
       <c r="Z32" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AA32" t="n">
-        <v>13</v>
+        <v>16.1</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AC32" t="n">
-        <v>6.7</v>
+        <v>7.6</v>
       </c>
       <c r="AD32" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="AF32" t="n">
-        <v>229.48</v>
+        <v>229.5</v>
       </c>
       <c r="AG32" t="n">
-        <v>6.05</v>
+        <v>0.02</v>
       </c>
       <c r="AH32" t="n">
         <v>215</v>
@@ -3546,100 +3534,112 @@
       <c r="AI32" t="n">
         <v>235</v>
       </c>
+      <c r="AK32" t="n">
+        <v>128.37</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>8.09</v>
+      </c>
       <c r="AM32" t="n">
         <v>110</v>
       </c>
       <c r="AN32" t="n">
         <v>142</v>
       </c>
+      <c r="AP32" t="n">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>15.97</v>
+      </c>
       <c r="BL32" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="B33" t="n">
-        <v>129.4</v>
+        <v>142.9</v>
       </c>
       <c r="C33" t="n">
-        <v>50.6</v>
+        <v>52.7</v>
       </c>
       <c r="D33" t="n">
-        <v>31.5</v>
+        <v>34.7</v>
       </c>
       <c r="E33" t="n">
-        <v>19.4</v>
+        <v>24.8</v>
       </c>
       <c r="F33" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="H33" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I33" t="n">
-        <v>10.4</v>
+        <v>9.9</v>
       </c>
       <c r="J33" t="n">
-        <v>38.9</v>
+        <v>38.2</v>
       </c>
       <c r="K33" t="n">
-        <v>73.3</v>
+        <v>70</v>
       </c>
       <c r="M33" t="n">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="N33" t="n">
-        <v>33.3</v>
+        <v>31.9</v>
       </c>
       <c r="O33" t="n">
-        <v>38</v>
+        <v>35.8</v>
       </c>
       <c r="Q33" t="n">
-        <v>21.4</v>
+        <v>19.7</v>
       </c>
       <c r="R33" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>21.4</v>
+        <v>19.7</v>
       </c>
       <c r="V33" t="n">
-        <v>14.3</v>
+        <v>12</v>
       </c>
       <c r="W33" t="n">
-        <v>23.9</v>
+        <v>25.8</v>
       </c>
       <c r="X33" t="n">
-        <v>19.1</v>
+        <v>18.9</v>
       </c>
       <c r="Y33" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Z33" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AA33" t="n">
-        <v>16.1</v>
+        <v>15</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.4</v>
+        <v>-0.1</v>
       </c>
       <c r="AC33" t="n">
-        <v>7.6</v>
+        <v>5.8</v>
       </c>
       <c r="AD33" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="AF33" t="n">
-        <v>229.5</v>
+        <v>238.69</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.02</v>
+        <v>-2.8</v>
       </c>
       <c r="AH33" t="n">
         <v>215</v>
@@ -3648,10 +3648,10 @@
         <v>235</v>
       </c>
       <c r="AK33" t="n">
-        <v>128.37</v>
+        <v>134.59</v>
       </c>
       <c r="AL33" t="n">
-        <v>8.09</v>
+        <v>6.22</v>
       </c>
       <c r="AM33" t="n">
         <v>110</v>
@@ -3660,99 +3660,99 @@
         <v>142</v>
       </c>
       <c r="AP33" t="n">
-        <v>91.59999999999999</v>
+        <v>89.05</v>
       </c>
       <c r="AS33" t="n">
-        <v>15.97</v>
+        <v>17.06</v>
       </c>
       <c r="BL33" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B34" t="n">
-        <v>142.9</v>
+        <v>148.1</v>
       </c>
       <c r="C34" t="n">
-        <v>52.7</v>
+        <v>51.9</v>
       </c>
       <c r="D34" t="n">
-        <v>34.7</v>
+        <v>35.4</v>
       </c>
       <c r="E34" t="n">
-        <v>24.8</v>
+        <v>31.5</v>
       </c>
       <c r="F34" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="H34" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="I34" t="n">
-        <v>9.9</v>
+        <v>9.6</v>
       </c>
       <c r="J34" t="n">
-        <v>38.2</v>
+        <v>39.6</v>
       </c>
       <c r="K34" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M34" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="N34" t="n">
-        <v>31.9</v>
+        <v>30.8</v>
       </c>
       <c r="O34" t="n">
-        <v>35.8</v>
+        <v>33.7</v>
       </c>
       <c r="Q34" t="n">
-        <v>19.7</v>
+        <v>20.7</v>
       </c>
       <c r="R34" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>19.7</v>
+        <v>20.7</v>
       </c>
       <c r="V34" t="n">
-        <v>12</v>
+        <v>13.1</v>
       </c>
       <c r="W34" t="n">
-        <v>25.8</v>
+        <v>25.5</v>
       </c>
       <c r="X34" t="n">
-        <v>18.9</v>
+        <v>19.3</v>
       </c>
       <c r="Y34" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z34" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AA34" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AB34" t="n">
-        <v>-0.1</v>
+        <v>-1</v>
       </c>
       <c r="AC34" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="AF34" t="n">
-        <v>238.69</v>
+        <v>233.48</v>
       </c>
       <c r="AG34" t="n">
-        <v>-2.8</v>
+        <v>-4.86</v>
       </c>
       <c r="AH34" t="n">
         <v>215</v>
@@ -3761,10 +3761,10 @@
         <v>235</v>
       </c>
       <c r="AK34" t="n">
-        <v>134.59</v>
+        <v>136.6</v>
       </c>
       <c r="AL34" t="n">
-        <v>6.22</v>
+        <v>2.01</v>
       </c>
       <c r="AM34" t="n">
         <v>110</v>
@@ -3773,99 +3773,99 @@
         <v>142</v>
       </c>
       <c r="AP34" t="n">
-        <v>89.05</v>
+        <v>86.25</v>
       </c>
       <c r="AS34" t="n">
-        <v>17.06</v>
+        <v>17.13</v>
       </c>
       <c r="BL34" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B35" t="n">
-        <v>148.1</v>
+        <v>143.4</v>
       </c>
       <c r="C35" t="n">
-        <v>51.9</v>
+        <v>50.9</v>
       </c>
       <c r="D35" t="n">
-        <v>35.4</v>
+        <v>35.7</v>
       </c>
       <c r="E35" t="n">
-        <v>31.5</v>
+        <v>26.2</v>
       </c>
       <c r="F35" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="H35" t="n">
-        <v>21.8</v>
+        <v>22.9</v>
       </c>
       <c r="I35" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J35" t="n">
-        <v>39.6</v>
+        <v>39.9</v>
       </c>
       <c r="K35" t="n">
-        <v>71</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="M35" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="N35" t="n">
-        <v>30.8</v>
+        <v>31.2</v>
       </c>
       <c r="O35" t="n">
-        <v>33.7</v>
+        <v>33.1</v>
       </c>
       <c r="Q35" t="n">
-        <v>20.7</v>
+        <v>21.6</v>
       </c>
       <c r="R35" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>20.7</v>
+        <v>21.6</v>
       </c>
       <c r="V35" t="n">
-        <v>13.1</v>
+        <v>12.9</v>
       </c>
       <c r="W35" t="n">
-        <v>25.5</v>
+        <v>28.3</v>
       </c>
       <c r="X35" t="n">
-        <v>19.3</v>
+        <v>20.6</v>
       </c>
       <c r="Y35" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z35" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AA35" t="n">
-        <v>15.5</v>
+        <v>17.9</v>
       </c>
       <c r="AB35" t="n">
-        <v>-1</v>
+        <v>-0.8</v>
       </c>
       <c r="AC35" t="n">
-        <v>6.4</v>
+        <v>8.1</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="AF35" t="n">
-        <v>233.48</v>
+        <v>235.13</v>
       </c>
       <c r="AG35" t="n">
-        <v>-4.86</v>
+        <v>1.66</v>
       </c>
       <c r="AH35" t="n">
         <v>215</v>
@@ -3874,10 +3874,10 @@
         <v>235</v>
       </c>
       <c r="AK35" t="n">
-        <v>136.6</v>
+        <v>135.66</v>
       </c>
       <c r="AL35" t="n">
-        <v>2.01</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AM35" t="n">
         <v>110</v>
@@ -3886,57 +3886,57 @@
         <v>142</v>
       </c>
       <c r="AP35" t="n">
-        <v>86.25</v>
+        <v>88.27</v>
       </c>
       <c r="AS35" t="n">
-        <v>17.13</v>
+        <v>17.6</v>
       </c>
       <c r="BL35" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B36" t="n">
-        <v>143.4</v>
+        <v>144.9</v>
       </c>
       <c r="C36" t="n">
-        <v>50.9</v>
+        <v>53</v>
       </c>
       <c r="D36" t="n">
-        <v>35.7</v>
+        <v>35.6</v>
       </c>
       <c r="E36" t="n">
-        <v>26.2</v>
+        <v>26</v>
       </c>
       <c r="F36" t="n">
-        <v>4.3</v>
+        <v>2.8</v>
       </c>
       <c r="H36" t="n">
-        <v>22.9</v>
+        <v>24</v>
       </c>
       <c r="I36" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J36" t="n">
-        <v>39.9</v>
+        <v>40.3</v>
       </c>
       <c r="K36" t="n">
-        <v>72.59999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="M36" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="N36" t="n">
-        <v>31.2</v>
+        <v>31.6</v>
       </c>
       <c r="O36" t="n">
-        <v>33.1</v>
+        <v>33.6</v>
       </c>
       <c r="Q36" t="n">
-        <v>21.6</v>
+        <v>21</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -3945,40 +3945,40 @@
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>21.6</v>
+        <v>21</v>
       </c>
       <c r="V36" t="n">
-        <v>12.9</v>
+        <v>14.4</v>
       </c>
       <c r="W36" t="n">
-        <v>28.3</v>
+        <v>27.7</v>
       </c>
       <c r="X36" t="n">
-        <v>20.6</v>
+        <v>21.1</v>
       </c>
       <c r="Y36" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z36" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AA36" t="n">
-        <v>17.9</v>
+        <v>16.3</v>
       </c>
       <c r="AB36" t="n">
-        <v>-0.8</v>
+        <v>-1.1</v>
       </c>
       <c r="AC36" t="n">
-        <v>8.1</v>
+        <v>6.6</v>
       </c>
       <c r="AD36" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="AF36" t="n">
-        <v>235.13</v>
+        <v>234.87</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.66</v>
+        <v>-0.26</v>
       </c>
       <c r="AH36" t="n">
         <v>215</v>
@@ -3987,10 +3987,10 @@
         <v>235</v>
       </c>
       <c r="AK36" t="n">
-        <v>135.66</v>
+        <v>136.33</v>
       </c>
       <c r="AL36" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="AM36" t="n">
         <v>110</v>
@@ -3999,99 +3999,60 @@
         <v>142</v>
       </c>
       <c r="AP36" t="n">
-        <v>88.27</v>
+        <v>87.09</v>
       </c>
       <c r="AS36" t="n">
-        <v>17.6</v>
+        <v>17.31</v>
       </c>
       <c r="BL36" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B37" t="n">
-        <v>144.9</v>
-      </c>
-      <c r="C37" t="n">
-        <v>53</v>
+        <v>132.2</v>
       </c>
       <c r="D37" t="n">
         <v>35.6</v>
       </c>
-      <c r="E37" t="n">
-        <v>26</v>
-      </c>
       <c r="F37" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="H37" t="n">
-        <v>24</v>
-      </c>
-      <c r="I37" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="J37" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="K37" t="n">
-        <v>73.7</v>
-      </c>
-      <c r="M37" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="N37" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="O37" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>21</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="V37" t="n">
-        <v>14.4</v>
+        <v>11.6</v>
       </c>
       <c r="W37" t="n">
-        <v>27.7</v>
+        <v>23.2</v>
       </c>
       <c r="X37" t="n">
-        <v>21.1</v>
+        <v>17.4</v>
       </c>
       <c r="Y37" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z37" t="n">
         <v>19</v>
       </c>
       <c r="AA37" t="n">
-        <v>16.3</v>
+        <v>13</v>
       </c>
       <c r="AB37" t="n">
-        <v>-1.1</v>
+        <v>0.9</v>
       </c>
       <c r="AC37" t="n">
-        <v>6.6</v>
+        <v>7.5</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="AF37" t="n">
-        <v>234.87</v>
+        <v>234.78</v>
       </c>
       <c r="AG37" t="n">
-        <v>-0.26</v>
+        <v>-0.09</v>
       </c>
       <c r="AH37" t="n">
         <v>215</v>
@@ -4099,73 +4060,61 @@
       <c r="AI37" t="n">
         <v>235</v>
       </c>
-      <c r="AK37" t="n">
-        <v>136.33</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>0.67</v>
-      </c>
       <c r="AM37" t="n">
         <v>110</v>
       </c>
       <c r="AN37" t="n">
         <v>142</v>
       </c>
-      <c r="AP37" t="n">
-        <v>87.09</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>17.31</v>
-      </c>
       <c r="BL37" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B38" t="n">
-        <v>132.2</v>
+        <v>137.1</v>
       </c>
       <c r="D38" t="n">
-        <v>35.6</v>
+        <v>35.1</v>
       </c>
       <c r="F38" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="V38" t="n">
-        <v>11.6</v>
+        <v>11</v>
       </c>
       <c r="W38" t="n">
-        <v>23.2</v>
+        <v>22</v>
       </c>
       <c r="X38" t="n">
-        <v>17.4</v>
+        <v>16.5</v>
       </c>
       <c r="Y38" t="n">
         <v>7</v>
       </c>
       <c r="Z38" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AA38" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.9</v>
+        <v>-5.3</v>
       </c>
       <c r="AC38" t="n">
-        <v>7.5</v>
+        <v>6.1</v>
       </c>
       <c r="AD38" t="n">
-        <v>4.2</v>
+        <v>0.4</v>
       </c>
       <c r="AF38" t="n">
-        <v>234.78</v>
+        <v>229.75</v>
       </c>
       <c r="AG38" t="n">
-        <v>-0.09</v>
+        <v>-5.03</v>
       </c>
       <c r="AH38" t="n">
         <v>215</v>
@@ -4180,54 +4129,93 @@
         <v>142</v>
       </c>
       <c r="BL38" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B39" t="n">
-        <v>137.1</v>
+        <v>166.2</v>
+      </c>
+      <c r="C39" t="n">
+        <v>72.40000000000001</v>
       </c>
       <c r="D39" t="n">
-        <v>35.1</v>
+        <v>32.7</v>
+      </c>
+      <c r="E39" t="n">
+        <v>28.1</v>
       </c>
       <c r="F39" t="n">
         <v>3.3</v>
       </c>
+      <c r="H39" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="I39" t="n">
+        <v>9</v>
+      </c>
+      <c r="J39" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="K39" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="M39" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="N39" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="O39" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="R39" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>23.7</v>
+      </c>
       <c r="V39" t="n">
-        <v>11</v>
+        <v>7.9</v>
       </c>
       <c r="W39" t="n">
-        <v>22</v>
+        <v>15.6</v>
       </c>
       <c r="X39" t="n">
-        <v>16.5</v>
+        <v>11.8</v>
       </c>
       <c r="Y39" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z39" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AA39" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AB39" t="n">
-        <v>-5.3</v>
+        <v>-3.5</v>
       </c>
       <c r="AC39" t="n">
-        <v>6.1</v>
+        <v>8.4</v>
       </c>
       <c r="AD39" t="n">
-        <v>0.4</v>
+        <v>2.5</v>
       </c>
       <c r="AF39" t="n">
-        <v>229.75</v>
+        <v>222.86</v>
       </c>
       <c r="AG39" t="n">
-        <v>-5.03</v>
+        <v>-6.9</v>
       </c>
       <c r="AH39" t="n">
         <v>215</v>
@@ -4235,100 +4223,112 @@
       <c r="AI39" t="n">
         <v>235</v>
       </c>
+      <c r="AK39" t="n">
+        <v>135.42</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>-0.91</v>
+      </c>
       <c r="AM39" t="n">
         <v>110</v>
       </c>
       <c r="AN39" t="n">
         <v>142</v>
       </c>
+      <c r="AP39" t="n">
+        <v>81.98</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>15.01</v>
+      </c>
       <c r="BL39" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B40" t="n">
-        <v>166.2</v>
+        <v>166.3</v>
       </c>
       <c r="C40" t="n">
-        <v>72.40000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="D40" t="n">
-        <v>32.7</v>
+        <v>32.8</v>
       </c>
       <c r="E40" t="n">
-        <v>28.1</v>
+        <v>28.8</v>
       </c>
       <c r="F40" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="H40" t="n">
         <v>23.4</v>
       </c>
       <c r="I40" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J40" t="n">
-        <v>42.1</v>
+        <v>41.2</v>
       </c>
       <c r="K40" t="n">
-        <v>74.5</v>
+        <v>73.8</v>
       </c>
       <c r="M40" t="n">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="N40" t="n">
-        <v>33.7</v>
+        <v>35.4</v>
       </c>
       <c r="O40" t="n">
-        <v>39.3</v>
+        <v>42.6</v>
       </c>
       <c r="Q40" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="R40" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="V40" t="n">
-        <v>7.9</v>
+        <v>6.7</v>
       </c>
       <c r="W40" t="n">
-        <v>15.6</v>
+        <v>18.1</v>
       </c>
       <c r="X40" t="n">
-        <v>11.8</v>
+        <v>12.4</v>
       </c>
       <c r="Y40" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Z40" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AA40" t="n">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AB40" t="n">
-        <v>-3.5</v>
+        <v>-2.9</v>
       </c>
       <c r="AC40" t="n">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.5</v>
+        <v>4.3</v>
       </c>
       <c r="AF40" t="n">
-        <v>222.86</v>
+        <v>218.37</v>
       </c>
       <c r="AG40" t="n">
-        <v>-6.9</v>
+        <v>-4.49</v>
       </c>
       <c r="AH40" t="n">
         <v>215</v>
@@ -4337,10 +4337,10 @@
         <v>235</v>
       </c>
       <c r="AK40" t="n">
-        <v>135.42</v>
+        <v>131.24</v>
       </c>
       <c r="AL40" t="n">
-        <v>-0.91</v>
+        <v>-4.18</v>
       </c>
       <c r="AM40" t="n">
         <v>110</v>
@@ -4349,99 +4349,99 @@
         <v>142</v>
       </c>
       <c r="AP40" t="n">
-        <v>81.98</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="AS40" t="n">
-        <v>15.01</v>
+        <v>12.97</v>
       </c>
       <c r="BL40" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B41" t="n">
-        <v>166.3</v>
+        <v>154.1</v>
       </c>
       <c r="C41" t="n">
-        <v>74.90000000000001</v>
+        <v>65</v>
       </c>
       <c r="D41" t="n">
-        <v>32.8</v>
+        <v>32</v>
       </c>
       <c r="E41" t="n">
-        <v>28.8</v>
+        <v>25.2</v>
       </c>
       <c r="F41" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="H41" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="I41" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="J41" t="n">
-        <v>41.2</v>
+        <v>38.5</v>
       </c>
       <c r="K41" t="n">
-        <v>73.8</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="M41" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="N41" t="n">
-        <v>35.4</v>
+        <v>32.3</v>
       </c>
       <c r="O41" t="n">
-        <v>42.6</v>
+        <v>40.3</v>
       </c>
       <c r="Q41" t="n">
-        <v>23.9</v>
+        <v>21.7</v>
       </c>
       <c r="R41" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="S41" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T41" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="V41" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="W41" t="n">
+        <v>21</v>
+      </c>
+      <c r="X41" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AD41" t="n">
         <v>3.9</v>
       </c>
-      <c r="S41" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="V41" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="W41" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="X41" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>11</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>-2.9</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AF41" t="n">
-        <v>218.37</v>
+        <v>218.04</v>
       </c>
       <c r="AG41" t="n">
-        <v>-4.49</v>
+        <v>-0.33</v>
       </c>
       <c r="AH41" t="n">
         <v>215</v>
@@ -4450,10 +4450,10 @@
         <v>235</v>
       </c>
       <c r="AK41" t="n">
-        <v>131.24</v>
+        <v>129.21</v>
       </c>
       <c r="AL41" t="n">
-        <v>-4.18</v>
+        <v>-2.03</v>
       </c>
       <c r="AM41" t="n">
         <v>110</v>
@@ -4462,99 +4462,99 @@
         <v>142</v>
       </c>
       <c r="AP41" t="n">
-        <v>79.98999999999999</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="AS41" t="n">
-        <v>12.97</v>
+        <v>15.23</v>
       </c>
       <c r="BL41" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B42" t="n">
-        <v>154.1</v>
+        <v>148.8</v>
       </c>
       <c r="C42" t="n">
-        <v>65</v>
+        <v>57.6</v>
       </c>
       <c r="D42" t="n">
-        <v>32</v>
+        <v>32.7</v>
       </c>
       <c r="E42" t="n">
-        <v>25.2</v>
+        <v>26.3</v>
       </c>
       <c r="F42" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="H42" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="I42" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="J42" t="n">
-        <v>38.5</v>
+        <v>41.6</v>
       </c>
       <c r="K42" t="n">
-        <v>70.90000000000001</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="M42" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="N42" t="n">
-        <v>32.3</v>
+        <v>35</v>
       </c>
       <c r="O42" t="n">
-        <v>40.3</v>
+        <v>42.4</v>
       </c>
       <c r="Q42" t="n">
         <v>21.7</v>
       </c>
       <c r="R42" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="S42" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
         <v>21.7</v>
       </c>
       <c r="V42" t="n">
-        <v>5.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W42" t="n">
-        <v>21</v>
+        <v>24.1</v>
       </c>
       <c r="X42" t="n">
-        <v>13.2</v>
+        <v>16.1</v>
       </c>
       <c r="Y42" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z42" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA42" t="n">
-        <v>14.5</v>
+        <v>15.6</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="AC42" t="n">
-        <v>7.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AD42" t="n">
-        <v>3.9</v>
+        <v>6.3</v>
       </c>
       <c r="AF42" t="n">
-        <v>218.04</v>
+        <v>220.84</v>
       </c>
       <c r="AG42" t="n">
-        <v>-0.33</v>
+        <v>2.8</v>
       </c>
       <c r="AH42" t="n">
         <v>215</v>
@@ -4563,10 +4563,10 @@
         <v>235</v>
       </c>
       <c r="AK42" t="n">
-        <v>129.21</v>
+        <v>129.07</v>
       </c>
       <c r="AL42" t="n">
-        <v>-2.03</v>
+        <v>-0.14</v>
       </c>
       <c r="AM42" t="n">
         <v>110</v>
@@ -4575,99 +4575,99 @@
         <v>142</v>
       </c>
       <c r="AP42" t="n">
-        <v>82.90000000000001</v>
+        <v>85.52</v>
       </c>
       <c r="AS42" t="n">
-        <v>15.23</v>
+        <v>15.82</v>
       </c>
       <c r="BL42" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B43" t="n">
-        <v>148.8</v>
+        <v>146.8</v>
       </c>
       <c r="C43" t="n">
-        <v>57.6</v>
+        <v>52.8</v>
       </c>
       <c r="D43" t="n">
-        <v>32.7</v>
+        <v>33.6</v>
       </c>
       <c r="E43" t="n">
-        <v>26.3</v>
+        <v>28.9</v>
       </c>
       <c r="F43" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="H43" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="I43" t="n">
-        <v>8.9</v>
+        <v>9.1</v>
       </c>
       <c r="J43" t="n">
-        <v>41.6</v>
+        <v>40.8</v>
       </c>
       <c r="K43" t="n">
-        <v>74.09999999999999</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="M43" t="n">
-        <v>7.4</v>
+        <v>5.6</v>
       </c>
       <c r="N43" t="n">
-        <v>35</v>
+        <v>33.1</v>
       </c>
       <c r="O43" t="n">
-        <v>42.4</v>
+        <v>38.7</v>
       </c>
       <c r="Q43" t="n">
-        <v>21.7</v>
+        <v>22</v>
       </c>
       <c r="R43" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>21.7</v>
+        <v>22</v>
       </c>
       <c r="V43" t="n">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="W43" t="n">
-        <v>24.1</v>
+        <v>22.9</v>
       </c>
       <c r="X43" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA43" t="n">
         <v>16.1</v>
       </c>
-      <c r="Y43" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>19</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>15.6</v>
-      </c>
       <c r="AB43" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="AC43" t="n">
-        <v>9.699999999999999</v>
+        <v>7</v>
       </c>
       <c r="AD43" t="n">
-        <v>6.3</v>
+        <v>4.5</v>
       </c>
       <c r="AF43" t="n">
-        <v>220.84</v>
+        <v>225.87</v>
       </c>
       <c r="AG43" t="n">
-        <v>2.8</v>
+        <v>5.03</v>
       </c>
       <c r="AH43" t="n">
         <v>215</v>
@@ -4676,10 +4676,10 @@
         <v>235</v>
       </c>
       <c r="AK43" t="n">
-        <v>129.07</v>
+        <v>130.73</v>
       </c>
       <c r="AL43" t="n">
-        <v>-0.14</v>
+        <v>1.66</v>
       </c>
       <c r="AM43" t="n">
         <v>110</v>
@@ -4688,99 +4688,54 @@
         <v>142</v>
       </c>
       <c r="AP43" t="n">
-        <v>85.52</v>
+        <v>88.2</v>
       </c>
       <c r="AS43" t="n">
-        <v>15.82</v>
+        <v>15.76</v>
       </c>
       <c r="BL43" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B44" t="n">
-        <v>146.8</v>
-      </c>
-      <c r="C44" t="n">
-        <v>52.8</v>
+        <v>133.9</v>
       </c>
       <c r="D44" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="E44" t="n">
-        <v>28.9</v>
+        <v>34.7</v>
       </c>
       <c r="F44" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="H44" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="I44" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="J44" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="K44" t="n">
-        <v>73.59999999999999</v>
-      </c>
-      <c r="M44" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="N44" t="n">
-        <v>33.1</v>
-      </c>
-      <c r="O44" t="n">
-        <v>38.7</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>22</v>
-      </c>
-      <c r="R44" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="S44" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" t="n">
-        <v>22</v>
+        <v>3.3</v>
       </c>
       <c r="V44" t="n">
-        <v>11</v>
+        <v>14.3</v>
       </c>
       <c r="W44" t="n">
-        <v>22.9</v>
+        <v>21.7</v>
       </c>
       <c r="X44" t="n">
-        <v>16.9</v>
+        <v>18</v>
       </c>
       <c r="Y44" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z44" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AA44" t="n">
-        <v>16.1</v>
+        <v>15</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.9</v>
+        <v>-3.5</v>
       </c>
       <c r="AC44" t="n">
-        <v>7</v>
+        <v>3.2</v>
       </c>
       <c r="AD44" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>225.87</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>5.03</v>
+        <v>-0.1</v>
       </c>
       <c r="AH44" t="n">
         <v>215</v>
@@ -4788,67 +4743,55 @@
       <c r="AI44" t="n">
         <v>235</v>
       </c>
-      <c r="AK44" t="n">
-        <v>130.73</v>
-      </c>
-      <c r="AL44" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AM44" t="n">
         <v>110</v>
       </c>
       <c r="AN44" t="n">
         <v>142</v>
       </c>
-      <c r="AP44" t="n">
-        <v>88.2</v>
-      </c>
-      <c r="AS44" t="n">
-        <v>15.76</v>
-      </c>
       <c r="BL44" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B45" t="n">
-        <v>133.9</v>
+        <v>137.5</v>
       </c>
       <c r="D45" t="n">
-        <v>34.7</v>
+        <v>32.8</v>
       </c>
       <c r="F45" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="V45" t="n">
-        <v>14.3</v>
+        <v>9</v>
       </c>
       <c r="W45" t="n">
-        <v>21.7</v>
+        <v>15.7</v>
       </c>
       <c r="X45" t="n">
-        <v>18</v>
+        <v>12.3</v>
       </c>
       <c r="Y45" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z45" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="AA45" t="n">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="AB45" t="n">
-        <v>-3.5</v>
+        <v>-6.6</v>
       </c>
       <c r="AC45" t="n">
-        <v>3.2</v>
+        <v>8.1</v>
       </c>
       <c r="AD45" t="n">
-        <v>-0.1</v>
+        <v>0.8</v>
       </c>
       <c r="AH45" t="n">
         <v>215</v>
@@ -4863,48 +4806,93 @@
         <v>142</v>
       </c>
       <c r="BL45" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B46" t="n">
-        <v>137.5</v>
+        <v>157.1</v>
+      </c>
+      <c r="C46" t="n">
+        <v>73.09999999999999</v>
       </c>
       <c r="D46" t="n">
-        <v>32.8</v>
+        <v>31.7</v>
+      </c>
+      <c r="E46" t="n">
+        <v>26.1</v>
       </c>
       <c r="F46" t="n">
-        <v>2.3</v>
+        <v>2</v>
+      </c>
+      <c r="H46" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="I46" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="J46" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="K46" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="M46" t="n">
+        <v>6</v>
+      </c>
+      <c r="N46" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="O46" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="R46" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>23.8</v>
       </c>
       <c r="V46" t="n">
-        <v>9</v>
+        <v>6.8</v>
       </c>
       <c r="W46" t="n">
-        <v>15.7</v>
+        <v>11</v>
       </c>
       <c r="X46" t="n">
-        <v>12.3</v>
+        <v>8.9</v>
       </c>
       <c r="Y46" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="Z46" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA46" t="n">
-        <v>10.5</v>
+        <v>7.9</v>
       </c>
       <c r="AB46" t="n">
-        <v>-6.6</v>
+        <v>-1.2</v>
       </c>
       <c r="AC46" t="n">
-        <v>8.1</v>
+        <v>12.6</v>
       </c>
       <c r="AD46" t="n">
-        <v>0.8</v>
+        <v>5.7</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>224.2</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>-1.67</v>
       </c>
       <c r="AH46" t="n">
         <v>215</v>
@@ -4912,100 +4900,112 @@
       <c r="AI46" t="n">
         <v>235</v>
       </c>
+      <c r="AK46" t="n">
+        <v>128.6</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>-2.13</v>
+      </c>
       <c r="AM46" t="n">
         <v>110</v>
       </c>
       <c r="AN46" t="n">
         <v>142</v>
       </c>
+      <c r="AP46" t="n">
+        <v>81.18000000000001</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>14.06</v>
+      </c>
       <c r="BL46" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B47" t="n">
-        <v>157.1</v>
+        <v>153.1</v>
       </c>
       <c r="C47" t="n">
-        <v>73.09999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="D47" t="n">
-        <v>31.7</v>
+        <v>32.2</v>
       </c>
       <c r="E47" t="n">
-        <v>26.1</v>
+        <v>25.9</v>
       </c>
       <c r="F47" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="H47" t="n">
-        <v>23.6</v>
+        <v>24.4</v>
       </c>
       <c r="I47" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="J47" t="n">
-        <v>40.5</v>
+        <v>39.6</v>
       </c>
       <c r="K47" t="n">
-        <v>73.5</v>
+        <v>73.3</v>
       </c>
       <c r="M47" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="N47" t="n">
-        <v>33.4</v>
+        <v>34.4</v>
       </c>
       <c r="O47" t="n">
-        <v>39.5</v>
+        <v>40.1</v>
       </c>
       <c r="Q47" t="n">
         <v>23.8</v>
       </c>
       <c r="R47" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T47" t="n">
         <v>23.8</v>
       </c>
       <c r="V47" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="W47" t="n">
-        <v>11</v>
+        <v>15.2</v>
       </c>
       <c r="X47" t="n">
-        <v>8.9</v>
+        <v>10.9</v>
       </c>
       <c r="Y47" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Z47" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA47" t="n">
         <v>12</v>
       </c>
-      <c r="AA47" t="n">
-        <v>7.9</v>
-      </c>
       <c r="AB47" t="n">
-        <v>-1.2</v>
+        <v>1.7</v>
       </c>
       <c r="AC47" t="n">
-        <v>12.6</v>
+        <v>10</v>
       </c>
       <c r="AD47" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AF47" t="n">
-        <v>224.2</v>
+        <v>223.35</v>
       </c>
       <c r="AG47" t="n">
-        <v>-1.67</v>
+        <v>-0.85</v>
       </c>
       <c r="AH47" t="n">
         <v>215</v>
@@ -5014,10 +5014,10 @@
         <v>235</v>
       </c>
       <c r="AK47" t="n">
-        <v>128.6</v>
+        <v>127.19</v>
       </c>
       <c r="AL47" t="n">
-        <v>-2.13</v>
+        <v>-1.41</v>
       </c>
       <c r="AM47" t="n">
         <v>110</v>
@@ -5026,99 +5026,99 @@
         <v>142</v>
       </c>
       <c r="AP47" t="n">
-        <v>81.18000000000001</v>
+        <v>81.06</v>
       </c>
       <c r="AS47" t="n">
-        <v>14.06</v>
+        <v>13.63</v>
       </c>
       <c r="BL47" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B48" t="n">
-        <v>153.1</v>
+        <v>145.5</v>
       </c>
       <c r="C48" t="n">
-        <v>69.59999999999999</v>
+        <v>62.3</v>
       </c>
       <c r="D48" t="n">
-        <v>32.2</v>
+        <v>34</v>
       </c>
       <c r="E48" t="n">
-        <v>25.9</v>
+        <v>22.5</v>
       </c>
       <c r="F48" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="H48" t="n">
-        <v>24.4</v>
+        <v>24.8</v>
       </c>
       <c r="I48" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J48" t="n">
-        <v>39.6</v>
+        <v>40.8</v>
       </c>
       <c r="K48" t="n">
-        <v>73.3</v>
+        <v>75</v>
       </c>
       <c r="M48" t="n">
-        <v>5.7</v>
+        <v>6.9</v>
       </c>
       <c r="N48" t="n">
-        <v>34.4</v>
+        <v>30.4</v>
       </c>
       <c r="O48" t="n">
-        <v>40.1</v>
+        <v>37.3</v>
       </c>
       <c r="Q48" t="n">
-        <v>23.8</v>
+        <v>22.1</v>
       </c>
       <c r="R48" t="n">
-        <v>3.8</v>
+        <v>4.9</v>
       </c>
       <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="V48" t="n">
         <v>4</v>
       </c>
-      <c r="T48" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="V48" t="n">
-        <v>6.6</v>
-      </c>
       <c r="W48" t="n">
-        <v>15.2</v>
+        <v>22.9</v>
       </c>
       <c r="X48" t="n">
-        <v>10.9</v>
+        <v>13.4</v>
       </c>
       <c r="Y48" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="Z48" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AA48" t="n">
-        <v>12</v>
+        <v>12.9</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="AC48" t="n">
-        <v>10</v>
+        <v>12.7</v>
       </c>
       <c r="AD48" t="n">
-        <v>5.8</v>
+        <v>6.7</v>
       </c>
       <c r="AF48" t="n">
-        <v>223.35</v>
+        <v>223.06</v>
       </c>
       <c r="AG48" t="n">
-        <v>-0.85</v>
+        <v>-0.29</v>
       </c>
       <c r="AH48" t="n">
         <v>215</v>
@@ -5127,10 +5127,10 @@
         <v>235</v>
       </c>
       <c r="AK48" t="n">
-        <v>127.19</v>
+        <v>129.17</v>
       </c>
       <c r="AL48" t="n">
-        <v>-1.41</v>
+        <v>1.98</v>
       </c>
       <c r="AM48" t="n">
         <v>110</v>
@@ -5139,96 +5139,96 @@
         <v>142</v>
       </c>
       <c r="AP48" t="n">
-        <v>81.06</v>
+        <v>82.36</v>
       </c>
       <c r="AS48" t="n">
-        <v>13.63</v>
+        <v>13.91</v>
       </c>
       <c r="BL48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B49" t="n">
-        <v>145.5</v>
+        <v>148</v>
       </c>
       <c r="C49" t="n">
-        <v>62.3</v>
+        <v>61.6</v>
       </c>
       <c r="D49" t="n">
-        <v>34</v>
+        <v>33.9</v>
       </c>
       <c r="E49" t="n">
-        <v>22.5</v>
+        <v>25</v>
       </c>
       <c r="F49" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="H49" t="n">
-        <v>24.8</v>
+        <v>25.1</v>
       </c>
       <c r="I49" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="J49" t="n">
-        <v>40.8</v>
+        <v>39.5</v>
       </c>
       <c r="K49" t="n">
-        <v>75</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="M49" t="n">
-        <v>6.9</v>
+        <v>5.9</v>
       </c>
       <c r="N49" t="n">
-        <v>30.4</v>
+        <v>28.6</v>
       </c>
       <c r="O49" t="n">
-        <v>37.3</v>
+        <v>34.5</v>
       </c>
       <c r="Q49" t="n">
-        <v>22.1</v>
+        <v>23.3</v>
       </c>
       <c r="R49" t="n">
-        <v>4.9</v>
+        <v>3.9</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>22.1</v>
+        <v>23.3</v>
       </c>
       <c r="V49" t="n">
-        <v>4</v>
+        <v>7.8</v>
       </c>
       <c r="W49" t="n">
-        <v>22.9</v>
+        <v>26</v>
       </c>
       <c r="X49" t="n">
-        <v>13.4</v>
+        <v>16.9</v>
       </c>
       <c r="Y49" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="Z49" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AA49" t="n">
-        <v>12.9</v>
+        <v>11.6</v>
       </c>
       <c r="AB49" t="n">
-        <v>0.7</v>
+        <v>4.2</v>
       </c>
       <c r="AC49" t="n">
-        <v>12.7</v>
+        <v>11.4</v>
       </c>
       <c r="AD49" t="n">
-        <v>6.7</v>
+        <v>7.8</v>
       </c>
       <c r="AF49" t="n">
-        <v>223.06</v>
+        <v>222.77</v>
       </c>
       <c r="AG49" t="n">
         <v>-0.29</v>
@@ -5240,10 +5240,10 @@
         <v>235</v>
       </c>
       <c r="AK49" t="n">
-        <v>129.17</v>
+        <v>130.42</v>
       </c>
       <c r="AL49" t="n">
-        <v>1.98</v>
+        <v>1.25</v>
       </c>
       <c r="AM49" t="n">
         <v>110</v>
@@ -5252,60 +5252,60 @@
         <v>142</v>
       </c>
       <c r="AP49" t="n">
-        <v>82.36</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="AS49" t="n">
-        <v>13.91</v>
+        <v>14</v>
       </c>
       <c r="BL49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B50" t="n">
-        <v>148</v>
+        <v>135.5</v>
       </c>
       <c r="C50" t="n">
-        <v>61.6</v>
+        <v>47.7</v>
       </c>
       <c r="D50" t="n">
-        <v>33.9</v>
+        <v>34.2</v>
       </c>
       <c r="E50" t="n">
-        <v>25</v>
+        <v>24.1</v>
       </c>
       <c r="F50" t="n">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="H50" t="n">
-        <v>25.1</v>
+        <v>24.9</v>
       </c>
       <c r="I50" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="J50" t="n">
-        <v>39.5</v>
+        <v>38.4</v>
       </c>
       <c r="K50" t="n">
-        <v>74.09999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="M50" t="n">
-        <v>5.9</v>
+        <v>3</v>
       </c>
       <c r="N50" t="n">
-        <v>28.6</v>
+        <v>30.3</v>
       </c>
       <c r="O50" t="n">
-        <v>34.5</v>
+        <v>33.3</v>
       </c>
       <c r="Q50" t="n">
         <v>23.3</v>
       </c>
       <c r="R50" t="n">
-        <v>3.9</v>
+        <v>1</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -5314,37 +5314,37 @@
         <v>23.3</v>
       </c>
       <c r="V50" t="n">
-        <v>7.8</v>
+        <v>11.3</v>
       </c>
       <c r="W50" t="n">
-        <v>26</v>
+        <v>27.6</v>
       </c>
       <c r="X50" t="n">
-        <v>16.9</v>
+        <v>19.5</v>
       </c>
       <c r="Y50" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Z50" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="AA50" t="n">
-        <v>11.6</v>
+        <v>18.8</v>
       </c>
       <c r="AB50" t="n">
-        <v>4.2</v>
+        <v>1.8</v>
       </c>
       <c r="AC50" t="n">
-        <v>11.4</v>
+        <v>15.5</v>
       </c>
       <c r="AD50" t="n">
-        <v>7.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AF50" t="n">
-        <v>222.77</v>
+        <v>221.86</v>
       </c>
       <c r="AG50" t="n">
-        <v>-0.29</v>
+        <v>-0.91</v>
       </c>
       <c r="AH50" t="n">
         <v>215</v>
@@ -5353,10 +5353,10 @@
         <v>235</v>
       </c>
       <c r="AK50" t="n">
-        <v>130.42</v>
+        <v>129.71</v>
       </c>
       <c r="AL50" t="n">
-        <v>1.25</v>
+        <v>-0.71</v>
       </c>
       <c r="AM50" t="n">
         <v>110</v>
@@ -5365,99 +5365,54 @@
         <v>142</v>
       </c>
       <c r="AP50" t="n">
-        <v>80.90000000000001</v>
+        <v>86.42</v>
       </c>
       <c r="AS50" t="n">
-        <v>14</v>
+        <v>16.05</v>
       </c>
       <c r="BL50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B51" t="n">
-        <v>135.5</v>
-      </c>
-      <c r="C51" t="n">
-        <v>47.7</v>
+        <v>118.1</v>
       </c>
       <c r="D51" t="n">
-        <v>34.2</v>
-      </c>
-      <c r="E51" t="n">
-        <v>24.1</v>
+        <v>34.7</v>
       </c>
       <c r="F51" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H51" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="I51" t="n">
-        <v>10</v>
-      </c>
-      <c r="J51" t="n">
-        <v>38.4</v>
-      </c>
-      <c r="K51" t="n">
-        <v>73.2</v>
-      </c>
-      <c r="M51" t="n">
-        <v>3</v>
-      </c>
-      <c r="N51" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="O51" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="R51" t="n">
-        <v>1</v>
-      </c>
-      <c r="S51" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" t="n">
-        <v>23.3</v>
+        <v>3.3</v>
       </c>
       <c r="V51" t="n">
-        <v>11.3</v>
+        <v>14.1</v>
       </c>
       <c r="W51" t="n">
         <v>27.6</v>
       </c>
       <c r="X51" t="n">
-        <v>19.5</v>
+        <v>20.9</v>
       </c>
       <c r="Y51" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Z51" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA51" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="AC51" t="n">
-        <v>15.5</v>
+        <v>14.9</v>
       </c>
       <c r="AD51" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>221.86</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>-0.91</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AH51" t="n">
         <v>215</v>
@@ -5465,67 +5420,55 @@
       <c r="AI51" t="n">
         <v>235</v>
       </c>
-      <c r="AK51" t="n">
-        <v>129.71</v>
-      </c>
-      <c r="AL51" t="n">
-        <v>-0.71</v>
-      </c>
       <c r="AM51" t="n">
         <v>110</v>
       </c>
       <c r="AN51" t="n">
         <v>142</v>
       </c>
-      <c r="AP51" t="n">
-        <v>86.42</v>
-      </c>
-      <c r="AS51" t="n">
-        <v>16.05</v>
-      </c>
       <c r="BL51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B52" t="n">
-        <v>118.1</v>
+        <v>100.3</v>
       </c>
       <c r="D52" t="n">
-        <v>34.7</v>
+        <v>34</v>
       </c>
       <c r="F52" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="V52" t="n">
-        <v>14.1</v>
+        <v>16</v>
       </c>
       <c r="W52" t="n">
-        <v>27.6</v>
+        <v>30.6</v>
       </c>
       <c r="X52" t="n">
-        <v>20.9</v>
+        <v>23.3</v>
       </c>
       <c r="Y52" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z52" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA52" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AB52" t="n">
-        <v>3.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC52" t="n">
-        <v>14.9</v>
+        <v>16.7</v>
       </c>
       <c r="AD52" t="n">
-        <v>9.199999999999999</v>
+        <v>12.8</v>
       </c>
       <c r="AH52" t="n">
         <v>215</v>
@@ -5540,48 +5483,93 @@
         <v>142</v>
       </c>
       <c r="BL52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="B53" t="n">
-        <v>100.3</v>
+        <v>104.9</v>
+      </c>
+      <c r="C53" t="n">
+        <v>36.3</v>
       </c>
       <c r="D53" t="n">
-        <v>34</v>
+        <v>32.7</v>
+      </c>
+      <c r="E53" t="n">
+        <v>17</v>
       </c>
       <c r="F53" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
+      </c>
+      <c r="H53" t="n">
+        <v>16</v>
+      </c>
+      <c r="I53" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="J53" t="n">
+        <v>25</v>
+      </c>
+      <c r="K53" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="M53" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N53" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="O53" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>10.5</v>
       </c>
       <c r="V53" t="n">
-        <v>16</v>
+        <v>15.8</v>
       </c>
       <c r="W53" t="n">
-        <v>30.6</v>
+        <v>33.6</v>
       </c>
       <c r="X53" t="n">
-        <v>23.3</v>
+        <v>24.7</v>
       </c>
       <c r="Y53" t="n">
         <v>16</v>
       </c>
       <c r="Z53" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA53" t="n">
-        <v>20</v>
+        <v>16.9</v>
       </c>
       <c r="AB53" t="n">
-        <v>8.800000000000001</v>
+        <v>4</v>
       </c>
       <c r="AC53" t="n">
-        <v>16.7</v>
+        <v>10.1</v>
       </c>
       <c r="AD53" t="n">
-        <v>12.8</v>
+        <v>7</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>234.9</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>13.04</v>
       </c>
       <c r="AH53" t="n">
         <v>215</v>
@@ -5589,58 +5577,70 @@
       <c r="AI53" t="n">
         <v>235</v>
       </c>
+      <c r="AK53" t="n">
+        <v>137.51</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>7.8</v>
+      </c>
       <c r="AM53" t="n">
         <v>110</v>
       </c>
       <c r="AN53" t="n">
         <v>142</v>
       </c>
+      <c r="AP53" t="n">
+        <v>94</v>
+      </c>
+      <c r="AS53" t="n">
+        <v>18.87</v>
+      </c>
       <c r="BL53" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="B54" t="n">
-        <v>104.9</v>
+        <v>134.9</v>
       </c>
       <c r="C54" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="D54" t="n">
         <v>36.3</v>
       </c>
-      <c r="D54" t="n">
-        <v>32.7</v>
-      </c>
       <c r="E54" t="n">
-        <v>17</v>
+        <v>20.6</v>
       </c>
       <c r="F54" t="n">
         <v>1.6</v>
       </c>
       <c r="H54" t="n">
-        <v>16</v>
+        <v>21.2</v>
       </c>
       <c r="I54" t="n">
-        <v>10.1</v>
+        <v>9.4</v>
       </c>
       <c r="J54" t="n">
-        <v>25</v>
+        <v>35.4</v>
       </c>
       <c r="K54" t="n">
-        <v>51.2</v>
+        <v>66</v>
       </c>
       <c r="M54" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="N54" t="n">
-        <v>25.5</v>
+        <v>24.8</v>
       </c>
       <c r="O54" t="n">
-        <v>27.3</v>
+        <v>26.7</v>
       </c>
       <c r="Q54" t="n">
-        <v>10.5</v>
+        <v>18.3</v>
       </c>
       <c r="R54" t="n">
         <v>0</v>
@@ -5649,40 +5649,40 @@
         <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>10.5</v>
+        <v>18.3</v>
       </c>
       <c r="V54" t="n">
-        <v>15.8</v>
+        <v>18.5</v>
       </c>
       <c r="W54" t="n">
-        <v>33.6</v>
+        <v>22.5</v>
       </c>
       <c r="X54" t="n">
-        <v>24.7</v>
+        <v>20.5</v>
       </c>
       <c r="Y54" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="Z54" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AA54" t="n">
-        <v>16.9</v>
+        <v>13.8</v>
       </c>
       <c r="AB54" t="n">
-        <v>4</v>
+        <v>1.3</v>
       </c>
       <c r="AC54" t="n">
-        <v>10.1</v>
+        <v>9.5</v>
       </c>
       <c r="AD54" t="n">
-        <v>7</v>
+        <v>5.4</v>
       </c>
       <c r="AF54" t="n">
-        <v>234.9</v>
+        <v>229.2</v>
       </c>
       <c r="AG54" t="n">
-        <v>13.04</v>
+        <v>-5.7</v>
       </c>
       <c r="AH54" t="n">
         <v>215</v>
@@ -5691,10 +5691,10 @@
         <v>235</v>
       </c>
       <c r="AK54" t="n">
-        <v>137.51</v>
+        <v>138.98</v>
       </c>
       <c r="AL54" t="n">
-        <v>7.8</v>
+        <v>1.47</v>
       </c>
       <c r="AM54" t="n">
         <v>110</v>
@@ -5703,57 +5703,57 @@
         <v>142</v>
       </c>
       <c r="AP54" t="n">
-        <v>94</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="AS54" t="n">
-        <v>18.87</v>
+        <v>16.02</v>
       </c>
       <c r="BL54" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B55" t="n">
-        <v>134.9</v>
+        <v>146.4</v>
       </c>
       <c r="C55" t="n">
-        <v>53.3</v>
+        <v>60.2</v>
       </c>
       <c r="D55" t="n">
-        <v>36.3</v>
+        <v>35.6</v>
       </c>
       <c r="E55" t="n">
-        <v>20.6</v>
+        <v>24.2</v>
       </c>
       <c r="F55" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="H55" t="n">
-        <v>21.2</v>
+        <v>23</v>
       </c>
       <c r="I55" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J55" t="n">
-        <v>35.4</v>
+        <v>38.2</v>
       </c>
       <c r="K55" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="M55" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="N55" t="n">
-        <v>24.8</v>
+        <v>30.2</v>
       </c>
       <c r="O55" t="n">
-        <v>26.7</v>
+        <v>31.9</v>
       </c>
       <c r="Q55" t="n">
-        <v>18.3</v>
+        <v>20.2</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
@@ -5762,40 +5762,40 @@
         <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>18.3</v>
+        <v>20.2</v>
       </c>
       <c r="V55" t="n">
-        <v>18.5</v>
+        <v>14.1</v>
       </c>
       <c r="W55" t="n">
-        <v>22.5</v>
+        <v>20.2</v>
       </c>
       <c r="X55" t="n">
-        <v>20.5</v>
+        <v>17.1</v>
       </c>
       <c r="Y55" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="Z55" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AA55" t="n">
-        <v>13.8</v>
+        <v>9.6</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.3</v>
+        <v>-0</v>
       </c>
       <c r="AC55" t="n">
-        <v>9.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AD55" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="AF55" t="n">
-        <v>229.2</v>
+        <v>224.9</v>
       </c>
       <c r="AG55" t="n">
-        <v>-5.7</v>
+        <v>-4.3</v>
       </c>
       <c r="AH55" t="n">
         <v>215</v>
@@ -5804,10 +5804,10 @@
         <v>235</v>
       </c>
       <c r="AK55" t="n">
-        <v>138.98</v>
+        <v>134.04</v>
       </c>
       <c r="AL55" t="n">
-        <v>1.47</v>
+        <v>-4.94</v>
       </c>
       <c r="AM55" t="n">
         <v>110</v>
@@ -5816,57 +5816,57 @@
         <v>142</v>
       </c>
       <c r="AP55" t="n">
-        <v>84.90000000000001</v>
+        <v>76.5</v>
       </c>
       <c r="AS55" t="n">
-        <v>16.02</v>
+        <v>13.68</v>
       </c>
       <c r="BL55" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B56" t="n">
-        <v>146.4</v>
+        <v>131.4</v>
       </c>
       <c r="C56" t="n">
-        <v>60.2</v>
+        <v>53.7</v>
       </c>
       <c r="D56" t="n">
-        <v>35.6</v>
+        <v>34.7</v>
       </c>
       <c r="E56" t="n">
-        <v>24.2</v>
+        <v>20.1</v>
       </c>
       <c r="F56" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="H56" t="n">
-        <v>23</v>
+        <v>24.1</v>
       </c>
       <c r="I56" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J56" t="n">
-        <v>38.2</v>
+        <v>37</v>
       </c>
       <c r="K56" t="n">
-        <v>70</v>
+        <v>69.8</v>
       </c>
       <c r="M56" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="N56" t="n">
-        <v>30.2</v>
+        <v>31.4</v>
       </c>
       <c r="O56" t="n">
-        <v>31.9</v>
+        <v>33.3</v>
       </c>
       <c r="Q56" t="n">
-        <v>20.2</v>
+        <v>22.3</v>
       </c>
       <c r="R56" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
         <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>20.2</v>
+        <v>22.3</v>
       </c>
       <c r="Y56" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z56" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AA56" t="n">
-        <v>9.6</v>
+        <v>14</v>
       </c>
       <c r="AF56" t="n">
-        <v>224.9</v>
+        <v>220.8</v>
       </c>
       <c r="AG56" t="n">
-        <v>-4.3</v>
+        <v>-4.1</v>
       </c>
       <c r="AH56" t="n">
         <v>215</v>
@@ -5899,10 +5899,10 @@
         <v>235</v>
       </c>
       <c r="AK56" t="n">
-        <v>134.04</v>
+        <v>131.01</v>
       </c>
       <c r="AL56" t="n">
-        <v>-4.94</v>
+        <v>-3.03</v>
       </c>
       <c r="AM56" t="n">
         <v>110</v>
@@ -5911,57 +5911,57 @@
         <v>142</v>
       </c>
       <c r="AP56" t="n">
-        <v>76.5</v>
+        <v>81.28</v>
       </c>
       <c r="AS56" t="n">
-        <v>13.68</v>
+        <v>13.92</v>
       </c>
       <c r="BL56" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B57" t="n">
-        <v>131.4</v>
+        <v>127.2</v>
       </c>
       <c r="C57" t="n">
-        <v>53.7</v>
+        <v>42.7</v>
       </c>
       <c r="D57" t="n">
-        <v>34.7</v>
+        <v>34.6</v>
       </c>
       <c r="E57" t="n">
-        <v>20.1</v>
+        <v>20.7</v>
       </c>
       <c r="F57" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="H57" t="n">
-        <v>24.1</v>
+        <v>21.2</v>
       </c>
       <c r="I57" t="n">
-        <v>8.6</v>
+        <v>9.1</v>
       </c>
       <c r="J57" t="n">
-        <v>37</v>
+        <v>36.8</v>
       </c>
       <c r="K57" t="n">
-        <v>69.8</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="M57" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="N57" t="n">
-        <v>31.4</v>
+        <v>27.9</v>
       </c>
       <c r="O57" t="n">
-        <v>33.3</v>
+        <v>29.8</v>
       </c>
       <c r="Q57" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
@@ -5970,22 +5970,22 @@
         <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="Y57" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="Z57" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AA57" t="n">
-        <v>14</v>
+        <v>19.7</v>
       </c>
       <c r="AF57" t="n">
-        <v>220.8</v>
+        <v>228.06</v>
       </c>
       <c r="AG57" t="n">
-        <v>-4.1</v>
+        <v>7.26</v>
       </c>
       <c r="AH57" t="n">
         <v>215</v>
@@ -5994,10 +5994,10 @@
         <v>235</v>
       </c>
       <c r="AK57" t="n">
-        <v>131.01</v>
+        <v>131.96</v>
       </c>
       <c r="AL57" t="n">
-        <v>-3.03</v>
+        <v>0.95</v>
       </c>
       <c r="AM57" t="n">
         <v>110</v>
@@ -6006,81 +6006,36 @@
         <v>142</v>
       </c>
       <c r="AP57" t="n">
-        <v>81.28</v>
+        <v>84.34</v>
       </c>
       <c r="AS57" t="n">
-        <v>13.92</v>
+        <v>17.57</v>
       </c>
       <c r="BL57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B58" t="n">
-        <v>127.2</v>
-      </c>
-      <c r="C58" t="n">
-        <v>42.7</v>
+        <v>116.2</v>
       </c>
       <c r="D58" t="n">
-        <v>34.6</v>
-      </c>
-      <c r="E58" t="n">
-        <v>20.7</v>
+        <v>35.4</v>
       </c>
       <c r="F58" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H58" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="I58" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="J58" t="n">
-        <v>36.8</v>
-      </c>
-      <c r="K58" t="n">
-        <v>67.09999999999999</v>
-      </c>
-      <c r="M58" t="n">
-        <v>2</v>
-      </c>
-      <c r="N58" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="O58" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="R58" t="n">
-        <v>0</v>
-      </c>
-      <c r="S58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T58" t="n">
-        <v>22.2</v>
+        <v>4.5</v>
       </c>
       <c r="Y58" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="Z58" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AA58" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="AF58" t="n">
-        <v>228.06</v>
-      </c>
-      <c r="AG58" t="n">
-        <v>7.26</v>
+        <v>21</v>
       </c>
       <c r="AH58" t="n">
         <v>215</v>
@@ -6088,49 +6043,37 @@
       <c r="AI58" t="n">
         <v>235</v>
       </c>
-      <c r="AK58" t="n">
-        <v>131.96</v>
-      </c>
-      <c r="AL58" t="n">
-        <v>0.95</v>
-      </c>
       <c r="AM58" t="n">
         <v>110</v>
       </c>
       <c r="AN58" t="n">
         <v>142</v>
       </c>
-      <c r="AP58" t="n">
-        <v>84.34</v>
-      </c>
-      <c r="AS58" t="n">
-        <v>17.57</v>
-      </c>
       <c r="BL58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B59" t="n">
-        <v>116.2</v>
+        <v>105.5</v>
       </c>
       <c r="D59" t="n">
-        <v>35.4</v>
+        <v>34</v>
       </c>
       <c r="F59" t="n">
         <v>4.5</v>
       </c>
       <c r="Y59" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Z59" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AA59" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AH59" t="n">
         <v>215</v>
@@ -6145,30 +6088,75 @@
         <v>142</v>
       </c>
       <c r="BL59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="B60" t="n">
-        <v>105.5</v>
+        <v>112.8</v>
+      </c>
+      <c r="C60" t="n">
+        <v>37</v>
       </c>
       <c r="D60" t="n">
-        <v>34</v>
+        <v>32.4</v>
+      </c>
+      <c r="E60" t="n">
+        <v>23.5</v>
       </c>
       <c r="F60" t="n">
-        <v>4.5</v>
+        <v>2.6</v>
+      </c>
+      <c r="H60" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="I60" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="J60" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="K60" t="n">
+        <v>56.9</v>
+      </c>
+      <c r="M60" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="N60" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="O60" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>17</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>17</v>
       </c>
       <c r="Y60" t="n">
         <v>15</v>
       </c>
       <c r="Z60" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AA60" t="n">
-        <v>18.5</v>
+        <v>16</v>
+      </c>
+      <c r="AF60" t="n">
+        <v>235</v>
+      </c>
+      <c r="AG60" t="n">
+        <v>6.94</v>
       </c>
       <c r="AH60" t="n">
         <v>215</v>
@@ -6176,28 +6164,40 @@
       <c r="AI60" t="n">
         <v>235</v>
       </c>
+      <c r="AK60" t="n">
+        <v>136.61</v>
+      </c>
+      <c r="AL60" t="n">
+        <v>4.65</v>
+      </c>
       <c r="AM60" t="n">
         <v>110</v>
       </c>
       <c r="AN60" t="n">
         <v>142</v>
       </c>
+      <c r="AP60" t="n">
+        <v>89.01000000000001</v>
+      </c>
+      <c r="AS60" t="n">
+        <v>18.21</v>
+      </c>
       <c r="BL60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="B61" t="n">
-        <v>99.59999999999999</v>
+        <v>116.4</v>
       </c>
       <c r="D61" t="n">
-        <v>33.5</v>
+        <v>35.3</v>
       </c>
       <c r="F61" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="Y61" t="n">
         <v>15</v>
@@ -6221,21 +6221,21 @@
         <v>142</v>
       </c>
       <c r="BL61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B62" t="n">
-        <v>116.4</v>
+        <v>118.3</v>
       </c>
       <c r="D62" t="n">
-        <v>35.3</v>
+        <v>37.2</v>
       </c>
       <c r="F62" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="Y62" t="n">
         <v>15</v>
@@ -6259,7 +6259,7 @@
         <v>142</v>
       </c>
       <c r="BL62" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -5877,6 +5877,15 @@
       <c r="T56" t="n">
         <v>22.3</v>
       </c>
+      <c r="V56" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="W56" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="X56" t="n">
+        <v>17.6</v>
+      </c>
       <c r="Y56" t="n">
         <v>7</v>
       </c>
@@ -5885,6 +5894,15 @@
       </c>
       <c r="AA56" t="n">
         <v>14</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>9.1</v>
       </c>
       <c r="AF56" t="n">
         <v>220.8</v>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -628,55 +628,88 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B2" t="n">
-        <v>137.6</v>
+        <v>137.2</v>
+      </c>
+      <c r="C2" t="n">
+        <v>56.3</v>
       </c>
       <c r="D2" t="n">
-        <v>35</v>
+        <v>32.1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>21.2</v>
       </c>
       <c r="F2" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="I2" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="J2" t="n">
+        <v>40.4</v>
       </c>
       <c r="K2" t="n">
-        <v>96.7</v>
+        <v>75.7</v>
+      </c>
+      <c r="M2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N2" t="n">
+        <v>29</v>
       </c>
       <c r="O2" t="n">
-        <v>35.1</v>
+        <v>32.6</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>21.6</v>
       </c>
       <c r="V2" t="n">
-        <v>13.6</v>
+        <v>10.7</v>
       </c>
       <c r="W2" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="X2" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Z2" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AA2" t="n">
-        <v>17.5</v>
+        <v>15.4</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0</v>
+        <v>0.9</v>
       </c>
       <c r="AC2" t="n">
         <v>5.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="AF2" t="n">
-        <v>221.78</v>
+        <v>232.22</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.94</v>
+        <v>7.43</v>
       </c>
       <c r="AH2" t="n">
         <v>215</v>
@@ -685,10 +718,10 @@
         <v>235</v>
       </c>
       <c r="AK2" t="n">
-        <v>138.76</v>
+        <v>143.61</v>
       </c>
       <c r="AL2" t="n">
-        <v>5.67</v>
+        <v>0.06</v>
       </c>
       <c r="AM2" t="n">
         <v>110</v>
@@ -696,61 +729,100 @@
       <c r="AN2" t="n">
         <v>142</v>
       </c>
+      <c r="AP2" t="n">
+        <v>89.31999999999999</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>18.02</v>
+      </c>
       <c r="BL2" s="1" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46235</v>
+        <v>46237</v>
       </c>
       <c r="B3" t="n">
-        <v>132.5</v>
+        <v>157.5</v>
+      </c>
+      <c r="C3" t="n">
+        <v>59.6</v>
       </c>
       <c r="D3" t="n">
-        <v>33.6</v>
+        <v>35</v>
+      </c>
+      <c r="E3" t="n">
+        <v>30.6</v>
       </c>
       <c r="F3" t="n">
-        <v>3.5</v>
+        <v>7.5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="I3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="J3" t="n">
+        <v>38.9</v>
       </c>
       <c r="K3" t="n">
-        <v>97.8</v>
+        <v>74.3</v>
+      </c>
+      <c r="M3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N3" t="n">
+        <v>33.4</v>
       </c>
       <c r="O3" t="n">
-        <v>31.6</v>
+        <v>37.1</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>21.1</v>
       </c>
       <c r="V3" t="n">
-        <v>14.8</v>
+        <v>13</v>
       </c>
       <c r="W3" t="n">
-        <v>24.7</v>
+        <v>26.3</v>
       </c>
       <c r="X3" t="n">
-        <v>19.8</v>
+        <v>19.6</v>
       </c>
       <c r="Y3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z3" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AA3" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.6</v>
+        <v>-2.1</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.6</v>
+        <v>6.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AF3" t="n">
-        <v>224.78</v>
+        <v>229.69</v>
       </c>
       <c r="AG3" t="n">
-        <v>3</v>
+        <v>-2.53</v>
       </c>
       <c r="AH3" t="n">
         <v>215</v>
@@ -759,10 +831,10 @@
         <v>235</v>
       </c>
       <c r="AK3" t="n">
-        <v>143.55</v>
+        <v>136.96</v>
       </c>
       <c r="AL3" t="n">
-        <v>4.79</v>
+        <v>-6.65</v>
       </c>
       <c r="AM3" t="n">
         <v>110</v>
@@ -770,94 +842,100 @@
       <c r="AN3" t="n">
         <v>142</v>
       </c>
+      <c r="AP3" t="n">
+        <v>86.59</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>16.96</v>
+      </c>
       <c r="BL3" s="1" t="n">
-        <v>46235</v>
+        <v>46237</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46236</v>
+        <v>46238</v>
       </c>
       <c r="B4" t="n">
-        <v>137.2</v>
+        <v>159.6</v>
       </c>
       <c r="C4" t="n">
-        <v>56.3</v>
+        <v>63</v>
       </c>
       <c r="D4" t="n">
-        <v>32.1</v>
+        <v>34.5</v>
       </c>
       <c r="E4" t="n">
-        <v>21.2</v>
+        <v>31.1</v>
       </c>
       <c r="F4" t="n">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="H4" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="I4" t="n">
-        <v>11.6</v>
+        <v>10.8</v>
       </c>
       <c r="J4" t="n">
-        <v>40.4</v>
+        <v>40.5</v>
       </c>
       <c r="K4" t="n">
-        <v>75.7</v>
+        <v>75.2</v>
       </c>
       <c r="M4" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="N4" t="n">
-        <v>29</v>
+        <v>34.3</v>
       </c>
       <c r="O4" t="n">
-        <v>32.6</v>
+        <v>38.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>21.6</v>
+        <v>21.3</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T4" t="n">
-        <v>21.6</v>
+        <v>21.3</v>
       </c>
       <c r="V4" t="n">
-        <v>10.7</v>
+        <v>17.5</v>
       </c>
       <c r="W4" t="n">
-        <v>24.3</v>
+        <v>22.5</v>
       </c>
       <c r="X4" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="Y4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z4" t="n">
         <v>15</v>
       </c>
       <c r="AA4" t="n">
-        <v>15.4</v>
+        <v>13.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.9</v>
+        <v>-2.2</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.2</v>
+        <v>1.2</v>
       </c>
       <c r="AF4" t="n">
-        <v>232.22</v>
+        <v>228.57</v>
       </c>
       <c r="AG4" t="n">
-        <v>7.43</v>
+        <v>-1.14</v>
       </c>
       <c r="AH4" t="n">
         <v>215</v>
@@ -866,10 +944,10 @@
         <v>235</v>
       </c>
       <c r="AK4" t="n">
-        <v>143.61</v>
+        <v>133.01</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.06</v>
+        <v>-3.95</v>
       </c>
       <c r="AM4" t="n">
         <v>110</v>
@@ -878,72 +956,72 @@
         <v>142</v>
       </c>
       <c r="AP4" t="n">
-        <v>89.31999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="AS4" t="n">
-        <v>18.02</v>
+        <v>15.95</v>
       </c>
       <c r="BL4" s="1" t="n">
-        <v>46236</v>
+        <v>46238</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="B5" t="n">
-        <v>157.5</v>
+        <v>160.4</v>
       </c>
       <c r="C5" t="n">
-        <v>59.6</v>
+        <v>62.6</v>
       </c>
       <c r="D5" t="n">
         <v>35</v>
       </c>
       <c r="E5" t="n">
-        <v>30.6</v>
+        <v>32.2</v>
       </c>
       <c r="F5" t="n">
-        <v>7.5</v>
+        <v>4.7</v>
       </c>
       <c r="H5" t="n">
-        <v>24.2</v>
+        <v>23.9</v>
       </c>
       <c r="I5" t="n">
-        <v>11.2</v>
+        <v>10.7</v>
       </c>
       <c r="J5" t="n">
-        <v>38.9</v>
+        <v>41.1</v>
       </c>
       <c r="K5" t="n">
-        <v>74.3</v>
+        <v>75.7</v>
       </c>
       <c r="M5" t="n">
-        <v>3.7</v>
+        <v>5.4</v>
       </c>
       <c r="N5" t="n">
-        <v>33.4</v>
+        <v>32.6</v>
       </c>
       <c r="O5" t="n">
-        <v>37.1</v>
+        <v>38</v>
       </c>
       <c r="Q5" t="n">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="T5" t="n">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="V5" t="n">
-        <v>13</v>
+        <v>16.4</v>
       </c>
       <c r="W5" t="n">
-        <v>26.3</v>
+        <v>22.8</v>
       </c>
       <c r="X5" t="n">
         <v>19.6</v>
@@ -955,22 +1033,22 @@
         <v>16</v>
       </c>
       <c r="AA5" t="n">
-        <v>15.5</v>
+        <v>14.1</v>
       </c>
       <c r="AB5" t="n">
-        <v>-2.1</v>
+        <v>-3.1</v>
       </c>
       <c r="AC5" t="n">
-        <v>6.2</v>
+        <v>4.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="AF5" t="n">
-        <v>229.69</v>
+        <v>225.08</v>
       </c>
       <c r="AG5" t="n">
-        <v>-2.53</v>
+        <v>-3.5</v>
       </c>
       <c r="AH5" t="n">
         <v>215</v>
@@ -979,10 +1057,10 @@
         <v>235</v>
       </c>
       <c r="AK5" t="n">
-        <v>136.96</v>
+        <v>135.24</v>
       </c>
       <c r="AL5" t="n">
-        <v>-6.65</v>
+        <v>2.23</v>
       </c>
       <c r="AM5" t="n">
         <v>110</v>
@@ -991,99 +1069,99 @@
         <v>142</v>
       </c>
       <c r="AP5" t="n">
-        <v>86.59</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="AS5" t="n">
-        <v>16.96</v>
+        <v>15.4</v>
       </c>
       <c r="BL5" s="1" t="n">
-        <v>46237</v>
+        <v>46239</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="B6" t="n">
-        <v>159.6</v>
+        <v>161.7</v>
       </c>
       <c r="C6" t="n">
-        <v>63</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>34.5</v>
+        <v>34.9</v>
       </c>
       <c r="E6" t="n">
-        <v>31.1</v>
+        <v>27.3</v>
       </c>
       <c r="F6" t="n">
-        <v>5.7</v>
+        <v>4.6</v>
       </c>
       <c r="H6" t="n">
-        <v>23.8</v>
+        <v>24.1</v>
       </c>
       <c r="I6" t="n">
-        <v>10.8</v>
+        <v>10.3</v>
       </c>
       <c r="J6" t="n">
-        <v>40.5</v>
+        <v>42.6</v>
       </c>
       <c r="K6" t="n">
-        <v>75.2</v>
+        <v>77</v>
       </c>
       <c r="M6" t="n">
-        <v>4</v>
+        <v>5.8</v>
       </c>
       <c r="N6" t="n">
-        <v>34.3</v>
+        <v>31.5</v>
       </c>
       <c r="O6" t="n">
-        <v>38.2</v>
+        <v>37.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>21.3</v>
+        <v>21</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T6" t="n">
-        <v>21.3</v>
+        <v>21</v>
       </c>
       <c r="V6" t="n">
-        <v>17.5</v>
+        <v>12.7</v>
       </c>
       <c r="W6" t="n">
-        <v>22.5</v>
+        <v>27</v>
       </c>
       <c r="X6" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="Y6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Z6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AA6" t="n">
-        <v>13.5</v>
+        <v>11.4</v>
       </c>
       <c r="AB6" t="n">
-        <v>-2.2</v>
+        <v>-5.2</v>
       </c>
       <c r="AC6" t="n">
         <v>4.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.2</v>
+        <v>-0.3</v>
       </c>
       <c r="AF6" t="n">
-        <v>228.57</v>
+        <v>225</v>
       </c>
       <c r="AG6" t="n">
-        <v>-1.14</v>
+        <v>-0.08</v>
       </c>
       <c r="AH6" t="n">
         <v>215</v>
@@ -1092,10 +1170,10 @@
         <v>235</v>
       </c>
       <c r="AK6" t="n">
-        <v>133.01</v>
+        <v>134.62</v>
       </c>
       <c r="AL6" t="n">
-        <v>-3.95</v>
+        <v>-0.62</v>
       </c>
       <c r="AM6" t="n">
         <v>110</v>
@@ -1104,99 +1182,60 @@
         <v>142</v>
       </c>
       <c r="AP6" t="n">
-        <v>84.59999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="AS6" t="n">
-        <v>15.95</v>
+        <v>13.86</v>
       </c>
       <c r="BL6" s="1" t="n">
-        <v>46238</v>
+        <v>46240</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="B7" t="n">
-        <v>160.4</v>
-      </c>
-      <c r="C7" t="n">
-        <v>62.6</v>
+        <v>151.5</v>
       </c>
       <c r="D7" t="n">
-        <v>35</v>
-      </c>
-      <c r="E7" t="n">
-        <v>32.2</v>
+        <v>35.1</v>
       </c>
       <c r="F7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H7" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="I7" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="J7" t="n">
-        <v>41.1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>75.7</v>
-      </c>
-      <c r="M7" t="n">
         <v>5.4</v>
       </c>
-      <c r="N7" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="O7" t="n">
-        <v>38</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="S7" t="n">
-        <v>8</v>
-      </c>
-      <c r="T7" t="n">
-        <v>20.9</v>
-      </c>
       <c r="V7" t="n">
-        <v>16.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W7" t="n">
-        <v>22.8</v>
+        <v>19.4</v>
       </c>
       <c r="X7" t="n">
-        <v>19.6</v>
+        <v>14</v>
       </c>
       <c r="Y7" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z7" t="n">
         <v>13</v>
       </c>
-      <c r="Z7" t="n">
-        <v>16</v>
-      </c>
       <c r="AA7" t="n">
-        <v>14.1</v>
+        <v>9</v>
       </c>
       <c r="AB7" t="n">
-        <v>-3.1</v>
+        <v>-4.7</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.3</v>
+        <v>1.9</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.6</v>
+        <v>-1.4</v>
       </c>
       <c r="AF7" t="n">
-        <v>225.08</v>
+        <v>221.37</v>
       </c>
       <c r="AG7" t="n">
-        <v>-3.5</v>
+        <v>0.05</v>
       </c>
       <c r="AH7" t="n">
         <v>215</v>
@@ -1205,10 +1244,10 @@
         <v>235</v>
       </c>
       <c r="AK7" t="n">
-        <v>135.24</v>
+        <v>135.21</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.23</v>
+        <v>0.59</v>
       </c>
       <c r="AM7" t="n">
         <v>110</v>
@@ -1216,100 +1255,61 @@
       <c r="AN7" t="n">
         <v>142</v>
       </c>
-      <c r="AP7" t="n">
-        <v>84.09999999999999</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>15.4</v>
-      </c>
       <c r="BL7" s="1" t="n">
-        <v>46239</v>
+        <v>46241</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46240</v>
+        <v>46242</v>
       </c>
       <c r="B8" t="n">
-        <v>161.7</v>
-      </c>
-      <c r="C8" t="n">
-        <v>71.09999999999999</v>
+        <v>145.2</v>
       </c>
       <c r="D8" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="E8" t="n">
-        <v>27.3</v>
+        <v>33.5</v>
       </c>
       <c r="F8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H8" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I8" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="J8" t="n">
-        <v>42.6</v>
+        <v>5</v>
       </c>
       <c r="K8" t="n">
-        <v>77</v>
-      </c>
-      <c r="M8" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="N8" t="n">
-        <v>31.5</v>
+        <v>100.3</v>
       </c>
       <c r="O8" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>21</v>
-      </c>
-      <c r="R8" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="S8" t="n">
-        <v>6</v>
-      </c>
-      <c r="T8" t="n">
-        <v>21</v>
+        <v>35.5</v>
       </c>
       <c r="V8" t="n">
-        <v>12.7</v>
+        <v>7.1</v>
       </c>
       <c r="W8" t="n">
-        <v>27</v>
+        <v>19.2</v>
       </c>
       <c r="X8" t="n">
-        <v>19.9</v>
+        <v>13.1</v>
       </c>
       <c r="Y8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA8" t="n">
-        <v>11.4</v>
+        <v>10</v>
       </c>
       <c r="AB8" t="n">
-        <v>-5.2</v>
+        <v>-5.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.6</v>
+        <v>2.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0.3</v>
+        <v>-1.5</v>
       </c>
       <c r="AF8" t="n">
-        <v>225</v>
+        <v>224.37</v>
       </c>
       <c r="AG8" t="n">
-        <v>-0.08</v>
+        <v>3</v>
       </c>
       <c r="AH8" t="n">
         <v>215</v>
@@ -1318,10 +1318,10 @@
         <v>235</v>
       </c>
       <c r="AK8" t="n">
-        <v>134.62</v>
+        <v>135.61</v>
       </c>
       <c r="AL8" t="n">
-        <v>-0.62</v>
+        <v>0.4</v>
       </c>
       <c r="AM8" t="n">
         <v>110</v>
@@ -1329,61 +1329,61 @@
       <c r="AN8" t="n">
         <v>142</v>
       </c>
-      <c r="AP8" t="n">
-        <v>80.2</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>13.86</v>
-      </c>
       <c r="BL8" s="1" t="n">
-        <v>46240</v>
+        <v>46242</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="B9" t="n">
-        <v>151.5</v>
+        <v>146.3</v>
       </c>
       <c r="D9" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="F9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K9" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="O9" t="n">
         <v>35.1</v>
       </c>
-      <c r="F9" t="n">
-        <v>5.4</v>
-      </c>
       <c r="V9" t="n">
-        <v>8.699999999999999</v>
+        <v>4.9</v>
       </c>
       <c r="W9" t="n">
-        <v>19.4</v>
+        <v>16.4</v>
       </c>
       <c r="X9" t="n">
-        <v>14</v>
+        <v>10.6</v>
       </c>
       <c r="Y9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Z9" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA9" t="n">
         <v>9</v>
       </c>
       <c r="AB9" t="n">
-        <v>-4.7</v>
+        <v>-6.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.9</v>
+        <v>-0.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>-1.4</v>
+        <v>-3.3</v>
       </c>
       <c r="AF9" t="n">
-        <v>221.37</v>
+        <v>225.93</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.05</v>
+        <v>1.56</v>
       </c>
       <c r="AH9" t="n">
         <v>215</v>
@@ -1392,10 +1392,10 @@
         <v>235</v>
       </c>
       <c r="AK9" t="n">
-        <v>135.21</v>
+        <v>135.28</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.59</v>
+        <v>-0.33</v>
       </c>
       <c r="AM9" t="n">
         <v>110</v>
@@ -1404,60 +1404,93 @@
         <v>142</v>
       </c>
       <c r="BL9" s="1" t="n">
-        <v>46241</v>
+        <v>46243</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46242</v>
+        <v>46244</v>
       </c>
       <c r="B10" t="n">
-        <v>145.2</v>
+        <v>182.8</v>
+      </c>
+      <c r="C10" t="n">
+        <v>86.8</v>
       </c>
       <c r="D10" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E10" t="n">
+        <v>33</v>
+      </c>
+      <c r="F10" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="H10" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="I10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="N10" t="n">
         <v>33.5</v>
       </c>
-      <c r="F10" t="n">
-        <v>5</v>
-      </c>
-      <c r="K10" t="n">
-        <v>100.3</v>
-      </c>
       <c r="O10" t="n">
-        <v>35.5</v>
+        <v>38.4</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="n">
+        <v>22.4</v>
       </c>
       <c r="V10" t="n">
-        <v>7.1</v>
+        <v>9.1</v>
       </c>
       <c r="W10" t="n">
-        <v>19.2</v>
+        <v>15</v>
       </c>
       <c r="X10" t="n">
-        <v>13.1</v>
+        <v>12.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Z10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA10" t="n">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>-5.4</v>
+        <v>-10.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.4</v>
+        <v>0.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>-1.5</v>
+        <v>-5.1</v>
       </c>
       <c r="AF10" t="n">
-        <v>224.37</v>
+        <v>218.63</v>
       </c>
       <c r="AG10" t="n">
-        <v>3</v>
+        <v>-7.3</v>
       </c>
       <c r="AH10" t="n">
         <v>215</v>
@@ -1466,10 +1499,10 @@
         <v>235</v>
       </c>
       <c r="AK10" t="n">
-        <v>135.61</v>
+        <v>126.27</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.4</v>
+        <v>-9.01</v>
       </c>
       <c r="AM10" t="n">
         <v>110</v>
@@ -1477,61 +1510,100 @@
       <c r="AN10" t="n">
         <v>142</v>
       </c>
+      <c r="AP10" t="n">
+        <v>82.66</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>14.7</v>
+      </c>
       <c r="BL10" s="1" t="n">
-        <v>46242</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46243</v>
+        <v>46245</v>
       </c>
       <c r="B11" t="n">
-        <v>146.3</v>
+        <v>181.8</v>
+      </c>
+      <c r="C11" t="n">
+        <v>86.5</v>
       </c>
       <c r="D11" t="n">
-        <v>33.4</v>
+        <v>31.4</v>
+      </c>
+      <c r="E11" t="n">
+        <v>34.2</v>
       </c>
       <c r="F11" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
+      </c>
+      <c r="H11" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="I11" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J11" t="n">
+        <v>41.9</v>
       </c>
       <c r="K11" t="n">
-        <v>98.2</v>
+        <v>76.8</v>
+      </c>
+      <c r="M11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N11" t="n">
+        <v>35.7</v>
       </c>
       <c r="O11" t="n">
-        <v>35.1</v>
+        <v>39.8</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>23</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>23</v>
       </c>
       <c r="V11" t="n">
-        <v>4.9</v>
+        <v>7.1</v>
       </c>
       <c r="W11" t="n">
-        <v>16.4</v>
+        <v>14.8</v>
       </c>
       <c r="X11" t="n">
-        <v>10.6</v>
+        <v>10.9</v>
       </c>
       <c r="Y11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Z11" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AA11" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AB11" t="n">
-        <v>-6.4</v>
+        <v>-4.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>-0.2</v>
+        <v>1.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>-3.3</v>
+        <v>-1.4</v>
       </c>
       <c r="AF11" t="n">
-        <v>225.93</v>
+        <v>216.39</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.56</v>
+        <v>-2.23</v>
       </c>
       <c r="AH11" t="n">
         <v>215</v>
@@ -1540,10 +1612,10 @@
         <v>235</v>
       </c>
       <c r="AK11" t="n">
-        <v>135.28</v>
+        <v>123.32</v>
       </c>
       <c r="AL11" t="n">
-        <v>-0.33</v>
+        <v>-2.95</v>
       </c>
       <c r="AM11" t="n">
         <v>110</v>
@@ -1551,94 +1623,100 @@
       <c r="AN11" t="n">
         <v>142</v>
       </c>
+      <c r="AP11" t="n">
+        <v>79.08</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>13.91</v>
+      </c>
       <c r="BL11" s="1" t="n">
-        <v>46243</v>
+        <v>46245</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="B12" t="n">
-        <v>182.8</v>
+        <v>183</v>
       </c>
       <c r="C12" t="n">
-        <v>86.8</v>
+        <v>84.7</v>
       </c>
       <c r="D12" t="n">
-        <v>31.8</v>
+        <v>30.9</v>
       </c>
       <c r="E12" t="n">
-        <v>33</v>
+        <v>33.7</v>
       </c>
       <c r="F12" t="n">
+        <v>7</v>
+      </c>
+      <c r="H12" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="I12" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="J12" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="K12" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="M12" t="n">
+        <v>4</v>
+      </c>
+      <c r="N12" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="O12" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S12" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="T12" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="V12" t="n">
         <v>5.7</v>
       </c>
-      <c r="H12" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="I12" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="J12" t="n">
-        <v>41.1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>74.2</v>
-      </c>
-      <c r="M12" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="N12" t="n">
-        <v>33.5</v>
-      </c>
-      <c r="O12" t="n">
-        <v>38.4</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="R12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="S12" t="n">
-        <v>15</v>
-      </c>
-      <c r="T12" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="V12" t="n">
-        <v>9.1</v>
-      </c>
       <c r="W12" t="n">
-        <v>15</v>
+        <v>16.1</v>
       </c>
       <c r="X12" t="n">
-        <v>12.1</v>
+        <v>10.9</v>
       </c>
       <c r="Y12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Z12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA12" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="AB12" t="n">
-        <v>-10.5</v>
+        <v>0.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.3</v>
+        <v>2.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>-5.1</v>
+        <v>1.8</v>
       </c>
       <c r="AF12" t="n">
-        <v>218.63</v>
+        <v>217.16</v>
       </c>
       <c r="AG12" t="n">
-        <v>-7.3</v>
+        <v>0.76</v>
       </c>
       <c r="AH12" t="n">
         <v>215</v>
@@ -1647,10 +1725,10 @@
         <v>235</v>
       </c>
       <c r="AK12" t="n">
-        <v>126.27</v>
+        <v>117.87</v>
       </c>
       <c r="AL12" t="n">
-        <v>-9.01</v>
+        <v>-5.45</v>
       </c>
       <c r="AM12" t="n">
         <v>110</v>
@@ -1659,99 +1737,66 @@
         <v>142</v>
       </c>
       <c r="AP12" t="n">
-        <v>82.66</v>
+        <v>78.56</v>
       </c>
       <c r="AS12" t="n">
-        <v>14.7</v>
+        <v>13.45</v>
       </c>
       <c r="BL12" s="1" t="n">
-        <v>46244</v>
+        <v>46246</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="B13" t="n">
-        <v>181.8</v>
-      </c>
-      <c r="C13" t="n">
-        <v>86.5</v>
+        <v>163.8</v>
       </c>
       <c r="D13" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="E13" t="n">
-        <v>34.2</v>
+        <v>29</v>
       </c>
       <c r="F13" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="H13" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="I13" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="J13" t="n">
-        <v>41.9</v>
+        <v>6.5</v>
       </c>
       <c r="K13" t="n">
-        <v>76.8</v>
-      </c>
-      <c r="M13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N13" t="n">
-        <v>35.7</v>
+        <v>101.2</v>
       </c>
       <c r="O13" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>23</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S13" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>23</v>
+        <v>40.2</v>
       </c>
       <c r="V13" t="n">
-        <v>7.1</v>
+        <v>6.3</v>
       </c>
       <c r="W13" t="n">
-        <v>14.8</v>
+        <v>17.2</v>
       </c>
       <c r="X13" t="n">
-        <v>10.9</v>
+        <v>11.8</v>
       </c>
       <c r="Y13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z13" t="n">
         <v>12</v>
       </c>
       <c r="AA13" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AB13" t="n">
-        <v>-4.5</v>
+        <v>1.2</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.8</v>
+        <v>4.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>-1.4</v>
+        <v>2.8</v>
       </c>
       <c r="AF13" t="n">
-        <v>216.39</v>
+        <v>220.31</v>
       </c>
       <c r="AG13" t="n">
-        <v>-2.23</v>
+        <v>3.16</v>
       </c>
       <c r="AH13" t="n">
         <v>215</v>
@@ -1760,10 +1805,10 @@
         <v>235</v>
       </c>
       <c r="AK13" t="n">
-        <v>123.32</v>
+        <v>116.52</v>
       </c>
       <c r="AL13" t="n">
-        <v>-2.95</v>
+        <v>-1.35</v>
       </c>
       <c r="AM13" t="n">
         <v>110</v>
@@ -1771,100 +1816,61 @@
       <c r="AN13" t="n">
         <v>142</v>
       </c>
-      <c r="AP13" t="n">
-        <v>79.08</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>13.91</v>
-      </c>
       <c r="BL13" s="1" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46246</v>
+        <v>46248</v>
       </c>
       <c r="B14" t="n">
-        <v>183</v>
-      </c>
-      <c r="C14" t="n">
-        <v>84.7</v>
+        <v>155.9</v>
       </c>
       <c r="D14" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="E14" t="n">
-        <v>33.7</v>
+        <v>28</v>
       </c>
       <c r="F14" t="n">
-        <v>7</v>
-      </c>
-      <c r="H14" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="I14" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="J14" t="n">
-        <v>42.3</v>
+        <v>6.5</v>
       </c>
       <c r="K14" t="n">
-        <v>76.40000000000001</v>
-      </c>
-      <c r="M14" t="n">
-        <v>4</v>
-      </c>
-      <c r="N14" t="n">
-        <v>36.7</v>
+        <v>99.3</v>
       </c>
       <c r="O14" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S14" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="T14" t="n">
-        <v>23.6</v>
+        <v>38.5</v>
       </c>
       <c r="V14" t="n">
-        <v>5.7</v>
+        <v>8.9</v>
       </c>
       <c r="W14" t="n">
-        <v>16.1</v>
+        <v>15.8</v>
       </c>
       <c r="X14" t="n">
-        <v>10.9</v>
+        <v>12.4</v>
       </c>
       <c r="Y14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z14" t="n">
         <v>13</v>
       </c>
       <c r="AA14" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.7</v>
+        <v>5.7</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.8</v>
+        <v>3.5</v>
       </c>
       <c r="AF14" t="n">
-        <v>217.16</v>
+        <v>221.99</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.76</v>
+        <v>1.67</v>
       </c>
       <c r="AH14" t="n">
         <v>215</v>
@@ -1873,10 +1879,10 @@
         <v>235</v>
       </c>
       <c r="AK14" t="n">
-        <v>117.87</v>
+        <v>116.37</v>
       </c>
       <c r="AL14" t="n">
-        <v>-5.45</v>
+        <v>-0.15</v>
       </c>
       <c r="AM14" t="n">
         <v>110</v>
@@ -1884,67 +1890,61 @@
       <c r="AN14" t="n">
         <v>142</v>
       </c>
-      <c r="AP14" t="n">
-        <v>78.56</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>13.45</v>
-      </c>
       <c r="BL14" s="1" t="n">
-        <v>46246</v>
+        <v>46248</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46247</v>
+        <v>46249</v>
       </c>
       <c r="B15" t="n">
-        <v>163.8</v>
+        <v>141.3</v>
       </c>
       <c r="D15" t="n">
-        <v>29</v>
+        <v>26.3</v>
       </c>
       <c r="F15" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="K15" t="n">
-        <v>101.2</v>
+        <v>97.8</v>
       </c>
       <c r="O15" t="n">
-        <v>40.2</v>
+        <v>39.8</v>
       </c>
       <c r="V15" t="n">
-        <v>6.3</v>
+        <v>9.5</v>
       </c>
       <c r="W15" t="n">
-        <v>17.2</v>
+        <v>17.7</v>
       </c>
       <c r="X15" t="n">
-        <v>11.8</v>
+        <v>13.6</v>
       </c>
       <c r="Y15" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="Z15" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AA15" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.3</v>
+        <v>7.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="AF15" t="n">
-        <v>220.31</v>
+        <v>225.14</v>
       </c>
       <c r="AG15" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="AH15" t="n">
         <v>215</v>
@@ -1952,12 +1952,6 @@
       <c r="AI15" t="n">
         <v>235</v>
       </c>
-      <c r="AK15" t="n">
-        <v>116.52</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>-1.35</v>
-      </c>
       <c r="AM15" t="n">
         <v>110</v>
       </c>
@@ -1965,60 +1959,54 @@
         <v>142</v>
       </c>
       <c r="BL15" s="1" t="n">
-        <v>46247</v>
+        <v>46249</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46248</v>
+        <v>46250</v>
       </c>
       <c r="B16" t="n">
-        <v>155.9</v>
+        <v>131.5</v>
       </c>
       <c r="D16" t="n">
-        <v>28</v>
+        <v>27.3</v>
       </c>
       <c r="F16" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="K16" t="n">
-        <v>99.3</v>
+        <v>97</v>
       </c>
       <c r="O16" t="n">
-        <v>38.5</v>
+        <v>35.7</v>
       </c>
       <c r="V16" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="W16" t="n">
-        <v>15.8</v>
+        <v>13.9</v>
       </c>
       <c r="X16" t="n">
-        <v>12.4</v>
+        <v>11.4</v>
       </c>
       <c r="Y16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z16" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AA16" t="n">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.4</v>
+        <v>-3.6</v>
       </c>
       <c r="AC16" t="n">
-        <v>5.7</v>
+        <v>2.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>221.99</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.67</v>
+        <v>-0.4</v>
       </c>
       <c r="AH16" t="n">
         <v>215</v>
@@ -2026,12 +2014,6 @@
       <c r="AI16" t="n">
         <v>235</v>
       </c>
-      <c r="AK16" t="n">
-        <v>116.37</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>-0.15</v>
-      </c>
       <c r="AM16" t="n">
         <v>110</v>
       </c>
@@ -2039,60 +2021,93 @@
         <v>142</v>
       </c>
       <c r="BL16" s="1" t="n">
-        <v>46248</v>
+        <v>46250</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46249</v>
+        <v>46251</v>
       </c>
       <c r="B17" t="n">
-        <v>141.3</v>
+        <v>153</v>
+      </c>
+      <c r="C17" t="n">
+        <v>71.8</v>
       </c>
       <c r="D17" t="n">
-        <v>26.3</v>
+        <v>28.6</v>
+      </c>
+      <c r="E17" t="n">
+        <v>24.7</v>
       </c>
       <c r="F17" t="n">
-        <v>5.5</v>
+        <v>4</v>
+      </c>
+      <c r="H17" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J17" t="n">
+        <v>41.1</v>
       </c>
       <c r="K17" t="n">
-        <v>97.8</v>
+        <v>75.90000000000001</v>
+      </c>
+      <c r="M17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N17" t="n">
+        <v>33.5</v>
       </c>
       <c r="O17" t="n">
-        <v>39.8</v>
+        <v>38.3</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>23.2</v>
       </c>
       <c r="V17" t="n">
-        <v>9.5</v>
+        <v>11.2</v>
       </c>
       <c r="W17" t="n">
-        <v>17.7</v>
+        <v>13</v>
       </c>
       <c r="X17" t="n">
-        <v>13.6</v>
+        <v>12.1</v>
       </c>
       <c r="Y17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AA17" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.2</v>
+        <v>-6.6</v>
       </c>
       <c r="AC17" t="n">
-        <v>7.5</v>
+        <v>5.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.9</v>
+        <v>-0.6</v>
       </c>
       <c r="AF17" t="n">
-        <v>225.14</v>
+        <v>229.96</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.15</v>
+        <v>-0.02</v>
       </c>
       <c r="AH17" t="n">
         <v>215</v>
@@ -2100,61 +2115,112 @@
       <c r="AI17" t="n">
         <v>235</v>
       </c>
+      <c r="AK17" t="n">
+        <v>128.14</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>11.77</v>
+      </c>
       <c r="AM17" t="n">
         <v>110</v>
       </c>
       <c r="AN17" t="n">
         <v>142</v>
       </c>
+      <c r="AP17" t="n">
+        <v>87.47</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>14.8</v>
+      </c>
       <c r="BL17" s="1" t="n">
-        <v>46249</v>
+        <v>46251</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46250</v>
+        <v>46252</v>
       </c>
       <c r="B18" t="n">
-        <v>131.5</v>
+        <v>165.8</v>
+      </c>
+      <c r="C18" t="n">
+        <v>77.3</v>
       </c>
       <c r="D18" t="n">
-        <v>27.3</v>
+        <v>29.3</v>
+      </c>
+      <c r="E18" t="n">
+        <v>27.7</v>
       </c>
       <c r="F18" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
+      </c>
+      <c r="H18" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="J18" t="n">
+        <v>41.6</v>
       </c>
       <c r="K18" t="n">
-        <v>97</v>
+        <v>76.59999999999999</v>
+      </c>
+      <c r="M18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N18" t="n">
+        <v>35.1</v>
       </c>
       <c r="O18" t="n">
-        <v>35.7</v>
+        <v>39.8</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S18" t="n">
+        <v>7</v>
+      </c>
+      <c r="T18" t="n">
+        <v>23.8</v>
       </c>
       <c r="V18" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="W18" t="n">
-        <v>13.9</v>
+        <v>17.4</v>
       </c>
       <c r="X18" t="n">
-        <v>11.4</v>
+        <v>13.4</v>
       </c>
       <c r="Y18" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z18" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AA18" t="n">
-        <v>15</v>
+        <v>10.1</v>
       </c>
       <c r="AB18" t="n">
-        <v>-3.6</v>
+        <v>-0.7</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.8</v>
+        <v>9.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>-0.4</v>
+        <v>4.4</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>227.01</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>-2.95</v>
       </c>
       <c r="AH18" t="n">
         <v>215</v>
@@ -2162,100 +2228,112 @@
       <c r="AI18" t="n">
         <v>235</v>
       </c>
+      <c r="AK18" t="n">
+        <v>128.15</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0.01</v>
+      </c>
       <c r="AM18" t="n">
         <v>110</v>
       </c>
       <c r="AN18" t="n">
         <v>142</v>
       </c>
+      <c r="AP18" t="n">
+        <v>83.41</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>14.52</v>
+      </c>
       <c r="BL18" s="1" t="n">
-        <v>46250</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="B19" t="n">
-        <v>153</v>
+        <v>158.1</v>
       </c>
       <c r="C19" t="n">
-        <v>71.8</v>
+        <v>73.7</v>
       </c>
       <c r="D19" t="n">
-        <v>28.6</v>
+        <v>30.3</v>
       </c>
       <c r="E19" t="n">
-        <v>24.7</v>
+        <v>26</v>
       </c>
       <c r="F19" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="H19" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="I19" t="n">
-        <v>10.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>41.1</v>
+        <v>40.9</v>
       </c>
       <c r="K19" t="n">
-        <v>75.90000000000001</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="N19" t="n">
-        <v>33.5</v>
+        <v>35.3</v>
       </c>
       <c r="O19" t="n">
-        <v>38.3</v>
+        <v>40.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>23.2</v>
+        <v>23.6</v>
       </c>
       <c r="R19" t="n">
         <v>2.5</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="T19" t="n">
-        <v>23.2</v>
+        <v>23.6</v>
       </c>
       <c r="V19" t="n">
-        <v>11.2</v>
+        <v>8.9</v>
       </c>
       <c r="W19" t="n">
-        <v>13</v>
+        <v>19.3</v>
       </c>
       <c r="X19" t="n">
-        <v>12.1</v>
+        <v>14.1</v>
       </c>
       <c r="Y19" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="Z19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA19" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AB19" t="n">
-        <v>-6.6</v>
+        <v>4.4</v>
       </c>
       <c r="AC19" t="n">
-        <v>5.3</v>
+        <v>8.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>-0.6</v>
+        <v>6.5</v>
       </c>
       <c r="AF19" t="n">
-        <v>229.96</v>
+        <v>228.35</v>
       </c>
       <c r="AG19" t="n">
-        <v>-0.02</v>
+        <v>1.33</v>
       </c>
       <c r="AH19" t="n">
         <v>215</v>
@@ -2264,10 +2342,10 @@
         <v>235</v>
       </c>
       <c r="AK19" t="n">
-        <v>128.14</v>
+        <v>128.86</v>
       </c>
       <c r="AL19" t="n">
-        <v>11.77</v>
+        <v>0.71</v>
       </c>
       <c r="AM19" t="n">
         <v>110</v>
@@ -2276,99 +2354,99 @@
         <v>142</v>
       </c>
       <c r="AP19" t="n">
-        <v>87.47</v>
+        <v>82.37</v>
       </c>
       <c r="AS19" t="n">
-        <v>14.8</v>
+        <v>14.22</v>
       </c>
       <c r="BL19" s="1" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B20" t="n">
-        <v>165.8</v>
+        <v>154.9</v>
       </c>
       <c r="C20" t="n">
-        <v>77.3</v>
+        <v>70.2</v>
       </c>
       <c r="D20" t="n">
-        <v>29.3</v>
+        <v>31.5</v>
       </c>
       <c r="E20" t="n">
         <v>27.7</v>
       </c>
       <c r="F20" t="n">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="H20" t="n">
         <v>24.1</v>
       </c>
       <c r="I20" t="n">
-        <v>10.8</v>
+        <v>11.3</v>
       </c>
       <c r="J20" t="n">
-        <v>41.6</v>
+        <v>40.3</v>
       </c>
       <c r="K20" t="n">
-        <v>76.59999999999999</v>
+        <v>75.8</v>
       </c>
       <c r="M20" t="n">
-        <v>4.7</v>
+        <v>6.1</v>
       </c>
       <c r="N20" t="n">
-        <v>35.1</v>
+        <v>32.9</v>
       </c>
       <c r="O20" t="n">
-        <v>39.8</v>
+        <v>39</v>
       </c>
       <c r="Q20" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="R20" t="n">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="T20" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="V20" t="n">
-        <v>9.4</v>
+        <v>6.3</v>
       </c>
       <c r="W20" t="n">
-        <v>17.4</v>
+        <v>25.2</v>
       </c>
       <c r="X20" t="n">
-        <v>13.4</v>
+        <v>15.8</v>
       </c>
       <c r="Y20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z20" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AA20" t="n">
-        <v>10.1</v>
+        <v>12.6</v>
       </c>
       <c r="AB20" t="n">
-        <v>-0.7</v>
+        <v>2.9</v>
       </c>
       <c r="AC20" t="n">
-        <v>9.5</v>
+        <v>8.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="AF20" t="n">
-        <v>227.01</v>
+        <v>231.16</v>
       </c>
       <c r="AG20" t="n">
-        <v>-2.95</v>
+        <v>2.81</v>
       </c>
       <c r="AH20" t="n">
         <v>215</v>
@@ -2377,10 +2455,10 @@
         <v>235</v>
       </c>
       <c r="AK20" t="n">
-        <v>128.15</v>
+        <v>130.88</v>
       </c>
       <c r="AL20" t="n">
-        <v>0.01</v>
+        <v>2.02</v>
       </c>
       <c r="AM20" t="n">
         <v>110</v>
@@ -2389,99 +2467,66 @@
         <v>142</v>
       </c>
       <c r="AP20" t="n">
-        <v>83.41</v>
+        <v>85.48999999999999</v>
       </c>
       <c r="AS20" t="n">
-        <v>14.52</v>
+        <v>13.1</v>
       </c>
       <c r="BL20" s="1" t="n">
-        <v>46252</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="B21" t="n">
-        <v>158.1</v>
-      </c>
-      <c r="C21" t="n">
-        <v>73.7</v>
+        <v>152.2</v>
       </c>
       <c r="D21" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="E21" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F21" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H21" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="I21" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="J21" t="n">
-        <v>40.9</v>
+        <v>3.5</v>
       </c>
       <c r="K21" t="n">
-        <v>74.40000000000001</v>
-      </c>
-      <c r="M21" t="n">
-        <v>5</v>
-      </c>
-      <c r="N21" t="n">
-        <v>35.3</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="R21" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S21" t="n">
-        <v>7</v>
-      </c>
-      <c r="T21" t="n">
-        <v>23.6</v>
+        <v>34.4</v>
       </c>
       <c r="V21" t="n">
-        <v>8.9</v>
+        <v>9.5</v>
       </c>
       <c r="W21" t="n">
-        <v>19.3</v>
+        <v>25.5</v>
       </c>
       <c r="X21" t="n">
-        <v>14.1</v>
+        <v>17.5</v>
       </c>
       <c r="Y21" t="n">
         <v>6</v>
       </c>
       <c r="Z21" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AA21" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AB21" t="n">
-        <v>4.4</v>
+        <v>-1.1</v>
       </c>
       <c r="AC21" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>6.5</v>
+        <v>3.8</v>
       </c>
       <c r="AF21" t="n">
-        <v>228.35</v>
+        <v>228.13</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.33</v>
+        <v>-3.03</v>
       </c>
       <c r="AH21" t="n">
         <v>215</v>
@@ -2489,112 +2534,67 @@
       <c r="AI21" t="n">
         <v>235</v>
       </c>
-      <c r="AK21" t="n">
-        <v>128.86</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>0.71</v>
-      </c>
       <c r="AM21" t="n">
         <v>110</v>
       </c>
       <c r="AN21" t="n">
         <v>142</v>
       </c>
-      <c r="AP21" t="n">
-        <v>82.37</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>14.22</v>
-      </c>
       <c r="BL21" s="1" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46254</v>
+        <v>46256</v>
       </c>
       <c r="B22" t="n">
-        <v>154.9</v>
-      </c>
-      <c r="C22" t="n">
-        <v>70.2</v>
+        <v>143.9</v>
       </c>
       <c r="D22" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="E22" t="n">
-        <v>27.7</v>
+        <v>30.8</v>
       </c>
       <c r="F22" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="H22" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I22" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J22" t="n">
-        <v>40.3</v>
+        <v>2.5</v>
       </c>
       <c r="K22" t="n">
-        <v>75.8</v>
-      </c>
-      <c r="M22" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="N22" t="n">
-        <v>32.9</v>
+        <v>99.2</v>
       </c>
       <c r="O22" t="n">
-        <v>39</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="R22" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="S22" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="T22" t="n">
-        <v>23.7</v>
+        <v>35.2</v>
       </c>
       <c r="V22" t="n">
-        <v>6.3</v>
+        <v>10.7</v>
       </c>
       <c r="W22" t="n">
-        <v>25.2</v>
+        <v>17.6</v>
       </c>
       <c r="X22" t="n">
-        <v>15.8</v>
+        <v>14.2</v>
       </c>
       <c r="Y22" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Z22" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AA22" t="n">
-        <v>12.6</v>
+        <v>9</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.9</v>
+        <v>-0.8</v>
       </c>
       <c r="AC22" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD22" t="n">
-        <v>5.8</v>
+        <v>4</v>
       </c>
       <c r="AF22" t="n">
-        <v>231.16</v>
+        <v>229.16</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.81</v>
+        <v>1.03</v>
       </c>
       <c r="AH22" t="n">
         <v>215</v>
@@ -2602,79 +2602,100 @@
       <c r="AI22" t="n">
         <v>235</v>
       </c>
-      <c r="AK22" t="n">
-        <v>130.88</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AM22" t="n">
         <v>110</v>
       </c>
       <c r="AN22" t="n">
         <v>142</v>
       </c>
-      <c r="AP22" t="n">
-        <v>85.48999999999999</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>13.1</v>
-      </c>
       <c r="BL22" s="1" t="n">
-        <v>46254</v>
+        <v>46256</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46255</v>
+        <v>46257</v>
       </c>
       <c r="B23" t="n">
-        <v>152.2</v>
+        <v>163.2</v>
+      </c>
+      <c r="C23" t="n">
+        <v>73.7</v>
       </c>
       <c r="D23" t="n">
-        <v>31</v>
+        <v>30</v>
+      </c>
+      <c r="E23" t="n">
+        <v>28.2</v>
       </c>
       <c r="F23" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
+      </c>
+      <c r="H23" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J23" t="n">
+        <v>40.1</v>
       </c>
       <c r="K23" t="n">
-        <v>98.40000000000001</v>
+        <v>75.59999999999999</v>
+      </c>
+      <c r="M23" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="N23" t="n">
+        <v>32.9</v>
       </c>
       <c r="O23" t="n">
-        <v>34.4</v>
+        <v>39.7</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="R23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="S23" t="n">
+        <v>6</v>
+      </c>
+      <c r="T23" t="n">
+        <v>23.5</v>
       </c>
       <c r="V23" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="W23" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="X23" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="AC23" t="n">
         <v>9.5</v>
       </c>
-      <c r="W23" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="X23" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>12</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>9</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>8.6</v>
-      </c>
       <c r="AD23" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="AF23" t="n">
-        <v>228.13</v>
+        <v>228.55</v>
       </c>
       <c r="AG23" t="n">
-        <v>-3.03</v>
+        <v>-0.61</v>
       </c>
       <c r="AH23" t="n">
         <v>215</v>
@@ -2682,67 +2703,112 @@
       <c r="AI23" t="n">
         <v>235</v>
       </c>
+      <c r="AK23" t="n">
+        <v>127.06</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>-3.82</v>
+      </c>
       <c r="AM23" t="n">
         <v>110</v>
       </c>
       <c r="AN23" t="n">
         <v>142</v>
       </c>
+      <c r="AP23" t="n">
+        <v>82.81</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>12.9</v>
+      </c>
       <c r="BL23" s="1" t="n">
-        <v>46255</v>
+        <v>46257</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46256</v>
+        <v>46258</v>
       </c>
       <c r="B24" t="n">
-        <v>143.9</v>
+        <v>174.4</v>
+      </c>
+      <c r="C24" t="n">
+        <v>75.40000000000001</v>
       </c>
       <c r="D24" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="E24" t="n">
         <v>30.8</v>
       </c>
       <c r="F24" t="n">
-        <v>2.5</v>
+        <v>6.6</v>
+      </c>
+      <c r="H24" t="n">
+        <v>24</v>
+      </c>
+      <c r="I24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J24" t="n">
+        <v>39.5</v>
       </c>
       <c r="K24" t="n">
-        <v>99.2</v>
+        <v>74</v>
+      </c>
+      <c r="M24" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="N24" t="n">
+        <v>35.8</v>
       </c>
       <c r="O24" t="n">
-        <v>35.2</v>
+        <v>42.6</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="R24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="S24" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="T24" t="n">
+        <v>23.1</v>
       </c>
       <c r="V24" t="n">
-        <v>10.7</v>
+        <v>12.8</v>
       </c>
       <c r="W24" t="n">
-        <v>17.6</v>
+        <v>22.1</v>
       </c>
       <c r="X24" t="n">
-        <v>14.2</v>
+        <v>17.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Z24" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA24" t="n">
-        <v>9</v>
+        <v>10.1</v>
       </c>
       <c r="AB24" t="n">
-        <v>-0.8</v>
+        <v>0.3</v>
       </c>
       <c r="AC24" t="n">
-        <v>8.800000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AD24" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="AF24" t="n">
-        <v>229.16</v>
+        <v>219.99</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.03</v>
+        <v>-8.56</v>
       </c>
       <c r="AH24" t="n">
         <v>215</v>
@@ -2750,100 +2816,112 @@
       <c r="AI24" t="n">
         <v>235</v>
       </c>
+      <c r="AK24" t="n">
+        <v>125.61</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>-1.45</v>
+      </c>
       <c r="AM24" t="n">
         <v>110</v>
       </c>
       <c r="AN24" t="n">
         <v>142</v>
       </c>
+      <c r="AP24" t="n">
+        <v>77.83</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>12.96</v>
+      </c>
       <c r="BL24" s="1" t="n">
-        <v>46256</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46257</v>
+        <v>46259</v>
       </c>
       <c r="B25" t="n">
         <v>163.2</v>
       </c>
       <c r="C25" t="n">
-        <v>73.7</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="D25" t="n">
-        <v>30</v>
+        <v>32.9</v>
       </c>
       <c r="E25" t="n">
-        <v>28.2</v>
+        <v>26</v>
       </c>
       <c r="F25" t="n">
-        <v>4.8</v>
+        <v>6.9</v>
       </c>
       <c r="H25" t="n">
-        <v>24.1</v>
+        <v>23.8</v>
       </c>
       <c r="I25" t="n">
-        <v>11.4</v>
+        <v>7.4</v>
       </c>
       <c r="J25" t="n">
         <v>40.1</v>
       </c>
       <c r="K25" t="n">
-        <v>75.59999999999999</v>
+        <v>71.3</v>
       </c>
       <c r="M25" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="N25" t="n">
-        <v>32.9</v>
+        <v>34.3</v>
       </c>
       <c r="O25" t="n">
-        <v>39.7</v>
+        <v>41.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>23.5</v>
+        <v>23.1</v>
       </c>
       <c r="R25" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="S25" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="T25" t="n">
-        <v>23.5</v>
+        <v>23.1</v>
       </c>
       <c r="V25" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="W25" t="n">
-        <v>20.1</v>
+        <v>23.3</v>
       </c>
       <c r="X25" t="n">
-        <v>14.8</v>
+        <v>16.4</v>
       </c>
       <c r="Y25" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Z25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA25" t="n">
-        <v>9.300000000000001</v>
+        <v>12.2</v>
       </c>
       <c r="AB25" t="n">
-        <v>-0.9</v>
+        <v>2.6</v>
       </c>
       <c r="AC25" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="AF25" t="n">
-        <v>228.55</v>
+        <v>219.22</v>
       </c>
       <c r="AG25" t="n">
-        <v>-0.61</v>
+        <v>-0.77</v>
       </c>
       <c r="AH25" t="n">
         <v>215</v>
@@ -2852,10 +2930,10 @@
         <v>235</v>
       </c>
       <c r="AK25" t="n">
-        <v>127.06</v>
+        <v>124.36</v>
       </c>
       <c r="AL25" t="n">
-        <v>-3.82</v>
+        <v>-1.25</v>
       </c>
       <c r="AM25" t="n">
         <v>110</v>
@@ -2864,99 +2942,99 @@
         <v>142</v>
       </c>
       <c r="AP25" t="n">
-        <v>82.81</v>
+        <v>76.81</v>
       </c>
       <c r="AS25" t="n">
-        <v>12.9</v>
+        <v>12.38</v>
       </c>
       <c r="BL25" s="1" t="n">
-        <v>46257</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="B26" t="n">
-        <v>174.4</v>
+        <v>152.7</v>
       </c>
       <c r="C26" t="n">
-        <v>75.40000000000001</v>
+        <v>62.6</v>
       </c>
       <c r="D26" t="n">
-        <v>32.1</v>
+        <v>32.7</v>
       </c>
       <c r="E26" t="n">
-        <v>30.8</v>
+        <v>24.6</v>
       </c>
       <c r="F26" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H26" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="I26" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J26" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="K26" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="M26" t="n">
         <v>6.6</v>
       </c>
-      <c r="H26" t="n">
-        <v>24</v>
-      </c>
-      <c r="I26" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="J26" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="K26" t="n">
-        <v>74</v>
-      </c>
-      <c r="M26" t="n">
-        <v>6.8</v>
-      </c>
       <c r="N26" t="n">
-        <v>35.8</v>
+        <v>33.5</v>
       </c>
       <c r="O26" t="n">
-        <v>42.6</v>
+        <v>40.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="R26" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="S26" t="n">
-        <v>8.5</v>
+        <v>4</v>
       </c>
       <c r="T26" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="V26" t="n">
-        <v>12.8</v>
+        <v>11.5</v>
       </c>
       <c r="W26" t="n">
-        <v>22.1</v>
+        <v>27.3</v>
       </c>
       <c r="X26" t="n">
-        <v>17.5</v>
+        <v>19.4</v>
       </c>
       <c r="Y26" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z26" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AA26" t="n">
-        <v>10.1</v>
+        <v>14</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="AC26" t="n">
-        <v>9.300000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="AF26" t="n">
-        <v>219.99</v>
+        <v>220.73</v>
       </c>
       <c r="AG26" t="n">
-        <v>-8.56</v>
+        <v>1.5</v>
       </c>
       <c r="AH26" t="n">
         <v>215</v>
@@ -2965,10 +3043,10 @@
         <v>235</v>
       </c>
       <c r="AK26" t="n">
-        <v>125.61</v>
+        <v>120.93</v>
       </c>
       <c r="AL26" t="n">
-        <v>-1.45</v>
+        <v>-3.43</v>
       </c>
       <c r="AM26" t="n">
         <v>110</v>
@@ -2977,99 +3055,99 @@
         <v>142</v>
       </c>
       <c r="AP26" t="n">
-        <v>77.83</v>
+        <v>77.87</v>
       </c>
       <c r="AS26" t="n">
-        <v>12.96</v>
+        <v>13.26</v>
       </c>
       <c r="BL26" s="1" t="n">
-        <v>46258</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="B27" t="n">
-        <v>163.2</v>
+        <v>150.7</v>
       </c>
       <c r="C27" t="n">
-        <v>70.90000000000001</v>
+        <v>64.8</v>
       </c>
       <c r="D27" t="n">
-        <v>32.9</v>
+        <v>33.7</v>
       </c>
       <c r="E27" t="n">
-        <v>26</v>
+        <v>27.1</v>
       </c>
       <c r="F27" t="n">
-        <v>6.9</v>
+        <v>3.8</v>
       </c>
       <c r="H27" t="n">
-        <v>23.8</v>
+        <v>23.4</v>
       </c>
       <c r="I27" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J27" t="n">
-        <v>40.1</v>
+        <v>39.9</v>
       </c>
       <c r="K27" t="n">
-        <v>71.3</v>
+        <v>70.5</v>
       </c>
       <c r="M27" t="n">
-        <v>7.2</v>
+        <v>5.6</v>
       </c>
       <c r="N27" t="n">
-        <v>34.3</v>
+        <v>33</v>
       </c>
       <c r="O27" t="n">
-        <v>41.5</v>
+        <v>38.6</v>
       </c>
       <c r="Q27" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="R27" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="S27" t="n">
-        <v>6.2</v>
+        <v>3</v>
       </c>
       <c r="T27" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="V27" t="n">
-        <v>9.6</v>
+        <v>14.5</v>
       </c>
       <c r="W27" t="n">
-        <v>23.3</v>
+        <v>28.9</v>
       </c>
       <c r="X27" t="n">
-        <v>16.4</v>
+        <v>21.7</v>
       </c>
       <c r="Y27" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z27" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AA27" t="n">
-        <v>12.2</v>
+        <v>13.1</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>8.5</v>
+        <v>10.8</v>
       </c>
       <c r="AD27" t="n">
-        <v>5.5</v>
+        <v>6.7</v>
       </c>
       <c r="AF27" t="n">
-        <v>219.22</v>
+        <v>220.58</v>
       </c>
       <c r="AG27" t="n">
-        <v>-0.77</v>
+        <v>-0.15</v>
       </c>
       <c r="AH27" t="n">
         <v>215</v>
@@ -3078,10 +3156,10 @@
         <v>235</v>
       </c>
       <c r="AK27" t="n">
-        <v>124.36</v>
+        <v>120.28</v>
       </c>
       <c r="AL27" t="n">
-        <v>-1.25</v>
+        <v>-0.65</v>
       </c>
       <c r="AM27" t="n">
         <v>110</v>
@@ -3090,99 +3168,54 @@
         <v>142</v>
       </c>
       <c r="AP27" t="n">
-        <v>76.81</v>
+        <v>77.22</v>
       </c>
       <c r="AS27" t="n">
-        <v>12.38</v>
+        <v>13.79</v>
       </c>
       <c r="BL27" s="1" t="n">
-        <v>46259</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="B28" t="n">
-        <v>152.7</v>
-      </c>
-      <c r="C28" t="n">
-        <v>62.6</v>
+        <v>138.2</v>
       </c>
       <c r="D28" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="E28" t="n">
-        <v>24.6</v>
+        <v>33.6</v>
       </c>
       <c r="F28" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="H28" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="I28" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="J28" t="n">
-        <v>38.9</v>
-      </c>
-      <c r="K28" t="n">
-        <v>69.90000000000001</v>
-      </c>
-      <c r="M28" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="N28" t="n">
-        <v>33.5</v>
-      </c>
-      <c r="O28" t="n">
-        <v>40.1</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="R28" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="S28" t="n">
-        <v>4</v>
-      </c>
-      <c r="T28" t="n">
-        <v>23.2</v>
+        <v>6.1</v>
       </c>
       <c r="V28" t="n">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
       <c r="W28" t="n">
-        <v>27.3</v>
+        <v>23.4</v>
       </c>
       <c r="X28" t="n">
         <v>19.4</v>
       </c>
       <c r="Y28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AA28" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="AC28" t="n">
-        <v>9.6</v>
+        <v>8.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>220.73</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="AH28" t="n">
         <v>215</v>
@@ -3190,112 +3223,61 @@
       <c r="AI28" t="n">
         <v>235</v>
       </c>
-      <c r="AK28" t="n">
-        <v>120.93</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>-3.43</v>
-      </c>
       <c r="AM28" t="n">
         <v>110</v>
       </c>
       <c r="AN28" t="n">
         <v>142</v>
       </c>
-      <c r="AP28" t="n">
-        <v>77.87</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>13.26</v>
-      </c>
       <c r="BL28" s="1" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46261</v>
+        <v>46263</v>
       </c>
       <c r="B29" t="n">
-        <v>150.7</v>
-      </c>
-      <c r="C29" t="n">
-        <v>64.8</v>
+        <v>126.5</v>
       </c>
       <c r="D29" t="n">
-        <v>33.7</v>
-      </c>
-      <c r="E29" t="n">
-        <v>27.1</v>
+        <v>33.2</v>
       </c>
       <c r="F29" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H29" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="I29" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="J29" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="K29" t="n">
-        <v>70.5</v>
-      </c>
-      <c r="M29" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="N29" t="n">
-        <v>33</v>
-      </c>
-      <c r="O29" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="R29" t="n">
         <v>3.4</v>
       </c>
-      <c r="S29" t="n">
-        <v>3</v>
-      </c>
-      <c r="T29" t="n">
-        <v>23.2</v>
-      </c>
       <c r="V29" t="n">
-        <v>14.5</v>
+        <v>12.6</v>
       </c>
       <c r="W29" t="n">
-        <v>28.9</v>
+        <v>22.3</v>
       </c>
       <c r="X29" t="n">
-        <v>21.7</v>
+        <v>17.4</v>
       </c>
       <c r="Y29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z29" t="n">
         <v>18</v>
       </c>
       <c r="AA29" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>10.8</v>
+        <v>6.7</v>
       </c>
       <c r="AD29" t="n">
-        <v>6.7</v>
+        <v>3.4</v>
       </c>
       <c r="AF29" t="n">
-        <v>220.58</v>
+        <v>229.48</v>
       </c>
       <c r="AG29" t="n">
-        <v>-0.15</v>
+        <v>6.05</v>
       </c>
       <c r="AH29" t="n">
         <v>215</v>
@@ -3303,67 +3285,100 @@
       <c r="AI29" t="n">
         <v>235</v>
       </c>
-      <c r="AK29" t="n">
-        <v>120.28</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>-0.65</v>
-      </c>
       <c r="AM29" t="n">
         <v>110</v>
       </c>
       <c r="AN29" t="n">
         <v>142</v>
       </c>
-      <c r="AP29" t="n">
-        <v>77.22</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>13.79</v>
-      </c>
       <c r="BL29" s="1" t="n">
-        <v>46261</v>
+        <v>46263</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46262</v>
+        <v>46264</v>
       </c>
       <c r="B30" t="n">
-        <v>138.2</v>
+        <v>129.4</v>
+      </c>
+      <c r="C30" t="n">
+        <v>50.6</v>
       </c>
       <c r="D30" t="n">
-        <v>33.6</v>
+        <v>31.5</v>
+      </c>
+      <c r="E30" t="n">
+        <v>19.4</v>
       </c>
       <c r="F30" t="n">
-        <v>6.1</v>
+        <v>2.7</v>
+      </c>
+      <c r="H30" t="n">
+        <v>24</v>
+      </c>
+      <c r="I30" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J30" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="K30" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="M30" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N30" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="O30" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>21.4</v>
       </c>
       <c r="V30" t="n">
-        <v>15.5</v>
+        <v>14.3</v>
       </c>
       <c r="W30" t="n">
-        <v>23.4</v>
+        <v>23.9</v>
       </c>
       <c r="X30" t="n">
-        <v>19.4</v>
+        <v>19.1</v>
       </c>
       <c r="Y30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z30" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AA30" t="n">
-        <v>13</v>
+        <v>16.1</v>
       </c>
       <c r="AB30" t="n">
         <v>0.4</v>
       </c>
       <c r="AC30" t="n">
-        <v>8.5</v>
+        <v>7.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>4.5</v>
+        <v>4</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>229.5</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0.02</v>
       </c>
       <c r="AH30" t="n">
         <v>215</v>
@@ -3371,61 +3386,112 @@
       <c r="AI30" t="n">
         <v>235</v>
       </c>
+      <c r="AK30" t="n">
+        <v>128.37</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>8.09</v>
+      </c>
       <c r="AM30" t="n">
         <v>110</v>
       </c>
       <c r="AN30" t="n">
         <v>142</v>
       </c>
+      <c r="AP30" t="n">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>15.97</v>
+      </c>
       <c r="BL30" s="1" t="n">
-        <v>46262</v>
+        <v>46264</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="B31" t="n">
-        <v>126.5</v>
+        <v>142.9</v>
+      </c>
+      <c r="C31" t="n">
+        <v>52.7</v>
       </c>
       <c r="D31" t="n">
-        <v>33.2</v>
+        <v>34.7</v>
+      </c>
+      <c r="E31" t="n">
+        <v>24.8</v>
       </c>
       <c r="F31" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
+      </c>
+      <c r="H31" t="n">
+        <v>22</v>
+      </c>
+      <c r="I31" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="J31" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="K31" t="n">
+        <v>70</v>
+      </c>
+      <c r="M31" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N31" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="O31" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>19.7</v>
       </c>
       <c r="V31" t="n">
-        <v>12.6</v>
+        <v>12</v>
       </c>
       <c r="W31" t="n">
-        <v>22.3</v>
+        <v>25.8</v>
       </c>
       <c r="X31" t="n">
-        <v>17.4</v>
+        <v>18.9</v>
       </c>
       <c r="Y31" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Z31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA31" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="AC31" t="n">
-        <v>6.7</v>
+        <v>5.8</v>
       </c>
       <c r="AD31" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="AF31" t="n">
-        <v>229.48</v>
+        <v>238.69</v>
       </c>
       <c r="AG31" t="n">
-        <v>6.05</v>
+        <v>-2.8</v>
       </c>
       <c r="AH31" t="n">
         <v>215</v>
@@ -3433,100 +3499,112 @@
       <c r="AI31" t="n">
         <v>235</v>
       </c>
+      <c r="AK31" t="n">
+        <v>134.59</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>6.22</v>
+      </c>
       <c r="AM31" t="n">
         <v>110</v>
       </c>
       <c r="AN31" t="n">
         <v>142</v>
       </c>
+      <c r="AP31" t="n">
+        <v>89.05</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>17.06</v>
+      </c>
       <c r="BL31" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46264</v>
+        <v>46266</v>
       </c>
       <c r="B32" t="n">
-        <v>129.4</v>
+        <v>148.1</v>
       </c>
       <c r="C32" t="n">
-        <v>50.6</v>
+        <v>51.9</v>
       </c>
       <c r="D32" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="E32" t="n">
         <v>31.5</v>
       </c>
-      <c r="E32" t="n">
-        <v>19.4</v>
-      </c>
       <c r="F32" t="n">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="H32" t="n">
-        <v>24</v>
+        <v>21.8</v>
       </c>
       <c r="I32" t="n">
-        <v>10.4</v>
+        <v>9.6</v>
       </c>
       <c r="J32" t="n">
-        <v>38.9</v>
+        <v>39.6</v>
       </c>
       <c r="K32" t="n">
-        <v>73.3</v>
+        <v>71</v>
       </c>
       <c r="M32" t="n">
-        <v>4.7</v>
+        <v>2.9</v>
       </c>
       <c r="N32" t="n">
-        <v>33.3</v>
+        <v>30.8</v>
       </c>
       <c r="O32" t="n">
-        <v>38</v>
+        <v>33.7</v>
       </c>
       <c r="Q32" t="n">
-        <v>21.4</v>
+        <v>20.7</v>
       </c>
       <c r="R32" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>21.4</v>
+        <v>20.7</v>
       </c>
       <c r="V32" t="n">
-        <v>14.3</v>
+        <v>13.1</v>
       </c>
       <c r="W32" t="n">
-        <v>23.9</v>
+        <v>25.5</v>
       </c>
       <c r="X32" t="n">
-        <v>19.1</v>
+        <v>19.3</v>
       </c>
       <c r="Y32" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z32" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AA32" t="n">
-        <v>16.1</v>
+        <v>15.5</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.4</v>
+        <v>-1</v>
       </c>
       <c r="AC32" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="AD32" t="n">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="AF32" t="n">
-        <v>229.5</v>
+        <v>233.48</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.02</v>
+        <v>-4.86</v>
       </c>
       <c r="AH32" t="n">
         <v>215</v>
@@ -3535,10 +3613,10 @@
         <v>235</v>
       </c>
       <c r="AK32" t="n">
-        <v>128.37</v>
+        <v>136.6</v>
       </c>
       <c r="AL32" t="n">
-        <v>8.09</v>
+        <v>2.01</v>
       </c>
       <c r="AM32" t="n">
         <v>110</v>
@@ -3547,99 +3625,99 @@
         <v>142</v>
       </c>
       <c r="AP32" t="n">
-        <v>91.59999999999999</v>
+        <v>86.25</v>
       </c>
       <c r="AS32" t="n">
-        <v>15.97</v>
+        <v>17.13</v>
       </c>
       <c r="BL32" s="1" t="n">
-        <v>46264</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="B33" t="n">
-        <v>142.9</v>
+        <v>143.4</v>
       </c>
       <c r="C33" t="n">
-        <v>52.7</v>
+        <v>50.9</v>
       </c>
       <c r="D33" t="n">
-        <v>34.7</v>
+        <v>35.7</v>
       </c>
       <c r="E33" t="n">
-        <v>24.8</v>
+        <v>26.2</v>
       </c>
       <c r="F33" t="n">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="H33" t="n">
-        <v>22</v>
+        <v>22.9</v>
       </c>
       <c r="I33" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J33" t="n">
-        <v>38.2</v>
+        <v>39.9</v>
       </c>
       <c r="K33" t="n">
-        <v>70</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="M33" t="n">
-        <v>3.9</v>
+        <v>2</v>
       </c>
       <c r="N33" t="n">
-        <v>31.9</v>
+        <v>31.2</v>
       </c>
       <c r="O33" t="n">
-        <v>35.8</v>
+        <v>33.1</v>
       </c>
       <c r="Q33" t="n">
-        <v>19.7</v>
+        <v>21.6</v>
       </c>
       <c r="R33" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>19.7</v>
+        <v>21.6</v>
       </c>
       <c r="V33" t="n">
-        <v>12</v>
+        <v>12.9</v>
       </c>
       <c r="W33" t="n">
-        <v>25.8</v>
+        <v>28.3</v>
       </c>
       <c r="X33" t="n">
-        <v>18.9</v>
+        <v>20.6</v>
       </c>
       <c r="Y33" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z33" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AA33" t="n">
-        <v>15</v>
+        <v>17.9</v>
       </c>
       <c r="AB33" t="n">
-        <v>-0.1</v>
+        <v>-0.8</v>
       </c>
       <c r="AC33" t="n">
-        <v>5.8</v>
+        <v>8.1</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="AF33" t="n">
-        <v>238.69</v>
+        <v>235.13</v>
       </c>
       <c r="AG33" t="n">
-        <v>-2.8</v>
+        <v>1.66</v>
       </c>
       <c r="AH33" t="n">
         <v>215</v>
@@ -3648,10 +3726,10 @@
         <v>235</v>
       </c>
       <c r="AK33" t="n">
-        <v>134.59</v>
+        <v>135.66</v>
       </c>
       <c r="AL33" t="n">
-        <v>6.22</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AM33" t="n">
         <v>110</v>
@@ -3660,99 +3738,99 @@
         <v>142</v>
       </c>
       <c r="AP33" t="n">
-        <v>89.05</v>
+        <v>88.27</v>
       </c>
       <c r="AS33" t="n">
-        <v>17.06</v>
+        <v>17.6</v>
       </c>
       <c r="BL33" s="1" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B34" t="n">
-        <v>148.1</v>
+        <v>144.9</v>
       </c>
       <c r="C34" t="n">
-        <v>51.9</v>
+        <v>53</v>
       </c>
       <c r="D34" t="n">
-        <v>35.4</v>
+        <v>35.6</v>
       </c>
       <c r="E34" t="n">
-        <v>31.5</v>
+        <v>26</v>
       </c>
       <c r="F34" t="n">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="H34" t="n">
-        <v>21.8</v>
+        <v>24</v>
       </c>
       <c r="I34" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="J34" t="n">
-        <v>39.6</v>
+        <v>40.3</v>
       </c>
       <c r="K34" t="n">
-        <v>71</v>
+        <v>73.7</v>
       </c>
       <c r="M34" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="N34" t="n">
-        <v>30.8</v>
+        <v>31.6</v>
       </c>
       <c r="O34" t="n">
-        <v>33.7</v>
+        <v>33.6</v>
       </c>
       <c r="Q34" t="n">
-        <v>20.7</v>
+        <v>21</v>
       </c>
       <c r="R34" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>20.7</v>
+        <v>21</v>
       </c>
       <c r="V34" t="n">
-        <v>13.1</v>
+        <v>14.4</v>
       </c>
       <c r="W34" t="n">
-        <v>25.5</v>
+        <v>27.7</v>
       </c>
       <c r="X34" t="n">
-        <v>19.3</v>
+        <v>21.1</v>
       </c>
       <c r="Y34" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z34" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA34" t="n">
-        <v>15.5</v>
+        <v>16.3</v>
       </c>
       <c r="AB34" t="n">
-        <v>-1</v>
+        <v>-1.1</v>
       </c>
       <c r="AC34" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AF34" t="n">
-        <v>233.48</v>
+        <v>234.87</v>
       </c>
       <c r="AG34" t="n">
-        <v>-4.86</v>
+        <v>-0.26</v>
       </c>
       <c r="AH34" t="n">
         <v>215</v>
@@ -3761,10 +3839,10 @@
         <v>235</v>
       </c>
       <c r="AK34" t="n">
-        <v>136.6</v>
+        <v>136.33</v>
       </c>
       <c r="AL34" t="n">
-        <v>2.01</v>
+        <v>0.67</v>
       </c>
       <c r="AM34" t="n">
         <v>110</v>
@@ -3773,99 +3851,60 @@
         <v>142</v>
       </c>
       <c r="AP34" t="n">
-        <v>86.25</v>
+        <v>87.09</v>
       </c>
       <c r="AS34" t="n">
-        <v>17.13</v>
+        <v>17.31</v>
       </c>
       <c r="BL34" s="1" t="n">
-        <v>46266</v>
+        <v>46268</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="B35" t="n">
-        <v>143.4</v>
-      </c>
-      <c r="C35" t="n">
-        <v>50.9</v>
+        <v>132.2</v>
       </c>
       <c r="D35" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="E35" t="n">
-        <v>26.2</v>
+        <v>35.6</v>
       </c>
       <c r="F35" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H35" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="I35" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="J35" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="K35" t="n">
-        <v>72.59999999999999</v>
-      </c>
-      <c r="M35" t="n">
-        <v>2</v>
-      </c>
-      <c r="N35" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="O35" t="n">
-        <v>33.1</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" t="n">
-        <v>21.6</v>
+        <v>4</v>
       </c>
       <c r="V35" t="n">
-        <v>12.9</v>
+        <v>11.6</v>
       </c>
       <c r="W35" t="n">
-        <v>28.3</v>
+        <v>23.2</v>
       </c>
       <c r="X35" t="n">
-        <v>20.6</v>
+        <v>17.4</v>
       </c>
       <c r="Y35" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Z35" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AA35" t="n">
-        <v>17.9</v>
+        <v>13</v>
       </c>
       <c r="AB35" t="n">
-        <v>-0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AC35" t="n">
-        <v>8.1</v>
+        <v>7.5</v>
       </c>
       <c r="AD35" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="AF35" t="n">
-        <v>235.13</v>
+        <v>234.78</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.66</v>
+        <v>-0.09</v>
       </c>
       <c r="AH35" t="n">
         <v>215</v>
@@ -3873,112 +3912,61 @@
       <c r="AI35" t="n">
         <v>235</v>
       </c>
-      <c r="AK35" t="n">
-        <v>135.66</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>-0.9399999999999999</v>
-      </c>
       <c r="AM35" t="n">
         <v>110</v>
       </c>
       <c r="AN35" t="n">
         <v>142</v>
       </c>
-      <c r="AP35" t="n">
-        <v>88.27</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>17.6</v>
-      </c>
       <c r="BL35" s="1" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>46268</v>
+        <v>46270</v>
       </c>
       <c r="B36" t="n">
-        <v>144.9</v>
-      </c>
-      <c r="C36" t="n">
-        <v>53</v>
+        <v>137.1</v>
       </c>
       <c r="D36" t="n">
-        <v>35.6</v>
-      </c>
-      <c r="E36" t="n">
-        <v>26</v>
+        <v>35.1</v>
       </c>
       <c r="F36" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="H36" t="n">
-        <v>24</v>
-      </c>
-      <c r="I36" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="J36" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="K36" t="n">
-        <v>73.7</v>
-      </c>
-      <c r="M36" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="N36" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="O36" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>21</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" t="n">
-        <v>21</v>
+        <v>3.3</v>
       </c>
       <c r="V36" t="n">
-        <v>14.4</v>
+        <v>11</v>
       </c>
       <c r="W36" t="n">
-        <v>27.7</v>
+        <v>22</v>
       </c>
       <c r="X36" t="n">
-        <v>21.1</v>
+        <v>16.5</v>
       </c>
       <c r="Y36" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z36" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AA36" t="n">
-        <v>16.3</v>
+        <v>10.5</v>
       </c>
       <c r="AB36" t="n">
-        <v>-1.1</v>
+        <v>-5.3</v>
       </c>
       <c r="AC36" t="n">
-        <v>6.6</v>
+        <v>6.1</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.8</v>
+        <v>0.4</v>
       </c>
       <c r="AF36" t="n">
-        <v>234.87</v>
+        <v>229.75</v>
       </c>
       <c r="AG36" t="n">
-        <v>-0.26</v>
+        <v>-5.03</v>
       </c>
       <c r="AH36" t="n">
         <v>215</v>
@@ -3986,73 +3974,100 @@
       <c r="AI36" t="n">
         <v>235</v>
       </c>
-      <c r="AK36" t="n">
-        <v>136.33</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>0.67</v>
-      </c>
       <c r="AM36" t="n">
         <v>110</v>
       </c>
       <c r="AN36" t="n">
         <v>142</v>
       </c>
-      <c r="AP36" t="n">
-        <v>87.09</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>17.31</v>
-      </c>
       <c r="BL36" s="1" t="n">
-        <v>46268</v>
+        <v>46270</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>46269</v>
+        <v>46271</v>
       </c>
       <c r="B37" t="n">
-        <v>132.2</v>
+        <v>166.2</v>
+      </c>
+      <c r="C37" t="n">
+        <v>72.40000000000001</v>
       </c>
       <c r="D37" t="n">
-        <v>35.6</v>
+        <v>32.7</v>
+      </c>
+      <c r="E37" t="n">
+        <v>28.1</v>
       </c>
       <c r="F37" t="n">
-        <v>4</v>
+        <v>3.3</v>
+      </c>
+      <c r="H37" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="I37" t="n">
+        <v>9</v>
+      </c>
+      <c r="J37" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="K37" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="M37" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="N37" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="O37" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="R37" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>23.7</v>
       </c>
       <c r="V37" t="n">
-        <v>11.6</v>
+        <v>7.9</v>
       </c>
       <c r="W37" t="n">
-        <v>23.2</v>
+        <v>15.6</v>
       </c>
       <c r="X37" t="n">
-        <v>17.4</v>
+        <v>11.8</v>
       </c>
       <c r="Y37" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z37" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="AA37" t="n">
-        <v>13</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.9</v>
+        <v>-3.5</v>
       </c>
       <c r="AC37" t="n">
-        <v>7.5</v>
+        <v>8.4</v>
       </c>
       <c r="AD37" t="n">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="AF37" t="n">
-        <v>234.78</v>
+        <v>222.86</v>
       </c>
       <c r="AG37" t="n">
-        <v>-0.09</v>
+        <v>-6.9</v>
       </c>
       <c r="AH37" t="n">
         <v>215</v>
@@ -4060,61 +4075,112 @@
       <c r="AI37" t="n">
         <v>235</v>
       </c>
+      <c r="AK37" t="n">
+        <v>135.42</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>-0.91</v>
+      </c>
       <c r="AM37" t="n">
         <v>110</v>
       </c>
       <c r="AN37" t="n">
         <v>142</v>
       </c>
+      <c r="AP37" t="n">
+        <v>81.98</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>15.01</v>
+      </c>
       <c r="BL37" s="1" t="n">
-        <v>46269</v>
+        <v>46271</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>46270</v>
+        <v>46272</v>
       </c>
       <c r="B38" t="n">
-        <v>137.1</v>
+        <v>166.3</v>
+      </c>
+      <c r="C38" t="n">
+        <v>74.90000000000001</v>
       </c>
       <c r="D38" t="n">
-        <v>35.1</v>
+        <v>32.8</v>
+      </c>
+      <c r="E38" t="n">
+        <v>28.8</v>
       </c>
       <c r="F38" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
+      </c>
+      <c r="H38" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="I38" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J38" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="K38" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="M38" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="N38" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="O38" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="R38" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>23.9</v>
       </c>
       <c r="V38" t="n">
-        <v>11</v>
+        <v>6.7</v>
       </c>
       <c r="W38" t="n">
-        <v>22</v>
+        <v>18.1</v>
       </c>
       <c r="X38" t="n">
-        <v>16.5</v>
+        <v>12.4</v>
       </c>
       <c r="Y38" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z38" t="n">
         <v>14</v>
       </c>
       <c r="AA38" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AB38" t="n">
-        <v>-5.3</v>
+        <v>-2.9</v>
       </c>
       <c r="AC38" t="n">
-        <v>6.1</v>
+        <v>11.5</v>
       </c>
       <c r="AD38" t="n">
-        <v>0.4</v>
+        <v>4.3</v>
       </c>
       <c r="AF38" t="n">
-        <v>229.75</v>
+        <v>218.37</v>
       </c>
       <c r="AG38" t="n">
-        <v>-5.03</v>
+        <v>-4.49</v>
       </c>
       <c r="AH38" t="n">
         <v>215</v>
@@ -4122,100 +4188,112 @@
       <c r="AI38" t="n">
         <v>235</v>
       </c>
+      <c r="AK38" t="n">
+        <v>131.24</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>-4.18</v>
+      </c>
       <c r="AM38" t="n">
         <v>110</v>
       </c>
       <c r="AN38" t="n">
         <v>142</v>
       </c>
+      <c r="AP38" t="n">
+        <v>79.98999999999999</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>12.97</v>
+      </c>
       <c r="BL38" s="1" t="n">
-        <v>46270</v>
+        <v>46272</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>46271</v>
+        <v>46273</v>
       </c>
       <c r="B39" t="n">
-        <v>166.2</v>
+        <v>154.1</v>
       </c>
       <c r="C39" t="n">
-        <v>72.40000000000001</v>
+        <v>65</v>
       </c>
       <c r="D39" t="n">
-        <v>32.7</v>
+        <v>32</v>
       </c>
       <c r="E39" t="n">
-        <v>28.1</v>
+        <v>25.2</v>
       </c>
       <c r="F39" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="H39" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="I39" t="n">
         <v>9</v>
       </c>
       <c r="J39" t="n">
-        <v>42.1</v>
+        <v>38.5</v>
       </c>
       <c r="K39" t="n">
-        <v>74.5</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="M39" t="n">
-        <v>5.6</v>
+        <v>8</v>
       </c>
       <c r="N39" t="n">
-        <v>33.7</v>
+        <v>32.3</v>
       </c>
       <c r="O39" t="n">
-        <v>39.3</v>
+        <v>40.3</v>
       </c>
       <c r="Q39" t="n">
-        <v>23.7</v>
+        <v>21.7</v>
       </c>
       <c r="R39" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T39" t="n">
-        <v>23.7</v>
+        <v>21.7</v>
       </c>
       <c r="V39" t="n">
-        <v>7.9</v>
+        <v>5.4</v>
       </c>
       <c r="W39" t="n">
-        <v>15.6</v>
+        <v>21</v>
       </c>
       <c r="X39" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="Y39" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Z39" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AA39" t="n">
-        <v>8.199999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="AB39" t="n">
-        <v>-3.5</v>
+        <v>0.4</v>
       </c>
       <c r="AC39" t="n">
-        <v>8.4</v>
+        <v>7.3</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="AF39" t="n">
-        <v>222.86</v>
+        <v>218.04</v>
       </c>
       <c r="AG39" t="n">
-        <v>-6.9</v>
+        <v>-0.33</v>
       </c>
       <c r="AH39" t="n">
         <v>215</v>
@@ -4224,10 +4302,10 @@
         <v>235</v>
       </c>
       <c r="AK39" t="n">
-        <v>135.42</v>
+        <v>129.21</v>
       </c>
       <c r="AL39" t="n">
-        <v>-0.91</v>
+        <v>-2.03</v>
       </c>
       <c r="AM39" t="n">
         <v>110</v>
@@ -4236,99 +4314,99 @@
         <v>142</v>
       </c>
       <c r="AP39" t="n">
-        <v>81.98</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="AS39" t="n">
-        <v>15.01</v>
+        <v>15.23</v>
       </c>
       <c r="BL39" s="1" t="n">
-        <v>46271</v>
+        <v>46273</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>46272</v>
+        <v>46274</v>
       </c>
       <c r="B40" t="n">
-        <v>166.3</v>
+        <v>148.8</v>
       </c>
       <c r="C40" t="n">
-        <v>74.90000000000001</v>
+        <v>57.6</v>
       </c>
       <c r="D40" t="n">
-        <v>32.8</v>
+        <v>32.7</v>
       </c>
       <c r="E40" t="n">
-        <v>28.8</v>
+        <v>26.3</v>
       </c>
       <c r="F40" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="H40" t="n">
-        <v>23.4</v>
+        <v>23.6</v>
       </c>
       <c r="I40" t="n">
-        <v>9.199999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="J40" t="n">
-        <v>41.2</v>
+        <v>41.6</v>
       </c>
       <c r="K40" t="n">
-        <v>73.8</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="M40" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="N40" t="n">
-        <v>35.4</v>
+        <v>35</v>
       </c>
       <c r="O40" t="n">
-        <v>42.6</v>
+        <v>42.4</v>
       </c>
       <c r="Q40" t="n">
-        <v>23.9</v>
+        <v>21.7</v>
       </c>
       <c r="R40" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>23.9</v>
+        <v>21.7</v>
       </c>
       <c r="V40" t="n">
-        <v>6.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W40" t="n">
-        <v>18.1</v>
+        <v>24.1</v>
       </c>
       <c r="X40" t="n">
-        <v>12.4</v>
+        <v>16.1</v>
       </c>
       <c r="Y40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z40" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AA40" t="n">
-        <v>11</v>
+        <v>15.6</v>
       </c>
       <c r="AB40" t="n">
-        <v>-2.9</v>
+        <v>2.9</v>
       </c>
       <c r="AC40" t="n">
-        <v>11.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AD40" t="n">
-        <v>4.3</v>
+        <v>6.3</v>
       </c>
       <c r="AF40" t="n">
-        <v>218.37</v>
+        <v>220.84</v>
       </c>
       <c r="AG40" t="n">
-        <v>-4.49</v>
+        <v>2.8</v>
       </c>
       <c r="AH40" t="n">
         <v>215</v>
@@ -4337,10 +4415,10 @@
         <v>235</v>
       </c>
       <c r="AK40" t="n">
-        <v>131.24</v>
+        <v>129.07</v>
       </c>
       <c r="AL40" t="n">
-        <v>-4.18</v>
+        <v>-0.14</v>
       </c>
       <c r="AM40" t="n">
         <v>110</v>
@@ -4349,99 +4427,99 @@
         <v>142</v>
       </c>
       <c r="AP40" t="n">
-        <v>79.98999999999999</v>
+        <v>85.52</v>
       </c>
       <c r="AS40" t="n">
-        <v>12.97</v>
+        <v>15.82</v>
       </c>
       <c r="BL40" s="1" t="n">
-        <v>46272</v>
+        <v>46274</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="B41" t="n">
-        <v>154.1</v>
+        <v>146.8</v>
       </c>
       <c r="C41" t="n">
-        <v>65</v>
+        <v>52.8</v>
       </c>
       <c r="D41" t="n">
-        <v>32</v>
+        <v>33.6</v>
       </c>
       <c r="E41" t="n">
-        <v>25.2</v>
+        <v>28.9</v>
       </c>
       <c r="F41" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="H41" t="n">
-        <v>23.5</v>
+        <v>23.7</v>
       </c>
       <c r="I41" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="J41" t="n">
-        <v>38.5</v>
+        <v>40.8</v>
       </c>
       <c r="K41" t="n">
-        <v>70.90000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="M41" t="n">
-        <v>8</v>
+        <v>5.6</v>
       </c>
       <c r="N41" t="n">
-        <v>32.3</v>
+        <v>33.1</v>
       </c>
       <c r="O41" t="n">
-        <v>40.3</v>
+        <v>38.7</v>
       </c>
       <c r="Q41" t="n">
-        <v>21.7</v>
+        <v>22</v>
       </c>
       <c r="R41" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>22</v>
+      </c>
+      <c r="V41" t="n">
+        <v>11</v>
+      </c>
+      <c r="W41" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="X41" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD41" t="n">
         <v>4.5</v>
       </c>
-      <c r="T41" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="V41" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="W41" t="n">
-        <v>21</v>
-      </c>
-      <c r="X41" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AF41" t="n">
-        <v>218.04</v>
+        <v>225.87</v>
       </c>
       <c r="AG41" t="n">
-        <v>-0.33</v>
+        <v>5.03</v>
       </c>
       <c r="AH41" t="n">
         <v>215</v>
@@ -4450,10 +4528,10 @@
         <v>235</v>
       </c>
       <c r="AK41" t="n">
-        <v>129.21</v>
+        <v>130.73</v>
       </c>
       <c r="AL41" t="n">
-        <v>-2.03</v>
+        <v>1.66</v>
       </c>
       <c r="AM41" t="n">
         <v>110</v>
@@ -4462,99 +4540,54 @@
         <v>142</v>
       </c>
       <c r="AP41" t="n">
-        <v>82.90000000000001</v>
+        <v>88.2</v>
       </c>
       <c r="AS41" t="n">
-        <v>15.23</v>
+        <v>15.76</v>
       </c>
       <c r="BL41" s="1" t="n">
-        <v>46273</v>
+        <v>46275</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="B42" t="n">
-        <v>148.8</v>
-      </c>
-      <c r="C42" t="n">
-        <v>57.6</v>
+        <v>133.9</v>
       </c>
       <c r="D42" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="E42" t="n">
-        <v>26.3</v>
+        <v>34.7</v>
       </c>
       <c r="F42" t="n">
         <v>3.3</v>
       </c>
-      <c r="H42" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="I42" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="J42" t="n">
-        <v>41.6</v>
-      </c>
-      <c r="K42" t="n">
-        <v>74.09999999999999</v>
-      </c>
-      <c r="M42" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="N42" t="n">
-        <v>35</v>
-      </c>
-      <c r="O42" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="Q42" t="n">
+      <c r="V42" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="W42" t="n">
         <v>21.7</v>
       </c>
-      <c r="R42" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="S42" t="n">
-        <v>0</v>
-      </c>
-      <c r="T42" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="V42" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="W42" t="n">
-        <v>24.1</v>
-      </c>
       <c r="X42" t="n">
-        <v>16.1</v>
+        <v>18</v>
       </c>
       <c r="Y42" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z42" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AA42" t="n">
-        <v>15.6</v>
+        <v>15</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.9</v>
+        <v>-3.5</v>
       </c>
       <c r="AC42" t="n">
-        <v>9.699999999999999</v>
+        <v>3.2</v>
       </c>
       <c r="AD42" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>220.84</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>2.8</v>
+        <v>-0.1</v>
       </c>
       <c r="AH42" t="n">
         <v>215</v>
@@ -4562,112 +4595,55 @@
       <c r="AI42" t="n">
         <v>235</v>
       </c>
-      <c r="AK42" t="n">
-        <v>129.07</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>-0.14</v>
-      </c>
       <c r="AM42" t="n">
         <v>110</v>
       </c>
       <c r="AN42" t="n">
         <v>142</v>
       </c>
-      <c r="AP42" t="n">
-        <v>85.52</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>15.82</v>
-      </c>
       <c r="BL42" s="1" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="B43" t="n">
-        <v>146.8</v>
-      </c>
-      <c r="C43" t="n">
-        <v>52.8</v>
+        <v>137.5</v>
       </c>
       <c r="D43" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="E43" t="n">
-        <v>28.9</v>
+        <v>32.8</v>
       </c>
       <c r="F43" t="n">
         <v>2.3</v>
       </c>
-      <c r="H43" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="I43" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="J43" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="K43" t="n">
-        <v>73.59999999999999</v>
-      </c>
-      <c r="M43" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="N43" t="n">
-        <v>33.1</v>
-      </c>
-      <c r="O43" t="n">
-        <v>38.7</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>22</v>
-      </c>
-      <c r="R43" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="S43" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" t="n">
-        <v>22</v>
-      </c>
       <c r="V43" t="n">
+        <v>9</v>
+      </c>
+      <c r="W43" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="X43" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z43" t="n">
         <v>11</v>
       </c>
-      <c r="W43" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="X43" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>20</v>
-      </c>
       <c r="AA43" t="n">
-        <v>16.1</v>
+        <v>10.5</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.9</v>
+        <v>-6.6</v>
       </c>
       <c r="AC43" t="n">
-        <v>7</v>
+        <v>8.1</v>
       </c>
       <c r="AD43" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>225.87</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>5.03</v>
+        <v>0.8</v>
       </c>
       <c r="AH43" t="n">
         <v>215</v>
@@ -4675,67 +4651,100 @@
       <c r="AI43" t="n">
         <v>235</v>
       </c>
-      <c r="AK43" t="n">
-        <v>130.73</v>
-      </c>
-      <c r="AL43" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AM43" t="n">
         <v>110</v>
       </c>
       <c r="AN43" t="n">
         <v>142</v>
       </c>
-      <c r="AP43" t="n">
-        <v>88.2</v>
-      </c>
-      <c r="AS43" t="n">
-        <v>15.76</v>
-      </c>
       <c r="BL43" s="1" t="n">
-        <v>46275</v>
+        <v>46277</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>46276</v>
+        <v>46278</v>
       </c>
       <c r="B44" t="n">
-        <v>133.9</v>
+        <v>157.1</v>
+      </c>
+      <c r="C44" t="n">
+        <v>73.09999999999999</v>
       </c>
       <c r="D44" t="n">
-        <v>34.7</v>
+        <v>31.7</v>
+      </c>
+      <c r="E44" t="n">
+        <v>26.1</v>
       </c>
       <c r="F44" t="n">
-        <v>3.3</v>
+        <v>2</v>
+      </c>
+      <c r="H44" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="I44" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="J44" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="K44" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="M44" t="n">
+        <v>6</v>
+      </c>
+      <c r="N44" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="O44" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="R44" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>23.8</v>
       </c>
       <c r="V44" t="n">
-        <v>14.3</v>
+        <v>6.8</v>
       </c>
       <c r="W44" t="n">
-        <v>21.7</v>
+        <v>11</v>
       </c>
       <c r="X44" t="n">
-        <v>18</v>
+        <v>8.9</v>
       </c>
       <c r="Y44" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z44" t="n">
         <v>12</v>
       </c>
-      <c r="Z44" t="n">
-        <v>18</v>
-      </c>
       <c r="AA44" t="n">
-        <v>15</v>
+        <v>7.9</v>
       </c>
       <c r="AB44" t="n">
-        <v>-3.5</v>
+        <v>-1.2</v>
       </c>
       <c r="AC44" t="n">
-        <v>3.2</v>
+        <v>12.6</v>
       </c>
       <c r="AD44" t="n">
-        <v>-0.1</v>
+        <v>5.7</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>224.2</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>-1.67</v>
       </c>
       <c r="AH44" t="n">
         <v>215</v>
@@ -4743,55 +4752,112 @@
       <c r="AI44" t="n">
         <v>235</v>
       </c>
+      <c r="AK44" t="n">
+        <v>128.6</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>-2.13</v>
+      </c>
       <c r="AM44" t="n">
         <v>110</v>
       </c>
       <c r="AN44" t="n">
         <v>142</v>
       </c>
+      <c r="AP44" t="n">
+        <v>81.18000000000001</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>14.06</v>
+      </c>
       <c r="BL44" s="1" t="n">
-        <v>46276</v>
+        <v>46278</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="B45" t="n">
-        <v>137.5</v>
+        <v>153.1</v>
+      </c>
+      <c r="C45" t="n">
+        <v>69.59999999999999</v>
       </c>
       <c r="D45" t="n">
-        <v>32.8</v>
+        <v>32.2</v>
+      </c>
+      <c r="E45" t="n">
+        <v>25.9</v>
       </c>
       <c r="F45" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
+      </c>
+      <c r="H45" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="I45" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="J45" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="K45" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="M45" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="N45" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="O45" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="R45" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="S45" t="n">
+        <v>4</v>
+      </c>
+      <c r="T45" t="n">
+        <v>23.8</v>
       </c>
       <c r="V45" t="n">
-        <v>9</v>
+        <v>6.6</v>
       </c>
       <c r="W45" t="n">
-        <v>15.7</v>
+        <v>15.2</v>
       </c>
       <c r="X45" t="n">
-        <v>12.3</v>
+        <v>10.9</v>
       </c>
       <c r="Y45" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>12</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC45" t="n">
         <v>10</v>
       </c>
-      <c r="Z45" t="n">
-        <v>11</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>-6.6</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>8.1</v>
-      </c>
       <c r="AD45" t="n">
-        <v>0.8</v>
+        <v>5.8</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>223.35</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>-0.85</v>
       </c>
       <c r="AH45" t="n">
         <v>215</v>
@@ -4799,100 +4865,112 @@
       <c r="AI45" t="n">
         <v>235</v>
       </c>
+      <c r="AK45" t="n">
+        <v>127.19</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>-1.41</v>
+      </c>
       <c r="AM45" t="n">
         <v>110</v>
       </c>
       <c r="AN45" t="n">
         <v>142</v>
       </c>
+      <c r="AP45" t="n">
+        <v>81.06</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>13.63</v>
+      </c>
       <c r="BL45" s="1" t="n">
-        <v>46277</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46278</v>
+        <v>46280</v>
       </c>
       <c r="B46" t="n">
-        <v>157.1</v>
+        <v>145.5</v>
       </c>
       <c r="C46" t="n">
-        <v>73.09999999999999</v>
+        <v>62.3</v>
       </c>
       <c r="D46" t="n">
-        <v>31.7</v>
+        <v>34</v>
       </c>
       <c r="E46" t="n">
-        <v>26.1</v>
+        <v>22.5</v>
       </c>
       <c r="F46" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="H46" t="n">
-        <v>23.6</v>
+        <v>24.8</v>
       </c>
       <c r="I46" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J46" t="n">
-        <v>40.5</v>
+        <v>40.8</v>
       </c>
       <c r="K46" t="n">
-        <v>73.5</v>
+        <v>75</v>
       </c>
       <c r="M46" t="n">
-        <v>6</v>
+        <v>6.9</v>
       </c>
       <c r="N46" t="n">
-        <v>33.4</v>
+        <v>30.4</v>
       </c>
       <c r="O46" t="n">
-        <v>39.5</v>
+        <v>37.3</v>
       </c>
       <c r="Q46" t="n">
-        <v>23.8</v>
+        <v>22.1</v>
       </c>
       <c r="R46" t="n">
-        <v>3.7</v>
+        <v>4.9</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>23.8</v>
+        <v>22.1</v>
       </c>
       <c r="V46" t="n">
-        <v>6.8</v>
+        <v>4</v>
       </c>
       <c r="W46" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="X46" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="Y46" t="n">
         <v>11</v>
       </c>
-      <c r="X46" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>3</v>
-      </c>
       <c r="Z46" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="AA46" t="n">
-        <v>7.9</v>
+        <v>12.9</v>
       </c>
       <c r="AB46" t="n">
-        <v>-1.2</v>
+        <v>0.7</v>
       </c>
       <c r="AC46" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="AD46" t="n">
-        <v>5.7</v>
+        <v>6.7</v>
       </c>
       <c r="AF46" t="n">
-        <v>224.2</v>
+        <v>223.06</v>
       </c>
       <c r="AG46" t="n">
-        <v>-1.67</v>
+        <v>-0.29</v>
       </c>
       <c r="AH46" t="n">
         <v>215</v>
@@ -4901,10 +4979,10 @@
         <v>235</v>
       </c>
       <c r="AK46" t="n">
-        <v>128.6</v>
+        <v>129.17</v>
       </c>
       <c r="AL46" t="n">
-        <v>-2.13</v>
+        <v>1.98</v>
       </c>
       <c r="AM46" t="n">
         <v>110</v>
@@ -4913,99 +4991,99 @@
         <v>142</v>
       </c>
       <c r="AP46" t="n">
-        <v>81.18000000000001</v>
+        <v>82.36</v>
       </c>
       <c r="AS46" t="n">
-        <v>14.06</v>
+        <v>13.91</v>
       </c>
       <c r="BL46" s="1" t="n">
-        <v>46278</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46279</v>
+        <v>46281</v>
       </c>
       <c r="B47" t="n">
-        <v>153.1</v>
+        <v>148</v>
       </c>
       <c r="C47" t="n">
-        <v>69.59999999999999</v>
+        <v>61.6</v>
       </c>
       <c r="D47" t="n">
-        <v>32.2</v>
+        <v>33.9</v>
       </c>
       <c r="E47" t="n">
-        <v>25.9</v>
+        <v>25</v>
       </c>
       <c r="F47" t="n">
         <v>2.2</v>
       </c>
       <c r="H47" t="n">
-        <v>24.4</v>
+        <v>25.1</v>
       </c>
       <c r="I47" t="n">
-        <v>9.300000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="J47" t="n">
-        <v>39.6</v>
+        <v>39.5</v>
       </c>
       <c r="K47" t="n">
-        <v>73.3</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="M47" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="N47" t="n">
-        <v>34.4</v>
+        <v>28.6</v>
       </c>
       <c r="O47" t="n">
-        <v>40.1</v>
+        <v>34.5</v>
       </c>
       <c r="Q47" t="n">
-        <v>23.8</v>
+        <v>23.3</v>
       </c>
       <c r="R47" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="S47" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>23.8</v>
+        <v>23.3</v>
       </c>
       <c r="V47" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="W47" t="n">
-        <v>15.2</v>
+        <v>26</v>
       </c>
       <c r="X47" t="n">
-        <v>10.9</v>
+        <v>16.9</v>
       </c>
       <c r="Y47" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z47" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA47" t="n">
-        <v>12</v>
+        <v>11.6</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.7</v>
+        <v>4.2</v>
       </c>
       <c r="AC47" t="n">
-        <v>10</v>
+        <v>11.4</v>
       </c>
       <c r="AD47" t="n">
-        <v>5.8</v>
+        <v>7.8</v>
       </c>
       <c r="AF47" t="n">
-        <v>223.35</v>
+        <v>222.77</v>
       </c>
       <c r="AG47" t="n">
-        <v>-0.85</v>
+        <v>-0.29</v>
       </c>
       <c r="AH47" t="n">
         <v>215</v>
@@ -5014,10 +5092,10 @@
         <v>235</v>
       </c>
       <c r="AK47" t="n">
-        <v>127.19</v>
+        <v>130.42</v>
       </c>
       <c r="AL47" t="n">
-        <v>-1.41</v>
+        <v>1.25</v>
       </c>
       <c r="AM47" t="n">
         <v>110</v>
@@ -5026,99 +5104,99 @@
         <v>142</v>
       </c>
       <c r="AP47" t="n">
-        <v>81.06</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="AS47" t="n">
-        <v>13.63</v>
+        <v>14</v>
       </c>
       <c r="BL47" s="1" t="n">
-        <v>46279</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B48" t="n">
-        <v>145.5</v>
+        <v>135.5</v>
       </c>
       <c r="C48" t="n">
-        <v>62.3</v>
+        <v>47.7</v>
       </c>
       <c r="D48" t="n">
-        <v>34</v>
+        <v>34.2</v>
       </c>
       <c r="E48" t="n">
-        <v>22.5</v>
+        <v>24.1</v>
       </c>
       <c r="F48" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="H48" t="n">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
       <c r="I48" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="J48" t="n">
-        <v>40.8</v>
+        <v>38.4</v>
       </c>
       <c r="K48" t="n">
-        <v>75</v>
+        <v>73.2</v>
       </c>
       <c r="M48" t="n">
-        <v>6.9</v>
+        <v>3</v>
       </c>
       <c r="N48" t="n">
-        <v>30.4</v>
+        <v>30.3</v>
       </c>
       <c r="O48" t="n">
-        <v>37.3</v>
+        <v>33.3</v>
       </c>
       <c r="Q48" t="n">
-        <v>22.1</v>
+        <v>23.3</v>
       </c>
       <c r="R48" t="n">
-        <v>4.9</v>
+        <v>1</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>22.1</v>
+        <v>23.3</v>
       </c>
       <c r="V48" t="n">
-        <v>4</v>
+        <v>11.3</v>
       </c>
       <c r="W48" t="n">
-        <v>22.9</v>
+        <v>27.6</v>
       </c>
       <c r="X48" t="n">
-        <v>13.4</v>
+        <v>19.5</v>
       </c>
       <c r="Y48" t="n">
         <v>11</v>
       </c>
       <c r="Z48" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA48" t="n">
-        <v>12.9</v>
+        <v>18.8</v>
       </c>
       <c r="AB48" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="AC48" t="n">
-        <v>12.7</v>
+        <v>15.5</v>
       </c>
       <c r="AD48" t="n">
-        <v>6.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AF48" t="n">
-        <v>223.06</v>
+        <v>221.86</v>
       </c>
       <c r="AG48" t="n">
-        <v>-0.29</v>
+        <v>-0.91</v>
       </c>
       <c r="AH48" t="n">
         <v>215</v>
@@ -5127,10 +5205,10 @@
         <v>235</v>
       </c>
       <c r="AK48" t="n">
-        <v>129.17</v>
+        <v>129.71</v>
       </c>
       <c r="AL48" t="n">
-        <v>1.98</v>
+        <v>-0.71</v>
       </c>
       <c r="AM48" t="n">
         <v>110</v>
@@ -5139,99 +5217,54 @@
         <v>142</v>
       </c>
       <c r="AP48" t="n">
-        <v>82.36</v>
+        <v>86.42</v>
       </c>
       <c r="AS48" t="n">
-        <v>13.91</v>
+        <v>16.05</v>
       </c>
       <c r="BL48" s="1" t="n">
-        <v>46280</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="B49" t="n">
-        <v>148</v>
-      </c>
-      <c r="C49" t="n">
-        <v>61.6</v>
+        <v>118.1</v>
       </c>
       <c r="D49" t="n">
-        <v>33.9</v>
-      </c>
-      <c r="E49" t="n">
-        <v>25</v>
+        <v>34.7</v>
       </c>
       <c r="F49" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="H49" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="I49" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="J49" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="K49" t="n">
-        <v>74.09999999999999</v>
-      </c>
-      <c r="M49" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="N49" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="O49" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="R49" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="S49" t="n">
-        <v>0</v>
-      </c>
-      <c r="T49" t="n">
-        <v>23.3</v>
+        <v>3.3</v>
       </c>
       <c r="V49" t="n">
-        <v>7.8</v>
+        <v>14.1</v>
       </c>
       <c r="W49" t="n">
-        <v>26</v>
+        <v>27.6</v>
       </c>
       <c r="X49" t="n">
-        <v>16.9</v>
+        <v>20.9</v>
       </c>
       <c r="Y49" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="Z49" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="AA49" t="n">
-        <v>11.6</v>
+        <v>19</v>
       </c>
       <c r="AB49" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="AC49" t="n">
-        <v>11.4</v>
+        <v>14.9</v>
       </c>
       <c r="AD49" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>222.77</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>-0.29</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AH49" t="n">
         <v>215</v>
@@ -5239,112 +5272,55 @@
       <c r="AI49" t="n">
         <v>235</v>
       </c>
-      <c r="AK49" t="n">
-        <v>130.42</v>
-      </c>
-      <c r="AL49" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AM49" t="n">
         <v>110</v>
       </c>
       <c r="AN49" t="n">
         <v>142</v>
       </c>
-      <c r="AP49" t="n">
-        <v>80.90000000000001</v>
-      </c>
-      <c r="AS49" t="n">
-        <v>14</v>
-      </c>
       <c r="BL49" s="1" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46282</v>
+        <v>46284</v>
       </c>
       <c r="B50" t="n">
-        <v>135.5</v>
-      </c>
-      <c r="C50" t="n">
-        <v>47.7</v>
+        <v>100.3</v>
       </c>
       <c r="D50" t="n">
-        <v>34.2</v>
-      </c>
-      <c r="E50" t="n">
-        <v>24.1</v>
+        <v>34</v>
       </c>
       <c r="F50" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H50" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="I50" t="n">
-        <v>10</v>
-      </c>
-      <c r="J50" t="n">
-        <v>38.4</v>
-      </c>
-      <c r="K50" t="n">
-        <v>73.2</v>
-      </c>
-      <c r="M50" t="n">
-        <v>3</v>
-      </c>
-      <c r="N50" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="O50" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="Q50" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V50" t="n">
+        <v>16</v>
+      </c>
+      <c r="W50" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="X50" t="n">
         <v>23.3</v>
       </c>
-      <c r="R50" t="n">
-        <v>1</v>
-      </c>
-      <c r="S50" t="n">
-        <v>0</v>
-      </c>
-      <c r="T50" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="V50" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="W50" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="X50" t="n">
-        <v>19.5</v>
-      </c>
       <c r="Y50" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="Z50" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AA50" t="n">
-        <v>18.8</v>
+        <v>20</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC50" t="n">
-        <v>15.5</v>
+        <v>16.7</v>
       </c>
       <c r="AD50" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>221.86</v>
-      </c>
-      <c r="AG50" t="n">
-        <v>-0.91</v>
+        <v>12.8</v>
       </c>
       <c r="AH50" t="n">
         <v>215</v>
@@ -5352,67 +5328,100 @@
       <c r="AI50" t="n">
         <v>235</v>
       </c>
-      <c r="AK50" t="n">
-        <v>129.71</v>
-      </c>
-      <c r="AL50" t="n">
-        <v>-0.71</v>
-      </c>
       <c r="AM50" t="n">
         <v>110</v>
       </c>
       <c r="AN50" t="n">
         <v>142</v>
       </c>
-      <c r="AP50" t="n">
-        <v>86.42</v>
-      </c>
-      <c r="AS50" t="n">
-        <v>16.05</v>
-      </c>
       <c r="BL50" s="1" t="n">
-        <v>46282</v>
+        <v>46284</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46283</v>
+        <v>46285</v>
       </c>
       <c r="B51" t="n">
-        <v>118.1</v>
+        <v>104.9</v>
+      </c>
+      <c r="C51" t="n">
+        <v>36.3</v>
       </c>
       <c r="D51" t="n">
-        <v>34.7</v>
+        <v>32.7</v>
+      </c>
+      <c r="E51" t="n">
+        <v>17</v>
       </c>
       <c r="F51" t="n">
-        <v>3.3</v>
+        <v>1.6</v>
+      </c>
+      <c r="H51" t="n">
+        <v>16</v>
+      </c>
+      <c r="I51" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="J51" t="n">
+        <v>25</v>
+      </c>
+      <c r="K51" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="M51" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N51" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="O51" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>10.5</v>
       </c>
       <c r="V51" t="n">
-        <v>14.1</v>
+        <v>15.8</v>
       </c>
       <c r="W51" t="n">
-        <v>27.6</v>
+        <v>33.6</v>
       </c>
       <c r="X51" t="n">
-        <v>20.9</v>
+        <v>24.7</v>
       </c>
       <c r="Y51" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z51" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AA51" t="n">
-        <v>19</v>
+        <v>16.9</v>
       </c>
       <c r="AB51" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="AC51" t="n">
-        <v>14.9</v>
+        <v>10.1</v>
       </c>
       <c r="AD51" t="n">
-        <v>9.199999999999999</v>
+        <v>7</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>234.9</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>13.04</v>
       </c>
       <c r="AH51" t="n">
         <v>215</v>
@@ -5420,55 +5429,112 @@
       <c r="AI51" t="n">
         <v>235</v>
       </c>
+      <c r="AK51" t="n">
+        <v>137.51</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>7.8</v>
+      </c>
       <c r="AM51" t="n">
         <v>110</v>
       </c>
       <c r="AN51" t="n">
         <v>142</v>
       </c>
+      <c r="AP51" t="n">
+        <v>94</v>
+      </c>
+      <c r="AS51" t="n">
+        <v>18.87</v>
+      </c>
       <c r="BL51" s="1" t="n">
-        <v>46283</v>
+        <v>46285</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="B52" t="n">
-        <v>100.3</v>
+        <v>134.9</v>
+      </c>
+      <c r="C52" t="n">
+        <v>53.3</v>
       </c>
       <c r="D52" t="n">
-        <v>34</v>
+        <v>36.3</v>
+      </c>
+      <c r="E52" t="n">
+        <v>20.6</v>
       </c>
       <c r="F52" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
+      </c>
+      <c r="H52" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="I52" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="J52" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="K52" t="n">
+        <v>66</v>
+      </c>
+      <c r="M52" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="N52" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="O52" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>18.3</v>
       </c>
       <c r="V52" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="W52" t="n">
-        <v>30.6</v>
+        <v>22.5</v>
       </c>
       <c r="X52" t="n">
-        <v>23.3</v>
+        <v>20.5</v>
       </c>
       <c r="Y52" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="Z52" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="AA52" t="n">
-        <v>20</v>
+        <v>13.8</v>
       </c>
       <c r="AB52" t="n">
-        <v>8.800000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="AC52" t="n">
-        <v>16.7</v>
+        <v>9.5</v>
       </c>
       <c r="AD52" t="n">
-        <v>12.8</v>
+        <v>5.4</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>229.2</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>-5.7</v>
       </c>
       <c r="AH52" t="n">
         <v>215</v>
@@ -5476,58 +5542,70 @@
       <c r="AI52" t="n">
         <v>235</v>
       </c>
+      <c r="AK52" t="n">
+        <v>138.98</v>
+      </c>
+      <c r="AL52" t="n">
+        <v>1.47</v>
+      </c>
       <c r="AM52" t="n">
         <v>110</v>
       </c>
       <c r="AN52" t="n">
         <v>142</v>
       </c>
+      <c r="AP52" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="AS52" t="n">
+        <v>16.02</v>
+      </c>
       <c r="BL52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46285</v>
+        <v>46287</v>
       </c>
       <c r="B53" t="n">
-        <v>104.9</v>
+        <v>146.4</v>
       </c>
       <c r="C53" t="n">
-        <v>36.3</v>
+        <v>60.2</v>
       </c>
       <c r="D53" t="n">
-        <v>32.7</v>
+        <v>35.6</v>
       </c>
       <c r="E53" t="n">
-        <v>17</v>
+        <v>24.2</v>
       </c>
       <c r="F53" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="H53" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I53" t="n">
-        <v>10.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J53" t="n">
-        <v>25</v>
+        <v>38.2</v>
       </c>
       <c r="K53" t="n">
-        <v>51.2</v>
+        <v>70</v>
       </c>
       <c r="M53" t="n">
         <v>1.8</v>
       </c>
       <c r="N53" t="n">
-        <v>25.5</v>
+        <v>30.2</v>
       </c>
       <c r="O53" t="n">
-        <v>27.3</v>
+        <v>31.9</v>
       </c>
       <c r="Q53" t="n">
-        <v>10.5</v>
+        <v>20.2</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
@@ -5536,40 +5614,40 @@
         <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>10.5</v>
+        <v>20.2</v>
       </c>
       <c r="V53" t="n">
-        <v>15.8</v>
+        <v>14.1</v>
       </c>
       <c r="W53" t="n">
-        <v>33.6</v>
+        <v>20.2</v>
       </c>
       <c r="X53" t="n">
-        <v>24.7</v>
+        <v>17.1</v>
       </c>
       <c r="Y53" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="Z53" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="AA53" t="n">
-        <v>16.9</v>
+        <v>9.6</v>
       </c>
       <c r="AB53" t="n">
-        <v>4</v>
+        <v>-0</v>
       </c>
       <c r="AC53" t="n">
-        <v>10.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AD53" t="n">
-        <v>7</v>
+        <v>4.8</v>
       </c>
       <c r="AF53" t="n">
-        <v>234.9</v>
+        <v>224.9</v>
       </c>
       <c r="AG53" t="n">
-        <v>13.04</v>
+        <v>-4.3</v>
       </c>
       <c r="AH53" t="n">
         <v>215</v>
@@ -5578,10 +5656,10 @@
         <v>235</v>
       </c>
       <c r="AK53" t="n">
-        <v>137.51</v>
+        <v>134.04</v>
       </c>
       <c r="AL53" t="n">
-        <v>7.8</v>
+        <v>-4.94</v>
       </c>
       <c r="AM53" t="n">
         <v>110</v>
@@ -5590,57 +5668,57 @@
         <v>142</v>
       </c>
       <c r="AP53" t="n">
-        <v>94</v>
+        <v>76.5</v>
       </c>
       <c r="AS53" t="n">
-        <v>18.87</v>
+        <v>13.68</v>
       </c>
       <c r="BL53" s="1" t="n">
-        <v>46285</v>
+        <v>46287</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="B54" t="n">
-        <v>134.9</v>
+        <v>131.4</v>
       </c>
       <c r="C54" t="n">
-        <v>53.3</v>
+        <v>53.7</v>
       </c>
       <c r="D54" t="n">
-        <v>36.3</v>
+        <v>34.7</v>
       </c>
       <c r="E54" t="n">
-        <v>20.6</v>
+        <v>20.1</v>
       </c>
       <c r="F54" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="H54" t="n">
-        <v>21.2</v>
+        <v>24.1</v>
       </c>
       <c r="I54" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="J54" t="n">
-        <v>35.4</v>
+        <v>37</v>
       </c>
       <c r="K54" t="n">
-        <v>66</v>
+        <v>69.8</v>
       </c>
       <c r="M54" t="n">
         <v>1.9</v>
       </c>
       <c r="N54" t="n">
-        <v>24.8</v>
+        <v>31.4</v>
       </c>
       <c r="O54" t="n">
-        <v>26.7</v>
+        <v>33.3</v>
       </c>
       <c r="Q54" t="n">
-        <v>18.3</v>
+        <v>22.3</v>
       </c>
       <c r="R54" t="n">
         <v>0</v>
@@ -5649,40 +5727,40 @@
         <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>18.3</v>
+        <v>22.3</v>
       </c>
       <c r="V54" t="n">
-        <v>18.5</v>
+        <v>9.1</v>
       </c>
       <c r="W54" t="n">
-        <v>22.5</v>
+        <v>26.1</v>
       </c>
       <c r="X54" t="n">
-        <v>20.5</v>
+        <v>17.6</v>
       </c>
       <c r="Y54" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z54" t="n">
         <v>18</v>
       </c>
       <c r="AA54" t="n">
-        <v>13.8</v>
+        <v>14</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.3</v>
+        <v>5.1</v>
       </c>
       <c r="AC54" t="n">
-        <v>9.5</v>
+        <v>13.2</v>
       </c>
       <c r="AD54" t="n">
-        <v>5.4</v>
+        <v>9.1</v>
       </c>
       <c r="AF54" t="n">
-        <v>229.2</v>
+        <v>220.8</v>
       </c>
       <c r="AG54" t="n">
-        <v>-5.7</v>
+        <v>-4.1</v>
       </c>
       <c r="AH54" t="n">
         <v>215</v>
@@ -5691,10 +5769,10 @@
         <v>235</v>
       </c>
       <c r="AK54" t="n">
-        <v>138.98</v>
+        <v>131.01</v>
       </c>
       <c r="AL54" t="n">
-        <v>1.47</v>
+        <v>-3.03</v>
       </c>
       <c r="AM54" t="n">
         <v>110</v>
@@ -5703,57 +5781,57 @@
         <v>142</v>
       </c>
       <c r="AP54" t="n">
-        <v>84.90000000000001</v>
+        <v>81.28</v>
       </c>
       <c r="AS54" t="n">
-        <v>16.02</v>
+        <v>13.92</v>
       </c>
       <c r="BL54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46287</v>
+        <v>46289</v>
       </c>
       <c r="B55" t="n">
-        <v>146.4</v>
+        <v>127.2</v>
       </c>
       <c r="C55" t="n">
-        <v>60.2</v>
+        <v>42.7</v>
       </c>
       <c r="D55" t="n">
-        <v>35.6</v>
+        <v>34.6</v>
       </c>
       <c r="E55" t="n">
-        <v>24.2</v>
+        <v>20.7</v>
       </c>
       <c r="F55" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="H55" t="n">
-        <v>23</v>
+        <v>21.2</v>
       </c>
       <c r="I55" t="n">
-        <v>8.800000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="J55" t="n">
-        <v>38.2</v>
+        <v>36.8</v>
       </c>
       <c r="K55" t="n">
-        <v>70</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="M55" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="N55" t="n">
-        <v>30.2</v>
+        <v>27.9</v>
       </c>
       <c r="O55" t="n">
-        <v>31.9</v>
+        <v>29.8</v>
       </c>
       <c r="Q55" t="n">
-        <v>20.2</v>
+        <v>22.2</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
@@ -5762,40 +5840,40 @@
         <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>20.2</v>
+        <v>22.2</v>
       </c>
       <c r="V55" t="n">
-        <v>14.1</v>
+        <v>11.9</v>
       </c>
       <c r="W55" t="n">
-        <v>20.2</v>
+        <v>31.2</v>
       </c>
       <c r="X55" t="n">
-        <v>17.1</v>
+        <v>21.6</v>
       </c>
       <c r="Y55" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="Z55" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="AA55" t="n">
-        <v>9.6</v>
+        <v>19.7</v>
       </c>
       <c r="AB55" t="n">
-        <v>-0</v>
+        <v>5.1</v>
       </c>
       <c r="AC55" t="n">
-        <v>9.699999999999999</v>
+        <v>11.1</v>
       </c>
       <c r="AD55" t="n">
-        <v>4.8</v>
+        <v>8.1</v>
       </c>
       <c r="AF55" t="n">
-        <v>224.9</v>
+        <v>228.06</v>
       </c>
       <c r="AG55" t="n">
-        <v>-4.3</v>
+        <v>7.26</v>
       </c>
       <c r="AH55" t="n">
         <v>215</v>
@@ -5804,10 +5882,10 @@
         <v>235</v>
       </c>
       <c r="AK55" t="n">
-        <v>134.04</v>
+        <v>131.96</v>
       </c>
       <c r="AL55" t="n">
-        <v>-4.94</v>
+        <v>0.95</v>
       </c>
       <c r="AM55" t="n">
         <v>110</v>
@@ -5816,99 +5894,36 @@
         <v>142</v>
       </c>
       <c r="AP55" t="n">
-        <v>76.5</v>
+        <v>84.34</v>
       </c>
       <c r="AS55" t="n">
-        <v>13.68</v>
+        <v>17.57</v>
       </c>
       <c r="BL55" s="1" t="n">
-        <v>46287</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46288</v>
+        <v>46290</v>
       </c>
       <c r="B56" t="n">
-        <v>131.4</v>
-      </c>
-      <c r="C56" t="n">
-        <v>53.7</v>
+        <v>116.2</v>
       </c>
       <c r="D56" t="n">
-        <v>34.7</v>
-      </c>
-      <c r="E56" t="n">
-        <v>20.1</v>
+        <v>35.4</v>
       </c>
       <c r="F56" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="H56" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I56" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="J56" t="n">
-        <v>37</v>
-      </c>
-      <c r="K56" t="n">
-        <v>69.8</v>
-      </c>
-      <c r="M56" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="N56" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="O56" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="R56" t="n">
-        <v>0</v>
-      </c>
-      <c r="S56" t="n">
-        <v>0</v>
-      </c>
-      <c r="T56" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="V56" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="W56" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="X56" t="n">
-        <v>17.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y56" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="Z56" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="AA56" t="n">
-        <v>14</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="AF56" t="n">
-        <v>220.8</v>
-      </c>
-      <c r="AG56" t="n">
-        <v>-4.1</v>
+        <v>21</v>
       </c>
       <c r="AH56" t="n">
         <v>215</v>
@@ -5916,94 +5931,37 @@
       <c r="AI56" t="n">
         <v>235</v>
       </c>
-      <c r="AK56" t="n">
-        <v>131.01</v>
-      </c>
-      <c r="AL56" t="n">
-        <v>-3.03</v>
-      </c>
       <c r="AM56" t="n">
         <v>110</v>
       </c>
       <c r="AN56" t="n">
         <v>142</v>
       </c>
-      <c r="AP56" t="n">
-        <v>81.28</v>
-      </c>
-      <c r="AS56" t="n">
-        <v>13.92</v>
-      </c>
       <c r="BL56" s="1" t="n">
-        <v>46288</v>
+        <v>46290</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46289</v>
+        <v>46291</v>
       </c>
       <c r="B57" t="n">
-        <v>127.2</v>
-      </c>
-      <c r="C57" t="n">
-        <v>42.7</v>
+        <v>105.5</v>
       </c>
       <c r="D57" t="n">
-        <v>34.6</v>
-      </c>
-      <c r="E57" t="n">
-        <v>20.7</v>
+        <v>34</v>
       </c>
       <c r="F57" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H57" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="I57" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="J57" t="n">
-        <v>36.8</v>
-      </c>
-      <c r="K57" t="n">
-        <v>67.09999999999999</v>
-      </c>
-      <c r="M57" t="n">
-        <v>2</v>
-      </c>
-      <c r="N57" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="O57" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="R57" t="n">
-        <v>0</v>
-      </c>
-      <c r="S57" t="n">
-        <v>0</v>
-      </c>
-      <c r="T57" t="n">
-        <v>22.2</v>
+        <v>4.5</v>
       </c>
       <c r="Y57" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Z57" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA57" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="AF57" t="n">
-        <v>228.06</v>
-      </c>
-      <c r="AG57" t="n">
-        <v>7.26</v>
+        <v>18.5</v>
       </c>
       <c r="AH57" t="n">
         <v>215</v>
@@ -6011,49 +5969,82 @@
       <c r="AI57" t="n">
         <v>235</v>
       </c>
-      <c r="AK57" t="n">
-        <v>131.96</v>
-      </c>
-      <c r="AL57" t="n">
-        <v>0.95</v>
-      </c>
       <c r="AM57" t="n">
         <v>110</v>
       </c>
       <c r="AN57" t="n">
         <v>142</v>
       </c>
-      <c r="AP57" t="n">
-        <v>84.34</v>
-      </c>
-      <c r="AS57" t="n">
-        <v>17.57</v>
-      </c>
       <c r="BL57" s="1" t="n">
-        <v>46289</v>
+        <v>46291</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46290</v>
+        <v>46292</v>
       </c>
       <c r="B58" t="n">
-        <v>116.2</v>
+        <v>112.8</v>
+      </c>
+      <c r="C58" t="n">
+        <v>37</v>
       </c>
       <c r="D58" t="n">
-        <v>35.4</v>
+        <v>32.4</v>
+      </c>
+      <c r="E58" t="n">
+        <v>23.5</v>
       </c>
       <c r="F58" t="n">
-        <v>4.5</v>
+        <v>2.6</v>
+      </c>
+      <c r="H58" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="I58" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="J58" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="K58" t="n">
+        <v>56.9</v>
+      </c>
+      <c r="M58" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="N58" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="O58" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>17</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>17</v>
       </c>
       <c r="Y58" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Z58" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="AA58" t="n">
-        <v>21</v>
+        <v>16</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>235</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>6.94</v>
       </c>
       <c r="AH58" t="n">
         <v>215</v>
@@ -6061,37 +6052,94 @@
       <c r="AI58" t="n">
         <v>235</v>
       </c>
+      <c r="AK58" t="n">
+        <v>136.61</v>
+      </c>
+      <c r="AL58" t="n">
+        <v>4.65</v>
+      </c>
       <c r="AM58" t="n">
         <v>110</v>
       </c>
       <c r="AN58" t="n">
         <v>142</v>
       </c>
+      <c r="AP58" t="n">
+        <v>89.01000000000001</v>
+      </c>
+      <c r="AS58" t="n">
+        <v>18.21</v>
+      </c>
       <c r="BL58" s="1" t="n">
-        <v>46290</v>
+        <v>46292</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="B59" t="n">
-        <v>105.5</v>
+        <v>126.8</v>
+      </c>
+      <c r="C59" t="n">
+        <v>40.9</v>
       </c>
       <c r="D59" t="n">
-        <v>34</v>
+        <v>34.8</v>
+      </c>
+      <c r="E59" t="n">
+        <v>27.9</v>
       </c>
       <c r="F59" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
+      </c>
+      <c r="H59" t="n">
+        <v>23</v>
+      </c>
+      <c r="I59" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="J59" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="K59" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="M59" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="N59" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="O59" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>20.3</v>
       </c>
       <c r="Y59" t="n">
         <v>15</v>
       </c>
       <c r="Z59" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AA59" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>233.68</v>
+      </c>
+      <c r="AG59" t="n">
+        <v>-1.32</v>
       </c>
       <c r="AH59" t="n">
         <v>215</v>
@@ -6099,58 +6147,70 @@
       <c r="AI59" t="n">
         <v>235</v>
       </c>
+      <c r="AK59" t="n">
+        <v>136.95</v>
+      </c>
+      <c r="AL59" t="n">
+        <v>0.34</v>
+      </c>
       <c r="AM59" t="n">
         <v>110</v>
       </c>
       <c r="AN59" t="n">
         <v>142</v>
       </c>
+      <c r="AP59" t="n">
+        <v>86.34</v>
+      </c>
+      <c r="AS59" t="n">
+        <v>17.39</v>
+      </c>
       <c r="BL59" s="1" t="n">
-        <v>46291</v>
+        <v>46293</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46292</v>
+        <v>46294</v>
       </c>
       <c r="B60" t="n">
-        <v>112.8</v>
+        <v>128.5</v>
       </c>
       <c r="C60" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D60" t="n">
-        <v>32.4</v>
+        <v>36.1</v>
       </c>
       <c r="E60" t="n">
-        <v>23.5</v>
+        <v>23.9</v>
       </c>
       <c r="F60" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="H60" t="n">
-        <v>17.9</v>
+        <v>23.6</v>
       </c>
       <c r="I60" t="n">
         <v>9.1</v>
       </c>
       <c r="J60" t="n">
-        <v>29.9</v>
+        <v>36.7</v>
       </c>
       <c r="K60" t="n">
-        <v>56.9</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="M60" t="n">
         <v>1.9</v>
       </c>
       <c r="N60" t="n">
-        <v>24.2</v>
+        <v>27.8</v>
       </c>
       <c r="O60" t="n">
-        <v>26.2</v>
+        <v>29.7</v>
       </c>
       <c r="Q60" t="n">
-        <v>17</v>
+        <v>20.5</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
@@ -6159,7 +6219,7 @@
         <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>17</v>
+        <v>20.5</v>
       </c>
       <c r="Y60" t="n">
         <v>15</v>
@@ -6168,13 +6228,13 @@
         <v>19</v>
       </c>
       <c r="AA60" t="n">
-        <v>16</v>
+        <v>18.2</v>
       </c>
       <c r="AF60" t="n">
-        <v>235</v>
+        <v>234.53</v>
       </c>
       <c r="AG60" t="n">
-        <v>6.94</v>
+        <v>0.85</v>
       </c>
       <c r="AH60" t="n">
         <v>215</v>
@@ -6183,10 +6243,10 @@
         <v>235</v>
       </c>
       <c r="AK60" t="n">
-        <v>136.61</v>
+        <v>136.49</v>
       </c>
       <c r="AL60" t="n">
-        <v>4.65</v>
+        <v>-0.46</v>
       </c>
       <c r="AM60" t="n">
         <v>110</v>
@@ -6195,36 +6255,36 @@
         <v>142</v>
       </c>
       <c r="AP60" t="n">
-        <v>89.01000000000001</v>
+        <v>88.23</v>
       </c>
       <c r="AS60" t="n">
-        <v>18.21</v>
+        <v>17.37</v>
       </c>
       <c r="BL60" s="1" t="n">
-        <v>46292</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="B61" t="n">
-        <v>116.4</v>
+        <v>120.3</v>
       </c>
       <c r="D61" t="n">
-        <v>35.3</v>
+        <v>36.2</v>
       </c>
       <c r="F61" t="n">
-        <v>3.5</v>
+        <v>5.3</v>
       </c>
       <c r="Y61" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="Z61" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AA61" t="n">
-        <v>17</v>
+        <v>13.5</v>
       </c>
       <c r="AH61" t="n">
         <v>215</v>
@@ -6239,30 +6299,30 @@
         <v>142</v>
       </c>
       <c r="BL61" s="1" t="n">
-        <v>46293</v>
+        <v>46295</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46294</v>
+        <v>46296</v>
       </c>
       <c r="B62" t="n">
-        <v>118.3</v>
+        <v>119.1</v>
       </c>
       <c r="D62" t="n">
-        <v>37.2</v>
+        <v>36.7</v>
       </c>
       <c r="F62" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="Y62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z62" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AA62" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AH62" t="n">
         <v>215</v>
@@ -6277,7 +6337,7 @@
         <v>142</v>
       </c>
       <c r="BL62" s="1" t="n">
-        <v>46294</v>
+        <v>46296</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -628,46 +628,46 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="B2" t="n">
-        <v>137.2</v>
+        <v>157.5</v>
       </c>
       <c r="C2" t="n">
-        <v>56.3</v>
+        <v>59.6</v>
       </c>
       <c r="D2" t="n">
-        <v>32.1</v>
+        <v>35</v>
       </c>
       <c r="E2" t="n">
-        <v>21.2</v>
+        <v>30.6</v>
       </c>
       <c r="F2" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="H2" t="n">
-        <v>23.7</v>
+        <v>24.2</v>
       </c>
       <c r="I2" t="n">
-        <v>11.6</v>
+        <v>11.2</v>
       </c>
       <c r="J2" t="n">
-        <v>40.4</v>
+        <v>38.9</v>
       </c>
       <c r="K2" t="n">
-        <v>75.7</v>
+        <v>74.3</v>
       </c>
       <c r="M2" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="N2" t="n">
-        <v>29</v>
+        <v>33.4</v>
       </c>
       <c r="O2" t="n">
-        <v>32.6</v>
+        <v>37.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="R2" t="n">
         <v>1.3</v>
@@ -676,40 +676,40 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="V2" t="n">
-        <v>10.7</v>
+        <v>13</v>
       </c>
       <c r="W2" t="n">
-        <v>24.3</v>
+        <v>26.3</v>
       </c>
       <c r="X2" t="n">
-        <v>17.5</v>
+        <v>19.6</v>
       </c>
       <c r="Y2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA2" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.9</v>
+        <v>-2.1</v>
       </c>
       <c r="AC2" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="AF2" t="n">
-        <v>232.22</v>
+        <v>229.69</v>
       </c>
       <c r="AG2" t="n">
-        <v>7.43</v>
+        <v>-2.53</v>
       </c>
       <c r="AH2" t="n">
         <v>215</v>
@@ -718,10 +718,10 @@
         <v>235</v>
       </c>
       <c r="AK2" t="n">
-        <v>143.61</v>
+        <v>136.96</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.06</v>
+        <v>-6.65</v>
       </c>
       <c r="AM2" t="n">
         <v>110</v>
@@ -730,99 +730,99 @@
         <v>142</v>
       </c>
       <c r="AP2" t="n">
-        <v>89.31999999999999</v>
+        <v>86.59</v>
       </c>
       <c r="AS2" t="n">
-        <v>18.02</v>
+        <v>16.96</v>
       </c>
       <c r="BL2" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B3" t="n">
-        <v>157.5</v>
+        <v>159.6</v>
       </c>
       <c r="C3" t="n">
-        <v>59.6</v>
+        <v>63</v>
       </c>
       <c r="D3" t="n">
-        <v>35</v>
+        <v>34.5</v>
       </c>
       <c r="E3" t="n">
-        <v>30.6</v>
+        <v>31.1</v>
       </c>
       <c r="F3" t="n">
-        <v>7.5</v>
+        <v>5.7</v>
       </c>
       <c r="H3" t="n">
-        <v>24.2</v>
+        <v>23.8</v>
       </c>
       <c r="I3" t="n">
-        <v>11.2</v>
+        <v>10.8</v>
       </c>
       <c r="J3" t="n">
-        <v>38.9</v>
+        <v>40.5</v>
       </c>
       <c r="K3" t="n">
-        <v>74.3</v>
+        <v>75.2</v>
       </c>
       <c r="M3" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="N3" t="n">
-        <v>33.4</v>
+        <v>34.3</v>
       </c>
       <c r="O3" t="n">
-        <v>37.1</v>
+        <v>38.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T3" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="V3" t="n">
-        <v>13</v>
+        <v>17.5</v>
       </c>
       <c r="W3" t="n">
-        <v>26.3</v>
+        <v>22.5</v>
       </c>
       <c r="X3" t="n">
-        <v>19.6</v>
+        <v>20</v>
       </c>
       <c r="Y3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA3" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>-2.1</v>
+        <v>-2.2</v>
       </c>
       <c r="AC3" t="n">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="AF3" t="n">
-        <v>229.69</v>
+        <v>228.57</v>
       </c>
       <c r="AG3" t="n">
-        <v>-2.53</v>
+        <v>-1.14</v>
       </c>
       <c r="AH3" t="n">
         <v>215</v>
@@ -831,10 +831,10 @@
         <v>235</v>
       </c>
       <c r="AK3" t="n">
-        <v>136.96</v>
+        <v>133.01</v>
       </c>
       <c r="AL3" t="n">
-        <v>-6.65</v>
+        <v>-3.95</v>
       </c>
       <c r="AM3" t="n">
         <v>110</v>
@@ -843,99 +843,99 @@
         <v>142</v>
       </c>
       <c r="AP3" t="n">
-        <v>86.59</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="AS3" t="n">
-        <v>16.96</v>
+        <v>15.95</v>
       </c>
       <c r="BL3" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B4" t="n">
-        <v>159.6</v>
+        <v>160.4</v>
       </c>
       <c r="C4" t="n">
-        <v>63</v>
+        <v>62.6</v>
       </c>
       <c r="D4" t="n">
-        <v>34.5</v>
+        <v>35</v>
       </c>
       <c r="E4" t="n">
-        <v>31.1</v>
+        <v>32.2</v>
       </c>
       <c r="F4" t="n">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="H4" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="I4" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="J4" t="n">
-        <v>40.5</v>
+        <v>41.1</v>
       </c>
       <c r="K4" t="n">
-        <v>75.2</v>
+        <v>75.7</v>
       </c>
       <c r="M4" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="N4" t="n">
-        <v>34.3</v>
+        <v>32.6</v>
       </c>
       <c r="O4" t="n">
-        <v>38.2</v>
+        <v>38</v>
       </c>
       <c r="Q4" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T4" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="V4" t="n">
-        <v>17.5</v>
+        <v>16.4</v>
       </c>
       <c r="W4" t="n">
-        <v>22.5</v>
+        <v>22.8</v>
       </c>
       <c r="X4" t="n">
-        <v>20</v>
+        <v>19.6</v>
       </c>
       <c r="Y4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Z4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA4" t="n">
-        <v>13.5</v>
+        <v>14.1</v>
       </c>
       <c r="AB4" t="n">
-        <v>-2.2</v>
+        <v>-3.1</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="AF4" t="n">
-        <v>228.57</v>
+        <v>225.08</v>
       </c>
       <c r="AG4" t="n">
-        <v>-1.14</v>
+        <v>-3.5</v>
       </c>
       <c r="AH4" t="n">
         <v>215</v>
@@ -944,10 +944,10 @@
         <v>235</v>
       </c>
       <c r="AK4" t="n">
-        <v>133.01</v>
+        <v>135.24</v>
       </c>
       <c r="AL4" t="n">
-        <v>-3.95</v>
+        <v>2.23</v>
       </c>
       <c r="AM4" t="n">
         <v>110</v>
@@ -956,99 +956,99 @@
         <v>142</v>
       </c>
       <c r="AP4" t="n">
-        <v>84.59999999999999</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="AS4" t="n">
-        <v>15.95</v>
+        <v>15.4</v>
       </c>
       <c r="BL4" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B5" t="n">
-        <v>160.4</v>
+        <v>161.7</v>
       </c>
       <c r="C5" t="n">
-        <v>62.6</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>35</v>
+        <v>34.9</v>
       </c>
       <c r="E5" t="n">
-        <v>32.2</v>
+        <v>27.3</v>
       </c>
       <c r="F5" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H5" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="I5" t="n">
-        <v>10.7</v>
+        <v>10.3</v>
       </c>
       <c r="J5" t="n">
-        <v>41.1</v>
+        <v>42.6</v>
       </c>
       <c r="K5" t="n">
-        <v>75.7</v>
+        <v>77</v>
       </c>
       <c r="M5" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="N5" t="n">
-        <v>32.6</v>
+        <v>31.5</v>
       </c>
       <c r="O5" t="n">
-        <v>38</v>
+        <v>37.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="R5" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T5" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="V5" t="n">
-        <v>16.4</v>
+        <v>12.7</v>
       </c>
       <c r="W5" t="n">
-        <v>22.8</v>
+        <v>27</v>
       </c>
       <c r="X5" t="n">
-        <v>19.6</v>
+        <v>19.9</v>
       </c>
       <c r="Y5" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Z5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AA5" t="n">
-        <v>14.1</v>
+        <v>11.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>-3.1</v>
+        <v>-5.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.6</v>
+        <v>-0.3</v>
       </c>
       <c r="AF5" t="n">
-        <v>225.08</v>
+        <v>225</v>
       </c>
       <c r="AG5" t="n">
-        <v>-3.5</v>
+        <v>-0.08</v>
       </c>
       <c r="AH5" t="n">
         <v>215</v>
@@ -1057,10 +1057,10 @@
         <v>235</v>
       </c>
       <c r="AK5" t="n">
-        <v>135.24</v>
+        <v>134.62</v>
       </c>
       <c r="AL5" t="n">
-        <v>2.23</v>
+        <v>-0.62</v>
       </c>
       <c r="AM5" t="n">
         <v>110</v>
@@ -1069,99 +1069,60 @@
         <v>142</v>
       </c>
       <c r="AP5" t="n">
-        <v>84.09999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="AS5" t="n">
-        <v>15.4</v>
+        <v>13.86</v>
       </c>
       <c r="BL5" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B6" t="n">
-        <v>161.7</v>
-      </c>
-      <c r="C6" t="n">
-        <v>71.09999999999999</v>
+        <v>151.5</v>
       </c>
       <c r="D6" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="E6" t="n">
-        <v>27.3</v>
+        <v>35.1</v>
       </c>
       <c r="F6" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H6" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="J6" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="K6" t="n">
-        <v>77</v>
-      </c>
-      <c r="M6" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="N6" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="O6" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>21</v>
-      </c>
-      <c r="R6" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="S6" t="n">
-        <v>6</v>
-      </c>
-      <c r="T6" t="n">
-        <v>21</v>
+        <v>5.4</v>
       </c>
       <c r="V6" t="n">
-        <v>12.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W6" t="n">
-        <v>27</v>
+        <v>19.4</v>
       </c>
       <c r="X6" t="n">
-        <v>19.9</v>
+        <v>14</v>
       </c>
       <c r="Y6" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA6" t="n">
         <v>9</v>
       </c>
-      <c r="Z6" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>11.4</v>
-      </c>
       <c r="AB6" t="n">
-        <v>-5.2</v>
+        <v>-4.7</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.6</v>
+        <v>1.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.3</v>
+        <v>-1.4</v>
       </c>
       <c r="AF6" t="n">
-        <v>225</v>
+        <v>221.37</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.08</v>
+        <v>0.05</v>
       </c>
       <c r="AH6" t="n">
         <v>215</v>
@@ -1170,10 +1131,10 @@
         <v>235</v>
       </c>
       <c r="AK6" t="n">
-        <v>134.62</v>
+        <v>135.21</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.62</v>
+        <v>0.59</v>
       </c>
       <c r="AM6" t="n">
         <v>110</v>
@@ -1181,61 +1142,61 @@
       <c r="AN6" t="n">
         <v>142</v>
       </c>
-      <c r="AP6" t="n">
-        <v>80.2</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>13.86</v>
-      </c>
       <c r="BL6" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B7" t="n">
-        <v>151.5</v>
+        <v>145.2</v>
       </c>
       <c r="D7" t="n">
-        <v>35.1</v>
+        <v>33.5</v>
       </c>
       <c r="F7" t="n">
-        <v>5.4</v>
+        <v>5</v>
+      </c>
+      <c r="K7" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="O7" t="n">
+        <v>35.5</v>
       </c>
       <c r="V7" t="n">
-        <v>8.699999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="W7" t="n">
-        <v>19.4</v>
+        <v>19.2</v>
       </c>
       <c r="X7" t="n">
-        <v>14</v>
+        <v>13.1</v>
       </c>
       <c r="Y7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z7" t="n">
         <v>13</v>
       </c>
       <c r="AA7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB7" t="n">
-        <v>-4.7</v>
+        <v>-5.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>-1.4</v>
+        <v>-1.5</v>
       </c>
       <c r="AF7" t="n">
-        <v>221.37</v>
+        <v>224.37</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.05</v>
+        <v>3</v>
       </c>
       <c r="AH7" t="n">
         <v>215</v>
@@ -1244,10 +1205,10 @@
         <v>235</v>
       </c>
       <c r="AK7" t="n">
-        <v>135.21</v>
+        <v>135.61</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.59</v>
+        <v>0.4</v>
       </c>
       <c r="AM7" t="n">
         <v>110</v>
@@ -1256,60 +1217,60 @@
         <v>142</v>
       </c>
       <c r="BL7" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B8" t="n">
-        <v>145.2</v>
+        <v>146.3</v>
       </c>
       <c r="D8" t="n">
-        <v>33.5</v>
+        <v>33.4</v>
       </c>
       <c r="F8" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="K8" t="n">
-        <v>100.3</v>
+        <v>98.2</v>
       </c>
       <c r="O8" t="n">
-        <v>35.5</v>
+        <v>35.1</v>
       </c>
       <c r="V8" t="n">
-        <v>7.1</v>
+        <v>4.9</v>
       </c>
       <c r="W8" t="n">
-        <v>19.2</v>
+        <v>16.4</v>
       </c>
       <c r="X8" t="n">
-        <v>13.1</v>
+        <v>10.6</v>
       </c>
       <c r="Y8" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z8" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB8" t="n">
-        <v>-5.4</v>
+        <v>-6.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.4</v>
+        <v>-0.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>-1.5</v>
+        <v>-3.3</v>
       </c>
       <c r="AF8" t="n">
-        <v>224.37</v>
+        <v>225.93</v>
       </c>
       <c r="AG8" t="n">
-        <v>3</v>
+        <v>1.56</v>
       </c>
       <c r="AH8" t="n">
         <v>215</v>
@@ -1318,10 +1279,10 @@
         <v>235</v>
       </c>
       <c r="AK8" t="n">
-        <v>135.61</v>
+        <v>135.28</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.4</v>
+        <v>-0.33</v>
       </c>
       <c r="AM8" t="n">
         <v>110</v>
@@ -1330,60 +1291,93 @@
         <v>142</v>
       </c>
       <c r="BL8" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B9" t="n">
-        <v>146.3</v>
+        <v>182.8</v>
+      </c>
+      <c r="C9" t="n">
+        <v>86.8</v>
       </c>
       <c r="D9" t="n">
-        <v>33.4</v>
+        <v>31.8</v>
+      </c>
+      <c r="E9" t="n">
+        <v>33</v>
       </c>
       <c r="F9" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
+      </c>
+      <c r="H9" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="I9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J9" t="n">
+        <v>41.1</v>
       </c>
       <c r="K9" t="n">
-        <v>98.2</v>
+        <v>74.2</v>
+      </c>
+      <c r="M9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="N9" t="n">
+        <v>33.5</v>
       </c>
       <c r="O9" t="n">
-        <v>35.1</v>
+        <v>38.4</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="n">
+        <v>22.4</v>
       </c>
       <c r="V9" t="n">
-        <v>4.9</v>
+        <v>9.1</v>
       </c>
       <c r="W9" t="n">
-        <v>16.4</v>
+        <v>15</v>
       </c>
       <c r="X9" t="n">
-        <v>10.6</v>
+        <v>12.1</v>
       </c>
       <c r="Y9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z9" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AA9" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>-6.4</v>
+        <v>-10.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>-3.3</v>
+        <v>-5.1</v>
       </c>
       <c r="AF9" t="n">
-        <v>225.93</v>
+        <v>218.63</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.56</v>
+        <v>-7.3</v>
       </c>
       <c r="AH9" t="n">
         <v>215</v>
@@ -1392,10 +1386,10 @@
         <v>235</v>
       </c>
       <c r="AK9" t="n">
-        <v>135.28</v>
+        <v>126.27</v>
       </c>
       <c r="AL9" t="n">
-        <v>-0.33</v>
+        <v>-9.01</v>
       </c>
       <c r="AM9" t="n">
         <v>110</v>
@@ -1403,94 +1397,100 @@
       <c r="AN9" t="n">
         <v>142</v>
       </c>
+      <c r="AP9" t="n">
+        <v>82.66</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>14.7</v>
+      </c>
       <c r="BL9" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B10" t="n">
-        <v>182.8</v>
+        <v>181.8</v>
       </c>
       <c r="C10" t="n">
-        <v>86.8</v>
+        <v>86.5</v>
       </c>
       <c r="D10" t="n">
-        <v>31.8</v>
+        <v>31.4</v>
       </c>
       <c r="E10" t="n">
-        <v>33</v>
+        <v>34.2</v>
       </c>
       <c r="F10" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="H10" t="n">
-        <v>23.5</v>
+        <v>24.4</v>
       </c>
       <c r="I10" t="n">
-        <v>9.6</v>
+        <v>10.4</v>
       </c>
       <c r="J10" t="n">
-        <v>41.1</v>
+        <v>41.9</v>
       </c>
       <c r="K10" t="n">
-        <v>74.2</v>
+        <v>76.8</v>
       </c>
       <c r="M10" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="N10" t="n">
-        <v>33.5</v>
+        <v>35.7</v>
       </c>
       <c r="O10" t="n">
-        <v>38.4</v>
+        <v>39.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>22.4</v>
+        <v>23</v>
       </c>
       <c r="R10" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>20.1</v>
       </c>
       <c r="T10" t="n">
-        <v>22.4</v>
+        <v>23</v>
       </c>
       <c r="V10" t="n">
-        <v>9.1</v>
+        <v>7.1</v>
       </c>
       <c r="W10" t="n">
-        <v>15</v>
+        <v>14.8</v>
       </c>
       <c r="X10" t="n">
-        <v>12.1</v>
+        <v>10.9</v>
       </c>
       <c r="Y10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z10" t="n">
         <v>12</v>
       </c>
       <c r="AA10" t="n">
-        <v>8.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AB10" t="n">
-        <v>-10.5</v>
+        <v>-4.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>-5.1</v>
+        <v>-1.4</v>
       </c>
       <c r="AF10" t="n">
-        <v>218.63</v>
+        <v>216.39</v>
       </c>
       <c r="AG10" t="n">
-        <v>-7.3</v>
+        <v>-2.23</v>
       </c>
       <c r="AH10" t="n">
         <v>215</v>
@@ -1499,10 +1499,10 @@
         <v>235</v>
       </c>
       <c r="AK10" t="n">
-        <v>126.27</v>
+        <v>123.32</v>
       </c>
       <c r="AL10" t="n">
-        <v>-9.01</v>
+        <v>-2.95</v>
       </c>
       <c r="AM10" t="n">
         <v>110</v>
@@ -1511,99 +1511,99 @@
         <v>142</v>
       </c>
       <c r="AP10" t="n">
-        <v>82.66</v>
+        <v>79.08</v>
       </c>
       <c r="AS10" t="n">
-        <v>14.7</v>
+        <v>13.91</v>
       </c>
       <c r="BL10" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B11" t="n">
-        <v>181.8</v>
+        <v>183</v>
       </c>
       <c r="C11" t="n">
-        <v>86.5</v>
+        <v>84.7</v>
       </c>
       <c r="D11" t="n">
-        <v>31.4</v>
+        <v>30.9</v>
       </c>
       <c r="E11" t="n">
-        <v>34.2</v>
+        <v>33.7</v>
       </c>
       <c r="F11" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="H11" t="n">
-        <v>24.4</v>
+        <v>23.4</v>
       </c>
       <c r="I11" t="n">
-        <v>10.4</v>
+        <v>10.6</v>
       </c>
       <c r="J11" t="n">
-        <v>41.9</v>
+        <v>42.3</v>
       </c>
       <c r="K11" t="n">
-        <v>76.8</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="N11" t="n">
-        <v>35.7</v>
+        <v>36.7</v>
       </c>
       <c r="O11" t="n">
-        <v>39.8</v>
+        <v>40.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>23</v>
+        <v>23.6</v>
       </c>
       <c r="R11" t="n">
         <v>1.8</v>
       </c>
       <c r="S11" t="n">
-        <v>20.1</v>
+        <v>20.8</v>
       </c>
       <c r="T11" t="n">
-        <v>23</v>
+        <v>23.6</v>
       </c>
       <c r="V11" t="n">
-        <v>7.1</v>
+        <v>5.7</v>
       </c>
       <c r="W11" t="n">
-        <v>14.8</v>
+        <v>16.1</v>
       </c>
       <c r="X11" t="n">
         <v>10.9</v>
       </c>
       <c r="Y11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA11" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AB11" t="n">
-        <v>-4.5</v>
+        <v>0.8</v>
       </c>
       <c r="AC11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD11" t="n">
         <v>1.8</v>
       </c>
-      <c r="AD11" t="n">
-        <v>-1.4</v>
-      </c>
       <c r="AF11" t="n">
-        <v>216.39</v>
+        <v>217.16</v>
       </c>
       <c r="AG11" t="n">
-        <v>-2.23</v>
+        <v>0.76</v>
       </c>
       <c r="AH11" t="n">
         <v>215</v>
@@ -1612,10 +1612,10 @@
         <v>235</v>
       </c>
       <c r="AK11" t="n">
-        <v>123.32</v>
+        <v>117.87</v>
       </c>
       <c r="AL11" t="n">
-        <v>-2.95</v>
+        <v>-5.45</v>
       </c>
       <c r="AM11" t="n">
         <v>110</v>
@@ -1624,99 +1624,66 @@
         <v>142</v>
       </c>
       <c r="AP11" t="n">
-        <v>79.08</v>
+        <v>78.56</v>
       </c>
       <c r="AS11" t="n">
-        <v>13.91</v>
+        <v>13.45</v>
       </c>
       <c r="BL11" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B12" t="n">
-        <v>183</v>
-      </c>
-      <c r="C12" t="n">
-        <v>84.7</v>
+        <v>163.8</v>
       </c>
       <c r="D12" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="E12" t="n">
-        <v>33.7</v>
+        <v>29</v>
       </c>
       <c r="F12" t="n">
-        <v>7</v>
-      </c>
-      <c r="H12" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="I12" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="J12" t="n">
-        <v>42.3</v>
+        <v>6.5</v>
       </c>
       <c r="K12" t="n">
-        <v>76.40000000000001</v>
-      </c>
-      <c r="M12" t="n">
-        <v>4</v>
-      </c>
-      <c r="N12" t="n">
-        <v>36.7</v>
+        <v>101.2</v>
       </c>
       <c r="O12" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S12" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="T12" t="n">
-        <v>23.6</v>
+        <v>40.2</v>
       </c>
       <c r="V12" t="n">
-        <v>5.7</v>
+        <v>6.3</v>
       </c>
       <c r="W12" t="n">
-        <v>16.1</v>
+        <v>17.2</v>
       </c>
       <c r="X12" t="n">
-        <v>10.9</v>
+        <v>11.8</v>
       </c>
       <c r="Y12" t="n">
         <v>8</v>
       </c>
       <c r="Z12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA12" t="n">
         <v>10</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.7</v>
+        <v>4.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="AF12" t="n">
-        <v>217.16</v>
+        <v>220.31</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.76</v>
+        <v>3.16</v>
       </c>
       <c r="AH12" t="n">
         <v>215</v>
@@ -1725,10 +1692,10 @@
         <v>235</v>
       </c>
       <c r="AK12" t="n">
-        <v>117.87</v>
+        <v>116.52</v>
       </c>
       <c r="AL12" t="n">
-        <v>-5.45</v>
+        <v>-1.35</v>
       </c>
       <c r="AM12" t="n">
         <v>110</v>
@@ -1736,67 +1703,61 @@
       <c r="AN12" t="n">
         <v>142</v>
       </c>
-      <c r="AP12" t="n">
-        <v>78.56</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>13.45</v>
-      </c>
       <c r="BL12" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B13" t="n">
-        <v>163.8</v>
+        <v>155.9</v>
       </c>
       <c r="D13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F13" t="n">
         <v>6.5</v>
       </c>
       <c r="K13" t="n">
-        <v>101.2</v>
+        <v>99.3</v>
       </c>
       <c r="O13" t="n">
-        <v>40.2</v>
+        <v>38.5</v>
       </c>
       <c r="V13" t="n">
-        <v>6.3</v>
+        <v>8.9</v>
       </c>
       <c r="W13" t="n">
-        <v>17.2</v>
+        <v>15.8</v>
       </c>
       <c r="X13" t="n">
-        <v>11.8</v>
+        <v>12.4</v>
       </c>
       <c r="Y13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA13" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="AF13" t="n">
-        <v>220.31</v>
+        <v>221.99</v>
       </c>
       <c r="AG13" t="n">
-        <v>3.16</v>
+        <v>1.67</v>
       </c>
       <c r="AH13" t="n">
         <v>215</v>
@@ -1805,10 +1766,10 @@
         <v>235</v>
       </c>
       <c r="AK13" t="n">
-        <v>116.52</v>
+        <v>116.37</v>
       </c>
       <c r="AL13" t="n">
-        <v>-1.35</v>
+        <v>-0.15</v>
       </c>
       <c r="AM13" t="n">
         <v>110</v>
@@ -1817,60 +1778,60 @@
         <v>142</v>
       </c>
       <c r="BL13" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B14" t="n">
-        <v>155.9</v>
+        <v>141.3</v>
       </c>
       <c r="D14" t="n">
-        <v>28</v>
+        <v>26.3</v>
       </c>
       <c r="F14" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="K14" t="n">
-        <v>99.3</v>
+        <v>97.8</v>
       </c>
       <c r="O14" t="n">
-        <v>38.5</v>
+        <v>39.8</v>
       </c>
       <c r="V14" t="n">
-        <v>8.9</v>
+        <v>9.5</v>
       </c>
       <c r="W14" t="n">
-        <v>15.8</v>
+        <v>17.7</v>
       </c>
       <c r="X14" t="n">
-        <v>12.4</v>
+        <v>13.6</v>
       </c>
       <c r="Y14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Z14" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA14" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.7</v>
+        <v>7.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="AF14" t="n">
-        <v>221.99</v>
+        <v>225.14</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.67</v>
+        <v>3.15</v>
       </c>
       <c r="AH14" t="n">
         <v>215</v>
@@ -1878,12 +1839,6 @@
       <c r="AI14" t="n">
         <v>235</v>
       </c>
-      <c r="AK14" t="n">
-        <v>116.37</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>-0.15</v>
-      </c>
       <c r="AM14" t="n">
         <v>110</v>
       </c>
@@ -1891,60 +1846,54 @@
         <v>142</v>
       </c>
       <c r="BL14" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B15" t="n">
-        <v>141.3</v>
+        <v>131.5</v>
       </c>
       <c r="D15" t="n">
-        <v>26.3</v>
+        <v>27.3</v>
       </c>
       <c r="F15" t="n">
         <v>5.5</v>
       </c>
       <c r="K15" t="n">
-        <v>97.8</v>
+        <v>97</v>
       </c>
       <c r="O15" t="n">
-        <v>39.8</v>
+        <v>35.7</v>
       </c>
       <c r="V15" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="W15" t="n">
-        <v>17.7</v>
+        <v>13.9</v>
       </c>
       <c r="X15" t="n">
-        <v>13.6</v>
+        <v>11.4</v>
       </c>
       <c r="Y15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z15" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA15" t="n">
         <v>15</v>
       </c>
-      <c r="AA15" t="n">
-        <v>14</v>
-      </c>
       <c r="AB15" t="n">
-        <v>0.2</v>
+        <v>-3.6</v>
       </c>
       <c r="AC15" t="n">
-        <v>7.5</v>
+        <v>2.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>225.14</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>3.15</v>
+        <v>-0.4</v>
       </c>
       <c r="AH15" t="n">
         <v>215</v>
@@ -1959,54 +1908,93 @@
         <v>142</v>
       </c>
       <c r="BL15" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="B16" t="n">
-        <v>131.5</v>
+        <v>153</v>
+      </c>
+      <c r="C16" t="n">
+        <v>71.8</v>
       </c>
       <c r="D16" t="n">
-        <v>27.3</v>
+        <v>28.6</v>
+      </c>
+      <c r="E16" t="n">
+        <v>24.7</v>
       </c>
       <c r="F16" t="n">
-        <v>5.5</v>
+        <v>4</v>
+      </c>
+      <c r="H16" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J16" t="n">
+        <v>41.1</v>
       </c>
       <c r="K16" t="n">
-        <v>97</v>
+        <v>75.90000000000001</v>
+      </c>
+      <c r="M16" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N16" t="n">
+        <v>33.5</v>
       </c>
       <c r="O16" t="n">
-        <v>35.7</v>
+        <v>38.3</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>23.2</v>
       </c>
       <c r="V16" t="n">
-        <v>9</v>
+        <v>11.2</v>
       </c>
       <c r="W16" t="n">
-        <v>13.9</v>
+        <v>13</v>
       </c>
       <c r="X16" t="n">
-        <v>11.4</v>
+        <v>12.1</v>
       </c>
       <c r="Y16" t="n">
         <v>12</v>
       </c>
       <c r="Z16" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AA16" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>-3.6</v>
+        <v>-6.6</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.8</v>
+        <v>5.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>-0.4</v>
+        <v>-0.6</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>229.96</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>-0.02</v>
       </c>
       <c r="AH16" t="n">
         <v>215</v>
@@ -2014,100 +2002,112 @@
       <c r="AI16" t="n">
         <v>235</v>
       </c>
+      <c r="AK16" t="n">
+        <v>128.14</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>11.77</v>
+      </c>
       <c r="AM16" t="n">
         <v>110</v>
       </c>
       <c r="AN16" t="n">
         <v>142</v>
       </c>
+      <c r="AP16" t="n">
+        <v>87.47</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>14.8</v>
+      </c>
       <c r="BL16" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B17" t="n">
-        <v>153</v>
+        <v>165.8</v>
       </c>
       <c r="C17" t="n">
-        <v>71.8</v>
+        <v>77.3</v>
       </c>
       <c r="D17" t="n">
-        <v>28.6</v>
+        <v>29.3</v>
       </c>
       <c r="E17" t="n">
-        <v>24.7</v>
+        <v>27.7</v>
       </c>
       <c r="F17" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="H17" t="n">
         <v>24.1</v>
       </c>
       <c r="I17" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="J17" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="K17" t="n">
-        <v>75.90000000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="N17" t="n">
-        <v>33.5</v>
+        <v>35.1</v>
       </c>
       <c r="O17" t="n">
-        <v>38.3</v>
+        <v>39.8</v>
       </c>
       <c r="Q17" t="n">
-        <v>23.2</v>
+        <v>23.8</v>
       </c>
       <c r="R17" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="T17" t="n">
-        <v>23.2</v>
+        <v>23.8</v>
       </c>
       <c r="V17" t="n">
-        <v>11.2</v>
+        <v>9.4</v>
       </c>
       <c r="W17" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="X17" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z17" t="n">
         <v>13</v>
       </c>
-      <c r="X17" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>14</v>
-      </c>
       <c r="AA17" t="n">
-        <v>12.5</v>
+        <v>10.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>-6.6</v>
+        <v>-0.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>5.3</v>
+        <v>9.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>-0.6</v>
+        <v>4.4</v>
       </c>
       <c r="AF17" t="n">
-        <v>229.96</v>
+        <v>227.01</v>
       </c>
       <c r="AG17" t="n">
-        <v>-0.02</v>
+        <v>-2.95</v>
       </c>
       <c r="AH17" t="n">
         <v>215</v>
@@ -2116,10 +2116,10 @@
         <v>235</v>
       </c>
       <c r="AK17" t="n">
-        <v>128.14</v>
+        <v>128.15</v>
       </c>
       <c r="AL17" t="n">
-        <v>11.77</v>
+        <v>0.01</v>
       </c>
       <c r="AM17" t="n">
         <v>110</v>
@@ -2128,99 +2128,99 @@
         <v>142</v>
       </c>
       <c r="AP17" t="n">
-        <v>87.47</v>
+        <v>83.41</v>
       </c>
       <c r="AS17" t="n">
-        <v>14.8</v>
+        <v>14.52</v>
       </c>
       <c r="BL17" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B18" t="n">
-        <v>165.8</v>
+        <v>158.1</v>
       </c>
       <c r="C18" t="n">
-        <v>77.3</v>
+        <v>73.7</v>
       </c>
       <c r="D18" t="n">
-        <v>29.3</v>
+        <v>30.3</v>
       </c>
       <c r="E18" t="n">
-        <v>27.7</v>
+        <v>26</v>
       </c>
       <c r="F18" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="H18" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="I18" t="n">
-        <v>10.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>41.6</v>
+        <v>40.9</v>
       </c>
       <c r="K18" t="n">
-        <v>76.59999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="N18" t="n">
-        <v>35.1</v>
+        <v>35.3</v>
       </c>
       <c r="O18" t="n">
-        <v>39.8</v>
+        <v>40.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S18" t="n">
         <v>7</v>
       </c>
       <c r="T18" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="V18" t="n">
-        <v>9.4</v>
+        <v>8.9</v>
       </c>
       <c r="W18" t="n">
-        <v>17.4</v>
+        <v>19.3</v>
       </c>
       <c r="X18" t="n">
-        <v>13.4</v>
+        <v>14.1</v>
       </c>
       <c r="Y18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z18" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA18" t="n">
-        <v>10.1</v>
+        <v>11</v>
       </c>
       <c r="AB18" t="n">
-        <v>-0.7</v>
+        <v>4.4</v>
       </c>
       <c r="AC18" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>4.4</v>
+        <v>6.5</v>
       </c>
       <c r="AF18" t="n">
-        <v>227.01</v>
+        <v>228.35</v>
       </c>
       <c r="AG18" t="n">
-        <v>-2.95</v>
+        <v>1.33</v>
       </c>
       <c r="AH18" t="n">
         <v>215</v>
@@ -2229,10 +2229,10 @@
         <v>235</v>
       </c>
       <c r="AK18" t="n">
-        <v>128.15</v>
+        <v>128.86</v>
       </c>
       <c r="AL18" t="n">
-        <v>0.01</v>
+        <v>0.71</v>
       </c>
       <c r="AM18" t="n">
         <v>110</v>
@@ -2241,99 +2241,99 @@
         <v>142</v>
       </c>
       <c r="AP18" t="n">
-        <v>83.41</v>
+        <v>82.37</v>
       </c>
       <c r="AS18" t="n">
-        <v>14.52</v>
+        <v>14.22</v>
       </c>
       <c r="BL18" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B19" t="n">
-        <v>158.1</v>
+        <v>154.9</v>
       </c>
       <c r="C19" t="n">
-        <v>73.7</v>
+        <v>70.2</v>
       </c>
       <c r="D19" t="n">
-        <v>30.3</v>
+        <v>31.5</v>
       </c>
       <c r="E19" t="n">
-        <v>26</v>
+        <v>27.7</v>
       </c>
       <c r="F19" t="n">
-        <v>4.1</v>
+        <v>2.7</v>
       </c>
       <c r="H19" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="I19" t="n">
-        <v>9.300000000000001</v>
+        <v>11.3</v>
       </c>
       <c r="J19" t="n">
-        <v>40.9</v>
+        <v>40.3</v>
       </c>
       <c r="K19" t="n">
-        <v>74.40000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="M19" t="n">
-        <v>5</v>
+        <v>6.1</v>
       </c>
       <c r="N19" t="n">
-        <v>35.3</v>
+        <v>32.9</v>
       </c>
       <c r="O19" t="n">
-        <v>40.3</v>
+        <v>39</v>
       </c>
       <c r="Q19" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="R19" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="T19" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="V19" t="n">
-        <v>8.9</v>
+        <v>6.3</v>
       </c>
       <c r="W19" t="n">
-        <v>19.3</v>
+        <v>25.2</v>
       </c>
       <c r="X19" t="n">
-        <v>14.1</v>
+        <v>15.8</v>
       </c>
       <c r="Y19" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z19" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA19" t="n">
-        <v>11</v>
+        <v>12.6</v>
       </c>
       <c r="AB19" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="AC19" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="AF19" t="n">
-        <v>228.35</v>
+        <v>231.16</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.33</v>
+        <v>2.81</v>
       </c>
       <c r="AH19" t="n">
         <v>215</v>
@@ -2342,10 +2342,10 @@
         <v>235</v>
       </c>
       <c r="AK19" t="n">
-        <v>128.86</v>
+        <v>130.88</v>
       </c>
       <c r="AL19" t="n">
-        <v>0.71</v>
+        <v>2.02</v>
       </c>
       <c r="AM19" t="n">
         <v>110</v>
@@ -2354,99 +2354,66 @@
         <v>142</v>
       </c>
       <c r="AP19" t="n">
-        <v>82.37</v>
+        <v>85.48999999999999</v>
       </c>
       <c r="AS19" t="n">
-        <v>14.22</v>
+        <v>13.1</v>
       </c>
       <c r="BL19" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B20" t="n">
-        <v>154.9</v>
-      </c>
-      <c r="C20" t="n">
-        <v>70.2</v>
+        <v>152.2</v>
       </c>
       <c r="D20" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="E20" t="n">
-        <v>27.7</v>
+        <v>31</v>
       </c>
       <c r="F20" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="H20" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I20" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J20" t="n">
-        <v>40.3</v>
+        <v>3.5</v>
       </c>
       <c r="K20" t="n">
-        <v>75.8</v>
-      </c>
-      <c r="M20" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="N20" t="n">
-        <v>32.9</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>39</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="R20" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="S20" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="T20" t="n">
-        <v>23.7</v>
+        <v>34.4</v>
       </c>
       <c r="V20" t="n">
-        <v>6.3</v>
+        <v>9.5</v>
       </c>
       <c r="W20" t="n">
-        <v>25.2</v>
+        <v>25.5</v>
       </c>
       <c r="X20" t="n">
-        <v>15.8</v>
+        <v>17.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Z20" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AA20" t="n">
-        <v>12.6</v>
+        <v>9</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.9</v>
+        <v>-1.1</v>
       </c>
       <c r="AC20" t="n">
         <v>8.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>5.8</v>
+        <v>3.8</v>
       </c>
       <c r="AF20" t="n">
-        <v>231.16</v>
+        <v>228.13</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.81</v>
+        <v>-3.03</v>
       </c>
       <c r="AH20" t="n">
         <v>215</v>
@@ -2454,79 +2421,67 @@
       <c r="AI20" t="n">
         <v>235</v>
       </c>
-      <c r="AK20" t="n">
-        <v>130.88</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AM20" t="n">
         <v>110</v>
       </c>
       <c r="AN20" t="n">
         <v>142</v>
       </c>
-      <c r="AP20" t="n">
-        <v>85.48999999999999</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>13.1</v>
-      </c>
       <c r="BL20" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B21" t="n">
-        <v>152.2</v>
+        <v>143.9</v>
       </c>
       <c r="D21" t="n">
-        <v>31</v>
+        <v>30.8</v>
       </c>
       <c r="F21" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="K21" t="n">
-        <v>98.40000000000001</v>
+        <v>99.2</v>
       </c>
       <c r="O21" t="n">
-        <v>34.4</v>
+        <v>35.2</v>
       </c>
       <c r="V21" t="n">
-        <v>9.5</v>
+        <v>10.7</v>
       </c>
       <c r="W21" t="n">
-        <v>25.5</v>
+        <v>17.6</v>
       </c>
       <c r="X21" t="n">
-        <v>17.5</v>
+        <v>14.2</v>
       </c>
       <c r="Y21" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Z21" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA21" t="n">
         <v>9</v>
       </c>
       <c r="AB21" t="n">
-        <v>-1.1</v>
+        <v>-0.8</v>
       </c>
       <c r="AC21" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AF21" t="n">
-        <v>228.13</v>
+        <v>229.16</v>
       </c>
       <c r="AG21" t="n">
-        <v>-3.03</v>
+        <v>1.03</v>
       </c>
       <c r="AH21" t="n">
         <v>215</v>
@@ -2541,60 +2496,93 @@
         <v>142</v>
       </c>
       <c r="BL21" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B22" t="n">
-        <v>143.9</v>
+        <v>163.2</v>
+      </c>
+      <c r="C22" t="n">
+        <v>73.7</v>
       </c>
       <c r="D22" t="n">
-        <v>30.8</v>
+        <v>30</v>
+      </c>
+      <c r="E22" t="n">
+        <v>28.2</v>
       </c>
       <c r="F22" t="n">
-        <v>2.5</v>
+        <v>4.8</v>
+      </c>
+      <c r="H22" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J22" t="n">
+        <v>40.1</v>
       </c>
       <c r="K22" t="n">
-        <v>99.2</v>
+        <v>75.59999999999999</v>
+      </c>
+      <c r="M22" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="N22" t="n">
+        <v>32.9</v>
       </c>
       <c r="O22" t="n">
-        <v>35.2</v>
+        <v>39.7</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="R22" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="S22" t="n">
+        <v>6</v>
+      </c>
+      <c r="T22" t="n">
+        <v>23.5</v>
       </c>
       <c r="V22" t="n">
-        <v>10.7</v>
+        <v>9.4</v>
       </c>
       <c r="W22" t="n">
-        <v>17.6</v>
+        <v>20.1</v>
       </c>
       <c r="X22" t="n">
-        <v>14.2</v>
+        <v>14.8</v>
       </c>
       <c r="Y22" t="n">
         <v>4</v>
       </c>
       <c r="Z22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA22" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AB22" t="n">
-        <v>-0.8</v>
+        <v>-0.9</v>
       </c>
       <c r="AC22" t="n">
-        <v>8.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AF22" t="n">
-        <v>229.16</v>
+        <v>228.55</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.03</v>
+        <v>-0.61</v>
       </c>
       <c r="AH22" t="n">
         <v>215</v>
@@ -2602,100 +2590,112 @@
       <c r="AI22" t="n">
         <v>235</v>
       </c>
+      <c r="AK22" t="n">
+        <v>127.06</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>-3.82</v>
+      </c>
       <c r="AM22" t="n">
         <v>110</v>
       </c>
       <c r="AN22" t="n">
         <v>142</v>
       </c>
+      <c r="AP22" t="n">
+        <v>82.81</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>12.9</v>
+      </c>
       <c r="BL22" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="B23" t="n">
-        <v>163.2</v>
+        <v>174.4</v>
       </c>
       <c r="C23" t="n">
-        <v>73.7</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="D23" t="n">
-        <v>30</v>
+        <v>32.1</v>
       </c>
       <c r="E23" t="n">
-        <v>28.2</v>
+        <v>30.8</v>
       </c>
       <c r="F23" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="H23" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="I23" t="n">
-        <v>11.4</v>
+        <v>10.5</v>
       </c>
       <c r="J23" t="n">
-        <v>40.1</v>
+        <v>39.5</v>
       </c>
       <c r="K23" t="n">
-        <v>75.59999999999999</v>
+        <v>74</v>
       </c>
       <c r="M23" t="n">
         <v>6.8</v>
       </c>
       <c r="N23" t="n">
-        <v>32.9</v>
+        <v>35.8</v>
       </c>
       <c r="O23" t="n">
-        <v>39.7</v>
+        <v>42.6</v>
       </c>
       <c r="Q23" t="n">
-        <v>23.5</v>
+        <v>23.1</v>
       </c>
       <c r="R23" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="S23" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="T23" t="n">
-        <v>23.5</v>
+        <v>23.1</v>
       </c>
       <c r="V23" t="n">
-        <v>9.4</v>
+        <v>12.8</v>
       </c>
       <c r="W23" t="n">
-        <v>20.1</v>
+        <v>22.1</v>
       </c>
       <c r="X23" t="n">
-        <v>14.8</v>
+        <v>17.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Z23" t="n">
         <v>13</v>
       </c>
       <c r="AA23" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AC23" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="AB23" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>9.5</v>
-      </c>
       <c r="AD23" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AF23" t="n">
-        <v>228.55</v>
+        <v>219.99</v>
       </c>
       <c r="AG23" t="n">
-        <v>-0.61</v>
+        <v>-8.56</v>
       </c>
       <c r="AH23" t="n">
         <v>215</v>
@@ -2704,10 +2704,10 @@
         <v>235</v>
       </c>
       <c r="AK23" t="n">
-        <v>127.06</v>
+        <v>125.61</v>
       </c>
       <c r="AL23" t="n">
-        <v>-3.82</v>
+        <v>-1.45</v>
       </c>
       <c r="AM23" t="n">
         <v>110</v>
@@ -2716,99 +2716,99 @@
         <v>142</v>
       </c>
       <c r="AP23" t="n">
-        <v>82.81</v>
+        <v>77.83</v>
       </c>
       <c r="AS23" t="n">
-        <v>12.9</v>
+        <v>12.96</v>
       </c>
       <c r="BL23" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B24" t="n">
-        <v>174.4</v>
+        <v>163.2</v>
       </c>
       <c r="C24" t="n">
-        <v>75.40000000000001</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="D24" t="n">
-        <v>32.1</v>
+        <v>32.9</v>
       </c>
       <c r="E24" t="n">
-        <v>30.8</v>
+        <v>26</v>
       </c>
       <c r="F24" t="n">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="H24" t="n">
-        <v>24</v>
+        <v>23.8</v>
       </c>
       <c r="I24" t="n">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="J24" t="n">
-        <v>39.5</v>
+        <v>40.1</v>
       </c>
       <c r="K24" t="n">
-        <v>74</v>
+        <v>71.3</v>
       </c>
       <c r="M24" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="N24" t="n">
-        <v>35.8</v>
+        <v>34.3</v>
       </c>
       <c r="O24" t="n">
-        <v>42.6</v>
+        <v>41.5</v>
       </c>
       <c r="Q24" t="n">
         <v>23.1</v>
       </c>
       <c r="R24" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="S24" t="n">
-        <v>8.5</v>
+        <v>6.2</v>
       </c>
       <c r="T24" t="n">
         <v>23.1</v>
       </c>
       <c r="V24" t="n">
-        <v>12.8</v>
+        <v>9.6</v>
       </c>
       <c r="W24" t="n">
-        <v>22.1</v>
+        <v>23.3</v>
       </c>
       <c r="X24" t="n">
-        <v>17.5</v>
+        <v>16.4</v>
       </c>
       <c r="Y24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z24" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA24" t="n">
-        <v>10.1</v>
+        <v>12.2</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.3</v>
+        <v>2.6</v>
       </c>
       <c r="AC24" t="n">
-        <v>9.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AF24" t="n">
-        <v>219.99</v>
+        <v>219.22</v>
       </c>
       <c r="AG24" t="n">
-        <v>-8.56</v>
+        <v>-0.77</v>
       </c>
       <c r="AH24" t="n">
         <v>215</v>
@@ -2817,10 +2817,10 @@
         <v>235</v>
       </c>
       <c r="AK24" t="n">
-        <v>125.61</v>
+        <v>124.36</v>
       </c>
       <c r="AL24" t="n">
-        <v>-1.45</v>
+        <v>-1.25</v>
       </c>
       <c r="AM24" t="n">
         <v>110</v>
@@ -2829,99 +2829,99 @@
         <v>142</v>
       </c>
       <c r="AP24" t="n">
-        <v>77.83</v>
+        <v>76.81</v>
       </c>
       <c r="AS24" t="n">
-        <v>12.96</v>
+        <v>12.38</v>
       </c>
       <c r="BL24" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B25" t="n">
-        <v>163.2</v>
+        <v>152.7</v>
       </c>
       <c r="C25" t="n">
-        <v>70.90000000000001</v>
+        <v>62.6</v>
       </c>
       <c r="D25" t="n">
-        <v>32.9</v>
+        <v>32.7</v>
       </c>
       <c r="E25" t="n">
-        <v>26</v>
+        <v>24.6</v>
       </c>
       <c r="F25" t="n">
-        <v>6.9</v>
+        <v>5.2</v>
       </c>
       <c r="H25" t="n">
         <v>23.8</v>
       </c>
       <c r="I25" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J25" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="K25" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="M25" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="N25" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="O25" t="n">
         <v>40.1</v>
       </c>
-      <c r="K25" t="n">
-        <v>71.3</v>
-      </c>
-      <c r="M25" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="N25" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="O25" t="n">
-        <v>41.5</v>
-      </c>
       <c r="Q25" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="R25" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="S25" t="n">
-        <v>6.2</v>
+        <v>4</v>
       </c>
       <c r="T25" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="V25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="W25" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="X25" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC25" t="n">
         <v>9.6</v>
       </c>
-      <c r="W25" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="X25" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>8.5</v>
-      </c>
       <c r="AD25" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AF25" t="n">
-        <v>219.22</v>
+        <v>220.73</v>
       </c>
       <c r="AG25" t="n">
-        <v>-0.77</v>
+        <v>1.5</v>
       </c>
       <c r="AH25" t="n">
         <v>215</v>
@@ -2930,10 +2930,10 @@
         <v>235</v>
       </c>
       <c r="AK25" t="n">
-        <v>124.36</v>
+        <v>120.93</v>
       </c>
       <c r="AL25" t="n">
-        <v>-1.25</v>
+        <v>-3.43</v>
       </c>
       <c r="AM25" t="n">
         <v>110</v>
@@ -2942,75 +2942,75 @@
         <v>142</v>
       </c>
       <c r="AP25" t="n">
-        <v>76.81</v>
+        <v>77.87</v>
       </c>
       <c r="AS25" t="n">
-        <v>12.38</v>
+        <v>13.26</v>
       </c>
       <c r="BL25" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B26" t="n">
-        <v>152.7</v>
+        <v>150.7</v>
       </c>
       <c r="C26" t="n">
-        <v>62.6</v>
+        <v>64.8</v>
       </c>
       <c r="D26" t="n">
-        <v>32.7</v>
+        <v>33.7</v>
       </c>
       <c r="E26" t="n">
-        <v>24.6</v>
+        <v>27.1</v>
       </c>
       <c r="F26" t="n">
-        <v>5.2</v>
+        <v>3.8</v>
       </c>
       <c r="H26" t="n">
-        <v>23.8</v>
+        <v>23.4</v>
       </c>
       <c r="I26" t="n">
         <v>7.2</v>
       </c>
       <c r="J26" t="n">
-        <v>38.9</v>
+        <v>39.9</v>
       </c>
       <c r="K26" t="n">
-        <v>69.90000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="M26" t="n">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="N26" t="n">
-        <v>33.5</v>
+        <v>33</v>
       </c>
       <c r="O26" t="n">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="Q26" t="n">
         <v>23.2</v>
       </c>
       <c r="R26" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T26" t="n">
         <v>23.2</v>
       </c>
       <c r="V26" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="W26" t="n">
-        <v>27.3</v>
+        <v>28.9</v>
       </c>
       <c r="X26" t="n">
-        <v>19.4</v>
+        <v>21.7</v>
       </c>
       <c r="Y26" t="n">
         <v>10</v>
@@ -3019,22 +3019,22 @@
         <v>18</v>
       </c>
       <c r="AA26" t="n">
-        <v>14</v>
+        <v>13.1</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>9.6</v>
+        <v>10.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>5.7</v>
+        <v>6.7</v>
       </c>
       <c r="AF26" t="n">
-        <v>220.73</v>
+        <v>220.58</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.5</v>
+        <v>-0.15</v>
       </c>
       <c r="AH26" t="n">
         <v>215</v>
@@ -3043,10 +3043,10 @@
         <v>235</v>
       </c>
       <c r="AK26" t="n">
-        <v>120.93</v>
+        <v>120.28</v>
       </c>
       <c r="AL26" t="n">
-        <v>-3.43</v>
+        <v>-0.65</v>
       </c>
       <c r="AM26" t="n">
         <v>110</v>
@@ -3055,99 +3055,54 @@
         <v>142</v>
       </c>
       <c r="AP26" t="n">
-        <v>77.87</v>
+        <v>77.22</v>
       </c>
       <c r="AS26" t="n">
-        <v>13.26</v>
+        <v>13.79</v>
       </c>
       <c r="BL26" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B27" t="n">
-        <v>150.7</v>
-      </c>
-      <c r="C27" t="n">
-        <v>64.8</v>
+        <v>138.2</v>
       </c>
       <c r="D27" t="n">
-        <v>33.7</v>
-      </c>
-      <c r="E27" t="n">
-        <v>27.1</v>
+        <v>33.6</v>
       </c>
       <c r="F27" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H27" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="V27" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="W27" t="n">
         <v>23.4</v>
       </c>
-      <c r="I27" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="J27" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="K27" t="n">
-        <v>70.5</v>
-      </c>
-      <c r="M27" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="N27" t="n">
-        <v>33</v>
-      </c>
-      <c r="O27" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="R27" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="S27" t="n">
-        <v>3</v>
-      </c>
-      <c r="T27" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="V27" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="W27" t="n">
-        <v>28.9</v>
-      </c>
       <c r="X27" t="n">
-        <v>21.7</v>
+        <v>19.4</v>
       </c>
       <c r="Y27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z27" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AA27" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="AC27" t="n">
-        <v>10.8</v>
+        <v>8.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>220.58</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>-0.15</v>
+        <v>4.5</v>
       </c>
       <c r="AH27" t="n">
         <v>215</v>
@@ -3155,67 +3110,61 @@
       <c r="AI27" t="n">
         <v>235</v>
       </c>
-      <c r="AK27" t="n">
-        <v>120.28</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>-0.65</v>
-      </c>
       <c r="AM27" t="n">
         <v>110</v>
       </c>
       <c r="AN27" t="n">
         <v>142</v>
       </c>
-      <c r="AP27" t="n">
-        <v>77.22</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>13.79</v>
-      </c>
       <c r="BL27" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B28" t="n">
-        <v>138.2</v>
+        <v>126.5</v>
       </c>
       <c r="D28" t="n">
-        <v>33.6</v>
+        <v>33.2</v>
       </c>
       <c r="F28" t="n">
-        <v>6.1</v>
+        <v>3.4</v>
       </c>
       <c r="V28" t="n">
-        <v>15.5</v>
+        <v>12.6</v>
       </c>
       <c r="W28" t="n">
-        <v>23.4</v>
+        <v>22.3</v>
       </c>
       <c r="X28" t="n">
-        <v>19.4</v>
+        <v>17.4</v>
       </c>
       <c r="Y28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA28" t="n">
         <v>13</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>8.5</v>
+        <v>6.7</v>
       </c>
       <c r="AD28" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>229.48</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>6.05</v>
       </c>
       <c r="AH28" t="n">
         <v>215</v>
@@ -3230,54 +3179,93 @@
         <v>142</v>
       </c>
       <c r="BL28" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B29" t="n">
-        <v>126.5</v>
+        <v>129.4</v>
+      </c>
+      <c r="C29" t="n">
+        <v>50.6</v>
       </c>
       <c r="D29" t="n">
-        <v>33.2</v>
+        <v>31.5</v>
+      </c>
+      <c r="E29" t="n">
+        <v>19.4</v>
       </c>
       <c r="F29" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
+      </c>
+      <c r="H29" t="n">
+        <v>24</v>
+      </c>
+      <c r="I29" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J29" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="K29" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="M29" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N29" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="O29" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>21.4</v>
       </c>
       <c r="V29" t="n">
-        <v>12.6</v>
+        <v>14.3</v>
       </c>
       <c r="W29" t="n">
-        <v>22.3</v>
+        <v>23.9</v>
       </c>
       <c r="X29" t="n">
-        <v>17.4</v>
+        <v>19.1</v>
       </c>
       <c r="Y29" t="n">
         <v>8</v>
       </c>
       <c r="Z29" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AA29" t="n">
-        <v>13</v>
+        <v>16.1</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AC29" t="n">
-        <v>6.7</v>
+        <v>7.6</v>
       </c>
       <c r="AD29" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="AF29" t="n">
-        <v>229.48</v>
+        <v>229.5</v>
       </c>
       <c r="AG29" t="n">
-        <v>6.05</v>
+        <v>0.02</v>
       </c>
       <c r="AH29" t="n">
         <v>215</v>
@@ -3285,100 +3273,112 @@
       <c r="AI29" t="n">
         <v>235</v>
       </c>
+      <c r="AK29" t="n">
+        <v>128.37</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>8.09</v>
+      </c>
       <c r="AM29" t="n">
         <v>110</v>
       </c>
       <c r="AN29" t="n">
         <v>142</v>
       </c>
+      <c r="AP29" t="n">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>15.97</v>
+      </c>
       <c r="BL29" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="B30" t="n">
-        <v>129.4</v>
+        <v>142.9</v>
       </c>
       <c r="C30" t="n">
-        <v>50.6</v>
+        <v>52.7</v>
       </c>
       <c r="D30" t="n">
-        <v>31.5</v>
+        <v>34.7</v>
       </c>
       <c r="E30" t="n">
-        <v>19.4</v>
+        <v>24.8</v>
       </c>
       <c r="F30" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="H30" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I30" t="n">
-        <v>10.4</v>
+        <v>9.9</v>
       </c>
       <c r="J30" t="n">
-        <v>38.9</v>
+        <v>38.2</v>
       </c>
       <c r="K30" t="n">
-        <v>73.3</v>
+        <v>70</v>
       </c>
       <c r="M30" t="n">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="N30" t="n">
-        <v>33.3</v>
+        <v>31.9</v>
       </c>
       <c r="O30" t="n">
-        <v>38</v>
+        <v>35.8</v>
       </c>
       <c r="Q30" t="n">
-        <v>21.4</v>
+        <v>19.7</v>
       </c>
       <c r="R30" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>21.4</v>
+        <v>19.7</v>
       </c>
       <c r="V30" t="n">
-        <v>14.3</v>
+        <v>12</v>
       </c>
       <c r="W30" t="n">
-        <v>23.9</v>
+        <v>25.8</v>
       </c>
       <c r="X30" t="n">
-        <v>19.1</v>
+        <v>18.9</v>
       </c>
       <c r="Y30" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Z30" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AA30" t="n">
-        <v>16.1</v>
+        <v>15</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.4</v>
+        <v>-0.1</v>
       </c>
       <c r="AC30" t="n">
-        <v>7.6</v>
+        <v>5.8</v>
       </c>
       <c r="AD30" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="AF30" t="n">
-        <v>229.5</v>
+        <v>238.69</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.02</v>
+        <v>-2.8</v>
       </c>
       <c r="AH30" t="n">
         <v>215</v>
@@ -3387,10 +3387,10 @@
         <v>235</v>
       </c>
       <c r="AK30" t="n">
-        <v>128.37</v>
+        <v>134.59</v>
       </c>
       <c r="AL30" t="n">
-        <v>8.09</v>
+        <v>6.22</v>
       </c>
       <c r="AM30" t="n">
         <v>110</v>
@@ -3399,99 +3399,99 @@
         <v>142</v>
       </c>
       <c r="AP30" t="n">
-        <v>91.59999999999999</v>
+        <v>89.05</v>
       </c>
       <c r="AS30" t="n">
-        <v>15.97</v>
+        <v>17.06</v>
       </c>
       <c r="BL30" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B31" t="n">
-        <v>142.9</v>
+        <v>148.1</v>
       </c>
       <c r="C31" t="n">
-        <v>52.7</v>
+        <v>51.9</v>
       </c>
       <c r="D31" t="n">
-        <v>34.7</v>
+        <v>35.4</v>
       </c>
       <c r="E31" t="n">
-        <v>24.8</v>
+        <v>31.5</v>
       </c>
       <c r="F31" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="H31" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="I31" t="n">
-        <v>9.9</v>
+        <v>9.6</v>
       </c>
       <c r="J31" t="n">
-        <v>38.2</v>
+        <v>39.6</v>
       </c>
       <c r="K31" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M31" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="N31" t="n">
-        <v>31.9</v>
+        <v>30.8</v>
       </c>
       <c r="O31" t="n">
-        <v>35.8</v>
+        <v>33.7</v>
       </c>
       <c r="Q31" t="n">
-        <v>19.7</v>
+        <v>20.7</v>
       </c>
       <c r="R31" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>19.7</v>
+        <v>20.7</v>
       </c>
       <c r="V31" t="n">
-        <v>12</v>
+        <v>13.1</v>
       </c>
       <c r="W31" t="n">
-        <v>25.8</v>
+        <v>25.5</v>
       </c>
       <c r="X31" t="n">
-        <v>18.9</v>
+        <v>19.3</v>
       </c>
       <c r="Y31" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z31" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AA31" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AB31" t="n">
-        <v>-0.1</v>
+        <v>-1</v>
       </c>
       <c r="AC31" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="AF31" t="n">
-        <v>238.69</v>
+        <v>233.48</v>
       </c>
       <c r="AG31" t="n">
-        <v>-2.8</v>
+        <v>-4.86</v>
       </c>
       <c r="AH31" t="n">
         <v>215</v>
@@ -3500,10 +3500,10 @@
         <v>235</v>
       </c>
       <c r="AK31" t="n">
-        <v>134.59</v>
+        <v>136.6</v>
       </c>
       <c r="AL31" t="n">
-        <v>6.22</v>
+        <v>2.01</v>
       </c>
       <c r="AM31" t="n">
         <v>110</v>
@@ -3512,99 +3512,99 @@
         <v>142</v>
       </c>
       <c r="AP31" t="n">
-        <v>89.05</v>
+        <v>86.25</v>
       </c>
       <c r="AS31" t="n">
-        <v>17.06</v>
+        <v>17.13</v>
       </c>
       <c r="BL31" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B32" t="n">
-        <v>148.1</v>
+        <v>143.4</v>
       </c>
       <c r="C32" t="n">
-        <v>51.9</v>
+        <v>50.9</v>
       </c>
       <c r="D32" t="n">
-        <v>35.4</v>
+        <v>35.7</v>
       </c>
       <c r="E32" t="n">
-        <v>31.5</v>
+        <v>26.2</v>
       </c>
       <c r="F32" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="H32" t="n">
-        <v>21.8</v>
+        <v>22.9</v>
       </c>
       <c r="I32" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J32" t="n">
-        <v>39.6</v>
+        <v>39.9</v>
       </c>
       <c r="K32" t="n">
-        <v>71</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="M32" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="N32" t="n">
-        <v>30.8</v>
+        <v>31.2</v>
       </c>
       <c r="O32" t="n">
-        <v>33.7</v>
+        <v>33.1</v>
       </c>
       <c r="Q32" t="n">
-        <v>20.7</v>
+        <v>21.6</v>
       </c>
       <c r="R32" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>20.7</v>
+        <v>21.6</v>
       </c>
       <c r="V32" t="n">
-        <v>13.1</v>
+        <v>12.9</v>
       </c>
       <c r="W32" t="n">
-        <v>25.5</v>
+        <v>28.3</v>
       </c>
       <c r="X32" t="n">
-        <v>19.3</v>
+        <v>20.6</v>
       </c>
       <c r="Y32" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z32" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AA32" t="n">
-        <v>15.5</v>
+        <v>17.9</v>
       </c>
       <c r="AB32" t="n">
-        <v>-1</v>
+        <v>-0.8</v>
       </c>
       <c r="AC32" t="n">
-        <v>6.4</v>
+        <v>8.1</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="AF32" t="n">
-        <v>233.48</v>
+        <v>235.13</v>
       </c>
       <c r="AG32" t="n">
-        <v>-4.86</v>
+        <v>1.66</v>
       </c>
       <c r="AH32" t="n">
         <v>215</v>
@@ -3613,10 +3613,10 @@
         <v>235</v>
       </c>
       <c r="AK32" t="n">
-        <v>136.6</v>
+        <v>135.66</v>
       </c>
       <c r="AL32" t="n">
-        <v>2.01</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AM32" t="n">
         <v>110</v>
@@ -3625,57 +3625,57 @@
         <v>142</v>
       </c>
       <c r="AP32" t="n">
-        <v>86.25</v>
+        <v>88.27</v>
       </c>
       <c r="AS32" t="n">
-        <v>17.13</v>
+        <v>17.6</v>
       </c>
       <c r="BL32" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B33" t="n">
-        <v>143.4</v>
+        <v>144.9</v>
       </c>
       <c r="C33" t="n">
-        <v>50.9</v>
+        <v>53</v>
       </c>
       <c r="D33" t="n">
-        <v>35.7</v>
+        <v>35.6</v>
       </c>
       <c r="E33" t="n">
-        <v>26.2</v>
+        <v>26</v>
       </c>
       <c r="F33" t="n">
-        <v>4.3</v>
+        <v>2.8</v>
       </c>
       <c r="H33" t="n">
-        <v>22.9</v>
+        <v>24</v>
       </c>
       <c r="I33" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J33" t="n">
-        <v>39.9</v>
+        <v>40.3</v>
       </c>
       <c r="K33" t="n">
-        <v>72.59999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="M33" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="N33" t="n">
-        <v>31.2</v>
+        <v>31.6</v>
       </c>
       <c r="O33" t="n">
-        <v>33.1</v>
+        <v>33.6</v>
       </c>
       <c r="Q33" t="n">
-        <v>21.6</v>
+        <v>21</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -3684,40 +3684,40 @@
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>21.6</v>
+        <v>21</v>
       </c>
       <c r="V33" t="n">
-        <v>12.9</v>
+        <v>14.4</v>
       </c>
       <c r="W33" t="n">
-        <v>28.3</v>
+        <v>27.7</v>
       </c>
       <c r="X33" t="n">
-        <v>20.6</v>
+        <v>21.1</v>
       </c>
       <c r="Y33" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z33" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AA33" t="n">
-        <v>17.9</v>
+        <v>16.3</v>
       </c>
       <c r="AB33" t="n">
-        <v>-0.8</v>
+        <v>-1.1</v>
       </c>
       <c r="AC33" t="n">
-        <v>8.1</v>
+        <v>6.6</v>
       </c>
       <c r="AD33" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="AF33" t="n">
-        <v>235.13</v>
+        <v>234.87</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.66</v>
+        <v>-0.26</v>
       </c>
       <c r="AH33" t="n">
         <v>215</v>
@@ -3726,10 +3726,10 @@
         <v>235</v>
       </c>
       <c r="AK33" t="n">
-        <v>135.66</v>
+        <v>136.33</v>
       </c>
       <c r="AL33" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="AM33" t="n">
         <v>110</v>
@@ -3738,99 +3738,60 @@
         <v>142</v>
       </c>
       <c r="AP33" t="n">
-        <v>88.27</v>
+        <v>87.09</v>
       </c>
       <c r="AS33" t="n">
-        <v>17.6</v>
+        <v>17.31</v>
       </c>
       <c r="BL33" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B34" t="n">
-        <v>144.9</v>
-      </c>
-      <c r="C34" t="n">
-        <v>53</v>
+        <v>132.2</v>
       </c>
       <c r="D34" t="n">
         <v>35.6</v>
       </c>
-      <c r="E34" t="n">
-        <v>26</v>
-      </c>
       <c r="F34" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="H34" t="n">
-        <v>24</v>
-      </c>
-      <c r="I34" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="J34" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="K34" t="n">
-        <v>73.7</v>
-      </c>
-      <c r="M34" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="N34" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="O34" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>21</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="V34" t="n">
-        <v>14.4</v>
+        <v>11.6</v>
       </c>
       <c r="W34" t="n">
-        <v>27.7</v>
+        <v>23.2</v>
       </c>
       <c r="X34" t="n">
-        <v>21.1</v>
+        <v>17.4</v>
       </c>
       <c r="Y34" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z34" t="n">
         <v>19</v>
       </c>
       <c r="AA34" t="n">
-        <v>16.3</v>
+        <v>13</v>
       </c>
       <c r="AB34" t="n">
-        <v>-1.1</v>
+        <v>0.9</v>
       </c>
       <c r="AC34" t="n">
-        <v>6.6</v>
+        <v>7.5</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="AF34" t="n">
-        <v>234.87</v>
+        <v>234.78</v>
       </c>
       <c r="AG34" t="n">
-        <v>-0.26</v>
+        <v>-0.09</v>
       </c>
       <c r="AH34" t="n">
         <v>215</v>
@@ -3838,73 +3799,61 @@
       <c r="AI34" t="n">
         <v>235</v>
       </c>
-      <c r="AK34" t="n">
-        <v>136.33</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>0.67</v>
-      </c>
       <c r="AM34" t="n">
         <v>110</v>
       </c>
       <c r="AN34" t="n">
         <v>142</v>
       </c>
-      <c r="AP34" t="n">
-        <v>87.09</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>17.31</v>
-      </c>
       <c r="BL34" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B35" t="n">
-        <v>132.2</v>
+        <v>137.1</v>
       </c>
       <c r="D35" t="n">
-        <v>35.6</v>
+        <v>35.1</v>
       </c>
       <c r="F35" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="V35" t="n">
-        <v>11.6</v>
+        <v>11</v>
       </c>
       <c r="W35" t="n">
-        <v>23.2</v>
+        <v>22</v>
       </c>
       <c r="X35" t="n">
-        <v>17.4</v>
+        <v>16.5</v>
       </c>
       <c r="Y35" t="n">
         <v>7</v>
       </c>
       <c r="Z35" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AA35" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.9</v>
+        <v>-5.3</v>
       </c>
       <c r="AC35" t="n">
-        <v>7.5</v>
+        <v>6.1</v>
       </c>
       <c r="AD35" t="n">
-        <v>4.2</v>
+        <v>0.4</v>
       </c>
       <c r="AF35" t="n">
-        <v>234.78</v>
+        <v>229.75</v>
       </c>
       <c r="AG35" t="n">
-        <v>-0.09</v>
+        <v>-5.03</v>
       </c>
       <c r="AH35" t="n">
         <v>215</v>
@@ -3919,54 +3868,93 @@
         <v>142</v>
       </c>
       <c r="BL35" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B36" t="n">
-        <v>137.1</v>
+        <v>166.2</v>
+      </c>
+      <c r="C36" t="n">
+        <v>72.40000000000001</v>
       </c>
       <c r="D36" t="n">
-        <v>35.1</v>
+        <v>32.7</v>
+      </c>
+      <c r="E36" t="n">
+        <v>28.1</v>
       </c>
       <c r="F36" t="n">
         <v>3.3</v>
       </c>
+      <c r="H36" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="I36" t="n">
+        <v>9</v>
+      </c>
+      <c r="J36" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="K36" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="M36" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="N36" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="O36" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="R36" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>23.7</v>
+      </c>
       <c r="V36" t="n">
-        <v>11</v>
+        <v>7.9</v>
       </c>
       <c r="W36" t="n">
-        <v>22</v>
+        <v>15.6</v>
       </c>
       <c r="X36" t="n">
-        <v>16.5</v>
+        <v>11.8</v>
       </c>
       <c r="Y36" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z36" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AA36" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AB36" t="n">
-        <v>-5.3</v>
+        <v>-3.5</v>
       </c>
       <c r="AC36" t="n">
-        <v>6.1</v>
+        <v>8.4</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.4</v>
+        <v>2.5</v>
       </c>
       <c r="AF36" t="n">
-        <v>229.75</v>
+        <v>222.86</v>
       </c>
       <c r="AG36" t="n">
-        <v>-5.03</v>
+        <v>-6.9</v>
       </c>
       <c r="AH36" t="n">
         <v>215</v>
@@ -3974,100 +3962,112 @@
       <c r="AI36" t="n">
         <v>235</v>
       </c>
+      <c r="AK36" t="n">
+        <v>135.42</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>-0.91</v>
+      </c>
       <c r="AM36" t="n">
         <v>110</v>
       </c>
       <c r="AN36" t="n">
         <v>142</v>
       </c>
+      <c r="AP36" t="n">
+        <v>81.98</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>15.01</v>
+      </c>
       <c r="BL36" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B37" t="n">
-        <v>166.2</v>
+        <v>166.3</v>
       </c>
       <c r="C37" t="n">
-        <v>72.40000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="D37" t="n">
-        <v>32.7</v>
+        <v>32.8</v>
       </c>
       <c r="E37" t="n">
-        <v>28.1</v>
+        <v>28.8</v>
       </c>
       <c r="F37" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="H37" t="n">
         <v>23.4</v>
       </c>
       <c r="I37" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J37" t="n">
-        <v>42.1</v>
+        <v>41.2</v>
       </c>
       <c r="K37" t="n">
-        <v>74.5</v>
+        <v>73.8</v>
       </c>
       <c r="M37" t="n">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="N37" t="n">
-        <v>33.7</v>
+        <v>35.4</v>
       </c>
       <c r="O37" t="n">
-        <v>39.3</v>
+        <v>42.6</v>
       </c>
       <c r="Q37" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="R37" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="V37" t="n">
-        <v>7.9</v>
+        <v>6.7</v>
       </c>
       <c r="W37" t="n">
-        <v>15.6</v>
+        <v>18.1</v>
       </c>
       <c r="X37" t="n">
-        <v>11.8</v>
+        <v>12.4</v>
       </c>
       <c r="Y37" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Z37" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AA37" t="n">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AB37" t="n">
-        <v>-3.5</v>
+        <v>-2.9</v>
       </c>
       <c r="AC37" t="n">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.5</v>
+        <v>4.3</v>
       </c>
       <c r="AF37" t="n">
-        <v>222.86</v>
+        <v>218.37</v>
       </c>
       <c r="AG37" t="n">
-        <v>-6.9</v>
+        <v>-4.49</v>
       </c>
       <c r="AH37" t="n">
         <v>215</v>
@@ -4076,10 +4076,10 @@
         <v>235</v>
       </c>
       <c r="AK37" t="n">
-        <v>135.42</v>
+        <v>131.24</v>
       </c>
       <c r="AL37" t="n">
-        <v>-0.91</v>
+        <v>-4.18</v>
       </c>
       <c r="AM37" t="n">
         <v>110</v>
@@ -4088,99 +4088,99 @@
         <v>142</v>
       </c>
       <c r="AP37" t="n">
-        <v>81.98</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="AS37" t="n">
-        <v>15.01</v>
+        <v>12.97</v>
       </c>
       <c r="BL37" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B38" t="n">
-        <v>166.3</v>
+        <v>154.1</v>
       </c>
       <c r="C38" t="n">
-        <v>74.90000000000001</v>
+        <v>65</v>
       </c>
       <c r="D38" t="n">
-        <v>32.8</v>
+        <v>32</v>
       </c>
       <c r="E38" t="n">
-        <v>28.8</v>
+        <v>25.2</v>
       </c>
       <c r="F38" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="H38" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="I38" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="J38" t="n">
-        <v>41.2</v>
+        <v>38.5</v>
       </c>
       <c r="K38" t="n">
-        <v>73.8</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="M38" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="N38" t="n">
-        <v>35.4</v>
+        <v>32.3</v>
       </c>
       <c r="O38" t="n">
-        <v>42.6</v>
+        <v>40.3</v>
       </c>
       <c r="Q38" t="n">
-        <v>23.9</v>
+        <v>21.7</v>
       </c>
       <c r="R38" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="S38" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T38" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="V38" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="W38" t="n">
+        <v>21</v>
+      </c>
+      <c r="X38" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AD38" t="n">
         <v>3.9</v>
       </c>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="V38" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="W38" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="X38" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>11</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>-2.9</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AF38" t="n">
-        <v>218.37</v>
+        <v>218.04</v>
       </c>
       <c r="AG38" t="n">
-        <v>-4.49</v>
+        <v>-0.33</v>
       </c>
       <c r="AH38" t="n">
         <v>215</v>
@@ -4189,10 +4189,10 @@
         <v>235</v>
       </c>
       <c r="AK38" t="n">
-        <v>131.24</v>
+        <v>129.21</v>
       </c>
       <c r="AL38" t="n">
-        <v>-4.18</v>
+        <v>-2.03</v>
       </c>
       <c r="AM38" t="n">
         <v>110</v>
@@ -4201,99 +4201,99 @@
         <v>142</v>
       </c>
       <c r="AP38" t="n">
-        <v>79.98999999999999</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="AS38" t="n">
-        <v>12.97</v>
+        <v>15.23</v>
       </c>
       <c r="BL38" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B39" t="n">
-        <v>154.1</v>
+        <v>148.8</v>
       </c>
       <c r="C39" t="n">
-        <v>65</v>
+        <v>57.6</v>
       </c>
       <c r="D39" t="n">
-        <v>32</v>
+        <v>32.7</v>
       </c>
       <c r="E39" t="n">
-        <v>25.2</v>
+        <v>26.3</v>
       </c>
       <c r="F39" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="H39" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="I39" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="J39" t="n">
-        <v>38.5</v>
+        <v>41.6</v>
       </c>
       <c r="K39" t="n">
-        <v>70.90000000000001</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="M39" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="N39" t="n">
-        <v>32.3</v>
+        <v>35</v>
       </c>
       <c r="O39" t="n">
-        <v>40.3</v>
+        <v>42.4</v>
       </c>
       <c r="Q39" t="n">
         <v>21.7</v>
       </c>
       <c r="R39" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="S39" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
         <v>21.7</v>
       </c>
       <c r="V39" t="n">
-        <v>5.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W39" t="n">
-        <v>21</v>
+        <v>24.1</v>
       </c>
       <c r="X39" t="n">
-        <v>13.2</v>
+        <v>16.1</v>
       </c>
       <c r="Y39" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z39" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA39" t="n">
-        <v>14.5</v>
+        <v>15.6</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="AC39" t="n">
-        <v>7.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AD39" t="n">
-        <v>3.9</v>
+        <v>6.3</v>
       </c>
       <c r="AF39" t="n">
-        <v>218.04</v>
+        <v>220.84</v>
       </c>
       <c r="AG39" t="n">
-        <v>-0.33</v>
+        <v>2.8</v>
       </c>
       <c r="AH39" t="n">
         <v>215</v>
@@ -4302,10 +4302,10 @@
         <v>235</v>
       </c>
       <c r="AK39" t="n">
-        <v>129.21</v>
+        <v>129.07</v>
       </c>
       <c r="AL39" t="n">
-        <v>-2.03</v>
+        <v>-0.14</v>
       </c>
       <c r="AM39" t="n">
         <v>110</v>
@@ -4314,99 +4314,99 @@
         <v>142</v>
       </c>
       <c r="AP39" t="n">
-        <v>82.90000000000001</v>
+        <v>85.52</v>
       </c>
       <c r="AS39" t="n">
-        <v>15.23</v>
+        <v>15.82</v>
       </c>
       <c r="BL39" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B40" t="n">
-        <v>148.8</v>
+        <v>146.8</v>
       </c>
       <c r="C40" t="n">
-        <v>57.6</v>
+        <v>52.8</v>
       </c>
       <c r="D40" t="n">
-        <v>32.7</v>
+        <v>33.6</v>
       </c>
       <c r="E40" t="n">
-        <v>26.3</v>
+        <v>28.9</v>
       </c>
       <c r="F40" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="H40" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="I40" t="n">
-        <v>8.9</v>
+        <v>9.1</v>
       </c>
       <c r="J40" t="n">
-        <v>41.6</v>
+        <v>40.8</v>
       </c>
       <c r="K40" t="n">
-        <v>74.09999999999999</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="M40" t="n">
-        <v>7.4</v>
+        <v>5.6</v>
       </c>
       <c r="N40" t="n">
-        <v>35</v>
+        <v>33.1</v>
       </c>
       <c r="O40" t="n">
-        <v>42.4</v>
+        <v>38.7</v>
       </c>
       <c r="Q40" t="n">
-        <v>21.7</v>
+        <v>22</v>
       </c>
       <c r="R40" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>21.7</v>
+        <v>22</v>
       </c>
       <c r="V40" t="n">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="W40" t="n">
-        <v>24.1</v>
+        <v>22.9</v>
       </c>
       <c r="X40" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA40" t="n">
         <v>16.1</v>
       </c>
-      <c r="Y40" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>19</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>15.6</v>
-      </c>
       <c r="AB40" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="AC40" t="n">
-        <v>9.699999999999999</v>
+        <v>7</v>
       </c>
       <c r="AD40" t="n">
-        <v>6.3</v>
+        <v>4.5</v>
       </c>
       <c r="AF40" t="n">
-        <v>220.84</v>
+        <v>225.87</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.8</v>
+        <v>5.03</v>
       </c>
       <c r="AH40" t="n">
         <v>215</v>
@@ -4415,10 +4415,10 @@
         <v>235</v>
       </c>
       <c r="AK40" t="n">
-        <v>129.07</v>
+        <v>130.73</v>
       </c>
       <c r="AL40" t="n">
-        <v>-0.14</v>
+        <v>1.66</v>
       </c>
       <c r="AM40" t="n">
         <v>110</v>
@@ -4427,99 +4427,54 @@
         <v>142</v>
       </c>
       <c r="AP40" t="n">
-        <v>85.52</v>
+        <v>88.2</v>
       </c>
       <c r="AS40" t="n">
-        <v>15.82</v>
+        <v>15.76</v>
       </c>
       <c r="BL40" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B41" t="n">
-        <v>146.8</v>
-      </c>
-      <c r="C41" t="n">
-        <v>52.8</v>
+        <v>133.9</v>
       </c>
       <c r="D41" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="E41" t="n">
-        <v>28.9</v>
+        <v>34.7</v>
       </c>
       <c r="F41" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="H41" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="I41" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="J41" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="K41" t="n">
-        <v>73.59999999999999</v>
-      </c>
-      <c r="M41" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="N41" t="n">
-        <v>33.1</v>
-      </c>
-      <c r="O41" t="n">
-        <v>38.7</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>22</v>
-      </c>
-      <c r="R41" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="S41" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" t="n">
-        <v>22</v>
+        <v>3.3</v>
       </c>
       <c r="V41" t="n">
-        <v>11</v>
+        <v>14.3</v>
       </c>
       <c r="W41" t="n">
-        <v>22.9</v>
+        <v>21.7</v>
       </c>
       <c r="X41" t="n">
-        <v>16.9</v>
+        <v>18</v>
       </c>
       <c r="Y41" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z41" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AA41" t="n">
-        <v>16.1</v>
+        <v>15</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.9</v>
+        <v>-3.5</v>
       </c>
       <c r="AC41" t="n">
-        <v>7</v>
+        <v>3.2</v>
       </c>
       <c r="AD41" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>225.87</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>5.03</v>
+        <v>-0.1</v>
       </c>
       <c r="AH41" t="n">
         <v>215</v>
@@ -4527,67 +4482,55 @@
       <c r="AI41" t="n">
         <v>235</v>
       </c>
-      <c r="AK41" t="n">
-        <v>130.73</v>
-      </c>
-      <c r="AL41" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AM41" t="n">
         <v>110</v>
       </c>
       <c r="AN41" t="n">
         <v>142</v>
       </c>
-      <c r="AP41" t="n">
-        <v>88.2</v>
-      </c>
-      <c r="AS41" t="n">
-        <v>15.76</v>
-      </c>
       <c r="BL41" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B42" t="n">
-        <v>133.9</v>
+        <v>137.5</v>
       </c>
       <c r="D42" t="n">
-        <v>34.7</v>
+        <v>32.8</v>
       </c>
       <c r="F42" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="V42" t="n">
-        <v>14.3</v>
+        <v>9</v>
       </c>
       <c r="W42" t="n">
-        <v>21.7</v>
+        <v>15.7</v>
       </c>
       <c r="X42" t="n">
-        <v>18</v>
+        <v>12.3</v>
       </c>
       <c r="Y42" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z42" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="AA42" t="n">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="AB42" t="n">
-        <v>-3.5</v>
+        <v>-6.6</v>
       </c>
       <c r="AC42" t="n">
-        <v>3.2</v>
+        <v>8.1</v>
       </c>
       <c r="AD42" t="n">
-        <v>-0.1</v>
+        <v>0.8</v>
       </c>
       <c r="AH42" t="n">
         <v>215</v>
@@ -4602,48 +4545,93 @@
         <v>142</v>
       </c>
       <c r="BL42" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B43" t="n">
-        <v>137.5</v>
+        <v>157.1</v>
+      </c>
+      <c r="C43" t="n">
+        <v>73.09999999999999</v>
       </c>
       <c r="D43" t="n">
-        <v>32.8</v>
+        <v>31.7</v>
+      </c>
+      <c r="E43" t="n">
+        <v>26.1</v>
       </c>
       <c r="F43" t="n">
-        <v>2.3</v>
+        <v>2</v>
+      </c>
+      <c r="H43" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="I43" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="J43" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="K43" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="M43" t="n">
+        <v>6</v>
+      </c>
+      <c r="N43" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="O43" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="R43" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>23.8</v>
       </c>
       <c r="V43" t="n">
-        <v>9</v>
+        <v>6.8</v>
       </c>
       <c r="W43" t="n">
-        <v>15.7</v>
+        <v>11</v>
       </c>
       <c r="X43" t="n">
-        <v>12.3</v>
+        <v>8.9</v>
       </c>
       <c r="Y43" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="Z43" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA43" t="n">
-        <v>10.5</v>
+        <v>7.9</v>
       </c>
       <c r="AB43" t="n">
-        <v>-6.6</v>
+        <v>-1.2</v>
       </c>
       <c r="AC43" t="n">
-        <v>8.1</v>
+        <v>12.6</v>
       </c>
       <c r="AD43" t="n">
-        <v>0.8</v>
+        <v>5.7</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>224.2</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>-1.67</v>
       </c>
       <c r="AH43" t="n">
         <v>215</v>
@@ -4651,100 +4639,112 @@
       <c r="AI43" t="n">
         <v>235</v>
       </c>
+      <c r="AK43" t="n">
+        <v>128.6</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>-2.13</v>
+      </c>
       <c r="AM43" t="n">
         <v>110</v>
       </c>
       <c r="AN43" t="n">
         <v>142</v>
       </c>
+      <c r="AP43" t="n">
+        <v>81.18000000000001</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>14.06</v>
+      </c>
       <c r="BL43" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B44" t="n">
-        <v>157.1</v>
+        <v>153.1</v>
       </c>
       <c r="C44" t="n">
-        <v>73.09999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="D44" t="n">
-        <v>31.7</v>
+        <v>32.2</v>
       </c>
       <c r="E44" t="n">
-        <v>26.1</v>
+        <v>25.9</v>
       </c>
       <c r="F44" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="H44" t="n">
-        <v>23.6</v>
+        <v>24.4</v>
       </c>
       <c r="I44" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="J44" t="n">
-        <v>40.5</v>
+        <v>39.6</v>
       </c>
       <c r="K44" t="n">
-        <v>73.5</v>
+        <v>73.3</v>
       </c>
       <c r="M44" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="N44" t="n">
-        <v>33.4</v>
+        <v>34.4</v>
       </c>
       <c r="O44" t="n">
-        <v>39.5</v>
+        <v>40.1</v>
       </c>
       <c r="Q44" t="n">
         <v>23.8</v>
       </c>
       <c r="R44" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T44" t="n">
         <v>23.8</v>
       </c>
       <c r="V44" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="W44" t="n">
-        <v>11</v>
+        <v>15.2</v>
       </c>
       <c r="X44" t="n">
-        <v>8.9</v>
+        <v>10.9</v>
       </c>
       <c r="Y44" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Z44" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA44" t="n">
         <v>12</v>
       </c>
-      <c r="AA44" t="n">
-        <v>7.9</v>
-      </c>
       <c r="AB44" t="n">
-        <v>-1.2</v>
+        <v>1.7</v>
       </c>
       <c r="AC44" t="n">
-        <v>12.6</v>
+        <v>10</v>
       </c>
       <c r="AD44" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AF44" t="n">
-        <v>224.2</v>
+        <v>223.35</v>
       </c>
       <c r="AG44" t="n">
-        <v>-1.67</v>
+        <v>-0.85</v>
       </c>
       <c r="AH44" t="n">
         <v>215</v>
@@ -4753,10 +4753,10 @@
         <v>235</v>
       </c>
       <c r="AK44" t="n">
-        <v>128.6</v>
+        <v>127.19</v>
       </c>
       <c r="AL44" t="n">
-        <v>-2.13</v>
+        <v>-1.41</v>
       </c>
       <c r="AM44" t="n">
         <v>110</v>
@@ -4765,99 +4765,99 @@
         <v>142</v>
       </c>
       <c r="AP44" t="n">
-        <v>81.18000000000001</v>
+        <v>81.06</v>
       </c>
       <c r="AS44" t="n">
-        <v>14.06</v>
+        <v>13.63</v>
       </c>
       <c r="BL44" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B45" t="n">
-        <v>153.1</v>
+        <v>145.5</v>
       </c>
       <c r="C45" t="n">
-        <v>69.59999999999999</v>
+        <v>62.3</v>
       </c>
       <c r="D45" t="n">
-        <v>32.2</v>
+        <v>34</v>
       </c>
       <c r="E45" t="n">
-        <v>25.9</v>
+        <v>22.5</v>
       </c>
       <c r="F45" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="H45" t="n">
-        <v>24.4</v>
+        <v>24.8</v>
       </c>
       <c r="I45" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J45" t="n">
-        <v>39.6</v>
+        <v>40.8</v>
       </c>
       <c r="K45" t="n">
-        <v>73.3</v>
+        <v>75</v>
       </c>
       <c r="M45" t="n">
-        <v>5.7</v>
+        <v>6.9</v>
       </c>
       <c r="N45" t="n">
-        <v>34.4</v>
+        <v>30.4</v>
       </c>
       <c r="O45" t="n">
-        <v>40.1</v>
+        <v>37.3</v>
       </c>
       <c r="Q45" t="n">
-        <v>23.8</v>
+        <v>22.1</v>
       </c>
       <c r="R45" t="n">
-        <v>3.8</v>
+        <v>4.9</v>
       </c>
       <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="V45" t="n">
         <v>4</v>
       </c>
-      <c r="T45" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="V45" t="n">
-        <v>6.6</v>
-      </c>
       <c r="W45" t="n">
-        <v>15.2</v>
+        <v>22.9</v>
       </c>
       <c r="X45" t="n">
-        <v>10.9</v>
+        <v>13.4</v>
       </c>
       <c r="Y45" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="Z45" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AA45" t="n">
-        <v>12</v>
+        <v>12.9</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="AC45" t="n">
-        <v>10</v>
+        <v>12.7</v>
       </c>
       <c r="AD45" t="n">
-        <v>5.8</v>
+        <v>6.7</v>
       </c>
       <c r="AF45" t="n">
-        <v>223.35</v>
+        <v>223.06</v>
       </c>
       <c r="AG45" t="n">
-        <v>-0.85</v>
+        <v>-0.29</v>
       </c>
       <c r="AH45" t="n">
         <v>215</v>
@@ -4866,10 +4866,10 @@
         <v>235</v>
       </c>
       <c r="AK45" t="n">
-        <v>127.19</v>
+        <v>129.17</v>
       </c>
       <c r="AL45" t="n">
-        <v>-1.41</v>
+        <v>1.98</v>
       </c>
       <c r="AM45" t="n">
         <v>110</v>
@@ -4878,96 +4878,96 @@
         <v>142</v>
       </c>
       <c r="AP45" t="n">
-        <v>81.06</v>
+        <v>82.36</v>
       </c>
       <c r="AS45" t="n">
-        <v>13.63</v>
+        <v>13.91</v>
       </c>
       <c r="BL45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B46" t="n">
-        <v>145.5</v>
+        <v>148</v>
       </c>
       <c r="C46" t="n">
-        <v>62.3</v>
+        <v>61.6</v>
       </c>
       <c r="D46" t="n">
-        <v>34</v>
+        <v>33.9</v>
       </c>
       <c r="E46" t="n">
-        <v>22.5</v>
+        <v>25</v>
       </c>
       <c r="F46" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="H46" t="n">
-        <v>24.8</v>
+        <v>25.1</v>
       </c>
       <c r="I46" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="J46" t="n">
-        <v>40.8</v>
+        <v>39.5</v>
       </c>
       <c r="K46" t="n">
-        <v>75</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="M46" t="n">
-        <v>6.9</v>
+        <v>5.9</v>
       </c>
       <c r="N46" t="n">
-        <v>30.4</v>
+        <v>28.6</v>
       </c>
       <c r="O46" t="n">
-        <v>37.3</v>
+        <v>34.5</v>
       </c>
       <c r="Q46" t="n">
-        <v>22.1</v>
+        <v>23.3</v>
       </c>
       <c r="R46" t="n">
-        <v>4.9</v>
+        <v>3.9</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>22.1</v>
+        <v>23.3</v>
       </c>
       <c r="V46" t="n">
-        <v>4</v>
+        <v>7.8</v>
       </c>
       <c r="W46" t="n">
-        <v>22.9</v>
+        <v>26</v>
       </c>
       <c r="X46" t="n">
-        <v>13.4</v>
+        <v>16.9</v>
       </c>
       <c r="Y46" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="Z46" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AA46" t="n">
-        <v>12.9</v>
+        <v>11.6</v>
       </c>
       <c r="AB46" t="n">
-        <v>0.7</v>
+        <v>4.2</v>
       </c>
       <c r="AC46" t="n">
-        <v>12.7</v>
+        <v>11.4</v>
       </c>
       <c r="AD46" t="n">
-        <v>6.7</v>
+        <v>7.8</v>
       </c>
       <c r="AF46" t="n">
-        <v>223.06</v>
+        <v>222.77</v>
       </c>
       <c r="AG46" t="n">
         <v>-0.29</v>
@@ -4979,10 +4979,10 @@
         <v>235</v>
       </c>
       <c r="AK46" t="n">
-        <v>129.17</v>
+        <v>130.42</v>
       </c>
       <c r="AL46" t="n">
-        <v>1.98</v>
+        <v>1.25</v>
       </c>
       <c r="AM46" t="n">
         <v>110</v>
@@ -4991,60 +4991,60 @@
         <v>142</v>
       </c>
       <c r="AP46" t="n">
-        <v>82.36</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="AS46" t="n">
-        <v>13.91</v>
+        <v>14</v>
       </c>
       <c r="BL46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B47" t="n">
-        <v>148</v>
+        <v>135.5</v>
       </c>
       <c r="C47" t="n">
-        <v>61.6</v>
+        <v>47.7</v>
       </c>
       <c r="D47" t="n">
-        <v>33.9</v>
+        <v>34.2</v>
       </c>
       <c r="E47" t="n">
-        <v>25</v>
+        <v>24.1</v>
       </c>
       <c r="F47" t="n">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="H47" t="n">
-        <v>25.1</v>
+        <v>24.9</v>
       </c>
       <c r="I47" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="J47" t="n">
-        <v>39.5</v>
+        <v>38.4</v>
       </c>
       <c r="K47" t="n">
-        <v>74.09999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="M47" t="n">
-        <v>5.9</v>
+        <v>3</v>
       </c>
       <c r="N47" t="n">
-        <v>28.6</v>
+        <v>30.3</v>
       </c>
       <c r="O47" t="n">
-        <v>34.5</v>
+        <v>33.3</v>
       </c>
       <c r="Q47" t="n">
         <v>23.3</v>
       </c>
       <c r="R47" t="n">
-        <v>3.9</v>
+        <v>1</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -5053,37 +5053,37 @@
         <v>23.3</v>
       </c>
       <c r="V47" t="n">
-        <v>7.8</v>
+        <v>11.3</v>
       </c>
       <c r="W47" t="n">
-        <v>26</v>
+        <v>27.6</v>
       </c>
       <c r="X47" t="n">
-        <v>16.9</v>
+        <v>19.5</v>
       </c>
       <c r="Y47" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Z47" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="AA47" t="n">
-        <v>11.6</v>
+        <v>18.8</v>
       </c>
       <c r="AB47" t="n">
-        <v>4.2</v>
+        <v>1.8</v>
       </c>
       <c r="AC47" t="n">
-        <v>11.4</v>
+        <v>15.5</v>
       </c>
       <c r="AD47" t="n">
-        <v>7.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AF47" t="n">
-        <v>222.77</v>
+        <v>221.86</v>
       </c>
       <c r="AG47" t="n">
-        <v>-0.29</v>
+        <v>-0.91</v>
       </c>
       <c r="AH47" t="n">
         <v>215</v>
@@ -5092,10 +5092,10 @@
         <v>235</v>
       </c>
       <c r="AK47" t="n">
-        <v>130.42</v>
+        <v>129.71</v>
       </c>
       <c r="AL47" t="n">
-        <v>1.25</v>
+        <v>-0.71</v>
       </c>
       <c r="AM47" t="n">
         <v>110</v>
@@ -5104,99 +5104,54 @@
         <v>142</v>
       </c>
       <c r="AP47" t="n">
-        <v>80.90000000000001</v>
+        <v>86.42</v>
       </c>
       <c r="AS47" t="n">
-        <v>14</v>
+        <v>16.05</v>
       </c>
       <c r="BL47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B48" t="n">
-        <v>135.5</v>
-      </c>
-      <c r="C48" t="n">
-        <v>47.7</v>
+        <v>118.1</v>
       </c>
       <c r="D48" t="n">
-        <v>34.2</v>
-      </c>
-      <c r="E48" t="n">
-        <v>24.1</v>
+        <v>34.7</v>
       </c>
       <c r="F48" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H48" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="I48" t="n">
-        <v>10</v>
-      </c>
-      <c r="J48" t="n">
-        <v>38.4</v>
-      </c>
-      <c r="K48" t="n">
-        <v>73.2</v>
-      </c>
-      <c r="M48" t="n">
-        <v>3</v>
-      </c>
-      <c r="N48" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="O48" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="R48" t="n">
-        <v>1</v>
-      </c>
-      <c r="S48" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" t="n">
-        <v>23.3</v>
+        <v>3.3</v>
       </c>
       <c r="V48" t="n">
-        <v>11.3</v>
+        <v>14.1</v>
       </c>
       <c r="W48" t="n">
         <v>27.6</v>
       </c>
       <c r="X48" t="n">
-        <v>19.5</v>
+        <v>20.9</v>
       </c>
       <c r="Y48" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Z48" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA48" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="AC48" t="n">
-        <v>15.5</v>
+        <v>14.9</v>
       </c>
       <c r="AD48" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>221.86</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>-0.91</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AH48" t="n">
         <v>215</v>
@@ -5204,67 +5159,55 @@
       <c r="AI48" t="n">
         <v>235</v>
       </c>
-      <c r="AK48" t="n">
-        <v>129.71</v>
-      </c>
-      <c r="AL48" t="n">
-        <v>-0.71</v>
-      </c>
       <c r="AM48" t="n">
         <v>110</v>
       </c>
       <c r="AN48" t="n">
         <v>142</v>
       </c>
-      <c r="AP48" t="n">
-        <v>86.42</v>
-      </c>
-      <c r="AS48" t="n">
-        <v>16.05</v>
-      </c>
       <c r="BL48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B49" t="n">
-        <v>118.1</v>
+        <v>100.3</v>
       </c>
       <c r="D49" t="n">
-        <v>34.7</v>
+        <v>34</v>
       </c>
       <c r="F49" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="V49" t="n">
-        <v>14.1</v>
+        <v>16</v>
       </c>
       <c r="W49" t="n">
-        <v>27.6</v>
+        <v>30.6</v>
       </c>
       <c r="X49" t="n">
-        <v>20.9</v>
+        <v>23.3</v>
       </c>
       <c r="Y49" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z49" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA49" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AB49" t="n">
-        <v>3.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC49" t="n">
-        <v>14.9</v>
+        <v>16.7</v>
       </c>
       <c r="AD49" t="n">
-        <v>9.199999999999999</v>
+        <v>12.8</v>
       </c>
       <c r="AH49" t="n">
         <v>215</v>
@@ -5279,48 +5222,93 @@
         <v>142</v>
       </c>
       <c r="BL49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="B50" t="n">
-        <v>100.3</v>
+        <v>104.9</v>
+      </c>
+      <c r="C50" t="n">
+        <v>36.3</v>
       </c>
       <c r="D50" t="n">
-        <v>34</v>
+        <v>32.7</v>
+      </c>
+      <c r="E50" t="n">
+        <v>17</v>
       </c>
       <c r="F50" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
+      </c>
+      <c r="H50" t="n">
+        <v>16</v>
+      </c>
+      <c r="I50" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="J50" t="n">
+        <v>25</v>
+      </c>
+      <c r="K50" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="M50" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N50" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="O50" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>10.5</v>
       </c>
       <c r="V50" t="n">
-        <v>16</v>
+        <v>15.8</v>
       </c>
       <c r="W50" t="n">
-        <v>30.6</v>
+        <v>33.6</v>
       </c>
       <c r="X50" t="n">
-        <v>23.3</v>
+        <v>24.7</v>
       </c>
       <c r="Y50" t="n">
         <v>16</v>
       </c>
       <c r="Z50" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA50" t="n">
-        <v>20</v>
+        <v>16.9</v>
       </c>
       <c r="AB50" t="n">
-        <v>8.800000000000001</v>
+        <v>4</v>
       </c>
       <c r="AC50" t="n">
-        <v>16.7</v>
+        <v>10.1</v>
       </c>
       <c r="AD50" t="n">
-        <v>12.8</v>
+        <v>7</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>234.9</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>13.04</v>
       </c>
       <c r="AH50" t="n">
         <v>215</v>
@@ -5328,58 +5316,70 @@
       <c r="AI50" t="n">
         <v>235</v>
       </c>
+      <c r="AK50" t="n">
+        <v>137.51</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>7.8</v>
+      </c>
       <c r="AM50" t="n">
         <v>110</v>
       </c>
       <c r="AN50" t="n">
         <v>142</v>
       </c>
+      <c r="AP50" t="n">
+        <v>94</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>18.87</v>
+      </c>
       <c r="BL50" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="B51" t="n">
-        <v>104.9</v>
+        <v>134.9</v>
       </c>
       <c r="C51" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="D51" t="n">
         <v>36.3</v>
       </c>
-      <c r="D51" t="n">
-        <v>32.7</v>
-      </c>
       <c r="E51" t="n">
-        <v>17</v>
+        <v>20.6</v>
       </c>
       <c r="F51" t="n">
         <v>1.6</v>
       </c>
       <c r="H51" t="n">
-        <v>16</v>
+        <v>21.2</v>
       </c>
       <c r="I51" t="n">
-        <v>10.1</v>
+        <v>9.4</v>
       </c>
       <c r="J51" t="n">
-        <v>25</v>
+        <v>35.4</v>
       </c>
       <c r="K51" t="n">
-        <v>51.2</v>
+        <v>66</v>
       </c>
       <c r="M51" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="N51" t="n">
-        <v>25.5</v>
+        <v>24.8</v>
       </c>
       <c r="O51" t="n">
-        <v>27.3</v>
+        <v>26.7</v>
       </c>
       <c r="Q51" t="n">
-        <v>10.5</v>
+        <v>18.3</v>
       </c>
       <c r="R51" t="n">
         <v>0</v>
@@ -5388,40 +5388,40 @@
         <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>10.5</v>
+        <v>18.3</v>
       </c>
       <c r="V51" t="n">
-        <v>15.8</v>
+        <v>18.5</v>
       </c>
       <c r="W51" t="n">
-        <v>33.6</v>
+        <v>22.5</v>
       </c>
       <c r="X51" t="n">
-        <v>24.7</v>
+        <v>20.5</v>
       </c>
       <c r="Y51" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="Z51" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AA51" t="n">
-        <v>16.9</v>
+        <v>13.8</v>
       </c>
       <c r="AB51" t="n">
-        <v>4</v>
+        <v>1.3</v>
       </c>
       <c r="AC51" t="n">
-        <v>10.1</v>
+        <v>9.5</v>
       </c>
       <c r="AD51" t="n">
-        <v>7</v>
+        <v>5.4</v>
       </c>
       <c r="AF51" t="n">
-        <v>234.9</v>
+        <v>229.2</v>
       </c>
       <c r="AG51" t="n">
-        <v>13.04</v>
+        <v>-5.7</v>
       </c>
       <c r="AH51" t="n">
         <v>215</v>
@@ -5430,10 +5430,10 @@
         <v>235</v>
       </c>
       <c r="AK51" t="n">
-        <v>137.51</v>
+        <v>138.98</v>
       </c>
       <c r="AL51" t="n">
-        <v>7.8</v>
+        <v>1.47</v>
       </c>
       <c r="AM51" t="n">
         <v>110</v>
@@ -5442,57 +5442,57 @@
         <v>142</v>
       </c>
       <c r="AP51" t="n">
-        <v>94</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="AS51" t="n">
-        <v>18.87</v>
+        <v>16.02</v>
       </c>
       <c r="BL51" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B52" t="n">
-        <v>134.9</v>
+        <v>146.4</v>
       </c>
       <c r="C52" t="n">
-        <v>53.3</v>
+        <v>60.2</v>
       </c>
       <c r="D52" t="n">
-        <v>36.3</v>
+        <v>35.6</v>
       </c>
       <c r="E52" t="n">
-        <v>20.6</v>
+        <v>24.2</v>
       </c>
       <c r="F52" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="H52" t="n">
-        <v>21.2</v>
+        <v>23</v>
       </c>
       <c r="I52" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J52" t="n">
-        <v>35.4</v>
+        <v>38.2</v>
       </c>
       <c r="K52" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="M52" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="N52" t="n">
-        <v>24.8</v>
+        <v>30.2</v>
       </c>
       <c r="O52" t="n">
-        <v>26.7</v>
+        <v>31.9</v>
       </c>
       <c r="Q52" t="n">
-        <v>18.3</v>
+        <v>20.2</v>
       </c>
       <c r="R52" t="n">
         <v>0</v>
@@ -5501,40 +5501,40 @@
         <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>18.3</v>
+        <v>20.2</v>
       </c>
       <c r="V52" t="n">
-        <v>18.5</v>
+        <v>14.1</v>
       </c>
       <c r="W52" t="n">
-        <v>22.5</v>
+        <v>20.2</v>
       </c>
       <c r="X52" t="n">
-        <v>20.5</v>
+        <v>17.1</v>
       </c>
       <c r="Y52" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="Z52" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AA52" t="n">
-        <v>13.8</v>
+        <v>9.6</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.3</v>
+        <v>-0</v>
       </c>
       <c r="AC52" t="n">
-        <v>9.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AD52" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="AF52" t="n">
-        <v>229.2</v>
+        <v>224.9</v>
       </c>
       <c r="AG52" t="n">
-        <v>-5.7</v>
+        <v>-4.3</v>
       </c>
       <c r="AH52" t="n">
         <v>215</v>
@@ -5543,10 +5543,10 @@
         <v>235</v>
       </c>
       <c r="AK52" t="n">
-        <v>138.98</v>
+        <v>134.04</v>
       </c>
       <c r="AL52" t="n">
-        <v>1.47</v>
+        <v>-4.94</v>
       </c>
       <c r="AM52" t="n">
         <v>110</v>
@@ -5555,57 +5555,57 @@
         <v>142</v>
       </c>
       <c r="AP52" t="n">
-        <v>84.90000000000001</v>
+        <v>76.5</v>
       </c>
       <c r="AS52" t="n">
-        <v>16.02</v>
+        <v>13.68</v>
       </c>
       <c r="BL52" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B53" t="n">
-        <v>146.4</v>
+        <v>131.4</v>
       </c>
       <c r="C53" t="n">
-        <v>60.2</v>
+        <v>53.7</v>
       </c>
       <c r="D53" t="n">
-        <v>35.6</v>
+        <v>34.7</v>
       </c>
       <c r="E53" t="n">
-        <v>24.2</v>
+        <v>20.1</v>
       </c>
       <c r="F53" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="H53" t="n">
-        <v>23</v>
+        <v>24.1</v>
       </c>
       <c r="I53" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J53" t="n">
-        <v>38.2</v>
+        <v>37</v>
       </c>
       <c r="K53" t="n">
-        <v>70</v>
+        <v>69.8</v>
       </c>
       <c r="M53" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="N53" t="n">
-        <v>30.2</v>
+        <v>31.4</v>
       </c>
       <c r="O53" t="n">
-        <v>31.9</v>
+        <v>33.3</v>
       </c>
       <c r="Q53" t="n">
-        <v>20.2</v>
+        <v>22.3</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
@@ -5614,40 +5614,40 @@
         <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>20.2</v>
+        <v>22.3</v>
       </c>
       <c r="V53" t="n">
-        <v>14.1</v>
+        <v>9.1</v>
       </c>
       <c r="W53" t="n">
-        <v>20.2</v>
+        <v>26.1</v>
       </c>
       <c r="X53" t="n">
-        <v>17.1</v>
+        <v>17.6</v>
       </c>
       <c r="Y53" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z53" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AA53" t="n">
-        <v>9.6</v>
+        <v>14</v>
       </c>
       <c r="AB53" t="n">
-        <v>-0</v>
+        <v>5.1</v>
       </c>
       <c r="AC53" t="n">
-        <v>9.699999999999999</v>
+        <v>13.2</v>
       </c>
       <c r="AD53" t="n">
-        <v>4.8</v>
+        <v>9.1</v>
       </c>
       <c r="AF53" t="n">
-        <v>224.9</v>
+        <v>220.8</v>
       </c>
       <c r="AG53" t="n">
-        <v>-4.3</v>
+        <v>-4.1</v>
       </c>
       <c r="AH53" t="n">
         <v>215</v>
@@ -5656,10 +5656,10 @@
         <v>235</v>
       </c>
       <c r="AK53" t="n">
-        <v>134.04</v>
+        <v>131.01</v>
       </c>
       <c r="AL53" t="n">
-        <v>-4.94</v>
+        <v>-3.03</v>
       </c>
       <c r="AM53" t="n">
         <v>110</v>
@@ -5668,57 +5668,57 @@
         <v>142</v>
       </c>
       <c r="AP53" t="n">
-        <v>76.5</v>
+        <v>81.28</v>
       </c>
       <c r="AS53" t="n">
-        <v>13.68</v>
+        <v>13.92</v>
       </c>
       <c r="BL53" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B54" t="n">
-        <v>131.4</v>
+        <v>127.2</v>
       </c>
       <c r="C54" t="n">
-        <v>53.7</v>
+        <v>42.7</v>
       </c>
       <c r="D54" t="n">
-        <v>34.7</v>
+        <v>34.6</v>
       </c>
       <c r="E54" t="n">
-        <v>20.1</v>
+        <v>20.7</v>
       </c>
       <c r="F54" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="H54" t="n">
-        <v>24.1</v>
+        <v>21.2</v>
       </c>
       <c r="I54" t="n">
-        <v>8.6</v>
+        <v>9.1</v>
       </c>
       <c r="J54" t="n">
-        <v>37</v>
+        <v>36.8</v>
       </c>
       <c r="K54" t="n">
-        <v>69.8</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="M54" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="N54" t="n">
-        <v>31.4</v>
+        <v>27.9</v>
       </c>
       <c r="O54" t="n">
-        <v>33.3</v>
+        <v>29.8</v>
       </c>
       <c r="Q54" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="R54" t="n">
         <v>0</v>
@@ -5727,40 +5727,40 @@
         <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="V54" t="n">
-        <v>9.1</v>
+        <v>11.9</v>
       </c>
       <c r="W54" t="n">
-        <v>26.1</v>
+        <v>31.2</v>
       </c>
       <c r="X54" t="n">
-        <v>17.6</v>
+        <v>21.6</v>
       </c>
       <c r="Y54" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="Z54" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AA54" t="n">
-        <v>14</v>
+        <v>19.7</v>
       </c>
       <c r="AB54" t="n">
         <v>5.1</v>
       </c>
       <c r="AC54" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="AD54" t="n">
-        <v>9.1</v>
+        <v>8.1</v>
       </c>
       <c r="AF54" t="n">
-        <v>220.8</v>
+        <v>228.06</v>
       </c>
       <c r="AG54" t="n">
-        <v>-4.1</v>
+        <v>7.26</v>
       </c>
       <c r="AH54" t="n">
         <v>215</v>
@@ -5769,10 +5769,10 @@
         <v>235</v>
       </c>
       <c r="AK54" t="n">
-        <v>131.01</v>
+        <v>131.96</v>
       </c>
       <c r="AL54" t="n">
-        <v>-3.03</v>
+        <v>0.95</v>
       </c>
       <c r="AM54" t="n">
         <v>110</v>
@@ -5781,99 +5781,54 @@
         <v>142</v>
       </c>
       <c r="AP54" t="n">
-        <v>81.28</v>
+        <v>84.34</v>
       </c>
       <c r="AS54" t="n">
-        <v>13.92</v>
+        <v>17.57</v>
       </c>
       <c r="BL54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B55" t="n">
-        <v>127.2</v>
-      </c>
-      <c r="C55" t="n">
-        <v>42.7</v>
+        <v>116.2</v>
       </c>
       <c r="D55" t="n">
-        <v>34.6</v>
-      </c>
-      <c r="E55" t="n">
-        <v>20.7</v>
+        <v>35.4</v>
       </c>
       <c r="F55" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H55" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="I55" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="J55" t="n">
-        <v>36.8</v>
-      </c>
-      <c r="K55" t="n">
-        <v>67.09999999999999</v>
-      </c>
-      <c r="M55" t="n">
-        <v>2</v>
-      </c>
-      <c r="N55" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="O55" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="R55" t="n">
-        <v>0</v>
-      </c>
-      <c r="S55" t="n">
-        <v>0</v>
-      </c>
-      <c r="T55" t="n">
-        <v>22.2</v>
+        <v>4.5</v>
       </c>
       <c r="V55" t="n">
-        <v>11.9</v>
+        <v>15.9</v>
       </c>
       <c r="W55" t="n">
-        <v>31.2</v>
+        <v>35.4</v>
       </c>
       <c r="X55" t="n">
-        <v>21.6</v>
+        <v>25.6</v>
       </c>
       <c r="Y55" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="Z55" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AA55" t="n">
-        <v>19.7</v>
+        <v>21</v>
       </c>
       <c r="AB55" t="n">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="AC55" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="AD55" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="AF55" t="n">
-        <v>228.06</v>
-      </c>
-      <c r="AG55" t="n">
-        <v>7.26</v>
+        <v>7.3</v>
       </c>
       <c r="AH55" t="n">
         <v>215</v>
@@ -5881,49 +5836,37 @@
       <c r="AI55" t="n">
         <v>235</v>
       </c>
-      <c r="AK55" t="n">
-        <v>131.96</v>
-      </c>
-      <c r="AL55" t="n">
-        <v>0.95</v>
-      </c>
       <c r="AM55" t="n">
         <v>110</v>
       </c>
       <c r="AN55" t="n">
         <v>142</v>
       </c>
-      <c r="AP55" t="n">
-        <v>84.34</v>
-      </c>
-      <c r="AS55" t="n">
-        <v>17.57</v>
-      </c>
       <c r="BL55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B56" t="n">
-        <v>116.2</v>
+        <v>105.5</v>
       </c>
       <c r="D56" t="n">
-        <v>35.4</v>
+        <v>34</v>
       </c>
       <c r="F56" t="n">
         <v>4.5</v>
       </c>
       <c r="Y56" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Z56" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AA56" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AH56" t="n">
         <v>215</v>
@@ -5938,30 +5881,75 @@
         <v>142</v>
       </c>
       <c r="BL56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="B57" t="n">
-        <v>105.5</v>
+        <v>112.8</v>
+      </c>
+      <c r="C57" t="n">
+        <v>37</v>
       </c>
       <c r="D57" t="n">
-        <v>34</v>
+        <v>32.4</v>
+      </c>
+      <c r="E57" t="n">
+        <v>23.5</v>
       </c>
       <c r="F57" t="n">
-        <v>4.5</v>
+        <v>2.6</v>
+      </c>
+      <c r="H57" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="I57" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="J57" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="K57" t="n">
+        <v>56.9</v>
+      </c>
+      <c r="M57" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="N57" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="O57" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>17</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>17</v>
       </c>
       <c r="Y57" t="n">
         <v>15</v>
       </c>
       <c r="Z57" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AA57" t="n">
-        <v>18.5</v>
+        <v>16</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>235</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>6.94</v>
       </c>
       <c r="AH57" t="n">
         <v>215</v>
@@ -5969,58 +5957,70 @@
       <c r="AI57" t="n">
         <v>235</v>
       </c>
+      <c r="AK57" t="n">
+        <v>136.61</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>4.65</v>
+      </c>
       <c r="AM57" t="n">
         <v>110</v>
       </c>
       <c r="AN57" t="n">
         <v>142</v>
       </c>
+      <c r="AP57" t="n">
+        <v>89.01000000000001</v>
+      </c>
+      <c r="AS57" t="n">
+        <v>18.21</v>
+      </c>
       <c r="BL57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="B58" t="n">
-        <v>112.8</v>
+        <v>126.8</v>
       </c>
       <c r="C58" t="n">
-        <v>37</v>
+        <v>40.9</v>
       </c>
       <c r="D58" t="n">
-        <v>32.4</v>
+        <v>34.8</v>
       </c>
       <c r="E58" t="n">
-        <v>23.5</v>
+        <v>27.9</v>
       </c>
       <c r="F58" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="H58" t="n">
-        <v>17.9</v>
+        <v>23</v>
       </c>
       <c r="I58" t="n">
         <v>9.1</v>
       </c>
       <c r="J58" t="n">
-        <v>29.9</v>
+        <v>32.2</v>
       </c>
       <c r="K58" t="n">
-        <v>56.9</v>
+        <v>64.3</v>
       </c>
       <c r="M58" t="n">
         <v>1.9</v>
       </c>
       <c r="N58" t="n">
-        <v>24.2</v>
+        <v>27.3</v>
       </c>
       <c r="O58" t="n">
-        <v>26.2</v>
+        <v>29.2</v>
       </c>
       <c r="Q58" t="n">
-        <v>17</v>
+        <v>20.3</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
@@ -6029,7 +6029,7 @@
         <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>17</v>
+        <v>20.3</v>
       </c>
       <c r="Y58" t="n">
         <v>15</v>
@@ -6038,13 +6038,13 @@
         <v>19</v>
       </c>
       <c r="AA58" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AF58" t="n">
-        <v>235</v>
+        <v>233.68</v>
       </c>
       <c r="AG58" t="n">
-        <v>6.94</v>
+        <v>-1.32</v>
       </c>
       <c r="AH58" t="n">
         <v>215</v>
@@ -6053,10 +6053,10 @@
         <v>235</v>
       </c>
       <c r="AK58" t="n">
-        <v>136.61</v>
+        <v>136.95</v>
       </c>
       <c r="AL58" t="n">
-        <v>4.65</v>
+        <v>0.34</v>
       </c>
       <c r="AM58" t="n">
         <v>110</v>
@@ -6065,57 +6065,57 @@
         <v>142</v>
       </c>
       <c r="AP58" t="n">
-        <v>89.01000000000001</v>
+        <v>86.34</v>
       </c>
       <c r="AS58" t="n">
-        <v>18.21</v>
+        <v>17.39</v>
       </c>
       <c r="BL58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B59" t="n">
-        <v>126.8</v>
+        <v>128.5</v>
       </c>
       <c r="C59" t="n">
-        <v>40.9</v>
+        <v>43</v>
       </c>
       <c r="D59" t="n">
-        <v>34.8</v>
+        <v>36.1</v>
       </c>
       <c r="E59" t="n">
-        <v>27.9</v>
+        <v>23.9</v>
       </c>
       <c r="F59" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="H59" t="n">
-        <v>23</v>
+        <v>23.6</v>
       </c>
       <c r="I59" t="n">
         <v>9.1</v>
       </c>
       <c r="J59" t="n">
-        <v>32.2</v>
+        <v>36.7</v>
       </c>
       <c r="K59" t="n">
-        <v>64.3</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="M59" t="n">
         <v>1.9</v>
       </c>
       <c r="N59" t="n">
-        <v>27.3</v>
+        <v>27.8</v>
       </c>
       <c r="O59" t="n">
-        <v>29.2</v>
+        <v>29.7</v>
       </c>
       <c r="Q59" t="n">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="R59" t="n">
         <v>0</v>
@@ -6124,7 +6124,7 @@
         <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="Y59" t="n">
         <v>15</v>
@@ -6133,13 +6133,13 @@
         <v>19</v>
       </c>
       <c r="AA59" t="n">
-        <v>17.5</v>
+        <v>18.2</v>
       </c>
       <c r="AF59" t="n">
-        <v>233.68</v>
+        <v>234.53</v>
       </c>
       <c r="AG59" t="n">
-        <v>-1.32</v>
+        <v>0.85</v>
       </c>
       <c r="AH59" t="n">
         <v>215</v>
@@ -6148,10 +6148,10 @@
         <v>235</v>
       </c>
       <c r="AK59" t="n">
-        <v>136.95</v>
+        <v>136.49</v>
       </c>
       <c r="AL59" t="n">
-        <v>0.34</v>
+        <v>-0.46</v>
       </c>
       <c r="AM59" t="n">
         <v>110</v>
@@ -6160,57 +6160,57 @@
         <v>142</v>
       </c>
       <c r="AP59" t="n">
-        <v>86.34</v>
+        <v>88.23</v>
       </c>
       <c r="AS59" t="n">
-        <v>17.39</v>
+        <v>17.37</v>
       </c>
       <c r="BL59" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B60" t="n">
-        <v>128.5</v>
+        <v>134.9</v>
       </c>
       <c r="C60" t="n">
-        <v>43</v>
+        <v>46.6</v>
       </c>
       <c r="D60" t="n">
-        <v>36.1</v>
+        <v>37</v>
       </c>
       <c r="E60" t="n">
-        <v>23.9</v>
+        <v>25</v>
       </c>
       <c r="F60" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="H60" t="n">
-        <v>23.6</v>
+        <v>22.9</v>
       </c>
       <c r="I60" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="J60" t="n">
-        <v>36.7</v>
+        <v>32.3</v>
       </c>
       <c r="K60" t="n">
-        <v>69.40000000000001</v>
+        <v>64.2</v>
       </c>
       <c r="M60" t="n">
         <v>1.9</v>
       </c>
       <c r="N60" t="n">
-        <v>27.8</v>
+        <v>25.2</v>
       </c>
       <c r="O60" t="n">
-        <v>29.7</v>
+        <v>27.1</v>
       </c>
       <c r="Q60" t="n">
-        <v>20.5</v>
+        <v>19.7</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
@@ -6219,22 +6219,22 @@
         <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>20.5</v>
+        <v>19.7</v>
       </c>
       <c r="Y60" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="Z60" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AA60" t="n">
-        <v>18.2</v>
+        <v>14.3</v>
       </c>
       <c r="AF60" t="n">
-        <v>234.53</v>
+        <v>237.85</v>
       </c>
       <c r="AG60" t="n">
-        <v>0.85</v>
+        <v>3.32</v>
       </c>
       <c r="AH60" t="n">
         <v>215</v>
@@ -6243,10 +6243,10 @@
         <v>235</v>
       </c>
       <c r="AK60" t="n">
-        <v>136.49</v>
+        <v>137.25</v>
       </c>
       <c r="AL60" t="n">
-        <v>-0.46</v>
+        <v>0.76</v>
       </c>
       <c r="AM60" t="n">
         <v>110</v>
@@ -6255,36 +6255,36 @@
         <v>142</v>
       </c>
       <c r="AP60" t="n">
-        <v>88.23</v>
+        <v>83.86</v>
       </c>
       <c r="AS60" t="n">
-        <v>17.37</v>
+        <v>16.5</v>
       </c>
       <c r="BL60" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B61" t="n">
-        <v>120.3</v>
+        <v>119.1</v>
       </c>
       <c r="D61" t="n">
-        <v>36.2</v>
+        <v>36.7</v>
       </c>
       <c r="F61" t="n">
-        <v>5.3</v>
+        <v>4.1</v>
       </c>
       <c r="Y61" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z61" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AA61" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH61" t="n">
         <v>215</v>
@@ -6299,30 +6299,30 @@
         <v>142</v>
       </c>
       <c r="BL61" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B62" t="n">
-        <v>119.1</v>
+        <v>114.5</v>
       </c>
       <c r="D62" t="n">
-        <v>36.7</v>
+        <v>36.4</v>
       </c>
       <c r="F62" t="n">
         <v>4.1</v>
       </c>
       <c r="Y62" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Z62" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA62" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH62" t="n">
         <v>215</v>
@@ -6337,7 +6337,7 @@
         <v>142</v>
       </c>
       <c r="BL62" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -628,88 +628,88 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B2" t="n">
-        <v>157.5</v>
+        <v>159.6</v>
       </c>
       <c r="C2" t="n">
-        <v>59.6</v>
+        <v>63</v>
       </c>
       <c r="D2" t="n">
-        <v>35</v>
+        <v>34.5</v>
       </c>
       <c r="E2" t="n">
-        <v>30.6</v>
+        <v>31.1</v>
       </c>
       <c r="F2" t="n">
-        <v>7.5</v>
+        <v>5.7</v>
       </c>
       <c r="H2" t="n">
-        <v>24.2</v>
+        <v>23.8</v>
       </c>
       <c r="I2" t="n">
-        <v>11.2</v>
+        <v>10.8</v>
       </c>
       <c r="J2" t="n">
-        <v>38.9</v>
+        <v>40.5</v>
       </c>
       <c r="K2" t="n">
-        <v>74.3</v>
+        <v>75.2</v>
       </c>
       <c r="M2" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="N2" t="n">
-        <v>33.4</v>
+        <v>34.3</v>
       </c>
       <c r="O2" t="n">
-        <v>37.1</v>
+        <v>38.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="R2" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="V2" t="n">
-        <v>13</v>
+        <v>17.5</v>
       </c>
       <c r="W2" t="n">
-        <v>26.3</v>
+        <v>22.5</v>
       </c>
       <c r="X2" t="n">
-        <v>19.6</v>
+        <v>20</v>
       </c>
       <c r="Y2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA2" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>-2.1</v>
+        <v>-2.2</v>
       </c>
       <c r="AC2" t="n">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="AF2" t="n">
-        <v>229.69</v>
+        <v>228.57</v>
       </c>
       <c r="AG2" t="n">
-        <v>-2.53</v>
+        <v>-1.14</v>
       </c>
       <c r="AH2" t="n">
         <v>215</v>
@@ -718,10 +718,10 @@
         <v>235</v>
       </c>
       <c r="AK2" t="n">
-        <v>136.96</v>
+        <v>133.01</v>
       </c>
       <c r="AL2" t="n">
-        <v>-6.65</v>
+        <v>-3.95</v>
       </c>
       <c r="AM2" t="n">
         <v>110</v>
@@ -730,99 +730,99 @@
         <v>142</v>
       </c>
       <c r="AP2" t="n">
-        <v>86.59</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="AS2" t="n">
-        <v>16.96</v>
+        <v>15.95</v>
       </c>
       <c r="BL2" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B3" t="n">
-        <v>159.6</v>
+        <v>160.4</v>
       </c>
       <c r="C3" t="n">
-        <v>63</v>
+        <v>62.6</v>
       </c>
       <c r="D3" t="n">
-        <v>34.5</v>
+        <v>35</v>
       </c>
       <c r="E3" t="n">
-        <v>31.1</v>
+        <v>32.2</v>
       </c>
       <c r="F3" t="n">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="H3" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="I3" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="J3" t="n">
-        <v>40.5</v>
+        <v>41.1</v>
       </c>
       <c r="K3" t="n">
-        <v>75.2</v>
+        <v>75.7</v>
       </c>
       <c r="M3" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="N3" t="n">
-        <v>34.3</v>
+        <v>32.6</v>
       </c>
       <c r="O3" t="n">
-        <v>38.2</v>
+        <v>38</v>
       </c>
       <c r="Q3" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T3" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="V3" t="n">
-        <v>17.5</v>
+        <v>16.4</v>
       </c>
       <c r="W3" t="n">
-        <v>22.5</v>
+        <v>22.8</v>
       </c>
       <c r="X3" t="n">
-        <v>20</v>
+        <v>19.6</v>
       </c>
       <c r="Y3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Z3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA3" t="n">
-        <v>13.5</v>
+        <v>14.1</v>
       </c>
       <c r="AB3" t="n">
-        <v>-2.2</v>
+        <v>-3.1</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="AF3" t="n">
-        <v>228.57</v>
+        <v>225.08</v>
       </c>
       <c r="AG3" t="n">
-        <v>-1.14</v>
+        <v>-3.5</v>
       </c>
       <c r="AH3" t="n">
         <v>215</v>
@@ -831,10 +831,10 @@
         <v>235</v>
       </c>
       <c r="AK3" t="n">
-        <v>133.01</v>
+        <v>135.24</v>
       </c>
       <c r="AL3" t="n">
-        <v>-3.95</v>
+        <v>2.23</v>
       </c>
       <c r="AM3" t="n">
         <v>110</v>
@@ -843,99 +843,99 @@
         <v>142</v>
       </c>
       <c r="AP3" t="n">
-        <v>84.59999999999999</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="AS3" t="n">
-        <v>15.95</v>
+        <v>15.4</v>
       </c>
       <c r="BL3" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B4" t="n">
-        <v>160.4</v>
+        <v>161.7</v>
       </c>
       <c r="C4" t="n">
-        <v>62.6</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>35</v>
+        <v>34.9</v>
       </c>
       <c r="E4" t="n">
-        <v>32.2</v>
+        <v>27.3</v>
       </c>
       <c r="F4" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H4" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="I4" t="n">
-        <v>10.7</v>
+        <v>10.3</v>
       </c>
       <c r="J4" t="n">
-        <v>41.1</v>
+        <v>42.6</v>
       </c>
       <c r="K4" t="n">
-        <v>75.7</v>
+        <v>77</v>
       </c>
       <c r="M4" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="N4" t="n">
-        <v>32.6</v>
+        <v>31.5</v>
       </c>
       <c r="O4" t="n">
-        <v>38</v>
+        <v>37.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="R4" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T4" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="V4" t="n">
-        <v>16.4</v>
+        <v>12.7</v>
       </c>
       <c r="W4" t="n">
-        <v>22.8</v>
+        <v>27</v>
       </c>
       <c r="X4" t="n">
-        <v>19.6</v>
+        <v>19.9</v>
       </c>
       <c r="Y4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Z4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AA4" t="n">
-        <v>14.1</v>
+        <v>11.4</v>
       </c>
       <c r="AB4" t="n">
-        <v>-3.1</v>
+        <v>-5.2</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.6</v>
+        <v>-0.3</v>
       </c>
       <c r="AF4" t="n">
-        <v>225.08</v>
+        <v>225</v>
       </c>
       <c r="AG4" t="n">
-        <v>-3.5</v>
+        <v>-0.08</v>
       </c>
       <c r="AH4" t="n">
         <v>215</v>
@@ -944,10 +944,10 @@
         <v>235</v>
       </c>
       <c r="AK4" t="n">
-        <v>135.24</v>
+        <v>134.62</v>
       </c>
       <c r="AL4" t="n">
-        <v>2.23</v>
+        <v>-0.62</v>
       </c>
       <c r="AM4" t="n">
         <v>110</v>
@@ -956,99 +956,60 @@
         <v>142</v>
       </c>
       <c r="AP4" t="n">
-        <v>84.09999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="AS4" t="n">
-        <v>15.4</v>
+        <v>13.86</v>
       </c>
       <c r="BL4" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B5" t="n">
-        <v>161.7</v>
-      </c>
-      <c r="C5" t="n">
-        <v>71.09999999999999</v>
+        <v>151.5</v>
       </c>
       <c r="D5" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="E5" t="n">
-        <v>27.3</v>
+        <v>35.1</v>
       </c>
       <c r="F5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H5" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I5" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="J5" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="K5" t="n">
-        <v>77</v>
-      </c>
-      <c r="M5" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="N5" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="O5" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>21</v>
-      </c>
-      <c r="R5" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="S5" t="n">
-        <v>6</v>
-      </c>
-      <c r="T5" t="n">
-        <v>21</v>
+        <v>5.4</v>
       </c>
       <c r="V5" t="n">
-        <v>12.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>27</v>
+        <v>19.4</v>
       </c>
       <c r="X5" t="n">
-        <v>19.9</v>
+        <v>14</v>
       </c>
       <c r="Y5" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA5" t="n">
         <v>9</v>
       </c>
-      <c r="Z5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>11.4</v>
-      </c>
       <c r="AB5" t="n">
-        <v>-5.2</v>
+        <v>-4.7</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.6</v>
+        <v>1.9</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.3</v>
+        <v>-1.4</v>
       </c>
       <c r="AF5" t="n">
-        <v>225</v>
+        <v>221.37</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.08</v>
+        <v>0.05</v>
       </c>
       <c r="AH5" t="n">
         <v>215</v>
@@ -1057,10 +1018,10 @@
         <v>235</v>
       </c>
       <c r="AK5" t="n">
-        <v>134.62</v>
+        <v>135.21</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.62</v>
+        <v>0.59</v>
       </c>
       <c r="AM5" t="n">
         <v>110</v>
@@ -1068,61 +1029,61 @@
       <c r="AN5" t="n">
         <v>142</v>
       </c>
-      <c r="AP5" t="n">
-        <v>80.2</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>13.86</v>
-      </c>
       <c r="BL5" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B6" t="n">
-        <v>151.5</v>
+        <v>145.2</v>
       </c>
       <c r="D6" t="n">
-        <v>35.1</v>
+        <v>33.5</v>
       </c>
       <c r="F6" t="n">
-        <v>5.4</v>
+        <v>5</v>
+      </c>
+      <c r="K6" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="O6" t="n">
+        <v>35.5</v>
       </c>
       <c r="V6" t="n">
-        <v>8.699999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="W6" t="n">
-        <v>19.4</v>
+        <v>19.2</v>
       </c>
       <c r="X6" t="n">
-        <v>14</v>
+        <v>13.1</v>
       </c>
       <c r="Y6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z6" t="n">
         <v>13</v>
       </c>
       <c r="AA6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB6" t="n">
-        <v>-4.7</v>
+        <v>-5.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>-1.4</v>
+        <v>-1.5</v>
       </c>
       <c r="AF6" t="n">
-        <v>221.37</v>
+        <v>224.37</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.05</v>
+        <v>3</v>
       </c>
       <c r="AH6" t="n">
         <v>215</v>
@@ -1131,10 +1092,10 @@
         <v>235</v>
       </c>
       <c r="AK6" t="n">
-        <v>135.21</v>
+        <v>135.61</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.59</v>
+        <v>0.4</v>
       </c>
       <c r="AM6" t="n">
         <v>110</v>
@@ -1143,60 +1104,60 @@
         <v>142</v>
       </c>
       <c r="BL6" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B7" t="n">
-        <v>145.2</v>
+        <v>146.3</v>
       </c>
       <c r="D7" t="n">
-        <v>33.5</v>
+        <v>33.4</v>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="K7" t="n">
-        <v>100.3</v>
+        <v>98.2</v>
       </c>
       <c r="O7" t="n">
-        <v>35.5</v>
+        <v>35.1</v>
       </c>
       <c r="V7" t="n">
-        <v>7.1</v>
+        <v>4.9</v>
       </c>
       <c r="W7" t="n">
-        <v>19.2</v>
+        <v>16.4</v>
       </c>
       <c r="X7" t="n">
-        <v>13.1</v>
+        <v>10.6</v>
       </c>
       <c r="Y7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z7" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB7" t="n">
-        <v>-5.4</v>
+        <v>-6.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.4</v>
+        <v>-0.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>-1.5</v>
+        <v>-3.3</v>
       </c>
       <c r="AF7" t="n">
-        <v>224.37</v>
+        <v>225.93</v>
       </c>
       <c r="AG7" t="n">
-        <v>3</v>
+        <v>1.56</v>
       </c>
       <c r="AH7" t="n">
         <v>215</v>
@@ -1205,10 +1166,10 @@
         <v>235</v>
       </c>
       <c r="AK7" t="n">
-        <v>135.61</v>
+        <v>135.28</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.4</v>
+        <v>-0.33</v>
       </c>
       <c r="AM7" t="n">
         <v>110</v>
@@ -1217,60 +1178,93 @@
         <v>142</v>
       </c>
       <c r="BL7" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B8" t="n">
-        <v>146.3</v>
+        <v>182.8</v>
+      </c>
+      <c r="C8" t="n">
+        <v>86.8</v>
       </c>
       <c r="D8" t="n">
-        <v>33.4</v>
+        <v>31.8</v>
+      </c>
+      <c r="E8" t="n">
+        <v>33</v>
       </c>
       <c r="F8" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
+      </c>
+      <c r="H8" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="I8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J8" t="n">
+        <v>41.1</v>
       </c>
       <c r="K8" t="n">
-        <v>98.2</v>
+        <v>74.2</v>
+      </c>
+      <c r="M8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="N8" t="n">
+        <v>33.5</v>
       </c>
       <c r="O8" t="n">
-        <v>35.1</v>
+        <v>38.4</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="n">
+        <v>22.4</v>
       </c>
       <c r="V8" t="n">
-        <v>4.9</v>
+        <v>9.1</v>
       </c>
       <c r="W8" t="n">
-        <v>16.4</v>
+        <v>15</v>
       </c>
       <c r="X8" t="n">
-        <v>10.6</v>
+        <v>12.1</v>
       </c>
       <c r="Y8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z8" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AA8" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>-6.4</v>
+        <v>-10.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>-3.3</v>
+        <v>-5.1</v>
       </c>
       <c r="AF8" t="n">
-        <v>225.93</v>
+        <v>218.63</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.56</v>
+        <v>-7.3</v>
       </c>
       <c r="AH8" t="n">
         <v>215</v>
@@ -1279,10 +1273,10 @@
         <v>235</v>
       </c>
       <c r="AK8" t="n">
-        <v>135.28</v>
+        <v>126.27</v>
       </c>
       <c r="AL8" t="n">
-        <v>-0.33</v>
+        <v>-9.01</v>
       </c>
       <c r="AM8" t="n">
         <v>110</v>
@@ -1290,94 +1284,100 @@
       <c r="AN8" t="n">
         <v>142</v>
       </c>
+      <c r="AP8" t="n">
+        <v>82.66</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>14.7</v>
+      </c>
       <c r="BL8" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B9" t="n">
-        <v>182.8</v>
+        <v>181.8</v>
       </c>
       <c r="C9" t="n">
-        <v>86.8</v>
+        <v>86.5</v>
       </c>
       <c r="D9" t="n">
-        <v>31.8</v>
+        <v>31.4</v>
       </c>
       <c r="E9" t="n">
-        <v>33</v>
+        <v>34.2</v>
       </c>
       <c r="F9" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="H9" t="n">
-        <v>23.5</v>
+        <v>24.4</v>
       </c>
       <c r="I9" t="n">
-        <v>9.6</v>
+        <v>10.4</v>
       </c>
       <c r="J9" t="n">
-        <v>41.1</v>
+        <v>41.9</v>
       </c>
       <c r="K9" t="n">
-        <v>74.2</v>
+        <v>76.8</v>
       </c>
       <c r="M9" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="N9" t="n">
-        <v>33.5</v>
+        <v>35.7</v>
       </c>
       <c r="O9" t="n">
-        <v>38.4</v>
+        <v>39.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>22.4</v>
+        <v>23</v>
       </c>
       <c r="R9" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>20.1</v>
       </c>
       <c r="T9" t="n">
-        <v>22.4</v>
+        <v>23</v>
       </c>
       <c r="V9" t="n">
-        <v>9.1</v>
+        <v>7.1</v>
       </c>
       <c r="W9" t="n">
-        <v>15</v>
+        <v>14.8</v>
       </c>
       <c r="X9" t="n">
-        <v>12.1</v>
+        <v>10.9</v>
       </c>
       <c r="Y9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z9" t="n">
         <v>12</v>
       </c>
       <c r="AA9" t="n">
-        <v>8.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AB9" t="n">
-        <v>-10.5</v>
+        <v>-4.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>-5.1</v>
+        <v>-1.4</v>
       </c>
       <c r="AF9" t="n">
-        <v>218.63</v>
+        <v>216.39</v>
       </c>
       <c r="AG9" t="n">
-        <v>-7.3</v>
+        <v>-2.23</v>
       </c>
       <c r="AH9" t="n">
         <v>215</v>
@@ -1386,10 +1386,10 @@
         <v>235</v>
       </c>
       <c r="AK9" t="n">
-        <v>126.27</v>
+        <v>123.32</v>
       </c>
       <c r="AL9" t="n">
-        <v>-9.01</v>
+        <v>-2.95</v>
       </c>
       <c r="AM9" t="n">
         <v>110</v>
@@ -1398,99 +1398,99 @@
         <v>142</v>
       </c>
       <c r="AP9" t="n">
-        <v>82.66</v>
+        <v>79.08</v>
       </c>
       <c r="AS9" t="n">
-        <v>14.7</v>
+        <v>13.91</v>
       </c>
       <c r="BL9" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B10" t="n">
-        <v>181.8</v>
+        <v>183</v>
       </c>
       <c r="C10" t="n">
-        <v>86.5</v>
+        <v>84.7</v>
       </c>
       <c r="D10" t="n">
-        <v>31.4</v>
+        <v>30.9</v>
       </c>
       <c r="E10" t="n">
-        <v>34.2</v>
+        <v>33.7</v>
       </c>
       <c r="F10" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="H10" t="n">
-        <v>24.4</v>
+        <v>23.4</v>
       </c>
       <c r="I10" t="n">
-        <v>10.4</v>
+        <v>10.6</v>
       </c>
       <c r="J10" t="n">
-        <v>41.9</v>
+        <v>42.3</v>
       </c>
       <c r="K10" t="n">
-        <v>76.8</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="N10" t="n">
-        <v>35.7</v>
+        <v>36.7</v>
       </c>
       <c r="O10" t="n">
-        <v>39.8</v>
+        <v>40.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>23</v>
+        <v>23.6</v>
       </c>
       <c r="R10" t="n">
         <v>1.8</v>
       </c>
       <c r="S10" t="n">
-        <v>20.1</v>
+        <v>20.8</v>
       </c>
       <c r="T10" t="n">
-        <v>23</v>
+        <v>23.6</v>
       </c>
       <c r="V10" t="n">
-        <v>7.1</v>
+        <v>5.7</v>
       </c>
       <c r="W10" t="n">
-        <v>14.8</v>
+        <v>16.1</v>
       </c>
       <c r="X10" t="n">
         <v>10.9</v>
       </c>
       <c r="Y10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AB10" t="n">
-        <v>-4.5</v>
+        <v>0.8</v>
       </c>
       <c r="AC10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD10" t="n">
         <v>1.8</v>
       </c>
-      <c r="AD10" t="n">
-        <v>-1.4</v>
-      </c>
       <c r="AF10" t="n">
-        <v>216.39</v>
+        <v>217.16</v>
       </c>
       <c r="AG10" t="n">
-        <v>-2.23</v>
+        <v>0.76</v>
       </c>
       <c r="AH10" t="n">
         <v>215</v>
@@ -1499,10 +1499,10 @@
         <v>235</v>
       </c>
       <c r="AK10" t="n">
-        <v>123.32</v>
+        <v>117.87</v>
       </c>
       <c r="AL10" t="n">
-        <v>-2.95</v>
+        <v>-5.45</v>
       </c>
       <c r="AM10" t="n">
         <v>110</v>
@@ -1511,99 +1511,66 @@
         <v>142</v>
       </c>
       <c r="AP10" t="n">
-        <v>79.08</v>
+        <v>78.56</v>
       </c>
       <c r="AS10" t="n">
-        <v>13.91</v>
+        <v>13.45</v>
       </c>
       <c r="BL10" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B11" t="n">
-        <v>183</v>
-      </c>
-      <c r="C11" t="n">
-        <v>84.7</v>
+        <v>163.8</v>
       </c>
       <c r="D11" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="E11" t="n">
-        <v>33.7</v>
+        <v>29</v>
       </c>
       <c r="F11" t="n">
-        <v>7</v>
-      </c>
-      <c r="H11" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="I11" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="J11" t="n">
-        <v>42.3</v>
+        <v>6.5</v>
       </c>
       <c r="K11" t="n">
-        <v>76.40000000000001</v>
-      </c>
-      <c r="M11" t="n">
-        <v>4</v>
-      </c>
-      <c r="N11" t="n">
-        <v>36.7</v>
+        <v>101.2</v>
       </c>
       <c r="O11" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S11" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="T11" t="n">
-        <v>23.6</v>
+        <v>40.2</v>
       </c>
       <c r="V11" t="n">
-        <v>5.7</v>
+        <v>6.3</v>
       </c>
       <c r="W11" t="n">
-        <v>16.1</v>
+        <v>17.2</v>
       </c>
       <c r="X11" t="n">
-        <v>10.9</v>
+        <v>11.8</v>
       </c>
       <c r="Y11" t="n">
         <v>8</v>
       </c>
       <c r="Z11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA11" t="n">
         <v>10</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.7</v>
+        <v>4.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="AF11" t="n">
-        <v>217.16</v>
+        <v>220.31</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.76</v>
+        <v>3.16</v>
       </c>
       <c r="AH11" t="n">
         <v>215</v>
@@ -1612,10 +1579,10 @@
         <v>235</v>
       </c>
       <c r="AK11" t="n">
-        <v>117.87</v>
+        <v>116.52</v>
       </c>
       <c r="AL11" t="n">
-        <v>-5.45</v>
+        <v>-1.35</v>
       </c>
       <c r="AM11" t="n">
         <v>110</v>
@@ -1623,67 +1590,61 @@
       <c r="AN11" t="n">
         <v>142</v>
       </c>
-      <c r="AP11" t="n">
-        <v>78.56</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>13.45</v>
-      </c>
       <c r="BL11" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B12" t="n">
-        <v>163.8</v>
+        <v>155.9</v>
       </c>
       <c r="D12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F12" t="n">
         <v>6.5</v>
       </c>
       <c r="K12" t="n">
-        <v>101.2</v>
+        <v>99.3</v>
       </c>
       <c r="O12" t="n">
-        <v>40.2</v>
+        <v>38.5</v>
       </c>
       <c r="V12" t="n">
-        <v>6.3</v>
+        <v>8.9</v>
       </c>
       <c r="W12" t="n">
-        <v>17.2</v>
+        <v>15.8</v>
       </c>
       <c r="X12" t="n">
-        <v>11.8</v>
+        <v>12.4</v>
       </c>
       <c r="Y12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA12" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="AF12" t="n">
-        <v>220.31</v>
+        <v>221.99</v>
       </c>
       <c r="AG12" t="n">
-        <v>3.16</v>
+        <v>1.67</v>
       </c>
       <c r="AH12" t="n">
         <v>215</v>
@@ -1692,10 +1653,10 @@
         <v>235</v>
       </c>
       <c r="AK12" t="n">
-        <v>116.52</v>
+        <v>116.37</v>
       </c>
       <c r="AL12" t="n">
-        <v>-1.35</v>
+        <v>-0.15</v>
       </c>
       <c r="AM12" t="n">
         <v>110</v>
@@ -1704,60 +1665,60 @@
         <v>142</v>
       </c>
       <c r="BL12" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B13" t="n">
-        <v>155.9</v>
+        <v>141.3</v>
       </c>
       <c r="D13" t="n">
-        <v>28</v>
+        <v>26.3</v>
       </c>
       <c r="F13" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="K13" t="n">
-        <v>99.3</v>
+        <v>97.8</v>
       </c>
       <c r="O13" t="n">
-        <v>38.5</v>
+        <v>39.8</v>
       </c>
       <c r="V13" t="n">
-        <v>8.9</v>
+        <v>9.5</v>
       </c>
       <c r="W13" t="n">
-        <v>15.8</v>
+        <v>17.7</v>
       </c>
       <c r="X13" t="n">
-        <v>12.4</v>
+        <v>13.6</v>
       </c>
       <c r="Y13" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Z13" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA13" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="AC13" t="n">
-        <v>5.7</v>
+        <v>7.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="AF13" t="n">
-        <v>221.99</v>
+        <v>225.14</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.67</v>
+        <v>3.15</v>
       </c>
       <c r="AH13" t="n">
         <v>215</v>
@@ -1765,12 +1726,6 @@
       <c r="AI13" t="n">
         <v>235</v>
       </c>
-      <c r="AK13" t="n">
-        <v>116.37</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>-0.15</v>
-      </c>
       <c r="AM13" t="n">
         <v>110</v>
       </c>
@@ -1778,60 +1733,54 @@
         <v>142</v>
       </c>
       <c r="BL13" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B14" t="n">
-        <v>141.3</v>
+        <v>131.5</v>
       </c>
       <c r="D14" t="n">
-        <v>26.3</v>
+        <v>27.3</v>
       </c>
       <c r="F14" t="n">
         <v>5.5</v>
       </c>
       <c r="K14" t="n">
-        <v>97.8</v>
+        <v>97</v>
       </c>
       <c r="O14" t="n">
-        <v>39.8</v>
+        <v>35.7</v>
       </c>
       <c r="V14" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="W14" t="n">
-        <v>17.7</v>
+        <v>13.9</v>
       </c>
       <c r="X14" t="n">
-        <v>13.6</v>
+        <v>11.4</v>
       </c>
       <c r="Y14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z14" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA14" t="n">
         <v>15</v>
       </c>
-      <c r="AA14" t="n">
-        <v>14</v>
-      </c>
       <c r="AB14" t="n">
-        <v>0.2</v>
+        <v>-3.6</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.5</v>
+        <v>2.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>225.14</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>3.15</v>
+        <v>-0.4</v>
       </c>
       <c r="AH14" t="n">
         <v>215</v>
@@ -1846,54 +1795,93 @@
         <v>142</v>
       </c>
       <c r="BL14" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="B15" t="n">
-        <v>131.5</v>
+        <v>153</v>
+      </c>
+      <c r="C15" t="n">
+        <v>71.8</v>
       </c>
       <c r="D15" t="n">
-        <v>27.3</v>
+        <v>28.6</v>
+      </c>
+      <c r="E15" t="n">
+        <v>24.7</v>
       </c>
       <c r="F15" t="n">
-        <v>5.5</v>
+        <v>4</v>
+      </c>
+      <c r="H15" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J15" t="n">
+        <v>41.1</v>
       </c>
       <c r="K15" t="n">
-        <v>97</v>
+        <v>75.90000000000001</v>
+      </c>
+      <c r="M15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N15" t="n">
+        <v>33.5</v>
       </c>
       <c r="O15" t="n">
-        <v>35.7</v>
+        <v>38.3</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>23.2</v>
       </c>
       <c r="V15" t="n">
-        <v>9</v>
+        <v>11.2</v>
       </c>
       <c r="W15" t="n">
-        <v>13.9</v>
+        <v>13</v>
       </c>
       <c r="X15" t="n">
-        <v>11.4</v>
+        <v>12.1</v>
       </c>
       <c r="Y15" t="n">
         <v>12</v>
       </c>
       <c r="Z15" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AA15" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>-3.6</v>
+        <v>-6.6</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.8</v>
+        <v>5.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>-0.4</v>
+        <v>-0.6</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>229.96</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>-0.02</v>
       </c>
       <c r="AH15" t="n">
         <v>215</v>
@@ -1901,100 +1889,112 @@
       <c r="AI15" t="n">
         <v>235</v>
       </c>
+      <c r="AK15" t="n">
+        <v>128.14</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>11.77</v>
+      </c>
       <c r="AM15" t="n">
         <v>110</v>
       </c>
       <c r="AN15" t="n">
         <v>142</v>
       </c>
+      <c r="AP15" t="n">
+        <v>87.47</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>14.8</v>
+      </c>
       <c r="BL15" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B16" t="n">
-        <v>153</v>
+        <v>165.8</v>
       </c>
       <c r="C16" t="n">
-        <v>71.8</v>
+        <v>77.3</v>
       </c>
       <c r="D16" t="n">
-        <v>28.6</v>
+        <v>29.3</v>
       </c>
       <c r="E16" t="n">
-        <v>24.7</v>
+        <v>27.7</v>
       </c>
       <c r="F16" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="H16" t="n">
         <v>24.1</v>
       </c>
       <c r="I16" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="J16" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="K16" t="n">
-        <v>75.90000000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="N16" t="n">
-        <v>33.5</v>
+        <v>35.1</v>
       </c>
       <c r="O16" t="n">
-        <v>38.3</v>
+        <v>39.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>23.2</v>
+        <v>23.8</v>
       </c>
       <c r="R16" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="T16" t="n">
-        <v>23.2</v>
+        <v>23.8</v>
       </c>
       <c r="V16" t="n">
-        <v>11.2</v>
+        <v>9.4</v>
       </c>
       <c r="W16" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="X16" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z16" t="n">
         <v>13</v>
       </c>
-      <c r="X16" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>14</v>
-      </c>
       <c r="AA16" t="n">
-        <v>12.5</v>
+        <v>10.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>-6.6</v>
+        <v>-0.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>5.3</v>
+        <v>9.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>-0.6</v>
+        <v>4.4</v>
       </c>
       <c r="AF16" t="n">
-        <v>229.96</v>
+        <v>227.01</v>
       </c>
       <c r="AG16" t="n">
-        <v>-0.02</v>
+        <v>-2.95</v>
       </c>
       <c r="AH16" t="n">
         <v>215</v>
@@ -2003,10 +2003,10 @@
         <v>235</v>
       </c>
       <c r="AK16" t="n">
-        <v>128.14</v>
+        <v>128.15</v>
       </c>
       <c r="AL16" t="n">
-        <v>11.77</v>
+        <v>0.01</v>
       </c>
       <c r="AM16" t="n">
         <v>110</v>
@@ -2015,99 +2015,99 @@
         <v>142</v>
       </c>
       <c r="AP16" t="n">
-        <v>87.47</v>
+        <v>83.41</v>
       </c>
       <c r="AS16" t="n">
-        <v>14.8</v>
+        <v>14.52</v>
       </c>
       <c r="BL16" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B17" t="n">
-        <v>165.8</v>
+        <v>158.1</v>
       </c>
       <c r="C17" t="n">
-        <v>77.3</v>
+        <v>73.7</v>
       </c>
       <c r="D17" t="n">
-        <v>29.3</v>
+        <v>30.3</v>
       </c>
       <c r="E17" t="n">
-        <v>27.7</v>
+        <v>26</v>
       </c>
       <c r="F17" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="H17" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="I17" t="n">
-        <v>10.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>41.6</v>
+        <v>40.9</v>
       </c>
       <c r="K17" t="n">
-        <v>76.59999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="N17" t="n">
-        <v>35.1</v>
+        <v>35.3</v>
       </c>
       <c r="O17" t="n">
-        <v>39.8</v>
+        <v>40.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S17" t="n">
         <v>7</v>
       </c>
       <c r="T17" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="V17" t="n">
-        <v>9.4</v>
+        <v>8.9</v>
       </c>
       <c r="W17" t="n">
-        <v>17.4</v>
+        <v>19.3</v>
       </c>
       <c r="X17" t="n">
-        <v>13.4</v>
+        <v>14.1</v>
       </c>
       <c r="Y17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z17" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA17" t="n">
-        <v>10.1</v>
+        <v>11</v>
       </c>
       <c r="AB17" t="n">
-        <v>-0.7</v>
+        <v>4.4</v>
       </c>
       <c r="AC17" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>4.4</v>
+        <v>6.5</v>
       </c>
       <c r="AF17" t="n">
-        <v>227.01</v>
+        <v>228.35</v>
       </c>
       <c r="AG17" t="n">
-        <v>-2.95</v>
+        <v>1.33</v>
       </c>
       <c r="AH17" t="n">
         <v>215</v>
@@ -2116,10 +2116,10 @@
         <v>235</v>
       </c>
       <c r="AK17" t="n">
-        <v>128.15</v>
+        <v>128.86</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.01</v>
+        <v>0.71</v>
       </c>
       <c r="AM17" t="n">
         <v>110</v>
@@ -2128,99 +2128,99 @@
         <v>142</v>
       </c>
       <c r="AP17" t="n">
-        <v>83.41</v>
+        <v>82.37</v>
       </c>
       <c r="AS17" t="n">
-        <v>14.52</v>
+        <v>14.22</v>
       </c>
       <c r="BL17" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B18" t="n">
-        <v>158.1</v>
+        <v>154.9</v>
       </c>
       <c r="C18" t="n">
-        <v>73.7</v>
+        <v>70.2</v>
       </c>
       <c r="D18" t="n">
-        <v>30.3</v>
+        <v>31.5</v>
       </c>
       <c r="E18" t="n">
-        <v>26</v>
+        <v>27.7</v>
       </c>
       <c r="F18" t="n">
-        <v>4.1</v>
+        <v>2.7</v>
       </c>
       <c r="H18" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="I18" t="n">
-        <v>9.300000000000001</v>
+        <v>11.3</v>
       </c>
       <c r="J18" t="n">
-        <v>40.9</v>
+        <v>40.3</v>
       </c>
       <c r="K18" t="n">
-        <v>74.40000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="M18" t="n">
-        <v>5</v>
+        <v>6.1</v>
       </c>
       <c r="N18" t="n">
-        <v>35.3</v>
+        <v>32.9</v>
       </c>
       <c r="O18" t="n">
-        <v>40.3</v>
+        <v>39</v>
       </c>
       <c r="Q18" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="R18" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="T18" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="V18" t="n">
-        <v>8.9</v>
+        <v>6.3</v>
       </c>
       <c r="W18" t="n">
-        <v>19.3</v>
+        <v>25.2</v>
       </c>
       <c r="X18" t="n">
-        <v>14.1</v>
+        <v>15.8</v>
       </c>
       <c r="Y18" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z18" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA18" t="n">
-        <v>11</v>
+        <v>12.6</v>
       </c>
       <c r="AB18" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="AC18" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="AF18" t="n">
-        <v>228.35</v>
+        <v>231.16</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.33</v>
+        <v>2.81</v>
       </c>
       <c r="AH18" t="n">
         <v>215</v>
@@ -2229,10 +2229,10 @@
         <v>235</v>
       </c>
       <c r="AK18" t="n">
-        <v>128.86</v>
+        <v>130.88</v>
       </c>
       <c r="AL18" t="n">
-        <v>0.71</v>
+        <v>2.02</v>
       </c>
       <c r="AM18" t="n">
         <v>110</v>
@@ -2241,99 +2241,66 @@
         <v>142</v>
       </c>
       <c r="AP18" t="n">
-        <v>82.37</v>
+        <v>85.48999999999999</v>
       </c>
       <c r="AS18" t="n">
-        <v>14.22</v>
+        <v>13.1</v>
       </c>
       <c r="BL18" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B19" t="n">
-        <v>154.9</v>
-      </c>
-      <c r="C19" t="n">
-        <v>70.2</v>
+        <v>152.2</v>
       </c>
       <c r="D19" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="E19" t="n">
-        <v>27.7</v>
+        <v>31</v>
       </c>
       <c r="F19" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="H19" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I19" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J19" t="n">
-        <v>40.3</v>
+        <v>3.5</v>
       </c>
       <c r="K19" t="n">
-        <v>75.8</v>
-      </c>
-      <c r="M19" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="N19" t="n">
-        <v>32.9</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>39</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="R19" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="S19" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="T19" t="n">
-        <v>23.7</v>
+        <v>34.4</v>
       </c>
       <c r="V19" t="n">
-        <v>6.3</v>
+        <v>9.5</v>
       </c>
       <c r="W19" t="n">
-        <v>25.2</v>
+        <v>25.5</v>
       </c>
       <c r="X19" t="n">
-        <v>15.8</v>
+        <v>17.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Z19" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AA19" t="n">
-        <v>12.6</v>
+        <v>9</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.9</v>
+        <v>-1.1</v>
       </c>
       <c r="AC19" t="n">
         <v>8.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>5.8</v>
+        <v>3.8</v>
       </c>
       <c r="AF19" t="n">
-        <v>231.16</v>
+        <v>228.13</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.81</v>
+        <v>-3.03</v>
       </c>
       <c r="AH19" t="n">
         <v>215</v>
@@ -2341,79 +2308,67 @@
       <c r="AI19" t="n">
         <v>235</v>
       </c>
-      <c r="AK19" t="n">
-        <v>130.88</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AM19" t="n">
         <v>110</v>
       </c>
       <c r="AN19" t="n">
         <v>142</v>
       </c>
-      <c r="AP19" t="n">
-        <v>85.48999999999999</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>13.1</v>
-      </c>
       <c r="BL19" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B20" t="n">
-        <v>152.2</v>
+        <v>143.9</v>
       </c>
       <c r="D20" t="n">
-        <v>31</v>
+        <v>30.8</v>
       </c>
       <c r="F20" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="K20" t="n">
-        <v>98.40000000000001</v>
+        <v>99.2</v>
       </c>
       <c r="O20" t="n">
-        <v>34.4</v>
+        <v>35.2</v>
       </c>
       <c r="V20" t="n">
-        <v>9.5</v>
+        <v>10.7</v>
       </c>
       <c r="W20" t="n">
-        <v>25.5</v>
+        <v>17.6</v>
       </c>
       <c r="X20" t="n">
-        <v>17.5</v>
+        <v>14.2</v>
       </c>
       <c r="Y20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Z20" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA20" t="n">
         <v>9</v>
       </c>
       <c r="AB20" t="n">
-        <v>-1.1</v>
+        <v>-0.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD20" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AF20" t="n">
-        <v>228.13</v>
+        <v>229.16</v>
       </c>
       <c r="AG20" t="n">
-        <v>-3.03</v>
+        <v>1.03</v>
       </c>
       <c r="AH20" t="n">
         <v>215</v>
@@ -2428,60 +2383,93 @@
         <v>142</v>
       </c>
       <c r="BL20" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B21" t="n">
-        <v>143.9</v>
+        <v>163.2</v>
+      </c>
+      <c r="C21" t="n">
+        <v>73.7</v>
       </c>
       <c r="D21" t="n">
-        <v>30.8</v>
+        <v>30</v>
+      </c>
+      <c r="E21" t="n">
+        <v>28.2</v>
       </c>
       <c r="F21" t="n">
-        <v>2.5</v>
+        <v>4.8</v>
+      </c>
+      <c r="H21" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J21" t="n">
+        <v>40.1</v>
       </c>
       <c r="K21" t="n">
-        <v>99.2</v>
+        <v>75.59999999999999</v>
+      </c>
+      <c r="M21" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="N21" t="n">
+        <v>32.9</v>
       </c>
       <c r="O21" t="n">
-        <v>35.2</v>
+        <v>39.7</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="R21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="S21" t="n">
+        <v>6</v>
+      </c>
+      <c r="T21" t="n">
+        <v>23.5</v>
       </c>
       <c r="V21" t="n">
-        <v>10.7</v>
+        <v>9.4</v>
       </c>
       <c r="W21" t="n">
-        <v>17.6</v>
+        <v>20.1</v>
       </c>
       <c r="X21" t="n">
-        <v>14.2</v>
+        <v>14.8</v>
       </c>
       <c r="Y21" t="n">
         <v>4</v>
       </c>
       <c r="Z21" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA21" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AB21" t="n">
-        <v>-0.8</v>
+        <v>-0.9</v>
       </c>
       <c r="AC21" t="n">
-        <v>8.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AF21" t="n">
-        <v>229.16</v>
+        <v>228.55</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.03</v>
+        <v>-0.61</v>
       </c>
       <c r="AH21" t="n">
         <v>215</v>
@@ -2489,100 +2477,112 @@
       <c r="AI21" t="n">
         <v>235</v>
       </c>
+      <c r="AK21" t="n">
+        <v>127.06</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>-3.82</v>
+      </c>
       <c r="AM21" t="n">
         <v>110</v>
       </c>
       <c r="AN21" t="n">
         <v>142</v>
       </c>
+      <c r="AP21" t="n">
+        <v>82.81</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>12.9</v>
+      </c>
       <c r="BL21" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="B22" t="n">
-        <v>163.2</v>
+        <v>174.4</v>
       </c>
       <c r="C22" t="n">
-        <v>73.7</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="D22" t="n">
-        <v>30</v>
+        <v>32.1</v>
       </c>
       <c r="E22" t="n">
-        <v>28.2</v>
+        <v>30.8</v>
       </c>
       <c r="F22" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="H22" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="I22" t="n">
-        <v>11.4</v>
+        <v>10.5</v>
       </c>
       <c r="J22" t="n">
-        <v>40.1</v>
+        <v>39.5</v>
       </c>
       <c r="K22" t="n">
-        <v>75.59999999999999</v>
+        <v>74</v>
       </c>
       <c r="M22" t="n">
         <v>6.8</v>
       </c>
       <c r="N22" t="n">
-        <v>32.9</v>
+        <v>35.8</v>
       </c>
       <c r="O22" t="n">
-        <v>39.7</v>
+        <v>42.6</v>
       </c>
       <c r="Q22" t="n">
-        <v>23.5</v>
+        <v>23.1</v>
       </c>
       <c r="R22" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="S22" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="T22" t="n">
-        <v>23.5</v>
+        <v>23.1</v>
       </c>
       <c r="V22" t="n">
-        <v>9.4</v>
+        <v>12.8</v>
       </c>
       <c r="W22" t="n">
-        <v>20.1</v>
+        <v>22.1</v>
       </c>
       <c r="X22" t="n">
-        <v>14.8</v>
+        <v>17.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Z22" t="n">
         <v>13</v>
       </c>
       <c r="AA22" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AC22" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="AB22" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>9.5</v>
-      </c>
       <c r="AD22" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AF22" t="n">
-        <v>228.55</v>
+        <v>219.99</v>
       </c>
       <c r="AG22" t="n">
-        <v>-0.61</v>
+        <v>-8.56</v>
       </c>
       <c r="AH22" t="n">
         <v>215</v>
@@ -2591,10 +2591,10 @@
         <v>235</v>
       </c>
       <c r="AK22" t="n">
-        <v>127.06</v>
+        <v>125.61</v>
       </c>
       <c r="AL22" t="n">
-        <v>-3.82</v>
+        <v>-1.45</v>
       </c>
       <c r="AM22" t="n">
         <v>110</v>
@@ -2603,99 +2603,99 @@
         <v>142</v>
       </c>
       <c r="AP22" t="n">
-        <v>82.81</v>
+        <v>77.83</v>
       </c>
       <c r="AS22" t="n">
-        <v>12.9</v>
+        <v>12.96</v>
       </c>
       <c r="BL22" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B23" t="n">
-        <v>174.4</v>
+        <v>163.2</v>
       </c>
       <c r="C23" t="n">
-        <v>75.40000000000001</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="D23" t="n">
-        <v>32.1</v>
+        <v>32.9</v>
       </c>
       <c r="E23" t="n">
-        <v>30.8</v>
+        <v>26</v>
       </c>
       <c r="F23" t="n">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="H23" t="n">
-        <v>24</v>
+        <v>23.8</v>
       </c>
       <c r="I23" t="n">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="J23" t="n">
-        <v>39.5</v>
+        <v>40.1</v>
       </c>
       <c r="K23" t="n">
-        <v>74</v>
+        <v>71.3</v>
       </c>
       <c r="M23" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="N23" t="n">
-        <v>35.8</v>
+        <v>34.3</v>
       </c>
       <c r="O23" t="n">
- 